--- a/XL-Int.xlsx
+++ b/XL-Int.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\foolu\Workspace\Excel\BigInt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F5CFFB-4725-434D-BCB5-86CDC927FB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350800F0-4F3A-4B0E-8CDD-306E176655ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23840" windowHeight="21000" xr2:uid="{36490472-0618-4E80-9469-F609392FABC8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24610" windowHeight="21000" xr2:uid="{36490472-0618-4E80-9469-F609392FABC8}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
     <sheet name="Notes" sheetId="5" r:id="rId2"/>
     <sheet name="div bench" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="BigInt.Abs" comment="Returns the unsigned magnitude of a BigInt string (absolute value)._x000a_@param big_int The BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, _xlfn.LET(_xlpm.num, BigInt.Norm(_xlpm.big_int), IF(LEFT(_xlpm.num) = "-", MID(_xlpm.num, 2, LEN(_xlpm.num) - 1), _xlpm.num)))</definedName>
@@ -23,11 +24,14 @@
     <definedName name="BigInt.Compare" comment="Compares two BigInt strings. Returns 1 (a &gt; b), -1 (a &lt; b), or 0 (a = b)._x000a_Evaluates signs and lengths. If identical, delegates to native limb array comparison._x000a_@param big_int_a The first BigInt string._x000a_@param big_int_b The second BigInt string.">_xlfn.LAMBDA(_xlpm.big_int_a,_xlpm.big_int_b, _xlfn.LET(_xlpm.norm_a, BigInt.Norm(_xlpm.big_int_a), _xlpm.norm_b, BigInt.Norm(_xlpm.big_int_b), _xlpm.sign_a, BigInt.Sign(_xlpm.norm_a), _xlpm.sign_b, BigInt.Sign(_xlpm.norm_b), IF(_xlpm.sign_a &lt;&gt; _xlpm.sign_b, SIGN(_xlpm.sign_a - _xlpm.sign_b), IF(_xlpm.sign_a = 0, 0, _xlfn.LET(_xlpm.len_a, LEN(_xlpm.norm_a), _xlpm.len_b, LEN(_xlpm.norm_b), IF(_xlpm.len_a &lt;&gt; _xlpm.len_b, SIGN(_xlpm.len_a - _xlpm.len_b) * _xlpm.sign_a, _xlfn.LET(_xlpm.k, core_BigInt.SafeK("ADD"), _xlpm.limbs_a, core_BigInt.Split(BigInt.Abs(_xlpm.norm_a), _xlpm.k), _xlpm.limbs_b, core_BigInt.Split(BigInt.Abs(_xlpm.norm_b), _xlpm.k), _xlpm.mag_comparison, core_BigInt.UCompare(_xlpm.limbs_a, _xlpm.limbs_b), _xlpm.mag_comparison * _xlpm.sign_a)))))))</definedName>
     <definedName name="BigInt.Div" comment="Divides the first BigInt by the second (A / B). _x000a_@param big_int_a The dividend BigInt string._x000a_@param big_int_b The divisor BigInt string._x000a_@param [use_floor] Optional boolean. TRUE for Python-style Floor division. Defaults to FALSE.">_xlfn.LAMBDA(_xlpm.big_int_a,_xlpm.big_int_b,_xlop.use_floor, INDEX(BigInt.DivMod(_xlpm.big_int_a, _xlpm.big_int_b, _xlpm.use_floor), 1, 1))</definedName>
     <definedName name="BigInt.DivMod" comment="Divides the first BigInt by the second (A / B). _x000a_Returns the quotient and modulus in rows 1 and 2, respectively._x000a_@param big_int_a The dividend BigInt string._x000a_@param big_int_b The divisor BigInt string._x000a_@param [use_floor] Optional boolean. TRUE for Python-">_xlfn.LAMBDA(_xlpm.big_int_a,_xlpm.big_int_b,_xlop.use_floor, _xlfn.LET(_xlpm.norm_a, BigInt.Norm(_xlpm.big_int_a), _xlpm.norm_b, BigInt.Norm(_xlpm.big_int_b), _xlpm.sign_a, BigInt.Sign(_xlpm.norm_a), _xlpm.sign_b, BigInt.Sign(_xlpm.norm_b), _xlpm.is_floor, IF(_xlfn.ISOMITTED(_xlpm.use_floor), FALSE, _xlpm.use_floor), IF(_xlpm.sign_b = 0, #DIV/0!, IF(_xlpm.sign_a = 0, {"0";"0"}, _xlfn.LET(_xlpm.k, core_BigInt.SafeK("DIV"), _xlpm.limbs_a, core_BigInt.Split(BigInt.Abs(_xlpm.norm_a), _xlpm.k), _xlpm.limbs_b, core_BigInt.Split(BigInt.Abs(_xlpm.norm_b), _xlpm.k), _xlpm.packed_result, core_BigInt.DivRouter(_xlpm.limbs_a, _xlpm.limbs_b, _xlpm.k), _xlpm.len_r, INDEX(_xlpm.packed_result, 1, 1), _xlpm.rem_limbs, _xlfn.CHOOSEROWS(_xlpm.packed_result, _xlfn.SEQUENCE(_xlpm.len_r, 1, 2)), _xlpm.quot_limbs, _xlfn.DROP(_xlpm.packed_result, _xlpm.len_r + 1), _xlpm.final_sign, _xlpm.sign_a * _xlpm.sign_b, _xlpm.merged_q, core_BigInt.Merge(_xlpm.quot_limbs, _xlpm.k), _xlpm.merged_r, core_BigInt.Merge(_xlpm.rem_limbs, _xlpm.k), _xlpm.trunc_q, IF(AND(_xlpm.final_sign = -1, _xlpm.merged_q &lt;&gt; "0"), "-" &amp; _xlpm.merged_q, _xlpm.merged_q), _xlpm.trunc_r, IF(AND(_xlpm.sign_a = -1, _xlpm.merged_r &lt;&gt; "0"), "-" &amp; _xlpm.merged_r, _xlpm.merged_r), _xlpm.needs_correction, AND(_xlpm.is_floor, _xlpm.final_sign = -1, _xlpm.merged_r &lt;&gt; "0"), _xlpm.final_q, IF(_xlpm.needs_correction, BigInt.Sub(_xlpm.trunc_q, "1"), _xlpm.trunc_q), _xlpm.final_r, IF(_xlpm.needs_correction, BigInt.Add(_xlpm.trunc_r, _xlpm.norm_b), _xlpm.trunc_r), _xlfn.VSTACK(_xlpm.final_q, _xlpm.final_r))))))</definedName>
+    <definedName name="BigInt.IsEven" comment="Returns TRUE if the BigInt is even._x000a_@param big_int The BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, ISEVEN(VALUE(RIGHT(BigInt.Norm(_xlpm.big_int)))))</definedName>
     <definedName name="BigInt.IsNeg" comment="Returns TRUE if the BigInt is negative._x000a_@param big_int The BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, LEFT(BigInt.Norm(_xlpm.big_int)) = "-")</definedName>
+    <definedName name="BigInt.IsOdd" comment="Returns TRUE if the BigInt is odd._x000a_@param big_int The BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, ISODD(VALUE(RIGHT(BigInt.Norm(_xlpm.big_int)))))</definedName>
     <definedName name="BigInt.IsZero" comment="Returns TRUE if the BigInt is exactly zero._x000a_@param big_int The BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, BigInt.Norm(_xlpm.big_int) = "0")</definedName>
     <definedName name="BigInt.Mod" comment="Computes the remainder of A / B._x000a_@param big_int_a The dividend BigInt string._x000a_@param big_int_b The divisor BigInt string._x000a_@param [use_floor] Optional boolean. TRUE for Python-style Modulo. Defaults to FALSE.">_xlfn.LAMBDA(_xlpm.big_int_a,_xlpm.big_int_b,_xlop.use_floor, INDEX(BigInt.DivMod(_xlpm.big_int_a, _xlpm.big_int_b, _xlpm.use_floor), 2, 1))</definedName>
     <definedName name="BigInt.Mul" comment="Multiplies two BigInt strings._x000a_@param big_int_a The first BigInt string._x000a_@param big_int_b The second BigInt string.">_xlfn.LAMBDA(_xlpm.big_int_a,_xlpm.big_int_b, _xlfn.LET(_xlpm.norm_a, BigInt.Norm(_xlpm.big_int_a), _xlpm.norm_b, BigInt.Norm(_xlpm.big_int_b), _xlpm.sign_a, BigInt.Sign(_xlpm.norm_a), _xlpm.sign_b, BigInt.Sign(_xlpm.norm_b), _xlpm.len_a, LEN(_xlpm.norm_a), _xlpm.len_b, LEN(_xlpm.norm_b), IF(OR(_xlpm.sign_a = 0, _xlpm.sign_b = 0), "0", IF(_xlpm.len_a + _xlpm.len_b &gt; 32766, #NUM!, _xlfn.LET(_xlpm.k, core_BigInt.SafeK("MUL", MIN(_xlpm.len_a, _xlpm.len_b)), _xlpm.limbs_a, core_BigInt.Split(BigInt.Abs(_xlpm.norm_a), _xlpm.k), _xlpm.limbs_b, core_BigInt.Split(BigInt.Abs(_xlpm.norm_b), _xlpm.k), _xlpm.final_limbs, core_BigInt.UMul(_xlpm.limbs_a, _xlpm.limbs_b, _xlpm.k), _xlpm.final_sign, _xlpm.sign_a * _xlpm.sign_b, _xlpm.merged, core_BigInt.Merge(_xlpm.final_limbs, _xlpm.k), IF(_xlpm.final_sign = -1, "-" &amp; _xlpm.merged, _xlpm.merged))))))</definedName>
     <definedName name="BigInt.Norm" comment="Normalises a BigInt string. Strips leading zeros, resolves &quot;-0&quot; to &quot;0&quot;, and throws #VALUE! on invalid characters._x000a_@param big_int The BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, _xlfn.LET(_xlpm.str, IF(OR(_xlfn.ISOMITTED(_xlpm.big_int), _xlpm.big_int = ""), "0", _xlpm.big_int &amp; ""), _xlpm.is_valid, _xlfn.REGEXTEST(_xlpm.str, "^-?\d+$"), _xlpm.stripped, _xlfn.REGEXREPLACE(_xlpm.str, "^(-?)0+(?=\d)", "$1"), IF(NOT(_xlpm.is_valid), VALUE("#VALUE!"), IF(_xlpm.stripped = "-0", "0", _xlpm.stripped))))</definedName>
+    <definedName name="BigInt.Pow" comment="Raises a BigInt base to the power of a BigInt exponent._x000a_@param base The base BigInt string._x000a_@param exponent The exponent BigInt string.">_xlfn.LAMBDA(_xlpm.base,_xlpm.exponent, _xlfn.LET(_xlpm.norm_base, BigInt.Norm(_xlpm.base), _xlpm.norm_exp, BigInt.Norm(_xlpm.exponent), _xlpm.sign_base, BigInt.Sign(_xlpm.norm_base), _xlpm.sign_exp, BigInt.Sign(_xlpm.norm_exp), _xlpm.abs_base, BigInt.Abs(_xlpm.norm_base), _xlpm.abs_exp, BigInt.Abs(_xlpm.norm_exp), _xlpm.is_exp_even, ISEVEN(VALUE(RIGHT(_xlpm.norm_exp, 1))), _xlpm.final_sign, IF(_xlpm.sign_base = -1, IF(_xlpm.is_exp_even, 1, -1), _xlpm.sign_base), IF(_xlpm.abs_base = "0", IF(_xlpm.norm_exp = "0", #NUM!, "0"), IF(_xlpm.abs_base = "1", IF(_xlpm.final_sign = -1, "-1", "1"), IF(_xlpm.sign_exp = -1, "0", IF(_xlpm.norm_exp = "0", "1", IF(LEN(_xlpm.norm_exp) &gt; 6, #NUM!, _xlfn.LET(_xlpm.num_exp, VALUE(_xlpm.norm_exp), _xlpm.base_log10,LOG10(VALUE(LEFT(_xlpm.abs_base, 14))) + MAX(0, LEN(_xlpm.abs_base) - 14), _xlpm.approx_digits, _xlpm.num_exp * _xlpm.base_log10, IF(_xlpm.approx_digits &gt; 32766, #NUM!, _xlfn.LET(_xlpm.k, core_BigInt.SafeK("MUL", _xlpm.approx_digits / 2), _xlpm.limbs_base, core_BigInt.Split(_xlpm.abs_base, _xlpm.k), _xlpm.final_limbs, core_BigInt.UPow(_xlpm.limbs_base, _xlpm.norm_exp, _xlpm.k), _xlpm.merged, core_BigInt.Merge(_xlpm.final_limbs, _xlpm.k), IF(_xlpm.final_sign = -1, "-" &amp; _xlpm.merged, _xlpm.merged)))))))))))</definedName>
     <definedName name="BigInt.RandBigIntArray" comment="[VOLATILE] Generates a dynamic array of integers as text._x000a_@param [num_rows] array height, default 1._x000a_@param [num_cols] array width, default 1._x000a_@param [min_digits] minimum number of digits, default 16 (min 1 digit)_x000a_@param [max_digits] maximum number of dig">_xlfn.LAMBDA(_xlop.num_rows,_xlop.num_cols,_xlop.min_digits,_xlop.max_digits, _xlfn.LET(_xlpm.n_rows, IF(_xlfn.ISOMITTED(_xlpm.num_rows), 1, _xlpm.num_rows), _xlpm.n_cols, IF(_xlfn.ISOMITTED(_xlpm.num_cols), 1, _xlpm.num_cols), _xlpm.min_len, IF(_xlfn.ISOMITTED(_xlpm.min_digits), 16, MIN(32767, MAX(1, _xlpm.min_digits))), _xlpm.max_len, IF(_xlfn.ISOMITTED(_xlpm.max_digits), 50, MAX(1, MIN(32766, _xlpm.max_digits))), _xlfn.MAP(_xlfn.RANDARRAY(_xlpm.n_rows, _xlpm.n_cols, _xlpm.min_len, _xlpm.max_len, TRUE), _xlfn.LAMBDA(_xlpm.length, _xlfn.LET(_xlpm.sign, CHOOSE(RANDBETWEEN(1, 2), "", "-"), _xlpm.digits, _xlfn.CONCAT(_xlfn.RANDARRAY(1, _xlpm.length, 0, 9, TRUE)), _xlpm.sign &amp; _xlfn.REGEXREPLACE(_xlpm.digits, "^0*", ""))))))</definedName>
     <definedName name="BigInt.Sign" comment="Returns the sign of a BigInt: 1 (positive), -1 (negative), or 0 (zero)._x000a_@param big_int The BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, _xlfn.LET(_xlpm.normed, BigInt.Norm(_xlpm.big_int), _xlfn.SWITCH(LEFT(_xlpm.normed), "0", 0, "-", -1, 1)))</definedName>
     <definedName name="BigInt.Sub" comment="Subtracts the second BigInt string from the first (A - B)._x000a_@param big_int_a The minuend BigInt string._x000a_@param big_int_b The subtrahend BigInt string.">_xlfn.LAMBDA(_xlpm.big_int_a,_xlpm.big_int_b, _xlfn.LET(_xlpm.norm_b, BigInt.Norm(_xlpm.big_int_b), _xlpm.inv_b, IF(_xlpm.norm_b = "0", "0", IF(LEFT(_xlpm.norm_b) = "-", MID(_xlpm.norm_b, 2, LEN(_xlpm.norm_b)), "-" &amp; _xlpm.norm_b)), BigInt.Add(_xlpm.big_int_a, _xlpm.inv_b)))</definedName>
@@ -41,12 +45,13 @@
     <definedName name="core_BigInt.NewtonRaphsonDiv" comment="[Internal] Heavyweight Newton-Raphson Division._x000a_Implements progressive scaling bounded to MAX(len_a, len_b)._x000a_@param limbs_a The dividend array._x000a_@param limbs_b The divisor array._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.len_a, ROWS(_xlpm.limbs_a), _xlpm.len_b, ROWS(_xlpm.limbs_b), _xlpm.target_len, MAX(_xlpm.len_a, _xlpm.len_b), _xlpm.r, core_BigInt.NewtonRaphsonReciprocal(_xlpm.limbs_b, _xlpm.target_len, _xlpm.k), _xlpm.drop_limbs, _xlpm.target_len + _xlpm.len_b, _xlpm.q_unscaled, core_BigInt.UMul(_xlpm.limbs_a, _xlpm.r, _xlpm.k), _xlpm.q_approx, IF(ROWS(_xlpm.q_unscaled) &lt;= _xlpm.drop_limbs, {0}, _xlfn.DROP(_xlpm.q_unscaled, _xlpm.drop_limbs)), _xlpm.q_prod, core_BigInt.UMul(_xlpm.limbs_b, _xlpm.q_approx, _xlpm.k), _xlpm.rem_approx, core_BigInt.USub(_xlpm.limbs_a, _xlpm.q_prod, _xlpm.k), _xlpm.comp, core_BigInt.UCompare(_xlpm.rem_approx, _xlpm.limbs_b), _xlpm.final_q, IF(_xlpm.comp &gt;= 0, core_BigInt.UAdd(_xlpm.q_approx, {1}, _xlpm.k), _xlpm.q_approx), _xlpm.final_r, IF(_xlpm.comp &gt;= 0, core_BigInt.USub(_xlpm.rem_approx, _xlpm.limbs_b, _xlpm.k), _xlpm.rem_approx), _xlfn.VSTACK(ROWS(_xlpm.final_r), _xlpm.final_r, _xlpm.final_q)))</definedName>
     <definedName name="core_BigInt.NewtonRaphsonReciprocal" comment="[Internal] Computes the Reciprocal progressively scaling up to the Dividend's precision._x000a_@param limbs_b The divisor limb array._x000a_@param target_len The limb-length of Dividend A._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.limbs_b,_xlpm.target_len,_xlpm.k, _xlfn.LET(_xlpm.len_b, ROWS(_xlpm.limbs_b), _xlpm.seed_len, MIN(3, _xlpm.len_b), _xlpm.r_seed_limbs, core_BigInt.NewtonRaphsonSeed(_xlpm.limbs_b, _xlpm.k), _xlpm.initial_state, _xlfn.VSTACK(_xlpm.seed_len, _xlpm.r_seed_limbs), _xlpm.req_iters, MAX(0, _xlfn.CEILING.MATH(LN(_xlpm.target_len / _xlpm.seed_len) / LN(2))), IF(_xlpm.req_iters = 0, _xlpm.r_seed_limbs, _xlfn.LET(_xlpm.iterations, _xlfn.SEQUENCE(_xlpm.req_iters), _xlpm.final_state, _xlfn.REDUCE(_xlpm.initial_state, _xlpm.iterations, _xlfn.LAMBDA(_xlpm.state,_xlpm.iter, _xlfn.LET(_xlpm.curr_len, INDEX(_xlpm.state, 1, 1), _xlpm.curr_r, _xlfn.DROP(_xlpm.state, 1), _xlpm.next_len, MIN(_xlpm.curr_len * 2, _xlpm.target_len), _xlpm.shift_limbs, _xlpm.next_len - _xlpm.curr_len, _xlpm.r_prime, IF(_xlpm.shift_limbs &gt; 0, _xlfn.VSTACK(_xlfn.EXPAND(0, _xlpm.shift_limbs, , 0), _xlpm.curr_r), _xlpm.curr_r), _xlpm.b_active, _xlfn.TAKE(_xlpm.limbs_b, -MIN(_xlpm.next_len, _xlpm.len_b)), _xlpm.p_raw, core_BigInt.UMul(_xlpm.b_active, _xlpm.r_prime, _xlpm.k), _xlpm.shift_p, MAX(0, _xlpm.next_len - _xlpm.len_b), _xlpm.p, IF(_xlpm.shift_p &gt; 0, _xlfn.VSTACK(_xlfn.EXPAND(0, _xlpm.shift_p, , 0), _xlpm.p_raw), _xlpm.p_raw), _xlpm.two_beta, _xlfn.VSTACK(_xlfn.EXPAND(0, 2 * _xlpm.next_len, , 0), 2), _xlpm.err, core_BigInt.USub(_xlpm.two_beta, _xlpm.p, _xlpm.k), _xlpm.next_r_unscaled, core_BigInt.UMul(_xlpm.r_prime, _xlpm.err, _xlpm.k), _xlpm.next_r, IF(ROWS(_xlpm.next_r_unscaled) &lt;= 2 * _xlpm.next_len, {0}, _xlfn.DROP(_xlpm.next_r_unscaled, 2 * _xlpm.next_len)), _xlfn.VSTACK(_xlpm.next_len, _xlpm.next_r)))), _xlfn.DROP(_xlpm.final_state, 1)))))</definedName>
     <definedName name="core_BigInt.NewtonRaphsonSeed" comment="[Internal] Generates the exact reciprocal seed for Newton-Raphson Division using Knuth Basecase._x000a_Extracts up to the top 3 limbs of B and calculates floor(Beta^(2*len) / B_top)._x000a_@param limbs_b The divisor limb array._x000a_@param k The dynamic chunk size context">_xlfn.LAMBDA(_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.len_b, ROWS(_xlpm.limbs_b), _xlpm.seed_len, MIN(3, _xlpm.len_b), _xlpm.b_top, _xlfn.TAKE(_xlpm.limbs_b, -_xlpm.seed_len), _xlpm.beta_2m, _xlfn.VSTACK(_xlfn.EXPAND(0, 2 * _xlpm.seed_len, , 0), 1), _xlpm.packed, core_BigInt.KnuthDiv(_xlpm.beta_2m, _xlpm.b_top, _xlpm.k), _xlpm.len_r, INDEX(_xlpm.packed, 1, 1), _xlfn.DROP(_xlpm.packed, _xlpm.len_r + 1)))</definedName>
-    <definedName name="core_BigInt.SafeK" comment="[Internal] Computes the maximum safe base-10 limb size (k) to avoid IEEE-754 precision loss._x000a_@param operation: &quot;ADD&quot; or &quot;MUL&quot;._x000a_@param [max_items] ADD: number of rows. MUL: shortest string digits count.">_xlfn.LAMBDA(_xlpm.operation,_xlop.max_items, _xlfn.LET(_xlpm.items, IF(OR(_xlpm.max_items = "", _xlfn.ISOMITTED(_xlpm.max_items)), 2, MAX(2, _xlpm.max_items)), _xlfn.SWITCH(_xlpm.operation, "ADD", 15 - LEN(_xlpm.items), "MUL", INT((15 - LEN(_xlpm.items)) / 2), "DIV", 7, #NAME?)))</definedName>
+    <definedName name="core_BigInt.SafeK" comment="[Internal] Computes the maximum safe base-10 limb size (k) to avoid IEEE-754 precision loss._x000a_@param operation: &quot;ADD&quot;, &quot;MUL&quot;, or &quot;DIV&quot;._x000a_@param [max_items] ADD: number of operands. MUL: shortest string digits count.">_xlfn.LAMBDA(_xlpm.operation,_xlop.max_items, _xlfn.LET(_xlpm.items, IF(OR(_xlpm.max_items = "", _xlfn.ISOMITTED(_xlpm.max_items)), 2, MAX(2, _xlpm.max_items)), _xlfn.SWITCH(_xlpm.operation, "ADD", 15 - LEN(_xlpm.items), "MUL", _xlfn.LET(_xlpm.test_k, {7;6;5;4;3;2;1}, _xlpm.max_overlap, ROUNDUP(_xlpm.items / _xlpm.test_k, 0), _xlpm.uncarried_max, _xlpm.max_overlap * (10 ^ _xlpm.test_k - 1) ^ 2, _xlpm.max_carry, INT(_xlpm.uncarried_max / 10 ^ _xlpm.test_k), _xlpm.peak_val, _xlpm.uncarried_max + _xlpm.max_carry, MAX(_xlfn._xlws.FILTER(_xlpm.test_k, _xlpm.peak_val &lt;= (10 ^ 15 - 1)))), "DIV", 7, #NAME?)))</definedName>
     <definedName name="core_BigInt.Split" comment="[Internal] Unified Splitter. Splits both scalars and arrays into Little-Endian limbs._x000a_Uses MAX() to guarantee scalar inputs to the SEQUENCE engine._x000a_@param big_ints The string or array of strings._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.big_ints,_xlpm.k, _xlfn.LET(_xlpm.big_int_row, _xlfn.TOROW(_xlpm.big_ints), _xlpm.lengths, LEN(_xlpm.big_int_row), _xlpm.max_len, MAX(_xlpm.lengths), _xlpm.pad_len, ROUNDUP(_xlpm.max_len / _xlpm.k, 0) * _xlpm.k, _xlpm.padded, REPT("0", _xlpm.pad_len - _xlpm.lengths) &amp; _xlpm.big_int_row, _xlpm.starts, _xlfn.SEQUENCE(_xlpm.pad_len / _xlpm.k, 1, _xlpm.pad_len - _xlpm.k + 1, -_xlpm.k), --MID(_xlpm.padded, _xlpm.starts, _xlpm.k)))</definedName>
     <definedName name="core_BigInt.UAdd" comment="[Internal] Unsigned addition of two Little-Endian limb arrays._x000a_@param limbs_a The first limb array._x000a_@param limbs_b The second limb array._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.a,_xlpm.b,_xlpm.k, _xlfn.LET(_xlpm.max_rows, MAX(ROWS(_xlpm.a), ROWS(_xlpm.b)), _xlpm.pad_a, _xlfn.EXPAND(_xlpm.a, _xlpm.max_rows, 1, 0), _xlpm.pad_b, _xlfn.EXPAND(_xlpm.b, _xlpm.max_rows, 1, 0), core_BigInt.Carry(_xlpm.pad_a + _xlpm.pad_b, _xlpm.k)))</definedName>
     <definedName name="core_BigInt.UCompare" comment="[Internal] Unsigned comparison of two Little-Endian limb arrays._x000a_Returns 1 (a &gt; b), -1 (a &lt; b), or 0 (a = b)._x000a_@param limbs_a The first limb array._x000a_@param limbs_b The second limb array.">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b, _xlfn.LET(_xlpm.max_rows, MAX(ROWS(_xlpm.limbs_a), ROWS(_xlpm.limbs_b)), _xlpm.pad_a, _xlfn.EXPAND(_xlpm.limbs_a, _xlpm.max_rows, 1, 0), _xlpm.pad_b, _xlfn.EXPAND(_xlpm.limbs_b, _xlpm.max_rows, 1, 0), _xlpm.diff, _xlpm.pad_a - _xlpm.pad_b, _xlpm.msd_idx, _xlfn.XMATCH(TRUE, _xlpm.diff &lt;&gt; 0, 0, -1), IF(ISNA(_xlpm.msd_idx), 0, SIGN(INDEX(_xlpm.diff, _xlpm.msd_idx, 1)))))</definedName>
     <definedName name="core_BigInt.UMatrixSum" comment="[Internal] Vectorized matrix sum of unsigned BigInt strings._x000a_@param ubig_int Horizontal array (1xN) of normalized magnitude strings._x000a_@param k The unified dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.ubig_ints,_xlpm.k, _xlfn.LET(_xlpm.grid, core_BigInt.Split(_xlpm.ubig_ints, _xlpm.k), _xlpm.raw_limbs, _xlfn.BYROW(_xlpm.grid, _xleta.SUM), core_BigInt.Carry(_xlpm.raw_limbs, _xlpm.k)))</definedName>
     <definedName name="core_BigInt.UMul" comment="[Internal] Unsigned multiplication of two Little-Endian limb arrays._x000a_Utilizes a 1D Discrete Convolution (Cauchy Product) array-slicing strategy._x000a_Zero dynamic memory reallocation. $O(N+M)$ memory footprint._x000a_@param limbs_a The multiplicand limb array._x000a_@para">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.len_a, ROWS(_xlpm.limbs_a), _xlpm.len_b, ROWS(_xlpm.limbs_b), _xlpm.max_rows, _xlpm.len_a + _xlpm.len_b - 1, _xlpm.raw_limbs, _xlfn.MAKEARRAY(_xlpm.max_rows, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, _xlfn.LET(_xlpm.start_i, MAX(1, _xlpm.r - _xlpm.len_b + 1), _xlpm.end_i, MIN(_xlpm.r, _xlpm.len_a), _xlpm.count, _xlpm.end_i - _xlpm.start_i + 1, _xlpm.seq_i, _xlfn.SEQUENCE(_xlpm.count, 1, _xlpm.start_i, 1), _xlpm.seq_j, _xlfn.SEQUENCE(_xlpm.count, 1, _xlpm.r - _xlpm.start_i + 1, -1), SUM(INDEX(_xlpm.limbs_a, _xlpm.seq_i, 1) * INDEX(_xlpm.limbs_b, _xlpm.seq_j, 1))))), core_BigInt.Carry(_xlpm.raw_limbs, _xlpm.k)))</definedName>
+    <definedName name="core_BigInt.UPow" comment="[Internal] Unsigned Base-10 Left-to-Right Exponentiation._x000a_Evaluates the exponent iteratively using a pre-computed 1-9 cache._x000a_@param limbs_base The little-endian limb array of the base._x000a_@param exp_string The exact text string of the exponent._x000a_@param k The ">_xlfn.LAMBDA(_xlpm.limbs_base,_xlpm.exp_string,_xlpm.k, _xlfn.LET(_xlpm.first, _xlpm.limbs_base, _xlpm.second, core_BigInt.UMul(_xlpm.first, _xlpm.first, _xlpm.k), _xlpm.third, core_BigInt.UMul(_xlpm.second, _xlpm.first, _xlpm.k), _xlpm.fourth, core_BigInt.UMul(_xlpm.second, _xlpm.second, _xlpm.k), _xlpm.fifth, core_BigInt.UMul(_xlpm.fourth, _xlpm.first, _xlpm.k), _xlpm.sixth, core_BigInt.UMul(_xlpm.third, _xlpm.third, _xlpm.k), _xlpm.seventh, core_BigInt.UMul(_xlpm.sixth, _xlpm.first, _xlpm.k), _xlpm.eigth, core_BigInt.UMul(_xlpm.fourth, _xlpm.fourth, _xlpm.k), _xlpm.ninth, core_BigInt.UMul(_xlpm.eigth, _xlpm.first, _xlpm.k), _xlpm.exp_digits, --MID(_xlpm.exp_string, _xlfn.SEQUENCE(LEN(_xlpm.exp_string)), 1), _xlfn.REDUCE(1, _xlpm.exp_digits, _xlfn.LAMBDA(_xlpm.acc,_xlpm.digit, _xlfn.LET(_xlpm.is_one, AND(ROWS(_xlpm.acc) = 1, INDEX(_xlpm.acc, 1, 1) = 1), _xlpm.acc_10, IF(_xlpm.is_one, _xlpm.acc, _xlfn.LET(_xlpm.acc_2, core_BigInt.UMul(_xlpm.acc, _xlpm.acc, _xlpm.k), _xlpm.acc_4, core_BigInt.UMul(_xlpm.acc_2, _xlpm.acc_2, _xlpm.k), _xlpm.acc_8, core_BigInt.UMul(_xlpm.acc_4, _xlpm.acc_4, _xlpm.k), core_BigInt.UMul(_xlpm.acc_8, _xlpm.acc_2, _xlpm.k))), IF(_xlpm.digit = 0, _xlpm.acc_10, _xlfn.LET(_xlpm.cache_val, CHOOSE(_xlpm.digit, _xlpm.first, _xlpm.second, _xlpm.third, _xlpm.fourth, _xlpm.fifth, _xlpm.sixth, _xlpm.seventh, _xlpm.eigth, _xlpm.ninth), IF(_xlpm.is_one, _xlpm.cache_val, core_BigInt.UMul(_xlpm.acc_10, _xlpm.cache_val, _xlpm.k)))))))))</definedName>
     <definedName name="core_BigInt.USub" comment="[Internal] Unsigned subtraction of two Little-Endian limb arrays._x000a_Assumes magnitudes A &gt;= B. Resolves borrows top-to-bottom and trims trailing zeros._x000a_@param limbs_a The minuend limb array (must be &gt;= limbs_b)._x000a_@param limbs_b The subtrahend limb array._x000a_@pa">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.max_rows, MAX(ROWS(_xlpm.limbs_a), ROWS(_xlpm.limbs_b)), _xlpm.pad_a, _xlfn.EXPAND(_xlpm.limbs_a, _xlpm.max_rows, 1, 0), _xlpm.pad_b, _xlfn.EXPAND(_xlpm.limbs_b, _xlpm.max_rows, 1, 0), _xlpm.diff, _xlpm.pad_a - _xlpm.pad_b, _xlpm.resolved, core_BigInt.Carry(_xlpm.diff, _xlpm.k), _xlpm.msd_idx, _xlfn.XMATCH(TRUE, _xlpm.resolved &lt;&gt; 0, 0, -1), IF(ISNA(_xlpm.msd_idx), {0}, _xlfn.TAKE(_xlpm.resolved, _xlpm.msd_idx))))</definedName>
     <definedName name="test_BigInt.AsymmetricABGrid">_xlfn.LAMBDA(_xlpm.start_a,_xlpm.max_a,_xlpm.step_a,_xlpm.start_b,_xlpm.max_b,_xlpm.step_b, _xlfn.LET(_xlpm.seq_a, _xlfn.SEQUENCE((_xlpm.max_a - _xlpm.start_a) / _xlpm.step_a + 1, 1, _xlpm.start_a, _xlpm.step_a), _xlpm.seq_b, _xlfn.SEQUENCE((_xlpm.max_b - _xlpm.start_b) / _xlpm.step_b + 1, 1, _xlpm.start_b, _xlpm.step_b), _xlpm.n_a, ROWS(_xlpm.seq_a), _xlpm.n_b, ROWS(_xlpm.seq_b), _xlpm.col_a, _xlfn.TOCOL(IF(_xlfn.SEQUENCE(1, _xlpm.n_b), _xlpm.seq_a)), _xlpm.col_b, _xlfn.TOCOL(IF(_xlfn.SEQUENCE(_xlpm.n_a), _xlfn.TOROW(_xlpm.seq_b))), _xlfn.HSTACK(_xlpm.col_a, _xlpm.col_b)))</definedName>
     <definedName name="test_BigInt.DivisionAlgorithmComparison" comment="Executes a strictly sequential benchmark suite to avoid multi-threading contamination._x000a_@param test_cases An N x 2 array of test lengths: [Length_A, Length_B]_x000a_@param iters Number of iterations per benchmark to smooth NOW() resolution.">_xlfn.LAMBDA(_xlpm.test_cases,_xlpm.iters,_xlpm.repeats, _xlfn.LET(_xlpm.n_tests, ROWS(_xlpm.test_cases), _xlpm.initial, {"Len_A","Len_B","Knuth_ms","NR_ms"}, _xlfn.REDUCE(_xlpm.initial, _xlfn.SEQUENCE(_xlpm.n_tests), _xlfn.LAMBDA(_xlpm.acc,_xlpm.i, _xlfn.LET(_xlpm.len_a, INDEX(_xlpm.test_cases, _xlpm.i, 1), _xlpm.len_b, INDEX(_xlpm.test_cases, _xlpm.i, 2), IF(_xlpm.len_b &gt; _xlpm.len_a, _xlpm.acc, _xlfn.LET(_xlpm.str_a, REPT("9", _xlpm.len_a), _xlpm.str_b, IF(_xlpm.len_b = 1, "7", "7" &amp; REPT("3", _xlpm.len_b - 1)), _xlpm.time_k, test_BigInt.DivisionAlgorithms(_xlpm.str_a, _xlpm.str_b, "KNUTH", _xlpm.iters, _xlpm.repeats), _xlpm.time_nr, test_BigInt.DivisionAlgorithms(_xlpm.str_a, _xlpm.str_b, "NR", _xlpm.iters, _xlpm.repeats), _xlfn.VSTACK(_xlpm.acc, _xlfn.HSTACK(_xlpm.len_a, _xlpm.len_b, _xlpm.time_k, _xlpm.time_nr)))))))))</definedName>
@@ -117,11 +122,20 @@
 </code>
     </initialization>
   </environmentDefinition>
+  <pythonScripts>
+    <pythonScript>
+      <code>import sys
+sys.set_int_max_str_digits(32766)
+a = int(xl(%P2%))
+b = int(xl(%P3%))
+str(a**b)</code>
+    </pythonScript>
+  </pythonScripts>
 </python>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="536">
   <si>
     <t>12345</t>
   </si>
@@ -5839,6 +5853,950 @@
   </si>
   <si>
     <t>Thus, we can calculate the divisor length that tips the probabliliity in NR's favour.</t>
+  </si>
+  <si>
+    <t>Sony WH-1000XM5 Wireless Noise Canceling</t>
+  </si>
+  <si>
+    <t>Bose QuietComfort Wireless Noise Canceling</t>
+  </si>
+  <si>
+    <t>Apple AirPods Pro Wireless Earbuds</t>
+  </si>
+  <si>
+    <t>Logitech G Pro Wireless Gaming Mouse</t>
+  </si>
+  <si>
+    <t>Razer BlackShark V2 Pro Wireless Gaming Headset</t>
+  </si>
+  <si>
+    <t>SteelSeries Arctis Nova Gaming Headset</t>
+  </si>
+  <si>
+    <t>Sony WF-1000XM5 Wireless Earbuds</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Search Term</t>
+  </si>
+  <si>
+    <t>result name</t>
+  </si>
+  <si>
+    <t>result value</t>
+  </si>
+  <si>
+    <t>Wireless Sony</t>
+  </si>
+  <si>
+    <t>BigInt.IsEven</t>
+  </si>
+  <si>
+    <t>BigInt.IsOdd</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2468</t>
+  </si>
+  <si>
+    <t>13579</t>
+  </si>
+  <si>
+    <t>-42</t>
+  </si>
+  <si>
+    <t>-17</t>
+  </si>
+  <si>
+    <t>0008</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Positive even.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Positive odd.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Zero:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Is even.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Negative even.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Negative odd.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Normalisation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Leading zeros.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Null:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Missingly values normalise to zero, which is positive.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Normalization:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Negative zero is coerced to zero, which is positive.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Zero:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Is even.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Standard: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Positive even.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Standard: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Positive odd.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Standard: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Negative even.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Standard: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Negative odd.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Normalisation: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Leading zeros.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Null: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Missingly values normalise to zero, which is positive.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Normalization: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Negative zero is coerced to zero, which is positive.</t>
+    </r>
+  </si>
+  <si>
+    <t>BigInt.Pow</t>
+  </si>
+  <si>
+    <t>1024</t>
+  </si>
+  <si>
+    <t>-8</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>1267650600228229401496703205376</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Undefined:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Zero to the power of zero.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Zero to any positive power</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Identity: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1 identity shortcut (Odd exponent)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Identity:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 1 and a positive exponent will always result in 1.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Identity:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -1 identity shortcut (Even exponent)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> base to power of 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> small power</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Negative base (Odd exponent retains sign)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Negative base (Even exponent flips sign)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BigInt:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Standard large power (Cache and loop stress test)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Shortcircuit:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Integer truncation of fractions ($1/25$)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Shortcircuit:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Exits early if the result is guaranteed to exceed cell limits</t>
+    </r>
+  </si>
+  <si>
+    <t>core_BigInt.UPow</t>
+  </si>
+  <si>
+    <t>{1}</t>
+  </si>
+  <si>
+    <t>{625}</t>
+  </si>
+  <si>
+    <t>{24;1}</t>
+  </si>
+  <si>
+    <t>{576;48;1}</t>
+  </si>
+  <si>
+    <t>base={24;1}
+exp=2
+k=3</t>
+  </si>
+  <si>
+    <t>base={999}
+exp=2
+k=3</t>
+  </si>
+  <si>
+    <t>base={10}
+exp=6
+k=3</t>
+  </si>
+  <si>
+    <t>base={2}
+exp=10
+k=3</t>
+  </si>
+  <si>
+    <t>base={5}
+exp=4
+k=3</t>
+  </si>
+  <si>
+    <t>base=0
+exp=0</t>
+  </si>
+  <si>
+    <t>base=0
+exp=123</t>
+  </si>
+  <si>
+    <t>base=1
+exp=99999999999</t>
+  </si>
+  <si>
+    <t>base=-1
+exp=100</t>
+  </si>
+  <si>
+    <t>base=-1
+exp=101</t>
+  </si>
+  <si>
+    <t>base=12345
+exp=0</t>
+  </si>
+  <si>
+    <t>base=2
+exp=10</t>
+  </si>
+  <si>
+    <t>base=-2
+exp=3</t>
+  </si>
+  <si>
+    <t>base=-2
+exp=4</t>
+  </si>
+  <si>
+    <t>base=2
+exp=100</t>
+  </si>
+  <si>
+    <t>base=5
+exp=-2</t>
+  </si>
+  <si>
+    <t>base=2
+exp=110000</t>
+  </si>
+  <si>
+    <t>base={2}
+exp=1
+k=3</t>
+  </si>
+  <si>
+    <t>base={5}
+exp=0
+k=3</t>
+  </si>
+  <si>
+    <t>base=2
+exp=1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Standard: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>base to power of 1 is base</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Single limb:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Internal resolution, no carry.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Multi-limb:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Base matrix squaring.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Single Limb: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Maximum single-limb carry.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Multi-limb: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Perfect boundary array generation.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Multi-limb:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Array expands to multiple limbs.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Standard: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>base to power of 1 is base.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> base to power of 0.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -5849,7 +6807,7 @@
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5945,8 +6903,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5959,8 +6932,13 @@
         <bgColor theme="4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -5988,11 +6966,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -6027,14 +7021,33 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Input" xfId="1" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="201">
+  <dxfs count="275">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6437,6 +7450,647 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -6468,9 +8122,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6486,27 +8137,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -6642,26 +8281,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -7121,8 +8745,8 @@
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2966838" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -7164,6 +8788,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMath>
@@ -7176,7 +8801,7 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-NZ" sz="1100" i="1">
+                          <a:rPr>
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -7195,7 +8820,7 @@
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-NZ" sz="1100" i="1">
+                          <a:rPr>
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -7218,7 +8843,7 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-NZ" sz="1100" i="1">
+                          <a:rPr>
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -7237,7 +8862,7 @@
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-NZ" sz="1100" i="1">
+                          <a:rPr>
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -7268,7 +8893,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -7332,8 +8957,8 @@
       <xdr:rowOff>27214</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3281539" cy="1352806"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -7375,6 +9000,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMath>
@@ -7384,7 +9010,7 @@
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-NZ" sz="1100" i="1">
+                          <a:rPr>
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -7407,7 +9033,7 @@
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-NZ" sz="1100" i="1">
+                          <a:rPr>
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -7419,7 +9045,7 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-NZ" sz="1100" i="1">
+                              <a:rPr>
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -7451,6 +9077,7 @@
               </a:endParaRPr>
             </a:p>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMath>
@@ -7460,7 +9087,7 @@
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-NZ" sz="1100" i="1">
+                          <a:rPr>
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -7472,7 +9099,7 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-NZ" sz="1100" i="1">
+                              <a:rPr>
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -7496,7 +9123,7 @@
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-NZ" sz="1100" i="1">
+                          <a:rPr>
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -7508,7 +9135,7 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-NZ" sz="1100" i="1">
+                              <a:rPr>
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -7540,6 +9167,7 @@
               </a:endParaRPr>
             </a:p>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMath>
@@ -7558,13 +9186,8 @@
                     <m:f>
                       <m:fPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-NZ" sz="1100">
-                            <a:solidFill>
-                              <a:schemeClr val="tx1"/>
-                            </a:solidFill>
-                            <a:latin typeface="+mn-lt"/>
-                            <a:ea typeface="+mn-ea"/>
-                            <a:cs typeface="+mn-cs"/>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:fPr>
@@ -7575,7 +9198,7 @@
                         <m:d>
                           <m:dPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-NZ" sz="1100" i="1">
+                              <a:rPr>
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -7613,6 +9236,7 @@
               </a:endParaRPr>
             </a:p>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMath>
@@ -7631,7 +9255,7 @@
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-NZ" sz="1100" i="1">
+                          <a:rPr>
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -7659,7 +9283,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -7923,12 +9547,12 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7798C9D4-D9A3-414B-919E-1762A05E858C}" name="Norm_Tests" displayName="Norm_Tests" ref="A7:E26" totalsRowCount="1">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2D415719-D29C-4B5B-8EEC-D6B547CA5D0E}" name="input" dataDxfId="200"/>
+    <tableColumn id="1" xr3:uid="{2D415719-D29C-4B5B-8EEC-D6B547CA5D0E}" name="input" dataDxfId="274"/>
     <tableColumn id="3" xr3:uid="{0ACC712F-EB7B-43DA-9965-8A4957A95DA2}" name="expected"/>
-    <tableColumn id="2" xr3:uid="{25F1E681-6FC0-4609-BF1F-1FF79BEB3CD8}" name="output" dataDxfId="199">
+    <tableColumn id="2" xr3:uid="{25F1E681-6FC0-4609-BF1F-1FF79BEB3CD8}" name="output" dataDxfId="273">
       <calculatedColumnFormula array="1">internal.xlInt.Norm(Norm_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{20432306-08A1-43B4-9B37-03610B79D73B}" name="passing" totalsRowFunction="custom" dataDxfId="198">
+    <tableColumn id="4" xr3:uid="{20432306-08A1-43B4-9B37-03610B79D73B}" name="passing" totalsRowFunction="custom" dataDxfId="272">
       <calculatedColumnFormula>IF(ISERROR(Norm_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Norm_Tests[[#This Row],[expected]]) = ERROR.TYPE(Norm_Tests[[#This Row],[output]]),
     Norm_Tests[[#This Row],[expected]] = Norm_Tests[[#This Row],[output]]
@@ -7942,11 +9566,11 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DCEBF05F-998F-47D8-A8F8-63C4E2771074}" name="UCompare_Tests" displayName="UCompare_Tests" ref="A127:E135" totalsRowCount="1" dataDxfId="159">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DCEBF05F-998F-47D8-A8F8-63C4E2771074}" name="UCompare_Tests" displayName="UCompare_Tests" ref="A127:E135" totalsRowCount="1" dataDxfId="233">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3554FEAC-3E95-4439-BF1F-B262B64D139D}" name="input" dataDxfId="158"/>
-    <tableColumn id="2" xr3:uid="{0EA61E63-F894-4F39-983A-67C6CDEA4B1D}" name="expected" dataDxfId="157"/>
-    <tableColumn id="3" xr3:uid="{B6F49B44-504D-4599-9F1E-49B98046B44D}" name="output" dataDxfId="156">
+    <tableColumn id="1" xr3:uid="{3554FEAC-3E95-4439-BF1F-B262B64D139D}" name="input" dataDxfId="232"/>
+    <tableColumn id="2" xr3:uid="{0EA61E63-F894-4F39-983A-67C6CDEA4B1D}" name="expected" dataDxfId="231"/>
+    <tableColumn id="3" xr3:uid="{B6F49B44-504D-4599-9F1E-49B98046B44D}" name="output" dataDxfId="230">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(UCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -7956,46 +9580,46 @@
     internal.xlInt.UCompare(_xlpm.limbs_a, _xlpm.limbs_b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{96B8A7F0-899C-4301-95D3-41FB0BA096A7}" name="passing" totalsRowFunction="custom" dataDxfId="155">
+    <tableColumn id="4" xr3:uid="{96B8A7F0-899C-4301-95D3-41FB0BA096A7}" name="passing" totalsRowFunction="custom" dataDxfId="229">
       <calculatedColumnFormula>IF(ISERROR(UCompare_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(UCompare_Tests[[#This Row],[output]]),
     UCompare_Tests[[#This Row],[expected]] = UCompare_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UCompare_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C5539D24-4ADC-4D77-B82F-27DAF4B3F109}" name="test" dataDxfId="154"/>
+    <tableColumn id="5" xr3:uid="{C5539D24-4ADC-4D77-B82F-27DAF4B3F109}" name="test" dataDxfId="228"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5E817537-E6E9-4069-8E14-531A3E42821F}" name="Internal_Sign_Tests" displayName="Internal_Sign_Tests" ref="A49:E60" totalsRowCount="1" tableBorderDxfId="153">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5E817537-E6E9-4069-8E14-531A3E42821F}" name="Internal_Sign_Tests" displayName="Internal_Sign_Tests" ref="A49:E60" totalsRowCount="1" tableBorderDxfId="227">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{C5C6E024-5D15-4650-BC06-AE3A9A4A3F9E}" name="input"/>
     <tableColumn id="2" xr3:uid="{2E349FE8-D8E4-4ABE-B47E-F0985AA6C672}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{49844921-4B71-4B13-957C-917C2841A9A3}" name="output" dataDxfId="152">
+    <tableColumn id="3" xr3:uid="{49844921-4B71-4B13-957C-917C2841A9A3}" name="output" dataDxfId="226">
       <calculatedColumnFormula array="1">xlInt.Sign(Internal_Sign_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0236DB85-60E5-4DC6-9655-C6D58A63C8D4}" name="passing" totalsRowFunction="custom" dataDxfId="151">
+    <tableColumn id="4" xr3:uid="{0236DB85-60E5-4DC6-9655-C6D58A63C8D4}" name="passing" totalsRowFunction="custom" dataDxfId="225">
       <calculatedColumnFormula>IF(ISERROR(Internal_Sign_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Internal_Sign_Tests[[#This Row],[expected]]) = ERROR.TYPE(Internal_Sign_Tests[[#This Row],[output]]),
     Internal_Sign_Tests[[#This Row],[expected]] = Internal_Sign_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Internal_Sign_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{396092C1-DC4F-4532-BB59-E0E779D9A525}" name="test" dataDxfId="150"/>
+    <tableColumn id="5" xr3:uid="{396092C1-DC4F-4532-BB59-E0E779D9A525}" name="test" dataDxfId="224"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1BF11AA1-9F01-403A-A5A2-CDAF85E5F9D0}" name="USub_Tests" displayName="USub_Tests" ref="A138:E146" totalsRowCount="1" dataDxfId="149">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1BF11AA1-9F01-403A-A5A2-CDAF85E5F9D0}" name="USub_Tests" displayName="USub_Tests" ref="A138:E146" totalsRowCount="1" dataDxfId="223">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5B979D84-AD0F-45AF-AB26-6C75CA981E58}" name="input" dataDxfId="148"/>
-    <tableColumn id="2" xr3:uid="{D8895FB5-11F4-4379-9B45-0D72ADA71E57}" name="expected" dataDxfId="147"/>
-    <tableColumn id="3" xr3:uid="{A4DDD8AE-0CC0-457E-A08D-2C94591CF878}" name="output" dataDxfId="146">
+    <tableColumn id="1" xr3:uid="{5B979D84-AD0F-45AF-AB26-6C75CA981E58}" name="input" dataDxfId="222"/>
+    <tableColumn id="2" xr3:uid="{D8895FB5-11F4-4379-9B45-0D72ADA71E57}" name="expected" dataDxfId="221"/>
+    <tableColumn id="3" xr3:uid="{A4DDD8AE-0CC0-457E-A08D-2C94591CF878}" name="output" dataDxfId="220">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(USub_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -8007,25 +9631,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BF616718-1C7F-4627-B496-8B6339CC2735}" name="passing" totalsRowFunction="custom" dataDxfId="145">
+    <tableColumn id="4" xr3:uid="{BF616718-1C7F-4627-B496-8B6339CC2735}" name="passing" totalsRowFunction="custom" dataDxfId="219">
       <calculatedColumnFormula>IF(ISERROR(USub_Tests[[#This Row],[expected]]),
     ERROR.TYPE(USub_Tests[[#This Row],[expected]]) = ERROR.TYPE(USub_Tests[[#This Row],[output]]),
     USub_Tests[[#This Row],[expected]] = USub_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(USub_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FCF52C7D-4E82-4BAA-8C93-974211CAC2AF}" name="test" dataDxfId="144"/>
+    <tableColumn id="5" xr3:uid="{FCF52C7D-4E82-4BAA-8C93-974211CAC2AF}" name="test" dataDxfId="218"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B5433254-33A6-4D35-8484-91940B628217}" name="Table6" displayName="Table6" ref="A149:E160" totalsRowCount="1" dataDxfId="143">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B5433254-33A6-4D35-8484-91940B628217}" name="Table6" displayName="Table6" ref="A149:E160" totalsRowCount="1" dataDxfId="217">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D52F6D10-66CD-4765-927A-94A578D3C30A}" name="input" dataDxfId="142" totalsRowDxfId="141"/>
-    <tableColumn id="2" xr3:uid="{DF2BEEE3-E1EF-4EA0-A6A8-77B06FB5C3EE}" name="expected" dataDxfId="140"/>
-    <tableColumn id="3" xr3:uid="{4FDE8849-AFE2-471E-8131-C5B45620EBDC}" name="output" dataDxfId="139">
+    <tableColumn id="1" xr3:uid="{D52F6D10-66CD-4765-927A-94A578D3C30A}" name="input" dataDxfId="216" totalsRowDxfId="215"/>
+    <tableColumn id="2" xr3:uid="{DF2BEEE3-E1EF-4EA0-A6A8-77B06FB5C3EE}" name="expected" dataDxfId="214"/>
+    <tableColumn id="3" xr3:uid="{4FDE8849-AFE2-471E-8131-C5B45620EBDC}" name="output" dataDxfId="213">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.input, _xlfn.REGEXEXTRACT(Table6[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.input,1,1),
@@ -8039,25 +9663,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5813AECE-7F35-45E7-8E1F-50DCC8404156}" name="passing" totalsRowFunction="custom" dataDxfId="138" totalsRowDxfId="137">
+    <tableColumn id="4" xr3:uid="{5813AECE-7F35-45E7-8E1F-50DCC8404156}" name="passing" totalsRowFunction="custom" dataDxfId="212" totalsRowDxfId="211">
       <calculatedColumnFormula>IF(ISERROR(Table6[[#This Row],[expected]]),
     ERROR.TYPE(Table6[[#This Row],[expected]]) = ERROR.TYPE(Table6[[#This Row],[output]]),
     Table6[[#This Row],[expected]] = Table6[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Table6[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6FEE6B80-DF03-48AD-BE0B-5CF10BB9952D}" name="test" dataDxfId="136"/>
+    <tableColumn id="5" xr3:uid="{6FEE6B80-DF03-48AD-BE0B-5CF10BB9952D}" name="test" dataDxfId="210"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{99918742-71F1-4CEE-8B31-04D0864B12BE}" name="Add_Tests" displayName="Add_Tests" ref="A163:E169" totalsRowCount="1" dataDxfId="135">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{99918742-71F1-4CEE-8B31-04D0864B12BE}" name="Add_Tests" displayName="Add_Tests" ref="A163:E169" totalsRowCount="1" dataDxfId="209">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BEDCABA1-70E6-4A6B-A326-B96D805DC792}" name="input" dataDxfId="134"/>
-    <tableColumn id="2" xr3:uid="{D2C344B5-4A5B-4F69-8FCC-B73D81DE29AD}" name="expected" dataDxfId="133"/>
-    <tableColumn id="3" xr3:uid="{B095BBF3-B41C-4F5B-9689-A075BCD3B3C6}" name="output" dataDxfId="132">
+    <tableColumn id="1" xr3:uid="{BEDCABA1-70E6-4A6B-A326-B96D805DC792}" name="input" dataDxfId="208"/>
+    <tableColumn id="2" xr3:uid="{D2C344B5-4A5B-4F69-8FCC-B73D81DE29AD}" name="expected" dataDxfId="207"/>
+    <tableColumn id="3" xr3:uid="{B095BBF3-B41C-4F5B-9689-A075BCD3B3C6}" name="output" dataDxfId="206">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Add_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -8065,25 +9689,25 @@
     xlInt.Add(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8A3FC5E9-718D-42AA-90B8-83E1D4F3B18A}" name="passing" totalsRowFunction="custom" dataDxfId="131" totalsRowDxfId="130">
+    <tableColumn id="4" xr3:uid="{8A3FC5E9-718D-42AA-90B8-83E1D4F3B18A}" name="passing" totalsRowFunction="custom" dataDxfId="205" totalsRowDxfId="204">
       <calculatedColumnFormula>IF(ISERROR(Add_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Add_Tests[[#This Row],[expected]]) = ERROR.TYPE(Add_Tests[[#This Row],[output]]),
     Add_Tests[[#This Row],[expected]] = Add_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Add_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DCB35414-E71F-476D-B8FC-5C98625552A8}" name="test" dataDxfId="129"/>
+    <tableColumn id="5" xr3:uid="{DCB35414-E71F-476D-B8FC-5C98625552A8}" name="test" dataDxfId="203"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{DE30AD6A-E7CB-4B0A-9AF6-2A68597C812D}" name="Sub_Tests" displayName="Sub_Tests" ref="A172:E176" totalsRowCount="1" dataDxfId="128">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{DE30AD6A-E7CB-4B0A-9AF6-2A68597C812D}" name="Sub_Tests" displayName="Sub_Tests" ref="A172:E176" totalsRowCount="1" dataDxfId="202">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{03074968-5409-421B-94C4-D5670F4C41D8}" name="input" dataDxfId="127"/>
-    <tableColumn id="2" xr3:uid="{DDFFA8C5-FCAB-4C4D-9AD1-92357F9E25A7}" name="expected" dataDxfId="126"/>
-    <tableColumn id="3" xr3:uid="{799B106A-FDF6-4F6C-8D67-8B6355524DD8}" name="output" dataDxfId="125">
+    <tableColumn id="1" xr3:uid="{03074968-5409-421B-94C4-D5670F4C41D8}" name="input" dataDxfId="201"/>
+    <tableColumn id="2" xr3:uid="{DDFFA8C5-FCAB-4C4D-9AD1-92357F9E25A7}" name="expected" dataDxfId="200"/>
+    <tableColumn id="3" xr3:uid="{799B106A-FDF6-4F6C-8D67-8B6355524DD8}" name="output" dataDxfId="199">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Sub_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -8091,25 +9715,25 @@
     xlInt.Sub(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{365F4930-D4D1-407A-94F0-4578BEFB456D}" name="passing" totalsRowFunction="custom" dataDxfId="124" totalsRowDxfId="123">
+    <tableColumn id="4" xr3:uid="{365F4930-D4D1-407A-94F0-4578BEFB456D}" name="passing" totalsRowFunction="custom" dataDxfId="198" totalsRowDxfId="197">
       <calculatedColumnFormula>IF(ISERROR(Sub_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Sub_Tests[[#This Row],[expected]]) = ERROR.TYPE(Sub_Tests[[#This Row],[output]]),
     Sub_Tests[[#This Row],[expected]] = Sub_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Sub_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CD9B4489-0AA4-43C4-9B29-8D70A32DD746}" name="test" dataDxfId="122"/>
+    <tableColumn id="5" xr3:uid="{CD9B4489-0AA4-43C4-9B29-8D70A32DD746}" name="test" dataDxfId="196"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{9E3906E7-DD79-4AAB-8367-36E413E4200E}" name="Split_Tests" displayName="Split_Tests" ref="A179:E183" totalsRowCount="1" dataDxfId="121">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{9E3906E7-DD79-4AAB-8367-36E413E4200E}" name="Split_Tests" displayName="Split_Tests" ref="A179:E183" totalsRowCount="1" dataDxfId="195">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{14CAD510-CB82-4DB3-9F1C-40F2CB704D1C}" name="input" dataDxfId="120"/>
-    <tableColumn id="2" xr3:uid="{5035D4AE-F48A-40D0-AF90-BDA3391536CB}" name="expected" dataDxfId="119"/>
-    <tableColumn id="3" xr3:uid="{99876D23-ABB8-4C24-98A4-1BEEEEDD07C4}" name="output" dataDxfId="118">
+    <tableColumn id="1" xr3:uid="{14CAD510-CB82-4DB3-9F1C-40F2CB704D1C}" name="input" dataDxfId="194"/>
+    <tableColumn id="2" xr3:uid="{5035D4AE-F48A-40D0-AF90-BDA3391536CB}" name="expected" dataDxfId="193"/>
+    <tableColumn id="3" xr3:uid="{99876D23-ABB8-4C24-98A4-1BEEEEDD07C4}" name="output" dataDxfId="192">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.input_k, _xlfn.REGEXEXTRACT(Split_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.input, INDEX(_xlpm.input_k,1,1),
@@ -8119,25 +9743,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A5A07BB4-21F2-4B01-9D44-1AA4366EAB7F}" name="passing" totalsRowFunction="custom" dataDxfId="117" totalsRowDxfId="116">
+    <tableColumn id="4" xr3:uid="{A5A07BB4-21F2-4B01-9D44-1AA4366EAB7F}" name="passing" totalsRowFunction="custom" dataDxfId="191" totalsRowDxfId="190">
       <calculatedColumnFormula>IF(ISERROR(Split_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Split_Tests[[#This Row],[expected]]) = ERROR.TYPE(Split_Tests[[#This Row],[output]]),
     Split_Tests[[#This Row],[expected]] = Split_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Split_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{12903E1A-EF63-4775-8029-4AC6E1371182}" name="test" dataDxfId="115"/>
+    <tableColumn id="5" xr3:uid="{12903E1A-EF63-4775-8029-4AC6E1371182}" name="test" dataDxfId="189"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{B4199465-17FF-401D-8825-47D1965ACDD0}" name="UMatrixSum_Tests" displayName="UMatrixSum_Tests" ref="A186:E191" totalsRowCount="1" dataDxfId="114">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{B4199465-17FF-401D-8825-47D1965ACDD0}" name="UMatrixSum_Tests" displayName="UMatrixSum_Tests" ref="A186:E191" totalsRowCount="1" dataDxfId="188">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{02600896-7D14-484F-821B-B4456983BB28}" name="input" dataDxfId="113"/>
-    <tableColumn id="2" xr3:uid="{173735CF-904D-4F11-81E2-08E18A2E350F}" name="expected" dataDxfId="112"/>
-    <tableColumn id="3" xr3:uid="{39C7D243-2D28-43C6-84E9-009686A8BE25}" name="output" dataDxfId="111">
+    <tableColumn id="1" xr3:uid="{02600896-7D14-484F-821B-B4456983BB28}" name="input" dataDxfId="187"/>
+    <tableColumn id="2" xr3:uid="{173735CF-904D-4F11-81E2-08E18A2E350F}" name="expected" dataDxfId="186"/>
+    <tableColumn id="3" xr3:uid="{39C7D243-2D28-43C6-84E9-009686A8BE25}" name="output" dataDxfId="185">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.limbs_k, _xlfn.REGEXEXTRACT(UMatrixSum_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.limbs, _xlfn.TEXTSPLIT(INDEX(_xlpm.limbs_k,1,1), ",", ";"),
@@ -8146,14 +9770,14 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{708213D7-3DCF-48EE-85F0-411FE836D86B}" name="passing" totalsRowFunction="custom" dataDxfId="110" totalsRowDxfId="109">
+    <tableColumn id="4" xr3:uid="{708213D7-3DCF-48EE-85F0-411FE836D86B}" name="passing" totalsRowFunction="custom" dataDxfId="184" totalsRowDxfId="183">
       <calculatedColumnFormula>IF(ISERROR(UMatrixSum_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UMatrixSum_Tests[[#This Row],[expected]]) = ERROR.TYPE(UMatrixSum_Tests[[#This Row],[output]]),
     UMatrixSum_Tests[[#This Row],[expected]] = UMatrixSum_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UMatrixSum_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{1A2B4059-059A-4B6D-8573-AF782E91D2A9}" name="test" dataDxfId="108"/>
+    <tableColumn id="5" xr3:uid="{1A2B4059-059A-4B6D-8573-AF782E91D2A9}" name="test" dataDxfId="182"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8164,14 +9788,14 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9C2FC9B7-0634-4588-8EFB-AD967A0F24A8}" name="input"/>
     <tableColumn id="2" xr3:uid="{282A94A0-1EBE-4152-8A9A-8F0EF95A0338}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{1B45BBB4-DEF0-4F8A-9D99-3837C2C1D0A6}" name="output" dataDxfId="107">
+    <tableColumn id="3" xr3:uid="{1B45BBB4-DEF0-4F8A-9D99-3837C2C1D0A6}" name="output" dataDxfId="181">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.range, _xlfn.REGEXEXTRACT(Sum_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.big_ints, IFERROR(_xlfn.TEXTSPLIT(INDEX(_xlpm.range,1,1), ",", ";"), ""),
     xlInt.Sum(_xlpm.big_ints)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EE8AD54F-5219-409B-ABCC-BA23AB35B017}" name="passing" totalsRowFunction="custom" dataDxfId="106" totalsRowDxfId="105">
+    <tableColumn id="4" xr3:uid="{EE8AD54F-5219-409B-ABCC-BA23AB35B017}" name="passing" totalsRowFunction="custom" dataDxfId="180" totalsRowDxfId="179">
       <calculatedColumnFormula>IF(ISERROR(Sum_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Sum_Tests[[#This Row],[expected]]) = ERROR.TYPE(Sum_Tests[[#This Row],[output]]),
     Sum_Tests[[#This Row],[expected]] = Sum_Tests[[#This Row],[output]]
@@ -8185,11 +9809,11 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{106EA359-E4B0-4842-9C9A-062E9FF7B5FB}" name="UMul_Tests" displayName="UMul_Tests" ref="A205:E211" totalsRowCount="1" dataDxfId="104">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{106EA359-E4B0-4842-9C9A-062E9FF7B5FB}" name="UMul_Tests" displayName="UMul_Tests" ref="A205:E211" totalsRowCount="1" dataDxfId="178">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8D4F0565-063F-4316-9C57-705162867D2A}" name="input" dataDxfId="103"/>
-    <tableColumn id="2" xr3:uid="{DAD4A921-C714-4DCC-AADE-BAF6086A3636}" name="expected" dataDxfId="102"/>
-    <tableColumn id="3" xr3:uid="{97E6E3DD-CA0A-4372-AC3D-9A495F7C3A53}" name="output" dataDxfId="101">
+    <tableColumn id="1" xr3:uid="{8D4F0565-063F-4316-9C57-705162867D2A}" name="input" dataDxfId="177"/>
+    <tableColumn id="2" xr3:uid="{DAD4A921-C714-4DCC-AADE-BAF6086A3636}" name="expected" dataDxfId="176"/>
+    <tableColumn id="3" xr3:uid="{97E6E3DD-CA0A-4372-AC3D-9A495F7C3A53}" name="output" dataDxfId="175">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(UMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -8201,25 +9825,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E46610B1-FA9D-4582-8D0C-63D1EC61D64E}" name="passing" totalsRowFunction="custom" dataDxfId="100" totalsRowDxfId="99">
+    <tableColumn id="4" xr3:uid="{E46610B1-FA9D-4582-8D0C-63D1EC61D64E}" name="passing" totalsRowFunction="custom" dataDxfId="174" totalsRowDxfId="173">
       <calculatedColumnFormula>IF(ISERROR(UMul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UMul_Tests[[#This Row],[output]]),
     UMul_Tests[[#This Row],[expected]] = UMul_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UMul_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5337E378-248A-4061-ABD9-D618DD84E539}" name="test" dataDxfId="98"/>
+    <tableColumn id="5" xr3:uid="{5337E378-248A-4061-ABD9-D618DD84E539}" name="test" dataDxfId="172"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D11AB36-7D48-42C4-B8E7-63DA272F75B3}" name="SafeK_Tests" displayName="SafeK_Tests" ref="A29:E37" totalsRowCount="1" dataDxfId="197">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D11AB36-7D48-42C4-B8E7-63DA272F75B3}" name="SafeK_Tests" displayName="SafeK_Tests" ref="A29:E37" totalsRowCount="1" dataDxfId="271">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{CD46518C-03B6-4B43-A7B8-7360525A290D}" name="input" dataDxfId="196"/>
-    <tableColumn id="3" xr3:uid="{F3B44865-B013-44C5-A9D4-1A13BFE5AA81}" name="expected" dataDxfId="195"/>
-    <tableColumn id="4" xr3:uid="{F40E0393-EF6C-4B2D-9F49-5CBB088EB267}" name="output" dataDxfId="194">
+    <tableColumn id="2" xr3:uid="{CD46518C-03B6-4B43-A7B8-7360525A290D}" name="input" dataDxfId="270"/>
+    <tableColumn id="3" xr3:uid="{F3B44865-B013-44C5-A9D4-1A13BFE5AA81}" name="expected" dataDxfId="269"/>
+    <tableColumn id="4" xr3:uid="{F40E0393-EF6C-4B2D-9F49-5CBB088EB267}" name="output" dataDxfId="268">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.op_items, _xlfn.REGEXEXTRACT(SafeK_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.op, INDEX(_xlpm.op_items,1,1),
@@ -8228,25 +9852,25 @@
     internal.xlInt.SafeK(_xlpm.op, _xlpm.max_items)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{62988A37-52EF-4F3E-82FE-0F2CD420BEF5}" name="passing" totalsRowFunction="custom" dataDxfId="193">
+    <tableColumn id="5" xr3:uid="{62988A37-52EF-4F3E-82FE-0F2CD420BEF5}" name="passing" totalsRowFunction="custom" dataDxfId="267">
       <calculatedColumnFormula>IF(ISERROR(SafeK_Tests[[#This Row],[expected]]),
     ERROR.TYPE(SafeK_Tests[[#This Row],[expected]]) = ERROR.TYPE(SafeK_Tests[[#This Row],[output]]),
     SafeK_Tests[[#This Row],[expected]] = SafeK_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(SafeK_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{FB9EC421-276B-4C54-8F46-BB5C01271314}" name="test" dataDxfId="192"/>
+    <tableColumn id="6" xr3:uid="{FB9EC421-276B-4C54-8F46-BB5C01271314}" name="test" dataDxfId="266"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C927379E-9D9F-446A-A7F8-18937FDB3BE9}" name="Mul_Tests" displayName="Mul_Tests" ref="A214:E221" totalsRowCount="1" dataDxfId="97">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C927379E-9D9F-446A-A7F8-18937FDB3BE9}" name="Mul_Tests" displayName="Mul_Tests" ref="A214:E221" totalsRowCount="1" dataDxfId="171">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3AEB129A-112F-4626-87D9-516E40338A3B}" name="input" dataDxfId="96" totalsRowDxfId="95"/>
-    <tableColumn id="2" xr3:uid="{17E1D158-0134-4800-97A0-9A914A48AA8F}" name="expected" dataDxfId="94" totalsRowDxfId="93"/>
-    <tableColumn id="3" xr3:uid="{B25D54E8-D438-48E6-9956-B82746478514}" name="output" dataDxfId="92" totalsRowDxfId="91">
+    <tableColumn id="1" xr3:uid="{3AEB129A-112F-4626-87D9-516E40338A3B}" name="input" dataDxfId="170" totalsRowDxfId="116"/>
+    <tableColumn id="2" xr3:uid="{17E1D158-0134-4800-97A0-9A914A48AA8F}" name="expected" dataDxfId="169" totalsRowDxfId="115"/>
+    <tableColumn id="3" xr3:uid="{B25D54E8-D438-48E6-9956-B82746478514}" name="output" dataDxfId="168" totalsRowDxfId="114">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Mul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -8254,25 +9878,25 @@
     xlInt.Mul(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5D503E6C-603A-418E-8D29-E96FF9E82626}" name="passing" totalsRowFunction="custom" dataDxfId="90" totalsRowDxfId="89">
+    <tableColumn id="4" xr3:uid="{5D503E6C-603A-418E-8D29-E96FF9E82626}" name="passing" totalsRowFunction="custom" dataDxfId="167" totalsRowDxfId="113">
       <calculatedColumnFormula>IF(ISERROR(Mul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Mul_Tests[[#This Row],[expected]]) = ERROR.TYPE(Mul_Tests[[#This Row],[output]]),
     Mul_Tests[[#This Row],[expected]] = Mul_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Mul_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{785B4909-13EC-4ABC-ADF8-0A6E8C364AE8}" name="test" dataDxfId="88" totalsRowDxfId="87"/>
+    <tableColumn id="5" xr3:uid="{785B4909-13EC-4ABC-ADF8-0A6E8C364AE8}" name="test" dataDxfId="166" totalsRowDxfId="112"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{4706FBB1-54D9-4F64-9481-F1D8984AE18E}" name="KnuthDiv_Tests" displayName="KnuthDiv_Tests" ref="A224:E233" totalsRowCount="1" dataDxfId="86">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{4706FBB1-54D9-4F64-9481-F1D8984AE18E}" name="KnuthDiv_Tests" displayName="KnuthDiv_Tests" ref="A224:E233" totalsRowCount="1" dataDxfId="165">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C9306945-CA62-4719-882E-A0FFCFC80239}" name="input" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{FF30C91E-2B8D-47FA-B34B-6CA5257E3EB7}" name="expected" dataDxfId="84"/>
-    <tableColumn id="3" xr3:uid="{3B324DA4-4AAE-408C-B627-929F7D5C7CBF}" name="output" dataDxfId="83">
+    <tableColumn id="1" xr3:uid="{C9306945-CA62-4719-882E-A0FFCFC80239}" name="input" dataDxfId="164"/>
+    <tableColumn id="2" xr3:uid="{FF30C91E-2B8D-47FA-B34B-6CA5257E3EB7}" name="expected" dataDxfId="163"/>
+    <tableColumn id="3" xr3:uid="{3B324DA4-4AAE-408C-B627-929F7D5C7CBF}" name="output" dataDxfId="162">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(KnuthDiv_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -8284,25 +9908,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{439AD3AD-5C90-48C6-AB74-B9DDF87C40B5}" name="passing" totalsRowFunction="custom" dataDxfId="82" totalsRowDxfId="81">
+    <tableColumn id="4" xr3:uid="{439AD3AD-5C90-48C6-AB74-B9DDF87C40B5}" name="passing" totalsRowFunction="custom" dataDxfId="161" totalsRowDxfId="160">
       <calculatedColumnFormula>IF(ISERROR(KnuthDiv_Tests[[#This Row],[expected]]),
     ERROR.TYPE(KnuthDiv_Tests[[#This Row],[expected]]) = ERROR.TYPE(KnuthDiv_Tests[[#This Row],[output]]),
     KnuthDiv_Tests[[#This Row],[expected]] = KnuthDiv_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(KnuthDiv_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7D4887A2-EC0B-4C52-8336-E300544022A1}" name="test" dataDxfId="80"/>
+    <tableColumn id="5" xr3:uid="{7D4887A2-EC0B-4C52-8336-E300544022A1}" name="test" dataDxfId="159"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B0C6E940-EAB6-4373-8987-1B7722C2CC79}" name="Div_Tests" displayName="Div_Tests" ref="A236:E247" totalsRowCount="1" dataDxfId="79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B0C6E940-EAB6-4373-8987-1B7722C2CC79}" name="Div_Tests" displayName="Div_Tests" ref="A236:E247" totalsRowCount="1" dataDxfId="158">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{0A49EAE4-5B09-4D2D-A863-D634A4825565}" name="input" dataDxfId="78" totalsRowDxfId="77"/>
-    <tableColumn id="2" xr3:uid="{4BF042F3-E337-4B63-A1E8-414D47019404}" name="expected" dataDxfId="76" totalsRowDxfId="75"/>
-    <tableColumn id="3" xr3:uid="{118ABB7A-7163-40CB-974E-69BFF6BE2BE0}" name="output" dataDxfId="74" totalsRowDxfId="73">
+    <tableColumn id="1" xr3:uid="{0A49EAE4-5B09-4D2D-A863-D634A4825565}" name="input" dataDxfId="157" totalsRowDxfId="156"/>
+    <tableColumn id="2" xr3:uid="{4BF042F3-E337-4B63-A1E8-414D47019404}" name="expected" dataDxfId="155" totalsRowDxfId="154"/>
+    <tableColumn id="3" xr3:uid="{118ABB7A-7163-40CB-974E-69BFF6BE2BE0}" name="output" dataDxfId="153" totalsRowDxfId="152">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Div_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -8310,25 +9934,25 @@
     xlInt.Div(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4344C6C8-3F96-4048-96D0-CA621258C1D7}" name="passing" totalsRowFunction="custom" dataDxfId="72" totalsRowDxfId="71">
+    <tableColumn id="4" xr3:uid="{4344C6C8-3F96-4048-96D0-CA621258C1D7}" name="passing" totalsRowFunction="custom" dataDxfId="151" totalsRowDxfId="150">
       <calculatedColumnFormula>IF(ISERROR(Div_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Div_Tests[[#This Row],[expected]]) = ERROR.TYPE(Div_Tests[[#This Row],[output]]),
     Div_Tests[[#This Row],[expected]] = Div_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Div_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7CF48835-D05B-4120-863E-A47318569688}" name="test" dataDxfId="70" totalsRowDxfId="69"/>
+    <tableColumn id="5" xr3:uid="{7CF48835-D05B-4120-863E-A47318569688}" name="test" dataDxfId="149" totalsRowDxfId="148"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{B3179C39-4489-4B3E-A2D2-1A2B50DC058E}" name="Mod_Tests" displayName="Mod_Tests" ref="A250:E261" totalsRowCount="1" dataDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{B3179C39-4489-4B3E-A2D2-1A2B50DC058E}" name="Mod_Tests" displayName="Mod_Tests" ref="A250:E261" totalsRowCount="1" dataDxfId="147">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F1BCBD73-ACF5-4609-87F5-A9FAB549955E}" name="input" dataDxfId="67" totalsRowDxfId="66"/>
-    <tableColumn id="2" xr3:uid="{E9604163-FD58-4190-8D72-28AA7831E8C8}" name="expected" dataDxfId="65" totalsRowDxfId="64"/>
-    <tableColumn id="3" xr3:uid="{9D21CE79-D00B-4182-97B3-60EF6DC8B18F}" name="output" dataDxfId="63" totalsRowDxfId="62">
+    <tableColumn id="1" xr3:uid="{F1BCBD73-ACF5-4609-87F5-A9FAB549955E}" name="input" dataDxfId="146" totalsRowDxfId="145"/>
+    <tableColumn id="2" xr3:uid="{E9604163-FD58-4190-8D72-28AA7831E8C8}" name="expected" dataDxfId="144" totalsRowDxfId="143"/>
+    <tableColumn id="3" xr3:uid="{9D21CE79-D00B-4182-97B3-60EF6DC8B18F}" name="output" dataDxfId="142" totalsRowDxfId="141">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Mod_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -8336,25 +9960,25 @@
     xlInt.Mod(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CEF047D2-0521-425D-99C4-E3B997A68B32}" name="passing" totalsRowFunction="custom" dataDxfId="61" totalsRowDxfId="60">
+    <tableColumn id="4" xr3:uid="{CEF047D2-0521-425D-99C4-E3B997A68B32}" name="passing" totalsRowFunction="custom" dataDxfId="140" totalsRowDxfId="139">
       <calculatedColumnFormula>IF(ISERROR(Mod_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Mod_Tests[[#This Row],[expected]]) = ERROR.TYPE(Mod_Tests[[#This Row],[output]]),
     Mod_Tests[[#This Row],[expected]] = Mod_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Mod_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{BB0A3941-EEFB-445E-AE7B-833C36649910}" name="test" dataDxfId="59" totalsRowDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{BB0A3941-EEFB-445E-AE7B-833C36649910}" name="test" dataDxfId="138" totalsRowDxfId="137"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{82953E35-FA6B-4DA1-B4AC-195D4F1BB7C8}" name="DivMod_Tests" displayName="DivMod_Tests" ref="A264:E280" totalsRowCount="1" dataDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{82953E35-FA6B-4DA1-B4AC-195D4F1BB7C8}" name="DivMod_Tests" displayName="DivMod_Tests" ref="A264:E280" totalsRowCount="1" dataDxfId="136">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E51BC97B-AA0D-4705-AF36-89CB4A3501FF}" name="input" dataDxfId="56" totalsRowDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{6D6483DD-139D-4DFE-BFEA-8BAA3E5C6FCF}" name="expected" dataDxfId="54" totalsRowDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{17DE90BB-4525-4C2D-9577-C4372DCD74B3}" name="output" dataDxfId="52" totalsRowDxfId="51">
+    <tableColumn id="1" xr3:uid="{E51BC97B-AA0D-4705-AF36-89CB4A3501FF}" name="input" dataDxfId="135" totalsRowDxfId="111"/>
+    <tableColumn id="2" xr3:uid="{6D6483DD-139D-4DFE-BFEA-8BAA3E5C6FCF}" name="expected" dataDxfId="134" totalsRowDxfId="110"/>
+    <tableColumn id="3" xr3:uid="{17DE90BB-4525-4C2D-9577-C4372DCD74B3}" name="output" dataDxfId="133" totalsRowDxfId="109">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.ab_flag, _xlfn.REGEXEXTRACT(DivMod_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab_flag,1,1),
@@ -8363,25 +9987,25 @@
     _xlfn.ARRAYTOTEXT(xlInt.DivMod(_xlpm.a, _xlpm.b, _xlpm.use_floor), 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{08745616-1601-437B-82EA-C1952393A99B}" name="passing" totalsRowFunction="custom" dataDxfId="50" totalsRowDxfId="49">
+    <tableColumn id="4" xr3:uid="{08745616-1601-437B-82EA-C1952393A99B}" name="passing" totalsRowFunction="custom" dataDxfId="132" totalsRowDxfId="108">
       <calculatedColumnFormula>IF(ISERROR(DivMod_Tests[[#This Row],[expected]]),
     ERROR.TYPE(DivMod_Tests[[#This Row],[expected]]) = ERROR.TYPE(DivMod_Tests[[#This Row],[output]]),
     DivMod_Tests[[#This Row],[expected]] = DivMod_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(DivMod_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{10C8AB14-1CD9-4B06-8A65-2B27B32A2550}" name="test" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{10C8AB14-1CD9-4B06-8A65-2B27B32A2550}" name="test" dataDxfId="131" totalsRowDxfId="107"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{3400C680-561E-4111-B80A-CA24DB597E3F}" name="Table25" displayName="Table25" ref="A283:E289" totalsRowCount="1" dataDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{3400C680-561E-4111-B80A-CA24DB597E3F}" name="Table25" displayName="Table25" ref="A283:E289" totalsRowCount="1" dataDxfId="130">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{37EA378F-E179-45E1-BF1A-FBA82C305DBA}" name="input" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{11DFB020-1D5E-4E26-A86F-6B73428F3709}" name="expected" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{943FD3EB-6145-4BEE-9408-F68BE0795A47}" name="output" dataDxfId="43">
+    <tableColumn id="1" xr3:uid="{37EA378F-E179-45E1-BF1A-FBA82C305DBA}" name="input" dataDxfId="129"/>
+    <tableColumn id="2" xr3:uid="{11DFB020-1D5E-4E26-A86F-6B73428F3709}" name="expected" dataDxfId="128"/>
+    <tableColumn id="3" xr3:uid="{943FD3EB-6145-4BEE-9408-F68BE0795A47}" name="output" dataDxfId="127">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.bk, _xlfn.REGEXEXTRACT(Table25[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.b, INDEX(_xlpm.bk,1,1),
@@ -8391,14 +10015,111 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{165ECACC-11AD-4EB0-AE14-7D528DA64799}" name="passing" totalsRowFunction="custom" dataDxfId="42" totalsRowDxfId="41">
+    <tableColumn id="4" xr3:uid="{165ECACC-11AD-4EB0-AE14-7D528DA64799}" name="passing" totalsRowFunction="custom" dataDxfId="126" totalsRowDxfId="125">
       <calculatedColumnFormula>IF(ISERROR(Table25[[#This Row],[expected]]),
     ERROR.TYPE(Table25[[#This Row],[expected]]) = ERROR.TYPE(Table25[[#This Row],[output]]),
     Table25[[#This Row],[expected]] = Table25[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Table25[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6FA8F2E3-9F29-41C5-8B60-45E4EF5BFD33}" name="test" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{6FA8F2E3-9F29-41C5-8B60-45E4EF5BFD33}" name="test" dataDxfId="124"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{12A27437-8E10-4142-9D59-10A781936664}" name="IsEven_Tests" displayName="IsEven_Tests" ref="A292:E301" totalsRowCount="1" tableBorderDxfId="123">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{72B34F2A-D724-472B-AEA6-85847044F8BB}" name="input"/>
+    <tableColumn id="2" xr3:uid="{8F1A9828-E68A-40FE-8534-E28D2B59C43A}" name="expected"/>
+    <tableColumn id="3" xr3:uid="{90993922-EF49-4320-BFDE-A85AAC37995B}" name="output" dataDxfId="120">
+      <calculatedColumnFormula array="1">BigInt.IsEven(IsEven_Tests[[#This Row],[input]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{4CD10349-78F4-4A08-8AD3-6AFDD4218B3F}" name="passing" totalsRowFunction="custom" dataDxfId="119">
+      <calculatedColumnFormula>IF(ISERROR(IsEven_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsEven_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsEven_Tests[[#This Row],[output]]),
+    IsEven_Tests[[#This Row],[expected]] = IsEven_Tests[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(IsEven_Tests[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{9C811914-2121-4942-94F0-B4760C307266}" name="test" dataDxfId="118"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{29B30C5B-F766-4073-878A-FEDF3C607366}" name="IsOdd_Tests" displayName="IsOdd_Tests" ref="A304:E313" totalsRowCount="1" tableBorderDxfId="122">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{8D247229-1BE2-49B1-BEC8-19AFBBF671FC}" name="input"/>
+    <tableColumn id="2" xr3:uid="{9F1FC5CC-11FA-4EB1-BA6E-3C18F4379652}" name="expected"/>
+    <tableColumn id="3" xr3:uid="{6B07B988-F191-4E41-81FA-8D0020D0AEF2}" name="output" dataDxfId="117">
+      <calculatedColumnFormula array="1">BigInt.IsOdd(IsOdd_Tests[[#This Row],[input]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{15820A65-99F4-420C-A89B-1F6FB8202BCC}" name="passing" totalsRowFunction="custom" dataDxfId="121">
+      <calculatedColumnFormula>IF(ISERROR(IsOdd_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsOdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsOdd_Tests[[#This Row],[output]]),
+    IsOdd_Tests[[#This Row],[expected]] = IsOdd_Tests[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(IsOdd_Tests[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{60D794CC-2FBF-4E93-9A30-99426CA9AD8A}" name="test"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{371705AE-DD2A-4348-9D77-10A58AFED934}" name="Pow_Tests" displayName="Pow_Tests" ref="A327:E341" totalsRowCount="1" dataDxfId="101">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{428DC074-F3C2-4541-81E6-FDDAE2482D27}" name="input" dataDxfId="106"/>
+    <tableColumn id="2" xr3:uid="{B5FD2A40-BCC5-4580-B8CD-768791024AC5}" name="expected" dataDxfId="105"/>
+    <tableColumn id="3" xr3:uid="{F4E39208-EEA5-4CF3-B04A-4707F3E1FB8E}" name="output" dataDxfId="104">
+      <calculatedColumnFormula array="1">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab, 1, 1),
+    _xlpm.b, INDEX(_xlpm.ab, 1, 2),
+    BigInt.Pow(_xlpm.a, _xlpm.b)
+)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{B407AC33-1B59-4CB2-91F2-8CA96B7CE117}" name="passing" totalsRowFunction="custom" dataDxfId="103">
+      <calculatedColumnFormula>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
+    Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(Pow_Tests[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{A1A7E0C2-F1B0-41A5-A740-EDF94ACD6051}" name="test" dataDxfId="102"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{83160072-B1B0-4FD1-88FC-006B8639CBE0}" name="UPow_Tests" displayName="UPow_Tests" ref="A316:E324" totalsRowCount="1" dataDxfId="96">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{20145995-7ED4-4B73-887D-9D74DA0828CF}" name="input" dataDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{82FBC2F1-B0A2-4D85-8D2F-0E9C3548EF52}" name="expected" dataDxfId="99"/>
+    <tableColumn id="3" xr3:uid="{30FC05F3-7A85-4F3C-B4CB-146B4FEBD37A}" name="output" dataDxfId="95">
+      <calculatedColumnFormula array="1">_xlfn.LET(
+    _xlpm.bek, _xlfn.REGEXEXTRACT(UPow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.base, INDEX(_xlpm.bek,1,1),
+    _xlpm.exp, INDEX(_xlpm.bek,1,2),
+    _xlpm.k, --INDEX(_xlpm.bek,1,3),
+    _xlpm.limbs_base, --_xlfn.TEXTSPLIT(_xlpm.base,",",";"),
+    _xlpm.output, core_BigInt.UPow(_xlpm.limbs_base, _xlpm.exp, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{13DDE135-8BB6-470E-A96F-6482CA5075E2}" name="passing" totalsRowFunction="custom" dataDxfId="98">
+      <calculatedColumnFormula>IF(ISERROR(UPow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(UPow_Tests[[#This Row],[expected]]) = ERROR.TYPE(UPow_Tests[[#This Row],[output]]),
+    UPow_Tests[[#This Row],[expected]] = UPow_Tests[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(UPow_Tests[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{45AF5A50-06F2-4581-B704-1F7379E7EFDB}" name="test" dataDxfId="97"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8409,7 +10130,7 @@
   <tableColumns count="5">
     <tableColumn id="2" xr3:uid="{2286D15B-F261-49FF-90E5-E32FAEEEA489}" name="input"/>
     <tableColumn id="3" xr3:uid="{1D45A0AC-7049-4C3E-9D4F-CF777F60006B}" name="expected"/>
-    <tableColumn id="4" xr3:uid="{725B7147-ED3D-42D7-9030-A0FCAF6502D0}" name="output" dataDxfId="191">
+    <tableColumn id="4" xr3:uid="{725B7147-ED3D-42D7-9030-A0FCAF6502D0}" name="output" dataDxfId="265">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.limbs_k, _xlfn.REGEXEXTRACT(Merge_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.limbs_text, INDEX(_xlpm.limbs_k,1,1),
@@ -8418,28 +10139,39 @@
     internal.xlInt.Merge(_xlpm.limbs, _xlpm.k)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7D40DA54-4D50-4770-9171-9F50106783D7}" name="passing" totalsRowFunction="custom" dataDxfId="190">
+    <tableColumn id="5" xr3:uid="{7D40DA54-4D50-4770-9171-9F50106783D7}" name="passing" totalsRowFunction="custom" dataDxfId="264">
       <calculatedColumnFormula>IF(ISERROR(Merge_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Merge_Tests[[#This Row],[expected]]) = ERROR.TYPE(Merge_Tests[[#This Row],[output]]),
     Merge_Tests[[#This Row],[expected]] = Merge_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Merge_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F906F95B-0DD5-4F50-9A36-C63DEC4B514C}" name="test" dataDxfId="189"/>
+    <tableColumn id="6" xr3:uid="{F906F95B-0DD5-4F50-9A36-C63DEC4B514C}" name="test" dataDxfId="263"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{C1458AB7-3AD7-44E9-B064-C2BEC4A41762}" name="Data" displayName="Data" ref="A1:B8" totalsRowShown="0">
+  <autoFilter ref="A1:B8" xr:uid="{C1458AB7-3AD7-44E9-B064-C2BEC4A41762}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{9A8BD9FA-DF38-4A2D-A72E-A480C042A429}" name="name"/>
+    <tableColumn id="2" xr3:uid="{5167F18E-1410-43BB-8E2F-ED5CAD279C57}" name="value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{8BE14E9C-9052-4C6B-91B5-74156B78161B}" name="IsZero_Tests" displayName="IsZero_Tests" ref="A63:E71" totalsRowCount="1" tableBorderDxfId="188">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{8BE14E9C-9052-4C6B-91B5-74156B78161B}" name="IsZero_Tests" displayName="IsZero_Tests" ref="A63:E71" totalsRowCount="1" tableBorderDxfId="262">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F079B266-FBE5-40B3-929D-6B075F83B32A}" name="input"/>
     <tableColumn id="2" xr3:uid="{D2EFB528-67FC-4490-876A-C72813F17A1C}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{735E5B6C-B3DA-49E2-B1F3-88323DE570B4}" name="output" dataDxfId="187">
+    <tableColumn id="3" xr3:uid="{735E5B6C-B3DA-49E2-B1F3-88323DE570B4}" name="output" dataDxfId="261">
       <calculatedColumnFormula array="1">xlInt.IsZero(IsZero_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BCB92B9B-DD7D-407D-BA1B-01844C06231A}" name="passing" totalsRowFunction="custom" dataDxfId="186">
+    <tableColumn id="4" xr3:uid="{BCB92B9B-DD7D-407D-BA1B-01844C06231A}" name="passing" totalsRowFunction="custom" dataDxfId="260">
       <calculatedColumnFormula>IF(ISERROR(IsZero_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsZero_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsZero_Tests[[#This Row],[output]]),
     IsZero_Tests[[#This Row],[expected]] = IsZero_Tests[[#This Row],[output]]
@@ -8453,14 +10185,14 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{5F9E4160-7872-486B-BC10-496D23C60B5A}" name="IsNeg_Tests" displayName="IsNeg_Tests" ref="A74:E82" totalsRowCount="1" tableBorderDxfId="185">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{5F9E4160-7872-486B-BC10-496D23C60B5A}" name="IsNeg_Tests" displayName="IsNeg_Tests" ref="A74:E82" totalsRowCount="1" tableBorderDxfId="259">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A7BB892B-ECAA-4176-AFC6-3449690829CA}" name="input"/>
     <tableColumn id="2" xr3:uid="{4B67C433-DA3F-4DC8-A14F-97407C2E1925}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{49ED0D04-2AA3-4848-8297-CAE5A7D726CD}" name="output" dataDxfId="184">
+    <tableColumn id="3" xr3:uid="{49ED0D04-2AA3-4848-8297-CAE5A7D726CD}" name="output" dataDxfId="258">
       <calculatedColumnFormula array="1">xlInt.IsNeg(IsNeg_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{186FF00B-FED3-490C-BB63-2A0FC55A43D4}" name="passing" totalsRowFunction="custom" dataDxfId="183">
+    <tableColumn id="4" xr3:uid="{186FF00B-FED3-490C-BB63-2A0FC55A43D4}" name="passing" totalsRowFunction="custom" dataDxfId="257">
       <calculatedColumnFormula>IF(ISERROR(IsNeg_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsNeg_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsNeg_Tests[[#This Row],[output]]),
     IsNeg_Tests[[#This Row],[expected]] = IsNeg_Tests[[#This Row],[output]]
@@ -8474,14 +10206,14 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1631B68B-6D5A-402C-92F6-EDA45141B375}" name="Abs_Tests" displayName="Abs_Tests" ref="A85:E94" totalsRowCount="1" tableBorderDxfId="182">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1631B68B-6D5A-402C-92F6-EDA45141B375}" name="Abs_Tests" displayName="Abs_Tests" ref="A85:E94" totalsRowCount="1" tableBorderDxfId="256">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{631C43FF-F966-4712-8BEB-7647066AF179}" name="input"/>
     <tableColumn id="2" xr3:uid="{70F5476C-B45C-439B-BA01-326EAD467334}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{1E90CD50-A25E-4E12-84D5-66BAAE6BAF0C}" name="output" dataDxfId="181">
+    <tableColumn id="3" xr3:uid="{1E90CD50-A25E-4E12-84D5-66BAAE6BAF0C}" name="output" dataDxfId="255">
       <calculatedColumnFormula array="1">BigInt.Abs(Abs_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6A0B92CA-92B2-4515-86E8-D91A4279D44E}" name="passing" totalsRowFunction="custom" dataDxfId="180">
+    <tableColumn id="4" xr3:uid="{6A0B92CA-92B2-4515-86E8-D91A4279D44E}" name="passing" totalsRowFunction="custom" dataDxfId="254">
       <calculatedColumnFormula>IF(ISERROR(Abs_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Abs_Tests[[#This Row],[expected]]) = ERROR.TYPE(Abs_Tests[[#This Row],[output]]),
     Abs_Tests[[#This Row],[expected]] = Abs_Tests[[#This Row],[output]]
@@ -8495,11 +10227,11 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{A4A096D6-4E75-4455-A80B-D324779CD007}" name="Compare_Tests" displayName="Compare_Tests" ref="A97:E104" totalsRowCount="1" dataDxfId="179" tableBorderDxfId="178">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{A4A096D6-4E75-4455-A80B-D324779CD007}" name="Compare_Tests" displayName="Compare_Tests" ref="A97:E104" totalsRowCount="1" dataDxfId="253" tableBorderDxfId="252">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{6ED51130-CCEE-49F5-AE6A-C115477DEEC1}" name="input" dataDxfId="177"/>
-    <tableColumn id="3" xr3:uid="{33B3A3D6-83B3-431F-A0B0-9371BBC16D08}" name="expected" dataDxfId="176"/>
-    <tableColumn id="4" xr3:uid="{C0A2BAFD-DD64-4B6D-8350-F0AF699F41AB}" name="output" dataDxfId="175">
+    <tableColumn id="2" xr3:uid="{6ED51130-CCEE-49F5-AE6A-C115477DEEC1}" name="input" dataDxfId="251"/>
+    <tableColumn id="3" xr3:uid="{33B3A3D6-83B3-431F-A0B0-9371BBC16D08}" name="expected" dataDxfId="250"/>
+    <tableColumn id="4" xr3:uid="{C0A2BAFD-DD64-4B6D-8350-F0AF699F41AB}" name="output" dataDxfId="249">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Compare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -8507,25 +10239,25 @@
     xlInt.Compare(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{25151C64-2D6E-4B12-87AA-02A64ED9EF2B}" name="passing" totalsRowFunction="custom" dataDxfId="174">
+    <tableColumn id="5" xr3:uid="{25151C64-2D6E-4B12-87AA-02A64ED9EF2B}" name="passing" totalsRowFunction="custom" dataDxfId="248">
       <calculatedColumnFormula>IF(ISERROR(Compare_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Compare_Tests[[#This Row],[expected]]) = ERROR.TYPE(Compare_Tests[[#This Row],[output]]),
     Compare_Tests[[#This Row],[expected]] = Compare_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Compare_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D859FAE6-EDFC-42C5-8B0C-0116D05E04F4}" name="test" dataDxfId="173"/>
+    <tableColumn id="6" xr3:uid="{D859FAE6-EDFC-42C5-8B0C-0116D05E04F4}" name="test" dataDxfId="247"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{AB2483E8-D478-4FD2-B96C-83A98FDDE6FA}" name="Carry_Tests" displayName="Carry_Tests" ref="A107:E114" totalsRowCount="1" dataDxfId="172">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{AB2483E8-D478-4FD2-B96C-83A98FDDE6FA}" name="Carry_Tests" displayName="Carry_Tests" ref="A107:E114" totalsRowCount="1" dataDxfId="246">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{58CF3EAC-5FAD-4E1D-8349-AFD0026A5A6F}" name="input" dataDxfId="171"/>
-    <tableColumn id="3" xr3:uid="{8D4EBB1D-1F70-4D9A-B9FB-C7B03997C3F4}" name="expected" dataDxfId="170"/>
-    <tableColumn id="4" xr3:uid="{54C37EF8-27DA-477C-BC79-632DD5E54F03}" name="output" dataDxfId="169">
+    <tableColumn id="2" xr3:uid="{58CF3EAC-5FAD-4E1D-8349-AFD0026A5A6F}" name="input" dataDxfId="245"/>
+    <tableColumn id="3" xr3:uid="{8D4EBB1D-1F70-4D9A-B9FB-C7B03997C3F4}" name="expected" dataDxfId="244"/>
+    <tableColumn id="4" xr3:uid="{54C37EF8-27DA-477C-BC79-632DD5E54F03}" name="output" dataDxfId="243">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.limbs_k, _xlfn.REGEXEXTRACT(Carry_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.limbs_text, INDEX(_xlpm.limbs_k,1,1),
@@ -8535,25 +10267,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9B430B30-AE60-423D-A6BE-D7D881CBC2A0}" name="passing" totalsRowFunction="custom" dataDxfId="168">
+    <tableColumn id="5" xr3:uid="{9B430B30-AE60-423D-A6BE-D7D881CBC2A0}" name="passing" totalsRowFunction="custom" dataDxfId="242">
       <calculatedColumnFormula>IF(ISERROR(Carry_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Carry_Tests[[#This Row],[expected]]) = ERROR.TYPE(Carry_Tests[[#This Row],[output]]),
     Carry_Tests[[#This Row],[expected]] = Carry_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Carry_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{5F961C10-163D-49CE-93C1-9CA6C9C623CA}" name="test" dataDxfId="167"/>
+    <tableColumn id="6" xr3:uid="{5F961C10-163D-49CE-93C1-9CA6C9C623CA}" name="test" dataDxfId="241"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{9541B332-DEB4-4260-9226-40E8C97DC59F}" name="UAdd_Tests" displayName="UAdd_Tests" ref="A117:E124" totalsRowCount="1" dataDxfId="166" tableBorderDxfId="165">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{9541B332-DEB4-4260-9226-40E8C97DC59F}" name="UAdd_Tests" displayName="UAdd_Tests" ref="A117:E124" totalsRowCount="1" dataDxfId="240" tableBorderDxfId="239">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{6C5FB7CE-3B1F-447E-9ED3-14E839061137}" name="input" dataDxfId="164"/>
-    <tableColumn id="3" xr3:uid="{56E7CDEA-877C-47CA-B875-1A1313998480}" name="expected" dataDxfId="163"/>
-    <tableColumn id="4" xr3:uid="{0AB7FE18-4035-4604-909F-956B1054DE95}" name="output" dataDxfId="162">
+    <tableColumn id="2" xr3:uid="{6C5FB7CE-3B1F-447E-9ED3-14E839061137}" name="input" dataDxfId="238"/>
+    <tableColumn id="3" xr3:uid="{56E7CDEA-877C-47CA-B875-1A1313998480}" name="expected" dataDxfId="237"/>
+    <tableColumn id="4" xr3:uid="{0AB7FE18-4035-4604-909F-956B1054DE95}" name="output" dataDxfId="236">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(UAdd_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -8565,14 +10297,14 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{148597F1-9D9D-45C9-949B-CA15D869DE95}" name="passing" totalsRowFunction="custom" dataDxfId="161">
+    <tableColumn id="5" xr3:uid="{148597F1-9D9D-45C9-949B-CA15D869DE95}" name="passing" totalsRowFunction="custom" dataDxfId="235">
       <calculatedColumnFormula>IF(ISERROR(UAdd_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UAdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(UAdd_Tests[[#This Row],[output]]),
     UAdd_Tests[[#This Row],[expected]] = UAdd_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UAdd_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{58290239-17D2-42FA-BE94-887F938260F4}" name="test" dataDxfId="160"/>
+    <tableColumn id="6" xr3:uid="{58290239-17D2-42FA-BE94-887F938260F4}" name="test" dataDxfId="234"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8895,7 +10627,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="1588" row="6">
+  <wetp:taskpane dockstate="right" visibility="0" width="1261" row="6">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -8927,7 +10659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23AD1BF5-F75F-465D-AC38-22DFE6D4806A}">
-  <dimension ref="A1:E289"/>
+  <dimension ref="A1:E365"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="23.6328125" customWidth="1"/>
@@ -8952,7 +10684,7 @@
       </c>
       <c r="B2">
         <f>COUNTIF(_xlfn._TRO_TRAILING(A:A), "input")</f>
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -8961,7 +10693,7 @@
       </c>
       <c r="B3" cm="1">
         <f t="array" ref="B3">SUM(--ISLOGICAL(_xlfn._TRO_TRAILING(D:D))) - $B$2</f>
-        <v>185</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8970,7 +10702,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(_xlfn._TRO_TRAILING(D:D), TRUE) - $B$2</f>
-        <v>185</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1"/>
@@ -14780,176 +16512,1285 @@
         <v>403</v>
       </c>
     </row>
-    <row r="289" spans="4:4" collapsed="1">
+    <row r="289" spans="1:5" collapsed="1">
       <c r="D289" s="9" t="b">
         <f>AND(Table25[passing])</f>
         <v>1</v>
       </c>
     </row>
+    <row r="290" spans="1:5" ht="15" thickBot="1"/>
+    <row r="291" spans="1:5" ht="18.5">
+      <c r="A291" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B291" s="5"/>
+      <c r="C291" s="5"/>
+      <c r="D291" s="5"/>
+      <c r="E291" s="5"/>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" t="s">
+        <v>110</v>
+      </c>
+      <c r="B292" t="s">
+        <v>35</v>
+      </c>
+      <c r="C292" t="s">
+        <v>36</v>
+      </c>
+      <c r="D292" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E292" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A293" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B293" t="b">
+        <v>1</v>
+      </c>
+      <c r="C293" t="b" cm="1">
+        <f t="array" ref="C293">BigInt.IsEven(IsEven_Tests[[#This Row],[input]])</f>
+        <v>1</v>
+      </c>
+      <c r="D293" t="b">
+        <f>IF(ISERROR(IsEven_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsEven_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsEven_Tests[[#This Row],[output]]),
+    IsEven_Tests[[#This Row],[expected]] = IsEven_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E293" s="18" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A294" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B294" t="b">
+        <v>1</v>
+      </c>
+      <c r="C294" t="b" cm="1">
+        <f t="array" ref="C294">BigInt.IsEven(IsEven_Tests[[#This Row],[input]])</f>
+        <v>1</v>
+      </c>
+      <c r="D294" t="b">
+        <f>IF(ISERROR(IsEven_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsEven_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsEven_Tests[[#This Row],[output]]),
+    IsEven_Tests[[#This Row],[expected]] = IsEven_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E294" s="18" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A295" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B295" t="b">
+        <v>0</v>
+      </c>
+      <c r="C295" t="b" cm="1">
+        <f t="array" ref="C295">BigInt.IsEven(IsEven_Tests[[#This Row],[input]])</f>
+        <v>0</v>
+      </c>
+      <c r="D295" t="b">
+        <f>IF(ISERROR(IsEven_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsEven_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsEven_Tests[[#This Row],[output]]),
+    IsEven_Tests[[#This Row],[expected]] = IsEven_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E295" s="18" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A296" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B296" t="b">
+        <v>1</v>
+      </c>
+      <c r="C296" t="b" cm="1">
+        <f t="array" ref="C296">BigInt.IsEven(IsEven_Tests[[#This Row],[input]])</f>
+        <v>1</v>
+      </c>
+      <c r="D296" t="b">
+        <f>IF(ISERROR(IsEven_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsEven_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsEven_Tests[[#This Row],[output]]),
+    IsEven_Tests[[#This Row],[expected]] = IsEven_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E296" s="18" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A297" t="s">
+        <v>468</v>
+      </c>
+      <c r="B297" t="b">
+        <v>0</v>
+      </c>
+      <c r="C297" t="b" cm="1">
+        <f t="array" ref="C297">BigInt.IsEven(IsEven_Tests[[#This Row],[input]])</f>
+        <v>0</v>
+      </c>
+      <c r="D297" t="b">
+        <f>IF(ISERROR(IsEven_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsEven_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsEven_Tests[[#This Row],[output]]),
+    IsEven_Tests[[#This Row],[expected]] = IsEven_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E297" s="18" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A298" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B298" t="b">
+        <v>1</v>
+      </c>
+      <c r="C298" t="b" cm="1">
+        <f t="array" ref="C298">BigInt.IsEven(IsEven_Tests[[#This Row],[input]])</f>
+        <v>1</v>
+      </c>
+      <c r="D298" t="b">
+        <f>IF(ISERROR(IsEven_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsEven_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsEven_Tests[[#This Row],[output]]),
+    IsEven_Tests[[#This Row],[expected]] = IsEven_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E298" s="18" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A299" s="2"/>
+      <c r="B299" t="b">
+        <v>1</v>
+      </c>
+      <c r="C299" s="19" t="b" cm="1">
+        <f t="array" ref="C299">BigInt.IsEven(IsEven_Tests[[#This Row],[input]])</f>
+        <v>1</v>
+      </c>
+      <c r="D299" s="19" t="b">
+        <f>IF(ISERROR(IsEven_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsEven_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsEven_Tests[[#This Row],[output]]),
+    IsEven_Tests[[#This Row],[expected]] = IsEven_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E299" s="18" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A300" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B300" t="b">
+        <v>1</v>
+      </c>
+      <c r="C300" t="b" cm="1">
+        <f t="array" ref="C300">BigInt.IsEven(IsEven_Tests[[#This Row],[input]])</f>
+        <v>1</v>
+      </c>
+      <c r="D300" t="b">
+        <f>IF(ISERROR(IsEven_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsEven_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsEven_Tests[[#This Row],[output]]),
+    IsEven_Tests[[#This Row],[expected]] = IsEven_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E300" s="18" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" collapsed="1">
+      <c r="A301" s="2"/>
+      <c r="D301" t="b">
+        <f>AND(IsEven_Tests[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" ht="15" thickBot="1"/>
+    <row r="303" spans="1:5" ht="18.5">
+      <c r="A303" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="B303" s="5"/>
+      <c r="C303" s="5"/>
+      <c r="D303" s="5"/>
+      <c r="E303" s="5"/>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" t="s">
+        <v>110</v>
+      </c>
+      <c r="B304" t="s">
+        <v>35</v>
+      </c>
+      <c r="C304" t="s">
+        <v>36</v>
+      </c>
+      <c r="D304" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E304" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A305" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B305" t="b">
+        <v>0</v>
+      </c>
+      <c r="C305" t="b" cm="1">
+        <f t="array" ref="C305">BigInt.IsOdd(IsOdd_Tests[[#This Row],[input]])</f>
+        <v>0</v>
+      </c>
+      <c r="D305" t="b">
+        <f>IF(ISERROR(IsOdd_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsOdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsOdd_Tests[[#This Row],[output]]),
+    IsOdd_Tests[[#This Row],[expected]] = IsOdd_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E305" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A306" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B306" t="b">
+        <v>0</v>
+      </c>
+      <c r="C306" t="b" cm="1">
+        <f t="array" ref="C306">BigInt.IsOdd(IsOdd_Tests[[#This Row],[input]])</f>
+        <v>0</v>
+      </c>
+      <c r="D306" t="b">
+        <f>IF(ISERROR(IsOdd_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsOdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsOdd_Tests[[#This Row],[output]]),
+    IsOdd_Tests[[#This Row],[expected]] = IsOdd_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E306" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A307" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B307" t="b">
+        <v>1</v>
+      </c>
+      <c r="C307" t="b" cm="1">
+        <f t="array" ref="C307">BigInt.IsOdd(IsOdd_Tests[[#This Row],[input]])</f>
+        <v>1</v>
+      </c>
+      <c r="D307" t="b">
+        <f>IF(ISERROR(IsOdd_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsOdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsOdd_Tests[[#This Row],[output]]),
+    IsOdd_Tests[[#This Row],[expected]] = IsOdd_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E307" s="4" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A308" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B308" t="b">
+        <v>0</v>
+      </c>
+      <c r="C308" t="b" cm="1">
+        <f t="array" ref="C308">BigInt.IsOdd(IsOdd_Tests[[#This Row],[input]])</f>
+        <v>0</v>
+      </c>
+      <c r="D308" t="b">
+        <f>IF(ISERROR(IsOdd_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsOdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsOdd_Tests[[#This Row],[output]]),
+    IsOdd_Tests[[#This Row],[expected]] = IsOdd_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E308" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A309" t="s">
+        <v>468</v>
+      </c>
+      <c r="B309" t="b">
+        <v>1</v>
+      </c>
+      <c r="C309" t="b" cm="1">
+        <f t="array" ref="C309">BigInt.IsOdd(IsOdd_Tests[[#This Row],[input]])</f>
+        <v>1</v>
+      </c>
+      <c r="D309" t="b">
+        <f>IF(ISERROR(IsOdd_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsOdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsOdd_Tests[[#This Row],[output]]),
+    IsOdd_Tests[[#This Row],[expected]] = IsOdd_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E309" s="4" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A310" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B310" t="b">
+        <v>0</v>
+      </c>
+      <c r="C310" t="b" cm="1">
+        <f t="array" ref="C310">BigInt.IsOdd(IsOdd_Tests[[#This Row],[input]])</f>
+        <v>0</v>
+      </c>
+      <c r="D310" t="b">
+        <f>IF(ISERROR(IsOdd_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsOdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsOdd_Tests[[#This Row],[output]]),
+    IsOdd_Tests[[#This Row],[expected]] = IsOdd_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E310" s="4" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A311" s="2"/>
+      <c r="B311" t="b">
+        <v>0</v>
+      </c>
+      <c r="C311" s="19" t="b" cm="1">
+        <f t="array" ref="C311">BigInt.IsOdd(IsOdd_Tests[[#This Row],[input]])</f>
+        <v>0</v>
+      </c>
+      <c r="D311" s="19" t="b">
+        <f>IF(ISERROR(IsOdd_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsOdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsOdd_Tests[[#This Row],[output]]),
+    IsOdd_Tests[[#This Row],[expected]] = IsOdd_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E311" s="4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A312" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B312" t="b">
+        <v>0</v>
+      </c>
+      <c r="C312" t="b" cm="1">
+        <f t="array" ref="C312">BigInt.IsOdd(IsOdd_Tests[[#This Row],[input]])</f>
+        <v>0</v>
+      </c>
+      <c r="D312" t="b">
+        <f>IF(ISERROR(IsOdd_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(IsOdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsOdd_Tests[[#This Row],[output]]),
+    IsOdd_Tests[[#This Row],[expected]] = IsOdd_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E312" s="4" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" collapsed="1">
+      <c r="A313" s="2"/>
+      <c r="D313" t="b">
+        <f>AND(IsOdd_Tests[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" ht="15" thickBot="1"/>
+    <row r="315" spans="1:5" ht="18.5">
+      <c r="A315" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="B315" s="5"/>
+      <c r="C315" s="5"/>
+      <c r="D315" s="5"/>
+      <c r="E315" s="5"/>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" t="s">
+        <v>110</v>
+      </c>
+      <c r="B316" t="s">
+        <v>35</v>
+      </c>
+      <c r="C316" t="s">
+        <v>36</v>
+      </c>
+      <c r="D316" t="s">
+        <v>48</v>
+      </c>
+      <c r="E316" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A317" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="B317" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="C317" s="9" t="str" cm="1">
+        <f t="array" ref="C317">_xlfn.LET(
+    _xlpm.bek, _xlfn.REGEXEXTRACT(UPow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.base, INDEX(_xlpm.bek,1,1),
+    _xlpm.exp, INDEX(_xlpm.bek,1,2),
+    _xlpm.k, --INDEX(_xlpm.bek,1,3),
+    _xlpm.limbs_base, --_xlfn.TEXTSPLIT(_xlpm.base,",",";"),
+    _xlpm.output, core_BigInt.UPow(_xlpm.limbs_base, _xlpm.exp, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{1}</v>
+      </c>
+      <c r="D317" s="9" t="b">
+        <f>IF(ISERROR(UPow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(UPow_Tests[[#This Row],[expected]]) = ERROR.TYPE(UPow_Tests[[#This Row],[output]]),
+    UPow_Tests[[#This Row],[expected]] = UPow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E317" s="9" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A318" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="B318" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C318" s="9" t="str" cm="1">
+        <f t="array" ref="C318">_xlfn.LET(
+    _xlpm.bek, _xlfn.REGEXEXTRACT(UPow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.base, INDEX(_xlpm.bek,1,1),
+    _xlpm.exp, INDEX(_xlpm.bek,1,2),
+    _xlpm.k, --INDEX(_xlpm.bek,1,3),
+    _xlpm.limbs_base, --_xlfn.TEXTSPLIT(_xlpm.base,",",";"),
+    _xlpm.output, core_BigInt.UPow(_xlpm.limbs_base, _xlpm.exp, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{2}</v>
+      </c>
+      <c r="D318" s="9" t="b">
+        <f>IF(ISERROR(UPow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(UPow_Tests[[#This Row],[expected]]) = ERROR.TYPE(UPow_Tests[[#This Row],[output]]),
+    UPow_Tests[[#This Row],[expected]] = UPow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E318" s="9" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A319" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="B319" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="C319" s="9" t="str" cm="1">
+        <f t="array" ref="C319">_xlfn.LET(
+    _xlpm.bek, _xlfn.REGEXEXTRACT(UPow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.base, INDEX(_xlpm.bek,1,1),
+    _xlpm.exp, INDEX(_xlpm.bek,1,2),
+    _xlpm.k, --INDEX(_xlpm.bek,1,3),
+    _xlpm.limbs_base, --_xlfn.TEXTSPLIT(_xlpm.base,",",";"),
+    _xlpm.output, core_BigInt.UPow(_xlpm.limbs_base, _xlpm.exp, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{625}</v>
+      </c>
+      <c r="D319" s="9" t="b">
+        <f>IF(ISERROR(UPow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(UPow_Tests[[#This Row],[expected]]) = ERROR.TYPE(UPow_Tests[[#This Row],[output]]),
+    UPow_Tests[[#This Row],[expected]] = UPow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E319" s="9" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A320" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="B320" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="C320" s="9" t="str" cm="1">
+        <f t="array" ref="C320">_xlfn.LET(
+    _xlpm.bek, _xlfn.REGEXEXTRACT(UPow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.base, INDEX(_xlpm.bek,1,1),
+    _xlpm.exp, INDEX(_xlpm.bek,1,2),
+    _xlpm.k, --INDEX(_xlpm.bek,1,3),
+    _xlpm.limbs_base, --_xlfn.TEXTSPLIT(_xlpm.base,",",";"),
+    _xlpm.output, core_BigInt.UPow(_xlpm.limbs_base, _xlpm.exp, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{24;1}</v>
+      </c>
+      <c r="D320" s="9" t="b">
+        <f>IF(ISERROR(UPow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(UPow_Tests[[#This Row],[expected]]) = ERROR.TYPE(UPow_Tests[[#This Row],[output]]),
+    UPow_Tests[[#This Row],[expected]] = UPow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E320" s="9" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A321" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="B321" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="C321" s="9" t="str" cm="1">
+        <f t="array" ref="C321">_xlfn.LET(
+    _xlpm.bek, _xlfn.REGEXEXTRACT(UPow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.base, INDEX(_xlpm.bek,1,1),
+    _xlpm.exp, INDEX(_xlpm.bek,1,2),
+    _xlpm.k, --INDEX(_xlpm.bek,1,3),
+    _xlpm.limbs_base, --_xlfn.TEXTSPLIT(_xlpm.base,",",";"),
+    _xlpm.output, core_BigInt.UPow(_xlpm.limbs_base, _xlpm.exp, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{0;0;1}</v>
+      </c>
+      <c r="D321" s="9" t="b">
+        <f>IF(ISERROR(UPow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(UPow_Tests[[#This Row],[expected]]) = ERROR.TYPE(UPow_Tests[[#This Row],[output]]),
+    UPow_Tests[[#This Row],[expected]] = UPow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E321" s="9" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A322" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="B322" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="C322" s="9" t="str" cm="1">
+        <f t="array" ref="C322">_xlfn.LET(
+    _xlpm.bek, _xlfn.REGEXEXTRACT(UPow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.base, INDEX(_xlpm.bek,1,1),
+    _xlpm.exp, INDEX(_xlpm.bek,1,2),
+    _xlpm.k, --INDEX(_xlpm.bek,1,3),
+    _xlpm.limbs_base, --_xlfn.TEXTSPLIT(_xlpm.base,",",";"),
+    _xlpm.output, core_BigInt.UPow(_xlpm.limbs_base, _xlpm.exp, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{1;998}</v>
+      </c>
+      <c r="D322" s="9" t="b">
+        <f>IF(ISERROR(UPow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(UPow_Tests[[#This Row],[expected]]) = ERROR.TYPE(UPow_Tests[[#This Row],[output]]),
+    UPow_Tests[[#This Row],[expected]] = UPow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E322" s="9" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A323" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="B323" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C323" s="9" t="str" cm="1">
+        <f t="array" ref="C323">_xlfn.LET(
+    _xlpm.bek, _xlfn.REGEXEXTRACT(UPow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.base, INDEX(_xlpm.bek,1,1),
+    _xlpm.exp, INDEX(_xlpm.bek,1,2),
+    _xlpm.k, --INDEX(_xlpm.bek,1,3),
+    _xlpm.limbs_base, --_xlfn.TEXTSPLIT(_xlpm.base,",",";"),
+    _xlpm.output, core_BigInt.UPow(_xlpm.limbs_base, _xlpm.exp, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{576;48;1}</v>
+      </c>
+      <c r="D323" s="9" t="b">
+        <f>IF(ISERROR(UPow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(UPow_Tests[[#This Row],[expected]]) = ERROR.TYPE(UPow_Tests[[#This Row],[output]]),
+    UPow_Tests[[#This Row],[expected]] = UPow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E323" s="9" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A324" s="2"/>
+      <c r="D324" t="b">
+        <f>AND(UPow_Tests[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" ht="15" collapsed="1" thickBot="1"/>
+    <row r="326" spans="1:5" ht="18.5">
+      <c r="A326" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="B326" s="5"/>
+      <c r="C326" s="5"/>
+      <c r="D326" s="5"/>
+      <c r="E326" s="5"/>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" t="s">
+        <v>110</v>
+      </c>
+      <c r="B327" t="s">
+        <v>35</v>
+      </c>
+      <c r="C327" t="s">
+        <v>36</v>
+      </c>
+      <c r="D327" t="s">
+        <v>48</v>
+      </c>
+      <c r="E327" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A328" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="B328" s="9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="C328" s="9" t="e" cm="1">
+        <f t="array" ref="C328">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab, 1, 1),
+    _xlpm.b, INDEX(_xlpm.ab, 1, 2),
+    BigInt.Pow(_xlpm.a, _xlpm.b)
+)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="D328" s="9" t="b">
+        <f>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
+    Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E328" s="9" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A329" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="B329" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C329" s="9" t="str" cm="1">
+        <f t="array" ref="C329">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab, 1, 1),
+    _xlpm.b, INDEX(_xlpm.ab, 1, 2),
+    BigInt.Pow(_xlpm.a, _xlpm.b)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="D329" s="9" t="b">
+        <f>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
+    Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E329" s="9" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A330" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="B330" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C330" s="9" t="str" cm="1">
+        <f t="array" ref="C330">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab, 1, 1),
+    _xlpm.b, INDEX(_xlpm.ab, 1, 2),
+    BigInt.Pow(_xlpm.a, _xlpm.b)
+)</f>
+        <v>1</v>
+      </c>
+      <c r="D330" s="9" t="b">
+        <f>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
+    Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E330" s="9" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A331" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="B331" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C331" s="9" t="str" cm="1">
+        <f t="array" ref="C331">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab, 1, 1),
+    _xlpm.b, INDEX(_xlpm.ab, 1, 2),
+    BigInt.Pow(_xlpm.a, _xlpm.b)
+)</f>
+        <v>1</v>
+      </c>
+      <c r="D331" s="9" t="b">
+        <f>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
+    Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E331" s="9" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A332" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="B332" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C332" s="9" t="str" cm="1">
+        <f t="array" ref="C332">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab, 1, 1),
+    _xlpm.b, INDEX(_xlpm.ab, 1, 2),
+    BigInt.Pow(_xlpm.a, _xlpm.b)
+)</f>
+        <v>-1</v>
+      </c>
+      <c r="D332" s="9" t="b">
+        <f>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
+    Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E332" s="9" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A333" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="B333" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C333" s="9" t="str" cm="1">
+        <f t="array" ref="C333">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab, 1, 1),
+    _xlpm.b, INDEX(_xlpm.ab, 1, 2),
+    BigInt.Pow(_xlpm.a, _xlpm.b)
+)</f>
+        <v>1</v>
+      </c>
+      <c r="D333" s="9" t="b">
+        <f>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
+    Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E333" s="9" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A334" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="B334" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="C334" s="20" t="str" cm="1">
+        <f t="array" ref="C334">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab, 1, 1),
+    _xlpm.b, INDEX(_xlpm.ab, 1, 2),
+    BigInt.Pow(_xlpm.a, _xlpm.b)
+)</f>
+        <v>2</v>
+      </c>
+      <c r="D334" s="20" t="b">
+        <f>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
+    Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E334" s="9" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A335" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="B335" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="C335" s="9" t="str" cm="1">
+        <f t="array" ref="C335">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab, 1, 1),
+    _xlpm.b, INDEX(_xlpm.ab, 1, 2),
+    BigInt.Pow(_xlpm.a, _xlpm.b)
+)</f>
+        <v>1024</v>
+      </c>
+      <c r="D335" s="9" t="b">
+        <f>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
+    Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E335" s="9" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A336" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="B336" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="C336" s="9" t="str" cm="1">
+        <f t="array" ref="C336">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab, 1, 1),
+    _xlpm.b, INDEX(_xlpm.ab, 1, 2),
+    BigInt.Pow(_xlpm.a, _xlpm.b)
+)</f>
+        <v>-8</v>
+      </c>
+      <c r="D336" s="9" t="b">
+        <f>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
+    Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E336" s="9" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A337" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="B337" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="C337" s="9" t="str" cm="1">
+        <f t="array" ref="C337">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab, 1, 1),
+    _xlpm.b, INDEX(_xlpm.ab, 1, 2),
+    BigInt.Pow(_xlpm.a, _xlpm.b)
+)</f>
+        <v>16</v>
+      </c>
+      <c r="D337" s="9" t="b">
+        <f>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
+    Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E337" s="9" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A338" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="B338" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="C338" s="9" t="str" cm="1">
+        <f t="array" ref="C338">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab, 1, 1),
+    _xlpm.b, INDEX(_xlpm.ab, 1, 2),
+    BigInt.Pow(_xlpm.a, _xlpm.b)
+)</f>
+        <v>1267650600228229401496703205376</v>
+      </c>
+      <c r="D338" s="9" t="b">
+        <f>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
+    Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E338" s="9" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A339" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="B339" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C339" s="9" t="str" cm="1">
+        <f t="array" ref="C339">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab, 1, 1),
+    _xlpm.b, INDEX(_xlpm.ab, 1, 2),
+    BigInt.Pow(_xlpm.a, _xlpm.b)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="D339" s="9" t="b">
+        <f>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
+    Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E339" s="9" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A340" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="B340" s="9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="C340" s="9" t="e" cm="1">
+        <f t="array" ref="C340">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab, 1, 1),
+    _xlpm.b, INDEX(_xlpm.ab, 1, 2),
+    BigInt.Pow(_xlpm.a, _xlpm.b)
+)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="D340" s="9" t="b">
+        <f>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
+    Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E340" s="9" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" collapsed="1">
+      <c r="A341" s="2"/>
+      <c r="D341" t="b">
+        <f>AND(Pow_Tests[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" cm="1">
+        <f t="array" ref="A361:A362">LEN(B361:B362)</f>
+        <v>22</v>
+      </c>
+      <c r="B361" t="str" cm="1">
+        <f t="array" ref="B361">BigInt.Pow(B364, B365)</f>
+        <v>1176246293903439668001</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362">
+        <v>22</v>
+      </c>
+      <c r="B362" t="str" cm="1">
+        <f t="array" ref="B362">_xlfn._xlws.PY(0,0,B364,B365)</f>
+        <v>1176246293903439668001</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="B363" t="b">
+        <f>B361 = B362</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="B364">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="B365">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D8:D26 D150:D160 D265:D280 D284:D289">
-    <cfRule type="expression" dxfId="39" priority="61" stopIfTrue="1">
+  <conditionalFormatting sqref="D8:D26 D150:D160 D265:D280 D284:D289 D317:D324">
+    <cfRule type="expression" dxfId="46" priority="70" stopIfTrue="1">
       <formula>$D8</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="62">
+    <cfRule type="expression" dxfId="45" priority="71">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:D37 D86:D94 D118:D124">
-    <cfRule type="expression" dxfId="37" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="68" stopIfTrue="1">
       <formula>$D30</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="60">
+    <cfRule type="expression" dxfId="43" priority="69">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41:D46">
-    <cfRule type="expression" dxfId="35" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="64" stopIfTrue="1">
       <formula>$D41</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="56">
+    <cfRule type="expression" dxfId="41" priority="65">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:D60">
-    <cfRule type="expression" dxfId="33" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="54" stopIfTrue="1">
       <formula>$D50</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="46">
+    <cfRule type="expression" dxfId="39" priority="55">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D64:D71">
-    <cfRule type="expression" dxfId="31" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="62" stopIfTrue="1">
       <formula>$D64</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="54">
+    <cfRule type="expression" dxfId="37" priority="63">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75:D82">
-    <cfRule type="expression" dxfId="29" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="60" stopIfTrue="1">
       <formula>$D75</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="52">
+    <cfRule type="expression" dxfId="35" priority="61">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D98:D104">
-    <cfRule type="expression" dxfId="27" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="52" stopIfTrue="1">
       <formula>$D98</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="44">
+    <cfRule type="expression" dxfId="33" priority="53">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:D114">
-    <cfRule type="expression" dxfId="25" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="50" stopIfTrue="1">
       <formula>$D108</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="42">
+    <cfRule type="expression" dxfId="31" priority="51">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D128:D135">
-    <cfRule type="expression" dxfId="23" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="46" stopIfTrue="1">
       <formula>$D128</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="38">
+    <cfRule type="expression" dxfId="29" priority="47">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D139:D146">
-    <cfRule type="expression" dxfId="21" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="44" stopIfTrue="1">
       <formula>$D139</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="36">
+    <cfRule type="expression" dxfId="27" priority="45">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D164:D169">
-    <cfRule type="expression" dxfId="19" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="38" stopIfTrue="1">
       <formula>$D164</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="30">
+    <cfRule type="expression" dxfId="25" priority="39">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D173:D176">
-    <cfRule type="expression" dxfId="17" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="36" stopIfTrue="1">
       <formula>$D173</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="28">
+    <cfRule type="expression" dxfId="23" priority="37">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D180:D183">
-    <cfRule type="expression" dxfId="15" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="32" stopIfTrue="1">
       <formula>$D180</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="24">
+    <cfRule type="expression" dxfId="21" priority="33">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D187:D191">
-    <cfRule type="expression" dxfId="13" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="30" stopIfTrue="1">
       <formula>$D187</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="22">
+    <cfRule type="expression" dxfId="19" priority="31">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D195:D202">
-    <cfRule type="expression" dxfId="11" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="28" stopIfTrue="1">
       <formula>$D195</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="20">
+    <cfRule type="expression" dxfId="17" priority="29">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D206:D211">
-    <cfRule type="expression" dxfId="9" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="24" stopIfTrue="1">
       <formula>$D206</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="16">
+    <cfRule type="expression" dxfId="15" priority="25">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D215:D221">
-    <cfRule type="expression" dxfId="7" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="22" stopIfTrue="1">
       <formula>$D215</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="14">
+    <cfRule type="expression" dxfId="13" priority="23">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D225:D233">
-    <cfRule type="expression" dxfId="5" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="18" stopIfTrue="1">
       <formula>$D225</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="10">
+    <cfRule type="expression" dxfId="11" priority="19">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D237:D247">
-    <cfRule type="expression" dxfId="3" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="16" stopIfTrue="1">
       <formula>$D237</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="8">
+    <cfRule type="expression" dxfId="9" priority="17">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D251:D261">
-    <cfRule type="expression" dxfId="1" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="14" stopIfTrue="1">
       <formula>$D251</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="7" priority="15">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D293:D301">
+    <cfRule type="expression" dxfId="6" priority="8" stopIfTrue="1">
+      <formula>$D293</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="9">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D305:D313">
+    <cfRule type="expression" dxfId="4" priority="6" stopIfTrue="1">
+      <formula>$D305</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="7">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D328:D341">
+    <cfRule type="expression" dxfId="2" priority="4" stopIfTrue="1">
+      <formula>$D328</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B363">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="25">
+  <tableParts count="29">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -14975,6 +17816,10 @@
     <tablePart r:id="rId24"/>
     <tablePart r:id="rId25"/>
     <tablePart r:id="rId26"/>
+    <tablePart r:id="rId27"/>
+    <tablePart r:id="rId28"/>
+    <tablePart r:id="rId29"/>
+    <tablePart r:id="rId30"/>
   </tableParts>
 </worksheet>
 </file>
@@ -14997,17 +17842,17 @@
       <c r="A2" s="4"/>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="14" t="s">
+      <c r="A3" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="14" t="s">
+      <c r="A4" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="14" t="s">
+      <c r="A5" t="s">
         <v>448</v>
       </c>
     </row>
@@ -15018,7 +17863,7 @@
       <c r="A7" t="s">
         <v>441</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="14">
         <v>5.7905521136680698E-3</v>
       </c>
     </row>
@@ -15026,7 +17871,7 @@
       <c r="A8" t="s">
         <v>440</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="14">
         <v>-5.3705137962931797E-2</v>
       </c>
     </row>
@@ -15034,7 +17879,7 @@
       <c r="A9" t="s">
         <v>439</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="14">
         <v>-11.917287699337001</v>
       </c>
     </row>
@@ -15042,7 +17887,7 @@
       <c r="A10" t="s">
         <v>442</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="14">
         <f>B7 / -B8</f>
         <v>0.10782119427129687</v>
       </c>
@@ -15051,7 +17896,7 @@
       <c r="A11" t="s">
         <v>443</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="15">
         <f>B9 / -B8</f>
         <v>-221.90218946206815</v>
       </c>
@@ -15091,8 +17936,125 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF1F7BB-C380-482D-90F7-8A14B24EE993}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="42.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" thickBot="1">
+      <c r="A1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B1" t="s">
+        <v>456</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B2">
+        <v>349</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>461</v>
+      </c>
+      <c r="F2" s="17"/>
+    </row>
+    <row r="3" spans="1:6" ht="15" thickBot="1">
+      <c r="A3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1">
+      <c r="A4" t="s">
+        <v>451</v>
+      </c>
+      <c r="B4">
+        <v>249</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>452</v>
+      </c>
+      <c r="B5">
+        <v>129</v>
+      </c>
+      <c r="E5" t="str" cm="1">
+        <f t="array" ref="E5:F6">_xlfn.LET(
+    _xlpm.data, Data[],
+    _xlpm.all_names, Data[name],
+    _xlpm.search_terms, _xlfn.TEXTSPLIT(E2, " "),
+    _xlpm.scores, _xlfn.MAP(_xlpm.all_names, _xlfn.LAMBDA(_xlpm.name, SUM(--ISNUMBER(SEARCH(_xlpm.search_terms, _xlpm.name))))),
+    _xlpm.max_score, MAX(_xlpm.scores),
+    IF(_xlpm.max_score = 0, "None", _xlfn._xlws.FILTER(_xlpm.data, _xlpm.scores = MAX(_xlpm.scores)))
+)</f>
+        <v>Sony WH-1000XM5 Wireless Noise Canceling</v>
+      </c>
+      <c r="F5">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>453</v>
+      </c>
+      <c r="B6">
+        <v>179</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Sony WF-1000XM5 Wireless Earbuds</v>
+      </c>
+      <c r="F6">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>454</v>
+      </c>
+      <c r="B7">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>455</v>
+      </c>
+      <c r="B8">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAFwAbgAvAC8AIABCAGkAZwAgAEkAbgB0AGUAZwBlAHIAIABBAHIAaQB0AGgAbQBlAHQAaQBjACAATABpAGIAcgBhAHIAeQAgAC8ALwBcAG4ALwAvACAAIAAgACAAIAAgACAAdABlAHMAdABfAEIAaQBnAEkAbgB0ACAATQBvAGQAdQBsAGUAIAAgACAAIAAgACAAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIAAgAFAAcgBpAHYAYQB0AGUAIABUAGUAcwB0AGkAbgBnACAAQQBQAEkAIAAgACAAIAAgACAALwAvAFwAbgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4AXABuAEsAbgB1AHQAaABEAGkAdgBpAHMAaQBvAG4APQBMAEEATQBCAEQAQQAoAGEALAAgAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2ACgAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYQAsACAAawApACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABiACwAIABrACkALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAEQAUgBPAFAAKABwAGEAYwBrAGUAZAAsACAASQBOAEQARQBYACgAcABhAGMAawBlAGQALAAgADEALAAgADEAKQAgACsAIAAxACkALAAgAGsAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAgAD0AIABMAEEATQBCAEQAQQAoAGEALAAgAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgAoAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAGEALAAgAGsAKQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYgAsACAAawApACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABEAFIATwBQACgAcABhAGMAawBlAGQALAAgAEkATgBEAEUAWAAoAHAAYQBjAGsAZQBkACwAIAAxACwAIAAxACkAIAArACAAMQApACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAcwB0AHIAaQBuAGcAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAHMAdAByAGkAbgBnAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG0AbwBkAGUAIABcACIASwBOAFUAVABIAFwAIgAgAG8AcgAgAFwAIgBOAFIAXAAiAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGkAdABlAHIAcwAgAEkAbgBuAGUAcgAgAGwAbwBvAHAAIABjAG8AdQBuAHQAIAAoAHQAbwAgAGQAZQBmAGUAYQB0ACAAYwBoAHUAbgBrAHkAIABjAGwAbwBjAGsAIAByAGUAcwBvAGwAdQB0AGkAbwBuACkAXABuACAAKgAgAEAAcABhAHIAYQBtACAAcgBlAHAAZQBhAHQAcwAgAE8AdQB0AGUAcgAgAGwAbwBvAHAAIABjAG8AdQBuAHQAIAAoAHQAbwAgAGQAZQBmAGUAYQB0ACAATwBTAC8ARwBhAHIAYgBhAGcAZQAgAEMAbwBsAGwAZQBjAHQAaQBvAG4AIABuAG8AaQBzAGUAKQBcAG4AIAAqAC8AXABuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACAAPQAgAEwAQQBNAEIARABBACgAYQAsACAAYgAsACAAbQBvAGQAZQAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAE0AYQBwACAAdABoAGUAIABvAHUAdABlAHIAIAByAGUAcABlAGEAdABzACAAbABvAG8AcABcAG4AIAAgACAAIAAgACAAIAAgAGIAYQB0AGMAaABfAHQAaQBtAGUAcwAsACAATQBBAFAAKABTAEUAUQBVAEUATgBDAEUAKAByAGUAcABlAGEAdABzACkALAAgAEwAQQBNAEIARABBACgAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdAAsACAATgBPAFcAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATQBhAHAAIAB0AGgAZQAgAGkAbgBuAGUAcgAgAGUAeABlAGMAdQB0AGkAbwBuACAAbABvAG8AcABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAHUAbgAsACAASQBGACgAbQBvAGQAZQAgAD0AIABcACIASwBOAFUAVABIAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBQACgAUwBFAFEAVQBFAE4AQwBFACgAaQB0AGUAcgBzACkALAAgAEwAQQBNAEIARABBACgAaQAsACAASwBuAHUAdABoAEQAaQB2AGkAcwBpAG8AbgAoAGEALAAgAGIAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFAAKABTAEUAUQBVAEUATgBDAEUAKABpAHQAZQByAHMAKQAsACAATABBAE0AQgBEAEEAKABpACwAIABOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAoAGEALAAgAGIAKQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEYAbwByAGMAZQAgAGUAdgBhAGwAdQBhAHQAaQBvAG4AIABiAGUAZgBvAHIAZQAgAHAAdQBsAGwAaQBuAGcAIABzAHQAbwBwACAAdABpAG0AZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAbwBwACwAIABOAE8AVwAoACkAIAArACAAKAAwACAAKgAgAEwARQBOACgASQBOAEQARQBYACgAcgB1AG4ALAAgADEALAAgADEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABUAG8AdABhAGwAIABiAGEAdABjAGgAIAB0AGkAbQBlACAAaQBuACAAbQBpAGwAbABpAHMAZQBjAG8AbgBkAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABzAHQAbwBwACAALQAgAHMAdABhAHIAdAApACAAKgAgADgANgA0ADAAMAAwADAAMABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAdABoAGUAIABjAGwAZQBhAG4AZQBzAHQAIAByAHUAbgAgAGEAbgBkACAAYQB2AGUAcgBhAGcAZQAgAGkAdAAgAGQAbwB3AG4AIAB0AG8AIABhACAAcwBpAG4AZwBsAGUAIABlAHgAZQBjAHUAdABpAG8AbgAgAHQAaQBtAGUAXABuACAAIAAgACAAIAAgACAAIABNAEkATgAoAGIAYQB0AGMAaABfAHQAaQBtAGUAcwApACAALwAgAGkAdABlAHIAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAARQB4AGUAYwB1AHQAZQBzACAAYQAgAHMAdAByAGkAYwB0AGwAeQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABiAGUAbgBjAGgAbQBhAHIAawAgAHMAdQBpAHQAZQAgAHQAbwAgAGEAdgBvAGkAZAAgAG0AdQBsAHQAaQAtAHQAaAByAGUAYQBkAGkAbgBnACAAYwBvAG4AdABhAG0AaQBuAGEAdABpAG8AbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHQAZQBzAHQAXwBjAGEAcwBlAHMAIABBAG4AIABOACAAeAAgADIAIABhAHIAcgBhAHkAIABvAGYAIAB0AGUAcwB0ACAAbABlAG4AZwB0AGgAcwA6ACAAWwBMAGUAbgBnAHQAaABfAEEALAAgAEwAZQBuAGcAdABoAF8AQgBdAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGkAdABlAHIAcwAgAE4AdQBtAGIAZQByACAAbwBmACAAaQB0AGUAcgBhAHQAaQBvAG4AcwAgAHAAZQByACAAYgBlAG4AYwBoAG0AYQByAGsAIAB0AG8AIABzAG0AbwBvAHQAaAAgAE4ATwBXACgAKQAgAHIAZQBzAG8AbAB1AHQAaQBvAG4ALgBcAG4AIAAqAC8AXABuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBDAG8AbQBwAGEAcgBpAHMAbwBuACAAPQAgAEwAQQBNAEIARABBACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwB0AGUAcwB0AHMALAAgAFIATwBXAFMAKAB0AGUAcwB0AF8AYwBhAHMAZQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAASQBuAGkAdABpAGEAbAAgAHMAdABhAHQAZQA6ACAARABhAHQAYQAgAGgAZQBhAGQAZQByAHMAIABmAG8AcgAgAEMAUwBWACAAZQB4AHAAbwByAHQAXABuACAAIAAgACAAIAAgACAAIABpAG4AaQB0AGkAYQBsACwAIAB7AFwAIgBMAGUAbgBfAEEAXAAiACwAIABcACIATABlAG4AXwBCAFwAIgAsACAAXAAiAEsAbgB1AHQAaABfAG0AcwBcACIALAAgAFwAIgBOAFIAXwBtAHMAXAAiAH0ALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsACwAIABTAEUAUQBVAEUATgBDAEUAKABuAF8AdABlAHMAdABzACkALAAgAEwAQQBNAEIARABBACgAYQBjAGMALAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAEkATgBEAEUAWAAoAHQAZQBzAHQAXwBjAGEAcwBlAHMALAAgAGkALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAASQBOAEQARQBYACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBrAGkAcAAgAEQAaQB2AGkAcwBvAHIAIAA+ACAARABpAHYAaQBkAGUAbgBkABQgaQB0ACcAcwAgAG4AZQB2AGUAcgAgAGEAbgAgAGkAbgB0AGUAZwBlAHIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbABlAG4AXwBiACAAPgAgAGwAZQBuAF8AYQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAYwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARwBlAG4AZQByAGEAdABlACAAZQB4AGEAYwB0AC0AbABlAG4AZwB0AGgAIAB0AGUAcwB0ACAAcwB0AHIAaQBuAGcAcwAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AHIAXwBhACwAIABSAEUAUABUACgAXAAiADkAXAAiACwAIABsAGUAbgBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAcgBfAGIALAAgAEkARgAoAGwAZQBuAF8AYgAgAD0AIAAxACwAIABcACIANwBcACIALAAgAFwAIgA3AFwAIgAgACYAIABSAEUAUABUACgAXAAiADMAXAAiACwAIABsAGUAbgBfAGIAIAAtACAAMQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeABlAGMAdQB0AGUAIABiAGUAbgBjAGgAbQBhAHIAawBzACAAcwB0AHIAaQBjAHQAbAB5ACAAbwBuAGUAIABhAGYAdABlAHIAIAB0AGgAZQAgAG8AdABoAGUAcgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABpAG0AZQBfAGsALAAgAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACgAcwB0AHIAXwBhACwAIABzAHQAcgBfAGIALAAgAFwAIgBLAE4AVQBUAEgAXAAiACwAIABpAHQAZQByAHMALAAgAHIAZQBwAGUAYQB0AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGkAbQBlAF8AbgByACwAIABEAGkAdgBpAHMAaQBvAG4AQQBsAGcAbwByAGkAdABoAG0AcwAoAHMAdAByAF8AYQAsACAAcwB0AHIAXwBiACwAIABcACIATgBSAFwAIgAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAcABwAGUAbgBkACAAdABoAGUAIAByAGUAcwB1AGwAdABzAC4AIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAGEAbABsAG8AYwBhAHQAaQBvAG4AIABkAGUAbABhAHkAIABvAGMAYwB1AHIAcwAgAGgAZQByAGUALAAgAHMAYQBmAGUAbAB5ACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAdABpAG0AZQBkACAAdwBpAG4AZABvAHcALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABhAGMAYwAsACAASABTAFQAQQBDAEsAKABsAGUAbgBfAGEALAAgAGwAZQBuAF8AYgAsACAAdABpAG0AZQBfAGsALAAgAHQAaQBtAGUAXwBuAHIAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgADIALQBjAG8AbAB1AG0AbgAgAGEAcgByAGEAeQAgAG8AZgAgAGUAdgBlAHIAeQAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgAgAG8AZgAgAGwAZQBuAGcAdABoAHMAXABuAEQAaQB2AGkAcwBpAG8AbgBCAGUAbgBjAGgAbQBhAHIAawBDAGEAcwBlAHMAIAA9ACAATABBAE0AQgBEAEEAKABzAHQAYQByAHQAXwBsAGUAbgAsACAAbQBhAHgAXwBsAGUAbgAsACAAcwB0AGUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQAsACAAUwBFAFEAVQBFAE4AQwBFACgAKABtAGEAeABfAGwAZQBuACAALQAgAHMAdABhAHIAdABfAGwAZQBuACkAIAAvACAAcwB0AGUAcAAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBsAGUAbgAsACAAcwB0AGUAcAApACwAXABuACAAIAAgACAAIAAgACAAIABuACwAIABSAE8AVwBTACgAcwBlAHEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDACsAKwAgAHMAdAB5AGwAZQAgAEMAYQByAHQAZQBzAGkAYQBuACAASgBvAGkAbgBcAG4AIAAgACAAIAAgACAAIAAgAGMAbwBsAF8AYQAsACAAVABPAEMATwBMACgASQBGACgAUwBFAFEAVQBFAE4AQwBFACgAMQAsACAAbgApACwAIABzAGUAcQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAGMAbwBsAF8AYgAsACAAVABPAEMATwBMACgASQBGACgAUwBFAFEAVQBFAE4AQwBFACgAbgAsACAAMQApACwAIABUAE8AUgBPAFcAKABzAGUAcQApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAGMAbwBsAF8AYQAsACAAYwBvAGwAXwBiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAvACAARwBlAG4AZQByAGEAdABlAHMAIABhACAAQwBhAHIAdABlAHMAaQBhAG4AIABnAHIAaQBkACAAZgByAG8AbQAgAHQAdwBvACAAaQBuAGQAZQBwAGUAbgBkAGUAbgB0ACAAcwBlAHEAdQBlAG4AYwBlAHMAXABuAEEAcwB5AG0AbQBlAHQAcgBpAGMAQQBCAEcAcgBpAGQAIAA9ACAATABBAE0AQgBEAEEAKABzAHQAYQByAHQAXwBhACwAIABtAGEAeABfAGEALAAgAHMAdABlAHAAXwBhACwAIABzAHQAYQByAHQAXwBiACwAIABtAGEAeABfAGIALAAgAHMAdABlAHAAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQBxAF8AYQAsACAAUwBFAFEAVQBFAE4AQwBFACgAKABtAGEAeABfAGEAIAAtACAAcwB0AGEAcgB0AF8AYQApACAALwAgAHMAdABlAHAAXwBhACAAKwAgADEALAAgADEALAAgAHMAdABhAHIAdABfAGEALAAgAHMAdABlAHAAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQBxAF8AYgAsACAAUwBFAFEAVQBFAE4AQwBFACgAKABtAGEAeABfAGIAIAAtACAAcwB0AGEAcgB0AF8AYgApACAALwAgAHMAdABlAHAAXwBiACAAKwAgADEALAAgADEALAAgAHMAdABhAHIAdABfAGIALAAgAHMAdABlAHAAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAbgBfAGEALAAgAFIATwBXAFMAKABzAGUAcQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBfAGIALAAgAFIATwBXAFMAKABzAGUAcQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABPAHIAdABoAG8AZwBvAG4AYQBsACAAYgByAG8AYQBkAGMAYQBzAHQAIAB1AHMAaQBuAGcAIABpAG4AZABlAHAAZQBuAGQAZQBuAHQAIABkAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgACAAIAAgACAAYwBvAGwAXwBhACwAIABUAE8AQwBPAEwAKABJAEYAKABTAEUAUQBVAEUATgBDAEUAKAAxACwAIABuAF8AYgApACwAIABzAGUAcQBfAGEAKQApACwAXABuACAAIAAgACAAIAAgACAAIABjAG8AbABfAGIALAAgAFQATwBDAE8ATAAoAEkARgAoAFMARQBRAFUARQBOAEMARQAoAG4AXwBhACkALAAgAFQATwBSAE8AVwAoAHMAZQBxAF8AYgApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAGMAbwBsAF8AYQAsACAAYwBvAGwAXwBiACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AYwBvAHIAZQBfAEIAaQBnAEkAbgB0ACIALAAiAHQAZQB4AHQAIgA6ACIALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8AXABuAC8ALwAgAEIAaQBnACAASQBuAHQAZQBnAGUAcgAgAEEAcgBpAHQAaABtAGUAdABpAGMAIABMAGkAYgByAGEAcgB5ACAALwAvAFwAbgAvAC8AIAAgACAAIAAgACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0ACAATQBvAGQAdQBsAGUAIAAgACAAIAAgACAAIAAgAC8ALwBcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACAAUAByAGkAdgBhAHQAZQAgAEEAUABJACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AXABuAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABDAG8AbQBwAHUAdABlAHMAIAB0AGgAZQAgAG0AYQB4AGkAbQB1AG0AIABzAGEAZgBlACAAYgBhAHMAZQAtADEAMAAgAGwAaQBtAGIAIABzAGkAegBlACAAKABrACkAIAB0AG8AIABhAHYAbwBpAGQAIABJAEUARQBFAC0ANwA1ADQAIABwAHIAZQBjAGkAcwBpAG8AbgAgAGwAbwBzAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABvAHAAZQByAGEAdABpAG8AbgA6ACAAXAAiAEEARABEAFwAIgAgAG8AcgAgAFwAIgBNAFUATABcACIALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG0AYQB4AF8AaQB0AGUAbQBzAF0AIABBAEQARAA6ACAAbgB1AG0AYgBlAHIAIABvAGYAIAByAG8AdwBzAC4AIABNAFUATAA6ACAAcwBoAG8AcgB0AGUAcwB0ACAAcwB0AHIAaQBuAGcAIABkAGkAZwBpAHQAcwAgAGMAbwB1AG4AdAAuAFwAbgAgACoALwBcAG4AUwBhAGYAZQBLACAAPQAgAEwAQQBNAEIARABBACgAbwBwAGUAcgBhAHQAaQBvAG4ALAAgAFsAbQBhAHgAXwBpAHQAZQBtAHMAXQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABpAHQAZQBtAHMALAAgAEkARgAoAE8AUgAoAG0AYQB4AF8AaQB0AGUAbQBzACAAPQAgAFwAIgBcACIALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAbQBhAHgAXwBpAHQAZQBtAHMAKQApACwAIAAyACwAIAAgAE0AQQBYACgAMgAsACAAbQBhAHgAXwBpAHQAZQBtAHMAKQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAUwBXAEkAVABDAEgAKABvAHAAZQByAGEAdABpAG8AbgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBEAEQAXAAiACwAIAAxADUAIAAtACAATABFAE4AKABpAHQAZQBtAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIATQBVAEwAXAAiACwAIABJAE4AVAAoACgAMQA1ACAALQAgAEwARQBOACgAaQB0AGUAbQBzACkAKQAgAC8AIAAyACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQASQBWAFwAIgAsACAANwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAE4AQQBNAEUAPwBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AaQBmAGkAZQBkACAAUwBwAGwAaQB0AHQAZQByAC4AIABTAHAAbABpAHQAcwAgAGIAbwB0AGgAIABzAGMAYQBsAGEAcgBzACAAYQBuAGQAIABhAHIAcgBhAHkAcwAgAGkAbgB0AG8AIABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuACAAbABpAG0AYgBzAC4AXABuACAAKgAgAFUAcwBlAHMAIABNAEEAWAAoACkAIAB0AG8AIABnAHUAYQByAGEAbgB0AGUAZQAgAHMAYwBhAGwAYQByACAAaQBuAHAAdQB0AHMAIAB0AG8AIAB0AGgAZQAgAFMARQBRAFUARQBOAEMARQAgAGUAbgBnAGkAbgBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABzACAAVABoAGUAIABzAHQAcgBpAG4AZwAgAG8AcgAgAGEAcgByAGEAeQAgAG8AZgAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFMAcABsAGkAdAAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAcwAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABiAGkAZwBfAGkAbgB0AF8AcgBvAHcALAAgAFQATwBSAE8AVwAoAGIAaQBnAF8AaQBuAHQAcwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBnAHQAaABzACwAIABMAEUATgAoAGIAaQBnAF8AaQBuAHQAXwByAG8AdwApACwAXABuACAAIAAgACAAIAAgACAAIABtAGEAeABfAGwAZQBuACwAIABNAEEAWAAoAGwAZQBuAGcAdABoAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBsAGUAbgAsACAAUgBPAFUATgBEAFUAUAAoAG0AYQB4AF8AbABlAG4AIAAvACAAawAsACAAMAApACAAKgAgAGsALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAZABlAGQALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAHAAYQBkAF8AbABlAG4AIAAtACAAbABlAG4AZwB0AGgAcwApACAAJgAgAGIAaQBnAF8AaQBuAHQAXwByAG8AdwAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALAAgAFMARQBRAFUARQBOAEMARQAoAHAAYQBkAF8AbABlAG4AIAAvACAAawAsACAAMQAsACAAcABhAGQAXwBsAGUAbgAgAC0AIABrACAAKwAgADEALAAgAC0AawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC0ALQBNAEkARAAoAHAAYQBkAGQAZQBkACwAIABzAHQAYQByAHQAcwAsACAAawApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAQwBvAG4AYwBhAHQAZQBuAGEAdABlAHMAIABhAG4AIABhAHIAcgBhAHkAIABvAGYAIABuAHUAbQBlAHIAaQBjACAAbABpAG0AYgBzACAAaQBuAHQAbwAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnACwAIAB6AGUAcgBvAC0AcABhAGQAZABpAG4AZwAgAGEAbABsACAAYgB1AHQAIAB0AGgAZQAgAGYAaQByAHMAdAAgAGwAaQBtAGIALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAIABUAGgAZQAgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAG4AdQBtAGUAcgBpAGMAIABsAGkAbQBiAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABsAGkAbQBiACAAcwBpAHoAZQAgAHUAcwBlAGQAIABkAHUAcgBpAG4AZwAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAuAFwAbgAgACoALwBcAG4ATQBlAHIAZwBlACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AdQBtAF8AbABpAG0AYgBzACwAIABSAE8AVwBTACgAbABpAG0AYgBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQB2AF8AbABpAG0AYgBzACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAbABpAG0AYgBzACwAIABTAEUAUQBVAEUATgBDAEUAKABuAHUAbQBfAGwAaQBtAGIAcwAsACAAMQAsACAAbgB1AG0AXwBsAGkAbQBiAHMALAAgAC0AMQApACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AdQBtAF8AbABpAG0AYgBzACAAPQAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHYAXwBsAGkAbQBiAHMAIAAmACAAXAAiAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATgBDAEEAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAcgBlAHYAXwBsAGkAbQBiAHMALAAgADEAKQAgACYAIABcACIAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEUAWABUACgARABSAE8AUAAoAHIAZQB2AF8AbABpAG0AYgBzACwAIAAxACkALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAGsAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAUgBlAHMAbwBsAHYAZQBzACAAYwBhAHIAcgBpAGUAcwAgAHIAaQBnAGgAdAAtAHQAbwAtAGwAZQBmAHQAIABhAGMAcgBvAHMAcwAgAGEAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkAIABvAGYAIABiAGEAcwBlAC0AMQAwAF4AawAgAGwAaQBtAGIAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwAgAFQAaABlACAAYQByAHIAYQB5ACAAbwBmACAAbgB1AG0AZQByAGkAYwAgAGwAaQBtAGIAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGwAaQBtAGIAIABzAGkAegBlAC4AXABuACAAKgAvAFwAbgBDAGEAcgByAHkAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwApACwAXABuACAAIAAgACAAIAAgACAAIABiAGEAcwBlACwAIAAxADAAXgBrACwAXABuACAAIAAgACAAIAAgACAAIABzAGMAYQBuAG4AZQBkACwAIABTAEMAQQBOACgAMAAsACAAbABpAG0AYgBzACwAIABMAEEATQBCAEQAQQAoAGEAYwBjACwAIAB2AGEAbAAsACAAdgBhAGwAIAArACAASQBOAFQAKABhAGMAYwAgAC8AIABiAGEAcwBlACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAByAGUAbQBhAGkAbgBkAGUAcgBzACwAIABNAE8ARAAoAHMAYwBhAG4AbgBlAGQALAAgAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AYwBhAHIAcgB5ACwAIABJAE4AVAAoAEkATgBEAEUAWAAoAHMAYwBhAG4AbgBlAGQALAAgAG4ALAAgADEAKQAgAC8AIABiAGEAcwBlACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABmAGkAbgBhAGwAXwBjAGEAcgByAHkAIAA+ACAAMAAsACAAVgBTAFQAQQBDAEsAKAByAGUAbQBhAGkAbgBkAGUAcgBzACwAIABmAGkAbgBhAGwAXwBjAGEAcgByAHkAKQAsACAAcgBlAG0AYQBpAG4AZABlAHIAcwApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAC0ALQAtACAAVQBuAHMAaQBnAG4AZQBkACAASwBlAHIAbgBlAGwAcwAgAC0ALQAtACAAXABcAFwAXABcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAVQBuAHMAaQBnAG4AZQBkACAAYwBvAG0AcABhAHIAaQBzAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAMQAgACgAYQAgAD4AIABiACkALAAgAC0AMQAgACgAYQAgADwAIABiACkALAAgAG8AcgAgADAAIAAoAGEAIAA9ACAAYgApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAIABUAGgAZQAgAHMAZQBjAG8AbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoALwBcAG4AVQBDAG8AbQBwAGEAcgBlACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAeABfAHIAbwB3AHMALAAgAE0AQQBYACgAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEAKQAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAZABfAGEALAAgAEUAWABQAEEATgBEACgAbABpAG0AYgBzAF8AYQAsACAAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAYQBkAF8AYgAsACAARQBYAFAAQQBOAEQAKABsAGkAbQBiAHMAXwBiACwAIABtAGEAeABfAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABkAGkAZgBmACwAIABwAGEAZABfAGEAIAAtACAAcABhAGQAXwBiACwAXABuACAAIAAgACAAIAAgACAAIABtAHMAZABfAGkAZAB4ACwAIABYAE0AQQBUAEMASAAoAFQAUgBVAEUALAAgAGQAaQBmAGYAIAA8AD4AIAAwACwAIAAwACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATgBBACgAbQBzAGQAXwBpAGQAeAApACwAIAAwACwAIABTAEkARwBOACgASQBOAEQARQBYACgAZABpAGYAZgAsACAAbQBzAGQAXwBpAGQAeAAsACAAMQApACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAGEAZABkAGkAdABpAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFUAQQBkAGQAIAA9ACAATABBAE0AQgBEAEEAKABhACwAIABiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AcgBvAHcAcwAsACAATQBBAFgAKABSAE8AVwBTACgAYQApACwAIABSAE8AVwBTACgAYgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAYQBkAF8AYQAsACAARQBYAFAAQQBOAEQAKABhACwAIABtAGEAeABfAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBiACwAIABFAFgAUABBAE4ARAAoAGIALAAgAG0AYQB4AF8AcgBvAHcAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHAAYQBkAF8AYQAgACsAIABwAGEAZABfAGIALAAgAGsAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAHMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABBAHMAcwB1AG0AZQBzACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAgAEEAIAA+AD0AIABCAC4AIABSAGUAcwBvAGwAdgBlAHMAIABiAG8AcgByAG8AdwBzACAAdABvAHAALQB0AG8ALQBiAG8AdAB0AG8AbQAgAGEAbgBkACAAdAByAGkAbQBzACAAdAByAGEAaQBsAGkAbgBnACAAegBlAHIAbwBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAbQBpAG4AdQBlAG4AZAAgAGwAaQBtAGIAIABhAHIAcgBhAHkAIAAoAG0AdQBzAHQAIABiAGUAIAA+AD0AIABsAGkAbQBiAHMAXwBiACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABzAHUAYgB0AHIAYQBoAGUAbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AVQBTAHUAYgAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwByAG8AdwBzACwAIABNAEEAWAAoAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBhACwAIABFAFgAUABBAE4ARAAoAGwAaQBtAGIAcwBfAGEALAAgAG0AYQB4AF8AcgBvAHcAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAZABfAGIALAAgAEUAWABQAEEATgBEACgAbABpAG0AYgBzAF8AYgAsACAAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAZABpAGYAZgAsACAAcABhAGQAXwBhACAALQAgAHAAYQBkAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBlAHMAbwBsAHYAZQBkACwAIABDAGEAcgByAHkAKABkAGkAZgBmACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAbQBzAGQAXwBpAGQAeAAsACAAWABNAEEAVABDAEgAKABUAFIAVQBFACwAIAByAGUAcwBvAGwAdgBlAGQAIAA8AD4AIAAwACwAIAAwACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATgBBACgAbQBzAGQAXwBpAGQAeAApACwAIAB7ADAAfQAsACAAVABBAEsARQAoAHIAZQBzAG8AbAB2AGUAZAAsACAAbQBzAGQAXwBpAGQAeAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABWAGUAYwB0AG8AcgBpAHoAZQBkACAAbQBhAHQAcgBpAHgAIABzAHUAbQAgAG8AZgAgAHUAbgBzAGkAZwBuAGUAZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHUAYgBpAGcAXwBpAG4AdAAgAEgAbwByAGkAegBvAG4AdABhAGwAIABhAHIAcgBhAHkAIAAoADEAeABOACkAIABvAGYAIABuAG8AcgBtAGEAbABpAHoAZQBkACAAbQBhAGcAbgBpAHQAdQBkAGUAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAdQBuAGkAZgBpAGUAZAAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AVQBNAGEAdAByAGkAeABTAHUAbQAgAD0AIABMAEEATQBCAEQAQQAoAHUAYgBpAGcAXwBpAG4AdABzACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAGcAcgBpAGQALAAgAFMAcABsAGkAdAAoAHUAYgBpAGcAXwBpAG4AdABzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAYQB3AF8AbABpAG0AYgBzACwAIABCAFkAUgBPAFcAKABnAHIAaQBkACwAIABTAFUATQApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHIAYQB3AF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABSAG8AdQB0AGUAcwAgAGEAZABkAGkAdABpAG8AbgAvAHMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAGIAYQBzAGUAZAAgAG8AbgAgAHMAaQBnAG4AcwAgAGEAbgBkACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAuAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAYQAgAHQAdQBwAGwAZQAgAGEAcgByAGEAeQA6ACAAVgBTAFQAQQBDAEsAKABsAGkAbQBiAHMALAAgAGYAaQBuAGEAbABfAHMAaQBnAG4AKQAgAHcAaABlAHIAZQAgAHQAaABlACAAZgBpAG4AYQBsACAAcgBvAHcAIABpAHMAIAB0AGgAZQAgAHMAYwBhAGwAYQByACAAcwBpAGcAbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAcwBlAGMAbwBuAGQAIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHMAaQBnAG4AXwBhACAAVABoAGUAIABzAGkAZwBuACAAbwBmACAAdABoAGUAIABmAGkAcgBzAHQAIABhAHIAcgBhAHkAIAAoADEALAAgAC0AMQAsACAAMAApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAcwBpAGcAbgBfAGIAIABUAGgAZQAgAHMAaQBnAG4AIABvAGYAIAB0AGgAZQAgAHMAZQBjAG8AbgBkACAAYQByAHIAYQB5ACAAKAAxACwAIAAtADEALAAgADAAKQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AQQBkAGQAUwB1AGIAUgBvAHUAdABlAHIAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABzAGkAZwBuAF8AYQAsACAAcwBpAGcAbgBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AcwBhAG0AZQBfAHMAaQBnAG4ALAAgAHMAaQBnAG4AXwBhACAAPQAgAHMAaQBnAG4AXwBiACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGkAcwBfAHMAYQBtAGUAXwBzAGkAZwBuACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAZABkAGkAdABpAG8AbgA6ACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAgAGMAbwBtAGIAaQBuAGUALAAgAHMAaQBnAG4AIAByAGUAbQBhAGkAbgBzACAAdABoAGUAIABzAGEAbQBlAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVQBBAGQAZAAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsACAAcwBpAGcAbgBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwB1AGIAdAByAGEAYwB0AGkAbwBuADoAIABlAHYAYQBsAHUAYQB0AGUAIABtAGEAZwBuAGkAdAB1AGQAZQBzACAAdABvACAAcwBhAHQAaQBzAGYAeQAgAFUAUwB1AGIAIAAoAEEAIAA+AD0AIABCACkAIABwAHIAZQBjAG8AbgBkAGkAdABpAG8AbgAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcAAsACAAVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFQAbwB0AGEAbAAgAGMAYQBuAGMAZQBsAGwAYQB0AGkAbwBuADoAIAByAGUAdAB1AHIAbgAgAHsAMAB9ACAAbABpAG0AYgAgAGEAbgBkACAAMAAgAHMAaQBnAG4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAMAA7ADAAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAGEAZwBfAGMAbwBtAHAAIAA+ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABBACAAaQBzACAAbABhAHIAZwBlAHIAOgAgAHMAaQBnAG4AIABiAGUAbABvAG4AZwBzACAAdABvACAAQQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFUAUwB1AGIAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALAAgAHMAaQBnAG4AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEIAIABpAHMAIABsAGEAcgBnAGUAcgA6ACAAcgBvAHUAdABlACAAQgAgAGYAaQByAHMAdAAsACAAcwBpAGcAbgAgAGIAZQBsAG8AbgBnAHMAIAB0AG8AIABCAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVQBTAHUAYgAoAGwAaQBtAGIAcwBfAGIALAAgAGwAaQBtAGIAcwBfAGEALAAgAGsAKQAsACAAcwBpAGcAbgBfAGIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AcwBpAGcAbgBlAGQAIABtAHUAbAB0AGkAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIAB0AHcAbwAgAEwAaQB0AHQAbABlAC0ARQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5AHMALgBcAG4AIAAqACAAVQB0AGkAbABpAHoAZQBzACAAYQAgADEARAAgAEQAaQBzAGMAcgBlAHQAZQAgAEMAbwBuAHYAbwBsAHUAdABpAG8AbgAgACgAQwBhAHUAYwBoAHkAIABQAHIAbwBkAHUAYwB0ACkAIABhAHIAcgBhAHkALQBzAGwAaQBjAGkAbgBnACAAcwB0AHIAYQB0AGUAZwB5AC4AXABuACAAKgAgAFoAZQByAG8AIABkAHkAbgBhAG0AaQBjACAAbQBlAG0AbwByAHkAIAByAGUAYQBsAGwAbwBjAGEAdABpAG8AbgAuACAAJABPACgATgArAE0AKQAkACAAbQBlAG0AbwByAHkAIABmAG8AbwB0AHAAcgBpAG4AdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAG0AdQBsAHQAaQBwAGwAaQBjAGEAbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAIABUAGgAZQAgAG0AdQBsAHQAaQBwAGwAaQBlAHIAIABsAGkAbQBiACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBVAE0AdQBsACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwByAG8AdwBzACwAIABsAGUAbgBfAGEAIAArACAAbABlAG4AXwBiACAALQAgADEALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAATABvAG8AcAAgAHAAdQByAGUAbAB5ACAAbwB2AGUAcgAgAHQAaABlACAAbABlAG4AZwB0AGgAIABvAGYAIAB0AGgAZQAgAGYAaQBuAGEAbAAgAG8AdQB0AHAAdQB0ACAAYQByAHIAYQB5AFwAbgAgACAAIAAgACAAIAAgACAAcgBhAHcAXwBsAGkAbQBiAHMALAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIABMAEEATQBCAEQAQQAoAHIALAAgAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAbABjAHUAbABhAHQAZQAgAHQAaABlACAAdgBhAGwAaQBkACAAbwB2AGUAcgBsAGEAcABwAGkAbgBnACAAdwBpAG4AZABvAHcAIABvAGYAIABpAG4AZABpAGMAZQBzACAAZgBvAHIAIAB0AGgAaQBzACAAbQBhAGcAbgBpAHQAdQBkAGUAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AF8AaQAsACAATQBBAFgAKAAxACwAIAByACAALQAgAGwAZQBuAF8AYgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAG4AZABfAGkALAAgAE0ASQBOACgAcgAsACAAbABlAG4AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AdQBuAHQALAAgAGUAbgBkAF8AaQAgAC0AIABzAHQAYQByAHQAXwBpACAAKwAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGUAcQB1AGUAbgBjAGUAIABpACAAYwBvAHUAbgB0AHMAIABVAFAALgAgAFMAZQBxAHUAZQBuAGMAZQAgAGoAIABjAG8AdQBuAHQAcwAgAEQATwBXAE4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGkALAAgAFMARQBRAFUARQBOAEMARQAoAGMAbwB1AG4AdAAsACAAMQAsACAAcwB0AGEAcgB0AF8AaQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBlAHEAXwBqACwAIABTAEUAUQBVAEUATgBDAEUAKABjAG8AdQBuAHQALAAgADEALAAgAHIAIAAtACAAcwB0AGEAcgB0AF8AaQAgACsAIAAxACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAbABpAGMAZQAgAHQAaABlACAAZQB4AGEAYwB0ACAAaQBuAHQAZQByAHMAZQBjAHQAaQBuAGcAIABsAGkAbQBiAHMALAAgAG0AdQBsAHQAaQBwAGwAeQAsACAAYQBuAGQAIABzAHUAbQAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUATQAoAEkATgBEAEUAWAAoAGwAaQBtAGIAcwBfAGEALAAgAHMAZQBxAF8AaQAsACAAMQApACAAKgAgAEkATgBEAEUAWAAoAGwAaQBtAGIAcwBfAGIALAAgAHMAZQBxAF8AagAsACAAMQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHMAbwBsAHYAZQAgAGEAbABsACAAYwBhAHIAcgBpAGUAcwAgAGIAbwB0AHQAbwBtAC0AdABvAC0AdABvAHAAIABlAHgAYQBjAHQAbAB5ACAAbwBuAGMAZQBcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHIAYQB3AF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABCAGkAbgBhAHIAeQAgAHMAZQBhAHIAYwBoACAAdABvACAAZgBpAG4AZAAgAHQAaABlACAAaABpAGcAaABlAHMAdAAgAHMAYwBhAGwAYQByACAAcQB1AG8AdABpAGUAbgB0ACAAbABpAG0AYgAgAHEAIAAoADAAIAA8AD0AIABxACAAPAAgADEAMABeAGsAKQBcAG4AoAAqACAAcwB1AGMAaAAgAHQAaABhAHQAIABCACAAKgAgAHEAIAA8AD0AIABhAGMAYwAuACAARQBsAGkAbQBpAG4AYQB0AGUAcwAgAHQAaABlACAAbgBlAGUAZAAgAGYAbwByACAASwBuAHUAdABoACAARAAgAGYAbABvAGEAdAAtAGUAcwB0AGkAbQBhAHQAaQBvAG4ALgBcAG4AoAAqACAAQABwAGEAcgBhAG0AIABhAGMAYwAgAFQAaABlACAAYwB1AHIAcgBlAG4AdAAgAHIAZQBtAGEAaQBuAGQAZQByACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAuAFwAbgCgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgCgACoALwBcAG4ARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAgAD0AIABMAEEATQBCAEQAQQAoAGEAYwBjACwAIABiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAYQBsAGMAdQBsAGEAdABlACAAcgBlAHEAdQBpAHIAZQBkACAAYgBpAHQAcwAgAGQAeQBuAGEAbQBpAGMAYQBsAGwAeQAuACAARgBvAHIAIABtAGEAeAAgAGsAPQA3ACwAIAB0AGgAaQBzACAAZQB2AGEAbAB1AGEAdABlAHMAIAB0AG8AIAAyADQAIABiAGkAdABzAC4AXABuACAAIAAgACAAIAAgACAAIABiAGkAdABzACwAIABDAEUASQBMAEkATgBHAC4ATQBBAFQASAAoAEwATwBHACgAMQAwAF4AawAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAbwB3AGUAcgBzACwAIAAyACAAXgAgAFMARQBRAFUARQBOAEMARQAoAGIAaQB0AHMALAAgADEALAAgAGIAaQB0AHMAIAAtACAAMQAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAUgBFAEQAVQBDAEUAKAAwACwAIABwAG8AdwBlAHIAcwAsACAATABBAE0AQgBEAEEAKABjAHUAcgByAF8AcQAsACAAcABvAHcAZQByACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABlAHMAdABfAHEALAAgAGMAdQByAHIAXwBxACAAKwAgAHAAbwB3AGUAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAawBpAHAAIABpAGYAIAB0AGUAcwB0AF8AcQAgAGUAeABjAGUAZQBkAHMAIAB0AGgAZQAgAGwAaQBtAGIAIABiAGEAcwBlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHQAZQBzAHQAXwBxACAAPgA9ACAAMQAwAF4AawAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATQB1AGwAdABpAHAAbAB5ACAAQgAgAGIAeQAgAHMAYwBhAGwAYQByACAAdABlAHMAdABfAHEAIABhAG4AZAAgAHIAZQBzAG8AbAB2AGUAIABjAGEAcgByAGkAZQBzACAAbgBhAHQAaQB2AGUAbAB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGUAcwB0AF8AcAByAG8AZAAsACAAQwBhAHIAcgB5ACgAYgAgACoAIAB0AGUAcwB0AF8AcQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAFUAQwBvAG0AcABhAHIAZQAoAGEAYwBjACwAIAB0AGUAcwB0AF8AcAByAG8AZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABjAG8AbQBwACAAPgA9ACAAMAAsACAAdABlAHMAdABfAHEALAAgAGMAdQByAHIAXwBxACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABCAGEAcwBlAGMAYQBzAGUAIABEAGkAdgBpAHMAaQBvAG4AIAB2AGkAYQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABzAGgAaQBmAHQALQBhAG4AZAAtAHMAdQBiAHQAcgBhAGMAdAAuAFwAbgCgACoAIABSAGUAdAB1AHIAbgBzACAAYQAgAHAAYQBjAGsAZQBkACAAMQBEACAAYQByAHIAYQB5ADoAIABWAFMAVABBAEMASwAoAEwAZQBuAGcAdABoAF8AUgAsACAAUgBfAGwAaQBtAGIAcwAsACAAUQBfAGwAaQBtAGIAcwApAC4AXABuAKAAKgAgAEUAbABpAG0AaQBuAGEAdABlAHMAIAAyAEQAIABhAHIAcgBhAHkAIABwAGEAZABkAGkAbgBnACAAdABvACAAcwB0AHIAaQBjAHQAbAB5ACAAcAByAGUAcwBlAHIAdgBlACAAbQBlAG0AbwByAHkAIABlAGYAZgBpAGMAaQBlAG4AYwB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAgACgAYQBzAHMAdQBtAGUAZAAgAG4AbwBuAC0AegBlAHIAbwApAC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuAKAAKgAvAFwAbgBLAG4AdQB0AGgARABpAHYAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcAAsACAAVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAIAByAG8AdQB0AGkAbgBnACAAdwBpAHQAaAAgAHQAaABlACAAbgBlAHcAIABwAGEAYwBrAGUAZAAgAG0AZQBtAG8AcgB5ACAAYwBvAG4AdAByAGEAYwB0AFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbABpAG0AYgBzAF8AYQApACwAIABsAGkAbQBiAHMAXwBhACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADEALAAgADAALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEkAdABlAHIAYQB0AGUAIABvAHYAZQByACAAQQAgAGYAcgBvAG0AIABNAFMAQgAgACgAdABvAHAAKQAgAHQAbwAgAEwAUwBCACAAKABiAG8AdAB0AG8AbQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHYAZQByAHMAZQBkAF8AYQAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEALAAgAFMARQBRAFUARQBOAEMARQAoAGwAZQBuAF8AYQAsACAAMQAsACAAbABlAG4AXwBhACwAIAAtADEAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAdABhAHQAZQAgAHMAZQBwAGEAcgBhAHQAbwByADoAIABWAFMAVABBAEMASwAoAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABxAHUAbwB0AGkAZQBuAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAbgBpAHQAaQBhAGwAXwBzAHQAYQB0AGUALAAgAFYAUwBUAEEAQwBLACgAMQAsACAAMAAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsAF8AcwB0AGEAdABlACwAIAByAGUAdgBlAHIAcwBlAGQAXwBhACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAdgBhAGwALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcwB0AGEAdABlACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHEAdQBvAHQAaQBlAG4AdAAsACAARABSAE8AUAAoAHMAdABhAHQAZQAsACAAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGgAaQBmAHQAIABhAGMAYwAgAHUAcAAgAGIAeQAgADEAIABsAGkAbQBiACAAKABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuADoAIABpAG4AcwBlAHIAdAAgAGEAdAAgAGkAbgBkAGUAeAAgADEAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAHgAdABlAG4AZABlAGQAXwByAGUAbQBhAGkAbgBkAGUAcgAsACAASQBGACgAQQBOAEQAKABSAE8AVwBTACgAcgBlAG0AYQBpAG4AZABlAHIAKQAgAD0AIAAxACwAIABJAE4ARABFAFgAKAByAGUAbQBhAGkAbgBkAGUAcgAsACAAMQAsACAAMQApACAAPQAgADAAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB2AGEAbAAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAHYAYQBsACwAIAByAGUAbQBhAGkAbgBkAGUAcgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgAsACAARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAoAGUAeAB0AGUAbgBkAGUAZABfAHIAZQBtAGEAaQBuAGQAZQByACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAHIAbwBkACwAIABDAGEAcgByAHkAKABsAGkAbQBiAHMAXwBiACAAKgAgAG4AZQB4AHQAXwBxAHUAbwB0AGkAZQBuAHQAXwBsAGkAbQBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAdwBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABVAFMAdQBiACgAZQB4AHQAZQBuAGQAZQBkAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHAAcgBvAGQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGgAYQBzAF8AcQB1AG8AdABpAGUAbgB0ACwAIABPAFIAKABSAE8AVwBTACgAcQB1AG8AdABpAGUAbgB0ACkAIAA+ACAAMQAsACAASQBOAEQARQBYACgAcQB1AG8AdABpAGUAbgB0ACwAMQAsADEAKQAgAD4AIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQB1AG8AdAAsACAASQBGACgAaABhAHMAXwBxAHUAbwB0AGkAZQBuAHQALAAgAFYAUwBUAEEAQwBLACgAcQB1AG8AdABpAGUAbgB0ACwAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgApACwAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbgBlAHcAXwByAGUAbQBhAGkAbgBkAGUAcgApACwAIABuAGUAdwBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABuAGUAeAB0AF8AcQB1AG8AdAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAEkATgBEAEUAWAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAbQBhAGkAbgBkAGUAcgAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAsACAAMQAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQB2AGUAcgBzAGUAZABfAHEAdQBvAHQAaQBlAG4AdAAsACAARABSAE8AUAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAcQB1AG8AdABfAHIAYQB3ACAAdwBhAHMAIABiAHUAaQBsAHQAIABNAFMAQgAgAHQAbwAgAEwAUwBCACAAKABCAGkAZwAtAEUAbgBkAGkAYQBuACkALgAgAFIAZQB2AGUAcgBzAGUAIAB0AG8AIABpAG4AdABlAHIAbgBhAGwAIABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHEAdQBvAHQAaQBlAG4AdAAsACAAUgBPAFcAUwAoAHIAZQB2AGUAcgBzAGUAZABfAHEAdQBvAHQAaQBlAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABxAHUAbwB0AGkAZQBuAHQALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKAByAGUAdgBlAHIAcwBlAGQAXwBxAHUAbwB0AGkAZQBuAHQALAAgAFMARQBRAFUARQBOAEMARQAoAGwAZQBuAF8AcQB1AG8AdABpAGUAbgB0ACwAIAAxACwAIABsAGUAbgBfAHEAdQBvAHQAaQBlAG4AdAAsACAALQAxACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABMAGUAYQBkAGkAbgBnAC8AdAByAGEAaQBsAGkAbgBnACAAegBlAHIAbwBzACAAYQByAGUAIABjAG8AbgB0AGkAbgB1AG8AdQBzAGwAeQAgAHIAZQBtAG8AdgBlAGQAIABpAG4AcwBpAGQAZQAgAHQAaABlACAAbABvAG8AcAAsACAAbgBvACAAbgBlAGUAZAAgAHQAbwAgAHIAZQBwAGUAYQB0ACAAaQB0AC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAcwB0AHIAaQBjAHQAbAB5ACAAcABhAGMAawBlAGQAIAAxAEQAIABhAHIAcgBhAHkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABxAHUAbwB0AGkAZQBuAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AoAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEgAeQBiAHIAaQBkACAARABpAHYAaQBzAGkAbwBuACAAUgBvAHUAdABlAHIALgBcAG4AoAAqACAARABpAHIAZQBjAHQAcwAgAGQAaQB2AGkAcwBpAG8AbgAgAHQAbwAgAHQAaABlACAAbwBwAHQAaQBtAGEAbAAgAGsAZQByAG4AZQBsACAAYgBhAHMAZQBkACAAbwBuACAARABpAHYAaQBkAGUAbgBkACAAbABlAG4AZwB0AGgALgBcAG4AoAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBhACAAVABoAGUAIABkAGkAdgBpAGQAZQBuAGQAIABhAHIAcgBhAHkALgBcAG4AoAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuAKAAKgAvAFwAbgBEAGkAdgBSAG8AdQB0AGUAcgAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARABpAGcAaQB0ACAAYwBvAHUAbgB0AHMAIABhAHIAZQAgAGEAcABwAHIAbwB4AGkAbQBhAHQAZQAsACAAYgB1AHQAIABzAHUAZgBmAGkAYwBpAGUAbgB0AFwAbgAgACAAIAAgACAAIAAgACAAZABpAGcAaQB0AHMAXwBhACwAIABSAE8AVwBTACgAbABpAG0AYgBzAF8AYQApACAAKgAgAGsALABcAG4AIAAgACAAIAAgACAAIAAgAGQAaQBnAGkAdABzAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAgACoAIABrACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAE0AYQBjAGgAaQBuAGUALQBsAGUAYQByAG4AZQBkACAAYwBvAGUAZgBmAGkAYwBpAGUAbgB0AHMAIABmAHIAbwBtACAATABvAGcAaQBzAHQAaQBjACAAUgBlAGcAcgBlAHMAcwBpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgAG0ALAAgADAALgAxADAANwA4ADIAMQAxADkANAAyADcAMQAyADkANwAsAFwAbgAgACAAIAAgACAAIAAgACAAYwAsACAALQAyADIAMQAuADkAMAAyADEAOAA5ADQANgAyADAANgA4ACwAXABuACAAIAAgACAAIAAgACAAIAB0AGgAcgBlAHMAaABvAGwAZAAsACAAKABtACAAKgAgAGQAaQBnAGkAdABzAF8AYQApACAAKwAgAGMALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAZABpAGcAaQB0AHMAXwBiACAAPAA9ACAAdABoAHIAZQBzAGgAbwBsAGQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASwBuAHUAdABoAEQAaQB2ACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4ARABpAHYAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAARwBlAG4AZQByAGEAdABlAHMAIAB0AGgAZQAgAGUAeABhAGMAdAAgAHIAZQBjAGkAcAByAG8AYwBhAGwAIABzAGUAZQBkACAAZgBvAHIAIABOAGUAdwB0AG8AbgAtAFIAYQBwAGgAcwBvAG4AIABEAGkAdgBpAHMAaQBvAG4AIAB1AHMAaQBuAGcAIABLAG4AdQB0AGgAIABCAGEAcwBlAGMAYQBzAGUALgBcAG4AIAAqACAARQB4AHQAcgBhAGMAdABzACAAdQBwACAAdABvACAAdABoAGUAIAB0AG8AcAAgADMAIABsAGkAbQBiAHMAIABvAGYAIABCACAAYQBuAGQAIABjAGEAbABjAHUAbABhAHQAZQBzACAAZgBsAG8AbwByACgAQgBlAHQAYQBeACgAMgAqAGwAZQBuACkAIAAvACAAQgBfAHQAbwBwACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBTAGUAZQBkACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYgAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGIALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQBlAGQAXwBsAGUAbgAsACAATQBJAE4AKAAzACwAIABsAGUAbgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAdABvAHAAIAAnAHMAZQBlAGQAXwBsAGUAbgAnACAAbABpAG0AYgBzACAAKABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuADoAIAB0AGEAawBlACAAZgByAG8AbQAgAHQAaABlACAAYgBvAHQAdABvAG0AKQBcAG4AIAAgACAAIAAgACAAIAAgAGIAXwB0AG8AcAAsACAAVABBAEsARQAoAGwAaQBtAGIAcwBfAGIALAAgAC0AcwBlAGUAZABfAGwAZQBuACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwBvAG4AcwB0AHIAdQBjAHQAIABCAGUAdABhAF4AKAAyACAAKgAgAHMAZQBlAGQAXwBsAGUAbgApACAAbgBhAHQAaQB2AGUAbAB5AFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAZQAuAGcALgAsACAAaQBmACAAcwBlAGUAZABfAGwAZQBuACAAPQAgADEALAAgAHQAaABlAG4AIAAxACAAZgBvAGwAbABvAHcAZQBkACAAYgB5ACAAdAB3AG8AIAB6AGUAcgBvACAAbABpAG0AYgBzADoAIABWAFMAVABBAEMASwAoADAALAAgADAALAAgADEAKQBcAG4AIAAgACAAIAAgACAAIAAgAGIAZQB0AGEAXwAyAG0ALAAgAFYAUwBUAEEAQwBLACgARQBYAFAAQQBOAEQAKAAwACwAIAAyACAAKgAgAHMAZQBlAGQAXwBsAGUAbgAsACAALAAgADAAKQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEsAbgB1AHQAaAAgAEQAaQB2AGkAcwBpAG8AbgAgAHkAaQBlAGwAZABzACAAZQB4AGEAYwB0ACAAaQBuAGkAdABpAGEAbAAgAHIAZQBjAGkAcAByAG8AYwBhAGwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAASwBuAHUAdABoAEQAaQB2ACgAYgBlAHQAYQBfADIAbQAsACAAYgBfAHQAbwBwACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAFEAdQBvAHQAaQBlAG4AdAAgAGEAcgByAGEAeQAgAGYAcgBvAG0AIAB0AGgAZQAgAHAAYQBjAGsAZQBkACAAVgBTAFQAQQBDAEsAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHIALAAgAEkATgBEAEUAWAAoAHAAYQBjAGsAZQBkACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABwAGEAYwBrAGUAZAAsACAAbABlAG4AXwByACAAKwAgADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEMAbwBtAHAAdQB0AGUAcwAgAHQAaABlACAAUgBlAGMAaQBwAHIAbwBjAGEAbAAgAHAAcgBvAGcAcgBlAHMAcwBpAHYAZQBsAHkAIABzAGMAYQBsAGkAbgBnACAAdQBwACAAdABvACAAdABoAGUAIABEAGkAdgBpAGQAZQBuAGQAJwBzACAAcAByAGUAYwBpAHMAaQBvAG4ALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHQAYQByAGcAZQB0AF8AbABlAG4AIABUAGgAZQAgAGwAaQBtAGIALQBsAGUAbgBnAHQAaAAgAG8AZgAgAEQAaQB2AGkAZABlAG4AZAAgAEEALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4AUgBlAGMAaQBwAHIAbwBjAGEAbAAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGIALAAgAHQAYQByAGcAZQB0AF8AbABlAG4ALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwBiACwAIABSAE8AVwBTACgAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAZQBkAF8AbABlAG4ALAAgAE0ASQBOACgAMwAsACAAbABlAG4AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAXwBzAGUAZQBkAF8AbABpAG0AYgBzACwAIABOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAFMAZQBlAGQAKABsAGkAbQBiAHMAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKABzAGUAZQBkAF8AbABlAG4ALAAgAHIAXwBzAGUAZQBkAF8AbABpAG0AYgBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQBxAF8AaQB0AGUAcgBzACwAIABNAEEAWAAoADAALAAgAEMARQBJAEwASQBOAEcALgBNAEEAVABIACgATABOACgAdABhAHIAZwBlAHQAXwBsAGUAbgAgAC8AIABzAGUAZQBkAF8AbABlAG4AKQAgAC8AIABMAE4AKAAyACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAHIAZQBxAF8AaQB0AGUAcgBzACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBfAHMAZQBlAGQAXwBsAGkAbQBiAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAHQAZQByAGEAdABpAG8AbgBzACwAIABTAEUAUQBVAEUATgBDAEUAKAByAGUAcQBfAGkAdABlAHIAcwApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcwB0AGEAdABlACwAIABSAEUARABVAEMARQAoAGkAbgBpAHQAaQBhAGwAXwBzAHQAYQB0AGUALAAgAGkAdABlAHIAYQB0AGkAbwBuAHMALAAgAEwAQQBNAEIARABBACgAcwB0AGEAdABlACwAIABpAHQAZQByACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AbABlAG4ALAAgAEkATgBEAEUAWAAoAHMAdABhAHQAZQAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwByACwAIABEAFIATwBQACgAcwB0AGEAdABlACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwBsAGUAbgAsACAATQBJAE4AKABjAHUAcgByAF8AbABlAG4AIAAqACAAMgAsACAAdABhAHIAZwBlAHQAXwBsAGUAbgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAaABpAGYAdABfAGwAaQBtAGIAcwAsACAAbgBlAHgAdABfAGwAZQBuACAALQAgAGMAdQByAHIAXwBsAGUAbgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBfAHAAcgBpAG0AZQAsACAASQBGACgAcwBoAGkAZgB0AF8AbABpAG0AYgBzACAAPgAgADAALAAgAFYAUwBUAEEAQwBLACgARQBYAFAAQQBOAEQAKAAwACwAIABzAGgAaQBmAHQAXwBsAGkAbQBiAHMALAAgACwAIAAwACkALAAgAGMAdQByAHIAXwByACkALAAgAGMAdQByAHIAXwByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAbABpAGMAZQAgAEIAIAB0AG8AIABpAHQAcwAgAG4AYQB0AHUAcgBhAGwAIABsAGkAbQBpAHQAcwAsACAAcABhAGQAZABpAG4AZwAgAHcAaQB0AGgAIAB6AGUAcgBvAHMAIABkAGUAcwB0AHIAbwB5AHMAIABwAGUAcgBmAG8AcgBtAGEAbgBjAGUALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYgBfAGEAYwB0AGkAdgBlACwAIABUAEEASwBFACgAbABpAG0AYgBzAF8AYgAsACAALQBNAEkATgAoAG4AZQB4AHQAXwBsAGUAbgAsACAAbABlAG4AXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATwAoAE4AKgBNACkAIABpAG4AcwB0AGUAYQBkACAAbwBmACAATwAoAE4AXgAyACkAIABmAG8AcgAgAFAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAXwByAGEAdwAsACAAVQBNAHUAbAAoAGIAXwBhAGMAdABpAHYAZQAsACAAcgBfAHAAcgBpAG0AZQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGgAaQBmAHQAaQBuAGcAIAB0AGgAZQAgAHIAZQBzAHUAbAB0ACAAYQByAHIAYQB5ACAAcgBlAHAAbABpAGMAYQB0AGUAcwAgAEIAZQB0AGEAIABtAHUAbAB0AGkAcABsAGkAYwBhAHQAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAaABpAGYAdABfAHAALAAgAE0AQQBYACgAMAAsACAAbgBlAHgAdABfAGwAZQBuACAALQAgAGwAZQBuAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAALAAgAEkARgAoAHMAaABpAGYAdABfAHAAIAA+ACAAMAAsACAAVgBTAFQAQQBDAEsAKABFAFgAUABBAE4ARAAoADAALAAgAHMAaABpAGYAdABfAHAALAAgACwAIAAwACkALAAgAHAAXwByAGEAdwApACwAIABwAF8AcgBhAHcAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdAB3AG8AXwBiAGUAdABhACwAIABWAFMAVABBAEMASwAoAEUAWABQAEEATgBEACgAMAAsACAAMgAgACoAIABuAGUAeAB0AF8AbABlAG4ALAAgACwAIAAwACkALAAgADIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAHIAcgAsACAAVQBTAHUAYgAoAHQAdwBvAF8AYgBlAHQAYQAsACAAcAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcgBfAHUAbgBzAGMAYQBsAGUAZAAsACAAVQBNAHUAbAAoAHIAXwBwAHIAaQBtAGUALAAgAGUAcgByACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBlAHgAdABfAHIALAAgAEkARgAoAFIATwBXAFMAKABuAGUAeAB0AF8AcgBfAHUAbgBzAGMAYQBsAGUAZAApACAAPAA9ACAAMgAgACoAIABuAGUAeAB0AF8AbABlAG4ALAAgAHsAMAB9ACwAIABEAFIATwBQACgAbgBlAHgAdABfAHIAXwB1AG4AcwBjAGEAbABlAGQALAAgADIAIAAqACAAbgBlAHgAdABfAGwAZQBuACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABuAGUAeAB0AF8AbABlAG4ALAAgAG4AZQB4AHQAXwByACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABmAGkAbgBhAGwAXwBzAHQAYQB0AGUALAAgADEAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABIAGUAYQB2AHkAdwBlAGkAZwBoAHQAIABOAGUAdwB0AG8AbgAtAFIAYQBwAGgAcwBvAG4AIABEAGkAdgBpAHMAaQBvAG4ALgBcAG4AIAAqACAASQBtAHAAbABlAG0AZQBuAHQAcwAgAHAAcgBvAGcAcgBlAHMAcwBpAHYAZQAgAHMAYwBhAGwAaQBuAGcAIABiAG8AdQBuAGQAZQBkACAAdABvACAATQBBAFgAKABsAGUAbgBfAGEALAAgAGwAZQBuAF8AYgApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwBhACwAIABSAE8AVwBTACgAbABpAG0AYgBzAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGIALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQByAGcAZQB0AF8AbABlAG4ALAAgAE0AQQBYACgAbABlAG4AXwBhACwAIABsAGUAbgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAAxAC4AIABDAGEAbABjAHUAbABhAHQAZQAgAHIAZQBjAGkAcAByAG8AYwBhAGwAIABSACAAcwBjAGEAbABlAGQAIABkAHkAbgBhAG0AaQBjAGEAbABsAHkAIAB0AG8AIAB0AGEAcgBnAGUAdABfAGwAZQBuAFwAbgAgACAAIAAgACAAIAAgACAAcgAsACAATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBSAGUAYwBpAHAAcgBvAGMAYQBsACgAbABpAG0AYgBzAF8AYgAsACAAdABhAHIAZwBlAHQAXwBsAGUAbgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgADIALgAgAEEAcABwAHIAbwB4AGkAbQBhAHQAZQAgAFEAdQBvAHQAaQBlAG4AdAA6ACAAUQBfAGEAcABwAHIAbwB4ACAAPQAgAEEAIAAqACAAUgAgAC8AIABCAGUAdABhAF4AKAB0AGEAcgBnAGUAdABfAGwAZQBuACAAKwAgAGwAZQBuAF8AYgApAFwAbgAgACAAIAAgACAAIAAgACAAZAByAG8AcABfAGwAaQBtAGIAcwAsACAAdABhAHIAZwBlAHQAXwBsAGUAbgAgACsAIABsAGUAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgAHEAXwB1AG4AcwBjAGEAbABlAGQALAAgAFUATQB1AGwAKABsAGkAbQBiAHMAXwBhACwAIAByACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHEAXwBhAHAAcAByAG8AeAAsACAASQBGACgAUgBPAFcAUwAoAHEAXwB1AG4AcwBjAGEAbABlAGQAKQAgADwAPQAgAGQAcgBvAHAAXwBsAGkAbQBiAHMALAAgAHsAMAB9ACwAIABEAFIATwBQACgAcQBfAHUAbgBzAGMAYQBsAGUAZAAsACAAZAByAG8AcABfAGwAaQBtAGIAcwApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAMwAuACAARQByAHIAbwByACAAQwBvAHIAcgBlAGMAdABpAG8AbgAgAFMAdwBlAGUAcAAgACgAUgBlAG0AYQBpAG4AZABlAHIAIAA9ACAAQQAgAC0AIAAoAEIAIAAqACAAUQBfAGEAcABwAHIAbwB4ACkAKQBcAG4AIAAgACAAIAAgACAAIAAgAHEAXwBwAHIAbwBkACwAIABVAE0AdQBsACgAbABpAG0AYgBzAF8AYgAsACAAcQBfAGEAcABwAHIAbwB4ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQBtAF8AYQBwAHAAcgBvAHgALAAgAFUAUwB1AGIAKABsAGkAbQBiAHMAXwBhACwAIABxAF8AcAByAG8AZAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAFUAQwBvAG0AcABhAHIAZQAoAHIAZQBtAF8AYQBwAHAAcgBvAHgALAAgAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAG8AcgByAGUAYwB0ACAAZgBsAG8AbwByACAAdAByAHUAbgBjAGEAdABpAG8AbgAgAGYAcgBvAG0AIABpAG4AdABlAGcAZQByACAAcgBlAGMAaQBwAHIAbwBjAGEAbABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHEALAAgAEkARgAoAGMAbwBtAHAAIAA+AD0AIAAwACwAIABVAEEAZABkACgAcQBfAGEAcABwAHIAbwB4ACwAIAB7ADEAfQAsACAAawApACwAIABxAF8AYQBwAHAAcgBvAHgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsACAASQBGACgAYwBvAG0AcAAgAD4APQAgADAALAAgAFUAUwB1AGIAKAByAGUAbQBfAGEAcABwAHIAbwB4ACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALAAgAHIAZQBtAF8AYQBwAHAAcgBvAHgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZgBpAG4AYQBsAF8AcgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQgBpAGcASQBuAHQAIgAsACIAdABlAHgAdAAiADoAIgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4ALwAvACAAQgBpAGcAIABJAG4AdABlAGcAZQByACAAQQByAGkAdABoAG0AZQB0AGkAYwAgAEwAaQBiAHIAYQByAHkAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIAAgACAAQgBpAGcASQBuAHQAIABNAG8AZAB1AGwAZQAgACAAIAAgACAAIAAgACAAIAAgACAALwAvAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIABQAHUAYgBsAGkAYwAgAEEAUABJACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwBcAG4ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8AXABuAFwAbgAvACoAKgBcAG4AIAAqACAATgBvAHIAbQBhAGwAaQBzAGUAcwAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AIABTAHQAcgBpAHAAcwAgAGwAZQBhAGQAaQBuAGcAIAB6AGUAcgBvAHMALAAgAHIAZQBzAG8AbAB2AGUAcwAgAFwAIgAtADAAXAAiACAAdABvACAAXAAiADAAXAAiACwAIABhAG4AZAAgAHQAaAByAG8AdwBzACAAIwBWAEEATABVAEUAIQAgAG8AbgAgAGkAbgB2AGEAbABpAGQAIABjAGgAYQByAGEAYwB0AGUAcgBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ATgBvAHIAbQAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AHIALAAgAEkARgAoAE8AUgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYgBpAGcAXwBpAG4AdAApACwAIABiAGkAZwBfAGkAbgB0ACAAPQAgAFwAIgBcACIAKQAsACAAXAAiADAAXAAiACwAIABiAGkAZwBfAGkAbgB0ACAAJgAgAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AdgBhAGwAaQBkACwAIABSAEUARwBFAFgAVABFAFMAVAAoAHMAdAByACwAIABcACIAXgAtAD8AXABcAGQAKwAkAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAcgBpAHAAcABlAGQALAAgAFIARQBHAEUAWABSAEUAUABMAEEAQwBFACgAcwB0AHIALAAgAFwAIgBeACgALQA/ACkAMAArACgAPwA9AFwAXABkACkAXAAiACwAIABcACIAJAAxAFwAIgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATgBPAFQAKABpAHMAXwB2AGEAbABpAGQAKQAsACAAVgBBAEwAVQBFACgAXAAiACMAVgBBAEwAVQBFACEAXAAiACkALAAgAEkARgAoAHMAdAByAGkAcABwAGUAZAAgAD0AIABcACIALQAwAFwAIgAsACAAXAAiADAAXAAiACwAIABzAHQAcgBpAHAAcABlAGQAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIABzAGkAZwBuACAAbwBmACAAYQAgAEIAaQBnAEkAbgB0ADoAIAAxACAAKABwAG8AcwBpAHQAaQB2AGUAKQAsACAALQAxACAAKABuAGUAZwBhAHQAaQB2AGUAKQAsACAAbwByACAAMAAgACgAegBlAHIAbwApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AUwBpAGcAbgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALAAgAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAGUAZAAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUwBXAEkAVABDAEgAKABMAEUARgBUACgAbgBvAHIAbQBlAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMABcACIALAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIAAtADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAvACAALQAtAC0AIABQAHIAZQBkAGkAYwBhAHQAZQBzACAALQAtAC0AIABcAFwAXABcAFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFIAZQB0AHUAcgBuAHMAIABUAFIAVQBFACAAaQBmACAAdABoAGUAIABCAGkAZwBJAG4AdAAgAGkAcwAgAGUAeABhAGMAdABsAHkAIAB6AGUAcgBvAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ASQBzAFoAZQByAG8AIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACAAPQAgAFwAIgAwAFwAIgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAFQAUgBVAEUAIABpAGYAIAB0AGgAZQAgAEIAaQBnAEkAbgB0ACAAaQBzACAAbgBlAGcAYQB0AGkAdgBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ASQBzAE4AZQBnACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsACAATABFAEYAVAAoAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0ACkAKQAgAD0AIABcACIALQBcACIAKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFIAZQB0AHUAcgBuAHMAIAB0AGgAZQAgAHUAbgBzAGkAZwBuAGUAZAAgAG0AYQBnAG4AaQB0AHUAZABlACAAbwBmACAAYQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAIAAoAGEAYgBzAG8AbAB1AHQAZQAgAHYAYQBsAHUAZQApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AQQBiAHMAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAIABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgB1AG0ALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwARQBGAFQAKABuAHUAbQApACAAPQAgAFwAIgAtAFwAIgAsACAATQBJAEQAKABuAHUAbQAsACAAMgAsACAATABFAE4AKABuAHUAbQApACAALQAgADEAKQAsACAAbgB1AG0AKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAQwBvAG0AcABhAHIAZQBzACAAdAB3AG8AIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMALgAgAFIAZQB0AHUAcgBuAHMAIAAxACAAKABhACAAPgAgAGIAKQAsACAALQAxACAAKABhACAAPAAgAGIAKQAsACAAbwByACAAMAAgACgAYQAgAD0AIABiACkALgBcAG4AIAAqACAARQB2AGEAbAB1AGEAdABlAHMAIABzAGkAZwBuAHMAIABhAG4AZAAgAGwAZQBuAGcAdABoAHMALgAgAEkAZgAgAGkAZABlAG4AdABpAGMAYQBsACwAIABkAGUAbABlAGcAYQB0AGUAcwAgAHQAbwAgAG4AYQB0AGkAdgBlACAAbABpAG0AYgAgAGEAcgByAGEAeQAgAGMAbwBtAHAAYQByAGkAcwBvAG4ALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEMAbwBtAHAAYQByAGUAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGEALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBhACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgAsACAAQgBpAGcAaQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAHMAaQBnAG4AXwBhACAAPAA+ACAAcwBpAGcAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBJAEcATgAoAHMAaQBnAG4AXwBhACAALQAgAHMAaQBnAG4AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAcwBpAGcAbgBfAGEAIAA9ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwBhACwAIABMAEUATgAoAG4AbwByAG0AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAATABFAE4AKABuAG8AcgBtAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGwAZQBuAF8AYQAgADwAPgAgAGwAZQBuAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEkARwBOACgAbABlAG4AXwBhACAALQAgAGwAZQBuAF8AYgApACAAKgAgAHMAaQBnAG4AXwBhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEEARABEAFwAIgApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBhACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGEAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBiACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcABhAHIAaQBzAG8AbgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAGcAXwBjAG8AbQBwAGEAcgBpAHMAbwBuACAAKgAgAHMAaQBnAG4AXwBhAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIAAtACAAQQBkAGQAaQB0AGkAbwBuACAAJgAgAFMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAC0AIAAgACAAIAAgACAAIABcAFwAXABcAFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEEAZABkAHMAIAB0AHcAbwAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBhACAAVABoAGUAIABmAGkAcgBzAHQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGIAIABUAGgAZQAgAHMAZQBjAG8AbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AQQBkAGQAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGEALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBhACwAIABCAGkAZwBpAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIAQQBEAEQAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGEALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYQApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYgApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHUAdABlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEEAZABkAFMAdQBiAFIAbwB1AHQAZQByACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAcwBpAGcAbgBfAGEALAAgAHMAaQBnAG4AXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAaQBnAG4ALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKAByAG8AdQB0AGUAZAAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAARABSAE8AUAAoAHIAbwB1AHQAZQBkACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABtAGUAcgBnAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAFwAIgAtAFwAIgAgACYAIABtAGUAcgBnAGUAZAAsACAAbQBlAHIAZwBlAGQAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUwB1AGIAdAByAGEAYwB0AHMAIAB0AGgAZQAgAHMAZQBjAG8AbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAGYAaQByAHMAdAAgACgAQQAgAC0AIABCACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAbQBpAG4AdQBlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAcwB1AGIAdAByAGEAaABlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAFMAdQBiACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBiACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABJAG4AdgBlAHIAdAAgAHQAaABlACAAcwBpAGcAbgAgAG8AZgAgAEIAIABhAHQAIAB0AGgAZQAgAHQAZQB4AHQAIABsAGUAdgBlAGwAXABuACAAIAAgACAAIAAgACAAIABpAG4AdgBfAGIALAAgAEkARgAoAG4AbwByAG0AXwBiACAAPQAgAFwAIgAwAFwAIgAsACAAXAAiADAAXAAiACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATABFAEYAVAAoAG4AbwByAG0AXwBiACkAIAA9ACAAXAAiAC0AXAAiACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkARAAoAG4AbwByAG0AXwBiACwAIAAyACwAIABMAEUATgAoAG4AbwByAG0AXwBiACkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACAAJgAgAG4AbwByAG0AXwBiAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABQAGEAcwBzACAAdABvACAAQQBkAGQAXABuACAAIAAgACAAIAAgACAAIABBAGQAZAAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABpAG4AdgBfAGIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUwB1AG0AcwAgAGEAbgAgAGEAcgByAGEAeQAgAG8AcgAgAHIAYQBuAGcAZQAgAG8AZgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAgAHYAaQBhACAAdgBlAGMAdABvAHIAaQB6AGUAZAAgAGcAcgBvAHUAcAAgAG0AYQB0AHIAaQBjAGUAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHIAYQBuAGcAZQAgAEEAIABjAG8AbgB0AGkAZwB1AG8AdQBzACAAcgBhAG4AZwBlACAAbwByACAAYQByAHIAYQB5ACAAbwBmACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAKgAvAFwAbgBTAHUAbQAgAD0AIABMAEEATQBCAEQAQQAoAHIAYQBuAGcAZQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABmAGwAYQB0ACwAIABUAE8AUgBPAFcAKAByAGEAbgBnAGUALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABJAFMARQBSAFIATwBSACgAZgBsAGEAdAApACwAIABDAE8ATABVAE0ATgBTACgAZgBsAGEAdAApACAAPQAgADAAKQAsACAAXAAiADAAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBzACwAIABNAEEAUAAoAGYAbABhAHQALAAgAEwAQQBNAEIARABBACgAeAAsACAATgBvAHIAbQAoAHgAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGkAZwBuAHMALAAgAE0AQQBQACgATABFAEYAVAAoAG4AbwByAG0AcwApACwAIABMAEEATQBCAEQAQQAoAHgALAAgAEkARgAoAHgAIAA9ACAAXAAiADAAXAAiACwAIAAwACwAIABpAGYAKAB4ACAAPQAgAFwAIgAtAFwAIgAsACAALQAxACwAIAAxACkAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGIAcwBfAG4AbwByAG0AcwAsACAATQBBAFAAKABuAG8AcgBtAHMALAAgAHMAaQBnAG4AcwAsACAATABBAE0AQgBEAEEAKAB4ACwAIABzAGkAZwBuACwAIABJAEYAKABzAGkAZwBuACAAPQAgAC0AMQAsACAATQBJAEQAKAB4ACwAIAAyACwAIABMAEUATgAoAHgAKQAtADEAKQAsACAAeAApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAbwBzAF8AcwB0AHIAcwAsACAARgBJAEwAVABFAFIAKABhAGIAcwBfAG4AbwByAG0AcwAsACAAcwBpAGcAbgBzACAAPQAgADEALAAgAHsAXAAiADAAXAAiAH0AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQBnAF8AcwB0AHIAcwAsACAARgBJAEwAVABFAFIAKABhAGIAcwBfAG4AbwByAG0AcwAsACAAcwBpAGcAbgBzACAAPQAgAC0AMQAsACAAewBcACIAMABcACIAfQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdQBuAGkAZgBpAGUAZABfAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBBAEQARABcACIALAAgAEMATwBMAFUATQBOAFMAKABmAGwAYQB0ACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAbwBzAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AYQB0AHIAaQB4AFMAdQBtACgAcABvAHMAXwBzAHQAcgBzACwAIAB1AG4AaQBmAGkAZQBkAF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBlAGcAXwBsAGkAbQBiAHMALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQBhAHQAcgBpAHgAUwB1AG0AKABuAGUAZwBfAHMAdAByAHMALAAgAHUAbgBpAGYAaQBlAGQAXwBrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAG8AdQB0AGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AQQBkAGQAUwB1AGIAUgBvAHUAdABlAHIAKABwAG8AcwBfAGwAaQBtAGIAcwAsACAAbgBlAGcAXwBsAGkAbQBiAHMALAAgADEALAAgAC0AMQAsACAAdQBuAGkAZgBpAGUAZABfAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAaQBnAG4ALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKAByAG8AdQB0AGUAZAAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAEQAUgBPAFAAKAByAG8AdQB0AGUAZAAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGUAcgBnAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIAB1AG4AaQBmAGkAZQBkAF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAFwAIgAtAFwAIgAgACYAIABtAGUAcgBnAGUAZAAsACAAbQBlAHIAZwBlAGQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAE0AdQBsAHQAaQBwAGwAaQBlAHMAIAB0AHcAbwAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBhACAAVABoAGUAIABmAGkAcgBzAHQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGIAIABUAGgAZQAgAHMAZQBjAG8AbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ATQB1AGwAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGEALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBhACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwBhACwAIABMAEUATgAoAG4AbwByAG0AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAATABFAE4AKABuAG8AcgBtAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAOgAgADAAIABtAHUAbAB0AGkAcABsAGkAZQBkACAAYgB5ACAAYQBuAHkAdABoAGkAbgBnACAAaQBzACAAMABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAE8AUgAoAHMAaQBnAG4AXwBhACAAPQAgADAALAAgAHMAaQBnAG4AXwBiACAAPQAgADAAKQAsACAAXAAiADAAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABsAGUAbgBfAGEAIAArACAAbABlAG4AXwBiACAAPgAgADMAMgA3ADYANgAsACAAIwBOAFUATQAhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIABkAHkAbgBhAG0AaQBjACAAcwBhAGYAZQAgAEsAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHMAaABvAHIAdABlAHMAdAAgAHMAdAByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBNAFUATABcACIALAAgAE0ASQBOACgAbABlAG4AXwBhACwAIABsAGUAbgBfAGIAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBwAGwAaQB0ACAAYQBiAHMAbwBsAHUAdABlACAAcwB0AHIAaQBuAGcAcwAgAGkAbgB0AG8AIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAYQByAHIAYQB5AHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBhACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYgApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAbABjAHUAbABhAHQAZQAgAG0AYQBnAG4AaQB0AHUAZABlACAAYQBuAGQAIAByAGUAcwBvAGwAdgBlACAAcwBpAGcAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAGkAZwBuACwAIABzAGkAZwBuAF8AYQAgACoAIABzAGkAZwBuAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AZQByAGcAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGYAaQBuAGEAbABfAHMAaQBnAG4AIAA9ACAALQAxACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQALAAgAG0AZQByAGcAZQBkACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsAVgBPAEwAQQBUAEkATABFAF0AIABHAGUAbgBlAHIAYQB0AGUAcwAgAGEAIABkAHkAbgBhAG0AaQBjACAAYQByAHIAYQB5ACAAbwBmACAAaQBuAHQAZQBnAGUAcgBzACAAYQBzACAAdABlAHgAdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAbgB1AG0AXwByAG8AdwBzAF0AIABhAHIAcgBhAHkAIABoAGUAaQBnAGgAdAAsACAAZABlAGYAYQB1AGwAdAAgADEALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG4AdQBtAF8AYwBvAGwAcwBdACAAYQByAHIAYQB5ACAAdwBpAGQAdABoACwAIABkAGUAZgBhAHUAbAB0ACAAMQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAbQBpAG4AXwBkAGkAZwBpAHQAcwBdACAAbQBpAG4AaQBtAHUAbQAgAG4AdQBtAGIAZQByACAAbwBmACAAZABpAGcAaQB0AHMALAAgAGQAZQBmAGEAdQBsAHQAIAAxADYAIAAoAG0AaQBuACAAMQAgAGQAaQBnAGkAdAApAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAbQBhAHgAXwBkAGkAZwBpAHQAcwBdACAAbQBhAHgAaQBtAHUAbQAgAG4AdQBtAGIAZQByACAAbwBmACAAZABpAGcAaQB0AHMALAAgAGQAZQBmAGEAdQBsAHQAIAA1ADAAIAAoAG0AYQB4ACAAMwAyACwANwA2ADcAIABjAGgAYQByAHMALAAgAGkAbgBjAGwAdQBkAGkAbgBnACAAcwBpAGcAbgApAFwAbgAgACoALwBcAG4AUgBhAG4AZABCAGkAZwBJAG4AdABBAHIAcgBhAHkAIAA9ACAATABBAE0AQgBEAEEAKABbAG4AdQBtAF8AcgBvAHcAcwBdACwAIABbAG4AdQBtAF8AYwBvAGwAcwBdACwAIABbAG0AaQBuAF8AZABpAGcAaQB0AHMAXQAsACAAWwBtAGEAeABfAGQAaQBnAGkAdABzAF0ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBfAHIAbwB3AHMALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbgB1AG0AXwByAG8AdwBzACkALAAgADEALAAgAG4AdQBtAF8AcgBvAHcAcwApACwAXABuACAAIAAgACAAIAAgACAAIABuAF8AYwBvAGwAcwAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABuAHUAbQBfAGMAbwBsAHMAKQAsACAAMQAsACAAbgB1AG0AXwBjAG8AbABzACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAbQBpAG4AXwBsAGUAbgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABtAGkAbgBfAGQAaQBnAGkAdABzACkALAAgADEANgAsACAATQBJAE4AKAAzADIANwA2ADcALAAgAE0AQQBYACgAMQAsACAAbQBpAG4AXwBkAGkAZwBpAHQAcwApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwBsAGUAbgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABtAGEAeABfAGQAaQBnAGkAdABzACkALAAgADUAMAAsACAATQBBAFgAKAAxACwAIABNAEkATgAoADMAMgA3ADYANgAsACAAbQBhAHgAXwBkAGkAZwBpAHQAcwApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBQACgAUgBBAE4ARABBAFIAUgBBAFkAKABuAF8AcgBvAHcAcwAsACAAbgBfAGMAbwBsAHMALAAgAG0AaQBuAF8AbABlAG4ALAAgAG0AYQB4AF8AbABlAG4ALAAgAFQAUgBVAEUAKQAsACAATABBAE0AQgBEAEEAKABsAGUAbgBnAHQAaAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAaQBnAG4ALAAgAEMASABPAE8AUwBFACgAUgBBAE4ARABCAEUAVABXAEUARQBOACgAMQAsACAAMgApACwAIABcACIAXAAiACwAIABcACIALQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGQAaQBnAGkAdABzACwAIABDAE8ATgBDAEEAVAAoAFIAQQBOAEQAQQBSAFIAQQBZACgAMQAsACAAbABlAG4AZwB0AGgALAAgADAALAAgADkALAAgAFQAUgBVAEUAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBpAGcAbgAgACYAIABSAEUARwBFAFgAUgBFAFAATABBAEMARQAoAGQAaQBnAGkAdABzACwAIABcACIAXgAwACoAXAAiACwAIABcACIAXAAiACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEQAaQB2AGkAZABlAHMAIAB0AGgAZQAgAGYAaQByAHMAdAAgAEIAaQBnAEkAbgB0ACAAYgB5ACAAdABoAGUAIABzAGUAYwBvAG4AZAAgACgAQQAgAC8AIABCACkALgAgAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIABxAHUAbwB0AGkAZQBuAHQAIABhAG4AZAAgAG0AbwBkAHUAbAB1AHMAIABpAG4AIAByAG8AdwBzACAAMQAgAGEAbgBkACAAMgAsACAAcgBlAHMAcABlAGMAdABpAHYAZQBsAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAdQBzAGUAXwBmAGwAbwBvAHIAXQAgAE8AcAB0AGkAbwBuAGEAbAAgAGIAbwBvAGwAZQBhAG4ALgAgAFQAUgBVAEUAIABmAG8AcgAgAFAAeQB0AGgAbwBuAC0AcwB0AHkAbABlACAARgBsAG8AbwByACAAZABpAHYAaQBzAGkAbwBuACwAIABGAEEATABTAEUAIABmAG8AcgAgAFQAcgB1AG4AYwBhAHQAZQBkAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABGAEEATABTAEUALgBcAG4AIAAqAC8AXABuAEQAaQB2AE0AbwBkACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAIABbAHUAcwBlAF8AZgBsAG8AbwByAF0ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGEALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBhACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AZgBsAG8AbwByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHUAcwBlAF8AZgBsAG8AbwByACkALAAgAEYAQQBMAFMARQAsACAAdQBzAGUAXwBmAGwAbwBvAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AYgAgAD0AIAAwACwAIAAjAEQASQBWAC8AMAAhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHMAaQBnAG4AXwBhACAAPQAgADAALAAgAHsAXAAiADAAXAAiADsAXAAiADAAXAAiAH0ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBhACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGEAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBiACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGIAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAYQBjAGsAZQBkAF8AcgBlAHMAdQBsAHQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEQAaQB2AFIAbwB1AHQAZQByACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABSAGUAbQBhAGkAbgBkAGUAcgAgAGEAbgBkACAAUQB1AG8AdABpAGUAbgB0ACAAYQByAHIAYQB5AHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHIALAAgAEkATgBEAEUAWAAoAHAAYQBjAGsAZQBkAF8AcgBlAHMAdQBsAHQALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAG0AXwBsAGkAbQBiAHMALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKABwAGEAYwBrAGUAZABfAHIAZQBzAHUAbAB0ACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHIALAAgADEALAAgADIAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABxAHUAbwB0AF8AbABpAG0AYgBzACwAIABEAFIATwBQACgAcABhAGMAawBlAGQAXwByAGUAcwB1AGwAdAAsACAAbABlAG4AXwByACAAKwAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAcwBvAGwAdgBlACAAVAByAHUAbgBjAGEAdABlAGQAIABzAGkAZwBuAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAGkAZwBuACwAIABzAGkAZwBuAF8AYQAgACoAIABzAGkAZwBuAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBlAHIAZwBlAGQAXwBxACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABxAHUAbwB0AF8AbABpAG0AYgBzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AZQByAGcAZQBkAF8AcgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAcgBlAG0AXwBsAGkAbQBiAHMALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AHIAdQBuAGMAXwBxACwAIABJAEYAKABBAE4ARAAoAGYAaQBuAGEAbABfAHMAaQBnAG4AIAA9ACAALQAxACwAIABtAGUAcgBnAGUAZABfAHEAIAA8AD4AIABcACIAMABcACIAKQAgACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQAXwBxACwAIABtAGUAcgBnAGUAZABfAHEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdAByAHUAbgBjAF8AcgAsACAASQBGACgAYQBuAGQAKABzAGkAZwBuAF8AYQAgAD0AIAAtADEALAAgAG0AZQByAGcAZQBkAF8AcgAgADwAPgAgAFwAIgAwAFwAIgApACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQAXwByACwAIABtAGUAcgBnAGUAZABfAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABGAGwAbwBvAHIAIABDAG8AcgByAGUAYwB0AGkAbwBuADoAIABUAHIAaQBnAGcAZQByACAATwBOAEwAWQAgAGkAZgAgAGYAbABvAG8AcgAgAGkAcwAgAHIAZQBxAHUAZQBzAHQAZQBkACwAIABzAGkAZwBuAHMAIABkAGkAZgBmAGUAcgAsACAAYQBuAGQAIAByAGUAbQBhAGkAbgBkAGUAcgAgAGkAcwAgAG4AbwBuAC0AegBlAHIAbwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQBlAGQAcwBfAGMAbwByAHIAZQBjAHQAaQBvAG4ALAAgAEEATgBEACgAaQBzAF8AZgBsAG8AbwByACwAIABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAbQBlAHIAZwBlAGQAXwByACAAPAA+ACAAXAAiADAAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcQAsACAASQBGACgAbgBlAGUAZABzAF8AYwBvAHIAcgBlAGMAdABpAG8AbgAsACAAUwB1AGIAKAB0AHIAdQBuAGMAXwBxACwAIABcACIAMQBcACIAKQAsACAAdAByAHUAbgBjAF8AcQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwByACwAIABJAEYAKABuAGUAZQBkAHMAXwBjAG8AcgByAGUAYwB0AGkAbwBuACwAIABBAGQAZAAoAHQAcgB1AG4AYwBfAHIALAAgAG4AbwByAG0AXwBiACkALAAgAHQAcgB1AG4AYwBfAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAGYAaQBuAGEAbABfAHEALAAgAGYAaQBuAGEAbABfAHIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAARABpAHYAaQBkAGUAcwAgAHQAaABlACAAZgBpAHIAcwB0ACAAQgBpAGcASQBuAHQAIABiAHkAIAB0AGgAZQAgAHMAZQBjAG8AbgBkACAAKABBACAALwAgAEIAKQAuACAAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAGQAaQB2AGkAZABlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAHUAcwBlAF8AZgBsAG8AbwByAF0AIABPAHAAdABpAG8AbgBhAGwAIABiAG8AbwBsAGUAYQBuAC4AIABUAFIAVQBFACAAZgBvAHIAIABQAHkAdABoAG8AbgAtAHMAdAB5AGwAZQAgAEYAbABvAG8AcgAgAGQAaQB2AGkAcwBpAG8AbgAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAARgBBAEwAUwBFAC4AXABuACAAKgAvAFwAbgBEAGkAdgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABiAGkAZwBfAGkAbgB0AF8AYgAsACAAWwB1AHMAZQBfAGYAbABvAG8AcgBdACwAXABuACAAIAAgACAASQBOAEQARQBYACgARABpAHYATQBvAGQAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALAAgAHUAcwBlAF8AZgBsAG8AbwByACkALAAgADEALAAgADEAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEMAbwBtAHAAdQB0AGUAcwAgAHQAaABlACAAcgBlAG0AYQBpAG4AZABlAHIAIABvAGYAIABBACAALwAgAEIALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAdQBzAGUAXwBmAGwAbwBvAHIAXQAgAE8AcAB0AGkAbwBuAGEAbAAgAGIAbwBvAGwAZQBhAG4ALgAgAFQAUgBVAEUAIABmAG8AcgAgAFAAeQB0AGgAbwBuAC0AcwB0AHkAbABlACAATQBvAGQAdQBsAG8ALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAEYAQQBMAFMARQAuAFwAbgAgACoALwBcAG4ATQBvAGQAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALAAgAFsAdQBzAGUAXwBmAGwAbwBvAHIAXQAsAFwAbgAgACAAIAAgAEkATgBEAEUAWAAoAEQAaQB2AE0AbwBkACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAIAB1AHMAZQBfAGYAbABvAG8AcgApACwAIAAyACwAIAAxACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgB0AGUAcwB0AF8AQgBpAGcASQBuAHQALgBLAG4AdQB0AGgARABpAHYAaQBzAGkAbwBuACIALAAiAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4ARABpAHYAaQBzAGkAbwBuACIALAAiAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACIALAAiAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBDAG8AbQBwAGEAcgBpAHMAbwBuACIALAAiAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAuAEQAaQB2AGkAcwBpAG8AbgBCAGUAbgBjAGgAbQBhAHIAawBDAGEAcwBlAHMAIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4AQQBzAHkAbQBtAGUAdAByAGkAYwBBAEIARwByAGkAZAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBDAGEAcgByAHkAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBDAG8AbQBwAGEAcgBlACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQQBkAGQAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBTAHUAYgAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AYQB0AHIAaQB4AFMAdQBtACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEEAZABkAFMAdQBiAFIAbwB1AHQAZQByACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBLAG4AdQB0AGgARABpAHYAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ARABpAHYAUgBvAHUAdABlAHIAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBTAGUAZQBkACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4AUgBlAGMAaQBwAHIAbwBjAGEAbAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2ACIALAAiAEIAaQBnAEkAbgB0AC4ATgBvAHIAbQAiACwAIgBCAGkAZwBJAG4AdAAuAFMAaQBnAG4AIgAsACIAQgBpAGcASQBuAHQALgBJAHMAWgBlAHIAbwAiACwAIgBCAGkAZwBJAG4AdAAuAEkAcwBOAGUAZwAiACwAIgBCAGkAZwBJAG4AdAAuAEEAYgBzACIALAAiAEIAaQBnAEkAbgB0AC4AQwBvAG0AcABhAHIAZQAiACwAIgBCAGkAZwBJAG4AdAAuAEEAZABkACIALAAiAEIAaQBnAEkAbgB0AC4AUwB1AGIAIgAsACIAQgBpAGcASQBuAHQALgBTAHUAbQAiACwAIgBCAGkAZwBJAG4AdAAuAE0AdQBsACIALAAiAEIAaQBnAEkAbgB0AC4AUgBhAG4AZABCAGkAZwBJAG4AdABBAHIAcgBhAHkAIgAsACIAQgBpAGcASQBuAHQALgBEAGkAdgBNAG8AZAAiACwAIgBCAGkAZwBJAG4AdAAuAEQAaQB2ACIALAAiAEIAaQBnAEkAbgB0AC4ATQBvAGQAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAFwAbgAvAC8AIABCAGkAZwAgAEkAbgB0AGUAZwBlAHIAIABBAHIAaQB0AGgAbQBlAHQAaQBjACAATABpAGIAcgBhAHIAeQAgAC8ALwBcAG4ALwAvACAAIAAgACAAIAAgACAAdABlAHMAdABfAEIAaQBnAEkAbgB0ACAATQBvAGQAdQBsAGUAIAAgACAAIAAgACAAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIAAgAFAAcgBpAHYAYQB0AGUAIABUAGUAcwB0AGkAbgBnACAAQQBQAEkAIAAgACAAIAAgACAALwAvAFwAbgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4AXABuAEsAbgB1AHQAaABEAGkAdgBpAHMAaQBvAG4APQBMAEEATQBCAEQAQQAoAGEALAAgAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2ACgAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYQAsACAAawApACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABiACwAIABrACkALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAEQAUgBPAFAAKABwAGEAYwBrAGUAZAAsACAASQBOAEQARQBYACgAcABhAGMAawBlAGQALAAgADEALAAgADEAKQAgACsAIAAxACkALAAgAGsAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAgAD0AIABMAEEATQBCAEQAQQAoAGEALAAgAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgAoAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAGEALAAgAGsAKQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYgAsACAAawApACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABEAFIATwBQACgAcABhAGMAawBlAGQALAAgAEkATgBEAEUAWAAoAHAAYQBjAGsAZQBkACwAIAAxACwAIAAxACkAIAArACAAMQApACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAcwB0AHIAaQBuAGcAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAHMAdAByAGkAbgBnAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG0AbwBkAGUAIABcACIASwBOAFUAVABIAFwAIgAgAG8AcgAgAFwAIgBOAFIAXAAiAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGkAdABlAHIAcwAgAEkAbgBuAGUAcgAgAGwAbwBvAHAAIABjAG8AdQBuAHQAIAAoAHQAbwAgAGQAZQBmAGUAYQB0ACAAYwBoAHUAbgBrAHkAIABjAGwAbwBjAGsAIAByAGUAcwBvAGwAdQB0AGkAbwBuACkAXABuACAAKgAgAEAAcABhAHIAYQBtACAAcgBlAHAAZQBhAHQAcwAgAE8AdQB0AGUAcgAgAGwAbwBvAHAAIABjAG8AdQBuAHQAIAAoAHQAbwAgAGQAZQBmAGUAYQB0ACAATwBTAC8ARwBhAHIAYgBhAGcAZQAgAEMAbwBsAGwAZQBjAHQAaQBvAG4AIABuAG8AaQBzAGUAKQBcAG4AIAAqAC8AXABuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACAAPQAgAEwAQQBNAEIARABBACgAYQAsACAAYgAsACAAbQBvAGQAZQAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAE0AYQBwACAAdABoAGUAIABvAHUAdABlAHIAIAByAGUAcABlAGEAdABzACAAbABvAG8AcABcAG4AIAAgACAAIAAgACAAIAAgAGIAYQB0AGMAaABfAHQAaQBtAGUAcwAsACAATQBBAFAAKABTAEUAUQBVAEUATgBDAEUAKAByAGUAcABlAGEAdABzACkALAAgAEwAQQBNAEIARABBACgAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdAAsACAATgBPAFcAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATQBhAHAAIAB0AGgAZQAgAGkAbgBuAGUAcgAgAGUAeABlAGMAdQB0AGkAbwBuACAAbABvAG8AcABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAHUAbgAsACAASQBGACgAbQBvAGQAZQAgAD0AIABcACIASwBOAFUAVABIAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBQACgAUwBFAFEAVQBFAE4AQwBFACgAaQB0AGUAcgBzACkALAAgAEwAQQBNAEIARABBACgAaQAsACAASwBuAHUAdABoAEQAaQB2AGkAcwBpAG8AbgAoAGEALAAgAGIAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFAAKABTAEUAUQBVAEUATgBDAEUAKABpAHQAZQByAHMAKQAsACAATABBAE0AQgBEAEEAKABpACwAIABOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAoAGEALAAgAGIAKQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEYAbwByAGMAZQAgAGUAdgBhAGwAdQBhAHQAaQBvAG4AIABiAGUAZgBvAHIAZQAgAHAAdQBsAGwAaQBuAGcAIABzAHQAbwBwACAAdABpAG0AZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAbwBwACwAIABOAE8AVwAoACkAIAArACAAKAAwACAAKgAgAEwARQBOACgASQBOAEQARQBYACgAcgB1AG4ALAAgADEALAAgADEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABUAG8AdABhAGwAIABiAGEAdABjAGgAIAB0AGkAbQBlACAAaQBuACAAbQBpAGwAbABpAHMAZQBjAG8AbgBkAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABzAHQAbwBwACAALQAgAHMAdABhAHIAdAApACAAKgAgADgANgA0ADAAMAAwADAAMABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAdABoAGUAIABjAGwAZQBhAG4AZQBzAHQAIAByAHUAbgAgAGEAbgBkACAAYQB2AGUAcgBhAGcAZQAgAGkAdAAgAGQAbwB3AG4AIAB0AG8AIABhACAAcwBpAG4AZwBsAGUAIABlAHgAZQBjAHUAdABpAG8AbgAgAHQAaQBtAGUAXABuACAAIAAgACAAIAAgACAAIABNAEkATgAoAGIAYQB0AGMAaABfAHQAaQBtAGUAcwApACAALwAgAGkAdABlAHIAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAARQB4AGUAYwB1AHQAZQBzACAAYQAgAHMAdAByAGkAYwB0AGwAeQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABiAGUAbgBjAGgAbQBhAHIAawAgAHMAdQBpAHQAZQAgAHQAbwAgAGEAdgBvAGkAZAAgAG0AdQBsAHQAaQAtAHQAaAByAGUAYQBkAGkAbgBnACAAYwBvAG4AdABhAG0AaQBuAGEAdABpAG8AbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHQAZQBzAHQAXwBjAGEAcwBlAHMAIABBAG4AIABOACAAeAAgADIAIABhAHIAcgBhAHkAIABvAGYAIAB0AGUAcwB0ACAAbABlAG4AZwB0AGgAcwA6ACAAWwBMAGUAbgBnAHQAaABfAEEALAAgAEwAZQBuAGcAdABoAF8AQgBdAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGkAdABlAHIAcwAgAE4AdQBtAGIAZQByACAAbwBmACAAaQB0AGUAcgBhAHQAaQBvAG4AcwAgAHAAZQByACAAYgBlAG4AYwBoAG0AYQByAGsAIAB0AG8AIABzAG0AbwBvAHQAaAAgAE4ATwBXACgAKQAgAHIAZQBzAG8AbAB1AHQAaQBvAG4ALgBcAG4AIAAqAC8AXABuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBDAG8AbQBwAGEAcgBpAHMAbwBuACAAPQAgAEwAQQBNAEIARABBACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwB0AGUAcwB0AHMALAAgAFIATwBXAFMAKAB0AGUAcwB0AF8AYwBhAHMAZQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAASQBuAGkAdABpAGEAbAAgAHMAdABhAHQAZQA6ACAARABhAHQAYQAgAGgAZQBhAGQAZQByAHMAIABmAG8AcgAgAEMAUwBWACAAZQB4AHAAbwByAHQAXABuACAAIAAgACAAIAAgACAAIABpAG4AaQB0AGkAYQBsACwAIAB7AFwAIgBMAGUAbgBfAEEAXAAiACwAIABcACIATABlAG4AXwBCAFwAIgAsACAAXAAiAEsAbgB1AHQAaABfAG0AcwBcACIALAAgAFwAIgBOAFIAXwBtAHMAXAAiAH0ALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsACwAIABTAEUAUQBVAEUATgBDAEUAKABuAF8AdABlAHMAdABzACkALAAgAEwAQQBNAEIARABBACgAYQBjAGMALAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAEkATgBEAEUAWAAoAHQAZQBzAHQAXwBjAGEAcwBlAHMALAAgAGkALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAASQBOAEQARQBYACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBrAGkAcAAgAEQAaQB2AGkAcwBvAHIAIAA+ACAARABpAHYAaQBkAGUAbgBkABQgaQB0ACcAcwAgAG4AZQB2AGUAcgAgAGEAbgAgAGkAbgB0AGUAZwBlAHIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbABlAG4AXwBiACAAPgAgAGwAZQBuAF8AYQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAYwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARwBlAG4AZQByAGEAdABlACAAZQB4AGEAYwB0AC0AbABlAG4AZwB0AGgAIAB0AGUAcwB0ACAAcwB0AHIAaQBuAGcAcwAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AHIAXwBhACwAIABSAEUAUABUACgAXAAiADkAXAAiACwAIABsAGUAbgBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAcgBfAGIALAAgAEkARgAoAGwAZQBuAF8AYgAgAD0AIAAxACwAIABcACIANwBcACIALAAgAFwAIgA3AFwAIgAgACYAIABSAEUAUABUACgAXAAiADMAXAAiACwAIABsAGUAbgBfAGIAIAAtACAAMQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeABlAGMAdQB0AGUAIABiAGUAbgBjAGgAbQBhAHIAawBzACAAcwB0AHIAaQBjAHQAbAB5ACAAbwBuAGUAIABhAGYAdABlAHIAIAB0AGgAZQAgAG8AdABoAGUAcgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABpAG0AZQBfAGsALAAgAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACgAcwB0AHIAXwBhACwAIABzAHQAcgBfAGIALAAgAFwAIgBLAE4AVQBUAEgAXAAiACwAIABpAHQAZQByAHMALAAgAHIAZQBwAGUAYQB0AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGkAbQBlAF8AbgByACwAIABEAGkAdgBpAHMAaQBvAG4AQQBsAGcAbwByAGkAdABoAG0AcwAoAHMAdAByAF8AYQAsACAAcwB0AHIAXwBiACwAIABcACIATgBSAFwAIgAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAcABwAGUAbgBkACAAdABoAGUAIAByAGUAcwB1AGwAdABzAC4AIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAGEAbABsAG8AYwBhAHQAaQBvAG4AIABkAGUAbABhAHkAIABvAGMAYwB1AHIAcwAgAGgAZQByAGUALAAgAHMAYQBmAGUAbAB5ACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAdABpAG0AZQBkACAAdwBpAG4AZABvAHcALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABhAGMAYwAsACAASABTAFQAQQBDAEsAKABsAGUAbgBfAGEALAAgAGwAZQBuAF8AYgAsACAAdABpAG0AZQBfAGsALAAgAHQAaQBtAGUAXwBuAHIAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgADIALQBjAG8AbAB1AG0AbgAgAGEAcgByAGEAeQAgAG8AZgAgAGUAdgBlAHIAeQAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgAgAG8AZgAgAGwAZQBuAGcAdABoAHMAXABuAEQAaQB2AGkAcwBpAG8AbgBCAGUAbgBjAGgAbQBhAHIAawBDAGEAcwBlAHMAIAA9ACAATABBAE0AQgBEAEEAKABzAHQAYQByAHQAXwBsAGUAbgAsACAAbQBhAHgAXwBsAGUAbgAsACAAcwB0AGUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQAsACAAUwBFAFEAVQBFAE4AQwBFACgAKABtAGEAeABfAGwAZQBuACAALQAgAHMAdABhAHIAdABfAGwAZQBuACkAIAAvACAAcwB0AGUAcAAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBsAGUAbgAsACAAcwB0AGUAcAApACwAXABuACAAIAAgACAAIAAgACAAIABuACwAIABSAE8AVwBTACgAcwBlAHEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDACsAKwAgAHMAdAB5AGwAZQAgAEMAYQByAHQAZQBzAGkAYQBuACAASgBvAGkAbgBcAG4AIAAgACAAIAAgACAAIAAgAGMAbwBsAF8AYQAsACAAVABPAEMATwBMACgASQBGACgAUwBFAFEAVQBFAE4AQwBFACgAMQAsACAAbgApACwAIABzAGUAcQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAGMAbwBsAF8AYgAsACAAVABPAEMATwBMACgASQBGACgAUwBFAFEAVQBFAE4AQwBFACgAbgAsACAAMQApACwAIABUAE8AUgBPAFcAKABzAGUAcQApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAGMAbwBsAF8AYQAsACAAYwBvAGwAXwBiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAvACAARwBlAG4AZQByAGEAdABlAHMAIABhACAAQwBhAHIAdABlAHMAaQBhAG4AIABnAHIAaQBkACAAZgByAG8AbQAgAHQAdwBvACAAaQBuAGQAZQBwAGUAbgBkAGUAbgB0ACAAcwBlAHEAdQBlAG4AYwBlAHMAXABuAEEAcwB5AG0AbQBlAHQAcgBpAGMAQQBCAEcAcgBpAGQAIAA9ACAATABBAE0AQgBEAEEAKABzAHQAYQByAHQAXwBhACwAIABtAGEAeABfAGEALAAgAHMAdABlAHAAXwBhACwAIABzAHQAYQByAHQAXwBiACwAIABtAGEAeABfAGIALAAgAHMAdABlAHAAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQBxAF8AYQAsACAAUwBFAFEAVQBFAE4AQwBFACgAKABtAGEAeABfAGEAIAAtACAAcwB0AGEAcgB0AF8AYQApACAALwAgAHMAdABlAHAAXwBhACAAKwAgADEALAAgADEALAAgAHMAdABhAHIAdABfAGEALAAgAHMAdABlAHAAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQBxAF8AYgAsACAAUwBFAFEAVQBFAE4AQwBFACgAKABtAGEAeABfAGIAIAAtACAAcwB0AGEAcgB0AF8AYgApACAALwAgAHMAdABlAHAAXwBiACAAKwAgADEALAAgADEALAAgAHMAdABhAHIAdABfAGIALAAgAHMAdABlAHAAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAbgBfAGEALAAgAFIATwBXAFMAKABzAGUAcQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBfAGIALAAgAFIATwBXAFMAKABzAGUAcQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABPAHIAdABoAG8AZwBvAG4AYQBsACAAYgByAG8AYQBkAGMAYQBzAHQAIAB1AHMAaQBuAGcAIABpAG4AZABlAHAAZQBuAGQAZQBuAHQAIABkAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgACAAIAAgACAAYwBvAGwAXwBhACwAIABUAE8AQwBPAEwAKABJAEYAKABTAEUAUQBVAEUATgBDAEUAKAAxACwAIABuAF8AYgApACwAIABzAGUAcQBfAGEAKQApACwAXABuACAAIAAgACAAIAAgACAAIABjAG8AbABfAGIALAAgAFQATwBDAE8ATAAoAEkARgAoAFMARQBRAFUARQBOAEMARQAoAG4AXwBhACkALAAgAFQATwBSAE8AVwAoAHMAZQBxAF8AYgApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAGMAbwBsAF8AYQAsACAAYwBvAGwAXwBiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBjAG8AcgBlAF8AQgBpAGcASQBuAHQAIgAsACIAdABlAHgAdAAiADoAIgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4ALwAvACAAQgBpAGcAIABJAG4AdABlAGcAZQByACAAQQByAGkAdABoAG0AZQB0AGkAYwAgAEwAaQBiAHIAYQByAHkAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQAIABNAG8AZAB1AGwAZQAgACAAIAAgACAAIAAgACAALwAvAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIABQAHIAaQB2AGEAdABlACAAQQBQAEkAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwBcAG4ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8AXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEMAbwBtAHAAdQB0AGUAcwAgAHQAaABlACAAbQBhAHgAaQBtAHUAbQAgAHMAYQBmAGUAIABiAGEAcwBlAC0AMQAwACAAbABpAG0AYgAgAHMAaQB6AGUAIAAoAGsAKQAgAHQAbwAgAGEAdgBvAGkAZAAgAEkARQBFAEUALQA3ADUANAAgAHAAcgBlAGMAaQBzAGkAbwBuACAAbABvAHMAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG8AcABlAHIAYQB0AGkAbwBuADoAIABcACIAQQBEAEQAXAAiACwAIABcACIATQBVAEwAXAAiACwAIABvAHIAIABcACIARABJAFYAXAAiAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAWwBtAGEAeABfAGkAdABlAG0AcwBdACAAQQBEAEQAOgAgAG4AdQBtAGIAZQByACAAbwBmACAAbwBwAGUAcgBhAG4AZABzAC4AIABNAFUATAA6ACAAcwBoAG8AcgB0AGUAcwB0ACAAcwB0AHIAaQBuAGcAIABkAGkAZwBpAHQAcwAgAGMAbwB1AG4AdAAuAFwAbgAgACoALwBcAG4AUwBhAGYAZQBLACAAPQAgAEwAQQBNAEIARABBACgAbwBwAGUAcgBhAHQAaQBvAG4ALAAgAFsAbQBhAHgAXwBpAHQAZQBtAHMAXQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABpAHQAZQBtAHMALAAgAEkARgAoAE8AUgAoAG0AYQB4AF8AaQB0AGUAbQBzACAAPQAgAFwAIgBcACIALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAbQBhAHgAXwBpAHQAZQBtAHMAKQApACwAIAAyACwAIABNAEEAWAAoADIALAAgAG0AYQB4AF8AaQB0AGUAbQBzACkAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVwBJAFQAQwBIACgAbwBwAGUAcgBhAHQAaQBvAG4ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEARABEAFwAIgAsACAAMQA1ACAALQAgAEwARQBOACgAaQB0AGUAbQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFUATABcACIALAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARQB2AGEAbAB1AGEAdABlACAAcABvAHMAcwBpAGIAbABlACAAawAgAHYAYQBsAHUAZQBzACAAZAB5AG4AYQBtAGkAYwBhAGwAbAB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAZQBzAHQAXwBrACwAIAB7ADcAOwAgADYAOwAgADUAOwAgADQAOwAgADMAOwAgADIAOwAgADEAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AbwB2AGUAcgBsAGEAcAAsACAAUgBPAFUATgBEAFUAUAAoAGkAdABlAG0AcwAgAC8AIAB0AGUAcwB0AF8AawAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIAB0AGgAZQAgAGEAYgBzAG8AbAB1AHQAZQAgAHAAZQBhAGsAIAB2AGEAbAB1AGUAIABpAG4AcwBpAGQAZQAgAHQAaABlACAAZQBuAGcAaQBuAGUAIAAoAEMAbwBuAHYAbwBsAHUAdABpAG8AbgAgACsAIABDAGEAcgByAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB1AG4AYwBhAHIAcgBpAGUAZABfAG0AYQB4ACwAIABtAGEAeABfAG8AdgBlAHIAbABhAHAAIAAqACAAKAAxADAAXgB0AGUAcwB0AF8AawAgAC0AIAAxACkAXgAyACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAHgAXwBjAGEAcgByAHkALAAgAEkATgBUACgAdQBuAGMAYQByAHIAaQBlAGQAXwBtAGEAeAAgAC8AIAAxADAAXgB0AGUAcwB0AF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABlAGEAawBfAHYAYQBsACwAIAB1AG4AYwBhAHIAcgBpAGUAZABfAG0AYQB4ACAAKwAgAG0AYQB4AF8AYwBhAHIAcgB5ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHQAdQByAG4AIAB0AGgAZQAgAG0AYQB4ACAAawAgADwAPQAgAEUAeABjAGUAbAAnAHMAIAAxADUALQBkAGkAZwBpAHQAIABjAGUAaQBsAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgARgBJAEwAVABFAFIAKAB0AGUAcwB0AF8AawAsACAAcABlAGEAawBfAHYAYQBsACAAPAA9ACAAKAAxADAAXgAxADUAIAAtACAAMQApACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQASQBWAFwAIgAsACAANwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAE4AQQBNAEUAPwBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AaQBmAGkAZQBkACAAUwBwAGwAaQB0AHQAZQByAC4AIABTAHAAbABpAHQAcwAgAGIAbwB0AGgAIABzAGMAYQBsAGEAcgBzACAAYQBuAGQAIABhAHIAcgBhAHkAcwAgAGkAbgB0AG8AIABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuACAAbABpAG0AYgBzAC4AXABuACAAKgAgAFUAcwBlAHMAIABNAEEAWAAoACkAIAB0AG8AIABnAHUAYQByAGEAbgB0AGUAZQAgAHMAYwBhAGwAYQByACAAaQBuAHAAdQB0AHMAIAB0AG8AIAB0AGgAZQAgAFMARQBRAFUARQBOAEMARQAgAGUAbgBnAGkAbgBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABzACAAVABoAGUAIABzAHQAcgBpAG4AZwAgAG8AcgAgAGEAcgByAGEAeQAgAG8AZgAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFMAcABsAGkAdAAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAcwAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABiAGkAZwBfAGkAbgB0AF8AcgBvAHcALAAgAFQATwBSAE8AVwAoAGIAaQBnAF8AaQBuAHQAcwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBnAHQAaABzACwAIABMAEUATgAoAGIAaQBnAF8AaQBuAHQAXwByAG8AdwApACwAXABuACAAIAAgACAAIAAgACAAIABtAGEAeABfAGwAZQBuACwAIABNAEEAWAAoAGwAZQBuAGcAdABoAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBsAGUAbgAsACAAUgBPAFUATgBEAFUAUAAoAG0AYQB4AF8AbABlAG4AIAAvACAAawAsACAAMAApACAAKgAgAGsALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAZABlAGQALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAHAAYQBkAF8AbABlAG4AIAAtACAAbABlAG4AZwB0AGgAcwApACAAJgAgAGIAaQBnAF8AaQBuAHQAXwByAG8AdwAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALAAgAFMARQBRAFUARQBOAEMARQAoAHAAYQBkAF8AbABlAG4AIAAvACAAawAsACAAMQAsACAAcABhAGQAXwBsAGUAbgAgAC0AIABrACAAKwAgADEALAAgAC0AawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC0ALQBNAEkARAAoAHAAYQBkAGQAZQBkACwAIABzAHQAYQByAHQAcwAsACAAawApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAQwBvAG4AYwBhAHQAZQBuAGEAdABlAHMAIABhAG4AIABhAHIAcgBhAHkAIABvAGYAIABuAHUAbQBlAHIAaQBjACAAbABpAG0AYgBzACAAaQBuAHQAbwAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnACwAIAB6AGUAcgBvAC0AcABhAGQAZABpAG4AZwAgAGEAbABsACAAYgB1AHQAIAB0AGgAZQAgAGYAaQByAHMAdAAgAGwAaQBtAGIALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAIABUAGgAZQAgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAG4AdQBtAGUAcgBpAGMAIABsAGkAbQBiAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABsAGkAbQBiACAAcwBpAHoAZQAgAHUAcwBlAGQAIABkAHUAcgBpAG4AZwAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAuAFwAbgAgACoALwBcAG4ATQBlAHIAZwBlACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AdQBtAF8AbABpAG0AYgBzACwAIABSAE8AVwBTACgAbABpAG0AYgBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQB2AF8AbABpAG0AYgBzACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAbABpAG0AYgBzACwAIABTAEUAUQBVAEUATgBDAEUAKABuAHUAbQBfAGwAaQBtAGIAcwAsACAAMQAsACAAbgB1AG0AXwBsAGkAbQBiAHMALAAgAC0AMQApACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AdQBtAF8AbABpAG0AYgBzACAAPQAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHYAXwBsAGkAbQBiAHMAIAAmACAAXAAiAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATgBDAEEAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAcgBlAHYAXwBsAGkAbQBiAHMALAAgADEAKQAgACYAIABcACIAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEUAWABUACgARABSAE8AUAAoAHIAZQB2AF8AbABpAG0AYgBzACwAIAAxACkALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAGsAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAUgBlAHMAbwBsAHYAZQBzACAAYwBhAHIAcgBpAGUAcwAgAHIAaQBnAGgAdAAtAHQAbwAtAGwAZQBmAHQAIABhAGMAcgBvAHMAcwAgAGEAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkAIABvAGYAIABiAGEAcwBlAC0AMQAwAF4AawAgAGwAaQBtAGIAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwAgAFQAaABlACAAYQByAHIAYQB5ACAAbwBmACAAbgB1AG0AZQByAGkAYwAgAGwAaQBtAGIAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGwAaQBtAGIAIABzAGkAegBlAC4AXABuACAAKgAvAFwAbgBDAGEAcgByAHkAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwApACwAXABuACAAIAAgACAAIAAgACAAIABiAGEAcwBlACwAIAAxADAAXgBrACwAXABuACAAIAAgACAAIAAgACAAIABzAGMAYQBuAG4AZQBkACwAIABTAEMAQQBOACgAMAAsACAAbABpAG0AYgBzACwAIABMAEEATQBCAEQAQQAoAGEAYwBjACwAIAB2AGEAbAAsACAAdgBhAGwAIAArACAASQBOAFQAKABhAGMAYwAgAC8AIABiAGEAcwBlACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAByAGUAbQBhAGkAbgBkAGUAcgBzACwAIABNAE8ARAAoAHMAYwBhAG4AbgBlAGQALAAgAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AYwBhAHIAcgB5ACwAIABJAE4AVAAoAEkATgBEAEUAWAAoAHMAYwBhAG4AbgBlAGQALAAgAG4ALAAgADEAKQAgAC8AIABiAGEAcwBlACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABmAGkAbgBhAGwAXwBjAGEAcgByAHkAIAA+ACAAMAAsACAAVgBTAFQAQQBDAEsAKAByAGUAbQBhAGkAbgBkAGUAcgBzACwAIABmAGkAbgBhAGwAXwBjAGEAcgByAHkAKQAsACAAcgBlAG0AYQBpAG4AZABlAHIAcwApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAC0ALQAtACAAVQBuAHMAaQBnAG4AZQBkACAASwBlAHIAbgBlAGwAcwAgAC0ALQAtACAAXABcAFwAXABcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAVQBuAHMAaQBnAG4AZQBkACAAYwBvAG0AcABhAHIAaQBzAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAMQAgACgAYQAgAD4AIABiACkALAAgAC0AMQAgACgAYQAgADwAIABiACkALAAgAG8AcgAgADAAIAAoAGEAIAA9ACAAYgApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAIABUAGgAZQAgAHMAZQBjAG8AbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoALwBcAG4AVQBDAG8AbQBwAGEAcgBlACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAeABfAHIAbwB3AHMALAAgAE0AQQBYACgAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEAKQAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAZABfAGEALAAgAEUAWABQAEEATgBEACgAbABpAG0AYgBzAF8AYQAsACAAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAYQBkAF8AYgAsACAARQBYAFAAQQBOAEQAKABsAGkAbQBiAHMAXwBiACwAIABtAGEAeABfAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABkAGkAZgBmACwAIABwAGEAZABfAGEAIAAtACAAcABhAGQAXwBiACwAXABuACAAIAAgACAAIAAgACAAIABtAHMAZABfAGkAZAB4ACwAIABYAE0AQQBUAEMASAAoAFQAUgBVAEUALAAgAGQAaQBmAGYAIAA8AD4AIAAwACwAIAAwACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATgBBACgAbQBzAGQAXwBpAGQAeAApACwAIAAwACwAIABTAEkARwBOACgASQBOAEQARQBYACgAZABpAGYAZgAsACAAbQBzAGQAXwBpAGQAeAAsACAAMQApACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAGEAZABkAGkAdABpAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFUAQQBkAGQAIAA9ACAATABBAE0AQgBEAEEAKABhACwAIABiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AcgBvAHcAcwAsACAATQBBAFgAKABSAE8AVwBTACgAYQApACwAIABSAE8AVwBTACgAYgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAYQBkAF8AYQAsACAARQBYAFAAQQBOAEQAKABhACwAIABtAGEAeABfAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBiACwAIABFAFgAUABBAE4ARAAoAGIALAAgAG0AYQB4AF8AcgBvAHcAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHAAYQBkAF8AYQAgACsAIABwAGEAZABfAGIALAAgAGsAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAHMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABBAHMAcwB1AG0AZQBzACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAgAEEAIAA+AD0AIABCAC4AIABSAGUAcwBvAGwAdgBlAHMAIABiAG8AcgByAG8AdwBzACAAdABvAHAALQB0AG8ALQBiAG8AdAB0AG8AbQAgAGEAbgBkACAAdAByAGkAbQBzACAAdAByAGEAaQBsAGkAbgBnACAAegBlAHIAbwBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAbQBpAG4AdQBlAG4AZAAgAGwAaQBtAGIAIABhAHIAcgBhAHkAIAAoAG0AdQBzAHQAIABiAGUAIAA+AD0AIABsAGkAbQBiAHMAXwBiACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABzAHUAYgB0AHIAYQBoAGUAbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AVQBTAHUAYgAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwByAG8AdwBzACwAIABNAEEAWAAoAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBhACwAIABFAFgAUABBAE4ARAAoAGwAaQBtAGIAcwBfAGEALAAgAG0AYQB4AF8AcgBvAHcAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAZABfAGIALAAgAEUAWABQAEEATgBEACgAbABpAG0AYgBzAF8AYgAsACAAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAZABpAGYAZgAsACAAcABhAGQAXwBhACAALQAgAHAAYQBkAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBlAHMAbwBsAHYAZQBkACwAIABDAGEAcgByAHkAKABkAGkAZgBmACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAbQBzAGQAXwBpAGQAeAAsACAAWABNAEEAVABDAEgAKABUAFIAVQBFACwAIAByAGUAcwBvAGwAdgBlAGQAIAA8AD4AIAAwACwAIAAwACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATgBBACgAbQBzAGQAXwBpAGQAeAApACwAIAB7ADAAfQAsACAAVABBAEsARQAoAHIAZQBzAG8AbAB2AGUAZAAsACAAbQBzAGQAXwBpAGQAeAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABWAGUAYwB0AG8AcgBpAHoAZQBkACAAbQBhAHQAcgBpAHgAIABzAHUAbQAgAG8AZgAgAHUAbgBzAGkAZwBuAGUAZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHUAYgBpAGcAXwBpAG4AdAAgAEgAbwByAGkAegBvAG4AdABhAGwAIABhAHIAcgBhAHkAIAAoADEAeABOACkAIABvAGYAIABuAG8AcgBtAGEAbABpAHoAZQBkACAAbQBhAGcAbgBpAHQAdQBkAGUAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAdQBuAGkAZgBpAGUAZAAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AVQBNAGEAdAByAGkAeABTAHUAbQAgAD0AIABMAEEATQBCAEQAQQAoAHUAYgBpAGcAXwBpAG4AdABzACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAGcAcgBpAGQALAAgAFMAcABsAGkAdAAoAHUAYgBpAGcAXwBpAG4AdABzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAYQB3AF8AbABpAG0AYgBzACwAIABCAFkAUgBPAFcAKABnAHIAaQBkACwAIABTAFUATQApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHIAYQB3AF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABSAG8AdQB0AGUAcwAgAGEAZABkAGkAdABpAG8AbgAvAHMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAGIAYQBzAGUAZAAgAG8AbgAgAHMAaQBnAG4AcwAgAGEAbgBkACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAuAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAYQAgAHQAdQBwAGwAZQAgAGEAcgByAGEAeQA6ACAAVgBTAFQAQQBDAEsAKABsAGkAbQBiAHMALAAgAGYAaQBuAGEAbABfAHMAaQBnAG4AKQAgAHcAaABlAHIAZQAgAHQAaABlACAAZgBpAG4AYQBsACAAcgBvAHcAIABpAHMAIAB0AGgAZQAgAHMAYwBhAGwAYQByACAAcwBpAGcAbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAcwBlAGMAbwBuAGQAIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHMAaQBnAG4AXwBhACAAVABoAGUAIABzAGkAZwBuACAAbwBmACAAdABoAGUAIABmAGkAcgBzAHQAIABhAHIAcgBhAHkAIAAoADEALAAgAC0AMQAsACAAMAApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAcwBpAGcAbgBfAGIAIABUAGgAZQAgAHMAaQBnAG4AIABvAGYAIAB0AGgAZQAgAHMAZQBjAG8AbgBkACAAYQByAHIAYQB5ACAAKAAxACwAIAAtADEALAAgADAAKQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AQQBkAGQAUwB1AGIAUgBvAHUAdABlAHIAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABzAGkAZwBuAF8AYQAsACAAcwBpAGcAbgBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AcwBhAG0AZQBfAHMAaQBnAG4ALAAgAHMAaQBnAG4AXwBhACAAPQAgAHMAaQBnAG4AXwBiACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGkAcwBfAHMAYQBtAGUAXwBzAGkAZwBuACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAZABkAGkAdABpAG8AbgA6ACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAgAGMAbwBtAGIAaQBuAGUALAAgAHMAaQBnAG4AIAByAGUAbQBhAGkAbgBzACAAdABoAGUAIABzAGEAbQBlAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVQBBAGQAZAAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsACAAcwBpAGcAbgBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwB1AGIAdAByAGEAYwB0AGkAbwBuADoAIABlAHYAYQBsAHUAYQB0AGUAIABtAGEAZwBuAGkAdAB1AGQAZQBzACAAdABvACAAcwBhAHQAaQBzAGYAeQAgAFUAUwB1AGIAIAAoAEEAIAA+AD0AIABCACkAIABwAHIAZQBjAG8AbgBkAGkAdABpAG8AbgAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcAAsACAAVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFQAbwB0AGEAbAAgAGMAYQBuAGMAZQBsAGwAYQB0AGkAbwBuADoAIAByAGUAdAB1AHIAbgAgAHsAMAB9ACAAbABpAG0AYgAgAGEAbgBkACAAMAAgAHMAaQBnAG4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAMAA7ADAAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAGEAZwBfAGMAbwBtAHAAIAA+ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABBACAAaQBzACAAbABhAHIAZwBlAHIAOgAgAHMAaQBnAG4AIABiAGUAbABvAG4AZwBzACAAdABvACAAQQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFUAUwB1AGIAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALAAgAHMAaQBnAG4AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEIAIABpAHMAIABsAGEAcgBnAGUAcgA6ACAAcgBvAHUAdABlACAAQgAgAGYAaQByAHMAdAAsACAAcwBpAGcAbgAgAGIAZQBsAG8AbgBnAHMAIAB0AG8AIABCAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVQBTAHUAYgAoAGwAaQBtAGIAcwBfAGIALAAgAGwAaQBtAGIAcwBfAGEALAAgAGsAKQAsACAAcwBpAGcAbgBfAGIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AcwBpAGcAbgBlAGQAIABtAHUAbAB0AGkAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIAB0AHcAbwAgAEwAaQB0AHQAbABlAC0ARQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5AHMALgBcAG4AIAAqACAAVQB0AGkAbABpAHoAZQBzACAAYQAgADEARAAgAEQAaQBzAGMAcgBlAHQAZQAgAEMAbwBuAHYAbwBsAHUAdABpAG8AbgAgACgAQwBhAHUAYwBoAHkAIABQAHIAbwBkAHUAYwB0ACkAIABhAHIAcgBhAHkALQBzAGwAaQBjAGkAbgBnACAAcwB0AHIAYQB0AGUAZwB5AC4AXABuACAAKgAgAFoAZQByAG8AIABkAHkAbgBhAG0AaQBjACAAbQBlAG0AbwByAHkAIAByAGUAYQBsAGwAbwBjAGEAdABpAG8AbgAuACAAJABPACgATgArAE0AKQAkACAAbQBlAG0AbwByAHkAIABmAG8AbwB0AHAAcgBpAG4AdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAG0AdQBsAHQAaQBwAGwAaQBjAGEAbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAIABUAGgAZQAgAG0AdQBsAHQAaQBwAGwAaQBlAHIAIABsAGkAbQBiACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBVAE0AdQBsACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwByAG8AdwBzACwAIABsAGUAbgBfAGEAIAArACAAbABlAG4AXwBiACAALQAgADEALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAATABvAG8AcAAgAHAAdQByAGUAbAB5ACAAbwB2AGUAcgAgAHQAaABlACAAbABlAG4AZwB0AGgAIABvAGYAIAB0AGgAZQAgAGYAaQBuAGEAbAAgAG8AdQB0AHAAdQB0ACAAYQByAHIAYQB5AFwAbgAgACAAIAAgACAAIAAgACAAcgBhAHcAXwBsAGkAbQBiAHMALAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIABMAEEATQBCAEQAQQAoAHIALAAgAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAbABjAHUAbABhAHQAZQAgAHQAaABlACAAdgBhAGwAaQBkACAAbwB2AGUAcgBsAGEAcABwAGkAbgBnACAAdwBpAG4AZABvAHcAIABvAGYAIABpAG4AZABpAGMAZQBzACAAZgBvAHIAIAB0AGgAaQBzACAAbQBhAGcAbgBpAHQAdQBkAGUAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AF8AaQAsACAATQBBAFgAKAAxACwAIAByACAALQAgAGwAZQBuAF8AYgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAG4AZABfAGkALAAgAE0ASQBOACgAcgAsACAAbABlAG4AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AdQBuAHQALAAgAGUAbgBkAF8AaQAgAC0AIABzAHQAYQByAHQAXwBpACAAKwAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGUAcQB1AGUAbgBjAGUAIABpACAAYwBvAHUAbgB0AHMAIABVAFAALgAgAFMAZQBxAHUAZQBuAGMAZQAgAGoAIABjAG8AdQBuAHQAcwAgAEQATwBXAE4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGkALAAgAFMARQBRAFUARQBOAEMARQAoAGMAbwB1AG4AdAAsACAAMQAsACAAcwB0AGEAcgB0AF8AaQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBlAHEAXwBqACwAIABTAEUAUQBVAEUATgBDAEUAKABjAG8AdQBuAHQALAAgADEALAAgAHIAIAAtACAAcwB0AGEAcgB0AF8AaQAgACsAIAAxACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAbABpAGMAZQAgAHQAaABlACAAZQB4AGEAYwB0ACAAaQBuAHQAZQByAHMAZQBjAHQAaQBuAGcAIABsAGkAbQBiAHMALAAgAG0AdQBsAHQAaQBwAGwAeQAsACAAYQBuAGQAIABzAHUAbQAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUATQAoAEkATgBEAEUAWAAoAGwAaQBtAGIAcwBfAGEALAAgAHMAZQBxAF8AaQAsACAAMQApACAAKgAgAEkATgBEAEUAWAAoAGwAaQBtAGIAcwBfAGIALAAgAHMAZQBxAF8AagAsACAAMQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHMAbwBsAHYAZQAgAGEAbABsACAAYwBhAHIAcgBpAGUAcwAgAGIAbwB0AHQAbwBtAC0AdABvAC0AdABvAHAAIABlAHgAYQBjAHQAbAB5ACAAbwBuAGMAZQBcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHIAYQB3AF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABCAGkAbgBhAHIAeQAgAHMAZQBhAHIAYwBoACAAdABvACAAZgBpAG4AZAAgAHQAaABlACAAaABpAGcAaABlAHMAdAAgAHMAYwBhAGwAYQByACAAcQB1AG8AdABpAGUAbgB0ACAAbABpAG0AYgAgAHEAIAAoADAAIAA8AD0AIABxACAAPAAgADEAMABeAGsAKQBcAG4AoAAqACAAcwB1AGMAaAAgAHQAaABhAHQAIABCACAAKgAgAHEAIAA8AD0AIABhAGMAYwAuACAARQBsAGkAbQBpAG4AYQB0AGUAcwAgAHQAaABlACAAbgBlAGUAZAAgAGYAbwByACAASwBuAHUAdABoACAARAAgAGYAbABvAGEAdAAtAGUAcwB0AGkAbQBhAHQAaQBvAG4ALgBcAG4AoAAqACAAQABwAGEAcgBhAG0AIABhAGMAYwAgAFQAaABlACAAYwB1AHIAcgBlAG4AdAAgAHIAZQBtAGEAaQBuAGQAZQByACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAuAFwAbgCgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgCgACoALwBcAG4ARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAgAD0AIABMAEEATQBCAEQAQQAoAGEAYwBjACwAIABiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAYQBsAGMAdQBsAGEAdABlACAAcgBlAHEAdQBpAHIAZQBkACAAYgBpAHQAcwAgAGQAeQBuAGEAbQBpAGMAYQBsAGwAeQAuACAARgBvAHIAIABtAGEAeAAgAGsAPQA3ACwAIAB0AGgAaQBzACAAZQB2AGEAbAB1AGEAdABlAHMAIAB0AG8AIAAyADQAIABiAGkAdABzAC4AXABuACAAIAAgACAAIAAgACAAIABiAGkAdABzACwAIABDAEUASQBMAEkATgBHAC4ATQBBAFQASAAoAEwATwBHACgAMQAwAF4AawAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAbwB3AGUAcgBzACwAIAAyACAAXgAgAFMARQBRAFUARQBOAEMARQAoAGIAaQB0AHMALAAgADEALAAgAGIAaQB0AHMAIAAtACAAMQAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAUgBFAEQAVQBDAEUAKAAwACwAIABwAG8AdwBlAHIAcwAsACAATABBAE0AQgBEAEEAKABjAHUAcgByAF8AcQAsACAAcABvAHcAZQByACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABlAHMAdABfAHEALAAgAGMAdQByAHIAXwBxACAAKwAgAHAAbwB3AGUAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAawBpAHAAIABpAGYAIAB0AGUAcwB0AF8AcQAgAGUAeABjAGUAZQBkAHMAIAB0AGgAZQAgAGwAaQBtAGIAIABiAGEAcwBlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHQAZQBzAHQAXwBxACAAPgA9ACAAMQAwAF4AawAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATQB1AGwAdABpAHAAbAB5ACAAQgAgAGIAeQAgAHMAYwBhAGwAYQByACAAdABlAHMAdABfAHEAIABhAG4AZAAgAHIAZQBzAG8AbAB2AGUAIABjAGEAcgByAGkAZQBzACAAbgBhAHQAaQB2AGUAbAB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGUAcwB0AF8AcAByAG8AZAAsACAAQwBhAHIAcgB5ACgAYgAgACoAIAB0AGUAcwB0AF8AcQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAFUAQwBvAG0AcABhAHIAZQAoAGEAYwBjACwAIAB0AGUAcwB0AF8AcAByAG8AZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABjAG8AbQBwACAAPgA9ACAAMAAsACAAdABlAHMAdABfAHEALAAgAGMAdQByAHIAXwBxACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABCAGEAcwBlAGMAYQBzAGUAIABEAGkAdgBpAHMAaQBvAG4AIAB2AGkAYQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABzAGgAaQBmAHQALQBhAG4AZAAtAHMAdQBiAHQAcgBhAGMAdAAuAFwAbgCgACoAIABSAGUAdAB1AHIAbgBzACAAYQAgAHAAYQBjAGsAZQBkACAAMQBEACAAYQByAHIAYQB5ADoAIABWAFMAVABBAEMASwAoAEwAZQBuAGcAdABoAF8AUgAsACAAUgBfAGwAaQBtAGIAcwAsACAAUQBfAGwAaQBtAGIAcwApAC4AXABuAKAAKgAgAEUAbABpAG0AaQBuAGEAdABlAHMAIAAyAEQAIABhAHIAcgBhAHkAIABwAGEAZABkAGkAbgBnACAAdABvACAAcwB0AHIAaQBjAHQAbAB5ACAAcAByAGUAcwBlAHIAdgBlACAAbQBlAG0AbwByAHkAIABlAGYAZgBpAGMAaQBlAG4AYwB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAgACgAYQBzAHMAdQBtAGUAZAAgAG4AbwBuAC0AegBlAHIAbwApAC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuAKAAKgAvAFwAbgBLAG4AdQB0AGgARABpAHYAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcAAsACAAVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAIAByAG8AdQB0AGkAbgBnACAAdwBpAHQAaAAgAHQAaABlACAAbgBlAHcAIABwAGEAYwBrAGUAZAAgAG0AZQBtAG8AcgB5ACAAYwBvAG4AdAByAGEAYwB0AFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbABpAG0AYgBzAF8AYQApACwAIABsAGkAbQBiAHMAXwBhACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADEALAAgADAALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEkAdABlAHIAYQB0AGUAIABvAHYAZQByACAAQQAgAGYAcgBvAG0AIABNAFMAQgAgACgAdABvAHAAKQAgAHQAbwAgAEwAUwBCACAAKABiAG8AdAB0AG8AbQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHYAZQByAHMAZQBkAF8AYQAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEALAAgAFMARQBRAFUARQBOAEMARQAoAGwAZQBuAF8AYQAsACAAMQAsACAAbABlAG4AXwBhACwAIAAtADEAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAdABhAHQAZQAgAHMAZQBwAGEAcgBhAHQAbwByADoAIABWAFMAVABBAEMASwAoAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABxAHUAbwB0AGkAZQBuAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAbgBpAHQAaQBhAGwAXwBzAHQAYQB0AGUALAAgAFYAUwBUAEEAQwBLACgAMQAsACAAMAAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsAF8AcwB0AGEAdABlACwAIAByAGUAdgBlAHIAcwBlAGQAXwBhACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAdgBhAGwALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcwB0AGEAdABlACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHEAdQBvAHQAaQBlAG4AdAAsACAARABSAE8AUAAoAHMAdABhAHQAZQAsACAAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGgAaQBmAHQAIABhAGMAYwAgAHUAcAAgAGIAeQAgADEAIABsAGkAbQBiACAAKABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuADoAIABpAG4AcwBlAHIAdAAgAGEAdAAgAGkAbgBkAGUAeAAgADEAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAHgAdABlAG4AZABlAGQAXwByAGUAbQBhAGkAbgBkAGUAcgAsACAASQBGACgAQQBOAEQAKABSAE8AVwBTACgAcgBlAG0AYQBpAG4AZABlAHIAKQAgAD0AIAAxACwAIABJAE4ARABFAFgAKAByAGUAbQBhAGkAbgBkAGUAcgAsACAAMQAsACAAMQApACAAPQAgADAAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB2AGEAbAAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAHYAYQBsACwAIAByAGUAbQBhAGkAbgBkAGUAcgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgAsACAARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAoAGUAeAB0AGUAbgBkAGUAZABfAHIAZQBtAGEAaQBuAGQAZQByACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAHIAbwBkACwAIABDAGEAcgByAHkAKABsAGkAbQBiAHMAXwBiACAAKgAgAG4AZQB4AHQAXwBxAHUAbwB0AGkAZQBuAHQAXwBsAGkAbQBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAdwBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABVAFMAdQBiACgAZQB4AHQAZQBuAGQAZQBkAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHAAcgBvAGQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGgAYQBzAF8AcQB1AG8AdABpAGUAbgB0ACwAIABPAFIAKABSAE8AVwBTACgAcQB1AG8AdABpAGUAbgB0ACkAIAA+ACAAMQAsACAASQBOAEQARQBYACgAcQB1AG8AdABpAGUAbgB0ACwAMQAsADEAKQAgAD4AIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQB1AG8AdAAsACAASQBGACgAaABhAHMAXwBxAHUAbwB0AGkAZQBuAHQALAAgAFYAUwBUAEEAQwBLACgAcQB1AG8AdABpAGUAbgB0ACwAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgApACwAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbgBlAHcAXwByAGUAbQBhAGkAbgBkAGUAcgApACwAIABuAGUAdwBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABuAGUAeAB0AF8AcQB1AG8AdAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAEkATgBEAEUAWAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAbQBhAGkAbgBkAGUAcgAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAsACAAMQAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQB2AGUAcgBzAGUAZABfAHEAdQBvAHQAaQBlAG4AdAAsACAARABSAE8AUAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAcQB1AG8AdABfAHIAYQB3ACAAdwBhAHMAIABiAHUAaQBsAHQAIABNAFMAQgAgAHQAbwAgAEwAUwBCACAAKABCAGkAZwAtAEUAbgBkAGkAYQBuACkALgAgAFIAZQB2AGUAcgBzAGUAIAB0AG8AIABpAG4AdABlAHIAbgBhAGwAIABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHEAdQBvAHQAaQBlAG4AdAAsACAAUgBPAFcAUwAoAHIAZQB2AGUAcgBzAGUAZABfAHEAdQBvAHQAaQBlAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABxAHUAbwB0AGkAZQBuAHQALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKAByAGUAdgBlAHIAcwBlAGQAXwBxAHUAbwB0AGkAZQBuAHQALAAgAFMARQBRAFUARQBOAEMARQAoAGwAZQBuAF8AcQB1AG8AdABpAGUAbgB0ACwAIAAxACwAIABsAGUAbgBfAHEAdQBvAHQAaQBlAG4AdAAsACAALQAxACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABMAGUAYQBkAGkAbgBnAC8AdAByAGEAaQBsAGkAbgBnACAAegBlAHIAbwBzACAAYQByAGUAIABjAG8AbgB0AGkAbgB1AG8AdQBzAGwAeQAgAHIAZQBtAG8AdgBlAGQAIABpAG4AcwBpAGQAZQAgAHQAaABlACAAbABvAG8AcAAsACAAbgBvACAAbgBlAGUAZAAgAHQAbwAgAHIAZQBwAGUAYQB0ACAAaQB0AC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAcwB0AHIAaQBjAHQAbAB5ACAAcABhAGMAawBlAGQAIAAxAEQAIABhAHIAcgBhAHkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABxAHUAbwB0AGkAZQBuAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AoAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEgAeQBiAHIAaQBkACAARABpAHYAaQBzAGkAbwBuACAAUgBvAHUAdABlAHIALgBcAG4AoAAqACAARABpAHIAZQBjAHQAcwAgAGQAaQB2AGkAcwBpAG8AbgAgAHQAbwAgAHQAaABlACAAbwBwAHQAaQBtAGEAbAAgAGsAZQByAG4AZQBsACAAYgBhAHMAZQBkACAAbwBuACAARABpAHYAaQBkAGUAbgBkACAAbABlAG4AZwB0AGgALgBcAG4AoAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBhACAAVABoAGUAIABkAGkAdgBpAGQAZQBuAGQAIABhAHIAcgBhAHkALgBcAG4AoAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuAKAAKgAvAFwAbgBEAGkAdgBSAG8AdQB0AGUAcgAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARABpAGcAaQB0ACAAYwBvAHUAbgB0AHMAIABhAHIAZQAgAGEAcABwAHIAbwB4AGkAbQBhAHQAZQAsACAAYgB1AHQAIABzAHUAZgBmAGkAYwBpAGUAbgB0AFwAbgAgACAAIAAgACAAIAAgACAAZABpAGcAaQB0AHMAXwBhACwAIABSAE8AVwBTACgAbABpAG0AYgBzAF8AYQApACAAKgAgAGsALABcAG4AIAAgACAAIAAgACAAIAAgAGQAaQBnAGkAdABzAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAgACoAIABrACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAE0AYQBjAGgAaQBuAGUALQBsAGUAYQByAG4AZQBkACAAYwBvAGUAZgBmAGkAYwBpAGUAbgB0AHMAIABmAHIAbwBtACAATABvAGcAaQBzAHQAaQBjACAAUgBlAGcAcgBlAHMAcwBpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgAG0ALAAgADAALgAxADAANwA4ADIAMQAxADkANAAyADcAMQAyADkANwAsAFwAbgAgACAAIAAgACAAIAAgACAAYwAsACAALQAyADIAMQAuADkAMAAyADEAOAA5ADQANgAyADAANgA4ACwAXABuACAAIAAgACAAIAAgACAAIAB0AGgAcgBlAHMAaABvAGwAZAAsACAAKABtACAAKgAgAGQAaQBnAGkAdABzAF8AYQApACAAKwAgAGMALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAZABpAGcAaQB0AHMAXwBiACAAPAA9ACAAdABoAHIAZQBzAGgAbwBsAGQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASwBuAHUAdABoAEQAaQB2ACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4ARABpAHYAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAARwBlAG4AZQByAGEAdABlAHMAIAB0AGgAZQAgAGUAeABhAGMAdAAgAHIAZQBjAGkAcAByAG8AYwBhAGwAIABzAGUAZQBkACAAZgBvAHIAIABOAGUAdwB0AG8AbgAtAFIAYQBwAGgAcwBvAG4AIABEAGkAdgBpAHMAaQBvAG4AIAB1AHMAaQBuAGcAIABLAG4AdQB0AGgAIABCAGEAcwBlAGMAYQBzAGUALgBcAG4AIAAqACAARQB4AHQAcgBhAGMAdABzACAAdQBwACAAdABvACAAdABoAGUAIAB0AG8AcAAgADMAIABsAGkAbQBiAHMAIABvAGYAIABCACAAYQBuAGQAIABjAGEAbABjAHUAbABhAHQAZQBzACAAZgBsAG8AbwByACgAQgBlAHQAYQBeACgAMgAqAGwAZQBuACkAIAAvACAAQgBfAHQAbwBwACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBTAGUAZQBkACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYgAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGIALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQBlAGQAXwBsAGUAbgAsACAATQBJAE4AKAAzACwAIABsAGUAbgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAdABvAHAAIAAnAHMAZQBlAGQAXwBsAGUAbgAnACAAbABpAG0AYgBzACAAKABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuADoAIAB0AGEAawBlACAAZgByAG8AbQAgAHQAaABlACAAYgBvAHQAdABvAG0AKQBcAG4AIAAgACAAIAAgACAAIAAgAGIAXwB0AG8AcAAsACAAVABBAEsARQAoAGwAaQBtAGIAcwBfAGIALAAgAC0AcwBlAGUAZABfAGwAZQBuACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwBvAG4AcwB0AHIAdQBjAHQAIABCAGUAdABhAF4AKAAyACAAKgAgAHMAZQBlAGQAXwBsAGUAbgApACAAbgBhAHQAaQB2AGUAbAB5AFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAZQAuAGcALgAsACAAaQBmACAAcwBlAGUAZABfAGwAZQBuACAAPQAgADEALAAgAHQAaABlAG4AIAAxACAAZgBvAGwAbABvAHcAZQBkACAAYgB5ACAAdAB3AG8AIAB6AGUAcgBvACAAbABpAG0AYgBzADoAIABWAFMAVABBAEMASwAoADAALAAgADAALAAgADEAKQBcAG4AIAAgACAAIAAgACAAIAAgAGIAZQB0AGEAXwAyAG0ALAAgAFYAUwBUAEEAQwBLACgARQBYAFAAQQBOAEQAKAAwACwAIAAyACAAKgAgAHMAZQBlAGQAXwBsAGUAbgAsACAALAAgADAAKQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEsAbgB1AHQAaAAgAEQAaQB2AGkAcwBpAG8AbgAgAHkAaQBlAGwAZABzACAAZQB4AGEAYwB0ACAAaQBuAGkAdABpAGEAbAAgAHIAZQBjAGkAcAByAG8AYwBhAGwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAASwBuAHUAdABoAEQAaQB2ACgAYgBlAHQAYQBfADIAbQAsACAAYgBfAHQAbwBwACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAFEAdQBvAHQAaQBlAG4AdAAgAGEAcgByAGEAeQAgAGYAcgBvAG0AIAB0AGgAZQAgAHAAYQBjAGsAZQBkACAAVgBTAFQAQQBDAEsAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHIALAAgAEkATgBEAEUAWAAoAHAAYQBjAGsAZQBkACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABwAGEAYwBrAGUAZAAsACAAbABlAG4AXwByACAAKwAgADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEMAbwBtAHAAdQB0AGUAcwAgAHQAaABlACAAUgBlAGMAaQBwAHIAbwBjAGEAbAAgAHAAcgBvAGcAcgBlAHMAcwBpAHYAZQBsAHkAIABzAGMAYQBsAGkAbgBnACAAdQBwACAAdABvACAAdABoAGUAIABEAGkAdgBpAGQAZQBuAGQAJwBzACAAcAByAGUAYwBpAHMAaQBvAG4ALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHQAYQByAGcAZQB0AF8AbABlAG4AIABUAGgAZQAgAGwAaQBtAGIALQBsAGUAbgBnAHQAaAAgAG8AZgAgAEQAaQB2AGkAZABlAG4AZAAgAEEALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4AUgBlAGMAaQBwAHIAbwBjAGEAbAAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGIALAAgAHQAYQByAGcAZQB0AF8AbABlAG4ALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwBiACwAIABSAE8AVwBTACgAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAZQBkAF8AbABlAG4ALAAgAE0ASQBOACgAMwAsACAAbABlAG4AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAXwBzAGUAZQBkAF8AbABpAG0AYgBzACwAIABOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAFMAZQBlAGQAKABsAGkAbQBiAHMAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKABzAGUAZQBkAF8AbABlAG4ALAAgAHIAXwBzAGUAZQBkAF8AbABpAG0AYgBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQBxAF8AaQB0AGUAcgBzACwAIABNAEEAWAAoADAALAAgAEMARQBJAEwASQBOAEcALgBNAEEAVABIACgATABOACgAdABhAHIAZwBlAHQAXwBsAGUAbgAgAC8AIABzAGUAZQBkAF8AbABlAG4AKQAgAC8AIABMAE4AKAAyACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAHIAZQBxAF8AaQB0AGUAcgBzACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBfAHMAZQBlAGQAXwBsAGkAbQBiAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAHQAZQByAGEAdABpAG8AbgBzACwAIABTAEUAUQBVAEUATgBDAEUAKAByAGUAcQBfAGkAdABlAHIAcwApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcwB0AGEAdABlACwAIABSAEUARABVAEMARQAoAGkAbgBpAHQAaQBhAGwAXwBzAHQAYQB0AGUALAAgAGkAdABlAHIAYQB0AGkAbwBuAHMALAAgAEwAQQBNAEIARABBACgAcwB0AGEAdABlACwAIABpAHQAZQByACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AbABlAG4ALAAgAEkATgBEAEUAWAAoAHMAdABhAHQAZQAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwByACwAIABEAFIATwBQACgAcwB0AGEAdABlACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwBsAGUAbgAsACAATQBJAE4AKABjAHUAcgByAF8AbABlAG4AIAAqACAAMgAsACAAdABhAHIAZwBlAHQAXwBsAGUAbgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAaABpAGYAdABfAGwAaQBtAGIAcwAsACAAbgBlAHgAdABfAGwAZQBuACAALQAgAGMAdQByAHIAXwBsAGUAbgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBfAHAAcgBpAG0AZQAsACAASQBGACgAcwBoAGkAZgB0AF8AbABpAG0AYgBzACAAPgAgADAALAAgAFYAUwBUAEEAQwBLACgARQBYAFAAQQBOAEQAKAAwACwAIABzAGgAaQBmAHQAXwBsAGkAbQBiAHMALAAgACwAIAAwACkALAAgAGMAdQByAHIAXwByACkALAAgAGMAdQByAHIAXwByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAbABpAGMAZQAgAEIAIAB0AG8AIABpAHQAcwAgAG4AYQB0AHUAcgBhAGwAIABsAGkAbQBpAHQAcwAsACAAcABhAGQAZABpAG4AZwAgAHcAaQB0AGgAIAB6AGUAcgBvAHMAIABkAGUAcwB0AHIAbwB5AHMAIABwAGUAcgBmAG8AcgBtAGEAbgBjAGUALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYgBfAGEAYwB0AGkAdgBlACwAIABUAEEASwBFACgAbABpAG0AYgBzAF8AYgAsACAALQBNAEkATgAoAG4AZQB4AHQAXwBsAGUAbgAsACAAbABlAG4AXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATwAoAE4AKgBNACkAIABpAG4AcwB0AGUAYQBkACAAbwBmACAATwAoAE4AXgAyACkAIABmAG8AcgAgAFAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAXwByAGEAdwAsACAAVQBNAHUAbAAoAGIAXwBhAGMAdABpAHYAZQAsACAAcgBfAHAAcgBpAG0AZQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGgAaQBmAHQAaQBuAGcAIAB0AGgAZQAgAHIAZQBzAHUAbAB0ACAAYQByAHIAYQB5ACAAcgBlAHAAbABpAGMAYQB0AGUAcwAgAEIAZQB0AGEAIABtAHUAbAB0AGkAcABsAGkAYwBhAHQAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAaABpAGYAdABfAHAALAAgAE0AQQBYACgAMAAsACAAbgBlAHgAdABfAGwAZQBuACAALQAgAGwAZQBuAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAALAAgAEkARgAoAHMAaABpAGYAdABfAHAAIAA+ACAAMAAsACAAVgBTAFQAQQBDAEsAKABFAFgAUABBAE4ARAAoADAALAAgAHMAaABpAGYAdABfAHAALAAgACwAIAAwACkALAAgAHAAXwByAGEAdwApACwAIABwAF8AcgBhAHcAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdAB3AG8AXwBiAGUAdABhACwAIABWAFMAVABBAEMASwAoAEUAWABQAEEATgBEACgAMAAsACAAMgAgACoAIABuAGUAeAB0AF8AbABlAG4ALAAgACwAIAAwACkALAAgADIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAHIAcgAsACAAVQBTAHUAYgAoAHQAdwBvAF8AYgBlAHQAYQAsACAAcAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcgBfAHUAbgBzAGMAYQBsAGUAZAAsACAAVQBNAHUAbAAoAHIAXwBwAHIAaQBtAGUALAAgAGUAcgByACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBlAHgAdABfAHIALAAgAEkARgAoAFIATwBXAFMAKABuAGUAeAB0AF8AcgBfAHUAbgBzAGMAYQBsAGUAZAApACAAPAA9ACAAMgAgACoAIABuAGUAeAB0AF8AbABlAG4ALAAgAHsAMAB9ACwAIABEAFIATwBQACgAbgBlAHgAdABfAHIAXwB1AG4AcwBjAGEAbABlAGQALAAgADIAIAAqACAAbgBlAHgAdABfAGwAZQBuACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABuAGUAeAB0AF8AbABlAG4ALAAgAG4AZQB4AHQAXwByACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABmAGkAbgBhAGwAXwBzAHQAYQB0AGUALAAgADEAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABIAGUAYQB2AHkAdwBlAGkAZwBoAHQAIABOAGUAdwB0AG8AbgAtAFIAYQBwAGgAcwBvAG4AIABEAGkAdgBpAHMAaQBvAG4ALgBcAG4AIAAqACAASQBtAHAAbABlAG0AZQBuAHQAcwAgAHAAcgBvAGcAcgBlAHMAcwBpAHYAZQAgAHMAYwBhAGwAaQBuAGcAIABiAG8AdQBuAGQAZQBkACAAdABvACAATQBBAFgAKABsAGUAbgBfAGEALAAgAGwAZQBuAF8AYgApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwBhACwAIABSAE8AVwBTACgAbABpAG0AYgBzAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGIALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQByAGcAZQB0AF8AbABlAG4ALAAgAE0AQQBYACgAbABlAG4AXwBhACwAIABsAGUAbgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAAxAC4AIABDAGEAbABjAHUAbABhAHQAZQAgAHIAZQBjAGkAcAByAG8AYwBhAGwAIABSACAAcwBjAGEAbABlAGQAIABkAHkAbgBhAG0AaQBjAGEAbABsAHkAIAB0AG8AIAB0AGEAcgBnAGUAdABfAGwAZQBuAFwAbgAgACAAIAAgACAAIAAgACAAcgAsACAATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBSAGUAYwBpAHAAcgBvAGMAYQBsACgAbABpAG0AYgBzAF8AYgAsACAAdABhAHIAZwBlAHQAXwBsAGUAbgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgADIALgAgAEEAcABwAHIAbwB4AGkAbQBhAHQAZQAgAFEAdQBvAHQAaQBlAG4AdAA6ACAAUQBfAGEAcABwAHIAbwB4ACAAPQAgAEEAIAAqACAAUgAgAC8AIABCAGUAdABhAF4AKAB0AGEAcgBnAGUAdABfAGwAZQBuACAAKwAgAGwAZQBuAF8AYgApAFwAbgAgACAAIAAgACAAIAAgACAAZAByAG8AcABfAGwAaQBtAGIAcwAsACAAdABhAHIAZwBlAHQAXwBsAGUAbgAgACsAIABsAGUAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgAHEAXwB1AG4AcwBjAGEAbABlAGQALAAgAFUATQB1AGwAKABsAGkAbQBiAHMAXwBhACwAIAByACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHEAXwBhAHAAcAByAG8AeAAsACAASQBGACgAUgBPAFcAUwAoAHEAXwB1AG4AcwBjAGEAbABlAGQAKQAgADwAPQAgAGQAcgBvAHAAXwBsAGkAbQBiAHMALAAgAHsAMAB9ACwAIABEAFIATwBQACgAcQBfAHUAbgBzAGMAYQBsAGUAZAAsACAAZAByAG8AcABfAGwAaQBtAGIAcwApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAMwAuACAARQByAHIAbwByACAAQwBvAHIAcgBlAGMAdABpAG8AbgAgAFMAdwBlAGUAcAAgACgAUgBlAG0AYQBpAG4AZABlAHIAIAA9ACAAQQAgAC0AIAAoAEIAIAAqACAAUQBfAGEAcABwAHIAbwB4ACkAKQBcAG4AIAAgACAAIAAgACAAIAAgAHEAXwBwAHIAbwBkACwAIABVAE0AdQBsACgAbABpAG0AYgBzAF8AYgAsACAAcQBfAGEAcABwAHIAbwB4ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQBtAF8AYQBwAHAAcgBvAHgALAAgAFUAUwB1AGIAKABsAGkAbQBiAHMAXwBhACwAIABxAF8AcAByAG8AZAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAFUAQwBvAG0AcABhAHIAZQAoAHIAZQBtAF8AYQBwAHAAcgBvAHgALAAgAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAG8AcgByAGUAYwB0ACAAZgBsAG8AbwByACAAdAByAHUAbgBjAGEAdABpAG8AbgAgAGYAcgBvAG0AIABpAG4AdABlAGcAZQByACAAcgBlAGMAaQBwAHIAbwBjAGEAbABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHEALAAgAEkARgAoAGMAbwBtAHAAIAA+AD0AIAAwACwAIABVAEEAZABkACgAcQBfAGEAcABwAHIAbwB4ACwAIAB7ADEAfQAsACAAawApACwAIABxAF8AYQBwAHAAcgBvAHgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsACAASQBGACgAYwBvAG0AcAAgAD4APQAgADAALAAgAFUAUwB1AGIAKAByAGUAbQBfAGEAcABwAHIAbwB4ACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALAAgAHIAZQBtAF8AYQBwAHAAcgBvAHgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZgBpAG4AYQBsAF8AcgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AcwBpAGcAbgBlAGQAIABCAGEAcwBlAC0AMQAwACAATABlAGYAdAAtAHQAbwAtAFIAaQBnAGgAdAAgAEUAeABwAG8AbgBlAG4AdABpAGEAdABpAG8AbgAuAFwAbgAgACoAIABFAHYAYQBsAHUAYQB0AGUAcwAgAHQAaABlACAAZQB4AHAAbwBuAGUAbgB0ACAAaQB0AGUAcgBhAHQAaQB2AGUAbAB5ACAAdQBzAGkAbgBnACAAYQAgAHAAcgBlAC0AYwBvAG0AcAB1AHQAZQBkACAAMQAtADkAIABjAGEAYwBoAGUALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiAGEAcwBlACAAVABoAGUAIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAbABpAG0AYgAgAGEAcgByAGEAeQAgAG8AZgAgAHQAaABlACAAYgBhAHMAZQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGUAeABwAF8AcwB0AHIAaQBuAGcAIABUAGgAZQAgAGUAeABhAGMAdAAgAHQAZQB4AHQAIABzAHQAcgBpAG4AZwAgAG8AZgAgAHQAaABlACAAZQB4AHAAbwBuAGUAbgB0AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBVAFAAbwB3ACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYgBhAHMAZQAsACAAZQB4AHAAXwBzAHQAcgBpAG4AZwAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABQAHIAZQAtAGMAbwBtAHAAdQB0AGUAIABwAG8AdwBlAHIAcwAgADEAIAB0AGgAcgBvAHUAZwBoACAAOQAuAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0ACwAIABsAGkAbQBiAHMAXwBiAGEAcwBlACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAYwBvAG4AZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGYAaQByAHMAdAAsACAAZgBpAHIAcwB0ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAaABpAHIAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAHMAZQBjAG8AbgBkACwAIABmAGkAcgBzAHQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBvAHUAcgB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABzAGUAYwBvAG4AZAAsACAAcwBlAGMAbwBuAGQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAGYAdABoACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAZgBvAHUAcgB0AGgALAAgAGYAaQByAHMAdAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAeAB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKAB0AGgAaQByAGQALAAgAHQAaABpAHIAZAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAdgBlAG4AdABoACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAcwBpAHgAdABoACwAIABmAGkAcgBzAHQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBpAGcAdABoACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAZgBvAHUAcgB0AGgALAAgAGYAbwB1AHIAdABoACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4AaQBuAHQAaAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGUAaQBnAHQAaAAsACAAZgBpAHIAcwB0ACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABlAHgAcABfAGQAaQBnAGkAdABzACwAIAAtAC0ATQBJAEQAKABlAHgAcABfAHMAdAByAGkAbgBnACwAIABTAEUAUQBVAEUATgBDAEUAKABMAEUATgAoAGUAeABwAF8AcwB0AHIAaQBuAGcAKQApACwAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABSAEUARABVAEMARQAoADEALAAgAGUAeABwAF8AZABpAGcAaQB0AHMALAAgAEwAQQBNAEIARABBACgAYQBjAGMALAAgAGQAaQBnAGkAdAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAOgAgAFMAawBpAHAAIABjAGEAbABjAHUAbABhAHQAaQBuAGcAIAAxAF4AMQAwACAAZAB1AHIAaQBuAGcAIABsAGUAYQBkAGkAbgBnACAAaQB0AGUAcgBhAHQAaQBvAG4AcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAHMAXwBvAG4AZQAsACAAQQBOAEQAKABSAE8AVwBTACgAYQBjAGMAKQAgAD0AIAAxACwAIABJAE4ARABFAFgAKABhAGMAYwAsACAAMQAsACAAMQApACAAPQAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgADEALgAgAFIAYQBpAHMAZQAgAEEAYwBjACAAdABvACAAdABoAGUAIAAxADAAdABoACAAcABvAHcAZQByACAAdQBzAGkAbgBnACAAZQB4AGEAYwB0AGwAeQAgADQAIABtAHUAbAB0AGkAcABsAGkAYwBhAHQAaQBvAG4AcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAYwBfADEAMAAsACAASQBGACgAaQBzAF8AbwBuAGUALAAgAGEAYwBjACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAYwBfADIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABhAGMAYwAsACAAYQBjAGMALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAYwBfADQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABhAGMAYwBfADIALAAgAGEAYwBjAF8AMgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8AOAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGEAYwBjAF8ANAAsACAAYQBjAGMAXwA0ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGEAYwBjAF8AOAAsACAAYQBjAGMAXwAyACwAIABrACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAMgAuACAATQB1AGwAdABpAHAAbAB5ACAAYgB5ACAAdABoAGUAIABjAG8AcgByAGUAcwBwAG8AbgBkAGkAbgBnACAAcAByAGUALQBjAG8AbQBwAHUAdABlAGQAIABjAGEAYwBoAGUAIAB2AGEAbAB1AGUAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAZABpAGcAaQB0ACAAPQAgADAALAAgAGEAYwBjAF8AMQAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAGEAYwBoAGUAXwB2AGEAbAAsACAAQwBIAE8ATwBTAEUAKABkAGkAZwBpAHQALAAgAGYAaQByAHMAdAAsACAAcwBlAGMAbwBuAGQALAAgAHQAaABpAHIAZAAsACAAZgBvAHUAcgB0AGgALAAgAGYAaQBmAHQAaAAsACAAcwBpAHgAdABoACwAIABzAGUAdgBlAG4AdABoACwAIABlAGkAZwB0AGgALAAgAG4AaQBuAHQAaAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGkAcwBfAG8AbgBlACwAIABjAGEAYwBoAGUAXwB2AGEAbAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGEAYwBjAF8AMQAwACwAIABjAGEAYwBoAGUAXwB2AGEAbAAsACAAawApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQgBpAGcASQBuAHQAIgAsACIAdABlAHgAdAAiADoAIgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4ALwAvACAAQgBpAGcAIABJAG4AdABlAGcAZQByACAAQQByAGkAdABoAG0AZQB0AGkAYwAgAEwAaQBiAHIAYQByAHkAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIAAgACAAQgBpAGcASQBuAHQAIABNAG8AZAB1AGwAZQAgACAAIAAgACAAIAAgACAAIAAgACAALwAvAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIABQAHUAYgBsAGkAYwAgAEEAUABJACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwBcAG4ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8AXABuAFwAbgAvACoAKgBcAG4AIAAqACAATgBvAHIAbQBhAGwAaQBzAGUAcwAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AIABTAHQAcgBpAHAAcwAgAGwAZQBhAGQAaQBuAGcAIAB6AGUAcgBvAHMALAAgAHIAZQBzAG8AbAB2AGUAcwAgAFwAIgAtADAAXAAiACAAdABvACAAXAAiADAAXAAiACwAIABhAG4AZAAgAHQAaAByAG8AdwBzACAAIwBWAEEATABVAEUAIQAgAG8AbgAgAGkAbgB2AGEAbABpAGQAIABjAGgAYQByAGEAYwB0AGUAcgBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ATgBvAHIAbQAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AHIALAAgAEkARgAoAE8AUgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYgBpAGcAXwBpAG4AdAApACwAIABiAGkAZwBfAGkAbgB0ACAAPQAgAFwAIgBcACIAKQAsACAAXAAiADAAXAAiACwAIABiAGkAZwBfAGkAbgB0ACAAJgAgAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AdgBhAGwAaQBkACwAIABSAEUARwBFAFgAVABFAFMAVAAoAHMAdAByACwAIABcACIAXgAtAD8AXABcAGQAKwAkAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAcgBpAHAAcABlAGQALAAgAFIARQBHAEUAWABSAEUAUABMAEEAQwBFACgAcwB0AHIALAAgAFwAIgBeACgALQA/ACkAMAArACgAPwA9AFwAXABkACkAXAAiACwAIABcACIAJAAxAFwAIgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATgBPAFQAKABpAHMAXwB2AGEAbABpAGQAKQAsACAAVgBBAEwAVQBFACgAXAAiACMAVgBBAEwAVQBFACEAXAAiACkALAAgAEkARgAoAHMAdAByAGkAcABwAGUAZAAgAD0AIABcACIALQAwAFwAIgAsACAAXAAiADAAXAAiACwAIABzAHQAcgBpAHAAcABlAGQAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIABzAGkAZwBuACAAbwBmACAAYQAgAEIAaQBnAEkAbgB0ADoAIAAxACAAKABwAG8AcwBpAHQAaQB2AGUAKQAsACAALQAxACAAKABuAGUAZwBhAHQAaQB2AGUAKQAsACAAbwByACAAMAAgACgAegBlAHIAbwApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AUwBpAGcAbgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALAAgAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAGUAZAAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUwBXAEkAVABDAEgAKABMAEUARgBUACgAbgBvAHIAbQBlAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMABcACIALAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIAAtADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAvACAALQAtAC0AIABQAHIAZQBkAGkAYwBhAHQAZQBzACAALQAtAC0AIABcAFwAXABcAFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFIAZQB0AHUAcgBuAHMAIABUAFIAVQBFACAAaQBmACAAdABoAGUAIABCAGkAZwBJAG4AdAAgAGkAcwAgAGUAeABhAGMAdABsAHkAIAB6AGUAcgBvAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ASQBzAFoAZQByAG8AIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACAAPQAgAFwAIgAwAFwAIgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAFQAUgBVAEUAIABpAGYAIAB0AGgAZQAgAEIAaQBnAEkAbgB0ACAAaQBzACAAbgBlAGcAYQB0AGkAdgBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ASQBzAE4AZQBnACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsACAATABFAEYAVAAoAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0ACkAKQAgAD0AIABcACIALQBcACIAKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFIAZQB0AHUAcgBuAHMAIABUAFIAVQBFACAAaQBmACAAdABoAGUAIABCAGkAZwBJAG4AdAAgAGkAcwAgAGUAdgBlAG4ALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBJAHMARQB2AGUAbgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALAAgAEkAUwBFAFYARQBOACgAVgBBAEwAVQBFACgAUgBJAEcASABUACgATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAKQApACkAKQApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAFQAUgBVAEUAIABpAGYAIAB0AGgAZQAgAEIAaQBnAEkAbgB0ACAAaQBzACAAbwBkAGQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBJAHMATwBkAGQAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAIABJAFMATwBEAEQAKABWAEEATABVAEUAKABSAEkARwBIAFQAKABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACkAKQApACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIAB1AG4AcwBpAGcAbgBlAGQAIABtAGEAZwBuAGkAdAB1AGQAZQAgAG8AZgAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnACAAKABhAGIAcwBvAGwAdQB0AGUAIAB2AGEAbAB1AGUAKQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAIABUAGgAZQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEEAYgBzACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsACAAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AdQBtACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAEUARgBUACgAbgB1AG0AKQAgAD0AIABcACIALQBcACIALAAgAE0ASQBEACgAbgB1AG0ALAAgADIALAAgAEwARQBOACgAbgB1AG0AKQAgAC0AIAAxACkALAAgAG4AdQBtACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEMAbwBtAHAAYQByAGUAcwAgAHQAdwBvACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwBzAC4AIABSAGUAdAB1AHIAbgBzACAAMQAgACgAYQAgAD4AIABiACkALAAgAC0AMQAgACgAYQAgADwAIABiACkALAAgAG8AcgAgADAAIAAoAGEAIAA9ACAAYgApAC4AXABuACAAKgAgAEUAdgBhAGwAdQBhAHQAZQBzACAAcwBpAGcAbgBzACAAYQBuAGQAIABsAGUAbgBnAHQAaABzAC4AIABJAGYAIABpAGQAZQBuAHQAaQBjAGEAbAAsACAAZABlAGwAZQBnAGEAdABlAHMAIAB0AG8AIABuAGEAdABpAHYAZQAgAGwAaQBtAGIAIABhAHIAcgBhAHkAIABjAG8AbQBwAGEAcgBpAHMAbwBuAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAcwBlAGMAbwBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBDAG8AbQBwAGEAcgBlACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBhACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYQAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGIALAAgAEIAaQBnAGkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBiACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AYQAgADwAPgAgAHMAaQBnAG4AXwBiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMASQBHAE4AKABzAGkAZwBuAF8AYQAgAC0AIABzAGkAZwBuAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHMAaQBnAG4AXwBhACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYQAsACAATABFAE4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGIALAAgAEwARQBOACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABsAGUAbgBfAGEAIAA8AD4AIABsAGUAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBJAEcATgAoAGwAZQBuAF8AYQAgAC0AIABsAGUAbgBfAGIAKQAgACoAIABzAGkAZwBuAF8AYQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBBAEQARABcACIAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBhACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYgApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGEAZwBfAGMAbwBtAHAAYQByAGkAcwBvAG4ALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQwBvAG0AcABhAHIAZQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcABhAHIAaQBzAG8AbgAgACoAIABzAGkAZwBuAF8AYQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACAALQAgAEEAZABkAGkAdABpAG8AbgAgACYAIABTAHUAYgB0AHIAYQBjAHQAaQBvAG4AIAAtACAAIAAgACAAIAAgACAAXABcAFwAXABcAG4AXABuAC8AKgAqAFwAbgAgACoAIABBAGQAZABzACAAdAB3AG8AIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEEAZABkACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBhACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYQAsACAAQgBpAGcAaQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGIALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEEARABEAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBhACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGEAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBiACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGIAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAHIAbwB1AHQAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBBAGQAZABTAHUAYgBSAG8AdQB0AGUAcgAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAHMAaQBnAG4AXwBhACwAIABzAGkAZwBuAF8AYgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAGkAZwBuACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcgBvAHUAdABlAGQALAAgAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAEQAUgBPAFAAKAByAG8AdQB0AGUAZAAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAbQBlAHIAZwBlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGYAaQBuAGEAbABfAHMAaQBnAG4AIAA9ACAALQAxACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQALAAgAG0AZQByAGcAZQBkACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFMAdQBiAHQAcgBhAGMAdABzACAAdABoAGUAIABzAGUAYwBvAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAIABmAHIAbwBtACAAdABoAGUAIABmAGkAcgBzAHQAIAAoAEEAIAAtACAAQgApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAG0AaQBuAHUAZQBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGIAIABUAGgAZQAgAHMAdQBiAHQAcgBhAGgAZQBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBTAHUAYgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABiAGkAZwBfAGkAbgB0AF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAASQBuAHYAZQByAHQAIAB0AGgAZQAgAHMAaQBnAG4AIABvAGYAIABCACAAYQB0ACAAdABoAGUAIAB0AGUAeAB0ACAAbABlAHYAZQBsAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAHYAXwBiACwAIABJAEYAKABuAG8AcgBtAF8AYgAgAD0AIABcACIAMABcACIALAAgAFwAIgAwAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEwARQBGAFQAKABuAG8AcgBtAF8AYgApACAAPQAgAFwAIgAtAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAEQAKABuAG8AcgBtAF8AYgAsACAAMgAsACAATABFAE4AKABuAG8AcgBtAF8AYgApACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAgACYAIABuAG8AcgBtAF8AYgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUABhAHMAcwAgAHQAbwAgAEEAZABkAFwAbgAgACAAIAAgACAAIAAgACAAQQBkAGQAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAaQBuAHYAXwBiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFMAdQBtAHMAIABhAG4AIABhAHIAcgBhAHkAIABvAHIAIAByAGEAbgBnAGUAIABvAGYAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMAIAB2AGkAYQAgAHYAZQBjAHQAbwByAGkAegBlAGQAIABnAHIAbwB1AHAAIABtAGEAdAByAGkAYwBlAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIAByAGEAbgBnAGUAIABBACAAYwBvAG4AdABpAGcAdQBvAHUAcwAgAHIAYQBuAGcAZQAgAG8AcgAgAGEAcgByAGEAeQAgAG8AZgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoALwBcAG4AUwB1AG0AIAA9ACAATABBAE0AQgBEAEEAKAByAGEAbgBnAGUALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAZgBsAGEAdAAsACAAVABPAFIATwBXACgAcgBhAG4AZwBlACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATwBSACgASQBTAEUAUgBSAE8AUgAoAGYAbABhAHQAKQAsACAAQwBPAEwAVQBNAE4AUwAoAGYAbABhAHQAKQAgAD0AIAAwACkALAAgAFwAIgAwAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AbwByAG0AcwAsACAATQBBAFAAKABmAGwAYQB0ACwAIABMAEEATQBCAEQAQQAoAHgALAAgAE4AbwByAG0AKAB4ACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBzACwAIABNAEEAUAAoAEwARQBGAFQAKABuAG8AcgBtAHMAKQAsACAATABBAE0AQgBEAEEAKAB4ACwAIABJAEYAKAB4ACAAPQAgAFwAIgAwAFwAIgAsACAAMAAsACAAaQBmACgAeAAgAD0AIABcACIALQBcACIALAAgAC0AMQAsACAAMQApACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBiAHMAXwBuAG8AcgBtAHMALAAgAE0AQQBQACgAbgBvAHIAbQBzACwAIABzAGkAZwBuAHMALAAgAEwAQQBNAEIARABBACgAeAAsACAAcwBpAGcAbgAsACAASQBGACgAcwBpAGcAbgAgAD0AIAAtADEALAAgAE0ASQBEACgAeAAsACAAMgAsACAATABFAE4AKAB4ACkALQAxACkALAAgAHgAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAG8AcwBfAHMAdAByAHMALAAgAEYASQBMAFQARQBSACgAYQBiAHMAXwBuAG8AcgBtAHMALAAgAHMAaQBnAG4AcwAgAD0AIAAxACwAIAB7AFwAIgAwAFwAIgB9ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAZwBfAHMAdAByAHMALAAgAEYASQBMAFQARQBSACgAYQBiAHMAXwBuAG8AcgBtAHMALAAgAHMAaQBnAG4AcwAgAD0AIAAtADEALAAgAHsAXAAiADAAXAAiAH0AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHUAbgBpAGYAaQBlAGQAXwBrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIAQQBEAEQAXAAiACwAIABDAE8ATABVAE0ATgBTACgAZgBsAGEAdAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAG8AcwBfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAGEAdAByAGkAeABTAHUAbQAoAHAAbwBzAF8AcwB0AHIAcwAsACAAdQBuAGkAZgBpAGUAZABfAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQBnAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AYQB0AHIAaQB4AFMAdQBtACgAbgBlAGcAXwBzAHQAcgBzACwAIAB1AG4AaQBmAGkAZQBkAF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBvAHUAdABlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEEAZABkAFMAdQBiAFIAbwB1AHQAZQByACgAcABvAHMAXwBsAGkAbQBiAHMALAAgAG4AZQBnAF8AbABpAG0AYgBzACwAIAAxACwAIAAtADEALAAgAHUAbgBpAGYAaQBlAGQAXwBrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAGkAZwBuACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcgBvAHUAdABlAGQALAAgAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABEAFIATwBQACgAcgBvAHUAdABlAGQALAAgAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBlAHIAZwBlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAdQBuAGkAZgBpAGUAZABfAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGYAaQBuAGEAbABfAHMAaQBnAG4AIAA9ACAALQAxACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQALAAgAG0AZQByAGcAZQBkACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABNAHUAbAB0AGkAcABsAGkAZQBzACAAdAB3AG8AIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAE0AdQBsACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBhACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYQAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGIALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYQAsACAATABFAE4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGIALAAgAEwARQBOACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGgAbwByAHQALQBjAGkAcgBjAHUAaQB0ADoAIAAwACAAbQB1AGwAdABpAHAAbABpAGUAZAAgAGIAeQAgAGEAbgB5AHQAaABpAG4AZwAgAGkAcwAgADAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABzAGkAZwBuAF8AYQAgAD0AIAAwACwAIABzAGkAZwBuAF8AYgAgAD0AIAAwACkALAAgAFwAIgAwAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbABlAG4AXwBhACAAKwAgAGwAZQBuAF8AYgAgAD4AIAAzADIANwA2ADYALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAYQBsAGMAdQBsAGEAdABlACAAZAB5AG4AYQBtAGkAYwAgAHMAYQBmAGUAIABLACAAYgBhAHMAZQBkACAAbwBuACAAdABoAGUAIABzAGgAbwByAHQAZQBzAHQAIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIATQBVAEwAXAAiACwAIABNAEkATgAoAGwAZQBuAF8AYQAsACAAbABlAG4AXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAcABsAGkAdAAgAGEAYgBzAG8AbAB1AHQAZQAgAHMAdAByAGkAbgBnAHMAIABpAG4AdABvACAAbABpAHQAdABsAGUALQBlAG4AZABpAGEAbgAgAGEAcgByAGEAeQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGEALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYQApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBiACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGIAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIABtAGEAZwBuAGkAdAB1AGQAZQAgAGEAbgBkACAAcgBlAHMAbwBsAHYAZQAgAHMAaQBnAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcwBpAGcAbgAsACAAcwBpAGcAbgBfAGEAIAAqACAAcwBpAGcAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGUAcgBnAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAXAAiAC0AXAAiACAAJgAgAG0AZQByAGcAZQBkACwAIABtAGUAcgBnAGUAZAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAFYATwBMAEEAVABJAEwARQBdACAARwBlAG4AZQByAGEAdABlAHMAIABhACAAZAB5AG4AYQBtAGkAYwAgAGEAcgByAGEAeQAgAG8AZgAgAGkAbgB0AGUAZwBlAHIAcwAgAGEAcwAgAHQAZQB4AHQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG4AdQBtAF8AcgBvAHcAcwBdACAAYQByAHIAYQB5ACAAaABlAGkAZwBoAHQALAAgAGQAZQBmAGEAdQBsAHQAIAAxAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAWwBuAHUAbQBfAGMAbwBsAHMAXQAgAGEAcgByAGEAeQAgAHcAaQBkAHQAaAAsACAAZABlAGYAYQB1AGwAdAAgADEALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG0AaQBuAF8AZABpAGcAaQB0AHMAXQAgAG0AaQBuAGkAbQB1AG0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAaQBnAGkAdABzACwAIABkAGUAZgBhAHUAbAB0ACAAMQA2ACAAKABtAGkAbgAgADEAIABkAGkAZwBpAHQAKQBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG0AYQB4AF8AZABpAGcAaQB0AHMAXQAgAG0AYQB4AGkAbQB1AG0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAaQBnAGkAdABzACwAIABkAGUAZgBhAHUAbAB0ACAANQAwACAAKABtAGEAeAAgADMAMgAsADcANgA3ACAAYwBoAGEAcgBzACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAHMAaQBnAG4AKQBcAG4AIAAqAC8AXABuAFIAYQBuAGQAQgBpAGcASQBuAHQAQQByAHIAYQB5ACAAPQAgAEwAQQBNAEIARABBACgAWwBuAHUAbQBfAHIAbwB3AHMAXQAsACAAWwBuAHUAbQBfAGMAbwBsAHMAXQAsACAAWwBtAGkAbgBfAGQAaQBnAGkAdABzAF0ALAAgAFsAbQBhAHgAXwBkAGkAZwBpAHQAcwBdACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwByAG8AdwBzACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAG4AdQBtAF8AcgBvAHcAcwApACwAIAAxACwAIABuAHUAbQBfAHIAbwB3AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBfAGMAbwBsAHMALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbgB1AG0AXwBjAG8AbABzACkALAAgADEALAAgAG4AdQBtAF8AYwBvAGwAcwApACwAIABcAG4AIAAgACAAIAAgACAAIAAgAG0AaQBuAF8AbABlAG4ALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbQBpAG4AXwBkAGkAZwBpAHQAcwApACwAIAAxADYALAAgAE0ASQBOACgAMwAyADcANgA3ACwAIABNAEEAWAAoADEALAAgAG0AaQBuAF8AZABpAGcAaQB0AHMAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AbABlAG4ALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbQBhAHgAXwBkAGkAZwBpAHQAcwApACwAIAA1ADAALAAgAE0AQQBYACgAMQAsACAATQBJAE4AKAAzADIANwA2ADYALAAgAG0AYQB4AF8AZABpAGcAaQB0AHMAKQApACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABNAEEAUAAoAFIAQQBOAEQAQQBSAFIAQQBZACgAbgBfAHIAbwB3AHMALAAgAG4AXwBjAG8AbABzACwAIABtAGkAbgBfAGwAZQBuACwAIABtAGEAeABfAGwAZQBuACwAIABUAFIAVQBFACkALAAgAEwAQQBNAEIARABBACgAbABlAG4AZwB0AGgALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGkAZwBuACwAIABDAEgATwBPAFMARQAoAFIAQQBOAEQAQgBFAFQAVwBFAEUATgAoADEALAAgADIAKQAsACAAXAAiAFwAIgAsACAAXAAiAC0AXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGkAZwBpAHQAcwAsACAAQwBPAE4AQwBBAFQAKABSAEEATgBEAEEAUgBSAEEAWQAoADEALAAgAGwAZQBuAGcAdABoACwAIAAwACwAIAA5ACwAIABUAFIAVQBFACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AIAAmACAAUgBFAEcARQBYAFIARQBQAEwAQQBDAEUAKABkAGkAZwBpAHQAcwAsACAAXAAiAF4AMAAqAFwAIgAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABEAGkAdgBpAGQAZQBzACAAdABoAGUAIABmAGkAcgBzAHQAIABCAGkAZwBJAG4AdAAgAGIAeQAgAHQAaABlACAAcwBlAGMAbwBuAGQAIAAoAEEAIAAvACAAQgApAC4AIABcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAHQAaABlACAAcQB1AG8AdABpAGUAbgB0ACAAYQBuAGQAIABtAG8AZAB1AGwAdQBzACAAaQBuACAAcgBvAHcAcwAgADEAIABhAG4AZAAgADIALAAgAHIAZQBzAHAAZQBjAHQAaQB2AGUAbAB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAGQAaQB2AGkAZABlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAHUAcwBlAF8AZgBsAG8AbwByAF0AIABPAHAAdABpAG8AbgBhAGwAIABiAG8AbwBsAGUAYQBuAC4AIABUAFIAVQBFACAAZgBvAHIAIABQAHkAdABoAG8AbgAtAHMAdAB5AGwAZQAgAEYAbABvAG8AcgAgAGQAaQB2AGkAcwBpAG8AbgAsACAARgBBAEwAUwBFACAAZgBvAHIAIABUAHIAdQBuAGMAYQB0AGUAZAAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAARgBBAEwAUwBFAC4AXABuACAAKgAvAFwAbgBEAGkAdgBNAG8AZAAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABiAGkAZwBfAGkAbgB0AF8AYgAsACAAWwB1AHMAZQBfAGYAbABvAG8AcgBdACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBhACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYQAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGIALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGkAcwBfAGYAbABvAG8AcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAB1AHMAZQBfAGYAbABvAG8AcgApACwAIABGAEEATABTAEUALAAgAHUAcwBlAF8AZgBsAG8AbwByACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAcwBpAGcAbgBfAGIAIAA9ACAAMAAsACAAIwBEAEkAVgAvADAAIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AYQAgAD0AIAAwACwAIAB7AFwAIgAwAFwAIgA7AFwAIgAwAFwAIgB9ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBEAEkAVgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBhACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBiACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZABfAHIAZQBzAHUAbAB0ACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBEAGkAdgBSAG8AdQB0AGUAcgAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAUgBlAG0AYQBpAG4AZABlAHIAIABhAG4AZAAgAFEAdQBvAHQAaQBlAG4AdAAgAGEAcgByAGEAeQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwByACwAIABJAE4ARABFAFgAKABwAGEAYwBrAGUAZABfAHIAZQBzAHUAbAB0ACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBtAF8AbABpAG0AYgBzACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcABhAGMAawBlAGQAXwByAGUAcwB1AGwAdAAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwByACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcQB1AG8AdABfAGwAaQBtAGIAcwAsACAARABSAE8AUAAoAHAAYQBjAGsAZQBkAF8AcgBlAHMAdQBsAHQALAAgAGwAZQBuAF8AcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHMAbwBsAHYAZQAgAFQAcgB1AG4AYwBhAHQAZQBkACAAcwBpAGcAbgBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcwBpAGcAbgAsACAAcwBpAGcAbgBfAGEAIAAqACAAcwBpAGcAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AZQByAGcAZQBkAF8AcQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAcQB1AG8AdABfAGwAaQBtAGIAcwAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGUAcgBnAGUAZABfAHIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAHIAZQBtAF8AbABpAG0AYgBzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdAByAHUAbgBjAF8AcQAsACAASQBGACgAQQBOAEQAKABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAbQBlAHIAZwBlAGQAXwBxACAAPAA+ACAAXAAiADAAXAAiACkAIAAsACAAXAAiAC0AXAAiACAAJgAgAG0AZQByAGcAZQBkAF8AcQAsACAAbQBlAHIAZwBlAGQAXwBxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAcgB1AG4AYwBfAHIALAAgAEkARgAoAGEAbgBkACgAcwBpAGcAbgBfAGEAIAA9ACAALQAxACwAIABtAGUAcgBnAGUAZABfAHIAIAA8AD4AIABcACIAMABcACIAKQAsACAAXAAiAC0AXAAiACAAJgAgAG0AZQByAGcAZQBkAF8AcgAsACAAbQBlAHIAZwBlAGQAXwByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARgBsAG8AbwByACAAQwBvAHIAcgBlAGMAdABpAG8AbgA6ACAAVAByAGkAZwBnAGUAcgAgAE8ATgBMAFkAIABpAGYAIABmAGwAbwBvAHIAIABpAHMAIAByAGUAcQB1AGUAcwB0AGUAZAAsACAAcwBpAGcAbgBzACAAZABpAGYAZgBlAHIALAAgAGEAbgBkACAAcgBlAG0AYQBpAG4AZABlAHIAIABpAHMAIABuAG8AbgAtAHoAZQByAG8AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAZQBkAHMAXwBjAG8AcgByAGUAYwB0AGkAbwBuACwAIABBAE4ARAAoAGkAcwBfAGYAbABvAG8AcgAsACAAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAG0AZQByAGcAZQBkAF8AcgAgADwAPgAgAFwAIgAwAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHEALAAgAEkARgAoAG4AZQBlAGQAcwBfAGMAbwByAHIAZQBjAHQAaQBvAG4ALAAgAFMAdQBiACgAdAByAHUAbgBjAF8AcQAsACAAXAAiADEAXAAiACkALAAgAHQAcgB1AG4AYwBfAHEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsACAASQBGACgAbgBlAGUAZABzAF8AYwBvAHIAcgBlAGMAdABpAG8AbgAsACAAQQBkAGQAKAB0AHIAdQBuAGMAXwByACwAIABuAG8AcgBtAF8AYgApACwAIAB0AHIAdQBuAGMAXwByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABmAGkAbgBhAGwAXwBxACwAIABmAGkAbgBhAGwAXwByACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEQAaQB2AGkAZABlAHMAIAB0AGgAZQAgAGYAaQByAHMAdAAgAEIAaQBnAEkAbgB0ACAAYgB5ACAAdABoAGUAIABzAGUAYwBvAG4AZAAgACgAQQAgAC8AIABCACkALgAgAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBhACAAVABoAGUAIABkAGkAdgBpAGQAZQBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGIAIABUAGgAZQAgAGQAaQB2AGkAcwBvAHIAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAWwB1AHMAZQBfAGYAbABvAG8AcgBdACAATwBwAHQAaQBvAG4AYQBsACAAYgBvAG8AbABlAGEAbgAuACAAVABSAFUARQAgAGYAbwByACAAUAB5AHQAaABvAG4ALQBzAHQAeQBsAGUAIABGAGwAbwBvAHIAIABkAGkAdgBpAHMAaQBvAG4ALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAEYAQQBMAFMARQAuAFwAbgAgACoALwBcAG4ARABpAHYAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALAAgAFsAdQBzAGUAXwBmAGwAbwBvAHIAXQAsAFwAbgAgACAAIAAgAEkATgBEAEUAWAAoAEQAaQB2AE0AbwBkACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAIAB1AHMAZQBfAGYAbABvAG8AcgApACwAIAAxACwAIAAxACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABDAG8AbQBwAHUAdABlAHMAIAB0AGgAZQAgAHIAZQBtAGEAaQBuAGQAZQByACAAbwBmACAAQQAgAC8AIABCAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAGQAaQB2AGkAZABlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAHUAcwBlAF8AZgBsAG8AbwByAF0AIABPAHAAdABpAG8AbgBhAGwAIABiAG8AbwBsAGUAYQBuAC4AIABUAFIAVQBFACAAZgBvAHIAIABQAHkAdABoAG8AbgAtAHMAdAB5AGwAZQAgAE0AbwBkAHUAbABvAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABGAEEATABTAEUALgBcAG4AIAAqAC8AXABuAE0AbwBkACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAIABbAHUAcwBlAF8AZgBsAG8AbwByAF0ALABcAG4AIAAgACAAIABJAE4ARABFAFgAKABEAGkAdgBNAG8AZAAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABiAGkAZwBfAGkAbgB0AF8AYgAsACAAdQBzAGUAXwBmAGwAbwBvAHIAKQAsACAAMgAsACAAMQApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBhAGkAcwBlAHMAIABhACAAQgBpAGcASQBuAHQAIABiAGEAcwBlACAAdABvACAAdABoAGUAIABwAG8AdwBlAHIAIABvAGYAIABhACAAQgBpAGcASQBuAHQAIABlAHgAcABvAG4AZQBuAHQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGEAcwBlACAAVABoAGUAIABiAGEAcwBlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGUAeABwAG8AbgBlAG4AdAAgAFQAaABlACAAZQB4AHAAbwBuAGUAbgB0ACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AUABvAHcAIAA9ACAATABBAE0AQgBEAEEAKABiAGEAcwBlACwAIABlAHgAcABvAG4AZQBuAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIAYQBzAGUALAAgAE4AbwByAG0AKABiAGEAcwBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBlAHgAcAAsACAATgBvAHIAbQAoAGUAeABwAG8AbgBlAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgBhAHMAZQAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGUAeABwACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AZQB4AHAAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGEAYgBzAF8AYgBhAHMAZQAsACAAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBiAGEAcwBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAGEAYgBzAF8AZQB4AHAALAAgAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AZQB4AHAAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGkAcwBfAGUAeABwAF8AZQB2AGUAbgAsACAASQBTAEUAVgBFAE4AKABWAEEATABVAEUAKABSAEkARwBIAFQAKABuAG8AcgBtAF8AZQB4AHAALAAgADEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAaQBnAG4ALAAgAEkARgAoAHMAaQBnAG4AXwBiAGEAcwBlACAAPQAgAC0AMQAsACAASQBGACgAaQBzAF8AZQB4AHAAXwBlAHYAZQBuACwAIAAxACwAIAAtADEAKQAsACAAcwBpAGcAbgBfAGIAYQBzAGUAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEgAYQBuAGQAbABlACAAbQBhAHQAaABlAG0AYQB0AGkAYwBhAGwAIABiAG8AdQBuAGQAYQByAGkAZQBzACAAYQBuAGQAIABiAGEAcwBlACAAbABpAG0AaQB0AHMAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABhAGIAcwBfAGIAYQBzAGUAIAA9ACAAXAAiADAAXAAiACwAIABJAEYAKABuAG8AcgBtAF8AZQB4AHAAIAA9ACAAXAAiADAAXAAiACwAIAAjAE4AVQBNACEALAAgAFwAIgAwAFwAIgApACwAIAAvAC8AIAAwAF4AMAAgAGkAcwAgAHUAbgBkAGUAZgBpAG4AZQBkAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAYQBiAHMAXwBiAGEAcwBlACAAPQAgAFwAIgAxAFwAIgAsACAASQBGACgAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAFwAIgAtADEAXAAiACwAIABcACIAMQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAcwBpAGcAbgBfAGUAeABwACAAPQAgAC0AMQAsACAAXAAiADAAXAAiACwAIAAvAC8AIABJAG4AdABlAGcAZQByACAAdAByAHUAbgBjAGEAdABpAG8AbgA6ACAAbgBlAGcAYQB0AGkAdgBlACAAZQB4AHAAbwBuAGUAbgB0AHMAIAB5AGkAZQBsAGQAIAAwACAAZgBvAHIAIABiAGEAcwBlAHMAIAA+AD0AIAAyAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgBvAHIAbQBfAGUAeABwACAAPQAgAFwAIgAwAFwAIgAsACAAXAAiADEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHMAdQBsAHQAcwAgAGYAcgBvAG0AIABlAHgAcABvAG4AZQBuAHQAcwAgAGcAcgBlAGEAdABlAHIAIAB0AGgAYQBuACAANgAgAGQAaQBnAGkAdABzACAAYwBhAG4AbgBvAHQAIABiAGUAIABkAGkAcwBwAGwAYQB5AGUAZAAuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABFAE4AKABuAG8AcgBtAF8AZQB4AHAAKQAgAD4AIAA2ACwAIAAjAE4AVQBNACEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAHUAbQBfAGUAeABwACwAIABWAEEATABVAEUAKABuAG8AcgBtAF8AZQB4AHAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAcABwAHIAbwB4AGkAbQBhAHQAZQAgAHQAaABlACAAZgBpAG4AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAIABjAG8AdQBuAHQAOgAgAEIAIAAqACAATABvAGcAMQAwACgAQQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGIAYQBzAGUAXwBsAG8AZwAxADAALAAgAEwATwBHADEAMAAoAFYAQQBMAFUARQAoAEwARQBGAFQAKABhAGIAcwBfAGIAYQBzAGUALAAgADEANAApACkAKQAgACsAIABNAEEAWAAoADAALAAgAEwARQBOACgAYQBiAHMAXwBiAGEAcwBlACkAIAAtACAAMQA0ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAHAAcAByAG8AeABfAGQAaQBnAGkAdABzACwAIABuAHUAbQBfAGUAeABwACAAKgAgAGIAYQBzAGUAXwBsAG8AZwAxADAALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYQBwAHAAcgBvAHgAXwBkAGkAZwBpAHQAcwAgAD4AIAAzADIANwA2ADYALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAE0AVQBMAFwAIgAsACAAYQBwAHAAcgBvAHgAXwBkAGkAZwBpAHQAcwAgAC8AIAAyACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYgBhAHMAZQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYQBiAHMAXwBiAGEAcwBlACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBQAG8AdwAoAGwAaQBtAGIAcwBfAGIAYQBzAGUALAAgAG4AbwByAG0AXwBlAHgAcAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AZQByAGcAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAFwAIgAtAFwAIgAgACYAIABtAGUAcgBnAGUAZAAsACAAbQBlAHIAZwBlAGQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQApACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2AGkAcwBpAG8AbgAiACwAIgB0AGUAcwB0AF8AQgBpAGcASQBuAHQALgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAiACwAIgB0AGUAcwB0AF8AQgBpAGcASQBuAHQALgBEAGkAdgBpAHMAaQBvAG4AQQBsAGcAbwByAGkAdABoAG0AcwAiACwAIgB0AGUAcwB0AF8AQgBpAGcASQBuAHQALgBEAGkAdgBpAHMAaQBvAG4AQQBsAGcAbwByAGkAdABoAG0AQwBvAG0AcABhAHIAaQBzAG8AbgAiACwAIgB0AGUAcwB0AF8AQgBpAGcASQBuAHQALgBEAGkAdgBpAHMAaQBvAG4AQgBlAG4AYwBoAG0AYQByAGsAQwBhAHMAZQBzACIALAAiAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAuAEEAcwB5AG0AbQBlAHQAcgBpAGMAQQBCAEcAcgBpAGQAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AQwBhAHIAcgB5ACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQwBvAG0AcABhAHIAZQAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEEAZABkACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAUwB1AGIAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAGEAdAByAGkAeABTAHUAbQAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBBAGQAZABTAHUAYgBSAG8AdQB0AGUAcgAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEYAaQBuAGQAUQB1AG8AdABpAGUAbgB0AEwAaQBtAGIAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2ACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEQAaQB2AFIAbwB1AHQAZQByACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4AUwBlAGUAZAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAFIAZQBjAGkAcAByAG8AYwBhAGwAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFAAbwB3ACIALAAiAEIAaQBnAEkAbgB0AC4ATgBvAHIAbQAiACwAIgBCAGkAZwBJAG4AdAAuAFMAaQBnAG4AIgAsACIAQgBpAGcASQBuAHQALgBJAHMAWgBlAHIAbwAiACwAIgBCAGkAZwBJAG4AdAAuAEkAcwBOAGUAZwAiACwAIgBCAGkAZwBJAG4AdAAuAEkAcwBFAHYAZQBuACIALAAiAEIAaQBnAEkAbgB0AC4ASQBzAE8AZABkACIALAAiAEIAaQBnAEkAbgB0AC4AQQBiAHMAIgAsACIAQgBpAGcASQBuAHQALgBDAG8AbQBwAGEAcgBlACIALAAiAEIAaQBnAEkAbgB0AC4AQQBkAGQAIgAsACIAQgBpAGcASQBuAHQALgBTAHUAYgAiACwAIgBCAGkAZwBJAG4AdAAuAFMAdQBtACIALAAiAEIAaQBnAEkAbgB0AC4ATQB1AGwAIgAsACIAQgBpAGcASQBuAHQALgBSAGEAbgBkAEIAaQBnAEkAbgB0AEEAcgByAGEAeQAiACwAIgBCAGkAZwBJAG4AdAAuAEQAaQB2AE0AbwBkACIALAAiAEIAaQBnAEkAbgB0AC4ARABpAHYAIgAsACIAQgBpAGcASQBuAHQALgBNAG8AZAAiACwAIgBCAGkAZwBJAG4AdAAuAFAAbwB3ACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/XL-Int.xlsx
+++ b/XL-Int.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\foolu\Workspace\Excel\BigInt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350800F0-4F3A-4B0E-8CDD-306E176655ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E87F10-6374-4B7D-A550-271D240B70DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24610" windowHeight="21000" xr2:uid="{36490472-0618-4E80-9469-F609392FABC8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{36490472-0618-4E80-9469-F609392FABC8}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,7 @@
     <definedName name="BigInt.Pow" comment="Raises a BigInt base to the power of a BigInt exponent._x000a_@param base The base BigInt string._x000a_@param exponent The exponent BigInt string.">_xlfn.LAMBDA(_xlpm.base,_xlpm.exponent, _xlfn.LET(_xlpm.norm_base, BigInt.Norm(_xlpm.base), _xlpm.norm_exp, BigInt.Norm(_xlpm.exponent), _xlpm.sign_base, BigInt.Sign(_xlpm.norm_base), _xlpm.sign_exp, BigInt.Sign(_xlpm.norm_exp), _xlpm.abs_base, BigInt.Abs(_xlpm.norm_base), _xlpm.abs_exp, BigInt.Abs(_xlpm.norm_exp), _xlpm.is_exp_even, ISEVEN(VALUE(RIGHT(_xlpm.norm_exp, 1))), _xlpm.final_sign, IF(_xlpm.sign_base = -1, IF(_xlpm.is_exp_even, 1, -1), _xlpm.sign_base), IF(_xlpm.abs_base = "0", IF(_xlpm.norm_exp = "0", #NUM!, "0"), IF(_xlpm.abs_base = "1", IF(_xlpm.final_sign = -1, "-1", "1"), IF(_xlpm.sign_exp = -1, "0", IF(_xlpm.norm_exp = "0", "1", IF(LEN(_xlpm.norm_exp) &gt; 6, #NUM!, _xlfn.LET(_xlpm.num_exp, VALUE(_xlpm.norm_exp), _xlpm.base_log10,LOG10(VALUE(LEFT(_xlpm.abs_base, 14))) + MAX(0, LEN(_xlpm.abs_base) - 14), _xlpm.approx_digits, _xlpm.num_exp * _xlpm.base_log10, IF(_xlpm.approx_digits &gt; 32766, #NUM!, _xlfn.LET(_xlpm.k, core_BigInt.SafeK("MUL", _xlpm.approx_digits / 2), _xlpm.limbs_base, core_BigInt.Split(_xlpm.abs_base, _xlpm.k), _xlpm.final_limbs, core_BigInt.UPow(_xlpm.limbs_base, _xlpm.norm_exp, _xlpm.k), _xlpm.merged, core_BigInt.Merge(_xlpm.final_limbs, _xlpm.k), IF(_xlpm.final_sign = -1, "-" &amp; _xlpm.merged, _xlpm.merged)))))))))))</definedName>
     <definedName name="BigInt.RandBigIntArray" comment="[VOLATILE] Generates a dynamic array of integers as text._x000a_@param [num_rows] array height, default 1._x000a_@param [num_cols] array width, default 1._x000a_@param [min_digits] minimum number of digits, default 16 (min 1 digit)_x000a_@param [max_digits] maximum number of dig">_xlfn.LAMBDA(_xlop.num_rows,_xlop.num_cols,_xlop.min_digits,_xlop.max_digits, _xlfn.LET(_xlpm.n_rows, IF(_xlfn.ISOMITTED(_xlpm.num_rows), 1, _xlpm.num_rows), _xlpm.n_cols, IF(_xlfn.ISOMITTED(_xlpm.num_cols), 1, _xlpm.num_cols), _xlpm.min_len, IF(_xlfn.ISOMITTED(_xlpm.min_digits), 16, MIN(32767, MAX(1, _xlpm.min_digits))), _xlpm.max_len, IF(_xlfn.ISOMITTED(_xlpm.max_digits), 50, MAX(1, MIN(32766, _xlpm.max_digits))), _xlfn.MAP(_xlfn.RANDARRAY(_xlpm.n_rows, _xlpm.n_cols, _xlpm.min_len, _xlpm.max_len, TRUE), _xlfn.LAMBDA(_xlpm.length, _xlfn.LET(_xlpm.sign, CHOOSE(RANDBETWEEN(1, 2), "", "-"), _xlpm.digits, _xlfn.CONCAT(_xlfn.RANDARRAY(1, _xlpm.length, 0, 9, TRUE)), _xlpm.sign &amp; _xlfn.REGEXREPLACE(_xlpm.digits, "^0*", ""))))))</definedName>
     <definedName name="BigInt.Sign" comment="Returns the sign of a BigInt: 1 (positive), -1 (negative), or 0 (zero)._x000a_@param big_int The BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, _xlfn.LET(_xlpm.normed, BigInt.Norm(_xlpm.big_int), _xlfn.SWITCH(LEFT(_xlpm.normed), "0", 0, "-", -1, 1)))</definedName>
+    <definedName name="BigInt.Sqrt" comment="Calculates the integer square root (floor) of a BigInt._x000a_@param big_int The radicand BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, _xlfn.LET(_xlpm.norm_n, BigInt.Norm(_xlpm.big_int), _xlpm.sign_n, BigInt.Sign(_xlpm.norm_n), IF(_xlpm.sign_n = -1, #NUM!, IF(_xlpm.norm_n = "0", "0", IF(_xlpm.norm_n = "1", "1", _xlfn.LET(_xlpm.len_n, LEN(_xlpm.norm_n), _xlpm.take_digits, IF(_xlpm.len_n &lt;= 14, _xlpm.len_n, IF(ISEVEN(_xlpm.len_n), 14, 13)), _xlpm.v_str, LEFT(_xlpm.norm_n, _xlpm.take_digits), _xlpm.v_num, VALUE(_xlpm.v_str), _xlpm.zero_count, (_xlpm.len_n - _xlpm.take_digits) / 2, _xlpm.seed_prefix, TEXT(ROUNDUP(SQRT(_xlpm.v_num), 0) + 1, "0"), _xlpm.seed_str, _xlpm.seed_prefix &amp; REPT("0", _xlpm.zero_count), _xlpm.k, core_BigInt.SafeK("MUL", _xlpm.len_n), _xlpm.limbs_n, core_BigInt.Split(_xlpm.norm_n, _xlpm.k), _xlpm.limbs_seed, core_BigInt.Split(_xlpm.seed_str, _xlpm.k), _xlpm.final_limbs, core_BigInt.USqrt(_xlpm.limbs_n, _xlpm.limbs_seed, _xlpm.k), core_BigInt.Merge(_xlpm.final_limbs, _xlpm.k)))))))</definedName>
     <definedName name="BigInt.Sub" comment="Subtracts the second BigInt string from the first (A - B)._x000a_@param big_int_a The minuend BigInt string._x000a_@param big_int_b The subtrahend BigInt string.">_xlfn.LAMBDA(_xlpm.big_int_a,_xlpm.big_int_b, _xlfn.LET(_xlpm.norm_b, BigInt.Norm(_xlpm.big_int_b), _xlpm.inv_b, IF(_xlpm.norm_b = "0", "0", IF(LEFT(_xlpm.norm_b) = "-", MID(_xlpm.norm_b, 2, LEN(_xlpm.norm_b)), "-" &amp; _xlpm.norm_b)), BigInt.Add(_xlpm.big_int_a, _xlpm.inv_b)))</definedName>
     <definedName name="BigInt.Sum" comment="Sums an array or range of BigInt strings via vectorized group matrices._x000a_@param range A contiguous range or array of BigInt strings.">_xlfn.LAMBDA(_xlpm.range, _xlfn.LET(_xlpm.flat, _xlfn.TOROW(_xlpm.range, 1), IF(OR(ISERROR(_xlpm.flat), COLUMNS(_xlpm.flat) = 0), "0", _xlfn.LET(_xlpm.norms, _xlfn.MAP(_xlpm.flat, _xlfn.LAMBDA(_xlpm.x, BigInt.Norm(_xlpm.x))), _xlpm.signs, _xlfn.MAP(LEFT(_xlpm.norms), _xlfn.LAMBDA(_xlpm.x, IF(_xlpm.x = "0", 0, IF(_xlpm.x = "-", -1, 1)))), _xlpm.abs_norms, _xlfn.MAP(_xlpm.norms, _xlpm.signs, _xlfn.LAMBDA(_xlpm.x,_xlpm.sign, IF(_xlpm.sign = -1, MID(_xlpm.x, 2, LEN(_xlpm.x) - 1), _xlpm.x))), _xlpm.pos_strs, _xlfn._xlws.FILTER(_xlpm.abs_norms, _xlpm.signs = 1, {"0"}), _xlpm.neg_strs, _xlfn._xlws.FILTER(_xlpm.abs_norms, _xlpm.signs = -1, {"0"}), _xlpm.unified_k, core_BigInt.SafeK("ADD", COLUMNS(_xlpm.flat)), _xlpm.pos_limbs, core_BigInt.UMatrixSum(_xlpm.pos_strs, _xlpm.unified_k), _xlpm.neg_limbs, core_BigInt.UMatrixSum(_xlpm.neg_strs, _xlpm.unified_k), _xlpm.routed, core_BigInt.AddSubRouter(_xlpm.pos_limbs, _xlpm.neg_limbs, 1, -1, _xlpm.unified_k), _xlpm.final_sign, _xlfn.CHOOSEROWS(_xlpm.routed, -1), _xlpm.final_limbs, _xlfn.DROP(_xlpm.routed, -1), _xlpm.merged, core_BigInt.Merge(_xlpm.final_limbs, _xlpm.unified_k), IF(_xlpm.final_sign = -1, "-" &amp; _xlpm.merged, _xlpm.merged)))))</definedName>
     <definedName name="core_BigInt.AddSubRouter" comment="[Internal] Routes addition/subtraction based on signs and magnitudes._x000a_Returns a tuple array: VSTACK(limbs, final_sign) where the final row is the scalar sign._x000a_@param limbs_a The first little-endian limb array._x000a_@param limbs_b The second little-endian limb ">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b,_xlpm.sign_a,_xlpm.sign_b,_xlpm.k, _xlfn.LET(_xlpm.is_same_sign, _xlpm.sign_a = _xlpm.sign_b, IF(_xlpm.is_same_sign, _xlfn.VSTACK(core_BigInt.UAdd(_xlpm.limbs_a, _xlpm.limbs_b, _xlpm.k), _xlpm.sign_a), _xlfn.LET(_xlpm.mag_comp, core_BigInt.UCompare(_xlpm.limbs_a, _xlpm.limbs_b), IF(_xlpm.mag_comp = 0, {0;0}, IF(_xlpm.mag_comp &gt; 0, _xlfn.VSTACK(core_BigInt.USub(_xlpm.limbs_a, _xlpm.limbs_b, _xlpm.k), _xlpm.sign_a), _xlfn.VSTACK(core_BigInt.USub(_xlpm.limbs_b, _xlpm.limbs_a, _xlpm.k), _xlpm.sign_b)))))))</definedName>
@@ -42,8 +43,8 @@
     <definedName name="core_BigInt.FindQuotientLimb" comment=" * [Internal] Binary search to find the highest scalar quotient limb q (0 &lt;= q &lt; 10^k)_x000a_ * such that B * q &lt;= acc. Eliminates the need for Knuth D float-estimation._x000a_ * @param acc The current remainder array._x000a_ * @param b The divisor array._x000a_ * @param k The d">_xlfn.LAMBDA(_xlpm.acc,_xlpm.b,_xlpm.k, _xlfn.LET(_xlpm.bits, _xlfn.CEILING.MATH(LOG(10 ^ _xlpm.k, 2)), _xlpm.powers, 2 ^ _xlfn.SEQUENCE(_xlpm.bits, 1, _xlpm.bits - 1, -1), _xlfn.REDUCE(0, _xlpm.powers, _xlfn.LAMBDA(_xlpm.curr_q,_xlpm.power, _xlfn.LET(_xlpm.test_q, _xlpm.curr_q + _xlpm.power, IF(_xlpm.test_q &gt;= 10 ^ _xlpm.k, _xlpm.curr_q, _xlfn.LET(_xlpm.test_prod, core_BigInt.Carry(_xlpm.b * _xlpm.test_q, _xlpm.k), _xlpm.comp, core_BigInt.UCompare(_xlpm.acc, _xlpm.test_prod), IF(_xlpm.comp &gt;= 0, _xlpm.test_q, _xlpm.curr_q))))))))</definedName>
     <definedName name="core_BigInt.KnuthDiv" comment=" * [Internal] Basecase Division via sequential shift-and-subtract._x000a_ * Returns a packed 1D array: VSTACK(Length_R, R_limbs, Q_limbs)._x000a_ * Eliminates 2D array padding to strictly preserve memory efficiency._x000a_ * @param limbs_a The dividend array._x000a_ * @param lim">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.mag_comp, core_BigInt.UCompare(_xlpm.limbs_a, _xlpm.limbs_b), IF(_xlpm.mag_comp &lt; 0, _xlfn.VSTACK(ROWS(_xlpm.limbs_a), _xlpm.limbs_a, 0), IF(_xlpm.mag_comp = 0, _xlfn.VSTACK(1, 0, 1), _xlfn.LET(_xlpm.len_a, ROWS(_xlpm.limbs_a), _xlpm.reversed_a, _xlfn.CHOOSEROWS(_xlpm.limbs_a, _xlfn.SEQUENCE(_xlpm.len_a, 1, _xlpm.len_a, -1)), _xlpm.initial_state, _xlfn.VSTACK(1, 0, 0), _xlpm.final_state, _xlfn.REDUCE(_xlpm.initial_state, _xlpm.reversed_a, _xlfn.LAMBDA(_xlpm.state,_xlpm.val, _xlfn.LET(_xlpm.len_remainder, INDEX(_xlpm.state, 1, 1), _xlpm.remainder, _xlfn.CHOOSEROWS(_xlpm.state, _xlfn.SEQUENCE(_xlpm.len_remainder, 1, 2)), _xlpm.quotient, _xlfn.DROP(_xlpm.state, _xlpm.len_remainder + 1), _xlpm.extended_remainder, IF(AND(ROWS(_xlpm.remainder) = 1, INDEX(_xlpm.remainder, 1, 1) = 0), _xlpm.val, _xlfn.VSTACK(_xlpm.val, _xlpm.remainder)), _xlpm.next_quotient_limb, core_BigInt.FindQuotientLimb(_xlpm.extended_remainder, _xlpm.limbs_b, _xlpm.k), _xlpm.prod, core_BigInt.Carry(_xlpm.limbs_b * _xlpm.next_quotient_limb, _xlpm.k), _xlpm.new_remainder, core_BigInt.USub(_xlpm.extended_remainder, _xlpm.prod, _xlpm.k), _xlpm.has_quotient, OR(ROWS(_xlpm.quotient) &gt; 1, INDEX(_xlpm.quotient, 1, 1) &gt; 0), _xlpm.next_quot, IF(_xlpm.has_quotient, _xlfn.VSTACK(_xlpm.quotient, _xlpm.next_quotient_limb), _xlpm.next_quotient_limb), _xlfn.VSTACK(ROWS(_xlpm.new_remainder), _xlpm.new_remainder, _xlpm.next_quot)))), _xlpm.len_remainder, INDEX(_xlpm.final_state, 1, 1), _xlpm.remainder, _xlfn.CHOOSEROWS(_xlpm.final_state, _xlfn.SEQUENCE(_xlpm.len_remainder, 1, 2)), _xlpm.reversed_quotient, _xlfn.DROP(_xlpm.final_state, _xlpm.len_remainder + 1), _xlpm.len_quotient, ROWS(_xlpm.reversed_quotient), _xlpm.quotient, _xlfn.CHOOSEROWS(_xlpm.reversed_quotient, _xlfn.SEQUENCE(_xlpm.len_quotient, 1, _xlpm.len_quotient, -1)), _xlfn.VSTACK(_xlpm.len_remainder, _xlpm.remainder, _xlpm.quotient))))))</definedName>
     <definedName name="core_BigInt.Merge" comment="[Internal] Concatenates an array of numeric limbs into a BigInt string, zero-padding all but the first limb._x000a_@param limbs The vertical array of numeric limbs._x000a_@param k The limb size used during calculation.">_xlfn.LAMBDA(_xlpm.limbs,_xlpm.k, _xlfn.LET(_xlpm.num_limbs, ROWS(_xlpm.limbs), _xlpm.rev_limbs, _xlfn.CHOOSEROWS(_xlpm.limbs, _xlfn.SEQUENCE(_xlpm.num_limbs, 1, _xlpm.num_limbs, -1)), IF(_xlpm.num_limbs = 1, _xlpm.rev_limbs &amp; "", _xlfn.CONCAT(_xlfn.VSTACK(_xlfn.TAKE(_xlpm.rev_limbs, 1) &amp; "", TEXT(_xlfn.DROP(_xlpm.rev_limbs, 1), REPT("0", _xlpm.k)))))))</definedName>
-    <definedName name="core_BigInt.NewtonRaphsonDiv" comment="[Internal] Heavyweight Newton-Raphson Division._x000a_Implements progressive scaling bounded to MAX(len_a, len_b)._x000a_@param limbs_a The dividend array._x000a_@param limbs_b The divisor array._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.len_a, ROWS(_xlpm.limbs_a), _xlpm.len_b, ROWS(_xlpm.limbs_b), _xlpm.target_len, MAX(_xlpm.len_a, _xlpm.len_b), _xlpm.r, core_BigInt.NewtonRaphsonReciprocal(_xlpm.limbs_b, _xlpm.target_len, _xlpm.k), _xlpm.drop_limbs, _xlpm.target_len + _xlpm.len_b, _xlpm.q_unscaled, core_BigInt.UMul(_xlpm.limbs_a, _xlpm.r, _xlpm.k), _xlpm.q_approx, IF(ROWS(_xlpm.q_unscaled) &lt;= _xlpm.drop_limbs, {0}, _xlfn.DROP(_xlpm.q_unscaled, _xlpm.drop_limbs)), _xlpm.q_prod, core_BigInt.UMul(_xlpm.limbs_b, _xlpm.q_approx, _xlpm.k), _xlpm.rem_approx, core_BigInt.USub(_xlpm.limbs_a, _xlpm.q_prod, _xlpm.k), _xlpm.comp, core_BigInt.UCompare(_xlpm.rem_approx, _xlpm.limbs_b), _xlpm.final_q, IF(_xlpm.comp &gt;= 0, core_BigInt.UAdd(_xlpm.q_approx, {1}, _xlpm.k), _xlpm.q_approx), _xlpm.final_r, IF(_xlpm.comp &gt;= 0, core_BigInt.USub(_xlpm.rem_approx, _xlpm.limbs_b, _xlpm.k), _xlpm.rem_approx), _xlfn.VSTACK(ROWS(_xlpm.final_r), _xlpm.final_r, _xlpm.final_q)))</definedName>
-    <definedName name="core_BigInt.NewtonRaphsonReciprocal" comment="[Internal] Computes the Reciprocal progressively scaling up to the Dividend's precision._x000a_@param limbs_b The divisor limb array._x000a_@param target_len The limb-length of Dividend A._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.limbs_b,_xlpm.target_len,_xlpm.k, _xlfn.LET(_xlpm.len_b, ROWS(_xlpm.limbs_b), _xlpm.seed_len, MIN(3, _xlpm.len_b), _xlpm.r_seed_limbs, core_BigInt.NewtonRaphsonSeed(_xlpm.limbs_b, _xlpm.k), _xlpm.initial_state, _xlfn.VSTACK(_xlpm.seed_len, _xlpm.r_seed_limbs), _xlpm.req_iters, MAX(0, _xlfn.CEILING.MATH(LN(_xlpm.target_len / _xlpm.seed_len) / LN(2))), IF(_xlpm.req_iters = 0, _xlpm.r_seed_limbs, _xlfn.LET(_xlpm.iterations, _xlfn.SEQUENCE(_xlpm.req_iters), _xlpm.final_state, _xlfn.REDUCE(_xlpm.initial_state, _xlpm.iterations, _xlfn.LAMBDA(_xlpm.state,_xlpm.iter, _xlfn.LET(_xlpm.curr_len, INDEX(_xlpm.state, 1, 1), _xlpm.curr_r, _xlfn.DROP(_xlpm.state, 1), _xlpm.next_len, MIN(_xlpm.curr_len * 2, _xlpm.target_len), _xlpm.shift_limbs, _xlpm.next_len - _xlpm.curr_len, _xlpm.r_prime, IF(_xlpm.shift_limbs &gt; 0, _xlfn.VSTACK(_xlfn.EXPAND(0, _xlpm.shift_limbs, , 0), _xlpm.curr_r), _xlpm.curr_r), _xlpm.b_active, _xlfn.TAKE(_xlpm.limbs_b, -MIN(_xlpm.next_len, _xlpm.len_b)), _xlpm.p_raw, core_BigInt.UMul(_xlpm.b_active, _xlpm.r_prime, _xlpm.k), _xlpm.shift_p, MAX(0, _xlpm.next_len - _xlpm.len_b), _xlpm.p, IF(_xlpm.shift_p &gt; 0, _xlfn.VSTACK(_xlfn.EXPAND(0, _xlpm.shift_p, , 0), _xlpm.p_raw), _xlpm.p_raw), _xlpm.two_beta, _xlfn.VSTACK(_xlfn.EXPAND(0, 2 * _xlpm.next_len, , 0), 2), _xlpm.err, core_BigInt.USub(_xlpm.two_beta, _xlpm.p, _xlpm.k), _xlpm.next_r_unscaled, core_BigInt.UMul(_xlpm.r_prime, _xlpm.err, _xlpm.k), _xlpm.next_r, IF(ROWS(_xlpm.next_r_unscaled) &lt;= 2 * _xlpm.next_len, {0}, _xlfn.DROP(_xlpm.next_r_unscaled, 2 * _xlpm.next_len)), _xlfn.VSTACK(_xlpm.next_len, _xlpm.next_r)))), _xlfn.DROP(_xlpm.final_state, 1)))))</definedName>
+    <definedName name="core_BigInt.NewtonRaphsonDiv" comment="[Internal] Heavyweight Newton-Raphson Division._x000a_Implements progressive scaling bounded to MAX(len_a, len_b)._x000a_@param limbs_a The dividend array._x000a_@param limbs_b The divisor array._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.len_a, ROWS(_xlpm.limbs_a), _xlpm.len_b, ROWS(_xlpm.limbs_b), _xlpm.target_len, MAX(_xlpm.len_a, _xlpm.len_b), _xlpm.r, core_BigInt.NewtonRaphsonReciprocal(_xlpm.limbs_b, _xlpm.target_len, _xlpm.k), _xlpm.drop_limbs, 2 * _xlpm.target_len, _xlpm.q_unscaled, core_BigInt.UMul(_xlpm.limbs_a, _xlpm.r, _xlpm.k), _xlpm.q_approx, IF(ROWS(_xlpm.q_unscaled) &lt;= _xlpm.drop_limbs, {0}, _xlfn.DROP(_xlpm.q_unscaled, _xlpm.drop_limbs)), _xlpm.p_baseline, core_BigInt.UMul(_xlpm.limbs_b, _xlpm.q_approx, _xlpm.k), _xlpm.initial_state, _xlfn.VSTACK(ROWS(_xlpm.q_approx), _xlpm.q_approx, _xlpm.p_baseline), _xlpm.sweep_down, _xlfn.REDUCE(_xlpm.initial_state, {1;2}, _xlfn.LAMBDA(_xlpm.state,_xlpm.i, _xlfn.LET(_xlpm.len_q, INDEX(_xlpm.state, 1, 1), _xlpm.curr_q, _xlfn.CHOOSEROWS(_xlpm.state, _xlfn.SEQUENCE(_xlpm.len_q, 1, 2)), _xlpm.curr_p, _xlfn.DROP(_xlpm.state, _xlpm.len_q + 1), IF(core_BigInt.UCompare(_xlpm.curr_p, _xlpm.limbs_a) &gt; 0, _xlfn.LET(_xlpm.next_q, core_BigInt.USub(_xlpm.curr_q, {1}, _xlpm.k), _xlpm.next_p, core_BigInt.USub(_xlpm.curr_p, _xlpm.limbs_b, _xlpm.k), _xlfn.VSTACK(ROWS(_xlpm.next_q), _xlpm.next_q, _xlpm.next_p)), _xlpm.state)))), _xlpm.sweep_up, _xlfn.REDUCE(_xlpm.sweep_down, {1;2}, _xlfn.LAMBDA(_xlpm.state,_xlpm.i, _xlfn.LET(_xlpm.len_q, INDEX(_xlpm.state, 1, 1), _xlpm.curr_q, _xlfn.CHOOSEROWS(_xlpm.state, _xlfn.SEQUENCE(_xlpm.len_q, 1, 2)), _xlpm.curr_p, _xlfn.DROP(_xlpm.state, _xlpm.len_q + 1), _xlpm.next_p_test, core_BigInt.UAdd(_xlpm.curr_p, _xlpm.limbs_b, _xlpm.k), IF(core_BigInt.UCompare(_xlpm.next_p_test, _xlpm.limbs_a) &lt;= 0, _xlfn.LET(_xlpm.next_q, core_BigInt.UAdd(_xlpm.curr_q, {1}, _xlpm.k), _xlfn.VSTACK(ROWS(_xlpm.next_q), _xlpm.next_q, _xlpm.next_p_test)), _xlpm.state)))), _xlpm.final_len_q, INDEX(_xlpm.sweep_up, 1, 1), _xlpm.final_q, _xlfn.CHOOSEROWS(_xlpm.sweep_up, _xlfn.SEQUENCE(_xlpm.final_len_q, 1, 2)), _xlpm.final_p, _xlfn.DROP(_xlpm.sweep_up, _xlpm.final_len_q + 1), _xlpm.final_r, core_BigInt.USub(_xlpm.limbs_a, _xlpm.final_p, _xlpm.k), _xlfn.VSTACK(ROWS(_xlpm.final_r), _xlpm.final_r, _xlpm.final_q)))</definedName>
+    <definedName name="core_BigInt.NewtonRaphsonReciprocal" comment="[Internal] Computes the Reciprocal progressively scaling up to the Dividend's precision._x000a_@param limbs_b The divisor limb array._x000a_@param target_len The limb-length of Dividend A._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.limbs_b,_xlpm.target_len,_xlpm.k, _xlfn.LET(_xlpm.len_b, ROWS(_xlpm.limbs_b), _xlpm.seed_len, MIN(3, _xlpm.len_b), _xlpm.r_seed_limbs, core_BigInt.NewtonRaphsonSeed(_xlpm.limbs_b, _xlpm.k), _xlpm.initial_state, _xlfn.VSTACK(_xlpm.seed_len, _xlpm.r_seed_limbs), _xlpm.req_iters, MAX(0, _xlfn.CEILING.MATH(LN(_xlpm.target_len / _xlpm.seed_len) / LN(2))) + 1, IF(_xlpm.req_iters = 0, _xlpm.r_seed_limbs, _xlfn.LET(_xlpm.iterations, _xlfn.SEQUENCE(_xlpm.req_iters), _xlpm.final_state, _xlfn.REDUCE(_xlpm.initial_state, _xlpm.iterations, _xlfn.LAMBDA(_xlpm.state,_xlpm.iter, _xlfn.LET(_xlpm.curr_len, INDEX(_xlpm.state, 1, 1), _xlpm.curr_r, _xlfn.DROP(_xlpm.state, 1), _xlpm.next_len, MIN(_xlpm.curr_len * 2, _xlpm.target_len), _xlpm.active_curr, MIN(_xlpm.curr_len, _xlpm.len_b), _xlpm.active_next, MIN(_xlpm.next_len, _xlpm.len_b), _xlpm.shift_limbs, 2 * (_xlpm.next_len - _xlpm.curr_len) - (_xlpm.active_next - _xlpm.active_curr), _xlpm.r_prime, IF(_xlpm.shift_limbs &gt; 0, _xlfn.VSTACK(_xlfn.EXPAND(0, _xlpm.shift_limbs, , 0), _xlpm.curr_r), _xlpm.curr_r), _xlpm.b_active, _xlfn.TAKE(_xlpm.limbs_b, -_xlpm.active_next), _xlpm.p, core_BigInt.UMul(_xlpm.b_active, _xlpm.r_prime, _xlpm.k), _xlpm.two_beta, _xlfn.VSTACK(_xlfn.EXPAND(0, 2 * _xlpm.next_len, , 0), 2), _xlpm.err, core_BigInt.USub(_xlpm.two_beta, _xlpm.p, _xlpm.k), _xlpm.next_r_unscaled, core_BigInt.UMul(_xlpm.r_prime, _xlpm.err, _xlpm.k), _xlpm.next_r, IF(ROWS(_xlpm.next_r_unscaled) &lt;= 2 * _xlpm.next_len, {0}, _xlfn.DROP(_xlpm.next_r_unscaled, 2 * _xlpm.next_len)), _xlfn.VSTACK(_xlpm.next_len, _xlpm.next_r)))), _xlfn.DROP(_xlpm.final_state, 1)))))</definedName>
     <definedName name="core_BigInt.NewtonRaphsonSeed" comment="[Internal] Generates the exact reciprocal seed for Newton-Raphson Division using Knuth Basecase._x000a_Extracts up to the top 3 limbs of B and calculates floor(Beta^(2*len) / B_top)._x000a_@param limbs_b The divisor limb array._x000a_@param k The dynamic chunk size context">_xlfn.LAMBDA(_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.len_b, ROWS(_xlpm.limbs_b), _xlpm.seed_len, MIN(3, _xlpm.len_b), _xlpm.b_top, _xlfn.TAKE(_xlpm.limbs_b, -_xlpm.seed_len), _xlpm.beta_2m, _xlfn.VSTACK(_xlfn.EXPAND(0, 2 * _xlpm.seed_len, , 0), 1), _xlpm.packed, core_BigInt.KnuthDiv(_xlpm.beta_2m, _xlpm.b_top, _xlpm.k), _xlpm.len_r, INDEX(_xlpm.packed, 1, 1), _xlfn.DROP(_xlpm.packed, _xlpm.len_r + 1)))</definedName>
     <definedName name="core_BigInt.SafeK" comment="[Internal] Computes the maximum safe base-10 limb size (k) to avoid IEEE-754 precision loss._x000a_@param operation: &quot;ADD&quot;, &quot;MUL&quot;, or &quot;DIV&quot;._x000a_@param [max_items] ADD: number of operands. MUL: shortest string digits count.">_xlfn.LAMBDA(_xlpm.operation,_xlop.max_items, _xlfn.LET(_xlpm.items, IF(OR(_xlpm.max_items = "", _xlfn.ISOMITTED(_xlpm.max_items)), 2, MAX(2, _xlpm.max_items)), _xlfn.SWITCH(_xlpm.operation, "ADD", 15 - LEN(_xlpm.items), "MUL", _xlfn.LET(_xlpm.test_k, {7;6;5;4;3;2;1}, _xlpm.max_overlap, ROUNDUP(_xlpm.items / _xlpm.test_k, 0), _xlpm.uncarried_max, _xlpm.max_overlap * (10 ^ _xlpm.test_k - 1) ^ 2, _xlpm.max_carry, INT(_xlpm.uncarried_max / 10 ^ _xlpm.test_k), _xlpm.peak_val, _xlpm.uncarried_max + _xlpm.max_carry, MAX(_xlfn._xlws.FILTER(_xlpm.test_k, _xlpm.peak_val &lt;= (10 ^ 15 - 1)))), "DIV", 7, #NAME?)))</definedName>
     <definedName name="core_BigInt.Split" comment="[Internal] Unified Splitter. Splits both scalars and arrays into Little-Endian limbs._x000a_Uses MAX() to guarantee scalar inputs to the SEQUENCE engine._x000a_@param big_ints The string or array of strings._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.big_ints,_xlpm.k, _xlfn.LET(_xlpm.big_int_row, _xlfn.TOROW(_xlpm.big_ints), _xlpm.lengths, LEN(_xlpm.big_int_row), _xlpm.max_len, MAX(_xlpm.lengths), _xlpm.pad_len, ROUNDUP(_xlpm.max_len / _xlpm.k, 0) * _xlpm.k, _xlpm.padded, REPT("0", _xlpm.pad_len - _xlpm.lengths) &amp; _xlpm.big_int_row, _xlpm.starts, _xlfn.SEQUENCE(_xlpm.pad_len / _xlpm.k, 1, _xlpm.pad_len - _xlpm.k + 1, -_xlpm.k), --MID(_xlpm.padded, _xlpm.starts, _xlpm.k)))</definedName>
@@ -52,6 +53,7 @@
     <definedName name="core_BigInt.UMatrixSum" comment="[Internal] Vectorized matrix sum of unsigned BigInt strings._x000a_@param ubig_int Horizontal array (1xN) of normalized magnitude strings._x000a_@param k The unified dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.ubig_ints,_xlpm.k, _xlfn.LET(_xlpm.grid, core_BigInt.Split(_xlpm.ubig_ints, _xlpm.k), _xlpm.raw_limbs, _xlfn.BYROW(_xlpm.grid, _xleta.SUM), core_BigInt.Carry(_xlpm.raw_limbs, _xlpm.k)))</definedName>
     <definedName name="core_BigInt.UMul" comment="[Internal] Unsigned multiplication of two Little-Endian limb arrays._x000a_Utilizes a 1D Discrete Convolution (Cauchy Product) array-slicing strategy._x000a_Zero dynamic memory reallocation. $O(N+M)$ memory footprint._x000a_@param limbs_a The multiplicand limb array._x000a_@para">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.len_a, ROWS(_xlpm.limbs_a), _xlpm.len_b, ROWS(_xlpm.limbs_b), _xlpm.max_rows, _xlpm.len_a + _xlpm.len_b - 1, _xlpm.raw_limbs, _xlfn.MAKEARRAY(_xlpm.max_rows, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, _xlfn.LET(_xlpm.start_i, MAX(1, _xlpm.r - _xlpm.len_b + 1), _xlpm.end_i, MIN(_xlpm.r, _xlpm.len_a), _xlpm.count, _xlpm.end_i - _xlpm.start_i + 1, _xlpm.seq_i, _xlfn.SEQUENCE(_xlpm.count, 1, _xlpm.start_i, 1), _xlpm.seq_j, _xlfn.SEQUENCE(_xlpm.count, 1, _xlpm.r - _xlpm.start_i + 1, -1), SUM(INDEX(_xlpm.limbs_a, _xlpm.seq_i, 1) * INDEX(_xlpm.limbs_b, _xlpm.seq_j, 1))))), core_BigInt.Carry(_xlpm.raw_limbs, _xlpm.k)))</definedName>
     <definedName name="core_BigInt.UPow" comment="[Internal] Unsigned Base-10 Left-to-Right Exponentiation._x000a_Evaluates the exponent iteratively using a pre-computed 1-9 cache._x000a_@param limbs_base The little-endian limb array of the base._x000a_@param exp_string The exact text string of the exponent._x000a_@param k The ">_xlfn.LAMBDA(_xlpm.limbs_base,_xlpm.exp_string,_xlpm.k, _xlfn.LET(_xlpm.first, _xlpm.limbs_base, _xlpm.second, core_BigInt.UMul(_xlpm.first, _xlpm.first, _xlpm.k), _xlpm.third, core_BigInt.UMul(_xlpm.second, _xlpm.first, _xlpm.k), _xlpm.fourth, core_BigInt.UMul(_xlpm.second, _xlpm.second, _xlpm.k), _xlpm.fifth, core_BigInt.UMul(_xlpm.fourth, _xlpm.first, _xlpm.k), _xlpm.sixth, core_BigInt.UMul(_xlpm.third, _xlpm.third, _xlpm.k), _xlpm.seventh, core_BigInt.UMul(_xlpm.sixth, _xlpm.first, _xlpm.k), _xlpm.eigth, core_BigInt.UMul(_xlpm.fourth, _xlpm.fourth, _xlpm.k), _xlpm.ninth, core_BigInt.UMul(_xlpm.eigth, _xlpm.first, _xlpm.k), _xlpm.exp_digits, --MID(_xlpm.exp_string, _xlfn.SEQUENCE(LEN(_xlpm.exp_string)), 1), _xlfn.REDUCE(1, _xlpm.exp_digits, _xlfn.LAMBDA(_xlpm.acc,_xlpm.digit, _xlfn.LET(_xlpm.is_one, AND(ROWS(_xlpm.acc) = 1, INDEX(_xlpm.acc, 1, 1) = 1), _xlpm.acc_10, IF(_xlpm.is_one, _xlpm.acc, _xlfn.LET(_xlpm.acc_2, core_BigInt.UMul(_xlpm.acc, _xlpm.acc, _xlpm.k), _xlpm.acc_4, core_BigInt.UMul(_xlpm.acc_2, _xlpm.acc_2, _xlpm.k), _xlpm.acc_8, core_BigInt.UMul(_xlpm.acc_4, _xlpm.acc_4, _xlpm.k), core_BigInt.UMul(_xlpm.acc_8, _xlpm.acc_2, _xlpm.k))), IF(_xlpm.digit = 0, _xlpm.acc_10, _xlfn.LET(_xlpm.cache_val, CHOOSE(_xlpm.digit, _xlpm.first, _xlpm.second, _xlpm.third, _xlpm.fourth, _xlpm.fifth, _xlpm.sixth, _xlpm.seventh, _xlpm.eigth, _xlpm.ninth), IF(_xlpm.is_one, _xlpm.cache_val, core_BigInt.UMul(_xlpm.acc_10, _xlpm.cache_val, _xlpm.k)))))))))</definedName>
+    <definedName name="core_BigInt.USqrt" comment="[Internal] Unsigned Integer Square Root using Newton's Method._x000a_@param limbs_n Radicand little-endian array._x000a_@param limbs_seed Over-estimated little-endian seed array._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.limbs_n,_xlpm.limbs_seed,_xlpm.k, _xlfn.LET(_xlpm.initial_state, _xlfn.VSTACK(0, _xlpm.limbs_seed), _xlpm.max_iters, 35, _xlpm.final_state, _xlfn.REDUCE(_xlpm.initial_state, _xlfn.SEQUENCE(_xlpm.max_iters), _xlfn.LAMBDA(_xlpm.state,_xlpm.i, _xlfn.LET(_xlpm.is_done, INDEX(_xlpm.state, 1, 1), _xlpm.curr_x, _xlfn.DROP(_xlpm.state, 1), IF(_xlpm.is_done, _xlpm.state, _xlfn.LET(_xlpm.div_packed, core_BigInt.DivRouter(_xlpm.limbs_n, _xlpm.curr_x, _xlpm.k), _xlpm.len_r, INDEX(_xlpm.div_packed, 1, 1), _xlpm.q, _xlfn.DROP(_xlpm.div_packed, _xlpm.len_r + 1), _xlpm.sum_xq, core_BigInt.UAdd(_xlpm.curr_x, _xlpm.q, _xlpm.k), _xlpm.div_2_packed, core_BigInt.KnuthDiv(_xlpm.sum_xq, {2}, _xlpm.k), _xlpm.len_r2, INDEX(_xlpm.div_2_packed, 1, 1), _xlpm.x_next, _xlfn.DROP(_xlpm.div_2_packed, _xlpm.len_r2 + 1), _xlpm.comp, core_BigInt.UCompare(_xlpm.x_next, _xlpm.curr_x), IF(_xlpm.comp &gt;= 0, _xlfn.VSTACK(1, _xlpm.curr_x), _xlfn.VSTACK(0, _xlpm.x_next))))))), _xlfn.DROP(_xlpm.final_state, 1)))</definedName>
     <definedName name="core_BigInt.USub" comment="[Internal] Unsigned subtraction of two Little-Endian limb arrays._x000a_Assumes magnitudes A &gt;= B. Resolves borrows top-to-bottom and trims trailing zeros._x000a_@param limbs_a The minuend limb array (must be &gt;= limbs_b)._x000a_@param limbs_b The subtrahend limb array._x000a_@pa">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.max_rows, MAX(ROWS(_xlpm.limbs_a), ROWS(_xlpm.limbs_b)), _xlpm.pad_a, _xlfn.EXPAND(_xlpm.limbs_a, _xlpm.max_rows, 1, 0), _xlpm.pad_b, _xlfn.EXPAND(_xlpm.limbs_b, _xlpm.max_rows, 1, 0), _xlpm.diff, _xlpm.pad_a - _xlpm.pad_b, _xlpm.resolved, core_BigInt.Carry(_xlpm.diff, _xlpm.k), _xlpm.msd_idx, _xlfn.XMATCH(TRUE, _xlpm.resolved &lt;&gt; 0, 0, -1), IF(ISNA(_xlpm.msd_idx), {0}, _xlfn.TAKE(_xlpm.resolved, _xlpm.msd_idx))))</definedName>
     <definedName name="test_BigInt.AsymmetricABGrid">_xlfn.LAMBDA(_xlpm.start_a,_xlpm.max_a,_xlpm.step_a,_xlpm.start_b,_xlpm.max_b,_xlpm.step_b, _xlfn.LET(_xlpm.seq_a, _xlfn.SEQUENCE((_xlpm.max_a - _xlpm.start_a) / _xlpm.step_a + 1, 1, _xlpm.start_a, _xlpm.step_a), _xlpm.seq_b, _xlfn.SEQUENCE((_xlpm.max_b - _xlpm.start_b) / _xlpm.step_b + 1, 1, _xlpm.start_b, _xlpm.step_b), _xlpm.n_a, ROWS(_xlpm.seq_a), _xlpm.n_b, ROWS(_xlpm.seq_b), _xlpm.col_a, _xlfn.TOCOL(IF(_xlfn.SEQUENCE(1, _xlpm.n_b), _xlpm.seq_a)), _xlpm.col_b, _xlfn.TOCOL(IF(_xlfn.SEQUENCE(_xlpm.n_a), _xlfn.TOROW(_xlpm.seq_b))), _xlfn.HSTACK(_xlpm.col_a, _xlpm.col_b)))</definedName>
     <definedName name="test_BigInt.DivisionAlgorithmComparison" comment="Executes a strictly sequential benchmark suite to avoid multi-threading contamination._x000a_@param test_cases An N x 2 array of test lengths: [Length_A, Length_B]_x000a_@param iters Number of iterations per benchmark to smooth NOW() resolution.">_xlfn.LAMBDA(_xlpm.test_cases,_xlpm.iters,_xlpm.repeats, _xlfn.LET(_xlpm.n_tests, ROWS(_xlpm.test_cases), _xlpm.initial, {"Len_A","Len_B","Knuth_ms","NR_ms"}, _xlfn.REDUCE(_xlpm.initial, _xlfn.SEQUENCE(_xlpm.n_tests), _xlfn.LAMBDA(_xlpm.acc,_xlpm.i, _xlfn.LET(_xlpm.len_a, INDEX(_xlpm.test_cases, _xlpm.i, 1), _xlpm.len_b, INDEX(_xlpm.test_cases, _xlpm.i, 2), IF(_xlpm.len_b &gt; _xlpm.len_a, _xlpm.acc, _xlfn.LET(_xlpm.str_a, REPT("9", _xlpm.len_a), _xlpm.str_b, IF(_xlpm.len_b = 1, "7", "7" &amp; REPT("3", _xlpm.len_b - 1)), _xlpm.time_k, test_BigInt.DivisionAlgorithms(_xlpm.str_a, _xlpm.str_b, "KNUTH", _xlpm.iters, _xlpm.repeats), _xlpm.time_nr, test_BigInt.DivisionAlgorithms(_xlpm.str_a, _xlpm.str_b, "NR", _xlpm.iters, _xlpm.repeats), _xlfn.VSTACK(_xlpm.acc, _xlfn.HSTACK(_xlpm.len_a, _xlpm.len_b, _xlpm.time_k, _xlpm.time_nr)))))))))</definedName>
@@ -125,17 +127,18 @@
   <pythonScripts>
     <pythonScript>
       <code>import sys
+from math import isqrt
 sys.set_int_max_str_digits(32766)
 a = int(xl(%P2%))
 b = int(xl(%P3%))
-str(a**b)</code>
+str(isqrt(a))</code>
     </pythonScript>
   </pythonScripts>
 </python>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="572">
   <si>
     <t>12345</t>
   </si>
@@ -6797,6 +6800,318 @@
       </rPr>
       <t xml:space="preserve"> base to power of 0.</t>
     </r>
+  </si>
+  <si>
+    <t>{10}</t>
+  </si>
+  <si>
+    <t>core_BigInt.USqrt</t>
+  </si>
+  <si>
+    <t>n={15}
+seed={4}
+k=7</t>
+  </si>
+  <si>
+    <t>n={100}
+seed={11}
+k=7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Standard: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Small non-perfect square. Evaluates oscillation floor and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> context.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Array Boundary:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Multi-limb division, halving, and magnitude comparisons.</t>
+    </r>
+  </si>
+  <si>
+    <t>{3641828;351}</t>
+  </si>
+  <si>
+    <t>core_BigInt.NewtonRaphsonReciprocal</t>
+  </si>
+  <si>
+    <t>b={3}
+target_len=1
+k=7</t>
+  </si>
+  <si>
+    <t>b={2}
+target_len=2
+k=7</t>
+  </si>
+  <si>
+    <t>b={1234567; 890}
+target_len=2
+k=7</t>
+  </si>
+  <si>
+    <t>b={0; 0; 1}
+target_len=3
+k=7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Standard: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Perfect square. Converges without oscillating past the root.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Scalar approximation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Evaluates $\lfloor 10^{14} / 3 \rfloor$. Ensures correct behavior when $B$ is a single limb and $n=1$.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upscaling exact divisors:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Evaluates $10^{28} / 2$. Ensures the zero-padding logic does not drop significance when shifting.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Multi-limb approximation:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Divisor is $8901234567$. Evaluates $\lfloor 10^{28} / 8901234567 \rfloor$.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Power-of-base exactness:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Divisor is exactly $10^{14}$. Evaluates $10^{42} / 10^{14}$. Verifies edge-case behavior when $B$ perfectly matches internal base chunking.</t>
+    </r>
+  </si>
+  <si>
+    <t>core_BigInt.NewtonRaphsonDiv</t>
+  </si>
+  <si>
+    <t>Over-estimation vulnerability: Forces the integer-scaled reciprocal to slightly over-estimate Q, triggering the USub invariant violation.</t>
+  </si>
+  <si>
+    <t>Under-estimation limits: Evaluates whether the sweep correctly catches and resolves truncation drifts.</t>
+  </si>
+  <si>
+    <t>Fractional bypass: A &lt; B. Should instantly return {0} for Q and exact A for R.</t>
+  </si>
+  <si>
+    <t>Exact division (small): Verifies that exactly matching bounds do not cause off-by-one errors in either direction.</t>
+  </si>
+  <si>
+    <t>Exact division (large arrays): Tests bounds logic crossing the array size scaling shift inside the reciprocal calculation.</t>
+  </si>
+  <si>
+    <t>{1;1;3333333;3333333}</t>
+  </si>
+  <si>
+    <t>{1;999999;0}</t>
+  </si>
+  <si>
+    <t>{1;0;12}</t>
+  </si>
+  <si>
+    <t>{1;0;0;0;10}</t>
+  </si>
+  <si>
+    <t>a={4567890; 7890123; 123456}
+b={3641830; 351}
+k=7</t>
+  </si>
+  <si>
+    <t>a={0; 0; 1}
+b={3}
+k=7</t>
+  </si>
+  <si>
+    <t>a={999999}
+b={1000000}
+k=7</t>
+  </si>
+  <si>
+    <t>a={144}
+b={12}
+k=7</t>
+  </si>
+  <si>
+    <t>a={0; 0; 0; 0; 100}
+b={0; 0; 10}
+k=7</t>
+  </si>
+  <si>
+    <t>{2;9744480;224;3641827;351}</t>
+  </si>
+  <si>
+    <t>{2733835;3966724;11234}</t>
+  </si>
+  <si>
+    <t>{0;0;0;0;1}</t>
+  </si>
+  <si>
+    <t>n={4567890;7890123;123456}
+seed={3641830; 351}
+k=7</t>
   </si>
 </sst>
 </file>
@@ -6807,7 +7122,7 @@
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6918,6 +7233,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -6986,7 +7308,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -7027,8 +7349,9 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -7037,7 +7360,17 @@
     <cellStyle name="Input" xfId="1" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="275">
+  <dxfs count="254">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -7550,16 +7883,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -7569,525 +7892,12 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color theme="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color theme="1"/>
-        </top>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -8101,10 +7911,33 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -8112,16 +7945,150 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -8137,15 +8104,27 @@
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -8281,11 +8260,26 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -9547,12 +9541,12 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7798C9D4-D9A3-414B-919E-1762A05E858C}" name="Norm_Tests" displayName="Norm_Tests" ref="A7:E26" totalsRowCount="1">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2D415719-D29C-4B5B-8EEC-D6B547CA5D0E}" name="input" dataDxfId="274"/>
+    <tableColumn id="1" xr3:uid="{2D415719-D29C-4B5B-8EEC-D6B547CA5D0E}" name="input" dataDxfId="253"/>
     <tableColumn id="3" xr3:uid="{0ACC712F-EB7B-43DA-9965-8A4957A95DA2}" name="expected"/>
-    <tableColumn id="2" xr3:uid="{25F1E681-6FC0-4609-BF1F-1FF79BEB3CD8}" name="output" dataDxfId="273">
+    <tableColumn id="2" xr3:uid="{25F1E681-6FC0-4609-BF1F-1FF79BEB3CD8}" name="output" dataDxfId="252">
       <calculatedColumnFormula array="1">internal.xlInt.Norm(Norm_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{20432306-08A1-43B4-9B37-03610B79D73B}" name="passing" totalsRowFunction="custom" dataDxfId="272">
+    <tableColumn id="4" xr3:uid="{20432306-08A1-43B4-9B37-03610B79D73B}" name="passing" totalsRowFunction="custom" dataDxfId="251">
       <calculatedColumnFormula>IF(ISERROR(Norm_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Norm_Tests[[#This Row],[expected]]) = ERROR.TYPE(Norm_Tests[[#This Row],[output]]),
     Norm_Tests[[#This Row],[expected]] = Norm_Tests[[#This Row],[output]]
@@ -9566,11 +9560,11 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DCEBF05F-998F-47D8-A8F8-63C4E2771074}" name="UCompare_Tests" displayName="UCompare_Tests" ref="A127:E135" totalsRowCount="1" dataDxfId="233">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DCEBF05F-998F-47D8-A8F8-63C4E2771074}" name="UCompare_Tests" displayName="UCompare_Tests" ref="A127:E135" totalsRowCount="1" dataDxfId="212">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3554FEAC-3E95-4439-BF1F-B262B64D139D}" name="input" dataDxfId="232"/>
-    <tableColumn id="2" xr3:uid="{0EA61E63-F894-4F39-983A-67C6CDEA4B1D}" name="expected" dataDxfId="231"/>
-    <tableColumn id="3" xr3:uid="{B6F49B44-504D-4599-9F1E-49B98046B44D}" name="output" dataDxfId="230">
+    <tableColumn id="1" xr3:uid="{3554FEAC-3E95-4439-BF1F-B262B64D139D}" name="input" dataDxfId="211"/>
+    <tableColumn id="2" xr3:uid="{0EA61E63-F894-4F39-983A-67C6CDEA4B1D}" name="expected" dataDxfId="210"/>
+    <tableColumn id="3" xr3:uid="{B6F49B44-504D-4599-9F1E-49B98046B44D}" name="output" dataDxfId="209">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(UCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -9580,46 +9574,46 @@
     internal.xlInt.UCompare(_xlpm.limbs_a, _xlpm.limbs_b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{96B8A7F0-899C-4301-95D3-41FB0BA096A7}" name="passing" totalsRowFunction="custom" dataDxfId="229">
+    <tableColumn id="4" xr3:uid="{96B8A7F0-899C-4301-95D3-41FB0BA096A7}" name="passing" totalsRowFunction="custom" dataDxfId="208">
       <calculatedColumnFormula>IF(ISERROR(UCompare_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(UCompare_Tests[[#This Row],[output]]),
     UCompare_Tests[[#This Row],[expected]] = UCompare_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UCompare_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C5539D24-4ADC-4D77-B82F-27DAF4B3F109}" name="test" dataDxfId="228"/>
+    <tableColumn id="5" xr3:uid="{C5539D24-4ADC-4D77-B82F-27DAF4B3F109}" name="test" dataDxfId="207"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5E817537-E6E9-4069-8E14-531A3E42821F}" name="Internal_Sign_Tests" displayName="Internal_Sign_Tests" ref="A49:E60" totalsRowCount="1" tableBorderDxfId="227">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5E817537-E6E9-4069-8E14-531A3E42821F}" name="Internal_Sign_Tests" displayName="Internal_Sign_Tests" ref="A49:E60" totalsRowCount="1" tableBorderDxfId="206">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{C5C6E024-5D15-4650-BC06-AE3A9A4A3F9E}" name="input"/>
     <tableColumn id="2" xr3:uid="{2E349FE8-D8E4-4ABE-B47E-F0985AA6C672}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{49844921-4B71-4B13-957C-917C2841A9A3}" name="output" dataDxfId="226">
+    <tableColumn id="3" xr3:uid="{49844921-4B71-4B13-957C-917C2841A9A3}" name="output" dataDxfId="205">
       <calculatedColumnFormula array="1">xlInt.Sign(Internal_Sign_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0236DB85-60E5-4DC6-9655-C6D58A63C8D4}" name="passing" totalsRowFunction="custom" dataDxfId="225">
+    <tableColumn id="4" xr3:uid="{0236DB85-60E5-4DC6-9655-C6D58A63C8D4}" name="passing" totalsRowFunction="custom" dataDxfId="204">
       <calculatedColumnFormula>IF(ISERROR(Internal_Sign_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Internal_Sign_Tests[[#This Row],[expected]]) = ERROR.TYPE(Internal_Sign_Tests[[#This Row],[output]]),
     Internal_Sign_Tests[[#This Row],[expected]] = Internal_Sign_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Internal_Sign_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{396092C1-DC4F-4532-BB59-E0E779D9A525}" name="test" dataDxfId="224"/>
+    <tableColumn id="5" xr3:uid="{396092C1-DC4F-4532-BB59-E0E779D9A525}" name="test" dataDxfId="203"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1BF11AA1-9F01-403A-A5A2-CDAF85E5F9D0}" name="USub_Tests" displayName="USub_Tests" ref="A138:E146" totalsRowCount="1" dataDxfId="223">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1BF11AA1-9F01-403A-A5A2-CDAF85E5F9D0}" name="USub_Tests" displayName="USub_Tests" ref="A138:E146" totalsRowCount="1" dataDxfId="202">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5B979D84-AD0F-45AF-AB26-6C75CA981E58}" name="input" dataDxfId="222"/>
-    <tableColumn id="2" xr3:uid="{D8895FB5-11F4-4379-9B45-0D72ADA71E57}" name="expected" dataDxfId="221"/>
-    <tableColumn id="3" xr3:uid="{A4DDD8AE-0CC0-457E-A08D-2C94591CF878}" name="output" dataDxfId="220">
+    <tableColumn id="1" xr3:uid="{5B979D84-AD0F-45AF-AB26-6C75CA981E58}" name="input" dataDxfId="201"/>
+    <tableColumn id="2" xr3:uid="{D8895FB5-11F4-4379-9B45-0D72ADA71E57}" name="expected" dataDxfId="200"/>
+    <tableColumn id="3" xr3:uid="{A4DDD8AE-0CC0-457E-A08D-2C94591CF878}" name="output" dataDxfId="199">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(USub_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -9631,25 +9625,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BF616718-1C7F-4627-B496-8B6339CC2735}" name="passing" totalsRowFunction="custom" dataDxfId="219">
+    <tableColumn id="4" xr3:uid="{BF616718-1C7F-4627-B496-8B6339CC2735}" name="passing" totalsRowFunction="custom" dataDxfId="198">
       <calculatedColumnFormula>IF(ISERROR(USub_Tests[[#This Row],[expected]]),
     ERROR.TYPE(USub_Tests[[#This Row],[expected]]) = ERROR.TYPE(USub_Tests[[#This Row],[output]]),
     USub_Tests[[#This Row],[expected]] = USub_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(USub_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FCF52C7D-4E82-4BAA-8C93-974211CAC2AF}" name="test" dataDxfId="218"/>
+    <tableColumn id="5" xr3:uid="{FCF52C7D-4E82-4BAA-8C93-974211CAC2AF}" name="test" dataDxfId="197"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B5433254-33A6-4D35-8484-91940B628217}" name="Table6" displayName="Table6" ref="A149:E160" totalsRowCount="1" dataDxfId="217">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B5433254-33A6-4D35-8484-91940B628217}" name="Table6" displayName="Table6" ref="A149:E160" totalsRowCount="1" dataDxfId="196">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D52F6D10-66CD-4765-927A-94A578D3C30A}" name="input" dataDxfId="216" totalsRowDxfId="215"/>
-    <tableColumn id="2" xr3:uid="{DF2BEEE3-E1EF-4EA0-A6A8-77B06FB5C3EE}" name="expected" dataDxfId="214"/>
-    <tableColumn id="3" xr3:uid="{4FDE8849-AFE2-471E-8131-C5B45620EBDC}" name="output" dataDxfId="213">
+    <tableColumn id="1" xr3:uid="{D52F6D10-66CD-4765-927A-94A578D3C30A}" name="input" dataDxfId="195" totalsRowDxfId="194"/>
+    <tableColumn id="2" xr3:uid="{DF2BEEE3-E1EF-4EA0-A6A8-77B06FB5C3EE}" name="expected" dataDxfId="193"/>
+    <tableColumn id="3" xr3:uid="{4FDE8849-AFE2-471E-8131-C5B45620EBDC}" name="output" dataDxfId="192">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.input, _xlfn.REGEXEXTRACT(Table6[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.input,1,1),
@@ -9663,25 +9657,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5813AECE-7F35-45E7-8E1F-50DCC8404156}" name="passing" totalsRowFunction="custom" dataDxfId="212" totalsRowDxfId="211">
+    <tableColumn id="4" xr3:uid="{5813AECE-7F35-45E7-8E1F-50DCC8404156}" name="passing" totalsRowFunction="custom" dataDxfId="191" totalsRowDxfId="190">
       <calculatedColumnFormula>IF(ISERROR(Table6[[#This Row],[expected]]),
     ERROR.TYPE(Table6[[#This Row],[expected]]) = ERROR.TYPE(Table6[[#This Row],[output]]),
     Table6[[#This Row],[expected]] = Table6[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Table6[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6FEE6B80-DF03-48AD-BE0B-5CF10BB9952D}" name="test" dataDxfId="210"/>
+    <tableColumn id="5" xr3:uid="{6FEE6B80-DF03-48AD-BE0B-5CF10BB9952D}" name="test" dataDxfId="189"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{99918742-71F1-4CEE-8B31-04D0864B12BE}" name="Add_Tests" displayName="Add_Tests" ref="A163:E169" totalsRowCount="1" dataDxfId="209">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{99918742-71F1-4CEE-8B31-04D0864B12BE}" name="Add_Tests" displayName="Add_Tests" ref="A163:E169" totalsRowCount="1" dataDxfId="188">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BEDCABA1-70E6-4A6B-A326-B96D805DC792}" name="input" dataDxfId="208"/>
-    <tableColumn id="2" xr3:uid="{D2C344B5-4A5B-4F69-8FCC-B73D81DE29AD}" name="expected" dataDxfId="207"/>
-    <tableColumn id="3" xr3:uid="{B095BBF3-B41C-4F5B-9689-A075BCD3B3C6}" name="output" dataDxfId="206">
+    <tableColumn id="1" xr3:uid="{BEDCABA1-70E6-4A6B-A326-B96D805DC792}" name="input" dataDxfId="187"/>
+    <tableColumn id="2" xr3:uid="{D2C344B5-4A5B-4F69-8FCC-B73D81DE29AD}" name="expected" dataDxfId="186"/>
+    <tableColumn id="3" xr3:uid="{B095BBF3-B41C-4F5B-9689-A075BCD3B3C6}" name="output" dataDxfId="185">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Add_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -9689,25 +9683,25 @@
     xlInt.Add(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8A3FC5E9-718D-42AA-90B8-83E1D4F3B18A}" name="passing" totalsRowFunction="custom" dataDxfId="205" totalsRowDxfId="204">
+    <tableColumn id="4" xr3:uid="{8A3FC5E9-718D-42AA-90B8-83E1D4F3B18A}" name="passing" totalsRowFunction="custom" dataDxfId="184" totalsRowDxfId="183">
       <calculatedColumnFormula>IF(ISERROR(Add_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Add_Tests[[#This Row],[expected]]) = ERROR.TYPE(Add_Tests[[#This Row],[output]]),
     Add_Tests[[#This Row],[expected]] = Add_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Add_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DCB35414-E71F-476D-B8FC-5C98625552A8}" name="test" dataDxfId="203"/>
+    <tableColumn id="5" xr3:uid="{DCB35414-E71F-476D-B8FC-5C98625552A8}" name="test" dataDxfId="182"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{DE30AD6A-E7CB-4B0A-9AF6-2A68597C812D}" name="Sub_Tests" displayName="Sub_Tests" ref="A172:E176" totalsRowCount="1" dataDxfId="202">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{DE30AD6A-E7CB-4B0A-9AF6-2A68597C812D}" name="Sub_Tests" displayName="Sub_Tests" ref="A172:E176" totalsRowCount="1" dataDxfId="181">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{03074968-5409-421B-94C4-D5670F4C41D8}" name="input" dataDxfId="201"/>
-    <tableColumn id="2" xr3:uid="{DDFFA8C5-FCAB-4C4D-9AD1-92357F9E25A7}" name="expected" dataDxfId="200"/>
-    <tableColumn id="3" xr3:uid="{799B106A-FDF6-4F6C-8D67-8B6355524DD8}" name="output" dataDxfId="199">
+    <tableColumn id="1" xr3:uid="{03074968-5409-421B-94C4-D5670F4C41D8}" name="input" dataDxfId="180"/>
+    <tableColumn id="2" xr3:uid="{DDFFA8C5-FCAB-4C4D-9AD1-92357F9E25A7}" name="expected" dataDxfId="179"/>
+    <tableColumn id="3" xr3:uid="{799B106A-FDF6-4F6C-8D67-8B6355524DD8}" name="output" dataDxfId="178">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Sub_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -9715,25 +9709,25 @@
     xlInt.Sub(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{365F4930-D4D1-407A-94F0-4578BEFB456D}" name="passing" totalsRowFunction="custom" dataDxfId="198" totalsRowDxfId="197">
+    <tableColumn id="4" xr3:uid="{365F4930-D4D1-407A-94F0-4578BEFB456D}" name="passing" totalsRowFunction="custom" dataDxfId="177" totalsRowDxfId="176">
       <calculatedColumnFormula>IF(ISERROR(Sub_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Sub_Tests[[#This Row],[expected]]) = ERROR.TYPE(Sub_Tests[[#This Row],[output]]),
     Sub_Tests[[#This Row],[expected]] = Sub_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Sub_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CD9B4489-0AA4-43C4-9B29-8D70A32DD746}" name="test" dataDxfId="196"/>
+    <tableColumn id="5" xr3:uid="{CD9B4489-0AA4-43C4-9B29-8D70A32DD746}" name="test" dataDxfId="175"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{9E3906E7-DD79-4AAB-8367-36E413E4200E}" name="Split_Tests" displayName="Split_Tests" ref="A179:E183" totalsRowCount="1" dataDxfId="195">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{9E3906E7-DD79-4AAB-8367-36E413E4200E}" name="Split_Tests" displayName="Split_Tests" ref="A179:E183" totalsRowCount="1" dataDxfId="174">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{14CAD510-CB82-4DB3-9F1C-40F2CB704D1C}" name="input" dataDxfId="194"/>
-    <tableColumn id="2" xr3:uid="{5035D4AE-F48A-40D0-AF90-BDA3391536CB}" name="expected" dataDxfId="193"/>
-    <tableColumn id="3" xr3:uid="{99876D23-ABB8-4C24-98A4-1BEEEEDD07C4}" name="output" dataDxfId="192">
+    <tableColumn id="1" xr3:uid="{14CAD510-CB82-4DB3-9F1C-40F2CB704D1C}" name="input" dataDxfId="173"/>
+    <tableColumn id="2" xr3:uid="{5035D4AE-F48A-40D0-AF90-BDA3391536CB}" name="expected" dataDxfId="172"/>
+    <tableColumn id="3" xr3:uid="{99876D23-ABB8-4C24-98A4-1BEEEEDD07C4}" name="output" dataDxfId="171">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.input_k, _xlfn.REGEXEXTRACT(Split_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.input, INDEX(_xlpm.input_k,1,1),
@@ -9743,25 +9737,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A5A07BB4-21F2-4B01-9D44-1AA4366EAB7F}" name="passing" totalsRowFunction="custom" dataDxfId="191" totalsRowDxfId="190">
+    <tableColumn id="4" xr3:uid="{A5A07BB4-21F2-4B01-9D44-1AA4366EAB7F}" name="passing" totalsRowFunction="custom" dataDxfId="170" totalsRowDxfId="169">
       <calculatedColumnFormula>IF(ISERROR(Split_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Split_Tests[[#This Row],[expected]]) = ERROR.TYPE(Split_Tests[[#This Row],[output]]),
     Split_Tests[[#This Row],[expected]] = Split_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Split_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{12903E1A-EF63-4775-8029-4AC6E1371182}" name="test" dataDxfId="189"/>
+    <tableColumn id="5" xr3:uid="{12903E1A-EF63-4775-8029-4AC6E1371182}" name="test" dataDxfId="168"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{B4199465-17FF-401D-8825-47D1965ACDD0}" name="UMatrixSum_Tests" displayName="UMatrixSum_Tests" ref="A186:E191" totalsRowCount="1" dataDxfId="188">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{B4199465-17FF-401D-8825-47D1965ACDD0}" name="UMatrixSum_Tests" displayName="UMatrixSum_Tests" ref="A186:E191" totalsRowCount="1" dataDxfId="167">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{02600896-7D14-484F-821B-B4456983BB28}" name="input" dataDxfId="187"/>
-    <tableColumn id="2" xr3:uid="{173735CF-904D-4F11-81E2-08E18A2E350F}" name="expected" dataDxfId="186"/>
-    <tableColumn id="3" xr3:uid="{39C7D243-2D28-43C6-84E9-009686A8BE25}" name="output" dataDxfId="185">
+    <tableColumn id="1" xr3:uid="{02600896-7D14-484F-821B-B4456983BB28}" name="input" dataDxfId="166"/>
+    <tableColumn id="2" xr3:uid="{173735CF-904D-4F11-81E2-08E18A2E350F}" name="expected" dataDxfId="165"/>
+    <tableColumn id="3" xr3:uid="{39C7D243-2D28-43C6-84E9-009686A8BE25}" name="output" dataDxfId="164">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.limbs_k, _xlfn.REGEXEXTRACT(UMatrixSum_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.limbs, _xlfn.TEXTSPLIT(INDEX(_xlpm.limbs_k,1,1), ",", ";"),
@@ -9770,14 +9764,14 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{708213D7-3DCF-48EE-85F0-411FE836D86B}" name="passing" totalsRowFunction="custom" dataDxfId="184" totalsRowDxfId="183">
+    <tableColumn id="4" xr3:uid="{708213D7-3DCF-48EE-85F0-411FE836D86B}" name="passing" totalsRowFunction="custom" dataDxfId="163" totalsRowDxfId="162">
       <calculatedColumnFormula>IF(ISERROR(UMatrixSum_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UMatrixSum_Tests[[#This Row],[expected]]) = ERROR.TYPE(UMatrixSum_Tests[[#This Row],[output]]),
     UMatrixSum_Tests[[#This Row],[expected]] = UMatrixSum_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UMatrixSum_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{1A2B4059-059A-4B6D-8573-AF782E91D2A9}" name="test" dataDxfId="182"/>
+    <tableColumn id="5" xr3:uid="{1A2B4059-059A-4B6D-8573-AF782E91D2A9}" name="test" dataDxfId="161"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9788,14 +9782,14 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9C2FC9B7-0634-4588-8EFB-AD967A0F24A8}" name="input"/>
     <tableColumn id="2" xr3:uid="{282A94A0-1EBE-4152-8A9A-8F0EF95A0338}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{1B45BBB4-DEF0-4F8A-9D99-3837C2C1D0A6}" name="output" dataDxfId="181">
+    <tableColumn id="3" xr3:uid="{1B45BBB4-DEF0-4F8A-9D99-3837C2C1D0A6}" name="output" dataDxfId="160">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.range, _xlfn.REGEXEXTRACT(Sum_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.big_ints, IFERROR(_xlfn.TEXTSPLIT(INDEX(_xlpm.range,1,1), ",", ";"), ""),
     xlInt.Sum(_xlpm.big_ints)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EE8AD54F-5219-409B-ABCC-BA23AB35B017}" name="passing" totalsRowFunction="custom" dataDxfId="180" totalsRowDxfId="179">
+    <tableColumn id="4" xr3:uid="{EE8AD54F-5219-409B-ABCC-BA23AB35B017}" name="passing" totalsRowFunction="custom" dataDxfId="159" totalsRowDxfId="158">
       <calculatedColumnFormula>IF(ISERROR(Sum_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Sum_Tests[[#This Row],[expected]]) = ERROR.TYPE(Sum_Tests[[#This Row],[output]]),
     Sum_Tests[[#This Row],[expected]] = Sum_Tests[[#This Row],[output]]
@@ -9809,11 +9803,11 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{106EA359-E4B0-4842-9C9A-062E9FF7B5FB}" name="UMul_Tests" displayName="UMul_Tests" ref="A205:E211" totalsRowCount="1" dataDxfId="178">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{106EA359-E4B0-4842-9C9A-062E9FF7B5FB}" name="UMul_Tests" displayName="UMul_Tests" ref="A205:E211" totalsRowCount="1" dataDxfId="157">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8D4F0565-063F-4316-9C57-705162867D2A}" name="input" dataDxfId="177"/>
-    <tableColumn id="2" xr3:uid="{DAD4A921-C714-4DCC-AADE-BAF6086A3636}" name="expected" dataDxfId="176"/>
-    <tableColumn id="3" xr3:uid="{97E6E3DD-CA0A-4372-AC3D-9A495F7C3A53}" name="output" dataDxfId="175">
+    <tableColumn id="1" xr3:uid="{8D4F0565-063F-4316-9C57-705162867D2A}" name="input" dataDxfId="156"/>
+    <tableColumn id="2" xr3:uid="{DAD4A921-C714-4DCC-AADE-BAF6086A3636}" name="expected" dataDxfId="155"/>
+    <tableColumn id="3" xr3:uid="{97E6E3DD-CA0A-4372-AC3D-9A495F7C3A53}" name="output" dataDxfId="154">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(UMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -9825,25 +9819,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E46610B1-FA9D-4582-8D0C-63D1EC61D64E}" name="passing" totalsRowFunction="custom" dataDxfId="174" totalsRowDxfId="173">
+    <tableColumn id="4" xr3:uid="{E46610B1-FA9D-4582-8D0C-63D1EC61D64E}" name="passing" totalsRowFunction="custom" dataDxfId="153" totalsRowDxfId="152">
       <calculatedColumnFormula>IF(ISERROR(UMul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UMul_Tests[[#This Row],[output]]),
     UMul_Tests[[#This Row],[expected]] = UMul_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UMul_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5337E378-248A-4061-ABD9-D618DD84E539}" name="test" dataDxfId="172"/>
+    <tableColumn id="5" xr3:uid="{5337E378-248A-4061-ABD9-D618DD84E539}" name="test" dataDxfId="151"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D11AB36-7D48-42C4-B8E7-63DA272F75B3}" name="SafeK_Tests" displayName="SafeK_Tests" ref="A29:E37" totalsRowCount="1" dataDxfId="271">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D11AB36-7D48-42C4-B8E7-63DA272F75B3}" name="SafeK_Tests" displayName="SafeK_Tests" ref="A29:E37" totalsRowCount="1" dataDxfId="250">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{CD46518C-03B6-4B43-A7B8-7360525A290D}" name="input" dataDxfId="270"/>
-    <tableColumn id="3" xr3:uid="{F3B44865-B013-44C5-A9D4-1A13BFE5AA81}" name="expected" dataDxfId="269"/>
-    <tableColumn id="4" xr3:uid="{F40E0393-EF6C-4B2D-9F49-5CBB088EB267}" name="output" dataDxfId="268">
+    <tableColumn id="2" xr3:uid="{CD46518C-03B6-4B43-A7B8-7360525A290D}" name="input" dataDxfId="249"/>
+    <tableColumn id="3" xr3:uid="{F3B44865-B013-44C5-A9D4-1A13BFE5AA81}" name="expected" dataDxfId="248"/>
+    <tableColumn id="4" xr3:uid="{F40E0393-EF6C-4B2D-9F49-5CBB088EB267}" name="output" dataDxfId="247">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.op_items, _xlfn.REGEXEXTRACT(SafeK_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.op, INDEX(_xlpm.op_items,1,1),
@@ -9852,25 +9846,25 @@
     internal.xlInt.SafeK(_xlpm.op, _xlpm.max_items)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{62988A37-52EF-4F3E-82FE-0F2CD420BEF5}" name="passing" totalsRowFunction="custom" dataDxfId="267">
+    <tableColumn id="5" xr3:uid="{62988A37-52EF-4F3E-82FE-0F2CD420BEF5}" name="passing" totalsRowFunction="custom" dataDxfId="246">
       <calculatedColumnFormula>IF(ISERROR(SafeK_Tests[[#This Row],[expected]]),
     ERROR.TYPE(SafeK_Tests[[#This Row],[expected]]) = ERROR.TYPE(SafeK_Tests[[#This Row],[output]]),
     SafeK_Tests[[#This Row],[expected]] = SafeK_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(SafeK_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{FB9EC421-276B-4C54-8F46-BB5C01271314}" name="test" dataDxfId="266"/>
+    <tableColumn id="6" xr3:uid="{FB9EC421-276B-4C54-8F46-BB5C01271314}" name="test" dataDxfId="245"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C927379E-9D9F-446A-A7F8-18937FDB3BE9}" name="Mul_Tests" displayName="Mul_Tests" ref="A214:E221" totalsRowCount="1" dataDxfId="171">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C927379E-9D9F-446A-A7F8-18937FDB3BE9}" name="Mul_Tests" displayName="Mul_Tests" ref="A214:E221" totalsRowCount="1" dataDxfId="150">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3AEB129A-112F-4626-87D9-516E40338A3B}" name="input" dataDxfId="170" totalsRowDxfId="116"/>
-    <tableColumn id="2" xr3:uid="{17E1D158-0134-4800-97A0-9A914A48AA8F}" name="expected" dataDxfId="169" totalsRowDxfId="115"/>
-    <tableColumn id="3" xr3:uid="{B25D54E8-D438-48E6-9956-B82746478514}" name="output" dataDxfId="168" totalsRowDxfId="114">
+    <tableColumn id="1" xr3:uid="{3AEB129A-112F-4626-87D9-516E40338A3B}" name="input" dataDxfId="149" totalsRowDxfId="148"/>
+    <tableColumn id="2" xr3:uid="{17E1D158-0134-4800-97A0-9A914A48AA8F}" name="expected" dataDxfId="147" totalsRowDxfId="146"/>
+    <tableColumn id="3" xr3:uid="{B25D54E8-D438-48E6-9956-B82746478514}" name="output" dataDxfId="145" totalsRowDxfId="144">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Mul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -9878,25 +9872,25 @@
     xlInt.Mul(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5D503E6C-603A-418E-8D29-E96FF9E82626}" name="passing" totalsRowFunction="custom" dataDxfId="167" totalsRowDxfId="113">
+    <tableColumn id="4" xr3:uid="{5D503E6C-603A-418E-8D29-E96FF9E82626}" name="passing" totalsRowFunction="custom" dataDxfId="143" totalsRowDxfId="142">
       <calculatedColumnFormula>IF(ISERROR(Mul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Mul_Tests[[#This Row],[expected]]) = ERROR.TYPE(Mul_Tests[[#This Row],[output]]),
     Mul_Tests[[#This Row],[expected]] = Mul_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Mul_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{785B4909-13EC-4ABC-ADF8-0A6E8C364AE8}" name="test" dataDxfId="166" totalsRowDxfId="112"/>
+    <tableColumn id="5" xr3:uid="{785B4909-13EC-4ABC-ADF8-0A6E8C364AE8}" name="test" dataDxfId="141" totalsRowDxfId="140"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{4706FBB1-54D9-4F64-9481-F1D8984AE18E}" name="KnuthDiv_Tests" displayName="KnuthDiv_Tests" ref="A224:E233" totalsRowCount="1" dataDxfId="165">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{4706FBB1-54D9-4F64-9481-F1D8984AE18E}" name="KnuthDiv_Tests" displayName="KnuthDiv_Tests" ref="A224:E233" totalsRowCount="1" dataDxfId="139">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C9306945-CA62-4719-882E-A0FFCFC80239}" name="input" dataDxfId="164"/>
-    <tableColumn id="2" xr3:uid="{FF30C91E-2B8D-47FA-B34B-6CA5257E3EB7}" name="expected" dataDxfId="163"/>
-    <tableColumn id="3" xr3:uid="{3B324DA4-4AAE-408C-B627-929F7D5C7CBF}" name="output" dataDxfId="162">
+    <tableColumn id="1" xr3:uid="{C9306945-CA62-4719-882E-A0FFCFC80239}" name="input" dataDxfId="138"/>
+    <tableColumn id="2" xr3:uid="{FF30C91E-2B8D-47FA-B34B-6CA5257E3EB7}" name="expected" dataDxfId="137"/>
+    <tableColumn id="3" xr3:uid="{3B324DA4-4AAE-408C-B627-929F7D5C7CBF}" name="output" dataDxfId="136">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(KnuthDiv_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -9908,25 +9902,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{439AD3AD-5C90-48C6-AB74-B9DDF87C40B5}" name="passing" totalsRowFunction="custom" dataDxfId="161" totalsRowDxfId="160">
+    <tableColumn id="4" xr3:uid="{439AD3AD-5C90-48C6-AB74-B9DDF87C40B5}" name="passing" totalsRowFunction="custom" dataDxfId="135" totalsRowDxfId="134">
       <calculatedColumnFormula>IF(ISERROR(KnuthDiv_Tests[[#This Row],[expected]]),
     ERROR.TYPE(KnuthDiv_Tests[[#This Row],[expected]]) = ERROR.TYPE(KnuthDiv_Tests[[#This Row],[output]]),
     KnuthDiv_Tests[[#This Row],[expected]] = KnuthDiv_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(KnuthDiv_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7D4887A2-EC0B-4C52-8336-E300544022A1}" name="test" dataDxfId="159"/>
+    <tableColumn id="5" xr3:uid="{7D4887A2-EC0B-4C52-8336-E300544022A1}" name="test" dataDxfId="133"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B0C6E940-EAB6-4373-8987-1B7722C2CC79}" name="Div_Tests" displayName="Div_Tests" ref="A236:E247" totalsRowCount="1" dataDxfId="158">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B0C6E940-EAB6-4373-8987-1B7722C2CC79}" name="Div_Tests" displayName="Div_Tests" ref="A236:E247" totalsRowCount="1" dataDxfId="132">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{0A49EAE4-5B09-4D2D-A863-D634A4825565}" name="input" dataDxfId="157" totalsRowDxfId="156"/>
-    <tableColumn id="2" xr3:uid="{4BF042F3-E337-4B63-A1E8-414D47019404}" name="expected" dataDxfId="155" totalsRowDxfId="154"/>
-    <tableColumn id="3" xr3:uid="{118ABB7A-7163-40CB-974E-69BFF6BE2BE0}" name="output" dataDxfId="153" totalsRowDxfId="152">
+    <tableColumn id="1" xr3:uid="{0A49EAE4-5B09-4D2D-A863-D634A4825565}" name="input" dataDxfId="131" totalsRowDxfId="130"/>
+    <tableColumn id="2" xr3:uid="{4BF042F3-E337-4B63-A1E8-414D47019404}" name="expected" dataDxfId="129" totalsRowDxfId="128"/>
+    <tableColumn id="3" xr3:uid="{118ABB7A-7163-40CB-974E-69BFF6BE2BE0}" name="output" dataDxfId="127" totalsRowDxfId="126">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Div_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -9934,25 +9928,25 @@
     xlInt.Div(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4344C6C8-3F96-4048-96D0-CA621258C1D7}" name="passing" totalsRowFunction="custom" dataDxfId="151" totalsRowDxfId="150">
+    <tableColumn id="4" xr3:uid="{4344C6C8-3F96-4048-96D0-CA621258C1D7}" name="passing" totalsRowFunction="custom" dataDxfId="125" totalsRowDxfId="124">
       <calculatedColumnFormula>IF(ISERROR(Div_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Div_Tests[[#This Row],[expected]]) = ERROR.TYPE(Div_Tests[[#This Row],[output]]),
     Div_Tests[[#This Row],[expected]] = Div_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Div_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7CF48835-D05B-4120-863E-A47318569688}" name="test" dataDxfId="149" totalsRowDxfId="148"/>
+    <tableColumn id="5" xr3:uid="{7CF48835-D05B-4120-863E-A47318569688}" name="test" dataDxfId="123" totalsRowDxfId="122"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{B3179C39-4489-4B3E-A2D2-1A2B50DC058E}" name="Mod_Tests" displayName="Mod_Tests" ref="A250:E261" totalsRowCount="1" dataDxfId="147">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{B3179C39-4489-4B3E-A2D2-1A2B50DC058E}" name="Mod_Tests" displayName="Mod_Tests" ref="A250:E261" totalsRowCount="1" dataDxfId="121">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F1BCBD73-ACF5-4609-87F5-A9FAB549955E}" name="input" dataDxfId="146" totalsRowDxfId="145"/>
-    <tableColumn id="2" xr3:uid="{E9604163-FD58-4190-8D72-28AA7831E8C8}" name="expected" dataDxfId="144" totalsRowDxfId="143"/>
-    <tableColumn id="3" xr3:uid="{9D21CE79-D00B-4182-97B3-60EF6DC8B18F}" name="output" dataDxfId="142" totalsRowDxfId="141">
+    <tableColumn id="1" xr3:uid="{F1BCBD73-ACF5-4609-87F5-A9FAB549955E}" name="input" dataDxfId="120" totalsRowDxfId="119"/>
+    <tableColumn id="2" xr3:uid="{E9604163-FD58-4190-8D72-28AA7831E8C8}" name="expected" dataDxfId="118" totalsRowDxfId="117"/>
+    <tableColumn id="3" xr3:uid="{9D21CE79-D00B-4182-97B3-60EF6DC8B18F}" name="output" dataDxfId="116" totalsRowDxfId="115">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Mod_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -9960,25 +9954,25 @@
     xlInt.Mod(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CEF047D2-0521-425D-99C4-E3B997A68B32}" name="passing" totalsRowFunction="custom" dataDxfId="140" totalsRowDxfId="139">
+    <tableColumn id="4" xr3:uid="{CEF047D2-0521-425D-99C4-E3B997A68B32}" name="passing" totalsRowFunction="custom" dataDxfId="114" totalsRowDxfId="113">
       <calculatedColumnFormula>IF(ISERROR(Mod_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Mod_Tests[[#This Row],[expected]]) = ERROR.TYPE(Mod_Tests[[#This Row],[output]]),
     Mod_Tests[[#This Row],[expected]] = Mod_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Mod_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{BB0A3941-EEFB-445E-AE7B-833C36649910}" name="test" dataDxfId="138" totalsRowDxfId="137"/>
+    <tableColumn id="5" xr3:uid="{BB0A3941-EEFB-445E-AE7B-833C36649910}" name="test" dataDxfId="112" totalsRowDxfId="111"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{82953E35-FA6B-4DA1-B4AC-195D4F1BB7C8}" name="DivMod_Tests" displayName="DivMod_Tests" ref="A264:E280" totalsRowCount="1" dataDxfId="136">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{82953E35-FA6B-4DA1-B4AC-195D4F1BB7C8}" name="DivMod_Tests" displayName="DivMod_Tests" ref="A264:E280" totalsRowCount="1" dataDxfId="110">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E51BC97B-AA0D-4705-AF36-89CB4A3501FF}" name="input" dataDxfId="135" totalsRowDxfId="111"/>
-    <tableColumn id="2" xr3:uid="{6D6483DD-139D-4DFE-BFEA-8BAA3E5C6FCF}" name="expected" dataDxfId="134" totalsRowDxfId="110"/>
-    <tableColumn id="3" xr3:uid="{17DE90BB-4525-4C2D-9577-C4372DCD74B3}" name="output" dataDxfId="133" totalsRowDxfId="109">
+    <tableColumn id="1" xr3:uid="{E51BC97B-AA0D-4705-AF36-89CB4A3501FF}" name="input" dataDxfId="109" totalsRowDxfId="108"/>
+    <tableColumn id="2" xr3:uid="{6D6483DD-139D-4DFE-BFEA-8BAA3E5C6FCF}" name="expected" dataDxfId="107" totalsRowDxfId="106"/>
+    <tableColumn id="3" xr3:uid="{17DE90BB-4525-4C2D-9577-C4372DCD74B3}" name="output" dataDxfId="105" totalsRowDxfId="104">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.ab_flag, _xlfn.REGEXEXTRACT(DivMod_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab_flag,1,1),
@@ -9987,25 +9981,25 @@
     _xlfn.ARRAYTOTEXT(xlInt.DivMod(_xlpm.a, _xlpm.b, _xlpm.use_floor), 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{08745616-1601-437B-82EA-C1952393A99B}" name="passing" totalsRowFunction="custom" dataDxfId="132" totalsRowDxfId="108">
+    <tableColumn id="4" xr3:uid="{08745616-1601-437B-82EA-C1952393A99B}" name="passing" totalsRowFunction="custom" dataDxfId="103" totalsRowDxfId="102">
       <calculatedColumnFormula>IF(ISERROR(DivMod_Tests[[#This Row],[expected]]),
     ERROR.TYPE(DivMod_Tests[[#This Row],[expected]]) = ERROR.TYPE(DivMod_Tests[[#This Row],[output]]),
     DivMod_Tests[[#This Row],[expected]] = DivMod_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(DivMod_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{10C8AB14-1CD9-4B06-8A65-2B27B32A2550}" name="test" dataDxfId="131" totalsRowDxfId="107"/>
+    <tableColumn id="5" xr3:uid="{10C8AB14-1CD9-4B06-8A65-2B27B32A2550}" name="test" dataDxfId="101" totalsRowDxfId="100"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{3400C680-561E-4111-B80A-CA24DB597E3F}" name="Table25" displayName="Table25" ref="A283:E289" totalsRowCount="1" dataDxfId="130">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{3400C680-561E-4111-B80A-CA24DB597E3F}" name="Table25" displayName="Table25" ref="A283:E289" totalsRowCount="1" dataDxfId="99">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{37EA378F-E179-45E1-BF1A-FBA82C305DBA}" name="input" dataDxfId="129"/>
-    <tableColumn id="2" xr3:uid="{11DFB020-1D5E-4E26-A86F-6B73428F3709}" name="expected" dataDxfId="128"/>
-    <tableColumn id="3" xr3:uid="{943FD3EB-6145-4BEE-9408-F68BE0795A47}" name="output" dataDxfId="127">
+    <tableColumn id="1" xr3:uid="{37EA378F-E179-45E1-BF1A-FBA82C305DBA}" name="input" dataDxfId="98"/>
+    <tableColumn id="2" xr3:uid="{11DFB020-1D5E-4E26-A86F-6B73428F3709}" name="expected" dataDxfId="97"/>
+    <tableColumn id="3" xr3:uid="{943FD3EB-6145-4BEE-9408-F68BE0795A47}" name="output" dataDxfId="96">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.bk, _xlfn.REGEXEXTRACT(Table25[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.b, INDEX(_xlpm.bk,1,1),
@@ -10015,49 +10009,49 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{165ECACC-11AD-4EB0-AE14-7D528DA64799}" name="passing" totalsRowFunction="custom" dataDxfId="126" totalsRowDxfId="125">
+    <tableColumn id="4" xr3:uid="{165ECACC-11AD-4EB0-AE14-7D528DA64799}" name="passing" totalsRowFunction="custom" dataDxfId="95" totalsRowDxfId="94">
       <calculatedColumnFormula>IF(ISERROR(Table25[[#This Row],[expected]]),
     ERROR.TYPE(Table25[[#This Row],[expected]]) = ERROR.TYPE(Table25[[#This Row],[output]]),
     Table25[[#This Row],[expected]] = Table25[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Table25[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6FA8F2E3-9F29-41C5-8B60-45E4EF5BFD33}" name="test" dataDxfId="124"/>
+    <tableColumn id="5" xr3:uid="{6FA8F2E3-9F29-41C5-8B60-45E4EF5BFD33}" name="test" dataDxfId="93"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{12A27437-8E10-4142-9D59-10A781936664}" name="IsEven_Tests" displayName="IsEven_Tests" ref="A292:E301" totalsRowCount="1" tableBorderDxfId="123">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{12A27437-8E10-4142-9D59-10A781936664}" name="IsEven_Tests" displayName="IsEven_Tests" ref="A292:E301" totalsRowCount="1" tableBorderDxfId="92">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{72B34F2A-D724-472B-AEA6-85847044F8BB}" name="input"/>
     <tableColumn id="2" xr3:uid="{8F1A9828-E68A-40FE-8534-E28D2B59C43A}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{90993922-EF49-4320-BFDE-A85AAC37995B}" name="output" dataDxfId="120">
+    <tableColumn id="3" xr3:uid="{90993922-EF49-4320-BFDE-A85AAC37995B}" name="output" dataDxfId="91">
       <calculatedColumnFormula array="1">BigInt.IsEven(IsEven_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4CD10349-78F4-4A08-8AD3-6AFDD4218B3F}" name="passing" totalsRowFunction="custom" dataDxfId="119">
+    <tableColumn id="4" xr3:uid="{4CD10349-78F4-4A08-8AD3-6AFDD4218B3F}" name="passing" totalsRowFunction="custom" dataDxfId="90">
       <calculatedColumnFormula>IF(ISERROR(IsEven_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsEven_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsEven_Tests[[#This Row],[output]]),
     IsEven_Tests[[#This Row],[expected]] = IsEven_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(IsEven_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9C811914-2121-4942-94F0-B4760C307266}" name="test" dataDxfId="118"/>
+    <tableColumn id="5" xr3:uid="{9C811914-2121-4942-94F0-B4760C307266}" name="test" dataDxfId="89"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{29B30C5B-F766-4073-878A-FEDF3C607366}" name="IsOdd_Tests" displayName="IsOdd_Tests" ref="A304:E313" totalsRowCount="1" tableBorderDxfId="122">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{29B30C5B-F766-4073-878A-FEDF3C607366}" name="IsOdd_Tests" displayName="IsOdd_Tests" ref="A304:E313" totalsRowCount="1" tableBorderDxfId="88">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8D247229-1BE2-49B1-BEC8-19AFBBF671FC}" name="input"/>
     <tableColumn id="2" xr3:uid="{9F1FC5CC-11FA-4EB1-BA6E-3C18F4379652}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{6B07B988-F191-4E41-81FA-8D0020D0AEF2}" name="output" dataDxfId="117">
+    <tableColumn id="3" xr3:uid="{6B07B988-F191-4E41-81FA-8D0020D0AEF2}" name="output" dataDxfId="87">
       <calculatedColumnFormula array="1">BigInt.IsOdd(IsOdd_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{15820A65-99F4-420C-A89B-1F6FB8202BCC}" name="passing" totalsRowFunction="custom" dataDxfId="121">
+    <tableColumn id="4" xr3:uid="{15820A65-99F4-420C-A89B-1F6FB8202BCC}" name="passing" totalsRowFunction="custom" dataDxfId="86">
       <calculatedColumnFormula>IF(ISERROR(IsOdd_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsOdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsOdd_Tests[[#This Row],[output]]),
     IsOdd_Tests[[#This Row],[expected]] = IsOdd_Tests[[#This Row],[output]]
@@ -10071,11 +10065,11 @@
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{371705AE-DD2A-4348-9D77-10A58AFED934}" name="Pow_Tests" displayName="Pow_Tests" ref="A327:E341" totalsRowCount="1" dataDxfId="101">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{371705AE-DD2A-4348-9D77-10A58AFED934}" name="Pow_Tests" displayName="Pow_Tests" ref="A327:E341" totalsRowCount="1" dataDxfId="85">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{428DC074-F3C2-4541-81E6-FDDAE2482D27}" name="input" dataDxfId="106"/>
-    <tableColumn id="2" xr3:uid="{B5FD2A40-BCC5-4580-B8CD-768791024AC5}" name="expected" dataDxfId="105"/>
-    <tableColumn id="3" xr3:uid="{F4E39208-EEA5-4CF3-B04A-4707F3E1FB8E}" name="output" dataDxfId="104">
+    <tableColumn id="1" xr3:uid="{428DC074-F3C2-4541-81E6-FDDAE2482D27}" name="input" dataDxfId="84"/>
+    <tableColumn id="2" xr3:uid="{B5FD2A40-BCC5-4580-B8CD-768791024AC5}" name="expected" dataDxfId="83"/>
+    <tableColumn id="3" xr3:uid="{F4E39208-EEA5-4CF3-B04A-4707F3E1FB8E}" name="output" dataDxfId="82">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab, 1, 1),
@@ -10083,25 +10077,25 @@
     BigInt.Pow(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B407AC33-1B59-4CB2-91F2-8CA96B7CE117}" name="passing" totalsRowFunction="custom" dataDxfId="103">
+    <tableColumn id="4" xr3:uid="{B407AC33-1B59-4CB2-91F2-8CA96B7CE117}" name="passing" totalsRowFunction="custom" dataDxfId="81">
       <calculatedColumnFormula>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
     Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Pow_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A1A7E0C2-F1B0-41A5-A740-EDF94ACD6051}" name="test" dataDxfId="102"/>
+    <tableColumn id="5" xr3:uid="{A1A7E0C2-F1B0-41A5-A740-EDF94ACD6051}" name="test" dataDxfId="80"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{83160072-B1B0-4FD1-88FC-006B8639CBE0}" name="UPow_Tests" displayName="UPow_Tests" ref="A316:E324" totalsRowCount="1" dataDxfId="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{83160072-B1B0-4FD1-88FC-006B8639CBE0}" name="UPow_Tests" displayName="UPow_Tests" ref="A316:E324" totalsRowCount="1" dataDxfId="79">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{20145995-7ED4-4B73-887D-9D74DA0828CF}" name="input" dataDxfId="100"/>
-    <tableColumn id="2" xr3:uid="{82FBC2F1-B0A2-4D85-8D2F-0E9C3548EF52}" name="expected" dataDxfId="99"/>
-    <tableColumn id="3" xr3:uid="{30FC05F3-7A85-4F3C-B4CB-146B4FEBD37A}" name="output" dataDxfId="95">
+    <tableColumn id="1" xr3:uid="{20145995-7ED4-4B73-887D-9D74DA0828CF}" name="input" dataDxfId="78"/>
+    <tableColumn id="2" xr3:uid="{82FBC2F1-B0A2-4D85-8D2F-0E9C3548EF52}" name="expected" dataDxfId="77"/>
+    <tableColumn id="3" xr3:uid="{30FC05F3-7A85-4F3C-B4CB-146B4FEBD37A}" name="output" dataDxfId="76">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.bek, _xlfn.REGEXEXTRACT(UPow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.base, INDEX(_xlpm.bek,1,1),
@@ -10112,14 +10106,14 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{13DDE135-8BB6-470E-A96F-6482CA5075E2}" name="passing" totalsRowFunction="custom" dataDxfId="98">
+    <tableColumn id="4" xr3:uid="{13DDE135-8BB6-470E-A96F-6482CA5075E2}" name="passing" totalsRowFunction="custom" dataDxfId="75">
       <calculatedColumnFormula>IF(ISERROR(UPow_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UPow_Tests[[#This Row],[expected]]) = ERROR.TYPE(UPow_Tests[[#This Row],[output]]),
     UPow_Tests[[#This Row],[expected]] = UPow_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UPow_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{45AF5A50-06F2-4581-B704-1F7379E7EFDB}" name="test" dataDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{45AF5A50-06F2-4581-B704-1F7379E7EFDB}" name="test" dataDxfId="74"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10130,7 +10124,7 @@
   <tableColumns count="5">
     <tableColumn id="2" xr3:uid="{2286D15B-F261-49FF-90E5-E32FAEEEA489}" name="input"/>
     <tableColumn id="3" xr3:uid="{1D45A0AC-7049-4C3E-9D4F-CF777F60006B}" name="expected"/>
-    <tableColumn id="4" xr3:uid="{725B7147-ED3D-42D7-9030-A0FCAF6502D0}" name="output" dataDxfId="265">
+    <tableColumn id="4" xr3:uid="{725B7147-ED3D-42D7-9030-A0FCAF6502D0}" name="output" dataDxfId="244">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.limbs_k, _xlfn.REGEXEXTRACT(Merge_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.limbs_text, INDEX(_xlpm.limbs_k,1,1),
@@ -10139,20 +10133,111 @@
     internal.xlInt.Merge(_xlpm.limbs, _xlpm.k)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7D40DA54-4D50-4770-9171-9F50106783D7}" name="passing" totalsRowFunction="custom" dataDxfId="264">
+    <tableColumn id="5" xr3:uid="{7D40DA54-4D50-4770-9171-9F50106783D7}" name="passing" totalsRowFunction="custom" dataDxfId="243">
       <calculatedColumnFormula>IF(ISERROR(Merge_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Merge_Tests[[#This Row],[expected]]) = ERROR.TYPE(Merge_Tests[[#This Row],[output]]),
     Merge_Tests[[#This Row],[expected]] = Merge_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Merge_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F906F95B-0DD5-4F50-9A36-C63DEC4B514C}" name="test" dataDxfId="263"/>
+    <tableColumn id="6" xr3:uid="{F906F95B-0DD5-4F50-9A36-C63DEC4B514C}" name="test" dataDxfId="242"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{56E07932-566C-4BD6-8077-730BDDB685D7}" name="USqrt_Tests" displayName="USqrt_Tests" ref="A344:E348" totalsRowCount="1" dataDxfId="67">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{7D0B28FD-9EB7-4A3D-892B-9C8FB4B3B2F5}" name="input" dataDxfId="72"/>
+    <tableColumn id="2" xr3:uid="{CFF29D88-DF87-4564-930E-26EAF1CB3332}" name="expected" dataDxfId="71"/>
+    <tableColumn id="3" xr3:uid="{4738BA38-2D1B-4B90-8625-6A923FAABAE8}" name="output" dataDxfId="70">
+      <calculatedColumnFormula array="1">_xlfn.LET(
+    _xlpm.radicand_seed_k, _xlfn.REGEXEXTRACT(USqrt_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.radicand, INDEX(_xlpm.radicand_seed_k,1,1),
+    _xlpm.seed, INDEX(_xlpm.radicand_seed_k,1,2),
+    _xlpm.k, --INDEX(_xlpm.radicand_seed_k,1,3),
+    _xlpm.limbs_radicand, --_xlfn.TEXTSPLIT(_xlpm.radicand,",",";"),
+    _xlpm.limbs_seed, --_xlfn.TEXTSPLIT(_xlpm.seed,",",";"),
+    _xlpm.output, core_BigInt.USqrt(_xlpm.limbs_radicand, _xlpm.limbs_seed, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{118D95C4-A916-4992-AEA0-6F30E3EE33F9}" name="passing" totalsRowFunction="custom" dataDxfId="69" totalsRowDxfId="73">
+      <calculatedColumnFormula>IF(ISERROR(USqrt_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(USqrt_Tests[[#This Row],[expected]]) = ERROR.TYPE(USqrt_Tests[[#This Row],[output]]),
+    USqrt_Tests[[#This Row],[expected]] = USqrt_Tests[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(USqrt_Tests[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{36AF6E6D-247D-40D4-8B02-20DF4A48BDF2}" name="test" dataDxfId="68"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{A9B2C3B0-D156-4BA1-8DBC-CCD97E178DEB}" name="NewtonRaphsonReciprocal_Tests" displayName="NewtonRaphsonReciprocal_Tests" ref="A351:E356" totalsRowCount="1" dataDxfId="63">
+  <autoFilter ref="A351:E355" xr:uid="{A9B2C3B0-D156-4BA1-8DBC-CCD97E178DEB}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{668CC6CC-FAA8-4201-AF7C-80B23CDDC2E9}" name="input" dataDxfId="65"/>
+    <tableColumn id="2" xr3:uid="{25DCB2CE-672E-4637-9E18-5B6DB9547223}" name="expected" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{90B5F5EA-1862-438B-A0B0-E7B33D47B422}" name="output" dataDxfId="62">
+      <calculatedColumnFormula array="1">_xlfn.LET(
+    _xlpm.b_len_k, _xlfn.REGEXEXTRACT(NewtonRaphsonReciprocal_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.b, INDEX(_xlpm.b_len_k,1,1),
+    _xlpm.target_len, INDEX(_xlpm.b_len_k,1,2),
+    _xlpm.k, --INDEX(_xlpm.b_len_k,1,3),
+    _xlpm.limbs_b, --_xlfn.TEXTSPLIT(_xlpm.b,",",";"),
+    _xlpm.output, core_BigInt.NewtonRaphsonReciprocal(_xlpm.limbs_b, _xlpm.target_len, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{A229F032-C11B-467F-A66D-15E5E90AC98D}" name="passing" totalsRowFunction="custom" dataDxfId="61" totalsRowDxfId="66">
+      <calculatedColumnFormula>IF(ISERROR(NewtonRaphsonReciprocal_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NewtonRaphsonReciprocal_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonReciprocal_Tests[[#This Row],[output]]),
+    NewtonRaphsonReciprocal_Tests[[#This Row],[expected]] = NewtonRaphsonReciprocal_Tests[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(NewtonRaphsonReciprocal_Tests[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{F159BE0D-B6F5-4516-9322-421576A9CFAC}" name="test" dataDxfId="60"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{9E5B9787-3CCB-4F73-B127-FE62EEB658A9}" name="NewtonRaphsonDiv_Tests" displayName="NewtonRaphsonDiv_Tests" ref="A359:E365" totalsRowCount="1" dataDxfId="59">
+  <autoFilter ref="A359:E364" xr:uid="{9E5B9787-3CCB-4F73-B127-FE62EEB658A9}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{1DD49B57-7E7E-4B1C-B300-6AC09AA4507D}" name="input" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{F726FD71-2E54-4ACE-8BDB-45E8C22B8958}" name="expected" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{51451E9D-81A3-4433-AABC-FCAE4ED0B82C}" name="output" dataDxfId="53">
+      <calculatedColumnFormula array="1">_xlfn.LET(
+    _xlpm.abk, _xlfn.REGEXEXTRACT(NewtonRaphsonDiv_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.abk,1,1),
+    _xlpm.b, INDEX(_xlpm.abk,1,2),
+    _xlpm.k, --INDEX(_xlpm.abk,1,3),
+    _xlpm.limbs_a, --_xlfn.TEXTSPLIT(_xlpm.a,",",";"),
+    _xlpm.limbs_b, --_xlfn.TEXTSPLIT(_xlpm.b,",",";"),
+    _xlpm.output, core_BigInt.NewtonRaphsonDiv(_xlpm.limbs_a, _xlpm.limbs_b, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{3511251B-5389-4721-A1A1-8AE06E90F9D7}" name="passing" totalsRowFunction="custom" dataDxfId="54" totalsRowDxfId="56">
+      <calculatedColumnFormula>IF(ISERROR(NewtonRaphsonDiv_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[output]]),
+    NewtonRaphsonDiv_Tests[[#This Row],[expected]] = NewtonRaphsonDiv_Tests[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(NewtonRaphsonDiv_Tests[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{8FBD496E-700B-47C8-B9CA-AD0871776B53}" name="test" dataDxfId="55"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{C1458AB7-3AD7-44E9-B064-C2BEC4A41762}" name="Data" displayName="Data" ref="A1:B8" totalsRowShown="0">
   <autoFilter ref="A1:B8" xr:uid="{C1458AB7-3AD7-44E9-B064-C2BEC4A41762}"/>
   <tableColumns count="2">
@@ -10164,14 +10249,14 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{8BE14E9C-9052-4C6B-91B5-74156B78161B}" name="IsZero_Tests" displayName="IsZero_Tests" ref="A63:E71" totalsRowCount="1" tableBorderDxfId="262">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{8BE14E9C-9052-4C6B-91B5-74156B78161B}" name="IsZero_Tests" displayName="IsZero_Tests" ref="A63:E71" totalsRowCount="1" tableBorderDxfId="241">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F079B266-FBE5-40B3-929D-6B075F83B32A}" name="input"/>
     <tableColumn id="2" xr3:uid="{D2EFB528-67FC-4490-876A-C72813F17A1C}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{735E5B6C-B3DA-49E2-B1F3-88323DE570B4}" name="output" dataDxfId="261">
+    <tableColumn id="3" xr3:uid="{735E5B6C-B3DA-49E2-B1F3-88323DE570B4}" name="output" dataDxfId="240">
       <calculatedColumnFormula array="1">xlInt.IsZero(IsZero_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BCB92B9B-DD7D-407D-BA1B-01844C06231A}" name="passing" totalsRowFunction="custom" dataDxfId="260">
+    <tableColumn id="4" xr3:uid="{BCB92B9B-DD7D-407D-BA1B-01844C06231A}" name="passing" totalsRowFunction="custom" dataDxfId="239">
       <calculatedColumnFormula>IF(ISERROR(IsZero_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsZero_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsZero_Tests[[#This Row],[output]]),
     IsZero_Tests[[#This Row],[expected]] = IsZero_Tests[[#This Row],[output]]
@@ -10185,14 +10270,14 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{5F9E4160-7872-486B-BC10-496D23C60B5A}" name="IsNeg_Tests" displayName="IsNeg_Tests" ref="A74:E82" totalsRowCount="1" tableBorderDxfId="259">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{5F9E4160-7872-486B-BC10-496D23C60B5A}" name="IsNeg_Tests" displayName="IsNeg_Tests" ref="A74:E82" totalsRowCount="1" tableBorderDxfId="238">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A7BB892B-ECAA-4176-AFC6-3449690829CA}" name="input"/>
     <tableColumn id="2" xr3:uid="{4B67C433-DA3F-4DC8-A14F-97407C2E1925}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{49ED0D04-2AA3-4848-8297-CAE5A7D726CD}" name="output" dataDxfId="258">
+    <tableColumn id="3" xr3:uid="{49ED0D04-2AA3-4848-8297-CAE5A7D726CD}" name="output" dataDxfId="237">
       <calculatedColumnFormula array="1">xlInt.IsNeg(IsNeg_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{186FF00B-FED3-490C-BB63-2A0FC55A43D4}" name="passing" totalsRowFunction="custom" dataDxfId="257">
+    <tableColumn id="4" xr3:uid="{186FF00B-FED3-490C-BB63-2A0FC55A43D4}" name="passing" totalsRowFunction="custom" dataDxfId="236">
       <calculatedColumnFormula>IF(ISERROR(IsNeg_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsNeg_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsNeg_Tests[[#This Row],[output]]),
     IsNeg_Tests[[#This Row],[expected]] = IsNeg_Tests[[#This Row],[output]]
@@ -10206,14 +10291,14 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1631B68B-6D5A-402C-92F6-EDA45141B375}" name="Abs_Tests" displayName="Abs_Tests" ref="A85:E94" totalsRowCount="1" tableBorderDxfId="256">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1631B68B-6D5A-402C-92F6-EDA45141B375}" name="Abs_Tests" displayName="Abs_Tests" ref="A85:E94" totalsRowCount="1" tableBorderDxfId="235">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{631C43FF-F966-4712-8BEB-7647066AF179}" name="input"/>
     <tableColumn id="2" xr3:uid="{70F5476C-B45C-439B-BA01-326EAD467334}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{1E90CD50-A25E-4E12-84D5-66BAAE6BAF0C}" name="output" dataDxfId="255">
+    <tableColumn id="3" xr3:uid="{1E90CD50-A25E-4E12-84D5-66BAAE6BAF0C}" name="output" dataDxfId="234">
       <calculatedColumnFormula array="1">BigInt.Abs(Abs_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6A0B92CA-92B2-4515-86E8-D91A4279D44E}" name="passing" totalsRowFunction="custom" dataDxfId="254">
+    <tableColumn id="4" xr3:uid="{6A0B92CA-92B2-4515-86E8-D91A4279D44E}" name="passing" totalsRowFunction="custom" dataDxfId="233">
       <calculatedColumnFormula>IF(ISERROR(Abs_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Abs_Tests[[#This Row],[expected]]) = ERROR.TYPE(Abs_Tests[[#This Row],[output]]),
     Abs_Tests[[#This Row],[expected]] = Abs_Tests[[#This Row],[output]]
@@ -10227,11 +10312,11 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{A4A096D6-4E75-4455-A80B-D324779CD007}" name="Compare_Tests" displayName="Compare_Tests" ref="A97:E104" totalsRowCount="1" dataDxfId="253" tableBorderDxfId="252">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{A4A096D6-4E75-4455-A80B-D324779CD007}" name="Compare_Tests" displayName="Compare_Tests" ref="A97:E104" totalsRowCount="1" dataDxfId="232" tableBorderDxfId="231">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{6ED51130-CCEE-49F5-AE6A-C115477DEEC1}" name="input" dataDxfId="251"/>
-    <tableColumn id="3" xr3:uid="{33B3A3D6-83B3-431F-A0B0-9371BBC16D08}" name="expected" dataDxfId="250"/>
-    <tableColumn id="4" xr3:uid="{C0A2BAFD-DD64-4B6D-8350-F0AF699F41AB}" name="output" dataDxfId="249">
+    <tableColumn id="2" xr3:uid="{6ED51130-CCEE-49F5-AE6A-C115477DEEC1}" name="input" dataDxfId="230"/>
+    <tableColumn id="3" xr3:uid="{33B3A3D6-83B3-431F-A0B0-9371BBC16D08}" name="expected" dataDxfId="229"/>
+    <tableColumn id="4" xr3:uid="{C0A2BAFD-DD64-4B6D-8350-F0AF699F41AB}" name="output" dataDxfId="228">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Compare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -10239,25 +10324,25 @@
     xlInt.Compare(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{25151C64-2D6E-4B12-87AA-02A64ED9EF2B}" name="passing" totalsRowFunction="custom" dataDxfId="248">
+    <tableColumn id="5" xr3:uid="{25151C64-2D6E-4B12-87AA-02A64ED9EF2B}" name="passing" totalsRowFunction="custom" dataDxfId="227">
       <calculatedColumnFormula>IF(ISERROR(Compare_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Compare_Tests[[#This Row],[expected]]) = ERROR.TYPE(Compare_Tests[[#This Row],[output]]),
     Compare_Tests[[#This Row],[expected]] = Compare_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Compare_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D859FAE6-EDFC-42C5-8B0C-0116D05E04F4}" name="test" dataDxfId="247"/>
+    <tableColumn id="6" xr3:uid="{D859FAE6-EDFC-42C5-8B0C-0116D05E04F4}" name="test" dataDxfId="226"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{AB2483E8-D478-4FD2-B96C-83A98FDDE6FA}" name="Carry_Tests" displayName="Carry_Tests" ref="A107:E114" totalsRowCount="1" dataDxfId="246">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{AB2483E8-D478-4FD2-B96C-83A98FDDE6FA}" name="Carry_Tests" displayName="Carry_Tests" ref="A107:E114" totalsRowCount="1" dataDxfId="225">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{58CF3EAC-5FAD-4E1D-8349-AFD0026A5A6F}" name="input" dataDxfId="245"/>
-    <tableColumn id="3" xr3:uid="{8D4EBB1D-1F70-4D9A-B9FB-C7B03997C3F4}" name="expected" dataDxfId="244"/>
-    <tableColumn id="4" xr3:uid="{54C37EF8-27DA-477C-BC79-632DD5E54F03}" name="output" dataDxfId="243">
+    <tableColumn id="2" xr3:uid="{58CF3EAC-5FAD-4E1D-8349-AFD0026A5A6F}" name="input" dataDxfId="224"/>
+    <tableColumn id="3" xr3:uid="{8D4EBB1D-1F70-4D9A-B9FB-C7B03997C3F4}" name="expected" dataDxfId="223"/>
+    <tableColumn id="4" xr3:uid="{54C37EF8-27DA-477C-BC79-632DD5E54F03}" name="output" dataDxfId="222">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.limbs_k, _xlfn.REGEXEXTRACT(Carry_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.limbs_text, INDEX(_xlpm.limbs_k,1,1),
@@ -10267,25 +10352,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9B430B30-AE60-423D-A6BE-D7D881CBC2A0}" name="passing" totalsRowFunction="custom" dataDxfId="242">
+    <tableColumn id="5" xr3:uid="{9B430B30-AE60-423D-A6BE-D7D881CBC2A0}" name="passing" totalsRowFunction="custom" dataDxfId="221">
       <calculatedColumnFormula>IF(ISERROR(Carry_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Carry_Tests[[#This Row],[expected]]) = ERROR.TYPE(Carry_Tests[[#This Row],[output]]),
     Carry_Tests[[#This Row],[expected]] = Carry_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Carry_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{5F961C10-163D-49CE-93C1-9CA6C9C623CA}" name="test" dataDxfId="241"/>
+    <tableColumn id="6" xr3:uid="{5F961C10-163D-49CE-93C1-9CA6C9C623CA}" name="test" dataDxfId="220"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{9541B332-DEB4-4260-9226-40E8C97DC59F}" name="UAdd_Tests" displayName="UAdd_Tests" ref="A117:E124" totalsRowCount="1" dataDxfId="240" tableBorderDxfId="239">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{9541B332-DEB4-4260-9226-40E8C97DC59F}" name="UAdd_Tests" displayName="UAdd_Tests" ref="A117:E124" totalsRowCount="1" dataDxfId="219" tableBorderDxfId="218">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{6C5FB7CE-3B1F-447E-9ED3-14E839061137}" name="input" dataDxfId="238"/>
-    <tableColumn id="3" xr3:uid="{56E7CDEA-877C-47CA-B875-1A1313998480}" name="expected" dataDxfId="237"/>
-    <tableColumn id="4" xr3:uid="{0AB7FE18-4035-4604-909F-956B1054DE95}" name="output" dataDxfId="236">
+    <tableColumn id="2" xr3:uid="{6C5FB7CE-3B1F-447E-9ED3-14E839061137}" name="input" dataDxfId="217"/>
+    <tableColumn id="3" xr3:uid="{56E7CDEA-877C-47CA-B875-1A1313998480}" name="expected" dataDxfId="216"/>
+    <tableColumn id="4" xr3:uid="{0AB7FE18-4035-4604-909F-956B1054DE95}" name="output" dataDxfId="215">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(UAdd_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -10297,14 +10382,14 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{148597F1-9D9D-45C9-949B-CA15D869DE95}" name="passing" totalsRowFunction="custom" dataDxfId="235">
+    <tableColumn id="5" xr3:uid="{148597F1-9D9D-45C9-949B-CA15D869DE95}" name="passing" totalsRowFunction="custom" dataDxfId="214">
       <calculatedColumnFormula>IF(ISERROR(UAdd_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UAdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(UAdd_Tests[[#This Row],[output]]),
     UAdd_Tests[[#This Row],[expected]] = UAdd_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UAdd_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{58290239-17D2-42FA-BE94-887F938260F4}" name="test" dataDxfId="234"/>
+    <tableColumn id="6" xr3:uid="{58290239-17D2-42FA-BE94-887F938260F4}" name="test" dataDxfId="213"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10627,7 +10712,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="1261" row="6">
+  <wetp:taskpane dockstate="right" visibility="0" width="892" row="6">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -10659,12 +10744,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23AD1BF5-F75F-465D-AC38-22DFE6D4806A}">
-  <dimension ref="A1:E365"/>
+  <dimension ref="A1:E391"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="23.6328125" customWidth="1"/>
-    <col min="2" max="2" width="24.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.36328125" customWidth="1"/>
+    <col min="1" max="1" width="27.54296875" customWidth="1"/>
+    <col min="2" max="2" width="26.6328125" customWidth="1"/>
+    <col min="3" max="3" width="24.6328125" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
     <col min="5" max="5" width="66.453125" bestFit="1" customWidth="1"/>
   </cols>
@@ -10684,7 +10769,7 @@
       </c>
       <c r="B2">
         <f>COUNTIF(_xlfn._TRO_TRAILING(A:A), "input")</f>
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -10692,17 +10777,17 @@
         <v>140</v>
       </c>
       <c r="B3" cm="1">
-        <f t="array" ref="B3">SUM(--ISLOGICAL(_xlfn._TRO_TRAILING(D:D))) - $B$2</f>
-        <v>221</v>
+        <f t="array" aca="1" ref="B3" ca="1">SUM(--ISNUMBER(SEARCH("[@expected] = [@output]", _xlfn.FORMULATEXT(_xlfn._TRO_TRAILING(D:D)))))</f>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="B4">
-        <f>COUNTIF(_xlfn._TRO_TRAILING(D:D), TRUE) - $B$2</f>
-        <v>221</v>
+      <c r="B4" cm="1">
+        <f t="array" aca="1" ref="B4" ca="1">SUM(ISNUMBER(SEARCH("[@expected] = [@output]", _xlfn.FORMULATEXT(_xlfn._TRO_TRAILING(D:D)))) * (_xlfn._TRO_TRAILING(D:D) = TRUE))</f>
+        <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1"/>
@@ -16425,7 +16510,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+    <row r="286" spans="1:5" ht="29" hidden="1" outlineLevel="1">
       <c r="A286" s="12" t="s">
         <v>406</v>
       </c>
@@ -16563,7 +16648,7 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="E293" s="18" t="s">
+      <c r="E293" t="s">
         <v>472</v>
       </c>
     </row>
@@ -16585,7 +16670,7 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="E294" s="18" t="s">
+      <c r="E294" t="s">
         <v>470</v>
       </c>
     </row>
@@ -16607,7 +16692,7 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="E295" s="18" t="s">
+      <c r="E295" t="s">
         <v>471</v>
       </c>
     </row>
@@ -16629,7 +16714,7 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="E296" s="18" t="s">
+      <c r="E296" t="s">
         <v>473</v>
       </c>
     </row>
@@ -16651,7 +16736,7 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="E297" s="18" t="s">
+      <c r="E297" t="s">
         <v>474</v>
       </c>
     </row>
@@ -16673,7 +16758,7 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="E298" s="18" t="s">
+      <c r="E298" t="s">
         <v>475</v>
       </c>
     </row>
@@ -16682,18 +16767,18 @@
       <c r="B299" t="b">
         <v>1</v>
       </c>
-      <c r="C299" s="19" t="b" cm="1">
+      <c r="C299" t="b" cm="1">
         <f t="array" ref="C299">BigInt.IsEven(IsEven_Tests[[#This Row],[input]])</f>
         <v>1</v>
       </c>
-      <c r="D299" s="19" t="b">
+      <c r="D299" t="b">
         <f>IF(ISERROR(IsEven_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsEven_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsEven_Tests[[#This Row],[output]]),
     IsEven_Tests[[#This Row],[expected]] = IsEven_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E299" s="18" t="s">
+      <c r="E299" t="s">
         <v>476</v>
       </c>
     </row>
@@ -16715,7 +16800,7 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="E300" s="18" t="s">
+      <c r="E300" t="s">
         <v>477</v>
       </c>
     </row>
@@ -16890,11 +16975,11 @@
       <c r="B311" t="b">
         <v>0</v>
       </c>
-      <c r="C311" s="19" t="b" cm="1">
+      <c r="C311" t="b" cm="1">
         <f t="array" ref="C311">BigInt.IsOdd(IsOdd_Tests[[#This Row],[input]])</f>
         <v>0</v>
       </c>
-      <c r="D311" s="19" t="b">
+      <c r="D311" t="b">
         <f>IF(ISERROR(IsOdd_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsOdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsOdd_Tests[[#This Row],[output]]),
     IsOdd_Tests[[#This Row],[expected]] = IsOdd_Tests[[#This Row],[output]]
@@ -17374,7 +17459,7 @@
       <c r="B334" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="C334" s="20" t="str" cm="1">
+      <c r="C334" s="9" t="str" cm="1">
         <f t="array" ref="C334">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab, 1, 1),
@@ -17383,7 +17468,7 @@
 )</f>
         <v>2</v>
       </c>
-      <c r="D334" s="20" t="b">
+      <c r="D334" s="9" t="b">
         <f>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
     Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
@@ -17563,234 +17648,739 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:2">
-      <c r="A361" cm="1">
-        <f t="array" ref="A361:A362">LEN(B361:B362)</f>
-        <v>22</v>
-      </c>
-      <c r="B361" t="str" cm="1">
-        <f t="array" ref="B361">BigInt.Pow(B364, B365)</f>
-        <v>1176246293903439668001</v>
-      </c>
-    </row>
-    <row r="362" spans="1:2">
-      <c r="A362">
-        <v>22</v>
-      </c>
-      <c r="B362" t="str" cm="1">
-        <f t="array" ref="B362">_xlfn._xlws.PY(0,0,B364,B365)</f>
-        <v>1176246293903439668001</v>
-      </c>
-    </row>
-    <row r="363" spans="1:2">
-      <c r="B363" t="b">
-        <f>B361 = B362</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="364" spans="1:2">
-      <c r="B364">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="365" spans="1:2">
-      <c r="B365">
+    <row r="342" spans="1:5" ht="15" thickBot="1"/>
+    <row r="343" spans="1:5" ht="18.5">
+      <c r="A343" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="B343" s="5"/>
+      <c r="C343" s="5"/>
+      <c r="D343" s="5"/>
+      <c r="E343" s="5"/>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" t="s">
+        <v>110</v>
+      </c>
+      <c r="B344" t="s">
+        <v>35</v>
+      </c>
+      <c r="C344" t="s">
+        <v>36</v>
+      </c>
+      <c r="D344" t="s">
+        <v>48</v>
+      </c>
+      <c r="E344" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A345" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="B345" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C345" s="9" t="str" cm="1">
+        <f t="array" ref="C345">_xlfn.LET(
+    _xlpm.radicand_seed_k, _xlfn.REGEXEXTRACT(USqrt_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.radicand, INDEX(_xlpm.radicand_seed_k,1,1),
+    _xlpm.seed, INDEX(_xlpm.radicand_seed_k,1,2),
+    _xlpm.k, --INDEX(_xlpm.radicand_seed_k,1,3),
+    _xlpm.limbs_radicand, --_xlfn.TEXTSPLIT(_xlpm.radicand,",",";"),
+    _xlpm.limbs_seed, --_xlfn.TEXTSPLIT(_xlpm.seed,",",";"),
+    _xlpm.output, core_BigInt.USqrt(_xlpm.limbs_radicand, _xlpm.limbs_seed, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{3}</v>
+      </c>
+      <c r="D345" s="9" t="b">
+        <f>IF(ISERROR(USqrt_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(USqrt_Tests[[#This Row],[expected]]) = ERROR.TYPE(USqrt_Tests[[#This Row],[output]]),
+    USqrt_Tests[[#This Row],[expected]] = USqrt_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E345" s="9" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A346" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="B346" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="C346" s="9" t="str" cm="1">
+        <f t="array" ref="C346">_xlfn.LET(
+    _xlpm.radicand_seed_k, _xlfn.REGEXEXTRACT(USqrt_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.radicand, INDEX(_xlpm.radicand_seed_k,1,1),
+    _xlpm.seed, INDEX(_xlpm.radicand_seed_k,1,2),
+    _xlpm.k, --INDEX(_xlpm.radicand_seed_k,1,3),
+    _xlpm.limbs_radicand, --_xlfn.TEXTSPLIT(_xlpm.radicand,",",";"),
+    _xlpm.limbs_seed, --_xlfn.TEXTSPLIT(_xlpm.seed,",",";"),
+    _xlpm.output, core_BigInt.USqrt(_xlpm.limbs_radicand, _xlpm.limbs_seed, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{10}</v>
+      </c>
+      <c r="D346" s="9" t="b">
+        <f>IF(ISERROR(USqrt_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(USqrt_Tests[[#This Row],[expected]]) = ERROR.TYPE(USqrt_Tests[[#This Row],[output]]),
+    USqrt_Tests[[#This Row],[expected]] = USqrt_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E346" s="18" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A347" s="12" t="s">
+        <v>571</v>
+      </c>
+      <c r="B347" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="C347" s="9" t="str" cm="1">
+        <f t="array" ref="C347">_xlfn.LET(
+    _xlpm.radicand_seed_k, _xlfn.REGEXEXTRACT(USqrt_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.radicand, INDEX(_xlpm.radicand_seed_k,1,1),
+    _xlpm.seed, INDEX(_xlpm.radicand_seed_k,1,2),
+    _xlpm.k, --INDEX(_xlpm.radicand_seed_k,1,3),
+    _xlpm.limbs_radicand, --_xlfn.TEXTSPLIT(_xlpm.radicand,",",";"),
+    _xlpm.limbs_seed, --_xlfn.TEXTSPLIT(_xlpm.seed,",",";"),
+    _xlpm.output, core_BigInt.USqrt(_xlpm.limbs_radicand, _xlpm.limbs_seed, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{3641828;351}</v>
+      </c>
+      <c r="D347" s="9" t="b">
+        <f>IF(ISERROR(USqrt_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(USqrt_Tests[[#This Row],[expected]]) = ERROR.TYPE(USqrt_Tests[[#This Row],[output]]),
+    USqrt_Tests[[#This Row],[expected]] = USqrt_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E347" s="9" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" collapsed="1">
+      <c r="D348" s="9" t="b">
+        <f>AND(USqrt_Tests[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" ht="15" thickBot="1"/>
+    <row r="350" spans="1:5" ht="18.5">
+      <c r="A350" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="B350" s="5"/>
+      <c r="C350" s="5"/>
+      <c r="D350" s="5"/>
+      <c r="E350" s="5"/>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" t="s">
+        <v>110</v>
+      </c>
+      <c r="B351" t="s">
+        <v>35</v>
+      </c>
+      <c r="C351" t="s">
+        <v>36</v>
+      </c>
+      <c r="D351" t="s">
+        <v>48</v>
+      </c>
+      <c r="E351" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A352" s="12" t="s">
+        <v>544</v>
+      </c>
+      <c r="B352" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C352" s="9" t="str" cm="1">
+        <f t="array" ref="C352">_xlfn.LET(
+    _xlpm.b_len_k, _xlfn.REGEXEXTRACT(NewtonRaphsonReciprocal_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.b, INDEX(_xlpm.b_len_k,1,1),
+    _xlpm.target_len, INDEX(_xlpm.b_len_k,1,2),
+    _xlpm.k, --INDEX(_xlpm.b_len_k,1,3),
+    _xlpm.limbs_b, --_xlfn.TEXTSPLIT(_xlpm.b,",",";"),
+    _xlpm.output, core_BigInt.NewtonRaphsonReciprocal(_xlpm.limbs_b, _xlpm.target_len, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{3333333;3333333}</v>
+      </c>
+      <c r="D352" s="9" t="b">
+        <f>IF(ISERROR(NewtonRaphsonReciprocal_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NewtonRaphsonReciprocal_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonReciprocal_Tests[[#This Row],[output]]),
+    NewtonRaphsonReciprocal_Tests[[#This Row],[expected]] = NewtonRaphsonReciprocal_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E352" s="18" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A353" s="12" t="s">
+        <v>545</v>
+      </c>
+      <c r="B353" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="C353" s="9" t="str" cm="1">
+        <f t="array" ref="C353">_xlfn.LET(
+    _xlpm.b_len_k, _xlfn.REGEXEXTRACT(NewtonRaphsonReciprocal_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.b, INDEX(_xlpm.b_len_k,1,1),
+    _xlpm.target_len, INDEX(_xlpm.b_len_k,1,2),
+    _xlpm.k, --INDEX(_xlpm.b_len_k,1,3),
+    _xlpm.limbs_b, --_xlfn.TEXTSPLIT(_xlpm.b,",",";"),
+    _xlpm.output, core_BigInt.NewtonRaphsonReciprocal(_xlpm.limbs_b, _xlpm.target_len, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{0;0;0;5000000}</v>
+      </c>
+      <c r="D353" s="9" t="b">
+        <f>IF(ISERROR(NewtonRaphsonReciprocal_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NewtonRaphsonReciprocal_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonReciprocal_Tests[[#This Row],[output]]),
+    NewtonRaphsonReciprocal_Tests[[#This Row],[expected]] = NewtonRaphsonReciprocal_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E353" s="18" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A354" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="B354" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="C354" s="9" t="str" cm="1">
+        <f t="array" ref="C354">_xlfn.LET(
+    _xlpm.b_len_k, _xlfn.REGEXEXTRACT(NewtonRaphsonReciprocal_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.b, INDEX(_xlpm.b_len_k,1,1),
+    _xlpm.target_len, INDEX(_xlpm.b_len_k,1,2),
+    _xlpm.k, --INDEX(_xlpm.b_len_k,1,3),
+    _xlpm.limbs_b, --_xlfn.TEXTSPLIT(_xlpm.b,",",";"),
+    _xlpm.output, core_BigInt.NewtonRaphsonReciprocal(_xlpm.limbs_b, _xlpm.target_len, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{2733835;3966724;11234}</v>
+      </c>
+      <c r="D354" s="9" t="b">
+        <f>IF(ISERROR(NewtonRaphsonReciprocal_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NewtonRaphsonReciprocal_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonReciprocal_Tests[[#This Row],[output]]),
+    NewtonRaphsonReciprocal_Tests[[#This Row],[expected]] = NewtonRaphsonReciprocal_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E354" s="18" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A355" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="B355" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="C355" s="9" t="str" cm="1">
+        <f t="array" ref="C355">_xlfn.LET(
+    _xlpm.b_len_k, _xlfn.REGEXEXTRACT(NewtonRaphsonReciprocal_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.b, INDEX(_xlpm.b_len_k,1,1),
+    _xlpm.target_len, INDEX(_xlpm.b_len_k,1,2),
+    _xlpm.k, --INDEX(_xlpm.b_len_k,1,3),
+    _xlpm.limbs_b, --_xlfn.TEXTSPLIT(_xlpm.b,",",";"),
+    _xlpm.output, core_BigInt.NewtonRaphsonReciprocal(_xlpm.limbs_b, _xlpm.target_len, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{0;0;0;0;1}</v>
+      </c>
+      <c r="D355" s="9" t="b">
+        <f>IF(ISERROR(NewtonRaphsonReciprocal_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NewtonRaphsonReciprocal_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonReciprocal_Tests[[#This Row],[output]]),
+    NewtonRaphsonReciprocal_Tests[[#This Row],[expected]] = NewtonRaphsonReciprocal_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E355" s="18" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" collapsed="1">
+      <c r="D356" s="9" t="b">
+        <f>AND(NewtonRaphsonReciprocal_Tests[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" ht="15" thickBot="1"/>
+    <row r="358" spans="1:5" ht="18.5">
+      <c r="A358" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="B358" s="5"/>
+      <c r="C358" s="5"/>
+      <c r="D358" s="5"/>
+      <c r="E358" s="5"/>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" t="s">
+        <v>110</v>
+      </c>
+      <c r="B359" t="s">
+        <v>35</v>
+      </c>
+      <c r="C359" t="s">
+        <v>36</v>
+      </c>
+      <c r="D359" t="s">
+        <v>48</v>
+      </c>
+      <c r="E359" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A360" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="B360" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="C360" s="9" t="str" cm="1">
+        <f t="array" ref="C360">_xlfn.LET(
+    _xlpm.abk, _xlfn.REGEXEXTRACT(NewtonRaphsonDiv_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.abk,1,1),
+    _xlpm.b, INDEX(_xlpm.abk,1,2),
+    _xlpm.k, --INDEX(_xlpm.abk,1,3),
+    _xlpm.limbs_a, --_xlfn.TEXTSPLIT(_xlpm.a,",",";"),
+    _xlpm.limbs_b, --_xlfn.TEXTSPLIT(_xlpm.b,",",";"),
+    _xlpm.output, core_BigInt.NewtonRaphsonDiv(_xlpm.limbs_a, _xlpm.limbs_b, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{2;9744480;224;3641827;351}</v>
+      </c>
+      <c r="D360" s="9" t="b">
+        <f>IF(ISERROR(NewtonRaphsonDiv_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[output]]),
+    NewtonRaphsonDiv_Tests[[#This Row],[expected]] = NewtonRaphsonDiv_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E360" s="18" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A361" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="B361" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="C361" s="9" t="str" cm="1">
+        <f t="array" ref="C361">_xlfn.LET(
+    _xlpm.abk, _xlfn.REGEXEXTRACT(NewtonRaphsonDiv_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.abk,1,1),
+    _xlpm.b, INDEX(_xlpm.abk,1,2),
+    _xlpm.k, --INDEX(_xlpm.abk,1,3),
+    _xlpm.limbs_a, --_xlfn.TEXTSPLIT(_xlpm.a,",",";"),
+    _xlpm.limbs_b, --_xlfn.TEXTSPLIT(_xlpm.b,",",";"),
+    _xlpm.output, core_BigInt.NewtonRaphsonDiv(_xlpm.limbs_a, _xlpm.limbs_b, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{1;1;3333333;3333333}</v>
+      </c>
+      <c r="D361" s="9" t="b">
+        <f>IF(ISERROR(NewtonRaphsonDiv_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[output]]),
+    NewtonRaphsonDiv_Tests[[#This Row],[expected]] = NewtonRaphsonDiv_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E361" s="18" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A362" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="B362" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="C362" s="9" t="str" cm="1">
+        <f t="array" ref="C362">_xlfn.LET(
+    _xlpm.abk, _xlfn.REGEXEXTRACT(NewtonRaphsonDiv_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.abk,1,1),
+    _xlpm.b, INDEX(_xlpm.abk,1,2),
+    _xlpm.k, --INDEX(_xlpm.abk,1,3),
+    _xlpm.limbs_a, --_xlfn.TEXTSPLIT(_xlpm.a,",",";"),
+    _xlpm.limbs_b, --_xlfn.TEXTSPLIT(_xlpm.b,",",";"),
+    _xlpm.output, core_BigInt.NewtonRaphsonDiv(_xlpm.limbs_a, _xlpm.limbs_b, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{1;999999;0}</v>
+      </c>
+      <c r="D362" s="9" t="b">
+        <f>IF(ISERROR(NewtonRaphsonDiv_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[output]]),
+    NewtonRaphsonDiv_Tests[[#This Row],[expected]] = NewtonRaphsonDiv_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E362" s="18" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A363" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="B363" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="C363" s="9" t="str" cm="1">
+        <f t="array" ref="C363">_xlfn.LET(
+    _xlpm.abk, _xlfn.REGEXEXTRACT(NewtonRaphsonDiv_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.abk,1,1),
+    _xlpm.b, INDEX(_xlpm.abk,1,2),
+    _xlpm.k, --INDEX(_xlpm.abk,1,3),
+    _xlpm.limbs_a, --_xlfn.TEXTSPLIT(_xlpm.a,",",";"),
+    _xlpm.limbs_b, --_xlfn.TEXTSPLIT(_xlpm.b,",",";"),
+    _xlpm.output, core_BigInt.NewtonRaphsonDiv(_xlpm.limbs_a, _xlpm.limbs_b, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{1;0;12}</v>
+      </c>
+      <c r="D363" s="9" t="b">
+        <f>IF(ISERROR(NewtonRaphsonDiv_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[output]]),
+    NewtonRaphsonDiv_Tests[[#This Row],[expected]] = NewtonRaphsonDiv_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E363" s="18" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" ht="43.5" hidden="1" outlineLevel="1">
+      <c r="A364" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="B364" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="C364" s="19" t="str" cm="1">
+        <f t="array" ref="C364">_xlfn.LET(
+    _xlpm.abk, _xlfn.REGEXEXTRACT(NewtonRaphsonDiv_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.abk,1,1),
+    _xlpm.b, INDEX(_xlpm.abk,1,2),
+    _xlpm.k, --INDEX(_xlpm.abk,1,3),
+    _xlpm.limbs_a, --_xlfn.TEXTSPLIT(_xlpm.a,",",";"),
+    _xlpm.limbs_b, --_xlfn.TEXTSPLIT(_xlpm.b,",",";"),
+    _xlpm.output, core_BigInt.NewtonRaphsonDiv(_xlpm.limbs_a, _xlpm.limbs_b, _xlpm.k),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{1;0;0;0;10}</v>
+      </c>
+      <c r="D364" s="19" t="b">
+        <f>IF(ISERROR(NewtonRaphsonDiv_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[output]]),
+    NewtonRaphsonDiv_Tests[[#This Row],[expected]] = NewtonRaphsonDiv_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E364" s="18" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" collapsed="1">
+      <c r="D365" s="9" t="b">
+        <f>AND(NewtonRaphsonDiv_Tests[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2"/>
+      <c r="B368" s="2"/>
+    </row>
+    <row r="373" ht="14.5" customHeight="1"/>
+    <row r="376" ht="14.5" customHeight="1"/>
+    <row r="379" ht="14.5" customHeight="1"/>
+    <row r="382" ht="14.5" customHeight="1"/>
+    <row r="385" spans="1:2" ht="14.5" customHeight="1"/>
+    <row r="387" spans="1:2">
+      <c r="A387" cm="1">
+        <f t="array" ref="A387:A388">LEN(B387:B388)</f>
+        <v>5</v>
+      </c>
+      <c r="B387" t="str" cm="1">
+        <f t="array" ref="B387">BigInt.Sqrt(B390)</f>
+        <v>46340</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388">
+        <v>5</v>
+      </c>
+      <c r="B388" t="str" cm="1">
+        <f t="array" ref="B388">_xlfn._xlws.PY(0,0,B390,B391)</f>
+        <v>46340</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="B389" t="b">
+        <f>B387 = B388</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390">
+        <f>LEN(B390)</f>
+        <v>10</v>
+      </c>
+      <c r="B390" s="2">
+        <f>2^31-1</f>
+        <v>2147483647</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="B391">
         <v>12</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B389">
+    <cfRule type="cellIs" dxfId="52" priority="7" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D8:D26 D150:D160 D265:D280 D284:D289 D317:D324">
-    <cfRule type="expression" dxfId="46" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="76" stopIfTrue="1">
       <formula>$D8</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="71">
+    <cfRule type="expression" dxfId="50" priority="77">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:D37 D86:D94 D118:D124">
-    <cfRule type="expression" dxfId="44" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="74" stopIfTrue="1">
       <formula>$D30</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="69">
+    <cfRule type="expression" dxfId="48" priority="75">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41:D46">
-    <cfRule type="expression" dxfId="42" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="70" stopIfTrue="1">
       <formula>$D41</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="65">
+    <cfRule type="expression" dxfId="46" priority="71">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:D60">
-    <cfRule type="expression" dxfId="40" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="60" stopIfTrue="1">
       <formula>$D50</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="55">
+    <cfRule type="expression" dxfId="44" priority="61">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D64:D71">
-    <cfRule type="expression" dxfId="38" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="68" stopIfTrue="1">
       <formula>$D64</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="63">
+    <cfRule type="expression" dxfId="42" priority="69">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75:D82">
-    <cfRule type="expression" dxfId="36" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="66" stopIfTrue="1">
       <formula>$D75</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="61">
+    <cfRule type="expression" dxfId="40" priority="67">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D98:D104">
-    <cfRule type="expression" dxfId="34" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="58" stopIfTrue="1">
       <formula>$D98</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="53">
+    <cfRule type="expression" dxfId="38" priority="59">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:D114">
-    <cfRule type="expression" dxfId="32" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="56" stopIfTrue="1">
       <formula>$D108</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="51">
+    <cfRule type="expression" dxfId="36" priority="57">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D128:D135">
-    <cfRule type="expression" dxfId="30" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="52" stopIfTrue="1">
       <formula>$D128</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="47">
+    <cfRule type="expression" dxfId="34" priority="53">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D139:D146">
-    <cfRule type="expression" dxfId="28" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="50" stopIfTrue="1">
       <formula>$D139</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="45">
+    <cfRule type="expression" dxfId="32" priority="51">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D164:D169">
-    <cfRule type="expression" dxfId="26" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="44" stopIfTrue="1">
       <formula>$D164</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="39">
+    <cfRule type="expression" dxfId="30" priority="45">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D173:D176">
-    <cfRule type="expression" dxfId="24" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="42" stopIfTrue="1">
       <formula>$D173</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="37">
+    <cfRule type="expression" dxfId="28" priority="43">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D180:D183">
-    <cfRule type="expression" dxfId="22" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="38" stopIfTrue="1">
       <formula>$D180</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="33">
+    <cfRule type="expression" dxfId="26" priority="39">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D187:D191">
-    <cfRule type="expression" dxfId="20" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="36" stopIfTrue="1">
       <formula>$D187</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="31">
+    <cfRule type="expression" dxfId="24" priority="37">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D195:D202">
-    <cfRule type="expression" dxfId="18" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="34" stopIfTrue="1">
       <formula>$D195</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="29">
+    <cfRule type="expression" dxfId="22" priority="35">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D206:D211">
-    <cfRule type="expression" dxfId="16" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="30" stopIfTrue="1">
       <formula>$D206</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="25">
+    <cfRule type="expression" dxfId="20" priority="31">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D215:D221">
-    <cfRule type="expression" dxfId="14" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="28" stopIfTrue="1">
       <formula>$D215</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="23">
+    <cfRule type="expression" dxfId="18" priority="29">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D225:D233">
-    <cfRule type="expression" dxfId="12" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="24" stopIfTrue="1">
       <formula>$D225</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="19">
+    <cfRule type="expression" dxfId="16" priority="25">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D237:D247">
-    <cfRule type="expression" dxfId="10" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="22" stopIfTrue="1">
       <formula>$D237</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="17">
+    <cfRule type="expression" dxfId="14" priority="23">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D251:D261">
-    <cfRule type="expression" dxfId="8" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="20" stopIfTrue="1">
       <formula>$D251</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="15">
+    <cfRule type="expression" dxfId="12" priority="21">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D293:D301">
-    <cfRule type="expression" dxfId="6" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="14" stopIfTrue="1">
       <formula>$D293</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="9">
+    <cfRule type="expression" dxfId="10" priority="15">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D305:D313">
-    <cfRule type="expression" dxfId="4" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="12" stopIfTrue="1">
       <formula>$D305</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="7">
+    <cfRule type="expression" dxfId="8" priority="13">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D328:D341">
-    <cfRule type="expression" dxfId="2" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="10" stopIfTrue="1">
       <formula>$D328</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="6" priority="11">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B363">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="D345:D348">
+    <cfRule type="expression" dxfId="5" priority="5" stopIfTrue="1">
+      <formula>$D345</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="6">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D352:D356">
+    <cfRule type="expression" dxfId="3" priority="3" stopIfTrue="1">
+      <formula>$D352</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="4">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D360:D365">
+    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
+      <formula>$D360</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="29">
+  <tableParts count="32">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -17820,6 +18410,9 @@
     <tablePart r:id="rId28"/>
     <tablePart r:id="rId29"/>
     <tablePart r:id="rId30"/>
+    <tablePart r:id="rId31"/>
+    <tablePart r:id="rId32"/>
+    <tablePart r:id="rId33"/>
   </tableParts>
 </worksheet>
 </file>
@@ -18054,7 +18647,7 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAFwAbgAvAC8AIABCAGkAZwAgAEkAbgB0AGUAZwBlAHIAIABBAHIAaQB0AGgAbQBlAHQAaQBjACAATABpAGIAcgBhAHIAeQAgAC8ALwBcAG4ALwAvACAAIAAgACAAIAAgACAAdABlAHMAdABfAEIAaQBnAEkAbgB0ACAATQBvAGQAdQBsAGUAIAAgACAAIAAgACAAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIAAgAFAAcgBpAHYAYQB0AGUAIABUAGUAcwB0AGkAbgBnACAAQQBQAEkAIAAgACAAIAAgACAALwAvAFwAbgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4AXABuAEsAbgB1AHQAaABEAGkAdgBpAHMAaQBvAG4APQBMAEEATQBCAEQAQQAoAGEALAAgAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2ACgAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYQAsACAAawApACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABiACwAIABrACkALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAEQAUgBPAFAAKABwAGEAYwBrAGUAZAAsACAASQBOAEQARQBYACgAcABhAGMAawBlAGQALAAgADEALAAgADEAKQAgACsAIAAxACkALAAgAGsAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAgAD0AIABMAEEATQBCAEQAQQAoAGEALAAgAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgAoAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAGEALAAgAGsAKQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYgAsACAAawApACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABEAFIATwBQACgAcABhAGMAawBlAGQALAAgAEkATgBEAEUAWAAoAHAAYQBjAGsAZQBkACwAIAAxACwAIAAxACkAIAArACAAMQApACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAcwB0AHIAaQBuAGcAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAHMAdAByAGkAbgBnAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG0AbwBkAGUAIABcACIASwBOAFUAVABIAFwAIgAgAG8AcgAgAFwAIgBOAFIAXAAiAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGkAdABlAHIAcwAgAEkAbgBuAGUAcgAgAGwAbwBvAHAAIABjAG8AdQBuAHQAIAAoAHQAbwAgAGQAZQBmAGUAYQB0ACAAYwBoAHUAbgBrAHkAIABjAGwAbwBjAGsAIAByAGUAcwBvAGwAdQB0AGkAbwBuACkAXABuACAAKgAgAEAAcABhAHIAYQBtACAAcgBlAHAAZQBhAHQAcwAgAE8AdQB0AGUAcgAgAGwAbwBvAHAAIABjAG8AdQBuAHQAIAAoAHQAbwAgAGQAZQBmAGUAYQB0ACAATwBTAC8ARwBhAHIAYgBhAGcAZQAgAEMAbwBsAGwAZQBjAHQAaQBvAG4AIABuAG8AaQBzAGUAKQBcAG4AIAAqAC8AXABuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACAAPQAgAEwAQQBNAEIARABBACgAYQAsACAAYgAsACAAbQBvAGQAZQAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAE0AYQBwACAAdABoAGUAIABvAHUAdABlAHIAIAByAGUAcABlAGEAdABzACAAbABvAG8AcABcAG4AIAAgACAAIAAgACAAIAAgAGIAYQB0AGMAaABfAHQAaQBtAGUAcwAsACAATQBBAFAAKABTAEUAUQBVAEUATgBDAEUAKAByAGUAcABlAGEAdABzACkALAAgAEwAQQBNAEIARABBACgAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdAAsACAATgBPAFcAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATQBhAHAAIAB0AGgAZQAgAGkAbgBuAGUAcgAgAGUAeABlAGMAdQB0AGkAbwBuACAAbABvAG8AcABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAHUAbgAsACAASQBGACgAbQBvAGQAZQAgAD0AIABcACIASwBOAFUAVABIAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBQACgAUwBFAFEAVQBFAE4AQwBFACgAaQB0AGUAcgBzACkALAAgAEwAQQBNAEIARABBACgAaQAsACAASwBuAHUAdABoAEQAaQB2AGkAcwBpAG8AbgAoAGEALAAgAGIAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFAAKABTAEUAUQBVAEUATgBDAEUAKABpAHQAZQByAHMAKQAsACAATABBAE0AQgBEAEEAKABpACwAIABOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAoAGEALAAgAGIAKQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEYAbwByAGMAZQAgAGUAdgBhAGwAdQBhAHQAaQBvAG4AIABiAGUAZgBvAHIAZQAgAHAAdQBsAGwAaQBuAGcAIABzAHQAbwBwACAAdABpAG0AZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAbwBwACwAIABOAE8AVwAoACkAIAArACAAKAAwACAAKgAgAEwARQBOACgASQBOAEQARQBYACgAcgB1AG4ALAAgADEALAAgADEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABUAG8AdABhAGwAIABiAGEAdABjAGgAIAB0AGkAbQBlACAAaQBuACAAbQBpAGwAbABpAHMAZQBjAG8AbgBkAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABzAHQAbwBwACAALQAgAHMAdABhAHIAdAApACAAKgAgADgANgA0ADAAMAAwADAAMABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAdABoAGUAIABjAGwAZQBhAG4AZQBzAHQAIAByAHUAbgAgAGEAbgBkACAAYQB2AGUAcgBhAGcAZQAgAGkAdAAgAGQAbwB3AG4AIAB0AG8AIABhACAAcwBpAG4AZwBsAGUAIABlAHgAZQBjAHUAdABpAG8AbgAgAHQAaQBtAGUAXABuACAAIAAgACAAIAAgACAAIABNAEkATgAoAGIAYQB0AGMAaABfAHQAaQBtAGUAcwApACAALwAgAGkAdABlAHIAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAARQB4AGUAYwB1AHQAZQBzACAAYQAgAHMAdAByAGkAYwB0AGwAeQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABiAGUAbgBjAGgAbQBhAHIAawAgAHMAdQBpAHQAZQAgAHQAbwAgAGEAdgBvAGkAZAAgAG0AdQBsAHQAaQAtAHQAaAByAGUAYQBkAGkAbgBnACAAYwBvAG4AdABhAG0AaQBuAGEAdABpAG8AbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHQAZQBzAHQAXwBjAGEAcwBlAHMAIABBAG4AIABOACAAeAAgADIAIABhAHIAcgBhAHkAIABvAGYAIAB0AGUAcwB0ACAAbABlAG4AZwB0AGgAcwA6ACAAWwBMAGUAbgBnAHQAaABfAEEALAAgAEwAZQBuAGcAdABoAF8AQgBdAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGkAdABlAHIAcwAgAE4AdQBtAGIAZQByACAAbwBmACAAaQB0AGUAcgBhAHQAaQBvAG4AcwAgAHAAZQByACAAYgBlAG4AYwBoAG0AYQByAGsAIAB0AG8AIABzAG0AbwBvAHQAaAAgAE4ATwBXACgAKQAgAHIAZQBzAG8AbAB1AHQAaQBvAG4ALgBcAG4AIAAqAC8AXABuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBDAG8AbQBwAGEAcgBpAHMAbwBuACAAPQAgAEwAQQBNAEIARABBACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwB0AGUAcwB0AHMALAAgAFIATwBXAFMAKAB0AGUAcwB0AF8AYwBhAHMAZQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAASQBuAGkAdABpAGEAbAAgAHMAdABhAHQAZQA6ACAARABhAHQAYQAgAGgAZQBhAGQAZQByAHMAIABmAG8AcgAgAEMAUwBWACAAZQB4AHAAbwByAHQAXABuACAAIAAgACAAIAAgACAAIABpAG4AaQB0AGkAYQBsACwAIAB7AFwAIgBMAGUAbgBfAEEAXAAiACwAIABcACIATABlAG4AXwBCAFwAIgAsACAAXAAiAEsAbgB1AHQAaABfAG0AcwBcACIALAAgAFwAIgBOAFIAXwBtAHMAXAAiAH0ALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsACwAIABTAEUAUQBVAEUATgBDAEUAKABuAF8AdABlAHMAdABzACkALAAgAEwAQQBNAEIARABBACgAYQBjAGMALAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAEkATgBEAEUAWAAoAHQAZQBzAHQAXwBjAGEAcwBlAHMALAAgAGkALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAASQBOAEQARQBYACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBrAGkAcAAgAEQAaQB2AGkAcwBvAHIAIAA+ACAARABpAHYAaQBkAGUAbgBkABQgaQB0ACcAcwAgAG4AZQB2AGUAcgAgAGEAbgAgAGkAbgB0AGUAZwBlAHIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbABlAG4AXwBiACAAPgAgAGwAZQBuAF8AYQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAYwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARwBlAG4AZQByAGEAdABlACAAZQB4AGEAYwB0AC0AbABlAG4AZwB0AGgAIAB0AGUAcwB0ACAAcwB0AHIAaQBuAGcAcwAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AHIAXwBhACwAIABSAEUAUABUACgAXAAiADkAXAAiACwAIABsAGUAbgBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAcgBfAGIALAAgAEkARgAoAGwAZQBuAF8AYgAgAD0AIAAxACwAIABcACIANwBcACIALAAgAFwAIgA3AFwAIgAgACYAIABSAEUAUABUACgAXAAiADMAXAAiACwAIABsAGUAbgBfAGIAIAAtACAAMQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeABlAGMAdQB0AGUAIABiAGUAbgBjAGgAbQBhAHIAawBzACAAcwB0AHIAaQBjAHQAbAB5ACAAbwBuAGUAIABhAGYAdABlAHIAIAB0AGgAZQAgAG8AdABoAGUAcgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABpAG0AZQBfAGsALAAgAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACgAcwB0AHIAXwBhACwAIABzAHQAcgBfAGIALAAgAFwAIgBLAE4AVQBUAEgAXAAiACwAIABpAHQAZQByAHMALAAgAHIAZQBwAGUAYQB0AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGkAbQBlAF8AbgByACwAIABEAGkAdgBpAHMAaQBvAG4AQQBsAGcAbwByAGkAdABoAG0AcwAoAHMAdAByAF8AYQAsACAAcwB0AHIAXwBiACwAIABcACIATgBSAFwAIgAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAcABwAGUAbgBkACAAdABoAGUAIAByAGUAcwB1AGwAdABzAC4AIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAGEAbABsAG8AYwBhAHQAaQBvAG4AIABkAGUAbABhAHkAIABvAGMAYwB1AHIAcwAgAGgAZQByAGUALAAgAHMAYQBmAGUAbAB5ACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAdABpAG0AZQBkACAAdwBpAG4AZABvAHcALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABhAGMAYwAsACAASABTAFQAQQBDAEsAKABsAGUAbgBfAGEALAAgAGwAZQBuAF8AYgAsACAAdABpAG0AZQBfAGsALAAgAHQAaQBtAGUAXwBuAHIAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgADIALQBjAG8AbAB1AG0AbgAgAGEAcgByAGEAeQAgAG8AZgAgAGUAdgBlAHIAeQAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgAgAG8AZgAgAGwAZQBuAGcAdABoAHMAXABuAEQAaQB2AGkAcwBpAG8AbgBCAGUAbgBjAGgAbQBhAHIAawBDAGEAcwBlAHMAIAA9ACAATABBAE0AQgBEAEEAKABzAHQAYQByAHQAXwBsAGUAbgAsACAAbQBhAHgAXwBsAGUAbgAsACAAcwB0AGUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQAsACAAUwBFAFEAVQBFAE4AQwBFACgAKABtAGEAeABfAGwAZQBuACAALQAgAHMAdABhAHIAdABfAGwAZQBuACkAIAAvACAAcwB0AGUAcAAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBsAGUAbgAsACAAcwB0AGUAcAApACwAXABuACAAIAAgACAAIAAgACAAIABuACwAIABSAE8AVwBTACgAcwBlAHEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDACsAKwAgAHMAdAB5AGwAZQAgAEMAYQByAHQAZQBzAGkAYQBuACAASgBvAGkAbgBcAG4AIAAgACAAIAAgACAAIAAgAGMAbwBsAF8AYQAsACAAVABPAEMATwBMACgASQBGACgAUwBFAFEAVQBFAE4AQwBFACgAMQAsACAAbgApACwAIABzAGUAcQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAGMAbwBsAF8AYgAsACAAVABPAEMATwBMACgASQBGACgAUwBFAFEAVQBFAE4AQwBFACgAbgAsACAAMQApACwAIABUAE8AUgBPAFcAKABzAGUAcQApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAGMAbwBsAF8AYQAsACAAYwBvAGwAXwBiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAvACAARwBlAG4AZQByAGEAdABlAHMAIABhACAAQwBhAHIAdABlAHMAaQBhAG4AIABnAHIAaQBkACAAZgByAG8AbQAgAHQAdwBvACAAaQBuAGQAZQBwAGUAbgBkAGUAbgB0ACAAcwBlAHEAdQBlAG4AYwBlAHMAXABuAEEAcwB5AG0AbQBlAHQAcgBpAGMAQQBCAEcAcgBpAGQAIAA9ACAATABBAE0AQgBEAEEAKABzAHQAYQByAHQAXwBhACwAIABtAGEAeABfAGEALAAgAHMAdABlAHAAXwBhACwAIABzAHQAYQByAHQAXwBiACwAIABtAGEAeABfAGIALAAgAHMAdABlAHAAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQBxAF8AYQAsACAAUwBFAFEAVQBFAE4AQwBFACgAKABtAGEAeABfAGEAIAAtACAAcwB0AGEAcgB0AF8AYQApACAALwAgAHMAdABlAHAAXwBhACAAKwAgADEALAAgADEALAAgAHMAdABhAHIAdABfAGEALAAgAHMAdABlAHAAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQBxAF8AYgAsACAAUwBFAFEAVQBFAE4AQwBFACgAKABtAGEAeABfAGIAIAAtACAAcwB0AGEAcgB0AF8AYgApACAALwAgAHMAdABlAHAAXwBiACAAKwAgADEALAAgADEALAAgAHMAdABhAHIAdABfAGIALAAgAHMAdABlAHAAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAbgBfAGEALAAgAFIATwBXAFMAKABzAGUAcQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBfAGIALAAgAFIATwBXAFMAKABzAGUAcQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABPAHIAdABoAG8AZwBvAG4AYQBsACAAYgByAG8AYQBkAGMAYQBzAHQAIAB1AHMAaQBuAGcAIABpAG4AZABlAHAAZQBuAGQAZQBuAHQAIABkAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgACAAIAAgACAAYwBvAGwAXwBhACwAIABUAE8AQwBPAEwAKABJAEYAKABTAEUAUQBVAEUATgBDAEUAKAAxACwAIABuAF8AYgApACwAIABzAGUAcQBfAGEAKQApACwAXABuACAAIAAgACAAIAAgACAAIABjAG8AbABfAGIALAAgAFQATwBDAE8ATAAoAEkARgAoAFMARQBRAFUARQBOAEMARQAoAG4AXwBhACkALAAgAFQATwBSAE8AVwAoAHMAZQBxAF8AYgApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABIAFMAVABBAEMASwAoAGMAbwBsAF8AYQAsACAAYwBvAGwAXwBiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBjAG8AcgBlAF8AQgBpAGcASQBuAHQAIgAsACIAdABlAHgAdAAiADoAIgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4ALwAvACAAQgBpAGcAIABJAG4AdABlAGcAZQByACAAQQByAGkAdABoAG0AZQB0AGkAYwAgAEwAaQBiAHIAYQByAHkAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQAIABNAG8AZAB1AGwAZQAgACAAIAAgACAAIAAgACAALwAvAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIABQAHIAaQB2AGEAdABlACAAQQBQAEkAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwBcAG4ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8AXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEMAbwBtAHAAdQB0AGUAcwAgAHQAaABlACAAbQBhAHgAaQBtAHUAbQAgAHMAYQBmAGUAIABiAGEAcwBlAC0AMQAwACAAbABpAG0AYgAgAHMAaQB6AGUAIAAoAGsAKQAgAHQAbwAgAGEAdgBvAGkAZAAgAEkARQBFAEUALQA3ADUANAAgAHAAcgBlAGMAaQBzAGkAbwBuACAAbABvAHMAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG8AcABlAHIAYQB0AGkAbwBuADoAIABcACIAQQBEAEQAXAAiACwAIABcACIATQBVAEwAXAAiACwAIABvAHIAIABcACIARABJAFYAXAAiAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAWwBtAGEAeABfAGkAdABlAG0AcwBdACAAQQBEAEQAOgAgAG4AdQBtAGIAZQByACAAbwBmACAAbwBwAGUAcgBhAG4AZABzAC4AIABNAFUATAA6ACAAcwBoAG8AcgB0AGUAcwB0ACAAcwB0AHIAaQBuAGcAIABkAGkAZwBpAHQAcwAgAGMAbwB1AG4AdAAuAFwAbgAgACoALwBcAG4AUwBhAGYAZQBLACAAPQAgAEwAQQBNAEIARABBACgAbwBwAGUAcgBhAHQAaQBvAG4ALAAgAFsAbQBhAHgAXwBpAHQAZQBtAHMAXQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABpAHQAZQBtAHMALAAgAEkARgAoAE8AUgAoAG0AYQB4AF8AaQB0AGUAbQBzACAAPQAgAFwAIgBcACIALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAbQBhAHgAXwBpAHQAZQBtAHMAKQApACwAIAAyACwAIABNAEEAWAAoADIALAAgAG0AYQB4AF8AaQB0AGUAbQBzACkAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVwBJAFQAQwBIACgAbwBwAGUAcgBhAHQAaQBvAG4ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEARABEAFwAIgAsACAAMQA1ACAALQAgAEwARQBOACgAaQB0AGUAbQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFUATABcACIALAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARQB2AGEAbAB1AGEAdABlACAAcABvAHMAcwBpAGIAbABlACAAawAgAHYAYQBsAHUAZQBzACAAZAB5AG4AYQBtAGkAYwBhAGwAbAB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAZQBzAHQAXwBrACwAIAB7ADcAOwAgADYAOwAgADUAOwAgADQAOwAgADMAOwAgADIAOwAgADEAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AbwB2AGUAcgBsAGEAcAAsACAAUgBPAFUATgBEAFUAUAAoAGkAdABlAG0AcwAgAC8AIAB0AGUAcwB0AF8AawAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIAB0AGgAZQAgAGEAYgBzAG8AbAB1AHQAZQAgAHAAZQBhAGsAIAB2AGEAbAB1AGUAIABpAG4AcwBpAGQAZQAgAHQAaABlACAAZQBuAGcAaQBuAGUAIAAoAEMAbwBuAHYAbwBsAHUAdABpAG8AbgAgACsAIABDAGEAcgByAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB1AG4AYwBhAHIAcgBpAGUAZABfAG0AYQB4ACwAIABtAGEAeABfAG8AdgBlAHIAbABhAHAAIAAqACAAKAAxADAAXgB0AGUAcwB0AF8AawAgAC0AIAAxACkAXgAyACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAHgAXwBjAGEAcgByAHkALAAgAEkATgBUACgAdQBuAGMAYQByAHIAaQBlAGQAXwBtAGEAeAAgAC8AIAAxADAAXgB0AGUAcwB0AF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABlAGEAawBfAHYAYQBsACwAIAB1AG4AYwBhAHIAcgBpAGUAZABfAG0AYQB4ACAAKwAgAG0AYQB4AF8AYwBhAHIAcgB5ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHQAdQByAG4AIAB0AGgAZQAgAG0AYQB4ACAAawAgADwAPQAgAEUAeABjAGUAbAAnAHMAIAAxADUALQBkAGkAZwBpAHQAIABjAGUAaQBsAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgARgBJAEwAVABFAFIAKAB0AGUAcwB0AF8AawAsACAAcABlAGEAawBfAHYAYQBsACAAPAA9ACAAKAAxADAAXgAxADUAIAAtACAAMQApACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQASQBWAFwAIgAsACAANwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAE4AQQBNAEUAPwBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AaQBmAGkAZQBkACAAUwBwAGwAaQB0AHQAZQByAC4AIABTAHAAbABpAHQAcwAgAGIAbwB0AGgAIABzAGMAYQBsAGEAcgBzACAAYQBuAGQAIABhAHIAcgBhAHkAcwAgAGkAbgB0AG8AIABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuACAAbABpAG0AYgBzAC4AXABuACAAKgAgAFUAcwBlAHMAIABNAEEAWAAoACkAIAB0AG8AIABnAHUAYQByAGEAbgB0AGUAZQAgAHMAYwBhAGwAYQByACAAaQBuAHAAdQB0AHMAIAB0AG8AIAB0AGgAZQAgAFMARQBRAFUARQBOAEMARQAgAGUAbgBnAGkAbgBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABzACAAVABoAGUAIABzAHQAcgBpAG4AZwAgAG8AcgAgAGEAcgByAGEAeQAgAG8AZgAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFMAcABsAGkAdAAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAcwAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABiAGkAZwBfAGkAbgB0AF8AcgBvAHcALAAgAFQATwBSAE8AVwAoAGIAaQBnAF8AaQBuAHQAcwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBnAHQAaABzACwAIABMAEUATgAoAGIAaQBnAF8AaQBuAHQAXwByAG8AdwApACwAXABuACAAIAAgACAAIAAgACAAIABtAGEAeABfAGwAZQBuACwAIABNAEEAWAAoAGwAZQBuAGcAdABoAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBsAGUAbgAsACAAUgBPAFUATgBEAFUAUAAoAG0AYQB4AF8AbABlAG4AIAAvACAAawAsACAAMAApACAAKgAgAGsALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAZABlAGQALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAHAAYQBkAF8AbABlAG4AIAAtACAAbABlAG4AZwB0AGgAcwApACAAJgAgAGIAaQBnAF8AaQBuAHQAXwByAG8AdwAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALAAgAFMARQBRAFUARQBOAEMARQAoAHAAYQBkAF8AbABlAG4AIAAvACAAawAsACAAMQAsACAAcABhAGQAXwBsAGUAbgAgAC0AIABrACAAKwAgADEALAAgAC0AawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC0ALQBNAEkARAAoAHAAYQBkAGQAZQBkACwAIABzAHQAYQByAHQAcwAsACAAawApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAQwBvAG4AYwBhAHQAZQBuAGEAdABlAHMAIABhAG4AIABhAHIAcgBhAHkAIABvAGYAIABuAHUAbQBlAHIAaQBjACAAbABpAG0AYgBzACAAaQBuAHQAbwAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnACwAIAB6AGUAcgBvAC0AcABhAGQAZABpAG4AZwAgAGEAbABsACAAYgB1AHQAIAB0AGgAZQAgAGYAaQByAHMAdAAgAGwAaQBtAGIALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAIABUAGgAZQAgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAG4AdQBtAGUAcgBpAGMAIABsAGkAbQBiAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABsAGkAbQBiACAAcwBpAHoAZQAgAHUAcwBlAGQAIABkAHUAcgBpAG4AZwAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAuAFwAbgAgACoALwBcAG4ATQBlAHIAZwBlACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AdQBtAF8AbABpAG0AYgBzACwAIABSAE8AVwBTACgAbABpAG0AYgBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQB2AF8AbABpAG0AYgBzACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAbABpAG0AYgBzACwAIABTAEUAUQBVAEUATgBDAEUAKABuAHUAbQBfAGwAaQBtAGIAcwAsACAAMQAsACAAbgB1AG0AXwBsAGkAbQBiAHMALAAgAC0AMQApACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AdQBtAF8AbABpAG0AYgBzACAAPQAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHYAXwBsAGkAbQBiAHMAIAAmACAAXAAiAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATgBDAEEAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAcgBlAHYAXwBsAGkAbQBiAHMALAAgADEAKQAgACYAIABcACIAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEUAWABUACgARABSAE8AUAAoAHIAZQB2AF8AbABpAG0AYgBzACwAIAAxACkALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAGsAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAUgBlAHMAbwBsAHYAZQBzACAAYwBhAHIAcgBpAGUAcwAgAHIAaQBnAGgAdAAtAHQAbwAtAGwAZQBmAHQAIABhAGMAcgBvAHMAcwAgAGEAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkAIABvAGYAIABiAGEAcwBlAC0AMQAwAF4AawAgAGwAaQBtAGIAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwAgAFQAaABlACAAYQByAHIAYQB5ACAAbwBmACAAbgB1AG0AZQByAGkAYwAgAGwAaQBtAGIAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGwAaQBtAGIAIABzAGkAegBlAC4AXABuACAAKgAvAFwAbgBDAGEAcgByAHkAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwApACwAXABuACAAIAAgACAAIAAgACAAIABiAGEAcwBlACwAIAAxADAAXgBrACwAXABuACAAIAAgACAAIAAgACAAIABzAGMAYQBuAG4AZQBkACwAIABTAEMAQQBOACgAMAAsACAAbABpAG0AYgBzACwAIABMAEEATQBCAEQAQQAoAGEAYwBjACwAIAB2AGEAbAAsACAAdgBhAGwAIAArACAASQBOAFQAKABhAGMAYwAgAC8AIABiAGEAcwBlACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAByAGUAbQBhAGkAbgBkAGUAcgBzACwAIABNAE8ARAAoAHMAYwBhAG4AbgBlAGQALAAgAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AYwBhAHIAcgB5ACwAIABJAE4AVAAoAEkATgBEAEUAWAAoAHMAYwBhAG4AbgBlAGQALAAgAG4ALAAgADEAKQAgAC8AIABiAGEAcwBlACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABmAGkAbgBhAGwAXwBjAGEAcgByAHkAIAA+ACAAMAAsACAAVgBTAFQAQQBDAEsAKAByAGUAbQBhAGkAbgBkAGUAcgBzACwAIABmAGkAbgBhAGwAXwBjAGEAcgByAHkAKQAsACAAcgBlAG0AYQBpAG4AZABlAHIAcwApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAC0ALQAtACAAVQBuAHMAaQBnAG4AZQBkACAASwBlAHIAbgBlAGwAcwAgAC0ALQAtACAAXABcAFwAXABcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAVQBuAHMAaQBnAG4AZQBkACAAYwBvAG0AcABhAHIAaQBzAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAMQAgACgAYQAgAD4AIABiACkALAAgAC0AMQAgACgAYQAgADwAIABiACkALAAgAG8AcgAgADAAIAAoAGEAIAA9ACAAYgApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAIABUAGgAZQAgAHMAZQBjAG8AbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoALwBcAG4AVQBDAG8AbQBwAGEAcgBlACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAeABfAHIAbwB3AHMALAAgAE0AQQBYACgAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEAKQAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAZABfAGEALAAgAEUAWABQAEEATgBEACgAbABpAG0AYgBzAF8AYQAsACAAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAYQBkAF8AYgAsACAARQBYAFAAQQBOAEQAKABsAGkAbQBiAHMAXwBiACwAIABtAGEAeABfAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABkAGkAZgBmACwAIABwAGEAZABfAGEAIAAtACAAcABhAGQAXwBiACwAXABuACAAIAAgACAAIAAgACAAIABtAHMAZABfAGkAZAB4ACwAIABYAE0AQQBUAEMASAAoAFQAUgBVAEUALAAgAGQAaQBmAGYAIAA8AD4AIAAwACwAIAAwACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATgBBACgAbQBzAGQAXwBpAGQAeAApACwAIAAwACwAIABTAEkARwBOACgASQBOAEQARQBYACgAZABpAGYAZgAsACAAbQBzAGQAXwBpAGQAeAAsACAAMQApACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAGEAZABkAGkAdABpAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFUAQQBkAGQAIAA9ACAATABBAE0AQgBEAEEAKABhACwAIABiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AcgBvAHcAcwAsACAATQBBAFgAKABSAE8AVwBTACgAYQApACwAIABSAE8AVwBTACgAYgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAYQBkAF8AYQAsACAARQBYAFAAQQBOAEQAKABhACwAIABtAGEAeABfAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBiACwAIABFAFgAUABBAE4ARAAoAGIALAAgAG0AYQB4AF8AcgBvAHcAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHAAYQBkAF8AYQAgACsAIABwAGEAZABfAGIALAAgAGsAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAHMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABBAHMAcwB1AG0AZQBzACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAgAEEAIAA+AD0AIABCAC4AIABSAGUAcwBvAGwAdgBlAHMAIABiAG8AcgByAG8AdwBzACAAdABvAHAALQB0AG8ALQBiAG8AdAB0AG8AbQAgAGEAbgBkACAAdAByAGkAbQBzACAAdAByAGEAaQBsAGkAbgBnACAAegBlAHIAbwBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAbQBpAG4AdQBlAG4AZAAgAGwAaQBtAGIAIABhAHIAcgBhAHkAIAAoAG0AdQBzAHQAIABiAGUAIAA+AD0AIABsAGkAbQBiAHMAXwBiACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABzAHUAYgB0AHIAYQBoAGUAbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AVQBTAHUAYgAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwByAG8AdwBzACwAIABNAEEAWAAoAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBhACwAIABFAFgAUABBAE4ARAAoAGwAaQBtAGIAcwBfAGEALAAgAG0AYQB4AF8AcgBvAHcAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAZABfAGIALAAgAEUAWABQAEEATgBEACgAbABpAG0AYgBzAF8AYgAsACAAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAZABpAGYAZgAsACAAcABhAGQAXwBhACAALQAgAHAAYQBkAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBlAHMAbwBsAHYAZQBkACwAIABDAGEAcgByAHkAKABkAGkAZgBmACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAbQBzAGQAXwBpAGQAeAAsACAAWABNAEEAVABDAEgAKABUAFIAVQBFACwAIAByAGUAcwBvAGwAdgBlAGQAIAA8AD4AIAAwACwAIAAwACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATgBBACgAbQBzAGQAXwBpAGQAeAApACwAIAB7ADAAfQAsACAAVABBAEsARQAoAHIAZQBzAG8AbAB2AGUAZAAsACAAbQBzAGQAXwBpAGQAeAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABWAGUAYwB0AG8AcgBpAHoAZQBkACAAbQBhAHQAcgBpAHgAIABzAHUAbQAgAG8AZgAgAHUAbgBzAGkAZwBuAGUAZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHUAYgBpAGcAXwBpAG4AdAAgAEgAbwByAGkAegBvAG4AdABhAGwAIABhAHIAcgBhAHkAIAAoADEAeABOACkAIABvAGYAIABuAG8AcgBtAGEAbABpAHoAZQBkACAAbQBhAGcAbgBpAHQAdQBkAGUAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAdQBuAGkAZgBpAGUAZAAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AVQBNAGEAdAByAGkAeABTAHUAbQAgAD0AIABMAEEATQBCAEQAQQAoAHUAYgBpAGcAXwBpAG4AdABzACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAGcAcgBpAGQALAAgAFMAcABsAGkAdAAoAHUAYgBpAGcAXwBpAG4AdABzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAYQB3AF8AbABpAG0AYgBzACwAIABCAFkAUgBPAFcAKABnAHIAaQBkACwAIABTAFUATQApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHIAYQB3AF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABSAG8AdQB0AGUAcwAgAGEAZABkAGkAdABpAG8AbgAvAHMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAGIAYQBzAGUAZAAgAG8AbgAgAHMAaQBnAG4AcwAgAGEAbgBkACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAuAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAYQAgAHQAdQBwAGwAZQAgAGEAcgByAGEAeQA6ACAAVgBTAFQAQQBDAEsAKABsAGkAbQBiAHMALAAgAGYAaQBuAGEAbABfAHMAaQBnAG4AKQAgAHcAaABlAHIAZQAgAHQAaABlACAAZgBpAG4AYQBsACAAcgBvAHcAIABpAHMAIAB0AGgAZQAgAHMAYwBhAGwAYQByACAAcwBpAGcAbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAcwBlAGMAbwBuAGQAIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHMAaQBnAG4AXwBhACAAVABoAGUAIABzAGkAZwBuACAAbwBmACAAdABoAGUAIABmAGkAcgBzAHQAIABhAHIAcgBhAHkAIAAoADEALAAgAC0AMQAsACAAMAApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAcwBpAGcAbgBfAGIAIABUAGgAZQAgAHMAaQBnAG4AIABvAGYAIAB0AGgAZQAgAHMAZQBjAG8AbgBkACAAYQByAHIAYQB5ACAAKAAxACwAIAAtADEALAAgADAAKQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AQQBkAGQAUwB1AGIAUgBvAHUAdABlAHIAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABzAGkAZwBuAF8AYQAsACAAcwBpAGcAbgBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AcwBhAG0AZQBfAHMAaQBnAG4ALAAgAHMAaQBnAG4AXwBhACAAPQAgAHMAaQBnAG4AXwBiACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGkAcwBfAHMAYQBtAGUAXwBzAGkAZwBuACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAZABkAGkAdABpAG8AbgA6ACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAgAGMAbwBtAGIAaQBuAGUALAAgAHMAaQBnAG4AIAByAGUAbQBhAGkAbgBzACAAdABoAGUAIABzAGEAbQBlAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVQBBAGQAZAAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsACAAcwBpAGcAbgBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwB1AGIAdAByAGEAYwB0AGkAbwBuADoAIABlAHYAYQBsAHUAYQB0AGUAIABtAGEAZwBuAGkAdAB1AGQAZQBzACAAdABvACAAcwBhAHQAaQBzAGYAeQAgAFUAUwB1AGIAIAAoAEEAIAA+AD0AIABCACkAIABwAHIAZQBjAG8AbgBkAGkAdABpAG8AbgAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcAAsACAAVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFQAbwB0AGEAbAAgAGMAYQBuAGMAZQBsAGwAYQB0AGkAbwBuADoAIAByAGUAdAB1AHIAbgAgAHsAMAB9ACAAbABpAG0AYgAgAGEAbgBkACAAMAAgAHMAaQBnAG4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAMAA7ADAAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAGEAZwBfAGMAbwBtAHAAIAA+ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABBACAAaQBzACAAbABhAHIAZwBlAHIAOgAgAHMAaQBnAG4AIABiAGUAbABvAG4AZwBzACAAdABvACAAQQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFUAUwB1AGIAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALAAgAHMAaQBnAG4AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEIAIABpAHMAIABsAGEAcgBnAGUAcgA6ACAAcgBvAHUAdABlACAAQgAgAGYAaQByAHMAdAAsACAAcwBpAGcAbgAgAGIAZQBsAG8AbgBnAHMAIAB0AG8AIABCAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVQBTAHUAYgAoAGwAaQBtAGIAcwBfAGIALAAgAGwAaQBtAGIAcwBfAGEALAAgAGsAKQAsACAAcwBpAGcAbgBfAGIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AcwBpAGcAbgBlAGQAIABtAHUAbAB0AGkAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIAB0AHcAbwAgAEwAaQB0AHQAbABlAC0ARQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5AHMALgBcAG4AIAAqACAAVQB0AGkAbABpAHoAZQBzACAAYQAgADEARAAgAEQAaQBzAGMAcgBlAHQAZQAgAEMAbwBuAHYAbwBsAHUAdABpAG8AbgAgACgAQwBhAHUAYwBoAHkAIABQAHIAbwBkAHUAYwB0ACkAIABhAHIAcgBhAHkALQBzAGwAaQBjAGkAbgBnACAAcwB0AHIAYQB0AGUAZwB5AC4AXABuACAAKgAgAFoAZQByAG8AIABkAHkAbgBhAG0AaQBjACAAbQBlAG0AbwByAHkAIAByAGUAYQBsAGwAbwBjAGEAdABpAG8AbgAuACAAJABPACgATgArAE0AKQAkACAAbQBlAG0AbwByAHkAIABmAG8AbwB0AHAAcgBpAG4AdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAG0AdQBsAHQAaQBwAGwAaQBjAGEAbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAIABUAGgAZQAgAG0AdQBsAHQAaQBwAGwAaQBlAHIAIABsAGkAbQBiACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBVAE0AdQBsACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwByAG8AdwBzACwAIABsAGUAbgBfAGEAIAArACAAbABlAG4AXwBiACAALQAgADEALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAATABvAG8AcAAgAHAAdQByAGUAbAB5ACAAbwB2AGUAcgAgAHQAaABlACAAbABlAG4AZwB0AGgAIABvAGYAIAB0AGgAZQAgAGYAaQBuAGEAbAAgAG8AdQB0AHAAdQB0ACAAYQByAHIAYQB5AFwAbgAgACAAIAAgACAAIAAgACAAcgBhAHcAXwBsAGkAbQBiAHMALAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIABMAEEATQBCAEQAQQAoAHIALAAgAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAbABjAHUAbABhAHQAZQAgAHQAaABlACAAdgBhAGwAaQBkACAAbwB2AGUAcgBsAGEAcABwAGkAbgBnACAAdwBpAG4AZABvAHcAIABvAGYAIABpAG4AZABpAGMAZQBzACAAZgBvAHIAIAB0AGgAaQBzACAAbQBhAGcAbgBpAHQAdQBkAGUAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AF8AaQAsACAATQBBAFgAKAAxACwAIAByACAALQAgAGwAZQBuAF8AYgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAG4AZABfAGkALAAgAE0ASQBOACgAcgAsACAAbABlAG4AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AdQBuAHQALAAgAGUAbgBkAF8AaQAgAC0AIABzAHQAYQByAHQAXwBpACAAKwAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGUAcQB1AGUAbgBjAGUAIABpACAAYwBvAHUAbgB0AHMAIABVAFAALgAgAFMAZQBxAHUAZQBuAGMAZQAgAGoAIABjAG8AdQBuAHQAcwAgAEQATwBXAE4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGkALAAgAFMARQBRAFUARQBOAEMARQAoAGMAbwB1AG4AdAAsACAAMQAsACAAcwB0AGEAcgB0AF8AaQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBlAHEAXwBqACwAIABTAEUAUQBVAEUATgBDAEUAKABjAG8AdQBuAHQALAAgADEALAAgAHIAIAAtACAAcwB0AGEAcgB0AF8AaQAgACsAIAAxACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAbABpAGMAZQAgAHQAaABlACAAZQB4AGEAYwB0ACAAaQBuAHQAZQByAHMAZQBjAHQAaQBuAGcAIABsAGkAbQBiAHMALAAgAG0AdQBsAHQAaQBwAGwAeQAsACAAYQBuAGQAIABzAHUAbQAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUATQAoAEkATgBEAEUAWAAoAGwAaQBtAGIAcwBfAGEALAAgAHMAZQBxAF8AaQAsACAAMQApACAAKgAgAEkATgBEAEUAWAAoAGwAaQBtAGIAcwBfAGIALAAgAHMAZQBxAF8AagAsACAAMQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHMAbwBsAHYAZQAgAGEAbABsACAAYwBhAHIAcgBpAGUAcwAgAGIAbwB0AHQAbwBtAC0AdABvAC0AdABvAHAAIABlAHgAYQBjAHQAbAB5ACAAbwBuAGMAZQBcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHIAYQB3AF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABCAGkAbgBhAHIAeQAgAHMAZQBhAHIAYwBoACAAdABvACAAZgBpAG4AZAAgAHQAaABlACAAaABpAGcAaABlAHMAdAAgAHMAYwBhAGwAYQByACAAcQB1AG8AdABpAGUAbgB0ACAAbABpAG0AYgAgAHEAIAAoADAAIAA8AD0AIABxACAAPAAgADEAMABeAGsAKQBcAG4AoAAqACAAcwB1AGMAaAAgAHQAaABhAHQAIABCACAAKgAgAHEAIAA8AD0AIABhAGMAYwAuACAARQBsAGkAbQBpAG4AYQB0AGUAcwAgAHQAaABlACAAbgBlAGUAZAAgAGYAbwByACAASwBuAHUAdABoACAARAAgAGYAbABvAGEAdAAtAGUAcwB0AGkAbQBhAHQAaQBvAG4ALgBcAG4AoAAqACAAQABwAGEAcgBhAG0AIABhAGMAYwAgAFQAaABlACAAYwB1AHIAcgBlAG4AdAAgAHIAZQBtAGEAaQBuAGQAZQByACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAuAFwAbgCgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgCgACoALwBcAG4ARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAgAD0AIABMAEEATQBCAEQAQQAoAGEAYwBjACwAIABiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAYQBsAGMAdQBsAGEAdABlACAAcgBlAHEAdQBpAHIAZQBkACAAYgBpAHQAcwAgAGQAeQBuAGEAbQBpAGMAYQBsAGwAeQAuACAARgBvAHIAIABtAGEAeAAgAGsAPQA3ACwAIAB0AGgAaQBzACAAZQB2AGEAbAB1AGEAdABlAHMAIAB0AG8AIAAyADQAIABiAGkAdABzAC4AXABuACAAIAAgACAAIAAgACAAIABiAGkAdABzACwAIABDAEUASQBMAEkATgBHAC4ATQBBAFQASAAoAEwATwBHACgAMQAwAF4AawAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAbwB3AGUAcgBzACwAIAAyACAAXgAgAFMARQBRAFUARQBOAEMARQAoAGIAaQB0AHMALAAgADEALAAgAGIAaQB0AHMAIAAtACAAMQAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAUgBFAEQAVQBDAEUAKAAwACwAIABwAG8AdwBlAHIAcwAsACAATABBAE0AQgBEAEEAKABjAHUAcgByAF8AcQAsACAAcABvAHcAZQByACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABlAHMAdABfAHEALAAgAGMAdQByAHIAXwBxACAAKwAgAHAAbwB3AGUAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAawBpAHAAIABpAGYAIAB0AGUAcwB0AF8AcQAgAGUAeABjAGUAZQBkAHMAIAB0AGgAZQAgAGwAaQBtAGIAIABiAGEAcwBlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHQAZQBzAHQAXwBxACAAPgA9ACAAMQAwAF4AawAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATQB1AGwAdABpAHAAbAB5ACAAQgAgAGIAeQAgAHMAYwBhAGwAYQByACAAdABlAHMAdABfAHEAIABhAG4AZAAgAHIAZQBzAG8AbAB2AGUAIABjAGEAcgByAGkAZQBzACAAbgBhAHQAaQB2AGUAbAB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGUAcwB0AF8AcAByAG8AZAAsACAAQwBhAHIAcgB5ACgAYgAgACoAIAB0AGUAcwB0AF8AcQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAFUAQwBvAG0AcABhAHIAZQAoAGEAYwBjACwAIAB0AGUAcwB0AF8AcAByAG8AZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABjAG8AbQBwACAAPgA9ACAAMAAsACAAdABlAHMAdABfAHEALAAgAGMAdQByAHIAXwBxACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABCAGEAcwBlAGMAYQBzAGUAIABEAGkAdgBpAHMAaQBvAG4AIAB2AGkAYQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABzAGgAaQBmAHQALQBhAG4AZAAtAHMAdQBiAHQAcgBhAGMAdAAuAFwAbgCgACoAIABSAGUAdAB1AHIAbgBzACAAYQAgAHAAYQBjAGsAZQBkACAAMQBEACAAYQByAHIAYQB5ADoAIABWAFMAVABBAEMASwAoAEwAZQBuAGcAdABoAF8AUgAsACAAUgBfAGwAaQBtAGIAcwAsACAAUQBfAGwAaQBtAGIAcwApAC4AXABuAKAAKgAgAEUAbABpAG0AaQBuAGEAdABlAHMAIAAyAEQAIABhAHIAcgBhAHkAIABwAGEAZABkAGkAbgBnACAAdABvACAAcwB0AHIAaQBjAHQAbAB5ACAAcAByAGUAcwBlAHIAdgBlACAAbQBlAG0AbwByAHkAIABlAGYAZgBpAGMAaQBlAG4AYwB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAgACgAYQBzAHMAdQBtAGUAZAAgAG4AbwBuAC0AegBlAHIAbwApAC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuAKAAKgAvAFwAbgBLAG4AdQB0AGgARABpAHYAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcAAsACAAVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAIAByAG8AdQB0AGkAbgBnACAAdwBpAHQAaAAgAHQAaABlACAAbgBlAHcAIABwAGEAYwBrAGUAZAAgAG0AZQBtAG8AcgB5ACAAYwBvAG4AdAByAGEAYwB0AFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbABpAG0AYgBzAF8AYQApACwAIABsAGkAbQBiAHMAXwBhACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADEALAAgADAALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEkAdABlAHIAYQB0AGUAIABvAHYAZQByACAAQQAgAGYAcgBvAG0AIABNAFMAQgAgACgAdABvAHAAKQAgAHQAbwAgAEwAUwBCACAAKABiAG8AdAB0AG8AbQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHYAZQByAHMAZQBkAF8AYQAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEALAAgAFMARQBRAFUARQBOAEMARQAoAGwAZQBuAF8AYQAsACAAMQAsACAAbABlAG4AXwBhACwAIAAtADEAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAdABhAHQAZQAgAHMAZQBwAGEAcgBhAHQAbwByADoAIABWAFMAVABBAEMASwAoAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABxAHUAbwB0AGkAZQBuAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAbgBpAHQAaQBhAGwAXwBzAHQAYQB0AGUALAAgAFYAUwBUAEEAQwBLACgAMQAsACAAMAAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsAF8AcwB0AGEAdABlACwAIAByAGUAdgBlAHIAcwBlAGQAXwBhACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAdgBhAGwALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcwB0AGEAdABlACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHEAdQBvAHQAaQBlAG4AdAAsACAARABSAE8AUAAoAHMAdABhAHQAZQAsACAAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGgAaQBmAHQAIABhAGMAYwAgAHUAcAAgAGIAeQAgADEAIABsAGkAbQBiACAAKABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuADoAIABpAG4AcwBlAHIAdAAgAGEAdAAgAGkAbgBkAGUAeAAgADEAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAHgAdABlAG4AZABlAGQAXwByAGUAbQBhAGkAbgBkAGUAcgAsACAASQBGACgAQQBOAEQAKABSAE8AVwBTACgAcgBlAG0AYQBpAG4AZABlAHIAKQAgAD0AIAAxACwAIABJAE4ARABFAFgAKAByAGUAbQBhAGkAbgBkAGUAcgAsACAAMQAsACAAMQApACAAPQAgADAAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB2AGEAbAAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAHYAYQBsACwAIAByAGUAbQBhAGkAbgBkAGUAcgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgAsACAARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAoAGUAeAB0AGUAbgBkAGUAZABfAHIAZQBtAGEAaQBuAGQAZQByACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAHIAbwBkACwAIABDAGEAcgByAHkAKABsAGkAbQBiAHMAXwBiACAAKgAgAG4AZQB4AHQAXwBxAHUAbwB0AGkAZQBuAHQAXwBsAGkAbQBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAdwBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABVAFMAdQBiACgAZQB4AHQAZQBuAGQAZQBkAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHAAcgBvAGQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGgAYQBzAF8AcQB1AG8AdABpAGUAbgB0ACwAIABPAFIAKABSAE8AVwBTACgAcQB1AG8AdABpAGUAbgB0ACkAIAA+ACAAMQAsACAASQBOAEQARQBYACgAcQB1AG8AdABpAGUAbgB0ACwAMQAsADEAKQAgAD4AIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQB1AG8AdAAsACAASQBGACgAaABhAHMAXwBxAHUAbwB0AGkAZQBuAHQALAAgAFYAUwBUAEEAQwBLACgAcQB1AG8AdABpAGUAbgB0ACwAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgApACwAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbgBlAHcAXwByAGUAbQBhAGkAbgBkAGUAcgApACwAIABuAGUAdwBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABuAGUAeAB0AF8AcQB1AG8AdAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAEkATgBEAEUAWAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAbQBhAGkAbgBkAGUAcgAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAsACAAMQAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQB2AGUAcgBzAGUAZABfAHEAdQBvAHQAaQBlAG4AdAAsACAARABSAE8AUAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAcQB1AG8AdABfAHIAYQB3ACAAdwBhAHMAIABiAHUAaQBsAHQAIABNAFMAQgAgAHQAbwAgAEwAUwBCACAAKABCAGkAZwAtAEUAbgBkAGkAYQBuACkALgAgAFIAZQB2AGUAcgBzAGUAIAB0AG8AIABpAG4AdABlAHIAbgBhAGwAIABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHEAdQBvAHQAaQBlAG4AdAAsACAAUgBPAFcAUwAoAHIAZQB2AGUAcgBzAGUAZABfAHEAdQBvAHQAaQBlAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABxAHUAbwB0AGkAZQBuAHQALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKAByAGUAdgBlAHIAcwBlAGQAXwBxAHUAbwB0AGkAZQBuAHQALAAgAFMARQBRAFUARQBOAEMARQAoAGwAZQBuAF8AcQB1AG8AdABpAGUAbgB0ACwAIAAxACwAIABsAGUAbgBfAHEAdQBvAHQAaQBlAG4AdAAsACAALQAxACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABMAGUAYQBkAGkAbgBnAC8AdAByAGEAaQBsAGkAbgBnACAAegBlAHIAbwBzACAAYQByAGUAIABjAG8AbgB0AGkAbgB1AG8AdQBzAGwAeQAgAHIAZQBtAG8AdgBlAGQAIABpAG4AcwBpAGQAZQAgAHQAaABlACAAbABvAG8AcAAsACAAbgBvACAAbgBlAGUAZAAgAHQAbwAgAHIAZQBwAGUAYQB0ACAAaQB0AC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAcwB0AHIAaQBjAHQAbAB5ACAAcABhAGMAawBlAGQAIAAxAEQAIABhAHIAcgBhAHkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABxAHUAbwB0AGkAZQBuAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AoAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEgAeQBiAHIAaQBkACAARABpAHYAaQBzAGkAbwBuACAAUgBvAHUAdABlAHIALgBcAG4AoAAqACAARABpAHIAZQBjAHQAcwAgAGQAaQB2AGkAcwBpAG8AbgAgAHQAbwAgAHQAaABlACAAbwBwAHQAaQBtAGEAbAAgAGsAZQByAG4AZQBsACAAYgBhAHMAZQBkACAAbwBuACAARABpAHYAaQBkAGUAbgBkACAAbABlAG4AZwB0AGgALgBcAG4AoAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBhACAAVABoAGUAIABkAGkAdgBpAGQAZQBuAGQAIABhAHIAcgBhAHkALgBcAG4AoAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuAKAAKgAvAFwAbgBEAGkAdgBSAG8AdQB0AGUAcgAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARABpAGcAaQB0ACAAYwBvAHUAbgB0AHMAIABhAHIAZQAgAGEAcABwAHIAbwB4AGkAbQBhAHQAZQAsACAAYgB1AHQAIABzAHUAZgBmAGkAYwBpAGUAbgB0AFwAbgAgACAAIAAgACAAIAAgACAAZABpAGcAaQB0AHMAXwBhACwAIABSAE8AVwBTACgAbABpAG0AYgBzAF8AYQApACAAKgAgAGsALABcAG4AIAAgACAAIAAgACAAIAAgAGQAaQBnAGkAdABzAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAgACoAIABrACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAE0AYQBjAGgAaQBuAGUALQBsAGUAYQByAG4AZQBkACAAYwBvAGUAZgBmAGkAYwBpAGUAbgB0AHMAIABmAHIAbwBtACAATABvAGcAaQBzAHQAaQBjACAAUgBlAGcAcgBlAHMAcwBpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgAG0ALAAgADAALgAxADAANwA4ADIAMQAxADkANAAyADcAMQAyADkANwAsAFwAbgAgACAAIAAgACAAIAAgACAAYwAsACAALQAyADIAMQAuADkAMAAyADEAOAA5ADQANgAyADAANgA4ACwAXABuACAAIAAgACAAIAAgACAAIAB0AGgAcgBlAHMAaABvAGwAZAAsACAAKABtACAAKgAgAGQAaQBnAGkAdABzAF8AYQApACAAKwAgAGMALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAZABpAGcAaQB0AHMAXwBiACAAPAA9ACAAdABoAHIAZQBzAGgAbwBsAGQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASwBuAHUAdABoAEQAaQB2ACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4ARABpAHYAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAARwBlAG4AZQByAGEAdABlAHMAIAB0AGgAZQAgAGUAeABhAGMAdAAgAHIAZQBjAGkAcAByAG8AYwBhAGwAIABzAGUAZQBkACAAZgBvAHIAIABOAGUAdwB0AG8AbgAtAFIAYQBwAGgAcwBvAG4AIABEAGkAdgBpAHMAaQBvAG4AIAB1AHMAaQBuAGcAIABLAG4AdQB0AGgAIABCAGEAcwBlAGMAYQBzAGUALgBcAG4AIAAqACAARQB4AHQAcgBhAGMAdABzACAAdQBwACAAdABvACAAdABoAGUAIAB0AG8AcAAgADMAIABsAGkAbQBiAHMAIABvAGYAIABCACAAYQBuAGQAIABjAGEAbABjAHUAbABhAHQAZQBzACAAZgBsAG8AbwByACgAQgBlAHQAYQBeACgAMgAqAGwAZQBuACkAIAAvACAAQgBfAHQAbwBwACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBTAGUAZQBkACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYgAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGIALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQBlAGQAXwBsAGUAbgAsACAATQBJAE4AKAAzACwAIABsAGUAbgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAdABvAHAAIAAnAHMAZQBlAGQAXwBsAGUAbgAnACAAbABpAG0AYgBzACAAKABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuADoAIAB0AGEAawBlACAAZgByAG8AbQAgAHQAaABlACAAYgBvAHQAdABvAG0AKQBcAG4AIAAgACAAIAAgACAAIAAgAGIAXwB0AG8AcAAsACAAVABBAEsARQAoAGwAaQBtAGIAcwBfAGIALAAgAC0AcwBlAGUAZABfAGwAZQBuACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwBvAG4AcwB0AHIAdQBjAHQAIABCAGUAdABhAF4AKAAyACAAKgAgAHMAZQBlAGQAXwBsAGUAbgApACAAbgBhAHQAaQB2AGUAbAB5AFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAZQAuAGcALgAsACAAaQBmACAAcwBlAGUAZABfAGwAZQBuACAAPQAgADEALAAgAHQAaABlAG4AIAAxACAAZgBvAGwAbABvAHcAZQBkACAAYgB5ACAAdAB3AG8AIAB6AGUAcgBvACAAbABpAG0AYgBzADoAIABWAFMAVABBAEMASwAoADAALAAgADAALAAgADEAKQBcAG4AIAAgACAAIAAgACAAIAAgAGIAZQB0AGEAXwAyAG0ALAAgAFYAUwBUAEEAQwBLACgARQBYAFAAQQBOAEQAKAAwACwAIAAyACAAKgAgAHMAZQBlAGQAXwBsAGUAbgAsACAALAAgADAAKQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEsAbgB1AHQAaAAgAEQAaQB2AGkAcwBpAG8AbgAgAHkAaQBlAGwAZABzACAAZQB4AGEAYwB0ACAAaQBuAGkAdABpAGEAbAAgAHIAZQBjAGkAcAByAG8AYwBhAGwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAASwBuAHUAdABoAEQAaQB2ACgAYgBlAHQAYQBfADIAbQAsACAAYgBfAHQAbwBwACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAFEAdQBvAHQAaQBlAG4AdAAgAGEAcgByAGEAeQAgAGYAcgBvAG0AIAB0AGgAZQAgAHAAYQBjAGsAZQBkACAAVgBTAFQAQQBDAEsAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHIALAAgAEkATgBEAEUAWAAoAHAAYQBjAGsAZQBkACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABwAGEAYwBrAGUAZAAsACAAbABlAG4AXwByACAAKwAgADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEMAbwBtAHAAdQB0AGUAcwAgAHQAaABlACAAUgBlAGMAaQBwAHIAbwBjAGEAbAAgAHAAcgBvAGcAcgBlAHMAcwBpAHYAZQBsAHkAIABzAGMAYQBsAGkAbgBnACAAdQBwACAAdABvACAAdABoAGUAIABEAGkAdgBpAGQAZQBuAGQAJwBzACAAcAByAGUAYwBpAHMAaQBvAG4ALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHQAYQByAGcAZQB0AF8AbABlAG4AIABUAGgAZQAgAGwAaQBtAGIALQBsAGUAbgBnAHQAaAAgAG8AZgAgAEQAaQB2AGkAZABlAG4AZAAgAEEALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4AUgBlAGMAaQBwAHIAbwBjAGEAbAAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGIALAAgAHQAYQByAGcAZQB0AF8AbABlAG4ALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwBiACwAIABSAE8AVwBTACgAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAZQBkAF8AbABlAG4ALAAgAE0ASQBOACgAMwAsACAAbABlAG4AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAXwBzAGUAZQBkAF8AbABpAG0AYgBzACwAIABOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAFMAZQBlAGQAKABsAGkAbQBiAHMAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKABzAGUAZQBkAF8AbABlAG4ALAAgAHIAXwBzAGUAZQBkAF8AbABpAG0AYgBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQBxAF8AaQB0AGUAcgBzACwAIABNAEEAWAAoADAALAAgAEMARQBJAEwASQBOAEcALgBNAEEAVABIACgATABOACgAdABhAHIAZwBlAHQAXwBsAGUAbgAgAC8AIABzAGUAZQBkAF8AbABlAG4AKQAgAC8AIABMAE4AKAAyACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAHIAZQBxAF8AaQB0AGUAcgBzACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBfAHMAZQBlAGQAXwBsAGkAbQBiAHMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAHQAZQByAGEAdABpAG8AbgBzACwAIABTAEUAUQBVAEUATgBDAEUAKAByAGUAcQBfAGkAdABlAHIAcwApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcwB0AGEAdABlACwAIABSAEUARABVAEMARQAoAGkAbgBpAHQAaQBhAGwAXwBzAHQAYQB0AGUALAAgAGkAdABlAHIAYQB0AGkAbwBuAHMALAAgAEwAQQBNAEIARABBACgAcwB0AGEAdABlACwAIABpAHQAZQByACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AbABlAG4ALAAgAEkATgBEAEUAWAAoAHMAdABhAHQAZQAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwByACwAIABEAFIATwBQACgAcwB0AGEAdABlACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwBsAGUAbgAsACAATQBJAE4AKABjAHUAcgByAF8AbABlAG4AIAAqACAAMgAsACAAdABhAHIAZwBlAHQAXwBsAGUAbgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAaABpAGYAdABfAGwAaQBtAGIAcwAsACAAbgBlAHgAdABfAGwAZQBuACAALQAgAGMAdQByAHIAXwBsAGUAbgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBfAHAAcgBpAG0AZQAsACAASQBGACgAcwBoAGkAZgB0AF8AbABpAG0AYgBzACAAPgAgADAALAAgAFYAUwBUAEEAQwBLACgARQBYAFAAQQBOAEQAKAAwACwAIABzAGgAaQBmAHQAXwBsAGkAbQBiAHMALAAgACwAIAAwACkALAAgAGMAdQByAHIAXwByACkALAAgAGMAdQByAHIAXwByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAbABpAGMAZQAgAEIAIAB0AG8AIABpAHQAcwAgAG4AYQB0AHUAcgBhAGwAIABsAGkAbQBpAHQAcwAsACAAcABhAGQAZABpAG4AZwAgAHcAaQB0AGgAIAB6AGUAcgBvAHMAIABkAGUAcwB0AHIAbwB5AHMAIABwAGUAcgBmAG8AcgBtAGEAbgBjAGUALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYgBfAGEAYwB0AGkAdgBlACwAIABUAEEASwBFACgAbABpAG0AYgBzAF8AYgAsACAALQBNAEkATgAoAG4AZQB4AHQAXwBsAGUAbgAsACAAbABlAG4AXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATwAoAE4AKgBNACkAIABpAG4AcwB0AGUAYQBkACAAbwBmACAATwAoAE4AXgAyACkAIABmAG8AcgAgAFAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAXwByAGEAdwAsACAAVQBNAHUAbAAoAGIAXwBhAGMAdABpAHYAZQAsACAAcgBfAHAAcgBpAG0AZQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGgAaQBmAHQAaQBuAGcAIAB0AGgAZQAgAHIAZQBzAHUAbAB0ACAAYQByAHIAYQB5ACAAcgBlAHAAbABpAGMAYQB0AGUAcwAgAEIAZQB0AGEAIABtAHUAbAB0AGkAcABsAGkAYwBhAHQAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAaABpAGYAdABfAHAALAAgAE0AQQBYACgAMAAsACAAbgBlAHgAdABfAGwAZQBuACAALQAgAGwAZQBuAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAALAAgAEkARgAoAHMAaABpAGYAdABfAHAAIAA+ACAAMAAsACAAVgBTAFQAQQBDAEsAKABFAFgAUABBAE4ARAAoADAALAAgAHMAaABpAGYAdABfAHAALAAgACwAIAAwACkALAAgAHAAXwByAGEAdwApACwAIABwAF8AcgBhAHcAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdAB3AG8AXwBiAGUAdABhACwAIABWAFMAVABBAEMASwAoAEUAWABQAEEATgBEACgAMAAsACAAMgAgACoAIABuAGUAeAB0AF8AbABlAG4ALAAgACwAIAAwACkALAAgADIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAHIAcgAsACAAVQBTAHUAYgAoAHQAdwBvAF8AYgBlAHQAYQAsACAAcAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcgBfAHUAbgBzAGMAYQBsAGUAZAAsACAAVQBNAHUAbAAoAHIAXwBwAHIAaQBtAGUALAAgAGUAcgByACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBlAHgAdABfAHIALAAgAEkARgAoAFIATwBXAFMAKABuAGUAeAB0AF8AcgBfAHUAbgBzAGMAYQBsAGUAZAApACAAPAA9ACAAMgAgACoAIABuAGUAeAB0AF8AbABlAG4ALAAgAHsAMAB9ACwAIABEAFIATwBQACgAbgBlAHgAdABfAHIAXwB1AG4AcwBjAGEAbABlAGQALAAgADIAIAAqACAAbgBlAHgAdABfAGwAZQBuACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABuAGUAeAB0AF8AbABlAG4ALAAgAG4AZQB4AHQAXwByACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAUgBPAFAAKABmAGkAbgBhAGwAXwBzAHQAYQB0AGUALAAgADEAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABIAGUAYQB2AHkAdwBlAGkAZwBoAHQAIABOAGUAdwB0AG8AbgAtAFIAYQBwAGgAcwBvAG4AIABEAGkAdgBpAHMAaQBvAG4ALgBcAG4AIAAqACAASQBtAHAAbABlAG0AZQBuAHQAcwAgAHAAcgBvAGcAcgBlAHMAcwBpAHYAZQAgAHMAYwBhAGwAaQBuAGcAIABiAG8AdQBuAGQAZQBkACAAdABvACAATQBBAFgAKABsAGUAbgBfAGEALAAgAGwAZQBuAF8AYgApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwBhACwAIABSAE8AVwBTACgAbABpAG0AYgBzAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGIALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQByAGcAZQB0AF8AbABlAG4ALAAgAE0AQQBYACgAbABlAG4AXwBhACwAIABsAGUAbgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAAxAC4AIABDAGEAbABjAHUAbABhAHQAZQAgAHIAZQBjAGkAcAByAG8AYwBhAGwAIABSACAAcwBjAGEAbABlAGQAIABkAHkAbgBhAG0AaQBjAGEAbABsAHkAIAB0AG8AIAB0AGEAcgBnAGUAdABfAGwAZQBuAFwAbgAgACAAIAAgACAAIAAgACAAcgAsACAATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBSAGUAYwBpAHAAcgBvAGMAYQBsACgAbABpAG0AYgBzAF8AYgAsACAAdABhAHIAZwBlAHQAXwBsAGUAbgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgADIALgAgAEEAcABwAHIAbwB4AGkAbQBhAHQAZQAgAFEAdQBvAHQAaQBlAG4AdAA6ACAAUQBfAGEAcABwAHIAbwB4ACAAPQAgAEEAIAAqACAAUgAgAC8AIABCAGUAdABhAF4AKAB0AGEAcgBnAGUAdABfAGwAZQBuACAAKwAgAGwAZQBuAF8AYgApAFwAbgAgACAAIAAgACAAIAAgACAAZAByAG8AcABfAGwAaQBtAGIAcwAsACAAdABhAHIAZwBlAHQAXwBsAGUAbgAgACsAIABsAGUAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgAHEAXwB1AG4AcwBjAGEAbABlAGQALAAgAFUATQB1AGwAKABsAGkAbQBiAHMAXwBhACwAIAByACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHEAXwBhAHAAcAByAG8AeAAsACAASQBGACgAUgBPAFcAUwAoAHEAXwB1AG4AcwBjAGEAbABlAGQAKQAgADwAPQAgAGQAcgBvAHAAXwBsAGkAbQBiAHMALAAgAHsAMAB9ACwAIABEAFIATwBQACgAcQBfAHUAbgBzAGMAYQBsAGUAZAAsACAAZAByAG8AcABfAGwAaQBtAGIAcwApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAMwAuACAARQByAHIAbwByACAAQwBvAHIAcgBlAGMAdABpAG8AbgAgAFMAdwBlAGUAcAAgACgAUgBlAG0AYQBpAG4AZABlAHIAIAA9ACAAQQAgAC0AIAAoAEIAIAAqACAAUQBfAGEAcABwAHIAbwB4ACkAKQBcAG4AIAAgACAAIAAgACAAIAAgAHEAXwBwAHIAbwBkACwAIABVAE0AdQBsACgAbABpAG0AYgBzAF8AYgAsACAAcQBfAGEAcABwAHIAbwB4ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQBtAF8AYQBwAHAAcgBvAHgALAAgAFUAUwB1AGIAKABsAGkAbQBiAHMAXwBhACwAIABxAF8AcAByAG8AZAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAFUAQwBvAG0AcABhAHIAZQAoAHIAZQBtAF8AYQBwAHAAcgBvAHgALAAgAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAG8AcgByAGUAYwB0ACAAZgBsAG8AbwByACAAdAByAHUAbgBjAGEAdABpAG8AbgAgAGYAcgBvAG0AIABpAG4AdABlAGcAZQByACAAcgBlAGMAaQBwAHIAbwBjAGEAbABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHEALAAgAEkARgAoAGMAbwBtAHAAIAA+AD0AIAAwACwAIABVAEEAZABkACgAcQBfAGEAcABwAHIAbwB4ACwAIAB7ADEAfQAsACAAawApACwAIABxAF8AYQBwAHAAcgBvAHgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsACAASQBGACgAYwBvAG0AcAAgAD4APQAgADAALAAgAFUAUwB1AGIAKAByAGUAbQBfAGEAcABwAHIAbwB4ACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALAAgAHIAZQBtAF8AYQBwAHAAcgBvAHgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAZgBpAG4AYQBsAF8AcgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AcwBpAGcAbgBlAGQAIABCAGEAcwBlAC0AMQAwACAATABlAGYAdAAtAHQAbwAtAFIAaQBnAGgAdAAgAEUAeABwAG8AbgBlAG4AdABpAGEAdABpAG8AbgAuAFwAbgAgACoAIABFAHYAYQBsAHUAYQB0AGUAcwAgAHQAaABlACAAZQB4AHAAbwBuAGUAbgB0ACAAaQB0AGUAcgBhAHQAaQB2AGUAbAB5ACAAdQBzAGkAbgBnACAAYQAgAHAAcgBlAC0AYwBvAG0AcAB1AHQAZQBkACAAMQAtADkAIABjAGEAYwBoAGUALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiAGEAcwBlACAAVABoAGUAIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAbABpAG0AYgAgAGEAcgByAGEAeQAgAG8AZgAgAHQAaABlACAAYgBhAHMAZQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGUAeABwAF8AcwB0AHIAaQBuAGcAIABUAGgAZQAgAGUAeABhAGMAdAAgAHQAZQB4AHQAIABzAHQAcgBpAG4AZwAgAG8AZgAgAHQAaABlACAAZQB4AHAAbwBuAGUAbgB0AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBVAFAAbwB3ACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYgBhAHMAZQAsACAAZQB4AHAAXwBzAHQAcgBpAG4AZwAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABQAHIAZQAtAGMAbwBtAHAAdQB0AGUAIABwAG8AdwBlAHIAcwAgADEAIAB0AGgAcgBvAHUAZwBoACAAOQAuAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0ACwAIABsAGkAbQBiAHMAXwBiAGEAcwBlACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAYwBvAG4AZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGYAaQByAHMAdAAsACAAZgBpAHIAcwB0ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAaABpAHIAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAHMAZQBjAG8AbgBkACwAIABmAGkAcgBzAHQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBvAHUAcgB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABzAGUAYwBvAG4AZAAsACAAcwBlAGMAbwBuAGQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAGYAdABoACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAZgBvAHUAcgB0AGgALAAgAGYAaQByAHMAdAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAeAB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKAB0AGgAaQByAGQALAAgAHQAaABpAHIAZAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAdgBlAG4AdABoACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAcwBpAHgAdABoACwAIABmAGkAcgBzAHQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBpAGcAdABoACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAZgBvAHUAcgB0AGgALAAgAGYAbwB1AHIAdABoACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4AaQBuAHQAaAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGUAaQBnAHQAaAAsACAAZgBpAHIAcwB0ACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABlAHgAcABfAGQAaQBnAGkAdABzACwAIAAtAC0ATQBJAEQAKABlAHgAcABfAHMAdAByAGkAbgBnACwAIABTAEUAUQBVAEUATgBDAEUAKABMAEUATgAoAGUAeABwAF8AcwB0AHIAaQBuAGcAKQApACwAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABSAEUARABVAEMARQAoADEALAAgAGUAeABwAF8AZABpAGcAaQB0AHMALAAgAEwAQQBNAEIARABBACgAYQBjAGMALAAgAGQAaQBnAGkAdAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAOgAgAFMAawBpAHAAIABjAGEAbABjAHUAbABhAHQAaQBuAGcAIAAxAF4AMQAwACAAZAB1AHIAaQBuAGcAIABsAGUAYQBkAGkAbgBnACAAaQB0AGUAcgBhAHQAaQBvAG4AcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAHMAXwBvAG4AZQAsACAAQQBOAEQAKABSAE8AVwBTACgAYQBjAGMAKQAgAD0AIAAxACwAIABJAE4ARABFAFgAKABhAGMAYwAsACAAMQAsACAAMQApACAAPQAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgADEALgAgAFIAYQBpAHMAZQAgAEEAYwBjACAAdABvACAAdABoAGUAIAAxADAAdABoACAAcABvAHcAZQByACAAdQBzAGkAbgBnACAAZQB4AGEAYwB0AGwAeQAgADQAIABtAHUAbAB0AGkAcABsAGkAYwBhAHQAaQBvAG4AcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAYwBfADEAMAAsACAASQBGACgAaQBzAF8AbwBuAGUALAAgAGEAYwBjACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAYwBfADIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABhAGMAYwAsACAAYQBjAGMALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAYwBfADQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABhAGMAYwBfADIALAAgAGEAYwBjAF8AMgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8AOAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGEAYwBjAF8ANAAsACAAYQBjAGMAXwA0ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGEAYwBjAF8AOAAsACAAYQBjAGMAXwAyACwAIABrACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAMgAuACAATQB1AGwAdABpAHAAbAB5ACAAYgB5ACAAdABoAGUAIABjAG8AcgByAGUAcwBwAG8AbgBkAGkAbgBnACAAcAByAGUALQBjAG8AbQBwAHUAdABlAGQAIABjAGEAYwBoAGUAIAB2AGEAbAB1AGUAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAZABpAGcAaQB0ACAAPQAgADAALAAgAGEAYwBjAF8AMQAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAGEAYwBoAGUAXwB2AGEAbAAsACAAQwBIAE8ATwBTAEUAKABkAGkAZwBpAHQALAAgAGYAaQByAHMAdAAsACAAcwBlAGMAbwBuAGQALAAgAHQAaABpAHIAZAAsACAAZgBvAHUAcgB0AGgALAAgAGYAaQBmAHQAaAAsACAAcwBpAHgAdABoACwAIABzAGUAdgBlAG4AdABoACwAIABlAGkAZwB0AGgALAAgAG4AaQBuAHQAaAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGkAcwBfAG8AbgBlACwAIABjAGEAYwBoAGUAXwB2AGEAbAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGEAYwBjAF8AMQAwACwAIABjAGEAYwBoAGUAXwB2AGEAbAAsACAAawApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQgBpAGcASQBuAHQAIgAsACIAdABlAHgAdAAiADoAIgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4ALwAvACAAQgBpAGcAIABJAG4AdABlAGcAZQByACAAQQByAGkAdABoAG0AZQB0AGkAYwAgAEwAaQBiAHIAYQByAHkAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIAAgACAAQgBpAGcASQBuAHQAIABNAG8AZAB1AGwAZQAgACAAIAAgACAAIAAgACAAIAAgACAALwAvAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIABQAHUAYgBsAGkAYwAgAEEAUABJACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwBcAG4ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8AXABuAFwAbgAvACoAKgBcAG4AIAAqACAATgBvAHIAbQBhAGwAaQBzAGUAcwAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AIABTAHQAcgBpAHAAcwAgAGwAZQBhAGQAaQBuAGcAIAB6AGUAcgBvAHMALAAgAHIAZQBzAG8AbAB2AGUAcwAgAFwAIgAtADAAXAAiACAAdABvACAAXAAiADAAXAAiACwAIABhAG4AZAAgAHQAaAByAG8AdwBzACAAIwBWAEEATABVAEUAIQAgAG8AbgAgAGkAbgB2AGEAbABpAGQAIABjAGgAYQByAGEAYwB0AGUAcgBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ATgBvAHIAbQAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AHIALAAgAEkARgAoAE8AUgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYgBpAGcAXwBpAG4AdAApACwAIABiAGkAZwBfAGkAbgB0ACAAPQAgAFwAIgBcACIAKQAsACAAXAAiADAAXAAiACwAIABiAGkAZwBfAGkAbgB0ACAAJgAgAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AdgBhAGwAaQBkACwAIABSAEUARwBFAFgAVABFAFMAVAAoAHMAdAByACwAIABcACIAXgAtAD8AXABcAGQAKwAkAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAcgBpAHAAcABlAGQALAAgAFIARQBHAEUAWABSAEUAUABMAEEAQwBFACgAcwB0AHIALAAgAFwAIgBeACgALQA/ACkAMAArACgAPwA9AFwAXABkACkAXAAiACwAIABcACIAJAAxAFwAIgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATgBPAFQAKABpAHMAXwB2AGEAbABpAGQAKQAsACAAVgBBAEwAVQBFACgAXAAiACMAVgBBAEwAVQBFACEAXAAiACkALAAgAEkARgAoAHMAdAByAGkAcABwAGUAZAAgAD0AIABcACIALQAwAFwAIgAsACAAXAAiADAAXAAiACwAIABzAHQAcgBpAHAAcABlAGQAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIABzAGkAZwBuACAAbwBmACAAYQAgAEIAaQBnAEkAbgB0ADoAIAAxACAAKABwAG8AcwBpAHQAaQB2AGUAKQAsACAALQAxACAAKABuAGUAZwBhAHQAaQB2AGUAKQAsACAAbwByACAAMAAgACgAegBlAHIAbwApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AUwBpAGcAbgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALAAgAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAGUAZAAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUwBXAEkAVABDAEgAKABMAEUARgBUACgAbgBvAHIAbQBlAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMABcACIALAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIAAtADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAvACAALQAtAC0AIABQAHIAZQBkAGkAYwBhAHQAZQBzACAALQAtAC0AIABcAFwAXABcAFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFIAZQB0AHUAcgBuAHMAIABUAFIAVQBFACAAaQBmACAAdABoAGUAIABCAGkAZwBJAG4AdAAgAGkAcwAgAGUAeABhAGMAdABsAHkAIAB6AGUAcgBvAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ASQBzAFoAZQByAG8AIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACAAPQAgAFwAIgAwAFwAIgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAFQAUgBVAEUAIABpAGYAIAB0AGgAZQAgAEIAaQBnAEkAbgB0ACAAaQBzACAAbgBlAGcAYQB0AGkAdgBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ASQBzAE4AZQBnACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsACAATABFAEYAVAAoAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0ACkAKQAgAD0AIABcACIALQBcACIAKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFIAZQB0AHUAcgBuAHMAIABUAFIAVQBFACAAaQBmACAAdABoAGUAIABCAGkAZwBJAG4AdAAgAGkAcwAgAGUAdgBlAG4ALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBJAHMARQB2AGUAbgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALAAgAEkAUwBFAFYARQBOACgAVgBBAEwAVQBFACgAUgBJAEcASABUACgATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAKQApACkAKQApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAFQAUgBVAEUAIABpAGYAIAB0AGgAZQAgAEIAaQBnAEkAbgB0ACAAaQBzACAAbwBkAGQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBJAHMATwBkAGQAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAIABJAFMATwBEAEQAKABWAEEATABVAEUAKABSAEkARwBIAFQAKABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACkAKQApACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIAB1AG4AcwBpAGcAbgBlAGQAIABtAGEAZwBuAGkAdAB1AGQAZQAgAG8AZgAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnACAAKABhAGIAcwBvAGwAdQB0AGUAIAB2AGEAbAB1AGUAKQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAIABUAGgAZQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEEAYgBzACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsACAAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AdQBtACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAEUARgBUACgAbgB1AG0AKQAgAD0AIABcACIALQBcACIALAAgAE0ASQBEACgAbgB1AG0ALAAgADIALAAgAEwARQBOACgAbgB1AG0AKQAgAC0AIAAxACkALAAgAG4AdQBtACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEMAbwBtAHAAYQByAGUAcwAgAHQAdwBvACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwBzAC4AIABSAGUAdAB1AHIAbgBzACAAMQAgACgAYQAgAD4AIABiACkALAAgAC0AMQAgACgAYQAgADwAIABiACkALAAgAG8AcgAgADAAIAAoAGEAIAA9ACAAYgApAC4AXABuACAAKgAgAEUAdgBhAGwAdQBhAHQAZQBzACAAcwBpAGcAbgBzACAAYQBuAGQAIABsAGUAbgBnAHQAaABzAC4AIABJAGYAIABpAGQAZQBuAHQAaQBjAGEAbAAsACAAZABlAGwAZQBnAGEAdABlAHMAIAB0AG8AIABuAGEAdABpAHYAZQAgAGwAaQBtAGIAIABhAHIAcgBhAHkAIABjAG8AbQBwAGEAcgBpAHMAbwBuAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAcwBlAGMAbwBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBDAG8AbQBwAGEAcgBlACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBhACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYQAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGIALAAgAEIAaQBnAGkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBiACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AYQAgADwAPgAgAHMAaQBnAG4AXwBiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMASQBHAE4AKABzAGkAZwBuAF8AYQAgAC0AIABzAGkAZwBuAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHMAaQBnAG4AXwBhACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYQAsACAATABFAE4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGIALAAgAEwARQBOACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABsAGUAbgBfAGEAIAA8AD4AIABsAGUAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBJAEcATgAoAGwAZQBuAF8AYQAgAC0AIABsAGUAbgBfAGIAKQAgACoAIABzAGkAZwBuAF8AYQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBBAEQARABcACIAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBhACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYgApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGEAZwBfAGMAbwBtAHAAYQByAGkAcwBvAG4ALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQwBvAG0AcABhAHIAZQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcABhAHIAaQBzAG8AbgAgACoAIABzAGkAZwBuAF8AYQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACAALQAgAEEAZABkAGkAdABpAG8AbgAgACYAIABTAHUAYgB0AHIAYQBjAHQAaQBvAG4AIAAtACAAIAAgACAAIAAgACAAXABcAFwAXABcAG4AXABuAC8AKgAqAFwAbgAgACoAIABBAGQAZABzACAAdAB3AG8AIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEEAZABkACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBhACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYQAsACAAQgBpAGcAaQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGIALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEEARABEAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBhACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGEAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBiACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGIAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAHIAbwB1AHQAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBBAGQAZABTAHUAYgBSAG8AdQB0AGUAcgAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAHMAaQBnAG4AXwBhACwAIABzAGkAZwBuAF8AYgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAGkAZwBuACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcgBvAHUAdABlAGQALAAgAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAEQAUgBPAFAAKAByAG8AdQB0AGUAZAAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAbQBlAHIAZwBlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGYAaQBuAGEAbABfAHMAaQBnAG4AIAA9ACAALQAxACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQALAAgAG0AZQByAGcAZQBkACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFMAdQBiAHQAcgBhAGMAdABzACAAdABoAGUAIABzAGUAYwBvAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAIABmAHIAbwBtACAAdABoAGUAIABmAGkAcgBzAHQAIAAoAEEAIAAtACAAQgApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAG0AaQBuAHUAZQBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGIAIABUAGgAZQAgAHMAdQBiAHQAcgBhAGgAZQBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBTAHUAYgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABiAGkAZwBfAGkAbgB0AF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAASQBuAHYAZQByAHQAIAB0AGgAZQAgAHMAaQBnAG4AIABvAGYAIABCACAAYQB0ACAAdABoAGUAIAB0AGUAeAB0ACAAbABlAHYAZQBsAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAHYAXwBiACwAIABJAEYAKABuAG8AcgBtAF8AYgAgAD0AIABcACIAMABcACIALAAgAFwAIgAwAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEwARQBGAFQAKABuAG8AcgBtAF8AYgApACAAPQAgAFwAIgAtAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAEQAKABuAG8AcgBtAF8AYgAsACAAMgAsACAATABFAE4AKABuAG8AcgBtAF8AYgApACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAgACYAIABuAG8AcgBtAF8AYgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUABhAHMAcwAgAHQAbwAgAEEAZABkAFwAbgAgACAAIAAgACAAIAAgACAAQQBkAGQAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAaQBuAHYAXwBiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFMAdQBtAHMAIABhAG4AIABhAHIAcgBhAHkAIABvAHIAIAByAGEAbgBnAGUAIABvAGYAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMAIAB2AGkAYQAgAHYAZQBjAHQAbwByAGkAegBlAGQAIABnAHIAbwB1AHAAIABtAGEAdAByAGkAYwBlAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIAByAGEAbgBnAGUAIABBACAAYwBvAG4AdABpAGcAdQBvAHUAcwAgAHIAYQBuAGcAZQAgAG8AcgAgAGEAcgByAGEAeQAgAG8AZgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoALwBcAG4AUwB1AG0AIAA9ACAATABBAE0AQgBEAEEAKAByAGEAbgBnAGUALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAZgBsAGEAdAAsACAAVABPAFIATwBXACgAcgBhAG4AZwBlACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATwBSACgASQBTAEUAUgBSAE8AUgAoAGYAbABhAHQAKQAsACAAQwBPAEwAVQBNAE4AUwAoAGYAbABhAHQAKQAgAD0AIAAwACkALAAgAFwAIgAwAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AbwByAG0AcwAsACAATQBBAFAAKABmAGwAYQB0ACwAIABMAEEATQBCAEQAQQAoAHgALAAgAE4AbwByAG0AKAB4ACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBzACwAIABNAEEAUAAoAEwARQBGAFQAKABuAG8AcgBtAHMAKQAsACAATABBAE0AQgBEAEEAKAB4ACwAIABJAEYAKAB4ACAAPQAgAFwAIgAwAFwAIgAsACAAMAAsACAAaQBmACgAeAAgAD0AIABcACIALQBcACIALAAgAC0AMQAsACAAMQApACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBiAHMAXwBuAG8AcgBtAHMALAAgAE0AQQBQACgAbgBvAHIAbQBzACwAIABzAGkAZwBuAHMALAAgAEwAQQBNAEIARABBACgAeAAsACAAcwBpAGcAbgAsACAASQBGACgAcwBpAGcAbgAgAD0AIAAtADEALAAgAE0ASQBEACgAeAAsACAAMgAsACAATABFAE4AKAB4ACkALQAxACkALAAgAHgAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAG8AcwBfAHMAdAByAHMALAAgAEYASQBMAFQARQBSACgAYQBiAHMAXwBuAG8AcgBtAHMALAAgAHMAaQBnAG4AcwAgAD0AIAAxACwAIAB7AFwAIgAwAFwAIgB9ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAZwBfAHMAdAByAHMALAAgAEYASQBMAFQARQBSACgAYQBiAHMAXwBuAG8AcgBtAHMALAAgAHMAaQBnAG4AcwAgAD0AIAAtADEALAAgAHsAXAAiADAAXAAiAH0AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHUAbgBpAGYAaQBlAGQAXwBrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIAQQBEAEQAXAAiACwAIABDAE8ATABVAE0ATgBTACgAZgBsAGEAdAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAG8AcwBfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAGEAdAByAGkAeABTAHUAbQAoAHAAbwBzAF8AcwB0AHIAcwAsACAAdQBuAGkAZgBpAGUAZABfAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQBnAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AYQB0AHIAaQB4AFMAdQBtACgAbgBlAGcAXwBzAHQAcgBzACwAIAB1AG4AaQBmAGkAZQBkAF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBvAHUAdABlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEEAZABkAFMAdQBiAFIAbwB1AHQAZQByACgAcABvAHMAXwBsAGkAbQBiAHMALAAgAG4AZQBnAF8AbABpAG0AYgBzACwAIAAxACwAIAAtADEALAAgAHUAbgBpAGYAaQBlAGQAXwBrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAGkAZwBuACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcgBvAHUAdABlAGQALAAgAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABEAFIATwBQACgAcgBvAHUAdABlAGQALAAgAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBlAHIAZwBlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAdQBuAGkAZgBpAGUAZABfAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGYAaQBuAGEAbABfAHMAaQBnAG4AIAA9ACAALQAxACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQALAAgAG0AZQByAGcAZQBkACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABNAHUAbAB0AGkAcABsAGkAZQBzACAAdAB3AG8AIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAE0AdQBsACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBhACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYQAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGIALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYQAsACAATABFAE4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGIALAAgAEwARQBOACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGgAbwByAHQALQBjAGkAcgBjAHUAaQB0ADoAIAAwACAAbQB1AGwAdABpAHAAbABpAGUAZAAgAGIAeQAgAGEAbgB5AHQAaABpAG4AZwAgAGkAcwAgADAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABzAGkAZwBuAF8AYQAgAD0AIAAwACwAIABzAGkAZwBuAF8AYgAgAD0AIAAwACkALAAgAFwAIgAwAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbABlAG4AXwBhACAAKwAgAGwAZQBuAF8AYgAgAD4AIAAzADIANwA2ADYALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAYQBsAGMAdQBsAGEAdABlACAAZAB5AG4AYQBtAGkAYwAgAHMAYQBmAGUAIABLACAAYgBhAHMAZQBkACAAbwBuACAAdABoAGUAIABzAGgAbwByAHQAZQBzAHQAIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIATQBVAEwAXAAiACwAIABNAEkATgAoAGwAZQBuAF8AYQAsACAAbABlAG4AXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAcABsAGkAdAAgAGEAYgBzAG8AbAB1AHQAZQAgAHMAdAByAGkAbgBnAHMAIABpAG4AdABvACAAbABpAHQAdABsAGUALQBlAG4AZABpAGEAbgAgAGEAcgByAGEAeQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGEALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYQApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBiACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGIAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIABtAGEAZwBuAGkAdAB1AGQAZQAgAGEAbgBkACAAcgBlAHMAbwBsAHYAZQAgAHMAaQBnAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcwBpAGcAbgAsACAAcwBpAGcAbgBfAGEAIAAqACAAcwBpAGcAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGUAcgBnAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAXAAiAC0AXAAiACAAJgAgAG0AZQByAGcAZQBkACwAIABtAGUAcgBnAGUAZAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAFYATwBMAEEAVABJAEwARQBdACAARwBlAG4AZQByAGEAdABlAHMAIABhACAAZAB5AG4AYQBtAGkAYwAgAGEAcgByAGEAeQAgAG8AZgAgAGkAbgB0AGUAZwBlAHIAcwAgAGEAcwAgAHQAZQB4AHQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG4AdQBtAF8AcgBvAHcAcwBdACAAYQByAHIAYQB5ACAAaABlAGkAZwBoAHQALAAgAGQAZQBmAGEAdQBsAHQAIAAxAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAWwBuAHUAbQBfAGMAbwBsAHMAXQAgAGEAcgByAGEAeQAgAHcAaQBkAHQAaAAsACAAZABlAGYAYQB1AGwAdAAgADEALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG0AaQBuAF8AZABpAGcAaQB0AHMAXQAgAG0AaQBuAGkAbQB1AG0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAaQBnAGkAdABzACwAIABkAGUAZgBhAHUAbAB0ACAAMQA2ACAAKABtAGkAbgAgADEAIABkAGkAZwBpAHQAKQBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG0AYQB4AF8AZABpAGcAaQB0AHMAXQAgAG0AYQB4AGkAbQB1AG0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAaQBnAGkAdABzACwAIABkAGUAZgBhAHUAbAB0ACAANQAwACAAKABtAGEAeAAgADMAMgAsADcANgA3ACAAYwBoAGEAcgBzACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAHMAaQBnAG4AKQBcAG4AIAAqAC8AXABuAFIAYQBuAGQAQgBpAGcASQBuAHQAQQByAHIAYQB5ACAAPQAgAEwAQQBNAEIARABBACgAWwBuAHUAbQBfAHIAbwB3AHMAXQAsACAAWwBuAHUAbQBfAGMAbwBsAHMAXQAsACAAWwBtAGkAbgBfAGQAaQBnAGkAdABzAF0ALAAgAFsAbQBhAHgAXwBkAGkAZwBpAHQAcwBdACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwByAG8AdwBzACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAG4AdQBtAF8AcgBvAHcAcwApACwAIAAxACwAIABuAHUAbQBfAHIAbwB3AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBfAGMAbwBsAHMALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbgB1AG0AXwBjAG8AbABzACkALAAgADEALAAgAG4AdQBtAF8AYwBvAGwAcwApACwAIABcAG4AIAAgACAAIAAgACAAIAAgAG0AaQBuAF8AbABlAG4ALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbQBpAG4AXwBkAGkAZwBpAHQAcwApACwAIAAxADYALAAgAE0ASQBOACgAMwAyADcANgA3ACwAIABNAEEAWAAoADEALAAgAG0AaQBuAF8AZABpAGcAaQB0AHMAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AbABlAG4ALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbQBhAHgAXwBkAGkAZwBpAHQAcwApACwAIAA1ADAALAAgAE0AQQBYACgAMQAsACAATQBJAE4AKAAzADIANwA2ADYALAAgAG0AYQB4AF8AZABpAGcAaQB0AHMAKQApACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABNAEEAUAAoAFIAQQBOAEQAQQBSAFIAQQBZACgAbgBfAHIAbwB3AHMALAAgAG4AXwBjAG8AbABzACwAIABtAGkAbgBfAGwAZQBuACwAIABtAGEAeABfAGwAZQBuACwAIABUAFIAVQBFACkALAAgAEwAQQBNAEIARABBACgAbABlAG4AZwB0AGgALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGkAZwBuACwAIABDAEgATwBPAFMARQAoAFIAQQBOAEQAQgBFAFQAVwBFAEUATgAoADEALAAgADIAKQAsACAAXAAiAFwAIgAsACAAXAAiAC0AXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGkAZwBpAHQAcwAsACAAQwBPAE4AQwBBAFQAKABSAEEATgBEAEEAUgBSAEEAWQAoADEALAAgAGwAZQBuAGcAdABoACwAIAAwACwAIAA5ACwAIABUAFIAVQBFACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AIAAmACAAUgBFAEcARQBYAFIARQBQAEwAQQBDAEUAKABkAGkAZwBpAHQAcwAsACAAXAAiAF4AMAAqAFwAIgAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABEAGkAdgBpAGQAZQBzACAAdABoAGUAIABmAGkAcgBzAHQAIABCAGkAZwBJAG4AdAAgAGIAeQAgAHQAaABlACAAcwBlAGMAbwBuAGQAIAAoAEEAIAAvACAAQgApAC4AIABcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAHQAaABlACAAcQB1AG8AdABpAGUAbgB0ACAAYQBuAGQAIABtAG8AZAB1AGwAdQBzACAAaQBuACAAcgBvAHcAcwAgADEAIABhAG4AZAAgADIALAAgAHIAZQBzAHAAZQBjAHQAaQB2AGUAbAB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAGQAaQB2AGkAZABlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAHUAcwBlAF8AZgBsAG8AbwByAF0AIABPAHAAdABpAG8AbgBhAGwAIABiAG8AbwBsAGUAYQBuAC4AIABUAFIAVQBFACAAZgBvAHIAIABQAHkAdABoAG8AbgAtAHMAdAB5AGwAZQAgAEYAbABvAG8AcgAgAGQAaQB2AGkAcwBpAG8AbgAsACAARgBBAEwAUwBFACAAZgBvAHIAIABUAHIAdQBuAGMAYQB0AGUAZAAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAARgBBAEwAUwBFAC4AXABuACAAKgAvAFwAbgBEAGkAdgBNAG8AZAAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABiAGkAZwBfAGkAbgB0AF8AYgAsACAAWwB1AHMAZQBfAGYAbABvAG8AcgBdACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBhACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYQAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGIALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGkAcwBfAGYAbABvAG8AcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAB1AHMAZQBfAGYAbABvAG8AcgApACwAIABGAEEATABTAEUALAAgAHUAcwBlAF8AZgBsAG8AbwByACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAcwBpAGcAbgBfAGIAIAA9ACAAMAAsACAAIwBEAEkAVgAvADAAIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AYQAgAD0AIAAwACwAIAB7AFwAIgAwAFwAIgA7AFwAIgAwAFwAIgB9ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBEAEkAVgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBhACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBiACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZABfAHIAZQBzAHUAbAB0ACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBEAGkAdgBSAG8AdQB0AGUAcgAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAUgBlAG0AYQBpAG4AZABlAHIAIABhAG4AZAAgAFEAdQBvAHQAaQBlAG4AdAAgAGEAcgByAGEAeQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwByACwAIABJAE4ARABFAFgAKABwAGEAYwBrAGUAZABfAHIAZQBzAHUAbAB0ACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBtAF8AbABpAG0AYgBzACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcABhAGMAawBlAGQAXwByAGUAcwB1AGwAdAAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwByACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcQB1AG8AdABfAGwAaQBtAGIAcwAsACAARABSAE8AUAAoAHAAYQBjAGsAZQBkAF8AcgBlAHMAdQBsAHQALAAgAGwAZQBuAF8AcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHMAbwBsAHYAZQAgAFQAcgB1AG4AYwBhAHQAZQBkACAAcwBpAGcAbgBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcwBpAGcAbgAsACAAcwBpAGcAbgBfAGEAIAAqACAAcwBpAGcAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AZQByAGcAZQBkAF8AcQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAcQB1AG8AdABfAGwAaQBtAGIAcwAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGUAcgBnAGUAZABfAHIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAHIAZQBtAF8AbABpAG0AYgBzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdAByAHUAbgBjAF8AcQAsACAASQBGACgAQQBOAEQAKABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAbQBlAHIAZwBlAGQAXwBxACAAPAA+ACAAXAAiADAAXAAiACkAIAAsACAAXAAiAC0AXAAiACAAJgAgAG0AZQByAGcAZQBkAF8AcQAsACAAbQBlAHIAZwBlAGQAXwBxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAcgB1AG4AYwBfAHIALAAgAEkARgAoAGEAbgBkACgAcwBpAGcAbgBfAGEAIAA9ACAALQAxACwAIABtAGUAcgBnAGUAZABfAHIAIAA8AD4AIABcACIAMABcACIAKQAsACAAXAAiAC0AXAAiACAAJgAgAG0AZQByAGcAZQBkAF8AcgAsACAAbQBlAHIAZwBlAGQAXwByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARgBsAG8AbwByACAAQwBvAHIAcgBlAGMAdABpAG8AbgA6ACAAVAByAGkAZwBnAGUAcgAgAE8ATgBMAFkAIABpAGYAIABmAGwAbwBvAHIAIABpAHMAIAByAGUAcQB1AGUAcwB0AGUAZAAsACAAcwBpAGcAbgBzACAAZABpAGYAZgBlAHIALAAgAGEAbgBkACAAcgBlAG0AYQBpAG4AZABlAHIAIABpAHMAIABuAG8AbgAtAHoAZQByAG8AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAZQBkAHMAXwBjAG8AcgByAGUAYwB0AGkAbwBuACwAIABBAE4ARAAoAGkAcwBfAGYAbABvAG8AcgAsACAAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAG0AZQByAGcAZQBkAF8AcgAgADwAPgAgAFwAIgAwAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHEALAAgAEkARgAoAG4AZQBlAGQAcwBfAGMAbwByAHIAZQBjAHQAaQBvAG4ALAAgAFMAdQBiACgAdAByAHUAbgBjAF8AcQAsACAAXAAiADEAXAAiACkALAAgAHQAcgB1AG4AYwBfAHEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsACAASQBGACgAbgBlAGUAZABzAF8AYwBvAHIAcgBlAGMAdABpAG8AbgAsACAAQQBkAGQAKAB0AHIAdQBuAGMAXwByACwAIABuAG8AcgBtAF8AYgApACwAIAB0AHIAdQBuAGMAXwByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABmAGkAbgBhAGwAXwBxACwAIABmAGkAbgBhAGwAXwByACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEQAaQB2AGkAZABlAHMAIAB0AGgAZQAgAGYAaQByAHMAdAAgAEIAaQBnAEkAbgB0ACAAYgB5ACAAdABoAGUAIABzAGUAYwBvAG4AZAAgACgAQQAgAC8AIABCACkALgAgAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBhACAAVABoAGUAIABkAGkAdgBpAGQAZQBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGIAIABUAGgAZQAgAGQAaQB2AGkAcwBvAHIAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAWwB1AHMAZQBfAGYAbABvAG8AcgBdACAATwBwAHQAaQBvAG4AYQBsACAAYgBvAG8AbABlAGEAbgAuACAAVABSAFUARQAgAGYAbwByACAAUAB5AHQAaABvAG4ALQBzAHQAeQBsAGUAIABGAGwAbwBvAHIAIABkAGkAdgBpAHMAaQBvAG4ALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAEYAQQBMAFMARQAuAFwAbgAgACoALwBcAG4ARABpAHYAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALAAgAFsAdQBzAGUAXwBmAGwAbwBvAHIAXQAsAFwAbgAgACAAIAAgAEkATgBEAEUAWAAoAEQAaQB2AE0AbwBkACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAIAB1AHMAZQBfAGYAbABvAG8AcgApACwAIAAxACwAIAAxACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABDAG8AbQBwAHUAdABlAHMAIAB0AGgAZQAgAHIAZQBtAGEAaQBuAGQAZQByACAAbwBmACAAQQAgAC8AIABCAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAGQAaQB2AGkAZABlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAHUAcwBlAF8AZgBsAG8AbwByAF0AIABPAHAAdABpAG8AbgBhAGwAIABiAG8AbwBsAGUAYQBuAC4AIABUAFIAVQBFACAAZgBvAHIAIABQAHkAdABoAG8AbgAtAHMAdAB5AGwAZQAgAE0AbwBkAHUAbABvAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABGAEEATABTAEUALgBcAG4AIAAqAC8AXABuAE0AbwBkACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAIABbAHUAcwBlAF8AZgBsAG8AbwByAF0ALABcAG4AIAAgACAAIABJAE4ARABFAFgAKABEAGkAdgBNAG8AZAAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABiAGkAZwBfAGkAbgB0AF8AYgAsACAAdQBzAGUAXwBmAGwAbwBvAHIAKQAsACAAMgAsACAAMQApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBhAGkAcwBlAHMAIABhACAAQgBpAGcASQBuAHQAIABiAGEAcwBlACAAdABvACAAdABoAGUAIABwAG8AdwBlAHIAIABvAGYAIABhACAAQgBpAGcASQBuAHQAIABlAHgAcABvAG4AZQBuAHQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGEAcwBlACAAVABoAGUAIABiAGEAcwBlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGUAeABwAG8AbgBlAG4AdAAgAFQAaABlACAAZQB4AHAAbwBuAGUAbgB0ACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AUABvAHcAIAA9ACAATABBAE0AQgBEAEEAKABiAGEAcwBlACwAIABlAHgAcABvAG4AZQBuAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIAYQBzAGUALAAgAE4AbwByAG0AKABiAGEAcwBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBlAHgAcAAsACAATgBvAHIAbQAoAGUAeABwAG8AbgBlAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgBhAHMAZQAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGUAeABwACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AZQB4AHAAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGEAYgBzAF8AYgBhAHMAZQAsACAAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBiAGEAcwBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAGEAYgBzAF8AZQB4AHAALAAgAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AZQB4AHAAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGkAcwBfAGUAeABwAF8AZQB2AGUAbgAsACAASQBTAEUAVgBFAE4AKABWAEEATABVAEUAKABSAEkARwBIAFQAKABuAG8AcgBtAF8AZQB4AHAALAAgADEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAaQBnAG4ALAAgAEkARgAoAHMAaQBnAG4AXwBiAGEAcwBlACAAPQAgAC0AMQAsACAASQBGACgAaQBzAF8AZQB4AHAAXwBlAHYAZQBuACwAIAAxACwAIAAtADEAKQAsACAAcwBpAGcAbgBfAGIAYQBzAGUAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEgAYQBuAGQAbABlACAAbQBhAHQAaABlAG0AYQB0AGkAYwBhAGwAIABiAG8AdQBuAGQAYQByAGkAZQBzACAAYQBuAGQAIABiAGEAcwBlACAAbABpAG0AaQB0AHMAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABhAGIAcwBfAGIAYQBzAGUAIAA9ACAAXAAiADAAXAAiACwAIABJAEYAKABuAG8AcgBtAF8AZQB4AHAAIAA9ACAAXAAiADAAXAAiACwAIAAjAE4AVQBNACEALAAgAFwAIgAwAFwAIgApACwAIAAvAC8AIAAwAF4AMAAgAGkAcwAgAHUAbgBkAGUAZgBpAG4AZQBkAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAYQBiAHMAXwBiAGEAcwBlACAAPQAgAFwAIgAxAFwAIgAsACAASQBGACgAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAFwAIgAtADEAXAAiACwAIABcACIAMQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAcwBpAGcAbgBfAGUAeABwACAAPQAgAC0AMQAsACAAXAAiADAAXAAiACwAIAAvAC8AIABJAG4AdABlAGcAZQByACAAdAByAHUAbgBjAGEAdABpAG8AbgA6ACAAbgBlAGcAYQB0AGkAdgBlACAAZQB4AHAAbwBuAGUAbgB0AHMAIAB5AGkAZQBsAGQAIAAwACAAZgBvAHIAIABiAGEAcwBlAHMAIAA+AD0AIAAyAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgBvAHIAbQBfAGUAeABwACAAPQAgAFwAIgAwAFwAIgAsACAAXAAiADEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHMAdQBsAHQAcwAgAGYAcgBvAG0AIABlAHgAcABvAG4AZQBuAHQAcwAgAGcAcgBlAGEAdABlAHIAIAB0AGgAYQBuACAANgAgAGQAaQBnAGkAdABzACAAYwBhAG4AbgBvAHQAIABiAGUAIABkAGkAcwBwAGwAYQB5AGUAZAAuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABFAE4AKABuAG8AcgBtAF8AZQB4AHAAKQAgAD4AIAA2ACwAIAAjAE4AVQBNACEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAHUAbQBfAGUAeABwACwAIABWAEEATABVAEUAKABuAG8AcgBtAF8AZQB4AHAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAcABwAHIAbwB4AGkAbQBhAHQAZQAgAHQAaABlACAAZgBpAG4AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAIABjAG8AdQBuAHQAOgAgAEIAIAAqACAATABvAGcAMQAwACgAQQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGIAYQBzAGUAXwBsAG8AZwAxADAALAAgAEwATwBHADEAMAAoAFYAQQBMAFUARQAoAEwARQBGAFQAKABhAGIAcwBfAGIAYQBzAGUALAAgADEANAApACkAKQAgACsAIABNAEEAWAAoADAALAAgAEwARQBOACgAYQBiAHMAXwBiAGEAcwBlACkAIAAtACAAMQA0ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAHAAcAByAG8AeABfAGQAaQBnAGkAdABzACwAIABuAHUAbQBfAGUAeABwACAAKgAgAGIAYQBzAGUAXwBsAG8AZwAxADAALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYQBwAHAAcgBvAHgAXwBkAGkAZwBpAHQAcwAgAD4AIAAzADIANwA2ADYALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAE0AVQBMAFwAIgAsACAAYQBwAHAAcgBvAHgAXwBkAGkAZwBpAHQAcwAgAC8AIAAyACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYgBhAHMAZQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYQBiAHMAXwBiAGEAcwBlACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBQAG8AdwAoAGwAaQBtAGIAcwBfAGIAYQBzAGUALAAgAG4AbwByAG0AXwBlAHgAcAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AZQByAGcAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAFwAIgAtAFwAIgAgACYAIABtAGUAcgBnAGUAZAAsACAAbQBlAHIAZwBlAGQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQApACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2AGkAcwBpAG8AbgAiACwAIgB0AGUAcwB0AF8AQgBpAGcASQBuAHQALgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAiACwAIgB0AGUAcwB0AF8AQgBpAGcASQBuAHQALgBEAGkAdgBpAHMAaQBvAG4AQQBsAGcAbwByAGkAdABoAG0AcwAiACwAIgB0AGUAcwB0AF8AQgBpAGcASQBuAHQALgBEAGkAdgBpAHMAaQBvAG4AQQBsAGcAbwByAGkAdABoAG0AQwBvAG0AcABhAHIAaQBzAG8AbgAiACwAIgB0AGUAcwB0AF8AQgBpAGcASQBuAHQALgBEAGkAdgBpAHMAaQBvAG4AQgBlAG4AYwBoAG0AYQByAGsAQwBhAHMAZQBzACIALAAiAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAuAEEAcwB5AG0AbQBlAHQAcgBpAGMAQQBCAEcAcgBpAGQAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AQwBhAHIAcgB5ACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQwBvAG0AcABhAHIAZQAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEEAZABkACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAUwB1AGIAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAGEAdAByAGkAeABTAHUAbQAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBBAGQAZABTAHUAYgBSAG8AdQB0AGUAcgAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEYAaQBuAGQAUQB1AG8AdABpAGUAbgB0AEwAaQBtAGIAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2ACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEQAaQB2AFIAbwB1AHQAZQByACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4AUwBlAGUAZAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAFIAZQBjAGkAcAByAG8AYwBhAGwAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFAAbwB3ACIALAAiAEIAaQBnAEkAbgB0AC4ATgBvAHIAbQAiACwAIgBCAGkAZwBJAG4AdAAuAFMAaQBnAG4AIgAsACIAQgBpAGcASQBuAHQALgBJAHMAWgBlAHIAbwAiACwAIgBCAGkAZwBJAG4AdAAuAEkAcwBOAGUAZwAiACwAIgBCAGkAZwBJAG4AdAAuAEkAcwBFAHYAZQBuACIALAAiAEIAaQBnAEkAbgB0AC4ASQBzAE8AZABkACIALAAiAEIAaQBnAEkAbgB0AC4AQQBiAHMAIgAsACIAQgBpAGcASQBuAHQALgBDAG8AbQBwAGEAcgBlACIALAAiAEIAaQBnAEkAbgB0AC4AQQBkAGQAIgAsACIAQgBpAGcASQBuAHQALgBTAHUAYgAiACwAIgBCAGkAZwBJAG4AdAAuAFMAdQBtACIALAAiAEIAaQBnAEkAbgB0AC4ATQB1AGwAIgAsACIAQgBpAGcASQBuAHQALgBSAGEAbgBkAEIAaQBnAEkAbgB0AEEAcgByAGEAeQAiACwAIgBCAGkAZwBJAG4AdAAuAEQAaQB2AE0AbwBkACIALAAiAEIAaQBnAEkAbgB0AC4ARABpAHYAIgAsACIAQgBpAGcASQBuAHQALgBNAG8AZAAiACwAIgBCAGkAZwBJAG4AdAAuAFAAbwB3ACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAFwAbgAvAC8AIABCAGkAZwAgAEkAbgB0AGUAZwBlAHIAIABBAHIAaQB0AGgAbQBlAHQAaQBjACAATABpAGIAcgBhAHIAeQAgAC8ALwBcAG4ALwAvACAAIAAgACAAIAAgACAAdABlAHMAdABfAEIAaQBnAEkAbgB0ACAATQBvAGQAdQBsAGUAIAAgACAAIAAgACAAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIAAgAFAAcgBpAHYAYQB0AGUAIABUAGUAcwB0AGkAbgBnACAAQQBQAEkAIAAgACAAIAAgACAALwAvAFwAbgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4AXABuAEsAbgB1AHQAaABEAGkAdgBpAHMAaQBvAG4APQBMAEEATQBCAEQAQQAoAGEALAAgAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2ACgAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYQAsACAAawApACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABiACwAIABrACkALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAEQAUgBPAFAAKABwAGEAYwBrAGUAZAAsACAASQBOAEQARQBYACgAcABhAGMAawBlAGQALAAgADEALAAgADEAKQAgACsAIAAxACkALAAgAGsAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAgAD0AIABMAEEATQBCAEQAQQAoAGEALAAgAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgAoAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAGEALAAgAGsAKQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYgAsACAAawApACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABEAFIATwBQACgAcABhAGMAawBlAGQALAAgAEkATgBEAEUAWAAoAHAAYQBjAGsAZQBkACwAIAAxACwAIAAxACkAIAArACAAMQApACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAcwB0AHIAaQBuAGcAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAHMAdAByAGkAbgBnAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG0AbwBkAGUAIABcACIASwBOAFUAVABIAFwAIgAgAG8AcgAgAFwAIgBOAFIAXAAiAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGkAdABlAHIAcwAgAEkAbgBuAGUAcgAgAGwAbwBvAHAAIABjAG8AdQBuAHQAIAAoAHQAbwAgAGQAZQBmAGUAYQB0ACAAYwBoAHUAbgBrAHkAIABjAGwAbwBjAGsAIAByAGUAcwBvAGwAdQB0AGkAbwBuACkAXABuACAAKgAgAEAAcABhAHIAYQBtACAAcgBlAHAAZQBhAHQAcwAgAE8AdQB0AGUAcgAgAGwAbwBvAHAAIABjAG8AdQBuAHQAIAAoAHQAbwAgAGQAZQBmAGUAYQB0ACAATwBTAC8ARwBhAHIAYgBhAGcAZQAgAEMAbwBsAGwAZQBjAHQAaQBvAG4AIABuAG8AaQBzAGUAKQBcAG4AIAAqAC8AXABuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACAAPQAgAEwAQQBNAEIARABBACgAYQAsACAAYgAsACAAbQBvAGQAZQAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAE0AYQBwACAAdABoAGUAIABvAHUAdABlAHIAIAByAGUAcABlAGEAdABzACAAbABvAG8AcABcAG4AIAAgACAAIAAgACAAIAAgAGIAYQB0AGMAaABfAHQAaQBtAGUAcwAsACAATQBBAFAAKABTAEUAUQBVAEUATgBDAEUAKAByAGUAcABlAGEAdABzACkALAAgAEwAQQBNAEIARABBACgAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdAAsACAATgBPAFcAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATQBhAHAAIAB0AGgAZQAgAGkAbgBuAGUAcgAgAGUAeABlAGMAdQB0AGkAbwBuACAAbABvAG8AcABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAHUAbgAsACAASQBGACgAbQBvAGQAZQAgAD0AIABcACIASwBOAFUAVABIAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBQACgAUwBFAFEAVQBFAE4AQwBFACgAaQB0AGUAcgBzACkALAAgAEwAQQBNAEIARABBACgAaQAsACAASwBuAHUAdABoAEQAaQB2AGkAcwBpAG8AbgAoAGEALAAgAGIAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFAAKABTAEUAUQBVAEUATgBDAEUAKABpAHQAZQByAHMAKQAsACAATABBAE0AQgBEAEEAKABpACwAIABOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAoAGEALAAgAGIAKQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEYAbwByAGMAZQAgAGUAdgBhAGwAdQBhAHQAaQBvAG4AIABiAGUAZgBvAHIAZQAgAHAAdQBsAGwAaQBuAGcAIABzAHQAbwBwACAAdABpAG0AZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAbwBwACwAIABOAE8AVwAoACkAIAArACAAKAAwACAAKgAgAEwARQBOACgASQBOAEQARQBYACgAcgB1AG4ALAAgADEALAAgADEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABUAG8AdABhAGwAIABiAGEAdABjAGgAIAB0AGkAbQBlACAAaQBuACAAbQBpAGwAbABpAHMAZQBjAG8AbgBkAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABzAHQAbwBwACAALQAgAHMAdABhAHIAdAApACAAKgAgADgANgA0ADAAMAAwADAAMABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAdABoAGUAIABjAGwAZQBhAG4AZQBzAHQAIAByAHUAbgAgAGEAbgBkACAAYQB2AGUAcgBhAGcAZQAgAGkAdAAgAGQAbwB3AG4AIAB0AG8AIABhACAAcwBpAG4AZwBsAGUAIABlAHgAZQBjAHUAdABpAG8AbgAgAHQAaQBtAGUAXABuACAAIAAgACAAIAAgACAAIABNAEkATgAoAGIAYQB0AGMAaABfAHQAaQBtAGUAcwApACAALwAgAGkAdABlAHIAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAARQB4AGUAYwB1AHQAZQBzACAAYQAgAHMAdAByAGkAYwB0AGwAeQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABiAGUAbgBjAGgAbQBhAHIAawAgAHMAdQBpAHQAZQAgAHQAbwAgAGEAdgBvAGkAZAAgAG0AdQBsAHQAaQAtAHQAaAByAGUAYQBkAGkAbgBnACAAYwBvAG4AdABhAG0AaQBuAGEAdABpAG8AbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHQAZQBzAHQAXwBjAGEAcwBlAHMAIABBAG4AIABOACAAeAAgADIAIABhAHIAcgBhAHkAIABvAGYAIAB0AGUAcwB0ACAAbABlAG4AZwB0AGgAcwA6ACAAWwBMAGUAbgBnAHQAaABfAEEALAAgAEwAZQBuAGcAdABoAF8AQgBdAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGkAdABlAHIAcwAgAE4AdQBtAGIAZQByACAAbwBmACAAaQB0AGUAcgBhAHQAaQBvAG4AcwAgAHAAZQByACAAYgBlAG4AYwBoAG0AYQByAGsAIAB0AG8AIABzAG0AbwBvAHQAaAAgAE4ATwBXACgAKQAgAHIAZQBzAG8AbAB1AHQAaQBvAG4ALgBcAG4AIAAqAC8AXABuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBDAG8AbQBwAGEAcgBpAHMAbwBuACAAPQAgAEwAQQBNAEIARABBACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwB0AGUAcwB0AHMALAAgAFIATwBXAFMAKAB0AGUAcwB0AF8AYwBhAHMAZQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAASQBuAGkAdABpAGEAbAAgAHMAdABhAHQAZQA6ACAARABhAHQAYQAgAGgAZQBhAGQAZQByAHMAIABmAG8AcgAgAEMAUwBWACAAZQB4AHAAbwByAHQAXABuACAAIAAgACAAIAAgACAAIABpAG4AaQB0AGkAYQBsACwAIAB7AFwAIgBMAGUAbgBfAEEAXAAiACwAIABcACIATABlAG4AXwBCAFwAIgAsACAAXAAiAEsAbgB1AHQAaABfAG0AcwBcACIALAAgAFwAIgBOAFIAXwBtAHMAXAAiAH0ALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsACwAIABTAEUAUQBVAEUATgBDAEUAKABuAF8AdABlAHMAdABzACkALAAgAEwAQQBNAEIARABBACgAYQBjAGMALAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAEkATgBEAEUAWAAoAHQAZQBzAHQAXwBjAGEAcwBlAHMALAAgAGkALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAASQBOAEQARQBYACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBrAGkAcAAgAEQAaQB2AGkAcwBvAHIAIAA+ACAARABpAHYAaQBkAGUAbgBkABQgaQB0ACcAcwAgAG4AZQB2AGUAcgAgAGEAbgAgAGkAbgB0AGUAZwBlAHIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbABlAG4AXwBiACAAPgAgAGwAZQBuAF8AYQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAYwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARwBlAG4AZQByAGEAdABlACAAZQB4AGEAYwB0AC0AbABlAG4AZwB0AGgAIAB0AGUAcwB0ACAAcwB0AHIAaQBuAGcAcwAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AHIAXwBhACwAIABSAEUAUABUACgAXAAiADkAXAAiACwAIABsAGUAbgBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAcgBfAGIALAAgAEkARgAoAGwAZQBuAF8AYgAgAD0AIAAxACwAIABcACIANwBcACIALAAgAFwAIgA3AFwAIgAgACYAIABSAEUAUABUACgAXAAiADMAXAAiACwAIABsAGUAbgBfAGIAIAAtACAAMQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeABlAGMAdQB0AGUAIABiAGUAbgBjAGgAbQBhAHIAawBzACAAcwB0AHIAaQBjAHQAbAB5ACAAbwBuAGUAIABhAGYAdABlAHIAIAB0AGgAZQAgAG8AdABoAGUAcgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABpAG0AZQBfAGsALAAgAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACgAcwB0AHIAXwBhACwAIABzAHQAcgBfAGIALAAgAFwAIgBLAE4AVQBUAEgAXAAiACwAIABpAHQAZQByAHMALAAgAHIAZQBwAGUAYQB0AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGkAbQBlAF8AbgByACwAIABEAGkAdgBpAHMAaQBvAG4AQQBsAGcAbwByAGkAdABoAG0AcwAoAHMAdAByAF8AYQAsACAAcwB0AHIAXwBiACwAIABcACIATgBSAFwAIgAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAcABwAGUAbgBkACAAdABoAGUAIAByAGUAcwB1AGwAdABzAC4AIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAGEAbABsAG8AYwBhAHQAaQBvAG4AIABkAGUAbABhAHkAIABvAGMAYwB1AHIAcwAgAGgAZQByAGUALAAgAHMAYQBmAGUAbAB5ACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAdABpAG0AZQBkACAAdwBpAG4AZABvAHcALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABhAGMAYwAsACAASABTAFQAQQBDAEsAKABsAGUAbgBfAGEALAAgAGwAZQBuAF8AYgAsACAAdABpAG0AZQBfAGsALAAgAHQAaQBtAGUAXwBuAHIAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgADIALQBjAG8AbAB1AG0AbgAgAGEAcgByAGEAeQAgAG8AZgAgAGUAdgBlAHIAeQAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgAgAG8AZgAgAGwAZQBuAGcAdABoAHMAXABuAEQAaQB2AGkAcwBpAG8AbgBCAGUAbgBjAGgAbQBhAHIAawBDAGEAcwBlAHMAIAA9ACAATABBAE0AQgBEAEEAKABzAHQAYQByAHQAXwBsAGUAbgAsACAAbQBhAHgAXwBsAGUAbgAsACAAcwB0AGUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQAsACAAUwBFAFEAVQBFAE4AQwBFACgAKABtAGEAeABfAGwAZQBuACAALQAgAHMAdABhAHIAdABfAGwAZQBuACkAIAAvACAAcwB0AGUAcAAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBsAGUAbgAsACAAcwB0AGUAcAApACwAXABuACAAIAAgACAAIAAgACAAIABuACwAIABSAE8AVwBTACgAcwBlAHEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAcgB0AGUAcwBpAGEAbgAgAEoAbwBpAG4AXABuACAAIAAgACAAIAAgACAAIABjAG8AbABfAGEALAAgAFQATwBDAE8ATAAoAEkARgAoAFMARQBRAFUARQBOAEMARQAoADEALAAgAG4AKQAsACAAcwBlAHEAKQApACwAXABuACAAIAAgACAAIAAgACAAIABjAG8AbABfAGIALAAgAFQATwBDAE8ATAAoAEkARgAoAFMARQBRAFUARQBOAEMARQAoAG4ALAAgADEAKQAsACAAVABPAFIATwBXACgAcwBlAHEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABjAG8AbABfAGEALAAgAGMAbwBsAF8AYgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgAEMAYQByAHQAZQBzAGkAYQBuACAAZwByAGkAZAAgAGYAcgBvAG0AIAB0AHcAbwAgAGkAbgBkAGUAcABlAG4AZABlAG4AdAAgAHMAZQBxAHUAZQBuAGMAZQBzAFwAbgBBAHMAeQBtAG0AZQB0AHIAaQBjAEEAQgBHAHIAaQBkACAAPQAgAEwAQQBNAEIARABBACgAcwB0AGEAcgB0AF8AYQAsACAAbQBhAHgAXwBhACwAIABzAHQAZQBwAF8AYQAsACAAcwB0AGEAcgB0AF8AYgAsACAAbQBhAHgAXwBiACwAIABzAHQAZQBwAF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGEALAAgAFMARQBRAFUARQBOAEMARQAoACgAbQBhAHgAXwBhACAALQAgAHMAdABhAHIAdABfAGEAKQAgAC8AIABzAHQAZQBwAF8AYQAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBhACwAIABzAHQAZQBwAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGIALAAgAFMARQBRAFUARQBOAEMARQAoACgAbQBhAHgAXwBiACAALQAgAHMAdABhAHIAdABfAGIAKQAgAC8AIABzAHQAZQBwAF8AYgAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBiACwAIABzAHQAZQBwAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwBhACwAIABSAE8AVwBTACgAcwBlAHEAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwBiACwAIABSAE8AVwBTACgAcwBlAHEAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAATwByAHQAaABvAGcAbwBuAGEAbAAgAGIAcgBvAGEAZABjAGEAcwB0ACAAdQBzAGkAbgBnACAAaQBuAGQAZQBwAGUAbgBkAGUAbgB0ACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIAAgACAAIAAgAGMAbwBsAF8AYQAsACAAVABPAEMATwBMACgASQBGACgAUwBFAFEAVQBFAE4AQwBFACgAMQAsACAAbgBfAGIAKQAsACAAcwBlAHEAXwBhACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBvAGwAXwBiACwAIABUAE8AQwBPAEwAKABJAEYAKABTAEUAUQBVAEUATgBDAEUAKABuAF8AYQApACwAIABUAE8AUgBPAFcAKABzAGUAcQBfAGIAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABjAG8AbABfAGEALAAgAGMAbwBsAF8AYgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBjAG8AcgBlAF8AQgBpAGcASQBuAHQAIgAsACIAdABlAHgAdAAiADoAIgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4ALwAvACAAQgBpAGcAIABJAG4AdABlAGcAZQByACAAQQByAGkAdABoAG0AZQB0AGkAYwAgAEwAaQBiAHIAYQByAHkAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQAIABNAG8AZAB1AGwAZQAgACAAIAAgACAAIAAgACAALwAvAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIABQAHIAaQB2AGEAdABlACAAQQBQAEkAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwBcAG4ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8AXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEMAbwBtAHAAdQB0AGUAcwAgAHQAaABlACAAbQBhAHgAaQBtAHUAbQAgAHMAYQBmAGUAIABiAGEAcwBlAC0AMQAwACAAbABpAG0AYgAgAHMAaQB6AGUAIAAoAGsAKQAgAHQAbwAgAGEAdgBvAGkAZAAgAEkARQBFAEUALQA3ADUANAAgAHAAcgBlAGMAaQBzAGkAbwBuACAAbABvAHMAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG8AcABlAHIAYQB0AGkAbwBuADoAIABcACIAQQBEAEQAXAAiACwAIABcACIATQBVAEwAXAAiACwAIABvAHIAIABcACIARABJAFYAXAAiAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAWwBtAGEAeABfAGkAdABlAG0AcwBdACAAQQBEAEQAOgAgAG4AdQBtAGIAZQByACAAbwBmACAAbwBwAGUAcgBhAG4AZABzAC4AIABNAFUATAA6ACAAcwBoAG8AcgB0AGUAcwB0ACAAcwB0AHIAaQBuAGcAIABkAGkAZwBpAHQAcwAgAGMAbwB1AG4AdAAuAFwAbgAgACoALwBcAG4AUwBhAGYAZQBLACAAPQAgAEwAQQBNAEIARABBACgAbwBwAGUAcgBhAHQAaQBvAG4ALAAgAFsAbQBhAHgAXwBpAHQAZQBtAHMAXQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABpAHQAZQBtAHMALAAgAEkARgAoAE8AUgAoAG0AYQB4AF8AaQB0AGUAbQBzACAAPQAgAFwAIgBcACIALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAbQBhAHgAXwBpAHQAZQBtAHMAKQApACwAIAAyACwAIABNAEEAWAAoADIALAAgAG0AYQB4AF8AaQB0AGUAbQBzACkAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVwBJAFQAQwBIACgAbwBwAGUAcgBhAHQAaQBvAG4ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEARABEAFwAIgAsACAAMQA1ACAALQAgAEwARQBOACgAaQB0AGUAbQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFUATABcACIALAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARQB2AGEAbAB1AGEAdABlACAAcABvAHMAcwBpAGIAbABlACAAawAgAHYAYQBsAHUAZQBzACAAZAB5AG4AYQBtAGkAYwBhAGwAbAB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAZQBzAHQAXwBrACwAIAB7ADcAOwAgADYAOwAgADUAOwAgADQAOwAgADMAOwAgADIAOwAgADEAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AbwB2AGUAcgBsAGEAcAAsACAAUgBPAFUATgBEAFUAUAAoAGkAdABlAG0AcwAgAC8AIAB0AGUAcwB0AF8AawAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIAB0AGgAZQAgAGEAYgBzAG8AbAB1AHQAZQAgAHAAZQBhAGsAIAB2AGEAbAB1AGUAIABpAG4AcwBpAGQAZQAgAHQAaABlACAAZQBuAGcAaQBuAGUAIAAoAEMAbwBuAHYAbwBsAHUAdABpAG8AbgAgACsAIABDAGEAcgByAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB1AG4AYwBhAHIAcgBpAGUAZABfAG0AYQB4ACwAIABtAGEAeABfAG8AdgBlAHIAbABhAHAAIAAqACAAKAAxADAAXgB0AGUAcwB0AF8AawAgAC0AIAAxACkAXgAyACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAHgAXwBjAGEAcgByAHkALAAgAEkATgBUACgAdQBuAGMAYQByAHIAaQBlAGQAXwBtAGEAeAAgAC8AIAAxADAAXgB0AGUAcwB0AF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABlAGEAawBfAHYAYQBsACwAIAB1AG4AYwBhAHIAcgBpAGUAZABfAG0AYQB4ACAAKwAgAG0AYQB4AF8AYwBhAHIAcgB5ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHQAdQByAG4AIAB0AGgAZQAgAG0AYQB4ACAAawAgADwAPQAgAEUAeABjAGUAbAAnAHMAIAAxADUALQBkAGkAZwBpAHQAIABjAGUAaQBsAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgARgBJAEwAVABFAFIAKAB0AGUAcwB0AF8AawAsACAAcABlAGEAawBfAHYAYQBsACAAPAA9ACAAKAAxADAAXgAxADUAIAAtACAAMQApACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQASQBWAFwAIgAsACAANwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAE4AQQBNAEUAPwBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AaQBmAGkAZQBkACAAUwBwAGwAaQB0AHQAZQByAC4AIABTAHAAbABpAHQAcwAgAGIAbwB0AGgAIABzAGMAYQBsAGEAcgBzACAAYQBuAGQAIABhAHIAcgBhAHkAcwAgAGkAbgB0AG8AIABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuACAAbABpAG0AYgBzAC4AXABuACAAKgAgAFUAcwBlAHMAIABNAEEAWAAoACkAIAB0AG8AIABnAHUAYQByAGEAbgB0AGUAZQAgAHMAYwBhAGwAYQByACAAaQBuAHAAdQB0AHMAIAB0AG8AIAB0AGgAZQAgAFMARQBRAFUARQBOAEMARQAgAGUAbgBnAGkAbgBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABzACAAVABoAGUAIABzAHQAcgBpAG4AZwAgAG8AcgAgAGEAcgByAGEAeQAgAG8AZgAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFMAcABsAGkAdAAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAcwAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABiAGkAZwBfAGkAbgB0AF8AcgBvAHcALAAgAFQATwBSAE8AVwAoAGIAaQBnAF8AaQBuAHQAcwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBnAHQAaABzACwAIABMAEUATgAoAGIAaQBnAF8AaQBuAHQAXwByAG8AdwApACwAXABuACAAIAAgACAAIAAgACAAIABtAGEAeABfAGwAZQBuACwAIABNAEEAWAAoAGwAZQBuAGcAdABoAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBsAGUAbgAsACAAUgBPAFUATgBEAFUAUAAoAG0AYQB4AF8AbABlAG4AIAAvACAAawAsACAAMAApACAAKgAgAGsALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAZABlAGQALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAHAAYQBkAF8AbABlAG4AIAAtACAAbABlAG4AZwB0AGgAcwApACAAJgAgAGIAaQBnAF8AaQBuAHQAXwByAG8AdwAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALAAgAFMARQBRAFUARQBOAEMARQAoAHAAYQBkAF8AbABlAG4AIAAvACAAawAsACAAMQAsACAAcABhAGQAXwBsAGUAbgAgAC0AIABrACAAKwAgADEALAAgAC0AawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC0ALQBNAEkARAAoAHAAYQBkAGQAZQBkACwAIABzAHQAYQByAHQAcwAsACAAawApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAQwBvAG4AYwBhAHQAZQBuAGEAdABlAHMAIABhAG4AIABhAHIAcgBhAHkAIABvAGYAIABuAHUAbQBlAHIAaQBjACAAbABpAG0AYgBzACAAaQBuAHQAbwAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnACwAIAB6AGUAcgBvAC0AcABhAGQAZABpAG4AZwAgAGEAbABsACAAYgB1AHQAIAB0AGgAZQAgAGYAaQByAHMAdAAgAGwAaQBtAGIALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAIABUAGgAZQAgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAG4AdQBtAGUAcgBpAGMAIABsAGkAbQBiAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABsAGkAbQBiACAAcwBpAHoAZQAgAHUAcwBlAGQAIABkAHUAcgBpAG4AZwAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAuAFwAbgAgACoALwBcAG4ATQBlAHIAZwBlACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AdQBtAF8AbABpAG0AYgBzACwAIABSAE8AVwBTACgAbABpAG0AYgBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQB2AF8AbABpAG0AYgBzACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAbABpAG0AYgBzACwAIABTAEUAUQBVAEUATgBDAEUAKABuAHUAbQBfAGwAaQBtAGIAcwAsACAAMQAsACAAbgB1AG0AXwBsAGkAbQBiAHMALAAgAC0AMQApACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AdQBtAF8AbABpAG0AYgBzACAAPQAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHYAXwBsAGkAbQBiAHMAIAAmACAAXAAiAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATgBDAEEAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAcgBlAHYAXwBsAGkAbQBiAHMALAAgADEAKQAgACYAIABcACIAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEUAWABUACgARABSAE8AUAAoAHIAZQB2AF8AbABpAG0AYgBzACwAIAAxACkALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAGsAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAUgBlAHMAbwBsAHYAZQBzACAAYwBhAHIAcgBpAGUAcwAgAHIAaQBnAGgAdAAtAHQAbwAtAGwAZQBmAHQAIABhAGMAcgBvAHMAcwAgAGEAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkAIABvAGYAIABiAGEAcwBlAC0AMQAwAF4AawAgAGwAaQBtAGIAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwAgAFQAaABlACAAYQByAHIAYQB5ACAAbwBmACAAbgB1AG0AZQByAGkAYwAgAGwAaQBtAGIAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGwAaQBtAGIAIABzAGkAegBlAC4AXABuACAAKgAvAFwAbgBDAGEAcgByAHkAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwApACwAXABuACAAIAAgACAAIAAgACAAIABiAGEAcwBlACwAIAAxADAAXgBrACwAXABuACAAIAAgACAAIAAgACAAIABzAGMAYQBuAG4AZQBkACwAIABTAEMAQQBOACgAMAAsACAAbABpAG0AYgBzACwAIABMAEEATQBCAEQAQQAoAGEAYwBjACwAIAB2AGEAbAAsACAAdgBhAGwAIAArACAASQBOAFQAKABhAGMAYwAgAC8AIABiAGEAcwBlACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAByAGUAbQBhAGkAbgBkAGUAcgBzACwAIABNAE8ARAAoAHMAYwBhAG4AbgBlAGQALAAgAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AYwBhAHIAcgB5ACwAIABJAE4AVAAoAEkATgBEAEUAWAAoAHMAYwBhAG4AbgBlAGQALAAgAG4ALAAgADEAKQAgAC8AIABiAGEAcwBlACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABmAGkAbgBhAGwAXwBjAGEAcgByAHkAIAA+ACAAMAAsACAAVgBTAFQAQQBDAEsAKAByAGUAbQBhAGkAbgBkAGUAcgBzACwAIABmAGkAbgBhAGwAXwBjAGEAcgByAHkAKQAsACAAcgBlAG0AYQBpAG4AZABlAHIAcwApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAC0ALQAtACAAVQBuAHMAaQBnAG4AZQBkACAASwBlAHIAbgBlAGwAcwAgAC0ALQAtACAAXABcAFwAXABcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAVQBuAHMAaQBnAG4AZQBkACAAYwBvAG0AcABhAHIAaQBzAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAMQAgACgAYQAgAD4AIABiACkALAAgAC0AMQAgACgAYQAgADwAIABiACkALAAgAG8AcgAgADAAIAAoAGEAIAA9ACAAYgApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAIABUAGgAZQAgAHMAZQBjAG8AbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoALwBcAG4AVQBDAG8AbQBwAGEAcgBlACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAeABfAHIAbwB3AHMALAAgAE0AQQBYACgAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEAKQAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAZABfAGEALAAgAEUAWABQAEEATgBEACgAbABpAG0AYgBzAF8AYQAsACAAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAYQBkAF8AYgAsACAARQBYAFAAQQBOAEQAKABsAGkAbQBiAHMAXwBiACwAIABtAGEAeABfAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABkAGkAZgBmACwAIABwAGEAZABfAGEAIAAtACAAcABhAGQAXwBiACwAXABuACAAIAAgACAAIAAgACAAIABtAHMAZABfAGkAZAB4ACwAIABYAE0AQQBUAEMASAAoAFQAUgBVAEUALAAgAGQAaQBmAGYAIAA8AD4AIAAwACwAIAAwACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATgBBACgAbQBzAGQAXwBpAGQAeAApACwAIAAwACwAIABTAEkARwBOACgASQBOAEQARQBYACgAZABpAGYAZgAsACAAbQBzAGQAXwBpAGQAeAAsACAAMQApACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAGEAZABkAGkAdABpAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFUAQQBkAGQAIAA9ACAATABBAE0AQgBEAEEAKABhACwAIABiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AcgBvAHcAcwAsACAATQBBAFgAKABSAE8AVwBTACgAYQApACwAIABSAE8AVwBTACgAYgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAYQBkAF8AYQAsACAARQBYAFAAQQBOAEQAKABhACwAIABtAGEAeABfAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBiACwAIABFAFgAUABBAE4ARAAoAGIALAAgAG0AYQB4AF8AcgBvAHcAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHAAYQBkAF8AYQAgACsAIABwAGEAZABfAGIALAAgAGsAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAHMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABBAHMAcwB1AG0AZQBzACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAgAEEAIAA+AD0AIABCAC4AIABSAGUAcwBvAGwAdgBlAHMAIABiAG8AcgByAG8AdwBzACAAdABvAHAALQB0AG8ALQBiAG8AdAB0AG8AbQAgAGEAbgBkACAAdAByAGkAbQBzACAAdAByAGEAaQBsAGkAbgBnACAAegBlAHIAbwBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAbQBpAG4AdQBlAG4AZAAgAGwAaQBtAGIAIABhAHIAcgBhAHkAIAAoAG0AdQBzAHQAIABiAGUAIAA+AD0AIABsAGkAbQBiAHMAXwBiACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABzAHUAYgB0AHIAYQBoAGUAbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AVQBTAHUAYgAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwByAG8AdwBzACwAIABNAEEAWAAoAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBhACwAIABFAFgAUABBAE4ARAAoAGwAaQBtAGIAcwBfAGEALAAgAG0AYQB4AF8AcgBvAHcAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAZABfAGIALAAgAEUAWABQAEEATgBEACgAbABpAG0AYgBzAF8AYgAsACAAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAZABpAGYAZgAsACAAcABhAGQAXwBhACAALQAgAHAAYQBkAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBlAHMAbwBsAHYAZQBkACwAIABDAGEAcgByAHkAKABkAGkAZgBmACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAbQBzAGQAXwBpAGQAeAAsACAAWABNAEEAVABDAEgAKABUAFIAVQBFACwAIAByAGUAcwBvAGwAdgBlAGQAIAA8AD4AIAAwACwAIAAwACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATgBBACgAbQBzAGQAXwBpAGQAeAApACwAIAB7ADAAfQAsACAAVABBAEsARQAoAHIAZQBzAG8AbAB2AGUAZAAsACAAbQBzAGQAXwBpAGQAeAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABWAGUAYwB0AG8AcgBpAHoAZQBkACAAbQBhAHQAcgBpAHgAIABzAHUAbQAgAG8AZgAgAHUAbgBzAGkAZwBuAGUAZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHUAYgBpAGcAXwBpAG4AdAAgAEgAbwByAGkAegBvAG4AdABhAGwAIABhAHIAcgBhAHkAIAAoADEAeABOACkAIABvAGYAIABuAG8AcgBtAGEAbABpAHoAZQBkACAAbQBhAGcAbgBpAHQAdQBkAGUAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAdQBuAGkAZgBpAGUAZAAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AVQBNAGEAdAByAGkAeABTAHUAbQAgAD0AIABMAEEATQBCAEQAQQAoAHUAYgBpAGcAXwBpAG4AdABzACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAGcAcgBpAGQALAAgAFMAcABsAGkAdAAoAHUAYgBpAGcAXwBpAG4AdABzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAYQB3AF8AbABpAG0AYgBzACwAIABCAFkAUgBPAFcAKABnAHIAaQBkACwAIABTAFUATQApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHIAYQB3AF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABSAG8AdQB0AGUAcwAgAGEAZABkAGkAdABpAG8AbgAvAHMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAGIAYQBzAGUAZAAgAG8AbgAgAHMAaQBnAG4AcwAgAGEAbgBkACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAuAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAYQAgAHQAdQBwAGwAZQAgAGEAcgByAGEAeQA6ACAAVgBTAFQAQQBDAEsAKABsAGkAbQBiAHMALAAgAGYAaQBuAGEAbABfAHMAaQBnAG4AKQAgAHcAaABlAHIAZQAgAHQAaABlACAAZgBpAG4AYQBsACAAcgBvAHcAIABpAHMAIAB0AGgAZQAgAHMAYwBhAGwAYQByACAAcwBpAGcAbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAcwBlAGMAbwBuAGQAIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHMAaQBnAG4AXwBhACAAVABoAGUAIABzAGkAZwBuACAAbwBmACAAdABoAGUAIABmAGkAcgBzAHQAIABhAHIAcgBhAHkAIAAoADEALAAgAC0AMQAsACAAMAApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAcwBpAGcAbgBfAGIAIABUAGgAZQAgAHMAaQBnAG4AIABvAGYAIAB0AGgAZQAgAHMAZQBjAG8AbgBkACAAYQByAHIAYQB5ACAAKAAxACwAIAAtADEALAAgADAAKQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AQQBkAGQAUwB1AGIAUgBvAHUAdABlAHIAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABzAGkAZwBuAF8AYQAsACAAcwBpAGcAbgBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AcwBhAG0AZQBfAHMAaQBnAG4ALAAgAHMAaQBnAG4AXwBhACAAPQAgAHMAaQBnAG4AXwBiACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGkAcwBfAHMAYQBtAGUAXwBzAGkAZwBuACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAZABkAGkAdABpAG8AbgA6ACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAgAGMAbwBtAGIAaQBuAGUALAAgAHMAaQBnAG4AIAByAGUAbQBhAGkAbgBzACAAdABoAGUAIABzAGEAbQBlAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVQBBAGQAZAAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsACAAcwBpAGcAbgBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwB1AGIAdAByAGEAYwB0AGkAbwBuADoAIABlAHYAYQBsAHUAYQB0AGUAIABtAGEAZwBuAGkAdAB1AGQAZQBzACAAdABvACAAcwBhAHQAaQBzAGYAeQAgAFUAUwB1AGIAIAAoAEEAIAA+AD0AIABCACkAIABwAHIAZQBjAG8AbgBkAGkAdABpAG8AbgAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcAAsACAAVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFQAbwB0AGEAbAAgAGMAYQBuAGMAZQBsAGwAYQB0AGkAbwBuADoAIAByAGUAdAB1AHIAbgAgAHsAMAB9ACAAbABpAG0AYgAgAGEAbgBkACAAMAAgAHMAaQBnAG4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAMAA7ADAAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAGEAZwBfAGMAbwBtAHAAIAA+ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABBACAAaQBzACAAbABhAHIAZwBlAHIAOgAgAHMAaQBnAG4AIABiAGUAbABvAG4AZwBzACAAdABvACAAQQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFUAUwB1AGIAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALAAgAHMAaQBnAG4AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEIAIABpAHMAIABsAGEAcgBnAGUAcgA6ACAAcgBvAHUAdABlACAAQgAgAGYAaQByAHMAdAAsACAAcwBpAGcAbgAgAGIAZQBsAG8AbgBnAHMAIAB0AG8AIABCAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVQBTAHUAYgAoAGwAaQBtAGIAcwBfAGIALAAgAGwAaQBtAGIAcwBfAGEALAAgAGsAKQAsACAAcwBpAGcAbgBfAGIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AcwBpAGcAbgBlAGQAIABtAHUAbAB0AGkAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIAB0AHcAbwAgAEwAaQB0AHQAbABlAC0ARQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5AHMALgBcAG4AIAAqACAAVQB0AGkAbABpAHoAZQBzACAAYQAgADEARAAgAEQAaQBzAGMAcgBlAHQAZQAgAEMAbwBuAHYAbwBsAHUAdABpAG8AbgAgACgAQwBhAHUAYwBoAHkAIABQAHIAbwBkAHUAYwB0ACkAIABhAHIAcgBhAHkALQBzAGwAaQBjAGkAbgBnACAAcwB0AHIAYQB0AGUAZwB5AC4AXABuACAAKgAgAFoAZQByAG8AIABkAHkAbgBhAG0AaQBjACAAbQBlAG0AbwByAHkAIAByAGUAYQBsAGwAbwBjAGEAdABpAG8AbgAuACAAJABPACgATgArAE0AKQAkACAAbQBlAG0AbwByAHkAIABmAG8AbwB0AHAAcgBpAG4AdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAG0AdQBsAHQAaQBwAGwAaQBjAGEAbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAIABUAGgAZQAgAG0AdQBsAHQAaQBwAGwAaQBlAHIAIABsAGkAbQBiACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBVAE0AdQBsACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwByAG8AdwBzACwAIABsAGUAbgBfAGEAIAArACAAbABlAG4AXwBiACAALQAgADEALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAATABvAG8AcAAgAHAAdQByAGUAbAB5ACAAbwB2AGUAcgAgAHQAaABlACAAbABlAG4AZwB0AGgAIABvAGYAIAB0AGgAZQAgAGYAaQBuAGEAbAAgAG8AdQB0AHAAdQB0ACAAYQByAHIAYQB5AFwAbgAgACAAIAAgACAAIAAgACAAcgBhAHcAXwBsAGkAbQBiAHMALAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIABMAEEATQBCAEQAQQAoAHIALAAgAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAbABjAHUAbABhAHQAZQAgAHQAaABlACAAdgBhAGwAaQBkACAAbwB2AGUAcgBsAGEAcABwAGkAbgBnACAAdwBpAG4AZABvAHcAIABvAGYAIABpAG4AZABpAGMAZQBzACAAZgBvAHIAIAB0AGgAaQBzACAAbQBhAGcAbgBpAHQAdQBkAGUAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AF8AaQAsACAATQBBAFgAKAAxACwAIAByACAALQAgAGwAZQBuAF8AYgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAG4AZABfAGkALAAgAE0ASQBOACgAcgAsACAAbABlAG4AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AdQBuAHQALAAgAGUAbgBkAF8AaQAgAC0AIABzAHQAYQByAHQAXwBpACAAKwAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGUAcQB1AGUAbgBjAGUAIABpACAAYwBvAHUAbgB0AHMAIABVAFAALgAgAFMAZQBxAHUAZQBuAGMAZQAgAGoAIABjAG8AdQBuAHQAcwAgAEQATwBXAE4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGkALAAgAFMARQBRAFUARQBOAEMARQAoAGMAbwB1AG4AdAAsACAAMQAsACAAcwB0AGEAcgB0AF8AaQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBlAHEAXwBqACwAIABTAEUAUQBVAEUATgBDAEUAKABjAG8AdQBuAHQALAAgADEALAAgAHIAIAAtACAAcwB0AGEAcgB0AF8AaQAgACsAIAAxACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAbABpAGMAZQAgAHQAaABlACAAZQB4AGEAYwB0ACAAaQBuAHQAZQByAHMAZQBjAHQAaQBuAGcAIABsAGkAbQBiAHMALAAgAG0AdQBsAHQAaQBwAGwAeQAsACAAYQBuAGQAIABzAHUAbQAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUATQAoAEkATgBEAEUAWAAoAGwAaQBtAGIAcwBfAGEALAAgAHMAZQBxAF8AaQAsACAAMQApACAAKgAgAEkATgBEAEUAWAAoAGwAaQBtAGIAcwBfAGIALAAgAHMAZQBxAF8AagAsACAAMQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHMAbwBsAHYAZQAgAGEAbABsACAAYwBhAHIAcgBpAGUAcwAgAGIAbwB0AHQAbwBtAC0AdABvAC0AdABvAHAAIABlAHgAYQBjAHQAbAB5ACAAbwBuAGMAZQBcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHIAYQB3AF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABCAGkAbgBhAHIAeQAgAHMAZQBhAHIAYwBoACAAdABvACAAZgBpAG4AZAAgAHQAaABlACAAaABpAGcAaABlAHMAdAAgAHMAYwBhAGwAYQByACAAcQB1AG8AdABpAGUAbgB0ACAAbABpAG0AYgAgAHEAIAAoADAAIAA8AD0AIABxACAAPAAgADEAMABeAGsAKQBcAG4AoAAqACAAcwB1AGMAaAAgAHQAaABhAHQAIABCACAAKgAgAHEAIAA8AD0AIABhAGMAYwAuACAARQBsAGkAbQBpAG4AYQB0AGUAcwAgAHQAaABlACAAbgBlAGUAZAAgAGYAbwByACAASwBuAHUAdABoACAARAAgAGYAbABvAGEAdAAtAGUAcwB0AGkAbQBhAHQAaQBvAG4ALgBcAG4AoAAqACAAQABwAGEAcgBhAG0AIABhAGMAYwAgAFQAaABlACAAYwB1AHIAcgBlAG4AdAAgAHIAZQBtAGEAaQBuAGQAZQByACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAuAFwAbgCgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgCgACoALwBcAG4ARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAgAD0AIABMAEEATQBCAEQAQQAoAGEAYwBjACwAIABiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAYQBsAGMAdQBsAGEAdABlACAAcgBlAHEAdQBpAHIAZQBkACAAYgBpAHQAcwAgAGQAeQBuAGEAbQBpAGMAYQBsAGwAeQAuACAARgBvAHIAIABtAGEAeAAgAGsAPQA3ACwAIAB0AGgAaQBzACAAZQB2AGEAbAB1AGEAdABlAHMAIAB0AG8AIAAyADQAIABiAGkAdABzAC4AXABuACAAIAAgACAAIAAgACAAIABiAGkAdABzACwAIABDAEUASQBMAEkATgBHAC4ATQBBAFQASAAoAEwATwBHACgAMQAwAF4AawAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAbwB3AGUAcgBzACwAIAAyACAAXgAgAFMARQBRAFUARQBOAEMARQAoAGIAaQB0AHMALAAgADEALAAgAGIAaQB0AHMAIAAtACAAMQAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAUgBFAEQAVQBDAEUAKAAwACwAIABwAG8AdwBlAHIAcwAsACAATABBAE0AQgBEAEEAKABjAHUAcgByAF8AcQAsACAAcABvAHcAZQByACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABlAHMAdABfAHEALAAgAGMAdQByAHIAXwBxACAAKwAgAHAAbwB3AGUAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAawBpAHAAIABpAGYAIAB0AGUAcwB0AF8AcQAgAGUAeABjAGUAZQBkAHMAIAB0AGgAZQAgAGwAaQBtAGIAIABiAGEAcwBlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHQAZQBzAHQAXwBxACAAPgA9ACAAMQAwAF4AawAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATQB1AGwAdABpAHAAbAB5ACAAQgAgAGIAeQAgAHMAYwBhAGwAYQByACAAdABlAHMAdABfAHEAIABhAG4AZAAgAHIAZQBzAG8AbAB2AGUAIABjAGEAcgByAGkAZQBzACAAbgBhAHQAaQB2AGUAbAB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGUAcwB0AF8AcAByAG8AZAAsACAAQwBhAHIAcgB5ACgAYgAgACoAIAB0AGUAcwB0AF8AcQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAFUAQwBvAG0AcABhAHIAZQAoAGEAYwBjACwAIAB0AGUAcwB0AF8AcAByAG8AZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABjAG8AbQBwACAAPgA9ACAAMAAsACAAdABlAHMAdABfAHEALAAgAGMAdQByAHIAXwBxACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABCAGEAcwBlAGMAYQBzAGUAIABEAGkAdgBpAHMAaQBvAG4AIAB2AGkAYQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABzAGgAaQBmAHQALQBhAG4AZAAtAHMAdQBiAHQAcgBhAGMAdAAuAFwAbgCgACoAIABSAGUAdAB1AHIAbgBzACAAYQAgAHAAYQBjAGsAZQBkACAAMQBEACAAYQByAHIAYQB5ADoAIABWAFMAVABBAEMASwAoAEwAZQBuAGcAdABoAF8AUgAsACAAUgBfAGwAaQBtAGIAcwAsACAAUQBfAGwAaQBtAGIAcwApAC4AXABuAKAAKgAgAEUAbABpAG0AaQBuAGEAdABlAHMAIAAyAEQAIABhAHIAcgBhAHkAIABwAGEAZABkAGkAbgBnACAAdABvACAAcwB0AHIAaQBjAHQAbAB5ACAAcAByAGUAcwBlAHIAdgBlACAAbQBlAG0AbwByAHkAIABlAGYAZgBpAGMAaQBlAG4AYwB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAgACgAYQBzAHMAdQBtAGUAZAAgAG4AbwBuAC0AegBlAHIAbwApAC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuAKAAKgAvAFwAbgBLAG4AdQB0AGgARABpAHYAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcAAsACAAVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAIAByAG8AdQB0AGkAbgBnACAAdwBpAHQAaAAgAHQAaABlACAAbgBlAHcAIABwAGEAYwBrAGUAZAAgAG0AZQBtAG8AcgB5ACAAYwBvAG4AdAByAGEAYwB0AFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbABpAG0AYgBzAF8AYQApACwAIABsAGkAbQBiAHMAXwBhACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADEALAAgADAALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEkAdABlAHIAYQB0AGUAIABvAHYAZQByACAAQQAgAGYAcgBvAG0AIABNAFMAQgAgACgAdABvAHAAKQAgAHQAbwAgAEwAUwBCACAAKABiAG8AdAB0AG8AbQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHYAZQByAHMAZQBkAF8AYQAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEALAAgAFMARQBRAFUARQBOAEMARQAoAGwAZQBuAF8AYQAsACAAMQAsACAAbABlAG4AXwBhACwAIAAtADEAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAdABhAHQAZQAgAHMAZQBwAGEAcgBhAHQAbwByADoAIABWAFMAVABBAEMASwAoAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABxAHUAbwB0AGkAZQBuAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAbgBpAHQAaQBhAGwAXwBzAHQAYQB0AGUALAAgAFYAUwBUAEEAQwBLACgAMQAsACAAMAAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsAF8AcwB0AGEAdABlACwAIAByAGUAdgBlAHIAcwBlAGQAXwBhACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAdgBhAGwALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcwB0AGEAdABlACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHEAdQBvAHQAaQBlAG4AdAAsACAARABSAE8AUAAoAHMAdABhAHQAZQAsACAAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGgAaQBmAHQAIABhAGMAYwAgAHUAcAAgAGIAeQAgADEAIABsAGkAbQBiACAAKABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuADoAIABpAG4AcwBlAHIAdAAgAGEAdAAgAGkAbgBkAGUAeAAgADEAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAHgAdABlAG4AZABlAGQAXwByAGUAbQBhAGkAbgBkAGUAcgAsACAASQBGACgAQQBOAEQAKABSAE8AVwBTACgAcgBlAG0AYQBpAG4AZABlAHIAKQAgAD0AIAAxACwAIABJAE4ARABFAFgAKAByAGUAbQBhAGkAbgBkAGUAcgAsACAAMQAsACAAMQApACAAPQAgADAAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB2AGEAbAAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAHYAYQBsACwAIAByAGUAbQBhAGkAbgBkAGUAcgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgAsACAARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAoAGUAeAB0AGUAbgBkAGUAZABfAHIAZQBtAGEAaQBuAGQAZQByACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAHIAbwBkACwAIABDAGEAcgByAHkAKABsAGkAbQBiAHMAXwBiACAAKgAgAG4AZQB4AHQAXwBxAHUAbwB0AGkAZQBuAHQAXwBsAGkAbQBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAdwBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABVAFMAdQBiACgAZQB4AHQAZQBuAGQAZQBkAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHAAcgBvAGQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGgAYQBzAF8AcQB1AG8AdABpAGUAbgB0ACwAIABPAFIAKABSAE8AVwBTACgAcQB1AG8AdABpAGUAbgB0ACkAIAA+ACAAMQAsACAASQBOAEQARQBYACgAcQB1AG8AdABpAGUAbgB0ACwAMQAsADEAKQAgAD4AIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQB1AG8AdAAsACAASQBGACgAaABhAHMAXwBxAHUAbwB0AGkAZQBuAHQALAAgAFYAUwBUAEEAQwBLACgAcQB1AG8AdABpAGUAbgB0ACwAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgApACwAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbgBlAHcAXwByAGUAbQBhAGkAbgBkAGUAcgApACwAIABuAGUAdwBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABuAGUAeAB0AF8AcQB1AG8AdAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAEkATgBEAEUAWAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAbQBhAGkAbgBkAGUAcgAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAsACAAMQAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQB2AGUAcgBzAGUAZABfAHEAdQBvAHQAaQBlAG4AdAAsACAARABSAE8AUAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAcQB1AG8AdABfAHIAYQB3ACAAdwBhAHMAIABiAHUAaQBsAHQAIABNAFMAQgAgAHQAbwAgAEwAUwBCACAAKABCAGkAZwAtAEUAbgBkAGkAYQBuACkALgAgAFIAZQB2AGUAcgBzAGUAIAB0AG8AIABpAG4AdABlAHIAbgBhAGwAIABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHEAdQBvAHQAaQBlAG4AdAAsACAAUgBPAFcAUwAoAHIAZQB2AGUAcgBzAGUAZABfAHEAdQBvAHQAaQBlAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABxAHUAbwB0AGkAZQBuAHQALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKAByAGUAdgBlAHIAcwBlAGQAXwBxAHUAbwB0AGkAZQBuAHQALAAgAFMARQBRAFUARQBOAEMARQAoAGwAZQBuAF8AcQB1AG8AdABpAGUAbgB0ACwAIAAxACwAIABsAGUAbgBfAHEAdQBvAHQAaQBlAG4AdAAsACAALQAxACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAHMAdAByAGkAYwB0AGwAeQAgAHAAYQBjAGsAZQBkACAAMQBEACAAYQByAHIAYQB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIAByAGUAbQBhAGkAbgBkAGUAcgAsACAAcQB1AG8AdABpAGUAbgB0ACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABIAHkAYgByAGkAZAAgAEQAaQB2AGkAcwBpAG8AbgAgAFIAbwB1AHQAZQByAC4AXABuAKAAKgAgAEQAaQByAGUAYwB0AHMAIABkAGkAdgBpAHMAaQBvAG4AIAB0AG8AIAB0AGgAZQAgAG8AcAB0AGkAbQBhAGwAIABrAGUAcgBuAGUAbAAgAGIAYQBzAGUAZAAgAG8AbgAgAEQAaQB2AGkAZABlAG4AZAAgAGwAZQBuAGcAdABoAC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAuAFwAbgCgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgCgACoALwBcAG4ARABpAHYAUgBvAHUAdABlAHIAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEQAaQBnAGkAdAAgAGMAbwB1AG4AdABzACAAYQByAGUAIABhAHAAcAByAG8AeABpAG0AYQB0AGUALAAgAGIAdQB0ACAAcwB1AGYAZgBpAGMAaQBlAG4AdABcAG4AIAAgACAAIAAgACAAIAAgAGQAaQBnAGkAdABzAF8AYQAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEAKQAgACoAIABrACwAXABuACAAIAAgACAAIAAgACAAIABkAGkAZwBpAHQAcwBfAGIALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkAIAAqACAAawAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABNAGEAYwBoAGkAbgBlAC0AbABlAGEAcgBuAGUAZAAgAGMAbwBlAGYAZgBpAGMAaQBlAG4AdABzACAAZgByAG8AbQAgAEwAbwBnAGkAcwB0AGkAYwAgAFIAZQBnAHIAZQBzAHMAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIABtACwAIAAwAC4AMQAwADcAOAAyADEAMQA5ADQAMgA3ADEAMgA5ADcALABcAG4AIAAgACAAIAAgACAAIAAgAGMALAAgAC0AMgAyADEALgA5ADAAMgAxADgAOQA0ADYAMgAwADYAOAAsAFwAbgAgACAAIAAgACAAIAAgACAAdABoAHIAZQBzAGgAbwBsAGQALAAgACgAbQAgACoAIABkAGkAZwBpAHQAcwBfAGEAKQAgACsAIABjACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGQAaQBnAGkAdABzAF8AYgAgADwAPQAgAHQAaAByAGUAcwBoAG8AbABkACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEsAbgB1AHQAaABEAGkAdgAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2ACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEcAZQBuAGUAcgBhAHQAZQBzACAAdABoAGUAIABlAHgAYQBjAHQAIAByAGUAYwBpAHAAcgBvAGMAYQBsACAAcwBlAGUAZAAgAGYAbwByACAATgBlAHcAdABvAG4ALQBSAGEAcABoAHMAbwBuACAARABpAHYAaQBzAGkAbwBuACAAdQBzAGkAbgBnACAASwBuAHUAdABoACAAQgBhAHMAZQBjAGEAcwBlAC4AXABuACAAKgAgAEUAeAB0AHIAYQBjAHQAcwAgAHUAcAAgAHQAbwAgAHQAaABlACAAdABvAHAAIAAzACAAbABpAG0AYgBzACAAbwBmACAAQgAgAGEAbgBkACAAYwBhAGwAYwB1AGwAYQB0AGUAcwAgAGYAbABvAG8AcgAoAEIAZQB0AGEAXgAoADIAKgBsAGUAbgApACAALwAgAEIAXwB0AG8AcAApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4AUwBlAGUAZAAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwBiACwAIABSAE8AVwBTACgAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAZQBkAF8AbABlAG4ALAAgAE0ASQBOACgAMwAsACAAbABlAG4AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAHQAbwBwACAAJwBzAGUAZQBkAF8AbABlAG4AJwAgAGwAaQBtAGIAcwAgACgATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgA6ACAAdABhAGsAZQAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAbwB0AHQAbwBtACkAXABuACAAIAAgACAAIAAgACAAIABiAF8AdABvAHAALAAgAFQAQQBLAEUAKABsAGkAbQBiAHMAXwBiACwAIAAtAHMAZQBlAGQAXwBsAGUAbgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAbwBuAHMAdAByAHUAYwB0ACAAQgBlAHQAYQBeACgAMgAgACoAIABzAGUAZQBkAF8AbABlAG4AKQAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAGUALgBnAC4ALAAgAGkAZgAgAHMAZQBlAGQAXwBsAGUAbgAgAD0AIAAxACwAIAB0AGgAZQBuACAAMQAgAGYAbwBsAGwAbwB3AGUAZAAgAGIAeQAgAHQAdwBvACAAegBlAHIAbwAgAGwAaQBtAGIAcwA6ACAAVgBTAFQAQQBDAEsAKAAwACwAIAAwACwAIAAxACkAXABuACAAIAAgACAAIAAgACAAIABiAGUAdABhAF8AMgBtACwAIABWAFMAVABBAEMASwAoAEUAWABQAEEATgBEACgAMAAsACAAMgAgACoAIABzAGUAZQBkAF8AbABlAG4ALAAgACwAIAAwACkALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABLAG4AdQB0AGgAIABEAGkAdgBpAHMAaQBvAG4AIAB5AGkAZQBsAGQAcwAgAGUAeABhAGMAdAAgAGkAbgBpAHQAaQBhAGwAIAByAGUAYwBpAHAAcgBvAGMAYQBsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGMAawBlAGQALAAgAEsAbgB1AHQAaABEAGkAdgAoAGIAZQB0AGEAXwAyAG0ALAAgAGIAXwB0AG8AcAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABRAHUAbwB0AGkAZQBuAHQAIABhAHIAcgBhAHkAIABmAHIAbwBtACAAdABoAGUAIABwAGEAYwBrAGUAZAAgAFYAUwBUAEEAQwBLAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwByACwAIABJAE4ARABFAFgAKABwAGEAYwBrAGUAZAAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAcABhAGMAawBlAGQALAAgAGwAZQBuAF8AcgAgACsAIAAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABDAG8AbQBwAHUAdABlAHMAIAB0AGgAZQAgAFIAZQBjAGkAcAByAG8AYwBhAGwAIABwAHIAbwBnAHIAZQBzAHMAaQB2AGUAbAB5ACAAcwBjAGEAbABpAG4AZwAgAHUAcAAgAHQAbwAgAHQAaABlACAARABpAHYAaQBkAGUAbgBkACcAcwAgAHAAcgBlAGMAaQBzAGkAbwBuAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIAB0AGEAcgBnAGUAdABfAGwAZQBuACAAVABoAGUAIABsAGkAbQBiAC0AbABlAG4AZwB0AGgAIABvAGYAIABEAGkAdgBpAGQAZQBuAGQAIABBAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAFIAZQBjAGkAcAByAG8AYwBhAGwAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBiACwAIAB0AGEAcgBnAGUAdABfAGwAZQBuACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBlAGUAZABfAGwAZQBuACwAIABNAEkATgAoADMALAAgAGwAZQBuAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAByAF8AcwBlAGUAZABfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBTAGUAZQBkACgAbABpAG0AYgBzAF8AYgAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKABzAGUAZQBkAF8AbABlAG4ALAAgAHIAXwBzAGUAZQBkAF8AbABpAG0AYgBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQBxAF8AaQB0AGUAcgBzACwAIABNAEEAWAAoADAALAAgAEMARQBJAEwASQBOAEcALgBNAEEAVABIACgATABOACgAdABhAHIAZwBlAHQAXwBsAGUAbgAgAC8AIABzAGUAZQBkAF8AbABlAG4AKQAgAC8AIABMAE4AKAAyACkAKQApACAAKwAgADEALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKAByAGUAcQBfAGkAdABlAHIAcwAgAD0AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAXwBzAGUAZQBkAF8AbABpAG0AYgBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQB0AGUAcgBhAHQAaQBvAG4AcwAsACAAUwBFAFEAVQBFAE4AQwBFACgAcgBlAHEAXwBpAHQAZQByAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsAF8AcwB0AGEAdABlACwAIABpAHQAZQByAGEAdABpAG8AbgBzACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAaQB0AGUAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwB1AHIAcgBfAGwAZQBuACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcgAsACAARABSAE8AUAAoAHMAdABhAHQAZQAsACAAMQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AbABlAG4ALAAgAE0ASQBOACgAYwB1AHIAcgBfAGwAZQBuACAAKgAgADIALAAgAHQAYQByAGcAZQB0AF8AbABlAG4AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARAB5AG4AYQBtAGkAYwAgAFMAYwBhAGwAaQBuAGcAIABTAGgAaQBmAHQAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAASQBmACAAQgAgAGgAYQBzACAAcABsAGEAdABlAGEAdQBlAGQALAAgAFIAIABtAHUAcwB0ACAAcwBjAGEAbABlACAAYgB5ACAAMgAqACgAbgAtAG0AKQAuACAASQBmACAAQgAgAGkAcwAgAGcAcgBvAHcAaQBuAGcALAAgAFIAIABzAGMAYQBsAGUAcwAgAGIAeQAgACgAbgAtAG0AKQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAdABpAHYAZQBfAGMAdQByAHIALAAgAE0ASQBOACgAYwB1AHIAcgBfAGwAZQBuACwAIABsAGUAbgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAdABpAHYAZQBfAG4AZQB4AHQALAAgAE0ASQBOACgAbgBlAHgAdABfAGwAZQBuACwAIABsAGUAbgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGgAaQBmAHQAXwBsAGkAbQBiAHMALAAgADIAIAAqACAAKABuAGUAeAB0AF8AbABlAG4AIAAtACAAYwB1AHIAcgBfAGwAZQBuACkAIAAtACAAKABhAGMAdABpAHYAZQBfAG4AZQB4AHQAIAAtACAAYQBjAHQAaQB2AGUAXwBjAHUAcgByACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAXwBwAHIAaQBtAGUALAAgAEkARgAoAHMAaABpAGYAdABfAGwAaQBtAGIAcwAgAD4AIAAwACwAIABWAFMAVABBAEMASwAoAEUAWABQAEEATgBEACgAMAAsACAAcwBoAGkAZgB0AF8AbABpAG0AYgBzACwAIAAsACAAMAApACwAIABjAHUAcgByAF8AcgApACwAIABjAHUAcgByAF8AcgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABiAF8AYQBjAHQAaQB2AGUALAAgAFQAQQBLAEUAKABsAGkAbQBiAHMAXwBiACwAIAAtAGEAYwB0AGkAdgBlAF8AbgBlAHgAdAApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABQACAAaQBzACAAbgBhAHQAaQB2AGUAbAB5ACAAYQBsAGkAZwBuAGUAZAAgAHQAbwAgADIAKgBuAGUAeAB0AF8AbABlAG4AIABiAGUAYwBhAHUAcwBlACAAbwBmACAAdABoAGUAIABjAG8AcgByAGUAYwB0AGUAZAAgAHMAaABpAGYAdABfAGwAaQBtAGIAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGIAXwBhAGMAdABpAHYAZQAsACAAcgBfAHAAcgBpAG0AZQAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AHcAbwBfAGIAZQB0AGEALAAgAFYAUwBUAEEAQwBLACgARQBYAFAAQQBOAEQAKAAwACwAIAAyACAAKgAgAG4AZQB4AHQAXwBsAGUAbgAsACAALAAgADAAKQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGUAcgByACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAdQBiACgAdAB3AG8AXwBiAGUAdABhACwAIABwACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwByAF8AdQBuAHMAYwBhAGwAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAcgBfAHAAcgBpAG0AZQAsACAAZQByAHIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcgAsACAASQBGACgAUgBPAFcAUwAoAG4AZQB4AHQAXwByAF8AdQBuAHMAYwBhAGwAZQBkACkAIAA8AD0AIAAyACAAKgAgAG4AZQB4AHQAXwBsAGUAbgAsACAAewAwAH0ALAAgAEQAUgBPAFAAKABuAGUAeAB0AF8AcgBfAHUAbgBzAGMAYQBsAGUAZAAsACAAMgAgACoAIABuAGUAeAB0AF8AbABlAG4AKQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAG4AZQB4AHQAXwBsAGUAbgAsACAAbgBlAHgAdABfAHIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAMQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEgAZQBhAHYAeQB3AGUAaQBnAGgAdAAgAE4AZQB3AHQAbwBuAC0AUgBhAHAAaABzAG8AbgAgAEQAaQB2AGkAcwBpAG8AbgAuAFwAbgAgACoAIABJAG0AcABsAGUAbQBlAG4AdABzACAAcAByAG8AZwByAGUAcwBzAGkAdgBlACAAcwBjAGEAbABpAG4AZwAgAGIAbwB1AG4AZABlAGQAIAB0AG8AIABNAEEAWAAoAGwAZQBuAF8AYQAsACAAbABlAG4AXwBiACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBhACAAVABoAGUAIABkAGkAdgBpAGQAZQBuAGQAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2ACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAHIAZwBlAHQAXwBsAGUAbgAsACAATQBBAFgAKABsAGUAbgBfAGEALAAgAGwAZQBuAF8AYgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAMQAuACAAQwBhAGwAYwB1AGwAYQB0AGUAIAByAGUAYwBpAHAAcgBvAGMAYQBsACAAUgAgAHMAYwBhAGwAZQBkACAAZAB5AG4AYQBtAGkAYwBhAGwAbAB5ACAAdABvACAAMgAgACoAIAB0AGEAcgBnAGUAdABfAGwAZQBuAFwAbgAgACAAIAAgACAAIAAgACAAcgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBSAGUAYwBpAHAAcgBvAGMAYQBsACgAbABpAG0AYgBzAF8AYgAsACAAdABhAHIAZwBlAHQAXwBsAGUAbgAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAMgAuACAAQQBwAHAAcgBvAHgAaQBtAGEAdABlACAAUQB1AG8AdABpAGUAbgB0ADoAIABRAF8AYQBwAHAAcgBvAHgAIAA9ACAAQQAgACoAIABSACAALwAgAEIAZQB0AGEAXgAoADIAIAAqACAAdABhAHIAZwBlAHQAXwBsAGUAbgApAFwAbgAgACAAIAAgACAAIAAgACAAZAByAG8AcABfAGwAaQBtAGIAcwAsACAAMgAgACoAIAB0AGEAcgBnAGUAdABfAGwAZQBuACwAXABuACAAIAAgACAAIAAgACAAIABxAF8AdQBuAHMAYwBhAGwAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAbABpAG0AYgBzAF8AYQAsACAAcgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABxAF8AYQBwAHAAcgBvAHgALAAgAEkARgAoAFIATwBXAFMAKABxAF8AdQBuAHMAYwBhAGwAZQBkACkAIAA8AD0AIABkAHIAbwBwAF8AbABpAG0AYgBzACwAIAB7ADAAfQAsACAARABSAE8AUAAoAHEAXwB1AG4AcwBjAGEAbABlAGQALAAgAGQAcgBvAHAAXwBsAGkAbQBiAHMAKQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIAB0AGgAZQAgAG0AYQBzAHMAaQB2AGUAIABiAGEAcwBlAGwAaQBuAGUAIABwAHIAbwBkAHUAYwB0ACAAZQB4AGEAYwB0AGwAeQAgAE8ATgBDAEUAXABuACAAIAAgACAAIAAgACAAIABwAF8AYgBhAHMAZQBsAGkAbgBlACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAbABpAG0AYgBzAF8AYgAsACAAcQBfAGEAcABwAHIAbwB4ACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAAzAC4AIABCAG8AdQBuAGQAZQBkACAARQByAHIAbwByACAAQwBvAHIAcgBlAGMAdABpAG8AbgAgAFMAdwBlAGUAcAAgACgATwBwAHQAaQBtAGkAegBlAGQAIABPACgATgApACAAUwB0AGUAcABwAGkAbgBnACkAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABTAHQAYQB0AGUAIABwAGEAYwBrAGkAbgBnADoAIABWAFMAVABBAEMASwAoAEwAZQBuAGcAdABoAF8AUQAsACAAUQBfAGwAaQBtAGIAcwAsACAAUABfAGwAaQBtAGIAcwApAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAcQBfAGEAcABwAHIAbwB4ACkALAAgAHEAXwBhAHAAcAByAG8AeAAsACAAcABfAGIAYQBzAGUAbABpAG4AZQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUwB3AGUAZQBwACAARABvAHcAbgA6ACAASQBmACAAUAAgAD4AIABBACwAIABRACAAaQBzACAAdABvAG8AIABiAGkAZwAuACAAUwB0AGUAcAAgAFEAIABkAG8AdwBuACAAYgB5ACAAMQAsACAAYQBuAGQAIABQACAAZABvAHcAbgAgAGIAeQAgAEIALgBcAG4AIAAgACAAIAAgACAAIAAgAHMAdwBlAGUAcABfAGQAbwB3AG4ALAAgAFIARQBEAFUAQwBFACgAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAewAxADsAIAAyAH0ALAAgAEwAQQBNAEIARABBACgAcwB0AGEAdABlACwAIABpACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwBxACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwBxACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcwB0AGEAdABlACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHEALAAgADEALAAgADIAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwB1AHIAcgBfAHAALAAgAEQAUgBPAFAAKABzAHQAYQB0AGUALAAgAGwAZQBuAF8AcQAgACsAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBDAG8AbQBwAGEAcgBlACgAYwB1AHIAcgBfAHAALAAgAGwAaQBtAGIAcwBfAGEAKQAgAD4AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBTAHUAYgAoAGMAdQByAHIAXwBxACwAIAB7ADEAfQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwBwACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAdQBiACgAYwB1AHIAcgBfAHAALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFIATwBXAFMAKABuAGUAeAB0AF8AcQApACwAIABuAGUAeAB0AF8AcQAsACAAbgBlAHgAdABfAHAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAdABhAHQAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUwB3AGUAZQBwACAAVQBwADoAIABJAGYAIABQACAAKwAgAEIAIAA8AD0AIABBACwAIABRACAAaQBzACAAdABvAG8AIABzAG0AYQBsAGwALgAgAFMAdABlAHAAIABRACAAdQBwACAAYgB5ACAAMQAsACAAYQBuAGQAIABQACAAdQBwACAAYgB5ACAAQgAuAFwAbgAgACAAIAAgACAAIAAgACAAcwB3AGUAZQBwAF8AdQBwACwAIABSAEUARABVAEMARQAoAHMAdwBlAGUAcABfAGQAbwB3AG4ALAAgAHsAMQA7ACAAMgB9ACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAaQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcQAsACAASQBOAEQARQBYACgAcwB0AGEAdABlACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcQAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwBxACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwBwACwAIABEAFIATwBQACgAcwB0AGEAdABlACwAIABsAGUAbgBfAHEAIAArACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBlAHgAdABfAHAAXwB0AGUAcwB0ACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEEAZABkACgAYwB1AHIAcgBfAHAALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEMAbwBtAHAAYQByAGUAKABuAGUAeAB0AF8AcABfAHQAZQBzAHQALAAgAGwAaQBtAGIAcwBfAGEAKQAgADwAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwBxACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEEAZABkACgAYwB1AHIAcgBfAHEALAAgAHsAMQB9ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbgBlAHgAdABfAHEAKQAsACAAbgBlAHgAdABfAHEALAAgAG4AZQB4AHQAXwBwAF8AdABlAHMAdAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAdABlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAARgBpAG4AYQBsACAAUQAgAGEAbgBkACAAUABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAZQBuAF8AcQAsACAASQBOAEQARQBYACgAcwB3AGUAZQBwAF8AdQBwACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHEALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKABzAHcAZQBlAHAAXwB1AHAALAAgAFMARQBRAFUARQBOAEMARQAoAGYAaQBuAGEAbABfAGwAZQBuAF8AcQAsACAAMQAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHAALAAgAEQAUgBPAFAAKABzAHcAZQBlAHAAXwB1AHAALAAgAGYAaQBuAGEAbABfAGwAZQBuAF8AcQAgACsAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAA0AC4AIABFAHgAdAByAGEAYwB0ACAAVAByAHUAZQAgAFIAZQBtAGEAaQBuAGQAZQByACAAUwBhAGYAZQBsAHkAIAAoAEEAIAAtACAARgBpAG4AYQBsAF8AUAApAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBTAHUAYgAoAGwAaQBtAGIAcwBfAGEALAAgAGYAaQBuAGEAbABfAHAALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABmAGkAbgBhAGwAXwByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAEIAYQBzAGUALQAxADAAIABMAGUAZgB0AC0AdABvAC0AUgBpAGcAaAB0ACAARQB4AHAAbwBuAGUAbgB0AGkAYQB0AGkAbwBuAC4AXABuACAAKgAgAEUAdgBhAGwAdQBhAHQAZQBzACAAdABoAGUAIABlAHgAcABvAG4AZQBuAHQAIABpAHQAZQByAGEAdABpAHYAZQBsAHkAIAB1AHMAaQBuAGcAIABhACAAcAByAGUALQBjAG8AbQBwAHUAdABlAGQAIAAxAC0AOQAgAGMAYQBjAGgAZQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAYQBzAGUAIABUAGgAZQAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5ACAAbwBmACAAdABoAGUAIABiAGEAcwBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAZQB4AHAAXwBzAHQAcgBpAG4AZwAgAFQAaABlACAAZQB4AGEAYwB0ACAAdABlAHgAdAAgAHMAdAByAGkAbgBnACAAbwBmACAAdABoAGUAIABlAHgAcABvAG4AZQBuAHQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFUAUABvAHcAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBiAGEAcwBlACwAIABlAHgAcABfAHMAdAByAGkAbgBnACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFAAcgBlAC0AYwBvAG0AcAB1AHQAZQAgAHAAbwB3AGUAcgBzACAAMQAgAHQAaAByAG8AdQBnAGgAIAA5AC4AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQALAAgAGwAaQBtAGIAcwBfAGIAYQBzAGUALABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQBjAG8AbgBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAZgBpAHIAcwB0ACwAIABmAGkAcgBzAHQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABoAGkAcgBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAcwBlAGMAbwBuAGQALAAgAGYAaQByAHMAdAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABmAG8AdQByAHQAaAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAHMAZQBjAG8AbgBkACwAIABzAGUAYwBvAG4AZAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAZgB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABmAG8AdQByAHQAaAAsACAAZgBpAHIAcwB0ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQB4AHQAaAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAHQAaABpAHIAZAAsACAAdABoAGkAcgBkACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQB2AGUAbgB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABzAGkAeAB0AGgALAAgAGYAaQByAHMAdAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABlAGkAZwB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABmAG8AdQByAHQAaAAsACAAZgBvAHUAcgB0AGgALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBpAG4AdABoACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAZQBpAGcAdABoACwAIABmAGkAcgBzAHQALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGUAeABwAF8AZABpAGcAaQB0AHMALAAgAC0ALQBNAEkARAAoAGUAeABwAF8AcwB0AHIAaQBuAGcALAAgAFMARQBRAFUARQBOAEMARQAoAEwARQBOACgAZQB4AHAAXwBzAHQAcgBpAG4AZwApACkALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFIARQBEAFUAQwBFACgAMQAsACAAZQB4AHAAXwBkAGkAZwBpAHQAcwAsACAATABBAE0AQgBEAEEAKABhAGMAYwAsACAAZABpAGcAaQB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBoAG8AcgB0AC0AYwBpAHIAYwB1AGkAdAA6ACAAUwBrAGkAcAAgAGMAYQBsAGMAdQBsAGEAdABpAG4AZwAgADEAXgAxADAAIABkAHUAcgBpAG4AZwAgAGwAZQBhAGQAaQBuAGcAIABpAHQAZQByAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAcwBfAG8AbgBlACwAIABBAE4ARAAoAFIATwBXAFMAKABhAGMAYwApACAAPQAgADEALAAgAEkATgBEAEUAWAAoAGEAYwBjACwAIAAxACwAIAAxACkAIAA9ACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAMQAuACAAUgBhAGkAcwBlACAAQQBjAGMAIAB0AG8AIAB0AGgAZQAgADEAMAB0AGgAIABwAG8AdwBlAHIAIAB1AHMAaQBuAGcAIABlAHgAYQBjAHQAbAB5ACAANAAgAG0AdQBsAHQAaQBwAGwAaQBjAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8AMQAwACwAIABJAEYAKABpAHMAXwBvAG4AZQAsACAAYQBjAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8AMgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGEAYwBjACwAIABhAGMAYwAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8ANAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGEAYwBjAF8AMgAsACAAYQBjAGMAXwAyACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBjAGMAXwA4ACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAYQBjAGMAXwA0ACwAIABhAGMAYwBfADQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAYQBjAGMAXwA4ACwAIABhAGMAYwBfADIALAAgAGsAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAyAC4AIABNAHUAbAB0AGkAcABsAHkAIABiAHkAIAB0AGgAZQAgAGMAbwByAHIAZQBzAHAAbwBuAGQAaQBuAGcAIABwAHIAZQAtAGMAbwBtAHAAdQB0AGUAZAAgAGMAYQBjAGgAZQAgAHYAYQBsAHUAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABkAGkAZwBpAHQAIAA9ACAAMAAsACAAYQBjAGMAXwAxADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAYQBjAGgAZQBfAHYAYQBsACwAIABDAEgATwBPAFMARQAoAGQAaQBnAGkAdAAsACAAZgBpAHIAcwB0ACwAIABzAGUAYwBvAG4AZAAsACAAdABoAGkAcgBkACwAIABmAG8AdQByAHQAaAAsACAAZgBpAGYAdABoACwAIABzAGkAeAB0AGgALAAgAHMAZQB2AGUAbgB0AGgALAAgAGUAaQBnAHQAaAAsACAAbgBpAG4AdABoACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAaQBzAF8AbwBuAGUALAAgAGMAYQBjAGgAZQBfAHYAYQBsACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAYQBjAGMAXwAxADAALAAgAGMAYQBjAGgAZQBfAHYAYQBsACwAIABrACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAEkAbgB0AGUAZwBlAHIAIABTAHEAdQBhAHIAZQAgAFIAbwBvAHQAIAB1AHMAaQBuAGcAIABOAGUAdwB0AG8AbgAnAHMAIABNAGUAdABoAG8AZAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAG4AIABSAGEAZABpAGMAYQBuAGQAIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AcwBlAGUAZAAgAE8AdgBlAHIALQBlAHMAdABpAG0AYQB0AGUAZAAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABzAGUAZQBkACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBVAFMAcQByAHQAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBuACwAIABsAGkAbQBiAHMAXwBzAGUAZQBkACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAdABhAHQAZQAgAGkAcwAgAHAAYQBjAGsAZQBkADoAIABWAFMAVABBAEMASwAoAGkAcwBfAGQAbwBuAGUAXwBmAGwAYQBnACwAIABjAHUAcgByAGUAbgB0AF8AeAApAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKAAwACwAIABsAGkAbQBiAHMAXwBzAGUAZQBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AaQB0AGUAcgBzACwAIAAzADUALABcAG4AXABuACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAHQAYQB0AGUALAAgAFIARQBEAFUAQwBFACgAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbQBhAHgAXwBpAHQAZQByAHMAKQAsACAATABBAE0AQgBEAEEAKABzAHQAYQB0AGUALAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAHMAXwBkAG8AbgBlACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwB4ACwAIABEAFIATwBQACgAcwB0AGEAdABlACwAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAaQBzAF8AZABvAG4AZQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAdABlACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAxAC4AIABEAGkAdgBpAHMAaQBvAG4AOgAgAG4AIAAvACAAeABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZABpAHYAXwBwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ARABpAHYAUgBvAHUAdABlAHIAKABsAGkAbQBiAHMAXwBuACwAIABjAHUAcgByAF8AeAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcgAsACAASQBOAEQARQBYACgAZABpAHYAXwBwAGEAYwBrAGUAZAAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHEALAAgAEQAUgBPAFAAKABkAGkAdgBfAHAAYQBjAGsAZQBkACwAIABsAGUAbgBfAHIAIAArACAAMQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAyAC4AIABBAGQAZABpAHQAaQBvAG4AOgAgAHgAIAArACAAKABuACAALwAgAHgAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB1AG0AXwB4AHEALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQQBkAGQAKABjAHUAcgByAF8AeAAsACAAcQAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAzAC4AIABIAGEAbAB2AGkAbgBnADoAIAAoAHgAIAArACAAKABuACAALwAgAHgAKQApACAALwAgADIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEsAbgB1AHQAaABEAGkAdgAgAGkAbgBoAGUAcgBlAG4AdABsAHkAIABzAHUAcABwAG8AcgB0AHMAIABzAGMAYQBsAGEAcgAgAGQAaQB2AGkAcwBvAHIAcwAgAHcAaQB0AGgAIAB6AGUAcgBvACAAbwB2AGUAcgBoAGUAYQBkAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGkAdgBfADIAXwBwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2ACgAcwB1AG0AXwB4AHEALAAgAHsAMgB9ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwByADIALAAgAEkATgBEAEUAWAAoAGQAaQB2AF8AMgBfAHAAYQBjAGsAZQBkACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAeABfAG4AZQB4AHQALAAgAEQAUgBPAFAAKABkAGkAdgBfADIAXwBwAGEAYwBrAGUAZAAsACAAbABlAG4AXwByADIAIAArACAAMQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAA0AC4AIABDAG8AbgB2AGUAcgBnAGUAbgBjAGUAIABDAGgAZQBjAGsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQwBvAG0AcABhAHIAZQAoAHgAXwBuAGUAeAB0ACwAIABjAHUAcgByAF8AeAApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABOAGUAdwB0AG8AbgAnAHMAIABtAGUAdABoAG8AZAAgAGMAbwBuAHYAZQByAGcAZQBzACAAbwBuACAAdABoAGUAIABmAGwAbwBvAHIAIAByAG8AbwB0ACwAIABhAG4AZAAgAHMAdABhAGIAaQBsAGkAegBlAHMAIABvAHIAIABvAHMAYwBpAGwAbABhAHQAZQBzACAAdQBwACAAYgB5ACAAMQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABUAGgAZQByAGUAZgBvAHIAZQAsACAAaQBmACAAeABfAG4AZQB4AHQAIAA+AD0AIABjAHUAcgByAF8AeAAsACAAdABoAGUAIABhAGwAZwBvAHIAaQB0AGgAbQAgAGgAYQBzACAAYwBvAG4AdgBlAHIAZwBlAGQALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYwBvAG0AcAAgAD4APQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADEALAAgAGMAdQByAHIAXwB4ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADAALAAgAHgAXwBuAGUAeAB0ACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAZgBpAG4AYQBsAF8AcwB0AGEAdABlACwAIAAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQgBpAGcASQBuAHQAIgAsACIAdABlAHgAdAAiADoAIgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4ALwAvACAAQgBpAGcAIABJAG4AdABlAGcAZQByACAAQQByAGkAdABoAG0AZQB0AGkAYwAgAEwAaQBiAHIAYQByAHkAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIAAgACAAQgBpAGcASQBuAHQAIABNAG8AZAB1AGwAZQAgACAAIAAgACAAIAAgACAAIAAgACAALwAvAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIABQAHUAYgBsAGkAYwAgAEEAUABJACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwBcAG4ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8AXABuAFwAbgAvACoAKgBcAG4AIAAqACAATgBvAHIAbQBhAGwAaQBzAGUAcwAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AIABTAHQAcgBpAHAAcwAgAGwAZQBhAGQAaQBuAGcAIAB6AGUAcgBvAHMALAAgAHIAZQBzAG8AbAB2AGUAcwAgAFwAIgAtADAAXAAiACAAdABvACAAXAAiADAAXAAiACwAIABhAG4AZAAgAHQAaAByAG8AdwBzACAAIwBWAEEATABVAEUAIQAgAG8AbgAgAGkAbgB2AGEAbABpAGQAIABjAGgAYQByAGEAYwB0AGUAcgBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ATgBvAHIAbQAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AHIALAAgAEkARgAoAE8AUgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYgBpAGcAXwBpAG4AdAApACwAIABiAGkAZwBfAGkAbgB0ACAAPQAgAFwAIgBcACIAKQAsACAAXAAiADAAXAAiACwAIABiAGkAZwBfAGkAbgB0ACAAJgAgAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AdgBhAGwAaQBkACwAIABSAEUARwBFAFgAVABFAFMAVAAoAHMAdAByACwAIABcACIAXgAtAD8AXABcAGQAKwAkAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAcgBpAHAAcABlAGQALAAgAFIARQBHAEUAWABSAEUAUABMAEEAQwBFACgAcwB0AHIALAAgAFwAIgBeACgALQA/ACkAMAArACgAPwA9AFwAXABkACkAXAAiACwAIABcACIAJAAxAFwAIgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATgBPAFQAKABpAHMAXwB2AGEAbABpAGQAKQAsACAAVgBBAEwAVQBFACgAXAAiACMAVgBBAEwAVQBFACEAXAAiACkALAAgAEkARgAoAHMAdAByAGkAcABwAGUAZAAgAD0AIABcACIALQAwAFwAIgAsACAAXAAiADAAXAAiACwAIABzAHQAcgBpAHAAcABlAGQAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIABzAGkAZwBuACAAbwBmACAAYQAgAEIAaQBnAEkAbgB0ADoAIAAxACAAKABwAG8AcwBpAHQAaQB2AGUAKQAsACAALQAxACAAKABuAGUAZwBhAHQAaQB2AGUAKQAsACAAbwByACAAMAAgACgAegBlAHIAbwApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AUwBpAGcAbgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALAAgAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAGUAZAAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUwBXAEkAVABDAEgAKABMAEUARgBUACgAbgBvAHIAbQBlAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMABcACIALAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIAAtADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAvACAALQAtAC0AIABQAHIAZQBkAGkAYwBhAHQAZQBzACAALQAtAC0AIABcAFwAXABcAFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFIAZQB0AHUAcgBuAHMAIABUAFIAVQBFACAAaQBmACAAdABoAGUAIABCAGkAZwBJAG4AdAAgAGkAcwAgAGUAeABhAGMAdABsAHkAIAB6AGUAcgBvAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ASQBzAFoAZQByAG8AIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACAAPQAgAFwAIgAwAFwAIgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAFQAUgBVAEUAIABpAGYAIAB0AGgAZQAgAEIAaQBnAEkAbgB0ACAAaQBzACAAbgBlAGcAYQB0AGkAdgBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ASQBzAE4AZQBnACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsACAATABFAEYAVAAoAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0ACkAKQAgAD0AIABcACIALQBcACIAKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFIAZQB0AHUAcgBuAHMAIABUAFIAVQBFACAAaQBmACAAdABoAGUAIABCAGkAZwBJAG4AdAAgAGkAcwAgAGUAdgBlAG4ALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBJAHMARQB2AGUAbgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALAAgAEkAUwBFAFYARQBOACgAVgBBAEwAVQBFACgAUgBJAEcASABUACgATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAKQApACkAKQApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAFQAUgBVAEUAIABpAGYAIAB0AGgAZQAgAEIAaQBnAEkAbgB0ACAAaQBzACAAbwBkAGQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBJAHMATwBkAGQAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAIABJAFMATwBEAEQAKABWAEEATABVAEUAKABSAEkARwBIAFQAKABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACkAKQApACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIAB1AG4AcwBpAGcAbgBlAGQAIABtAGEAZwBuAGkAdAB1AGQAZQAgAG8AZgAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnACAAKABhAGIAcwBvAGwAdQB0AGUAIAB2AGEAbAB1AGUAKQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAIABUAGgAZQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEEAYgBzACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsACAAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AdQBtACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAEUARgBUACgAbgB1AG0AKQAgAD0AIABcACIALQBcACIALAAgAE0ASQBEACgAbgB1AG0ALAAgADIALAAgAEwARQBOACgAbgB1AG0AKQAgAC0AIAAxACkALAAgAG4AdQBtACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEMAbwBtAHAAYQByAGUAcwAgAHQAdwBvACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwBzAC4AIABSAGUAdAB1AHIAbgBzACAAMQAgACgAYQAgAD4AIABiACkALAAgAC0AMQAgACgAYQAgADwAIABiACkALAAgAG8AcgAgADAAIAAoAGEAIAA9ACAAYgApAC4AXABuACAAKgAgAEUAdgBhAGwAdQBhAHQAZQBzACAAcwBpAGcAbgBzACAAYQBuAGQAIABsAGUAbgBnAHQAaABzAC4AIABJAGYAIABpAGQAZQBuAHQAaQBjAGEAbAAsACAAZABlAGwAZQBnAGEAdABlAHMAIAB0AG8AIABuAGEAdABpAHYAZQAgAGwAaQBtAGIAIABhAHIAcgBhAHkAIABjAG8AbQBwAGEAcgBpAHMAbwBuAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAcwBlAGMAbwBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBDAG8AbQBwAGEAcgBlACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBhACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYQAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGIALAAgAEIAaQBnAGkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBiACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AYQAgADwAPgAgAHMAaQBnAG4AXwBiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMASQBHAE4AKABzAGkAZwBuAF8AYQAgAC0AIABzAGkAZwBuAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHMAaQBnAG4AXwBhACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYQAsACAATABFAE4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGIALAAgAEwARQBOACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABsAGUAbgBfAGEAIAA8AD4AIABsAGUAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBJAEcATgAoAGwAZQBuAF8AYQAgAC0AIABsAGUAbgBfAGIAKQAgACoAIABzAGkAZwBuAF8AYQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBBAEQARABcACIAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBhACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYgApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGEAZwBfAGMAbwBtAHAAYQByAGkAcwBvAG4ALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQwBvAG0AcABhAHIAZQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcABhAHIAaQBzAG8AbgAgACoAIABzAGkAZwBuAF8AYQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACAALQAgAEEAZABkAGkAdABpAG8AbgAgACYAIABTAHUAYgB0AHIAYQBjAHQAaQBvAG4AIAAtACAAIAAgACAAIAAgACAAXABcAFwAXABcAG4AXABuAC8AKgAqAFwAbgAgACoAIABBAGQAZABzACAAdAB3AG8AIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEEAZABkACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBhACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYQAsACAAQgBpAGcAaQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGIALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEEARABEAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBhACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGEAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBiACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGIAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAHIAbwB1AHQAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBBAGQAZABTAHUAYgBSAG8AdQB0AGUAcgAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAHMAaQBnAG4AXwBhACwAIABzAGkAZwBuAF8AYgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAGkAZwBuACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcgBvAHUAdABlAGQALAAgAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAEQAUgBPAFAAKAByAG8AdQB0AGUAZAAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAbQBlAHIAZwBlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGYAaQBuAGEAbABfAHMAaQBnAG4AIAA9ACAALQAxACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQALAAgAG0AZQByAGcAZQBkACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFMAdQBiAHQAcgBhAGMAdABzACAAdABoAGUAIABzAGUAYwBvAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAIABmAHIAbwBtACAAdABoAGUAIABmAGkAcgBzAHQAIAAoAEEAIAAtACAAQgApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAG0AaQBuAHUAZQBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGIAIABUAGgAZQAgAHMAdQBiAHQAcgBhAGgAZQBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBTAHUAYgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABiAGkAZwBfAGkAbgB0AF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAASQBuAHYAZQByAHQAIAB0AGgAZQAgAHMAaQBnAG4AIABvAGYAIABCACAAYQB0ACAAdABoAGUAIAB0AGUAeAB0ACAAbABlAHYAZQBsAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAHYAXwBiACwAIABJAEYAKABuAG8AcgBtAF8AYgAgAD0AIABcACIAMABcACIALAAgAFwAIgAwAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEwARQBGAFQAKABuAG8AcgBtAF8AYgApACAAPQAgAFwAIgAtAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAEQAKABuAG8AcgBtAF8AYgAsACAAMgAsACAATABFAE4AKABuAG8AcgBtAF8AYgApACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAgACYAIABuAG8AcgBtAF8AYgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUABhAHMAcwAgAHQAbwAgAEEAZABkAFwAbgAgACAAIAAgACAAIAAgACAAQQBkAGQAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAaQBuAHYAXwBiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFMAdQBtAHMAIABhAG4AIABhAHIAcgBhAHkAIABvAHIAIAByAGEAbgBnAGUAIABvAGYAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMAIAB2AGkAYQAgAHYAZQBjAHQAbwByAGkAegBlAGQAIABnAHIAbwB1AHAAIABtAGEAdAByAGkAYwBlAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIAByAGEAbgBnAGUAIABBACAAYwBvAG4AdABpAGcAdQBvAHUAcwAgAHIAYQBuAGcAZQAgAG8AcgAgAGEAcgByAGEAeQAgAG8AZgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoALwBcAG4AUwB1AG0AIAA9ACAATABBAE0AQgBEAEEAKAByAGEAbgBnAGUALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAZgBsAGEAdAAsACAAVABPAFIATwBXACgAcgBhAG4AZwBlACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATwBSACgASQBTAEUAUgBSAE8AUgAoAGYAbABhAHQAKQAsACAAQwBPAEwAVQBNAE4AUwAoAGYAbABhAHQAKQAgAD0AIAAwACkALAAgAFwAIgAwAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AbwByAG0AcwAsACAATQBBAFAAKABmAGwAYQB0ACwAIABMAEEATQBCAEQAQQAoAHgALAAgAE4AbwByAG0AKAB4ACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBzACwAIABNAEEAUAAoAEwARQBGAFQAKABuAG8AcgBtAHMAKQAsACAATABBAE0AQgBEAEEAKAB4ACwAIABJAEYAKAB4ACAAPQAgAFwAIgAwAFwAIgAsACAAMAAsACAAaQBmACgAeAAgAD0AIABcACIALQBcACIALAAgAC0AMQAsACAAMQApACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBiAHMAXwBuAG8AcgBtAHMALAAgAE0AQQBQACgAbgBvAHIAbQBzACwAIABzAGkAZwBuAHMALAAgAEwAQQBNAEIARABBACgAeAAsACAAcwBpAGcAbgAsACAASQBGACgAcwBpAGcAbgAgAD0AIAAtADEALAAgAE0ASQBEACgAeAAsACAAMgAsACAATABFAE4AKAB4ACkALQAxACkALAAgAHgAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAG8AcwBfAHMAdAByAHMALAAgAEYASQBMAFQARQBSACgAYQBiAHMAXwBuAG8AcgBtAHMALAAgAHMAaQBnAG4AcwAgAD0AIAAxACwAIAB7AFwAIgAwAFwAIgB9ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAZwBfAHMAdAByAHMALAAgAEYASQBMAFQARQBSACgAYQBiAHMAXwBuAG8AcgBtAHMALAAgAHMAaQBnAG4AcwAgAD0AIAAtADEALAAgAHsAXAAiADAAXAAiAH0AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHUAbgBpAGYAaQBlAGQAXwBrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIAQQBEAEQAXAAiACwAIABDAE8ATABVAE0ATgBTACgAZgBsAGEAdAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAG8AcwBfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAGEAdAByAGkAeABTAHUAbQAoAHAAbwBzAF8AcwB0AHIAcwAsACAAdQBuAGkAZgBpAGUAZABfAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQBnAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AYQB0AHIAaQB4AFMAdQBtACgAbgBlAGcAXwBzAHQAcgBzACwAIAB1AG4AaQBmAGkAZQBkAF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBvAHUAdABlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEEAZABkAFMAdQBiAFIAbwB1AHQAZQByACgAcABvAHMAXwBsAGkAbQBiAHMALAAgAG4AZQBnAF8AbABpAG0AYgBzACwAIAAxACwAIAAtADEALAAgAHUAbgBpAGYAaQBlAGQAXwBrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAGkAZwBuACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcgBvAHUAdABlAGQALAAgAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABEAFIATwBQACgAcgBvAHUAdABlAGQALAAgAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBlAHIAZwBlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAdQBuAGkAZgBpAGUAZABfAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGYAaQBuAGEAbABfAHMAaQBnAG4AIAA9ACAALQAxACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQALAAgAG0AZQByAGcAZQBkACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABNAHUAbAB0AGkAcABsAGkAZQBzACAAdAB3AG8AIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAE0AdQBsACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBhACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYQAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGIALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYQAsACAATABFAE4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGIALAAgAEwARQBOACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGgAbwByAHQALQBjAGkAcgBjAHUAaQB0ADoAIAAwACAAbQB1AGwAdABpAHAAbABpAGUAZAAgAGIAeQAgAGEAbgB5AHQAaABpAG4AZwAgAGkAcwAgADAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABzAGkAZwBuAF8AYQAgAD0AIAAwACwAIABzAGkAZwBuAF8AYgAgAD0AIAAwACkALAAgAFwAIgAwAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbABlAG4AXwBhACAAKwAgAGwAZQBuAF8AYgAgAD4AIAAzADIANwA2ADYALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAYQBsAGMAdQBsAGEAdABlACAAZAB5AG4AYQBtAGkAYwAgAHMAYQBmAGUAIABLACAAYgBhAHMAZQBkACAAbwBuACAAdABoAGUAIABzAGgAbwByAHQAZQBzAHQAIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIATQBVAEwAXAAiACwAIABNAEkATgAoAGwAZQBuAF8AYQAsACAAbABlAG4AXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAcABsAGkAdAAgAGEAYgBzAG8AbAB1AHQAZQAgAHMAdAByAGkAbgBnAHMAIABpAG4AdABvACAAbABpAHQAdABsAGUALQBlAG4AZABpAGEAbgAgAGEAcgByAGEAeQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGEALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYQApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBiACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGIAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIABtAGEAZwBuAGkAdAB1AGQAZQAgAGEAbgBkACAAcgBlAHMAbwBsAHYAZQAgAHMAaQBnAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcwBpAGcAbgAsACAAcwBpAGcAbgBfAGEAIAAqACAAcwBpAGcAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGUAcgBnAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAXAAiAC0AXAAiACAAJgAgAG0AZQByAGcAZQBkACwAIABtAGUAcgBnAGUAZAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAFYATwBMAEEAVABJAEwARQBdACAARwBlAG4AZQByAGEAdABlAHMAIABhACAAZAB5AG4AYQBtAGkAYwAgAGEAcgByAGEAeQAgAG8AZgAgAGkAbgB0AGUAZwBlAHIAcwAgAGEAcwAgAHQAZQB4AHQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG4AdQBtAF8AcgBvAHcAcwBdACAAYQByAHIAYQB5ACAAaABlAGkAZwBoAHQALAAgAGQAZQBmAGEAdQBsAHQAIAAxAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAWwBuAHUAbQBfAGMAbwBsAHMAXQAgAGEAcgByAGEAeQAgAHcAaQBkAHQAaAAsACAAZABlAGYAYQB1AGwAdAAgADEALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG0AaQBuAF8AZABpAGcAaQB0AHMAXQAgAG0AaQBuAGkAbQB1AG0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAaQBnAGkAdABzACwAIABkAGUAZgBhAHUAbAB0ACAAMQA2ACAAKABtAGkAbgAgADEAIABkAGkAZwBpAHQAKQBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG0AYQB4AF8AZABpAGcAaQB0AHMAXQAgAG0AYQB4AGkAbQB1AG0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAaQBnAGkAdABzACwAIABkAGUAZgBhAHUAbAB0ACAANQAwACAAKABtAGEAeAAgADMAMgAsADcANgA3ACAAYwBoAGEAcgBzACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAHMAaQBnAG4AKQBcAG4AIAAqAC8AXABuAFIAYQBuAGQAQgBpAGcASQBuAHQAQQByAHIAYQB5ACAAPQAgAEwAQQBNAEIARABBACgAWwBuAHUAbQBfAHIAbwB3AHMAXQAsACAAWwBuAHUAbQBfAGMAbwBsAHMAXQAsACAAWwBtAGkAbgBfAGQAaQBnAGkAdABzAF0ALAAgAFsAbQBhAHgAXwBkAGkAZwBpAHQAcwBdACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwByAG8AdwBzACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAG4AdQBtAF8AcgBvAHcAcwApACwAIAAxACwAIABuAHUAbQBfAHIAbwB3AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBfAGMAbwBsAHMALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbgB1AG0AXwBjAG8AbABzACkALAAgADEALAAgAG4AdQBtAF8AYwBvAGwAcwApACwAIABcAG4AIAAgACAAIAAgACAAIAAgAG0AaQBuAF8AbABlAG4ALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbQBpAG4AXwBkAGkAZwBpAHQAcwApACwAIAAxADYALAAgAE0ASQBOACgAMwAyADcANgA3ACwAIABNAEEAWAAoADEALAAgAG0AaQBuAF8AZABpAGcAaQB0AHMAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AbABlAG4ALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbQBhAHgAXwBkAGkAZwBpAHQAcwApACwAIAA1ADAALAAgAE0AQQBYACgAMQAsACAATQBJAE4AKAAzADIANwA2ADYALAAgAG0AYQB4AF8AZABpAGcAaQB0AHMAKQApACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABNAEEAUAAoAFIAQQBOAEQAQQBSAFIAQQBZACgAbgBfAHIAbwB3AHMALAAgAG4AXwBjAG8AbABzACwAIABtAGkAbgBfAGwAZQBuACwAIABtAGEAeABfAGwAZQBuACwAIABUAFIAVQBFACkALAAgAEwAQQBNAEIARABBACgAbABlAG4AZwB0AGgALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGkAZwBuACwAIABDAEgATwBPAFMARQAoAFIAQQBOAEQAQgBFAFQAVwBFAEUATgAoADEALAAgADIAKQAsACAAXAAiAFwAIgAsACAAXAAiAC0AXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGkAZwBpAHQAcwAsACAAQwBPAE4AQwBBAFQAKABSAEEATgBEAEEAUgBSAEEAWQAoADEALAAgAGwAZQBuAGcAdABoACwAIAAwACwAIAA5ACwAIABUAFIAVQBFACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AIAAmACAAUgBFAEcARQBYAFIARQBQAEwAQQBDAEUAKABkAGkAZwBpAHQAcwAsACAAXAAiAF4AMAAqAFwAIgAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABEAGkAdgBpAGQAZQBzACAAdABoAGUAIABmAGkAcgBzAHQAIABCAGkAZwBJAG4AdAAgAGIAeQAgAHQAaABlACAAcwBlAGMAbwBuAGQAIAAoAEEAIAAvACAAQgApAC4AIABcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAHQAaABlACAAcQB1AG8AdABpAGUAbgB0ACAAYQBuAGQAIABtAG8AZAB1AGwAdQBzACAAaQBuACAAcgBvAHcAcwAgADEAIABhAG4AZAAgADIALAAgAHIAZQBzAHAAZQBjAHQAaQB2AGUAbAB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAGQAaQB2AGkAZABlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAHUAcwBlAF8AZgBsAG8AbwByAF0AIABPAHAAdABpAG8AbgBhAGwAIABiAG8AbwBsAGUAYQBuAC4AIABUAFIAVQBFACAAZgBvAHIAIABQAHkAdABoAG8AbgAtAHMAdAB5AGwAZQAgAEYAbABvAG8AcgAgAGQAaQB2AGkAcwBpAG8AbgAsACAARgBBAEwAUwBFACAAZgBvAHIAIABUAHIAdQBuAGMAYQB0AGUAZAAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAARgBBAEwAUwBFAC4AXABuACAAKgAvAFwAbgBEAGkAdgBNAG8AZAAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABiAGkAZwBfAGkAbgB0AF8AYgAsACAAWwB1AHMAZQBfAGYAbABvAG8AcgBdACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBhACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYQAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGIALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGkAcwBfAGYAbABvAG8AcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAB1AHMAZQBfAGYAbABvAG8AcgApACwAIABGAEEATABTAEUALAAgAHUAcwBlAF8AZgBsAG8AbwByACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAcwBpAGcAbgBfAGIAIAA9ACAAMAAsACAAIwBEAEkAVgAvADAAIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AYQAgAD0AIAAwACwAIAB7AFwAIgAwAFwAIgA7AFwAIgAwAFwAIgB9ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBEAEkAVgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBhACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBiACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZABfAHIAZQBzAHUAbAB0ACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBEAGkAdgBSAG8AdQB0AGUAcgAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAUgBlAG0AYQBpAG4AZABlAHIAIABhAG4AZAAgAFEAdQBvAHQAaQBlAG4AdAAgAGEAcgByAGEAeQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwByACwAIABJAE4ARABFAFgAKABwAGEAYwBrAGUAZABfAHIAZQBzAHUAbAB0ACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBtAF8AbABpAG0AYgBzACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcABhAGMAawBlAGQAXwByAGUAcwB1AGwAdAAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwByACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcQB1AG8AdABfAGwAaQBtAGIAcwAsACAARABSAE8AUAAoAHAAYQBjAGsAZQBkAF8AcgBlAHMAdQBsAHQALAAgAGwAZQBuAF8AcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHMAbwBsAHYAZQAgAFQAcgB1AG4AYwBhAHQAZQBkACAAcwBpAGcAbgBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcwBpAGcAbgAsACAAcwBpAGcAbgBfAGEAIAAqACAAcwBpAGcAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AZQByAGcAZQBkAF8AcQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAcQB1AG8AdABfAGwAaQBtAGIAcwAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGUAcgBnAGUAZABfAHIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAHIAZQBtAF8AbABpAG0AYgBzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdAByAHUAbgBjAF8AcQAsACAASQBGACgAQQBOAEQAKABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAbQBlAHIAZwBlAGQAXwBxACAAPAA+ACAAXAAiADAAXAAiACkAIAAsACAAXAAiAC0AXAAiACAAJgAgAG0AZQByAGcAZQBkAF8AcQAsACAAbQBlAHIAZwBlAGQAXwBxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAcgB1AG4AYwBfAHIALAAgAEkARgAoAGEAbgBkACgAcwBpAGcAbgBfAGEAIAA9ACAALQAxACwAIABtAGUAcgBnAGUAZABfAHIAIAA8AD4AIABcACIAMABcACIAKQAsACAAXAAiAC0AXAAiACAAJgAgAG0AZQByAGcAZQBkAF8AcgAsACAAbQBlAHIAZwBlAGQAXwByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARgBsAG8AbwByACAAQwBvAHIAcgBlAGMAdABpAG8AbgA6ACAAVAByAGkAZwBnAGUAcgAgAE8ATgBMAFkAIABpAGYAIABmAGwAbwBvAHIAIABpAHMAIAByAGUAcQB1AGUAcwB0AGUAZAAsACAAcwBpAGcAbgBzACAAZABpAGYAZgBlAHIALAAgAGEAbgBkACAAcgBlAG0AYQBpAG4AZABlAHIAIABpAHMAIABuAG8AbgAtAHoAZQByAG8AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAZQBkAHMAXwBjAG8AcgByAGUAYwB0AGkAbwBuACwAIABBAE4ARAAoAGkAcwBfAGYAbABvAG8AcgAsACAAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAG0AZQByAGcAZQBkAF8AcgAgADwAPgAgAFwAIgAwAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHEALAAgAEkARgAoAG4AZQBlAGQAcwBfAGMAbwByAHIAZQBjAHQAaQBvAG4ALAAgAFMAdQBiACgAdAByAHUAbgBjAF8AcQAsACAAXAAiADEAXAAiACkALAAgAHQAcgB1AG4AYwBfAHEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsACAASQBGACgAbgBlAGUAZABzAF8AYwBvAHIAcgBlAGMAdABpAG8AbgAsACAAQQBkAGQAKAB0AHIAdQBuAGMAXwByACwAIABuAG8AcgBtAF8AYgApACwAIAB0AHIAdQBuAGMAXwByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABmAGkAbgBhAGwAXwBxACwAIABmAGkAbgBhAGwAXwByACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEQAaQB2AGkAZABlAHMAIAB0AGgAZQAgAGYAaQByAHMAdAAgAEIAaQBnAEkAbgB0ACAAYgB5ACAAdABoAGUAIABzAGUAYwBvAG4AZAAgACgAQQAgAC8AIABCACkALgAgAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBhACAAVABoAGUAIABkAGkAdgBpAGQAZQBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGIAIABUAGgAZQAgAGQAaQB2AGkAcwBvAHIAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAWwB1AHMAZQBfAGYAbABvAG8AcgBdACAATwBwAHQAaQBvAG4AYQBsACAAYgBvAG8AbABlAGEAbgAuACAAVABSAFUARQAgAGYAbwByACAAUAB5AHQAaABvAG4ALQBzAHQAeQBsAGUAIABGAGwAbwBvAHIAIABkAGkAdgBpAHMAaQBvAG4ALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAEYAQQBMAFMARQAuAFwAbgAgACoALwBcAG4ARABpAHYAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALAAgAFsAdQBzAGUAXwBmAGwAbwBvAHIAXQAsAFwAbgAgACAAIAAgAEkATgBEAEUAWAAoAEQAaQB2AE0AbwBkACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAIAB1AHMAZQBfAGYAbABvAG8AcgApACwAIAAxACwAIAAxACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABDAG8AbQBwAHUAdABlAHMAIAB0AGgAZQAgAHIAZQBtAGEAaQBuAGQAZQByACAAbwBmACAAQQAgAC8AIABCAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAGQAaQB2AGkAZABlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAHUAcwBlAF8AZgBsAG8AbwByAF0AIABPAHAAdABpAG8AbgBhAGwAIABiAG8AbwBsAGUAYQBuAC4AIABUAFIAVQBFACAAZgBvAHIAIABQAHkAdABoAG8AbgAtAHMAdAB5AGwAZQAgAE0AbwBkAHUAbABvAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABGAEEATABTAEUALgBcAG4AIAAqAC8AXABuAE0AbwBkACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAIABbAHUAcwBlAF8AZgBsAG8AbwByAF0ALABcAG4AIAAgACAAIABJAE4ARABFAFgAKABEAGkAdgBNAG8AZAAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABiAGkAZwBfAGkAbgB0AF8AYgAsACAAdQBzAGUAXwBmAGwAbwBvAHIAKQAsACAAMgAsACAAMQApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBhAGkAcwBlAHMAIABhACAAQgBpAGcASQBuAHQAIABiAGEAcwBlACAAdABvACAAdABoAGUAIABwAG8AdwBlAHIAIABvAGYAIABhACAAQgBpAGcASQBuAHQAIABlAHgAcABvAG4AZQBuAHQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGEAcwBlACAAVABoAGUAIABiAGEAcwBlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGUAeABwAG8AbgBlAG4AdAAgAFQAaABlACAAZQB4AHAAbwBuAGUAbgB0ACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AUABvAHcAIAA9ACAATABBAE0AQgBEAEEAKABiAGEAcwBlACwAIABlAHgAcABvAG4AZQBuAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIAYQBzAGUALAAgAE4AbwByAG0AKABiAGEAcwBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBlAHgAcAAsACAATgBvAHIAbQAoAGUAeABwAG8AbgBlAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgBhAHMAZQAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGUAeABwACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AZQB4AHAAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGEAYgBzAF8AYgBhAHMAZQAsACAAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBiAGEAcwBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAGEAYgBzAF8AZQB4AHAALAAgAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AZQB4AHAAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGkAcwBfAGUAeABwAF8AZQB2AGUAbgAsACAASQBTAEUAVgBFAE4AKABWAEEATABVAEUAKABSAEkARwBIAFQAKABuAG8AcgBtAF8AZQB4AHAALAAgADEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAaQBnAG4ALAAgAEkARgAoAHMAaQBnAG4AXwBiAGEAcwBlACAAPQAgAC0AMQAsACAASQBGACgAaQBzAF8AZQB4AHAAXwBlAHYAZQBuACwAIAAxACwAIAAtADEAKQAsACAAcwBpAGcAbgBfAGIAYQBzAGUAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEgAYQBuAGQAbABlACAAbQBhAHQAaABlAG0AYQB0AGkAYwBhAGwAIABiAG8AdQBuAGQAYQByAGkAZQBzACAAYQBuAGQAIABiAGEAcwBlACAAbABpAG0AaQB0AHMAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABhAGIAcwBfAGIAYQBzAGUAIAA9ACAAXAAiADAAXAAiACwAIABJAEYAKABuAG8AcgBtAF8AZQB4AHAAIAA9ACAAXAAiADAAXAAiACwAIAAjAE4AVQBNACEALAAgAFwAIgAwAFwAIgApACwAIAAvAC8AIAAwAF4AMAAgAGkAcwAgAHUAbgBkAGUAZgBpAG4AZQBkAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAYQBiAHMAXwBiAGEAcwBlACAAPQAgAFwAIgAxAFwAIgAsACAASQBGACgAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAFwAIgAtADEAXAAiACwAIABcACIAMQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAcwBpAGcAbgBfAGUAeABwACAAPQAgAC0AMQAsACAAXAAiADAAXAAiACwAIAAvAC8AIABJAG4AdABlAGcAZQByACAAdAByAHUAbgBjAGEAdABpAG8AbgA6ACAAbgBlAGcAYQB0AGkAdgBlACAAZQB4AHAAbwBuAGUAbgB0AHMAIAB5AGkAZQBsAGQAIAAwACAAZgBvAHIAIABiAGEAcwBlAHMAIAA+AD0AIAAyAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgBvAHIAbQBfAGUAeABwACAAPQAgAFwAIgAwAFwAIgAsACAAXAAiADEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHMAdQBsAHQAcwAgAGYAcgBvAG0AIABlAHgAcABvAG4AZQBuAHQAcwAgAGcAcgBlAGEAdABlAHIAIAB0AGgAYQBuACAANgAgAGQAaQBnAGkAdABzACAAYwBhAG4AbgBvAHQAIABiAGUAIABkAGkAcwBwAGwAYQB5AGUAZAAuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABFAE4AKABuAG8AcgBtAF8AZQB4AHAAKQAgAD4AIAA2ACwAIAAjAE4AVQBNACEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAHUAbQBfAGUAeABwACwAIABWAEEATABVAEUAKABuAG8AcgBtAF8AZQB4AHAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAcABwAHIAbwB4AGkAbQBhAHQAZQAgAHQAaABlACAAZgBpAG4AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAIABjAG8AdQBuAHQAOgAgAEIAIAAqACAATABvAGcAMQAwACgAQQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGIAYQBzAGUAXwBsAG8AZwAxADAALAAgAEwATwBHADEAMAAoAFYAQQBMAFUARQAoAEwARQBGAFQAKABhAGIAcwBfAGIAYQBzAGUALAAgADEANAApACkAKQAgACsAIABNAEEAWAAoADAALAAgAEwARQBOACgAYQBiAHMAXwBiAGEAcwBlACkAIAAtACAAMQA0ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAHAAcAByAG8AeABfAGQAaQBnAGkAdABzACwAIABuAHUAbQBfAGUAeABwACAAKgAgAGIAYQBzAGUAXwBsAG8AZwAxADAALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYQBwAHAAcgBvAHgAXwBkAGkAZwBpAHQAcwAgAD4AIAAzADIANwA2ADYALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAE0AVQBMAFwAIgAsACAAYQBwAHAAcgBvAHgAXwBkAGkAZwBpAHQAcwAgAC8AIAAyACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYgBhAHMAZQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYQBiAHMAXwBiAGEAcwBlACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBQAG8AdwAoAGwAaQBtAGIAcwBfAGIAYQBzAGUALAAgAG4AbwByAG0AXwBlAHgAcAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AZQByAGcAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAFwAIgAtAFwAIgAgACYAIABtAGUAcgBnAGUAZAAsACAAbQBlAHIAZwBlAGQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQApACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAQwBhAGwAYwB1AGwAYQB0AGUAcwAgAHQAaABlACAAaQBuAHQAZQBnAGUAcgAgAHMAcQB1AGEAcgBlACAAcgBvAG8AdAAgACgAZgBsAG8AbwByACkAIABvAGYAIABhACAAQgBpAGcASQBuAHQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIAByAGEAZABpAGMAYQBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBTAHEAcgB0ACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AbgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAG4ALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBuACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AbgAgAD0AIAAtADEALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgBvAHIAbQBfAG4AIAA9ACAAXAAiADAAXAAiACwAIABcACIAMABcACIALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AbwByAG0AXwBuACAAPQAgAFwAIgAxAFwAIgAsACAAXAAiADEAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwBuACwAIABMAEUATgAoAG4AbwByAG0AXwBuACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGEAawBlAF8AZABpAGcAaQB0AHMALAAgAEkARgAoAGwAZQBuAF8AbgAgADwAPQAgADEANAAsACAAbABlAG4AXwBuACwAIABJAEYAKABJAFMARQBWAEUATgAoAGwAZQBuAF8AbgApACwAIAAxADQALAAgADEAMwApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB2AF8AcwB0AHIALAAgAEwARQBGAFQAKABuAG8AcgBtAF8AbgAsACAAdABhAGsAZQBfAGQAaQBnAGkAdABzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB2AF8AbgB1AG0ALAAgAFYAQQBMAFUARQAoAHYAXwBzAHQAcgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAegBlAHIAbwBfAGMAbwB1AG4AdAAsACAAKABsAGUAbgBfAG4AIAAtACAAdABhAGsAZQBfAGQAaQBnAGkAdABzACkAIAAvACAAMgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGUAZQBkAF8AcAByAGUAZgBpAHgALAAgAFQARQBYAFQAKABSAE8AVQBOAEQAVQBQACgAUwBRAFIAVAAoAHYAXwBuAHUAbQApACwAIAAwACkAIAArACAAMQAsACAAXAAiADAAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGUAZQBkAF8AcwB0AHIALAAgAHMAZQBlAGQAXwBwAHIAZQBmAGkAeAAgACYAIABSAEUAUABUACgAXAAiADAAXAAiACwAIAB6AGUAcgBvAF8AYwBvAHUAbgB0ACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBjAGEAbABlAHMAIABrACAAYgB5ACAAdABoAGUAIABtAGEAeABpAG0AdQBtACAAbwB2AGUAcgBsAGEAcAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBNAFUATABcACIALAAgAGwAZQBuAF8AbgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AbgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAbgBvAHIAbQBfAG4ALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAHMAZQBlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAHMAZQBlAGQAXwBzAHQAcgAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBTAHEAcgB0ACgAbABpAG0AYgBzAF8AbgAsACAAbABpAG0AYgBzAF8AcwBlAGUAZAAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAawApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAuAEsAbgB1AHQAaABEAGkAdgBpAHMAaQBvAG4AIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgBpAHMAaQBvAG4AIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ARABpAHYAaQBzAGkAbwBuAEEAbABnAG8AcgBpAHQAaABtAHMAIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ARABpAHYAaQBzAGkAbwBuAEEAbABnAG8AcgBpAHQAaABtAEMAbwBtAHAAYQByAGkAcwBvAG4AIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ARABpAHYAaQBzAGkAbwBuAEIAZQBuAGMAaABtAGEAcgBrAEMAYQBzAGUAcwAiACwAIgB0AGUAcwB0AF8AQgBpAGcASQBuAHQALgBBAHMAeQBtAG0AZQB0AHIAaQBjAEEAQgBHAHIAaQBkACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEMAYQByAHIAeQAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEMAbwBtAHAAYQByAGUAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBBAGQAZAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAdQBiACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQBhAHQAcgBpAHgAUwB1AG0AIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AQQBkAGQAUwB1AGIAUgBvAHUAdABlAHIAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBGAGkAbgBkAFEAdQBvAHQAaQBlAG4AdABMAGkAbQBiACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEsAbgB1AHQAaABEAGkAdgAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBEAGkAdgBSAG8AdQB0AGUAcgAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAFMAZQBlAGQAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBSAGUAYwBpAHAAcgBvAGMAYQBsACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4ARABpAHYAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBQAG8AdwAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAcQByAHQAIgAsACIAQgBpAGcASQBuAHQALgBOAG8AcgBtACIALAAiAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAiACwAIgBCAGkAZwBJAG4AdAAuAEkAcwBaAGUAcgBvACIALAAiAEIAaQBnAEkAbgB0AC4ASQBzAE4AZQBnACIALAAiAEIAaQBnAEkAbgB0AC4ASQBzAEUAdgBlAG4AIgAsACIAQgBpAGcASQBuAHQALgBJAHMATwBkAGQAIgAsACIAQgBpAGcASQBuAHQALgBBAGIAcwAiACwAIgBCAGkAZwBJAG4AdAAuAEMAbwBtAHAAYQByAGUAIgAsACIAQgBpAGcASQBuAHQALgBBAGQAZAAiACwAIgBCAGkAZwBJAG4AdAAuAFMAdQBiACIALAAiAEIAaQBnAEkAbgB0AC4AUwB1AG0AIgAsACIAQgBpAGcASQBuAHQALgBNAHUAbAAiACwAIgBCAGkAZwBJAG4AdAAuAFIAYQBuAGQAQgBpAGcASQBuAHQAQQByAHIAYQB5ACIALAAiAEIAaQBnAEkAbgB0AC4ARABpAHYATQBvAGQAIgAsACIAQgBpAGcASQBuAHQALgBEAGkAdgAiACwAIgBCAGkAZwBJAG4AdAAuAE0AbwBkACIALAAiAEIAaQBnAEkAbgB0AC4AUABvAHcAIgAsACIAQgBpAGcASQBuAHQALgBTAHEAcgB0ACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/XL-Int.xlsx
+++ b/XL-Int.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\foolu\Workspace\Excel\BigInt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E87F10-6374-4B7D-A550-271D240B70DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3CD98F-A623-483E-B1D6-2DA9C96CBDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{36490472-0618-4E80-9469-F609392FABC8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24610" windowHeight="21000" xr2:uid="{36490472-0618-4E80-9469-F609392FABC8}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <definedName name="BigInt.Compare" comment="Compares two BigInt strings. Returns 1 (a &gt; b), -1 (a &lt; b), or 0 (a = b)._x000a_Evaluates signs and lengths. If identical, delegates to native limb array comparison._x000a_@param big_int_a The first BigInt string._x000a_@param big_int_b The second BigInt string.">_xlfn.LAMBDA(_xlpm.big_int_a,_xlpm.big_int_b, _xlfn.LET(_xlpm.norm_a, BigInt.Norm(_xlpm.big_int_a), _xlpm.norm_b, BigInt.Norm(_xlpm.big_int_b), _xlpm.sign_a, BigInt.Sign(_xlpm.norm_a), _xlpm.sign_b, BigInt.Sign(_xlpm.norm_b), IF(_xlpm.sign_a &lt;&gt; _xlpm.sign_b, SIGN(_xlpm.sign_a - _xlpm.sign_b), IF(_xlpm.sign_a = 0, 0, _xlfn.LET(_xlpm.len_a, LEN(_xlpm.norm_a), _xlpm.len_b, LEN(_xlpm.norm_b), IF(_xlpm.len_a &lt;&gt; _xlpm.len_b, SIGN(_xlpm.len_a - _xlpm.len_b) * _xlpm.sign_a, _xlfn.LET(_xlpm.k, core_BigInt.SafeK("ADD"), _xlpm.limbs_a, core_BigInt.Split(BigInt.Abs(_xlpm.norm_a), _xlpm.k), _xlpm.limbs_b, core_BigInt.Split(BigInt.Abs(_xlpm.norm_b), _xlpm.k), _xlpm.mag_comparison, core_BigInt.UCompare(_xlpm.limbs_a, _xlpm.limbs_b), _xlpm.mag_comparison * _xlpm.sign_a)))))))</definedName>
     <definedName name="BigInt.Div" comment="Divides the first BigInt by the second (A / B). _x000a_@param big_int_a The dividend BigInt string._x000a_@param big_int_b The divisor BigInt string._x000a_@param [use_floor] Optional boolean. TRUE for Python-style Floor division. Defaults to FALSE.">_xlfn.LAMBDA(_xlpm.big_int_a,_xlpm.big_int_b,_xlop.use_floor, INDEX(BigInt.DivMod(_xlpm.big_int_a, _xlpm.big_int_b, _xlpm.use_floor), 1, 1))</definedName>
     <definedName name="BigInt.DivMod" comment="Divides the first BigInt by the second (A / B). _x000a_Returns the quotient and modulus in rows 1 and 2, respectively._x000a_@param big_int_a The dividend BigInt string._x000a_@param big_int_b The divisor BigInt string._x000a_@param [use_floor] Optional boolean. TRUE for Python-">_xlfn.LAMBDA(_xlpm.big_int_a,_xlpm.big_int_b,_xlop.use_floor, _xlfn.LET(_xlpm.norm_a, BigInt.Norm(_xlpm.big_int_a), _xlpm.norm_b, BigInt.Norm(_xlpm.big_int_b), _xlpm.sign_a, BigInt.Sign(_xlpm.norm_a), _xlpm.sign_b, BigInt.Sign(_xlpm.norm_b), _xlpm.is_floor, IF(_xlfn.ISOMITTED(_xlpm.use_floor), FALSE, _xlpm.use_floor), IF(_xlpm.sign_b = 0, #DIV/0!, IF(_xlpm.sign_a = 0, {"0";"0"}, _xlfn.LET(_xlpm.k, core_BigInt.SafeK("DIV"), _xlpm.limbs_a, core_BigInt.Split(BigInt.Abs(_xlpm.norm_a), _xlpm.k), _xlpm.limbs_b, core_BigInt.Split(BigInt.Abs(_xlpm.norm_b), _xlpm.k), _xlpm.packed_result, core_BigInt.DivRouter(_xlpm.limbs_a, _xlpm.limbs_b, _xlpm.k), _xlpm.len_r, INDEX(_xlpm.packed_result, 1, 1), _xlpm.rem_limbs, _xlfn.CHOOSEROWS(_xlpm.packed_result, _xlfn.SEQUENCE(_xlpm.len_r, 1, 2)), _xlpm.quot_limbs, _xlfn.DROP(_xlpm.packed_result, _xlpm.len_r + 1), _xlpm.final_sign, _xlpm.sign_a * _xlpm.sign_b, _xlpm.merged_q, core_BigInt.Merge(_xlpm.quot_limbs, _xlpm.k), _xlpm.merged_r, core_BigInt.Merge(_xlpm.rem_limbs, _xlpm.k), _xlpm.trunc_q, IF(AND(_xlpm.final_sign = -1, _xlpm.merged_q &lt;&gt; "0"), "-" &amp; _xlpm.merged_q, _xlpm.merged_q), _xlpm.trunc_r, IF(AND(_xlpm.sign_a = -1, _xlpm.merged_r &lt;&gt; "0"), "-" &amp; _xlpm.merged_r, _xlpm.merged_r), _xlpm.needs_correction, AND(_xlpm.is_floor, _xlpm.final_sign = -1, _xlpm.merged_r &lt;&gt; "0"), _xlpm.final_q, IF(_xlpm.needs_correction, BigInt.Sub(_xlpm.trunc_q, "1"), _xlpm.trunc_q), _xlpm.final_r, IF(_xlpm.needs_correction, BigInt.Add(_xlpm.trunc_r, _xlpm.norm_b), _xlpm.trunc_r), _xlfn.VSTACK(_xlpm.final_q, _xlpm.final_r))))))</definedName>
+    <definedName name="BigInt.Fact" comment="Computes the factorial of a BigInt (n!)._x000a_Utilizes Legendre's formula and logarithmic tree multiplication to bypass stack/memory limits._x000a_@param big_int The BigInt string. Maximum supported input is 9273.">_xlfn.LAMBDA(_xlpm.big_int, _xlfn.LET(_xlpm.norm_n, BigInt.Norm(_xlpm.big_int), _xlpm.sign_n, BigInt.Sign(_xlpm.norm_n), IF(_xlpm.sign_n = -1, #NUM!, IF(_xlpm.norm_n = "0", "1", IF(_xlpm.norm_n = "1", "1", IF(LEN(_xlpm.norm_n) &gt; 4, #NUM!, IF(VALUE(_xlpm.norm_n) &gt; 9273, #NUM!, _xlfn.LET(_xlpm.n_val, VALUE(_xlpm.norm_n), _xlpm.primes, core_BigInt.NativePrimes(_xlpm.n_val), _xlpm.exponents, core_BigInt.NativeLegendre(_xlpm.n_val, _xlpm.primes), _xlpm.prime_powers, _xlfn.MAP(_xlpm.primes, _xlpm.exponents, _xlfn.LAMBDA(_xlpm.p,_xlpm.e, BigInt.Pow(_xlpm.p &amp; "", _xlpm.e &amp; ""))), core_BigInt.TextTreeProd(_xlpm.prime_powers)))))))))</definedName>
     <definedName name="BigInt.IsEven" comment="Returns TRUE if the BigInt is even._x000a_@param big_int The BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, ISEVEN(VALUE(RIGHT(BigInt.Norm(_xlpm.big_int)))))</definedName>
     <definedName name="BigInt.IsNeg" comment="Returns TRUE if the BigInt is negative._x000a_@param big_int The BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, LEFT(BigInt.Norm(_xlpm.big_int)) = "-")</definedName>
     <definedName name="BigInt.IsOdd" comment="Returns TRUE if the BigInt is odd._x000a_@param big_int The BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, ISODD(VALUE(RIGHT(BigInt.Norm(_xlpm.big_int)))))</definedName>
@@ -43,11 +44,14 @@
     <definedName name="core_BigInt.FindQuotientLimb" comment=" * [Internal] Binary search to find the highest scalar quotient limb q (0 &lt;= q &lt; 10^k)_x000a_ * such that B * q &lt;= acc. Eliminates the need for Knuth D float-estimation._x000a_ * @param acc The current remainder array._x000a_ * @param b The divisor array._x000a_ * @param k The d">_xlfn.LAMBDA(_xlpm.acc,_xlpm.b,_xlpm.k, _xlfn.LET(_xlpm.bits, _xlfn.CEILING.MATH(LOG(10 ^ _xlpm.k, 2)), _xlpm.powers, 2 ^ _xlfn.SEQUENCE(_xlpm.bits, 1, _xlpm.bits - 1, -1), _xlfn.REDUCE(0, _xlpm.powers, _xlfn.LAMBDA(_xlpm.curr_q,_xlpm.power, _xlfn.LET(_xlpm.test_q, _xlpm.curr_q + _xlpm.power, IF(_xlpm.test_q &gt;= 10 ^ _xlpm.k, _xlpm.curr_q, _xlfn.LET(_xlpm.test_prod, core_BigInt.Carry(_xlpm.b * _xlpm.test_q, _xlpm.k), _xlpm.comp, core_BigInt.UCompare(_xlpm.acc, _xlpm.test_prod), IF(_xlpm.comp &gt;= 0, _xlpm.test_q, _xlpm.curr_q))))))))</definedName>
     <definedName name="core_BigInt.KnuthDiv" comment=" * [Internal] Basecase Division via sequential shift-and-subtract._x000a_ * Returns a packed 1D array: VSTACK(Length_R, R_limbs, Q_limbs)._x000a_ * Eliminates 2D array padding to strictly preserve memory efficiency._x000a_ * @param limbs_a The dividend array._x000a_ * @param lim">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.mag_comp, core_BigInt.UCompare(_xlpm.limbs_a, _xlpm.limbs_b), IF(_xlpm.mag_comp &lt; 0, _xlfn.VSTACK(ROWS(_xlpm.limbs_a), _xlpm.limbs_a, 0), IF(_xlpm.mag_comp = 0, _xlfn.VSTACK(1, 0, 1), _xlfn.LET(_xlpm.len_a, ROWS(_xlpm.limbs_a), _xlpm.reversed_a, _xlfn.CHOOSEROWS(_xlpm.limbs_a, _xlfn.SEQUENCE(_xlpm.len_a, 1, _xlpm.len_a, -1)), _xlpm.initial_state, _xlfn.VSTACK(1, 0, 0), _xlpm.final_state, _xlfn.REDUCE(_xlpm.initial_state, _xlpm.reversed_a, _xlfn.LAMBDA(_xlpm.state,_xlpm.val, _xlfn.LET(_xlpm.len_remainder, INDEX(_xlpm.state, 1, 1), _xlpm.remainder, _xlfn.CHOOSEROWS(_xlpm.state, _xlfn.SEQUENCE(_xlpm.len_remainder, 1, 2)), _xlpm.quotient, _xlfn.DROP(_xlpm.state, _xlpm.len_remainder + 1), _xlpm.extended_remainder, IF(AND(ROWS(_xlpm.remainder) = 1, INDEX(_xlpm.remainder, 1, 1) = 0), _xlpm.val, _xlfn.VSTACK(_xlpm.val, _xlpm.remainder)), _xlpm.next_quotient_limb, core_BigInt.FindQuotientLimb(_xlpm.extended_remainder, _xlpm.limbs_b, _xlpm.k), _xlpm.prod, core_BigInt.Carry(_xlpm.limbs_b * _xlpm.next_quotient_limb, _xlpm.k), _xlpm.new_remainder, core_BigInt.USub(_xlpm.extended_remainder, _xlpm.prod, _xlpm.k), _xlpm.has_quotient, OR(ROWS(_xlpm.quotient) &gt; 1, INDEX(_xlpm.quotient, 1, 1) &gt; 0), _xlpm.next_quot, IF(_xlpm.has_quotient, _xlfn.VSTACK(_xlpm.quotient, _xlpm.next_quotient_limb), _xlpm.next_quotient_limb), _xlfn.VSTACK(ROWS(_xlpm.new_remainder), _xlpm.new_remainder, _xlpm.next_quot)))), _xlpm.len_remainder, INDEX(_xlpm.final_state, 1, 1), _xlpm.remainder, _xlfn.CHOOSEROWS(_xlpm.final_state, _xlfn.SEQUENCE(_xlpm.len_remainder, 1, 2)), _xlpm.reversed_quotient, _xlfn.DROP(_xlpm.final_state, _xlpm.len_remainder + 1), _xlpm.len_quotient, ROWS(_xlpm.reversed_quotient), _xlpm.quotient, _xlfn.CHOOSEROWS(_xlpm.reversed_quotient, _xlfn.SEQUENCE(_xlpm.len_quotient, 1, _xlpm.len_quotient, -1)), _xlfn.VSTACK(_xlpm.len_remainder, _xlpm.remainder, _xlpm.quotient))))))</definedName>
     <definedName name="core_BigInt.Merge" comment="[Internal] Concatenates an array of numeric limbs into a BigInt string, zero-padding all but the first limb._x000a_@param limbs The vertical array of numeric limbs._x000a_@param k The limb size used during calculation.">_xlfn.LAMBDA(_xlpm.limbs,_xlpm.k, _xlfn.LET(_xlpm.num_limbs, ROWS(_xlpm.limbs), _xlpm.rev_limbs, _xlfn.CHOOSEROWS(_xlpm.limbs, _xlfn.SEQUENCE(_xlpm.num_limbs, 1, _xlpm.num_limbs, -1)), IF(_xlpm.num_limbs = 1, _xlpm.rev_limbs &amp; "", _xlfn.CONCAT(_xlfn.VSTACK(_xlfn.TAKE(_xlpm.rev_limbs, 1) &amp; "", TEXT(_xlfn.DROP(_xlpm.rev_limbs, 1), REPT("0", _xlpm.k)))))))</definedName>
+    <definedName name="core_BigInt.NativeLegendre" comment="[Internal] Calculates the exponent for an array of prime numbers natively using Legendre's Formula._x000a_Evaluates purely in native C++ with zero BigInt overhead._x000a_@param n The integer factorial base (&lt;= 9273)._x000a_@param primes A vertical array of prime numbers (&lt;">_xlfn.LAMBDA(_xlpm.n,_xlpm.primes, _xlfn.MAP(_xlpm.primes, _xlfn.LAMBDA(_xlpm.p, _xlfn.LET(_xlpm.max_k, INT(LOG(_xlpm.n, _xlpm.p)), _xlpm.powers, _xlpm.p ^ _xlfn.SEQUENCE(_xlpm.max_k), SUM(INT(_xlpm.n / _xlpm.powers))))))</definedName>
+    <definedName name="core_BigInt.NativePrimes" comment="[Internal] Generates a 1D vertical array of all prime numbers up to n._x000a_Evaluates purely in native C++ using a dynamic sieve._x000a_@param n The upper bound integer (assumed &lt;= 9273).">_xlfn.LAMBDA(_xlpm.n, IF(_xlpm.n &lt; 2, #NUM!, _xlfn.LET(_xlpm.seq, _xlfn.SEQUENCE(_xlpm.n - 1, 1, 2), _xlfn._xlws.FILTER(_xlpm.seq, _xlfn.MAP(_xlpm.seq, _xlfn.LAMBDA(_xlpm.x, _xlfn.LET(_xlpm.limit, INT(SQRT(_xlpm.x)), IF(_xlpm.limit &lt; 2, TRUE, MIN(MOD(_xlpm.x, _xlfn.SEQUENCE(_xlpm.limit - 1, 1, 2))) &gt; 0))))))))</definedName>
     <definedName name="core_BigInt.NewtonRaphsonDiv" comment="[Internal] Heavyweight Newton-Raphson Division._x000a_Implements progressive scaling bounded to MAX(len_a, len_b)._x000a_@param limbs_a The dividend array._x000a_@param limbs_b The divisor array._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.len_a, ROWS(_xlpm.limbs_a), _xlpm.len_b, ROWS(_xlpm.limbs_b), _xlpm.target_len, MAX(_xlpm.len_a, _xlpm.len_b), _xlpm.r, core_BigInt.NewtonRaphsonReciprocal(_xlpm.limbs_b, _xlpm.target_len, _xlpm.k), _xlpm.drop_limbs, 2 * _xlpm.target_len, _xlpm.q_unscaled, core_BigInt.UMul(_xlpm.limbs_a, _xlpm.r, _xlpm.k), _xlpm.q_approx, IF(ROWS(_xlpm.q_unscaled) &lt;= _xlpm.drop_limbs, {0}, _xlfn.DROP(_xlpm.q_unscaled, _xlpm.drop_limbs)), _xlpm.p_baseline, core_BigInt.UMul(_xlpm.limbs_b, _xlpm.q_approx, _xlpm.k), _xlpm.initial_state, _xlfn.VSTACK(ROWS(_xlpm.q_approx), _xlpm.q_approx, _xlpm.p_baseline), _xlpm.sweep_down, _xlfn.REDUCE(_xlpm.initial_state, {1;2}, _xlfn.LAMBDA(_xlpm.state,_xlpm.i, _xlfn.LET(_xlpm.len_q, INDEX(_xlpm.state, 1, 1), _xlpm.curr_q, _xlfn.CHOOSEROWS(_xlpm.state, _xlfn.SEQUENCE(_xlpm.len_q, 1, 2)), _xlpm.curr_p, _xlfn.DROP(_xlpm.state, _xlpm.len_q + 1), IF(core_BigInt.UCompare(_xlpm.curr_p, _xlpm.limbs_a) &gt; 0, _xlfn.LET(_xlpm.next_q, core_BigInt.USub(_xlpm.curr_q, {1}, _xlpm.k), _xlpm.next_p, core_BigInt.USub(_xlpm.curr_p, _xlpm.limbs_b, _xlpm.k), _xlfn.VSTACK(ROWS(_xlpm.next_q), _xlpm.next_q, _xlpm.next_p)), _xlpm.state)))), _xlpm.sweep_up, _xlfn.REDUCE(_xlpm.sweep_down, {1;2}, _xlfn.LAMBDA(_xlpm.state,_xlpm.i, _xlfn.LET(_xlpm.len_q, INDEX(_xlpm.state, 1, 1), _xlpm.curr_q, _xlfn.CHOOSEROWS(_xlpm.state, _xlfn.SEQUENCE(_xlpm.len_q, 1, 2)), _xlpm.curr_p, _xlfn.DROP(_xlpm.state, _xlpm.len_q + 1), _xlpm.next_p_test, core_BigInt.UAdd(_xlpm.curr_p, _xlpm.limbs_b, _xlpm.k), IF(core_BigInt.UCompare(_xlpm.next_p_test, _xlpm.limbs_a) &lt;= 0, _xlfn.LET(_xlpm.next_q, core_BigInt.UAdd(_xlpm.curr_q, {1}, _xlpm.k), _xlfn.VSTACK(ROWS(_xlpm.next_q), _xlpm.next_q, _xlpm.next_p_test)), _xlpm.state)))), _xlpm.final_len_q, INDEX(_xlpm.sweep_up, 1, 1), _xlpm.final_q, _xlfn.CHOOSEROWS(_xlpm.sweep_up, _xlfn.SEQUENCE(_xlpm.final_len_q, 1, 2)), _xlpm.final_p, _xlfn.DROP(_xlpm.sweep_up, _xlpm.final_len_q + 1), _xlpm.final_r, core_BigInt.USub(_xlpm.limbs_a, _xlpm.final_p, _xlpm.k), _xlfn.VSTACK(ROWS(_xlpm.final_r), _xlpm.final_r, _xlpm.final_q)))</definedName>
     <definedName name="core_BigInt.NewtonRaphsonReciprocal" comment="[Internal] Computes the Reciprocal progressively scaling up to the Dividend's precision._x000a_@param limbs_b The divisor limb array._x000a_@param target_len The limb-length of Dividend A._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.limbs_b,_xlpm.target_len,_xlpm.k, _xlfn.LET(_xlpm.len_b, ROWS(_xlpm.limbs_b), _xlpm.seed_len, MIN(3, _xlpm.len_b), _xlpm.r_seed_limbs, core_BigInt.NewtonRaphsonSeed(_xlpm.limbs_b, _xlpm.k), _xlpm.initial_state, _xlfn.VSTACK(_xlpm.seed_len, _xlpm.r_seed_limbs), _xlpm.req_iters, MAX(0, _xlfn.CEILING.MATH(LN(_xlpm.target_len / _xlpm.seed_len) / LN(2))) + 1, IF(_xlpm.req_iters = 0, _xlpm.r_seed_limbs, _xlfn.LET(_xlpm.iterations, _xlfn.SEQUENCE(_xlpm.req_iters), _xlpm.final_state, _xlfn.REDUCE(_xlpm.initial_state, _xlpm.iterations, _xlfn.LAMBDA(_xlpm.state,_xlpm.iter, _xlfn.LET(_xlpm.curr_len, INDEX(_xlpm.state, 1, 1), _xlpm.curr_r, _xlfn.DROP(_xlpm.state, 1), _xlpm.next_len, MIN(_xlpm.curr_len * 2, _xlpm.target_len), _xlpm.active_curr, MIN(_xlpm.curr_len, _xlpm.len_b), _xlpm.active_next, MIN(_xlpm.next_len, _xlpm.len_b), _xlpm.shift_limbs, 2 * (_xlpm.next_len - _xlpm.curr_len) - (_xlpm.active_next - _xlpm.active_curr), _xlpm.r_prime, IF(_xlpm.shift_limbs &gt; 0, _xlfn.VSTACK(_xlfn.EXPAND(0, _xlpm.shift_limbs, , 0), _xlpm.curr_r), _xlpm.curr_r), _xlpm.b_active, _xlfn.TAKE(_xlpm.limbs_b, -_xlpm.active_next), _xlpm.p, core_BigInt.UMul(_xlpm.b_active, _xlpm.r_prime, _xlpm.k), _xlpm.two_beta, _xlfn.VSTACK(_xlfn.EXPAND(0, 2 * _xlpm.next_len, , 0), 2), _xlpm.err, core_BigInt.USub(_xlpm.two_beta, _xlpm.p, _xlpm.k), _xlpm.next_r_unscaled, core_BigInt.UMul(_xlpm.r_prime, _xlpm.err, _xlpm.k), _xlpm.next_r, IF(ROWS(_xlpm.next_r_unscaled) &lt;= 2 * _xlpm.next_len, {0}, _xlfn.DROP(_xlpm.next_r_unscaled, 2 * _xlpm.next_len)), _xlfn.VSTACK(_xlpm.next_len, _xlpm.next_r)))), _xlfn.DROP(_xlpm.final_state, 1)))))</definedName>
     <definedName name="core_BigInt.NewtonRaphsonSeed" comment="[Internal] Generates the exact reciprocal seed for Newton-Raphson Division using Knuth Basecase._x000a_Extracts up to the top 3 limbs of B and calculates floor(Beta^(2*len) / B_top)._x000a_@param limbs_b The divisor limb array._x000a_@param k The dynamic chunk size context">_xlfn.LAMBDA(_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.len_b, ROWS(_xlpm.limbs_b), _xlpm.seed_len, MIN(3, _xlpm.len_b), _xlpm.b_top, _xlfn.TAKE(_xlpm.limbs_b, -_xlpm.seed_len), _xlpm.beta_2m, _xlfn.VSTACK(_xlfn.EXPAND(0, 2 * _xlpm.seed_len, , 0), 1), _xlpm.packed, core_BigInt.KnuthDiv(_xlpm.beta_2m, _xlpm.b_top, _xlpm.k), _xlpm.len_r, INDEX(_xlpm.packed, 1, 1), _xlfn.DROP(_xlpm.packed, _xlpm.len_r + 1)))</definedName>
     <definedName name="core_BigInt.SafeK" comment="[Internal] Computes the maximum safe base-10 limb size (k) to avoid IEEE-754 precision loss._x000a_@param operation: &quot;ADD&quot;, &quot;MUL&quot;, or &quot;DIV&quot;._x000a_@param [max_items] ADD: number of operands. MUL: shortest string digits count.">_xlfn.LAMBDA(_xlpm.operation,_xlop.max_items, _xlfn.LET(_xlpm.items, IF(OR(_xlpm.max_items = "", _xlfn.ISOMITTED(_xlpm.max_items)), 2, MAX(2, _xlpm.max_items)), _xlfn.SWITCH(_xlpm.operation, "ADD", 15 - LEN(_xlpm.items), "MUL", _xlfn.LET(_xlpm.test_k, {7;6;5;4;3;2;1}, _xlpm.max_overlap, ROUNDUP(_xlpm.items / _xlpm.test_k, 0), _xlpm.uncarried_max, _xlpm.max_overlap * (10 ^ _xlpm.test_k - 1) ^ 2, _xlpm.max_carry, INT(_xlpm.uncarried_max / 10 ^ _xlpm.test_k), _xlpm.peak_val, _xlpm.uncarried_max + _xlpm.max_carry, MAX(_xlfn._xlws.FILTER(_xlpm.test_k, _xlpm.peak_val &lt;= (10 ^ 15 - 1)))), "DIV", 7, #NAME?)))</definedName>
     <definedName name="core_BigInt.Split" comment="[Internal] Unified Splitter. Splits both scalars and arrays into Little-Endian limbs._x000a_Uses MAX() to guarantee scalar inputs to the SEQUENCE engine._x000a_@param big_ints The string or array of strings._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.big_ints,_xlpm.k, _xlfn.LET(_xlpm.big_int_row, _xlfn.TOROW(_xlpm.big_ints), _xlpm.lengths, LEN(_xlpm.big_int_row), _xlpm.max_len, MAX(_xlpm.lengths), _xlpm.pad_len, ROUNDUP(_xlpm.max_len / _xlpm.k, 0) * _xlpm.k, _xlpm.padded, REPT("0", _xlpm.pad_len - _xlpm.lengths) &amp; _xlpm.big_int_row, _xlpm.starts, _xlfn.SEQUENCE(_xlpm.pad_len / _xlpm.k, 1, _xlpm.pad_len - _xlpm.k + 1, -_xlpm.k), --MID(_xlpm.padded, _xlpm.starts, _xlpm.k)))</definedName>
+    <definedName name="core_BigInt.TextTreeProd" comment="[Internal] Vectorized logarithmic product of an array of BigInt strings._x000a_Recursively cuts the array in half to bypass REDUCE sequential memory allocations._x000a_@param text_arr A 1D vertical array of BigInt strings.">_xlfn.LAMBDA(_xlpm.text_arr, _xlfn.LET(_xlpm.n, ROWS(_xlpm.text_arr), IF(_xlpm.n = 1, INDEX(_xlpm.text_arr, 1, 1), _xlfn.LET(_xlpm.paired, _xlfn.WRAPROWS(_xlpm.text_arr, 2, "1"), _xlpm.next_arr, _xlfn.BYROW(_xlpm.paired, _xlfn.LAMBDA(_xlpm.row, core_BigInt.UTextMul(INDEX(_xlpm.row, 1, 1), INDEX(_xlpm.row, 1, 2)))), core_BigInt.TextTreeProd(_xlpm.next_arr)))))</definedName>
     <definedName name="core_BigInt.UAdd" comment="[Internal] Unsigned addition of two Little-Endian limb arrays._x000a_@param limbs_a The first limb array._x000a_@param limbs_b The second limb array._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.a,_xlpm.b,_xlpm.k, _xlfn.LET(_xlpm.max_rows, MAX(ROWS(_xlpm.a), ROWS(_xlpm.b)), _xlpm.pad_a, _xlfn.EXPAND(_xlpm.a, _xlpm.max_rows, 1, 0), _xlpm.pad_b, _xlfn.EXPAND(_xlpm.b, _xlpm.max_rows, 1, 0), core_BigInt.Carry(_xlpm.pad_a + _xlpm.pad_b, _xlpm.k)))</definedName>
     <definedName name="core_BigInt.UCompare" comment="[Internal] Unsigned comparison of two Little-Endian limb arrays._x000a_Returns 1 (a &gt; b), -1 (a &lt; b), or 0 (a = b)._x000a_@param limbs_a The first limb array._x000a_@param limbs_b The second limb array.">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b, _xlfn.LET(_xlpm.max_rows, MAX(ROWS(_xlpm.limbs_a), ROWS(_xlpm.limbs_b)), _xlpm.pad_a, _xlfn.EXPAND(_xlpm.limbs_a, _xlpm.max_rows, 1, 0), _xlpm.pad_b, _xlfn.EXPAND(_xlpm.limbs_b, _xlpm.max_rows, 1, 0), _xlpm.diff, _xlpm.pad_a - _xlpm.pad_b, _xlpm.msd_idx, _xlfn.XMATCH(TRUE, _xlpm.diff &lt;&gt; 0, 0, -1), IF(ISNA(_xlpm.msd_idx), 0, SIGN(INDEX(_xlpm.diff, _xlpm.msd_idx, 1)))))</definedName>
     <definedName name="core_BigInt.UMatrixSum" comment="[Internal] Vectorized matrix sum of unsigned BigInt strings._x000a_@param ubig_int Horizontal array (1xN) of normalized magnitude strings._x000a_@param k The unified dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.ubig_ints,_xlpm.k, _xlfn.LET(_xlpm.grid, core_BigInt.Split(_xlpm.ubig_ints, _xlpm.k), _xlpm.raw_limbs, _xlfn.BYROW(_xlpm.grid, _xleta.SUM), core_BigInt.Carry(_xlpm.raw_limbs, _xlpm.k)))</definedName>
@@ -55,6 +59,7 @@
     <definedName name="core_BigInt.UPow" comment="[Internal] Unsigned Base-10 Left-to-Right Exponentiation._x000a_Evaluates the exponent iteratively using a pre-computed 1-9 cache._x000a_@param limbs_base The little-endian limb array of the base._x000a_@param exp_string The exact text string of the exponent._x000a_@param k The ">_xlfn.LAMBDA(_xlpm.limbs_base,_xlpm.exp_string,_xlpm.k, _xlfn.LET(_xlpm.first, _xlpm.limbs_base, _xlpm.second, core_BigInt.UMul(_xlpm.first, _xlpm.first, _xlpm.k), _xlpm.third, core_BigInt.UMul(_xlpm.second, _xlpm.first, _xlpm.k), _xlpm.fourth, core_BigInt.UMul(_xlpm.second, _xlpm.second, _xlpm.k), _xlpm.fifth, core_BigInt.UMul(_xlpm.fourth, _xlpm.first, _xlpm.k), _xlpm.sixth, core_BigInt.UMul(_xlpm.third, _xlpm.third, _xlpm.k), _xlpm.seventh, core_BigInt.UMul(_xlpm.sixth, _xlpm.first, _xlpm.k), _xlpm.eigth, core_BigInt.UMul(_xlpm.fourth, _xlpm.fourth, _xlpm.k), _xlpm.ninth, core_BigInt.UMul(_xlpm.eigth, _xlpm.first, _xlpm.k), _xlpm.exp_digits, --MID(_xlpm.exp_string, _xlfn.SEQUENCE(LEN(_xlpm.exp_string)), 1), _xlfn.REDUCE(1, _xlpm.exp_digits, _xlfn.LAMBDA(_xlpm.acc,_xlpm.digit, _xlfn.LET(_xlpm.is_one, AND(ROWS(_xlpm.acc) = 1, INDEX(_xlpm.acc, 1, 1) = 1), _xlpm.acc_10, IF(_xlpm.is_one, _xlpm.acc, _xlfn.LET(_xlpm.acc_2, core_BigInt.UMul(_xlpm.acc, _xlpm.acc, _xlpm.k), _xlpm.acc_4, core_BigInt.UMul(_xlpm.acc_2, _xlpm.acc_2, _xlpm.k), _xlpm.acc_8, core_BigInt.UMul(_xlpm.acc_4, _xlpm.acc_4, _xlpm.k), core_BigInt.UMul(_xlpm.acc_8, _xlpm.acc_2, _xlpm.k))), IF(_xlpm.digit = 0, _xlpm.acc_10, _xlfn.LET(_xlpm.cache_val, CHOOSE(_xlpm.digit, _xlpm.first, _xlpm.second, _xlpm.third, _xlpm.fourth, _xlpm.fifth, _xlpm.sixth, _xlpm.seventh, _xlpm.eigth, _xlpm.ninth), IF(_xlpm.is_one, _xlpm.cache_val, core_BigInt.UMul(_xlpm.acc_10, _xlpm.cache_val, _xlpm.k)))))))))</definedName>
     <definedName name="core_BigInt.USqrt" comment="[Internal] Unsigned Integer Square Root using Newton's Method._x000a_@param limbs_n Radicand little-endian array._x000a_@param limbs_seed Over-estimated little-endian seed array._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.limbs_n,_xlpm.limbs_seed,_xlpm.k, _xlfn.LET(_xlpm.initial_state, _xlfn.VSTACK(0, _xlpm.limbs_seed), _xlpm.max_iters, 35, _xlpm.final_state, _xlfn.REDUCE(_xlpm.initial_state, _xlfn.SEQUENCE(_xlpm.max_iters), _xlfn.LAMBDA(_xlpm.state,_xlpm.i, _xlfn.LET(_xlpm.is_done, INDEX(_xlpm.state, 1, 1), _xlpm.curr_x, _xlfn.DROP(_xlpm.state, 1), IF(_xlpm.is_done, _xlpm.state, _xlfn.LET(_xlpm.div_packed, core_BigInt.DivRouter(_xlpm.limbs_n, _xlpm.curr_x, _xlpm.k), _xlpm.len_r, INDEX(_xlpm.div_packed, 1, 1), _xlpm.q, _xlfn.DROP(_xlpm.div_packed, _xlpm.len_r + 1), _xlpm.sum_xq, core_BigInt.UAdd(_xlpm.curr_x, _xlpm.q, _xlpm.k), _xlpm.div_2_packed, core_BigInt.KnuthDiv(_xlpm.sum_xq, {2}, _xlpm.k), _xlpm.len_r2, INDEX(_xlpm.div_2_packed, 1, 1), _xlpm.x_next, _xlfn.DROP(_xlpm.div_2_packed, _xlpm.len_r2 + 1), _xlpm.comp, core_BigInt.UCompare(_xlpm.x_next, _xlpm.curr_x), IF(_xlpm.comp &gt;= 0, _xlfn.VSTACK(1, _xlpm.curr_x), _xlfn.VSTACK(0, _xlpm.x_next))))))), _xlfn.DROP(_xlpm.final_state, 1)))</definedName>
     <definedName name="core_BigInt.USub" comment="[Internal] Unsigned subtraction of two Little-Endian limb arrays._x000a_Assumes magnitudes A &gt;= B. Resolves borrows top-to-bottom and trims trailing zeros._x000a_@param limbs_a The minuend limb array (must be &gt;= limbs_b)._x000a_@param limbs_b The subtrahend limb array._x000a_@pa">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.max_rows, MAX(ROWS(_xlpm.limbs_a), ROWS(_xlpm.limbs_b)), _xlpm.pad_a, _xlfn.EXPAND(_xlpm.limbs_a, _xlpm.max_rows, 1, 0), _xlpm.pad_b, _xlfn.EXPAND(_xlpm.limbs_b, _xlpm.max_rows, 1, 0), _xlpm.diff, _xlpm.pad_a - _xlpm.pad_b, _xlpm.resolved, core_BigInt.Carry(_xlpm.diff, _xlpm.k), _xlpm.msd_idx, _xlfn.XMATCH(TRUE, _xlpm.resolved &lt;&gt; 0, 0, -1), IF(ISNA(_xlpm.msd_idx), {0}, _xlfn.TAKE(_xlpm.resolved, _xlpm.msd_idx))))</definedName>
+    <definedName name="core_BigInt.UTextMul" comment="[Internal] Unsafe, high-performance text multiplication for trusted, positive BigInt strings._x000a_Bypasses Layer 0 validation. Implements strict short-circuits for padding optimization._x000a_@param str_a The first trusted BigInt string._x000a_@param str_b The second tru">_xlfn.LAMBDA(_xlpm.str_a,_xlpm.str_b, IF(OR(_xlpm.str_a = "0", _xlpm.str_b = "0"), "0", IF(_xlpm.str_a = "1", _xlpm.str_b, IF(_xlpm.str_b = "1", _xlpm.str_a, _xlfn.LET(_xlpm.len_a, LEN(_xlpm.str_a), _xlpm.len_b, LEN(_xlpm.str_b), _xlpm.k, core_BigInt.SafeK("MUL", MIN(_xlpm.len_a, _xlpm.len_b)), _xlpm.limbs_a, core_BigInt.Split(_xlpm.str_a, _xlpm.k), _xlpm.limbs_b, core_BigInt.Split(_xlpm.str_b, _xlpm.k), _xlpm.final_limbs, core_BigInt.UMul(_xlpm.limbs_a, _xlpm.limbs_b, _xlpm.k), core_BigInt.Merge(_xlpm.final_limbs, _xlpm.k))))))</definedName>
     <definedName name="test_BigInt.AsymmetricABGrid">_xlfn.LAMBDA(_xlpm.start_a,_xlpm.max_a,_xlpm.step_a,_xlpm.start_b,_xlpm.max_b,_xlpm.step_b, _xlfn.LET(_xlpm.seq_a, _xlfn.SEQUENCE((_xlpm.max_a - _xlpm.start_a) / _xlpm.step_a + 1, 1, _xlpm.start_a, _xlpm.step_a), _xlpm.seq_b, _xlfn.SEQUENCE((_xlpm.max_b - _xlpm.start_b) / _xlpm.step_b + 1, 1, _xlpm.start_b, _xlpm.step_b), _xlpm.n_a, ROWS(_xlpm.seq_a), _xlpm.n_b, ROWS(_xlpm.seq_b), _xlpm.col_a, _xlfn.TOCOL(IF(_xlfn.SEQUENCE(1, _xlpm.n_b), _xlpm.seq_a)), _xlpm.col_b, _xlfn.TOCOL(IF(_xlfn.SEQUENCE(_xlpm.n_a), _xlfn.TOROW(_xlpm.seq_b))), _xlfn.HSTACK(_xlpm.col_a, _xlpm.col_b)))</definedName>
     <definedName name="test_BigInt.DivisionAlgorithmComparison" comment="Executes a strictly sequential benchmark suite to avoid multi-threading contamination._x000a_@param test_cases An N x 2 array of test lengths: [Length_A, Length_B]_x000a_@param iters Number of iterations per benchmark to smooth NOW() resolution.">_xlfn.LAMBDA(_xlpm.test_cases,_xlpm.iters,_xlpm.repeats, _xlfn.LET(_xlpm.n_tests, ROWS(_xlpm.test_cases), _xlpm.initial, {"Len_A","Len_B","Knuth_ms","NR_ms"}, _xlfn.REDUCE(_xlpm.initial, _xlfn.SEQUENCE(_xlpm.n_tests), _xlfn.LAMBDA(_xlpm.acc,_xlpm.i, _xlfn.LET(_xlpm.len_a, INDEX(_xlpm.test_cases, _xlpm.i, 1), _xlpm.len_b, INDEX(_xlpm.test_cases, _xlpm.i, 2), IF(_xlpm.len_b &gt; _xlpm.len_a, _xlpm.acc, _xlfn.LET(_xlpm.str_a, REPT("9", _xlpm.len_a), _xlpm.str_b, IF(_xlpm.len_b = 1, "7", "7" &amp; REPT("3", _xlpm.len_b - 1)), _xlpm.time_k, test_BigInt.DivisionAlgorithms(_xlpm.str_a, _xlpm.str_b, "KNUTH", _xlpm.iters, _xlpm.repeats), _xlpm.time_nr, test_BigInt.DivisionAlgorithms(_xlpm.str_a, _xlpm.str_b, "NR", _xlpm.iters, _xlpm.repeats), _xlfn.VSTACK(_xlpm.acc, _xlfn.HSTACK(_xlpm.len_a, _xlpm.len_b, _xlpm.time_k, _xlpm.time_nr)))))))))</definedName>
     <definedName name="test_BigInt.DivisionAlgorithms" comment="@param a The dividend string_x000a_@param b The divisor string_x000a_@param mode &quot;KNUTH&quot; or &quot;NR&quot;_x000a_@param iters Inner loop count (to defeat chunky clock resolution)_x000a_@param repeats Outer loop count (to defeat OS/Garbage Collection noise)">_xlfn.LAMBDA(_xlpm.a,_xlpm.b,_xlpm.mode,_xlpm.iters,_xlpm.repeats, _xlfn.LET(_xlpm.batch_times, _xlfn.MAP(_xlfn.SEQUENCE(_xlpm.repeats), _xlfn.LAMBDA(_xlpm.r, _xlfn.LET(_xlpm.start, NOW(), _xlpm.run, IF(_xlpm.mode = "KNUTH", _xlfn.MAP(_xlfn.SEQUENCE(_xlpm.iters), _xlfn.LAMBDA(_xlpm.i, test_BigInt.KnuthDivision(_xlpm.a, _xlpm.b))), _xlfn.MAP(_xlfn.SEQUENCE(_xlpm.iters), _xlfn.LAMBDA(_xlpm.i, test_BigInt.NewtonRaphsonDivision(_xlpm.a, _xlpm.b)))), _xlpm.stop, NOW() + (0 * LEN(INDEX(_xlpm.run, 1, 1))), (_xlpm.stop - _xlpm.start) * 86400000))), MIN(_xlpm.batch_times) / _xlpm.iters))</definedName>
@@ -127,18 +132,18 @@
   <pythonScripts>
     <pythonScript>
       <code>import sys
-from math import isqrt
+from math import factorial
 sys.set_int_max_str_digits(32766)
 a = int(xl(%P2%))
 b = int(xl(%P3%))
-str(isqrt(a))</code>
+str(factorial(a))</code>
     </pythonScript>
   </pythonScripts>
 </python>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="623">
   <si>
     <t>12345</t>
   </si>
@@ -7112,6 +7117,405 @@
     <t>n={4567890;7890123;123456}
 seed={3641830; 351}
 k=7</t>
+  </si>
+  <si>
+    <t>{2;3;5;7}</t>
+  </si>
+  <si>
+    <t>{2;3;5;7;11;13;17;19}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Minimum: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Smallest prime boundary</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> small sequence</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Standard: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Larger sequence verification</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Invalid:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Below mathematical minimum trap</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Invalid: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Zero bounds trap</t>
+    </r>
+  </si>
+  <si>
+    <t>Smallest boundary</t>
+  </si>
+  <si>
+    <t>core_BigInt.NativePrimes</t>
+  </si>
+  <si>
+    <t>{8;4;2;1}</t>
+  </si>
+  <si>
+    <t>{3;1;1}</t>
+  </si>
+  <si>
+    <t>n=10
+primes={2; 3; 5; 7}</t>
+  </si>
+  <si>
+    <t>n=2
+primes={2}</t>
+  </si>
+  <si>
+    <t>n=5
+primes={2; 3; 5}</t>
+  </si>
+  <si>
+    <t>Larger multi-power sequence (10! = 2^8 × 3^4 × 5^2 × 7^1)</t>
+  </si>
+  <si>
+    <t>Standard small boundary (5! = 2^3 × 3^1 × 5^1)</t>
+  </si>
+  <si>
+    <t>core_BigInt.NativeLegendre</t>
+  </si>
+  <si>
+    <t>core_BigInt.TextTreeProd</t>
+  </si>
+  <si>
+    <t>{5}</t>
+  </si>
+  <si>
+    <t>{2;3}</t>
+  </si>
+  <si>
+    <t>{2;3;4}</t>
+  </si>
+  <si>
+    <t>{2;3;4;5}</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Even Elements:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> folds two items.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Odd Elements:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> folds three items by padding with a fourth.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Multi-Tier:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> folding four items.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Base:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bypasses one item.</t>
+    </r>
+  </si>
+  <si>
+    <t>core_BigInt.UTextMul</t>
+  </si>
+  <si>
+    <t>a=123456
+b=2</t>
+  </si>
+  <si>
+    <t>246912</t>
+  </si>
+  <si>
+    <t>a=1000
+b=1000</t>
+  </si>
+  <si>
+    <t>1000000</t>
+  </si>
+  <si>
+    <t>a=0
+b=123456789</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> boundary max check.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Magnitude Discrepancy:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Negative * positive is negative.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Shift/Padding:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> limbs extend</t>
+    </r>
+  </si>
+  <si>
+    <t>Zero factorial identity</t>
+  </si>
+  <si>
+    <t>One factorial identity</t>
+  </si>
+  <si>
+    <t>Standard small factorial evaluation</t>
+  </si>
+  <si>
+    <t>Standard larger factorial evaluation</t>
+  </si>
+  <si>
+    <t>Trap negative integer inputs</t>
+  </si>
+  <si>
+    <t>Value bounds trap (Firewall 2)</t>
+  </si>
+  <si>
+    <t>String length bounds trap (Firewall 1)</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>3628800</t>
+  </si>
+  <si>
+    <t>-5</t>
+  </si>
+  <si>
+    <t>9274</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>BigInt.Fact</t>
   </si>
 </sst>
 </file>
@@ -7122,7 +7526,7 @@
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7233,13 +7637,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -7308,7 +7705,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -7349,10 +7746,16 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -7360,7 +7763,11 @@
     <cellStyle name="Input" xfId="1" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="254">
+  <dxfs count="297">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -7883,6 +8290,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -7892,12 +8309,99 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -7911,19 +8415,30 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -7937,7 +8452,29 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -7945,25 +8482,37 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -7980,7 +8529,64 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -8785,28 +9391,43 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMath>
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>𝐿𝑜𝑔𝑂𝑑𝑑𝑠</m:t>
                     </m:r>
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>=</m:t>
                     </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr>
+                          <a:rPr i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>𝑊</m:t>
                         </m:r>
                       </m:e>
                       <m:sub>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>𝑎</m:t>
                         </m:r>
                       </m:sub>
@@ -8814,41 +9435,59 @@
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr>
+                          <a:rPr i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:dPr>
                       <m:e>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>𝑙𝑒𝑛</m:t>
                         </m:r>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>_</m:t>
                         </m:r>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>𝑎</m:t>
                         </m:r>
                       </m:e>
                     </m:d>
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>+</m:t>
                     </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr>
+                          <a:rPr i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>𝑊</m:t>
                         </m:r>
                       </m:e>
                       <m:sub>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>𝑏</m:t>
                         </m:r>
                       </m:sub>
@@ -8856,27 +9495,42 @@
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr>
+                          <a:rPr i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:dPr>
                       <m:e>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>𝑙𝑒𝑛</m:t>
                         </m:r>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>_</m:t>
                         </m:r>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>𝑏</m:t>
                         </m:r>
                       </m:e>
                     </m:d>
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>+</m:t>
                     </m:r>
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>𝐼𝑛𝑡𝑒𝑟𝑐𝑒𝑝𝑡</m:t>
                     </m:r>
                   </m:oMath>
@@ -8997,60 +9651,87 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMath>
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>0.005791</m:t>
                     </m:r>
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr>
+                          <a:rPr i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:dPr>
                       <m:e>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>𝑙𝑒𝑛</m:t>
                         </m:r>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>_</m:t>
                         </m:r>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>𝑎</m:t>
                         </m:r>
                       </m:e>
                     </m:d>
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>−0.053705</m:t>
                     </m:r>
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr>
+                          <a:rPr i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:dPr>
                       <m:e>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>𝑙𝑒</m:t>
                         </m:r>
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr>
+                              <a:rPr i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:sSubPr>
                           <m:e>
                             <m:r>
+                              <a:rPr>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
                               <m:t>𝑛</m:t>
                             </m:r>
                           </m:e>
                           <m:sub>
                             <m:r>
+                              <a:rPr>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
                               <m:t>𝑏</m:t>
                             </m:r>
                           </m:sub>
@@ -9058,6 +9739,9 @@
                       </m:e>
                     </m:d>
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>−11.917287=0</m:t>
                     </m:r>
                   </m:oMath>
@@ -9074,37 +9758,52 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMath>
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>−0.053705</m:t>
                     </m:r>
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr>
+                          <a:rPr i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:dPr>
                       <m:e>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>𝑙𝑒</m:t>
                         </m:r>
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr>
+                              <a:rPr i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:sSubPr>
                           <m:e>
                             <m:r>
+                              <a:rPr>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
                               <m:t>𝑛</m:t>
                             </m:r>
                           </m:e>
                           <m:sub>
                             <m:r>
+                              <a:rPr>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
                               <m:t>𝑏</m:t>
                             </m:r>
                           </m:sub>
@@ -9112,35 +9811,47 @@
                       </m:e>
                     </m:d>
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>=−0.005791</m:t>
                     </m:r>
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr>
+                          <a:rPr i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:dPr>
                       <m:e>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>𝑙𝑒</m:t>
                         </m:r>
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr>
+                              <a:rPr i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:sSubPr>
                           <m:e>
                             <m:r>
+                              <a:rPr>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
                               <m:t>𝑛</m:t>
                             </m:r>
                           </m:e>
                           <m:sub>
                             <m:r>
+                              <a:rPr>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
                               <m:t>𝑎</m:t>
                             </m:r>
                           </m:sub>
@@ -9148,6 +9859,9 @@
                       </m:e>
                     </m:d>
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>+11.917288</m:t>
                     </m:r>
                   </m:oMath>
@@ -9164,57 +9878,90 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMath>
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>𝑙𝑒𝑛</m:t>
                     </m:r>
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>_</m:t>
                     </m:r>
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>𝑏</m:t>
                     </m:r>
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>=</m:t>
                     </m:r>
                     <m:f>
                       <m:fPr>
                         <m:ctrlPr>
-                          <a:rPr>
+                          <a:rPr i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:fPr>
                       <m:num>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>0.005791</m:t>
                         </m:r>
                         <m:d>
                           <m:dPr>
                             <m:ctrlPr>
-                              <a:rPr>
+                              <a:rPr i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:dPr>
                           <m:e>
                             <m:r>
+                              <a:rPr>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
                               <m:t>𝑙𝑒𝑛</m:t>
                             </m:r>
                             <m:r>
+                              <a:rPr>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
                               <m:t>_</m:t>
                             </m:r>
                             <m:r>
+                              <a:rPr>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
                               <m:t>𝑎</m:t>
                             </m:r>
                           </m:e>
                         </m:d>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>−11.917288</m:t>
                         </m:r>
                       </m:num>
                       <m:den>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>0.053705</m:t>
                         </m:r>
                       </m:den>
@@ -9233,40 +9980,67 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMath>
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>𝑙𝑒𝑛</m:t>
                     </m:r>
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>_</m:t>
                     </m:r>
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>𝑏</m:t>
                     </m:r>
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>=0.107821</m:t>
                     </m:r>
                     <m:d>
                       <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr>
+                          <a:rPr i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:dPr>
                       <m:e>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>𝑙𝑒𝑛</m:t>
                         </m:r>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>_</m:t>
                         </m:r>
                         <m:r>
+                          <a:rPr>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
                           <m:t>𝑎</m:t>
                         </m:r>
                       </m:e>
                     </m:d>
                     <m:r>
+                      <a:rPr>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
                       <m:t>−221.9022</m:t>
                     </m:r>
                   </m:oMath>
@@ -9541,12 +10315,12 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7798C9D4-D9A3-414B-919E-1762A05E858C}" name="Norm_Tests" displayName="Norm_Tests" ref="A7:E26" totalsRowCount="1">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2D415719-D29C-4B5B-8EEC-D6B547CA5D0E}" name="input" dataDxfId="253"/>
+    <tableColumn id="1" xr3:uid="{2D415719-D29C-4B5B-8EEC-D6B547CA5D0E}" name="input" dataDxfId="296"/>
     <tableColumn id="3" xr3:uid="{0ACC712F-EB7B-43DA-9965-8A4957A95DA2}" name="expected"/>
-    <tableColumn id="2" xr3:uid="{25F1E681-6FC0-4609-BF1F-1FF79BEB3CD8}" name="output" dataDxfId="252">
+    <tableColumn id="2" xr3:uid="{25F1E681-6FC0-4609-BF1F-1FF79BEB3CD8}" name="output" dataDxfId="295">
       <calculatedColumnFormula array="1">internal.xlInt.Norm(Norm_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{20432306-08A1-43B4-9B37-03610B79D73B}" name="passing" totalsRowFunction="custom" dataDxfId="251">
+    <tableColumn id="4" xr3:uid="{20432306-08A1-43B4-9B37-03610B79D73B}" name="passing" totalsRowFunction="custom" dataDxfId="294">
       <calculatedColumnFormula>IF(ISERROR(Norm_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Norm_Tests[[#This Row],[expected]]) = ERROR.TYPE(Norm_Tests[[#This Row],[output]]),
     Norm_Tests[[#This Row],[expected]] = Norm_Tests[[#This Row],[output]]
@@ -9560,11 +10334,11 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DCEBF05F-998F-47D8-A8F8-63C4E2771074}" name="UCompare_Tests" displayName="UCompare_Tests" ref="A127:E135" totalsRowCount="1" dataDxfId="212">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DCEBF05F-998F-47D8-A8F8-63C4E2771074}" name="UCompare_Tests" displayName="UCompare_Tests" ref="A127:E135" totalsRowCount="1" dataDxfId="255">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3554FEAC-3E95-4439-BF1F-B262B64D139D}" name="input" dataDxfId="211"/>
-    <tableColumn id="2" xr3:uid="{0EA61E63-F894-4F39-983A-67C6CDEA4B1D}" name="expected" dataDxfId="210"/>
-    <tableColumn id="3" xr3:uid="{B6F49B44-504D-4599-9F1E-49B98046B44D}" name="output" dataDxfId="209">
+    <tableColumn id="1" xr3:uid="{3554FEAC-3E95-4439-BF1F-B262B64D139D}" name="input" dataDxfId="254"/>
+    <tableColumn id="2" xr3:uid="{0EA61E63-F894-4F39-983A-67C6CDEA4B1D}" name="expected" dataDxfId="253"/>
+    <tableColumn id="3" xr3:uid="{B6F49B44-504D-4599-9F1E-49B98046B44D}" name="output" dataDxfId="252">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(UCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -9574,46 +10348,46 @@
     internal.xlInt.UCompare(_xlpm.limbs_a, _xlpm.limbs_b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{96B8A7F0-899C-4301-95D3-41FB0BA096A7}" name="passing" totalsRowFunction="custom" dataDxfId="208">
+    <tableColumn id="4" xr3:uid="{96B8A7F0-899C-4301-95D3-41FB0BA096A7}" name="passing" totalsRowFunction="custom" dataDxfId="251">
       <calculatedColumnFormula>IF(ISERROR(UCompare_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(UCompare_Tests[[#This Row],[output]]),
     UCompare_Tests[[#This Row],[expected]] = UCompare_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UCompare_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C5539D24-4ADC-4D77-B82F-27DAF4B3F109}" name="test" dataDxfId="207"/>
+    <tableColumn id="5" xr3:uid="{C5539D24-4ADC-4D77-B82F-27DAF4B3F109}" name="test" dataDxfId="250"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5E817537-E6E9-4069-8E14-531A3E42821F}" name="Internal_Sign_Tests" displayName="Internal_Sign_Tests" ref="A49:E60" totalsRowCount="1" tableBorderDxfId="206">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5E817537-E6E9-4069-8E14-531A3E42821F}" name="Internal_Sign_Tests" displayName="Internal_Sign_Tests" ref="A49:E60" totalsRowCount="1" tableBorderDxfId="249">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{C5C6E024-5D15-4650-BC06-AE3A9A4A3F9E}" name="input"/>
     <tableColumn id="2" xr3:uid="{2E349FE8-D8E4-4ABE-B47E-F0985AA6C672}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{49844921-4B71-4B13-957C-917C2841A9A3}" name="output" dataDxfId="205">
+    <tableColumn id="3" xr3:uid="{49844921-4B71-4B13-957C-917C2841A9A3}" name="output" dataDxfId="248">
       <calculatedColumnFormula array="1">xlInt.Sign(Internal_Sign_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0236DB85-60E5-4DC6-9655-C6D58A63C8D4}" name="passing" totalsRowFunction="custom" dataDxfId="204">
+    <tableColumn id="4" xr3:uid="{0236DB85-60E5-4DC6-9655-C6D58A63C8D4}" name="passing" totalsRowFunction="custom" dataDxfId="247">
       <calculatedColumnFormula>IF(ISERROR(Internal_Sign_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Internal_Sign_Tests[[#This Row],[expected]]) = ERROR.TYPE(Internal_Sign_Tests[[#This Row],[output]]),
     Internal_Sign_Tests[[#This Row],[expected]] = Internal_Sign_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Internal_Sign_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{396092C1-DC4F-4532-BB59-E0E779D9A525}" name="test" dataDxfId="203"/>
+    <tableColumn id="5" xr3:uid="{396092C1-DC4F-4532-BB59-E0E779D9A525}" name="test" dataDxfId="246"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1BF11AA1-9F01-403A-A5A2-CDAF85E5F9D0}" name="USub_Tests" displayName="USub_Tests" ref="A138:E146" totalsRowCount="1" dataDxfId="202">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1BF11AA1-9F01-403A-A5A2-CDAF85E5F9D0}" name="USub_Tests" displayName="USub_Tests" ref="A138:E146" totalsRowCount="1" dataDxfId="245">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5B979D84-AD0F-45AF-AB26-6C75CA981E58}" name="input" dataDxfId="201"/>
-    <tableColumn id="2" xr3:uid="{D8895FB5-11F4-4379-9B45-0D72ADA71E57}" name="expected" dataDxfId="200"/>
-    <tableColumn id="3" xr3:uid="{A4DDD8AE-0CC0-457E-A08D-2C94591CF878}" name="output" dataDxfId="199">
+    <tableColumn id="1" xr3:uid="{5B979D84-AD0F-45AF-AB26-6C75CA981E58}" name="input" dataDxfId="244"/>
+    <tableColumn id="2" xr3:uid="{D8895FB5-11F4-4379-9B45-0D72ADA71E57}" name="expected" dataDxfId="243"/>
+    <tableColumn id="3" xr3:uid="{A4DDD8AE-0CC0-457E-A08D-2C94591CF878}" name="output" dataDxfId="242">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(USub_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -9625,25 +10399,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BF616718-1C7F-4627-B496-8B6339CC2735}" name="passing" totalsRowFunction="custom" dataDxfId="198">
+    <tableColumn id="4" xr3:uid="{BF616718-1C7F-4627-B496-8B6339CC2735}" name="passing" totalsRowFunction="custom" dataDxfId="241">
       <calculatedColumnFormula>IF(ISERROR(USub_Tests[[#This Row],[expected]]),
     ERROR.TYPE(USub_Tests[[#This Row],[expected]]) = ERROR.TYPE(USub_Tests[[#This Row],[output]]),
     USub_Tests[[#This Row],[expected]] = USub_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(USub_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FCF52C7D-4E82-4BAA-8C93-974211CAC2AF}" name="test" dataDxfId="197"/>
+    <tableColumn id="5" xr3:uid="{FCF52C7D-4E82-4BAA-8C93-974211CAC2AF}" name="test" dataDxfId="240"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B5433254-33A6-4D35-8484-91940B628217}" name="Table6" displayName="Table6" ref="A149:E160" totalsRowCount="1" dataDxfId="196">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B5433254-33A6-4D35-8484-91940B628217}" name="Table6" displayName="Table6" ref="A149:E160" totalsRowCount="1" dataDxfId="239">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D52F6D10-66CD-4765-927A-94A578D3C30A}" name="input" dataDxfId="195" totalsRowDxfId="194"/>
-    <tableColumn id="2" xr3:uid="{DF2BEEE3-E1EF-4EA0-A6A8-77B06FB5C3EE}" name="expected" dataDxfId="193"/>
-    <tableColumn id="3" xr3:uid="{4FDE8849-AFE2-471E-8131-C5B45620EBDC}" name="output" dataDxfId="192">
+    <tableColumn id="1" xr3:uid="{D52F6D10-66CD-4765-927A-94A578D3C30A}" name="input" dataDxfId="238" totalsRowDxfId="237"/>
+    <tableColumn id="2" xr3:uid="{DF2BEEE3-E1EF-4EA0-A6A8-77B06FB5C3EE}" name="expected" dataDxfId="236"/>
+    <tableColumn id="3" xr3:uid="{4FDE8849-AFE2-471E-8131-C5B45620EBDC}" name="output" dataDxfId="235">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.input, _xlfn.REGEXEXTRACT(Table6[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.input,1,1),
@@ -9657,25 +10431,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5813AECE-7F35-45E7-8E1F-50DCC8404156}" name="passing" totalsRowFunction="custom" dataDxfId="191" totalsRowDxfId="190">
+    <tableColumn id="4" xr3:uid="{5813AECE-7F35-45E7-8E1F-50DCC8404156}" name="passing" totalsRowFunction="custom" dataDxfId="234" totalsRowDxfId="233">
       <calculatedColumnFormula>IF(ISERROR(Table6[[#This Row],[expected]]),
     ERROR.TYPE(Table6[[#This Row],[expected]]) = ERROR.TYPE(Table6[[#This Row],[output]]),
     Table6[[#This Row],[expected]] = Table6[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Table6[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6FEE6B80-DF03-48AD-BE0B-5CF10BB9952D}" name="test" dataDxfId="189"/>
+    <tableColumn id="5" xr3:uid="{6FEE6B80-DF03-48AD-BE0B-5CF10BB9952D}" name="test" dataDxfId="232"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{99918742-71F1-4CEE-8B31-04D0864B12BE}" name="Add_Tests" displayName="Add_Tests" ref="A163:E169" totalsRowCount="1" dataDxfId="188">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{99918742-71F1-4CEE-8B31-04D0864B12BE}" name="Add_Tests" displayName="Add_Tests" ref="A163:E169" totalsRowCount="1" dataDxfId="231">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BEDCABA1-70E6-4A6B-A326-B96D805DC792}" name="input" dataDxfId="187"/>
-    <tableColumn id="2" xr3:uid="{D2C344B5-4A5B-4F69-8FCC-B73D81DE29AD}" name="expected" dataDxfId="186"/>
-    <tableColumn id="3" xr3:uid="{B095BBF3-B41C-4F5B-9689-A075BCD3B3C6}" name="output" dataDxfId="185">
+    <tableColumn id="1" xr3:uid="{BEDCABA1-70E6-4A6B-A326-B96D805DC792}" name="input" dataDxfId="230"/>
+    <tableColumn id="2" xr3:uid="{D2C344B5-4A5B-4F69-8FCC-B73D81DE29AD}" name="expected" dataDxfId="229"/>
+    <tableColumn id="3" xr3:uid="{B095BBF3-B41C-4F5B-9689-A075BCD3B3C6}" name="output" dataDxfId="228">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Add_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -9683,25 +10457,25 @@
     xlInt.Add(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8A3FC5E9-718D-42AA-90B8-83E1D4F3B18A}" name="passing" totalsRowFunction="custom" dataDxfId="184" totalsRowDxfId="183">
+    <tableColumn id="4" xr3:uid="{8A3FC5E9-718D-42AA-90B8-83E1D4F3B18A}" name="passing" totalsRowFunction="custom" dataDxfId="227" totalsRowDxfId="226">
       <calculatedColumnFormula>IF(ISERROR(Add_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Add_Tests[[#This Row],[expected]]) = ERROR.TYPE(Add_Tests[[#This Row],[output]]),
     Add_Tests[[#This Row],[expected]] = Add_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Add_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DCB35414-E71F-476D-B8FC-5C98625552A8}" name="test" dataDxfId="182"/>
+    <tableColumn id="5" xr3:uid="{DCB35414-E71F-476D-B8FC-5C98625552A8}" name="test" dataDxfId="225"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{DE30AD6A-E7CB-4B0A-9AF6-2A68597C812D}" name="Sub_Tests" displayName="Sub_Tests" ref="A172:E176" totalsRowCount="1" dataDxfId="181">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{DE30AD6A-E7CB-4B0A-9AF6-2A68597C812D}" name="Sub_Tests" displayName="Sub_Tests" ref="A172:E176" totalsRowCount="1" dataDxfId="224">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{03074968-5409-421B-94C4-D5670F4C41D8}" name="input" dataDxfId="180"/>
-    <tableColumn id="2" xr3:uid="{DDFFA8C5-FCAB-4C4D-9AD1-92357F9E25A7}" name="expected" dataDxfId="179"/>
-    <tableColumn id="3" xr3:uid="{799B106A-FDF6-4F6C-8D67-8B6355524DD8}" name="output" dataDxfId="178">
+    <tableColumn id="1" xr3:uid="{03074968-5409-421B-94C4-D5670F4C41D8}" name="input" dataDxfId="223"/>
+    <tableColumn id="2" xr3:uid="{DDFFA8C5-FCAB-4C4D-9AD1-92357F9E25A7}" name="expected" dataDxfId="222"/>
+    <tableColumn id="3" xr3:uid="{799B106A-FDF6-4F6C-8D67-8B6355524DD8}" name="output" dataDxfId="221">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Sub_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -9709,25 +10483,25 @@
     xlInt.Sub(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{365F4930-D4D1-407A-94F0-4578BEFB456D}" name="passing" totalsRowFunction="custom" dataDxfId="177" totalsRowDxfId="176">
+    <tableColumn id="4" xr3:uid="{365F4930-D4D1-407A-94F0-4578BEFB456D}" name="passing" totalsRowFunction="custom" dataDxfId="220" totalsRowDxfId="219">
       <calculatedColumnFormula>IF(ISERROR(Sub_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Sub_Tests[[#This Row],[expected]]) = ERROR.TYPE(Sub_Tests[[#This Row],[output]]),
     Sub_Tests[[#This Row],[expected]] = Sub_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Sub_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CD9B4489-0AA4-43C4-9B29-8D70A32DD746}" name="test" dataDxfId="175"/>
+    <tableColumn id="5" xr3:uid="{CD9B4489-0AA4-43C4-9B29-8D70A32DD746}" name="test" dataDxfId="218"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{9E3906E7-DD79-4AAB-8367-36E413E4200E}" name="Split_Tests" displayName="Split_Tests" ref="A179:E183" totalsRowCount="1" dataDxfId="174">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{9E3906E7-DD79-4AAB-8367-36E413E4200E}" name="Split_Tests" displayName="Split_Tests" ref="A179:E183" totalsRowCount="1" dataDxfId="217">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{14CAD510-CB82-4DB3-9F1C-40F2CB704D1C}" name="input" dataDxfId="173"/>
-    <tableColumn id="2" xr3:uid="{5035D4AE-F48A-40D0-AF90-BDA3391536CB}" name="expected" dataDxfId="172"/>
-    <tableColumn id="3" xr3:uid="{99876D23-ABB8-4C24-98A4-1BEEEEDD07C4}" name="output" dataDxfId="171">
+    <tableColumn id="1" xr3:uid="{14CAD510-CB82-4DB3-9F1C-40F2CB704D1C}" name="input" dataDxfId="216"/>
+    <tableColumn id="2" xr3:uid="{5035D4AE-F48A-40D0-AF90-BDA3391536CB}" name="expected" dataDxfId="215"/>
+    <tableColumn id="3" xr3:uid="{99876D23-ABB8-4C24-98A4-1BEEEEDD07C4}" name="output" dataDxfId="214">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.input_k, _xlfn.REGEXEXTRACT(Split_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.input, INDEX(_xlpm.input_k,1,1),
@@ -9737,25 +10511,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A5A07BB4-21F2-4B01-9D44-1AA4366EAB7F}" name="passing" totalsRowFunction="custom" dataDxfId="170" totalsRowDxfId="169">
+    <tableColumn id="4" xr3:uid="{A5A07BB4-21F2-4B01-9D44-1AA4366EAB7F}" name="passing" totalsRowFunction="custom" dataDxfId="213" totalsRowDxfId="212">
       <calculatedColumnFormula>IF(ISERROR(Split_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Split_Tests[[#This Row],[expected]]) = ERROR.TYPE(Split_Tests[[#This Row],[output]]),
     Split_Tests[[#This Row],[expected]] = Split_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Split_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{12903E1A-EF63-4775-8029-4AC6E1371182}" name="test" dataDxfId="168"/>
+    <tableColumn id="5" xr3:uid="{12903E1A-EF63-4775-8029-4AC6E1371182}" name="test" dataDxfId="211"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{B4199465-17FF-401D-8825-47D1965ACDD0}" name="UMatrixSum_Tests" displayName="UMatrixSum_Tests" ref="A186:E191" totalsRowCount="1" dataDxfId="167">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{B4199465-17FF-401D-8825-47D1965ACDD0}" name="UMatrixSum_Tests" displayName="UMatrixSum_Tests" ref="A186:E191" totalsRowCount="1" dataDxfId="210">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{02600896-7D14-484F-821B-B4456983BB28}" name="input" dataDxfId="166"/>
-    <tableColumn id="2" xr3:uid="{173735CF-904D-4F11-81E2-08E18A2E350F}" name="expected" dataDxfId="165"/>
-    <tableColumn id="3" xr3:uid="{39C7D243-2D28-43C6-84E9-009686A8BE25}" name="output" dataDxfId="164">
+    <tableColumn id="1" xr3:uid="{02600896-7D14-484F-821B-B4456983BB28}" name="input" dataDxfId="209"/>
+    <tableColumn id="2" xr3:uid="{173735CF-904D-4F11-81E2-08E18A2E350F}" name="expected" dataDxfId="208"/>
+    <tableColumn id="3" xr3:uid="{39C7D243-2D28-43C6-84E9-009686A8BE25}" name="output" dataDxfId="207">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.limbs_k, _xlfn.REGEXEXTRACT(UMatrixSum_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.limbs, _xlfn.TEXTSPLIT(INDEX(_xlpm.limbs_k,1,1), ",", ";"),
@@ -9764,14 +10538,14 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{708213D7-3DCF-48EE-85F0-411FE836D86B}" name="passing" totalsRowFunction="custom" dataDxfId="163" totalsRowDxfId="162">
+    <tableColumn id="4" xr3:uid="{708213D7-3DCF-48EE-85F0-411FE836D86B}" name="passing" totalsRowFunction="custom" dataDxfId="206" totalsRowDxfId="205">
       <calculatedColumnFormula>IF(ISERROR(UMatrixSum_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UMatrixSum_Tests[[#This Row],[expected]]) = ERROR.TYPE(UMatrixSum_Tests[[#This Row],[output]]),
     UMatrixSum_Tests[[#This Row],[expected]] = UMatrixSum_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UMatrixSum_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{1A2B4059-059A-4B6D-8573-AF782E91D2A9}" name="test" dataDxfId="161"/>
+    <tableColumn id="5" xr3:uid="{1A2B4059-059A-4B6D-8573-AF782E91D2A9}" name="test" dataDxfId="204"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9782,14 +10556,14 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9C2FC9B7-0634-4588-8EFB-AD967A0F24A8}" name="input"/>
     <tableColumn id="2" xr3:uid="{282A94A0-1EBE-4152-8A9A-8F0EF95A0338}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{1B45BBB4-DEF0-4F8A-9D99-3837C2C1D0A6}" name="output" dataDxfId="160">
+    <tableColumn id="3" xr3:uid="{1B45BBB4-DEF0-4F8A-9D99-3837C2C1D0A6}" name="output" dataDxfId="203">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.range, _xlfn.REGEXEXTRACT(Sum_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.big_ints, IFERROR(_xlfn.TEXTSPLIT(INDEX(_xlpm.range,1,1), ",", ";"), ""),
     xlInt.Sum(_xlpm.big_ints)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EE8AD54F-5219-409B-ABCC-BA23AB35B017}" name="passing" totalsRowFunction="custom" dataDxfId="159" totalsRowDxfId="158">
+    <tableColumn id="4" xr3:uid="{EE8AD54F-5219-409B-ABCC-BA23AB35B017}" name="passing" totalsRowFunction="custom" dataDxfId="202" totalsRowDxfId="201">
       <calculatedColumnFormula>IF(ISERROR(Sum_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Sum_Tests[[#This Row],[expected]]) = ERROR.TYPE(Sum_Tests[[#This Row],[output]]),
     Sum_Tests[[#This Row],[expected]] = Sum_Tests[[#This Row],[output]]
@@ -9803,11 +10577,11 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{106EA359-E4B0-4842-9C9A-062E9FF7B5FB}" name="UMul_Tests" displayName="UMul_Tests" ref="A205:E211" totalsRowCount="1" dataDxfId="157">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{106EA359-E4B0-4842-9C9A-062E9FF7B5FB}" name="UMul_Tests" displayName="UMul_Tests" ref="A205:E211" totalsRowCount="1" dataDxfId="200">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8D4F0565-063F-4316-9C57-705162867D2A}" name="input" dataDxfId="156"/>
-    <tableColumn id="2" xr3:uid="{DAD4A921-C714-4DCC-AADE-BAF6086A3636}" name="expected" dataDxfId="155"/>
-    <tableColumn id="3" xr3:uid="{97E6E3DD-CA0A-4372-AC3D-9A495F7C3A53}" name="output" dataDxfId="154">
+    <tableColumn id="1" xr3:uid="{8D4F0565-063F-4316-9C57-705162867D2A}" name="input" dataDxfId="199"/>
+    <tableColumn id="2" xr3:uid="{DAD4A921-C714-4DCC-AADE-BAF6086A3636}" name="expected" dataDxfId="198"/>
+    <tableColumn id="3" xr3:uid="{97E6E3DD-CA0A-4372-AC3D-9A495F7C3A53}" name="output" dataDxfId="197">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(UMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -9819,25 +10593,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E46610B1-FA9D-4582-8D0C-63D1EC61D64E}" name="passing" totalsRowFunction="custom" dataDxfId="153" totalsRowDxfId="152">
+    <tableColumn id="4" xr3:uid="{E46610B1-FA9D-4582-8D0C-63D1EC61D64E}" name="passing" totalsRowFunction="custom" dataDxfId="196" totalsRowDxfId="195">
       <calculatedColumnFormula>IF(ISERROR(UMul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UMul_Tests[[#This Row],[output]]),
     UMul_Tests[[#This Row],[expected]] = UMul_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UMul_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5337E378-248A-4061-ABD9-D618DD84E539}" name="test" dataDxfId="151"/>
+    <tableColumn id="5" xr3:uid="{5337E378-248A-4061-ABD9-D618DD84E539}" name="test" dataDxfId="194"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D11AB36-7D48-42C4-B8E7-63DA272F75B3}" name="SafeK_Tests" displayName="SafeK_Tests" ref="A29:E37" totalsRowCount="1" dataDxfId="250">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D11AB36-7D48-42C4-B8E7-63DA272F75B3}" name="SafeK_Tests" displayName="SafeK_Tests" ref="A29:E37" totalsRowCount="1" dataDxfId="293">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{CD46518C-03B6-4B43-A7B8-7360525A290D}" name="input" dataDxfId="249"/>
-    <tableColumn id="3" xr3:uid="{F3B44865-B013-44C5-A9D4-1A13BFE5AA81}" name="expected" dataDxfId="248"/>
-    <tableColumn id="4" xr3:uid="{F40E0393-EF6C-4B2D-9F49-5CBB088EB267}" name="output" dataDxfId="247">
+    <tableColumn id="2" xr3:uid="{CD46518C-03B6-4B43-A7B8-7360525A290D}" name="input" dataDxfId="292"/>
+    <tableColumn id="3" xr3:uid="{F3B44865-B013-44C5-A9D4-1A13BFE5AA81}" name="expected" dataDxfId="291"/>
+    <tableColumn id="4" xr3:uid="{F40E0393-EF6C-4B2D-9F49-5CBB088EB267}" name="output" dataDxfId="290">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.op_items, _xlfn.REGEXEXTRACT(SafeK_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.op, INDEX(_xlpm.op_items,1,1),
@@ -9846,25 +10620,25 @@
     internal.xlInt.SafeK(_xlpm.op, _xlpm.max_items)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{62988A37-52EF-4F3E-82FE-0F2CD420BEF5}" name="passing" totalsRowFunction="custom" dataDxfId="246">
+    <tableColumn id="5" xr3:uid="{62988A37-52EF-4F3E-82FE-0F2CD420BEF5}" name="passing" totalsRowFunction="custom" dataDxfId="289">
       <calculatedColumnFormula>IF(ISERROR(SafeK_Tests[[#This Row],[expected]]),
     ERROR.TYPE(SafeK_Tests[[#This Row],[expected]]) = ERROR.TYPE(SafeK_Tests[[#This Row],[output]]),
     SafeK_Tests[[#This Row],[expected]] = SafeK_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(SafeK_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{FB9EC421-276B-4C54-8F46-BB5C01271314}" name="test" dataDxfId="245"/>
+    <tableColumn id="6" xr3:uid="{FB9EC421-276B-4C54-8F46-BB5C01271314}" name="test" dataDxfId="288"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C927379E-9D9F-446A-A7F8-18937FDB3BE9}" name="Mul_Tests" displayName="Mul_Tests" ref="A214:E221" totalsRowCount="1" dataDxfId="150">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C927379E-9D9F-446A-A7F8-18937FDB3BE9}" name="Mul_Tests" displayName="Mul_Tests" ref="A214:E221" totalsRowCount="1" dataDxfId="193">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3AEB129A-112F-4626-87D9-516E40338A3B}" name="input" dataDxfId="149" totalsRowDxfId="148"/>
-    <tableColumn id="2" xr3:uid="{17E1D158-0134-4800-97A0-9A914A48AA8F}" name="expected" dataDxfId="147" totalsRowDxfId="146"/>
-    <tableColumn id="3" xr3:uid="{B25D54E8-D438-48E6-9956-B82746478514}" name="output" dataDxfId="145" totalsRowDxfId="144">
+    <tableColumn id="1" xr3:uid="{3AEB129A-112F-4626-87D9-516E40338A3B}" name="input" dataDxfId="192" totalsRowDxfId="191"/>
+    <tableColumn id="2" xr3:uid="{17E1D158-0134-4800-97A0-9A914A48AA8F}" name="expected" dataDxfId="190" totalsRowDxfId="189"/>
+    <tableColumn id="3" xr3:uid="{B25D54E8-D438-48E6-9956-B82746478514}" name="output" dataDxfId="188" totalsRowDxfId="187">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Mul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -9872,25 +10646,25 @@
     xlInt.Mul(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5D503E6C-603A-418E-8D29-E96FF9E82626}" name="passing" totalsRowFunction="custom" dataDxfId="143" totalsRowDxfId="142">
+    <tableColumn id="4" xr3:uid="{5D503E6C-603A-418E-8D29-E96FF9E82626}" name="passing" totalsRowFunction="custom" dataDxfId="186" totalsRowDxfId="185">
       <calculatedColumnFormula>IF(ISERROR(Mul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Mul_Tests[[#This Row],[expected]]) = ERROR.TYPE(Mul_Tests[[#This Row],[output]]),
     Mul_Tests[[#This Row],[expected]] = Mul_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Mul_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{785B4909-13EC-4ABC-ADF8-0A6E8C364AE8}" name="test" dataDxfId="141" totalsRowDxfId="140"/>
+    <tableColumn id="5" xr3:uid="{785B4909-13EC-4ABC-ADF8-0A6E8C364AE8}" name="test" dataDxfId="184" totalsRowDxfId="183"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{4706FBB1-54D9-4F64-9481-F1D8984AE18E}" name="KnuthDiv_Tests" displayName="KnuthDiv_Tests" ref="A224:E233" totalsRowCount="1" dataDxfId="139">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{4706FBB1-54D9-4F64-9481-F1D8984AE18E}" name="KnuthDiv_Tests" displayName="KnuthDiv_Tests" ref="A224:E233" totalsRowCount="1" dataDxfId="182">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C9306945-CA62-4719-882E-A0FFCFC80239}" name="input" dataDxfId="138"/>
-    <tableColumn id="2" xr3:uid="{FF30C91E-2B8D-47FA-B34B-6CA5257E3EB7}" name="expected" dataDxfId="137"/>
-    <tableColumn id="3" xr3:uid="{3B324DA4-4AAE-408C-B627-929F7D5C7CBF}" name="output" dataDxfId="136">
+    <tableColumn id="1" xr3:uid="{C9306945-CA62-4719-882E-A0FFCFC80239}" name="input" dataDxfId="181"/>
+    <tableColumn id="2" xr3:uid="{FF30C91E-2B8D-47FA-B34B-6CA5257E3EB7}" name="expected" dataDxfId="180"/>
+    <tableColumn id="3" xr3:uid="{3B324DA4-4AAE-408C-B627-929F7D5C7CBF}" name="output" dataDxfId="179">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(KnuthDiv_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -9902,25 +10676,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{439AD3AD-5C90-48C6-AB74-B9DDF87C40B5}" name="passing" totalsRowFunction="custom" dataDxfId="135" totalsRowDxfId="134">
+    <tableColumn id="4" xr3:uid="{439AD3AD-5C90-48C6-AB74-B9DDF87C40B5}" name="passing" totalsRowFunction="custom" dataDxfId="178" totalsRowDxfId="177">
       <calculatedColumnFormula>IF(ISERROR(KnuthDiv_Tests[[#This Row],[expected]]),
     ERROR.TYPE(KnuthDiv_Tests[[#This Row],[expected]]) = ERROR.TYPE(KnuthDiv_Tests[[#This Row],[output]]),
     KnuthDiv_Tests[[#This Row],[expected]] = KnuthDiv_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(KnuthDiv_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7D4887A2-EC0B-4C52-8336-E300544022A1}" name="test" dataDxfId="133"/>
+    <tableColumn id="5" xr3:uid="{7D4887A2-EC0B-4C52-8336-E300544022A1}" name="test" dataDxfId="176"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B0C6E940-EAB6-4373-8987-1B7722C2CC79}" name="Div_Tests" displayName="Div_Tests" ref="A236:E247" totalsRowCount="1" dataDxfId="132">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B0C6E940-EAB6-4373-8987-1B7722C2CC79}" name="Div_Tests" displayName="Div_Tests" ref="A236:E247" totalsRowCount="1" dataDxfId="175">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{0A49EAE4-5B09-4D2D-A863-D634A4825565}" name="input" dataDxfId="131" totalsRowDxfId="130"/>
-    <tableColumn id="2" xr3:uid="{4BF042F3-E337-4B63-A1E8-414D47019404}" name="expected" dataDxfId="129" totalsRowDxfId="128"/>
-    <tableColumn id="3" xr3:uid="{118ABB7A-7163-40CB-974E-69BFF6BE2BE0}" name="output" dataDxfId="127" totalsRowDxfId="126">
+    <tableColumn id="1" xr3:uid="{0A49EAE4-5B09-4D2D-A863-D634A4825565}" name="input" dataDxfId="174" totalsRowDxfId="173"/>
+    <tableColumn id="2" xr3:uid="{4BF042F3-E337-4B63-A1E8-414D47019404}" name="expected" dataDxfId="172" totalsRowDxfId="171"/>
+    <tableColumn id="3" xr3:uid="{118ABB7A-7163-40CB-974E-69BFF6BE2BE0}" name="output" dataDxfId="170" totalsRowDxfId="169">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Div_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -9928,25 +10702,25 @@
     xlInt.Div(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4344C6C8-3F96-4048-96D0-CA621258C1D7}" name="passing" totalsRowFunction="custom" dataDxfId="125" totalsRowDxfId="124">
+    <tableColumn id="4" xr3:uid="{4344C6C8-3F96-4048-96D0-CA621258C1D7}" name="passing" totalsRowFunction="custom" dataDxfId="168" totalsRowDxfId="167">
       <calculatedColumnFormula>IF(ISERROR(Div_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Div_Tests[[#This Row],[expected]]) = ERROR.TYPE(Div_Tests[[#This Row],[output]]),
     Div_Tests[[#This Row],[expected]] = Div_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Div_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7CF48835-D05B-4120-863E-A47318569688}" name="test" dataDxfId="123" totalsRowDxfId="122"/>
+    <tableColumn id="5" xr3:uid="{7CF48835-D05B-4120-863E-A47318569688}" name="test" dataDxfId="166" totalsRowDxfId="165"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{B3179C39-4489-4B3E-A2D2-1A2B50DC058E}" name="Mod_Tests" displayName="Mod_Tests" ref="A250:E261" totalsRowCount="1" dataDxfId="121">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{B3179C39-4489-4B3E-A2D2-1A2B50DC058E}" name="Mod_Tests" displayName="Mod_Tests" ref="A250:E261" totalsRowCount="1" dataDxfId="164">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F1BCBD73-ACF5-4609-87F5-A9FAB549955E}" name="input" dataDxfId="120" totalsRowDxfId="119"/>
-    <tableColumn id="2" xr3:uid="{E9604163-FD58-4190-8D72-28AA7831E8C8}" name="expected" dataDxfId="118" totalsRowDxfId="117"/>
-    <tableColumn id="3" xr3:uid="{9D21CE79-D00B-4182-97B3-60EF6DC8B18F}" name="output" dataDxfId="116" totalsRowDxfId="115">
+    <tableColumn id="1" xr3:uid="{F1BCBD73-ACF5-4609-87F5-A9FAB549955E}" name="input" dataDxfId="163" totalsRowDxfId="162"/>
+    <tableColumn id="2" xr3:uid="{E9604163-FD58-4190-8D72-28AA7831E8C8}" name="expected" dataDxfId="161" totalsRowDxfId="160"/>
+    <tableColumn id="3" xr3:uid="{9D21CE79-D00B-4182-97B3-60EF6DC8B18F}" name="output" dataDxfId="159" totalsRowDxfId="158">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Mod_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -9954,25 +10728,25 @@
     xlInt.Mod(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CEF047D2-0521-425D-99C4-E3B997A68B32}" name="passing" totalsRowFunction="custom" dataDxfId="114" totalsRowDxfId="113">
+    <tableColumn id="4" xr3:uid="{CEF047D2-0521-425D-99C4-E3B997A68B32}" name="passing" totalsRowFunction="custom" dataDxfId="157" totalsRowDxfId="156">
       <calculatedColumnFormula>IF(ISERROR(Mod_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Mod_Tests[[#This Row],[expected]]) = ERROR.TYPE(Mod_Tests[[#This Row],[output]]),
     Mod_Tests[[#This Row],[expected]] = Mod_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Mod_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{BB0A3941-EEFB-445E-AE7B-833C36649910}" name="test" dataDxfId="112" totalsRowDxfId="111"/>
+    <tableColumn id="5" xr3:uid="{BB0A3941-EEFB-445E-AE7B-833C36649910}" name="test" dataDxfId="155" totalsRowDxfId="154"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{82953E35-FA6B-4DA1-B4AC-195D4F1BB7C8}" name="DivMod_Tests" displayName="DivMod_Tests" ref="A264:E280" totalsRowCount="1" dataDxfId="110">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{82953E35-FA6B-4DA1-B4AC-195D4F1BB7C8}" name="DivMod_Tests" displayName="DivMod_Tests" ref="A264:E280" totalsRowCount="1" dataDxfId="153">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E51BC97B-AA0D-4705-AF36-89CB4A3501FF}" name="input" dataDxfId="109" totalsRowDxfId="108"/>
-    <tableColumn id="2" xr3:uid="{6D6483DD-139D-4DFE-BFEA-8BAA3E5C6FCF}" name="expected" dataDxfId="107" totalsRowDxfId="106"/>
-    <tableColumn id="3" xr3:uid="{17DE90BB-4525-4C2D-9577-C4372DCD74B3}" name="output" dataDxfId="105" totalsRowDxfId="104">
+    <tableColumn id="1" xr3:uid="{E51BC97B-AA0D-4705-AF36-89CB4A3501FF}" name="input" dataDxfId="152" totalsRowDxfId="151"/>
+    <tableColumn id="2" xr3:uid="{6D6483DD-139D-4DFE-BFEA-8BAA3E5C6FCF}" name="expected" dataDxfId="150" totalsRowDxfId="149"/>
+    <tableColumn id="3" xr3:uid="{17DE90BB-4525-4C2D-9577-C4372DCD74B3}" name="output" dataDxfId="148" totalsRowDxfId="147">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.ab_flag, _xlfn.REGEXEXTRACT(DivMod_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab_flag,1,1),
@@ -9981,25 +10755,25 @@
     _xlfn.ARRAYTOTEXT(xlInt.DivMod(_xlpm.a, _xlpm.b, _xlpm.use_floor), 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{08745616-1601-437B-82EA-C1952393A99B}" name="passing" totalsRowFunction="custom" dataDxfId="103" totalsRowDxfId="102">
+    <tableColumn id="4" xr3:uid="{08745616-1601-437B-82EA-C1952393A99B}" name="passing" totalsRowFunction="custom" dataDxfId="146" totalsRowDxfId="145">
       <calculatedColumnFormula>IF(ISERROR(DivMod_Tests[[#This Row],[expected]]),
     ERROR.TYPE(DivMod_Tests[[#This Row],[expected]]) = ERROR.TYPE(DivMod_Tests[[#This Row],[output]]),
     DivMod_Tests[[#This Row],[expected]] = DivMod_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(DivMod_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{10C8AB14-1CD9-4B06-8A65-2B27B32A2550}" name="test" dataDxfId="101" totalsRowDxfId="100"/>
+    <tableColumn id="5" xr3:uid="{10C8AB14-1CD9-4B06-8A65-2B27B32A2550}" name="test" dataDxfId="144" totalsRowDxfId="143"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{3400C680-561E-4111-B80A-CA24DB597E3F}" name="Table25" displayName="Table25" ref="A283:E289" totalsRowCount="1" dataDxfId="99">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{3400C680-561E-4111-B80A-CA24DB597E3F}" name="Table25" displayName="Table25" ref="A283:E289" totalsRowCount="1" dataDxfId="142">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{37EA378F-E179-45E1-BF1A-FBA82C305DBA}" name="input" dataDxfId="98"/>
-    <tableColumn id="2" xr3:uid="{11DFB020-1D5E-4E26-A86F-6B73428F3709}" name="expected" dataDxfId="97"/>
-    <tableColumn id="3" xr3:uid="{943FD3EB-6145-4BEE-9408-F68BE0795A47}" name="output" dataDxfId="96">
+    <tableColumn id="1" xr3:uid="{37EA378F-E179-45E1-BF1A-FBA82C305DBA}" name="input" dataDxfId="141"/>
+    <tableColumn id="2" xr3:uid="{11DFB020-1D5E-4E26-A86F-6B73428F3709}" name="expected" dataDxfId="140"/>
+    <tableColumn id="3" xr3:uid="{943FD3EB-6145-4BEE-9408-F68BE0795A47}" name="output" dataDxfId="139">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.bk, _xlfn.REGEXEXTRACT(Table25[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.b, INDEX(_xlpm.bk,1,1),
@@ -10009,49 +10783,49 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{165ECACC-11AD-4EB0-AE14-7D528DA64799}" name="passing" totalsRowFunction="custom" dataDxfId="95" totalsRowDxfId="94">
+    <tableColumn id="4" xr3:uid="{165ECACC-11AD-4EB0-AE14-7D528DA64799}" name="passing" totalsRowFunction="custom" dataDxfId="138" totalsRowDxfId="137">
       <calculatedColumnFormula>IF(ISERROR(Table25[[#This Row],[expected]]),
     ERROR.TYPE(Table25[[#This Row],[expected]]) = ERROR.TYPE(Table25[[#This Row],[output]]),
     Table25[[#This Row],[expected]] = Table25[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Table25[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6FA8F2E3-9F29-41C5-8B60-45E4EF5BFD33}" name="test" dataDxfId="93"/>
+    <tableColumn id="5" xr3:uid="{6FA8F2E3-9F29-41C5-8B60-45E4EF5BFD33}" name="test" dataDxfId="136"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{12A27437-8E10-4142-9D59-10A781936664}" name="IsEven_Tests" displayName="IsEven_Tests" ref="A292:E301" totalsRowCount="1" tableBorderDxfId="92">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{12A27437-8E10-4142-9D59-10A781936664}" name="IsEven_Tests" displayName="IsEven_Tests" ref="A292:E301" totalsRowCount="1" tableBorderDxfId="135">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{72B34F2A-D724-472B-AEA6-85847044F8BB}" name="input"/>
     <tableColumn id="2" xr3:uid="{8F1A9828-E68A-40FE-8534-E28D2B59C43A}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{90993922-EF49-4320-BFDE-A85AAC37995B}" name="output" dataDxfId="91">
+    <tableColumn id="3" xr3:uid="{90993922-EF49-4320-BFDE-A85AAC37995B}" name="output" dataDxfId="134">
       <calculatedColumnFormula array="1">BigInt.IsEven(IsEven_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4CD10349-78F4-4A08-8AD3-6AFDD4218B3F}" name="passing" totalsRowFunction="custom" dataDxfId="90">
+    <tableColumn id="4" xr3:uid="{4CD10349-78F4-4A08-8AD3-6AFDD4218B3F}" name="passing" totalsRowFunction="custom" dataDxfId="133">
       <calculatedColumnFormula>IF(ISERROR(IsEven_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsEven_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsEven_Tests[[#This Row],[output]]),
     IsEven_Tests[[#This Row],[expected]] = IsEven_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(IsEven_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9C811914-2121-4942-94F0-B4760C307266}" name="test" dataDxfId="89"/>
+    <tableColumn id="5" xr3:uid="{9C811914-2121-4942-94F0-B4760C307266}" name="test" dataDxfId="132"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{29B30C5B-F766-4073-878A-FEDF3C607366}" name="IsOdd_Tests" displayName="IsOdd_Tests" ref="A304:E313" totalsRowCount="1" tableBorderDxfId="88">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{29B30C5B-F766-4073-878A-FEDF3C607366}" name="IsOdd_Tests" displayName="IsOdd_Tests" ref="A304:E313" totalsRowCount="1" tableBorderDxfId="131">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8D247229-1BE2-49B1-BEC8-19AFBBF671FC}" name="input"/>
     <tableColumn id="2" xr3:uid="{9F1FC5CC-11FA-4EB1-BA6E-3C18F4379652}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{6B07B988-F191-4E41-81FA-8D0020D0AEF2}" name="output" dataDxfId="87">
+    <tableColumn id="3" xr3:uid="{6B07B988-F191-4E41-81FA-8D0020D0AEF2}" name="output" dataDxfId="130">
       <calculatedColumnFormula array="1">BigInt.IsOdd(IsOdd_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{15820A65-99F4-420C-A89B-1F6FB8202BCC}" name="passing" totalsRowFunction="custom" dataDxfId="86">
+    <tableColumn id="4" xr3:uid="{15820A65-99F4-420C-A89B-1F6FB8202BCC}" name="passing" totalsRowFunction="custom" dataDxfId="129">
       <calculatedColumnFormula>IF(ISERROR(IsOdd_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsOdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsOdd_Tests[[#This Row],[output]]),
     IsOdd_Tests[[#This Row],[expected]] = IsOdd_Tests[[#This Row],[output]]
@@ -10065,11 +10839,11 @@
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{371705AE-DD2A-4348-9D77-10A58AFED934}" name="Pow_Tests" displayName="Pow_Tests" ref="A327:E341" totalsRowCount="1" dataDxfId="85">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{371705AE-DD2A-4348-9D77-10A58AFED934}" name="Pow_Tests" displayName="Pow_Tests" ref="A327:E341" totalsRowCount="1" dataDxfId="128">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{428DC074-F3C2-4541-81E6-FDDAE2482D27}" name="input" dataDxfId="84"/>
-    <tableColumn id="2" xr3:uid="{B5FD2A40-BCC5-4580-B8CD-768791024AC5}" name="expected" dataDxfId="83"/>
-    <tableColumn id="3" xr3:uid="{F4E39208-EEA5-4CF3-B04A-4707F3E1FB8E}" name="output" dataDxfId="82">
+    <tableColumn id="1" xr3:uid="{428DC074-F3C2-4541-81E6-FDDAE2482D27}" name="input" dataDxfId="127"/>
+    <tableColumn id="2" xr3:uid="{B5FD2A40-BCC5-4580-B8CD-768791024AC5}" name="expected" dataDxfId="126"/>
+    <tableColumn id="3" xr3:uid="{F4E39208-EEA5-4CF3-B04A-4707F3E1FB8E}" name="output" dataDxfId="125">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab, 1, 1),
@@ -10077,25 +10851,25 @@
     BigInt.Pow(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B407AC33-1B59-4CB2-91F2-8CA96B7CE117}" name="passing" totalsRowFunction="custom" dataDxfId="81">
+    <tableColumn id="4" xr3:uid="{B407AC33-1B59-4CB2-91F2-8CA96B7CE117}" name="passing" totalsRowFunction="custom" dataDxfId="124">
       <calculatedColumnFormula>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
     Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Pow_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A1A7E0C2-F1B0-41A5-A740-EDF94ACD6051}" name="test" dataDxfId="80"/>
+    <tableColumn id="5" xr3:uid="{A1A7E0C2-F1B0-41A5-A740-EDF94ACD6051}" name="test" dataDxfId="123"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{83160072-B1B0-4FD1-88FC-006B8639CBE0}" name="UPow_Tests" displayName="UPow_Tests" ref="A316:E324" totalsRowCount="1" dataDxfId="79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{83160072-B1B0-4FD1-88FC-006B8639CBE0}" name="UPow_Tests" displayName="UPow_Tests" ref="A316:E324" totalsRowCount="1" dataDxfId="122">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{20145995-7ED4-4B73-887D-9D74DA0828CF}" name="input" dataDxfId="78"/>
-    <tableColumn id="2" xr3:uid="{82FBC2F1-B0A2-4D85-8D2F-0E9C3548EF52}" name="expected" dataDxfId="77"/>
-    <tableColumn id="3" xr3:uid="{30FC05F3-7A85-4F3C-B4CB-146B4FEBD37A}" name="output" dataDxfId="76">
+    <tableColumn id="1" xr3:uid="{20145995-7ED4-4B73-887D-9D74DA0828CF}" name="input" dataDxfId="121"/>
+    <tableColumn id="2" xr3:uid="{82FBC2F1-B0A2-4D85-8D2F-0E9C3548EF52}" name="expected" dataDxfId="120"/>
+    <tableColumn id="3" xr3:uid="{30FC05F3-7A85-4F3C-B4CB-146B4FEBD37A}" name="output" dataDxfId="119">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.bek, _xlfn.REGEXEXTRACT(UPow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.base, INDEX(_xlpm.bek,1,1),
@@ -10106,14 +10880,14 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{13DDE135-8BB6-470E-A96F-6482CA5075E2}" name="passing" totalsRowFunction="custom" dataDxfId="75">
+    <tableColumn id="4" xr3:uid="{13DDE135-8BB6-470E-A96F-6482CA5075E2}" name="passing" totalsRowFunction="custom" dataDxfId="118">
       <calculatedColumnFormula>IF(ISERROR(UPow_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UPow_Tests[[#This Row],[expected]]) = ERROR.TYPE(UPow_Tests[[#This Row],[output]]),
     UPow_Tests[[#This Row],[expected]] = UPow_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UPow_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{45AF5A50-06F2-4581-B704-1F7379E7EFDB}" name="test" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{45AF5A50-06F2-4581-B704-1F7379E7EFDB}" name="test" dataDxfId="117"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10124,7 +10898,7 @@
   <tableColumns count="5">
     <tableColumn id="2" xr3:uid="{2286D15B-F261-49FF-90E5-E32FAEEEA489}" name="input"/>
     <tableColumn id="3" xr3:uid="{1D45A0AC-7049-4C3E-9D4F-CF777F60006B}" name="expected"/>
-    <tableColumn id="4" xr3:uid="{725B7147-ED3D-42D7-9030-A0FCAF6502D0}" name="output" dataDxfId="244">
+    <tableColumn id="4" xr3:uid="{725B7147-ED3D-42D7-9030-A0FCAF6502D0}" name="output" dataDxfId="287">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.limbs_k, _xlfn.REGEXEXTRACT(Merge_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.limbs_text, INDEX(_xlpm.limbs_k,1,1),
@@ -10133,25 +10907,25 @@
     internal.xlInt.Merge(_xlpm.limbs, _xlpm.k)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7D40DA54-4D50-4770-9171-9F50106783D7}" name="passing" totalsRowFunction="custom" dataDxfId="243">
+    <tableColumn id="5" xr3:uid="{7D40DA54-4D50-4770-9171-9F50106783D7}" name="passing" totalsRowFunction="custom" dataDxfId="286">
       <calculatedColumnFormula>IF(ISERROR(Merge_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Merge_Tests[[#This Row],[expected]]) = ERROR.TYPE(Merge_Tests[[#This Row],[output]]),
     Merge_Tests[[#This Row],[expected]] = Merge_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Merge_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F906F95B-0DD5-4F50-9A36-C63DEC4B514C}" name="test" dataDxfId="242"/>
+    <tableColumn id="6" xr3:uid="{F906F95B-0DD5-4F50-9A36-C63DEC4B514C}" name="test" dataDxfId="285"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{56E07932-566C-4BD6-8077-730BDDB685D7}" name="USqrt_Tests" displayName="USqrt_Tests" ref="A344:E348" totalsRowCount="1" dataDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{56E07932-566C-4BD6-8077-730BDDB685D7}" name="USqrt_Tests" displayName="USqrt_Tests" ref="A344:E348" totalsRowCount="1" dataDxfId="116">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7D0B28FD-9EB7-4A3D-892B-9C8FB4B3B2F5}" name="input" dataDxfId="72"/>
-    <tableColumn id="2" xr3:uid="{CFF29D88-DF87-4564-930E-26EAF1CB3332}" name="expected" dataDxfId="71"/>
-    <tableColumn id="3" xr3:uid="{4738BA38-2D1B-4B90-8625-6A923FAABAE8}" name="output" dataDxfId="70">
+    <tableColumn id="1" xr3:uid="{7D0B28FD-9EB7-4A3D-892B-9C8FB4B3B2F5}" name="input" dataDxfId="115"/>
+    <tableColumn id="2" xr3:uid="{CFF29D88-DF87-4564-930E-26EAF1CB3332}" name="expected" dataDxfId="114"/>
+    <tableColumn id="3" xr3:uid="{4738BA38-2D1B-4B90-8625-6A923FAABAE8}" name="output" dataDxfId="113">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.radicand_seed_k, _xlfn.REGEXEXTRACT(USqrt_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.radicand, INDEX(_xlpm.radicand_seed_k,1,1),
@@ -10163,26 +10937,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{118D95C4-A916-4992-AEA0-6F30E3EE33F9}" name="passing" totalsRowFunction="custom" dataDxfId="69" totalsRowDxfId="73">
+    <tableColumn id="4" xr3:uid="{118D95C4-A916-4992-AEA0-6F30E3EE33F9}" name="passing" totalsRowFunction="custom" dataDxfId="112" totalsRowDxfId="111">
       <calculatedColumnFormula>IF(ISERROR(USqrt_Tests[[#This Row],[expected]]),
     ERROR.TYPE(USqrt_Tests[[#This Row],[expected]]) = ERROR.TYPE(USqrt_Tests[[#This Row],[output]]),
     USqrt_Tests[[#This Row],[expected]] = USqrt_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(USqrt_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{36AF6E6D-247D-40D4-8B02-20DF4A48BDF2}" name="test" dataDxfId="68"/>
+    <tableColumn id="5" xr3:uid="{36AF6E6D-247D-40D4-8B02-20DF4A48BDF2}" name="test" dataDxfId="110"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{A9B2C3B0-D156-4BA1-8DBC-CCD97E178DEB}" name="NewtonRaphsonReciprocal_Tests" displayName="NewtonRaphsonReciprocal_Tests" ref="A351:E356" totalsRowCount="1" dataDxfId="63">
-  <autoFilter ref="A351:E355" xr:uid="{A9B2C3B0-D156-4BA1-8DBC-CCD97E178DEB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{A9B2C3B0-D156-4BA1-8DBC-CCD97E178DEB}" name="NewtonRaphsonReciprocal_Tests" displayName="NewtonRaphsonReciprocal_Tests" ref="A351:E356" totalsRowCount="1" dataDxfId="109">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{668CC6CC-FAA8-4201-AF7C-80B23CDDC2E9}" name="input" dataDxfId="65"/>
-    <tableColumn id="2" xr3:uid="{25DCB2CE-672E-4637-9E18-5B6DB9547223}" name="expected" dataDxfId="64"/>
-    <tableColumn id="3" xr3:uid="{90B5F5EA-1862-438B-A0B0-E7B33D47B422}" name="output" dataDxfId="62">
+    <tableColumn id="1" xr3:uid="{668CC6CC-FAA8-4201-AF7C-80B23CDDC2E9}" name="input" dataDxfId="108"/>
+    <tableColumn id="2" xr3:uid="{25DCB2CE-672E-4637-9E18-5B6DB9547223}" name="expected" dataDxfId="107"/>
+    <tableColumn id="3" xr3:uid="{90B5F5EA-1862-438B-A0B0-E7B33D47B422}" name="output" dataDxfId="106">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.b_len_k, _xlfn.REGEXEXTRACT(NewtonRaphsonReciprocal_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.b, INDEX(_xlpm.b_len_k,1,1),
@@ -10193,26 +10966,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A229F032-C11B-467F-A66D-15E5E90AC98D}" name="passing" totalsRowFunction="custom" dataDxfId="61" totalsRowDxfId="66">
+    <tableColumn id="4" xr3:uid="{A229F032-C11B-467F-A66D-15E5E90AC98D}" name="passing" totalsRowFunction="custom" dataDxfId="105" totalsRowDxfId="104">
       <calculatedColumnFormula>IF(ISERROR(NewtonRaphsonReciprocal_Tests[[#This Row],[expected]]),
     ERROR.TYPE(NewtonRaphsonReciprocal_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonReciprocal_Tests[[#This Row],[output]]),
     NewtonRaphsonReciprocal_Tests[[#This Row],[expected]] = NewtonRaphsonReciprocal_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(NewtonRaphsonReciprocal_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F159BE0D-B6F5-4516-9322-421576A9CFAC}" name="test" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{F159BE0D-B6F5-4516-9322-421576A9CFAC}" name="test" dataDxfId="103"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{9E5B9787-3CCB-4F73-B127-FE62EEB658A9}" name="NewtonRaphsonDiv_Tests" displayName="NewtonRaphsonDiv_Tests" ref="A359:E365" totalsRowCount="1" dataDxfId="59">
-  <autoFilter ref="A359:E364" xr:uid="{9E5B9787-3CCB-4F73-B127-FE62EEB658A9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{9E5B9787-3CCB-4F73-B127-FE62EEB658A9}" name="NewtonRaphsonDiv_Tests" displayName="NewtonRaphsonDiv_Tests" ref="A359:E365" totalsRowCount="1" dataDxfId="102">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1DD49B57-7E7E-4B1C-B300-6AC09AA4507D}" name="input" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{F726FD71-2E54-4ACE-8BDB-45E8C22B8958}" name="expected" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{51451E9D-81A3-4433-AABC-FCAE4ED0B82C}" name="output" dataDxfId="53">
+    <tableColumn id="1" xr3:uid="{1DD49B57-7E7E-4B1C-B300-6AC09AA4507D}" name="input" dataDxfId="101"/>
+    <tableColumn id="2" xr3:uid="{F726FD71-2E54-4ACE-8BDB-45E8C22B8958}" name="expected" dataDxfId="100"/>
+    <tableColumn id="3" xr3:uid="{51451E9D-81A3-4433-AABC-FCAE4ED0B82C}" name="output" dataDxfId="99">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(NewtonRaphsonDiv_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -10224,20 +10996,141 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3511251B-5389-4721-A1A1-8AE06E90F9D7}" name="passing" totalsRowFunction="custom" dataDxfId="54" totalsRowDxfId="56">
+    <tableColumn id="4" xr3:uid="{3511251B-5389-4721-A1A1-8AE06E90F9D7}" name="passing" totalsRowFunction="custom" dataDxfId="98" totalsRowDxfId="97">
       <calculatedColumnFormula>IF(ISERROR(NewtonRaphsonDiv_Tests[[#This Row],[expected]]),
     ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[output]]),
     NewtonRaphsonDiv_Tests[[#This Row],[expected]] = NewtonRaphsonDiv_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(NewtonRaphsonDiv_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8FBD496E-700B-47C8-B9CA-AD0871776B53}" name="test" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{8FBD496E-700B-47C8-B9CA-AD0871776B53}" name="test" dataDxfId="96"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{27C0A819-84B9-4A0A-8097-03A8C95F5E27}" name="NativePrimes_Tests" displayName="NativePrimes_Tests" ref="A368:E374" totalsRowCount="1" dataDxfId="89" tableBorderDxfId="95">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{F29CD078-1065-436A-811B-D67567316769}" name="input" dataDxfId="94"/>
+    <tableColumn id="2" xr3:uid="{6122EAC1-506A-441B-8004-4B02E143A802}" name="expected" dataDxfId="93"/>
+    <tableColumn id="3" xr3:uid="{778AEC62-886A-4A2A-BD39-EB9F715A732B}" name="output" dataDxfId="92">
+      <calculatedColumnFormula>_xlfn.ARRAYTOTEXT(core_BigInt.NativePrimes(NativePrimes_Tests[[#This Row],[input]]), 1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{F3546CB4-2246-45FB-B499-CB4B13BA76E1}" name="passing" totalsRowFunction="custom" dataDxfId="91">
+      <calculatedColumnFormula>IF(ISERROR(NativePrimes_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NativePrimes_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativePrimes_Tests[[#This Row],[output]]),
+    NativePrimes_Tests[[#This Row],[expected]] = NativePrimes_Tests[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(NativePrimes_Tests[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{8190D20C-0392-4F85-929A-69F9BDF57A0A}" name="test" dataDxfId="90"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table34.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{59E466E6-AFB8-402E-BCED-A4DA6DCFEC1A}" name="NativeLegendre_Tests" displayName="NativeLegendre_Tests" ref="A377:E381" totalsRowCount="1" dataDxfId="83">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{E23E090E-81D9-47D4-8198-B1ABBEE94C6B}" name="input" dataDxfId="87"/>
+    <tableColumn id="2" xr3:uid="{D1878000-78EF-43C5-946A-0BAFB2F760F9}" name="expected" dataDxfId="86"/>
+    <tableColumn id="3" xr3:uid="{C7FC6EEE-BC05-4AD9-93FA-E3E482244768}" name="output" dataDxfId="82">
+      <calculatedColumnFormula array="1">_xlfn.LET(
+    _xlpm.n_primes, _xlfn.REGEXEXTRACT(NativeLegendre_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.n, --INDEX(_xlpm.n_primes,1,1),
+    _xlpm.primes, INDEX(_xlpm.n_primes,1,2),
+    _xlpm.primes_arr, --_xlfn.TEXTSPLIT(_xlpm.primes,",",";"),
+    _xlpm.output, core_BigInt.NativeLegendre(_xlpm.n, _xlpm.primes_arr),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{6B550009-EA49-4BEF-8603-A7366A531DBE}" name="passing" totalsRowFunction="custom" dataDxfId="85" totalsRowDxfId="88">
+      <calculatedColumnFormula>IF(ISERROR(NativeLegendre_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NativeLegendre_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativeLegendre_Tests[[#This Row],[output]]),
+    NativeLegendre_Tests[[#This Row],[expected]] = NativeLegendre_Tests[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(NativeLegendre_Tests[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{A0D783D9-731F-42E5-8EBE-FEFE8CD7AAF6}" name="test" dataDxfId="84"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table35.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{49BD0AFE-381A-4E2F-A35C-4D1CCCA7584E}" name="TextTreeProd_Tests37" displayName="TextTreeProd_Tests37" ref="A393:E398" totalsRowCount="1" dataDxfId="81">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{998EF311-8CF0-4498-BF3E-C7591D617740}" name="input" dataDxfId="80"/>
+    <tableColumn id="2" xr3:uid="{030D33E6-C011-4057-AFBE-F1FEC05B0E3D}" name="expected" dataDxfId="79"/>
+    <tableColumn id="3" xr3:uid="{4A32034C-1A35-45CF-A8F5-5BB1FB3300A5}" name="output" dataDxfId="75">
+      <calculatedColumnFormula array="1">_xlfn.LET(
+    _xlpm.big_ints, _xlfn.REGEXEXTRACT(TextTreeProd_Tests37[[#This Row],[input]], "{\K[\w,; .-]*"),
+    _xlpm.big_int_arr, _xlfn.TEXTSPLIT(_xlpm.big_ints,",",";"),
+    core_BigInt.TextTreeProd(_xlpm.big_int_arr)
+)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{F4493AC7-8D4A-4E9D-A9A4-52B87367C964}" name="passing" totalsRowFunction="custom" dataDxfId="77" totalsRowDxfId="78">
+      <calculatedColumnFormula>IF(ISERROR(TextTreeProd_Tests37[[#This Row],[expected]]),
+    ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[expected]]) = ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[output]]),
+    TextTreeProd_Tests37[[#This Row],[expected]] = TextTreeProd_Tests37[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(TextTreeProd_Tests37[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{9E2E183E-0AFC-4266-8D1C-760BDBA95E9A}" name="test" dataDxfId="76"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table36.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{4BA5BDEF-A87F-4855-AD37-C3A378790A0D}" name="UTextMul_Tests" displayName="UTextMul_Tests" ref="A384:E390" totalsRowCount="1" dataDxfId="74">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{3F5F3FFD-5DC8-4A88-908C-7CEE90688FD2}" name="input" dataDxfId="73" totalsRowDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{6AD81AC4-371F-4E12-BB01-43913712ADEC}" name="expected" dataDxfId="72" totalsRowDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{554D388F-417A-46F4-9FA2-AACDEAA24237}" name="output" dataDxfId="64" totalsRowDxfId="67">
+      <calculatedColumnFormula array="1">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(UTextMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab,1,1),
+    _xlpm.b, INDEX(_xlpm.ab,1,2),
+    core_BigInt.UTextMul(_xlpm.a, _xlpm.b)
+)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{98F15F6B-80F5-487B-9965-2D3178956C0C}" name="passing" totalsRowFunction="custom" dataDxfId="71" totalsRowDxfId="66">
+      <calculatedColumnFormula>IF(ISERROR(UTextMul_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(UTextMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UTextMul_Tests[[#This Row],[output]]),
+    UTextMul_Tests[[#This Row],[expected]] = UTextMul_Tests[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(UTextMul_Tests[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{2218ADB1-42B3-401A-BDE3-B0DC0D6D6959}" name="test" dataDxfId="70" totalsRowDxfId="65"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table37.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{C18280EB-8AA6-4449-955D-681E77E7D1F0}" name="Fact_Tests" displayName="Fact_Tests" ref="A401:E409" totalsRowCount="1" dataDxfId="63" tableBorderDxfId="62">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{D95EE39E-5251-4170-8888-9530E87C134B}" name="input" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{15AD0C64-A61C-4834-B444-C19248449496}" name="expected" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{B1B2AF0C-A9CA-494D-9393-F9EB601C03AE}" name="output" dataDxfId="0">
+      <calculatedColumnFormula array="1">BigInt.Fact(Fact_Tests[[#This Row],[input]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{67D2CAD7-A3A0-464E-A151-2D279B301872}" name="passing" totalsRowFunction="custom" dataDxfId="59">
+      <calculatedColumnFormula>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
+    Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(Fact_Tests[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{AD0FAFD6-A476-479B-A804-9F518E2EB8F4}" name="test" dataDxfId="58"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table38.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{C1458AB7-3AD7-44E9-B064-C2BEC4A41762}" name="Data" displayName="Data" ref="A1:B8" totalsRowShown="0">
   <autoFilter ref="A1:B8" xr:uid="{C1458AB7-3AD7-44E9-B064-C2BEC4A41762}"/>
   <tableColumns count="2">
@@ -10249,14 +11142,14 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{8BE14E9C-9052-4C6B-91B5-74156B78161B}" name="IsZero_Tests" displayName="IsZero_Tests" ref="A63:E71" totalsRowCount="1" tableBorderDxfId="241">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{8BE14E9C-9052-4C6B-91B5-74156B78161B}" name="IsZero_Tests" displayName="IsZero_Tests" ref="A63:E71" totalsRowCount="1" tableBorderDxfId="284">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F079B266-FBE5-40B3-929D-6B075F83B32A}" name="input"/>
     <tableColumn id="2" xr3:uid="{D2EFB528-67FC-4490-876A-C72813F17A1C}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{735E5B6C-B3DA-49E2-B1F3-88323DE570B4}" name="output" dataDxfId="240">
+    <tableColumn id="3" xr3:uid="{735E5B6C-B3DA-49E2-B1F3-88323DE570B4}" name="output" dataDxfId="283">
       <calculatedColumnFormula array="1">xlInt.IsZero(IsZero_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BCB92B9B-DD7D-407D-BA1B-01844C06231A}" name="passing" totalsRowFunction="custom" dataDxfId="239">
+    <tableColumn id="4" xr3:uid="{BCB92B9B-DD7D-407D-BA1B-01844C06231A}" name="passing" totalsRowFunction="custom" dataDxfId="282">
       <calculatedColumnFormula>IF(ISERROR(IsZero_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsZero_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsZero_Tests[[#This Row],[output]]),
     IsZero_Tests[[#This Row],[expected]] = IsZero_Tests[[#This Row],[output]]
@@ -10270,14 +11163,14 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{5F9E4160-7872-486B-BC10-496D23C60B5A}" name="IsNeg_Tests" displayName="IsNeg_Tests" ref="A74:E82" totalsRowCount="1" tableBorderDxfId="238">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{5F9E4160-7872-486B-BC10-496D23C60B5A}" name="IsNeg_Tests" displayName="IsNeg_Tests" ref="A74:E82" totalsRowCount="1" tableBorderDxfId="281">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A7BB892B-ECAA-4176-AFC6-3449690829CA}" name="input"/>
     <tableColumn id="2" xr3:uid="{4B67C433-DA3F-4DC8-A14F-97407C2E1925}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{49ED0D04-2AA3-4848-8297-CAE5A7D726CD}" name="output" dataDxfId="237">
+    <tableColumn id="3" xr3:uid="{49ED0D04-2AA3-4848-8297-CAE5A7D726CD}" name="output" dataDxfId="280">
       <calculatedColumnFormula array="1">xlInt.IsNeg(IsNeg_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{186FF00B-FED3-490C-BB63-2A0FC55A43D4}" name="passing" totalsRowFunction="custom" dataDxfId="236">
+    <tableColumn id="4" xr3:uid="{186FF00B-FED3-490C-BB63-2A0FC55A43D4}" name="passing" totalsRowFunction="custom" dataDxfId="279">
       <calculatedColumnFormula>IF(ISERROR(IsNeg_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsNeg_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsNeg_Tests[[#This Row],[output]]),
     IsNeg_Tests[[#This Row],[expected]] = IsNeg_Tests[[#This Row],[output]]
@@ -10291,14 +11184,14 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1631B68B-6D5A-402C-92F6-EDA45141B375}" name="Abs_Tests" displayName="Abs_Tests" ref="A85:E94" totalsRowCount="1" tableBorderDxfId="235">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1631B68B-6D5A-402C-92F6-EDA45141B375}" name="Abs_Tests" displayName="Abs_Tests" ref="A85:E94" totalsRowCount="1" tableBorderDxfId="278">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{631C43FF-F966-4712-8BEB-7647066AF179}" name="input"/>
     <tableColumn id="2" xr3:uid="{70F5476C-B45C-439B-BA01-326EAD467334}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{1E90CD50-A25E-4E12-84D5-66BAAE6BAF0C}" name="output" dataDxfId="234">
+    <tableColumn id="3" xr3:uid="{1E90CD50-A25E-4E12-84D5-66BAAE6BAF0C}" name="output" dataDxfId="277">
       <calculatedColumnFormula array="1">BigInt.Abs(Abs_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6A0B92CA-92B2-4515-86E8-D91A4279D44E}" name="passing" totalsRowFunction="custom" dataDxfId="233">
+    <tableColumn id="4" xr3:uid="{6A0B92CA-92B2-4515-86E8-D91A4279D44E}" name="passing" totalsRowFunction="custom" dataDxfId="276">
       <calculatedColumnFormula>IF(ISERROR(Abs_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Abs_Tests[[#This Row],[expected]]) = ERROR.TYPE(Abs_Tests[[#This Row],[output]]),
     Abs_Tests[[#This Row],[expected]] = Abs_Tests[[#This Row],[output]]
@@ -10312,11 +11205,11 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{A4A096D6-4E75-4455-A80B-D324779CD007}" name="Compare_Tests" displayName="Compare_Tests" ref="A97:E104" totalsRowCount="1" dataDxfId="232" tableBorderDxfId="231">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{A4A096D6-4E75-4455-A80B-D324779CD007}" name="Compare_Tests" displayName="Compare_Tests" ref="A97:E104" totalsRowCount="1" dataDxfId="275" tableBorderDxfId="274">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{6ED51130-CCEE-49F5-AE6A-C115477DEEC1}" name="input" dataDxfId="230"/>
-    <tableColumn id="3" xr3:uid="{33B3A3D6-83B3-431F-A0B0-9371BBC16D08}" name="expected" dataDxfId="229"/>
-    <tableColumn id="4" xr3:uid="{C0A2BAFD-DD64-4B6D-8350-F0AF699F41AB}" name="output" dataDxfId="228">
+    <tableColumn id="2" xr3:uid="{6ED51130-CCEE-49F5-AE6A-C115477DEEC1}" name="input" dataDxfId="273"/>
+    <tableColumn id="3" xr3:uid="{33B3A3D6-83B3-431F-A0B0-9371BBC16D08}" name="expected" dataDxfId="272"/>
+    <tableColumn id="4" xr3:uid="{C0A2BAFD-DD64-4B6D-8350-F0AF699F41AB}" name="output" dataDxfId="271">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Compare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -10324,25 +11217,25 @@
     xlInt.Compare(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{25151C64-2D6E-4B12-87AA-02A64ED9EF2B}" name="passing" totalsRowFunction="custom" dataDxfId="227">
+    <tableColumn id="5" xr3:uid="{25151C64-2D6E-4B12-87AA-02A64ED9EF2B}" name="passing" totalsRowFunction="custom" dataDxfId="270">
       <calculatedColumnFormula>IF(ISERROR(Compare_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Compare_Tests[[#This Row],[expected]]) = ERROR.TYPE(Compare_Tests[[#This Row],[output]]),
     Compare_Tests[[#This Row],[expected]] = Compare_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Compare_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D859FAE6-EDFC-42C5-8B0C-0116D05E04F4}" name="test" dataDxfId="226"/>
+    <tableColumn id="6" xr3:uid="{D859FAE6-EDFC-42C5-8B0C-0116D05E04F4}" name="test" dataDxfId="269"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{AB2483E8-D478-4FD2-B96C-83A98FDDE6FA}" name="Carry_Tests" displayName="Carry_Tests" ref="A107:E114" totalsRowCount="1" dataDxfId="225">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{AB2483E8-D478-4FD2-B96C-83A98FDDE6FA}" name="Carry_Tests" displayName="Carry_Tests" ref="A107:E114" totalsRowCount="1" dataDxfId="268">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{58CF3EAC-5FAD-4E1D-8349-AFD0026A5A6F}" name="input" dataDxfId="224"/>
-    <tableColumn id="3" xr3:uid="{8D4EBB1D-1F70-4D9A-B9FB-C7B03997C3F4}" name="expected" dataDxfId="223"/>
-    <tableColumn id="4" xr3:uid="{54C37EF8-27DA-477C-BC79-632DD5E54F03}" name="output" dataDxfId="222">
+    <tableColumn id="2" xr3:uid="{58CF3EAC-5FAD-4E1D-8349-AFD0026A5A6F}" name="input" dataDxfId="267"/>
+    <tableColumn id="3" xr3:uid="{8D4EBB1D-1F70-4D9A-B9FB-C7B03997C3F4}" name="expected" dataDxfId="266"/>
+    <tableColumn id="4" xr3:uid="{54C37EF8-27DA-477C-BC79-632DD5E54F03}" name="output" dataDxfId="265">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.limbs_k, _xlfn.REGEXEXTRACT(Carry_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.limbs_text, INDEX(_xlpm.limbs_k,1,1),
@@ -10352,25 +11245,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9B430B30-AE60-423D-A6BE-D7D881CBC2A0}" name="passing" totalsRowFunction="custom" dataDxfId="221">
+    <tableColumn id="5" xr3:uid="{9B430B30-AE60-423D-A6BE-D7D881CBC2A0}" name="passing" totalsRowFunction="custom" dataDxfId="264">
       <calculatedColumnFormula>IF(ISERROR(Carry_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Carry_Tests[[#This Row],[expected]]) = ERROR.TYPE(Carry_Tests[[#This Row],[output]]),
     Carry_Tests[[#This Row],[expected]] = Carry_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Carry_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{5F961C10-163D-49CE-93C1-9CA6C9C623CA}" name="test" dataDxfId="220"/>
+    <tableColumn id="6" xr3:uid="{5F961C10-163D-49CE-93C1-9CA6C9C623CA}" name="test" dataDxfId="263"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{9541B332-DEB4-4260-9226-40E8C97DC59F}" name="UAdd_Tests" displayName="UAdd_Tests" ref="A117:E124" totalsRowCount="1" dataDxfId="219" tableBorderDxfId="218">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{9541B332-DEB4-4260-9226-40E8C97DC59F}" name="UAdd_Tests" displayName="UAdd_Tests" ref="A117:E124" totalsRowCount="1" dataDxfId="262" tableBorderDxfId="261">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{6C5FB7CE-3B1F-447E-9ED3-14E839061137}" name="input" dataDxfId="217"/>
-    <tableColumn id="3" xr3:uid="{56E7CDEA-877C-47CA-B875-1A1313998480}" name="expected" dataDxfId="216"/>
-    <tableColumn id="4" xr3:uid="{0AB7FE18-4035-4604-909F-956B1054DE95}" name="output" dataDxfId="215">
+    <tableColumn id="2" xr3:uid="{6C5FB7CE-3B1F-447E-9ED3-14E839061137}" name="input" dataDxfId="260"/>
+    <tableColumn id="3" xr3:uid="{56E7CDEA-877C-47CA-B875-1A1313998480}" name="expected" dataDxfId="259"/>
+    <tableColumn id="4" xr3:uid="{0AB7FE18-4035-4604-909F-956B1054DE95}" name="output" dataDxfId="258">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(UAdd_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -10382,14 +11275,14 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{148597F1-9D9D-45C9-949B-CA15D869DE95}" name="passing" totalsRowFunction="custom" dataDxfId="214">
+    <tableColumn id="5" xr3:uid="{148597F1-9D9D-45C9-949B-CA15D869DE95}" name="passing" totalsRowFunction="custom" dataDxfId="257">
       <calculatedColumnFormula>IF(ISERROR(UAdd_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UAdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(UAdd_Tests[[#This Row],[output]]),
     UAdd_Tests[[#This Row],[expected]] = UAdd_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UAdd_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{58290239-17D2-42FA-BE94-887F938260F4}" name="test" dataDxfId="213"/>
+    <tableColumn id="6" xr3:uid="{58290239-17D2-42FA-BE94-887F938260F4}" name="test" dataDxfId="256"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10712,7 +11605,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="892" row="6">
+  <wetp:taskpane dockstate="right" visibility="0" width="985" row="6">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -10744,7 +11637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23AD1BF5-F75F-465D-AC38-22DFE6D4806A}">
-  <dimension ref="A1:E391"/>
+  <dimension ref="A1:E431"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="27.54296875" customWidth="1"/>
@@ -10769,7 +11662,7 @@
       </c>
       <c r="B2">
         <f>COUNTIF(_xlfn._TRO_TRAILING(A:A), "input")</f>
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -10778,7 +11671,7 @@
       </c>
       <c r="B3" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">SUM(--ISNUMBER(SEARCH("[@expected] = [@output]", _xlfn.FORMULATEXT(_xlfn._TRO_TRAILING(D:D)))))</f>
-        <v>233</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -10787,7 +11680,7 @@
       </c>
       <c r="B4" cm="1">
         <f t="array" aca="1" ref="B4" ca="1">SUM(ISNUMBER(SEARCH("[@expected] = [@output]", _xlfn.FORMULATEXT(_xlfn._TRO_TRAILING(D:D)))) * (_xlfn._TRO_TRAILING(D:D) = TRUE))</f>
-        <v>233</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1"/>
@@ -17733,7 +18626,7 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="E346" s="18" t="s">
+      <c r="E346" s="9" t="s">
         <v>548</v>
       </c>
     </row>
@@ -17827,7 +18720,7 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="E352" s="18" t="s">
+      <c r="E352" s="9" t="s">
         <v>549</v>
       </c>
     </row>
@@ -17857,7 +18750,7 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="E353" s="18" t="s">
+      <c r="E353" s="9" t="s">
         <v>550</v>
       </c>
     </row>
@@ -17887,7 +18780,7 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="E354" s="18" t="s">
+      <c r="E354" s="9" t="s">
         <v>551</v>
       </c>
     </row>
@@ -17917,7 +18810,7 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="E355" s="18" t="s">
+      <c r="E355" s="9" t="s">
         <v>552</v>
       </c>
     </row>
@@ -17981,7 +18874,7 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="E360" s="18" t="s">
+      <c r="E360" s="9" t="s">
         <v>554</v>
       </c>
     </row>
@@ -18012,7 +18905,7 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="E361" s="18" t="s">
+      <c r="E361" s="9" t="s">
         <v>555</v>
       </c>
     </row>
@@ -18043,7 +18936,7 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="E362" s="18" t="s">
+      <c r="E362" s="9" t="s">
         <v>556</v>
       </c>
     </row>
@@ -18074,7 +18967,7 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="E363" s="18" t="s">
+      <c r="E363" s="9" t="s">
         <v>557</v>
       </c>
     </row>
@@ -18085,7 +18978,7 @@
       <c r="B364" s="9" t="s">
         <v>562</v>
       </c>
-      <c r="C364" s="19" t="str" cm="1">
+      <c r="C364" s="9" t="str" cm="1">
         <f t="array" ref="C364">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(NewtonRaphsonDiv_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -18098,14 +18991,14 @@
 )</f>
         <v>{1;0;0;0;10}</v>
       </c>
-      <c r="D364" s="19" t="b">
+      <c r="D364" s="9" t="b">
         <f>IF(ISERROR(NewtonRaphsonDiv_Tests[[#This Row],[expected]]),
     ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[output]]),
     NewtonRaphsonDiv_Tests[[#This Row],[expected]] = NewtonRaphsonDiv_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E364" s="18" t="s">
+      <c r="E364" s="9" t="s">
         <v>558</v>
       </c>
     </row>
@@ -18115,272 +19008,1047 @@
         <v>1</v>
       </c>
     </row>
+    <row r="366" spans="1:5" ht="15" thickBot="1"/>
+    <row r="367" spans="1:5" ht="18.5">
+      <c r="A367" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="B367" s="5"/>
+      <c r="C367" s="5"/>
+      <c r="D367" s="5"/>
+      <c r="E367" s="5"/>
+    </row>
     <row r="368" spans="1:5">
-      <c r="A368" s="2"/>
-      <c r="B368" s="2"/>
-    </row>
-    <row r="373" ht="14.5" customHeight="1"/>
-    <row r="376" ht="14.5" customHeight="1"/>
-    <row r="379" ht="14.5" customHeight="1"/>
-    <row r="382" ht="14.5" customHeight="1"/>
-    <row r="385" spans="1:2" ht="14.5" customHeight="1"/>
-    <row r="387" spans="1:2">
-      <c r="A387" cm="1">
-        <f t="array" ref="A387:A388">LEN(B387:B388)</f>
+      <c r="A368" t="s">
+        <v>110</v>
+      </c>
+      <c r="B368" t="s">
+        <v>35</v>
+      </c>
+      <c r="C368" t="s">
+        <v>36</v>
+      </c>
+      <c r="D368" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E368" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A369" s="9">
+        <v>2</v>
+      </c>
+      <c r="B369" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C369" s="9" t="str">
+        <f>_xlfn.ARRAYTOTEXT(core_BigInt.NativePrimes(NativePrimes_Tests[[#This Row],[input]]), 1)</f>
+        <v>{2}</v>
+      </c>
+      <c r="D369" s="9" t="b">
+        <f>IF(ISERROR(NativePrimes_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NativePrimes_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativePrimes_Tests[[#This Row],[output]]),
+    NativePrimes_Tests[[#This Row],[expected]] = NativePrimes_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E369" s="9" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A370" s="9">
+        <v>10</v>
+      </c>
+      <c r="B370" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="C370" s="9" t="str">
+        <f>_xlfn.ARRAYTOTEXT(core_BigInt.NativePrimes(NativePrimes_Tests[[#This Row],[input]]), 1)</f>
+        <v>{2;3;5;7}</v>
+      </c>
+      <c r="D370" s="9" t="b">
+        <f>IF(ISERROR(NativePrimes_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NativePrimes_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativePrimes_Tests[[#This Row],[output]]),
+    NativePrimes_Tests[[#This Row],[expected]] = NativePrimes_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E370" s="9" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A371" s="9">
+        <v>20</v>
+      </c>
+      <c r="B371" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="C371" s="9" t="str">
+        <f>_xlfn.ARRAYTOTEXT(core_BigInt.NativePrimes(NativePrimes_Tests[[#This Row],[input]]), 1)</f>
+        <v>{2;3;5;7;11;13;17;19}</v>
+      </c>
+      <c r="D371" s="9" t="b">
+        <f>IF(ISERROR(NativePrimes_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NativePrimes_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativePrimes_Tests[[#This Row],[output]]),
+    NativePrimes_Tests[[#This Row],[expected]] = NativePrimes_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E371" s="9" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A372" s="9">
+        <v>1</v>
+      </c>
+      <c r="B372" s="9" t="e">
+        <f>_xlfn.ARRAYTOTEXT(core_BigInt.NativePrimes(NativePrimes_Tests[[#This Row],[input]]), 1)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="C372" s="9" t="e">
+        <f>_xlfn.ARRAYTOTEXT(core_BigInt.NativePrimes(NativePrimes_Tests[[#This Row],[input]]), 1)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="D372" s="9" t="b">
+        <f>IF(ISERROR(NativePrimes_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NativePrimes_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativePrimes_Tests[[#This Row],[output]]),
+    NativePrimes_Tests[[#This Row],[expected]] = NativePrimes_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E372" s="9" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A373" s="9">
+        <v>0</v>
+      </c>
+      <c r="B373" s="9" t="e">
+        <f>_xlfn.ARRAYTOTEXT(core_BigInt.NativePrimes(NativePrimes_Tests[[#This Row],[input]]), 1)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="C373" s="9" t="e">
+        <f>_xlfn.ARRAYTOTEXT(core_BigInt.NativePrimes(NativePrimes_Tests[[#This Row],[input]]), 1)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="D373" s="9" t="b">
+        <f>IF(ISERROR(NativePrimes_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NativePrimes_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativePrimes_Tests[[#This Row],[output]]),
+    NativePrimes_Tests[[#This Row],[expected]] = NativePrimes_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E373" s="9" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" collapsed="1">
+      <c r="A374" s="2"/>
+      <c r="D374" t="b">
+        <f>AND(NativePrimes_Tests[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" ht="15" thickBot="1"/>
+    <row r="376" spans="1:5" ht="18.5">
+      <c r="A376" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="B376" s="5"/>
+      <c r="C376" s="5"/>
+      <c r="D376" s="5"/>
+      <c r="E376" s="5"/>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" t="s">
+        <v>110</v>
+      </c>
+      <c r="B377" t="s">
+        <v>35</v>
+      </c>
+      <c r="C377" t="s">
+        <v>36</v>
+      </c>
+      <c r="D377" t="s">
+        <v>48</v>
+      </c>
+      <c r="E377" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A378" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="B378" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="C378" s="12" t="str" cm="1">
+        <f t="array" ref="C378">_xlfn.LET(
+    _xlpm.n_primes, _xlfn.REGEXEXTRACT(NativeLegendre_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.n, --INDEX(_xlpm.n_primes,1,1),
+    _xlpm.primes, INDEX(_xlpm.n_primes,1,2),
+    _xlpm.primes_arr, --_xlfn.TEXTSPLIT(_xlpm.primes,",",";"),
+    _xlpm.output, core_BigInt.NativeLegendre(_xlpm.n, _xlpm.primes_arr),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{8;4;2;1}</v>
+      </c>
+      <c r="D378" s="12" t="b">
+        <f>IF(ISERROR(NativeLegendre_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NativeLegendre_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativeLegendre_Tests[[#This Row],[output]]),
+    NativeLegendre_Tests[[#This Row],[expected]] = NativeLegendre_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E378" s="12" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A379" s="12" t="s">
+        <v>584</v>
+      </c>
+      <c r="B379" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="C379" s="12" t="str" cm="1">
+        <f t="array" ref="C379">_xlfn.LET(
+    _xlpm.n_primes, _xlfn.REGEXEXTRACT(NativeLegendre_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.n, --INDEX(_xlpm.n_primes,1,1),
+    _xlpm.primes, INDEX(_xlpm.n_primes,1,2),
+    _xlpm.primes_arr, --_xlfn.TEXTSPLIT(_xlpm.primes,",",";"),
+    _xlpm.output, core_BigInt.NativeLegendre(_xlpm.n, _xlpm.primes_arr),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{1}</v>
+      </c>
+      <c r="D379" s="12" t="b">
+        <f>IF(ISERROR(NativeLegendre_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NativeLegendre_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativeLegendre_Tests[[#This Row],[output]]),
+    NativeLegendre_Tests[[#This Row],[expected]] = NativeLegendre_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E379" s="12" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A380" s="12" t="s">
+        <v>585</v>
+      </c>
+      <c r="B380" s="12" t="s">
+        <v>582</v>
+      </c>
+      <c r="C380" s="12" t="str" cm="1">
+        <f t="array" ref="C380">_xlfn.LET(
+    _xlpm.n_primes, _xlfn.REGEXEXTRACT(NativeLegendre_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.n, --INDEX(_xlpm.n_primes,1,1),
+    _xlpm.primes, INDEX(_xlpm.n_primes,1,2),
+    _xlpm.primes_arr, --_xlfn.TEXTSPLIT(_xlpm.primes,",",";"),
+    _xlpm.output, core_BigInt.NativeLegendre(_xlpm.n, _xlpm.primes_arr),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{3;1;1}</v>
+      </c>
+      <c r="D380" s="12" t="b">
+        <f>IF(ISERROR(NativeLegendre_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NativeLegendre_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativeLegendre_Tests[[#This Row],[output]]),
+    NativeLegendre_Tests[[#This Row],[expected]] = NativeLegendre_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E380" s="12" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" collapsed="1">
+      <c r="D381" s="9" t="b">
+        <f>AND(NativeLegendre_Tests[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" ht="15" thickBot="1"/>
+    <row r="383" spans="1:5" ht="18.5">
+      <c r="A383" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="B383" s="5"/>
+      <c r="C383" s="5"/>
+      <c r="D383" s="5"/>
+      <c r="E383" s="5"/>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" t="s">
+        <v>110</v>
+      </c>
+      <c r="B384" t="s">
+        <v>35</v>
+      </c>
+      <c r="C384" t="s">
+        <v>36</v>
+      </c>
+      <c r="D384" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E384" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A385" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="B385" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C385" s="12" t="str" cm="1">
+        <f t="array" ref="C385">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(UTextMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab,1,1),
+    _xlpm.b, INDEX(_xlpm.ab,1,2),
+    core_BigInt.UTextMul(_xlpm.a, _xlpm.b)
+)</f>
+        <v>998001</v>
+      </c>
+      <c r="D385" s="9" t="b">
+        <f>IF(ISERROR(UTextMul_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(UTextMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UTextMul_Tests[[#This Row],[output]]),
+    UTextMul_Tests[[#This Row],[expected]] = UTextMul_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E385" s="12" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A386" s="12" t="s">
+        <v>602</v>
+      </c>
+      <c r="B386" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="C386" s="12" t="str" cm="1">
+        <f t="array" ref="C386">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(UTextMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab,1,1),
+    _xlpm.b, INDEX(_xlpm.ab,1,2),
+    core_BigInt.UTextMul(_xlpm.a, _xlpm.b)
+)</f>
+        <v>246912</v>
+      </c>
+      <c r="D386" s="9" t="b">
+        <f>IF(ISERROR(UTextMul_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(UTextMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UTextMul_Tests[[#This Row],[output]]),
+    UTextMul_Tests[[#This Row],[expected]] = UTextMul_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E386" s="12" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A387" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="B387" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="C387" s="12" t="str" cm="1">
+        <f t="array" ref="C387">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(UTextMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab,1,1),
+    _xlpm.b, INDEX(_xlpm.ab,1,2),
+    core_BigInt.UTextMul(_xlpm.a, _xlpm.b)
+)</f>
+        <v>1000000</v>
+      </c>
+      <c r="D387" s="9" t="b">
+        <f>IF(ISERROR(UTextMul_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(UTextMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UTextMul_Tests[[#This Row],[output]]),
+    UTextMul_Tests[[#This Row],[expected]] = UTextMul_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E387" s="12" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A388" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="B388" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C388" s="12" t="str" cm="1">
+        <f t="array" ref="C388">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(UTextMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab,1,1),
+    _xlpm.b, INDEX(_xlpm.ab,1,2),
+    core_BigInt.UTextMul(_xlpm.a, _xlpm.b)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="D388" s="9" t="b">
+        <f>IF(ISERROR(UTextMul_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(UTextMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UTextMul_Tests[[#This Row],[output]]),
+    UTextMul_Tests[[#This Row],[expected]] = UTextMul_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E388" s="12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A389" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="B389" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C389" s="12" t="str" cm="1">
+        <f t="array" ref="C389">_xlfn.LET(
+    _xlpm.ab, _xlfn.REGEXEXTRACT(UTextMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.a, INDEX(_xlpm.ab,1,1),
+    _xlpm.b, INDEX(_xlpm.ab,1,2),
+    core_BigInt.UTextMul(_xlpm.a, _xlpm.b)
+)</f>
+        <v>999999999999999999</v>
+      </c>
+      <c r="D389" s="9" t="b">
+        <f>IF(ISERROR(UTextMul_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(UTextMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UTextMul_Tests[[#This Row],[output]]),
+    UTextMul_Tests[[#This Row],[expected]] = UTextMul_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E389" s="12" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A390" s="12"/>
+      <c r="B390" s="12"/>
+      <c r="C390" s="12"/>
+      <c r="D390" s="9" t="b">
+        <f>AND(UTextMul_Tests[passing])</f>
+        <v>1</v>
+      </c>
+      <c r="E390" s="12"/>
+    </row>
+    <row r="391" spans="1:5" ht="15" collapsed="1" thickBot="1"/>
+    <row r="392" spans="1:5" ht="18.5">
+      <c r="A392" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="B392" s="5"/>
+      <c r="C392" s="5"/>
+      <c r="D392" s="5"/>
+      <c r="E392" s="5"/>
+    </row>
+    <row r="393" spans="1:5">
+      <c r="A393" t="s">
+        <v>110</v>
+      </c>
+      <c r="B393" t="s">
+        <v>35</v>
+      </c>
+      <c r="C393" t="s">
+        <v>36</v>
+      </c>
+      <c r="D393" t="s">
+        <v>48</v>
+      </c>
+      <c r="E393" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A394" s="12" t="s">
+        <v>590</v>
+      </c>
+      <c r="B394" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C394" s="12" t="str" cm="1">
+        <f t="array" ref="C394">_xlfn.LET(
+    _xlpm.big_ints, _xlfn.REGEXEXTRACT(TextTreeProd_Tests37[[#This Row],[input]], "{\K[\w,; .-]*"),
+    _xlpm.big_int_arr, _xlfn.TEXTSPLIT(_xlpm.big_ints,",",";"),
+    core_BigInt.TextTreeProd(_xlpm.big_int_arr)
+)</f>
         <v>5</v>
       </c>
-      <c r="B387" t="str" cm="1">
-        <f t="array" ref="B387">BigInt.Sqrt(B390)</f>
-        <v>46340</v>
-      </c>
-    </row>
-    <row r="388" spans="1:2">
-      <c r="A388">
-        <v>5</v>
-      </c>
-      <c r="B388" t="str" cm="1">
-        <f t="array" ref="B388">_xlfn._xlws.PY(0,0,B390,B391)</f>
-        <v>46340</v>
-      </c>
-    </row>
-    <row r="389" spans="1:2">
-      <c r="B389" t="b">
-        <f>B387 = B388</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="390" spans="1:2">
-      <c r="A390">
-        <f>LEN(B390)</f>
-        <v>10</v>
-      </c>
-      <c r="B390" s="2">
-        <f>2^31-1</f>
-        <v>2147483647</v>
-      </c>
-    </row>
-    <row r="391" spans="1:2">
-      <c r="B391">
+      <c r="D394" s="12" t="b">
+        <f>IF(ISERROR(TextTreeProd_Tests37[[#This Row],[expected]]),
+    ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[expected]]) = ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[output]]),
+    TextTreeProd_Tests37[[#This Row],[expected]] = TextTreeProd_Tests37[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E394" s="12" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A395" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="B395" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="C395" s="12" t="str" cm="1">
+        <f t="array" ref="C395">_xlfn.LET(
+    _xlpm.big_ints, _xlfn.REGEXEXTRACT(TextTreeProd_Tests37[[#This Row],[input]], "{\K[\w,; .-]*"),
+    _xlpm.big_int_arr, _xlfn.TEXTSPLIT(_xlpm.big_ints,",",";"),
+    core_BigInt.TextTreeProd(_xlpm.big_int_arr)
+)</f>
+        <v>6</v>
+      </c>
+      <c r="D395" s="12" t="b">
+        <f>IF(ISERROR(TextTreeProd_Tests37[[#This Row],[expected]]),
+    ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[expected]]) = ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[output]]),
+    TextTreeProd_Tests37[[#This Row],[expected]] = TextTreeProd_Tests37[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E395" s="12" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A396" s="12" t="s">
+        <v>592</v>
+      </c>
+      <c r="B396" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="C396" s="12" t="str" cm="1">
+        <f t="array" ref="C396">_xlfn.LET(
+    _xlpm.big_ints, _xlfn.REGEXEXTRACT(TextTreeProd_Tests37[[#This Row],[input]], "{\K[\w,; .-]*"),
+    _xlpm.big_int_arr, _xlfn.TEXTSPLIT(_xlpm.big_ints,",",";"),
+    core_BigInt.TextTreeProd(_xlpm.big_int_arr)
+)</f>
+        <v>24</v>
+      </c>
+      <c r="D396" s="12" t="b">
+        <f>IF(ISERROR(TextTreeProd_Tests37[[#This Row],[expected]]),
+    ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[expected]]) = ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[output]]),
+    TextTreeProd_Tests37[[#This Row],[expected]] = TextTreeProd_Tests37[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E396" s="12" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A397" s="12" t="s">
+        <v>593</v>
+      </c>
+      <c r="B397" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="C397" s="18" t="str" cm="1">
+        <f t="array" ref="C397">_xlfn.LET(
+    _xlpm.big_ints, _xlfn.REGEXEXTRACT(TextTreeProd_Tests37[[#This Row],[input]], "{\K[\w,; .-]*"),
+    _xlpm.big_int_arr, _xlfn.TEXTSPLIT(_xlpm.big_ints,",",";"),
+    core_BigInt.TextTreeProd(_xlpm.big_int_arr)
+)</f>
+        <v>120</v>
+      </c>
+      <c r="D397" s="18" t="b">
+        <f>IF(ISERROR(TextTreeProd_Tests37[[#This Row],[expected]]),
+    ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[expected]]) = ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[output]]),
+    TextTreeProd_Tests37[[#This Row],[expected]] = TextTreeProd_Tests37[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E397" s="19" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" collapsed="1">
+      <c r="D398" s="9" t="b">
+        <f>AND(TextTreeProd_Tests37[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" ht="15" thickBot="1"/>
+    <row r="400" spans="1:5" ht="18.5">
+      <c r="A400" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="B400" s="5"/>
+      <c r="C400" s="5"/>
+      <c r="D400" s="5"/>
+      <c r="E400" s="5"/>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401" t="s">
+        <v>110</v>
+      </c>
+      <c r="B401" t="s">
+        <v>35</v>
+      </c>
+      <c r="C401" t="s">
+        <v>36</v>
+      </c>
+      <c r="D401" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E401" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A402" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B402" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C402" s="9" t="str" cm="1">
+        <f t="array" ref="C402">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
+        <v>1</v>
+      </c>
+      <c r="D402" s="9" t="b">
+        <f>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
+    Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E402" s="9" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A403" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B403" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C403" s="9" t="str" cm="1">
+        <f t="array" ref="C403">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
+        <v>1</v>
+      </c>
+      <c r="D403" s="9" t="b">
+        <f>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
+    Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E403" s="9" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A404" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B404" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="C404" s="9" t="str" cm="1">
+        <f t="array" ref="C404">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
+        <v>120</v>
+      </c>
+      <c r="D404" s="9" t="b">
+        <f>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
+    Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E404" s="9" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A405" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="B405" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="C405" s="20" t="str" cm="1">
+        <f t="array" ref="C405">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
+        <v>3628800</v>
+      </c>
+      <c r="D405" s="20" t="b">
+        <f>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
+    Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E405" s="21" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A406" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="B406" s="9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="C406" s="20" t="e" cm="1">
+        <f t="array" ref="C406">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="D406" s="20" t="b">
+        <f>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
+    Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E406" s="21" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A407" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="B407" s="9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="C407" s="9" t="e" cm="1">
+        <f t="array" ref="C407">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="D407" s="9" t="b">
+        <f>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
+    Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E407" s="9" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A408" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="B408" s="9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="C408" s="9" t="e" cm="1">
+        <f t="array" ref="C408">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="D408" s="9" t="b">
+        <f>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
+    Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E408" s="9" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" collapsed="1">
+      <c r="A409" s="2"/>
+      <c r="D409" t="b">
+        <f>AND(Fact_Tests[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" ht="14.5" customHeight="1"/>
+    <row r="421" spans="1:2" ht="14.5" customHeight="1"/>
+    <row r="424" spans="1:2" ht="14.5" customHeight="1"/>
+    <row r="427" spans="1:2" ht="14.5" customHeight="1">
+      <c r="A427" cm="1">
+        <f t="array" ref="A427:A428">LEN(B427:B428)</f>
+        <v>68</v>
+      </c>
+      <c r="B427" t="str" cm="1">
+        <f t="array" ref="B427">BigInt.Fact(B430)</f>
+        <v>80658175170943878571660636856403766975289505440883277824000000000000</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428">
+        <v>68</v>
+      </c>
+      <c r="B428" t="str" cm="1">
+        <f t="array" ref="B428">_xlfn._xlws.PY(0,0,B430,B431)</f>
+        <v>80658175170943878571660636856403766975289505440883277824000000000000</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="B429" t="b">
+        <f>B427 = B428</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" ht="14.5" customHeight="1">
+      <c r="A430">
+        <f>LEN(B430)</f>
+        <v>2</v>
+      </c>
+      <c r="B430" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="B431">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B389">
-    <cfRule type="cellIs" dxfId="52" priority="7" operator="equal">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A420:E422">
+    <sortCondition ref="A418:A422"/>
+  </sortState>
+  <conditionalFormatting sqref="B429">
+    <cfRule type="cellIs" dxfId="57" priority="19" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8:D26 D150:D160 D265:D280 D284:D289 D317:D324">
-    <cfRule type="expression" dxfId="51" priority="76" stopIfTrue="1">
+  <conditionalFormatting sqref="D8:D26 D150:D160 D265:D280 D284:D289 D317:D324 D378:D381 D394:D398 D385:D390">
+    <cfRule type="expression" dxfId="56" priority="88" stopIfTrue="1">
       <formula>$D8</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="77">
+    <cfRule type="expression" dxfId="55" priority="89">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:D37 D86:D94 D118:D124">
-    <cfRule type="expression" dxfId="49" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="86" stopIfTrue="1">
       <formula>$D30</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="75">
+    <cfRule type="expression" dxfId="53" priority="87">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41:D46">
-    <cfRule type="expression" dxfId="47" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="82" stopIfTrue="1">
       <formula>$D41</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="71">
+    <cfRule type="expression" dxfId="51" priority="83">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:D60">
-    <cfRule type="expression" dxfId="45" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="72" stopIfTrue="1">
       <formula>$D50</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="61">
+    <cfRule type="expression" dxfId="49" priority="73">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D64:D71">
-    <cfRule type="expression" dxfId="43" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="80" stopIfTrue="1">
       <formula>$D64</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="69">
+    <cfRule type="expression" dxfId="47" priority="81">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75:D82">
-    <cfRule type="expression" dxfId="41" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="78" stopIfTrue="1">
       <formula>$D75</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="67">
+    <cfRule type="expression" dxfId="45" priority="79">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D98:D104">
-    <cfRule type="expression" dxfId="39" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="70" stopIfTrue="1">
       <formula>$D98</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="59">
+    <cfRule type="expression" dxfId="43" priority="71">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:D114">
-    <cfRule type="expression" dxfId="37" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="68" stopIfTrue="1">
       <formula>$D108</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="57">
+    <cfRule type="expression" dxfId="41" priority="69">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D128:D135">
-    <cfRule type="expression" dxfId="35" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="64" stopIfTrue="1">
       <formula>$D128</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="53">
+    <cfRule type="expression" dxfId="39" priority="65">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D139:D146">
-    <cfRule type="expression" dxfId="33" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="62" stopIfTrue="1">
       <formula>$D139</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="51">
+    <cfRule type="expression" dxfId="37" priority="63">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D164:D169">
-    <cfRule type="expression" dxfId="31" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="56" stopIfTrue="1">
       <formula>$D164</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="45">
+    <cfRule type="expression" dxfId="35" priority="57">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D173:D176">
-    <cfRule type="expression" dxfId="29" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="54" stopIfTrue="1">
       <formula>$D173</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="43">
+    <cfRule type="expression" dxfId="33" priority="55">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D180:D183">
-    <cfRule type="expression" dxfId="27" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="50" stopIfTrue="1">
       <formula>$D180</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="39">
+    <cfRule type="expression" dxfId="31" priority="51">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D187:D191">
-    <cfRule type="expression" dxfId="25" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="48" stopIfTrue="1">
       <formula>$D187</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="37">
+    <cfRule type="expression" dxfId="29" priority="49">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D195:D202">
-    <cfRule type="expression" dxfId="23" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="46" stopIfTrue="1">
       <formula>$D195</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="35">
+    <cfRule type="expression" dxfId="27" priority="47">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D206:D211">
-    <cfRule type="expression" dxfId="21" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="42" stopIfTrue="1">
       <formula>$D206</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="31">
+    <cfRule type="expression" dxfId="25" priority="43">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D215:D221">
-    <cfRule type="expression" dxfId="19" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="40" stopIfTrue="1">
       <formula>$D215</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="29">
+    <cfRule type="expression" dxfId="23" priority="41">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D225:D233">
-    <cfRule type="expression" dxfId="17" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="36" stopIfTrue="1">
       <formula>$D225</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="25">
+    <cfRule type="expression" dxfId="21" priority="37">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D237:D247">
-    <cfRule type="expression" dxfId="15" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="34" stopIfTrue="1">
       <formula>$D237</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="23">
+    <cfRule type="expression" dxfId="19" priority="35">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D251:D261">
-    <cfRule type="expression" dxfId="13" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="32" stopIfTrue="1">
       <formula>$D251</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="21">
+    <cfRule type="expression" dxfId="17" priority="33">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D293:D301">
-    <cfRule type="expression" dxfId="11" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="26" stopIfTrue="1">
       <formula>$D293</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="15">
+    <cfRule type="expression" dxfId="15" priority="27">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D305:D313">
-    <cfRule type="expression" dxfId="9" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="24" stopIfTrue="1">
       <formula>$D305</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="13">
+    <cfRule type="expression" dxfId="13" priority="25">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D328:D341">
-    <cfRule type="expression" dxfId="7" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="22" stopIfTrue="1">
       <formula>$D328</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="11">
+    <cfRule type="expression" dxfId="11" priority="23">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D345:D348">
-    <cfRule type="expression" dxfId="5" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="17" stopIfTrue="1">
       <formula>$D345</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="9" priority="18">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D352:D356">
-    <cfRule type="expression" dxfId="3" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="15" stopIfTrue="1">
       <formula>$D352</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="7" priority="16">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D360:D365">
-    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="13" stopIfTrue="1">
       <formula>$D360</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="5" priority="14">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D369:D374">
+    <cfRule type="expression" dxfId="4" priority="9" stopIfTrue="1">
+      <formula>$D369</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="10">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D402:D409">
+    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
+      <formula>$D402</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="32">
+  <tableParts count="37">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -18413,6 +20081,11 @@
     <tablePart r:id="rId31"/>
     <tablePart r:id="rId32"/>
     <tablePart r:id="rId33"/>
+    <tablePart r:id="rId34"/>
+    <tablePart r:id="rId35"/>
+    <tablePart r:id="rId36"/>
+    <tablePart r:id="rId37"/>
+    <tablePart r:id="rId38"/>
   </tableParts>
 </worksheet>
 </file>
@@ -18647,7 +20320,7 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAFwAbgAvAC8AIABCAGkAZwAgAEkAbgB0AGUAZwBlAHIAIABBAHIAaQB0AGgAbQBlAHQAaQBjACAATABpAGIAcgBhAHIAeQAgAC8ALwBcAG4ALwAvACAAIAAgACAAIAAgACAAdABlAHMAdABfAEIAaQBnAEkAbgB0ACAATQBvAGQAdQBsAGUAIAAgACAAIAAgACAAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIAAgAFAAcgBpAHYAYQB0AGUAIABUAGUAcwB0AGkAbgBnACAAQQBQAEkAIAAgACAAIAAgACAALwAvAFwAbgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4AXABuAEsAbgB1AHQAaABEAGkAdgBpAHMAaQBvAG4APQBMAEEATQBCAEQAQQAoAGEALAAgAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2ACgAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYQAsACAAawApACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABiACwAIABrACkALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAEQAUgBPAFAAKABwAGEAYwBrAGUAZAAsACAASQBOAEQARQBYACgAcABhAGMAawBlAGQALAAgADEALAAgADEAKQAgACsAIAAxACkALAAgAGsAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAgAD0AIABMAEEATQBCAEQAQQAoAGEALAAgAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgAoAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAGEALAAgAGsAKQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYgAsACAAawApACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABEAFIATwBQACgAcABhAGMAawBlAGQALAAgAEkATgBEAEUAWAAoAHAAYQBjAGsAZQBkACwAIAAxACwAIAAxACkAIAArACAAMQApACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAcwB0AHIAaQBuAGcAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAHMAdAByAGkAbgBnAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG0AbwBkAGUAIABcACIASwBOAFUAVABIAFwAIgAgAG8AcgAgAFwAIgBOAFIAXAAiAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGkAdABlAHIAcwAgAEkAbgBuAGUAcgAgAGwAbwBvAHAAIABjAG8AdQBuAHQAIAAoAHQAbwAgAGQAZQBmAGUAYQB0ACAAYwBoAHUAbgBrAHkAIABjAGwAbwBjAGsAIAByAGUAcwBvAGwAdQB0AGkAbwBuACkAXABuACAAKgAgAEAAcABhAHIAYQBtACAAcgBlAHAAZQBhAHQAcwAgAE8AdQB0AGUAcgAgAGwAbwBvAHAAIABjAG8AdQBuAHQAIAAoAHQAbwAgAGQAZQBmAGUAYQB0ACAATwBTAC8ARwBhAHIAYgBhAGcAZQAgAEMAbwBsAGwAZQBjAHQAaQBvAG4AIABuAG8AaQBzAGUAKQBcAG4AIAAqAC8AXABuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACAAPQAgAEwAQQBNAEIARABBACgAYQAsACAAYgAsACAAbQBvAGQAZQAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAE0AYQBwACAAdABoAGUAIABvAHUAdABlAHIAIAByAGUAcABlAGEAdABzACAAbABvAG8AcABcAG4AIAAgACAAIAAgACAAIAAgAGIAYQB0AGMAaABfAHQAaQBtAGUAcwAsACAATQBBAFAAKABTAEUAUQBVAEUATgBDAEUAKAByAGUAcABlAGEAdABzACkALAAgAEwAQQBNAEIARABBACgAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdAAsACAATgBPAFcAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATQBhAHAAIAB0AGgAZQAgAGkAbgBuAGUAcgAgAGUAeABlAGMAdQB0AGkAbwBuACAAbABvAG8AcABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAHUAbgAsACAASQBGACgAbQBvAGQAZQAgAD0AIABcACIASwBOAFUAVABIAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBQACgAUwBFAFEAVQBFAE4AQwBFACgAaQB0AGUAcgBzACkALAAgAEwAQQBNAEIARABBACgAaQAsACAASwBuAHUAdABoAEQAaQB2AGkAcwBpAG8AbgAoAGEALAAgAGIAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFAAKABTAEUAUQBVAEUATgBDAEUAKABpAHQAZQByAHMAKQAsACAATABBAE0AQgBEAEEAKABpACwAIABOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAoAGEALAAgAGIAKQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEYAbwByAGMAZQAgAGUAdgBhAGwAdQBhAHQAaQBvAG4AIABiAGUAZgBvAHIAZQAgAHAAdQBsAGwAaQBuAGcAIABzAHQAbwBwACAAdABpAG0AZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAbwBwACwAIABOAE8AVwAoACkAIAArACAAKAAwACAAKgAgAEwARQBOACgASQBOAEQARQBYACgAcgB1AG4ALAAgADEALAAgADEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABUAG8AdABhAGwAIABiAGEAdABjAGgAIAB0AGkAbQBlACAAaQBuACAAbQBpAGwAbABpAHMAZQBjAG8AbgBkAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABzAHQAbwBwACAALQAgAHMAdABhAHIAdAApACAAKgAgADgANgA0ADAAMAAwADAAMABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAdABoAGUAIABjAGwAZQBhAG4AZQBzAHQAIAByAHUAbgAgAGEAbgBkACAAYQB2AGUAcgBhAGcAZQAgAGkAdAAgAGQAbwB3AG4AIAB0AG8AIABhACAAcwBpAG4AZwBsAGUAIABlAHgAZQBjAHUAdABpAG8AbgAgAHQAaQBtAGUAXABuACAAIAAgACAAIAAgACAAIABNAEkATgAoAGIAYQB0AGMAaABfAHQAaQBtAGUAcwApACAALwAgAGkAdABlAHIAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAARQB4AGUAYwB1AHQAZQBzACAAYQAgAHMAdAByAGkAYwB0AGwAeQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABiAGUAbgBjAGgAbQBhAHIAawAgAHMAdQBpAHQAZQAgAHQAbwAgAGEAdgBvAGkAZAAgAG0AdQBsAHQAaQAtAHQAaAByAGUAYQBkAGkAbgBnACAAYwBvAG4AdABhAG0AaQBuAGEAdABpAG8AbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHQAZQBzAHQAXwBjAGEAcwBlAHMAIABBAG4AIABOACAAeAAgADIAIABhAHIAcgBhAHkAIABvAGYAIAB0AGUAcwB0ACAAbABlAG4AZwB0AGgAcwA6ACAAWwBMAGUAbgBnAHQAaABfAEEALAAgAEwAZQBuAGcAdABoAF8AQgBdAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGkAdABlAHIAcwAgAE4AdQBtAGIAZQByACAAbwBmACAAaQB0AGUAcgBhAHQAaQBvAG4AcwAgAHAAZQByACAAYgBlAG4AYwBoAG0AYQByAGsAIAB0AG8AIABzAG0AbwBvAHQAaAAgAE4ATwBXACgAKQAgAHIAZQBzAG8AbAB1AHQAaQBvAG4ALgBcAG4AIAAqAC8AXABuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBDAG8AbQBwAGEAcgBpAHMAbwBuACAAPQAgAEwAQQBNAEIARABBACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwB0AGUAcwB0AHMALAAgAFIATwBXAFMAKAB0AGUAcwB0AF8AYwBhAHMAZQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAASQBuAGkAdABpAGEAbAAgAHMAdABhAHQAZQA6ACAARABhAHQAYQAgAGgAZQBhAGQAZQByAHMAIABmAG8AcgAgAEMAUwBWACAAZQB4AHAAbwByAHQAXABuACAAIAAgACAAIAAgACAAIABpAG4AaQB0AGkAYQBsACwAIAB7AFwAIgBMAGUAbgBfAEEAXAAiACwAIABcACIATABlAG4AXwBCAFwAIgAsACAAXAAiAEsAbgB1AHQAaABfAG0AcwBcACIALAAgAFwAIgBOAFIAXwBtAHMAXAAiAH0ALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsACwAIABTAEUAUQBVAEUATgBDAEUAKABuAF8AdABlAHMAdABzACkALAAgAEwAQQBNAEIARABBACgAYQBjAGMALAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAEkATgBEAEUAWAAoAHQAZQBzAHQAXwBjAGEAcwBlAHMALAAgAGkALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAASQBOAEQARQBYACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBrAGkAcAAgAEQAaQB2AGkAcwBvAHIAIAA+ACAARABpAHYAaQBkAGUAbgBkABQgaQB0ACcAcwAgAG4AZQB2AGUAcgAgAGEAbgAgAGkAbgB0AGUAZwBlAHIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbABlAG4AXwBiACAAPgAgAGwAZQBuAF8AYQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAYwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARwBlAG4AZQByAGEAdABlACAAZQB4AGEAYwB0AC0AbABlAG4AZwB0AGgAIAB0AGUAcwB0ACAAcwB0AHIAaQBuAGcAcwAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AHIAXwBhACwAIABSAEUAUABUACgAXAAiADkAXAAiACwAIABsAGUAbgBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAcgBfAGIALAAgAEkARgAoAGwAZQBuAF8AYgAgAD0AIAAxACwAIABcACIANwBcACIALAAgAFwAIgA3AFwAIgAgACYAIABSAEUAUABUACgAXAAiADMAXAAiACwAIABsAGUAbgBfAGIAIAAtACAAMQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeABlAGMAdQB0AGUAIABiAGUAbgBjAGgAbQBhAHIAawBzACAAcwB0AHIAaQBjAHQAbAB5ACAAbwBuAGUAIABhAGYAdABlAHIAIAB0AGgAZQAgAG8AdABoAGUAcgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABpAG0AZQBfAGsALAAgAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACgAcwB0AHIAXwBhACwAIABzAHQAcgBfAGIALAAgAFwAIgBLAE4AVQBUAEgAXAAiACwAIABpAHQAZQByAHMALAAgAHIAZQBwAGUAYQB0AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGkAbQBlAF8AbgByACwAIABEAGkAdgBpAHMAaQBvAG4AQQBsAGcAbwByAGkAdABoAG0AcwAoAHMAdAByAF8AYQAsACAAcwB0AHIAXwBiACwAIABcACIATgBSAFwAIgAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAcABwAGUAbgBkACAAdABoAGUAIAByAGUAcwB1AGwAdABzAC4AIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAGEAbABsAG8AYwBhAHQAaQBvAG4AIABkAGUAbABhAHkAIABvAGMAYwB1AHIAcwAgAGgAZQByAGUALAAgAHMAYQBmAGUAbAB5ACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAdABpAG0AZQBkACAAdwBpAG4AZABvAHcALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABhAGMAYwAsACAASABTAFQAQQBDAEsAKABsAGUAbgBfAGEALAAgAGwAZQBuAF8AYgAsACAAdABpAG0AZQBfAGsALAAgAHQAaQBtAGUAXwBuAHIAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgADIALQBjAG8AbAB1AG0AbgAgAGEAcgByAGEAeQAgAG8AZgAgAGUAdgBlAHIAeQAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgAgAG8AZgAgAGwAZQBuAGcAdABoAHMAXABuAEQAaQB2AGkAcwBpAG8AbgBCAGUAbgBjAGgAbQBhAHIAawBDAGEAcwBlAHMAIAA9ACAATABBAE0AQgBEAEEAKABzAHQAYQByAHQAXwBsAGUAbgAsACAAbQBhAHgAXwBsAGUAbgAsACAAcwB0AGUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQAsACAAUwBFAFEAVQBFAE4AQwBFACgAKABtAGEAeABfAGwAZQBuACAALQAgAHMAdABhAHIAdABfAGwAZQBuACkAIAAvACAAcwB0AGUAcAAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBsAGUAbgAsACAAcwB0AGUAcAApACwAXABuACAAIAAgACAAIAAgACAAIABuACwAIABSAE8AVwBTACgAcwBlAHEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAcgB0AGUAcwBpAGEAbgAgAEoAbwBpAG4AXABuACAAIAAgACAAIAAgACAAIABjAG8AbABfAGEALAAgAFQATwBDAE8ATAAoAEkARgAoAFMARQBRAFUARQBOAEMARQAoADEALAAgAG4AKQAsACAAcwBlAHEAKQApACwAXABuACAAIAAgACAAIAAgACAAIABjAG8AbABfAGIALAAgAFQATwBDAE8ATAAoAEkARgAoAFMARQBRAFUARQBOAEMARQAoAG4ALAAgADEAKQAsACAAVABPAFIATwBXACgAcwBlAHEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABjAG8AbABfAGEALAAgAGMAbwBsAF8AYgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgAEMAYQByAHQAZQBzAGkAYQBuACAAZwByAGkAZAAgAGYAcgBvAG0AIAB0AHcAbwAgAGkAbgBkAGUAcABlAG4AZABlAG4AdAAgAHMAZQBxAHUAZQBuAGMAZQBzAFwAbgBBAHMAeQBtAG0AZQB0AHIAaQBjAEEAQgBHAHIAaQBkACAAPQAgAEwAQQBNAEIARABBACgAcwB0AGEAcgB0AF8AYQAsACAAbQBhAHgAXwBhACwAIABzAHQAZQBwAF8AYQAsACAAcwB0AGEAcgB0AF8AYgAsACAAbQBhAHgAXwBiACwAIABzAHQAZQBwAF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGEALAAgAFMARQBRAFUARQBOAEMARQAoACgAbQBhAHgAXwBhACAALQAgAHMAdABhAHIAdABfAGEAKQAgAC8AIABzAHQAZQBwAF8AYQAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBhACwAIABzAHQAZQBwAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGIALAAgAFMARQBRAFUARQBOAEMARQAoACgAbQBhAHgAXwBiACAALQAgAHMAdABhAHIAdABfAGIAKQAgAC8AIABzAHQAZQBwAF8AYgAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBiACwAIABzAHQAZQBwAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwBhACwAIABSAE8AVwBTACgAcwBlAHEAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwBiACwAIABSAE8AVwBTACgAcwBlAHEAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAATwByAHQAaABvAGcAbwBuAGEAbAAgAGIAcgBvAGEAZABjAGEAcwB0ACAAdQBzAGkAbgBnACAAaQBuAGQAZQBwAGUAbgBkAGUAbgB0ACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIAAgACAAIAAgAGMAbwBsAF8AYQAsACAAVABPAEMATwBMACgASQBGACgAUwBFAFEAVQBFAE4AQwBFACgAMQAsACAAbgBfAGIAKQAsACAAcwBlAHEAXwBhACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBvAGwAXwBiACwAIABUAE8AQwBPAEwAKABJAEYAKABTAEUAUQBVAEUATgBDAEUAKABuAF8AYQApACwAIABUAE8AUgBPAFcAKABzAGUAcQBfAGIAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABjAG8AbABfAGEALAAgAGMAbwBsAF8AYgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBjAG8AcgBlAF8AQgBpAGcASQBuAHQAIgAsACIAdABlAHgAdAAiADoAIgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4ALwAvACAAQgBpAGcAIABJAG4AdABlAGcAZQByACAAQQByAGkAdABoAG0AZQB0AGkAYwAgAEwAaQBiAHIAYQByAHkAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQAIABNAG8AZAB1AGwAZQAgACAAIAAgACAAIAAgACAALwAvAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIABQAHIAaQB2AGEAdABlACAAQQBQAEkAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwBcAG4ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8AXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEMAbwBtAHAAdQB0AGUAcwAgAHQAaABlACAAbQBhAHgAaQBtAHUAbQAgAHMAYQBmAGUAIABiAGEAcwBlAC0AMQAwACAAbABpAG0AYgAgAHMAaQB6AGUAIAAoAGsAKQAgAHQAbwAgAGEAdgBvAGkAZAAgAEkARQBFAEUALQA3ADUANAAgAHAAcgBlAGMAaQBzAGkAbwBuACAAbABvAHMAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG8AcABlAHIAYQB0AGkAbwBuADoAIABcACIAQQBEAEQAXAAiACwAIABcACIATQBVAEwAXAAiACwAIABvAHIAIABcACIARABJAFYAXAAiAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAWwBtAGEAeABfAGkAdABlAG0AcwBdACAAQQBEAEQAOgAgAG4AdQBtAGIAZQByACAAbwBmACAAbwBwAGUAcgBhAG4AZABzAC4AIABNAFUATAA6ACAAcwBoAG8AcgB0AGUAcwB0ACAAcwB0AHIAaQBuAGcAIABkAGkAZwBpAHQAcwAgAGMAbwB1AG4AdAAuAFwAbgAgACoALwBcAG4AUwBhAGYAZQBLACAAPQAgAEwAQQBNAEIARABBACgAbwBwAGUAcgBhAHQAaQBvAG4ALAAgAFsAbQBhAHgAXwBpAHQAZQBtAHMAXQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABpAHQAZQBtAHMALAAgAEkARgAoAE8AUgAoAG0AYQB4AF8AaQB0AGUAbQBzACAAPQAgAFwAIgBcACIALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAbQBhAHgAXwBpAHQAZQBtAHMAKQApACwAIAAyACwAIABNAEEAWAAoADIALAAgAG0AYQB4AF8AaQB0AGUAbQBzACkAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVwBJAFQAQwBIACgAbwBwAGUAcgBhAHQAaQBvAG4ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEARABEAFwAIgAsACAAMQA1ACAALQAgAEwARQBOACgAaQB0AGUAbQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFUATABcACIALAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARQB2AGEAbAB1AGEAdABlACAAcABvAHMAcwBpAGIAbABlACAAawAgAHYAYQBsAHUAZQBzACAAZAB5AG4AYQBtAGkAYwBhAGwAbAB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAZQBzAHQAXwBrACwAIAB7ADcAOwAgADYAOwAgADUAOwAgADQAOwAgADMAOwAgADIAOwAgADEAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AbwB2AGUAcgBsAGEAcAAsACAAUgBPAFUATgBEAFUAUAAoAGkAdABlAG0AcwAgAC8AIAB0AGUAcwB0AF8AawAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIAB0AGgAZQAgAGEAYgBzAG8AbAB1AHQAZQAgAHAAZQBhAGsAIAB2AGEAbAB1AGUAIABpAG4AcwBpAGQAZQAgAHQAaABlACAAZQBuAGcAaQBuAGUAIAAoAEMAbwBuAHYAbwBsAHUAdABpAG8AbgAgACsAIABDAGEAcgByAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB1AG4AYwBhAHIAcgBpAGUAZABfAG0AYQB4ACwAIABtAGEAeABfAG8AdgBlAHIAbABhAHAAIAAqACAAKAAxADAAXgB0AGUAcwB0AF8AawAgAC0AIAAxACkAXgAyACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAHgAXwBjAGEAcgByAHkALAAgAEkATgBUACgAdQBuAGMAYQByAHIAaQBlAGQAXwBtAGEAeAAgAC8AIAAxADAAXgB0AGUAcwB0AF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABlAGEAawBfAHYAYQBsACwAIAB1AG4AYwBhAHIAcgBpAGUAZABfAG0AYQB4ACAAKwAgAG0AYQB4AF8AYwBhAHIAcgB5ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHQAdQByAG4AIAB0AGgAZQAgAG0AYQB4ACAAawAgADwAPQAgAEUAeABjAGUAbAAnAHMAIAAxADUALQBkAGkAZwBpAHQAIABjAGUAaQBsAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgARgBJAEwAVABFAFIAKAB0AGUAcwB0AF8AawAsACAAcABlAGEAawBfAHYAYQBsACAAPAA9ACAAKAAxADAAXgAxADUAIAAtACAAMQApACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQASQBWAFwAIgAsACAANwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAE4AQQBNAEUAPwBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AaQBmAGkAZQBkACAAUwBwAGwAaQB0AHQAZQByAC4AIABTAHAAbABpAHQAcwAgAGIAbwB0AGgAIABzAGMAYQBsAGEAcgBzACAAYQBuAGQAIABhAHIAcgBhAHkAcwAgAGkAbgB0AG8AIABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuACAAbABpAG0AYgBzAC4AXABuACAAKgAgAFUAcwBlAHMAIABNAEEAWAAoACkAIAB0AG8AIABnAHUAYQByAGEAbgB0AGUAZQAgAHMAYwBhAGwAYQByACAAaQBuAHAAdQB0AHMAIAB0AG8AIAB0AGgAZQAgAFMARQBRAFUARQBOAEMARQAgAGUAbgBnAGkAbgBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABzACAAVABoAGUAIABzAHQAcgBpAG4AZwAgAG8AcgAgAGEAcgByAGEAeQAgAG8AZgAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFMAcABsAGkAdAAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAcwAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABiAGkAZwBfAGkAbgB0AF8AcgBvAHcALAAgAFQATwBSAE8AVwAoAGIAaQBnAF8AaQBuAHQAcwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBnAHQAaABzACwAIABMAEUATgAoAGIAaQBnAF8AaQBuAHQAXwByAG8AdwApACwAXABuACAAIAAgACAAIAAgACAAIABtAGEAeABfAGwAZQBuACwAIABNAEEAWAAoAGwAZQBuAGcAdABoAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBsAGUAbgAsACAAUgBPAFUATgBEAFUAUAAoAG0AYQB4AF8AbABlAG4AIAAvACAAawAsACAAMAApACAAKgAgAGsALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAZABlAGQALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAHAAYQBkAF8AbABlAG4AIAAtACAAbABlAG4AZwB0AGgAcwApACAAJgAgAGIAaQBnAF8AaQBuAHQAXwByAG8AdwAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALAAgAFMARQBRAFUARQBOAEMARQAoAHAAYQBkAF8AbABlAG4AIAAvACAAawAsACAAMQAsACAAcABhAGQAXwBsAGUAbgAgAC0AIABrACAAKwAgADEALAAgAC0AawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC0ALQBNAEkARAAoAHAAYQBkAGQAZQBkACwAIABzAHQAYQByAHQAcwAsACAAawApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAQwBvAG4AYwBhAHQAZQBuAGEAdABlAHMAIABhAG4AIABhAHIAcgBhAHkAIABvAGYAIABuAHUAbQBlAHIAaQBjACAAbABpAG0AYgBzACAAaQBuAHQAbwAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnACwAIAB6AGUAcgBvAC0AcABhAGQAZABpAG4AZwAgAGEAbABsACAAYgB1AHQAIAB0AGgAZQAgAGYAaQByAHMAdAAgAGwAaQBtAGIALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAIABUAGgAZQAgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAG4AdQBtAGUAcgBpAGMAIABsAGkAbQBiAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABsAGkAbQBiACAAcwBpAHoAZQAgAHUAcwBlAGQAIABkAHUAcgBpAG4AZwAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAuAFwAbgAgACoALwBcAG4ATQBlAHIAZwBlACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AdQBtAF8AbABpAG0AYgBzACwAIABSAE8AVwBTACgAbABpAG0AYgBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQB2AF8AbABpAG0AYgBzACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAbABpAG0AYgBzACwAIABTAEUAUQBVAEUATgBDAEUAKABuAHUAbQBfAGwAaQBtAGIAcwAsACAAMQAsACAAbgB1AG0AXwBsAGkAbQBiAHMALAAgAC0AMQApACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AdQBtAF8AbABpAG0AYgBzACAAPQAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHYAXwBsAGkAbQBiAHMAIAAmACAAXAAiAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATgBDAEEAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAcgBlAHYAXwBsAGkAbQBiAHMALAAgADEAKQAgACYAIABcACIAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEUAWABUACgARABSAE8AUAAoAHIAZQB2AF8AbABpAG0AYgBzACwAIAAxACkALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAGsAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAUgBlAHMAbwBsAHYAZQBzACAAYwBhAHIAcgBpAGUAcwAgAHIAaQBnAGgAdAAtAHQAbwAtAGwAZQBmAHQAIABhAGMAcgBvAHMAcwAgAGEAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkAIABvAGYAIABiAGEAcwBlAC0AMQAwAF4AawAgAGwAaQBtAGIAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwAgAFQAaABlACAAYQByAHIAYQB5ACAAbwBmACAAbgB1AG0AZQByAGkAYwAgAGwAaQBtAGIAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGwAaQBtAGIAIABzAGkAegBlAC4AXABuACAAKgAvAFwAbgBDAGEAcgByAHkAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwApACwAXABuACAAIAAgACAAIAAgACAAIABiAGEAcwBlACwAIAAxADAAXgBrACwAXABuACAAIAAgACAAIAAgACAAIABzAGMAYQBuAG4AZQBkACwAIABTAEMAQQBOACgAMAAsACAAbABpAG0AYgBzACwAIABMAEEATQBCAEQAQQAoAGEAYwBjACwAIAB2AGEAbAAsACAAdgBhAGwAIAArACAASQBOAFQAKABhAGMAYwAgAC8AIABiAGEAcwBlACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAByAGUAbQBhAGkAbgBkAGUAcgBzACwAIABNAE8ARAAoAHMAYwBhAG4AbgBlAGQALAAgAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AYwBhAHIAcgB5ACwAIABJAE4AVAAoAEkATgBEAEUAWAAoAHMAYwBhAG4AbgBlAGQALAAgAG4ALAAgADEAKQAgAC8AIABiAGEAcwBlACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABmAGkAbgBhAGwAXwBjAGEAcgByAHkAIAA+ACAAMAAsACAAVgBTAFQAQQBDAEsAKAByAGUAbQBhAGkAbgBkAGUAcgBzACwAIABmAGkAbgBhAGwAXwBjAGEAcgByAHkAKQAsACAAcgBlAG0AYQBpAG4AZABlAHIAcwApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAC0ALQAtACAAVQBuAHMAaQBnAG4AZQBkACAASwBlAHIAbgBlAGwAcwAgAC0ALQAtACAAXABcAFwAXABcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAVQBuAHMAaQBnAG4AZQBkACAAYwBvAG0AcABhAHIAaQBzAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAMQAgACgAYQAgAD4AIABiACkALAAgAC0AMQAgACgAYQAgADwAIABiACkALAAgAG8AcgAgADAAIAAoAGEAIAA9ACAAYgApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAIABUAGgAZQAgAHMAZQBjAG8AbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoALwBcAG4AVQBDAG8AbQBwAGEAcgBlACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAeABfAHIAbwB3AHMALAAgAE0AQQBYACgAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEAKQAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAZABfAGEALAAgAEUAWABQAEEATgBEACgAbABpAG0AYgBzAF8AYQAsACAAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAYQBkAF8AYgAsACAARQBYAFAAQQBOAEQAKABsAGkAbQBiAHMAXwBiACwAIABtAGEAeABfAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABkAGkAZgBmACwAIABwAGEAZABfAGEAIAAtACAAcABhAGQAXwBiACwAXABuACAAIAAgACAAIAAgACAAIABtAHMAZABfAGkAZAB4ACwAIABYAE0AQQBUAEMASAAoAFQAUgBVAEUALAAgAGQAaQBmAGYAIAA8AD4AIAAwACwAIAAwACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATgBBACgAbQBzAGQAXwBpAGQAeAApACwAIAAwACwAIABTAEkARwBOACgASQBOAEQARQBYACgAZABpAGYAZgAsACAAbQBzAGQAXwBpAGQAeAAsACAAMQApACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAGEAZABkAGkAdABpAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFUAQQBkAGQAIAA9ACAATABBAE0AQgBEAEEAKABhACwAIABiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AcgBvAHcAcwAsACAATQBBAFgAKABSAE8AVwBTACgAYQApACwAIABSAE8AVwBTACgAYgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAYQBkAF8AYQAsACAARQBYAFAAQQBOAEQAKABhACwAIABtAGEAeABfAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBiACwAIABFAFgAUABBAE4ARAAoAGIALAAgAG0AYQB4AF8AcgBvAHcAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHAAYQBkAF8AYQAgACsAIABwAGEAZABfAGIALAAgAGsAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAHMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABBAHMAcwB1AG0AZQBzACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAgAEEAIAA+AD0AIABCAC4AIABSAGUAcwBvAGwAdgBlAHMAIABiAG8AcgByAG8AdwBzACAAdABvAHAALQB0AG8ALQBiAG8AdAB0AG8AbQAgAGEAbgBkACAAdAByAGkAbQBzACAAdAByAGEAaQBsAGkAbgBnACAAegBlAHIAbwBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAbQBpAG4AdQBlAG4AZAAgAGwAaQBtAGIAIABhAHIAcgBhAHkAIAAoAG0AdQBzAHQAIABiAGUAIAA+AD0AIABsAGkAbQBiAHMAXwBiACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABzAHUAYgB0AHIAYQBoAGUAbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AVQBTAHUAYgAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwByAG8AdwBzACwAIABNAEEAWAAoAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBhACwAIABFAFgAUABBAE4ARAAoAGwAaQBtAGIAcwBfAGEALAAgAG0AYQB4AF8AcgBvAHcAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAZABfAGIALAAgAEUAWABQAEEATgBEACgAbABpAG0AYgBzAF8AYgAsACAAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAZABpAGYAZgAsACAAcABhAGQAXwBhACAALQAgAHAAYQBkAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBlAHMAbwBsAHYAZQBkACwAIABDAGEAcgByAHkAKABkAGkAZgBmACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAbQBzAGQAXwBpAGQAeAAsACAAWABNAEEAVABDAEgAKABUAFIAVQBFACwAIAByAGUAcwBvAGwAdgBlAGQAIAA8AD4AIAAwACwAIAAwACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATgBBACgAbQBzAGQAXwBpAGQAeAApACwAIAB7ADAAfQAsACAAVABBAEsARQAoAHIAZQBzAG8AbAB2AGUAZAAsACAAbQBzAGQAXwBpAGQAeAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABWAGUAYwB0AG8AcgBpAHoAZQBkACAAbQBhAHQAcgBpAHgAIABzAHUAbQAgAG8AZgAgAHUAbgBzAGkAZwBuAGUAZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHUAYgBpAGcAXwBpAG4AdAAgAEgAbwByAGkAegBvAG4AdABhAGwAIABhAHIAcgBhAHkAIAAoADEAeABOACkAIABvAGYAIABuAG8AcgBtAGEAbABpAHoAZQBkACAAbQBhAGcAbgBpAHQAdQBkAGUAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAdQBuAGkAZgBpAGUAZAAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AVQBNAGEAdAByAGkAeABTAHUAbQAgAD0AIABMAEEATQBCAEQAQQAoAHUAYgBpAGcAXwBpAG4AdABzACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAGcAcgBpAGQALAAgAFMAcABsAGkAdAAoAHUAYgBpAGcAXwBpAG4AdABzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAYQB3AF8AbABpAG0AYgBzACwAIABCAFkAUgBPAFcAKABnAHIAaQBkACwAIABTAFUATQApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHIAYQB3AF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABSAG8AdQB0AGUAcwAgAGEAZABkAGkAdABpAG8AbgAvAHMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAGIAYQBzAGUAZAAgAG8AbgAgAHMAaQBnAG4AcwAgAGEAbgBkACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAuAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAYQAgAHQAdQBwAGwAZQAgAGEAcgByAGEAeQA6ACAAVgBTAFQAQQBDAEsAKABsAGkAbQBiAHMALAAgAGYAaQBuAGEAbABfAHMAaQBnAG4AKQAgAHcAaABlAHIAZQAgAHQAaABlACAAZgBpAG4AYQBsACAAcgBvAHcAIABpAHMAIAB0AGgAZQAgAHMAYwBhAGwAYQByACAAcwBpAGcAbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAcwBlAGMAbwBuAGQAIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHMAaQBnAG4AXwBhACAAVABoAGUAIABzAGkAZwBuACAAbwBmACAAdABoAGUAIABmAGkAcgBzAHQAIABhAHIAcgBhAHkAIAAoADEALAAgAC0AMQAsACAAMAApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAcwBpAGcAbgBfAGIAIABUAGgAZQAgAHMAaQBnAG4AIABvAGYAIAB0AGgAZQAgAHMAZQBjAG8AbgBkACAAYQByAHIAYQB5ACAAKAAxACwAIAAtADEALAAgADAAKQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AQQBkAGQAUwB1AGIAUgBvAHUAdABlAHIAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABzAGkAZwBuAF8AYQAsACAAcwBpAGcAbgBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AcwBhAG0AZQBfAHMAaQBnAG4ALAAgAHMAaQBnAG4AXwBhACAAPQAgAHMAaQBnAG4AXwBiACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGkAcwBfAHMAYQBtAGUAXwBzAGkAZwBuACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAZABkAGkAdABpAG8AbgA6ACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAgAGMAbwBtAGIAaQBuAGUALAAgAHMAaQBnAG4AIAByAGUAbQBhAGkAbgBzACAAdABoAGUAIABzAGEAbQBlAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVQBBAGQAZAAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsACAAcwBpAGcAbgBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwB1AGIAdAByAGEAYwB0AGkAbwBuADoAIABlAHYAYQBsAHUAYQB0AGUAIABtAGEAZwBuAGkAdAB1AGQAZQBzACAAdABvACAAcwBhAHQAaQBzAGYAeQAgAFUAUwB1AGIAIAAoAEEAIAA+AD0AIABCACkAIABwAHIAZQBjAG8AbgBkAGkAdABpAG8AbgAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcAAsACAAVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFQAbwB0AGEAbAAgAGMAYQBuAGMAZQBsAGwAYQB0AGkAbwBuADoAIAByAGUAdAB1AHIAbgAgAHsAMAB9ACAAbABpAG0AYgAgAGEAbgBkACAAMAAgAHMAaQBnAG4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAMAA7ADAAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAGEAZwBfAGMAbwBtAHAAIAA+ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABBACAAaQBzACAAbABhAHIAZwBlAHIAOgAgAHMAaQBnAG4AIABiAGUAbABvAG4AZwBzACAAdABvACAAQQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFUAUwB1AGIAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALAAgAHMAaQBnAG4AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEIAIABpAHMAIABsAGEAcgBnAGUAcgA6ACAAcgBvAHUAdABlACAAQgAgAGYAaQByAHMAdAAsACAAcwBpAGcAbgAgAGIAZQBsAG8AbgBnAHMAIAB0AG8AIABCAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVQBTAHUAYgAoAGwAaQBtAGIAcwBfAGIALAAgAGwAaQBtAGIAcwBfAGEALAAgAGsAKQAsACAAcwBpAGcAbgBfAGIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AcwBpAGcAbgBlAGQAIABtAHUAbAB0AGkAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIAB0AHcAbwAgAEwAaQB0AHQAbABlAC0ARQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5AHMALgBcAG4AIAAqACAAVQB0AGkAbABpAHoAZQBzACAAYQAgADEARAAgAEQAaQBzAGMAcgBlAHQAZQAgAEMAbwBuAHYAbwBsAHUAdABpAG8AbgAgACgAQwBhAHUAYwBoAHkAIABQAHIAbwBkAHUAYwB0ACkAIABhAHIAcgBhAHkALQBzAGwAaQBjAGkAbgBnACAAcwB0AHIAYQB0AGUAZwB5AC4AXABuACAAKgAgAFoAZQByAG8AIABkAHkAbgBhAG0AaQBjACAAbQBlAG0AbwByAHkAIAByAGUAYQBsAGwAbwBjAGEAdABpAG8AbgAuACAAJABPACgATgArAE0AKQAkACAAbQBlAG0AbwByAHkAIABmAG8AbwB0AHAAcgBpAG4AdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAG0AdQBsAHQAaQBwAGwAaQBjAGEAbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAIABUAGgAZQAgAG0AdQBsAHQAaQBwAGwAaQBlAHIAIABsAGkAbQBiACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBVAE0AdQBsACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwByAG8AdwBzACwAIABsAGUAbgBfAGEAIAArACAAbABlAG4AXwBiACAALQAgADEALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAATABvAG8AcAAgAHAAdQByAGUAbAB5ACAAbwB2AGUAcgAgAHQAaABlACAAbABlAG4AZwB0AGgAIABvAGYAIAB0AGgAZQAgAGYAaQBuAGEAbAAgAG8AdQB0AHAAdQB0ACAAYQByAHIAYQB5AFwAbgAgACAAIAAgACAAIAAgACAAcgBhAHcAXwBsAGkAbQBiAHMALAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIABMAEEATQBCAEQAQQAoAHIALAAgAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAbABjAHUAbABhAHQAZQAgAHQAaABlACAAdgBhAGwAaQBkACAAbwB2AGUAcgBsAGEAcABwAGkAbgBnACAAdwBpAG4AZABvAHcAIABvAGYAIABpAG4AZABpAGMAZQBzACAAZgBvAHIAIAB0AGgAaQBzACAAbQBhAGcAbgBpAHQAdQBkAGUAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AF8AaQAsACAATQBBAFgAKAAxACwAIAByACAALQAgAGwAZQBuAF8AYgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAG4AZABfAGkALAAgAE0ASQBOACgAcgAsACAAbABlAG4AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AdQBuAHQALAAgAGUAbgBkAF8AaQAgAC0AIABzAHQAYQByAHQAXwBpACAAKwAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGUAcQB1AGUAbgBjAGUAIABpACAAYwBvAHUAbgB0AHMAIABVAFAALgAgAFMAZQBxAHUAZQBuAGMAZQAgAGoAIABjAG8AdQBuAHQAcwAgAEQATwBXAE4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGkALAAgAFMARQBRAFUARQBOAEMARQAoAGMAbwB1AG4AdAAsACAAMQAsACAAcwB0AGEAcgB0AF8AaQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBlAHEAXwBqACwAIABTAEUAUQBVAEUATgBDAEUAKABjAG8AdQBuAHQALAAgADEALAAgAHIAIAAtACAAcwB0AGEAcgB0AF8AaQAgACsAIAAxACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAbABpAGMAZQAgAHQAaABlACAAZQB4AGEAYwB0ACAAaQBuAHQAZQByAHMAZQBjAHQAaQBuAGcAIABsAGkAbQBiAHMALAAgAG0AdQBsAHQAaQBwAGwAeQAsACAAYQBuAGQAIABzAHUAbQAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUATQAoAEkATgBEAEUAWAAoAGwAaQBtAGIAcwBfAGEALAAgAHMAZQBxAF8AaQAsACAAMQApACAAKgAgAEkATgBEAEUAWAAoAGwAaQBtAGIAcwBfAGIALAAgAHMAZQBxAF8AagAsACAAMQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHMAbwBsAHYAZQAgAGEAbABsACAAYwBhAHIAcgBpAGUAcwAgAGIAbwB0AHQAbwBtAC0AdABvAC0AdABvAHAAIABlAHgAYQBjAHQAbAB5ACAAbwBuAGMAZQBcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHIAYQB3AF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABCAGkAbgBhAHIAeQAgAHMAZQBhAHIAYwBoACAAdABvACAAZgBpAG4AZAAgAHQAaABlACAAaABpAGcAaABlAHMAdAAgAHMAYwBhAGwAYQByACAAcQB1AG8AdABpAGUAbgB0ACAAbABpAG0AYgAgAHEAIAAoADAAIAA8AD0AIABxACAAPAAgADEAMABeAGsAKQBcAG4AoAAqACAAcwB1AGMAaAAgAHQAaABhAHQAIABCACAAKgAgAHEAIAA8AD0AIABhAGMAYwAuACAARQBsAGkAbQBpAG4AYQB0AGUAcwAgAHQAaABlACAAbgBlAGUAZAAgAGYAbwByACAASwBuAHUAdABoACAARAAgAGYAbABvAGEAdAAtAGUAcwB0AGkAbQBhAHQAaQBvAG4ALgBcAG4AoAAqACAAQABwAGEAcgBhAG0AIABhAGMAYwAgAFQAaABlACAAYwB1AHIAcgBlAG4AdAAgAHIAZQBtAGEAaQBuAGQAZQByACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAuAFwAbgCgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgCgACoALwBcAG4ARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAgAD0AIABMAEEATQBCAEQAQQAoAGEAYwBjACwAIABiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAYQBsAGMAdQBsAGEAdABlACAAcgBlAHEAdQBpAHIAZQBkACAAYgBpAHQAcwAgAGQAeQBuAGEAbQBpAGMAYQBsAGwAeQAuACAARgBvAHIAIABtAGEAeAAgAGsAPQA3ACwAIAB0AGgAaQBzACAAZQB2AGEAbAB1AGEAdABlAHMAIAB0AG8AIAAyADQAIABiAGkAdABzAC4AXABuACAAIAAgACAAIAAgACAAIABiAGkAdABzACwAIABDAEUASQBMAEkATgBHAC4ATQBBAFQASAAoAEwATwBHACgAMQAwAF4AawAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAbwB3AGUAcgBzACwAIAAyACAAXgAgAFMARQBRAFUARQBOAEMARQAoAGIAaQB0AHMALAAgADEALAAgAGIAaQB0AHMAIAAtACAAMQAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAUgBFAEQAVQBDAEUAKAAwACwAIABwAG8AdwBlAHIAcwAsACAATABBAE0AQgBEAEEAKABjAHUAcgByAF8AcQAsACAAcABvAHcAZQByACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABlAHMAdABfAHEALAAgAGMAdQByAHIAXwBxACAAKwAgAHAAbwB3AGUAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAawBpAHAAIABpAGYAIAB0AGUAcwB0AF8AcQAgAGUAeABjAGUAZQBkAHMAIAB0AGgAZQAgAGwAaQBtAGIAIABiAGEAcwBlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHQAZQBzAHQAXwBxACAAPgA9ACAAMQAwAF4AawAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATQB1AGwAdABpAHAAbAB5ACAAQgAgAGIAeQAgAHMAYwBhAGwAYQByACAAdABlAHMAdABfAHEAIABhAG4AZAAgAHIAZQBzAG8AbAB2AGUAIABjAGEAcgByAGkAZQBzACAAbgBhAHQAaQB2AGUAbAB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGUAcwB0AF8AcAByAG8AZAAsACAAQwBhAHIAcgB5ACgAYgAgACoAIAB0AGUAcwB0AF8AcQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAFUAQwBvAG0AcABhAHIAZQAoAGEAYwBjACwAIAB0AGUAcwB0AF8AcAByAG8AZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABjAG8AbQBwACAAPgA9ACAAMAAsACAAdABlAHMAdABfAHEALAAgAGMAdQByAHIAXwBxACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABCAGEAcwBlAGMAYQBzAGUAIABEAGkAdgBpAHMAaQBvAG4AIAB2AGkAYQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABzAGgAaQBmAHQALQBhAG4AZAAtAHMAdQBiAHQAcgBhAGMAdAAuAFwAbgCgACoAIABSAGUAdAB1AHIAbgBzACAAYQAgAHAAYQBjAGsAZQBkACAAMQBEACAAYQByAHIAYQB5ADoAIABWAFMAVABBAEMASwAoAEwAZQBuAGcAdABoAF8AUgAsACAAUgBfAGwAaQBtAGIAcwAsACAAUQBfAGwAaQBtAGIAcwApAC4AXABuAKAAKgAgAEUAbABpAG0AaQBuAGEAdABlAHMAIAAyAEQAIABhAHIAcgBhAHkAIABwAGEAZABkAGkAbgBnACAAdABvACAAcwB0AHIAaQBjAHQAbAB5ACAAcAByAGUAcwBlAHIAdgBlACAAbQBlAG0AbwByAHkAIABlAGYAZgBpAGMAaQBlAG4AYwB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAgACgAYQBzAHMAdQBtAGUAZAAgAG4AbwBuAC0AegBlAHIAbwApAC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuAKAAKgAvAFwAbgBLAG4AdQB0AGgARABpAHYAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcAAsACAAVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAIAByAG8AdQB0AGkAbgBnACAAdwBpAHQAaAAgAHQAaABlACAAbgBlAHcAIABwAGEAYwBrAGUAZAAgAG0AZQBtAG8AcgB5ACAAYwBvAG4AdAByAGEAYwB0AFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbABpAG0AYgBzAF8AYQApACwAIABsAGkAbQBiAHMAXwBhACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADEALAAgADAALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEkAdABlAHIAYQB0AGUAIABvAHYAZQByACAAQQAgAGYAcgBvAG0AIABNAFMAQgAgACgAdABvAHAAKQAgAHQAbwAgAEwAUwBCACAAKABiAG8AdAB0AG8AbQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHYAZQByAHMAZQBkAF8AYQAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEALAAgAFMARQBRAFUARQBOAEMARQAoAGwAZQBuAF8AYQAsACAAMQAsACAAbABlAG4AXwBhACwAIAAtADEAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAdABhAHQAZQAgAHMAZQBwAGEAcgBhAHQAbwByADoAIABWAFMAVABBAEMASwAoAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABxAHUAbwB0AGkAZQBuAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAbgBpAHQAaQBhAGwAXwBzAHQAYQB0AGUALAAgAFYAUwBUAEEAQwBLACgAMQAsACAAMAAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsAF8AcwB0AGEAdABlACwAIAByAGUAdgBlAHIAcwBlAGQAXwBhACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAdgBhAGwALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcwB0AGEAdABlACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHEAdQBvAHQAaQBlAG4AdAAsACAARABSAE8AUAAoAHMAdABhAHQAZQAsACAAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGgAaQBmAHQAIABhAGMAYwAgAHUAcAAgAGIAeQAgADEAIABsAGkAbQBiACAAKABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuADoAIABpAG4AcwBlAHIAdAAgAGEAdAAgAGkAbgBkAGUAeAAgADEAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAHgAdABlAG4AZABlAGQAXwByAGUAbQBhAGkAbgBkAGUAcgAsACAASQBGACgAQQBOAEQAKABSAE8AVwBTACgAcgBlAG0AYQBpAG4AZABlAHIAKQAgAD0AIAAxACwAIABJAE4ARABFAFgAKAByAGUAbQBhAGkAbgBkAGUAcgAsACAAMQAsACAAMQApACAAPQAgADAAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB2AGEAbAAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAHYAYQBsACwAIAByAGUAbQBhAGkAbgBkAGUAcgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgAsACAARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAoAGUAeAB0AGUAbgBkAGUAZABfAHIAZQBtAGEAaQBuAGQAZQByACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAHIAbwBkACwAIABDAGEAcgByAHkAKABsAGkAbQBiAHMAXwBiACAAKgAgAG4AZQB4AHQAXwBxAHUAbwB0AGkAZQBuAHQAXwBsAGkAbQBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAdwBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABVAFMAdQBiACgAZQB4AHQAZQBuAGQAZQBkAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHAAcgBvAGQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGgAYQBzAF8AcQB1AG8AdABpAGUAbgB0ACwAIABPAFIAKABSAE8AVwBTACgAcQB1AG8AdABpAGUAbgB0ACkAIAA+ACAAMQAsACAASQBOAEQARQBYACgAcQB1AG8AdABpAGUAbgB0ACwAMQAsADEAKQAgAD4AIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQB1AG8AdAAsACAASQBGACgAaABhAHMAXwBxAHUAbwB0AGkAZQBuAHQALAAgAFYAUwBUAEEAQwBLACgAcQB1AG8AdABpAGUAbgB0ACwAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgApACwAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbgBlAHcAXwByAGUAbQBhAGkAbgBkAGUAcgApACwAIABuAGUAdwBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABuAGUAeAB0AF8AcQB1AG8AdAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAEkATgBEAEUAWAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAbQBhAGkAbgBkAGUAcgAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAsACAAMQAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQB2AGUAcgBzAGUAZABfAHEAdQBvAHQAaQBlAG4AdAAsACAARABSAE8AUAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAcQB1AG8AdABfAHIAYQB3ACAAdwBhAHMAIABiAHUAaQBsAHQAIABNAFMAQgAgAHQAbwAgAEwAUwBCACAAKABCAGkAZwAtAEUAbgBkAGkAYQBuACkALgAgAFIAZQB2AGUAcgBzAGUAIAB0AG8AIABpAG4AdABlAHIAbgBhAGwAIABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHEAdQBvAHQAaQBlAG4AdAAsACAAUgBPAFcAUwAoAHIAZQB2AGUAcgBzAGUAZABfAHEAdQBvAHQAaQBlAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABxAHUAbwB0AGkAZQBuAHQALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKAByAGUAdgBlAHIAcwBlAGQAXwBxAHUAbwB0AGkAZQBuAHQALAAgAFMARQBRAFUARQBOAEMARQAoAGwAZQBuAF8AcQB1AG8AdABpAGUAbgB0ACwAIAAxACwAIABsAGUAbgBfAHEAdQBvAHQAaQBlAG4AdAAsACAALQAxACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAHMAdAByAGkAYwB0AGwAeQAgAHAAYQBjAGsAZQBkACAAMQBEACAAYQByAHIAYQB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIAByAGUAbQBhAGkAbgBkAGUAcgAsACAAcQB1AG8AdABpAGUAbgB0ACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABIAHkAYgByAGkAZAAgAEQAaQB2AGkAcwBpAG8AbgAgAFIAbwB1AHQAZQByAC4AXABuAKAAKgAgAEQAaQByAGUAYwB0AHMAIABkAGkAdgBpAHMAaQBvAG4AIAB0AG8AIAB0AGgAZQAgAG8AcAB0AGkAbQBhAGwAIABrAGUAcgBuAGUAbAAgAGIAYQBzAGUAZAAgAG8AbgAgAEQAaQB2AGkAZABlAG4AZAAgAGwAZQBuAGcAdABoAC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAuAFwAbgCgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgCgACoALwBcAG4ARABpAHYAUgBvAHUAdABlAHIAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEQAaQBnAGkAdAAgAGMAbwB1AG4AdABzACAAYQByAGUAIABhAHAAcAByAG8AeABpAG0AYQB0AGUALAAgAGIAdQB0ACAAcwB1AGYAZgBpAGMAaQBlAG4AdABcAG4AIAAgACAAIAAgACAAIAAgAGQAaQBnAGkAdABzAF8AYQAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEAKQAgACoAIABrACwAXABuACAAIAAgACAAIAAgACAAIABkAGkAZwBpAHQAcwBfAGIALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkAIAAqACAAawAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABNAGEAYwBoAGkAbgBlAC0AbABlAGEAcgBuAGUAZAAgAGMAbwBlAGYAZgBpAGMAaQBlAG4AdABzACAAZgByAG8AbQAgAEwAbwBnAGkAcwB0AGkAYwAgAFIAZQBnAHIAZQBzAHMAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIABtACwAIAAwAC4AMQAwADcAOAAyADEAMQA5ADQAMgA3ADEAMgA5ADcALABcAG4AIAAgACAAIAAgACAAIAAgAGMALAAgAC0AMgAyADEALgA5ADAAMgAxADgAOQA0ADYAMgAwADYAOAAsAFwAbgAgACAAIAAgACAAIAAgACAAdABoAHIAZQBzAGgAbwBsAGQALAAgACgAbQAgACoAIABkAGkAZwBpAHQAcwBfAGEAKQAgACsAIABjACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGQAaQBnAGkAdABzAF8AYgAgADwAPQAgAHQAaAByAGUAcwBoAG8AbABkACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEsAbgB1AHQAaABEAGkAdgAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2ACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEcAZQBuAGUAcgBhAHQAZQBzACAAdABoAGUAIABlAHgAYQBjAHQAIAByAGUAYwBpAHAAcgBvAGMAYQBsACAAcwBlAGUAZAAgAGYAbwByACAATgBlAHcAdABvAG4ALQBSAGEAcABoAHMAbwBuACAARABpAHYAaQBzAGkAbwBuACAAdQBzAGkAbgBnACAASwBuAHUAdABoACAAQgBhAHMAZQBjAGEAcwBlAC4AXABuACAAKgAgAEUAeAB0AHIAYQBjAHQAcwAgAHUAcAAgAHQAbwAgAHQAaABlACAAdABvAHAAIAAzACAAbABpAG0AYgBzACAAbwBmACAAQgAgAGEAbgBkACAAYwBhAGwAYwB1AGwAYQB0AGUAcwAgAGYAbABvAG8AcgAoAEIAZQB0AGEAXgAoADIAKgBsAGUAbgApACAALwAgAEIAXwB0AG8AcAApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4AUwBlAGUAZAAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwBiACwAIABSAE8AVwBTACgAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAZQBkAF8AbABlAG4ALAAgAE0ASQBOACgAMwAsACAAbABlAG4AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAHQAbwBwACAAJwBzAGUAZQBkAF8AbABlAG4AJwAgAGwAaQBtAGIAcwAgACgATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgA6ACAAdABhAGsAZQAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAbwB0AHQAbwBtACkAXABuACAAIAAgACAAIAAgACAAIABiAF8AdABvAHAALAAgAFQAQQBLAEUAKABsAGkAbQBiAHMAXwBiACwAIAAtAHMAZQBlAGQAXwBsAGUAbgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAbwBuAHMAdAByAHUAYwB0ACAAQgBlAHQAYQBeACgAMgAgACoAIABzAGUAZQBkAF8AbABlAG4AKQAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAGUALgBnAC4ALAAgAGkAZgAgAHMAZQBlAGQAXwBsAGUAbgAgAD0AIAAxACwAIAB0AGgAZQBuACAAMQAgAGYAbwBsAGwAbwB3AGUAZAAgAGIAeQAgAHQAdwBvACAAegBlAHIAbwAgAGwAaQBtAGIAcwA6ACAAVgBTAFQAQQBDAEsAKAAwACwAIAAwACwAIAAxACkAXABuACAAIAAgACAAIAAgACAAIABiAGUAdABhAF8AMgBtACwAIABWAFMAVABBAEMASwAoAEUAWABQAEEATgBEACgAMAAsACAAMgAgACoAIABzAGUAZQBkAF8AbABlAG4ALAAgACwAIAAwACkALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABLAG4AdQB0AGgAIABEAGkAdgBpAHMAaQBvAG4AIAB5AGkAZQBsAGQAcwAgAGUAeABhAGMAdAAgAGkAbgBpAHQAaQBhAGwAIAByAGUAYwBpAHAAcgBvAGMAYQBsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGMAawBlAGQALAAgAEsAbgB1AHQAaABEAGkAdgAoAGIAZQB0AGEAXwAyAG0ALAAgAGIAXwB0AG8AcAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABRAHUAbwB0AGkAZQBuAHQAIABhAHIAcgBhAHkAIABmAHIAbwBtACAAdABoAGUAIABwAGEAYwBrAGUAZAAgAFYAUwBUAEEAQwBLAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwByACwAIABJAE4ARABFAFgAKABwAGEAYwBrAGUAZAAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAcABhAGMAawBlAGQALAAgAGwAZQBuAF8AcgAgACsAIAAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABDAG8AbQBwAHUAdABlAHMAIAB0AGgAZQAgAFIAZQBjAGkAcAByAG8AYwBhAGwAIABwAHIAbwBnAHIAZQBzAHMAaQB2AGUAbAB5ACAAcwBjAGEAbABpAG4AZwAgAHUAcAAgAHQAbwAgAHQAaABlACAARABpAHYAaQBkAGUAbgBkACcAcwAgAHAAcgBlAGMAaQBzAGkAbwBuAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIAB0AGEAcgBnAGUAdABfAGwAZQBuACAAVABoAGUAIABsAGkAbQBiAC0AbABlAG4AZwB0AGgAIABvAGYAIABEAGkAdgBpAGQAZQBuAGQAIABBAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAFIAZQBjAGkAcAByAG8AYwBhAGwAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBiACwAIAB0AGEAcgBnAGUAdABfAGwAZQBuACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBlAGUAZABfAGwAZQBuACwAIABNAEkATgAoADMALAAgAGwAZQBuAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAByAF8AcwBlAGUAZABfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBTAGUAZQBkACgAbABpAG0AYgBzAF8AYgAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKABzAGUAZQBkAF8AbABlAG4ALAAgAHIAXwBzAGUAZQBkAF8AbABpAG0AYgBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQBxAF8AaQB0AGUAcgBzACwAIABNAEEAWAAoADAALAAgAEMARQBJAEwASQBOAEcALgBNAEEAVABIACgATABOACgAdABhAHIAZwBlAHQAXwBsAGUAbgAgAC8AIABzAGUAZQBkAF8AbABlAG4AKQAgAC8AIABMAE4AKAAyACkAKQApACAAKwAgADEALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKAByAGUAcQBfAGkAdABlAHIAcwAgAD0AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAXwBzAGUAZQBkAF8AbABpAG0AYgBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQB0AGUAcgBhAHQAaQBvAG4AcwAsACAAUwBFAFEAVQBFAE4AQwBFACgAcgBlAHEAXwBpAHQAZQByAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsAF8AcwB0AGEAdABlACwAIABpAHQAZQByAGEAdABpAG8AbgBzACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAaQB0AGUAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwB1AHIAcgBfAGwAZQBuACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcgAsACAARABSAE8AUAAoAHMAdABhAHQAZQAsACAAMQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AbABlAG4ALAAgAE0ASQBOACgAYwB1AHIAcgBfAGwAZQBuACAAKgAgADIALAAgAHQAYQByAGcAZQB0AF8AbABlAG4AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARAB5AG4AYQBtAGkAYwAgAFMAYwBhAGwAaQBuAGcAIABTAGgAaQBmAHQAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAASQBmACAAQgAgAGgAYQBzACAAcABsAGEAdABlAGEAdQBlAGQALAAgAFIAIABtAHUAcwB0ACAAcwBjAGEAbABlACAAYgB5ACAAMgAqACgAbgAtAG0AKQAuACAASQBmACAAQgAgAGkAcwAgAGcAcgBvAHcAaQBuAGcALAAgAFIAIABzAGMAYQBsAGUAcwAgAGIAeQAgACgAbgAtAG0AKQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAdABpAHYAZQBfAGMAdQByAHIALAAgAE0ASQBOACgAYwB1AHIAcgBfAGwAZQBuACwAIABsAGUAbgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAdABpAHYAZQBfAG4AZQB4AHQALAAgAE0ASQBOACgAbgBlAHgAdABfAGwAZQBuACwAIABsAGUAbgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGgAaQBmAHQAXwBsAGkAbQBiAHMALAAgADIAIAAqACAAKABuAGUAeAB0AF8AbABlAG4AIAAtACAAYwB1AHIAcgBfAGwAZQBuACkAIAAtACAAKABhAGMAdABpAHYAZQBfAG4AZQB4AHQAIAAtACAAYQBjAHQAaQB2AGUAXwBjAHUAcgByACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAXwBwAHIAaQBtAGUALAAgAEkARgAoAHMAaABpAGYAdABfAGwAaQBtAGIAcwAgAD4AIAAwACwAIABWAFMAVABBAEMASwAoAEUAWABQAEEATgBEACgAMAAsACAAcwBoAGkAZgB0AF8AbABpAG0AYgBzACwAIAAsACAAMAApACwAIABjAHUAcgByAF8AcgApACwAIABjAHUAcgByAF8AcgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABiAF8AYQBjAHQAaQB2AGUALAAgAFQAQQBLAEUAKABsAGkAbQBiAHMAXwBiACwAIAAtAGEAYwB0AGkAdgBlAF8AbgBlAHgAdAApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABQACAAaQBzACAAbgBhAHQAaQB2AGUAbAB5ACAAYQBsAGkAZwBuAGUAZAAgAHQAbwAgADIAKgBuAGUAeAB0AF8AbABlAG4AIABiAGUAYwBhAHUAcwBlACAAbwBmACAAdABoAGUAIABjAG8AcgByAGUAYwB0AGUAZAAgAHMAaABpAGYAdABfAGwAaQBtAGIAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGIAXwBhAGMAdABpAHYAZQAsACAAcgBfAHAAcgBpAG0AZQAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AHcAbwBfAGIAZQB0AGEALAAgAFYAUwBUAEEAQwBLACgARQBYAFAAQQBOAEQAKAAwACwAIAAyACAAKgAgAG4AZQB4AHQAXwBsAGUAbgAsACAALAAgADAAKQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGUAcgByACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAdQBiACgAdAB3AG8AXwBiAGUAdABhACwAIABwACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwByAF8AdQBuAHMAYwBhAGwAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAcgBfAHAAcgBpAG0AZQAsACAAZQByAHIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcgAsACAASQBGACgAUgBPAFcAUwAoAG4AZQB4AHQAXwByAF8AdQBuAHMAYwBhAGwAZQBkACkAIAA8AD0AIAAyACAAKgAgAG4AZQB4AHQAXwBsAGUAbgAsACAAewAwAH0ALAAgAEQAUgBPAFAAKABuAGUAeAB0AF8AcgBfAHUAbgBzAGMAYQBsAGUAZAAsACAAMgAgACoAIABuAGUAeAB0AF8AbABlAG4AKQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAG4AZQB4AHQAXwBsAGUAbgAsACAAbgBlAHgAdABfAHIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAMQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEgAZQBhAHYAeQB3AGUAaQBnAGgAdAAgAE4AZQB3AHQAbwBuAC0AUgBhAHAAaABzAG8AbgAgAEQAaQB2AGkAcwBpAG8AbgAuAFwAbgAgACoAIABJAG0AcABsAGUAbQBlAG4AdABzACAAcAByAG8AZwByAGUAcwBzAGkAdgBlACAAcwBjAGEAbABpAG4AZwAgAGIAbwB1AG4AZABlAGQAIAB0AG8AIABNAEEAWAAoAGwAZQBuAF8AYQAsACAAbABlAG4AXwBiACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBhACAAVABoAGUAIABkAGkAdgBpAGQAZQBuAGQAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2ACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAHIAZwBlAHQAXwBsAGUAbgAsACAATQBBAFgAKABsAGUAbgBfAGEALAAgAGwAZQBuAF8AYgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAMQAuACAAQwBhAGwAYwB1AGwAYQB0AGUAIAByAGUAYwBpAHAAcgBvAGMAYQBsACAAUgAgAHMAYwBhAGwAZQBkACAAZAB5AG4AYQBtAGkAYwBhAGwAbAB5ACAAdABvACAAMgAgACoAIAB0AGEAcgBnAGUAdABfAGwAZQBuAFwAbgAgACAAIAAgACAAIAAgACAAcgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBSAGUAYwBpAHAAcgBvAGMAYQBsACgAbABpAG0AYgBzAF8AYgAsACAAdABhAHIAZwBlAHQAXwBsAGUAbgAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAMgAuACAAQQBwAHAAcgBvAHgAaQBtAGEAdABlACAAUQB1AG8AdABpAGUAbgB0ADoAIABRAF8AYQBwAHAAcgBvAHgAIAA9ACAAQQAgACoAIABSACAALwAgAEIAZQB0AGEAXgAoADIAIAAqACAAdABhAHIAZwBlAHQAXwBsAGUAbgApAFwAbgAgACAAIAAgACAAIAAgACAAZAByAG8AcABfAGwAaQBtAGIAcwAsACAAMgAgACoAIAB0AGEAcgBnAGUAdABfAGwAZQBuACwAXABuACAAIAAgACAAIAAgACAAIABxAF8AdQBuAHMAYwBhAGwAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAbABpAG0AYgBzAF8AYQAsACAAcgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABxAF8AYQBwAHAAcgBvAHgALAAgAEkARgAoAFIATwBXAFMAKABxAF8AdQBuAHMAYwBhAGwAZQBkACkAIAA8AD0AIABkAHIAbwBwAF8AbABpAG0AYgBzACwAIAB7ADAAfQAsACAARABSAE8AUAAoAHEAXwB1AG4AcwBjAGEAbABlAGQALAAgAGQAcgBvAHAAXwBsAGkAbQBiAHMAKQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIAB0AGgAZQAgAG0AYQBzAHMAaQB2AGUAIABiAGEAcwBlAGwAaQBuAGUAIABwAHIAbwBkAHUAYwB0ACAAZQB4AGEAYwB0AGwAeQAgAE8ATgBDAEUAXABuACAAIAAgACAAIAAgACAAIABwAF8AYgBhAHMAZQBsAGkAbgBlACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAbABpAG0AYgBzAF8AYgAsACAAcQBfAGEAcABwAHIAbwB4ACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAAzAC4AIABCAG8AdQBuAGQAZQBkACAARQByAHIAbwByACAAQwBvAHIAcgBlAGMAdABpAG8AbgAgAFMAdwBlAGUAcAAgACgATwBwAHQAaQBtAGkAegBlAGQAIABPACgATgApACAAUwB0AGUAcABwAGkAbgBnACkAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABTAHQAYQB0AGUAIABwAGEAYwBrAGkAbgBnADoAIABWAFMAVABBAEMASwAoAEwAZQBuAGcAdABoAF8AUQAsACAAUQBfAGwAaQBtAGIAcwAsACAAUABfAGwAaQBtAGIAcwApAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAcQBfAGEAcABwAHIAbwB4ACkALAAgAHEAXwBhAHAAcAByAG8AeAAsACAAcABfAGIAYQBzAGUAbABpAG4AZQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUwB3AGUAZQBwACAARABvAHcAbgA6ACAASQBmACAAUAAgAD4AIABBACwAIABRACAAaQBzACAAdABvAG8AIABiAGkAZwAuACAAUwB0AGUAcAAgAFEAIABkAG8AdwBuACAAYgB5ACAAMQAsACAAYQBuAGQAIABQACAAZABvAHcAbgAgAGIAeQAgAEIALgBcAG4AIAAgACAAIAAgACAAIAAgAHMAdwBlAGUAcABfAGQAbwB3AG4ALAAgAFIARQBEAFUAQwBFACgAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAewAxADsAIAAyAH0ALAAgAEwAQQBNAEIARABBACgAcwB0AGEAdABlACwAIABpACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwBxACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwBxACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcwB0AGEAdABlACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHEALAAgADEALAAgADIAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwB1AHIAcgBfAHAALAAgAEQAUgBPAFAAKABzAHQAYQB0AGUALAAgAGwAZQBuAF8AcQAgACsAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBDAG8AbQBwAGEAcgBlACgAYwB1AHIAcgBfAHAALAAgAGwAaQBtAGIAcwBfAGEAKQAgAD4AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBTAHUAYgAoAGMAdQByAHIAXwBxACwAIAB7ADEAfQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwBwACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAdQBiACgAYwB1AHIAcgBfAHAALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFIATwBXAFMAKABuAGUAeAB0AF8AcQApACwAIABuAGUAeAB0AF8AcQAsACAAbgBlAHgAdABfAHAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAdABhAHQAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUwB3AGUAZQBwACAAVQBwADoAIABJAGYAIABQACAAKwAgAEIAIAA8AD0AIABBACwAIABRACAAaQBzACAAdABvAG8AIABzAG0AYQBsAGwALgAgAFMAdABlAHAAIABRACAAdQBwACAAYgB5ACAAMQAsACAAYQBuAGQAIABQACAAdQBwACAAYgB5ACAAQgAuAFwAbgAgACAAIAAgACAAIAAgACAAcwB3AGUAZQBwAF8AdQBwACwAIABSAEUARABVAEMARQAoAHMAdwBlAGUAcABfAGQAbwB3AG4ALAAgAHsAMQA7ACAAMgB9ACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAaQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcQAsACAASQBOAEQARQBYACgAcwB0AGEAdABlACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcQAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwBxACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwBwACwAIABEAFIATwBQACgAcwB0AGEAdABlACwAIABsAGUAbgBfAHEAIAArACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBlAHgAdABfAHAAXwB0AGUAcwB0ACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEEAZABkACgAYwB1AHIAcgBfAHAALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEMAbwBtAHAAYQByAGUAKABuAGUAeAB0AF8AcABfAHQAZQBzAHQALAAgAGwAaQBtAGIAcwBfAGEAKQAgADwAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwBxACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEEAZABkACgAYwB1AHIAcgBfAHEALAAgAHsAMQB9ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbgBlAHgAdABfAHEAKQAsACAAbgBlAHgAdABfAHEALAAgAG4AZQB4AHQAXwBwAF8AdABlAHMAdAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAdABlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAARgBpAG4AYQBsACAAUQAgAGEAbgBkACAAUABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAZQBuAF8AcQAsACAASQBOAEQARQBYACgAcwB3AGUAZQBwAF8AdQBwACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHEALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKABzAHcAZQBlAHAAXwB1AHAALAAgAFMARQBRAFUARQBOAEMARQAoAGYAaQBuAGEAbABfAGwAZQBuAF8AcQAsACAAMQAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHAALAAgAEQAUgBPAFAAKABzAHcAZQBlAHAAXwB1AHAALAAgAGYAaQBuAGEAbABfAGwAZQBuAF8AcQAgACsAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAA0AC4AIABFAHgAdAByAGEAYwB0ACAAVAByAHUAZQAgAFIAZQBtAGEAaQBuAGQAZQByACAAUwBhAGYAZQBsAHkAIAAoAEEAIAAtACAARgBpAG4AYQBsAF8AUAApAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBTAHUAYgAoAGwAaQBtAGIAcwBfAGEALAAgAGYAaQBuAGEAbABfAHAALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABmAGkAbgBhAGwAXwByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAEIAYQBzAGUALQAxADAAIABMAGUAZgB0AC0AdABvAC0AUgBpAGcAaAB0ACAARQB4AHAAbwBuAGUAbgB0AGkAYQB0AGkAbwBuAC4AXABuACAAKgAgAEUAdgBhAGwAdQBhAHQAZQBzACAAdABoAGUAIABlAHgAcABvAG4AZQBuAHQAIABpAHQAZQByAGEAdABpAHYAZQBsAHkAIAB1AHMAaQBuAGcAIABhACAAcAByAGUALQBjAG8AbQBwAHUAdABlAGQAIAAxAC0AOQAgAGMAYQBjAGgAZQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAYQBzAGUAIABUAGgAZQAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5ACAAbwBmACAAdABoAGUAIABiAGEAcwBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAZQB4AHAAXwBzAHQAcgBpAG4AZwAgAFQAaABlACAAZQB4AGEAYwB0ACAAdABlAHgAdAAgAHMAdAByAGkAbgBnACAAbwBmACAAdABoAGUAIABlAHgAcABvAG4AZQBuAHQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFUAUABvAHcAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBiAGEAcwBlACwAIABlAHgAcABfAHMAdAByAGkAbgBnACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFAAcgBlAC0AYwBvAG0AcAB1AHQAZQAgAHAAbwB3AGUAcgBzACAAMQAgAHQAaAByAG8AdQBnAGgAIAA5AC4AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQALAAgAGwAaQBtAGIAcwBfAGIAYQBzAGUALABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQBjAG8AbgBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAZgBpAHIAcwB0ACwAIABmAGkAcgBzAHQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABoAGkAcgBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAcwBlAGMAbwBuAGQALAAgAGYAaQByAHMAdAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABmAG8AdQByAHQAaAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAHMAZQBjAG8AbgBkACwAIABzAGUAYwBvAG4AZAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAZgB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABmAG8AdQByAHQAaAAsACAAZgBpAHIAcwB0ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQB4AHQAaAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAHQAaABpAHIAZAAsACAAdABoAGkAcgBkACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQB2AGUAbgB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABzAGkAeAB0AGgALAAgAGYAaQByAHMAdAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABlAGkAZwB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABmAG8AdQByAHQAaAAsACAAZgBvAHUAcgB0AGgALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBpAG4AdABoACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAZQBpAGcAdABoACwAIABmAGkAcgBzAHQALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGUAeABwAF8AZABpAGcAaQB0AHMALAAgAC0ALQBNAEkARAAoAGUAeABwAF8AcwB0AHIAaQBuAGcALAAgAFMARQBRAFUARQBOAEMARQAoAEwARQBOACgAZQB4AHAAXwBzAHQAcgBpAG4AZwApACkALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFIARQBEAFUAQwBFACgAMQAsACAAZQB4AHAAXwBkAGkAZwBpAHQAcwAsACAATABBAE0AQgBEAEEAKABhAGMAYwAsACAAZABpAGcAaQB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBoAG8AcgB0AC0AYwBpAHIAYwB1AGkAdAA6ACAAUwBrAGkAcAAgAGMAYQBsAGMAdQBsAGEAdABpAG4AZwAgADEAXgAxADAAIABkAHUAcgBpAG4AZwAgAGwAZQBhAGQAaQBuAGcAIABpAHQAZQByAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAcwBfAG8AbgBlACwAIABBAE4ARAAoAFIATwBXAFMAKABhAGMAYwApACAAPQAgADEALAAgAEkATgBEAEUAWAAoAGEAYwBjACwAIAAxACwAIAAxACkAIAA9ACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAMQAuACAAUgBhAGkAcwBlACAAQQBjAGMAIAB0AG8AIAB0AGgAZQAgADEAMAB0AGgAIABwAG8AdwBlAHIAIAB1AHMAaQBuAGcAIABlAHgAYQBjAHQAbAB5ACAANAAgAG0AdQBsAHQAaQBwAGwAaQBjAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8AMQAwACwAIABJAEYAKABpAHMAXwBvAG4AZQAsACAAYQBjAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8AMgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGEAYwBjACwAIABhAGMAYwAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8ANAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGEAYwBjAF8AMgAsACAAYQBjAGMAXwAyACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBjAGMAXwA4ACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAYQBjAGMAXwA0ACwAIABhAGMAYwBfADQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAYQBjAGMAXwA4ACwAIABhAGMAYwBfADIALAAgAGsAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAyAC4AIABNAHUAbAB0AGkAcABsAHkAIABiAHkAIAB0AGgAZQAgAGMAbwByAHIAZQBzAHAAbwBuAGQAaQBuAGcAIABwAHIAZQAtAGMAbwBtAHAAdQB0AGUAZAAgAGMAYQBjAGgAZQAgAHYAYQBsAHUAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABkAGkAZwBpAHQAIAA9ACAAMAAsACAAYQBjAGMAXwAxADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAYQBjAGgAZQBfAHYAYQBsACwAIABDAEgATwBPAFMARQAoAGQAaQBnAGkAdAAsACAAZgBpAHIAcwB0ACwAIABzAGUAYwBvAG4AZAAsACAAdABoAGkAcgBkACwAIABmAG8AdQByAHQAaAAsACAAZgBpAGYAdABoACwAIABzAGkAeAB0AGgALAAgAHMAZQB2AGUAbgB0AGgALAAgAGUAaQBnAHQAaAAsACAAbgBpAG4AdABoACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAaQBzAF8AbwBuAGUALAAgAGMAYQBjAGgAZQBfAHYAYQBsACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAYQBjAGMAXwAxADAALAAgAGMAYQBjAGgAZQBfAHYAYQBsACwAIABrACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAEkAbgB0AGUAZwBlAHIAIABTAHEAdQBhAHIAZQAgAFIAbwBvAHQAIAB1AHMAaQBuAGcAIABOAGUAdwB0AG8AbgAnAHMAIABNAGUAdABoAG8AZAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAG4AIABSAGEAZABpAGMAYQBuAGQAIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AcwBlAGUAZAAgAE8AdgBlAHIALQBlAHMAdABpAG0AYQB0AGUAZAAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABzAGUAZQBkACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBVAFMAcQByAHQAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBuACwAIABsAGkAbQBiAHMAXwBzAGUAZQBkACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAdABhAHQAZQAgAGkAcwAgAHAAYQBjAGsAZQBkADoAIABWAFMAVABBAEMASwAoAGkAcwBfAGQAbwBuAGUAXwBmAGwAYQBnACwAIABjAHUAcgByAGUAbgB0AF8AeAApAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKAAwACwAIABsAGkAbQBiAHMAXwBzAGUAZQBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AaQB0AGUAcgBzACwAIAAzADUALABcAG4AXABuACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAHQAYQB0AGUALAAgAFIARQBEAFUAQwBFACgAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbQBhAHgAXwBpAHQAZQByAHMAKQAsACAATABBAE0AQgBEAEEAKABzAHQAYQB0AGUALAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAHMAXwBkAG8AbgBlACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwB4ACwAIABEAFIATwBQACgAcwB0AGEAdABlACwAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAaQBzAF8AZABvAG4AZQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAdABlACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAxAC4AIABEAGkAdgBpAHMAaQBvAG4AOgAgAG4AIAAvACAAeABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZABpAHYAXwBwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ARABpAHYAUgBvAHUAdABlAHIAKABsAGkAbQBiAHMAXwBuACwAIABjAHUAcgByAF8AeAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcgAsACAASQBOAEQARQBYACgAZABpAHYAXwBwAGEAYwBrAGUAZAAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHEALAAgAEQAUgBPAFAAKABkAGkAdgBfAHAAYQBjAGsAZQBkACwAIABsAGUAbgBfAHIAIAArACAAMQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAyAC4AIABBAGQAZABpAHQAaQBvAG4AOgAgAHgAIAArACAAKABuACAALwAgAHgAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB1AG0AXwB4AHEALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQQBkAGQAKABjAHUAcgByAF8AeAAsACAAcQAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAzAC4AIABIAGEAbAB2AGkAbgBnADoAIAAoAHgAIAArACAAKABuACAALwAgAHgAKQApACAALwAgADIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEsAbgB1AHQAaABEAGkAdgAgAGkAbgBoAGUAcgBlAG4AdABsAHkAIABzAHUAcABwAG8AcgB0AHMAIABzAGMAYQBsAGEAcgAgAGQAaQB2AGkAcwBvAHIAcwAgAHcAaQB0AGgAIAB6AGUAcgBvACAAbwB2AGUAcgBoAGUAYQBkAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGkAdgBfADIAXwBwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2ACgAcwB1AG0AXwB4AHEALAAgAHsAMgB9ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwByADIALAAgAEkATgBEAEUAWAAoAGQAaQB2AF8AMgBfAHAAYQBjAGsAZQBkACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAeABfAG4AZQB4AHQALAAgAEQAUgBPAFAAKABkAGkAdgBfADIAXwBwAGEAYwBrAGUAZAAsACAAbABlAG4AXwByADIAIAArACAAMQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAA0AC4AIABDAG8AbgB2AGUAcgBnAGUAbgBjAGUAIABDAGgAZQBjAGsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQwBvAG0AcABhAHIAZQAoAHgAXwBuAGUAeAB0ACwAIABjAHUAcgByAF8AeAApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABOAGUAdwB0AG8AbgAnAHMAIABtAGUAdABoAG8AZAAgAGMAbwBuAHYAZQByAGcAZQBzACAAbwBuACAAdABoAGUAIABmAGwAbwBvAHIAIAByAG8AbwB0ACwAIABhAG4AZAAgAHMAdABhAGIAaQBsAGkAegBlAHMAIABvAHIAIABvAHMAYwBpAGwAbABhAHQAZQBzACAAdQBwACAAYgB5ACAAMQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABUAGgAZQByAGUAZgBvAHIAZQAsACAAaQBmACAAeABfAG4AZQB4AHQAIAA+AD0AIABjAHUAcgByAF8AeAAsACAAdABoAGUAIABhAGwAZwBvAHIAaQB0AGgAbQAgAGgAYQBzACAAYwBvAG4AdgBlAHIAZwBlAGQALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYwBvAG0AcAAgAD4APQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADEALAAgAGMAdQByAHIAXwB4ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADAALAAgAHgAXwBuAGUAeAB0ACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAZgBpAG4AYQBsAF8AcwB0AGEAdABlACwAIAAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQgBpAGcASQBuAHQAIgAsACIAdABlAHgAdAAiADoAIgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4ALwAvACAAQgBpAGcAIABJAG4AdABlAGcAZQByACAAQQByAGkAdABoAG0AZQB0AGkAYwAgAEwAaQBiAHIAYQByAHkAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIAAgACAAQgBpAGcASQBuAHQAIABNAG8AZAB1AGwAZQAgACAAIAAgACAAIAAgACAAIAAgACAALwAvAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIABQAHUAYgBsAGkAYwAgAEEAUABJACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwBcAG4ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8AXABuAFwAbgAvACoAKgBcAG4AIAAqACAATgBvAHIAbQBhAGwAaQBzAGUAcwAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AIABTAHQAcgBpAHAAcwAgAGwAZQBhAGQAaQBuAGcAIAB6AGUAcgBvAHMALAAgAHIAZQBzAG8AbAB2AGUAcwAgAFwAIgAtADAAXAAiACAAdABvACAAXAAiADAAXAAiACwAIABhAG4AZAAgAHQAaAByAG8AdwBzACAAIwBWAEEATABVAEUAIQAgAG8AbgAgAGkAbgB2AGEAbABpAGQAIABjAGgAYQByAGEAYwB0AGUAcgBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ATgBvAHIAbQAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AHIALAAgAEkARgAoAE8AUgAoAEkAUwBPAE0ASQBUAFQARQBEACgAYgBpAGcAXwBpAG4AdAApACwAIABiAGkAZwBfAGkAbgB0ACAAPQAgAFwAIgBcACIAKQAsACAAXAAiADAAXAAiACwAIABiAGkAZwBfAGkAbgB0ACAAJgAgAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AdgBhAGwAaQBkACwAIABSAEUARwBFAFgAVABFAFMAVAAoAHMAdAByACwAIABcACIAXgAtAD8AXABcAGQAKwAkAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAcgBpAHAAcABlAGQALAAgAFIARQBHAEUAWABSAEUAUABMAEEAQwBFACgAcwB0AHIALAAgAFwAIgBeACgALQA/ACkAMAArACgAPwA9AFwAXABkACkAXAAiACwAIABcACIAJAAxAFwAIgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATgBPAFQAKABpAHMAXwB2AGEAbABpAGQAKQAsACAAVgBBAEwAVQBFACgAXAAiACMAVgBBAEwAVQBFACEAXAAiACkALAAgAEkARgAoAHMAdAByAGkAcABwAGUAZAAgAD0AIABcACIALQAwAFwAIgAsACAAXAAiADAAXAAiACwAIABzAHQAcgBpAHAAcABlAGQAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIABzAGkAZwBuACAAbwBmACAAYQAgAEIAaQBnAEkAbgB0ADoAIAAxACAAKABwAG8AcwBpAHQAaQB2AGUAKQAsACAALQAxACAAKABuAGUAZwBhAHQAaQB2AGUAKQAsACAAbwByACAAMAAgACgAegBlAHIAbwApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AUwBpAGcAbgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALAAgAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAGUAZAAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUwBXAEkAVABDAEgAKABMAEUARgBUACgAbgBvAHIAbQBlAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMABcACIALAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIAAtADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAvACAALQAtAC0AIABQAHIAZQBkAGkAYwBhAHQAZQBzACAALQAtAC0AIABcAFwAXABcAFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFIAZQB0AHUAcgBuAHMAIABUAFIAVQBFACAAaQBmACAAdABoAGUAIABCAGkAZwBJAG4AdAAgAGkAcwAgAGUAeABhAGMAdABsAHkAIAB6AGUAcgBvAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ASQBzAFoAZQByAG8AIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACAAPQAgAFwAIgAwAFwAIgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAFQAUgBVAEUAIABpAGYAIAB0AGgAZQAgAEIAaQBnAEkAbgB0ACAAaQBzACAAbgBlAGcAYQB0AGkAdgBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ASQBzAE4AZQBnACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsACAATABFAEYAVAAoAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0ACkAKQAgAD0AIABcACIALQBcACIAKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFIAZQB0AHUAcgBuAHMAIABUAFIAVQBFACAAaQBmACAAdABoAGUAIABCAGkAZwBJAG4AdAAgAGkAcwAgAGUAdgBlAG4ALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBJAHMARQB2AGUAbgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALAAgAEkAUwBFAFYARQBOACgAVgBBAEwAVQBFACgAUgBJAEcASABUACgATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAKQApACkAKQApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAFQAUgBVAEUAIABpAGYAIAB0AGgAZQAgAEIAaQBnAEkAbgB0ACAAaQBzACAAbwBkAGQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBJAHMATwBkAGQAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAIABJAFMATwBEAEQAKABWAEEATABVAEUAKABSAEkARwBIAFQAKABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACkAKQApACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIAB1AG4AcwBpAGcAbgBlAGQAIABtAGEAZwBuAGkAdAB1AGQAZQAgAG8AZgAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnACAAKABhAGIAcwBvAGwAdQB0AGUAIAB2AGEAbAB1AGUAKQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAIABUAGgAZQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEEAYgBzACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsACAAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AdQBtACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAEUARgBUACgAbgB1AG0AKQAgAD0AIABcACIALQBcACIALAAgAE0ASQBEACgAbgB1AG0ALAAgADIALAAgAEwARQBOACgAbgB1AG0AKQAgAC0AIAAxACkALAAgAG4AdQBtACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEMAbwBtAHAAYQByAGUAcwAgAHQAdwBvACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwBzAC4AIABSAGUAdAB1AHIAbgBzACAAMQAgACgAYQAgAD4AIABiACkALAAgAC0AMQAgACgAYQAgADwAIABiACkALAAgAG8AcgAgADAAIAAoAGEAIAA9ACAAYgApAC4AXABuACAAKgAgAEUAdgBhAGwAdQBhAHQAZQBzACAAcwBpAGcAbgBzACAAYQBuAGQAIABsAGUAbgBnAHQAaABzAC4AIABJAGYAIABpAGQAZQBuAHQAaQBjAGEAbAAsACAAZABlAGwAZQBnAGEAdABlAHMAIAB0AG8AIABuAGEAdABpAHYAZQAgAGwAaQBtAGIAIABhAHIAcgBhAHkAIABjAG8AbQBwAGEAcgBpAHMAbwBuAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAcwBlAGMAbwBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBDAG8AbQBwAGEAcgBlACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBhACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYQAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGIALAAgAEIAaQBnAGkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBiACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AYQAgADwAPgAgAHMAaQBnAG4AXwBiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMASQBHAE4AKABzAGkAZwBuAF8AYQAgAC0AIABzAGkAZwBuAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHMAaQBnAG4AXwBhACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYQAsACAATABFAE4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGIALAAgAEwARQBOACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABsAGUAbgBfAGEAIAA8AD4AIABsAGUAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBJAEcATgAoAGwAZQBuAF8AYQAgAC0AIABsAGUAbgBfAGIAKQAgACoAIABzAGkAZwBuAF8AYQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBBAEQARABcACIAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBhACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYgApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGEAZwBfAGMAbwBtAHAAYQByAGkAcwBvAG4ALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQwBvAG0AcABhAHIAZQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcABhAHIAaQBzAG8AbgAgACoAIABzAGkAZwBuAF8AYQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACAALQAgAEEAZABkAGkAdABpAG8AbgAgACYAIABTAHUAYgB0AHIAYQBjAHQAaQBvAG4AIAAtACAAIAAgACAAIAAgACAAXABcAFwAXABcAG4AXABuAC8AKgAqAFwAbgAgACoAIABBAGQAZABzACAAdAB3AG8AIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEEAZABkACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBhACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYQAsACAAQgBpAGcAaQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGIALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEEARABEAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBhACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGEAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBiACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGIAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAHIAbwB1AHQAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBBAGQAZABTAHUAYgBSAG8AdQB0AGUAcgAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAHMAaQBnAG4AXwBhACwAIABzAGkAZwBuAF8AYgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAGkAZwBuACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcgBvAHUAdABlAGQALAAgAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAEQAUgBPAFAAKAByAG8AdQB0AGUAZAAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAbQBlAHIAZwBlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGYAaQBuAGEAbABfAHMAaQBnAG4AIAA9ACAALQAxACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQALAAgAG0AZQByAGcAZQBkACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFMAdQBiAHQAcgBhAGMAdABzACAAdABoAGUAIABzAGUAYwBvAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAIABmAHIAbwBtACAAdABoAGUAIABmAGkAcgBzAHQAIAAoAEEAIAAtACAAQgApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAG0AaQBuAHUAZQBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGIAIABUAGgAZQAgAHMAdQBiAHQAcgBhAGgAZQBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBTAHUAYgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABiAGkAZwBfAGkAbgB0AF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAASQBuAHYAZQByAHQAIAB0AGgAZQAgAHMAaQBnAG4AIABvAGYAIABCACAAYQB0ACAAdABoAGUAIAB0AGUAeAB0ACAAbABlAHYAZQBsAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAHYAXwBiACwAIABJAEYAKABuAG8AcgBtAF8AYgAgAD0AIABcACIAMABcACIALAAgAFwAIgAwAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEwARQBGAFQAKABuAG8AcgBtAF8AYgApACAAPQAgAFwAIgAtAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAEQAKABuAG8AcgBtAF8AYgAsACAAMgAsACAATABFAE4AKABuAG8AcgBtAF8AYgApACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAgACYAIABuAG8AcgBtAF8AYgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUABhAHMAcwAgAHQAbwAgAEEAZABkAFwAbgAgACAAIAAgACAAIAAgACAAQQBkAGQAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAaQBuAHYAXwBiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFMAdQBtAHMAIABhAG4AIABhAHIAcgBhAHkAIABvAHIAIAByAGEAbgBnAGUAIABvAGYAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMAIAB2AGkAYQAgAHYAZQBjAHQAbwByAGkAegBlAGQAIABnAHIAbwB1AHAAIABtAGEAdAByAGkAYwBlAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIAByAGEAbgBnAGUAIABBACAAYwBvAG4AdABpAGcAdQBvAHUAcwAgAHIAYQBuAGcAZQAgAG8AcgAgAGEAcgByAGEAeQAgAG8AZgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoALwBcAG4AUwB1AG0AIAA9ACAATABBAE0AQgBEAEEAKAByAGEAbgBnAGUALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAZgBsAGEAdAAsACAAVABPAFIATwBXACgAcgBhAG4AZwBlACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATwBSACgASQBTAEUAUgBSAE8AUgAoAGYAbABhAHQAKQAsACAAQwBPAEwAVQBNAE4AUwAoAGYAbABhAHQAKQAgAD0AIAAwACkALAAgAFwAIgAwAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AbwByAG0AcwAsACAATQBBAFAAKABmAGwAYQB0ACwAIABMAEEATQBCAEQAQQAoAHgALAAgAE4AbwByAG0AKAB4ACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBzACwAIABNAEEAUAAoAEwARQBGAFQAKABuAG8AcgBtAHMAKQAsACAATABBAE0AQgBEAEEAKAB4ACwAIABJAEYAKAB4ACAAPQAgAFwAIgAwAFwAIgAsACAAMAAsACAAaQBmACgAeAAgAD0AIABcACIALQBcACIALAAgAC0AMQAsACAAMQApACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBiAHMAXwBuAG8AcgBtAHMALAAgAE0AQQBQACgAbgBvAHIAbQBzACwAIABzAGkAZwBuAHMALAAgAEwAQQBNAEIARABBACgAeAAsACAAcwBpAGcAbgAsACAASQBGACgAcwBpAGcAbgAgAD0AIAAtADEALAAgAE0ASQBEACgAeAAsACAAMgAsACAATABFAE4AKAB4ACkALQAxACkALAAgAHgAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAG8AcwBfAHMAdAByAHMALAAgAEYASQBMAFQARQBSACgAYQBiAHMAXwBuAG8AcgBtAHMALAAgAHMAaQBnAG4AcwAgAD0AIAAxACwAIAB7AFwAIgAwAFwAIgB9ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAZwBfAHMAdAByAHMALAAgAEYASQBMAFQARQBSACgAYQBiAHMAXwBuAG8AcgBtAHMALAAgAHMAaQBnAG4AcwAgAD0AIAAtADEALAAgAHsAXAAiADAAXAAiAH0AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHUAbgBpAGYAaQBlAGQAXwBrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIAQQBEAEQAXAAiACwAIABDAE8ATABVAE0ATgBTACgAZgBsAGEAdAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAG8AcwBfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAGEAdAByAGkAeABTAHUAbQAoAHAAbwBzAF8AcwB0AHIAcwAsACAAdQBuAGkAZgBpAGUAZABfAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQBnAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AYQB0AHIAaQB4AFMAdQBtACgAbgBlAGcAXwBzAHQAcgBzACwAIAB1AG4AaQBmAGkAZQBkAF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBvAHUAdABlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEEAZABkAFMAdQBiAFIAbwB1AHQAZQByACgAcABvAHMAXwBsAGkAbQBiAHMALAAgAG4AZQBnAF8AbABpAG0AYgBzACwAIAAxACwAIAAtADEALAAgAHUAbgBpAGYAaQBlAGQAXwBrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAGkAZwBuACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcgBvAHUAdABlAGQALAAgAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABEAFIATwBQACgAcgBvAHUAdABlAGQALAAgAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBlAHIAZwBlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAdQBuAGkAZgBpAGUAZABfAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGYAaQBuAGEAbABfAHMAaQBnAG4AIAA9ACAALQAxACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQALAAgAG0AZQByAGcAZQBkACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABNAHUAbAB0AGkAcABsAGkAZQBzACAAdAB3AG8AIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAE0AdQBsACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBhACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYQAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGIALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYQAsACAATABFAE4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGIALAAgAEwARQBOACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGgAbwByAHQALQBjAGkAcgBjAHUAaQB0ADoAIAAwACAAbQB1AGwAdABpAHAAbABpAGUAZAAgAGIAeQAgAGEAbgB5AHQAaABpAG4AZwAgAGkAcwAgADAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABzAGkAZwBuAF8AYQAgAD0AIAAwACwAIABzAGkAZwBuAF8AYgAgAD0AIAAwACkALAAgAFwAIgAwAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbABlAG4AXwBhACAAKwAgAGwAZQBuAF8AYgAgAD4AIAAzADIANwA2ADYALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAYQBsAGMAdQBsAGEAdABlACAAZAB5AG4AYQBtAGkAYwAgAHMAYQBmAGUAIABLACAAYgBhAHMAZQBkACAAbwBuACAAdABoAGUAIABzAGgAbwByAHQAZQBzAHQAIABzAHQAcgBpAG4AZwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIATQBVAEwAXAAiACwAIABNAEkATgAoAGwAZQBuAF8AYQAsACAAbABlAG4AXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAcABsAGkAdAAgAGEAYgBzAG8AbAB1AHQAZQAgAHMAdAByAGkAbgBnAHMAIABpAG4AdABvACAAbABpAHQAdABsAGUALQBlAG4AZABpAGEAbgAgAGEAcgByAGEAeQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGEALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYQApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBiACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGIAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIABtAGEAZwBuAGkAdAB1AGQAZQAgAGEAbgBkACAAcgBlAHMAbwBsAHYAZQAgAHMAaQBnAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcwBpAGcAbgAsACAAcwBpAGcAbgBfAGEAIAAqACAAcwBpAGcAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGUAcgBnAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAXAAiAC0AXAAiACAAJgAgAG0AZQByAGcAZQBkACwAIABtAGUAcgBnAGUAZAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAFYATwBMAEEAVABJAEwARQBdACAARwBlAG4AZQByAGEAdABlAHMAIABhACAAZAB5AG4AYQBtAGkAYwAgAGEAcgByAGEAeQAgAG8AZgAgAGkAbgB0AGUAZwBlAHIAcwAgAGEAcwAgAHQAZQB4AHQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG4AdQBtAF8AcgBvAHcAcwBdACAAYQByAHIAYQB5ACAAaABlAGkAZwBoAHQALAAgAGQAZQBmAGEAdQBsAHQAIAAxAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAWwBuAHUAbQBfAGMAbwBsAHMAXQAgAGEAcgByAGEAeQAgAHcAaQBkAHQAaAAsACAAZABlAGYAYQB1AGwAdAAgADEALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG0AaQBuAF8AZABpAGcAaQB0AHMAXQAgAG0AaQBuAGkAbQB1AG0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAaQBnAGkAdABzACwAIABkAGUAZgBhAHUAbAB0ACAAMQA2ACAAKABtAGkAbgAgADEAIABkAGkAZwBpAHQAKQBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG0AYQB4AF8AZABpAGcAaQB0AHMAXQAgAG0AYQB4AGkAbQB1AG0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAaQBnAGkAdABzACwAIABkAGUAZgBhAHUAbAB0ACAANQAwACAAKABtAGEAeAAgADMAMgAsADcANgA3ACAAYwBoAGEAcgBzACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAHMAaQBnAG4AKQBcAG4AIAAqAC8AXABuAFIAYQBuAGQAQgBpAGcASQBuAHQAQQByAHIAYQB5ACAAPQAgAEwAQQBNAEIARABBACgAWwBuAHUAbQBfAHIAbwB3AHMAXQAsACAAWwBuAHUAbQBfAGMAbwBsAHMAXQAsACAAWwBtAGkAbgBfAGQAaQBnAGkAdABzAF0ALAAgAFsAbQBhAHgAXwBkAGkAZwBpAHQAcwBdACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwByAG8AdwBzACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAG4AdQBtAF8AcgBvAHcAcwApACwAIAAxACwAIABuAHUAbQBfAHIAbwB3AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBfAGMAbwBsAHMALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbgB1AG0AXwBjAG8AbABzACkALAAgADEALAAgAG4AdQBtAF8AYwBvAGwAcwApACwAIABcAG4AIAAgACAAIAAgACAAIAAgAG0AaQBuAF8AbABlAG4ALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbQBpAG4AXwBkAGkAZwBpAHQAcwApACwAIAAxADYALAAgAE0ASQBOACgAMwAyADcANgA3ACwAIABNAEEAWAAoADEALAAgAG0AaQBuAF8AZABpAGcAaQB0AHMAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AbABlAG4ALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbQBhAHgAXwBkAGkAZwBpAHQAcwApACwAIAA1ADAALAAgAE0AQQBYACgAMQAsACAATQBJAE4AKAAzADIANwA2ADYALAAgAG0AYQB4AF8AZABpAGcAaQB0AHMAKQApACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABNAEEAUAAoAFIAQQBOAEQAQQBSAFIAQQBZACgAbgBfAHIAbwB3AHMALAAgAG4AXwBjAG8AbABzACwAIABtAGkAbgBfAGwAZQBuACwAIABtAGEAeABfAGwAZQBuACwAIABUAFIAVQBFACkALAAgAEwAQQBNAEIARABBACgAbABlAG4AZwB0AGgALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGkAZwBuACwAIABDAEgATwBPAFMARQAoAFIAQQBOAEQAQgBFAFQAVwBFAEUATgAoADEALAAgADIAKQAsACAAXAAiAFwAIgAsACAAXAAiAC0AXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGkAZwBpAHQAcwAsACAAQwBPAE4AQwBBAFQAKABSAEEATgBEAEEAUgBSAEEAWQAoADEALAAgAGwAZQBuAGcAdABoACwAIAAwACwAIAA5ACwAIABUAFIAVQBFACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AIAAmACAAUgBFAEcARQBYAFIARQBQAEwAQQBDAEUAKABkAGkAZwBpAHQAcwAsACAAXAAiAF4AMAAqAFwAIgAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABEAGkAdgBpAGQAZQBzACAAdABoAGUAIABmAGkAcgBzAHQAIABCAGkAZwBJAG4AdAAgAGIAeQAgAHQAaABlACAAcwBlAGMAbwBuAGQAIAAoAEEAIAAvACAAQgApAC4AIABcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAHQAaABlACAAcQB1AG8AdABpAGUAbgB0ACAAYQBuAGQAIABtAG8AZAB1AGwAdQBzACAAaQBuACAAcgBvAHcAcwAgADEAIABhAG4AZAAgADIALAAgAHIAZQBzAHAAZQBjAHQAaQB2AGUAbAB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAGQAaQB2AGkAZABlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAHUAcwBlAF8AZgBsAG8AbwByAF0AIABPAHAAdABpAG8AbgBhAGwAIABiAG8AbwBsAGUAYQBuAC4AIABUAFIAVQBFACAAZgBvAHIAIABQAHkAdABoAG8AbgAtAHMAdAB5AGwAZQAgAEYAbABvAG8AcgAgAGQAaQB2AGkAcwBpAG8AbgAsACAARgBBAEwAUwBFACAAZgBvAHIAIABUAHIAdQBuAGMAYQB0AGUAZAAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAARgBBAEwAUwBFAC4AXABuACAAKgAvAFwAbgBEAGkAdgBNAG8AZAAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABiAGkAZwBfAGkAbgB0AF8AYgAsACAAWwB1AHMAZQBfAGYAbABvAG8AcgBdACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBhACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYQAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGIALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGkAcwBfAGYAbABvAG8AcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAB1AHMAZQBfAGYAbABvAG8AcgApACwAIABGAEEATABTAEUALAAgAHUAcwBlAF8AZgBsAG8AbwByACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAcwBpAGcAbgBfAGIAIAA9ACAAMAAsACAAIwBEAEkAVgAvADAAIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AYQAgAD0AIAAwACwAIAB7AFwAIgAwAFwAIgA7AFwAIgAwAFwAIgB9ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBEAEkAVgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBhACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBiACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZABfAHIAZQBzAHUAbAB0ACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBEAGkAdgBSAG8AdQB0AGUAcgAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAUgBlAG0AYQBpAG4AZABlAHIAIABhAG4AZAAgAFEAdQBvAHQAaQBlAG4AdAAgAGEAcgByAGEAeQBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwByACwAIABJAE4ARABFAFgAKABwAGEAYwBrAGUAZABfAHIAZQBzAHUAbAB0ACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBtAF8AbABpAG0AYgBzACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcABhAGMAawBlAGQAXwByAGUAcwB1AGwAdAAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwByACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcQB1AG8AdABfAGwAaQBtAGIAcwAsACAARABSAE8AUAAoAHAAYQBjAGsAZQBkAF8AcgBlAHMAdQBsAHQALAAgAGwAZQBuAF8AcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHMAbwBsAHYAZQAgAFQAcgB1AG4AYwBhAHQAZQBkACAAcwBpAGcAbgBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcwBpAGcAbgAsACAAcwBpAGcAbgBfAGEAIAAqACAAcwBpAGcAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AZQByAGcAZQBkAF8AcQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAcQB1AG8AdABfAGwAaQBtAGIAcwAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGUAcgBnAGUAZABfAHIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAHIAZQBtAF8AbABpAG0AYgBzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdAByAHUAbgBjAF8AcQAsACAASQBGACgAQQBOAEQAKABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAbQBlAHIAZwBlAGQAXwBxACAAPAA+ACAAXAAiADAAXAAiACkAIAAsACAAXAAiAC0AXAAiACAAJgAgAG0AZQByAGcAZQBkAF8AcQAsACAAbQBlAHIAZwBlAGQAXwBxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAcgB1AG4AYwBfAHIALAAgAEkARgAoAGEAbgBkACgAcwBpAGcAbgBfAGEAIAA9ACAALQAxACwAIABtAGUAcgBnAGUAZABfAHIAIAA8AD4AIABcACIAMABcACIAKQAsACAAXAAiAC0AXAAiACAAJgAgAG0AZQByAGcAZQBkAF8AcgAsACAAbQBlAHIAZwBlAGQAXwByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARgBsAG8AbwByACAAQwBvAHIAcgBlAGMAdABpAG8AbgA6ACAAVAByAGkAZwBnAGUAcgAgAE8ATgBMAFkAIABpAGYAIABmAGwAbwBvAHIAIABpAHMAIAByAGUAcQB1AGUAcwB0AGUAZAAsACAAcwBpAGcAbgBzACAAZABpAGYAZgBlAHIALAAgAGEAbgBkACAAcgBlAG0AYQBpAG4AZABlAHIAIABpAHMAIABuAG8AbgAtAHoAZQByAG8AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAZQBkAHMAXwBjAG8AcgByAGUAYwB0AGkAbwBuACwAIABBAE4ARAAoAGkAcwBfAGYAbABvAG8AcgAsACAAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAG0AZQByAGcAZQBkAF8AcgAgADwAPgAgAFwAIgAwAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHEALAAgAEkARgAoAG4AZQBlAGQAcwBfAGMAbwByAHIAZQBjAHQAaQBvAG4ALAAgAFMAdQBiACgAdAByAHUAbgBjAF8AcQAsACAAXAAiADEAXAAiACkALAAgAHQAcgB1AG4AYwBfAHEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsACAASQBGACgAbgBlAGUAZABzAF8AYwBvAHIAcgBlAGMAdABpAG8AbgAsACAAQQBkAGQAKAB0AHIAdQBuAGMAXwByACwAIABuAG8AcgBtAF8AYgApACwAIAB0AHIAdQBuAGMAXwByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABmAGkAbgBhAGwAXwBxACwAIABmAGkAbgBhAGwAXwByACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEQAaQB2AGkAZABlAHMAIAB0AGgAZQAgAGYAaQByAHMAdAAgAEIAaQBnAEkAbgB0ACAAYgB5ACAAdABoAGUAIABzAGUAYwBvAG4AZAAgACgAQQAgAC8AIABCACkALgAgAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBhACAAVABoAGUAIABkAGkAdgBpAGQAZQBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGIAIABUAGgAZQAgAGQAaQB2AGkAcwBvAHIAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAWwB1AHMAZQBfAGYAbABvAG8AcgBdACAATwBwAHQAaQBvAG4AYQBsACAAYgBvAG8AbABlAGEAbgAuACAAVABSAFUARQAgAGYAbwByACAAUAB5AHQAaABvAG4ALQBzAHQAeQBsAGUAIABGAGwAbwBvAHIAIABkAGkAdgBpAHMAaQBvAG4ALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAEYAQQBMAFMARQAuAFwAbgAgACoALwBcAG4ARABpAHYAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALAAgAFsAdQBzAGUAXwBmAGwAbwBvAHIAXQAsAFwAbgAgACAAIAAgAEkATgBEAEUAWAAoAEQAaQB2AE0AbwBkACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAIAB1AHMAZQBfAGYAbABvAG8AcgApACwAIAAxACwAIAAxACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABDAG8AbQBwAHUAdABlAHMAIAB0AGgAZQAgAHIAZQBtAGEAaQBuAGQAZQByACAAbwBmACAAQQAgAC8AIABCAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAGQAaQB2AGkAZABlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAHUAcwBlAF8AZgBsAG8AbwByAF0AIABPAHAAdABpAG8AbgBhAGwAIABiAG8AbwBsAGUAYQBuAC4AIABUAFIAVQBFACAAZgBvAHIAIABQAHkAdABoAG8AbgAtAHMAdAB5AGwAZQAgAE0AbwBkAHUAbABvAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABGAEEATABTAEUALgBcAG4AIAAqAC8AXABuAE0AbwBkACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAIABbAHUAcwBlAF8AZgBsAG8AbwByAF0ALABcAG4AIAAgACAAIABJAE4ARABFAFgAKABEAGkAdgBNAG8AZAAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABiAGkAZwBfAGkAbgB0AF8AYgAsACAAdQBzAGUAXwBmAGwAbwBvAHIAKQAsACAAMgAsACAAMQApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBhAGkAcwBlAHMAIABhACAAQgBpAGcASQBuAHQAIABiAGEAcwBlACAAdABvACAAdABoAGUAIABwAG8AdwBlAHIAIABvAGYAIABhACAAQgBpAGcASQBuAHQAIABlAHgAcABvAG4AZQBuAHQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGEAcwBlACAAVABoAGUAIABiAGEAcwBlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGUAeABwAG8AbgBlAG4AdAAgAFQAaABlACAAZQB4AHAAbwBuAGUAbgB0ACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AUABvAHcAIAA9ACAATABBAE0AQgBEAEEAKABiAGEAcwBlACwAIABlAHgAcABvAG4AZQBuAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGIAYQBzAGUALAAgAE4AbwByAG0AKABiAGEAcwBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBlAHgAcAAsACAATgBvAHIAbQAoAGUAeABwAG8AbgBlAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgBhAHMAZQAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAGUAeABwACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AZQB4AHAAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGEAYgBzAF8AYgBhAHMAZQAsACAAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBiAGEAcwBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAGEAYgBzAF8AZQB4AHAALAAgAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AZQB4AHAAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGkAcwBfAGUAeABwAF8AZQB2AGUAbgAsACAASQBTAEUAVgBFAE4AKABWAEEATABVAEUAKABSAEkARwBIAFQAKABuAG8AcgBtAF8AZQB4AHAALAAgADEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAaQBnAG4ALAAgAEkARgAoAHMAaQBnAG4AXwBiAGEAcwBlACAAPQAgAC0AMQAsACAASQBGACgAaQBzAF8AZQB4AHAAXwBlAHYAZQBuACwAIAAxACwAIAAtADEAKQAsACAAcwBpAGcAbgBfAGIAYQBzAGUAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEgAYQBuAGQAbABlACAAbQBhAHQAaABlAG0AYQB0AGkAYwBhAGwAIABiAG8AdQBuAGQAYQByAGkAZQBzACAAYQBuAGQAIABiAGEAcwBlACAAbABpAG0AaQB0AHMAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABhAGIAcwBfAGIAYQBzAGUAIAA9ACAAXAAiADAAXAAiACwAIABJAEYAKABuAG8AcgBtAF8AZQB4AHAAIAA9ACAAXAAiADAAXAAiACwAIAAjAE4AVQBNACEALAAgAFwAIgAwAFwAIgApACwAIAAvAC8AIAAwAF4AMAAgAGkAcwAgAHUAbgBkAGUAZgBpAG4AZQBkAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAYQBiAHMAXwBiAGEAcwBlACAAPQAgAFwAIgAxAFwAIgAsACAASQBGACgAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAFwAIgAtADEAXAAiACwAIABcACIAMQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAcwBpAGcAbgBfAGUAeABwACAAPQAgAC0AMQAsACAAXAAiADAAXAAiACwAIAAvAC8AIABJAG4AdABlAGcAZQByACAAdAByAHUAbgBjAGEAdABpAG8AbgA6ACAAbgBlAGcAYQB0AGkAdgBlACAAZQB4AHAAbwBuAGUAbgB0AHMAIAB5AGkAZQBsAGQAIAAwACAAZgBvAHIAIABiAGEAcwBlAHMAIAA+AD0AIAAyAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgBvAHIAbQBfAGUAeABwACAAPQAgAFwAIgAwAFwAIgAsACAAXAAiADEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHMAdQBsAHQAcwAgAGYAcgBvAG0AIABlAHgAcABvAG4AZQBuAHQAcwAgAGcAcgBlAGEAdABlAHIAIAB0AGgAYQBuACAANgAgAGQAaQBnAGkAdABzACAAYwBhAG4AbgBvAHQAIABiAGUAIABkAGkAcwBwAGwAYQB5AGUAZAAuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABFAE4AKABuAG8AcgBtAF8AZQB4AHAAKQAgAD4AIAA2ACwAIAAjAE4AVQBNACEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAHUAbQBfAGUAeABwACwAIABWAEEATABVAEUAKABuAG8AcgBtAF8AZQB4AHAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAcABwAHIAbwB4AGkAbQBhAHQAZQAgAHQAaABlACAAZgBpAG4AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAIABjAG8AdQBuAHQAOgAgAEIAIAAqACAATABvAGcAMQAwACgAQQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGIAYQBzAGUAXwBsAG8AZwAxADAALAAgAEwATwBHADEAMAAoAFYAQQBMAFUARQAoAEwARQBGAFQAKABhAGIAcwBfAGIAYQBzAGUALAAgADEANAApACkAKQAgACsAIABNAEEAWAAoADAALAAgAEwARQBOACgAYQBiAHMAXwBiAGEAcwBlACkAIAAtACAAMQA0ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAHAAcAByAG8AeABfAGQAaQBnAGkAdABzACwAIABuAHUAbQBfAGUAeABwACAAKgAgAGIAYQBzAGUAXwBsAG8AZwAxADAALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYQBwAHAAcgBvAHgAXwBkAGkAZwBpAHQAcwAgAD4AIAAzADIANwA2ADYALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAE0AVQBMAFwAIgAsACAAYQBwAHAAcgBvAHgAXwBkAGkAZwBpAHQAcwAgAC8AIAAyACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYgBhAHMAZQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYQBiAHMAXwBiAGEAcwBlACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBQAG8AdwAoAGwAaQBtAGIAcwBfAGIAYQBzAGUALAAgAG4AbwByAG0AXwBlAHgAcAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AZQByAGcAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAFwAIgAtAFwAIgAgACYAIABtAGUAcgBnAGUAZAAsACAAbQBlAHIAZwBlAGQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQApACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAQwBhAGwAYwB1AGwAYQB0AGUAcwAgAHQAaABlACAAaQBuAHQAZQBnAGUAcgAgAHMAcQB1AGEAcgBlACAAcgBvAG8AdAAgACgAZgBsAG8AbwByACkAIABvAGYAIABhACAAQgBpAGcASQBuAHQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIAByAGEAZABpAGMAYQBuAGQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBTAHEAcgB0ACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AbgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAG4ALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBuACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AbgAgAD0AIAAtADEALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgBvAHIAbQBfAG4AIAA9ACAAXAAiADAAXAAiACwAIABcACIAMABcACIALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AbwByAG0AXwBuACAAPQAgAFwAIgAxAFwAIgAsACAAXAAiADEAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwBuACwAIABMAEUATgAoAG4AbwByAG0AXwBuACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGEAawBlAF8AZABpAGcAaQB0AHMALAAgAEkARgAoAGwAZQBuAF8AbgAgADwAPQAgADEANAAsACAAbABlAG4AXwBuACwAIABJAEYAKABJAFMARQBWAEUATgAoAGwAZQBuAF8AbgApACwAIAAxADQALAAgADEAMwApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB2AF8AcwB0AHIALAAgAEwARQBGAFQAKABuAG8AcgBtAF8AbgAsACAAdABhAGsAZQBfAGQAaQBnAGkAdABzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB2AF8AbgB1AG0ALAAgAFYAQQBMAFUARQAoAHYAXwBzAHQAcgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAegBlAHIAbwBfAGMAbwB1AG4AdAAsACAAKABsAGUAbgBfAG4AIAAtACAAdABhAGsAZQBfAGQAaQBnAGkAdABzACkAIAAvACAAMgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGUAZQBkAF8AcAByAGUAZgBpAHgALAAgAFQARQBYAFQAKABSAE8AVQBOAEQAVQBQACgAUwBRAFIAVAAoAHYAXwBuAHUAbQApACwAIAAwACkAIAArACAAMQAsACAAXAAiADAAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGUAZQBkAF8AcwB0AHIALAAgAHMAZQBlAGQAXwBwAHIAZQBmAGkAeAAgACYAIABSAEUAUABUACgAXAAiADAAXAAiACwAIAB6AGUAcgBvAF8AYwBvAHUAbgB0ACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBjAGEAbABlAHMAIABrACAAYgB5ACAAdABoAGUAIABtAGEAeABpAG0AdQBtACAAbwB2AGUAcgBsAGEAcAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBNAFUATABcACIALAAgAGwAZQBuAF8AbgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AbgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAbgBvAHIAbQBfAG4ALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAHMAZQBlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAHMAZQBlAGQAXwBzAHQAcgAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBTAHEAcgB0ACgAbABpAG0AYgBzAF8AbgAsACAAbABpAG0AYgBzAF8AcwBlAGUAZAAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAawApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAuAEsAbgB1AHQAaABEAGkAdgBpAHMAaQBvAG4AIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgBpAHMAaQBvAG4AIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ARABpAHYAaQBzAGkAbwBuAEEAbABnAG8AcgBpAHQAaABtAHMAIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ARABpAHYAaQBzAGkAbwBuAEEAbABnAG8AcgBpAHQAaABtAEMAbwBtAHAAYQByAGkAcwBvAG4AIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ARABpAHYAaQBzAGkAbwBuAEIAZQBuAGMAaABtAGEAcgBrAEMAYQBzAGUAcwAiACwAIgB0AGUAcwB0AF8AQgBpAGcASQBuAHQALgBBAHMAeQBtAG0AZQB0AHIAaQBjAEEAQgBHAHIAaQBkACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEMAYQByAHIAeQAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEMAbwBtAHAAYQByAGUAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBBAGQAZAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAdQBiACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQBhAHQAcgBpAHgAUwB1AG0AIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AQQBkAGQAUwB1AGIAUgBvAHUAdABlAHIAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBGAGkAbgBkAFEAdQBvAHQAaQBlAG4AdABMAGkAbQBiACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEsAbgB1AHQAaABEAGkAdgAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBEAGkAdgBSAG8AdQB0AGUAcgAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAFMAZQBlAGQAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBSAGUAYwBpAHAAcgBvAGMAYQBsACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4ARABpAHYAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBQAG8AdwAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAcQByAHQAIgAsACIAQgBpAGcASQBuAHQALgBOAG8AcgBtACIALAAiAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAiACwAIgBCAGkAZwBJAG4AdAAuAEkAcwBaAGUAcgBvACIALAAiAEIAaQBnAEkAbgB0AC4ASQBzAE4AZQBnACIALAAiAEIAaQBnAEkAbgB0AC4ASQBzAEUAdgBlAG4AIgAsACIAQgBpAGcASQBuAHQALgBJAHMATwBkAGQAIgAsACIAQgBpAGcASQBuAHQALgBBAGIAcwAiACwAIgBCAGkAZwBJAG4AdAAuAEMAbwBtAHAAYQByAGUAIgAsACIAQgBpAGcASQBuAHQALgBBAGQAZAAiACwAIgBCAGkAZwBJAG4AdAAuAFMAdQBiACIALAAiAEIAaQBnAEkAbgB0AC4AUwB1AG0AIgAsACIAQgBpAGcASQBuAHQALgBNAHUAbAAiACwAIgBCAGkAZwBJAG4AdAAuAFIAYQBuAGQAQgBpAGcASQBuAHQAQQByAHIAYQB5ACIALAAiAEIAaQBnAEkAbgB0AC4ARABpAHYATQBvAGQAIgAsACIAQgBpAGcASQBuAHQALgBEAGkAdgAiACwAIgBCAGkAZwBJAG4AdAAuAE0AbwBkACIALAAiAEIAaQBnAEkAbgB0AC4AUABvAHcAIgAsACIAQgBpAGcASQBuAHQALgBTAHEAcgB0ACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAFwAbgAvAC8AIABCAGkAZwAgAEkAbgB0AGUAZwBlAHIAIABBAHIAaQB0AGgAbQBlAHQAaQBjACAATABpAGIAcgBhAHIAeQAgAC8ALwBcAG4ALwAvACAAIAAgACAAIAAgACAAdABlAHMAdABfAEIAaQBnAEkAbgB0ACAATQBvAGQAdQBsAGUAIAAgACAAIAAgACAAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIAAgAFAAcgBpAHYAYQB0AGUAIABUAGUAcwB0AGkAbgBnACAAQQBQAEkAIAAgACAAIAAgACAALwAvAFwAbgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4AXABuAEsAbgB1AHQAaABEAGkAdgBpAHMAaQBvAG4APQBMAEEATQBCAEQAQQAoAGEALAAgAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2ACgAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYQAsACAAawApACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABiACwAIABrACkALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAEQAUgBPAFAAKABwAGEAYwBrAGUAZAAsACAASQBOAEQARQBYACgAcABhAGMAawBlAGQALAAgADEALAAgADEAKQAgACsAIAAxACkALAAgAGsAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAgAD0AIABMAEEATQBCAEQAQQAoAGEALAAgAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgAoAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAGEALAAgAGsAKQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYgAsACAAawApACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABEAFIATwBQACgAcABhAGMAawBlAGQALAAgAEkATgBEAEUAWAAoAHAAYQBjAGsAZQBkACwAIAAxACwAIAAxACkAIAArACAAMQApACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAcwB0AHIAaQBuAGcAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAHMAdAByAGkAbgBnAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG0AbwBkAGUAIABcACIASwBOAFUAVABIAFwAIgAgAG8AcgAgAFwAIgBOAFIAXAAiAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGkAdABlAHIAcwAgAEkAbgBuAGUAcgAgAGwAbwBvAHAAIABjAG8AdQBuAHQAIAAoAHQAbwAgAGQAZQBmAGUAYQB0ACAAYwBoAHUAbgBrAHkAIABjAGwAbwBjAGsAIAByAGUAcwBvAGwAdQB0AGkAbwBuACkAXABuACAAKgAgAEAAcABhAHIAYQBtACAAcgBlAHAAZQBhAHQAcwAgAE8AdQB0AGUAcgAgAGwAbwBvAHAAIABjAG8AdQBuAHQAIAAoAHQAbwAgAGQAZQBmAGUAYQB0ACAATwBTAC8ARwBhAHIAYgBhAGcAZQAgAEMAbwBsAGwAZQBjAHQAaQBvAG4AIABuAG8AaQBzAGUAKQBcAG4AIAAqAC8AXABuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACAAPQAgAEwAQQBNAEIARABBACgAYQAsACAAYgAsACAAbQBvAGQAZQAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAE0AYQBwACAAdABoAGUAIABvAHUAdABlAHIAIAByAGUAcABlAGEAdABzACAAbABvAG8AcABcAG4AIAAgACAAIAAgACAAIAAgAGIAYQB0AGMAaABfAHQAaQBtAGUAcwAsACAATQBBAFAAKABTAEUAUQBVAEUATgBDAEUAKAByAGUAcABlAGEAdABzACkALAAgAEwAQQBNAEIARABBACgAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdAAsACAATgBPAFcAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATQBhAHAAIAB0AGgAZQAgAGkAbgBuAGUAcgAgAGUAeABlAGMAdQB0AGkAbwBuACAAbABvAG8AcABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAHUAbgAsACAASQBGACgAbQBvAGQAZQAgAD0AIABcACIASwBOAFUAVABIAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBQACgAUwBFAFEAVQBFAE4AQwBFACgAaQB0AGUAcgBzACkALAAgAEwAQQBNAEIARABBACgAaQAsACAASwBuAHUAdABoAEQAaQB2AGkAcwBpAG8AbgAoAGEALAAgAGIAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFAAKABTAEUAUQBVAEUATgBDAEUAKABpAHQAZQByAHMAKQAsACAATABBAE0AQgBEAEEAKABpACwAIABOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAoAGEALAAgAGIAKQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEYAbwByAGMAZQAgAGUAdgBhAGwAdQBhAHQAaQBvAG4AIABiAGUAZgBvAHIAZQAgAHAAdQBsAGwAaQBuAGcAIABzAHQAbwBwACAAdABpAG0AZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAbwBwACwAIABOAE8AVwAoACkAIAArACAAKAAwACAAKgAgAEwARQBOACgASQBOAEQARQBYACgAcgB1AG4ALAAgADEALAAgADEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABUAG8AdABhAGwAIABiAGEAdABjAGgAIAB0AGkAbQBlACAAaQBuACAAbQBpAGwAbABpAHMAZQBjAG8AbgBkAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABzAHQAbwBwACAALQAgAHMAdABhAHIAdAApACAAKgAgADgANgA0ADAAMAAwADAAMABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAdABoAGUAIABjAGwAZQBhAG4AZQBzAHQAIAByAHUAbgAgAGEAbgBkACAAYQB2AGUAcgBhAGcAZQAgAGkAdAAgAGQAbwB3AG4AIAB0AG8AIABhACAAcwBpAG4AZwBsAGUAIABlAHgAZQBjAHUAdABpAG8AbgAgAHQAaQBtAGUAXABuACAAIAAgACAAIAAgACAAIABNAEkATgAoAGIAYQB0AGMAaABfAHQAaQBtAGUAcwApACAALwAgAGkAdABlAHIAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAARQB4AGUAYwB1AHQAZQBzACAAYQAgAHMAdAByAGkAYwB0AGwAeQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABiAGUAbgBjAGgAbQBhAHIAawAgAHMAdQBpAHQAZQAgAHQAbwAgAGEAdgBvAGkAZAAgAG0AdQBsAHQAaQAtAHQAaAByAGUAYQBkAGkAbgBnACAAYwBvAG4AdABhAG0AaQBuAGEAdABpAG8AbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHQAZQBzAHQAXwBjAGEAcwBlAHMAIABBAG4AIABOACAAeAAgADIAIABhAHIAcgBhAHkAIABvAGYAIAB0AGUAcwB0ACAAbABlAG4AZwB0AGgAcwA6ACAAWwBMAGUAbgBnAHQAaABfAEEALAAgAEwAZQBuAGcAdABoAF8AQgBdAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGkAdABlAHIAcwAgAE4AdQBtAGIAZQByACAAbwBmACAAaQB0AGUAcgBhAHQAaQBvAG4AcwAgAHAAZQByACAAYgBlAG4AYwBoAG0AYQByAGsAIAB0AG8AIABzAG0AbwBvAHQAaAAgAE4ATwBXACgAKQAgAHIAZQBzAG8AbAB1AHQAaQBvAG4ALgBcAG4AIAAqAC8AXABuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBDAG8AbQBwAGEAcgBpAHMAbwBuACAAPQAgAEwAQQBNAEIARABBACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwB0AGUAcwB0AHMALAAgAFIATwBXAFMAKAB0AGUAcwB0AF8AYwBhAHMAZQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAASQBuAGkAdABpAGEAbAAgAHMAdABhAHQAZQA6ACAARABhAHQAYQAgAGgAZQBhAGQAZQByAHMAIABmAG8AcgAgAEMAUwBWACAAZQB4AHAAbwByAHQAXABuACAAIAAgACAAIAAgACAAIABpAG4AaQB0AGkAYQBsACwAIAB7AFwAIgBMAGUAbgBfAEEAXAAiACwAIABcACIATABlAG4AXwBCAFwAIgAsACAAXAAiAEsAbgB1AHQAaABfAG0AcwBcACIALAAgAFwAIgBOAFIAXwBtAHMAXAAiAH0ALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsACwAIABTAEUAUQBVAEUATgBDAEUAKABuAF8AdABlAHMAdABzACkALAAgAEwAQQBNAEIARABBACgAYQBjAGMALAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAEkATgBEAEUAWAAoAHQAZQBzAHQAXwBjAGEAcwBlAHMALAAgAGkALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAASQBOAEQARQBYACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBrAGkAcAAgAEQAaQB2AGkAcwBvAHIAIAA+ACAARABpAHYAaQBkAGUAbgBkABQgaQB0ACcAcwAgAG4AZQB2AGUAcgAgAGEAbgAgAGkAbgB0AGUAZwBlAHIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbABlAG4AXwBiACAAPgAgAGwAZQBuAF8AYQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAYwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARwBlAG4AZQByAGEAdABlACAAZQB4AGEAYwB0AC0AbABlAG4AZwB0AGgAIAB0AGUAcwB0ACAAcwB0AHIAaQBuAGcAcwAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AHIAXwBhACwAIABSAEUAUABUACgAXAAiADkAXAAiACwAIABsAGUAbgBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAcgBfAGIALAAgAEkARgAoAGwAZQBuAF8AYgAgAD0AIAAxACwAIABcACIANwBcACIALAAgAFwAIgA3AFwAIgAgACYAIABSAEUAUABUACgAXAAiADMAXAAiACwAIABsAGUAbgBfAGIAIAAtACAAMQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeABlAGMAdQB0AGUAIABiAGUAbgBjAGgAbQBhAHIAawBzACAAcwB0AHIAaQBjAHQAbAB5ACAAbwBuAGUAIABhAGYAdABlAHIAIAB0AGgAZQAgAG8AdABoAGUAcgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABpAG0AZQBfAGsALAAgAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACgAcwB0AHIAXwBhACwAIABzAHQAcgBfAGIALAAgAFwAIgBLAE4AVQBUAEgAXAAiACwAIABpAHQAZQByAHMALAAgAHIAZQBwAGUAYQB0AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGkAbQBlAF8AbgByACwAIABEAGkAdgBpAHMAaQBvAG4AQQBsAGcAbwByAGkAdABoAG0AcwAoAHMAdAByAF8AYQAsACAAcwB0AHIAXwBiACwAIABcACIATgBSAFwAIgAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAcABwAGUAbgBkACAAdABoAGUAIAByAGUAcwB1AGwAdABzAC4AIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAGEAbABsAG8AYwBhAHQAaQBvAG4AIABkAGUAbABhAHkAIABvAGMAYwB1AHIAcwAgAGgAZQByAGUALAAgAHMAYQBmAGUAbAB5ACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAdABpAG0AZQBkACAAdwBpAG4AZABvAHcALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABhAGMAYwAsACAASABTAFQAQQBDAEsAKABsAGUAbgBfAGEALAAgAGwAZQBuAF8AYgAsACAAdABpAG0AZQBfAGsALAAgAHQAaQBtAGUAXwBuAHIAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgADIALQBjAG8AbAB1AG0AbgAgAGEAcgByAGEAeQAgAG8AZgAgAGUAdgBlAHIAeQAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgAgAG8AZgAgAGwAZQBuAGcAdABoAHMAXABuAEQAaQB2AGkAcwBpAG8AbgBCAGUAbgBjAGgAbQBhAHIAawBDAGEAcwBlAHMAIAA9ACAATABBAE0AQgBEAEEAKABzAHQAYQByAHQAXwBsAGUAbgAsACAAbQBhAHgAXwBsAGUAbgAsACAAcwB0AGUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQAsACAAUwBFAFEAVQBFAE4AQwBFACgAKABtAGEAeABfAGwAZQBuACAALQAgAHMAdABhAHIAdABfAGwAZQBuACkAIAAvACAAcwB0AGUAcAAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBsAGUAbgAsACAAcwB0AGUAcAApACwAXABuACAAIAAgACAAIAAgACAAIABuACwAIABSAE8AVwBTACgAcwBlAHEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAcgB0AGUAcwBpAGEAbgAgAEoAbwBpAG4AXABuACAAIAAgACAAIAAgACAAIABjAG8AbABfAGEALAAgAFQATwBDAE8ATAAoAEkARgAoAFMARQBRAFUARQBOAEMARQAoADEALAAgAG4AKQAsACAAcwBlAHEAKQApACwAXABuACAAIAAgACAAIAAgACAAIABjAG8AbABfAGIALAAgAFQATwBDAE8ATAAoAEkARgAoAFMARQBRAFUARQBOAEMARQAoAG4ALAAgADEAKQAsACAAVABPAFIATwBXACgAcwBlAHEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABjAG8AbABfAGEALAAgAGMAbwBsAF8AYgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgAEMAYQByAHQAZQBzAGkAYQBuACAAZwByAGkAZAAgAGYAcgBvAG0AIAB0AHcAbwAgAGkAbgBkAGUAcABlAG4AZABlAG4AdAAgAHMAZQBxAHUAZQBuAGMAZQBzAFwAbgBBAHMAeQBtAG0AZQB0AHIAaQBjAEEAQgBHAHIAaQBkACAAPQAgAEwAQQBNAEIARABBACgAcwB0AGEAcgB0AF8AYQAsACAAbQBhAHgAXwBhACwAIABzAHQAZQBwAF8AYQAsACAAcwB0AGEAcgB0AF8AYgAsACAAbQBhAHgAXwBiACwAIABzAHQAZQBwAF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGEALAAgAFMARQBRAFUARQBOAEMARQAoACgAbQBhAHgAXwBhACAALQAgAHMAdABhAHIAdABfAGEAKQAgAC8AIABzAHQAZQBwAF8AYQAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBhACwAIABzAHQAZQBwAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGIALAAgAFMARQBRAFUARQBOAEMARQAoACgAbQBhAHgAXwBiACAALQAgAHMAdABhAHIAdABfAGIAKQAgAC8AIABzAHQAZQBwAF8AYgAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBiACwAIABzAHQAZQBwAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwBhACwAIABSAE8AVwBTACgAcwBlAHEAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwBiACwAIABSAE8AVwBTACgAcwBlAHEAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAATwByAHQAaABvAGcAbwBuAGEAbAAgAGIAcgBvAGEAZABjAGEAcwB0ACAAdQBzAGkAbgBnACAAaQBuAGQAZQBwAGUAbgBkAGUAbgB0ACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIAAgACAAIAAgAGMAbwBsAF8AYQAsACAAVABPAEMATwBMACgASQBGACgAUwBFAFEAVQBFAE4AQwBFACgAMQAsACAAbgBfAGIAKQAsACAAcwBlAHEAXwBhACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBvAGwAXwBiACwAIABUAE8AQwBPAEwAKABJAEYAKABTAEUAUQBVAEUATgBDAEUAKABuAF8AYQApACwAIABUAE8AUgBPAFcAKABzAGUAcQBfAGIAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABjAG8AbABfAGEALAAgAGMAbwBsAF8AYgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBjAG8AcgBlAF8AQgBpAGcASQBuAHQAIgAsACIAdABlAHgAdAAiADoAIgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4ALwAvACAAQgBpAGcAIABJAG4AdABlAGcAZQByACAAQQByAGkAdABoAG0AZQB0AGkAYwAgAEwAaQBiAHIAYQByAHkAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQAIABNAG8AZAB1AGwAZQAgACAAIAAgACAAIAAgACAALwAvAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIABQAHIAaQB2AGEAdABlACAAQQBQAEkAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwBcAG4ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8AXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEMAbwBtAHAAdQB0AGUAcwAgAHQAaABlACAAbQBhAHgAaQBtAHUAbQAgAHMAYQBmAGUAIABiAGEAcwBlAC0AMQAwACAAbABpAG0AYgAgAHMAaQB6AGUAIAAoAGsAKQAgAHQAbwAgAGEAdgBvAGkAZAAgAEkARQBFAEUALQA3ADUANAAgAHAAcgBlAGMAaQBzAGkAbwBuACAAbABvAHMAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG8AcABlAHIAYQB0AGkAbwBuADoAIABcACIAQQBEAEQAXAAiACwAIABcACIATQBVAEwAXAAiACwAIABvAHIAIABcACIARABJAFYAXAAiAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAWwBtAGEAeABfAGkAdABlAG0AcwBdACAAQQBEAEQAOgAgAG4AdQBtAGIAZQByACAAbwBmACAAbwBwAGUAcgBhAG4AZABzAC4AIABNAFUATAA6ACAAcwBoAG8AcgB0AGUAcwB0ACAAcwB0AHIAaQBuAGcAIABkAGkAZwBpAHQAcwAgAGMAbwB1AG4AdAAuAFwAbgAgACoALwBcAG4AUwBhAGYAZQBLACAAPQAgAEwAQQBNAEIARABBACgAbwBwAGUAcgBhAHQAaQBvAG4ALAAgAFsAbQBhAHgAXwBpAHQAZQBtAHMAXQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABpAHQAZQBtAHMALAAgAEkARgAoAE8AUgAoAG0AYQB4AF8AaQB0AGUAbQBzACAAPQAgAFwAIgBcACIALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAbQBhAHgAXwBpAHQAZQBtAHMAKQApACwAIAAyACwAIABNAEEAWAAoADIALAAgAG0AYQB4AF8AaQB0AGUAbQBzACkAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVwBJAFQAQwBIACgAbwBwAGUAcgBhAHQAaQBvAG4ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEARABEAFwAIgAsACAAMQA1ACAALQAgAEwARQBOACgAaQB0AGUAbQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFUATABcACIALAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARQB2AGEAbAB1AGEAdABlACAAcABvAHMAcwBpAGIAbABlACAAawAgAHYAYQBsAHUAZQBzACAAZAB5AG4AYQBtAGkAYwBhAGwAbAB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAZQBzAHQAXwBrACwAIAB7ADcAOwAgADYAOwAgADUAOwAgADQAOwAgADMAOwAgADIAOwAgADEAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AbwB2AGUAcgBsAGEAcAAsACAAUgBPAFUATgBEAFUAUAAoAGkAdABlAG0AcwAgAC8AIAB0AGUAcwB0AF8AawAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIAB0AGgAZQAgAGEAYgBzAG8AbAB1AHQAZQAgAHAAZQBhAGsAIAB2AGEAbAB1AGUAIABpAG4AcwBpAGQAZQAgAHQAaABlACAAZQBuAGcAaQBuAGUAIAAoAEMAbwBuAHYAbwBsAHUAdABpAG8AbgAgACsAIABDAGEAcgByAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB1AG4AYwBhAHIAcgBpAGUAZABfAG0AYQB4ACwAIABtAGEAeABfAG8AdgBlAHIAbABhAHAAIAAqACAAKAAxADAAXgB0AGUAcwB0AF8AawAgAC0AIAAxACkAXgAyACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAHgAXwBjAGEAcgByAHkALAAgAEkATgBUACgAdQBuAGMAYQByAHIAaQBlAGQAXwBtAGEAeAAgAC8AIAAxADAAXgB0AGUAcwB0AF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABlAGEAawBfAHYAYQBsACwAIAB1AG4AYwBhAHIAcgBpAGUAZABfAG0AYQB4ACAAKwAgAG0AYQB4AF8AYwBhAHIAcgB5ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHQAdQByAG4AIAB0AGgAZQAgAG0AYQB4ACAAawAgADwAPQAgAEUAeABjAGUAbAAnAHMAIAAxADUALQBkAGkAZwBpAHQAIABjAGUAaQBsAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgARgBJAEwAVABFAFIAKAB0AGUAcwB0AF8AawAsACAAcABlAGEAawBfAHYAYQBsACAAPAA9ACAAKAAxADAAXgAxADUAIAAtACAAMQApACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQASQBWAFwAIgAsACAANwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAE4AQQBNAEUAPwBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AaQBmAGkAZQBkACAAUwBwAGwAaQB0AHQAZQByAC4AIABTAHAAbABpAHQAcwAgAGIAbwB0AGgAIABzAGMAYQBsAGEAcgBzACAAYQBuAGQAIABhAHIAcgBhAHkAcwAgAGkAbgB0AG8AIABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuACAAbABpAG0AYgBzAC4AXABuACAAKgAgAFUAcwBlAHMAIABNAEEAWAAoACkAIAB0AG8AIABnAHUAYQByAGEAbgB0AGUAZQAgAHMAYwBhAGwAYQByACAAaQBuAHAAdQB0AHMAIAB0AG8AIAB0AGgAZQAgAFMARQBRAFUARQBOAEMARQAgAGUAbgBnAGkAbgBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABzACAAVABoAGUAIABzAHQAcgBpAG4AZwAgAG8AcgAgAGEAcgByAGEAeQAgAG8AZgAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFMAcABsAGkAdAAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAcwAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABiAGkAZwBfAGkAbgB0AF8AcgBvAHcALAAgAFQATwBSAE8AVwAoAGIAaQBnAF8AaQBuAHQAcwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBnAHQAaABzACwAIABMAEUATgAoAGIAaQBnAF8AaQBuAHQAXwByAG8AdwApACwAXABuACAAIAAgACAAIAAgACAAIABtAGEAeABfAGwAZQBuACwAIABNAEEAWAAoAGwAZQBuAGcAdABoAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBsAGUAbgAsACAAUgBPAFUATgBEAFUAUAAoAG0AYQB4AF8AbABlAG4AIAAvACAAawAsACAAMAApACAAKgAgAGsALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAZABlAGQALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAHAAYQBkAF8AbABlAG4AIAAtACAAbABlAG4AZwB0AGgAcwApACAAJgAgAGIAaQBnAF8AaQBuAHQAXwByAG8AdwAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALAAgAFMARQBRAFUARQBOAEMARQAoAHAAYQBkAF8AbABlAG4AIAAvACAAawAsACAAMQAsACAAcABhAGQAXwBsAGUAbgAgAC0AIABrACAAKwAgADEALAAgAC0AawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC0ALQBNAEkARAAoAHAAYQBkAGQAZQBkACwAIABzAHQAYQByAHQAcwAsACAAawApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAQwBvAG4AYwBhAHQAZQBuAGEAdABlAHMAIABhAG4AIABhAHIAcgBhAHkAIABvAGYAIABuAHUAbQBlAHIAaQBjACAAbABpAG0AYgBzACAAaQBuAHQAbwAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnACwAIAB6AGUAcgBvAC0AcABhAGQAZABpAG4AZwAgAGEAbABsACAAYgB1AHQAIAB0AGgAZQAgAGYAaQByAHMAdAAgAGwAaQBtAGIALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAIABUAGgAZQAgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAG4AdQBtAGUAcgBpAGMAIABsAGkAbQBiAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABsAGkAbQBiACAAcwBpAHoAZQAgAHUAcwBlAGQAIABkAHUAcgBpAG4AZwAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAuAFwAbgAgACoALwBcAG4ATQBlAHIAZwBlACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AdQBtAF8AbABpAG0AYgBzACwAIABSAE8AVwBTACgAbABpAG0AYgBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQB2AF8AbABpAG0AYgBzACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAbABpAG0AYgBzACwAIABTAEUAUQBVAEUATgBDAEUAKABuAHUAbQBfAGwAaQBtAGIAcwAsACAAMQAsACAAbgB1AG0AXwBsAGkAbQBiAHMALAAgAC0AMQApACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AdQBtAF8AbABpAG0AYgBzACAAPQAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHYAXwBsAGkAbQBiAHMAIAAmACAAXAAiAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATgBDAEEAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAcgBlAHYAXwBsAGkAbQBiAHMALAAgADEAKQAgACYAIABcACIAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEUAWABUACgARABSAE8AUAAoAHIAZQB2AF8AbABpAG0AYgBzACwAIAAxACkALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAGsAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAUgBlAHMAbwBsAHYAZQBzACAAYwBhAHIAcgBpAGUAcwAgAHIAaQBnAGgAdAAtAHQAbwAtAGwAZQBmAHQAIABhAGMAcgBvAHMAcwAgAGEAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkAIABvAGYAIABiAGEAcwBlAC0AMQAwAF4AawAgAGwAaQBtAGIAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwAgAFQAaABlACAAYQByAHIAYQB5ACAAbwBmACAAbgB1AG0AZQByAGkAYwAgAGwAaQBtAGIAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGwAaQBtAGIAIABzAGkAegBlAC4AXABuACAAKgAvAFwAbgBDAGEAcgByAHkAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwApACwAXABuACAAIAAgACAAIAAgACAAIABiAGEAcwBlACwAIAAxADAAXgBrACwAXABuACAAIAAgACAAIAAgACAAIABzAGMAYQBuAG4AZQBkACwAIABTAEMAQQBOACgAMAAsACAAbABpAG0AYgBzACwAIABMAEEATQBCAEQAQQAoAGEAYwBjACwAIAB2AGEAbAAsACAAdgBhAGwAIAArACAASQBOAFQAKABhAGMAYwAgAC8AIABiAGEAcwBlACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAByAGUAbQBhAGkAbgBkAGUAcgBzACwAIABNAE8ARAAoAHMAYwBhAG4AbgBlAGQALAAgAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AYwBhAHIAcgB5ACwAIABJAE4AVAAoAEkATgBEAEUAWAAoAHMAYwBhAG4AbgBlAGQALAAgAG4ALAAgADEAKQAgAC8AIABiAGEAcwBlACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABmAGkAbgBhAGwAXwBjAGEAcgByAHkAIAA+ACAAMAAsACAAVgBTAFQAQQBDAEsAKAByAGUAbQBhAGkAbgBkAGUAcgBzACwAIABmAGkAbgBhAGwAXwBjAGEAcgByAHkAKQAsACAAcgBlAG0AYQBpAG4AZABlAHIAcwApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAC0ALQAtACAAVQBuAHMAaQBnAG4AZQBkACAASwBlAHIAbgBlAGwAcwAgAC0ALQAtACAAXABcAFwAXABcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAVQBuAHMAaQBnAG4AZQBkACAAYwBvAG0AcABhAHIAaQBzAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAMQAgACgAYQAgAD4AIABiACkALAAgAC0AMQAgACgAYQAgADwAIABiACkALAAgAG8AcgAgADAAIAAoAGEAIAA9ACAAYgApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAIABUAGgAZQAgAHMAZQBjAG8AbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoALwBcAG4AVQBDAG8AbQBwAGEAcgBlACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAeABfAHIAbwB3AHMALAAgAE0AQQBYACgAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEAKQAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAZABfAGEALAAgAEUAWABQAEEATgBEACgAbABpAG0AYgBzAF8AYQAsACAAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAYQBkAF8AYgAsACAARQBYAFAAQQBOAEQAKABsAGkAbQBiAHMAXwBiACwAIABtAGEAeABfAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABkAGkAZgBmACwAIABwAGEAZABfAGEAIAAtACAAcABhAGQAXwBiACwAXABuACAAIAAgACAAIAAgACAAIABtAHMAZABfAGkAZAB4ACwAIABYAE0AQQBUAEMASAAoAFQAUgBVAEUALAAgAGQAaQBmAGYAIAA8AD4AIAAwACwAIAAwACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATgBBACgAbQBzAGQAXwBpAGQAeAApACwAIAAwACwAIABTAEkARwBOACgASQBOAEQARQBYACgAZABpAGYAZgAsACAAbQBzAGQAXwBpAGQAeAAsACAAMQApACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAGEAZABkAGkAdABpAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFUAQQBkAGQAIAA9ACAATABBAE0AQgBEAEEAKABhACwAIABiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AcgBvAHcAcwAsACAATQBBAFgAKABSAE8AVwBTACgAYQApACwAIABSAE8AVwBTACgAYgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAYQBkAF8AYQAsACAARQBYAFAAQQBOAEQAKABhACwAIABtAGEAeABfAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBiACwAIABFAFgAUABBAE4ARAAoAGIALAAgAG0AYQB4AF8AcgBvAHcAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHAAYQBkAF8AYQAgACsAIABwAGEAZABfAGIALAAgAGsAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAHMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABBAHMAcwB1AG0AZQBzACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAgAEEAIAA+AD0AIABCAC4AIABSAGUAcwBvAGwAdgBlAHMAIABiAG8AcgByAG8AdwBzACAAdABvAHAALQB0AG8ALQBiAG8AdAB0AG8AbQAgAGEAbgBkACAAdAByAGkAbQBzACAAdAByAGEAaQBsAGkAbgBnACAAegBlAHIAbwBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAbQBpAG4AdQBlAG4AZAAgAGwAaQBtAGIAIABhAHIAcgBhAHkAIAAoAG0AdQBzAHQAIABiAGUAIAA+AD0AIABsAGkAbQBiAHMAXwBiACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABzAHUAYgB0AHIAYQBoAGUAbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AVQBTAHUAYgAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwByAG8AdwBzACwAIABNAEEAWAAoAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBhACwAIABFAFgAUABBAE4ARAAoAGwAaQBtAGIAcwBfAGEALAAgAG0AYQB4AF8AcgBvAHcAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAZABfAGIALAAgAEUAWABQAEEATgBEACgAbABpAG0AYgBzAF8AYgAsACAAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAZABpAGYAZgAsACAAcABhAGQAXwBhACAALQAgAHAAYQBkAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBlAHMAbwBsAHYAZQBkACwAIABDAGEAcgByAHkAKABkAGkAZgBmACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAbQBzAGQAXwBpAGQAeAAsACAAWABNAEEAVABDAEgAKABUAFIAVQBFACwAIAByAGUAcwBvAGwAdgBlAGQAIAA8AD4AIAAwACwAIAAwACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATgBBACgAbQBzAGQAXwBpAGQAeAApACwAIAB7ADAAfQAsACAAVABBAEsARQAoAHIAZQBzAG8AbAB2AGUAZAAsACAAbQBzAGQAXwBpAGQAeAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABWAGUAYwB0AG8AcgBpAHoAZQBkACAAbQBhAHQAcgBpAHgAIABzAHUAbQAgAG8AZgAgAHUAbgBzAGkAZwBuAGUAZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHUAYgBpAGcAXwBpAG4AdAAgAEgAbwByAGkAegBvAG4AdABhAGwAIABhAHIAcgBhAHkAIAAoADEAeABOACkAIABvAGYAIABuAG8AcgBtAGEAbABpAHoAZQBkACAAbQBhAGcAbgBpAHQAdQBkAGUAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAdQBuAGkAZgBpAGUAZAAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AVQBNAGEAdAByAGkAeABTAHUAbQAgAD0AIABMAEEATQBCAEQAQQAoAHUAYgBpAGcAXwBpAG4AdABzACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAGcAcgBpAGQALAAgAFMAcABsAGkAdAAoAHUAYgBpAGcAXwBpAG4AdABzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAYQB3AF8AbABpAG0AYgBzACwAIABCAFkAUgBPAFcAKABnAHIAaQBkACwAIABTAFUATQApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHIAYQB3AF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABSAG8AdQB0AGUAcwAgAGEAZABkAGkAdABpAG8AbgAvAHMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAGIAYQBzAGUAZAAgAG8AbgAgAHMAaQBnAG4AcwAgAGEAbgBkACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAuAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAYQAgAHQAdQBwAGwAZQAgAGEAcgByAGEAeQA6ACAAVgBTAFQAQQBDAEsAKABsAGkAbQBiAHMALAAgAGYAaQBuAGEAbABfAHMAaQBnAG4AKQAgAHcAaABlAHIAZQAgAHQAaABlACAAZgBpAG4AYQBsACAAcgBvAHcAIABpAHMAIAB0AGgAZQAgAHMAYwBhAGwAYQByACAAcwBpAGcAbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAcwBlAGMAbwBuAGQAIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHMAaQBnAG4AXwBhACAAVABoAGUAIABzAGkAZwBuACAAbwBmACAAdABoAGUAIABmAGkAcgBzAHQAIABhAHIAcgBhAHkAIAAoADEALAAgAC0AMQAsACAAMAApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAcwBpAGcAbgBfAGIAIABUAGgAZQAgAHMAaQBnAG4AIABvAGYAIAB0AGgAZQAgAHMAZQBjAG8AbgBkACAAYQByAHIAYQB5ACAAKAAxACwAIAAtADEALAAgADAAKQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AQQBkAGQAUwB1AGIAUgBvAHUAdABlAHIAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABzAGkAZwBuAF8AYQAsACAAcwBpAGcAbgBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AcwBhAG0AZQBfAHMAaQBnAG4ALAAgAHMAaQBnAG4AXwBhACAAPQAgAHMAaQBnAG4AXwBiACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGkAcwBfAHMAYQBtAGUAXwBzAGkAZwBuACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAZABkAGkAdABpAG8AbgA6ACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAgAGMAbwBtAGIAaQBuAGUALAAgAHMAaQBnAG4AIAByAGUAbQBhAGkAbgBzACAAdABoAGUAIABzAGEAbQBlAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVQBBAGQAZAAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsACAAcwBpAGcAbgBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwB1AGIAdAByAGEAYwB0AGkAbwBuADoAIABlAHYAYQBsAHUAYQB0AGUAIABtAGEAZwBuAGkAdAB1AGQAZQBzACAAdABvACAAcwBhAHQAaQBzAGYAeQAgAFUAUwB1AGIAIAAoAEEAIAA+AD0AIABCACkAIABwAHIAZQBjAG8AbgBkAGkAdABpAG8AbgAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcAAsACAAVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFQAbwB0AGEAbAAgAGMAYQBuAGMAZQBsAGwAYQB0AGkAbwBuADoAIAByAGUAdAB1AHIAbgAgAHsAMAB9ACAAbABpAG0AYgAgAGEAbgBkACAAMAAgAHMAaQBnAG4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAMAA7ADAAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAGEAZwBfAGMAbwBtAHAAIAA+ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABBACAAaQBzACAAbABhAHIAZwBlAHIAOgAgAHMAaQBnAG4AIABiAGUAbABvAG4AZwBzACAAdABvACAAQQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFUAUwB1AGIAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALAAgAHMAaQBnAG4AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEIAIABpAHMAIABsAGEAcgBnAGUAcgA6ACAAcgBvAHUAdABlACAAQgAgAGYAaQByAHMAdAAsACAAcwBpAGcAbgAgAGIAZQBsAG8AbgBnAHMAIAB0AG8AIABCAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVQBTAHUAYgAoAGwAaQBtAGIAcwBfAGIALAAgAGwAaQBtAGIAcwBfAGEALAAgAGsAKQAsACAAcwBpAGcAbgBfAGIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AcwBpAGcAbgBlAGQAIABtAHUAbAB0AGkAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIAB0AHcAbwAgAEwAaQB0AHQAbABlAC0ARQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5AHMALgBcAG4AIAAqACAAVQB0AGkAbABpAHoAZQBzACAAYQAgADEARAAgAEQAaQBzAGMAcgBlAHQAZQAgAEMAbwBuAHYAbwBsAHUAdABpAG8AbgAgACgAQwBhAHUAYwBoAHkAIABQAHIAbwBkAHUAYwB0ACkAIABhAHIAcgBhAHkALQBzAGwAaQBjAGkAbgBnACAAcwB0AHIAYQB0AGUAZwB5AC4AXABuACAAKgAgAFoAZQByAG8AIABkAHkAbgBhAG0AaQBjACAAbQBlAG0AbwByAHkAIAByAGUAYQBsAGwAbwBjAGEAdABpAG8AbgAuACAAJABPACgATgArAE0AKQAkACAAbQBlAG0AbwByAHkAIABmAG8AbwB0AHAAcgBpAG4AdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAG0AdQBsAHQAaQBwAGwAaQBjAGEAbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAIABUAGgAZQAgAG0AdQBsAHQAaQBwAGwAaQBlAHIAIABsAGkAbQBiACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBVAE0AdQBsACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwByAG8AdwBzACwAIABsAGUAbgBfAGEAIAArACAAbABlAG4AXwBiACAALQAgADEALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAATABvAG8AcAAgAHAAdQByAGUAbAB5ACAAbwB2AGUAcgAgAHQAaABlACAAbABlAG4AZwB0AGgAIABvAGYAIAB0AGgAZQAgAGYAaQBuAGEAbAAgAG8AdQB0AHAAdQB0ACAAYQByAHIAYQB5AFwAbgAgACAAIAAgACAAIAAgACAAcgBhAHcAXwBsAGkAbQBiAHMALAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIABMAEEATQBCAEQAQQAoAHIALAAgAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAbABjAHUAbABhAHQAZQAgAHQAaABlACAAdgBhAGwAaQBkACAAbwB2AGUAcgBsAGEAcABwAGkAbgBnACAAdwBpAG4AZABvAHcAIABvAGYAIABpAG4AZABpAGMAZQBzACAAZgBvAHIAIAB0AGgAaQBzACAAbQBhAGcAbgBpAHQAdQBkAGUAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AF8AaQAsACAATQBBAFgAKAAxACwAIAByACAALQAgAGwAZQBuAF8AYgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAG4AZABfAGkALAAgAE0ASQBOACgAcgAsACAAbABlAG4AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AdQBuAHQALAAgAGUAbgBkAF8AaQAgAC0AIABzAHQAYQByAHQAXwBpACAAKwAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGUAcQB1AGUAbgBjAGUAIABpACAAYwBvAHUAbgB0AHMAIABVAFAALgAgAFMAZQBxAHUAZQBuAGMAZQAgAGoAIABjAG8AdQBuAHQAcwAgAEQATwBXAE4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGkALAAgAFMARQBRAFUARQBOAEMARQAoAGMAbwB1AG4AdAAsACAAMQAsACAAcwB0AGEAcgB0AF8AaQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBlAHEAXwBqACwAIABTAEUAUQBVAEUATgBDAEUAKABjAG8AdQBuAHQALAAgADEALAAgAHIAIAAtACAAcwB0AGEAcgB0AF8AaQAgACsAIAAxACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAbABpAGMAZQAgAHQAaABlACAAZQB4AGEAYwB0ACAAaQBuAHQAZQByAHMAZQBjAHQAaQBuAGcAIABsAGkAbQBiAHMALAAgAG0AdQBsAHQAaQBwAGwAeQAsACAAYQBuAGQAIABzAHUAbQAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUATQAoAEkATgBEAEUAWAAoAGwAaQBtAGIAcwBfAGEALAAgAHMAZQBxAF8AaQAsACAAMQApACAAKgAgAEkATgBEAEUAWAAoAGwAaQBtAGIAcwBfAGIALAAgAHMAZQBxAF8AagAsACAAMQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHMAbwBsAHYAZQAgAGEAbABsACAAYwBhAHIAcgBpAGUAcwAgAGIAbwB0AHQAbwBtAC0AdABvAC0AdABvAHAAIABlAHgAYQBjAHQAbAB5ACAAbwBuAGMAZQBcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHIAYQB3AF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABCAGkAbgBhAHIAeQAgAHMAZQBhAHIAYwBoACAAdABvACAAZgBpAG4AZAAgAHQAaABlACAAaABpAGcAaABlAHMAdAAgAHMAYwBhAGwAYQByACAAcQB1AG8AdABpAGUAbgB0ACAAbABpAG0AYgAgAHEAIAAoADAAIAA8AD0AIABxACAAPAAgADEAMABeAGsAKQBcAG4AoAAqACAAcwB1AGMAaAAgAHQAaABhAHQAIABCACAAKgAgAHEAIAA8AD0AIABhAGMAYwAuACAARQBsAGkAbQBpAG4AYQB0AGUAcwAgAHQAaABlACAAbgBlAGUAZAAgAGYAbwByACAASwBuAHUAdABoACAARAAgAGYAbABvAGEAdAAtAGUAcwB0AGkAbQBhAHQAaQBvAG4ALgBcAG4AoAAqACAAQABwAGEAcgBhAG0AIABhAGMAYwAgAFQAaABlACAAYwB1AHIAcgBlAG4AdAAgAHIAZQBtAGEAaQBuAGQAZQByACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAuAFwAbgCgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgCgACoALwBcAG4ARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAgAD0AIABMAEEATQBCAEQAQQAoAGEAYwBjACwAIABiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAYQBsAGMAdQBsAGEAdABlACAAcgBlAHEAdQBpAHIAZQBkACAAYgBpAHQAcwAgAGQAeQBuAGEAbQBpAGMAYQBsAGwAeQAuACAARgBvAHIAIABtAGEAeAAgAGsAPQA3ACwAIAB0AGgAaQBzACAAZQB2AGEAbAB1AGEAdABlAHMAIAB0AG8AIAAyADQAIABiAGkAdABzAC4AXABuACAAIAAgACAAIAAgACAAIABiAGkAdABzACwAIABDAEUASQBMAEkATgBHAC4ATQBBAFQASAAoAEwATwBHACgAMQAwAF4AawAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAbwB3AGUAcgBzACwAIAAyACAAXgAgAFMARQBRAFUARQBOAEMARQAoAGIAaQB0AHMALAAgADEALAAgAGIAaQB0AHMAIAAtACAAMQAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAUgBFAEQAVQBDAEUAKAAwACwAIABwAG8AdwBlAHIAcwAsACAATABBAE0AQgBEAEEAKABjAHUAcgByAF8AcQAsACAAcABvAHcAZQByACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABlAHMAdABfAHEALAAgAGMAdQByAHIAXwBxACAAKwAgAHAAbwB3AGUAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAawBpAHAAIABpAGYAIAB0AGUAcwB0AF8AcQAgAGUAeABjAGUAZQBkAHMAIAB0AGgAZQAgAGwAaQBtAGIAIABiAGEAcwBlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHQAZQBzAHQAXwBxACAAPgA9ACAAMQAwAF4AawAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATQB1AGwAdABpAHAAbAB5ACAAQgAgAGIAeQAgAHMAYwBhAGwAYQByACAAdABlAHMAdABfAHEAIABhAG4AZAAgAHIAZQBzAG8AbAB2AGUAIABjAGEAcgByAGkAZQBzACAAbgBhAHQAaQB2AGUAbAB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGUAcwB0AF8AcAByAG8AZAAsACAAQwBhAHIAcgB5ACgAYgAgACoAIAB0AGUAcwB0AF8AcQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAFUAQwBvAG0AcABhAHIAZQAoAGEAYwBjACwAIAB0AGUAcwB0AF8AcAByAG8AZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABjAG8AbQBwACAAPgA9ACAAMAAsACAAdABlAHMAdABfAHEALAAgAGMAdQByAHIAXwBxACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABCAGEAcwBlAGMAYQBzAGUAIABEAGkAdgBpAHMAaQBvAG4AIAB2AGkAYQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABzAGgAaQBmAHQALQBhAG4AZAAtAHMAdQBiAHQAcgBhAGMAdAAuAFwAbgCgACoAIABSAGUAdAB1AHIAbgBzACAAYQAgAHAAYQBjAGsAZQBkACAAMQBEACAAYQByAHIAYQB5ADoAIABWAFMAVABBAEMASwAoAEwAZQBuAGcAdABoAF8AUgAsACAAUgBfAGwAaQBtAGIAcwAsACAAUQBfAGwAaQBtAGIAcwApAC4AXABuAKAAKgAgAEUAbABpAG0AaQBuAGEAdABlAHMAIAAyAEQAIABhAHIAcgBhAHkAIABwAGEAZABkAGkAbgBnACAAdABvACAAcwB0AHIAaQBjAHQAbAB5ACAAcAByAGUAcwBlAHIAdgBlACAAbQBlAG0AbwByAHkAIABlAGYAZgBpAGMAaQBlAG4AYwB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAgACgAYQBzAHMAdQBtAGUAZAAgAG4AbwBuAC0AegBlAHIAbwApAC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuAKAAKgAvAFwAbgBLAG4AdQB0AGgARABpAHYAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcAAsACAAVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAIAByAG8AdQB0AGkAbgBnACAAdwBpAHQAaAAgAHQAaABlACAAbgBlAHcAIABwAGEAYwBrAGUAZAAgAG0AZQBtAG8AcgB5ACAAYwBvAG4AdAByAGEAYwB0AFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbABpAG0AYgBzAF8AYQApACwAIABsAGkAbQBiAHMAXwBhACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADEALAAgADAALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEkAdABlAHIAYQB0AGUAIABvAHYAZQByACAAQQAgAGYAcgBvAG0AIABNAFMAQgAgACgAdABvAHAAKQAgAHQAbwAgAEwAUwBCACAAKABiAG8AdAB0AG8AbQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHYAZQByAHMAZQBkAF8AYQAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEALAAgAFMARQBRAFUARQBOAEMARQAoAGwAZQBuAF8AYQAsACAAMQAsACAAbABlAG4AXwBhACwAIAAtADEAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAdABhAHQAZQAgAHMAZQBwAGEAcgBhAHQAbwByADoAIABWAFMAVABBAEMASwAoAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABxAHUAbwB0AGkAZQBuAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAbgBpAHQAaQBhAGwAXwBzAHQAYQB0AGUALAAgAFYAUwBUAEEAQwBLACgAMQAsACAAMAAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsAF8AcwB0AGEAdABlACwAIAByAGUAdgBlAHIAcwBlAGQAXwBhACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAdgBhAGwALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcwB0AGEAdABlACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHEAdQBvAHQAaQBlAG4AdAAsACAARABSAE8AUAAoAHMAdABhAHQAZQAsACAAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGgAaQBmAHQAIABhAGMAYwAgAHUAcAAgAGIAeQAgADEAIABsAGkAbQBiACAAKABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuADoAIABpAG4AcwBlAHIAdAAgAGEAdAAgAGkAbgBkAGUAeAAgADEAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAHgAdABlAG4AZABlAGQAXwByAGUAbQBhAGkAbgBkAGUAcgAsACAASQBGACgAQQBOAEQAKABSAE8AVwBTACgAcgBlAG0AYQBpAG4AZABlAHIAKQAgAD0AIAAxACwAIABJAE4ARABFAFgAKAByAGUAbQBhAGkAbgBkAGUAcgAsACAAMQAsACAAMQApACAAPQAgADAAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB2AGEAbAAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAHYAYQBsACwAIAByAGUAbQBhAGkAbgBkAGUAcgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgAsACAARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAoAGUAeAB0AGUAbgBkAGUAZABfAHIAZQBtAGEAaQBuAGQAZQByACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAHIAbwBkACwAIABDAGEAcgByAHkAKABsAGkAbQBiAHMAXwBiACAAKgAgAG4AZQB4AHQAXwBxAHUAbwB0AGkAZQBuAHQAXwBsAGkAbQBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAdwBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABVAFMAdQBiACgAZQB4AHQAZQBuAGQAZQBkAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHAAcgBvAGQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGgAYQBzAF8AcQB1AG8AdABpAGUAbgB0ACwAIABPAFIAKABSAE8AVwBTACgAcQB1AG8AdABpAGUAbgB0ACkAIAA+ACAAMQAsACAASQBOAEQARQBYACgAcQB1AG8AdABpAGUAbgB0ACwAMQAsADEAKQAgAD4AIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQB1AG8AdAAsACAASQBGACgAaABhAHMAXwBxAHUAbwB0AGkAZQBuAHQALAAgAFYAUwBUAEEAQwBLACgAcQB1AG8AdABpAGUAbgB0ACwAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgApACwAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbgBlAHcAXwByAGUAbQBhAGkAbgBkAGUAcgApACwAIABuAGUAdwBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABuAGUAeAB0AF8AcQB1AG8AdAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAEkATgBEAEUAWAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAbQBhAGkAbgBkAGUAcgAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAsACAAMQAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQB2AGUAcgBzAGUAZABfAHEAdQBvAHQAaQBlAG4AdAAsACAARABSAE8AUAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAcQB1AG8AdABfAHIAYQB3ACAAdwBhAHMAIABiAHUAaQBsAHQAIABNAFMAQgAgAHQAbwAgAEwAUwBCACAAKABCAGkAZwAtAEUAbgBkAGkAYQBuACkALgAgAFIAZQB2AGUAcgBzAGUAIAB0AG8AIABpAG4AdABlAHIAbgBhAGwAIABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHEAdQBvAHQAaQBlAG4AdAAsACAAUgBPAFcAUwAoAHIAZQB2AGUAcgBzAGUAZABfAHEAdQBvAHQAaQBlAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABxAHUAbwB0AGkAZQBuAHQALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKAByAGUAdgBlAHIAcwBlAGQAXwBxAHUAbwB0AGkAZQBuAHQALAAgAFMARQBRAFUARQBOAEMARQAoAGwAZQBuAF8AcQB1AG8AdABpAGUAbgB0ACwAIAAxACwAIABsAGUAbgBfAHEAdQBvAHQAaQBlAG4AdAAsACAALQAxACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAHMAdAByAGkAYwB0AGwAeQAgAHAAYQBjAGsAZQBkACAAMQBEACAAYQByAHIAYQB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIAByAGUAbQBhAGkAbgBkAGUAcgAsACAAcQB1AG8AdABpAGUAbgB0ACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABIAHkAYgByAGkAZAAgAEQAaQB2AGkAcwBpAG8AbgAgAFIAbwB1AHQAZQByAC4AXABuAKAAKgAgAEQAaQByAGUAYwB0AHMAIABkAGkAdgBpAHMAaQBvAG4AIAB0AG8AIAB0AGgAZQAgAG8AcAB0AGkAbQBhAGwAIABrAGUAcgBuAGUAbAAgAGIAYQBzAGUAZAAgAG8AbgAgAEQAaQB2AGkAZABlAG4AZAAgAGwAZQBuAGcAdABoAC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAuAFwAbgCgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgCgACoALwBcAG4ARABpAHYAUgBvAHUAdABlAHIAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEQAaQBnAGkAdAAgAGMAbwB1AG4AdABzACAAYQByAGUAIABhAHAAcAByAG8AeABpAG0AYQB0AGUALAAgAGIAdQB0ACAAcwB1AGYAZgBpAGMAaQBlAG4AdABcAG4AIAAgACAAIAAgACAAIAAgAGQAaQBnAGkAdABzAF8AYQAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEAKQAgACoAIABrACwAXABuACAAIAAgACAAIAAgACAAIABkAGkAZwBpAHQAcwBfAGIALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkAIAAqACAAawAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABNAGEAYwBoAGkAbgBlAC0AbABlAGEAcgBuAGUAZAAgAGMAbwBlAGYAZgBpAGMAaQBlAG4AdABzACAAZgByAG8AbQAgAEwAbwBnAGkAcwB0AGkAYwAgAFIAZQBnAHIAZQBzAHMAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIABtACwAIAAwAC4AMQAwADcAOAAyADEAMQA5ADQAMgA3ADEAMgA5ADcALABcAG4AIAAgACAAIAAgACAAIAAgAGMALAAgAC0AMgAyADEALgA5ADAAMgAxADgAOQA0ADYAMgAwADYAOAAsAFwAbgAgACAAIAAgACAAIAAgACAAdABoAHIAZQBzAGgAbwBsAGQALAAgACgAbQAgACoAIABkAGkAZwBpAHQAcwBfAGEAKQAgACsAIABjACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGQAaQBnAGkAdABzAF8AYgAgADwAPQAgAHQAaAByAGUAcwBoAG8AbABkACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEsAbgB1AHQAaABEAGkAdgAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2ACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEcAZQBuAGUAcgBhAHQAZQBzACAAdABoAGUAIABlAHgAYQBjAHQAIAByAGUAYwBpAHAAcgBvAGMAYQBsACAAcwBlAGUAZAAgAGYAbwByACAATgBlAHcAdABvAG4ALQBSAGEAcABoAHMAbwBuACAARABpAHYAaQBzAGkAbwBuACAAdQBzAGkAbgBnACAASwBuAHUAdABoACAAQgBhAHMAZQBjAGEAcwBlAC4AXABuACAAKgAgAEUAeAB0AHIAYQBjAHQAcwAgAHUAcAAgAHQAbwAgAHQAaABlACAAdABvAHAAIAAzACAAbABpAG0AYgBzACAAbwBmACAAQgAgAGEAbgBkACAAYwBhAGwAYwB1AGwAYQB0AGUAcwAgAGYAbABvAG8AcgAoAEIAZQB0AGEAXgAoADIAKgBsAGUAbgApACAALwAgAEIAXwB0AG8AcAApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4AUwBlAGUAZAAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwBiACwAIABSAE8AVwBTACgAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAZQBkAF8AbABlAG4ALAAgAE0ASQBOACgAMwAsACAAbABlAG4AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAHQAbwBwACAAJwBzAGUAZQBkAF8AbABlAG4AJwAgAGwAaQBtAGIAcwAgACgATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgA6ACAAdABhAGsAZQAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAbwB0AHQAbwBtACkAXABuACAAIAAgACAAIAAgACAAIABiAF8AdABvAHAALAAgAFQAQQBLAEUAKABsAGkAbQBiAHMAXwBiACwAIAAtAHMAZQBlAGQAXwBsAGUAbgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAbwBuAHMAdAByAHUAYwB0ACAAQgBlAHQAYQBeACgAMgAgACoAIABzAGUAZQBkAF8AbABlAG4AKQAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAGUALgBnAC4ALAAgAGkAZgAgAHMAZQBlAGQAXwBsAGUAbgAgAD0AIAAxACwAIAB0AGgAZQBuACAAMQAgAGYAbwBsAGwAbwB3AGUAZAAgAGIAeQAgAHQAdwBvACAAegBlAHIAbwAgAGwAaQBtAGIAcwA6ACAAVgBTAFQAQQBDAEsAKAAwACwAIAAwACwAIAAxACkAXABuACAAIAAgACAAIAAgACAAIABiAGUAdABhAF8AMgBtACwAIABWAFMAVABBAEMASwAoAEUAWABQAEEATgBEACgAMAAsACAAMgAgACoAIABzAGUAZQBkAF8AbABlAG4ALAAgACwAIAAwACkALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABLAG4AdQB0AGgAIABEAGkAdgBpAHMAaQBvAG4AIAB5AGkAZQBsAGQAcwAgAGUAeABhAGMAdAAgAGkAbgBpAHQAaQBhAGwAIAByAGUAYwBpAHAAcgBvAGMAYQBsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGMAawBlAGQALAAgAEsAbgB1AHQAaABEAGkAdgAoAGIAZQB0AGEAXwAyAG0ALAAgAGIAXwB0AG8AcAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABRAHUAbwB0AGkAZQBuAHQAIABhAHIAcgBhAHkAIABmAHIAbwBtACAAdABoAGUAIABwAGEAYwBrAGUAZAAgAFYAUwBUAEEAQwBLAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwByACwAIABJAE4ARABFAFgAKABwAGEAYwBrAGUAZAAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAcABhAGMAawBlAGQALAAgAGwAZQBuAF8AcgAgACsAIAAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABDAG8AbQBwAHUAdABlAHMAIAB0AGgAZQAgAFIAZQBjAGkAcAByAG8AYwBhAGwAIABwAHIAbwBnAHIAZQBzAHMAaQB2AGUAbAB5ACAAcwBjAGEAbABpAG4AZwAgAHUAcAAgAHQAbwAgAHQAaABlACAARABpAHYAaQBkAGUAbgBkACcAcwAgAHAAcgBlAGMAaQBzAGkAbwBuAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIAB0AGEAcgBnAGUAdABfAGwAZQBuACAAVABoAGUAIABsAGkAbQBiAC0AbABlAG4AZwB0AGgAIABvAGYAIABEAGkAdgBpAGQAZQBuAGQAIABBAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAFIAZQBjAGkAcAByAG8AYwBhAGwAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBiACwAIAB0AGEAcgBnAGUAdABfAGwAZQBuACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBlAGUAZABfAGwAZQBuACwAIABNAEkATgAoADMALAAgAGwAZQBuAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAByAF8AcwBlAGUAZABfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBTAGUAZQBkACgAbABpAG0AYgBzAF8AYgAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKABzAGUAZQBkAF8AbABlAG4ALAAgAHIAXwBzAGUAZQBkAF8AbABpAG0AYgBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQBxAF8AaQB0AGUAcgBzACwAIABNAEEAWAAoADAALAAgAEMARQBJAEwASQBOAEcALgBNAEEAVABIACgATABOACgAdABhAHIAZwBlAHQAXwBsAGUAbgAgAC8AIABzAGUAZQBkAF8AbABlAG4AKQAgAC8AIABMAE4AKAAyACkAKQApACAAKwAgADEALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKAByAGUAcQBfAGkAdABlAHIAcwAgAD0AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAXwBzAGUAZQBkAF8AbABpAG0AYgBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQB0AGUAcgBhAHQAaQBvAG4AcwAsACAAUwBFAFEAVQBFAE4AQwBFACgAcgBlAHEAXwBpAHQAZQByAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsAF8AcwB0AGEAdABlACwAIABpAHQAZQByAGEAdABpAG8AbgBzACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAaQB0AGUAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwB1AHIAcgBfAGwAZQBuACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcgAsACAARABSAE8AUAAoAHMAdABhAHQAZQAsACAAMQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AbABlAG4ALAAgAE0ASQBOACgAYwB1AHIAcgBfAGwAZQBuACAAKgAgADIALAAgAHQAYQByAGcAZQB0AF8AbABlAG4AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARAB5AG4AYQBtAGkAYwAgAFMAYwBhAGwAaQBuAGcAIABTAGgAaQBmAHQAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAASQBmACAAQgAgAGgAYQBzACAAcABsAGEAdABlAGEAdQBlAGQALAAgAFIAIABtAHUAcwB0ACAAcwBjAGEAbABlACAAYgB5ACAAMgAqACgAbgAtAG0AKQAuACAASQBmACAAQgAgAGkAcwAgAGcAcgBvAHcAaQBuAGcALAAgAFIAIABzAGMAYQBsAGUAcwAgAGIAeQAgACgAbgAtAG0AKQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAdABpAHYAZQBfAGMAdQByAHIALAAgAE0ASQBOACgAYwB1AHIAcgBfAGwAZQBuACwAIABsAGUAbgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAdABpAHYAZQBfAG4AZQB4AHQALAAgAE0ASQBOACgAbgBlAHgAdABfAGwAZQBuACwAIABsAGUAbgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGgAaQBmAHQAXwBsAGkAbQBiAHMALAAgADIAIAAqACAAKABuAGUAeAB0AF8AbABlAG4AIAAtACAAYwB1AHIAcgBfAGwAZQBuACkAIAAtACAAKABhAGMAdABpAHYAZQBfAG4AZQB4AHQAIAAtACAAYQBjAHQAaQB2AGUAXwBjAHUAcgByACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAXwBwAHIAaQBtAGUALAAgAEkARgAoAHMAaABpAGYAdABfAGwAaQBtAGIAcwAgAD4AIAAwACwAIABWAFMAVABBAEMASwAoAEUAWABQAEEATgBEACgAMAAsACAAcwBoAGkAZgB0AF8AbABpAG0AYgBzACwAIAAsACAAMAApACwAIABjAHUAcgByAF8AcgApACwAIABjAHUAcgByAF8AcgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABiAF8AYQBjAHQAaQB2AGUALAAgAFQAQQBLAEUAKABsAGkAbQBiAHMAXwBiACwAIAAtAGEAYwB0AGkAdgBlAF8AbgBlAHgAdAApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABQACAAaQBzACAAbgBhAHQAaQB2AGUAbAB5ACAAYQBsAGkAZwBuAGUAZAAgAHQAbwAgADIAKgBuAGUAeAB0AF8AbABlAG4AIABiAGUAYwBhAHUAcwBlACAAbwBmACAAdABoAGUAIABjAG8AcgByAGUAYwB0AGUAZAAgAHMAaABpAGYAdABfAGwAaQBtAGIAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGIAXwBhAGMAdABpAHYAZQAsACAAcgBfAHAAcgBpAG0AZQAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AHcAbwBfAGIAZQB0AGEALAAgAFYAUwBUAEEAQwBLACgARQBYAFAAQQBOAEQAKAAwACwAIAAyACAAKgAgAG4AZQB4AHQAXwBsAGUAbgAsACAALAAgADAAKQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGUAcgByACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAdQBiACgAdAB3AG8AXwBiAGUAdABhACwAIABwACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwByAF8AdQBuAHMAYwBhAGwAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAcgBfAHAAcgBpAG0AZQAsACAAZQByAHIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcgAsACAASQBGACgAUgBPAFcAUwAoAG4AZQB4AHQAXwByAF8AdQBuAHMAYwBhAGwAZQBkACkAIAA8AD0AIAAyACAAKgAgAG4AZQB4AHQAXwBsAGUAbgAsACAAewAwAH0ALAAgAEQAUgBPAFAAKABuAGUAeAB0AF8AcgBfAHUAbgBzAGMAYQBsAGUAZAAsACAAMgAgACoAIABuAGUAeAB0AF8AbABlAG4AKQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAG4AZQB4AHQAXwBsAGUAbgAsACAAbgBlAHgAdABfAHIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAMQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEgAZQBhAHYAeQB3AGUAaQBnAGgAdAAgAE4AZQB3AHQAbwBuAC0AUgBhAHAAaABzAG8AbgAgAEQAaQB2AGkAcwBpAG8AbgAuAFwAbgAgACoAIABJAG0AcABsAGUAbQBlAG4AdABzACAAcAByAG8AZwByAGUAcwBzAGkAdgBlACAAcwBjAGEAbABpAG4AZwAgAGIAbwB1AG4AZABlAGQAIAB0AG8AIABNAEEAWAAoAGwAZQBuAF8AYQAsACAAbABlAG4AXwBiACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBhACAAVABoAGUAIABkAGkAdgBpAGQAZQBuAGQAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2ACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAHIAZwBlAHQAXwBsAGUAbgAsACAATQBBAFgAKABsAGUAbgBfAGEALAAgAGwAZQBuAF8AYgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAMQAuACAAQwBhAGwAYwB1AGwAYQB0AGUAIAByAGUAYwBpAHAAcgBvAGMAYQBsACAAUgAgAHMAYwBhAGwAZQBkACAAZAB5AG4AYQBtAGkAYwBhAGwAbAB5ACAAdABvACAAMgAgACoAIAB0AGEAcgBnAGUAdABfAGwAZQBuAFwAbgAgACAAIAAgACAAIAAgACAAcgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBSAGUAYwBpAHAAcgBvAGMAYQBsACgAbABpAG0AYgBzAF8AYgAsACAAdABhAHIAZwBlAHQAXwBsAGUAbgAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAMgAuACAAQQBwAHAAcgBvAHgAaQBtAGEAdABlACAAUQB1AG8AdABpAGUAbgB0ADoAIABRAF8AYQBwAHAAcgBvAHgAIAA9ACAAQQAgACoAIABSACAALwAgAEIAZQB0AGEAXgAoADIAIAAqACAAdABhAHIAZwBlAHQAXwBsAGUAbgApAFwAbgAgACAAIAAgACAAIAAgACAAZAByAG8AcABfAGwAaQBtAGIAcwAsACAAMgAgACoAIAB0AGEAcgBnAGUAdABfAGwAZQBuACwAXABuACAAIAAgACAAIAAgACAAIABxAF8AdQBuAHMAYwBhAGwAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAbABpAG0AYgBzAF8AYQAsACAAcgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABxAF8AYQBwAHAAcgBvAHgALAAgAEkARgAoAFIATwBXAFMAKABxAF8AdQBuAHMAYwBhAGwAZQBkACkAIAA8AD0AIABkAHIAbwBwAF8AbABpAG0AYgBzACwAIAB7ADAAfQAsACAARABSAE8AUAAoAHEAXwB1AG4AcwBjAGEAbABlAGQALAAgAGQAcgBvAHAAXwBsAGkAbQBiAHMAKQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIAB0AGgAZQAgAG0AYQBzAHMAaQB2AGUAIABiAGEAcwBlAGwAaQBuAGUAIABwAHIAbwBkAHUAYwB0ACAAZQB4AGEAYwB0AGwAeQAgAE8ATgBDAEUAXABuACAAIAAgACAAIAAgACAAIABwAF8AYgBhAHMAZQBsAGkAbgBlACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAbABpAG0AYgBzAF8AYgAsACAAcQBfAGEAcABwAHIAbwB4ACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAAzAC4AIABCAG8AdQBuAGQAZQBkACAARQByAHIAbwByACAAQwBvAHIAcgBlAGMAdABpAG8AbgAgAFMAdwBlAGUAcAAgACgATwBwAHQAaQBtAGkAegBlAGQAIABPACgATgApACAAUwB0AGUAcABwAGkAbgBnACkAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABTAHQAYQB0AGUAIABwAGEAYwBrAGkAbgBnADoAIABWAFMAVABBAEMASwAoAEwAZQBuAGcAdABoAF8AUQAsACAAUQBfAGwAaQBtAGIAcwAsACAAUABfAGwAaQBtAGIAcwApAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAcQBfAGEAcABwAHIAbwB4ACkALAAgAHEAXwBhAHAAcAByAG8AeAAsACAAcABfAGIAYQBzAGUAbABpAG4AZQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUwB3AGUAZQBwACAARABvAHcAbgA6ACAASQBmACAAUAAgAD4AIABBACwAIABRACAAaQBzACAAdABvAG8AIABiAGkAZwAuACAAUwB0AGUAcAAgAFEAIABkAG8AdwBuACAAYgB5ACAAMQAsACAAYQBuAGQAIABQACAAZABvAHcAbgAgAGIAeQAgAEIALgBcAG4AIAAgACAAIAAgACAAIAAgAHMAdwBlAGUAcABfAGQAbwB3AG4ALAAgAFIARQBEAFUAQwBFACgAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAewAxADsAIAAyAH0ALAAgAEwAQQBNAEIARABBACgAcwB0AGEAdABlACwAIABpACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwBxACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwBxACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcwB0AGEAdABlACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHEALAAgADEALAAgADIAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwB1AHIAcgBfAHAALAAgAEQAUgBPAFAAKABzAHQAYQB0AGUALAAgAGwAZQBuAF8AcQAgACsAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBDAG8AbQBwAGEAcgBlACgAYwB1AHIAcgBfAHAALAAgAGwAaQBtAGIAcwBfAGEAKQAgAD4AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBTAHUAYgAoAGMAdQByAHIAXwBxACwAIAB7ADEAfQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwBwACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAdQBiACgAYwB1AHIAcgBfAHAALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFIATwBXAFMAKABuAGUAeAB0AF8AcQApACwAIABuAGUAeAB0AF8AcQAsACAAbgBlAHgAdABfAHAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAdABhAHQAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUwB3AGUAZQBwACAAVQBwADoAIABJAGYAIABQACAAKwAgAEIAIAA8AD0AIABBACwAIABRACAAaQBzACAAdABvAG8AIABzAG0AYQBsAGwALgAgAFMAdABlAHAAIABRACAAdQBwACAAYgB5ACAAMQAsACAAYQBuAGQAIABQACAAdQBwACAAYgB5ACAAQgAuAFwAbgAgACAAIAAgACAAIAAgACAAcwB3AGUAZQBwAF8AdQBwACwAIABSAEUARABVAEMARQAoAHMAdwBlAGUAcABfAGQAbwB3AG4ALAAgAHsAMQA7ACAAMgB9ACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAaQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcQAsACAASQBOAEQARQBYACgAcwB0AGEAdABlACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcQAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwBxACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwBwACwAIABEAFIATwBQACgAcwB0AGEAdABlACwAIABsAGUAbgBfAHEAIAArACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBlAHgAdABfAHAAXwB0AGUAcwB0ACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEEAZABkACgAYwB1AHIAcgBfAHAALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEMAbwBtAHAAYQByAGUAKABuAGUAeAB0AF8AcABfAHQAZQBzAHQALAAgAGwAaQBtAGIAcwBfAGEAKQAgADwAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwBxACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEEAZABkACgAYwB1AHIAcgBfAHEALAAgAHsAMQB9ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbgBlAHgAdABfAHEAKQAsACAAbgBlAHgAdABfAHEALAAgAG4AZQB4AHQAXwBwAF8AdABlAHMAdAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAdABlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAARgBpAG4AYQBsACAAUQAgAGEAbgBkACAAUABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAZQBuAF8AcQAsACAASQBOAEQARQBYACgAcwB3AGUAZQBwAF8AdQBwACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHEALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKABzAHcAZQBlAHAAXwB1AHAALAAgAFMARQBRAFUARQBOAEMARQAoAGYAaQBuAGEAbABfAGwAZQBuAF8AcQAsACAAMQAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHAALAAgAEQAUgBPAFAAKABzAHcAZQBlAHAAXwB1AHAALAAgAGYAaQBuAGEAbABfAGwAZQBuAF8AcQAgACsAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAA0AC4AIABFAHgAdAByAGEAYwB0ACAAVAByAHUAZQAgAFIAZQBtAGEAaQBuAGQAZQByACAAUwBhAGYAZQBsAHkAIAAoAEEAIAAtACAARgBpAG4AYQBsAF8AUAApAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBTAHUAYgAoAGwAaQBtAGIAcwBfAGEALAAgAGYAaQBuAGEAbABfAHAALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABmAGkAbgBhAGwAXwByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAEIAYQBzAGUALQAxADAAIABMAGUAZgB0AC0AdABvAC0AUgBpAGcAaAB0ACAARQB4AHAAbwBuAGUAbgB0AGkAYQB0AGkAbwBuAC4AXABuACAAKgAgAEUAdgBhAGwAdQBhAHQAZQBzACAAdABoAGUAIABlAHgAcABvAG4AZQBuAHQAIABpAHQAZQByAGEAdABpAHYAZQBsAHkAIAB1AHMAaQBuAGcAIABhACAAcAByAGUALQBjAG8AbQBwAHUAdABlAGQAIAAxAC0AOQAgAGMAYQBjAGgAZQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAYQBzAGUAIABUAGgAZQAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5ACAAbwBmACAAdABoAGUAIABiAGEAcwBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAZQB4AHAAXwBzAHQAcgBpAG4AZwAgAFQAaABlACAAZQB4AGEAYwB0ACAAdABlAHgAdAAgAHMAdAByAGkAbgBnACAAbwBmACAAdABoAGUAIABlAHgAcABvAG4AZQBuAHQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFUAUABvAHcAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBiAGEAcwBlACwAIABlAHgAcABfAHMAdAByAGkAbgBnACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFAAcgBlAC0AYwBvAG0AcAB1AHQAZQAgAHAAbwB3AGUAcgBzACAAMQAgAHQAaAByAG8AdQBnAGgAIAA5AC4AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQALAAgAGwAaQBtAGIAcwBfAGIAYQBzAGUALABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQBjAG8AbgBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAZgBpAHIAcwB0ACwAIABmAGkAcgBzAHQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABoAGkAcgBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAcwBlAGMAbwBuAGQALAAgAGYAaQByAHMAdAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABmAG8AdQByAHQAaAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAHMAZQBjAG8AbgBkACwAIABzAGUAYwBvAG4AZAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAZgB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABmAG8AdQByAHQAaAAsACAAZgBpAHIAcwB0ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQB4AHQAaAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAHQAaABpAHIAZAAsACAAdABoAGkAcgBkACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQB2AGUAbgB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABzAGkAeAB0AGgALAAgAGYAaQByAHMAdAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABlAGkAZwB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABmAG8AdQByAHQAaAAsACAAZgBvAHUAcgB0AGgALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBpAG4AdABoACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAZQBpAGcAdABoACwAIABmAGkAcgBzAHQALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGUAeABwAF8AZABpAGcAaQB0AHMALAAgAC0ALQBNAEkARAAoAGUAeABwAF8AcwB0AHIAaQBuAGcALAAgAFMARQBRAFUARQBOAEMARQAoAEwARQBOACgAZQB4AHAAXwBzAHQAcgBpAG4AZwApACkALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFIARQBEAFUAQwBFACgAMQAsACAAZQB4AHAAXwBkAGkAZwBpAHQAcwAsACAATABBAE0AQgBEAEEAKABhAGMAYwAsACAAZABpAGcAaQB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBoAG8AcgB0AC0AYwBpAHIAYwB1AGkAdAA6ACAAUwBrAGkAcAAgAGMAYQBsAGMAdQBsAGEAdABpAG4AZwAgADEAXgAxADAAIABkAHUAcgBpAG4AZwAgAGwAZQBhAGQAaQBuAGcAIABpAHQAZQByAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAcwBfAG8AbgBlACwAIABBAE4ARAAoAFIATwBXAFMAKABhAGMAYwApACAAPQAgADEALAAgAEkATgBEAEUAWAAoAGEAYwBjACwAIAAxACwAIAAxACkAIAA9ACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAMQAuACAAUgBhAGkAcwBlACAAQQBjAGMAIAB0AG8AIAB0AGgAZQAgADEAMAB0AGgAIABwAG8AdwBlAHIAIAB1AHMAaQBuAGcAIABlAHgAYQBjAHQAbAB5ACAANAAgAG0AdQBsAHQAaQBwAGwAaQBjAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8AMQAwACwAIABJAEYAKABpAHMAXwBvAG4AZQAsACAAYQBjAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8AMgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGEAYwBjACwAIABhAGMAYwAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8ANAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGEAYwBjAF8AMgAsACAAYQBjAGMAXwAyACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBjAGMAXwA4ACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAYQBjAGMAXwA0ACwAIABhAGMAYwBfADQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAYQBjAGMAXwA4ACwAIABhAGMAYwBfADIALAAgAGsAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAyAC4AIABNAHUAbAB0AGkAcABsAHkAIABiAHkAIAB0AGgAZQAgAGMAbwByAHIAZQBzAHAAbwBuAGQAaQBuAGcAIABwAHIAZQAtAGMAbwBtAHAAdQB0AGUAZAAgAGMAYQBjAGgAZQAgAHYAYQBsAHUAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABkAGkAZwBpAHQAIAA9ACAAMAAsACAAYQBjAGMAXwAxADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAYQBjAGgAZQBfAHYAYQBsACwAIABDAEgATwBPAFMARQAoAGQAaQBnAGkAdAAsACAAZgBpAHIAcwB0ACwAIABzAGUAYwBvAG4AZAAsACAAdABoAGkAcgBkACwAIABmAG8AdQByAHQAaAAsACAAZgBpAGYAdABoACwAIABzAGkAeAB0AGgALAAgAHMAZQB2AGUAbgB0AGgALAAgAGUAaQBnAHQAaAAsACAAbgBpAG4AdABoACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAaQBzAF8AbwBuAGUALAAgAGMAYQBjAGgAZQBfAHYAYQBsACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAYQBjAGMAXwAxADAALAAgAGMAYQBjAGgAZQBfAHYAYQBsACwAIABrACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAEkAbgB0AGUAZwBlAHIAIABTAHEAdQBhAHIAZQAgAFIAbwBvAHQAIAB1AHMAaQBuAGcAIABOAGUAdwB0AG8AbgAnAHMAIABNAGUAdABoAG8AZAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAG4AIABSAGEAZABpAGMAYQBuAGQAIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AcwBlAGUAZAAgAE8AdgBlAHIALQBlAHMAdABpAG0AYQB0AGUAZAAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABzAGUAZQBkACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBVAFMAcQByAHQAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBuACwAIABsAGkAbQBiAHMAXwBzAGUAZQBkACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAdABhAHQAZQAgAGkAcwAgAHAAYQBjAGsAZQBkADoAIABWAFMAVABBAEMASwAoAGkAcwBfAGQAbwBuAGUAXwBmAGwAYQBnACwAIABjAHUAcgByAGUAbgB0AF8AeAApAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKAAwACwAIABsAGkAbQBiAHMAXwBzAGUAZQBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AaQB0AGUAcgBzACwAIAAzADUALABcAG4AXABuACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAHQAYQB0AGUALAAgAFIARQBEAFUAQwBFACgAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbQBhAHgAXwBpAHQAZQByAHMAKQAsACAATABBAE0AQgBEAEEAKABzAHQAYQB0AGUALAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAHMAXwBkAG8AbgBlACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwB4ACwAIABEAFIATwBQACgAcwB0AGEAdABlACwAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAaQBzAF8AZABvAG4AZQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAdABlACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAxAC4AIABEAGkAdgBpAHMAaQBvAG4AOgAgAG4AIAAvACAAeABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZABpAHYAXwBwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ARABpAHYAUgBvAHUAdABlAHIAKABsAGkAbQBiAHMAXwBuACwAIABjAHUAcgByAF8AeAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcgAsACAASQBOAEQARQBYACgAZABpAHYAXwBwAGEAYwBrAGUAZAAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHEALAAgAEQAUgBPAFAAKABkAGkAdgBfAHAAYQBjAGsAZQBkACwAIABsAGUAbgBfAHIAIAArACAAMQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAyAC4AIABBAGQAZABpAHQAaQBvAG4AOgAgAHgAIAArACAAKABuACAALwAgAHgAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB1AG0AXwB4AHEALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQQBkAGQAKABjAHUAcgByAF8AeAAsACAAcQAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAzAC4AIABIAGEAbAB2AGkAbgBnADoAIAAoAHgAIAArACAAKABuACAALwAgAHgAKQApACAALwAgADIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEsAbgB1AHQAaABEAGkAdgAgAGkAbgBoAGUAcgBlAG4AdABsAHkAIABzAHUAcABwAG8AcgB0AHMAIABzAGMAYQBsAGEAcgAgAGQAaQB2AGkAcwBvAHIAcwAgAHcAaQB0AGgAIAB6AGUAcgBvACAAbwB2AGUAcgBoAGUAYQBkAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGkAdgBfADIAXwBwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2ACgAcwB1AG0AXwB4AHEALAAgAHsAMgB9ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwByADIALAAgAEkATgBEAEUAWAAoAGQAaQB2AF8AMgBfAHAAYQBjAGsAZQBkACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAeABfAG4AZQB4AHQALAAgAEQAUgBPAFAAKABkAGkAdgBfADIAXwBwAGEAYwBrAGUAZAAsACAAbABlAG4AXwByADIAIAArACAAMQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAA0AC4AIABDAG8AbgB2AGUAcgBnAGUAbgBjAGUAIABDAGgAZQBjAGsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQwBvAG0AcABhAHIAZQAoAHgAXwBuAGUAeAB0ACwAIABjAHUAcgByAF8AeAApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABOAGUAdwB0AG8AbgAnAHMAIABtAGUAdABoAG8AZAAgAGMAbwBuAHYAZQByAGcAZQBzACAAbwBuACAAdABoAGUAIABmAGwAbwBvAHIAIAByAG8AbwB0ACwAIABhAG4AZAAgAHMAdABhAGIAaQBsAGkAegBlAHMAIABvAHIAIABvAHMAYwBpAGwAbABhAHQAZQBzACAAdQBwACAAYgB5ACAAMQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABUAGgAZQByAGUAZgBvAHIAZQAsACAAaQBmACAAeABfAG4AZQB4AHQAIAA+AD0AIABjAHUAcgByAF8AeAAsACAAdABoAGUAIABhAGwAZwBvAHIAaQB0AGgAbQAgAGgAYQBzACAAYwBvAG4AdgBlAHIAZwBlAGQALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYwBvAG0AcAAgAD4APQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADEALAAgAGMAdQByAHIAXwB4ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADAALAAgAHgAXwBuAGUAeAB0ACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAZgBpAG4AYQBsAF8AcwB0AGEAdABlACwAIAAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABHAGUAbgBlAHIAYQB0AGUAcwAgAGEAIAAxAEQAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkAIABvAGYAIABhAGwAbAAgAHAAcgBpAG0AZQAgAG4AdQBtAGIAZQByAHMAIAB1AHAAIAB0AG8AIABuAC4AXABuACAAKgAgAEUAdgBhAGwAdQBhAHQAZQBzACAAcAB1AHIAZQBsAHkAIABpAG4AIABuAGEAdABpAHYAZQAgAEMAKwArACAAdQBzAGkAbgBnACAAYQAgAGQAeQBuAGEAbQBpAGMAIABzAGkAZQB2AGUALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABuACAAVABoAGUAIAB1AHAAcABlAHIAIABiAG8AdQBuAGQAIABpAG4AdABlAGcAZQByACAAKABhAHMAcwB1AG0AZQBkACAAPAA9ACAAOQAyADcAMwApAC4AXABuACAAKgAvAFwAbgBOAGEAdABpAHYAZQBQAHIAaQBtAGUAcwAgAD0AIABMAEEATQBCAEQAQQAoAG4ALABcAG4AIAAgACAAIABJAEYAKABuACAAPAAgADIALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBlAHEALAAgAFMARQBRAFUARQBOAEMARQAoAG4AIAAtACAAMQAsACAAMQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAcwBlAHEALAAgAE0AQQBQACgAcwBlAHEALAAgAEwAQQBNAEIARABBACgAeAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBpAHQALAAgAEkATgBUACgAUwBRAFIAVAAoAHgAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABsAGkAbQBpAHQAIAA8ACAAMgAsACAAVABSAFUARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAE0ATwBEACgAeAAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABpAG0AaQB0ACAALQAgADEALAAgADEALAAgADIAKQApACkAIAA+ACAAMABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAQwBhAGwAYwB1AGwAYQB0AGUAcwAgAHQAaABlACAAZQB4AHAAbwBuAGUAbgB0ACAAZgBvAHIAIABhAG4AIABhAHIAcgBhAHkAIABvAGYAIABwAHIAaQBtAGUAIABuAHUAbQBiAGUAcgBzACAAbgBhAHQAaQB2AGUAbAB5ACAAdQBzAGkAbgBnACAATABlAGcAZQBuAGQAcgBlACcAcwAgAEYAbwByAG0AdQBsAGEALgBcAG4AIAAqACAARQB2AGEAbAB1AGEAdABlAHMAIABwAHUAcgBlAGwAeQAgAGkAbgAgAG4AYQB0AGkAdgBlACAAQwArACsAIAB3AGkAdABoACAAegBlAHIAbwAgAEIAaQBnAEkAbgB0ACAAbwB2AGUAcgBoAGUAYQBkAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbgAgAFQAaABlACAAaQBuAHQAZQBnAGUAcgAgAGYAYQBjAHQAbwByAGkAYQBsACAAYgBhAHMAZQAgACgAPAA9ACAAOQAyADcAMwApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAcAByAGkAbQBlAHMAIABBACAAdgBlAHIAdABpAGMAYQBsACAAYQByAHIAYQB5ACAAbwBmACAAcAByAGkAbQBlACAAbgB1AG0AYgBlAHIAcwAgACgAPAA9ACAAbgApAC4AXABuACAAKgAvAFwAbgBOAGEAdABpAHYAZQBMAGUAZwBlAG4AZAByAGUAIAA9ACAATABBAE0AQgBEAEEAKABuACwAIABwAHIAaQBtAGUAcwAsAFwAbgAgACAAIAAgAE0AQQBQACgAcAByAGkAbQBlAHMALAAgAEwAQQBNAEIARABBACgAcAAsAFwAbgAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAHgAXwBrACwAIABJAE4AVAAoAEwATwBHACgAbgAsACAAcAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABvAHcAZQByAHMALAAgAHAAIABeACAAUwBFAFEAVQBFAE4AQwBFACgAbQBhAHgAXwBrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAE0AKABJAE4AVAAoAG4AIAAvACAAcABvAHcAZQByAHMAKQApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAVQBuAHMAYQBmAGUALAAgAGgAaQBnAGgALQBwAGUAcgBmAG8AcgBtAGEAbgBjAGUAIAB0AGUAeAB0ACAAbQB1AGwAdABpAHAAbABpAGMAYQB0AGkAbwBuACAAZgBvAHIAIAB0AHIAdQBzAHQAZQBkACwAIABwAG8AcwBpAHQAaQB2AGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQgB5AHAAYQBzAHMAZQBzACAATABhAHkAZQByACAAMAAgAHYAYQBsAGkAZABhAHQAaQBvAG4ALgAgAEkAbQBwAGwAZQBtAGUAbgB0AHMAIABzAHQAcgBpAGMAdAAgAHMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAcwAgAGYAbwByACAAcABhAGQAZABpAG4AZwAgAG8AcAB0AGkAbQBpAHoAYQB0AGkAbwBuAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAcwB0AHIAXwBhACAAVABoAGUAIABmAGkAcgBzAHQAIAB0AHIAdQBzAHQAZQBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHMAdAByAF8AYgAgAFQAaABlACAAcwBlAGMAbwBuAGQAIAB0AHIAdQBzAHQAZQBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AVQBUAGUAeAB0AE0AdQBsACAAPQAgAEwAQQBNAEIARABBACgAcwB0AHIAXwBhACwAIABzAHQAcgBfAGIALABcAG4AIAAgACAAIABJAEYAKABPAFIAKABzAHQAcgBfAGEAIAA9ACAAXAAiADAAXAAiACwAIABzAHQAcgBfAGIAIAA9ACAAXAAiADAAXAAiACkALAAgAFwAIgAwAFwAIgAsAFwAbgAgACAAIAAgAEkARgAoAHMAdAByAF8AYQAgAD0AIABcACIAMQBcACIALAAgAHMAdAByAF8AYgAsAFwAbgAgACAAIAAgAEkARgAoAHMAdAByAF8AYgAgAD0AIABcACIAMQBcACIALAAgAHMAdAByAF8AYQAsAFwAbgAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwBhACwAIABMAEUATgAoAHMAdAByAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAATABFAE4AKABzAHQAcgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIATQBVAEwAXAAiACwAIABNAEkATgAoAGwAZQBuAF8AYQAsACAAbABlAG4AXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAcwB0AHIAXwBhACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAcwB0AHIAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAKQApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFYAZQBjAHQAbwByAGkAegBlAGQAIABsAG8AZwBhAHIAaQB0AGgAbQBpAGMAIABwAHIAbwBkAHUAYwB0ACAAbwBmACAAYQBuACAAYQByAHIAYQB5ACAAbwBmACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAKgAgAFIAZQBjAHUAcgBzAGkAdgBlAGwAeQAgAGMAdQB0AHMAIAB0AGgAZQAgAGEAcgByAGEAeQAgAGkAbgAgAGgAYQBsAGYAIAB0AG8AIABiAHkAcABhAHMAcwAgAFIARQBEAFUAQwBFACAAcwBlAHEAdQBlAG4AdABpAGEAbAAgAG0AZQBtAG8AcgB5ACAAYQBsAGwAbwBjAGEAdABpAG8AbgBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAdABlAHgAdABfAGEAcgByACAAQQAgADEARAAgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoALwBcAG4AVABlAHgAdABUAHIAZQBlAFAAcgBvAGQAIAA9ACAATABBAE0AQgBEAEEAKAB0AGUAeAB0AF8AYQByAHIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgAsACAAUgBPAFcAUwAoAHQAZQB4AHQAXwBhAHIAcgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AIAA9ACAAMQAsACAASQBOAEQARQBYACgAdABlAHgAdABfAGEAcgByACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAcwBoAGEAcABlACAAYQByAHIAYQB5ACAAaQBuAHQAbwAgAHAAYQBpAHIAcwAuACAATwBkAGQALQBsAGUAbgBnAHQAaAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABzAGEAZgBlAGwAeQAgAHAAYQBkAGQAZQBkACAAdwBpAHQAaAAgAHQAaABlACAAbQB1AGwAdABpAHAAbABpAGMAYQB0AGkAdgBlACAAaQBkAGUAbgB0AGkAdAB5ACAAXAAiADEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAYQBpAHIAZQBkACwAIABXAFIAQQBQAFIATwBXAFMAKAB0AGUAeAB0AF8AYQByAHIALAAgADIALAAgAFwAIgAxAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAVgBlAGMAdABvAHIAaQB6AGUAZAAgAG0AdQBsAHQAaQBwAGwAaQBjAGEAdABpAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABwAGEAaQByAHMAIABzAGkAbQB1AGwAdABhAG4AZQBvAHUAcwBsAHkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBlAHgAdABfAGEAcgByACwAIABCAFkAUgBPAFcAKABwAGEAaQByAGUAZAAsACAATABBAE0AQgBEAEEAKAByAG8AdwAsACAAVQBUAGUAeAB0AE0AdQBsACgASQBOAEQARQBYACgAcgBvAHcALAAgADEALAAgADEAKQAsACAASQBOAEQARQBYACgAcgBvAHcALAAgADEALAAgADIAKQApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABhAGwAbABvAHcAIAByAGUAYwB1AHIAcwBpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBUAGUAeAB0AFQAcgBlAGUAUAByAG8AZAAoAG4AZQB4AHQAXwBhAHIAcgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBCAGkAZwBJAG4AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAFwAbgAvAC8AIABCAGkAZwAgAEkAbgB0AGUAZwBlAHIAIABBAHIAaQB0AGgAbQBlAHQAaQBjACAATABpAGIAcgBhAHIAeQAgAC8ALwBcAG4ALwAvACAAIAAgACAAIAAgACAAIABCAGkAZwBJAG4AdAAgAE0AbwBkAHUAbABlACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAgAFAAdQBiAGwAaQBjACAAQQBQAEkAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvAFwAbgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABOAG8AcgBtAGEAbABpAHMAZQBzACAAYQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgAgAFMAdAByAGkAcABzACAAbABlAGEAZABpAG4AZwAgAHoAZQByAG8AcwAsACAAcgBlAHMAbwBsAHYAZQBzACAAXAAiAC0AMABcACIAIAB0AG8AIABcACIAMABcACIALAAgAGEAbgBkACAAdABoAHIAbwB3AHMAIAAjAFYAQQBMAFUARQAhACAAbwBuACAAaQBuAHYAYQBsAGkAZAAgAGMAaABhAHIAYQBjAHQAZQByAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBOAG8AcgBtACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABzAHQAcgAsACAASQBGACgATwBSACgASQBTAE8ATQBJAFQAVABFAEQAKABiAGkAZwBfAGkAbgB0ACkALAAgAGIAaQBnAF8AaQBuAHQAIAA9ACAAXAAiAFwAIgApACwAIABcACIAMABcACIALAAgAGIAaQBnAF8AaQBuAHQAIAAmACAAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABpAHMAXwB2AGEAbABpAGQALAAgAFIARQBHAEUAWABUAEUAUwBUACgAcwB0AHIALAAgAFwAIgBeAC0APwBcAFwAZAArACQAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdAByAGkAcABwAGUAZAAsACAAUgBFAEcARQBYAFIARQBQAEwAQQBDAEUAKABzAHQAcgAsACAAXAAiAF4AKAAtAD8AKQAwACsAKAA/AD0AXABcAGQAKQBcACIALAAgAFwAIgAkADEAXAAiACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABOAE8AVAAoAGkAcwBfAHYAYQBsAGkAZAApACwAIABWAEEATABVAEUAKABcACIAIwBWAEEATABVAEUAIQBcACIAKQAsACAASQBGACgAcwB0AHIAaQBwAHAAZQBkACAAPQAgAFwAIgAtADAAXAAiACwAIABcACIAMABcACIALAAgAHMAdAByAGkAcABwAGUAZAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFIAZQB0AHUAcgBuAHMAIAB0AGgAZQAgAHMAaQBnAG4AIABvAGYAIABhACAAQgBpAGcASQBuAHQAOgAgADEAIAAoAHAAbwBzAGkAdABpAHYAZQApACwAIAAtADEAIAAoAG4AZQBnAGEAdABpAHYAZQApACwAIABvAHIAIAAwACAAKAB6AGUAcgBvACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBTAGkAZwBuACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsACAAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AZQBkACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIABTAFcASQBUAEMASAAoAEwARQBGAFQAKABuAG8AcgBtAGUAZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAwAFwAIgAsACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAC0AMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvAC8AIAAtAC0ALQAgAFAAcgBlAGQAaQBjAGEAdABlAHMAIAAtAC0ALQAgAFwAXABcAFwAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAFQAUgBVAEUAIABpAGYAIAB0AGgAZQAgAEIAaQBnAEkAbgB0ACAAaQBzACAAZQB4AGEAYwB0AGwAeQAgAHoAZQByAG8ALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBJAHMAWgBlAHIAbwAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0ACkAIAA9ACAAXAAiADAAXAAiACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAVABSAFUARQAgAGkAZgAgAHQAaABlACAAQgBpAGcASQBuAHQAIABpAHMAIABuAGUAZwBhAHQAaQB2AGUALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBJAHMATgBlAGcAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAIABMAEUARgBUACgATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAKQApACAAPQAgAFwAIgAtAFwAIgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAFQAUgBVAEUAIABpAGYAIAB0AGgAZQAgAEIAaQBnAEkAbgB0ACAAaQBzACAAZQB2AGUAbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAIABUAGgAZQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEkAcwBFAHYAZQBuACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsACAASQBTAEUAVgBFAE4AKABWAEEATABVAEUAKABSAEkARwBIAFQAKABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACkAKQApACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAVABSAFUARQAgAGkAZgAgAHQAaABlACAAQgBpAGcASQBuAHQAIABpAHMAIABvAGQAZAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAIABUAGgAZQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEkAcwBPAGQAZAAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALAAgAEkAUwBPAEQARAAoAFYAQQBMAFUARQAoAFIASQBHAEgAVAAoAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0ACkAKQApACkAKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFIAZQB0AHUAcgBuAHMAIAB0AGgAZQAgAHUAbgBzAGkAZwBuAGUAZAAgAG0AYQBnAG4AaQB0AHUAZABlACAAbwBmACAAYQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAIAAoAGEAYgBzAG8AbAB1AHQAZQAgAHYAYQBsAHUAZQApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AQQBiAHMAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAIABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgB1AG0ALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwARQBGAFQAKABuAHUAbQApACAAPQAgAFwAIgAtAFwAIgAsACAATQBJAEQAKABuAHUAbQAsACAAMgAsACAATABFAE4AKABuAHUAbQApACAALQAgADEAKQAsACAAbgB1AG0AKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAQwBvAG0AcABhAHIAZQBzACAAdAB3AG8AIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMALgAgAFIAZQB0AHUAcgBuAHMAIAAxACAAKABhACAAPgAgAGIAKQAsACAALQAxACAAKABhACAAPAAgAGIAKQAsACAAbwByACAAMAAgACgAYQAgAD0AIABiACkALgBcAG4AIAAqACAARQB2AGEAbAB1AGEAdABlAHMAIABzAGkAZwBuAHMAIABhAG4AZAAgAGwAZQBuAGcAdABoAHMALgAgAEkAZgAgAGkAZABlAG4AdABpAGMAYQBsACwAIABkAGUAbABlAGcAYQB0AGUAcwAgAHQAbwAgAG4AYQB0AGkAdgBlACAAbABpAG0AYgAgAGEAcgByAGEAeQAgAGMAbwBtAHAAYQByAGkAcwBvAG4ALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEMAbwBtAHAAYQByAGUAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGEALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBhACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgAsACAAQgBpAGcAaQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAHMAaQBnAG4AXwBhACAAPAA+ACAAcwBpAGcAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBJAEcATgAoAHMAaQBnAG4AXwBhACAALQAgAHMAaQBnAG4AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAcwBpAGcAbgBfAGEAIAA9ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwBhACwAIABMAEUATgAoAG4AbwByAG0AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAATABFAE4AKABuAG8AcgBtAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGwAZQBuAF8AYQAgADwAPgAgAGwAZQBuAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEkARwBOACgAbABlAG4AXwBhACAALQAgAGwAZQBuAF8AYgApACAAKgAgAHMAaQBnAG4AXwBhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEEARABEAFwAIgApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBhACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGEAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBiACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcABhAHIAaQBzAG8AbgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAGcAXwBjAG8AbQBwAGEAcgBpAHMAbwBuACAAKgAgAHMAaQBnAG4AXwBhAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIAAtACAAQQBkAGQAaQB0AGkAbwBuACAAJgAgAFMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAC0AIAAgACAAIAAgACAAIABcAFwAXABcAFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEEAZABkAHMAIAB0AHcAbwAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBhACAAVABoAGUAIABmAGkAcgBzAHQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGIAIABUAGgAZQAgAHMAZQBjAG8AbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AQQBkAGQAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGEALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBhACwAIABCAGkAZwBpAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIAQQBEAEQAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGEALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYQApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYgApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHUAdABlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEEAZABkAFMAdQBiAFIAbwB1AHQAZQByACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAcwBpAGcAbgBfAGEALAAgAHMAaQBnAG4AXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAaQBnAG4ALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKAByAG8AdQB0AGUAZAAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAARABSAE8AUAAoAHIAbwB1AHQAZQBkACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABtAGUAcgBnAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAFwAIgAtAFwAIgAgACYAIABtAGUAcgBnAGUAZAAsACAAbQBlAHIAZwBlAGQAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUwB1AGIAdAByAGEAYwB0AHMAIAB0AGgAZQAgAHMAZQBjAG8AbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAGYAaQByAHMAdAAgACgAQQAgAC0AIABCACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAbQBpAG4AdQBlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAcwB1AGIAdAByAGEAaABlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAFMAdQBiACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBiACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABJAG4AdgBlAHIAdAAgAHQAaABlACAAcwBpAGcAbgAgAG8AZgAgAEIAIABhAHQAIAB0AGgAZQAgAHQAZQB4AHQAIABsAGUAdgBlAGwAXABuACAAIAAgACAAIAAgACAAIABpAG4AdgBfAGIALAAgAEkARgAoAG4AbwByAG0AXwBiACAAPQAgAFwAIgAwAFwAIgAsACAAXAAiADAAXAAiACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATABFAEYAVAAoAG4AbwByAG0AXwBiACkAIAA9ACAAXAAiAC0AXAAiACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkARAAoAG4AbwByAG0AXwBiACwAIAAyACwAIABMAEUATgAoAG4AbwByAG0AXwBiACkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACAAJgAgAG4AbwByAG0AXwBiAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABQAGEAcwBzACAAdABvACAAQQBkAGQAXABuACAAIAAgACAAIAAgACAAIABBAGQAZAAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABpAG4AdgBfAGIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUwB1AG0AcwAgAGEAbgAgAGEAcgByAGEAeQAgAG8AcgAgAHIAYQBuAGcAZQAgAG8AZgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAgAHYAaQBhACAAdgBlAGMAdABvAHIAaQB6AGUAZAAgAGcAcgBvAHUAcAAgAG0AYQB0AHIAaQBjAGUAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHIAYQBuAGcAZQAgAEEAIABjAG8AbgB0AGkAZwB1AG8AdQBzACAAcgBhAG4AZwBlACAAbwByACAAYQByAHIAYQB5ACAAbwBmACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAKgAvAFwAbgBTAHUAbQAgAD0AIABMAEEATQBCAEQAQQAoAHIAYQBuAGcAZQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABmAGwAYQB0ACwAIABUAE8AUgBPAFcAKAByAGEAbgBnAGUALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABJAFMARQBSAFIATwBSACgAZgBsAGEAdAApACwAIABDAE8ATABVAE0ATgBTACgAZgBsAGEAdAApACAAPQAgADAAKQAsACAAXAAiADAAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBzACwAIABNAEEAUAAoAGYAbABhAHQALAAgAEwAQQBNAEIARABBACgAeAAsACAATgBvAHIAbQAoAHgAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGkAZwBuAHMALAAgAE0AQQBQACgATABFAEYAVAAoAG4AbwByAG0AcwApACwAIABMAEEATQBCAEQAQQAoAHgALAAgAEkARgAoAHgAIAA9ACAAXAAiADAAXAAiACwAIAAwACwAIABpAGYAKAB4ACAAPQAgAFwAIgAtAFwAIgAsACAALQAxACwAIAAxACkAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGIAcwBfAG4AbwByAG0AcwAsACAATQBBAFAAKABuAG8AcgBtAHMALAAgAHMAaQBnAG4AcwAsACAATABBAE0AQgBEAEEAKAB4ACwAIABzAGkAZwBuACwAIABJAEYAKABzAGkAZwBuACAAPQAgAC0AMQAsACAATQBJAEQAKAB4ACwAIAAyACwAIABMAEUATgAoAHgAKQAtADEAKQAsACAAeAApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAbwBzAF8AcwB0AHIAcwAsACAARgBJAEwAVABFAFIAKABhAGIAcwBfAG4AbwByAG0AcwAsACAAcwBpAGcAbgBzACAAPQAgADEALAAgAHsAXAAiADAAXAAiAH0AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQBnAF8AcwB0AHIAcwAsACAARgBJAEwAVABFAFIAKABhAGIAcwBfAG4AbwByAG0AcwAsACAAcwBpAGcAbgBzACAAPQAgAC0AMQAsACAAewBcACIAMABcACIAfQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdQBuAGkAZgBpAGUAZABfAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBBAEQARABcACIALAAgAEMATwBMAFUATQBOAFMAKABmAGwAYQB0ACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAbwBzAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AYQB0AHIAaQB4AFMAdQBtACgAcABvAHMAXwBzAHQAcgBzACwAIAB1AG4AaQBmAGkAZQBkAF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBlAGcAXwBsAGkAbQBiAHMALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQBhAHQAcgBpAHgAUwB1AG0AKABuAGUAZwBfAHMAdAByAHMALAAgAHUAbgBpAGYAaQBlAGQAXwBrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAG8AdQB0AGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AQQBkAGQAUwB1AGIAUgBvAHUAdABlAHIAKABwAG8AcwBfAGwAaQBtAGIAcwAsACAAbgBlAGcAXwBsAGkAbQBiAHMALAAgADEALAAgAC0AMQAsACAAdQBuAGkAZgBpAGUAZABfAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAaQBnAG4ALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKAByAG8AdQB0AGUAZAAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAEQAUgBPAFAAKAByAG8AdQB0AGUAZAAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGUAcgBnAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIAB1AG4AaQBmAGkAZQBkAF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAFwAIgAtAFwAIgAgACYAIABtAGUAcgBnAGUAZAAsACAAbQBlAHIAZwBlAGQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAE0AdQBsAHQAaQBwAGwAaQBlAHMAIAB0AHcAbwAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBhACAAVABoAGUAIABmAGkAcgBzAHQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGIAIABUAGgAZQAgAHMAZQBjAG8AbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ATQB1AGwAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGEALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBhACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwBhACwAIABMAEUATgAoAG4AbwByAG0AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAATABFAE4AKABuAG8AcgBtAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAOgAgADAAIABtAHUAbAB0AGkAcABsAGkAZQBkACAAYgB5ACAAYQBuAHkAdABoAGkAbgBnACAAaQBzACAAMABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAE8AUgAoAHMAaQBnAG4AXwBhACAAPQAgADAALAAgAHMAaQBnAG4AXwBiACAAPQAgADAAKQAsACAAXAAiADAAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABsAGUAbgBfAGEAIAArACAAbABlAG4AXwBiACAAPgAgADMAMgA3ADYANgAsACAAIwBOAFUATQAhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIABkAHkAbgBhAG0AaQBjACAAcwBhAGYAZQAgAEsAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHMAaABvAHIAdABlAHMAdAAgAHMAdAByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBNAFUATABcACIALAAgAE0ASQBOACgAbABlAG4AXwBhACwAIABsAGUAbgBfAGIAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBwAGwAaQB0ACAAYQBiAHMAbwBsAHUAdABlACAAcwB0AHIAaQBuAGcAcwAgAGkAbgB0AG8AIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAYQByAHIAYQB5AHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBhACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYgApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAbABjAHUAbABhAHQAZQAgAG0AYQBnAG4AaQB0AHUAZABlACAAYQBuAGQAIAByAGUAcwBvAGwAdgBlACAAcwBpAGcAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAGkAZwBuACwAIABzAGkAZwBuAF8AYQAgACoAIABzAGkAZwBuAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AZQByAGcAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGYAaQBuAGEAbABfAHMAaQBnAG4AIAA9ACAALQAxACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQALAAgAG0AZQByAGcAZQBkACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsAVgBPAEwAQQBUAEkATABFAF0AIABHAGUAbgBlAHIAYQB0AGUAcwAgAGEAIABkAHkAbgBhAG0AaQBjACAAYQByAHIAYQB5ACAAbwBmACAAaQBuAHQAZQBnAGUAcgBzACAAYQBzACAAdABlAHgAdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAbgB1AG0AXwByAG8AdwBzAF0AIABhAHIAcgBhAHkAIABoAGUAaQBnAGgAdAAsACAAZABlAGYAYQB1AGwAdAAgADEALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG4AdQBtAF8AYwBvAGwAcwBdACAAYQByAHIAYQB5ACAAdwBpAGQAdABoACwAIABkAGUAZgBhAHUAbAB0ACAAMQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAbQBpAG4AXwBkAGkAZwBpAHQAcwBdACAAbQBpAG4AaQBtAHUAbQAgAG4AdQBtAGIAZQByACAAbwBmACAAZABpAGcAaQB0AHMALAAgAGQAZQBmAGEAdQBsAHQAIAAxADYAIAAoAG0AaQBuACAAMQAgAGQAaQBnAGkAdAApAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAbQBhAHgAXwBkAGkAZwBpAHQAcwBdACAAbQBhAHgAaQBtAHUAbQAgAG4AdQBtAGIAZQByACAAbwBmACAAZABpAGcAaQB0AHMALAAgAGQAZQBmAGEAdQBsAHQAIAA1ADAAIAAoAG0AYQB4ACAAMwAyACwANwA2ADcAIABjAGgAYQByAHMALAAgAGkAbgBjAGwAdQBkAGkAbgBnACAAcwBpAGcAbgApAFwAbgAgACoALwBcAG4AUgBhAG4AZABCAGkAZwBJAG4AdABBAHIAcgBhAHkAIAA9ACAATABBAE0AQgBEAEEAKABbAG4AdQBtAF8AcgBvAHcAcwBdACwAIABbAG4AdQBtAF8AYwBvAGwAcwBdACwAIABbAG0AaQBuAF8AZABpAGcAaQB0AHMAXQAsACAAWwBtAGEAeABfAGQAaQBnAGkAdABzAF0ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBfAHIAbwB3AHMALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbgB1AG0AXwByAG8AdwBzACkALAAgADEALAAgAG4AdQBtAF8AcgBvAHcAcwApACwAXABuACAAIAAgACAAIAAgACAAIABuAF8AYwBvAGwAcwAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABuAHUAbQBfAGMAbwBsAHMAKQAsACAAMQAsACAAbgB1AG0AXwBjAG8AbABzACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAbQBpAG4AXwBsAGUAbgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABtAGkAbgBfAGQAaQBnAGkAdABzACkALAAgADEANgAsACAATQBJAE4AKAAzADIANwA2ADcALAAgAE0AQQBYACgAMQAsACAAbQBpAG4AXwBkAGkAZwBpAHQAcwApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwBsAGUAbgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABtAGEAeABfAGQAaQBnAGkAdABzACkALAAgADUAMAAsACAATQBBAFgAKAAxACwAIABNAEkATgAoADMAMgA3ADYANgAsACAAbQBhAHgAXwBkAGkAZwBpAHQAcwApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBQACgAUgBBAE4ARABBAFIAUgBBAFkAKABuAF8AcgBvAHcAcwAsACAAbgBfAGMAbwBsAHMALAAgAG0AaQBuAF8AbABlAG4ALAAgAG0AYQB4AF8AbABlAG4ALAAgAFQAUgBVAEUAKQAsACAATABBAE0AQgBEAEEAKABsAGUAbgBnAHQAaAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAaQBnAG4ALAAgAEMASABPAE8AUwBFACgAUgBBAE4ARABCAEUAVABXAEUARQBOACgAMQAsACAAMgApACwAIABcACIAXAAiACwAIABcACIALQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGQAaQBnAGkAdABzACwAIABDAE8ATgBDAEEAVAAoAFIAQQBOAEQAQQBSAFIAQQBZACgAMQAsACAAbABlAG4AZwB0AGgALAAgADAALAAgADkALAAgAFQAUgBVAEUAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBpAGcAbgAgACYAIABSAEUARwBFAFgAUgBFAFAATABBAEMARQAoAGQAaQBnAGkAdABzACwAIABcACIAXgAwACoAXAAiACwAIABcACIAXAAiACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEQAaQB2AGkAZABlAHMAIAB0AGgAZQAgAGYAaQByAHMAdAAgAEIAaQBnAEkAbgB0ACAAYgB5ACAAdABoAGUAIABzAGUAYwBvAG4AZAAgACgAQQAgAC8AIABCACkALgAgAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIABxAHUAbwB0AGkAZQBuAHQAIABhAG4AZAAgAG0AbwBkAHUAbAB1AHMAIABpAG4AIAByAG8AdwBzACAAMQAgAGEAbgBkACAAMgAsACAAcgBlAHMAcABlAGMAdABpAHYAZQBsAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAdQBzAGUAXwBmAGwAbwBvAHIAXQAgAE8AcAB0AGkAbwBuAGEAbAAgAGIAbwBvAGwAZQBhAG4ALgAgAFQAUgBVAEUAIABmAG8AcgAgAFAAeQB0AGgAbwBuAC0AcwB0AHkAbABlACAARgBsAG8AbwByACAAZABpAHYAaQBzAGkAbwBuACwAIABGAEEATABTAEUAIABmAG8AcgAgAFQAcgB1AG4AYwBhAHQAZQBkAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABGAEEATABTAEUALgBcAG4AIAAqAC8AXABuAEQAaQB2AE0AbwBkACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAIABbAHUAcwBlAF8AZgBsAG8AbwByAF0ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGEALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBhACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AZgBsAG8AbwByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHUAcwBlAF8AZgBsAG8AbwByACkALAAgAEYAQQBMAFMARQAsACAAdQBzAGUAXwBmAGwAbwBvAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AYgAgAD0AIAAwACwAIAAjAEQASQBWAC8AMAAhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHMAaQBnAG4AXwBhACAAPQAgADAALAAgAHsAXAAiADAAXAAiADsAXAAiADAAXAAiAH0ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBhACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGEAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBiACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGIAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAYQBjAGsAZQBkAF8AcgBlAHMAdQBsAHQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEQAaQB2AFIAbwB1AHQAZQByACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABSAGUAbQBhAGkAbgBkAGUAcgAgAGEAbgBkACAAUQB1AG8AdABpAGUAbgB0ACAAYQByAHIAYQB5AHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHIALAAgAEkATgBEAEUAWAAoAHAAYQBjAGsAZQBkAF8AcgBlAHMAdQBsAHQALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAG0AXwBsAGkAbQBiAHMALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKABwAGEAYwBrAGUAZABfAHIAZQBzAHUAbAB0ACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHIALAAgADEALAAgADIAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABxAHUAbwB0AF8AbABpAG0AYgBzACwAIABEAFIATwBQACgAcABhAGMAawBlAGQAXwByAGUAcwB1AGwAdAAsACAAbABlAG4AXwByACAAKwAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAcwBvAGwAdgBlACAAVAByAHUAbgBjAGEAdABlAGQAIABzAGkAZwBuAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAGkAZwBuACwAIABzAGkAZwBuAF8AYQAgACoAIABzAGkAZwBuAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBlAHIAZwBlAGQAXwBxACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABxAHUAbwB0AF8AbABpAG0AYgBzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AZQByAGcAZQBkAF8AcgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAcgBlAG0AXwBsAGkAbQBiAHMALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AHIAdQBuAGMAXwBxACwAIABJAEYAKABBAE4ARAAoAGYAaQBuAGEAbABfAHMAaQBnAG4AIAA9ACAALQAxACwAIABtAGUAcgBnAGUAZABfAHEAIAA8AD4AIABcACIAMABcACIAKQAgACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQAXwBxACwAIABtAGUAcgBnAGUAZABfAHEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdAByAHUAbgBjAF8AcgAsACAASQBGACgAYQBuAGQAKABzAGkAZwBuAF8AYQAgAD0AIAAtADEALAAgAG0AZQByAGcAZQBkAF8AcgAgADwAPgAgAFwAIgAwAFwAIgApACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQAXwByACwAIABtAGUAcgBnAGUAZABfAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABGAGwAbwBvAHIAIABDAG8AcgByAGUAYwB0AGkAbwBuADoAIABUAHIAaQBnAGcAZQByACAATwBOAEwAWQAgAGkAZgAgAGYAbABvAG8AcgAgAGkAcwAgAHIAZQBxAHUAZQBzAHQAZQBkACwAIABzAGkAZwBuAHMAIABkAGkAZgBmAGUAcgAsACAAYQBuAGQAIAByAGUAbQBhAGkAbgBkAGUAcgAgAGkAcwAgAG4AbwBuAC0AegBlAHIAbwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQBlAGQAcwBfAGMAbwByAHIAZQBjAHQAaQBvAG4ALAAgAEEATgBEACgAaQBzAF8AZgBsAG8AbwByACwAIABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAbQBlAHIAZwBlAGQAXwByACAAPAA+ACAAXAAiADAAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcQAsACAASQBGACgAbgBlAGUAZABzAF8AYwBvAHIAcgBlAGMAdABpAG8AbgAsACAAUwB1AGIAKAB0AHIAdQBuAGMAXwBxACwAIABcACIAMQBcACIAKQAsACAAdAByAHUAbgBjAF8AcQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwByACwAIABJAEYAKABuAGUAZQBkAHMAXwBjAG8AcgByAGUAYwB0AGkAbwBuACwAIABBAGQAZAAoAHQAcgB1AG4AYwBfAHIALAAgAG4AbwByAG0AXwBiACkALAAgAHQAcgB1AG4AYwBfAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAGYAaQBuAGEAbABfAHEALAAgAGYAaQBuAGEAbABfAHIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAARABpAHYAaQBkAGUAcwAgAHQAaABlACAAZgBpAHIAcwB0ACAAQgBpAGcASQBuAHQAIABiAHkAIAB0AGgAZQAgAHMAZQBjAG8AbgBkACAAKABBACAALwAgAEIAKQAuACAAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAGQAaQB2AGkAZABlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAHUAcwBlAF8AZgBsAG8AbwByAF0AIABPAHAAdABpAG8AbgBhAGwAIABiAG8AbwBsAGUAYQBuAC4AIABUAFIAVQBFACAAZgBvAHIAIABQAHkAdABoAG8AbgAtAHMAdAB5AGwAZQAgAEYAbABvAG8AcgAgAGQAaQB2AGkAcwBpAG8AbgAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAARgBBAEwAUwBFAC4AXABuACAAKgAvAFwAbgBEAGkAdgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABiAGkAZwBfAGkAbgB0AF8AYgAsACAAWwB1AHMAZQBfAGYAbABvAG8AcgBdACwAXABuACAAIAAgACAASQBOAEQARQBYACgARABpAHYATQBvAGQAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALAAgAHUAcwBlAF8AZgBsAG8AbwByACkALAAgADEALAAgADEAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEMAbwBtAHAAdQB0AGUAcwAgAHQAaABlACAAcgBlAG0AYQBpAG4AZABlAHIAIABvAGYAIABBACAALwAgAEIALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAdQBzAGUAXwBmAGwAbwBvAHIAXQAgAE8AcAB0AGkAbwBuAGEAbAAgAGIAbwBvAGwAZQBhAG4ALgAgAFQAUgBVAEUAIABmAG8AcgAgAFAAeQB0AGgAbwBuAC0AcwB0AHkAbABlACAATQBvAGQAdQBsAG8ALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAEYAQQBMAFMARQAuAFwAbgAgACoALwBcAG4ATQBvAGQAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALAAgAFsAdQBzAGUAXwBmAGwAbwBvAHIAXQAsAFwAbgAgACAAIAAgAEkATgBEAEUAWAAoAEQAaQB2AE0AbwBkACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAIAB1AHMAZQBfAGYAbABvAG8AcgApACwAIAAyACwAIAAxACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGEAaQBzAGUAcwAgAGEAIABCAGkAZwBJAG4AdAAgAGIAYQBzAGUAIAB0AG8AIAB0AGgAZQAgAHAAbwB3AGUAcgAgAG8AZgAgAGEAIABCAGkAZwBJAG4AdAAgAGUAeABwAG8AbgBlAG4AdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAYQBzAGUAIABUAGgAZQAgAGIAYQBzAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAZQB4AHAAbwBuAGUAbgB0ACAAVABoAGUAIABlAHgAcABvAG4AZQBuAHQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBQAG8AdwAgAD0AIABMAEEATQBCAEQAQQAoAGIAYQBzAGUALAAgAGUAeABwAG8AbgBlAG4AdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgBhAHMAZQAsACAATgBvAHIAbQAoAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGUAeABwACwAIABOAG8AcgBtACgAZQB4AHAAbwBuAGUAbgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBiAGEAcwBlACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYgBhAHMAZQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AZQB4AHAALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBlAHgAcAApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAYQBiAHMAXwBiAGEAcwBlACwAIABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAYQBiAHMAXwBlAHgAcAAsACAAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBlAHgAcAApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AZQB4AHAAXwBlAHYAZQBuACwAIABJAFMARQBWAEUATgAoAFYAQQBMAFUARQAoAFIASQBHAEgAVAAoAG4AbwByAG0AXwBlAHgAcAAsACAAMQApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcwBpAGcAbgAsACAASQBGACgAcwBpAGcAbgBfAGIAYQBzAGUAIAA9ACAALQAxACwAIABJAEYAKABpAHMAXwBlAHgAcABfAGUAdgBlAG4ALAAgADEALAAgAC0AMQApACwAIABzAGkAZwBuAF8AYgBhAHMAZQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAASABhAG4AZABsAGUAIABtAGEAdABoAGUAbQBhAHQAaQBjAGEAbAAgAGIAbwB1AG4AZABhAHIAaQBlAHMAIABhAG4AZAAgAGIAYQBzAGUAIABsAGkAbQBpAHQAcwBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGEAYgBzAF8AYgBhAHMAZQAgAD0AIABcACIAMABcACIALAAgAEkARgAoAG4AbwByAG0AXwBlAHgAcAAgAD0AIABcACIAMABcACIALAAgACMATgBVAE0AIQAsACAAXAAiADAAXAAiACkALAAgAC8ALwAgADAAXgAwACAAaQBzACAAdQBuAGQAZQBmAGkAbgBlAGQAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABhAGIAcwBfAGIAYQBzAGUAIAA9ACAAXAAiADEAXAAiACwAIABJAEYAKABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAXAAiAC0AMQBcACIALAAgAFwAIgAxAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AZQB4AHAAIAA9ACAALQAxACwAIABcACIAMABcACIALAAgAC8ALwAgAEkAbgB0AGUAZwBlAHIAIAB0AHIAdQBuAGMAYQB0AGkAbwBuADoAIABuAGUAZwBhAHQAaQB2AGUAIABlAHgAcABvAG4AZQBuAHQAcwAgAHkAaQBlAGwAZAAgADAAIABmAG8AcgAgAGIAYQBzAGUAcwAgAD4APQAgADIAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAG8AcgBtAF8AZQB4AHAAIAA9ACAAXAAiADAAXAAiACwAIABcACIAMQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAcwB1AGwAdABzACAAZgByAG8AbQAgAGUAeABwAG8AbgBlAG4AdABzACAAZwByAGUAYQB0AGUAcgAgAHQAaABhAG4AIAA2ACAAZABpAGcAaQB0AHMAIABjAGEAbgBuAG8AdAAgAGIAZQAgAGQAaQBzAHAAbABhAHkAZQBkAC4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAEUATgAoAG4AbwByAG0AXwBlAHgAcAApACAAPgAgADYALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AdQBtAF8AZQB4AHAALAAgAFYAQQBMAFUARQAoAG4AbwByAG0AXwBlAHgAcAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQQBwAHAAcgBvAHgAaQBtAGEAdABlACAAdABoAGUAIABmAGkAbgBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgAgAGMAbwB1AG4AdAA6ACAAQgAgACoAIABMAG8AZwAxADAAKABBACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYgBhAHMAZQBfAGwAbwBnADEAMAAsACAATABPAEcAMQAwACgAVgBBAEwAVQBFACgATABFAEYAVAAoAGEAYgBzAF8AYgBhAHMAZQAsACAAMQA0ACkAKQApACAAKwAgAE0AQQBYACgAMAAsACAATABFAE4AKABhAGIAcwBfAGIAYQBzAGUAKQAgAC0AIAAxADQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAcABwAHIAbwB4AF8AZABpAGcAaQB0AHMALAAgAG4AdQBtAF8AZQB4AHAAIAAqACAAYgBhAHMAZQBfAGwAbwBnADEAMAAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABhAHAAcAByAG8AeABfAGQAaQBnAGkAdABzACAAPgAgADMAMgA3ADYANgAsACAAIwBOAFUATQAhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIATQBVAEwAXAAiACwAIABhAHAAcAByAG8AeABfAGQAaQBnAGkAdABzACAALwAgADIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBiAGEAcwBlACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABhAGIAcwBfAGIAYQBzAGUALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFAAbwB3ACgAbABpAG0AYgBzAF8AYgBhAHMAZQAsACAAbgBvAHIAbQBfAGUAeABwACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBlAHIAZwBlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAXAAiAC0AXAAiACAAJgAgAG0AZQByAGcAZQBkACwAIABtAGUAcgBnAGUAZAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApACkAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABDAGEAbABjAHUAbABhAHQAZQBzACAAdABoAGUAIABpAG4AdABlAGcAZQByACAAcwBxAHUAYQByAGUAIAByAG8AbwB0ACAAKABmAGwAbwBvAHIAKQAgAG8AZgAgAGEAIABCAGkAZwBJAG4AdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAIABUAGgAZQAgAHIAYQBkAGkAYwBhAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAFMAcQByAHQAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBuACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AbgAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAG4AKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAHMAaQBnAG4AXwBuACAAPQAgAC0AMQAsACAAIwBOAFUATQAhACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAG8AcgBtAF8AbgAgAD0AIABcACIAMABcACIALAAgAFwAIgAwAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgBvAHIAbQBfAG4AIAA9ACAAXAAiADEAXAAiACwAIABcACIAMQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAG4ALAAgAEwARQBOACgAbgBvAHIAbQBfAG4AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAYQBrAGUAXwBkAGkAZwBpAHQAcwAsACAASQBGACgAbABlAG4AXwBuACAAPAA9ACAAMQA0ACwAIABsAGUAbgBfAG4ALAAgAEkARgAoAEkAUwBFAFYARQBOACgAbABlAG4AXwBuACkALAAgADEANAAsACAAMQAzACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHYAXwBzAHQAcgAsACAATABFAEYAVAAoAG4AbwByAG0AXwBuACwAIAB0AGEAawBlAF8AZABpAGcAaQB0AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHYAXwBuAHUAbQAsACAAVgBBAEwAVQBFACgAdgBfAHMAdAByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB6AGUAcgBvAF8AYwBvAHUAbgB0ACwAIAAoAGwAZQBuAF8AbgAgAC0AIAB0AGEAawBlAF8AZABpAGcAaQB0AHMAKQAgAC8AIAAyACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAZQBlAGQAXwBwAHIAZQBmAGkAeAAsACAAVABFAFgAVAAoAFIATwBVAE4ARABVAFAAKABTAFEAUgBUACgAdgBfAG4AdQBtACkALAAgADAAKQAgACsAIAAxACwAIABcACIAMABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAZQBlAGQAXwBzAHQAcgAsACAAcwBlAGUAZABfAHAAcgBlAGYAaQB4ACAAJgAgAFIARQBQAFQAKABcACIAMABcACIALAAgAHoAZQByAG8AXwBjAG8AdQBuAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGMAYQBsAGUAcwAgAGsAIABiAHkAIAB0AGgAZQAgAG0AYQB4AGkAbQB1AG0AIABvAHYAZQByAGwAYQBwACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAE0AVQBMAFwAIgAsACAAbABlAG4AXwBuACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBuACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABuAG8AcgBtAF8AbgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AcwBlAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAcwBlAGUAZABfAHMAdAByACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAcQByAHQAKABsAGkAbQBiAHMAXwBuACwAIABsAGkAbQBiAHMAXwBzAGUAZQBkACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAQwBvAG0AcAB1AHQAZQBzACAAdABoAGUAIABmAGEAYwB0AG8AcgBpAGEAbAAgAG8AZgAgAGEAIABCAGkAZwBJAG4AdAAgACgAbgAhACkALgBcAG4AIAAqACAAVQB0AGkAbABpAHoAZQBzACAATABlAGcAZQBuAGQAcgBlACcAcwAgAGYAbwByAG0AdQBsAGEAIABhAG4AZAAgAGwAbwBnAGEAcgBpAHQAaABtAGkAYwAgAHQAcgBlAGUAIABtAHUAbAB0AGkAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABiAHkAcABhAHMAcwAgAHMAdABhAGMAawAvAG0AZQBtAG8AcgB5ACAAbABpAG0AaQB0AHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AIABNAGEAeABpAG0AdQBtACAAcwB1AHAAcABvAHIAdABlAGQAIABpAG4AcAB1AHQAIABpAHMAIAA5ADIANwAzAC4AXABuACAAKgAvAFwAbgBGAGEAYwB0ACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AbgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAG4ALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBuACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AbgAgAD0AIAAtADEALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgBvAHIAbQBfAG4AIAA9ACAAXAAiADAAXAAiACwAIABcACIAMQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AbwByAG0AXwBuACAAPQAgAFwAIgAxAFwAIgAsACAAXAAiADEAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABGAGkAcgBlAHcAYQBsAGwAIAAxADoAIABUAHIAYQBwACAAbQBhAHMAcwBpAHYAZQAgAHMAdAByAGkAbgBnAHMAIABiAGUAZgBvAHIAZQAgAHQAaABlAHkAIABoAGkAdAAgAFYAQQBMAFUARQAoACkAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAEUATgAoAG4AbwByAG0AXwBuACkAIAA+ACAANAAsACAAIwBOAFUATQAhACwAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEYAaQByAGUAdwBhAGwAbAAgADIAOgAgAFQAcgBhAHAAIABtAGEAdABoAGUAbQBhAHQAaQBjAGEAbAAgAGMAZQBpAGwAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABWAEEATABVAEUAKABuAG8AcgBtAF8AbgApACAAPgAgADkAMgA3ADMALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AXwB2AGEAbAAsACAAVgBBAEwAVQBFACgAbgBvAHIAbQBfAG4AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAcgBpAG0AZQBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBOAGEAdABpAHYAZQBQAHIAaQBtAGUAcwAoAG4AXwB2AGEAbAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZQB4AHAAbwBuAGUAbgB0AHMALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE4AYQB0AGkAdgBlAEwAZQBnAGUAbgBkAHIAZQAoAG4AXwB2AGEAbAAsACAAcAByAGkAbQBlAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAE0AYQBwACAAbwB2AGUAcgAgAHAAcgBpAG0AZQBzACAAYQBuAGQAIABlAHgAcABvAG4AZQBuAHQAcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAcABeAGUALgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAbwBlAHIAYwBlACAAbgBhAHQAaQB2AGUAIABpAG4AdABlAGcAZQByAHMAIABiAGEAYwBrACAAdABvACAAcwB0AHIAaQBuAGcAcwAgAGYAbwByACAAdABoAGUAIABQAG8AdwAgAGIAbwB1AG4AZABhAHIAeQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAcgBpAG0AZQBfAHAAbwB3AGUAcgBzACwAIABNAEEAUAAoAHAAcgBpAG0AZQBzACwAIABlAHgAcABvAG4AZQBuAHQAcwAsACAATABBAE0AQgBEAEEAKABwACwAIABlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAbwB3ACgAcAAgACYAIABcACIAXAAiACwAIABlACAAJgAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBUAGUAeAB0AFQAcgBlAGUAUAByAG8AZAAoAHAAcgBpAG0AZQBfAHAAbwB3AGUAcgBzACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAKQApACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAuAEsAbgB1AHQAaABEAGkAdgBpAHMAaQBvAG4AIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgBpAHMAaQBvAG4AIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ARABpAHYAaQBzAGkAbwBuAEEAbABnAG8AcgBpAHQAaABtAHMAIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ARABpAHYAaQBzAGkAbwBuAEEAbABnAG8AcgBpAHQAaABtAEMAbwBtAHAAYQByAGkAcwBvAG4AIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ARABpAHYAaQBzAGkAbwBuAEIAZQBuAGMAaABtAGEAcgBrAEMAYQBzAGUAcwAiACwAIgB0AGUAcwB0AF8AQgBpAGcASQBuAHQALgBBAHMAeQBtAG0AZQB0AHIAaQBjAEEAQgBHAHIAaQBkACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEMAYQByAHIAeQAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEMAbwBtAHAAYQByAGUAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBBAGQAZAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAdQBiACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQBhAHQAcgBpAHgAUwB1AG0AIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AQQBkAGQAUwB1AGIAUgBvAHUAdABlAHIAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBGAGkAbgBkAFEAdQBvAHQAaQBlAG4AdABMAGkAbQBiACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEsAbgB1AHQAaABEAGkAdgAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBEAGkAdgBSAG8AdQB0AGUAcgAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAFMAZQBlAGQAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBSAGUAYwBpAHAAcgBvAGMAYQBsACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4ARABpAHYAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBQAG8AdwAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAcQByAHQAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBhAHQAaQB2AGUAUAByAGkAbQBlAHMAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBhAHQAaQB2AGUATABlAGcAZQBuAGQAcgBlACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAVABlAHgAdABNAHUAbAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBUAGUAeAB0AFQAcgBlAGUAUAByAG8AZAAiACwAIgBCAGkAZwBJAG4AdAAuAE4AbwByAG0AIgAsACIAQgBpAGcASQBuAHQALgBTAGkAZwBuACIALAAiAEIAaQBnAEkAbgB0AC4ASQBzAFoAZQByAG8AIgAsACIAQgBpAGcASQBuAHQALgBJAHMATgBlAGcAIgAsACIAQgBpAGcASQBuAHQALgBJAHMARQB2AGUAbgAiACwAIgBCAGkAZwBJAG4AdAAuAEkAcwBPAGQAZAAiACwAIgBCAGkAZwBJAG4AdAAuAEEAYgBzACIALAAiAEIAaQBnAEkAbgB0AC4AQwBvAG0AcABhAHIAZQAiACwAIgBCAGkAZwBJAG4AdAAuAEEAZABkACIALAAiAEIAaQBnAEkAbgB0AC4AUwB1AGIAIgAsACIAQgBpAGcASQBuAHQALgBTAHUAbQAiACwAIgBCAGkAZwBJAG4AdAAuAE0AdQBsACIALAAiAEIAaQBnAEkAbgB0AC4AUgBhAG4AZABCAGkAZwBJAG4AdABBAHIAcgBhAHkAIgAsACIAQgBpAGcASQBuAHQALgBEAGkAdgBNAG8AZAAiACwAIgBCAGkAZwBJAG4AdAAuAEQAaQB2ACIALAAiAEIAaQBnAEkAbgB0AC4ATQBvAGQAIgAsACIAQgBpAGcASQBuAHQALgBQAG8AdwAiACwAIgBCAGkAZwBJAG4AdAAuAFMAcQByAHQAIgAsACIAQgBpAGcASQBuAHQALgBGAGEAYwB0ACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/XL-Int.xlsx
+++ b/XL-Int.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\foolu\Workspace\Excel\BigInt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3CD98F-A623-483E-B1D6-2DA9C96CBDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D93F4D3-4B6A-4C8A-BBEF-A27586E65BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24610" windowHeight="21000" xr2:uid="{36490472-0618-4E80-9469-F609392FABC8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24560" windowHeight="21000" xr2:uid="{36490472-0618-4E80-9469-F609392FABC8}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -24,11 +24,13 @@
     <definedName name="BigInt.Compare" comment="Compares two BigInt strings. Returns 1 (a &gt; b), -1 (a &lt; b), or 0 (a = b)._x000a_Evaluates signs and lengths. If identical, delegates to native limb array comparison._x000a_@param big_int_a The first BigInt string._x000a_@param big_int_b The second BigInt string.">_xlfn.LAMBDA(_xlpm.big_int_a,_xlpm.big_int_b, _xlfn.LET(_xlpm.norm_a, BigInt.Norm(_xlpm.big_int_a), _xlpm.norm_b, BigInt.Norm(_xlpm.big_int_b), _xlpm.sign_a, BigInt.Sign(_xlpm.norm_a), _xlpm.sign_b, BigInt.Sign(_xlpm.norm_b), IF(_xlpm.sign_a &lt;&gt; _xlpm.sign_b, SIGN(_xlpm.sign_a - _xlpm.sign_b), IF(_xlpm.sign_a = 0, 0, _xlfn.LET(_xlpm.len_a, LEN(_xlpm.norm_a), _xlpm.len_b, LEN(_xlpm.norm_b), IF(_xlpm.len_a &lt;&gt; _xlpm.len_b, SIGN(_xlpm.len_a - _xlpm.len_b) * _xlpm.sign_a, _xlfn.LET(_xlpm.k, core_BigInt.SafeK("ADD"), _xlpm.limbs_a, core_BigInt.Split(BigInt.Abs(_xlpm.norm_a), _xlpm.k), _xlpm.limbs_b, core_BigInt.Split(BigInt.Abs(_xlpm.norm_b), _xlpm.k), _xlpm.mag_comparison, core_BigInt.UCompare(_xlpm.limbs_a, _xlpm.limbs_b), _xlpm.mag_comparison * _xlpm.sign_a)))))))</definedName>
     <definedName name="BigInt.Div" comment="Divides the first BigInt by the second (A / B). _x000a_@param big_int_a The dividend BigInt string._x000a_@param big_int_b The divisor BigInt string._x000a_@param [use_floor] Optional boolean. TRUE for Python-style Floor division. Defaults to FALSE.">_xlfn.LAMBDA(_xlpm.big_int_a,_xlpm.big_int_b,_xlop.use_floor, INDEX(BigInt.DivMod(_xlpm.big_int_a, _xlpm.big_int_b, _xlpm.use_floor), 1, 1))</definedName>
     <definedName name="BigInt.DivMod" comment="Divides the first BigInt by the second (A / B). _x000a_Returns the quotient and modulus in rows 1 and 2, respectively._x000a_@param big_int_a The dividend BigInt string._x000a_@param big_int_b The divisor BigInt string._x000a_@param [use_floor] Optional boolean. TRUE for Python-">_xlfn.LAMBDA(_xlpm.big_int_a,_xlpm.big_int_b,_xlop.use_floor, _xlfn.LET(_xlpm.norm_a, BigInt.Norm(_xlpm.big_int_a), _xlpm.norm_b, BigInt.Norm(_xlpm.big_int_b), _xlpm.sign_a, BigInt.Sign(_xlpm.norm_a), _xlpm.sign_b, BigInt.Sign(_xlpm.norm_b), _xlpm.is_floor, IF(_xlfn.ISOMITTED(_xlpm.use_floor), FALSE, _xlpm.use_floor), IF(_xlpm.sign_b = 0, #DIV/0!, IF(_xlpm.sign_a = 0, {"0";"0"}, _xlfn.LET(_xlpm.k, core_BigInt.SafeK("DIV"), _xlpm.limbs_a, core_BigInt.Split(BigInt.Abs(_xlpm.norm_a), _xlpm.k), _xlpm.limbs_b, core_BigInt.Split(BigInt.Abs(_xlpm.norm_b), _xlpm.k), _xlpm.packed_result, core_BigInt.DivRouter(_xlpm.limbs_a, _xlpm.limbs_b, _xlpm.k), _xlpm.len_r, INDEX(_xlpm.packed_result, 1, 1), _xlpm.rem_limbs, _xlfn.CHOOSEROWS(_xlpm.packed_result, _xlfn.SEQUENCE(_xlpm.len_r, 1, 2)), _xlpm.quot_limbs, _xlfn.DROP(_xlpm.packed_result, _xlpm.len_r + 1), _xlpm.final_sign, _xlpm.sign_a * _xlpm.sign_b, _xlpm.merged_q, core_BigInt.Merge(_xlpm.quot_limbs, _xlpm.k), _xlpm.merged_r, core_BigInt.Merge(_xlpm.rem_limbs, _xlpm.k), _xlpm.trunc_q, IF(AND(_xlpm.final_sign = -1, _xlpm.merged_q &lt;&gt; "0"), "-" &amp; _xlpm.merged_q, _xlpm.merged_q), _xlpm.trunc_r, IF(AND(_xlpm.sign_a = -1, _xlpm.merged_r &lt;&gt; "0"), "-" &amp; _xlpm.merged_r, _xlpm.merged_r), _xlpm.needs_correction, AND(_xlpm.is_floor, _xlpm.final_sign = -1, _xlpm.merged_r &lt;&gt; "0"), _xlpm.final_q, IF(_xlpm.needs_correction, BigInt.Sub(_xlpm.trunc_q, "1"), _xlpm.trunc_q), _xlpm.final_r, IF(_xlpm.needs_correction, BigInt.Add(_xlpm.trunc_r, _xlpm.norm_b), _xlpm.trunc_r), _xlfn.VSTACK(_xlpm.final_q, _xlpm.final_r))))))</definedName>
-    <definedName name="BigInt.Fact" comment="Computes the factorial of a BigInt (n!)._x000a_Utilizes Legendre's formula and logarithmic tree multiplication to bypass stack/memory limits._x000a_@param big_int The BigInt string. Maximum supported input is 9273.">_xlfn.LAMBDA(_xlpm.big_int, _xlfn.LET(_xlpm.norm_n, BigInt.Norm(_xlpm.big_int), _xlpm.sign_n, BigInt.Sign(_xlpm.norm_n), IF(_xlpm.sign_n = -1, #NUM!, IF(_xlpm.norm_n = "0", "1", IF(_xlpm.norm_n = "1", "1", IF(LEN(_xlpm.norm_n) &gt; 4, #NUM!, IF(VALUE(_xlpm.norm_n) &gt; 9273, #NUM!, _xlfn.LET(_xlpm.n_val, VALUE(_xlpm.norm_n), _xlpm.primes, core_BigInt.NativePrimes(_xlpm.n_val), _xlpm.exponents, core_BigInt.NativeLegendre(_xlpm.n_val, _xlpm.primes), _xlpm.prime_powers, _xlfn.MAP(_xlpm.primes, _xlpm.exponents, _xlfn.LAMBDA(_xlpm.p,_xlpm.e, BigInt.Pow(_xlpm.p &amp; "", _xlpm.e &amp; ""))), core_BigInt.TextTreeProd(_xlpm.prime_powers)))))))))</definedName>
+    <definedName name="BigInt.Fact" comment="Computes the factorial of a BigInt (n!) using Peter Luschny's Prime Swing algorithm._x000a_@param big_int The BigInt string. Maximum supported input is 9273.">_xlfn.LAMBDA(_xlpm.big_int, _xlfn.LET(_xlpm.norm_n, BigInt.Norm(_xlpm.big_int), _xlpm.sign_n, BigInt.Sign(_xlpm.norm_n), IF(_xlpm.sign_n = -1, #NUM!, IF(_xlpm.norm_n = "0", "1", IF(_xlpm.norm_n = "1", "1", IF(LEN(_xlpm.norm_n) &gt; 4, #NUM!, IF(VALUE(_xlpm.norm_n) &gt; 9273, #NUM!, _xlfn.LET(_xlpm.n_val, VALUE(_xlpm.norm_n), _xlpm.global_primes, core_BigInt.NativePrimes(_xlpm.n_val), core_BigInt.PrimeSwingKernel(_xlpm.n_val, _xlpm.global_primes)))))))))</definedName>
     <definedName name="BigInt.IsEven" comment="Returns TRUE if the BigInt is even._x000a_@param big_int The BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, ISEVEN(VALUE(RIGHT(BigInt.Norm(_xlpm.big_int)))))</definedName>
     <definedName name="BigInt.IsNeg" comment="Returns TRUE if the BigInt is negative._x000a_@param big_int The BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, LEFT(BigInt.Norm(_xlpm.big_int)) = "-")</definedName>
     <definedName name="BigInt.IsOdd" comment="Returns TRUE if the BigInt is odd._x000a_@param big_int The BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, ISODD(VALUE(RIGHT(BigInt.Norm(_xlpm.big_int)))))</definedName>
     <definedName name="BigInt.IsZero" comment="Returns TRUE if the BigInt is exactly zero._x000a_@param big_int The BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, BigInt.Norm(_xlpm.big_int) = "0")</definedName>
+    <definedName name="BigInt.Max" comment="Returns the maximum BigInt from an array or range._x000a_@param range A contiguous range or array of BigInt strings.">_xlfn.LAMBDA(_xlpm.range, _xlfn.LET(_xlpm.clean_col, _xlfn.TOCOL(_xlpm.range, 1), IF(OR(ISERROR(_xlpm.clean_col), ROWS(_xlpm.clean_col) = 0), "0", core_BigInt.TreeCompare(_xlfn.MAP(_xlpm.clean_col, BigInt.Norm), 1))))</definedName>
+    <definedName name="BigInt.Min" comment="Returns the minimum BigInt from an array or range._x000a_@param range A contiguous range or array of BigInt strings.">_xlfn.LAMBDA(_xlpm.range, _xlfn.LET(_xlpm.clean_col, _xlfn.TOCOL(_xlpm.range, 1), IF(OR(ISERROR(_xlpm.clean_col), ROWS(_xlpm.clean_col) = 0), "0", core_BigInt.TreeCompare(_xlfn.MAP(_xlpm.clean_col, BigInt.Norm), -1))))</definedName>
     <definedName name="BigInt.Mod" comment="Computes the remainder of A / B._x000a_@param big_int_a The dividend BigInt string._x000a_@param big_int_b The divisor BigInt string._x000a_@param [use_floor] Optional boolean. TRUE for Python-style Modulo. Defaults to FALSE.">_xlfn.LAMBDA(_xlpm.big_int_a,_xlpm.big_int_b,_xlop.use_floor, INDEX(BigInt.DivMod(_xlpm.big_int_a, _xlpm.big_int_b, _xlpm.use_floor), 2, 1))</definedName>
     <definedName name="BigInt.Mul" comment="Multiplies two BigInt strings._x000a_@param big_int_a The first BigInt string._x000a_@param big_int_b The second BigInt string.">_xlfn.LAMBDA(_xlpm.big_int_a,_xlpm.big_int_b, _xlfn.LET(_xlpm.norm_a, BigInt.Norm(_xlpm.big_int_a), _xlpm.norm_b, BigInt.Norm(_xlpm.big_int_b), _xlpm.sign_a, BigInt.Sign(_xlpm.norm_a), _xlpm.sign_b, BigInt.Sign(_xlpm.norm_b), _xlpm.len_a, LEN(_xlpm.norm_a), _xlpm.len_b, LEN(_xlpm.norm_b), IF(OR(_xlpm.sign_a = 0, _xlpm.sign_b = 0), "0", IF(_xlpm.len_a + _xlpm.len_b &gt; 32766, #NUM!, _xlfn.LET(_xlpm.k, core_BigInt.SafeK("MUL", MIN(_xlpm.len_a, _xlpm.len_b)), _xlpm.limbs_a, core_BigInt.Split(BigInt.Abs(_xlpm.norm_a), _xlpm.k), _xlpm.limbs_b, core_BigInt.Split(BigInt.Abs(_xlpm.norm_b), _xlpm.k), _xlpm.final_limbs, core_BigInt.UMul(_xlpm.limbs_a, _xlpm.limbs_b, _xlpm.k), _xlpm.final_sign, _xlpm.sign_a * _xlpm.sign_b, _xlpm.merged, core_BigInt.Merge(_xlpm.final_limbs, _xlpm.k), IF(_xlpm.final_sign = -1, "-" &amp; _xlpm.merged, _xlpm.merged))))))</definedName>
     <definedName name="BigInt.Norm" comment="Normalises a BigInt string. Strips leading zeros, resolves &quot;-0&quot; to &quot;0&quot;, and throws #VALUE! on invalid characters._x000a_@param big_int The BigInt string.">_xlfn.LAMBDA(_xlpm.big_int, _xlfn.LET(_xlpm.str, IF(OR(_xlfn.ISOMITTED(_xlpm.big_int), _xlpm.big_int = ""), "0", _xlpm.big_int &amp; ""), _xlpm.is_valid, _xlfn.REGEXTEST(_xlpm.str, "^-?\d+$"), _xlpm.stripped, _xlfn.REGEXREPLACE(_xlpm.str, "^(-?)0+(?=\d)", "$1"), IF(NOT(_xlpm.is_valid), VALUE("#VALUE!"), IF(_xlpm.stripped = "-0", "0", _xlpm.stripped))))</definedName>
@@ -44,14 +46,17 @@
     <definedName name="core_BigInt.FindQuotientLimb" comment=" * [Internal] Binary search to find the highest scalar quotient limb q (0 &lt;= q &lt; 10^k)_x000a_ * such that B * q &lt;= acc. Eliminates the need for Knuth D float-estimation._x000a_ * @param acc The current remainder array._x000a_ * @param b The divisor array._x000a_ * @param k The d">_xlfn.LAMBDA(_xlpm.acc,_xlpm.b,_xlpm.k, _xlfn.LET(_xlpm.bits, _xlfn.CEILING.MATH(LOG(10 ^ _xlpm.k, 2)), _xlpm.powers, 2 ^ _xlfn.SEQUENCE(_xlpm.bits, 1, _xlpm.bits - 1, -1), _xlfn.REDUCE(0, _xlpm.powers, _xlfn.LAMBDA(_xlpm.curr_q,_xlpm.power, _xlfn.LET(_xlpm.test_q, _xlpm.curr_q + _xlpm.power, IF(_xlpm.test_q &gt;= 10 ^ _xlpm.k, _xlpm.curr_q, _xlfn.LET(_xlpm.test_prod, core_BigInt.Carry(_xlpm.b * _xlpm.test_q, _xlpm.k), _xlpm.comp, core_BigInt.UCompare(_xlpm.acc, _xlpm.test_prod), IF(_xlpm.comp &gt;= 0, _xlpm.test_q, _xlpm.curr_q))))))))</definedName>
     <definedName name="core_BigInt.KnuthDiv" comment=" * [Internal] Basecase Division via sequential shift-and-subtract._x000a_ * Returns a packed 1D array: VSTACK(Length_R, R_limbs, Q_limbs)._x000a_ * Eliminates 2D array padding to strictly preserve memory efficiency._x000a_ * @param limbs_a The dividend array._x000a_ * @param lim">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.mag_comp, core_BigInt.UCompare(_xlpm.limbs_a, _xlpm.limbs_b), IF(_xlpm.mag_comp &lt; 0, _xlfn.VSTACK(ROWS(_xlpm.limbs_a), _xlpm.limbs_a, 0), IF(_xlpm.mag_comp = 0, _xlfn.VSTACK(1, 0, 1), _xlfn.LET(_xlpm.len_a, ROWS(_xlpm.limbs_a), _xlpm.reversed_a, _xlfn.CHOOSEROWS(_xlpm.limbs_a, _xlfn.SEQUENCE(_xlpm.len_a, 1, _xlpm.len_a, -1)), _xlpm.initial_state, _xlfn.VSTACK(1, 0, 0), _xlpm.final_state, _xlfn.REDUCE(_xlpm.initial_state, _xlpm.reversed_a, _xlfn.LAMBDA(_xlpm.state,_xlpm.val, _xlfn.LET(_xlpm.len_remainder, INDEX(_xlpm.state, 1, 1), _xlpm.remainder, _xlfn.CHOOSEROWS(_xlpm.state, _xlfn.SEQUENCE(_xlpm.len_remainder, 1, 2)), _xlpm.quotient, _xlfn.DROP(_xlpm.state, _xlpm.len_remainder + 1), _xlpm.extended_remainder, IF(AND(ROWS(_xlpm.remainder) = 1, INDEX(_xlpm.remainder, 1, 1) = 0), _xlpm.val, _xlfn.VSTACK(_xlpm.val, _xlpm.remainder)), _xlpm.next_quotient_limb, core_BigInt.FindQuotientLimb(_xlpm.extended_remainder, _xlpm.limbs_b, _xlpm.k), _xlpm.prod, core_BigInt.Carry(_xlpm.limbs_b * _xlpm.next_quotient_limb, _xlpm.k), _xlpm.new_remainder, core_BigInt.USub(_xlpm.extended_remainder, _xlpm.prod, _xlpm.k), _xlpm.has_quotient, OR(ROWS(_xlpm.quotient) &gt; 1, INDEX(_xlpm.quotient, 1, 1) &gt; 0), _xlpm.next_quot, IF(_xlpm.has_quotient, _xlfn.VSTACK(_xlpm.quotient, _xlpm.next_quotient_limb), _xlpm.next_quotient_limb), _xlfn.VSTACK(ROWS(_xlpm.new_remainder), _xlpm.new_remainder, _xlpm.next_quot)))), _xlpm.len_remainder, INDEX(_xlpm.final_state, 1, 1), _xlpm.remainder, _xlfn.CHOOSEROWS(_xlpm.final_state, _xlfn.SEQUENCE(_xlpm.len_remainder, 1, 2)), _xlpm.reversed_quotient, _xlfn.DROP(_xlpm.final_state, _xlpm.len_remainder + 1), _xlpm.len_quotient, ROWS(_xlpm.reversed_quotient), _xlpm.quotient, _xlfn.CHOOSEROWS(_xlpm.reversed_quotient, _xlfn.SEQUENCE(_xlpm.len_quotient, 1, _xlpm.len_quotient, -1)), _xlfn.VSTACK(_xlpm.len_remainder, _xlpm.remainder, _xlpm.quotient))))))</definedName>
     <definedName name="core_BigInt.Merge" comment="[Internal] Concatenates an array of numeric limbs into a BigInt string, zero-padding all but the first limb._x000a_@param limbs The vertical array of numeric limbs._x000a_@param k The limb size used during calculation.">_xlfn.LAMBDA(_xlpm.limbs,_xlpm.k, _xlfn.LET(_xlpm.num_limbs, ROWS(_xlpm.limbs), _xlpm.rev_limbs, _xlfn.CHOOSEROWS(_xlpm.limbs, _xlfn.SEQUENCE(_xlpm.num_limbs, 1, _xlpm.num_limbs, -1)), IF(_xlpm.num_limbs = 1, _xlpm.rev_limbs &amp; "", _xlfn.CONCAT(_xlfn.VSTACK(_xlfn.TAKE(_xlpm.rev_limbs, 1) &amp; "", TEXT(_xlfn.DROP(_xlpm.rev_limbs, 1), REPT("0", _xlpm.k)))))))</definedName>
-    <definedName name="core_BigInt.NativeLegendre" comment="[Internal] Calculates the exponent for an array of prime numbers natively using Legendre's Formula._x000a_Evaluates purely in native C++ with zero BigInt overhead._x000a_@param n The integer factorial base (&lt;= 9273)._x000a_@param primes A vertical array of prime numbers (&lt;">_xlfn.LAMBDA(_xlpm.n,_xlpm.primes, _xlfn.MAP(_xlpm.primes, _xlfn.LAMBDA(_xlpm.p, _xlfn.LET(_xlpm.max_k, INT(LOG(_xlpm.n, _xlpm.p)), _xlpm.powers, _xlpm.p ^ _xlfn.SEQUENCE(_xlpm.max_k), SUM(INT(_xlpm.n / _xlpm.powers))))))</definedName>
     <definedName name="core_BigInt.NativePrimes" comment="[Internal] Generates a 1D vertical array of all prime numbers up to n._x000a_Evaluates purely in native C++ using a dynamic sieve._x000a_@param n The upper bound integer (assumed &lt;= 9273).">_xlfn.LAMBDA(_xlpm.n, IF(_xlpm.n &lt; 2, #NUM!, _xlfn.LET(_xlpm.seq, _xlfn.SEQUENCE(_xlpm.n - 1, 1, 2), _xlfn._xlws.FILTER(_xlpm.seq, _xlfn.MAP(_xlpm.seq, _xlfn.LAMBDA(_xlpm.x, _xlfn.LET(_xlpm.limit, INT(SQRT(_xlpm.x)), IF(_xlpm.limit &lt; 2, TRUE, MIN(MOD(_xlpm.x, _xlfn.SEQUENCE(_xlpm.limit - 1, 1, 2))) &gt; 0))))))))</definedName>
+    <definedName name="core_BigInt.NativeSwingExponents" comment="[Internal] Calculates the exponent for an array of primes in the Swing term of a factorial._x000a_@param n The current factorial magnitude (&lt;= 9273)._x000a_@param primes A vertical array of prime numbers (&lt;= n).">_xlfn.LAMBDA(_xlpm.n,_xlpm.primes, _xlfn.MAP(_xlpm.primes, _xlfn.LAMBDA(_xlpm.p, _xlfn.LET(_xlpm.max_k, INT(LOG(_xlpm.n, _xlpm.p)), _xlpm.powers, _xlpm.p ^ _xlfn.SEQUENCE(_xlpm.max_k), SUM(MOD(INT(_xlpm.n / _xlpm.powers), 2))))))</definedName>
     <definedName name="core_BigInt.NewtonRaphsonDiv" comment="[Internal] Heavyweight Newton-Raphson Division._x000a_Implements progressive scaling bounded to MAX(len_a, len_b)._x000a_@param limbs_a The dividend array._x000a_@param limbs_b The divisor array._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.len_a, ROWS(_xlpm.limbs_a), _xlpm.len_b, ROWS(_xlpm.limbs_b), _xlpm.target_len, MAX(_xlpm.len_a, _xlpm.len_b), _xlpm.r, core_BigInt.NewtonRaphsonReciprocal(_xlpm.limbs_b, _xlpm.target_len, _xlpm.k), _xlpm.drop_limbs, 2 * _xlpm.target_len, _xlpm.q_unscaled, core_BigInt.UMul(_xlpm.limbs_a, _xlpm.r, _xlpm.k), _xlpm.q_approx, IF(ROWS(_xlpm.q_unscaled) &lt;= _xlpm.drop_limbs, {0}, _xlfn.DROP(_xlpm.q_unscaled, _xlpm.drop_limbs)), _xlpm.p_baseline, core_BigInt.UMul(_xlpm.limbs_b, _xlpm.q_approx, _xlpm.k), _xlpm.initial_state, _xlfn.VSTACK(ROWS(_xlpm.q_approx), _xlpm.q_approx, _xlpm.p_baseline), _xlpm.sweep_down, _xlfn.REDUCE(_xlpm.initial_state, {1;2}, _xlfn.LAMBDA(_xlpm.state,_xlpm.i, _xlfn.LET(_xlpm.len_q, INDEX(_xlpm.state, 1, 1), _xlpm.curr_q, _xlfn.CHOOSEROWS(_xlpm.state, _xlfn.SEQUENCE(_xlpm.len_q, 1, 2)), _xlpm.curr_p, _xlfn.DROP(_xlpm.state, _xlpm.len_q + 1), IF(core_BigInt.UCompare(_xlpm.curr_p, _xlpm.limbs_a) &gt; 0, _xlfn.LET(_xlpm.next_q, core_BigInt.USub(_xlpm.curr_q, {1}, _xlpm.k), _xlpm.next_p, core_BigInt.USub(_xlpm.curr_p, _xlpm.limbs_b, _xlpm.k), _xlfn.VSTACK(ROWS(_xlpm.next_q), _xlpm.next_q, _xlpm.next_p)), _xlpm.state)))), _xlpm.sweep_up, _xlfn.REDUCE(_xlpm.sweep_down, {1;2}, _xlfn.LAMBDA(_xlpm.state,_xlpm.i, _xlfn.LET(_xlpm.len_q, INDEX(_xlpm.state, 1, 1), _xlpm.curr_q, _xlfn.CHOOSEROWS(_xlpm.state, _xlfn.SEQUENCE(_xlpm.len_q, 1, 2)), _xlpm.curr_p, _xlfn.DROP(_xlpm.state, _xlpm.len_q + 1), _xlpm.next_p_test, core_BigInt.UAdd(_xlpm.curr_p, _xlpm.limbs_b, _xlpm.k), IF(core_BigInt.UCompare(_xlpm.next_p_test, _xlpm.limbs_a) &lt;= 0, _xlfn.LET(_xlpm.next_q, core_BigInt.UAdd(_xlpm.curr_q, {1}, _xlpm.k), _xlfn.VSTACK(ROWS(_xlpm.next_q), _xlpm.next_q, _xlpm.next_p_test)), _xlpm.state)))), _xlpm.final_len_q, INDEX(_xlpm.sweep_up, 1, 1), _xlpm.final_q, _xlfn.CHOOSEROWS(_xlpm.sweep_up, _xlfn.SEQUENCE(_xlpm.final_len_q, 1, 2)), _xlpm.final_p, _xlfn.DROP(_xlpm.sweep_up, _xlpm.final_len_q + 1), _xlpm.final_r, core_BigInt.USub(_xlpm.limbs_a, _xlpm.final_p, _xlpm.k), _xlfn.VSTACK(ROWS(_xlpm.final_r), _xlpm.final_r, _xlpm.final_q)))</definedName>
     <definedName name="core_BigInt.NewtonRaphsonReciprocal" comment="[Internal] Computes the Reciprocal progressively scaling up to the Dividend's precision._x000a_@param limbs_b The divisor limb array._x000a_@param target_len The limb-length of Dividend A._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.limbs_b,_xlpm.target_len,_xlpm.k, _xlfn.LET(_xlpm.len_b, ROWS(_xlpm.limbs_b), _xlpm.seed_len, MIN(3, _xlpm.len_b), _xlpm.r_seed_limbs, core_BigInt.NewtonRaphsonSeed(_xlpm.limbs_b, _xlpm.k), _xlpm.initial_state, _xlfn.VSTACK(_xlpm.seed_len, _xlpm.r_seed_limbs), _xlpm.req_iters, MAX(0, _xlfn.CEILING.MATH(LN(_xlpm.target_len / _xlpm.seed_len) / LN(2))) + 1, IF(_xlpm.req_iters = 0, _xlpm.r_seed_limbs, _xlfn.LET(_xlpm.iterations, _xlfn.SEQUENCE(_xlpm.req_iters), _xlpm.final_state, _xlfn.REDUCE(_xlpm.initial_state, _xlpm.iterations, _xlfn.LAMBDA(_xlpm.state,_xlpm.iter, _xlfn.LET(_xlpm.curr_len, INDEX(_xlpm.state, 1, 1), _xlpm.curr_r, _xlfn.DROP(_xlpm.state, 1), _xlpm.next_len, MIN(_xlpm.curr_len * 2, _xlpm.target_len), _xlpm.active_curr, MIN(_xlpm.curr_len, _xlpm.len_b), _xlpm.active_next, MIN(_xlpm.next_len, _xlpm.len_b), _xlpm.shift_limbs, 2 * (_xlpm.next_len - _xlpm.curr_len) - (_xlpm.active_next - _xlpm.active_curr), _xlpm.r_prime, IF(_xlpm.shift_limbs &gt; 0, _xlfn.VSTACK(_xlfn.EXPAND(0, _xlpm.shift_limbs, , 0), _xlpm.curr_r), _xlpm.curr_r), _xlpm.b_active, _xlfn.TAKE(_xlpm.limbs_b, -_xlpm.active_next), _xlpm.p, core_BigInt.UMul(_xlpm.b_active, _xlpm.r_prime, _xlpm.k), _xlpm.two_beta, _xlfn.VSTACK(_xlfn.EXPAND(0, 2 * _xlpm.next_len, , 0), 2), _xlpm.err, core_BigInt.USub(_xlpm.two_beta, _xlpm.p, _xlpm.k), _xlpm.next_r_unscaled, core_BigInt.UMul(_xlpm.r_prime, _xlpm.err, _xlpm.k), _xlpm.next_r, IF(ROWS(_xlpm.next_r_unscaled) &lt;= 2 * _xlpm.next_len, {0}, _xlfn.DROP(_xlpm.next_r_unscaled, 2 * _xlpm.next_len)), _xlfn.VSTACK(_xlpm.next_len, _xlpm.next_r)))), _xlfn.DROP(_xlpm.final_state, 1)))))</definedName>
     <definedName name="core_BigInt.NewtonRaphsonSeed" comment="[Internal] Generates the exact reciprocal seed for Newton-Raphson Division using Knuth Basecase._x000a_Extracts up to the top 3 limbs of B and calculates floor(Beta^(2*len) / B_top)._x000a_@param limbs_b The divisor limb array._x000a_@param k The dynamic chunk size context">_xlfn.LAMBDA(_xlpm.limbs_b,_xlpm.k, _xlfn.LET(_xlpm.len_b, ROWS(_xlpm.limbs_b), _xlpm.seed_len, MIN(3, _xlpm.len_b), _xlpm.b_top, _xlfn.TAKE(_xlpm.limbs_b, -_xlpm.seed_len), _xlpm.beta_2m, _xlfn.VSTACK(_xlfn.EXPAND(0, 2 * _xlpm.seed_len, , 0), 1), _xlpm.packed, core_BigInt.KnuthDiv(_xlpm.beta_2m, _xlpm.b_top, _xlpm.k), _xlpm.len_r, INDEX(_xlpm.packed, 1, 1), _xlfn.DROP(_xlpm.packed, _xlpm.len_r + 1)))</definedName>
+    <definedName name="core_BigInt.PrimeSwingKernel" comment="[Internal] Recursive top-down LAMBDA calculating the Prime Swing factorial._x000a_@param n The current factorial magnitude._x000a_@param global_primes The unified vertical array of all primes up to the target factorial.">_xlfn.LAMBDA(_xlpm.n,_xlpm.global_primes, IF(_xlpm.n &lt; 2, "1", _xlfn.LET(_xlpm.half_n, INT(_xlpm.n / 2), _xlpm.half_fact, core_BigInt.PrimeSwingKernel(_xlpm.half_n, _xlpm.global_primes), _xlpm.squared_half, core_BigInt.UTextMul(_xlpm.half_fact, _xlpm.half_fact), _xlpm.tier_primes, _xlfn._xlws.FILTER(_xlpm.global_primes, _xlpm.global_primes &lt;= _xlpm.n), _xlpm.swing, core_BigInt.SwingTerm(_xlpm.n, _xlpm.tier_primes), core_BigInt.UTextMul(_xlpm.squared_half, _xlpm.swing))))</definedName>
     <definedName name="core_BigInt.SafeK" comment="[Internal] Computes the maximum safe base-10 limb size (k) to avoid IEEE-754 precision loss._x000a_@param operation: &quot;ADD&quot;, &quot;MUL&quot;, or &quot;DIV&quot;._x000a_@param [max_items] ADD: number of operands. MUL: shortest string digits count.">_xlfn.LAMBDA(_xlpm.operation,_xlop.max_items, _xlfn.LET(_xlpm.items, IF(OR(_xlpm.max_items = "", _xlfn.ISOMITTED(_xlpm.max_items)), 2, MAX(2, _xlpm.max_items)), _xlfn.SWITCH(_xlpm.operation, "ADD", 15 - LEN(_xlpm.items), "MUL", _xlfn.LET(_xlpm.test_k, {7;6;5;4;3;2;1}, _xlpm.max_overlap, ROUNDUP(_xlpm.items / _xlpm.test_k, 0), _xlpm.uncarried_max, _xlpm.max_overlap * (10 ^ _xlpm.test_k - 1) ^ 2, _xlpm.max_carry, INT(_xlpm.uncarried_max / 10 ^ _xlpm.test_k), _xlpm.peak_val, _xlpm.uncarried_max + _xlpm.max_carry, MAX(_xlfn._xlws.FILTER(_xlpm.test_k, _xlpm.peak_val &lt;= (10 ^ 15 - 1)))), "DIV", 7, #NAME?)))</definedName>
     <definedName name="core_BigInt.Split" comment="[Internal] Unified Splitter. Splits both scalars and arrays into Little-Endian limbs._x000a_Uses MAX() to guarantee scalar inputs to the SEQUENCE engine._x000a_@param big_ints The string or array of strings._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.big_ints,_xlpm.k, _xlfn.LET(_xlpm.big_int_row, _xlfn.TOROW(_xlpm.big_ints), _xlpm.lengths, LEN(_xlpm.big_int_row), _xlpm.max_len, MAX(_xlpm.lengths), _xlpm.pad_len, ROUNDUP(_xlpm.max_len / _xlpm.k, 0) * _xlpm.k, _xlpm.padded, REPT("0", _xlpm.pad_len - _xlpm.lengths) &amp; _xlpm.big_int_row, _xlpm.starts, _xlfn.SEQUENCE(_xlpm.pad_len / _xlpm.k, 1, _xlpm.pad_len - _xlpm.k + 1, -_xlpm.k), --MID(_xlpm.padded, _xlpm.starts, _xlpm.k)))</definedName>
+    <definedName name="core_BigInt.SwingTerm" comment="[Internal] Calculates the massive BigInt string for the Swing term of a factorial._x000a_@param n The current factorial magnitude._x000a_@param tier_primes A vertical array of prime numbers (&lt;= n).">_xlfn.LAMBDA(_xlpm.n,_xlpm.tier_primes, _xlfn.LET(_xlpm.exponents, core_BigInt.NativeSwingExponents(_xlpm.n, _xlpm.tier_primes), _xlpm.is_greater_than_zero, _xlpm.exponents &gt; 0, IF(AND(NOT(_xlpm.is_greater_than_zero)), "1", _xlfn.LET(_xlpm.filtered_primes, _xlfn._xlws.FILTER(_xlpm.tier_primes, _xlpm.is_greater_than_zero), _xlpm.filtered_exps, _xlfn._xlws.FILTER(_xlpm.exponents, _xlpm.is_greater_than_zero), _xlpm.prime_powers, _xlfn.MAP(_xlpm.filtered_primes, _xlpm.filtered_exps, _xlfn.LAMBDA(_xlpm.p,_xlpm.e, IF(_xlpm.e = 1, _xlpm.p &amp; "", BigInt.Pow(_xlpm.p &amp; "", _xlpm.e &amp; "")))), core_BigInt.TextTreeProd(_xlpm.prime_powers)))))</definedName>
     <definedName name="core_BigInt.TextTreeProd" comment="[Internal] Vectorized logarithmic product of an array of BigInt strings._x000a_Recursively cuts the array in half to bypass REDUCE sequential memory allocations._x000a_@param text_arr A 1D vertical array of BigInt strings.">_xlfn.LAMBDA(_xlpm.text_arr, _xlfn.LET(_xlpm.n, ROWS(_xlpm.text_arr), IF(_xlpm.n = 1, INDEX(_xlpm.text_arr, 1, 1), _xlfn.LET(_xlpm.paired, _xlfn.WRAPROWS(_xlpm.text_arr, 2, "1"), _xlpm.next_arr, _xlfn.BYROW(_xlpm.paired, _xlfn.LAMBDA(_xlpm.row, core_BigInt.UTextMul(INDEX(_xlpm.row, 1, 1), INDEX(_xlpm.row, 1, 2)))), core_BigInt.TextTreeProd(_xlpm.next_arr)))))</definedName>
+    <definedName name="core_BigInt.TreeCompare" comment="[Internal] Recursive tournament tree for Min/Max evaluations._x000a_@param col A 1D vertical array of normalized BigInt strings._x000a_@param mode 1 for Maximum, -1 for Minimum.">_xlfn.LAMBDA(_xlpm.col,_xlpm.mode, _xlfn.LET(_xlpm.n, ROWS(_xlpm.col), IF(_xlpm.n = 1, INDEX(_xlpm.col, 1, 1), _xlfn.LET(_xlpm.paired, _xlfn.WRAPROWS(_xlpm.col, 2, "#PAD#"), _xlpm.col_a, _xlfn.TAKE(_xlpm.paired, , 1), _xlpm.col_b, _xlfn.TAKE(_xlpm.paired, , -1), _xlpm.winners, _xlfn.MAP(_xlpm.col_a, _xlpm.col_b, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, IF(_xlpm.b = "#PAD#", _xlpm.a, _xlfn.LET(_xlpm.comp, BigInt.Compare(_xlpm.a, _xlpm.b), IF(_xlpm.comp * _xlpm.mode &gt;= 0, _xlpm.a, _xlpm.b))))), core_BigInt.TreeCompare(_xlpm.winners, _xlpm.mode)))))</definedName>
     <definedName name="core_BigInt.UAdd" comment="[Internal] Unsigned addition of two Little-Endian limb arrays._x000a_@param limbs_a The first limb array._x000a_@param limbs_b The second limb array._x000a_@param k The dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.a,_xlpm.b,_xlpm.k, _xlfn.LET(_xlpm.max_rows, MAX(ROWS(_xlpm.a), ROWS(_xlpm.b)), _xlpm.pad_a, _xlfn.EXPAND(_xlpm.a, _xlpm.max_rows, 1, 0), _xlpm.pad_b, _xlfn.EXPAND(_xlpm.b, _xlpm.max_rows, 1, 0), core_BigInt.Carry(_xlpm.pad_a + _xlpm.pad_b, _xlpm.k)))</definedName>
     <definedName name="core_BigInt.UCompare" comment="[Internal] Unsigned comparison of two Little-Endian limb arrays._x000a_Returns 1 (a &gt; b), -1 (a &lt; b), or 0 (a = b)._x000a_@param limbs_a The first limb array._x000a_@param limbs_b The second limb array.">_xlfn.LAMBDA(_xlpm.limbs_a,_xlpm.limbs_b, _xlfn.LET(_xlpm.max_rows, MAX(ROWS(_xlpm.limbs_a), ROWS(_xlpm.limbs_b)), _xlpm.pad_a, _xlfn.EXPAND(_xlpm.limbs_a, _xlpm.max_rows, 1, 0), _xlpm.pad_b, _xlfn.EXPAND(_xlpm.limbs_b, _xlpm.max_rows, 1, 0), _xlpm.diff, _xlpm.pad_a - _xlpm.pad_b, _xlpm.msd_idx, _xlfn.XMATCH(TRUE, _xlpm.diff &lt;&gt; 0, 0, -1), IF(ISNA(_xlpm.msd_idx), 0, SIGN(INDEX(_xlpm.diff, _xlpm.msd_idx, 1)))))</definedName>
     <definedName name="core_BigInt.UMatrixSum" comment="[Internal] Vectorized matrix sum of unsigned BigInt strings._x000a_@param ubig_int Horizontal array (1xN) of normalized magnitude strings._x000a_@param k The unified dynamic chunk size context.">_xlfn.LAMBDA(_xlpm.ubig_ints,_xlpm.k, _xlfn.LET(_xlpm.grid, core_BigInt.Split(_xlpm.ubig_ints, _xlpm.k), _xlpm.raw_limbs, _xlfn.BYROW(_xlpm.grid, _xleta.SUM), core_BigInt.Carry(_xlpm.raw_limbs, _xlpm.k)))</definedName>
@@ -64,6 +69,8 @@
     <definedName name="test_BigInt.DivisionAlgorithmComparison" comment="Executes a strictly sequential benchmark suite to avoid multi-threading contamination._x000a_@param test_cases An N x 2 array of test lengths: [Length_A, Length_B]_x000a_@param iters Number of iterations per benchmark to smooth NOW() resolution.">_xlfn.LAMBDA(_xlpm.test_cases,_xlpm.iters,_xlpm.repeats, _xlfn.LET(_xlpm.n_tests, ROWS(_xlpm.test_cases), _xlpm.initial, {"Len_A","Len_B","Knuth_ms","NR_ms"}, _xlfn.REDUCE(_xlpm.initial, _xlfn.SEQUENCE(_xlpm.n_tests), _xlfn.LAMBDA(_xlpm.acc,_xlpm.i, _xlfn.LET(_xlpm.len_a, INDEX(_xlpm.test_cases, _xlpm.i, 1), _xlpm.len_b, INDEX(_xlpm.test_cases, _xlpm.i, 2), IF(_xlpm.len_b &gt; _xlpm.len_a, _xlpm.acc, _xlfn.LET(_xlpm.str_a, REPT("9", _xlpm.len_a), _xlpm.str_b, IF(_xlpm.len_b = 1, "7", "7" &amp; REPT("3", _xlpm.len_b - 1)), _xlpm.time_k, test_BigInt.DivisionAlgorithms(_xlpm.str_a, _xlpm.str_b, "KNUTH", _xlpm.iters, _xlpm.repeats), _xlpm.time_nr, test_BigInt.DivisionAlgorithms(_xlpm.str_a, _xlpm.str_b, "NR", _xlpm.iters, _xlpm.repeats), _xlfn.VSTACK(_xlpm.acc, _xlfn.HSTACK(_xlpm.len_a, _xlpm.len_b, _xlpm.time_k, _xlpm.time_nr)))))))))</definedName>
     <definedName name="test_BigInt.DivisionAlgorithms" comment="@param a The dividend string_x000a_@param b The divisor string_x000a_@param mode &quot;KNUTH&quot; or &quot;NR&quot;_x000a_@param iters Inner loop count (to defeat chunky clock resolution)_x000a_@param repeats Outer loop count (to defeat OS/Garbage Collection noise)">_xlfn.LAMBDA(_xlpm.a,_xlpm.b,_xlpm.mode,_xlpm.iters,_xlpm.repeats, _xlfn.LET(_xlpm.batch_times, _xlfn.MAP(_xlfn.SEQUENCE(_xlpm.repeats), _xlfn.LAMBDA(_xlpm.r, _xlfn.LET(_xlpm.start, NOW(), _xlpm.run, IF(_xlpm.mode = "KNUTH", _xlfn.MAP(_xlfn.SEQUENCE(_xlpm.iters), _xlfn.LAMBDA(_xlpm.i, test_BigInt.KnuthDivision(_xlpm.a, _xlpm.b))), _xlfn.MAP(_xlfn.SEQUENCE(_xlpm.iters), _xlfn.LAMBDA(_xlpm.i, test_BigInt.NewtonRaphsonDivision(_xlpm.a, _xlpm.b)))), _xlpm.stop, NOW() + (0 * LEN(INDEX(_xlpm.run, 1, 1))), (_xlpm.stop - _xlpm.start) * 86400000))), MIN(_xlpm.batch_times) / _xlpm.iters))</definedName>
     <definedName name="test_BigInt.DivisionBenchmarkCases">_xlfn.LAMBDA(_xlpm.start_len,_xlpm.max_len,_xlpm.step, _xlfn.LET(_xlpm.seq, _xlfn.SEQUENCE((_xlpm.max_len - _xlpm.start_len) / _xlpm.step + 1, 1, _xlpm.start_len, _xlpm.step), _xlpm.n, ROWS(_xlpm.seq), _xlpm.col_a, _xlfn.TOCOL(IF(_xlfn.SEQUENCE(1, _xlpm.n), _xlpm.seq)), _xlpm.col_b, _xlfn.TOCOL(IF(_xlfn.SEQUENCE(_xlpm.n, 1), _xlfn.TOROW(_xlpm.seq))), _xlfn.HSTACK(_xlpm.col_a, _xlpm.col_b)))</definedName>
+    <definedName name="test_BigInt.FactorialAlgorithms">_xlfn.LAMBDA(_xlpm.input,_xlpm.mode,_xlpm.iters,_xlpm.repeats, _xlfn.LET(_xlpm.batch_times, _xlfn.MAP(_xlfn.SEQUENCE(_xlpm.repeats), _xlfn.LAMBDA(_xlpm.r, _xlfn.LET(_xlpm.start, NOW(), _xlpm.run, IF(_xlpm.mode = "Legendre", _xlfn.MAP(_xlfn.SEQUENCE(_xlpm.iters), _xlfn.LAMBDA(_xlpm.i, BigInt.Fact(_xlpm.input))), _xlfn.MAP(_xlfn.SEQUENCE(_xlpm.iters), _xlfn.LAMBDA(_xlpm.i, BigInt.FactSwing(_xlpm.input)))), _xlpm.stop, NOW() + (0 * LEN(INDEX(_xlpm.run, 1, 1))), (_xlpm.stop - _xlpm.start) * 86400000))), MIN(_xlpm.batch_times) / _xlpm.iters))</definedName>
+    <definedName name="test_BigInt.FactorialComparison" comment="Executes a strictly sequential benchmark suite to avoid multi-threading contamination._x000a_@param test_cases An N x 1 array of test inputs_x000a_@param iters Number of iterations per sample to smooth NOW() resolution._x000a_@param repeats Number of iterations per benchma">_xlfn.LAMBDA(_xlpm.test_cases,_xlpm.iters,_xlpm.repeats, _xlfn.LET(_xlpm.n_tests, ROWS(_xlpm.test_cases), _xlpm.initial, {"N","Legendre","Swing"}, _xlfn.REDUCE(_xlpm.initial, _xlfn.SEQUENCE(_xlpm.n_tests), _xlfn.LAMBDA(_xlpm.acc,_xlpm.i, _xlfn.LET(_xlpm.input, INDEX(_xlpm.test_cases, _xlpm.i, 1), _xlpm.time_legendre, test_BigInt.FactorialAlgorithms(_xlpm.input, "Legendre", _xlpm.iters, _xlpm.repeats), _xlpm.time_swing, test_BigInt.FactorialAlgorithms(_xlpm.input, "Swing", _xlpm.iters, _xlpm.repeats), _xlfn.VSTACK(_xlpm.acc, _xlfn.HSTACK(_xlpm.input, _xlpm.time_legendre, _xlpm.time_swing)))))))</definedName>
     <definedName name="test_BigInt.KnuthDivision">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, _xlfn.LET(_xlpm.k, core_BigInt.SafeK("DIV"), _xlpm.packed, core_BigInt.KnuthDiv(core_BigInt.Split(_xlpm.a, _xlpm.k), core_BigInt.Split(_xlpm.b, _xlpm.k), _xlpm.k), core_BigInt.Merge(_xlfn.DROP(_xlpm.packed, INDEX(_xlpm.packed, 1, 1) + 1), _xlpm.k)))</definedName>
     <definedName name="test_BigInt.NewtonRaphsonDivision">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, _xlfn.LET(_xlpm.k, core_BigInt.SafeK("DIV"), _xlpm.packed, core_BigInt.NewtonRaphsonDiv(core_BigInt.Split(_xlpm.a, _xlpm.k), core_BigInt.Split(_xlpm.b, _xlpm.k), _xlpm.k), core_BigInt.Merge(_xlfn.DROP(_xlpm.packed, INDEX(_xlpm.packed, 1, 1) + 1), _xlpm.k)))</definedName>
   </definedNames>
@@ -143,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="658">
   <si>
     <t>12345</t>
   </si>
@@ -7240,39 +7247,17 @@
     </r>
   </si>
   <si>
-    <t>Smallest boundary</t>
-  </si>
-  <si>
     <t>core_BigInt.NativePrimes</t>
-  </si>
-  <si>
-    <t>{8;4;2;1}</t>
-  </si>
-  <si>
-    <t>{3;1;1}</t>
   </si>
   <si>
     <t>n=10
 primes={2; 3; 5; 7}</t>
   </si>
   <si>
-    <t>n=2
-primes={2}</t>
-  </si>
-  <si>
     <t>n=5
 primes={2; 3; 5}</t>
   </si>
   <si>
-    <t>Larger multi-power sequence (10! = 2^8 × 3^4 × 5^2 × 7^1)</t>
-  </si>
-  <si>
-    <t>Standard small boundary (5! = 2^3 × 3^1 × 5^1)</t>
-  </si>
-  <si>
-    <t>core_BigInt.NativeLegendre</t>
-  </si>
-  <si>
     <t>core_BigInt.TextTreeProd</t>
   </si>
   <si>
@@ -7516,6 +7501,381 @@
   </si>
   <si>
     <t>BigInt.Fact</t>
+  </si>
+  <si>
+    <t>Standard small boundary</t>
+  </si>
+  <si>
+    <t>Even and zero exponents ($10!$ swing term excludes 3)</t>
+  </si>
+  <si>
+    <t>core_BigInt.NativeSwingExponents</t>
+  </si>
+  <si>
+    <t>{1;1;1}</t>
+  </si>
+  <si>
+    <t>{2;2;0;1}</t>
+  </si>
+  <si>
+    <t>Standard evaluation</t>
+  </si>
+  <si>
+    <t>Multi-tier evaluation</t>
+  </si>
+  <si>
+    <t>n=5
+global_primes={2; 3; 5}</t>
+  </si>
+  <si>
+    <t>n=10
+global_primes={2; 3; 5; 7}</t>
+  </si>
+  <si>
+    <t>core_BigInt.PrimeSwingKernel</t>
+  </si>
+  <si>
+    <t>core_BigInt.TreeCompare</t>
+  </si>
+  <si>
+    <t>range={42}
+mode=1</t>
+  </si>
+  <si>
+    <t>-10</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>range={10;20;5;30}
+mode=1</t>
+  </si>
+  <si>
+    <t>range={10;20;5;30}
+mode=-1</t>
+  </si>
+  <si>
+    <t>range={10;20;30}
+mode=1</t>
+  </si>
+  <si>
+    <t>range={10;20;30}
+mode=-1</t>
+  </si>
+  <si>
+    <t>range={-10;0;10}
+mode=-1</t>
+  </si>
+  <si>
+    <t>range={5;5;5}
+mode=1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Max:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Even length array (perfect halving)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Min:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Even length array (perfect halving)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Max:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Odd length array (tests #PAD# sentinel short-circuit)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Min:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Odd length array (tests #PAD# sentinel short-circuit)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Min: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mixed signs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Max:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tie values</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Edge:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Single element array (Recursion base case $N=1$)</t>
+    </r>
+  </si>
+  <si>
+    <t>range={""}</t>
+  </si>
+  <si>
+    <t>BigInt.Max</t>
+  </si>
+  <si>
+    <t>range={10,20,5}</t>
+  </si>
+  <si>
+    <t>range={007,8,09}</t>
+  </si>
+  <si>
+    <t>range={10,abc}</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>range={-0}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Delegates to TreeCompare successfully</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Boundary: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Normalizes leading zeros before comparison</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Error:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Invalid character triggers Norm fail-fast</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Edge: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>negative zero coerced to zero</t>
+    </r>
+  </si>
+  <si>
+    <t>BigInt.Min</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Edge:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Empty array fallback (intercepted before engine)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -7705,7 +8065,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -7752,22 +8112,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Input" xfId="1" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="297">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="452">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -8330,6 +8680,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -8340,63 +8700,1266 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <color rgb="FF9C0006"/>
       </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color theme="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -8434,13 +9997,6 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -8459,16 +10015,118 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -8496,6 +10154,108 @@
           <color theme="1"/>
         </top>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -10315,12 +12075,12 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7798C9D4-D9A3-414B-919E-1762A05E858C}" name="Norm_Tests" displayName="Norm_Tests" ref="A7:E26" totalsRowCount="1">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2D415719-D29C-4B5B-8EEC-D6B547CA5D0E}" name="input" dataDxfId="296"/>
+    <tableColumn id="1" xr3:uid="{2D415719-D29C-4B5B-8EEC-D6B547CA5D0E}" name="input" dataDxfId="451"/>
     <tableColumn id="3" xr3:uid="{0ACC712F-EB7B-43DA-9965-8A4957A95DA2}" name="expected"/>
-    <tableColumn id="2" xr3:uid="{25F1E681-6FC0-4609-BF1F-1FF79BEB3CD8}" name="output" dataDxfId="295">
+    <tableColumn id="2" xr3:uid="{25F1E681-6FC0-4609-BF1F-1FF79BEB3CD8}" name="output" dataDxfId="450">
       <calculatedColumnFormula array="1">internal.xlInt.Norm(Norm_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{20432306-08A1-43B4-9B37-03610B79D73B}" name="passing" totalsRowFunction="custom" dataDxfId="294">
+    <tableColumn id="4" xr3:uid="{20432306-08A1-43B4-9B37-03610B79D73B}" name="passing" totalsRowFunction="custom" dataDxfId="449">
       <calculatedColumnFormula>IF(ISERROR(Norm_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Norm_Tests[[#This Row],[expected]]) = ERROR.TYPE(Norm_Tests[[#This Row],[output]]),
     Norm_Tests[[#This Row],[expected]] = Norm_Tests[[#This Row],[output]]
@@ -10334,11 +12094,11 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DCEBF05F-998F-47D8-A8F8-63C4E2771074}" name="UCompare_Tests" displayName="UCompare_Tests" ref="A127:E135" totalsRowCount="1" dataDxfId="255">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DCEBF05F-998F-47D8-A8F8-63C4E2771074}" name="UCompare_Tests" displayName="UCompare_Tests" ref="A127:E135" totalsRowCount="1" dataDxfId="410">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3554FEAC-3E95-4439-BF1F-B262B64D139D}" name="input" dataDxfId="254"/>
-    <tableColumn id="2" xr3:uid="{0EA61E63-F894-4F39-983A-67C6CDEA4B1D}" name="expected" dataDxfId="253"/>
-    <tableColumn id="3" xr3:uid="{B6F49B44-504D-4599-9F1E-49B98046B44D}" name="output" dataDxfId="252">
+    <tableColumn id="1" xr3:uid="{3554FEAC-3E95-4439-BF1F-B262B64D139D}" name="input" dataDxfId="409"/>
+    <tableColumn id="2" xr3:uid="{0EA61E63-F894-4F39-983A-67C6CDEA4B1D}" name="expected" dataDxfId="408"/>
+    <tableColumn id="3" xr3:uid="{B6F49B44-504D-4599-9F1E-49B98046B44D}" name="output" dataDxfId="407">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(UCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -10348,46 +12108,46 @@
     internal.xlInt.UCompare(_xlpm.limbs_a, _xlpm.limbs_b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{96B8A7F0-899C-4301-95D3-41FB0BA096A7}" name="passing" totalsRowFunction="custom" dataDxfId="251">
+    <tableColumn id="4" xr3:uid="{96B8A7F0-899C-4301-95D3-41FB0BA096A7}" name="passing" totalsRowFunction="custom" dataDxfId="406">
       <calculatedColumnFormula>IF(ISERROR(UCompare_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(UCompare_Tests[[#This Row],[output]]),
     UCompare_Tests[[#This Row],[expected]] = UCompare_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UCompare_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C5539D24-4ADC-4D77-B82F-27DAF4B3F109}" name="test" dataDxfId="250"/>
+    <tableColumn id="5" xr3:uid="{C5539D24-4ADC-4D77-B82F-27DAF4B3F109}" name="test" dataDxfId="405"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5E817537-E6E9-4069-8E14-531A3E42821F}" name="Internal_Sign_Tests" displayName="Internal_Sign_Tests" ref="A49:E60" totalsRowCount="1" tableBorderDxfId="249">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5E817537-E6E9-4069-8E14-531A3E42821F}" name="Internal_Sign_Tests" displayName="Internal_Sign_Tests" ref="A49:E60" totalsRowCount="1" tableBorderDxfId="404">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{C5C6E024-5D15-4650-BC06-AE3A9A4A3F9E}" name="input"/>
     <tableColumn id="2" xr3:uid="{2E349FE8-D8E4-4ABE-B47E-F0985AA6C672}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{49844921-4B71-4B13-957C-917C2841A9A3}" name="output" dataDxfId="248">
+    <tableColumn id="3" xr3:uid="{49844921-4B71-4B13-957C-917C2841A9A3}" name="output" dataDxfId="403">
       <calculatedColumnFormula array="1">xlInt.Sign(Internal_Sign_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0236DB85-60E5-4DC6-9655-C6D58A63C8D4}" name="passing" totalsRowFunction="custom" dataDxfId="247">
+    <tableColumn id="4" xr3:uid="{0236DB85-60E5-4DC6-9655-C6D58A63C8D4}" name="passing" totalsRowFunction="custom" dataDxfId="402">
       <calculatedColumnFormula>IF(ISERROR(Internal_Sign_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Internal_Sign_Tests[[#This Row],[expected]]) = ERROR.TYPE(Internal_Sign_Tests[[#This Row],[output]]),
     Internal_Sign_Tests[[#This Row],[expected]] = Internal_Sign_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Internal_Sign_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{396092C1-DC4F-4532-BB59-E0E779D9A525}" name="test" dataDxfId="246"/>
+    <tableColumn id="5" xr3:uid="{396092C1-DC4F-4532-BB59-E0E779D9A525}" name="test" dataDxfId="401"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1BF11AA1-9F01-403A-A5A2-CDAF85E5F9D0}" name="USub_Tests" displayName="USub_Tests" ref="A138:E146" totalsRowCount="1" dataDxfId="245">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1BF11AA1-9F01-403A-A5A2-CDAF85E5F9D0}" name="USub_Tests" displayName="USub_Tests" ref="A138:E146" totalsRowCount="1" dataDxfId="400">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5B979D84-AD0F-45AF-AB26-6C75CA981E58}" name="input" dataDxfId="244"/>
-    <tableColumn id="2" xr3:uid="{D8895FB5-11F4-4379-9B45-0D72ADA71E57}" name="expected" dataDxfId="243"/>
-    <tableColumn id="3" xr3:uid="{A4DDD8AE-0CC0-457E-A08D-2C94591CF878}" name="output" dataDxfId="242">
+    <tableColumn id="1" xr3:uid="{5B979D84-AD0F-45AF-AB26-6C75CA981E58}" name="input" dataDxfId="399"/>
+    <tableColumn id="2" xr3:uid="{D8895FB5-11F4-4379-9B45-0D72ADA71E57}" name="expected" dataDxfId="398"/>
+    <tableColumn id="3" xr3:uid="{A4DDD8AE-0CC0-457E-A08D-2C94591CF878}" name="output" dataDxfId="397">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(USub_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -10399,25 +12159,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BF616718-1C7F-4627-B496-8B6339CC2735}" name="passing" totalsRowFunction="custom" dataDxfId="241">
+    <tableColumn id="4" xr3:uid="{BF616718-1C7F-4627-B496-8B6339CC2735}" name="passing" totalsRowFunction="custom" dataDxfId="396">
       <calculatedColumnFormula>IF(ISERROR(USub_Tests[[#This Row],[expected]]),
     ERROR.TYPE(USub_Tests[[#This Row],[expected]]) = ERROR.TYPE(USub_Tests[[#This Row],[output]]),
     USub_Tests[[#This Row],[expected]] = USub_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(USub_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FCF52C7D-4E82-4BAA-8C93-974211CAC2AF}" name="test" dataDxfId="240"/>
+    <tableColumn id="5" xr3:uid="{FCF52C7D-4E82-4BAA-8C93-974211CAC2AF}" name="test" dataDxfId="395"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B5433254-33A6-4D35-8484-91940B628217}" name="Table6" displayName="Table6" ref="A149:E160" totalsRowCount="1" dataDxfId="239">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B5433254-33A6-4D35-8484-91940B628217}" name="Table6" displayName="Table6" ref="A149:E160" totalsRowCount="1" dataDxfId="394">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D52F6D10-66CD-4765-927A-94A578D3C30A}" name="input" dataDxfId="238" totalsRowDxfId="237"/>
-    <tableColumn id="2" xr3:uid="{DF2BEEE3-E1EF-4EA0-A6A8-77B06FB5C3EE}" name="expected" dataDxfId="236"/>
-    <tableColumn id="3" xr3:uid="{4FDE8849-AFE2-471E-8131-C5B45620EBDC}" name="output" dataDxfId="235">
+    <tableColumn id="1" xr3:uid="{D52F6D10-66CD-4765-927A-94A578D3C30A}" name="input" dataDxfId="393" totalsRowDxfId="392"/>
+    <tableColumn id="2" xr3:uid="{DF2BEEE3-E1EF-4EA0-A6A8-77B06FB5C3EE}" name="expected" dataDxfId="391"/>
+    <tableColumn id="3" xr3:uid="{4FDE8849-AFE2-471E-8131-C5B45620EBDC}" name="output" dataDxfId="390">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.input, _xlfn.REGEXEXTRACT(Table6[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.input,1,1),
@@ -10431,25 +12191,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5813AECE-7F35-45E7-8E1F-50DCC8404156}" name="passing" totalsRowFunction="custom" dataDxfId="234" totalsRowDxfId="233">
+    <tableColumn id="4" xr3:uid="{5813AECE-7F35-45E7-8E1F-50DCC8404156}" name="passing" totalsRowFunction="custom" dataDxfId="389" totalsRowDxfId="388">
       <calculatedColumnFormula>IF(ISERROR(Table6[[#This Row],[expected]]),
     ERROR.TYPE(Table6[[#This Row],[expected]]) = ERROR.TYPE(Table6[[#This Row],[output]]),
     Table6[[#This Row],[expected]] = Table6[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Table6[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6FEE6B80-DF03-48AD-BE0B-5CF10BB9952D}" name="test" dataDxfId="232"/>
+    <tableColumn id="5" xr3:uid="{6FEE6B80-DF03-48AD-BE0B-5CF10BB9952D}" name="test" dataDxfId="387"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{99918742-71F1-4CEE-8B31-04D0864B12BE}" name="Add_Tests" displayName="Add_Tests" ref="A163:E169" totalsRowCount="1" dataDxfId="231">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{99918742-71F1-4CEE-8B31-04D0864B12BE}" name="Add_Tests" displayName="Add_Tests" ref="A163:E169" totalsRowCount="1" dataDxfId="386">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BEDCABA1-70E6-4A6B-A326-B96D805DC792}" name="input" dataDxfId="230"/>
-    <tableColumn id="2" xr3:uid="{D2C344B5-4A5B-4F69-8FCC-B73D81DE29AD}" name="expected" dataDxfId="229"/>
-    <tableColumn id="3" xr3:uid="{B095BBF3-B41C-4F5B-9689-A075BCD3B3C6}" name="output" dataDxfId="228">
+    <tableColumn id="1" xr3:uid="{BEDCABA1-70E6-4A6B-A326-B96D805DC792}" name="input" dataDxfId="385"/>
+    <tableColumn id="2" xr3:uid="{D2C344B5-4A5B-4F69-8FCC-B73D81DE29AD}" name="expected" dataDxfId="384"/>
+    <tableColumn id="3" xr3:uid="{B095BBF3-B41C-4F5B-9689-A075BCD3B3C6}" name="output" dataDxfId="383">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Add_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -10457,25 +12217,25 @@
     xlInt.Add(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8A3FC5E9-718D-42AA-90B8-83E1D4F3B18A}" name="passing" totalsRowFunction="custom" dataDxfId="227" totalsRowDxfId="226">
+    <tableColumn id="4" xr3:uid="{8A3FC5E9-718D-42AA-90B8-83E1D4F3B18A}" name="passing" totalsRowFunction="custom" dataDxfId="382" totalsRowDxfId="381">
       <calculatedColumnFormula>IF(ISERROR(Add_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Add_Tests[[#This Row],[expected]]) = ERROR.TYPE(Add_Tests[[#This Row],[output]]),
     Add_Tests[[#This Row],[expected]] = Add_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Add_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DCB35414-E71F-476D-B8FC-5C98625552A8}" name="test" dataDxfId="225"/>
+    <tableColumn id="5" xr3:uid="{DCB35414-E71F-476D-B8FC-5C98625552A8}" name="test" dataDxfId="380"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{DE30AD6A-E7CB-4B0A-9AF6-2A68597C812D}" name="Sub_Tests" displayName="Sub_Tests" ref="A172:E176" totalsRowCount="1" dataDxfId="224">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{DE30AD6A-E7CB-4B0A-9AF6-2A68597C812D}" name="Sub_Tests" displayName="Sub_Tests" ref="A172:E176" totalsRowCount="1" dataDxfId="379">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{03074968-5409-421B-94C4-D5670F4C41D8}" name="input" dataDxfId="223"/>
-    <tableColumn id="2" xr3:uid="{DDFFA8C5-FCAB-4C4D-9AD1-92357F9E25A7}" name="expected" dataDxfId="222"/>
-    <tableColumn id="3" xr3:uid="{799B106A-FDF6-4F6C-8D67-8B6355524DD8}" name="output" dataDxfId="221">
+    <tableColumn id="1" xr3:uid="{03074968-5409-421B-94C4-D5670F4C41D8}" name="input" dataDxfId="378"/>
+    <tableColumn id="2" xr3:uid="{DDFFA8C5-FCAB-4C4D-9AD1-92357F9E25A7}" name="expected" dataDxfId="377"/>
+    <tableColumn id="3" xr3:uid="{799B106A-FDF6-4F6C-8D67-8B6355524DD8}" name="output" dataDxfId="376">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Sub_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -10483,25 +12243,25 @@
     xlInt.Sub(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{365F4930-D4D1-407A-94F0-4578BEFB456D}" name="passing" totalsRowFunction="custom" dataDxfId="220" totalsRowDxfId="219">
+    <tableColumn id="4" xr3:uid="{365F4930-D4D1-407A-94F0-4578BEFB456D}" name="passing" totalsRowFunction="custom" dataDxfId="375" totalsRowDxfId="374">
       <calculatedColumnFormula>IF(ISERROR(Sub_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Sub_Tests[[#This Row],[expected]]) = ERROR.TYPE(Sub_Tests[[#This Row],[output]]),
     Sub_Tests[[#This Row],[expected]] = Sub_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Sub_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CD9B4489-0AA4-43C4-9B29-8D70A32DD746}" name="test" dataDxfId="218"/>
+    <tableColumn id="5" xr3:uid="{CD9B4489-0AA4-43C4-9B29-8D70A32DD746}" name="test" dataDxfId="373"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{9E3906E7-DD79-4AAB-8367-36E413E4200E}" name="Split_Tests" displayName="Split_Tests" ref="A179:E183" totalsRowCount="1" dataDxfId="217">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{9E3906E7-DD79-4AAB-8367-36E413E4200E}" name="Split_Tests" displayName="Split_Tests" ref="A179:E183" totalsRowCount="1" dataDxfId="372">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{14CAD510-CB82-4DB3-9F1C-40F2CB704D1C}" name="input" dataDxfId="216"/>
-    <tableColumn id="2" xr3:uid="{5035D4AE-F48A-40D0-AF90-BDA3391536CB}" name="expected" dataDxfId="215"/>
-    <tableColumn id="3" xr3:uid="{99876D23-ABB8-4C24-98A4-1BEEEEDD07C4}" name="output" dataDxfId="214">
+    <tableColumn id="1" xr3:uid="{14CAD510-CB82-4DB3-9F1C-40F2CB704D1C}" name="input" dataDxfId="371"/>
+    <tableColumn id="2" xr3:uid="{5035D4AE-F48A-40D0-AF90-BDA3391536CB}" name="expected" dataDxfId="370"/>
+    <tableColumn id="3" xr3:uid="{99876D23-ABB8-4C24-98A4-1BEEEEDD07C4}" name="output" dataDxfId="369">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.input_k, _xlfn.REGEXEXTRACT(Split_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.input, INDEX(_xlpm.input_k,1,1),
@@ -10511,25 +12271,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A5A07BB4-21F2-4B01-9D44-1AA4366EAB7F}" name="passing" totalsRowFunction="custom" dataDxfId="213" totalsRowDxfId="212">
+    <tableColumn id="4" xr3:uid="{A5A07BB4-21F2-4B01-9D44-1AA4366EAB7F}" name="passing" totalsRowFunction="custom" dataDxfId="368" totalsRowDxfId="367">
       <calculatedColumnFormula>IF(ISERROR(Split_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Split_Tests[[#This Row],[expected]]) = ERROR.TYPE(Split_Tests[[#This Row],[output]]),
     Split_Tests[[#This Row],[expected]] = Split_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Split_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{12903E1A-EF63-4775-8029-4AC6E1371182}" name="test" dataDxfId="211"/>
+    <tableColumn id="5" xr3:uid="{12903E1A-EF63-4775-8029-4AC6E1371182}" name="test" dataDxfId="366"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{B4199465-17FF-401D-8825-47D1965ACDD0}" name="UMatrixSum_Tests" displayName="UMatrixSum_Tests" ref="A186:E191" totalsRowCount="1" dataDxfId="210">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{B4199465-17FF-401D-8825-47D1965ACDD0}" name="UMatrixSum_Tests" displayName="UMatrixSum_Tests" ref="A186:E191" totalsRowCount="1" dataDxfId="365">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{02600896-7D14-484F-821B-B4456983BB28}" name="input" dataDxfId="209"/>
-    <tableColumn id="2" xr3:uid="{173735CF-904D-4F11-81E2-08E18A2E350F}" name="expected" dataDxfId="208"/>
-    <tableColumn id="3" xr3:uid="{39C7D243-2D28-43C6-84E9-009686A8BE25}" name="output" dataDxfId="207">
+    <tableColumn id="1" xr3:uid="{02600896-7D14-484F-821B-B4456983BB28}" name="input" dataDxfId="364"/>
+    <tableColumn id="2" xr3:uid="{173735CF-904D-4F11-81E2-08E18A2E350F}" name="expected" dataDxfId="363"/>
+    <tableColumn id="3" xr3:uid="{39C7D243-2D28-43C6-84E9-009686A8BE25}" name="output" dataDxfId="362">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.limbs_k, _xlfn.REGEXEXTRACT(UMatrixSum_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.limbs, _xlfn.TEXTSPLIT(INDEX(_xlpm.limbs_k,1,1), ",", ";"),
@@ -10538,14 +12298,14 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{708213D7-3DCF-48EE-85F0-411FE836D86B}" name="passing" totalsRowFunction="custom" dataDxfId="206" totalsRowDxfId="205">
+    <tableColumn id="4" xr3:uid="{708213D7-3DCF-48EE-85F0-411FE836D86B}" name="passing" totalsRowFunction="custom" dataDxfId="361" totalsRowDxfId="360">
       <calculatedColumnFormula>IF(ISERROR(UMatrixSum_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UMatrixSum_Tests[[#This Row],[expected]]) = ERROR.TYPE(UMatrixSum_Tests[[#This Row],[output]]),
     UMatrixSum_Tests[[#This Row],[expected]] = UMatrixSum_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UMatrixSum_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{1A2B4059-059A-4B6D-8573-AF782E91D2A9}" name="test" dataDxfId="204"/>
+    <tableColumn id="5" xr3:uid="{1A2B4059-059A-4B6D-8573-AF782E91D2A9}" name="test" dataDxfId="359"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10556,14 +12316,14 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9C2FC9B7-0634-4588-8EFB-AD967A0F24A8}" name="input"/>
     <tableColumn id="2" xr3:uid="{282A94A0-1EBE-4152-8A9A-8F0EF95A0338}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{1B45BBB4-DEF0-4F8A-9D99-3837C2C1D0A6}" name="output" dataDxfId="203">
+    <tableColumn id="3" xr3:uid="{1B45BBB4-DEF0-4F8A-9D99-3837C2C1D0A6}" name="output" dataDxfId="358">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.range, _xlfn.REGEXEXTRACT(Sum_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.big_ints, IFERROR(_xlfn.TEXTSPLIT(INDEX(_xlpm.range,1,1), ",", ";"), ""),
     xlInt.Sum(_xlpm.big_ints)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EE8AD54F-5219-409B-ABCC-BA23AB35B017}" name="passing" totalsRowFunction="custom" dataDxfId="202" totalsRowDxfId="201">
+    <tableColumn id="4" xr3:uid="{EE8AD54F-5219-409B-ABCC-BA23AB35B017}" name="passing" totalsRowFunction="custom" dataDxfId="357" totalsRowDxfId="356">
       <calculatedColumnFormula>IF(ISERROR(Sum_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Sum_Tests[[#This Row],[expected]]) = ERROR.TYPE(Sum_Tests[[#This Row],[output]]),
     Sum_Tests[[#This Row],[expected]] = Sum_Tests[[#This Row],[output]]
@@ -10577,11 +12337,11 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{106EA359-E4B0-4842-9C9A-062E9FF7B5FB}" name="UMul_Tests" displayName="UMul_Tests" ref="A205:E211" totalsRowCount="1" dataDxfId="200">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{106EA359-E4B0-4842-9C9A-062E9FF7B5FB}" name="UMul_Tests" displayName="UMul_Tests" ref="A205:E211" totalsRowCount="1" dataDxfId="355">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8D4F0565-063F-4316-9C57-705162867D2A}" name="input" dataDxfId="199"/>
-    <tableColumn id="2" xr3:uid="{DAD4A921-C714-4DCC-AADE-BAF6086A3636}" name="expected" dataDxfId="198"/>
-    <tableColumn id="3" xr3:uid="{97E6E3DD-CA0A-4372-AC3D-9A495F7C3A53}" name="output" dataDxfId="197">
+    <tableColumn id="1" xr3:uid="{8D4F0565-063F-4316-9C57-705162867D2A}" name="input" dataDxfId="354"/>
+    <tableColumn id="2" xr3:uid="{DAD4A921-C714-4DCC-AADE-BAF6086A3636}" name="expected" dataDxfId="353"/>
+    <tableColumn id="3" xr3:uid="{97E6E3DD-CA0A-4372-AC3D-9A495F7C3A53}" name="output" dataDxfId="352">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(UMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -10593,25 +12353,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E46610B1-FA9D-4582-8D0C-63D1EC61D64E}" name="passing" totalsRowFunction="custom" dataDxfId="196" totalsRowDxfId="195">
+    <tableColumn id="4" xr3:uid="{E46610B1-FA9D-4582-8D0C-63D1EC61D64E}" name="passing" totalsRowFunction="custom" dataDxfId="351" totalsRowDxfId="350">
       <calculatedColumnFormula>IF(ISERROR(UMul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UMul_Tests[[#This Row],[output]]),
     UMul_Tests[[#This Row],[expected]] = UMul_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UMul_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5337E378-248A-4061-ABD9-D618DD84E539}" name="test" dataDxfId="194"/>
+    <tableColumn id="5" xr3:uid="{5337E378-248A-4061-ABD9-D618DD84E539}" name="test" dataDxfId="349"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D11AB36-7D48-42C4-B8E7-63DA272F75B3}" name="SafeK_Tests" displayName="SafeK_Tests" ref="A29:E37" totalsRowCount="1" dataDxfId="293">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D11AB36-7D48-42C4-B8E7-63DA272F75B3}" name="SafeK_Tests" displayName="SafeK_Tests" ref="A29:E37" totalsRowCount="1" dataDxfId="448">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{CD46518C-03B6-4B43-A7B8-7360525A290D}" name="input" dataDxfId="292"/>
-    <tableColumn id="3" xr3:uid="{F3B44865-B013-44C5-A9D4-1A13BFE5AA81}" name="expected" dataDxfId="291"/>
-    <tableColumn id="4" xr3:uid="{F40E0393-EF6C-4B2D-9F49-5CBB088EB267}" name="output" dataDxfId="290">
+    <tableColumn id="2" xr3:uid="{CD46518C-03B6-4B43-A7B8-7360525A290D}" name="input" dataDxfId="447"/>
+    <tableColumn id="3" xr3:uid="{F3B44865-B013-44C5-A9D4-1A13BFE5AA81}" name="expected" dataDxfId="446"/>
+    <tableColumn id="4" xr3:uid="{F40E0393-EF6C-4B2D-9F49-5CBB088EB267}" name="output" dataDxfId="445">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.op_items, _xlfn.REGEXEXTRACT(SafeK_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.op, INDEX(_xlpm.op_items,1,1),
@@ -10620,25 +12380,25 @@
     internal.xlInt.SafeK(_xlpm.op, _xlpm.max_items)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{62988A37-52EF-4F3E-82FE-0F2CD420BEF5}" name="passing" totalsRowFunction="custom" dataDxfId="289">
+    <tableColumn id="5" xr3:uid="{62988A37-52EF-4F3E-82FE-0F2CD420BEF5}" name="passing" totalsRowFunction="custom" dataDxfId="444">
       <calculatedColumnFormula>IF(ISERROR(SafeK_Tests[[#This Row],[expected]]),
     ERROR.TYPE(SafeK_Tests[[#This Row],[expected]]) = ERROR.TYPE(SafeK_Tests[[#This Row],[output]]),
     SafeK_Tests[[#This Row],[expected]] = SafeK_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(SafeK_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{FB9EC421-276B-4C54-8F46-BB5C01271314}" name="test" dataDxfId="288"/>
+    <tableColumn id="6" xr3:uid="{FB9EC421-276B-4C54-8F46-BB5C01271314}" name="test" dataDxfId="443"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C927379E-9D9F-446A-A7F8-18937FDB3BE9}" name="Mul_Tests" displayName="Mul_Tests" ref="A214:E221" totalsRowCount="1" dataDxfId="193">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C927379E-9D9F-446A-A7F8-18937FDB3BE9}" name="Mul_Tests" displayName="Mul_Tests" ref="A214:E221" totalsRowCount="1" dataDxfId="348">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3AEB129A-112F-4626-87D9-516E40338A3B}" name="input" dataDxfId="192" totalsRowDxfId="191"/>
-    <tableColumn id="2" xr3:uid="{17E1D158-0134-4800-97A0-9A914A48AA8F}" name="expected" dataDxfId="190" totalsRowDxfId="189"/>
-    <tableColumn id="3" xr3:uid="{B25D54E8-D438-48E6-9956-B82746478514}" name="output" dataDxfId="188" totalsRowDxfId="187">
+    <tableColumn id="1" xr3:uid="{3AEB129A-112F-4626-87D9-516E40338A3B}" name="input" dataDxfId="347" totalsRowDxfId="346"/>
+    <tableColumn id="2" xr3:uid="{17E1D158-0134-4800-97A0-9A914A48AA8F}" name="expected" dataDxfId="345" totalsRowDxfId="344"/>
+    <tableColumn id="3" xr3:uid="{B25D54E8-D438-48E6-9956-B82746478514}" name="output" dataDxfId="343" totalsRowDxfId="342">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Mul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -10646,25 +12406,25 @@
     xlInt.Mul(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5D503E6C-603A-418E-8D29-E96FF9E82626}" name="passing" totalsRowFunction="custom" dataDxfId="186" totalsRowDxfId="185">
+    <tableColumn id="4" xr3:uid="{5D503E6C-603A-418E-8D29-E96FF9E82626}" name="passing" totalsRowFunction="custom" dataDxfId="341" totalsRowDxfId="340">
       <calculatedColumnFormula>IF(ISERROR(Mul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Mul_Tests[[#This Row],[expected]]) = ERROR.TYPE(Mul_Tests[[#This Row],[output]]),
     Mul_Tests[[#This Row],[expected]] = Mul_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Mul_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{785B4909-13EC-4ABC-ADF8-0A6E8C364AE8}" name="test" dataDxfId="184" totalsRowDxfId="183"/>
+    <tableColumn id="5" xr3:uid="{785B4909-13EC-4ABC-ADF8-0A6E8C364AE8}" name="test" dataDxfId="339" totalsRowDxfId="338"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{4706FBB1-54D9-4F64-9481-F1D8984AE18E}" name="KnuthDiv_Tests" displayName="KnuthDiv_Tests" ref="A224:E233" totalsRowCount="1" dataDxfId="182">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{4706FBB1-54D9-4F64-9481-F1D8984AE18E}" name="KnuthDiv_Tests" displayName="KnuthDiv_Tests" ref="A224:E233" totalsRowCount="1" dataDxfId="337">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C9306945-CA62-4719-882E-A0FFCFC80239}" name="input" dataDxfId="181"/>
-    <tableColumn id="2" xr3:uid="{FF30C91E-2B8D-47FA-B34B-6CA5257E3EB7}" name="expected" dataDxfId="180"/>
-    <tableColumn id="3" xr3:uid="{3B324DA4-4AAE-408C-B627-929F7D5C7CBF}" name="output" dataDxfId="179">
+    <tableColumn id="1" xr3:uid="{C9306945-CA62-4719-882E-A0FFCFC80239}" name="input" dataDxfId="336"/>
+    <tableColumn id="2" xr3:uid="{FF30C91E-2B8D-47FA-B34B-6CA5257E3EB7}" name="expected" dataDxfId="335"/>
+    <tableColumn id="3" xr3:uid="{3B324DA4-4AAE-408C-B627-929F7D5C7CBF}" name="output" dataDxfId="334">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(KnuthDiv_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -10676,25 +12436,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{439AD3AD-5C90-48C6-AB74-B9DDF87C40B5}" name="passing" totalsRowFunction="custom" dataDxfId="178" totalsRowDxfId="177">
+    <tableColumn id="4" xr3:uid="{439AD3AD-5C90-48C6-AB74-B9DDF87C40B5}" name="passing" totalsRowFunction="custom" dataDxfId="333" totalsRowDxfId="332">
       <calculatedColumnFormula>IF(ISERROR(KnuthDiv_Tests[[#This Row],[expected]]),
     ERROR.TYPE(KnuthDiv_Tests[[#This Row],[expected]]) = ERROR.TYPE(KnuthDiv_Tests[[#This Row],[output]]),
     KnuthDiv_Tests[[#This Row],[expected]] = KnuthDiv_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(KnuthDiv_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7D4887A2-EC0B-4C52-8336-E300544022A1}" name="test" dataDxfId="176"/>
+    <tableColumn id="5" xr3:uid="{7D4887A2-EC0B-4C52-8336-E300544022A1}" name="test" dataDxfId="331"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B0C6E940-EAB6-4373-8987-1B7722C2CC79}" name="Div_Tests" displayName="Div_Tests" ref="A236:E247" totalsRowCount="1" dataDxfId="175">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B0C6E940-EAB6-4373-8987-1B7722C2CC79}" name="Div_Tests" displayName="Div_Tests" ref="A236:E247" totalsRowCount="1" dataDxfId="330">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{0A49EAE4-5B09-4D2D-A863-D634A4825565}" name="input" dataDxfId="174" totalsRowDxfId="173"/>
-    <tableColumn id="2" xr3:uid="{4BF042F3-E337-4B63-A1E8-414D47019404}" name="expected" dataDxfId="172" totalsRowDxfId="171"/>
-    <tableColumn id="3" xr3:uid="{118ABB7A-7163-40CB-974E-69BFF6BE2BE0}" name="output" dataDxfId="170" totalsRowDxfId="169">
+    <tableColumn id="1" xr3:uid="{0A49EAE4-5B09-4D2D-A863-D634A4825565}" name="input" dataDxfId="329" totalsRowDxfId="328"/>
+    <tableColumn id="2" xr3:uid="{4BF042F3-E337-4B63-A1E8-414D47019404}" name="expected" dataDxfId="327" totalsRowDxfId="326"/>
+    <tableColumn id="3" xr3:uid="{118ABB7A-7163-40CB-974E-69BFF6BE2BE0}" name="output" dataDxfId="325" totalsRowDxfId="324">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Div_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -10702,25 +12462,25 @@
     xlInt.Div(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4344C6C8-3F96-4048-96D0-CA621258C1D7}" name="passing" totalsRowFunction="custom" dataDxfId="168" totalsRowDxfId="167">
+    <tableColumn id="4" xr3:uid="{4344C6C8-3F96-4048-96D0-CA621258C1D7}" name="passing" totalsRowFunction="custom" dataDxfId="323" totalsRowDxfId="322">
       <calculatedColumnFormula>IF(ISERROR(Div_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Div_Tests[[#This Row],[expected]]) = ERROR.TYPE(Div_Tests[[#This Row],[output]]),
     Div_Tests[[#This Row],[expected]] = Div_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Div_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7CF48835-D05B-4120-863E-A47318569688}" name="test" dataDxfId="166" totalsRowDxfId="165"/>
+    <tableColumn id="5" xr3:uid="{7CF48835-D05B-4120-863E-A47318569688}" name="test" dataDxfId="321" totalsRowDxfId="320"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{B3179C39-4489-4B3E-A2D2-1A2B50DC058E}" name="Mod_Tests" displayName="Mod_Tests" ref="A250:E261" totalsRowCount="1" dataDxfId="164">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{B3179C39-4489-4B3E-A2D2-1A2B50DC058E}" name="Mod_Tests" displayName="Mod_Tests" ref="A250:E261" totalsRowCount="1" dataDxfId="319">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F1BCBD73-ACF5-4609-87F5-A9FAB549955E}" name="input" dataDxfId="163" totalsRowDxfId="162"/>
-    <tableColumn id="2" xr3:uid="{E9604163-FD58-4190-8D72-28AA7831E8C8}" name="expected" dataDxfId="161" totalsRowDxfId="160"/>
-    <tableColumn id="3" xr3:uid="{9D21CE79-D00B-4182-97B3-60EF6DC8B18F}" name="output" dataDxfId="159" totalsRowDxfId="158">
+    <tableColumn id="1" xr3:uid="{F1BCBD73-ACF5-4609-87F5-A9FAB549955E}" name="input" dataDxfId="318" totalsRowDxfId="317"/>
+    <tableColumn id="2" xr3:uid="{E9604163-FD58-4190-8D72-28AA7831E8C8}" name="expected" dataDxfId="316" totalsRowDxfId="315"/>
+    <tableColumn id="3" xr3:uid="{9D21CE79-D00B-4182-97B3-60EF6DC8B18F}" name="output" dataDxfId="314" totalsRowDxfId="313">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Mod_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -10728,25 +12488,25 @@
     xlInt.Mod(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CEF047D2-0521-425D-99C4-E3B997A68B32}" name="passing" totalsRowFunction="custom" dataDxfId="157" totalsRowDxfId="156">
+    <tableColumn id="4" xr3:uid="{CEF047D2-0521-425D-99C4-E3B997A68B32}" name="passing" totalsRowFunction="custom" dataDxfId="312" totalsRowDxfId="311">
       <calculatedColumnFormula>IF(ISERROR(Mod_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Mod_Tests[[#This Row],[expected]]) = ERROR.TYPE(Mod_Tests[[#This Row],[output]]),
     Mod_Tests[[#This Row],[expected]] = Mod_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Mod_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{BB0A3941-EEFB-445E-AE7B-833C36649910}" name="test" dataDxfId="155" totalsRowDxfId="154"/>
+    <tableColumn id="5" xr3:uid="{BB0A3941-EEFB-445E-AE7B-833C36649910}" name="test" dataDxfId="310" totalsRowDxfId="309"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{82953E35-FA6B-4DA1-B4AC-195D4F1BB7C8}" name="DivMod_Tests" displayName="DivMod_Tests" ref="A264:E280" totalsRowCount="1" dataDxfId="153">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{82953E35-FA6B-4DA1-B4AC-195D4F1BB7C8}" name="DivMod_Tests" displayName="DivMod_Tests" ref="A264:E280" totalsRowCount="1" dataDxfId="308">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E51BC97B-AA0D-4705-AF36-89CB4A3501FF}" name="input" dataDxfId="152" totalsRowDxfId="151"/>
-    <tableColumn id="2" xr3:uid="{6D6483DD-139D-4DFE-BFEA-8BAA3E5C6FCF}" name="expected" dataDxfId="150" totalsRowDxfId="149"/>
-    <tableColumn id="3" xr3:uid="{17DE90BB-4525-4C2D-9577-C4372DCD74B3}" name="output" dataDxfId="148" totalsRowDxfId="147">
+    <tableColumn id="1" xr3:uid="{E51BC97B-AA0D-4705-AF36-89CB4A3501FF}" name="input" dataDxfId="307" totalsRowDxfId="306"/>
+    <tableColumn id="2" xr3:uid="{6D6483DD-139D-4DFE-BFEA-8BAA3E5C6FCF}" name="expected" dataDxfId="305" totalsRowDxfId="304"/>
+    <tableColumn id="3" xr3:uid="{17DE90BB-4525-4C2D-9577-C4372DCD74B3}" name="output" dataDxfId="303" totalsRowDxfId="302">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.ab_flag, _xlfn.REGEXEXTRACT(DivMod_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab_flag,1,1),
@@ -10755,25 +12515,25 @@
     _xlfn.ARRAYTOTEXT(xlInt.DivMod(_xlpm.a, _xlpm.b, _xlpm.use_floor), 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{08745616-1601-437B-82EA-C1952393A99B}" name="passing" totalsRowFunction="custom" dataDxfId="146" totalsRowDxfId="145">
+    <tableColumn id="4" xr3:uid="{08745616-1601-437B-82EA-C1952393A99B}" name="passing" totalsRowFunction="custom" dataDxfId="301" totalsRowDxfId="300">
       <calculatedColumnFormula>IF(ISERROR(DivMod_Tests[[#This Row],[expected]]),
     ERROR.TYPE(DivMod_Tests[[#This Row],[expected]]) = ERROR.TYPE(DivMod_Tests[[#This Row],[output]]),
     DivMod_Tests[[#This Row],[expected]] = DivMod_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(DivMod_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{10C8AB14-1CD9-4B06-8A65-2B27B32A2550}" name="test" dataDxfId="144" totalsRowDxfId="143"/>
+    <tableColumn id="5" xr3:uid="{10C8AB14-1CD9-4B06-8A65-2B27B32A2550}" name="test" dataDxfId="299" totalsRowDxfId="298"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{3400C680-561E-4111-B80A-CA24DB597E3F}" name="Table25" displayName="Table25" ref="A283:E289" totalsRowCount="1" dataDxfId="142">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{3400C680-561E-4111-B80A-CA24DB597E3F}" name="Table25" displayName="Table25" ref="A283:E289" totalsRowCount="1" dataDxfId="297">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{37EA378F-E179-45E1-BF1A-FBA82C305DBA}" name="input" dataDxfId="141"/>
-    <tableColumn id="2" xr3:uid="{11DFB020-1D5E-4E26-A86F-6B73428F3709}" name="expected" dataDxfId="140"/>
-    <tableColumn id="3" xr3:uid="{943FD3EB-6145-4BEE-9408-F68BE0795A47}" name="output" dataDxfId="139">
+    <tableColumn id="1" xr3:uid="{37EA378F-E179-45E1-BF1A-FBA82C305DBA}" name="input" dataDxfId="296"/>
+    <tableColumn id="2" xr3:uid="{11DFB020-1D5E-4E26-A86F-6B73428F3709}" name="expected" dataDxfId="295"/>
+    <tableColumn id="3" xr3:uid="{943FD3EB-6145-4BEE-9408-F68BE0795A47}" name="output" dataDxfId="294">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.bk, _xlfn.REGEXEXTRACT(Table25[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.b, INDEX(_xlpm.bk,1,1),
@@ -10783,49 +12543,49 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{165ECACC-11AD-4EB0-AE14-7D528DA64799}" name="passing" totalsRowFunction="custom" dataDxfId="138" totalsRowDxfId="137">
+    <tableColumn id="4" xr3:uid="{165ECACC-11AD-4EB0-AE14-7D528DA64799}" name="passing" totalsRowFunction="custom" dataDxfId="293" totalsRowDxfId="292">
       <calculatedColumnFormula>IF(ISERROR(Table25[[#This Row],[expected]]),
     ERROR.TYPE(Table25[[#This Row],[expected]]) = ERROR.TYPE(Table25[[#This Row],[output]]),
     Table25[[#This Row],[expected]] = Table25[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Table25[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6FA8F2E3-9F29-41C5-8B60-45E4EF5BFD33}" name="test" dataDxfId="136"/>
+    <tableColumn id="5" xr3:uid="{6FA8F2E3-9F29-41C5-8B60-45E4EF5BFD33}" name="test" dataDxfId="291"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{12A27437-8E10-4142-9D59-10A781936664}" name="IsEven_Tests" displayName="IsEven_Tests" ref="A292:E301" totalsRowCount="1" tableBorderDxfId="135">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{12A27437-8E10-4142-9D59-10A781936664}" name="IsEven_Tests" displayName="IsEven_Tests" ref="A292:E301" totalsRowCount="1" tableBorderDxfId="290">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{72B34F2A-D724-472B-AEA6-85847044F8BB}" name="input"/>
     <tableColumn id="2" xr3:uid="{8F1A9828-E68A-40FE-8534-E28D2B59C43A}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{90993922-EF49-4320-BFDE-A85AAC37995B}" name="output" dataDxfId="134">
+    <tableColumn id="3" xr3:uid="{90993922-EF49-4320-BFDE-A85AAC37995B}" name="output" dataDxfId="289">
       <calculatedColumnFormula array="1">BigInt.IsEven(IsEven_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4CD10349-78F4-4A08-8AD3-6AFDD4218B3F}" name="passing" totalsRowFunction="custom" dataDxfId="133">
+    <tableColumn id="4" xr3:uid="{4CD10349-78F4-4A08-8AD3-6AFDD4218B3F}" name="passing" totalsRowFunction="custom" dataDxfId="288">
       <calculatedColumnFormula>IF(ISERROR(IsEven_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsEven_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsEven_Tests[[#This Row],[output]]),
     IsEven_Tests[[#This Row],[expected]] = IsEven_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(IsEven_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9C811914-2121-4942-94F0-B4760C307266}" name="test" dataDxfId="132"/>
+    <tableColumn id="5" xr3:uid="{9C811914-2121-4942-94F0-B4760C307266}" name="test" dataDxfId="287"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{29B30C5B-F766-4073-878A-FEDF3C607366}" name="IsOdd_Tests" displayName="IsOdd_Tests" ref="A304:E313" totalsRowCount="1" tableBorderDxfId="131">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{29B30C5B-F766-4073-878A-FEDF3C607366}" name="IsOdd_Tests" displayName="IsOdd_Tests" ref="A304:E313" totalsRowCount="1" tableBorderDxfId="286">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8D247229-1BE2-49B1-BEC8-19AFBBF671FC}" name="input"/>
     <tableColumn id="2" xr3:uid="{9F1FC5CC-11FA-4EB1-BA6E-3C18F4379652}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{6B07B988-F191-4E41-81FA-8D0020D0AEF2}" name="output" dataDxfId="130">
+    <tableColumn id="3" xr3:uid="{6B07B988-F191-4E41-81FA-8D0020D0AEF2}" name="output" dataDxfId="285">
       <calculatedColumnFormula array="1">BigInt.IsOdd(IsOdd_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{15820A65-99F4-420C-A89B-1F6FB8202BCC}" name="passing" totalsRowFunction="custom" dataDxfId="129">
+    <tableColumn id="4" xr3:uid="{15820A65-99F4-420C-A89B-1F6FB8202BCC}" name="passing" totalsRowFunction="custom" dataDxfId="284">
       <calculatedColumnFormula>IF(ISERROR(IsOdd_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsOdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsOdd_Tests[[#This Row],[output]]),
     IsOdd_Tests[[#This Row],[expected]] = IsOdd_Tests[[#This Row],[output]]
@@ -10839,11 +12599,11 @@
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{371705AE-DD2A-4348-9D77-10A58AFED934}" name="Pow_Tests" displayName="Pow_Tests" ref="A327:E341" totalsRowCount="1" dataDxfId="128">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{371705AE-DD2A-4348-9D77-10A58AFED934}" name="Pow_Tests" displayName="Pow_Tests" ref="A327:E341" totalsRowCount="1" dataDxfId="283">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{428DC074-F3C2-4541-81E6-FDDAE2482D27}" name="input" dataDxfId="127"/>
-    <tableColumn id="2" xr3:uid="{B5FD2A40-BCC5-4580-B8CD-768791024AC5}" name="expected" dataDxfId="126"/>
-    <tableColumn id="3" xr3:uid="{F4E39208-EEA5-4CF3-B04A-4707F3E1FB8E}" name="output" dataDxfId="125">
+    <tableColumn id="1" xr3:uid="{428DC074-F3C2-4541-81E6-FDDAE2482D27}" name="input" dataDxfId="282"/>
+    <tableColumn id="2" xr3:uid="{B5FD2A40-BCC5-4580-B8CD-768791024AC5}" name="expected" dataDxfId="281"/>
+    <tableColumn id="3" xr3:uid="{F4E39208-EEA5-4CF3-B04A-4707F3E1FB8E}" name="output" dataDxfId="280">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab, 1, 1),
@@ -10851,25 +12611,25 @@
     BigInt.Pow(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B407AC33-1B59-4CB2-91F2-8CA96B7CE117}" name="passing" totalsRowFunction="custom" dataDxfId="124">
+    <tableColumn id="4" xr3:uid="{B407AC33-1B59-4CB2-91F2-8CA96B7CE117}" name="passing" totalsRowFunction="custom" dataDxfId="279">
       <calculatedColumnFormula>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
     Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Pow_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A1A7E0C2-F1B0-41A5-A740-EDF94ACD6051}" name="test" dataDxfId="123"/>
+    <tableColumn id="5" xr3:uid="{A1A7E0C2-F1B0-41A5-A740-EDF94ACD6051}" name="test" dataDxfId="278"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{83160072-B1B0-4FD1-88FC-006B8639CBE0}" name="UPow_Tests" displayName="UPow_Tests" ref="A316:E324" totalsRowCount="1" dataDxfId="122">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{83160072-B1B0-4FD1-88FC-006B8639CBE0}" name="UPow_Tests" displayName="UPow_Tests" ref="A316:E324" totalsRowCount="1" dataDxfId="277">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{20145995-7ED4-4B73-887D-9D74DA0828CF}" name="input" dataDxfId="121"/>
-    <tableColumn id="2" xr3:uid="{82FBC2F1-B0A2-4D85-8D2F-0E9C3548EF52}" name="expected" dataDxfId="120"/>
-    <tableColumn id="3" xr3:uid="{30FC05F3-7A85-4F3C-B4CB-146B4FEBD37A}" name="output" dataDxfId="119">
+    <tableColumn id="1" xr3:uid="{20145995-7ED4-4B73-887D-9D74DA0828CF}" name="input" dataDxfId="276"/>
+    <tableColumn id="2" xr3:uid="{82FBC2F1-B0A2-4D85-8D2F-0E9C3548EF52}" name="expected" dataDxfId="275"/>
+    <tableColumn id="3" xr3:uid="{30FC05F3-7A85-4F3C-B4CB-146B4FEBD37A}" name="output" dataDxfId="274">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.bek, _xlfn.REGEXEXTRACT(UPow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.base, INDEX(_xlpm.bek,1,1),
@@ -10880,14 +12640,14 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{13DDE135-8BB6-470E-A96F-6482CA5075E2}" name="passing" totalsRowFunction="custom" dataDxfId="118">
+    <tableColumn id="4" xr3:uid="{13DDE135-8BB6-470E-A96F-6482CA5075E2}" name="passing" totalsRowFunction="custom" dataDxfId="273">
       <calculatedColumnFormula>IF(ISERROR(UPow_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UPow_Tests[[#This Row],[expected]]) = ERROR.TYPE(UPow_Tests[[#This Row],[output]]),
     UPow_Tests[[#This Row],[expected]] = UPow_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UPow_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{45AF5A50-06F2-4581-B704-1F7379E7EFDB}" name="test" dataDxfId="117"/>
+    <tableColumn id="5" xr3:uid="{45AF5A50-06F2-4581-B704-1F7379E7EFDB}" name="test" dataDxfId="272"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10898,7 +12658,7 @@
   <tableColumns count="5">
     <tableColumn id="2" xr3:uid="{2286D15B-F261-49FF-90E5-E32FAEEEA489}" name="input"/>
     <tableColumn id="3" xr3:uid="{1D45A0AC-7049-4C3E-9D4F-CF777F60006B}" name="expected"/>
-    <tableColumn id="4" xr3:uid="{725B7147-ED3D-42D7-9030-A0FCAF6502D0}" name="output" dataDxfId="287">
+    <tableColumn id="4" xr3:uid="{725B7147-ED3D-42D7-9030-A0FCAF6502D0}" name="output" dataDxfId="442">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.limbs_k, _xlfn.REGEXEXTRACT(Merge_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.limbs_text, INDEX(_xlpm.limbs_k,1,1),
@@ -10907,25 +12667,25 @@
     internal.xlInt.Merge(_xlpm.limbs, _xlpm.k)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7D40DA54-4D50-4770-9171-9F50106783D7}" name="passing" totalsRowFunction="custom" dataDxfId="286">
+    <tableColumn id="5" xr3:uid="{7D40DA54-4D50-4770-9171-9F50106783D7}" name="passing" totalsRowFunction="custom" dataDxfId="441">
       <calculatedColumnFormula>IF(ISERROR(Merge_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Merge_Tests[[#This Row],[expected]]) = ERROR.TYPE(Merge_Tests[[#This Row],[output]]),
     Merge_Tests[[#This Row],[expected]] = Merge_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Merge_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F906F95B-0DD5-4F50-9A36-C63DEC4B514C}" name="test" dataDxfId="285"/>
+    <tableColumn id="6" xr3:uid="{F906F95B-0DD5-4F50-9A36-C63DEC4B514C}" name="test" dataDxfId="440"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{56E07932-566C-4BD6-8077-730BDDB685D7}" name="USqrt_Tests" displayName="USqrt_Tests" ref="A344:E348" totalsRowCount="1" dataDxfId="116">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{56E07932-566C-4BD6-8077-730BDDB685D7}" name="USqrt_Tests" displayName="USqrt_Tests" ref="A344:E348" totalsRowCount="1" dataDxfId="271">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7D0B28FD-9EB7-4A3D-892B-9C8FB4B3B2F5}" name="input" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{CFF29D88-DF87-4564-930E-26EAF1CB3332}" name="expected" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{4738BA38-2D1B-4B90-8625-6A923FAABAE8}" name="output" dataDxfId="113">
+    <tableColumn id="1" xr3:uid="{7D0B28FD-9EB7-4A3D-892B-9C8FB4B3B2F5}" name="input" dataDxfId="270"/>
+    <tableColumn id="2" xr3:uid="{CFF29D88-DF87-4564-930E-26EAF1CB3332}" name="expected" dataDxfId="269"/>
+    <tableColumn id="3" xr3:uid="{4738BA38-2D1B-4B90-8625-6A923FAABAE8}" name="output" dataDxfId="268">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.radicand_seed_k, _xlfn.REGEXEXTRACT(USqrt_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.radicand, INDEX(_xlpm.radicand_seed_k,1,1),
@@ -10937,25 +12697,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{118D95C4-A916-4992-AEA0-6F30E3EE33F9}" name="passing" totalsRowFunction="custom" dataDxfId="112" totalsRowDxfId="111">
+    <tableColumn id="4" xr3:uid="{118D95C4-A916-4992-AEA0-6F30E3EE33F9}" name="passing" totalsRowFunction="custom" dataDxfId="267" totalsRowDxfId="266">
       <calculatedColumnFormula>IF(ISERROR(USqrt_Tests[[#This Row],[expected]]),
     ERROR.TYPE(USqrt_Tests[[#This Row],[expected]]) = ERROR.TYPE(USqrt_Tests[[#This Row],[output]]),
     USqrt_Tests[[#This Row],[expected]] = USqrt_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(USqrt_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{36AF6E6D-247D-40D4-8B02-20DF4A48BDF2}" name="test" dataDxfId="110"/>
+    <tableColumn id="5" xr3:uid="{36AF6E6D-247D-40D4-8B02-20DF4A48BDF2}" name="test" dataDxfId="265"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{A9B2C3B0-D156-4BA1-8DBC-CCD97E178DEB}" name="NewtonRaphsonReciprocal_Tests" displayName="NewtonRaphsonReciprocal_Tests" ref="A351:E356" totalsRowCount="1" dataDxfId="109">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{A9B2C3B0-D156-4BA1-8DBC-CCD97E178DEB}" name="NewtonRaphsonReciprocal_Tests" displayName="NewtonRaphsonReciprocal_Tests" ref="A351:E356" totalsRowCount="1" dataDxfId="264">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{668CC6CC-FAA8-4201-AF7C-80B23CDDC2E9}" name="input" dataDxfId="108"/>
-    <tableColumn id="2" xr3:uid="{25DCB2CE-672E-4637-9E18-5B6DB9547223}" name="expected" dataDxfId="107"/>
-    <tableColumn id="3" xr3:uid="{90B5F5EA-1862-438B-A0B0-E7B33D47B422}" name="output" dataDxfId="106">
+    <tableColumn id="1" xr3:uid="{668CC6CC-FAA8-4201-AF7C-80B23CDDC2E9}" name="input" dataDxfId="263"/>
+    <tableColumn id="2" xr3:uid="{25DCB2CE-672E-4637-9E18-5B6DB9547223}" name="expected" dataDxfId="262"/>
+    <tableColumn id="3" xr3:uid="{90B5F5EA-1862-438B-A0B0-E7B33D47B422}" name="output" dataDxfId="261">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.b_len_k, _xlfn.REGEXEXTRACT(NewtonRaphsonReciprocal_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.b, INDEX(_xlpm.b_len_k,1,1),
@@ -10966,25 +12726,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A229F032-C11B-467F-A66D-15E5E90AC98D}" name="passing" totalsRowFunction="custom" dataDxfId="105" totalsRowDxfId="104">
+    <tableColumn id="4" xr3:uid="{A229F032-C11B-467F-A66D-15E5E90AC98D}" name="passing" totalsRowFunction="custom" dataDxfId="260" totalsRowDxfId="259">
       <calculatedColumnFormula>IF(ISERROR(NewtonRaphsonReciprocal_Tests[[#This Row],[expected]]),
     ERROR.TYPE(NewtonRaphsonReciprocal_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonReciprocal_Tests[[#This Row],[output]]),
     NewtonRaphsonReciprocal_Tests[[#This Row],[expected]] = NewtonRaphsonReciprocal_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(NewtonRaphsonReciprocal_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F159BE0D-B6F5-4516-9322-421576A9CFAC}" name="test" dataDxfId="103"/>
+    <tableColumn id="5" xr3:uid="{F159BE0D-B6F5-4516-9322-421576A9CFAC}" name="test" dataDxfId="258"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{9E5B9787-3CCB-4F73-B127-FE62EEB658A9}" name="NewtonRaphsonDiv_Tests" displayName="NewtonRaphsonDiv_Tests" ref="A359:E365" totalsRowCount="1" dataDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{9E5B9787-3CCB-4F73-B127-FE62EEB658A9}" name="NewtonRaphsonDiv_Tests" displayName="NewtonRaphsonDiv_Tests" ref="A359:E365" totalsRowCount="1" dataDxfId="257">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1DD49B57-7E7E-4B1C-B300-6AC09AA4507D}" name="input" dataDxfId="101"/>
-    <tableColumn id="2" xr3:uid="{F726FD71-2E54-4ACE-8BDB-45E8C22B8958}" name="expected" dataDxfId="100"/>
-    <tableColumn id="3" xr3:uid="{51451E9D-81A3-4433-AABC-FCAE4ED0B82C}" name="output" dataDxfId="99">
+    <tableColumn id="1" xr3:uid="{1DD49B57-7E7E-4B1C-B300-6AC09AA4507D}" name="input" dataDxfId="256"/>
+    <tableColumn id="2" xr3:uid="{F726FD71-2E54-4ACE-8BDB-45E8C22B8958}" name="expected" dataDxfId="255"/>
+    <tableColumn id="3" xr3:uid="{51451E9D-81A3-4433-AABC-FCAE4ED0B82C}" name="output" dataDxfId="254">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(NewtonRaphsonDiv_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -10996,99 +12756,71 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3511251B-5389-4721-A1A1-8AE06E90F9D7}" name="passing" totalsRowFunction="custom" dataDxfId="98" totalsRowDxfId="97">
+    <tableColumn id="4" xr3:uid="{3511251B-5389-4721-A1A1-8AE06E90F9D7}" name="passing" totalsRowFunction="custom" dataDxfId="253" totalsRowDxfId="252">
       <calculatedColumnFormula>IF(ISERROR(NewtonRaphsonDiv_Tests[[#This Row],[expected]]),
     ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[output]]),
     NewtonRaphsonDiv_Tests[[#This Row],[expected]] = NewtonRaphsonDiv_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(NewtonRaphsonDiv_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8FBD496E-700B-47C8-B9CA-AD0871776B53}" name="test" dataDxfId="96"/>
+    <tableColumn id="5" xr3:uid="{8FBD496E-700B-47C8-B9CA-AD0871776B53}" name="test" dataDxfId="251"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{27C0A819-84B9-4A0A-8097-03A8C95F5E27}" name="NativePrimes_Tests" displayName="NativePrimes_Tests" ref="A368:E374" totalsRowCount="1" dataDxfId="89" tableBorderDxfId="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{27C0A819-84B9-4A0A-8097-03A8C95F5E27}" name="NativePrimes_Tests" displayName="NativePrimes_Tests" ref="A368:E374" totalsRowCount="1" dataDxfId="250" tableBorderDxfId="249">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F29CD078-1065-436A-811B-D67567316769}" name="input" dataDxfId="94"/>
-    <tableColumn id="2" xr3:uid="{6122EAC1-506A-441B-8004-4B02E143A802}" name="expected" dataDxfId="93"/>
-    <tableColumn id="3" xr3:uid="{778AEC62-886A-4A2A-BD39-EB9F715A732B}" name="output" dataDxfId="92">
+    <tableColumn id="1" xr3:uid="{F29CD078-1065-436A-811B-D67567316769}" name="input" dataDxfId="248"/>
+    <tableColumn id="2" xr3:uid="{6122EAC1-506A-441B-8004-4B02E143A802}" name="expected" dataDxfId="247"/>
+    <tableColumn id="3" xr3:uid="{778AEC62-886A-4A2A-BD39-EB9F715A732B}" name="output" dataDxfId="246">
       <calculatedColumnFormula>_xlfn.ARRAYTOTEXT(core_BigInt.NativePrimes(NativePrimes_Tests[[#This Row],[input]]), 1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F3546CB4-2246-45FB-B499-CB4B13BA76E1}" name="passing" totalsRowFunction="custom" dataDxfId="91">
+    <tableColumn id="4" xr3:uid="{F3546CB4-2246-45FB-B499-CB4B13BA76E1}" name="passing" totalsRowFunction="custom" dataDxfId="245">
       <calculatedColumnFormula>IF(ISERROR(NativePrimes_Tests[[#This Row],[expected]]),
     ERROR.TYPE(NativePrimes_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativePrimes_Tests[[#This Row],[output]]),
     NativePrimes_Tests[[#This Row],[expected]] = NativePrimes_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(NativePrimes_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8190D20C-0392-4F85-929A-69F9BDF57A0A}" name="test" dataDxfId="90"/>
+    <tableColumn id="5" xr3:uid="{8190D20C-0392-4F85-929A-69F9BDF57A0A}" name="test" dataDxfId="244"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table34.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{59E466E6-AFB8-402E-BCED-A4DA6DCFEC1A}" name="NativeLegendre_Tests" displayName="NativeLegendre_Tests" ref="A377:E381" totalsRowCount="1" dataDxfId="83">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{49BD0AFE-381A-4E2F-A35C-4D1CCCA7584E}" name="TextTreeProd_Tests37" displayName="TextTreeProd_Tests37" ref="A386:E391" totalsRowCount="1" dataDxfId="243">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E23E090E-81D9-47D4-8198-B1ABBEE94C6B}" name="input" dataDxfId="87"/>
-    <tableColumn id="2" xr3:uid="{D1878000-78EF-43C5-946A-0BAFB2F760F9}" name="expected" dataDxfId="86"/>
-    <tableColumn id="3" xr3:uid="{C7FC6EEE-BC05-4AD9-93FA-E3E482244768}" name="output" dataDxfId="82">
+    <tableColumn id="1" xr3:uid="{998EF311-8CF0-4498-BF3E-C7591D617740}" name="input" dataDxfId="242"/>
+    <tableColumn id="2" xr3:uid="{030D33E6-C011-4057-AFBE-F1FEC05B0E3D}" name="expected" dataDxfId="241"/>
+    <tableColumn id="3" xr3:uid="{4A32034C-1A35-45CF-A8F5-5BB1FB3300A5}" name="output" dataDxfId="240">
       <calculatedColumnFormula array="1">_xlfn.LET(
-    _xlpm.n_primes, _xlfn.REGEXEXTRACT(NativeLegendre_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
-    _xlpm.n, --INDEX(_xlpm.n_primes,1,1),
-    _xlpm.primes, INDEX(_xlpm.n_primes,1,2),
-    _xlpm.primes_arr, --_xlfn.TEXTSPLIT(_xlpm.primes,",",";"),
-    _xlpm.output, core_BigInt.NativeLegendre(_xlpm.n, _xlpm.primes_arr),
-    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+    _xlpm.big_ints, _xlfn.REGEXEXTRACT(TextTreeProd_Tests37[[#This Row],[input]], "{\K[\w,; .-]*"),
+    _xlpm.big_int_arr, _xlfn.TEXTSPLIT(_xlpm.big_ints,",",";"),
+    core_BigInt.TextTreeProd(_xlpm.big_int_arr)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6B550009-EA49-4BEF-8603-A7366A531DBE}" name="passing" totalsRowFunction="custom" dataDxfId="85" totalsRowDxfId="88">
-      <calculatedColumnFormula>IF(ISERROR(NativeLegendre_Tests[[#This Row],[expected]]),
-    ERROR.TYPE(NativeLegendre_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativeLegendre_Tests[[#This Row],[output]]),
-    NativeLegendre_Tests[[#This Row],[expected]] = NativeLegendre_Tests[[#This Row],[output]]
+    <tableColumn id="4" xr3:uid="{F4493AC7-8D4A-4E9D-A9A4-52B87367C964}" name="passing" totalsRowFunction="custom" dataDxfId="239" totalsRowDxfId="238">
+      <calculatedColumnFormula>IF(ISERROR(TextTreeProd_Tests37[[#This Row],[expected]]),
+    ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[expected]]) = ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[output]]),
+    TextTreeProd_Tests37[[#This Row],[expected]] = TextTreeProd_Tests37[[#This Row],[output]]
 )</calculatedColumnFormula>
-      <totalsRowFormula>AND(NativeLegendre_Tests[passing])</totalsRowFormula>
+      <totalsRowFormula>AND(TextTreeProd_Tests37[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A0D783D9-731F-42E5-8EBE-FEFE8CD7AAF6}" name="test" dataDxfId="84"/>
+    <tableColumn id="5" xr3:uid="{9E2E183E-0AFC-4266-8D1C-760BDBA95E9A}" name="test" dataDxfId="237"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table35.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{49BD0AFE-381A-4E2F-A35C-4D1CCCA7584E}" name="TextTreeProd_Tests37" displayName="TextTreeProd_Tests37" ref="A393:E398" totalsRowCount="1" dataDxfId="81">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{4BA5BDEF-A87F-4855-AD37-C3A378790A0D}" name="UTextMul_Tests" displayName="UTextMul_Tests" ref="A377:E383" totalsRowCount="1" dataDxfId="236">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{998EF311-8CF0-4498-BF3E-C7591D617740}" name="input" dataDxfId="80"/>
-    <tableColumn id="2" xr3:uid="{030D33E6-C011-4057-AFBE-F1FEC05B0E3D}" name="expected" dataDxfId="79"/>
-    <tableColumn id="3" xr3:uid="{4A32034C-1A35-45CF-A8F5-5BB1FB3300A5}" name="output" dataDxfId="75">
-      <calculatedColumnFormula array="1">_xlfn.LET(
-    _xlpm.big_ints, _xlfn.REGEXEXTRACT(TextTreeProd_Tests37[[#This Row],[input]], "{\K[\w,; .-]*"),
-    _xlpm.big_int_arr, _xlfn.TEXTSPLIT(_xlpm.big_ints,",",";"),
-    core_BigInt.TextTreeProd(_xlpm.big_int_arr)
-)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{F4493AC7-8D4A-4E9D-A9A4-52B87367C964}" name="passing" totalsRowFunction="custom" dataDxfId="77" totalsRowDxfId="78">
-      <calculatedColumnFormula>IF(ISERROR(TextTreeProd_Tests37[[#This Row],[expected]]),
-    ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[expected]]) = ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[output]]),
-    TextTreeProd_Tests37[[#This Row],[expected]] = TextTreeProd_Tests37[[#This Row],[output]]
-)</calculatedColumnFormula>
-      <totalsRowFormula>AND(TextTreeProd_Tests37[passing])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="5" xr3:uid="{9E2E183E-0AFC-4266-8D1C-760BDBA95E9A}" name="test" dataDxfId="76"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table36.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{4BA5BDEF-A87F-4855-AD37-C3A378790A0D}" name="UTextMul_Tests" displayName="UTextMul_Tests" ref="A384:E390" totalsRowCount="1" dataDxfId="74">
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3F5F3FFD-5DC8-4A88-908C-7CEE90688FD2}" name="input" dataDxfId="73" totalsRowDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{6AD81AC4-371F-4E12-BB01-43913712ADEC}" name="expected" dataDxfId="72" totalsRowDxfId="68"/>
-    <tableColumn id="3" xr3:uid="{554D388F-417A-46F4-9FA2-AACDEAA24237}" name="output" dataDxfId="64" totalsRowDxfId="67">
+    <tableColumn id="1" xr3:uid="{3F5F3FFD-5DC8-4A88-908C-7CEE90688FD2}" name="input" dataDxfId="235" totalsRowDxfId="234"/>
+    <tableColumn id="2" xr3:uid="{6AD81AC4-371F-4E12-BB01-43913712ADEC}" name="expected" dataDxfId="233" totalsRowDxfId="232"/>
+    <tableColumn id="3" xr3:uid="{554D388F-417A-46F4-9FA2-AACDEAA24237}" name="output" dataDxfId="231" totalsRowDxfId="230">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(UTextMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -11096,60 +12828,131 @@
     core_BigInt.UTextMul(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{98F15F6B-80F5-487B-9965-2D3178956C0C}" name="passing" totalsRowFunction="custom" dataDxfId="71" totalsRowDxfId="66">
+    <tableColumn id="4" xr3:uid="{98F15F6B-80F5-487B-9965-2D3178956C0C}" name="passing" totalsRowFunction="custom" dataDxfId="229" totalsRowDxfId="228">
       <calculatedColumnFormula>IF(ISERROR(UTextMul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UTextMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UTextMul_Tests[[#This Row],[output]]),
     UTextMul_Tests[[#This Row],[expected]] = UTextMul_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UTextMul_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{2218ADB1-42B3-401A-BDE3-B0DC0D6D6959}" name="test" dataDxfId="70" totalsRowDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{2218ADB1-42B3-401A-BDE3-B0DC0D6D6959}" name="test" dataDxfId="227" totalsRowDxfId="226"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table36.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{C18280EB-8AA6-4449-955D-681E77E7D1F0}" name="Fact_Tests" displayName="Fact_Tests" ref="A394:E402" totalsRowCount="1" dataDxfId="225" tableBorderDxfId="224">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{D95EE39E-5251-4170-8888-9530E87C134B}" name="input" dataDxfId="223"/>
+    <tableColumn id="2" xr3:uid="{15AD0C64-A61C-4834-B444-C19248449496}" name="expected" dataDxfId="222"/>
+    <tableColumn id="3" xr3:uid="{B1B2AF0C-A9CA-494D-9393-F9EB601C03AE}" name="output" dataDxfId="221">
+      <calculatedColumnFormula array="1">BigInt.Fact(Fact_Tests[[#This Row],[input]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{67D2CAD7-A3A0-464E-A151-2D279B301872}" name="passing" totalsRowFunction="custom" dataDxfId="220">
+      <calculatedColumnFormula>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
+    Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(Fact_Tests[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{AD0FAFD6-A476-479B-A804-9F518E2EB8F4}" name="test" dataDxfId="219"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table37.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{C18280EB-8AA6-4449-955D-681E77E7D1F0}" name="Fact_Tests" displayName="Fact_Tests" ref="A401:E409" totalsRowCount="1" dataDxfId="63" tableBorderDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{1A442966-F97C-4CA5-BF93-28001E9F3115}" name="NativeSwingExponents_Tests" displayName="NativeSwingExponents_Tests" ref="A405:E408" totalsRowCount="1" dataDxfId="218">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D95EE39E-5251-4170-8888-9530E87C134B}" name="input" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{15AD0C64-A61C-4834-B444-C19248449496}" name="expected" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{B1B2AF0C-A9CA-494D-9393-F9EB601C03AE}" name="output" dataDxfId="0">
-      <calculatedColumnFormula array="1">BigInt.Fact(Fact_Tests[[#This Row],[input]])</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{A9F64071-671A-4BD5-BB0B-5605FA9B2FB2}" name="input" dataDxfId="217"/>
+    <tableColumn id="2" xr3:uid="{02211327-69A6-4349-A560-3AF62381C788}" name="expected" dataDxfId="216"/>
+    <tableColumn id="3" xr3:uid="{89446F11-EFC2-42C7-B521-B662FB138191}" name="output" dataDxfId="212">
+      <calculatedColumnFormula array="1">_xlfn.LET(
+    _xlpm.n_primes, _xlfn.REGEXEXTRACT(NativeSwingExponents_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.n, --INDEX(_xlpm.n_primes,1,1),
+    _xlpm.primes, INDEX(_xlpm.n_primes,1,2),
+    _xlpm.primes_arr, --_xlfn.TEXTSPLIT(_xlpm.primes,",",";"),
+    _xlpm.output, core_BigInt.NativeSwingExponents(_xlpm.n, _xlpm.primes_arr),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{67D2CAD7-A3A0-464E-A151-2D279B301872}" name="passing" totalsRowFunction="custom" dataDxfId="59">
-      <calculatedColumnFormula>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
-    ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
-    Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
+    <tableColumn id="4" xr3:uid="{C52D135F-5CEB-4D1A-8E45-EA8B58B2B163}" name="passing" totalsRowFunction="custom" dataDxfId="215" totalsRowDxfId="213">
+      <calculatedColumnFormula>IF(ISERROR(NativeSwingExponents_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NativeSwingExponents_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativeSwingExponents_Tests[[#This Row],[output]]),
+    NativeSwingExponents_Tests[[#This Row],[expected]] = NativeSwingExponents_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
-      <totalsRowFormula>AND(Fact_Tests[passing])</totalsRowFormula>
+      <totalsRowFormula>AND(NativeSwingExponents_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{AD0FAFD6-A476-479B-A804-9F518E2EB8F4}" name="test" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{B46E3978-1116-4B1A-913F-71B5FB4747AC}" name="test" dataDxfId="214"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table38.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{C1458AB7-3AD7-44E9-B064-C2BEC4A41762}" name="Data" displayName="Data" ref="A1:B8" totalsRowShown="0">
-  <autoFilter ref="A1:B8" xr:uid="{C1458AB7-3AD7-44E9-B064-C2BEC4A41762}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9A8BD9FA-DF38-4A2D-A72E-A480C042A429}" name="name"/>
-    <tableColumn id="2" xr3:uid="{5167F18E-1410-43BB-8E2F-ED5CAD279C57}" name="value"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{A5FEA778-9E36-4BC2-B573-658FC407B11D}" name="PrimeSwingKernel_Tests" displayName="PrimeSwingKernel_Tests" ref="A411:E414" totalsRowCount="1" dataDxfId="211">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{D9194B1A-7653-4C25-AD75-58E73FE195C9}" name="input" dataDxfId="210"/>
+    <tableColumn id="2" xr3:uid="{AE2B8C19-C9AE-4F57-A1CB-20DBB45C5BC7}" name="expected" dataDxfId="209"/>
+    <tableColumn id="3" xr3:uid="{D8958B27-2C1B-4EE7-ACB4-6D260A9AA527}" name="output" dataDxfId="205">
+      <calculatedColumnFormula array="1">_xlfn.LET(
+    _xlpm.n_primes, _xlfn.REGEXEXTRACT(PrimeSwingKernel_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.n, --INDEX(_xlpm.n_primes,1,1),
+    _xlpm.primes, INDEX(_xlpm.n_primes,1,2),
+    _xlpm.primes_arr, --_xlfn.TEXTSPLIT(_xlpm.primes,",",";"),
+    core_BigInt.PrimeSwingKernel(_xlpm.n, _xlpm.primes_arr)
+)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{3AABFC76-CC2A-401A-82D6-2360A18DBD72}" name="passing" totalsRowFunction="custom" dataDxfId="207" totalsRowDxfId="208">
+      <calculatedColumnFormula>IF(ISERROR(PrimeSwingKernel_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(PrimeSwingKernel_Tests[[#This Row],[expected]]) = ERROR.TYPE(PrimeSwingKernel_Tests[[#This Row],[output]]),
+    PrimeSwingKernel_Tests[[#This Row],[expected]] = PrimeSwingKernel_Tests[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(PrimeSwingKernel_Tests[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{819A85D8-0038-49F4-92B3-29D2B3DA3DA7}" name="test" dataDxfId="206"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table39.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{B9017739-8F7A-45C0-8849-8DA270727275}" name="TreeCompare_Tests" displayName="TreeCompare_Tests" ref="A417:E425" totalsRowCount="1" dataDxfId="204">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{BDAA1AA4-B401-4C1E-B07A-E7D2C895F02A}" name="input" dataDxfId="203"/>
+    <tableColumn id="2" xr3:uid="{EC652947-23C8-4457-88DD-80381C7FB3A2}" name="expected" dataDxfId="202"/>
+    <tableColumn id="3" xr3:uid="{9CE537BC-E9A5-4F26-88D5-ABBB9201C75C}" name="output" dataDxfId="198">
+      <calculatedColumnFormula array="1">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(TreeCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.mode, --INDEX(_xlpm.range_mode,1,2),
+    _xlpm.range_arr, _xlfn.TEXTSPLIT(_xlpm.range,",",";"),
+    core_BigInt.TreeCompare(_xlpm.range_arr, _xlpm.mode)
+)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{998A2330-0955-43FD-AA71-94CBD47AD512}" name="passing" totalsRowFunction="custom" dataDxfId="200" totalsRowDxfId="201">
+      <calculatedColumnFormula>IF(ISERROR(TreeCompare_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(TreeCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(TreeCompare_Tests[[#This Row],[output]]),
+    TreeCompare_Tests[[#This Row],[expected]] = TreeCompare_Tests[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(TreeCompare_Tests[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{785CE4BC-B5F9-4152-BB85-92FDF88F26FE}" name="test" dataDxfId="199"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{8BE14E9C-9052-4C6B-91B5-74156B78161B}" name="IsZero_Tests" displayName="IsZero_Tests" ref="A63:E71" totalsRowCount="1" tableBorderDxfId="284">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{8BE14E9C-9052-4C6B-91B5-74156B78161B}" name="IsZero_Tests" displayName="IsZero_Tests" ref="A63:E71" totalsRowCount="1" tableBorderDxfId="439">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F079B266-FBE5-40B3-929D-6B075F83B32A}" name="input"/>
     <tableColumn id="2" xr3:uid="{D2EFB528-67FC-4490-876A-C72813F17A1C}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{735E5B6C-B3DA-49E2-B1F3-88323DE570B4}" name="output" dataDxfId="283">
+    <tableColumn id="3" xr3:uid="{735E5B6C-B3DA-49E2-B1F3-88323DE570B4}" name="output" dataDxfId="438">
       <calculatedColumnFormula array="1">xlInt.IsZero(IsZero_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BCB92B9B-DD7D-407D-BA1B-01844C06231A}" name="passing" totalsRowFunction="custom" dataDxfId="282">
+    <tableColumn id="4" xr3:uid="{BCB92B9B-DD7D-407D-BA1B-01844C06231A}" name="passing" totalsRowFunction="custom" dataDxfId="437">
       <calculatedColumnFormula>IF(ISERROR(IsZero_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsZero_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsZero_Tests[[#This Row],[output]]),
     IsZero_Tests[[#This Row],[expected]] = IsZero_Tests[[#This Row],[output]]
@@ -11162,15 +12965,78 @@
 </table>
 </file>
 
+<file path=xl/tables/table40.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{DF19CB3E-C2E9-4DDF-B4F3-1CD37989A54B}" name="Max_Tests" displayName="Max_Tests" ref="A428:E434" totalsRowCount="1" dataDxfId="197">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{70E3AE18-4391-4958-8A2F-0E14867BC728}" name="input" dataDxfId="196"/>
+    <tableColumn id="2" xr3:uid="{8003646D-7F33-486B-B89C-73BC90D27E5F}" name="expected" dataDxfId="195"/>
+    <tableColumn id="3" xr3:uid="{0DDD1364-1D88-485D-9D85-7DBBD316CE60}" name="output" dataDxfId="185">
+      <calculatedColumnFormula array="1">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(Max_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.range_arr, IFERROR(_xlfn.TEXTSPLIT(_xlpm.range,",",";"),_xlpm.range),
+    BigInt.Max(_xlpm.range_arr)
+)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{93AA2604-CFEC-494D-8458-265B34FBDD48}" name="passing" totalsRowFunction="custom" dataDxfId="193" totalsRowDxfId="194">
+      <calculatedColumnFormula>IF(ISERROR(Max_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Max_Tests[[#This Row],[expected]]) = ERROR.TYPE(Max_Tests[[#This Row],[output]]),
+    Max_Tests[[#This Row],[expected]] = Max_Tests[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(Max_Tests[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{7BB76139-B909-48EB-BBE4-1B5FAEDF08FF}" name="test" dataDxfId="192"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table41.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="43" xr:uid="{96C2916B-F8E5-4BCB-878F-6E93D4C2588B}" name="Min_Tests" displayName="Min_Tests" ref="A436:E442" totalsRowCount="1" dataDxfId="191">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{7CB0024C-89AB-4AF4-B981-D0D9DC861640}" name="input" dataDxfId="190"/>
+    <tableColumn id="2" xr3:uid="{6E7270F8-57D3-4993-A767-C9138198E9D0}" name="expected" dataDxfId="189"/>
+    <tableColumn id="3" xr3:uid="{B2BFCE87-E91A-4BF5-91C3-2864C634D5AD}" name="output" dataDxfId="184">
+      <calculatedColumnFormula array="1">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(Min_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.range_arr, IFERROR(_xlfn.TEXTSPLIT(_xlpm.range,",",";"),_xlpm.range),
+    BigInt.Min(_xlpm.range_arr)
+)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{119495E5-A70B-4977-B718-87E0A3787A9E}" name="passing" totalsRowFunction="custom" dataDxfId="187" totalsRowDxfId="188">
+      <calculatedColumnFormula>IF(ISERROR(Min_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Min_Tests[[#This Row],[expected]]) = ERROR.TYPE(Min_Tests[[#This Row],[output]]),
+    Min_Tests[[#This Row],[expected]] = Min_Tests[[#This Row],[output]]
+)</calculatedColumnFormula>
+      <totalsRowFormula>AND(Min_Tests[passing])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{D2764F64-B563-420B-8C69-F976F65330B5}" name="test" dataDxfId="186"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table42.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{C1458AB7-3AD7-44E9-B064-C2BEC4A41762}" name="Data" displayName="Data" ref="A1:B8" totalsRowShown="0">
+  <autoFilter ref="A1:B8" xr:uid="{C1458AB7-3AD7-44E9-B064-C2BEC4A41762}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{9A8BD9FA-DF38-4A2D-A72E-A480C042A429}" name="name"/>
+    <tableColumn id="2" xr3:uid="{5167F18E-1410-43BB-8E2F-ED5CAD279C57}" name="value"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{5F9E4160-7872-486B-BC10-496D23C60B5A}" name="IsNeg_Tests" displayName="IsNeg_Tests" ref="A74:E82" totalsRowCount="1" tableBorderDxfId="281">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{5F9E4160-7872-486B-BC10-496D23C60B5A}" name="IsNeg_Tests" displayName="IsNeg_Tests" ref="A74:E82" totalsRowCount="1" tableBorderDxfId="436">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A7BB892B-ECAA-4176-AFC6-3449690829CA}" name="input"/>
     <tableColumn id="2" xr3:uid="{4B67C433-DA3F-4DC8-A14F-97407C2E1925}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{49ED0D04-2AA3-4848-8297-CAE5A7D726CD}" name="output" dataDxfId="280">
+    <tableColumn id="3" xr3:uid="{49ED0D04-2AA3-4848-8297-CAE5A7D726CD}" name="output" dataDxfId="435">
       <calculatedColumnFormula array="1">xlInt.IsNeg(IsNeg_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{186FF00B-FED3-490C-BB63-2A0FC55A43D4}" name="passing" totalsRowFunction="custom" dataDxfId="279">
+    <tableColumn id="4" xr3:uid="{186FF00B-FED3-490C-BB63-2A0FC55A43D4}" name="passing" totalsRowFunction="custom" dataDxfId="434">
       <calculatedColumnFormula>IF(ISERROR(IsNeg_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsNeg_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsNeg_Tests[[#This Row],[output]]),
     IsNeg_Tests[[#This Row],[expected]] = IsNeg_Tests[[#This Row],[output]]
@@ -11184,14 +13050,14 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1631B68B-6D5A-402C-92F6-EDA45141B375}" name="Abs_Tests" displayName="Abs_Tests" ref="A85:E94" totalsRowCount="1" tableBorderDxfId="278">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1631B68B-6D5A-402C-92F6-EDA45141B375}" name="Abs_Tests" displayName="Abs_Tests" ref="A85:E94" totalsRowCount="1" tableBorderDxfId="433">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{631C43FF-F966-4712-8BEB-7647066AF179}" name="input"/>
     <tableColumn id="2" xr3:uid="{70F5476C-B45C-439B-BA01-326EAD467334}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{1E90CD50-A25E-4E12-84D5-66BAAE6BAF0C}" name="output" dataDxfId="277">
+    <tableColumn id="3" xr3:uid="{1E90CD50-A25E-4E12-84D5-66BAAE6BAF0C}" name="output" dataDxfId="432">
       <calculatedColumnFormula array="1">BigInt.Abs(Abs_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6A0B92CA-92B2-4515-86E8-D91A4279D44E}" name="passing" totalsRowFunction="custom" dataDxfId="276">
+    <tableColumn id="4" xr3:uid="{6A0B92CA-92B2-4515-86E8-D91A4279D44E}" name="passing" totalsRowFunction="custom" dataDxfId="431">
       <calculatedColumnFormula>IF(ISERROR(Abs_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Abs_Tests[[#This Row],[expected]]) = ERROR.TYPE(Abs_Tests[[#This Row],[output]]),
     Abs_Tests[[#This Row],[expected]] = Abs_Tests[[#This Row],[output]]
@@ -11205,11 +13071,11 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{A4A096D6-4E75-4455-A80B-D324779CD007}" name="Compare_Tests" displayName="Compare_Tests" ref="A97:E104" totalsRowCount="1" dataDxfId="275" tableBorderDxfId="274">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{A4A096D6-4E75-4455-A80B-D324779CD007}" name="Compare_Tests" displayName="Compare_Tests" ref="A97:E104" totalsRowCount="1" dataDxfId="430" tableBorderDxfId="429">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{6ED51130-CCEE-49F5-AE6A-C115477DEEC1}" name="input" dataDxfId="273"/>
-    <tableColumn id="3" xr3:uid="{33B3A3D6-83B3-431F-A0B0-9371BBC16D08}" name="expected" dataDxfId="272"/>
-    <tableColumn id="4" xr3:uid="{C0A2BAFD-DD64-4B6D-8350-F0AF699F41AB}" name="output" dataDxfId="271">
+    <tableColumn id="2" xr3:uid="{6ED51130-CCEE-49F5-AE6A-C115477DEEC1}" name="input" dataDxfId="428"/>
+    <tableColumn id="3" xr3:uid="{33B3A3D6-83B3-431F-A0B0-9371BBC16D08}" name="expected" dataDxfId="427"/>
+    <tableColumn id="4" xr3:uid="{C0A2BAFD-DD64-4B6D-8350-F0AF699F41AB}" name="output" dataDxfId="426">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Compare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -11217,25 +13083,25 @@
     xlInt.Compare(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{25151C64-2D6E-4B12-87AA-02A64ED9EF2B}" name="passing" totalsRowFunction="custom" dataDxfId="270">
+    <tableColumn id="5" xr3:uid="{25151C64-2D6E-4B12-87AA-02A64ED9EF2B}" name="passing" totalsRowFunction="custom" dataDxfId="425">
       <calculatedColumnFormula>IF(ISERROR(Compare_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Compare_Tests[[#This Row],[expected]]) = ERROR.TYPE(Compare_Tests[[#This Row],[output]]),
     Compare_Tests[[#This Row],[expected]] = Compare_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Compare_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D859FAE6-EDFC-42C5-8B0C-0116D05E04F4}" name="test" dataDxfId="269"/>
+    <tableColumn id="6" xr3:uid="{D859FAE6-EDFC-42C5-8B0C-0116D05E04F4}" name="test" dataDxfId="424"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{AB2483E8-D478-4FD2-B96C-83A98FDDE6FA}" name="Carry_Tests" displayName="Carry_Tests" ref="A107:E114" totalsRowCount="1" dataDxfId="268">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{AB2483E8-D478-4FD2-B96C-83A98FDDE6FA}" name="Carry_Tests" displayName="Carry_Tests" ref="A107:E114" totalsRowCount="1" dataDxfId="423">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{58CF3EAC-5FAD-4E1D-8349-AFD0026A5A6F}" name="input" dataDxfId="267"/>
-    <tableColumn id="3" xr3:uid="{8D4EBB1D-1F70-4D9A-B9FB-C7B03997C3F4}" name="expected" dataDxfId="266"/>
-    <tableColumn id="4" xr3:uid="{54C37EF8-27DA-477C-BC79-632DD5E54F03}" name="output" dataDxfId="265">
+    <tableColumn id="2" xr3:uid="{58CF3EAC-5FAD-4E1D-8349-AFD0026A5A6F}" name="input" dataDxfId="422"/>
+    <tableColumn id="3" xr3:uid="{8D4EBB1D-1F70-4D9A-B9FB-C7B03997C3F4}" name="expected" dataDxfId="421"/>
+    <tableColumn id="4" xr3:uid="{54C37EF8-27DA-477C-BC79-632DD5E54F03}" name="output" dataDxfId="420">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.limbs_k, _xlfn.REGEXEXTRACT(Carry_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.limbs_text, INDEX(_xlpm.limbs_k,1,1),
@@ -11245,25 +13111,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9B430B30-AE60-423D-A6BE-D7D881CBC2A0}" name="passing" totalsRowFunction="custom" dataDxfId="264">
+    <tableColumn id="5" xr3:uid="{9B430B30-AE60-423D-A6BE-D7D881CBC2A0}" name="passing" totalsRowFunction="custom" dataDxfId="419">
       <calculatedColumnFormula>IF(ISERROR(Carry_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Carry_Tests[[#This Row],[expected]]) = ERROR.TYPE(Carry_Tests[[#This Row],[output]]),
     Carry_Tests[[#This Row],[expected]] = Carry_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Carry_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{5F961C10-163D-49CE-93C1-9CA6C9C623CA}" name="test" dataDxfId="263"/>
+    <tableColumn id="6" xr3:uid="{5F961C10-163D-49CE-93C1-9CA6C9C623CA}" name="test" dataDxfId="418"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{9541B332-DEB4-4260-9226-40E8C97DC59F}" name="UAdd_Tests" displayName="UAdd_Tests" ref="A117:E124" totalsRowCount="1" dataDxfId="262" tableBorderDxfId="261">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{9541B332-DEB4-4260-9226-40E8C97DC59F}" name="UAdd_Tests" displayName="UAdd_Tests" ref="A117:E124" totalsRowCount="1" dataDxfId="417" tableBorderDxfId="416">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{6C5FB7CE-3B1F-447E-9ED3-14E839061137}" name="input" dataDxfId="260"/>
-    <tableColumn id="3" xr3:uid="{56E7CDEA-877C-47CA-B875-1A1313998480}" name="expected" dataDxfId="259"/>
-    <tableColumn id="4" xr3:uid="{0AB7FE18-4035-4604-909F-956B1054DE95}" name="output" dataDxfId="258">
+    <tableColumn id="2" xr3:uid="{6C5FB7CE-3B1F-447E-9ED3-14E839061137}" name="input" dataDxfId="415"/>
+    <tableColumn id="3" xr3:uid="{56E7CDEA-877C-47CA-B875-1A1313998480}" name="expected" dataDxfId="414"/>
+    <tableColumn id="4" xr3:uid="{0AB7FE18-4035-4604-909F-956B1054DE95}" name="output" dataDxfId="413">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(UAdd_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -11275,14 +13141,14 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{148597F1-9D9D-45C9-949B-CA15D869DE95}" name="passing" totalsRowFunction="custom" dataDxfId="257">
+    <tableColumn id="5" xr3:uid="{148597F1-9D9D-45C9-949B-CA15D869DE95}" name="passing" totalsRowFunction="custom" dataDxfId="412">
       <calculatedColumnFormula>IF(ISERROR(UAdd_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UAdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(UAdd_Tests[[#This Row],[output]]),
     UAdd_Tests[[#This Row],[expected]] = UAdd_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UAdd_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{58290239-17D2-42FA-BE94-887F938260F4}" name="test" dataDxfId="256"/>
+    <tableColumn id="6" xr3:uid="{58290239-17D2-42FA-BE94-887F938260F4}" name="test" dataDxfId="411"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11605,7 +13471,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="985" row="6">
+  <wetp:taskpane dockstate="right" visibility="0" width="1103" row="6">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -11637,7 +13503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23AD1BF5-F75F-465D-AC38-22DFE6D4806A}">
-  <dimension ref="A1:E431"/>
+  <dimension ref="A1:E469"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="27.54296875" customWidth="1"/>
@@ -11645,6 +13511,9 @@
     <col min="3" max="3" width="24.6328125" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
     <col min="5" max="5" width="66.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="19" thickBot="1">
@@ -11662,7 +13531,7 @@
       </c>
       <c r="B2">
         <f>COUNTIF(_xlfn._TRO_TRAILING(A:A), "input")</f>
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -11671,7 +13540,7 @@
       </c>
       <c r="B3" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">SUM(--ISNUMBER(SEARCH("[@expected] = [@output]", _xlfn.FORMULATEXT(_xlfn._TRO_TRAILING(D:D)))))</f>
-        <v>257</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -11680,7 +13549,7 @@
       </c>
       <c r="B4" cm="1">
         <f t="array" aca="1" ref="B4" ca="1">SUM(ISNUMBER(SEARCH("[@expected] = [@output]", _xlfn.FORMULATEXT(_xlfn._TRO_TRAILING(D:D)))) * (_xlfn._TRO_TRAILING(D:D) = TRUE))</f>
-        <v>257</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1"/>
@@ -18149,14 +20018,14 @@
         <v>530</v>
       </c>
     </row>
-    <row r="324" spans="1:5" hidden="1" outlineLevel="1">
+    <row r="324" spans="1:5" collapsed="1">
       <c r="A324" s="2"/>
       <c r="D324" t="b">
         <f>AND(UPow_Tests[passing])</f>
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="15" collapsed="1" thickBot="1"/>
+    <row r="325" spans="1:5" ht="15" thickBot="1"/>
     <row r="326" spans="1:5" ht="18.5">
       <c r="A326" s="5" t="s">
         <v>486</v>
@@ -19011,7 +20880,7 @@
     <row r="366" spans="1:5" ht="15" thickBot="1"/>
     <row r="367" spans="1:5" ht="18.5">
       <c r="A367" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B367" s="5"/>
       <c r="C367" s="5"/>
@@ -19157,7 +21026,7 @@
     <row r="375" spans="1:5" ht="15" thickBot="1"/>
     <row r="376" spans="1:5" ht="18.5">
       <c r="A376" s="5" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="B376" s="5"/>
       <c r="C376" s="5"/>
@@ -19174,7 +21043,7 @@
       <c r="C377" t="s">
         <v>36</v>
       </c>
-      <c r="D377" t="s">
+      <c r="D377" s="6" t="s">
         <v>48</v>
       </c>
       <c r="E377" t="s">
@@ -19183,133 +21052,13 @@
     </row>
     <row r="378" spans="1:5" ht="29" hidden="1" outlineLevel="1">
       <c r="A378" s="12" t="s">
-        <v>583</v>
-      </c>
-      <c r="B378" s="12" t="s">
-        <v>581</v>
+        <v>280</v>
+      </c>
+      <c r="B378" s="7" t="s">
+        <v>287</v>
       </c>
       <c r="C378" s="12" t="str" cm="1">
         <f t="array" ref="C378">_xlfn.LET(
-    _xlpm.n_primes, _xlfn.REGEXEXTRACT(NativeLegendre_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
-    _xlpm.n, --INDEX(_xlpm.n_primes,1,1),
-    _xlpm.primes, INDEX(_xlpm.n_primes,1,2),
-    _xlpm.primes_arr, --_xlfn.TEXTSPLIT(_xlpm.primes,",",";"),
-    _xlpm.output, core_BigInt.NativeLegendre(_xlpm.n, _xlpm.primes_arr),
-    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
-)</f>
-        <v>{8;4;2;1}</v>
-      </c>
-      <c r="D378" s="12" t="b">
-        <f>IF(ISERROR(NativeLegendre_Tests[[#This Row],[expected]]),
-    ERROR.TYPE(NativeLegendre_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativeLegendre_Tests[[#This Row],[output]]),
-    NativeLegendre_Tests[[#This Row],[expected]] = NativeLegendre_Tests[[#This Row],[output]]
-)</f>
-        <v>1</v>
-      </c>
-      <c r="E378" s="12" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="379" spans="1:5" ht="29" hidden="1" outlineLevel="1">
-      <c r="A379" s="12" t="s">
-        <v>584</v>
-      </c>
-      <c r="B379" s="12" t="s">
-        <v>504</v>
-      </c>
-      <c r="C379" s="12" t="str" cm="1">
-        <f t="array" ref="C379">_xlfn.LET(
-    _xlpm.n_primes, _xlfn.REGEXEXTRACT(NativeLegendre_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
-    _xlpm.n, --INDEX(_xlpm.n_primes,1,1),
-    _xlpm.primes, INDEX(_xlpm.n_primes,1,2),
-    _xlpm.primes_arr, --_xlfn.TEXTSPLIT(_xlpm.primes,",",";"),
-    _xlpm.output, core_BigInt.NativeLegendre(_xlpm.n, _xlpm.primes_arr),
-    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
-)</f>
-        <v>{1}</v>
-      </c>
-      <c r="D379" s="12" t="b">
-        <f>IF(ISERROR(NativeLegendre_Tests[[#This Row],[expected]]),
-    ERROR.TYPE(NativeLegendre_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativeLegendre_Tests[[#This Row],[output]]),
-    NativeLegendre_Tests[[#This Row],[expected]] = NativeLegendre_Tests[[#This Row],[output]]
-)</f>
-        <v>1</v>
-      </c>
-      <c r="E379" s="12" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="380" spans="1:5" ht="29" hidden="1" outlineLevel="1">
-      <c r="A380" s="12" t="s">
-        <v>585</v>
-      </c>
-      <c r="B380" s="12" t="s">
-        <v>582</v>
-      </c>
-      <c r="C380" s="12" t="str" cm="1">
-        <f t="array" ref="C380">_xlfn.LET(
-    _xlpm.n_primes, _xlfn.REGEXEXTRACT(NativeLegendre_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
-    _xlpm.n, --INDEX(_xlpm.n_primes,1,1),
-    _xlpm.primes, INDEX(_xlpm.n_primes,1,2),
-    _xlpm.primes_arr, --_xlfn.TEXTSPLIT(_xlpm.primes,",",";"),
-    _xlpm.output, core_BigInt.NativeLegendre(_xlpm.n, _xlpm.primes_arr),
-    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
-)</f>
-        <v>{3;1;1}</v>
-      </c>
-      <c r="D380" s="12" t="b">
-        <f>IF(ISERROR(NativeLegendre_Tests[[#This Row],[expected]]),
-    ERROR.TYPE(NativeLegendre_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativeLegendre_Tests[[#This Row],[output]]),
-    NativeLegendre_Tests[[#This Row],[expected]] = NativeLegendre_Tests[[#This Row],[output]]
-)</f>
-        <v>1</v>
-      </c>
-      <c r="E380" s="12" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="381" spans="1:5" collapsed="1">
-      <c r="D381" s="9" t="b">
-        <f>AND(NativeLegendre_Tests[passing])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="382" spans="1:5" ht="15" thickBot="1"/>
-    <row r="383" spans="1:5" ht="18.5">
-      <c r="A383" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="B383" s="5"/>
-      <c r="C383" s="5"/>
-      <c r="D383" s="5"/>
-      <c r="E383" s="5"/>
-    </row>
-    <row r="384" spans="1:5">
-      <c r="A384" t="s">
-        <v>110</v>
-      </c>
-      <c r="B384" t="s">
-        <v>35</v>
-      </c>
-      <c r="C384" t="s">
-        <v>36</v>
-      </c>
-      <c r="D384" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E384" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="385" spans="1:5" ht="29" hidden="1" outlineLevel="1">
-      <c r="A385" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="B385" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="C385" s="12" t="str" cm="1">
-        <f t="array" ref="C385">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(UTextMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
     _xlpm.b, INDEX(_xlpm.ab,1,2),
@@ -19317,26 +21066,26 @@
 )</f>
         <v>998001</v>
       </c>
-      <c r="D385" s="9" t="b">
+      <c r="D378" s="9" t="b">
         <f>IF(ISERROR(UTextMul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UTextMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UTextMul_Tests[[#This Row],[output]]),
     UTextMul_Tests[[#This Row],[expected]] = UTextMul_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E385" s="12" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="386" spans="1:5" ht="29" hidden="1" outlineLevel="1">
-      <c r="A386" s="12" t="s">
-        <v>602</v>
-      </c>
-      <c r="B386" s="7" t="s">
-        <v>603</v>
-      </c>
-      <c r="C386" s="12" t="str" cm="1">
-        <f t="array" ref="C386">_xlfn.LET(
+      <c r="E378" s="12" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A379" s="12" t="s">
+        <v>595</v>
+      </c>
+      <c r="B379" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="C379" s="12" t="str" cm="1">
+        <f t="array" ref="C379">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(UTextMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
     _xlpm.b, INDEX(_xlpm.ab,1,2),
@@ -19344,26 +21093,26 @@
 )</f>
         <v>246912</v>
       </c>
-      <c r="D386" s="9" t="b">
+      <c r="D379" s="9" t="b">
         <f>IF(ISERROR(UTextMul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UTextMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UTextMul_Tests[[#This Row],[output]]),
     UTextMul_Tests[[#This Row],[expected]] = UTextMul_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E386" s="12" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="387" spans="1:5" ht="29" hidden="1" outlineLevel="1">
-      <c r="A387" s="12" t="s">
-        <v>604</v>
-      </c>
-      <c r="B387" s="7" t="s">
-        <v>605</v>
-      </c>
-      <c r="C387" s="12" t="str" cm="1">
-        <f t="array" ref="C387">_xlfn.LET(
+      <c r="E379" s="12" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A380" s="12" t="s">
+        <v>597</v>
+      </c>
+      <c r="B380" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="C380" s="12" t="str" cm="1">
+        <f t="array" ref="C380">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(UTextMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
     _xlpm.b, INDEX(_xlpm.ab,1,2),
@@ -19371,26 +21120,26 @@
 )</f>
         <v>1000000</v>
       </c>
-      <c r="D387" s="9" t="b">
+      <c r="D380" s="9" t="b">
         <f>IF(ISERROR(UTextMul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UTextMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UTextMul_Tests[[#This Row],[output]]),
     UTextMul_Tests[[#This Row],[expected]] = UTextMul_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E387" s="12" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="388" spans="1:5" ht="29" hidden="1" outlineLevel="1">
-      <c r="A388" s="12" t="s">
-        <v>606</v>
-      </c>
-      <c r="B388" s="7" t="s">
+      <c r="E380" s="12" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A381" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="B381" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C388" s="12" t="str" cm="1">
-        <f t="array" ref="C388">_xlfn.LET(
+      <c r="C381" s="12" t="str" cm="1">
+        <f t="array" ref="C381">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(UTextMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
     _xlpm.b, INDEX(_xlpm.ab,1,2),
@@ -19398,26 +21147,26 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D388" s="9" t="b">
+      <c r="D381" s="9" t="b">
         <f>IF(ISERROR(UTextMul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UTextMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UTextMul_Tests[[#This Row],[output]]),
     UTextMul_Tests[[#This Row],[expected]] = UTextMul_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E388" s="12" t="s">
+      <c r="E381" s="12" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="29" hidden="1" outlineLevel="1">
-      <c r="A389" s="12" t="s">
+    <row r="382" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A382" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="B389" s="7" t="s">
+      <c r="B382" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="C389" s="12" t="str" cm="1">
-        <f t="array" ref="C389">_xlfn.LET(
+      <c r="C382" s="12" t="str" cm="1">
+        <f t="array" ref="C382">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(UTextMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
     _xlpm.b, INDEX(_xlpm.ab,1,2),
@@ -19425,630 +21174,1390 @@
 )</f>
         <v>999999999999999999</v>
       </c>
-      <c r="D389" s="9" t="b">
+      <c r="D382" s="9" t="b">
         <f>IF(ISERROR(UTextMul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UTextMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UTextMul_Tests[[#This Row],[output]]),
     UTextMul_Tests[[#This Row],[expected]] = UTextMul_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E389" s="12" t="s">
+      <c r="E382" s="12" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="390" spans="1:5" hidden="1" outlineLevel="1">
-      <c r="A390" s="12"/>
-      <c r="B390" s="12"/>
-      <c r="C390" s="12"/>
-      <c r="D390" s="9" t="b">
+    <row r="383" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A383" s="12"/>
+      <c r="B383" s="12"/>
+      <c r="C383" s="12"/>
+      <c r="D383" s="9" t="b">
         <f>AND(UTextMul_Tests[passing])</f>
         <v>1</v>
       </c>
-      <c r="E390" s="12"/>
-    </row>
-    <row r="391" spans="1:5" ht="15" collapsed="1" thickBot="1"/>
-    <row r="392" spans="1:5" ht="18.5">
-      <c r="A392" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="B392" s="5"/>
-      <c r="C392" s="5"/>
-      <c r="D392" s="5"/>
-      <c r="E392" s="5"/>
-    </row>
-    <row r="393" spans="1:5">
-      <c r="A393" t="s">
+      <c r="E383" s="12"/>
+    </row>
+    <row r="384" spans="1:5" ht="15" collapsed="1" thickBot="1"/>
+    <row r="385" spans="1:5" ht="18.5">
+      <c r="A385" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="B385" s="5"/>
+      <c r="C385" s="5"/>
+      <c r="D385" s="5"/>
+      <c r="E385" s="5"/>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" t="s">
         <v>110</v>
       </c>
-      <c r="B393" t="s">
+      <c r="B386" t="s">
         <v>35</v>
       </c>
-      <c r="C393" t="s">
+      <c r="C386" t="s">
         <v>36</v>
       </c>
-      <c r="D393" t="s">
+      <c r="D386" t="s">
         <v>48</v>
       </c>
-      <c r="E393" t="s">
+      <c r="E386" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="394" spans="1:5" hidden="1" outlineLevel="1">
-      <c r="A394" s="12" t="s">
-        <v>590</v>
-      </c>
-      <c r="B394" s="7" t="s">
+    <row r="387" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A387" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="B387" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C394" s="12" t="str" cm="1">
-        <f t="array" ref="C394">_xlfn.LET(
+      <c r="C387" s="12" t="str" cm="1">
+        <f t="array" ref="C387">_xlfn.LET(
     _xlpm.big_ints, _xlfn.REGEXEXTRACT(TextTreeProd_Tests37[[#This Row],[input]], "{\K[\w,; .-]*"),
     _xlpm.big_int_arr, _xlfn.TEXTSPLIT(_xlpm.big_ints,",",";"),
     core_BigInt.TextTreeProd(_xlpm.big_int_arr)
 )</f>
         <v>5</v>
       </c>
-      <c r="D394" s="12" t="b">
+      <c r="D387" s="12" t="b">
         <f>IF(ISERROR(TextTreeProd_Tests37[[#This Row],[expected]]),
     ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[expected]]) = ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[output]]),
     TextTreeProd_Tests37[[#This Row],[expected]] = TextTreeProd_Tests37[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E394" s="12" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="395" spans="1:5" hidden="1" outlineLevel="1">
-      <c r="A395" s="12" t="s">
-        <v>591</v>
-      </c>
-      <c r="B395" s="7" t="s">
-        <v>594</v>
-      </c>
-      <c r="C395" s="12" t="str" cm="1">
-        <f t="array" ref="C395">_xlfn.LET(
+      <c r="E387" s="12" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A388" s="12" t="s">
+        <v>584</v>
+      </c>
+      <c r="B388" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="C388" s="12" t="str" cm="1">
+        <f t="array" ref="C388">_xlfn.LET(
     _xlpm.big_ints, _xlfn.REGEXEXTRACT(TextTreeProd_Tests37[[#This Row],[input]], "{\K[\w,; .-]*"),
     _xlpm.big_int_arr, _xlfn.TEXTSPLIT(_xlpm.big_ints,",",";"),
     core_BigInt.TextTreeProd(_xlpm.big_int_arr)
 )</f>
         <v>6</v>
       </c>
-      <c r="D395" s="12" t="b">
+      <c r="D388" s="12" t="b">
         <f>IF(ISERROR(TextTreeProd_Tests37[[#This Row],[expected]]),
     ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[expected]]) = ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[output]]),
     TextTreeProd_Tests37[[#This Row],[expected]] = TextTreeProd_Tests37[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E395" s="12" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="396" spans="1:5" hidden="1" outlineLevel="1">
-      <c r="A396" s="12" t="s">
-        <v>592</v>
-      </c>
-      <c r="B396" s="7" t="s">
-        <v>595</v>
-      </c>
-      <c r="C396" s="12" t="str" cm="1">
-        <f t="array" ref="C396">_xlfn.LET(
+      <c r="E388" s="12" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A389" s="12" t="s">
+        <v>585</v>
+      </c>
+      <c r="B389" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="C389" s="12" t="str" cm="1">
+        <f t="array" ref="C389">_xlfn.LET(
     _xlpm.big_ints, _xlfn.REGEXEXTRACT(TextTreeProd_Tests37[[#This Row],[input]], "{\K[\w,; .-]*"),
     _xlpm.big_int_arr, _xlfn.TEXTSPLIT(_xlpm.big_ints,",",";"),
     core_BigInt.TextTreeProd(_xlpm.big_int_arr)
 )</f>
         <v>24</v>
       </c>
-      <c r="D396" s="12" t="b">
+      <c r="D389" s="12" t="b">
         <f>IF(ISERROR(TextTreeProd_Tests37[[#This Row],[expected]]),
     ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[expected]]) = ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[output]]),
     TextTreeProd_Tests37[[#This Row],[expected]] = TextTreeProd_Tests37[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E396" s="12" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="397" spans="1:5" hidden="1" outlineLevel="1">
-      <c r="A397" s="12" t="s">
-        <v>593</v>
-      </c>
-      <c r="B397" s="7" t="s">
-        <v>596</v>
-      </c>
-      <c r="C397" s="18" t="str" cm="1">
-        <f t="array" ref="C397">_xlfn.LET(
+      <c r="E389" s="12" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A390" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="B390" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="C390" s="12" t="str" cm="1">
+        <f t="array" ref="C390">_xlfn.LET(
     _xlpm.big_ints, _xlfn.REGEXEXTRACT(TextTreeProd_Tests37[[#This Row],[input]], "{\K[\w,; .-]*"),
     _xlpm.big_int_arr, _xlfn.TEXTSPLIT(_xlpm.big_ints,",",";"),
     core_BigInt.TextTreeProd(_xlpm.big_int_arr)
 )</f>
         <v>120</v>
       </c>
-      <c r="D397" s="18" t="b">
+      <c r="D390" s="12" t="b">
         <f>IF(ISERROR(TextTreeProd_Tests37[[#This Row],[expected]]),
     ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[expected]]) = ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[output]]),
     TextTreeProd_Tests37[[#This Row],[expected]] = TextTreeProd_Tests37[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E397" s="19" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="398" spans="1:5" collapsed="1">
-      <c r="D398" s="9" t="b">
+      <c r="E390" s="12" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" collapsed="1">
+      <c r="D391" s="9" t="b">
         <f>AND(TextTreeProd_Tests37[passing])</f>
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="15" thickBot="1"/>
-    <row r="400" spans="1:5" ht="18.5">
-      <c r="A400" s="5" t="s">
-        <v>622</v>
-      </c>
-      <c r="B400" s="5"/>
-      <c r="C400" s="5"/>
-      <c r="D400" s="5"/>
-      <c r="E400" s="5"/>
-    </row>
-    <row r="401" spans="1:5">
-      <c r="A401" t="s">
+    <row r="392" spans="1:5" ht="15" thickBot="1"/>
+    <row r="393" spans="1:5" ht="18.5">
+      <c r="A393" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="B393" s="5"/>
+      <c r="C393" s="5"/>
+      <c r="D393" s="5"/>
+      <c r="E393" s="5"/>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394" t="s">
         <v>110</v>
       </c>
-      <c r="B401" t="s">
+      <c r="B394" t="s">
         <v>35</v>
       </c>
-      <c r="C401" t="s">
+      <c r="C394" t="s">
         <v>36</v>
       </c>
-      <c r="D401" s="6" t="s">
+      <c r="D394" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E401" t="s">
+      <c r="E394" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="402" spans="1:5" hidden="1" outlineLevel="1">
-      <c r="A402" s="9" t="s">
+    <row r="395" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A395" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B402" s="9" t="s">
+      <c r="B395" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C402" s="9" t="str" cm="1">
-        <f t="array" ref="C402">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
-        <v>1</v>
-      </c>
-      <c r="D402" s="9" t="b">
+      <c r="C395" s="9" t="str" cm="1">
+        <f t="array" ref="C395">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
+        <v>1</v>
+      </c>
+      <c r="D395" s="9" t="b">
         <f>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
     Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E402" s="9" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="403" spans="1:5" hidden="1" outlineLevel="1">
-      <c r="A403" s="9" t="s">
+      <c r="E395" s="9" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A396" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B403" s="9" t="s">
+      <c r="B396" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C403" s="9" t="str" cm="1">
-        <f t="array" ref="C403">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
-        <v>1</v>
-      </c>
-      <c r="D403" s="9" t="b">
+      <c r="C396" s="9" t="str" cm="1">
+        <f t="array" ref="C396">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
+        <v>1</v>
+      </c>
+      <c r="D396" s="9" t="b">
         <f>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
     Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E403" s="9" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="404" spans="1:5" hidden="1" outlineLevel="1">
-      <c r="A404" s="9" t="s">
+      <c r="E396" s="9" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A397" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B404" s="9" t="s">
-        <v>596</v>
-      </c>
-      <c r="C404" s="9" t="str" cm="1">
-        <f t="array" ref="C404">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
+      <c r="B397" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="C397" s="9" t="str" cm="1">
+        <f t="array" ref="C397">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
         <v>120</v>
       </c>
-      <c r="D404" s="9" t="b">
+      <c r="D397" s="9" t="b">
         <f>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
     Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E404" s="9" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="405" spans="1:5" hidden="1" outlineLevel="1">
-      <c r="A405" s="9" t="s">
-        <v>617</v>
-      </c>
-      <c r="B405" s="9" t="s">
-        <v>618</v>
-      </c>
-      <c r="C405" s="20" t="str" cm="1">
-        <f t="array" ref="C405">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
+      <c r="E397" s="9" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A398" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="B398" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="C398" s="9" t="str" cm="1">
+        <f t="array" ref="C398">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
         <v>3628800</v>
       </c>
-      <c r="D405" s="20" t="b">
+      <c r="D398" s="9" t="b">
         <f>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
     Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E405" s="21" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="406" spans="1:5" hidden="1" outlineLevel="1">
-      <c r="A406" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="B406" s="9" t="e">
+      <c r="E398" s="9" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A399" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="B399" s="9" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="C406" s="20" t="e" cm="1">
-        <f t="array" ref="C406">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
+      <c r="C399" s="9" t="e" cm="1">
+        <f t="array" ref="C399">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
         <v>#NUM!</v>
       </c>
-      <c r="D406" s="20" t="b">
+      <c r="D399" s="9" t="b">
         <f>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
     Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E406" s="21" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="407" spans="1:5" hidden="1" outlineLevel="1">
-      <c r="A407" s="9" t="s">
-        <v>620</v>
-      </c>
-      <c r="B407" s="9" t="e">
+      <c r="E399" s="9" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A400" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="B400" s="9" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="C407" s="9" t="e" cm="1">
-        <f t="array" ref="C407">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
+      <c r="C400" s="9" t="e" cm="1">
+        <f t="array" ref="C400">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
         <v>#NUM!</v>
       </c>
-      <c r="D407" s="9" t="b">
+      <c r="D400" s="9" t="b">
         <f>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
     Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E407" s="9" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="408" spans="1:5" hidden="1" outlineLevel="1">
-      <c r="A408" s="9" t="s">
-        <v>621</v>
-      </c>
-      <c r="B408" s="9" t="e">
+      <c r="E400" s="9" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A401" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="B401" s="9" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="C408" s="9" t="e" cm="1">
-        <f t="array" ref="C408">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
+      <c r="C401" s="9" t="e" cm="1">
+        <f t="array" ref="C401">BigInt.Fact(Fact_Tests[[#This Row],[input]])</f>
         <v>#NUM!</v>
       </c>
-      <c r="D408" s="9" t="b">
+      <c r="D401" s="9" t="b">
         <f>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
     Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E408" s="9" t="s">
+      <c r="E401" s="9" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" collapsed="1">
+      <c r="A402" s="2"/>
+      <c r="D402" t="b">
+        <f>AND(Fact_Tests[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" ht="15" thickBot="1"/>
+    <row r="404" spans="1:5" ht="18.5">
+      <c r="A404" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="B404" s="5"/>
+      <c r="C404" s="5"/>
+      <c r="D404" s="5"/>
+      <c r="E404" s="5"/>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405" t="s">
+        <v>110</v>
+      </c>
+      <c r="B405" t="s">
+        <v>35</v>
+      </c>
+      <c r="C405" t="s">
+        <v>36</v>
+      </c>
+      <c r="D405" t="s">
+        <v>48</v>
+      </c>
+      <c r="E405" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A406" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="B406" s="12" t="s">
+        <v>619</v>
+      </c>
+      <c r="C406" s="12" t="str" cm="1">
+        <f t="array" ref="C406">_xlfn.LET(
+    _xlpm.n_primes, _xlfn.REGEXEXTRACT(NativeSwingExponents_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.n, --INDEX(_xlpm.n_primes,1,1),
+    _xlpm.primes, INDEX(_xlpm.n_primes,1,2),
+    _xlpm.primes_arr, --_xlfn.TEXTSPLIT(_xlpm.primes,",",";"),
+    _xlpm.output, core_BigInt.NativeSwingExponents(_xlpm.n, _xlpm.primes_arr),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{1;1;1}</v>
+      </c>
+      <c r="D406" s="12" t="b">
+        <f>IF(ISERROR(NativeSwingExponents_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NativeSwingExponents_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativeSwingExponents_Tests[[#This Row],[output]]),
+    NativeSwingExponents_Tests[[#This Row],[expected]] = NativeSwingExponents_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E406" s="12" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="409" spans="1:5" collapsed="1">
-      <c r="A409" s="2"/>
-      <c r="D409" t="b">
-        <f>AND(Fact_Tests[passing])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="418" spans="1:2" ht="14.5" customHeight="1"/>
-    <row r="421" spans="1:2" ht="14.5" customHeight="1"/>
-    <row r="424" spans="1:2" ht="14.5" customHeight="1"/>
-    <row r="427" spans="1:2" ht="14.5" customHeight="1">
-      <c r="A427" cm="1">
-        <f t="array" ref="A427:A428">LEN(B427:B428)</f>
+    <row r="407" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A407" s="12" t="s">
+        <v>580</v>
+      </c>
+      <c r="B407" s="12" t="s">
+        <v>620</v>
+      </c>
+      <c r="C407" s="12" t="str" cm="1">
+        <f t="array" ref="C407">_xlfn.LET(
+    _xlpm.n_primes, _xlfn.REGEXEXTRACT(NativeSwingExponents_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.n, --INDEX(_xlpm.n_primes,1,1),
+    _xlpm.primes, INDEX(_xlpm.n_primes,1,2),
+    _xlpm.primes_arr, --_xlfn.TEXTSPLIT(_xlpm.primes,",",";"),
+    _xlpm.output, core_BigInt.NativeSwingExponents(_xlpm.n, _xlpm.primes_arr),
+    _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
+)</f>
+        <v>{2;2;0;1}</v>
+      </c>
+      <c r="D407" s="12" t="b">
+        <f>IF(ISERROR(NativeSwingExponents_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(NativeSwingExponents_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativeSwingExponents_Tests[[#This Row],[output]]),
+    NativeSwingExponents_Tests[[#This Row],[expected]] = NativeSwingExponents_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E407" s="12" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" collapsed="1">
+      <c r="D408" s="9" t="b">
+        <f>AND(NativeSwingExponents_Tests[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" ht="15" thickBot="1"/>
+    <row r="410" spans="1:5" ht="18.5">
+      <c r="A410" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="B410" s="5"/>
+      <c r="C410" s="5"/>
+      <c r="D410" s="5"/>
+      <c r="E410" s="5"/>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411" t="s">
+        <v>110</v>
+      </c>
+      <c r="B411" t="s">
+        <v>35</v>
+      </c>
+      <c r="C411" t="s">
+        <v>36</v>
+      </c>
+      <c r="D411" t="s">
+        <v>48</v>
+      </c>
+      <c r="E411" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A412" s="12" t="s">
+        <v>623</v>
+      </c>
+      <c r="B412" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="C412" s="12" t="str" cm="1">
+        <f t="array" ref="C412">_xlfn.LET(
+    _xlpm.n_primes, _xlfn.REGEXEXTRACT(PrimeSwingKernel_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.n, --INDEX(_xlpm.n_primes,1,1),
+    _xlpm.primes, INDEX(_xlpm.n_primes,1,2),
+    _xlpm.primes_arr, --_xlfn.TEXTSPLIT(_xlpm.primes,",",";"),
+    core_BigInt.PrimeSwingKernel(_xlpm.n, _xlpm.primes_arr)
+)</f>
+        <v>120</v>
+      </c>
+      <c r="D412" s="12" t="b">
+        <f>IF(ISERROR(PrimeSwingKernel_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(PrimeSwingKernel_Tests[[#This Row],[expected]]) = ERROR.TYPE(PrimeSwingKernel_Tests[[#This Row],[output]]),
+    PrimeSwingKernel_Tests[[#This Row],[expected]] = PrimeSwingKernel_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E412" s="12" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A413" s="12" t="s">
+        <v>624</v>
+      </c>
+      <c r="B413" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="C413" s="12" t="str" cm="1">
+        <f t="array" ref="C413">_xlfn.LET(
+    _xlpm.n_primes, _xlfn.REGEXEXTRACT(PrimeSwingKernel_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.n, --INDEX(_xlpm.n_primes,1,1),
+    _xlpm.primes, INDEX(_xlpm.n_primes,1,2),
+    _xlpm.primes_arr, --_xlfn.TEXTSPLIT(_xlpm.primes,",",";"),
+    core_BigInt.PrimeSwingKernel(_xlpm.n, _xlpm.primes_arr)
+)</f>
+        <v>3628800</v>
+      </c>
+      <c r="D413" s="12" t="b">
+        <f>IF(ISERROR(PrimeSwingKernel_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(PrimeSwingKernel_Tests[[#This Row],[expected]]) = ERROR.TYPE(PrimeSwingKernel_Tests[[#This Row],[output]]),
+    PrimeSwingKernel_Tests[[#This Row],[expected]] = PrimeSwingKernel_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E413" s="12" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" collapsed="1">
+      <c r="D414" s="9" t="b">
+        <f>AND(PrimeSwingKernel_Tests[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" ht="15" thickBot="1"/>
+    <row r="416" spans="1:5" ht="18.5">
+      <c r="A416" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="B416" s="5"/>
+      <c r="C416" s="5"/>
+      <c r="D416" s="5"/>
+      <c r="E416" s="5"/>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417" t="s">
+        <v>110</v>
+      </c>
+      <c r="B417" t="s">
+        <v>35</v>
+      </c>
+      <c r="C417" t="s">
+        <v>36</v>
+      </c>
+      <c r="D417" t="s">
+        <v>48</v>
+      </c>
+      <c r="E417" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A418" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="B418" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C418" s="12" t="str" cm="1">
+        <f t="array" ref="C418">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(TreeCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.mode, --INDEX(_xlpm.range_mode,1,2),
+    _xlpm.range_arr, _xlfn.TEXTSPLIT(_xlpm.range,",",";"),
+    core_BigInt.TreeCompare(_xlpm.range_arr, _xlpm.mode)
+)</f>
+        <v>30</v>
+      </c>
+      <c r="D418" s="12" t="b">
+        <f>IF(ISERROR(TreeCompare_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(TreeCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(TreeCompare_Tests[[#This Row],[output]]),
+    TreeCompare_Tests[[#This Row],[expected]] = TreeCompare_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E418" s="12" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A419" s="12" t="s">
+        <v>631</v>
+      </c>
+      <c r="B419" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C419" s="18" t="str" cm="1">
+        <f t="array" ref="C419">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(TreeCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.mode, --INDEX(_xlpm.range_mode,1,2),
+    _xlpm.range_arr, _xlfn.TEXTSPLIT(_xlpm.range,",",";"),
+    core_BigInt.TreeCompare(_xlpm.range_arr, _xlpm.mode)
+)</f>
+        <v>5</v>
+      </c>
+      <c r="D419" s="18" t="b">
+        <f>IF(ISERROR(TreeCompare_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(TreeCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(TreeCompare_Tests[[#This Row],[output]]),
+    TreeCompare_Tests[[#This Row],[expected]] = TreeCompare_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E419" s="19" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A420" s="12" t="s">
+        <v>632</v>
+      </c>
+      <c r="B420" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C420" s="18" t="str" cm="1">
+        <f t="array" ref="C420">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(TreeCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.mode, --INDEX(_xlpm.range_mode,1,2),
+    _xlpm.range_arr, _xlfn.TEXTSPLIT(_xlpm.range,",",";"),
+    core_BigInt.TreeCompare(_xlpm.range_arr, _xlpm.mode)
+)</f>
+        <v>30</v>
+      </c>
+      <c r="D420" s="18" t="b">
+        <f>IF(ISERROR(TreeCompare_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(TreeCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(TreeCompare_Tests[[#This Row],[output]]),
+    TreeCompare_Tests[[#This Row],[expected]] = TreeCompare_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E420" s="19" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A421" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="B421" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="C421" s="18" t="str" cm="1">
+        <f t="array" ref="C421">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(TreeCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.mode, --INDEX(_xlpm.range_mode,1,2),
+    _xlpm.range_arr, _xlfn.TEXTSPLIT(_xlpm.range,",",";"),
+    core_BigInt.TreeCompare(_xlpm.range_arr, _xlpm.mode)
+)</f>
+        <v>10</v>
+      </c>
+      <c r="D421" s="18" t="b">
+        <f>IF(ISERROR(TreeCompare_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(TreeCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(TreeCompare_Tests[[#This Row],[output]]),
+    TreeCompare_Tests[[#This Row],[expected]] = TreeCompare_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E421" s="19" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A422" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="B422" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="C422" s="18" t="str" cm="1">
+        <f t="array" ref="C422">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(TreeCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.mode, --INDEX(_xlpm.range_mode,1,2),
+    _xlpm.range_arr, _xlfn.TEXTSPLIT(_xlpm.range,",",";"),
+    core_BigInt.TreeCompare(_xlpm.range_arr, _xlpm.mode)
+)</f>
+        <v>-10</v>
+      </c>
+      <c r="D422" s="18" t="b">
+        <f>IF(ISERROR(TreeCompare_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(TreeCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(TreeCompare_Tests[[#This Row],[output]]),
+    TreeCompare_Tests[[#This Row],[expected]] = TreeCompare_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E422" s="19" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A423" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="B423" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C423" s="18" t="str" cm="1">
+        <f t="array" ref="C423">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(TreeCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.mode, --INDEX(_xlpm.range_mode,1,2),
+    _xlpm.range_arr, _xlfn.TEXTSPLIT(_xlpm.range,",",";"),
+    core_BigInt.TreeCompare(_xlpm.range_arr, _xlpm.mode)
+)</f>
+        <v>5</v>
+      </c>
+      <c r="D423" s="18" t="b">
+        <f>IF(ISERROR(TreeCompare_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(TreeCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(TreeCompare_Tests[[#This Row],[output]]),
+    TreeCompare_Tests[[#This Row],[expected]] = TreeCompare_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E423" s="19" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" ht="29" hidden="1" outlineLevel="1">
+      <c r="A424" s="12" t="s">
+        <v>627</v>
+      </c>
+      <c r="B424" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="C424" s="12" t="str" cm="1">
+        <f t="array" ref="C424">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(TreeCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.mode, --INDEX(_xlpm.range_mode,1,2),
+    _xlpm.range_arr, _xlfn.TEXTSPLIT(_xlpm.range,",",";"),
+    core_BigInt.TreeCompare(_xlpm.range_arr, _xlpm.mode)
+)</f>
+        <v>42</v>
+      </c>
+      <c r="D424" s="12" t="b">
+        <f>IF(ISERROR(TreeCompare_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(TreeCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(TreeCompare_Tests[[#This Row],[output]]),
+    TreeCompare_Tests[[#This Row],[expected]] = TreeCompare_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E424" s="12" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" collapsed="1">
+      <c r="D425" s="9" t="b">
+        <f>AND(TreeCompare_Tests[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" ht="15" thickBot="1"/>
+    <row r="427" spans="1:5" ht="18.5">
+      <c r="A427" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="B427" s="5"/>
+      <c r="C427" s="5"/>
+      <c r="D427" s="5"/>
+      <c r="E427" s="5"/>
+    </row>
+    <row r="428" spans="1:5">
+      <c r="A428" t="s">
+        <v>110</v>
+      </c>
+      <c r="B428" t="s">
+        <v>35</v>
+      </c>
+      <c r="C428" t="s">
+        <v>36</v>
+      </c>
+      <c r="D428" t="s">
+        <v>48</v>
+      </c>
+      <c r="E428" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A429" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="B429" s="12" t="s">
+        <v>648</v>
+      </c>
+      <c r="C429" s="12" t="str" cm="1">
+        <f t="array" ref="C429">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(Max_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.range_arr, IFERROR(_xlfn.TEXTSPLIT(_xlpm.range,",",";"),_xlpm.range),
+    BigInt.Max(_xlpm.range_arr)
+)</f>
+        <v>20</v>
+      </c>
+      <c r="D429" s="12" t="b">
+        <f>IF(ISERROR(Max_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Max_Tests[[#This Row],[expected]]) = ERROR.TYPE(Max_Tests[[#This Row],[output]]),
+    Max_Tests[[#This Row],[expected]] = Max_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E429" s="12" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A430" s="12" t="s">
+        <v>646</v>
+      </c>
+      <c r="B430" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="C430" s="18" t="str" cm="1">
+        <f t="array" ref="C430">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(Max_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.range_arr, IFERROR(_xlfn.TEXTSPLIT(_xlpm.range,",",";"),_xlpm.range),
+    BigInt.Max(_xlpm.range_arr)
+)</f>
+        <v>9</v>
+      </c>
+      <c r="D430" s="18" t="b">
+        <f>IF(ISERROR(Max_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Max_Tests[[#This Row],[expected]]) = ERROR.TYPE(Max_Tests[[#This Row],[output]]),
+    Max_Tests[[#This Row],[expected]] = Max_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E430" s="19" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A431" s="12" t="s">
+        <v>650</v>
+      </c>
+      <c r="B431" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C431" s="18" t="str" cm="1">
+        <f t="array" ref="C431">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(Max_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.range_arr, IFERROR(_xlfn.TEXTSPLIT(_xlpm.range,",",";"),_xlpm.range),
+    BigInt.Max(_xlpm.range_arr)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="D431" s="18" t="b">
+        <f>IF(ISERROR(Max_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Max_Tests[[#This Row],[expected]]) = ERROR.TYPE(Max_Tests[[#This Row],[output]]),
+    Max_Tests[[#This Row],[expected]] = Max_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E431" s="19" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A432" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="B432" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C432" s="18" t="str" cm="1">
+        <f t="array" ref="C432">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(Max_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.range_arr, IFERROR(_xlfn.TEXTSPLIT(_xlpm.range,",",";"),_xlpm.range),
+    BigInt.Max(_xlpm.range_arr)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="D432" s="18" t="b">
+        <f>IF(ISERROR(Max_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Max_Tests[[#This Row],[expected]]) = ERROR.TYPE(Max_Tests[[#This Row],[output]]),
+    Max_Tests[[#This Row],[expected]] = Max_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E432" s="19" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A433" s="12" t="s">
+        <v>647</v>
+      </c>
+      <c r="B433" s="12" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C433" s="18" t="e" cm="1">
+        <f t="array" ref="C433">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(Max_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.range_arr, IFERROR(_xlfn.TEXTSPLIT(_xlpm.range,",",";"),_xlpm.range),
+    BigInt.Max(_xlpm.range_arr)
+)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D433" s="18" t="b">
+        <f>IF(ISERROR(Max_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Max_Tests[[#This Row],[expected]]) = ERROR.TYPE(Max_Tests[[#This Row],[output]]),
+    Max_Tests[[#This Row],[expected]] = Max_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E433" s="19" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" ht="15" collapsed="1" thickBot="1">
+      <c r="D434" s="9" t="b">
+        <f>AND(Max_Tests[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" ht="18.5">
+      <c r="A435" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="B435" s="5"/>
+      <c r="C435" s="5"/>
+      <c r="D435" s="5"/>
+      <c r="E435" s="5"/>
+    </row>
+    <row r="436" spans="1:5">
+      <c r="A436" t="s">
+        <v>110</v>
+      </c>
+      <c r="B436" t="s">
+        <v>35</v>
+      </c>
+      <c r="C436" t="s">
+        <v>36</v>
+      </c>
+      <c r="D436" t="s">
+        <v>48</v>
+      </c>
+      <c r="E436" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A437" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="B437" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C437" s="12" t="str" cm="1">
+        <f t="array" ref="C437">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(Min_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.range_arr, IFERROR(_xlfn.TEXTSPLIT(_xlpm.range,",",";"),_xlpm.range),
+    BigInt.Min(_xlpm.range_arr)
+)</f>
+        <v>5</v>
+      </c>
+      <c r="D437" s="12" t="b">
+        <f>IF(ISERROR(Min_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Min_Tests[[#This Row],[expected]]) = ERROR.TYPE(Min_Tests[[#This Row],[output]]),
+    Min_Tests[[#This Row],[expected]] = Min_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E437" s="12" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A438" s="12" t="s">
+        <v>646</v>
+      </c>
+      <c r="B438" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="C438" s="18" t="str" cm="1">
+        <f t="array" ref="C438">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(Min_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.range_arr, IFERROR(_xlfn.TEXTSPLIT(_xlpm.range,",",";"),_xlpm.range),
+    BigInt.Min(_xlpm.range_arr)
+)</f>
+        <v>7</v>
+      </c>
+      <c r="D438" s="18" t="b">
+        <f>IF(ISERROR(Min_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Min_Tests[[#This Row],[expected]]) = ERROR.TYPE(Min_Tests[[#This Row],[output]]),
+    Min_Tests[[#This Row],[expected]] = Min_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E438" s="19" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A439" s="12" t="s">
+        <v>650</v>
+      </c>
+      <c r="B439" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C439" s="18" t="str" cm="1">
+        <f t="array" ref="C439">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(Min_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.range_arr, IFERROR(_xlfn.TEXTSPLIT(_xlpm.range,",",";"),_xlpm.range),
+    BigInt.Min(_xlpm.range_arr)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="D439" s="18" t="b">
+        <f>IF(ISERROR(Min_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Min_Tests[[#This Row],[expected]]) = ERROR.TYPE(Min_Tests[[#This Row],[output]]),
+    Min_Tests[[#This Row],[expected]] = Min_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E439" s="19" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A440" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="B440" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C440" s="18" t="str" cm="1">
+        <f t="array" ref="C440">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(Min_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.range_arr, IFERROR(_xlfn.TEXTSPLIT(_xlpm.range,",",";"),_xlpm.range),
+    BigInt.Min(_xlpm.range_arr)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="D440" s="18" t="b">
+        <f>IF(ISERROR(Min_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Min_Tests[[#This Row],[expected]]) = ERROR.TYPE(Min_Tests[[#This Row],[output]]),
+    Min_Tests[[#This Row],[expected]] = Min_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E440" s="19" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" hidden="1" outlineLevel="1">
+      <c r="A441" s="12" t="s">
+        <v>647</v>
+      </c>
+      <c r="B441" s="12" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C441" s="18" t="e" cm="1">
+        <f t="array" ref="C441">_xlfn.LET(
+    _xlpm.range_mode, _xlfn.REGEXEXTRACT(Min_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
+    _xlpm.range, INDEX(_xlpm.range_mode,1,1),
+    _xlpm.range_arr, IFERROR(_xlfn.TEXTSPLIT(_xlpm.range,",",";"),_xlpm.range),
+    BigInt.Min(_xlpm.range_arr)
+)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D441" s="18" t="b">
+        <f>IF(ISERROR(Min_Tests[[#This Row],[expected]]),
+    ERROR.TYPE(Min_Tests[[#This Row],[expected]]) = ERROR.TYPE(Min_Tests[[#This Row],[output]]),
+    Min_Tests[[#This Row],[expected]] = Min_Tests[[#This Row],[output]]
+)</f>
+        <v>1</v>
+      </c>
+      <c r="E441" s="19" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" collapsed="1">
+      <c r="D442" s="9" t="b">
+        <f>AND(Min_Tests[passing])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457" ht="14.5" customHeight="1"/>
+    <row r="460" ht="14.5" customHeight="1"/>
+    <row r="463" ht="14.5" customHeight="1"/>
+    <row r="465" spans="1:2">
+      <c r="A465" cm="1">
+        <f t="array" ref="A465:A466">LEN(B465:B466)</f>
         <v>68</v>
       </c>
-      <c r="B427" t="str" cm="1">
-        <f t="array" ref="B427">BigInt.Fact(B430)</f>
+      <c r="B465" t="str" cm="1">
+        <f t="array" ref="B465">BigInt.Fact(B468)</f>
         <v>80658175170943878571660636856403766975289505440883277824000000000000</v>
       </c>
     </row>
-    <row r="428" spans="1:2">
-      <c r="A428">
+    <row r="466" spans="1:2" ht="14.5" customHeight="1">
+      <c r="A466">
         <v>68</v>
       </c>
-      <c r="B428" t="str" cm="1">
-        <f t="array" ref="B428">_xlfn._xlws.PY(0,0,B430,B431)</f>
+      <c r="B466" t="str" cm="1">
+        <f t="array" ref="B466">_xlfn._xlws.PY(0,0,B468,B469)</f>
         <v>80658175170943878571660636856403766975289505440883277824000000000000</v>
       </c>
     </row>
-    <row r="429" spans="1:2">
-      <c r="B429" t="b">
-        <f>B427 = B428</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="430" spans="1:2" ht="14.5" customHeight="1">
-      <c r="A430">
-        <f>LEN(B430)</f>
+    <row r="467" spans="1:2">
+      <c r="B467" t="b">
+        <f>B465 = B466</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468">
+        <f>LEN(B468)</f>
         <v>2</v>
       </c>
-      <c r="B430" s="2">
+      <c r="B468" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="431" spans="1:2">
-      <c r="B431">
+    <row r="469" spans="1:2" ht="14.5" customHeight="1">
+      <c r="B469">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A420:E422">
-    <sortCondition ref="A418:A422"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A458:E460">
+    <sortCondition ref="A456:A460"/>
   </sortState>
-  <conditionalFormatting sqref="B429">
-    <cfRule type="cellIs" dxfId="57" priority="19" operator="equal">
+  <conditionalFormatting sqref="B467">
+    <cfRule type="cellIs" dxfId="60" priority="33" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8:D26 D150:D160 D265:D280 D284:D289 D317:D324 D378:D381 D394:D398 D385:D390">
-    <cfRule type="expression" dxfId="56" priority="88" stopIfTrue="1">
+  <conditionalFormatting sqref="D8:D26 D150:D160 D265:D280 D284:D289 D317:D324 D378:D383 D387:D391 D406:D408 D429:D434 D437:D442">
+    <cfRule type="expression" dxfId="59" priority="102" stopIfTrue="1">
       <formula>$D8</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="89">
+    <cfRule type="expression" dxfId="58" priority="103">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:D37 D86:D94 D118:D124">
-    <cfRule type="expression" dxfId="54" priority="86" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="100" stopIfTrue="1">
       <formula>$D30</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="87">
+    <cfRule type="expression" dxfId="56" priority="101">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41:D46">
-    <cfRule type="expression" dxfId="52" priority="82" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="96" stopIfTrue="1">
       <formula>$D41</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="83">
+    <cfRule type="expression" dxfId="54" priority="97">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:D60">
-    <cfRule type="expression" dxfId="50" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="86" stopIfTrue="1">
       <formula>$D50</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="73">
+    <cfRule type="expression" dxfId="52" priority="87">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D64:D71">
-    <cfRule type="expression" dxfId="48" priority="80" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="94" stopIfTrue="1">
       <formula>$D64</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="81">
+    <cfRule type="expression" dxfId="50" priority="95">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75:D82">
-    <cfRule type="expression" dxfId="46" priority="78" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="92" stopIfTrue="1">
       <formula>$D75</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="79">
+    <cfRule type="expression" dxfId="48" priority="93">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D98:D104">
-    <cfRule type="expression" dxfId="44" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="84" stopIfTrue="1">
       <formula>$D98</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="71">
+    <cfRule type="expression" dxfId="46" priority="85">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:D114">
-    <cfRule type="expression" dxfId="42" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="82" stopIfTrue="1">
       <formula>$D108</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="69">
+    <cfRule type="expression" dxfId="44" priority="83">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D128:D135">
-    <cfRule type="expression" dxfId="40" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="78" stopIfTrue="1">
       <formula>$D128</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="65">
+    <cfRule type="expression" dxfId="42" priority="79">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D139:D146">
-    <cfRule type="expression" dxfId="38" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="76" stopIfTrue="1">
       <formula>$D139</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="63">
+    <cfRule type="expression" dxfId="40" priority="77">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D164:D169">
-    <cfRule type="expression" dxfId="36" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="70" stopIfTrue="1">
       <formula>$D164</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="57">
+    <cfRule type="expression" dxfId="38" priority="71">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D173:D176">
-    <cfRule type="expression" dxfId="34" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="68" stopIfTrue="1">
       <formula>$D173</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="55">
+    <cfRule type="expression" dxfId="36" priority="69">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D180:D183">
-    <cfRule type="expression" dxfId="32" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="64" stopIfTrue="1">
       <formula>$D180</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="51">
+    <cfRule type="expression" dxfId="34" priority="65">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D187:D191">
-    <cfRule type="expression" dxfId="30" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="62" stopIfTrue="1">
       <formula>$D187</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="49">
+    <cfRule type="expression" dxfId="32" priority="63">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D195:D202">
-    <cfRule type="expression" dxfId="28" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="60" stopIfTrue="1">
       <formula>$D195</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="47">
+    <cfRule type="expression" dxfId="30" priority="61">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D206:D211">
-    <cfRule type="expression" dxfId="26" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="56" stopIfTrue="1">
       <formula>$D206</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="43">
+    <cfRule type="expression" dxfId="28" priority="57">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D215:D221">
-    <cfRule type="expression" dxfId="24" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="54" stopIfTrue="1">
       <formula>$D215</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="41">
+    <cfRule type="expression" dxfId="26" priority="55">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D225:D233">
-    <cfRule type="expression" dxfId="22" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="50" stopIfTrue="1">
       <formula>$D225</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="37">
+    <cfRule type="expression" dxfId="24" priority="51">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D237:D247">
-    <cfRule type="expression" dxfId="20" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="48" stopIfTrue="1">
       <formula>$D237</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="35">
+    <cfRule type="expression" dxfId="22" priority="49">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D251:D261">
-    <cfRule type="expression" dxfId="18" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="46" stopIfTrue="1">
       <formula>$D251</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="33">
+    <cfRule type="expression" dxfId="20" priority="47">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D293:D301">
-    <cfRule type="expression" dxfId="16" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="40" stopIfTrue="1">
       <formula>$D293</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="27">
+    <cfRule type="expression" dxfId="18" priority="41">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D305:D313">
-    <cfRule type="expression" dxfId="14" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="38" stopIfTrue="1">
       <formula>$D305</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="25">
+    <cfRule type="expression" dxfId="16" priority="39">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D328:D341">
-    <cfRule type="expression" dxfId="12" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="36" stopIfTrue="1">
       <formula>$D328</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="23">
+    <cfRule type="expression" dxfId="14" priority="37">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D345:D348">
-    <cfRule type="expression" dxfId="10" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="31" stopIfTrue="1">
       <formula>$D345</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="18">
+    <cfRule type="expression" dxfId="12" priority="32">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D352:D356">
-    <cfRule type="expression" dxfId="8" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="29" stopIfTrue="1">
       <formula>$D352</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="16">
+    <cfRule type="expression" dxfId="10" priority="30">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D360:D365">
-    <cfRule type="expression" dxfId="6" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="27" stopIfTrue="1">
       <formula>$D360</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="14">
+    <cfRule type="expression" dxfId="8" priority="28">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D369:D374">
-    <cfRule type="expression" dxfId="4" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="23" stopIfTrue="1">
       <formula>$D369</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="10">
+    <cfRule type="expression" dxfId="6" priority="24">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D402:D409">
-    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
-      <formula>$D402</formula>
+  <conditionalFormatting sqref="D395:D402">
+    <cfRule type="expression" dxfId="5" priority="15" stopIfTrue="1">
+      <formula>$D395</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="4" priority="16">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D412:D414">
+    <cfRule type="expression" dxfId="3" priority="11" stopIfTrue="1">
+      <formula>$D412</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="12">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D418:D425">
+    <cfRule type="expression" dxfId="1" priority="9" stopIfTrue="1">
+      <formula>$D418</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="37">
+  <tableParts count="41">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -20086,6 +22595,10 @@
     <tablePart r:id="rId36"/>
     <tablePart r:id="rId37"/>
     <tablePart r:id="rId38"/>
+    <tablePart r:id="rId39"/>
+    <tablePart r:id="rId40"/>
+    <tablePart r:id="rId41"/>
+    <tablePart r:id="rId42"/>
   </tableParts>
 </worksheet>
 </file>
@@ -20320,7 +22833,7 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAFwAbgAvAC8AIABCAGkAZwAgAEkAbgB0AGUAZwBlAHIAIABBAHIAaQB0AGgAbQBlAHQAaQBjACAATABpAGIAcgBhAHIAeQAgAC8ALwBcAG4ALwAvACAAIAAgACAAIAAgACAAdABlAHMAdABfAEIAaQBnAEkAbgB0ACAATQBvAGQAdQBsAGUAIAAgACAAIAAgACAAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIAAgAFAAcgBpAHYAYQB0AGUAIABUAGUAcwB0AGkAbgBnACAAQQBQAEkAIAAgACAAIAAgACAALwAvAFwAbgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4AXABuAEsAbgB1AHQAaABEAGkAdgBpAHMAaQBvAG4APQBMAEEATQBCAEQAQQAoAGEALAAgAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2ACgAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYQAsACAAawApACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABiACwAIABrACkALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAEQAUgBPAFAAKABwAGEAYwBrAGUAZAAsACAASQBOAEQARQBYACgAcABhAGMAawBlAGQALAAgADEALAAgADEAKQAgACsAIAAxACkALAAgAGsAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAgAD0AIABMAEEATQBCAEQAQQAoAGEALAAgAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgAoAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAGEALAAgAGsAKQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYgAsACAAawApACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABEAFIATwBQACgAcABhAGMAawBlAGQALAAgAEkATgBEAEUAWAAoAHAAYQBjAGsAZQBkACwAIAAxACwAIAAxACkAIAArACAAMQApACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAcwB0AHIAaQBuAGcAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAHMAdAByAGkAbgBnAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG0AbwBkAGUAIABcACIASwBOAFUAVABIAFwAIgAgAG8AcgAgAFwAIgBOAFIAXAAiAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGkAdABlAHIAcwAgAEkAbgBuAGUAcgAgAGwAbwBvAHAAIABjAG8AdQBuAHQAIAAoAHQAbwAgAGQAZQBmAGUAYQB0ACAAYwBoAHUAbgBrAHkAIABjAGwAbwBjAGsAIAByAGUAcwBvAGwAdQB0AGkAbwBuACkAXABuACAAKgAgAEAAcABhAHIAYQBtACAAcgBlAHAAZQBhAHQAcwAgAE8AdQB0AGUAcgAgAGwAbwBvAHAAIABjAG8AdQBuAHQAIAAoAHQAbwAgAGQAZQBmAGUAYQB0ACAATwBTAC8ARwBhAHIAYgBhAGcAZQAgAEMAbwBsAGwAZQBjAHQAaQBvAG4AIABuAG8AaQBzAGUAKQBcAG4AIAAqAC8AXABuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACAAPQAgAEwAQQBNAEIARABBACgAYQAsACAAYgAsACAAbQBvAGQAZQAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAE0AYQBwACAAdABoAGUAIABvAHUAdABlAHIAIAByAGUAcABlAGEAdABzACAAbABvAG8AcABcAG4AIAAgACAAIAAgACAAIAAgAGIAYQB0AGMAaABfAHQAaQBtAGUAcwAsACAATQBBAFAAKABTAEUAUQBVAEUATgBDAEUAKAByAGUAcABlAGEAdABzACkALAAgAEwAQQBNAEIARABBACgAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdAAsACAATgBPAFcAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATQBhAHAAIAB0AGgAZQAgAGkAbgBuAGUAcgAgAGUAeABlAGMAdQB0AGkAbwBuACAAbABvAG8AcABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAHUAbgAsACAASQBGACgAbQBvAGQAZQAgAD0AIABcACIASwBOAFUAVABIAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBQACgAUwBFAFEAVQBFAE4AQwBFACgAaQB0AGUAcgBzACkALAAgAEwAQQBNAEIARABBACgAaQAsACAASwBuAHUAdABoAEQAaQB2AGkAcwBpAG8AbgAoAGEALAAgAGIAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFAAKABTAEUAUQBVAEUATgBDAEUAKABpAHQAZQByAHMAKQAsACAATABBAE0AQgBEAEEAKABpACwAIABOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAoAGEALAAgAGIAKQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEYAbwByAGMAZQAgAGUAdgBhAGwAdQBhAHQAaQBvAG4AIABiAGUAZgBvAHIAZQAgAHAAdQBsAGwAaQBuAGcAIABzAHQAbwBwACAAdABpAG0AZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAbwBwACwAIABOAE8AVwAoACkAIAArACAAKAAwACAAKgAgAEwARQBOACgASQBOAEQARQBYACgAcgB1AG4ALAAgADEALAAgADEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABUAG8AdABhAGwAIABiAGEAdABjAGgAIAB0AGkAbQBlACAAaQBuACAAbQBpAGwAbABpAHMAZQBjAG8AbgBkAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABzAHQAbwBwACAALQAgAHMAdABhAHIAdAApACAAKgAgADgANgA0ADAAMAAwADAAMABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAdABoAGUAIABjAGwAZQBhAG4AZQBzAHQAIAByAHUAbgAgAGEAbgBkACAAYQB2AGUAcgBhAGcAZQAgAGkAdAAgAGQAbwB3AG4AIAB0AG8AIABhACAAcwBpAG4AZwBsAGUAIABlAHgAZQBjAHUAdABpAG8AbgAgAHQAaQBtAGUAXABuACAAIAAgACAAIAAgACAAIABNAEkATgAoAGIAYQB0AGMAaABfAHQAaQBtAGUAcwApACAALwAgAGkAdABlAHIAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAARQB4AGUAYwB1AHQAZQBzACAAYQAgAHMAdAByAGkAYwB0AGwAeQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABiAGUAbgBjAGgAbQBhAHIAawAgAHMAdQBpAHQAZQAgAHQAbwAgAGEAdgBvAGkAZAAgAG0AdQBsAHQAaQAtAHQAaAByAGUAYQBkAGkAbgBnACAAYwBvAG4AdABhAG0AaQBuAGEAdABpAG8AbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHQAZQBzAHQAXwBjAGEAcwBlAHMAIABBAG4AIABOACAAeAAgADIAIABhAHIAcgBhAHkAIABvAGYAIAB0AGUAcwB0ACAAbABlAG4AZwB0AGgAcwA6ACAAWwBMAGUAbgBnAHQAaABfAEEALAAgAEwAZQBuAGcAdABoAF8AQgBdAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGkAdABlAHIAcwAgAE4AdQBtAGIAZQByACAAbwBmACAAaQB0AGUAcgBhAHQAaQBvAG4AcwAgAHAAZQByACAAYgBlAG4AYwBoAG0AYQByAGsAIAB0AG8AIABzAG0AbwBvAHQAaAAgAE4ATwBXACgAKQAgAHIAZQBzAG8AbAB1AHQAaQBvAG4ALgBcAG4AIAAqAC8AXABuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBDAG8AbQBwAGEAcgBpAHMAbwBuACAAPQAgAEwAQQBNAEIARABBACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwB0AGUAcwB0AHMALAAgAFIATwBXAFMAKAB0AGUAcwB0AF8AYwBhAHMAZQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAASQBuAGkAdABpAGEAbAAgAHMAdABhAHQAZQA6ACAARABhAHQAYQAgAGgAZQBhAGQAZQByAHMAIABmAG8AcgAgAEMAUwBWACAAZQB4AHAAbwByAHQAXABuACAAIAAgACAAIAAgACAAIABpAG4AaQB0AGkAYQBsACwAIAB7AFwAIgBMAGUAbgBfAEEAXAAiACwAIABcACIATABlAG4AXwBCAFwAIgAsACAAXAAiAEsAbgB1AHQAaABfAG0AcwBcACIALAAgAFwAIgBOAFIAXwBtAHMAXAAiAH0ALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsACwAIABTAEUAUQBVAEUATgBDAEUAKABuAF8AdABlAHMAdABzACkALAAgAEwAQQBNAEIARABBACgAYQBjAGMALAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAEkATgBEAEUAWAAoAHQAZQBzAHQAXwBjAGEAcwBlAHMALAAgAGkALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAASQBOAEQARQBYACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBrAGkAcAAgAEQAaQB2AGkAcwBvAHIAIAA+ACAARABpAHYAaQBkAGUAbgBkABQgaQB0ACcAcwAgAG4AZQB2AGUAcgAgAGEAbgAgAGkAbgB0AGUAZwBlAHIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbABlAG4AXwBiACAAPgAgAGwAZQBuAF8AYQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAYwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARwBlAG4AZQByAGEAdABlACAAZQB4AGEAYwB0AC0AbABlAG4AZwB0AGgAIAB0AGUAcwB0ACAAcwB0AHIAaQBuAGcAcwAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AHIAXwBhACwAIABSAEUAUABUACgAXAAiADkAXAAiACwAIABsAGUAbgBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAcgBfAGIALAAgAEkARgAoAGwAZQBuAF8AYgAgAD0AIAAxACwAIABcACIANwBcACIALAAgAFwAIgA3AFwAIgAgACYAIABSAEUAUABUACgAXAAiADMAXAAiACwAIABsAGUAbgBfAGIAIAAtACAAMQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeABlAGMAdQB0AGUAIABiAGUAbgBjAGgAbQBhAHIAawBzACAAcwB0AHIAaQBjAHQAbAB5ACAAbwBuAGUAIABhAGYAdABlAHIAIAB0AGgAZQAgAG8AdABoAGUAcgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABpAG0AZQBfAGsALAAgAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACgAcwB0AHIAXwBhACwAIABzAHQAcgBfAGIALAAgAFwAIgBLAE4AVQBUAEgAXAAiACwAIABpAHQAZQByAHMALAAgAHIAZQBwAGUAYQB0AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGkAbQBlAF8AbgByACwAIABEAGkAdgBpAHMAaQBvAG4AQQBsAGcAbwByAGkAdABoAG0AcwAoAHMAdAByAF8AYQAsACAAcwB0AHIAXwBiACwAIABcACIATgBSAFwAIgAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAcABwAGUAbgBkACAAdABoAGUAIAByAGUAcwB1AGwAdABzAC4AIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAGEAbABsAG8AYwBhAHQAaQBvAG4AIABkAGUAbABhAHkAIABvAGMAYwB1AHIAcwAgAGgAZQByAGUALAAgAHMAYQBmAGUAbAB5ACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAdABpAG0AZQBkACAAdwBpAG4AZABvAHcALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABhAGMAYwAsACAASABTAFQAQQBDAEsAKABsAGUAbgBfAGEALAAgAGwAZQBuAF8AYgAsACAAdABpAG0AZQBfAGsALAAgAHQAaQBtAGUAXwBuAHIAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgADIALQBjAG8AbAB1AG0AbgAgAGEAcgByAGEAeQAgAG8AZgAgAGUAdgBlAHIAeQAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgAgAG8AZgAgAGwAZQBuAGcAdABoAHMAXABuAEQAaQB2AGkAcwBpAG8AbgBCAGUAbgBjAGgAbQBhAHIAawBDAGEAcwBlAHMAIAA9ACAATABBAE0AQgBEAEEAKABzAHQAYQByAHQAXwBsAGUAbgAsACAAbQBhAHgAXwBsAGUAbgAsACAAcwB0AGUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQAsACAAUwBFAFEAVQBFAE4AQwBFACgAKABtAGEAeABfAGwAZQBuACAALQAgAHMAdABhAHIAdABfAGwAZQBuACkAIAAvACAAcwB0AGUAcAAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBsAGUAbgAsACAAcwB0AGUAcAApACwAXABuACAAIAAgACAAIAAgACAAIABuACwAIABSAE8AVwBTACgAcwBlAHEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAcgB0AGUAcwBpAGEAbgAgAEoAbwBpAG4AXABuACAAIAAgACAAIAAgACAAIABjAG8AbABfAGEALAAgAFQATwBDAE8ATAAoAEkARgAoAFMARQBRAFUARQBOAEMARQAoADEALAAgAG4AKQAsACAAcwBlAHEAKQApACwAXABuACAAIAAgACAAIAAgACAAIABjAG8AbABfAGIALAAgAFQATwBDAE8ATAAoAEkARgAoAFMARQBRAFUARQBOAEMARQAoAG4ALAAgADEAKQAsACAAVABPAFIATwBXACgAcwBlAHEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABjAG8AbABfAGEALAAgAGMAbwBsAF8AYgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgAEMAYQByAHQAZQBzAGkAYQBuACAAZwByAGkAZAAgAGYAcgBvAG0AIAB0AHcAbwAgAGkAbgBkAGUAcABlAG4AZABlAG4AdAAgAHMAZQBxAHUAZQBuAGMAZQBzAFwAbgBBAHMAeQBtAG0AZQB0AHIAaQBjAEEAQgBHAHIAaQBkACAAPQAgAEwAQQBNAEIARABBACgAcwB0AGEAcgB0AF8AYQAsACAAbQBhAHgAXwBhACwAIABzAHQAZQBwAF8AYQAsACAAcwB0AGEAcgB0AF8AYgAsACAAbQBhAHgAXwBiACwAIABzAHQAZQBwAF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGEALAAgAFMARQBRAFUARQBOAEMARQAoACgAbQBhAHgAXwBhACAALQAgAHMAdABhAHIAdABfAGEAKQAgAC8AIABzAHQAZQBwAF8AYQAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBhACwAIABzAHQAZQBwAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGIALAAgAFMARQBRAFUARQBOAEMARQAoACgAbQBhAHgAXwBiACAALQAgAHMAdABhAHIAdABfAGIAKQAgAC8AIABzAHQAZQBwAF8AYgAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBiACwAIABzAHQAZQBwAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwBhACwAIABSAE8AVwBTACgAcwBlAHEAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwBiACwAIABSAE8AVwBTACgAcwBlAHEAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAATwByAHQAaABvAGcAbwBuAGEAbAAgAGIAcgBvAGEAZABjAGEAcwB0ACAAdQBzAGkAbgBnACAAaQBuAGQAZQBwAGUAbgBkAGUAbgB0ACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIAAgACAAIAAgAGMAbwBsAF8AYQAsACAAVABPAEMATwBMACgASQBGACgAUwBFAFEAVQBFAE4AQwBFACgAMQAsACAAbgBfAGIAKQAsACAAcwBlAHEAXwBhACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBvAGwAXwBiACwAIABUAE8AQwBPAEwAKABJAEYAKABTAEUAUQBVAEUATgBDAEUAKABuAF8AYQApACwAIABUAE8AUgBPAFcAKABzAGUAcQBfAGIAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABjAG8AbABfAGEALAAgAGMAbwBsAF8AYgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBjAG8AcgBlAF8AQgBpAGcASQBuAHQAIgAsACIAdABlAHgAdAAiADoAIgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4ALwAvACAAQgBpAGcAIABJAG4AdABlAGcAZQByACAAQQByAGkAdABoAG0AZQB0AGkAYwAgAEwAaQBiAHIAYQByAHkAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQAIABNAG8AZAB1AGwAZQAgACAAIAAgACAAIAAgACAALwAvAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIABQAHIAaQB2AGEAdABlACAAQQBQAEkAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwBcAG4ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8AXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEMAbwBtAHAAdQB0AGUAcwAgAHQAaABlACAAbQBhAHgAaQBtAHUAbQAgAHMAYQBmAGUAIABiAGEAcwBlAC0AMQAwACAAbABpAG0AYgAgAHMAaQB6AGUAIAAoAGsAKQAgAHQAbwAgAGEAdgBvAGkAZAAgAEkARQBFAEUALQA3ADUANAAgAHAAcgBlAGMAaQBzAGkAbwBuACAAbABvAHMAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG8AcABlAHIAYQB0AGkAbwBuADoAIABcACIAQQBEAEQAXAAiACwAIABcACIATQBVAEwAXAAiACwAIABvAHIAIABcACIARABJAFYAXAAiAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAWwBtAGEAeABfAGkAdABlAG0AcwBdACAAQQBEAEQAOgAgAG4AdQBtAGIAZQByACAAbwBmACAAbwBwAGUAcgBhAG4AZABzAC4AIABNAFUATAA6ACAAcwBoAG8AcgB0AGUAcwB0ACAAcwB0AHIAaQBuAGcAIABkAGkAZwBpAHQAcwAgAGMAbwB1AG4AdAAuAFwAbgAgACoALwBcAG4AUwBhAGYAZQBLACAAPQAgAEwAQQBNAEIARABBACgAbwBwAGUAcgBhAHQAaQBvAG4ALAAgAFsAbQBhAHgAXwBpAHQAZQBtAHMAXQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABpAHQAZQBtAHMALAAgAEkARgAoAE8AUgAoAG0AYQB4AF8AaQB0AGUAbQBzACAAPQAgAFwAIgBcACIALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAbQBhAHgAXwBpAHQAZQBtAHMAKQApACwAIAAyACwAIABNAEEAWAAoADIALAAgAG0AYQB4AF8AaQB0AGUAbQBzACkAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVwBJAFQAQwBIACgAbwBwAGUAcgBhAHQAaQBvAG4ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEARABEAFwAIgAsACAAMQA1ACAALQAgAEwARQBOACgAaQB0AGUAbQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFUATABcACIALAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARQB2AGEAbAB1AGEAdABlACAAcABvAHMAcwBpAGIAbABlACAAawAgAHYAYQBsAHUAZQBzACAAZAB5AG4AYQBtAGkAYwBhAGwAbAB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAZQBzAHQAXwBrACwAIAB7ADcAOwAgADYAOwAgADUAOwAgADQAOwAgADMAOwAgADIAOwAgADEAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AbwB2AGUAcgBsAGEAcAAsACAAUgBPAFUATgBEAFUAUAAoAGkAdABlAG0AcwAgAC8AIAB0AGUAcwB0AF8AawAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIAB0AGgAZQAgAGEAYgBzAG8AbAB1AHQAZQAgAHAAZQBhAGsAIAB2AGEAbAB1AGUAIABpAG4AcwBpAGQAZQAgAHQAaABlACAAZQBuAGcAaQBuAGUAIAAoAEMAbwBuAHYAbwBsAHUAdABpAG8AbgAgACsAIABDAGEAcgByAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB1AG4AYwBhAHIAcgBpAGUAZABfAG0AYQB4ACwAIABtAGEAeABfAG8AdgBlAHIAbABhAHAAIAAqACAAKAAxADAAXgB0AGUAcwB0AF8AawAgAC0AIAAxACkAXgAyACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAHgAXwBjAGEAcgByAHkALAAgAEkATgBUACgAdQBuAGMAYQByAHIAaQBlAGQAXwBtAGEAeAAgAC8AIAAxADAAXgB0AGUAcwB0AF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABlAGEAawBfAHYAYQBsACwAIAB1AG4AYwBhAHIAcgBpAGUAZABfAG0AYQB4ACAAKwAgAG0AYQB4AF8AYwBhAHIAcgB5ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHQAdQByAG4AIAB0AGgAZQAgAG0AYQB4ACAAawAgADwAPQAgAEUAeABjAGUAbAAnAHMAIAAxADUALQBkAGkAZwBpAHQAIABjAGUAaQBsAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgARgBJAEwAVABFAFIAKAB0AGUAcwB0AF8AawAsACAAcABlAGEAawBfAHYAYQBsACAAPAA9ACAAKAAxADAAXgAxADUAIAAtACAAMQApACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQASQBWAFwAIgAsACAANwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAE4AQQBNAEUAPwBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AaQBmAGkAZQBkACAAUwBwAGwAaQB0AHQAZQByAC4AIABTAHAAbABpAHQAcwAgAGIAbwB0AGgAIABzAGMAYQBsAGEAcgBzACAAYQBuAGQAIABhAHIAcgBhAHkAcwAgAGkAbgB0AG8AIABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuACAAbABpAG0AYgBzAC4AXABuACAAKgAgAFUAcwBlAHMAIABNAEEAWAAoACkAIAB0AG8AIABnAHUAYQByAGEAbgB0AGUAZQAgAHMAYwBhAGwAYQByACAAaQBuAHAAdQB0AHMAIAB0AG8AIAB0AGgAZQAgAFMARQBRAFUARQBOAEMARQAgAGUAbgBnAGkAbgBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABzACAAVABoAGUAIABzAHQAcgBpAG4AZwAgAG8AcgAgAGEAcgByAGEAeQAgAG8AZgAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFMAcABsAGkAdAAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAcwAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABiAGkAZwBfAGkAbgB0AF8AcgBvAHcALAAgAFQATwBSAE8AVwAoAGIAaQBnAF8AaQBuAHQAcwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBnAHQAaABzACwAIABMAEUATgAoAGIAaQBnAF8AaQBuAHQAXwByAG8AdwApACwAXABuACAAIAAgACAAIAAgACAAIABtAGEAeABfAGwAZQBuACwAIABNAEEAWAAoAGwAZQBuAGcAdABoAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBsAGUAbgAsACAAUgBPAFUATgBEAFUAUAAoAG0AYQB4AF8AbABlAG4AIAAvACAAawAsACAAMAApACAAKgAgAGsALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAZABlAGQALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAHAAYQBkAF8AbABlAG4AIAAtACAAbABlAG4AZwB0AGgAcwApACAAJgAgAGIAaQBnAF8AaQBuAHQAXwByAG8AdwAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALAAgAFMARQBRAFUARQBOAEMARQAoAHAAYQBkAF8AbABlAG4AIAAvACAAawAsACAAMQAsACAAcABhAGQAXwBsAGUAbgAgAC0AIABrACAAKwAgADEALAAgAC0AawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC0ALQBNAEkARAAoAHAAYQBkAGQAZQBkACwAIABzAHQAYQByAHQAcwAsACAAawApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAQwBvAG4AYwBhAHQAZQBuAGEAdABlAHMAIABhAG4AIABhAHIAcgBhAHkAIABvAGYAIABuAHUAbQBlAHIAaQBjACAAbABpAG0AYgBzACAAaQBuAHQAbwAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnACwAIAB6AGUAcgBvAC0AcABhAGQAZABpAG4AZwAgAGEAbABsACAAYgB1AHQAIAB0AGgAZQAgAGYAaQByAHMAdAAgAGwAaQBtAGIALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAIABUAGgAZQAgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAG4AdQBtAGUAcgBpAGMAIABsAGkAbQBiAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABsAGkAbQBiACAAcwBpAHoAZQAgAHUAcwBlAGQAIABkAHUAcgBpAG4AZwAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAuAFwAbgAgACoALwBcAG4ATQBlAHIAZwBlACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AdQBtAF8AbABpAG0AYgBzACwAIABSAE8AVwBTACgAbABpAG0AYgBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQB2AF8AbABpAG0AYgBzACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAbABpAG0AYgBzACwAIABTAEUAUQBVAEUATgBDAEUAKABuAHUAbQBfAGwAaQBtAGIAcwAsACAAMQAsACAAbgB1AG0AXwBsAGkAbQBiAHMALAAgAC0AMQApACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AdQBtAF8AbABpAG0AYgBzACAAPQAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHYAXwBsAGkAbQBiAHMAIAAmACAAXAAiAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATgBDAEEAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAcgBlAHYAXwBsAGkAbQBiAHMALAAgADEAKQAgACYAIABcACIAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEUAWABUACgARABSAE8AUAAoAHIAZQB2AF8AbABpAG0AYgBzACwAIAAxACkALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAGsAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAUgBlAHMAbwBsAHYAZQBzACAAYwBhAHIAcgBpAGUAcwAgAHIAaQBnAGgAdAAtAHQAbwAtAGwAZQBmAHQAIABhAGMAcgBvAHMAcwAgAGEAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkAIABvAGYAIABiAGEAcwBlAC0AMQAwAF4AawAgAGwAaQBtAGIAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwAgAFQAaABlACAAYQByAHIAYQB5ACAAbwBmACAAbgB1AG0AZQByAGkAYwAgAGwAaQBtAGIAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGwAaQBtAGIAIABzAGkAegBlAC4AXABuACAAKgAvAFwAbgBDAGEAcgByAHkAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwApACwAXABuACAAIAAgACAAIAAgACAAIABiAGEAcwBlACwAIAAxADAAXgBrACwAXABuACAAIAAgACAAIAAgACAAIABzAGMAYQBuAG4AZQBkACwAIABTAEMAQQBOACgAMAAsACAAbABpAG0AYgBzACwAIABMAEEATQBCAEQAQQAoAGEAYwBjACwAIAB2AGEAbAAsACAAdgBhAGwAIAArACAASQBOAFQAKABhAGMAYwAgAC8AIABiAGEAcwBlACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAByAGUAbQBhAGkAbgBkAGUAcgBzACwAIABNAE8ARAAoAHMAYwBhAG4AbgBlAGQALAAgAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AYwBhAHIAcgB5ACwAIABJAE4AVAAoAEkATgBEAEUAWAAoAHMAYwBhAG4AbgBlAGQALAAgAG4ALAAgADEAKQAgAC8AIABiAGEAcwBlACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABmAGkAbgBhAGwAXwBjAGEAcgByAHkAIAA+ACAAMAAsACAAVgBTAFQAQQBDAEsAKAByAGUAbQBhAGkAbgBkAGUAcgBzACwAIABmAGkAbgBhAGwAXwBjAGEAcgByAHkAKQAsACAAcgBlAG0AYQBpAG4AZABlAHIAcwApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAC0ALQAtACAAVQBuAHMAaQBnAG4AZQBkACAASwBlAHIAbgBlAGwAcwAgAC0ALQAtACAAXABcAFwAXABcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAVQBuAHMAaQBnAG4AZQBkACAAYwBvAG0AcABhAHIAaQBzAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAMQAgACgAYQAgAD4AIABiACkALAAgAC0AMQAgACgAYQAgADwAIABiACkALAAgAG8AcgAgADAAIAAoAGEAIAA9ACAAYgApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAIABUAGgAZQAgAHMAZQBjAG8AbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoALwBcAG4AVQBDAG8AbQBwAGEAcgBlACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAeABfAHIAbwB3AHMALAAgAE0AQQBYACgAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEAKQAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAZABfAGEALAAgAEUAWABQAEEATgBEACgAbABpAG0AYgBzAF8AYQAsACAAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAYQBkAF8AYgAsACAARQBYAFAAQQBOAEQAKABsAGkAbQBiAHMAXwBiACwAIABtAGEAeABfAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABkAGkAZgBmACwAIABwAGEAZABfAGEAIAAtACAAcABhAGQAXwBiACwAXABuACAAIAAgACAAIAAgACAAIABtAHMAZABfAGkAZAB4ACwAIABYAE0AQQBUAEMASAAoAFQAUgBVAEUALAAgAGQAaQBmAGYAIAA8AD4AIAAwACwAIAAwACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATgBBACgAbQBzAGQAXwBpAGQAeAApACwAIAAwACwAIABTAEkARwBOACgASQBOAEQARQBYACgAZABpAGYAZgAsACAAbQBzAGQAXwBpAGQAeAAsACAAMQApACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAGEAZABkAGkAdABpAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFUAQQBkAGQAIAA9ACAATABBAE0AQgBEAEEAKABhACwAIABiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AcgBvAHcAcwAsACAATQBBAFgAKABSAE8AVwBTACgAYQApACwAIABSAE8AVwBTACgAYgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAYQBkAF8AYQAsACAARQBYAFAAQQBOAEQAKABhACwAIABtAGEAeABfAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBiACwAIABFAFgAUABBAE4ARAAoAGIALAAgAG0AYQB4AF8AcgBvAHcAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHAAYQBkAF8AYQAgACsAIABwAGEAZABfAGIALAAgAGsAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAHMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABBAHMAcwB1AG0AZQBzACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAgAEEAIAA+AD0AIABCAC4AIABSAGUAcwBvAGwAdgBlAHMAIABiAG8AcgByAG8AdwBzACAAdABvAHAALQB0AG8ALQBiAG8AdAB0AG8AbQAgAGEAbgBkACAAdAByAGkAbQBzACAAdAByAGEAaQBsAGkAbgBnACAAegBlAHIAbwBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAbQBpAG4AdQBlAG4AZAAgAGwAaQBtAGIAIABhAHIAcgBhAHkAIAAoAG0AdQBzAHQAIABiAGUAIAA+AD0AIABsAGkAbQBiAHMAXwBiACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABzAHUAYgB0AHIAYQBoAGUAbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AVQBTAHUAYgAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwByAG8AdwBzACwAIABNAEEAWAAoAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBhACwAIABFAFgAUABBAE4ARAAoAGwAaQBtAGIAcwBfAGEALAAgAG0AYQB4AF8AcgBvAHcAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAZABfAGIALAAgAEUAWABQAEEATgBEACgAbABpAG0AYgBzAF8AYgAsACAAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAZABpAGYAZgAsACAAcABhAGQAXwBhACAALQAgAHAAYQBkAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBlAHMAbwBsAHYAZQBkACwAIABDAGEAcgByAHkAKABkAGkAZgBmACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAbQBzAGQAXwBpAGQAeAAsACAAWABNAEEAVABDAEgAKABUAFIAVQBFACwAIAByAGUAcwBvAGwAdgBlAGQAIAA8AD4AIAAwACwAIAAwACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATgBBACgAbQBzAGQAXwBpAGQAeAApACwAIAB7ADAAfQAsACAAVABBAEsARQAoAHIAZQBzAG8AbAB2AGUAZAAsACAAbQBzAGQAXwBpAGQAeAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABWAGUAYwB0AG8AcgBpAHoAZQBkACAAbQBhAHQAcgBpAHgAIABzAHUAbQAgAG8AZgAgAHUAbgBzAGkAZwBuAGUAZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHUAYgBpAGcAXwBpAG4AdAAgAEgAbwByAGkAegBvAG4AdABhAGwAIABhAHIAcgBhAHkAIAAoADEAeABOACkAIABvAGYAIABuAG8AcgBtAGEAbABpAHoAZQBkACAAbQBhAGcAbgBpAHQAdQBkAGUAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAdQBuAGkAZgBpAGUAZAAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AVQBNAGEAdAByAGkAeABTAHUAbQAgAD0AIABMAEEATQBCAEQAQQAoAHUAYgBpAGcAXwBpAG4AdABzACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAGcAcgBpAGQALAAgAFMAcABsAGkAdAAoAHUAYgBpAGcAXwBpAG4AdABzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAYQB3AF8AbABpAG0AYgBzACwAIABCAFkAUgBPAFcAKABnAHIAaQBkACwAIABTAFUATQApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHIAYQB3AF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABSAG8AdQB0AGUAcwAgAGEAZABkAGkAdABpAG8AbgAvAHMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAGIAYQBzAGUAZAAgAG8AbgAgAHMAaQBnAG4AcwAgAGEAbgBkACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAuAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAYQAgAHQAdQBwAGwAZQAgAGEAcgByAGEAeQA6ACAAVgBTAFQAQQBDAEsAKABsAGkAbQBiAHMALAAgAGYAaQBuAGEAbABfAHMAaQBnAG4AKQAgAHcAaABlAHIAZQAgAHQAaABlACAAZgBpAG4AYQBsACAAcgBvAHcAIABpAHMAIAB0AGgAZQAgAHMAYwBhAGwAYQByACAAcwBpAGcAbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAcwBlAGMAbwBuAGQAIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHMAaQBnAG4AXwBhACAAVABoAGUAIABzAGkAZwBuACAAbwBmACAAdABoAGUAIABmAGkAcgBzAHQAIABhAHIAcgBhAHkAIAAoADEALAAgAC0AMQAsACAAMAApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAcwBpAGcAbgBfAGIAIABUAGgAZQAgAHMAaQBnAG4AIABvAGYAIAB0AGgAZQAgAHMAZQBjAG8AbgBkACAAYQByAHIAYQB5ACAAKAAxACwAIAAtADEALAAgADAAKQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AQQBkAGQAUwB1AGIAUgBvAHUAdABlAHIAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABzAGkAZwBuAF8AYQAsACAAcwBpAGcAbgBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AcwBhAG0AZQBfAHMAaQBnAG4ALAAgAHMAaQBnAG4AXwBhACAAPQAgAHMAaQBnAG4AXwBiACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGkAcwBfAHMAYQBtAGUAXwBzAGkAZwBuACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAZABkAGkAdABpAG8AbgA6ACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAgAGMAbwBtAGIAaQBuAGUALAAgAHMAaQBnAG4AIAByAGUAbQBhAGkAbgBzACAAdABoAGUAIABzAGEAbQBlAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVQBBAGQAZAAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsACAAcwBpAGcAbgBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwB1AGIAdAByAGEAYwB0AGkAbwBuADoAIABlAHYAYQBsAHUAYQB0AGUAIABtAGEAZwBuAGkAdAB1AGQAZQBzACAAdABvACAAcwBhAHQAaQBzAGYAeQAgAFUAUwB1AGIAIAAoAEEAIAA+AD0AIABCACkAIABwAHIAZQBjAG8AbgBkAGkAdABpAG8AbgAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcAAsACAAVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFQAbwB0AGEAbAAgAGMAYQBuAGMAZQBsAGwAYQB0AGkAbwBuADoAIAByAGUAdAB1AHIAbgAgAHsAMAB9ACAAbABpAG0AYgAgAGEAbgBkACAAMAAgAHMAaQBnAG4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAMAA7ADAAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAGEAZwBfAGMAbwBtAHAAIAA+ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABBACAAaQBzACAAbABhAHIAZwBlAHIAOgAgAHMAaQBnAG4AIABiAGUAbABvAG4AZwBzACAAdABvACAAQQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFUAUwB1AGIAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALAAgAHMAaQBnAG4AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEIAIABpAHMAIABsAGEAcgBnAGUAcgA6ACAAcgBvAHUAdABlACAAQgAgAGYAaQByAHMAdAAsACAAcwBpAGcAbgAgAGIAZQBsAG8AbgBnAHMAIAB0AG8AIABCAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVQBTAHUAYgAoAGwAaQBtAGIAcwBfAGIALAAgAGwAaQBtAGIAcwBfAGEALAAgAGsAKQAsACAAcwBpAGcAbgBfAGIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AcwBpAGcAbgBlAGQAIABtAHUAbAB0AGkAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIAB0AHcAbwAgAEwAaQB0AHQAbABlAC0ARQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5AHMALgBcAG4AIAAqACAAVQB0AGkAbABpAHoAZQBzACAAYQAgADEARAAgAEQAaQBzAGMAcgBlAHQAZQAgAEMAbwBuAHYAbwBsAHUAdABpAG8AbgAgACgAQwBhAHUAYwBoAHkAIABQAHIAbwBkAHUAYwB0ACkAIABhAHIAcgBhAHkALQBzAGwAaQBjAGkAbgBnACAAcwB0AHIAYQB0AGUAZwB5AC4AXABuACAAKgAgAFoAZQByAG8AIABkAHkAbgBhAG0AaQBjACAAbQBlAG0AbwByAHkAIAByAGUAYQBsAGwAbwBjAGEAdABpAG8AbgAuACAAJABPACgATgArAE0AKQAkACAAbQBlAG0AbwByAHkAIABmAG8AbwB0AHAAcgBpAG4AdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAG0AdQBsAHQAaQBwAGwAaQBjAGEAbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAIABUAGgAZQAgAG0AdQBsAHQAaQBwAGwAaQBlAHIAIABsAGkAbQBiACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBVAE0AdQBsACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwByAG8AdwBzACwAIABsAGUAbgBfAGEAIAArACAAbABlAG4AXwBiACAALQAgADEALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAATABvAG8AcAAgAHAAdQByAGUAbAB5ACAAbwB2AGUAcgAgAHQAaABlACAAbABlAG4AZwB0AGgAIABvAGYAIAB0AGgAZQAgAGYAaQBuAGEAbAAgAG8AdQB0AHAAdQB0ACAAYQByAHIAYQB5AFwAbgAgACAAIAAgACAAIAAgACAAcgBhAHcAXwBsAGkAbQBiAHMALAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIABMAEEATQBCAEQAQQAoAHIALAAgAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAbABjAHUAbABhAHQAZQAgAHQAaABlACAAdgBhAGwAaQBkACAAbwB2AGUAcgBsAGEAcABwAGkAbgBnACAAdwBpAG4AZABvAHcAIABvAGYAIABpAG4AZABpAGMAZQBzACAAZgBvAHIAIAB0AGgAaQBzACAAbQBhAGcAbgBpAHQAdQBkAGUAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AF8AaQAsACAATQBBAFgAKAAxACwAIAByACAALQAgAGwAZQBuAF8AYgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAG4AZABfAGkALAAgAE0ASQBOACgAcgAsACAAbABlAG4AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AdQBuAHQALAAgAGUAbgBkAF8AaQAgAC0AIABzAHQAYQByAHQAXwBpACAAKwAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGUAcQB1AGUAbgBjAGUAIABpACAAYwBvAHUAbgB0AHMAIABVAFAALgAgAFMAZQBxAHUAZQBuAGMAZQAgAGoAIABjAG8AdQBuAHQAcwAgAEQATwBXAE4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGkALAAgAFMARQBRAFUARQBOAEMARQAoAGMAbwB1AG4AdAAsACAAMQAsACAAcwB0AGEAcgB0AF8AaQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBlAHEAXwBqACwAIABTAEUAUQBVAEUATgBDAEUAKABjAG8AdQBuAHQALAAgADEALAAgAHIAIAAtACAAcwB0AGEAcgB0AF8AaQAgACsAIAAxACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAbABpAGMAZQAgAHQAaABlACAAZQB4AGEAYwB0ACAAaQBuAHQAZQByAHMAZQBjAHQAaQBuAGcAIABsAGkAbQBiAHMALAAgAG0AdQBsAHQAaQBwAGwAeQAsACAAYQBuAGQAIABzAHUAbQAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUATQAoAEkATgBEAEUAWAAoAGwAaQBtAGIAcwBfAGEALAAgAHMAZQBxAF8AaQAsACAAMQApACAAKgAgAEkATgBEAEUAWAAoAGwAaQBtAGIAcwBfAGIALAAgAHMAZQBxAF8AagAsACAAMQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHMAbwBsAHYAZQAgAGEAbABsACAAYwBhAHIAcgBpAGUAcwAgAGIAbwB0AHQAbwBtAC0AdABvAC0AdABvAHAAIABlAHgAYQBjAHQAbAB5ACAAbwBuAGMAZQBcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHIAYQB3AF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABCAGkAbgBhAHIAeQAgAHMAZQBhAHIAYwBoACAAdABvACAAZgBpAG4AZAAgAHQAaABlACAAaABpAGcAaABlAHMAdAAgAHMAYwBhAGwAYQByACAAcQB1AG8AdABpAGUAbgB0ACAAbABpAG0AYgAgAHEAIAAoADAAIAA8AD0AIABxACAAPAAgADEAMABeAGsAKQBcAG4AoAAqACAAcwB1AGMAaAAgAHQAaABhAHQAIABCACAAKgAgAHEAIAA8AD0AIABhAGMAYwAuACAARQBsAGkAbQBpAG4AYQB0AGUAcwAgAHQAaABlACAAbgBlAGUAZAAgAGYAbwByACAASwBuAHUAdABoACAARAAgAGYAbABvAGEAdAAtAGUAcwB0AGkAbQBhAHQAaQBvAG4ALgBcAG4AoAAqACAAQABwAGEAcgBhAG0AIABhAGMAYwAgAFQAaABlACAAYwB1AHIAcgBlAG4AdAAgAHIAZQBtAGEAaQBuAGQAZQByACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAuAFwAbgCgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgCgACoALwBcAG4ARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAgAD0AIABMAEEATQBCAEQAQQAoAGEAYwBjACwAIABiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAYQBsAGMAdQBsAGEAdABlACAAcgBlAHEAdQBpAHIAZQBkACAAYgBpAHQAcwAgAGQAeQBuAGEAbQBpAGMAYQBsAGwAeQAuACAARgBvAHIAIABtAGEAeAAgAGsAPQA3ACwAIAB0AGgAaQBzACAAZQB2AGEAbAB1AGEAdABlAHMAIAB0AG8AIAAyADQAIABiAGkAdABzAC4AXABuACAAIAAgACAAIAAgACAAIABiAGkAdABzACwAIABDAEUASQBMAEkATgBHAC4ATQBBAFQASAAoAEwATwBHACgAMQAwAF4AawAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAbwB3AGUAcgBzACwAIAAyACAAXgAgAFMARQBRAFUARQBOAEMARQAoAGIAaQB0AHMALAAgADEALAAgAGIAaQB0AHMAIAAtACAAMQAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAUgBFAEQAVQBDAEUAKAAwACwAIABwAG8AdwBlAHIAcwAsACAATABBAE0AQgBEAEEAKABjAHUAcgByAF8AcQAsACAAcABvAHcAZQByACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABlAHMAdABfAHEALAAgAGMAdQByAHIAXwBxACAAKwAgAHAAbwB3AGUAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAawBpAHAAIABpAGYAIAB0AGUAcwB0AF8AcQAgAGUAeABjAGUAZQBkAHMAIAB0AGgAZQAgAGwAaQBtAGIAIABiAGEAcwBlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHQAZQBzAHQAXwBxACAAPgA9ACAAMQAwAF4AawAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATQB1AGwAdABpAHAAbAB5ACAAQgAgAGIAeQAgAHMAYwBhAGwAYQByACAAdABlAHMAdABfAHEAIABhAG4AZAAgAHIAZQBzAG8AbAB2AGUAIABjAGEAcgByAGkAZQBzACAAbgBhAHQAaQB2AGUAbAB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGUAcwB0AF8AcAByAG8AZAAsACAAQwBhAHIAcgB5ACgAYgAgACoAIAB0AGUAcwB0AF8AcQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAFUAQwBvAG0AcABhAHIAZQAoAGEAYwBjACwAIAB0AGUAcwB0AF8AcAByAG8AZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABjAG8AbQBwACAAPgA9ACAAMAAsACAAdABlAHMAdABfAHEALAAgAGMAdQByAHIAXwBxACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABCAGEAcwBlAGMAYQBzAGUAIABEAGkAdgBpAHMAaQBvAG4AIAB2AGkAYQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABzAGgAaQBmAHQALQBhAG4AZAAtAHMAdQBiAHQAcgBhAGMAdAAuAFwAbgCgACoAIABSAGUAdAB1AHIAbgBzACAAYQAgAHAAYQBjAGsAZQBkACAAMQBEACAAYQByAHIAYQB5ADoAIABWAFMAVABBAEMASwAoAEwAZQBuAGcAdABoAF8AUgAsACAAUgBfAGwAaQBtAGIAcwAsACAAUQBfAGwAaQBtAGIAcwApAC4AXABuAKAAKgAgAEUAbABpAG0AaQBuAGEAdABlAHMAIAAyAEQAIABhAHIAcgBhAHkAIABwAGEAZABkAGkAbgBnACAAdABvACAAcwB0AHIAaQBjAHQAbAB5ACAAcAByAGUAcwBlAHIAdgBlACAAbQBlAG0AbwByAHkAIABlAGYAZgBpAGMAaQBlAG4AYwB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAgACgAYQBzAHMAdQBtAGUAZAAgAG4AbwBuAC0AegBlAHIAbwApAC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuAKAAKgAvAFwAbgBLAG4AdQB0AGgARABpAHYAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcAAsACAAVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAIAByAG8AdQB0AGkAbgBnACAAdwBpAHQAaAAgAHQAaABlACAAbgBlAHcAIABwAGEAYwBrAGUAZAAgAG0AZQBtAG8AcgB5ACAAYwBvAG4AdAByAGEAYwB0AFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbABpAG0AYgBzAF8AYQApACwAIABsAGkAbQBiAHMAXwBhACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADEALAAgADAALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEkAdABlAHIAYQB0AGUAIABvAHYAZQByACAAQQAgAGYAcgBvAG0AIABNAFMAQgAgACgAdABvAHAAKQAgAHQAbwAgAEwAUwBCACAAKABiAG8AdAB0AG8AbQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHYAZQByAHMAZQBkAF8AYQAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEALAAgAFMARQBRAFUARQBOAEMARQAoAGwAZQBuAF8AYQAsACAAMQAsACAAbABlAG4AXwBhACwAIAAtADEAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAdABhAHQAZQAgAHMAZQBwAGEAcgBhAHQAbwByADoAIABWAFMAVABBAEMASwAoAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABxAHUAbwB0AGkAZQBuAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAbgBpAHQAaQBhAGwAXwBzAHQAYQB0AGUALAAgAFYAUwBUAEEAQwBLACgAMQAsACAAMAAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsAF8AcwB0AGEAdABlACwAIAByAGUAdgBlAHIAcwBlAGQAXwBhACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAdgBhAGwALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcwB0AGEAdABlACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHEAdQBvAHQAaQBlAG4AdAAsACAARABSAE8AUAAoAHMAdABhAHQAZQAsACAAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGgAaQBmAHQAIABhAGMAYwAgAHUAcAAgAGIAeQAgADEAIABsAGkAbQBiACAAKABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuADoAIABpAG4AcwBlAHIAdAAgAGEAdAAgAGkAbgBkAGUAeAAgADEAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAHgAdABlAG4AZABlAGQAXwByAGUAbQBhAGkAbgBkAGUAcgAsACAASQBGACgAQQBOAEQAKABSAE8AVwBTACgAcgBlAG0AYQBpAG4AZABlAHIAKQAgAD0AIAAxACwAIABJAE4ARABFAFgAKAByAGUAbQBhAGkAbgBkAGUAcgAsACAAMQAsACAAMQApACAAPQAgADAAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB2AGEAbAAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAHYAYQBsACwAIAByAGUAbQBhAGkAbgBkAGUAcgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgAsACAARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAoAGUAeAB0AGUAbgBkAGUAZABfAHIAZQBtAGEAaQBuAGQAZQByACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAHIAbwBkACwAIABDAGEAcgByAHkAKABsAGkAbQBiAHMAXwBiACAAKgAgAG4AZQB4AHQAXwBxAHUAbwB0AGkAZQBuAHQAXwBsAGkAbQBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAdwBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABVAFMAdQBiACgAZQB4AHQAZQBuAGQAZQBkAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHAAcgBvAGQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGgAYQBzAF8AcQB1AG8AdABpAGUAbgB0ACwAIABPAFIAKABSAE8AVwBTACgAcQB1AG8AdABpAGUAbgB0ACkAIAA+ACAAMQAsACAASQBOAEQARQBYACgAcQB1AG8AdABpAGUAbgB0ACwAMQAsADEAKQAgAD4AIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQB1AG8AdAAsACAASQBGACgAaABhAHMAXwBxAHUAbwB0AGkAZQBuAHQALAAgAFYAUwBUAEEAQwBLACgAcQB1AG8AdABpAGUAbgB0ACwAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgApACwAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbgBlAHcAXwByAGUAbQBhAGkAbgBkAGUAcgApACwAIABuAGUAdwBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABuAGUAeAB0AF8AcQB1AG8AdAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAEkATgBEAEUAWAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAbQBhAGkAbgBkAGUAcgAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAsACAAMQAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQB2AGUAcgBzAGUAZABfAHEAdQBvAHQAaQBlAG4AdAAsACAARABSAE8AUAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAcQB1AG8AdABfAHIAYQB3ACAAdwBhAHMAIABiAHUAaQBsAHQAIABNAFMAQgAgAHQAbwAgAEwAUwBCACAAKABCAGkAZwAtAEUAbgBkAGkAYQBuACkALgAgAFIAZQB2AGUAcgBzAGUAIAB0AG8AIABpAG4AdABlAHIAbgBhAGwAIABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHEAdQBvAHQAaQBlAG4AdAAsACAAUgBPAFcAUwAoAHIAZQB2AGUAcgBzAGUAZABfAHEAdQBvAHQAaQBlAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABxAHUAbwB0AGkAZQBuAHQALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKAByAGUAdgBlAHIAcwBlAGQAXwBxAHUAbwB0AGkAZQBuAHQALAAgAFMARQBRAFUARQBOAEMARQAoAGwAZQBuAF8AcQB1AG8AdABpAGUAbgB0ACwAIAAxACwAIABsAGUAbgBfAHEAdQBvAHQAaQBlAG4AdAAsACAALQAxACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAHMAdAByAGkAYwB0AGwAeQAgAHAAYQBjAGsAZQBkACAAMQBEACAAYQByAHIAYQB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIAByAGUAbQBhAGkAbgBkAGUAcgAsACAAcQB1AG8AdABpAGUAbgB0ACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABIAHkAYgByAGkAZAAgAEQAaQB2AGkAcwBpAG8AbgAgAFIAbwB1AHQAZQByAC4AXABuAKAAKgAgAEQAaQByAGUAYwB0AHMAIABkAGkAdgBpAHMAaQBvAG4AIAB0AG8AIAB0AGgAZQAgAG8AcAB0AGkAbQBhAGwAIABrAGUAcgBuAGUAbAAgAGIAYQBzAGUAZAAgAG8AbgAgAEQAaQB2AGkAZABlAG4AZAAgAGwAZQBuAGcAdABoAC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAuAFwAbgCgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgCgACoALwBcAG4ARABpAHYAUgBvAHUAdABlAHIAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEQAaQBnAGkAdAAgAGMAbwB1AG4AdABzACAAYQByAGUAIABhAHAAcAByAG8AeABpAG0AYQB0AGUALAAgAGIAdQB0ACAAcwB1AGYAZgBpAGMAaQBlAG4AdABcAG4AIAAgACAAIAAgACAAIAAgAGQAaQBnAGkAdABzAF8AYQAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEAKQAgACoAIABrACwAXABuACAAIAAgACAAIAAgACAAIABkAGkAZwBpAHQAcwBfAGIALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkAIAAqACAAawAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABNAGEAYwBoAGkAbgBlAC0AbABlAGEAcgBuAGUAZAAgAGMAbwBlAGYAZgBpAGMAaQBlAG4AdABzACAAZgByAG8AbQAgAEwAbwBnAGkAcwB0AGkAYwAgAFIAZQBnAHIAZQBzAHMAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIABtACwAIAAwAC4AMQAwADcAOAAyADEAMQA5ADQAMgA3ADEAMgA5ADcALABcAG4AIAAgACAAIAAgACAAIAAgAGMALAAgAC0AMgAyADEALgA5ADAAMgAxADgAOQA0ADYAMgAwADYAOAAsAFwAbgAgACAAIAAgACAAIAAgACAAdABoAHIAZQBzAGgAbwBsAGQALAAgACgAbQAgACoAIABkAGkAZwBpAHQAcwBfAGEAKQAgACsAIABjACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGQAaQBnAGkAdABzAF8AYgAgADwAPQAgAHQAaAByAGUAcwBoAG8AbABkACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEsAbgB1AHQAaABEAGkAdgAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2ACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEcAZQBuAGUAcgBhAHQAZQBzACAAdABoAGUAIABlAHgAYQBjAHQAIAByAGUAYwBpAHAAcgBvAGMAYQBsACAAcwBlAGUAZAAgAGYAbwByACAATgBlAHcAdABvAG4ALQBSAGEAcABoAHMAbwBuACAARABpAHYAaQBzAGkAbwBuACAAdQBzAGkAbgBnACAASwBuAHUAdABoACAAQgBhAHMAZQBjAGEAcwBlAC4AXABuACAAKgAgAEUAeAB0AHIAYQBjAHQAcwAgAHUAcAAgAHQAbwAgAHQAaABlACAAdABvAHAAIAAzACAAbABpAG0AYgBzACAAbwBmACAAQgAgAGEAbgBkACAAYwBhAGwAYwB1AGwAYQB0AGUAcwAgAGYAbABvAG8AcgAoAEIAZQB0AGEAXgAoADIAKgBsAGUAbgApACAALwAgAEIAXwB0AG8AcAApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4AUwBlAGUAZAAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwBiACwAIABSAE8AVwBTACgAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAZQBkAF8AbABlAG4ALAAgAE0ASQBOACgAMwAsACAAbABlAG4AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAHQAbwBwACAAJwBzAGUAZQBkAF8AbABlAG4AJwAgAGwAaQBtAGIAcwAgACgATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgA6ACAAdABhAGsAZQAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAbwB0AHQAbwBtACkAXABuACAAIAAgACAAIAAgACAAIABiAF8AdABvAHAALAAgAFQAQQBLAEUAKABsAGkAbQBiAHMAXwBiACwAIAAtAHMAZQBlAGQAXwBsAGUAbgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAbwBuAHMAdAByAHUAYwB0ACAAQgBlAHQAYQBeACgAMgAgACoAIABzAGUAZQBkAF8AbABlAG4AKQAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAGUALgBnAC4ALAAgAGkAZgAgAHMAZQBlAGQAXwBsAGUAbgAgAD0AIAAxACwAIAB0AGgAZQBuACAAMQAgAGYAbwBsAGwAbwB3AGUAZAAgAGIAeQAgAHQAdwBvACAAegBlAHIAbwAgAGwAaQBtAGIAcwA6ACAAVgBTAFQAQQBDAEsAKAAwACwAIAAwACwAIAAxACkAXABuACAAIAAgACAAIAAgACAAIABiAGUAdABhAF8AMgBtACwAIABWAFMAVABBAEMASwAoAEUAWABQAEEATgBEACgAMAAsACAAMgAgACoAIABzAGUAZQBkAF8AbABlAG4ALAAgACwAIAAwACkALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABLAG4AdQB0AGgAIABEAGkAdgBpAHMAaQBvAG4AIAB5AGkAZQBsAGQAcwAgAGUAeABhAGMAdAAgAGkAbgBpAHQAaQBhAGwAIAByAGUAYwBpAHAAcgBvAGMAYQBsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGMAawBlAGQALAAgAEsAbgB1AHQAaABEAGkAdgAoAGIAZQB0AGEAXwAyAG0ALAAgAGIAXwB0AG8AcAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABRAHUAbwB0AGkAZQBuAHQAIABhAHIAcgBhAHkAIABmAHIAbwBtACAAdABoAGUAIABwAGEAYwBrAGUAZAAgAFYAUwBUAEEAQwBLAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwByACwAIABJAE4ARABFAFgAKABwAGEAYwBrAGUAZAAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAcABhAGMAawBlAGQALAAgAGwAZQBuAF8AcgAgACsAIAAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABDAG8AbQBwAHUAdABlAHMAIAB0AGgAZQAgAFIAZQBjAGkAcAByAG8AYwBhAGwAIABwAHIAbwBnAHIAZQBzAHMAaQB2AGUAbAB5ACAAcwBjAGEAbABpAG4AZwAgAHUAcAAgAHQAbwAgAHQAaABlACAARABpAHYAaQBkAGUAbgBkACcAcwAgAHAAcgBlAGMAaQBzAGkAbwBuAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIAB0AGEAcgBnAGUAdABfAGwAZQBuACAAVABoAGUAIABsAGkAbQBiAC0AbABlAG4AZwB0AGgAIABvAGYAIABEAGkAdgBpAGQAZQBuAGQAIABBAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAFIAZQBjAGkAcAByAG8AYwBhAGwAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBiACwAIAB0AGEAcgBnAGUAdABfAGwAZQBuACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBlAGUAZABfAGwAZQBuACwAIABNAEkATgAoADMALAAgAGwAZQBuAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAByAF8AcwBlAGUAZABfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBTAGUAZQBkACgAbABpAG0AYgBzAF8AYgAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKABzAGUAZQBkAF8AbABlAG4ALAAgAHIAXwBzAGUAZQBkAF8AbABpAG0AYgBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQBxAF8AaQB0AGUAcgBzACwAIABNAEEAWAAoADAALAAgAEMARQBJAEwASQBOAEcALgBNAEEAVABIACgATABOACgAdABhAHIAZwBlAHQAXwBsAGUAbgAgAC8AIABzAGUAZQBkAF8AbABlAG4AKQAgAC8AIABMAE4AKAAyACkAKQApACAAKwAgADEALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKAByAGUAcQBfAGkAdABlAHIAcwAgAD0AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAXwBzAGUAZQBkAF8AbABpAG0AYgBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQB0AGUAcgBhAHQAaQBvAG4AcwAsACAAUwBFAFEAVQBFAE4AQwBFACgAcgBlAHEAXwBpAHQAZQByAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsAF8AcwB0AGEAdABlACwAIABpAHQAZQByAGEAdABpAG8AbgBzACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAaQB0AGUAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwB1AHIAcgBfAGwAZQBuACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcgAsACAARABSAE8AUAAoAHMAdABhAHQAZQAsACAAMQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AbABlAG4ALAAgAE0ASQBOACgAYwB1AHIAcgBfAGwAZQBuACAAKgAgADIALAAgAHQAYQByAGcAZQB0AF8AbABlAG4AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARAB5AG4AYQBtAGkAYwAgAFMAYwBhAGwAaQBuAGcAIABTAGgAaQBmAHQAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAASQBmACAAQgAgAGgAYQBzACAAcABsAGEAdABlAGEAdQBlAGQALAAgAFIAIABtAHUAcwB0ACAAcwBjAGEAbABlACAAYgB5ACAAMgAqACgAbgAtAG0AKQAuACAASQBmACAAQgAgAGkAcwAgAGcAcgBvAHcAaQBuAGcALAAgAFIAIABzAGMAYQBsAGUAcwAgAGIAeQAgACgAbgAtAG0AKQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAdABpAHYAZQBfAGMAdQByAHIALAAgAE0ASQBOACgAYwB1AHIAcgBfAGwAZQBuACwAIABsAGUAbgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAdABpAHYAZQBfAG4AZQB4AHQALAAgAE0ASQBOACgAbgBlAHgAdABfAGwAZQBuACwAIABsAGUAbgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGgAaQBmAHQAXwBsAGkAbQBiAHMALAAgADIAIAAqACAAKABuAGUAeAB0AF8AbABlAG4AIAAtACAAYwB1AHIAcgBfAGwAZQBuACkAIAAtACAAKABhAGMAdABpAHYAZQBfAG4AZQB4AHQAIAAtACAAYQBjAHQAaQB2AGUAXwBjAHUAcgByACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAXwBwAHIAaQBtAGUALAAgAEkARgAoAHMAaABpAGYAdABfAGwAaQBtAGIAcwAgAD4AIAAwACwAIABWAFMAVABBAEMASwAoAEUAWABQAEEATgBEACgAMAAsACAAcwBoAGkAZgB0AF8AbABpAG0AYgBzACwAIAAsACAAMAApACwAIABjAHUAcgByAF8AcgApACwAIABjAHUAcgByAF8AcgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABiAF8AYQBjAHQAaQB2AGUALAAgAFQAQQBLAEUAKABsAGkAbQBiAHMAXwBiACwAIAAtAGEAYwB0AGkAdgBlAF8AbgBlAHgAdAApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABQACAAaQBzACAAbgBhAHQAaQB2AGUAbAB5ACAAYQBsAGkAZwBuAGUAZAAgAHQAbwAgADIAKgBuAGUAeAB0AF8AbABlAG4AIABiAGUAYwBhAHUAcwBlACAAbwBmACAAdABoAGUAIABjAG8AcgByAGUAYwB0AGUAZAAgAHMAaABpAGYAdABfAGwAaQBtAGIAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGIAXwBhAGMAdABpAHYAZQAsACAAcgBfAHAAcgBpAG0AZQAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AHcAbwBfAGIAZQB0AGEALAAgAFYAUwBUAEEAQwBLACgARQBYAFAAQQBOAEQAKAAwACwAIAAyACAAKgAgAG4AZQB4AHQAXwBsAGUAbgAsACAALAAgADAAKQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGUAcgByACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAdQBiACgAdAB3AG8AXwBiAGUAdABhACwAIABwACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwByAF8AdQBuAHMAYwBhAGwAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAcgBfAHAAcgBpAG0AZQAsACAAZQByAHIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcgAsACAASQBGACgAUgBPAFcAUwAoAG4AZQB4AHQAXwByAF8AdQBuAHMAYwBhAGwAZQBkACkAIAA8AD0AIAAyACAAKgAgAG4AZQB4AHQAXwBsAGUAbgAsACAAewAwAH0ALAAgAEQAUgBPAFAAKABuAGUAeAB0AF8AcgBfAHUAbgBzAGMAYQBsAGUAZAAsACAAMgAgACoAIABuAGUAeAB0AF8AbABlAG4AKQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAG4AZQB4AHQAXwBsAGUAbgAsACAAbgBlAHgAdABfAHIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAMQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEgAZQBhAHYAeQB3AGUAaQBnAGgAdAAgAE4AZQB3AHQAbwBuAC0AUgBhAHAAaABzAG8AbgAgAEQAaQB2AGkAcwBpAG8AbgAuAFwAbgAgACoAIABJAG0AcABsAGUAbQBlAG4AdABzACAAcAByAG8AZwByAGUAcwBzAGkAdgBlACAAcwBjAGEAbABpAG4AZwAgAGIAbwB1AG4AZABlAGQAIAB0AG8AIABNAEEAWAAoAGwAZQBuAF8AYQAsACAAbABlAG4AXwBiACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBhACAAVABoAGUAIABkAGkAdgBpAGQAZQBuAGQAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2ACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAHIAZwBlAHQAXwBsAGUAbgAsACAATQBBAFgAKABsAGUAbgBfAGEALAAgAGwAZQBuAF8AYgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAMQAuACAAQwBhAGwAYwB1AGwAYQB0AGUAIAByAGUAYwBpAHAAcgBvAGMAYQBsACAAUgAgAHMAYwBhAGwAZQBkACAAZAB5AG4AYQBtAGkAYwBhAGwAbAB5ACAAdABvACAAMgAgACoAIAB0AGEAcgBnAGUAdABfAGwAZQBuAFwAbgAgACAAIAAgACAAIAAgACAAcgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBSAGUAYwBpAHAAcgBvAGMAYQBsACgAbABpAG0AYgBzAF8AYgAsACAAdABhAHIAZwBlAHQAXwBsAGUAbgAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAMgAuACAAQQBwAHAAcgBvAHgAaQBtAGEAdABlACAAUQB1AG8AdABpAGUAbgB0ADoAIABRAF8AYQBwAHAAcgBvAHgAIAA9ACAAQQAgACoAIABSACAALwAgAEIAZQB0AGEAXgAoADIAIAAqACAAdABhAHIAZwBlAHQAXwBsAGUAbgApAFwAbgAgACAAIAAgACAAIAAgACAAZAByAG8AcABfAGwAaQBtAGIAcwAsACAAMgAgACoAIAB0AGEAcgBnAGUAdABfAGwAZQBuACwAXABuACAAIAAgACAAIAAgACAAIABxAF8AdQBuAHMAYwBhAGwAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAbABpAG0AYgBzAF8AYQAsACAAcgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABxAF8AYQBwAHAAcgBvAHgALAAgAEkARgAoAFIATwBXAFMAKABxAF8AdQBuAHMAYwBhAGwAZQBkACkAIAA8AD0AIABkAHIAbwBwAF8AbABpAG0AYgBzACwAIAB7ADAAfQAsACAARABSAE8AUAAoAHEAXwB1AG4AcwBjAGEAbABlAGQALAAgAGQAcgBvAHAAXwBsAGkAbQBiAHMAKQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIAB0AGgAZQAgAG0AYQBzAHMAaQB2AGUAIABiAGEAcwBlAGwAaQBuAGUAIABwAHIAbwBkAHUAYwB0ACAAZQB4AGEAYwB0AGwAeQAgAE8ATgBDAEUAXABuACAAIAAgACAAIAAgACAAIABwAF8AYgBhAHMAZQBsAGkAbgBlACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAbABpAG0AYgBzAF8AYgAsACAAcQBfAGEAcABwAHIAbwB4ACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAAzAC4AIABCAG8AdQBuAGQAZQBkACAARQByAHIAbwByACAAQwBvAHIAcgBlAGMAdABpAG8AbgAgAFMAdwBlAGUAcAAgACgATwBwAHQAaQBtAGkAegBlAGQAIABPACgATgApACAAUwB0AGUAcABwAGkAbgBnACkAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABTAHQAYQB0AGUAIABwAGEAYwBrAGkAbgBnADoAIABWAFMAVABBAEMASwAoAEwAZQBuAGcAdABoAF8AUQAsACAAUQBfAGwAaQBtAGIAcwAsACAAUABfAGwAaQBtAGIAcwApAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAcQBfAGEAcABwAHIAbwB4ACkALAAgAHEAXwBhAHAAcAByAG8AeAAsACAAcABfAGIAYQBzAGUAbABpAG4AZQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUwB3AGUAZQBwACAARABvAHcAbgA6ACAASQBmACAAUAAgAD4AIABBACwAIABRACAAaQBzACAAdABvAG8AIABiAGkAZwAuACAAUwB0AGUAcAAgAFEAIABkAG8AdwBuACAAYgB5ACAAMQAsACAAYQBuAGQAIABQACAAZABvAHcAbgAgAGIAeQAgAEIALgBcAG4AIAAgACAAIAAgACAAIAAgAHMAdwBlAGUAcABfAGQAbwB3AG4ALAAgAFIARQBEAFUAQwBFACgAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAewAxADsAIAAyAH0ALAAgAEwAQQBNAEIARABBACgAcwB0AGEAdABlACwAIABpACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwBxACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwBxACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcwB0AGEAdABlACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHEALAAgADEALAAgADIAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwB1AHIAcgBfAHAALAAgAEQAUgBPAFAAKABzAHQAYQB0AGUALAAgAGwAZQBuAF8AcQAgACsAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBDAG8AbQBwAGEAcgBlACgAYwB1AHIAcgBfAHAALAAgAGwAaQBtAGIAcwBfAGEAKQAgAD4AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBTAHUAYgAoAGMAdQByAHIAXwBxACwAIAB7ADEAfQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwBwACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAdQBiACgAYwB1AHIAcgBfAHAALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFIATwBXAFMAKABuAGUAeAB0AF8AcQApACwAIABuAGUAeAB0AF8AcQAsACAAbgBlAHgAdABfAHAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAdABhAHQAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUwB3AGUAZQBwACAAVQBwADoAIABJAGYAIABQACAAKwAgAEIAIAA8AD0AIABBACwAIABRACAAaQBzACAAdABvAG8AIABzAG0AYQBsAGwALgAgAFMAdABlAHAAIABRACAAdQBwACAAYgB5ACAAMQAsACAAYQBuAGQAIABQACAAdQBwACAAYgB5ACAAQgAuAFwAbgAgACAAIAAgACAAIAAgACAAcwB3AGUAZQBwAF8AdQBwACwAIABSAEUARABVAEMARQAoAHMAdwBlAGUAcABfAGQAbwB3AG4ALAAgAHsAMQA7ACAAMgB9ACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAaQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcQAsACAASQBOAEQARQBYACgAcwB0AGEAdABlACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcQAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwBxACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwBwACwAIABEAFIATwBQACgAcwB0AGEAdABlACwAIABsAGUAbgBfAHEAIAArACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBlAHgAdABfAHAAXwB0AGUAcwB0ACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEEAZABkACgAYwB1AHIAcgBfAHAALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEMAbwBtAHAAYQByAGUAKABuAGUAeAB0AF8AcABfAHQAZQBzAHQALAAgAGwAaQBtAGIAcwBfAGEAKQAgADwAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwBxACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEEAZABkACgAYwB1AHIAcgBfAHEALAAgAHsAMQB9ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbgBlAHgAdABfAHEAKQAsACAAbgBlAHgAdABfAHEALAAgAG4AZQB4AHQAXwBwAF8AdABlAHMAdAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAdABlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAARgBpAG4AYQBsACAAUQAgAGEAbgBkACAAUABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAZQBuAF8AcQAsACAASQBOAEQARQBYACgAcwB3AGUAZQBwAF8AdQBwACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHEALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKABzAHcAZQBlAHAAXwB1AHAALAAgAFMARQBRAFUARQBOAEMARQAoAGYAaQBuAGEAbABfAGwAZQBuAF8AcQAsACAAMQAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHAALAAgAEQAUgBPAFAAKABzAHcAZQBlAHAAXwB1AHAALAAgAGYAaQBuAGEAbABfAGwAZQBuAF8AcQAgACsAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAA0AC4AIABFAHgAdAByAGEAYwB0ACAAVAByAHUAZQAgAFIAZQBtAGEAaQBuAGQAZQByACAAUwBhAGYAZQBsAHkAIAAoAEEAIAAtACAARgBpAG4AYQBsAF8AUAApAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBTAHUAYgAoAGwAaQBtAGIAcwBfAGEALAAgAGYAaQBuAGEAbABfAHAALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABmAGkAbgBhAGwAXwByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAEIAYQBzAGUALQAxADAAIABMAGUAZgB0AC0AdABvAC0AUgBpAGcAaAB0ACAARQB4AHAAbwBuAGUAbgB0AGkAYQB0AGkAbwBuAC4AXABuACAAKgAgAEUAdgBhAGwAdQBhAHQAZQBzACAAdABoAGUAIABlAHgAcABvAG4AZQBuAHQAIABpAHQAZQByAGEAdABpAHYAZQBsAHkAIAB1AHMAaQBuAGcAIABhACAAcAByAGUALQBjAG8AbQBwAHUAdABlAGQAIAAxAC0AOQAgAGMAYQBjAGgAZQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAYQBzAGUAIABUAGgAZQAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5ACAAbwBmACAAdABoAGUAIABiAGEAcwBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAZQB4AHAAXwBzAHQAcgBpAG4AZwAgAFQAaABlACAAZQB4AGEAYwB0ACAAdABlAHgAdAAgAHMAdAByAGkAbgBnACAAbwBmACAAdABoAGUAIABlAHgAcABvAG4AZQBuAHQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFUAUABvAHcAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBiAGEAcwBlACwAIABlAHgAcABfAHMAdAByAGkAbgBnACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFAAcgBlAC0AYwBvAG0AcAB1AHQAZQAgAHAAbwB3AGUAcgBzACAAMQAgAHQAaAByAG8AdQBnAGgAIAA5AC4AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQALAAgAGwAaQBtAGIAcwBfAGIAYQBzAGUALABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQBjAG8AbgBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAZgBpAHIAcwB0ACwAIABmAGkAcgBzAHQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABoAGkAcgBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAcwBlAGMAbwBuAGQALAAgAGYAaQByAHMAdAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABmAG8AdQByAHQAaAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAHMAZQBjAG8AbgBkACwAIABzAGUAYwBvAG4AZAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAZgB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABmAG8AdQByAHQAaAAsACAAZgBpAHIAcwB0ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQB4AHQAaAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAHQAaABpAHIAZAAsACAAdABoAGkAcgBkACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQB2AGUAbgB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABzAGkAeAB0AGgALAAgAGYAaQByAHMAdAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABlAGkAZwB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABmAG8AdQByAHQAaAAsACAAZgBvAHUAcgB0AGgALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBpAG4AdABoACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAZQBpAGcAdABoACwAIABmAGkAcgBzAHQALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGUAeABwAF8AZABpAGcAaQB0AHMALAAgAC0ALQBNAEkARAAoAGUAeABwAF8AcwB0AHIAaQBuAGcALAAgAFMARQBRAFUARQBOAEMARQAoAEwARQBOACgAZQB4AHAAXwBzAHQAcgBpAG4AZwApACkALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFIARQBEAFUAQwBFACgAMQAsACAAZQB4AHAAXwBkAGkAZwBpAHQAcwAsACAATABBAE0AQgBEAEEAKABhAGMAYwAsACAAZABpAGcAaQB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBoAG8AcgB0AC0AYwBpAHIAYwB1AGkAdAA6ACAAUwBrAGkAcAAgAGMAYQBsAGMAdQBsAGEAdABpAG4AZwAgADEAXgAxADAAIABkAHUAcgBpAG4AZwAgAGwAZQBhAGQAaQBuAGcAIABpAHQAZQByAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAcwBfAG8AbgBlACwAIABBAE4ARAAoAFIATwBXAFMAKABhAGMAYwApACAAPQAgADEALAAgAEkATgBEAEUAWAAoAGEAYwBjACwAIAAxACwAIAAxACkAIAA9ACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAMQAuACAAUgBhAGkAcwBlACAAQQBjAGMAIAB0AG8AIAB0AGgAZQAgADEAMAB0AGgAIABwAG8AdwBlAHIAIAB1AHMAaQBuAGcAIABlAHgAYQBjAHQAbAB5ACAANAAgAG0AdQBsAHQAaQBwAGwAaQBjAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8AMQAwACwAIABJAEYAKABpAHMAXwBvAG4AZQAsACAAYQBjAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8AMgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGEAYwBjACwAIABhAGMAYwAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8ANAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGEAYwBjAF8AMgAsACAAYQBjAGMAXwAyACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBjAGMAXwA4ACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAYQBjAGMAXwA0ACwAIABhAGMAYwBfADQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAYQBjAGMAXwA4ACwAIABhAGMAYwBfADIALAAgAGsAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAyAC4AIABNAHUAbAB0AGkAcABsAHkAIABiAHkAIAB0AGgAZQAgAGMAbwByAHIAZQBzAHAAbwBuAGQAaQBuAGcAIABwAHIAZQAtAGMAbwBtAHAAdQB0AGUAZAAgAGMAYQBjAGgAZQAgAHYAYQBsAHUAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABkAGkAZwBpAHQAIAA9ACAAMAAsACAAYQBjAGMAXwAxADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAYQBjAGgAZQBfAHYAYQBsACwAIABDAEgATwBPAFMARQAoAGQAaQBnAGkAdAAsACAAZgBpAHIAcwB0ACwAIABzAGUAYwBvAG4AZAAsACAAdABoAGkAcgBkACwAIABmAG8AdQByAHQAaAAsACAAZgBpAGYAdABoACwAIABzAGkAeAB0AGgALAAgAHMAZQB2AGUAbgB0AGgALAAgAGUAaQBnAHQAaAAsACAAbgBpAG4AdABoACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAaQBzAF8AbwBuAGUALAAgAGMAYQBjAGgAZQBfAHYAYQBsACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAYQBjAGMAXwAxADAALAAgAGMAYQBjAGgAZQBfAHYAYQBsACwAIABrACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAEkAbgB0AGUAZwBlAHIAIABTAHEAdQBhAHIAZQAgAFIAbwBvAHQAIAB1AHMAaQBuAGcAIABOAGUAdwB0AG8AbgAnAHMAIABNAGUAdABoAG8AZAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAG4AIABSAGEAZABpAGMAYQBuAGQAIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AcwBlAGUAZAAgAE8AdgBlAHIALQBlAHMAdABpAG0AYQB0AGUAZAAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABzAGUAZQBkACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBVAFMAcQByAHQAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBuACwAIABsAGkAbQBiAHMAXwBzAGUAZQBkACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAdABhAHQAZQAgAGkAcwAgAHAAYQBjAGsAZQBkADoAIABWAFMAVABBAEMASwAoAGkAcwBfAGQAbwBuAGUAXwBmAGwAYQBnACwAIABjAHUAcgByAGUAbgB0AF8AeAApAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKAAwACwAIABsAGkAbQBiAHMAXwBzAGUAZQBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AaQB0AGUAcgBzACwAIAAzADUALABcAG4AXABuACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAHQAYQB0AGUALAAgAFIARQBEAFUAQwBFACgAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbQBhAHgAXwBpAHQAZQByAHMAKQAsACAATABBAE0AQgBEAEEAKABzAHQAYQB0AGUALAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAHMAXwBkAG8AbgBlACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwB4ACwAIABEAFIATwBQACgAcwB0AGEAdABlACwAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAaQBzAF8AZABvAG4AZQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAdABlACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAxAC4AIABEAGkAdgBpAHMAaQBvAG4AOgAgAG4AIAAvACAAeABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZABpAHYAXwBwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ARABpAHYAUgBvAHUAdABlAHIAKABsAGkAbQBiAHMAXwBuACwAIABjAHUAcgByAF8AeAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcgAsACAASQBOAEQARQBYACgAZABpAHYAXwBwAGEAYwBrAGUAZAAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHEALAAgAEQAUgBPAFAAKABkAGkAdgBfAHAAYQBjAGsAZQBkACwAIABsAGUAbgBfAHIAIAArACAAMQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAyAC4AIABBAGQAZABpAHQAaQBvAG4AOgAgAHgAIAArACAAKABuACAALwAgAHgAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB1AG0AXwB4AHEALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQQBkAGQAKABjAHUAcgByAF8AeAAsACAAcQAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAzAC4AIABIAGEAbAB2AGkAbgBnADoAIAAoAHgAIAArACAAKABuACAALwAgAHgAKQApACAALwAgADIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEsAbgB1AHQAaABEAGkAdgAgAGkAbgBoAGUAcgBlAG4AdABsAHkAIABzAHUAcABwAG8AcgB0AHMAIABzAGMAYQBsAGEAcgAgAGQAaQB2AGkAcwBvAHIAcwAgAHcAaQB0AGgAIAB6AGUAcgBvACAAbwB2AGUAcgBoAGUAYQBkAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGkAdgBfADIAXwBwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2ACgAcwB1AG0AXwB4AHEALAAgAHsAMgB9ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwByADIALAAgAEkATgBEAEUAWAAoAGQAaQB2AF8AMgBfAHAAYQBjAGsAZQBkACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAeABfAG4AZQB4AHQALAAgAEQAUgBPAFAAKABkAGkAdgBfADIAXwBwAGEAYwBrAGUAZAAsACAAbABlAG4AXwByADIAIAArACAAMQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAA0AC4AIABDAG8AbgB2AGUAcgBnAGUAbgBjAGUAIABDAGgAZQBjAGsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQwBvAG0AcABhAHIAZQAoAHgAXwBuAGUAeAB0ACwAIABjAHUAcgByAF8AeAApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABOAGUAdwB0AG8AbgAnAHMAIABtAGUAdABoAG8AZAAgAGMAbwBuAHYAZQByAGcAZQBzACAAbwBuACAAdABoAGUAIABmAGwAbwBvAHIAIAByAG8AbwB0ACwAIABhAG4AZAAgAHMAdABhAGIAaQBsAGkAegBlAHMAIABvAHIAIABvAHMAYwBpAGwAbABhAHQAZQBzACAAdQBwACAAYgB5ACAAMQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABUAGgAZQByAGUAZgBvAHIAZQAsACAAaQBmACAAeABfAG4AZQB4AHQAIAA+AD0AIABjAHUAcgByAF8AeAAsACAAdABoAGUAIABhAGwAZwBvAHIAaQB0AGgAbQAgAGgAYQBzACAAYwBvAG4AdgBlAHIAZwBlAGQALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYwBvAG0AcAAgAD4APQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADEALAAgAGMAdQByAHIAXwB4ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADAALAAgAHgAXwBuAGUAeAB0ACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAZgBpAG4AYQBsAF8AcwB0AGEAdABlACwAIAAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABHAGUAbgBlAHIAYQB0AGUAcwAgAGEAIAAxAEQAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkAIABvAGYAIABhAGwAbAAgAHAAcgBpAG0AZQAgAG4AdQBtAGIAZQByAHMAIAB1AHAAIAB0AG8AIABuAC4AXABuACAAKgAgAEUAdgBhAGwAdQBhAHQAZQBzACAAcAB1AHIAZQBsAHkAIABpAG4AIABuAGEAdABpAHYAZQAgAEMAKwArACAAdQBzAGkAbgBnACAAYQAgAGQAeQBuAGEAbQBpAGMAIABzAGkAZQB2AGUALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABuACAAVABoAGUAIAB1AHAAcABlAHIAIABiAG8AdQBuAGQAIABpAG4AdABlAGcAZQByACAAKABhAHMAcwB1AG0AZQBkACAAPAA9ACAAOQAyADcAMwApAC4AXABuACAAKgAvAFwAbgBOAGEAdABpAHYAZQBQAHIAaQBtAGUAcwAgAD0AIABMAEEATQBCAEQAQQAoAG4ALABcAG4AIAAgACAAIABJAEYAKABuACAAPAAgADIALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBlAHEALAAgAFMARQBRAFUARQBOAEMARQAoAG4AIAAtACAAMQAsACAAMQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAcwBlAHEALAAgAE0AQQBQACgAcwBlAHEALAAgAEwAQQBNAEIARABBACgAeAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBpAHQALAAgAEkATgBUACgAUwBRAFIAVAAoAHgAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABsAGkAbQBpAHQAIAA8ACAAMgAsACAAVABSAFUARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAE0ATwBEACgAeAAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABpAG0AaQB0ACAALQAgADEALAAgADEALAAgADIAKQApACkAIAA+ACAAMABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAQwBhAGwAYwB1AGwAYQB0AGUAcwAgAHQAaABlACAAZQB4AHAAbwBuAGUAbgB0ACAAZgBvAHIAIABhAG4AIABhAHIAcgBhAHkAIABvAGYAIABwAHIAaQBtAGUAIABuAHUAbQBiAGUAcgBzACAAbgBhAHQAaQB2AGUAbAB5ACAAdQBzAGkAbgBnACAATABlAGcAZQBuAGQAcgBlACcAcwAgAEYAbwByAG0AdQBsAGEALgBcAG4AIAAqACAARQB2AGEAbAB1AGEAdABlAHMAIABwAHUAcgBlAGwAeQAgAGkAbgAgAG4AYQB0AGkAdgBlACAAQwArACsAIAB3AGkAdABoACAAegBlAHIAbwAgAEIAaQBnAEkAbgB0ACAAbwB2AGUAcgBoAGUAYQBkAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbgAgAFQAaABlACAAaQBuAHQAZQBnAGUAcgAgAGYAYQBjAHQAbwByAGkAYQBsACAAYgBhAHMAZQAgACgAPAA9ACAAOQAyADcAMwApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAcAByAGkAbQBlAHMAIABBACAAdgBlAHIAdABpAGMAYQBsACAAYQByAHIAYQB5ACAAbwBmACAAcAByAGkAbQBlACAAbgB1AG0AYgBlAHIAcwAgACgAPAA9ACAAbgApAC4AXABuACAAKgAvAFwAbgBOAGEAdABpAHYAZQBMAGUAZwBlAG4AZAByAGUAIAA9ACAATABBAE0AQgBEAEEAKABuACwAIABwAHIAaQBtAGUAcwAsAFwAbgAgACAAIAAgAE0AQQBQACgAcAByAGkAbQBlAHMALAAgAEwAQQBNAEIARABBACgAcAAsAFwAbgAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAHgAXwBrACwAIABJAE4AVAAoAEwATwBHACgAbgAsACAAcAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABvAHcAZQByAHMALAAgAHAAIABeACAAUwBFAFEAVQBFAE4AQwBFACgAbQBhAHgAXwBrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAE0AKABJAE4AVAAoAG4AIAAvACAAcABvAHcAZQByAHMAKQApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAVQBuAHMAYQBmAGUALAAgAGgAaQBnAGgALQBwAGUAcgBmAG8AcgBtAGEAbgBjAGUAIAB0AGUAeAB0ACAAbQB1AGwAdABpAHAAbABpAGMAYQB0AGkAbwBuACAAZgBvAHIAIAB0AHIAdQBzAHQAZQBkACwAIABwAG8AcwBpAHQAaQB2AGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQgB5AHAAYQBzAHMAZQBzACAATABhAHkAZQByACAAMAAgAHYAYQBsAGkAZABhAHQAaQBvAG4ALgAgAEkAbQBwAGwAZQBtAGUAbgB0AHMAIABzAHQAcgBpAGMAdAAgAHMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAcwAgAGYAbwByACAAcABhAGQAZABpAG4AZwAgAG8AcAB0AGkAbQBpAHoAYQB0AGkAbwBuAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAcwB0AHIAXwBhACAAVABoAGUAIABmAGkAcgBzAHQAIAB0AHIAdQBzAHQAZQBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHMAdAByAF8AYgAgAFQAaABlACAAcwBlAGMAbwBuAGQAIAB0AHIAdQBzAHQAZQBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AVQBUAGUAeAB0AE0AdQBsACAAPQAgAEwAQQBNAEIARABBACgAcwB0AHIAXwBhACwAIABzAHQAcgBfAGIALABcAG4AIAAgACAAIABJAEYAKABPAFIAKABzAHQAcgBfAGEAIAA9ACAAXAAiADAAXAAiACwAIABzAHQAcgBfAGIAIAA9ACAAXAAiADAAXAAiACkALAAgAFwAIgAwAFwAIgAsAFwAbgAgACAAIAAgAEkARgAoAHMAdAByAF8AYQAgAD0AIABcACIAMQBcACIALAAgAHMAdAByAF8AYgAsAFwAbgAgACAAIAAgAEkARgAoAHMAdAByAF8AYgAgAD0AIABcACIAMQBcACIALAAgAHMAdAByAF8AYQAsAFwAbgAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwBhACwAIABMAEUATgAoAHMAdAByAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAATABFAE4AKABzAHQAcgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIATQBVAEwAXAAiACwAIABNAEkATgAoAGwAZQBuAF8AYQAsACAAbABlAG4AXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAcwB0AHIAXwBhACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAcwB0AHIAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAKQApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFYAZQBjAHQAbwByAGkAegBlAGQAIABsAG8AZwBhAHIAaQB0AGgAbQBpAGMAIABwAHIAbwBkAHUAYwB0ACAAbwBmACAAYQBuACAAYQByAHIAYQB5ACAAbwBmACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAKgAgAFIAZQBjAHUAcgBzAGkAdgBlAGwAeQAgAGMAdQB0AHMAIAB0AGgAZQAgAGEAcgByAGEAeQAgAGkAbgAgAGgAYQBsAGYAIAB0AG8AIABiAHkAcABhAHMAcwAgAFIARQBEAFUAQwBFACAAcwBlAHEAdQBlAG4AdABpAGEAbAAgAG0AZQBtAG8AcgB5ACAAYQBsAGwAbwBjAGEAdABpAG8AbgBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAdABlAHgAdABfAGEAcgByACAAQQAgADEARAAgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoALwBcAG4AVABlAHgAdABUAHIAZQBlAFAAcgBvAGQAIAA9ACAATABBAE0AQgBEAEEAKAB0AGUAeAB0AF8AYQByAHIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgAsACAAUgBPAFcAUwAoAHQAZQB4AHQAXwBhAHIAcgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AIAA9ACAAMQAsACAASQBOAEQARQBYACgAdABlAHgAdABfAGEAcgByACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAcwBoAGEAcABlACAAYQByAHIAYQB5ACAAaQBuAHQAbwAgAHAAYQBpAHIAcwAuACAATwBkAGQALQBsAGUAbgBnAHQAaAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABzAGEAZgBlAGwAeQAgAHAAYQBkAGQAZQBkACAAdwBpAHQAaAAgAHQAaABlACAAbQB1AGwAdABpAHAAbABpAGMAYQB0AGkAdgBlACAAaQBkAGUAbgB0AGkAdAB5ACAAXAAiADEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAYQBpAHIAZQBkACwAIABXAFIAQQBQAFIATwBXAFMAKAB0AGUAeAB0AF8AYQByAHIALAAgADIALAAgAFwAIgAxAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAVgBlAGMAdABvAHIAaQB6AGUAZAAgAG0AdQBsAHQAaQBwAGwAaQBjAGEAdABpAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABwAGEAaQByAHMAIABzAGkAbQB1AGwAdABhAG4AZQBvAHUAcwBsAHkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBlAHgAdABfAGEAcgByACwAIABCAFkAUgBPAFcAKABwAGEAaQByAGUAZAAsACAATABBAE0AQgBEAEEAKAByAG8AdwAsACAAVQBUAGUAeAB0AE0AdQBsACgASQBOAEQARQBYACgAcgBvAHcALAAgADEALAAgADEAKQAsACAASQBOAEQARQBYACgAcgBvAHcALAAgADEALAAgADIAKQApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABhAGwAbABvAHcAIAByAGUAYwB1AHIAcwBpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBUAGUAeAB0AFQAcgBlAGUAUAByAG8AZAAoAG4AZQB4AHQAXwBhAHIAcgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBCAGkAZwBJAG4AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAFwAbgAvAC8AIABCAGkAZwAgAEkAbgB0AGUAZwBlAHIAIABBAHIAaQB0AGgAbQBlAHQAaQBjACAATABpAGIAcgBhAHIAeQAgAC8ALwBcAG4ALwAvACAAIAAgACAAIAAgACAAIABCAGkAZwBJAG4AdAAgAE0AbwBkAHUAbABlACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAgAFAAdQBiAGwAaQBjACAAQQBQAEkAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvAFwAbgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABOAG8AcgBtAGEAbABpAHMAZQBzACAAYQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgAgAFMAdAByAGkAcABzACAAbABlAGEAZABpAG4AZwAgAHoAZQByAG8AcwAsACAAcgBlAHMAbwBsAHYAZQBzACAAXAAiAC0AMABcACIAIAB0AG8AIABcACIAMABcACIALAAgAGEAbgBkACAAdABoAHIAbwB3AHMAIAAjAFYAQQBMAFUARQAhACAAbwBuACAAaQBuAHYAYQBsAGkAZAAgAGMAaABhAHIAYQBjAHQAZQByAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBOAG8AcgBtACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABzAHQAcgAsACAASQBGACgATwBSACgASQBTAE8ATQBJAFQAVABFAEQAKABiAGkAZwBfAGkAbgB0ACkALAAgAGIAaQBnAF8AaQBuAHQAIAA9ACAAXAAiAFwAIgApACwAIABcACIAMABcACIALAAgAGIAaQBnAF8AaQBuAHQAIAAmACAAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABpAHMAXwB2AGEAbABpAGQALAAgAFIARQBHAEUAWABUAEUAUwBUACgAcwB0AHIALAAgAFwAIgBeAC0APwBcAFwAZAArACQAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdAByAGkAcABwAGUAZAAsACAAUgBFAEcARQBYAFIARQBQAEwAQQBDAEUAKABzAHQAcgAsACAAXAAiAF4AKAAtAD8AKQAwACsAKAA/AD0AXABcAGQAKQBcACIALAAgAFwAIgAkADEAXAAiACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABOAE8AVAAoAGkAcwBfAHYAYQBsAGkAZAApACwAIABWAEEATABVAEUAKABcACIAIwBWAEEATABVAEUAIQBcACIAKQAsACAASQBGACgAcwB0AHIAaQBwAHAAZQBkACAAPQAgAFwAIgAtADAAXAAiACwAIABcACIAMABcACIALAAgAHMAdAByAGkAcABwAGUAZAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFIAZQB0AHUAcgBuAHMAIAB0AGgAZQAgAHMAaQBnAG4AIABvAGYAIABhACAAQgBpAGcASQBuAHQAOgAgADEAIAAoAHAAbwBzAGkAdABpAHYAZQApACwAIAAtADEAIAAoAG4AZQBnAGEAdABpAHYAZQApACwAIABvAHIAIAAwACAAKAB6AGUAcgBvACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBTAGkAZwBuACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsACAAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AZQBkACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIABTAFcASQBUAEMASAAoAEwARQBGAFQAKABuAG8AcgBtAGUAZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAwAFwAIgAsACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAC0AMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvAC8AIAAtAC0ALQAgAFAAcgBlAGQAaQBjAGEAdABlAHMAIAAtAC0ALQAgAFwAXABcAFwAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAFQAUgBVAEUAIABpAGYAIAB0AGgAZQAgAEIAaQBnAEkAbgB0ACAAaQBzACAAZQB4AGEAYwB0AGwAeQAgAHoAZQByAG8ALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBJAHMAWgBlAHIAbwAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0ACkAIAA9ACAAXAAiADAAXAAiACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAVABSAFUARQAgAGkAZgAgAHQAaABlACAAQgBpAGcASQBuAHQAIABpAHMAIABuAGUAZwBhAHQAaQB2AGUALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBJAHMATgBlAGcAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAIABMAEUARgBUACgATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAKQApACAAPQAgAFwAIgAtAFwAIgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAFQAUgBVAEUAIABpAGYAIAB0AGgAZQAgAEIAaQBnAEkAbgB0ACAAaQBzACAAZQB2AGUAbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAIABUAGgAZQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEkAcwBFAHYAZQBuACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsACAASQBTAEUAVgBFAE4AKABWAEEATABVAEUAKABSAEkARwBIAFQAKABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACkAKQApACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAVABSAFUARQAgAGkAZgAgAHQAaABlACAAQgBpAGcASQBuAHQAIABpAHMAIABvAGQAZAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAIABUAGgAZQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEkAcwBPAGQAZAAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALAAgAEkAUwBPAEQARAAoAFYAQQBMAFUARQAoAFIASQBHAEgAVAAoAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0ACkAKQApACkAKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFIAZQB0AHUAcgBuAHMAIAB0AGgAZQAgAHUAbgBzAGkAZwBuAGUAZAAgAG0AYQBnAG4AaQB0AHUAZABlACAAbwBmACAAYQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAIAAoAGEAYgBzAG8AbAB1AHQAZQAgAHYAYQBsAHUAZQApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AQQBiAHMAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAIABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgB1AG0ALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwARQBGAFQAKABuAHUAbQApACAAPQAgAFwAIgAtAFwAIgAsACAATQBJAEQAKABuAHUAbQAsACAAMgAsACAATABFAE4AKABuAHUAbQApACAALQAgADEAKQAsACAAbgB1AG0AKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAQwBvAG0AcABhAHIAZQBzACAAdAB3AG8AIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMALgAgAFIAZQB0AHUAcgBuAHMAIAAxACAAKABhACAAPgAgAGIAKQAsACAALQAxACAAKABhACAAPAAgAGIAKQAsACAAbwByACAAMAAgACgAYQAgAD0AIABiACkALgBcAG4AIAAqACAARQB2AGEAbAB1AGEAdABlAHMAIABzAGkAZwBuAHMAIABhAG4AZAAgAGwAZQBuAGcAdABoAHMALgAgAEkAZgAgAGkAZABlAG4AdABpAGMAYQBsACwAIABkAGUAbABlAGcAYQB0AGUAcwAgAHQAbwAgAG4AYQB0AGkAdgBlACAAbABpAG0AYgAgAGEAcgByAGEAeQAgAGMAbwBtAHAAYQByAGkAcwBvAG4ALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEMAbwBtAHAAYQByAGUAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGEALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBhACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgAsACAAQgBpAGcAaQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAHMAaQBnAG4AXwBhACAAPAA+ACAAcwBpAGcAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBJAEcATgAoAHMAaQBnAG4AXwBhACAALQAgAHMAaQBnAG4AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAcwBpAGcAbgBfAGEAIAA9ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwBhACwAIABMAEUATgAoAG4AbwByAG0AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAATABFAE4AKABuAG8AcgBtAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGwAZQBuAF8AYQAgADwAPgAgAGwAZQBuAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEkARwBOACgAbABlAG4AXwBhACAALQAgAGwAZQBuAF8AYgApACAAKgAgAHMAaQBnAG4AXwBhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEEARABEAFwAIgApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBhACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGEAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBiACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcABhAHIAaQBzAG8AbgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAGcAXwBjAG8AbQBwAGEAcgBpAHMAbwBuACAAKgAgAHMAaQBnAG4AXwBhAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIAAtACAAQQBkAGQAaQB0AGkAbwBuACAAJgAgAFMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAC0AIAAgACAAIAAgACAAIABcAFwAXABcAFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEEAZABkAHMAIAB0AHcAbwAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBhACAAVABoAGUAIABmAGkAcgBzAHQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGIAIABUAGgAZQAgAHMAZQBjAG8AbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AQQBkAGQAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGEALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBhACwAIABCAGkAZwBpAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIAQQBEAEQAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGEALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYQApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYgApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHUAdABlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEEAZABkAFMAdQBiAFIAbwB1AHQAZQByACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAcwBpAGcAbgBfAGEALAAgAHMAaQBnAG4AXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAaQBnAG4ALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKAByAG8AdQB0AGUAZAAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAARABSAE8AUAAoAHIAbwB1AHQAZQBkACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABtAGUAcgBnAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAFwAIgAtAFwAIgAgACYAIABtAGUAcgBnAGUAZAAsACAAbQBlAHIAZwBlAGQAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUwB1AGIAdAByAGEAYwB0AHMAIAB0AGgAZQAgAHMAZQBjAG8AbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAGYAaQByAHMAdAAgACgAQQAgAC0AIABCACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAbQBpAG4AdQBlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAcwB1AGIAdAByAGEAaABlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAFMAdQBiACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBiACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABJAG4AdgBlAHIAdAAgAHQAaABlACAAcwBpAGcAbgAgAG8AZgAgAEIAIABhAHQAIAB0AGgAZQAgAHQAZQB4AHQAIABsAGUAdgBlAGwAXABuACAAIAAgACAAIAAgACAAIABpAG4AdgBfAGIALAAgAEkARgAoAG4AbwByAG0AXwBiACAAPQAgAFwAIgAwAFwAIgAsACAAXAAiADAAXAAiACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATABFAEYAVAAoAG4AbwByAG0AXwBiACkAIAA9ACAAXAAiAC0AXAAiACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkARAAoAG4AbwByAG0AXwBiACwAIAAyACwAIABMAEUATgAoAG4AbwByAG0AXwBiACkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACAAJgAgAG4AbwByAG0AXwBiAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABQAGEAcwBzACAAdABvACAAQQBkAGQAXABuACAAIAAgACAAIAAgACAAIABBAGQAZAAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABpAG4AdgBfAGIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUwB1AG0AcwAgAGEAbgAgAGEAcgByAGEAeQAgAG8AcgAgAHIAYQBuAGcAZQAgAG8AZgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAgAHYAaQBhACAAdgBlAGMAdABvAHIAaQB6AGUAZAAgAGcAcgBvAHUAcAAgAG0AYQB0AHIAaQBjAGUAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHIAYQBuAGcAZQAgAEEAIABjAG8AbgB0AGkAZwB1AG8AdQBzACAAcgBhAG4AZwBlACAAbwByACAAYQByAHIAYQB5ACAAbwBmACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAKgAvAFwAbgBTAHUAbQAgAD0AIABMAEEATQBCAEQAQQAoAHIAYQBuAGcAZQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABmAGwAYQB0ACwAIABUAE8AUgBPAFcAKAByAGEAbgBnAGUALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABJAFMARQBSAFIATwBSACgAZgBsAGEAdAApACwAIABDAE8ATABVAE0ATgBTACgAZgBsAGEAdAApACAAPQAgADAAKQAsACAAXAAiADAAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBzACwAIABNAEEAUAAoAGYAbABhAHQALAAgAEwAQQBNAEIARABBACgAeAAsACAATgBvAHIAbQAoAHgAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGkAZwBuAHMALAAgAE0AQQBQACgATABFAEYAVAAoAG4AbwByAG0AcwApACwAIABMAEEATQBCAEQAQQAoAHgALAAgAEkARgAoAHgAIAA9ACAAXAAiADAAXAAiACwAIAAwACwAIABpAGYAKAB4ACAAPQAgAFwAIgAtAFwAIgAsACAALQAxACwAIAAxACkAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGIAcwBfAG4AbwByAG0AcwAsACAATQBBAFAAKABuAG8AcgBtAHMALAAgAHMAaQBnAG4AcwAsACAATABBAE0AQgBEAEEAKAB4ACwAIABzAGkAZwBuACwAIABJAEYAKABzAGkAZwBuACAAPQAgAC0AMQAsACAATQBJAEQAKAB4ACwAIAAyACwAIABMAEUATgAoAHgAKQAtADEAKQAsACAAeAApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAbwBzAF8AcwB0AHIAcwAsACAARgBJAEwAVABFAFIAKABhAGIAcwBfAG4AbwByAG0AcwAsACAAcwBpAGcAbgBzACAAPQAgADEALAAgAHsAXAAiADAAXAAiAH0AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQBnAF8AcwB0AHIAcwAsACAARgBJAEwAVABFAFIAKABhAGIAcwBfAG4AbwByAG0AcwAsACAAcwBpAGcAbgBzACAAPQAgAC0AMQAsACAAewBcACIAMABcACIAfQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdQBuAGkAZgBpAGUAZABfAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBBAEQARABcACIALAAgAEMATwBMAFUATQBOAFMAKABmAGwAYQB0ACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAbwBzAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AYQB0AHIAaQB4AFMAdQBtACgAcABvAHMAXwBzAHQAcgBzACwAIAB1AG4AaQBmAGkAZQBkAF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBlAGcAXwBsAGkAbQBiAHMALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQBhAHQAcgBpAHgAUwB1AG0AKABuAGUAZwBfAHMAdAByAHMALAAgAHUAbgBpAGYAaQBlAGQAXwBrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAG8AdQB0AGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AQQBkAGQAUwB1AGIAUgBvAHUAdABlAHIAKABwAG8AcwBfAGwAaQBtAGIAcwAsACAAbgBlAGcAXwBsAGkAbQBiAHMALAAgADEALAAgAC0AMQAsACAAdQBuAGkAZgBpAGUAZABfAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAaQBnAG4ALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKAByAG8AdQB0AGUAZAAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAEQAUgBPAFAAKAByAG8AdQB0AGUAZAAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGUAcgBnAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIAB1AG4AaQBmAGkAZQBkAF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAFwAIgAtAFwAIgAgACYAIABtAGUAcgBnAGUAZAAsACAAbQBlAHIAZwBlAGQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAE0AdQBsAHQAaQBwAGwAaQBlAHMAIAB0AHcAbwAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBhACAAVABoAGUAIABmAGkAcgBzAHQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGIAIABUAGgAZQAgAHMAZQBjAG8AbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ATQB1AGwAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGEALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBhACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwBhACwAIABMAEUATgAoAG4AbwByAG0AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAATABFAE4AKABuAG8AcgBtAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAOgAgADAAIABtAHUAbAB0AGkAcABsAGkAZQBkACAAYgB5ACAAYQBuAHkAdABoAGkAbgBnACAAaQBzACAAMABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAE8AUgAoAHMAaQBnAG4AXwBhACAAPQAgADAALAAgAHMAaQBnAG4AXwBiACAAPQAgADAAKQAsACAAXAAiADAAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABsAGUAbgBfAGEAIAArACAAbABlAG4AXwBiACAAPgAgADMAMgA3ADYANgAsACAAIwBOAFUATQAhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIABkAHkAbgBhAG0AaQBjACAAcwBhAGYAZQAgAEsAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHMAaABvAHIAdABlAHMAdAAgAHMAdAByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBNAFUATABcACIALAAgAE0ASQBOACgAbABlAG4AXwBhACwAIABsAGUAbgBfAGIAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBwAGwAaQB0ACAAYQBiAHMAbwBsAHUAdABlACAAcwB0AHIAaQBuAGcAcwAgAGkAbgB0AG8AIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAYQByAHIAYQB5AHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBhACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYgApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAbABjAHUAbABhAHQAZQAgAG0AYQBnAG4AaQB0AHUAZABlACAAYQBuAGQAIAByAGUAcwBvAGwAdgBlACAAcwBpAGcAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAGkAZwBuACwAIABzAGkAZwBuAF8AYQAgACoAIABzAGkAZwBuAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AZQByAGcAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGYAaQBuAGEAbABfAHMAaQBnAG4AIAA9ACAALQAxACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQALAAgAG0AZQByAGcAZQBkACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsAVgBPAEwAQQBUAEkATABFAF0AIABHAGUAbgBlAHIAYQB0AGUAcwAgAGEAIABkAHkAbgBhAG0AaQBjACAAYQByAHIAYQB5ACAAbwBmACAAaQBuAHQAZQBnAGUAcgBzACAAYQBzACAAdABlAHgAdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAbgB1AG0AXwByAG8AdwBzAF0AIABhAHIAcgBhAHkAIABoAGUAaQBnAGgAdAAsACAAZABlAGYAYQB1AGwAdAAgADEALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG4AdQBtAF8AYwBvAGwAcwBdACAAYQByAHIAYQB5ACAAdwBpAGQAdABoACwAIABkAGUAZgBhAHUAbAB0ACAAMQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAbQBpAG4AXwBkAGkAZwBpAHQAcwBdACAAbQBpAG4AaQBtAHUAbQAgAG4AdQBtAGIAZQByACAAbwBmACAAZABpAGcAaQB0AHMALAAgAGQAZQBmAGEAdQBsAHQAIAAxADYAIAAoAG0AaQBuACAAMQAgAGQAaQBnAGkAdAApAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAbQBhAHgAXwBkAGkAZwBpAHQAcwBdACAAbQBhAHgAaQBtAHUAbQAgAG4AdQBtAGIAZQByACAAbwBmACAAZABpAGcAaQB0AHMALAAgAGQAZQBmAGEAdQBsAHQAIAA1ADAAIAAoAG0AYQB4ACAAMwAyACwANwA2ADcAIABjAGgAYQByAHMALAAgAGkAbgBjAGwAdQBkAGkAbgBnACAAcwBpAGcAbgApAFwAbgAgACoALwBcAG4AUgBhAG4AZABCAGkAZwBJAG4AdABBAHIAcgBhAHkAIAA9ACAATABBAE0AQgBEAEEAKABbAG4AdQBtAF8AcgBvAHcAcwBdACwAIABbAG4AdQBtAF8AYwBvAGwAcwBdACwAIABbAG0AaQBuAF8AZABpAGcAaQB0AHMAXQAsACAAWwBtAGEAeABfAGQAaQBnAGkAdABzAF0ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBfAHIAbwB3AHMALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbgB1AG0AXwByAG8AdwBzACkALAAgADEALAAgAG4AdQBtAF8AcgBvAHcAcwApACwAXABuACAAIAAgACAAIAAgACAAIABuAF8AYwBvAGwAcwAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABuAHUAbQBfAGMAbwBsAHMAKQAsACAAMQAsACAAbgB1AG0AXwBjAG8AbABzACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAbQBpAG4AXwBsAGUAbgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABtAGkAbgBfAGQAaQBnAGkAdABzACkALAAgADEANgAsACAATQBJAE4AKAAzADIANwA2ADcALAAgAE0AQQBYACgAMQAsACAAbQBpAG4AXwBkAGkAZwBpAHQAcwApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwBsAGUAbgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABtAGEAeABfAGQAaQBnAGkAdABzACkALAAgADUAMAAsACAATQBBAFgAKAAxACwAIABNAEkATgAoADMAMgA3ADYANgAsACAAbQBhAHgAXwBkAGkAZwBpAHQAcwApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBQACgAUgBBAE4ARABBAFIAUgBBAFkAKABuAF8AcgBvAHcAcwAsACAAbgBfAGMAbwBsAHMALAAgAG0AaQBuAF8AbABlAG4ALAAgAG0AYQB4AF8AbABlAG4ALAAgAFQAUgBVAEUAKQAsACAATABBAE0AQgBEAEEAKABsAGUAbgBnAHQAaAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAaQBnAG4ALAAgAEMASABPAE8AUwBFACgAUgBBAE4ARABCAEUAVABXAEUARQBOACgAMQAsACAAMgApACwAIABcACIAXAAiACwAIABcACIALQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGQAaQBnAGkAdABzACwAIABDAE8ATgBDAEEAVAAoAFIAQQBOAEQAQQBSAFIAQQBZACgAMQAsACAAbABlAG4AZwB0AGgALAAgADAALAAgADkALAAgAFQAUgBVAEUAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBpAGcAbgAgACYAIABSAEUARwBFAFgAUgBFAFAATABBAEMARQAoAGQAaQBnAGkAdABzACwAIABcACIAXgAwACoAXAAiACwAIABcACIAXAAiACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEQAaQB2AGkAZABlAHMAIAB0AGgAZQAgAGYAaQByAHMAdAAgAEIAaQBnAEkAbgB0ACAAYgB5ACAAdABoAGUAIABzAGUAYwBvAG4AZAAgACgAQQAgAC8AIABCACkALgAgAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIABxAHUAbwB0AGkAZQBuAHQAIABhAG4AZAAgAG0AbwBkAHUAbAB1AHMAIABpAG4AIAByAG8AdwBzACAAMQAgAGEAbgBkACAAMgAsACAAcgBlAHMAcABlAGMAdABpAHYAZQBsAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAdQBzAGUAXwBmAGwAbwBvAHIAXQAgAE8AcAB0AGkAbwBuAGEAbAAgAGIAbwBvAGwAZQBhAG4ALgAgAFQAUgBVAEUAIABmAG8AcgAgAFAAeQB0AGgAbwBuAC0AcwB0AHkAbABlACAARgBsAG8AbwByACAAZABpAHYAaQBzAGkAbwBuACwAIABGAEEATABTAEUAIABmAG8AcgAgAFQAcgB1AG4AYwBhAHQAZQBkAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABGAEEATABTAEUALgBcAG4AIAAqAC8AXABuAEQAaQB2AE0AbwBkACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAIABbAHUAcwBlAF8AZgBsAG8AbwByAF0ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGEALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBhACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AZgBsAG8AbwByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHUAcwBlAF8AZgBsAG8AbwByACkALAAgAEYAQQBMAFMARQAsACAAdQBzAGUAXwBmAGwAbwBvAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AYgAgAD0AIAAwACwAIAAjAEQASQBWAC8AMAAhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHMAaQBnAG4AXwBhACAAPQAgADAALAAgAHsAXAAiADAAXAAiADsAXAAiADAAXAAiAH0ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBhACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGEAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBiACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGIAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAYQBjAGsAZQBkAF8AcgBlAHMAdQBsAHQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEQAaQB2AFIAbwB1AHQAZQByACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABSAGUAbQBhAGkAbgBkAGUAcgAgAGEAbgBkACAAUQB1AG8AdABpAGUAbgB0ACAAYQByAHIAYQB5AHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHIALAAgAEkATgBEAEUAWAAoAHAAYQBjAGsAZQBkAF8AcgBlAHMAdQBsAHQALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAG0AXwBsAGkAbQBiAHMALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKABwAGEAYwBrAGUAZABfAHIAZQBzAHUAbAB0ACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHIALAAgADEALAAgADIAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABxAHUAbwB0AF8AbABpAG0AYgBzACwAIABEAFIATwBQACgAcABhAGMAawBlAGQAXwByAGUAcwB1AGwAdAAsACAAbABlAG4AXwByACAAKwAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAcwBvAGwAdgBlACAAVAByAHUAbgBjAGEAdABlAGQAIABzAGkAZwBuAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAGkAZwBuACwAIABzAGkAZwBuAF8AYQAgACoAIABzAGkAZwBuAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBlAHIAZwBlAGQAXwBxACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABxAHUAbwB0AF8AbABpAG0AYgBzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AZQByAGcAZQBkAF8AcgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAcgBlAG0AXwBsAGkAbQBiAHMALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AHIAdQBuAGMAXwBxACwAIABJAEYAKABBAE4ARAAoAGYAaQBuAGEAbABfAHMAaQBnAG4AIAA9ACAALQAxACwAIABtAGUAcgBnAGUAZABfAHEAIAA8AD4AIABcACIAMABcACIAKQAgACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQAXwBxACwAIABtAGUAcgBnAGUAZABfAHEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdAByAHUAbgBjAF8AcgAsACAASQBGACgAYQBuAGQAKABzAGkAZwBuAF8AYQAgAD0AIAAtADEALAAgAG0AZQByAGcAZQBkAF8AcgAgADwAPgAgAFwAIgAwAFwAIgApACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQAXwByACwAIABtAGUAcgBnAGUAZABfAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABGAGwAbwBvAHIAIABDAG8AcgByAGUAYwB0AGkAbwBuADoAIABUAHIAaQBnAGcAZQByACAATwBOAEwAWQAgAGkAZgAgAGYAbABvAG8AcgAgAGkAcwAgAHIAZQBxAHUAZQBzAHQAZQBkACwAIABzAGkAZwBuAHMAIABkAGkAZgBmAGUAcgAsACAAYQBuAGQAIAByAGUAbQBhAGkAbgBkAGUAcgAgAGkAcwAgAG4AbwBuAC0AegBlAHIAbwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQBlAGQAcwBfAGMAbwByAHIAZQBjAHQAaQBvAG4ALAAgAEEATgBEACgAaQBzAF8AZgBsAG8AbwByACwAIABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAbQBlAHIAZwBlAGQAXwByACAAPAA+ACAAXAAiADAAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcQAsACAASQBGACgAbgBlAGUAZABzAF8AYwBvAHIAcgBlAGMAdABpAG8AbgAsACAAUwB1AGIAKAB0AHIAdQBuAGMAXwBxACwAIABcACIAMQBcACIAKQAsACAAdAByAHUAbgBjAF8AcQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwByACwAIABJAEYAKABuAGUAZQBkAHMAXwBjAG8AcgByAGUAYwB0AGkAbwBuACwAIABBAGQAZAAoAHQAcgB1AG4AYwBfAHIALAAgAG4AbwByAG0AXwBiACkALAAgAHQAcgB1AG4AYwBfAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAGYAaQBuAGEAbABfAHEALAAgAGYAaQBuAGEAbABfAHIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAARABpAHYAaQBkAGUAcwAgAHQAaABlACAAZgBpAHIAcwB0ACAAQgBpAGcASQBuAHQAIABiAHkAIAB0AGgAZQAgAHMAZQBjAG8AbgBkACAAKABBACAALwAgAEIAKQAuACAAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAGQAaQB2AGkAZABlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAHUAcwBlAF8AZgBsAG8AbwByAF0AIABPAHAAdABpAG8AbgBhAGwAIABiAG8AbwBsAGUAYQBuAC4AIABUAFIAVQBFACAAZgBvAHIAIABQAHkAdABoAG8AbgAtAHMAdAB5AGwAZQAgAEYAbABvAG8AcgAgAGQAaQB2AGkAcwBpAG8AbgAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAARgBBAEwAUwBFAC4AXABuACAAKgAvAFwAbgBEAGkAdgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABiAGkAZwBfAGkAbgB0AF8AYgAsACAAWwB1AHMAZQBfAGYAbABvAG8AcgBdACwAXABuACAAIAAgACAASQBOAEQARQBYACgARABpAHYATQBvAGQAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALAAgAHUAcwBlAF8AZgBsAG8AbwByACkALAAgADEALAAgADEAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEMAbwBtAHAAdQB0AGUAcwAgAHQAaABlACAAcgBlAG0AYQBpAG4AZABlAHIAIABvAGYAIABBACAALwAgAEIALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAdQBzAGUAXwBmAGwAbwBvAHIAXQAgAE8AcAB0AGkAbwBuAGEAbAAgAGIAbwBvAGwAZQBhAG4ALgAgAFQAUgBVAEUAIABmAG8AcgAgAFAAeQB0AGgAbwBuAC0AcwB0AHkAbABlACAATQBvAGQAdQBsAG8ALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAEYAQQBMAFMARQAuAFwAbgAgACoALwBcAG4ATQBvAGQAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALAAgAFsAdQBzAGUAXwBmAGwAbwBvAHIAXQAsAFwAbgAgACAAIAAgAEkATgBEAEUAWAAoAEQAaQB2AE0AbwBkACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAIAB1AHMAZQBfAGYAbABvAG8AcgApACwAIAAyACwAIAAxACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGEAaQBzAGUAcwAgAGEAIABCAGkAZwBJAG4AdAAgAGIAYQBzAGUAIAB0AG8AIAB0AGgAZQAgAHAAbwB3AGUAcgAgAG8AZgAgAGEAIABCAGkAZwBJAG4AdAAgAGUAeABwAG8AbgBlAG4AdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAYQBzAGUAIABUAGgAZQAgAGIAYQBzAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAZQB4AHAAbwBuAGUAbgB0ACAAVABoAGUAIABlAHgAcABvAG4AZQBuAHQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBQAG8AdwAgAD0AIABMAEEATQBCAEQAQQAoAGIAYQBzAGUALAAgAGUAeABwAG8AbgBlAG4AdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgBhAHMAZQAsACAATgBvAHIAbQAoAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGUAeABwACwAIABOAG8AcgBtACgAZQB4AHAAbwBuAGUAbgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBiAGEAcwBlACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYgBhAHMAZQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AZQB4AHAALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBlAHgAcAApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAYQBiAHMAXwBiAGEAcwBlACwAIABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAYQBiAHMAXwBlAHgAcAAsACAAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBlAHgAcAApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AZQB4AHAAXwBlAHYAZQBuACwAIABJAFMARQBWAEUATgAoAFYAQQBMAFUARQAoAFIASQBHAEgAVAAoAG4AbwByAG0AXwBlAHgAcAAsACAAMQApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcwBpAGcAbgAsACAASQBGACgAcwBpAGcAbgBfAGIAYQBzAGUAIAA9ACAALQAxACwAIABJAEYAKABpAHMAXwBlAHgAcABfAGUAdgBlAG4ALAAgADEALAAgAC0AMQApACwAIABzAGkAZwBuAF8AYgBhAHMAZQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAASABhAG4AZABsAGUAIABtAGEAdABoAGUAbQBhAHQAaQBjAGEAbAAgAGIAbwB1AG4AZABhAHIAaQBlAHMAIABhAG4AZAAgAGIAYQBzAGUAIABsAGkAbQBpAHQAcwBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGEAYgBzAF8AYgBhAHMAZQAgAD0AIABcACIAMABcACIALAAgAEkARgAoAG4AbwByAG0AXwBlAHgAcAAgAD0AIABcACIAMABcACIALAAgACMATgBVAE0AIQAsACAAXAAiADAAXAAiACkALAAgAC8ALwAgADAAXgAwACAAaQBzACAAdQBuAGQAZQBmAGkAbgBlAGQAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABhAGIAcwBfAGIAYQBzAGUAIAA9ACAAXAAiADEAXAAiACwAIABJAEYAKABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAXAAiAC0AMQBcACIALAAgAFwAIgAxAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AZQB4AHAAIAA9ACAALQAxACwAIABcACIAMABcACIALAAgAC8ALwAgAEkAbgB0AGUAZwBlAHIAIAB0AHIAdQBuAGMAYQB0AGkAbwBuADoAIABuAGUAZwBhAHQAaQB2AGUAIABlAHgAcABvAG4AZQBuAHQAcwAgAHkAaQBlAGwAZAAgADAAIABmAG8AcgAgAGIAYQBzAGUAcwAgAD4APQAgADIAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAG8AcgBtAF8AZQB4AHAAIAA9ACAAXAAiADAAXAAiACwAIABcACIAMQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAcwB1AGwAdABzACAAZgByAG8AbQAgAGUAeABwAG8AbgBlAG4AdABzACAAZwByAGUAYQB0AGUAcgAgAHQAaABhAG4AIAA2ACAAZABpAGcAaQB0AHMAIABjAGEAbgBuAG8AdAAgAGIAZQAgAGQAaQBzAHAAbABhAHkAZQBkAC4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAEUATgAoAG4AbwByAG0AXwBlAHgAcAApACAAPgAgADYALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AdQBtAF8AZQB4AHAALAAgAFYAQQBMAFUARQAoAG4AbwByAG0AXwBlAHgAcAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQQBwAHAAcgBvAHgAaQBtAGEAdABlACAAdABoAGUAIABmAGkAbgBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgAgAGMAbwB1AG4AdAA6ACAAQgAgACoAIABMAG8AZwAxADAAKABBACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYgBhAHMAZQBfAGwAbwBnADEAMAAsACAATABPAEcAMQAwACgAVgBBAEwAVQBFACgATABFAEYAVAAoAGEAYgBzAF8AYgBhAHMAZQAsACAAMQA0ACkAKQApACAAKwAgAE0AQQBYACgAMAAsACAATABFAE4AKABhAGIAcwBfAGIAYQBzAGUAKQAgAC0AIAAxADQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAcABwAHIAbwB4AF8AZABpAGcAaQB0AHMALAAgAG4AdQBtAF8AZQB4AHAAIAAqACAAYgBhAHMAZQBfAGwAbwBnADEAMAAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABhAHAAcAByAG8AeABfAGQAaQBnAGkAdABzACAAPgAgADMAMgA3ADYANgAsACAAIwBOAFUATQAhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIATQBVAEwAXAAiACwAIABhAHAAcAByAG8AeABfAGQAaQBnAGkAdABzACAALwAgADIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBiAGEAcwBlACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABhAGIAcwBfAGIAYQBzAGUALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFAAbwB3ACgAbABpAG0AYgBzAF8AYgBhAHMAZQAsACAAbgBvAHIAbQBfAGUAeABwACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBlAHIAZwBlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAXAAiAC0AXAAiACAAJgAgAG0AZQByAGcAZQBkACwAIABtAGUAcgBnAGUAZAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApACkAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABDAGEAbABjAHUAbABhAHQAZQBzACAAdABoAGUAIABpAG4AdABlAGcAZQByACAAcwBxAHUAYQByAGUAIAByAG8AbwB0ACAAKABmAGwAbwBvAHIAKQAgAG8AZgAgAGEAIABCAGkAZwBJAG4AdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAIABUAGgAZQAgAHIAYQBkAGkAYwBhAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAFMAcQByAHQAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBuACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AbgAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAG4AKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAHMAaQBnAG4AXwBuACAAPQAgAC0AMQAsACAAIwBOAFUATQAhACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAG8AcgBtAF8AbgAgAD0AIABcACIAMABcACIALAAgAFwAIgAwAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgBvAHIAbQBfAG4AIAA9ACAAXAAiADEAXAAiACwAIABcACIAMQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAG4ALAAgAEwARQBOACgAbgBvAHIAbQBfAG4AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAYQBrAGUAXwBkAGkAZwBpAHQAcwAsACAASQBGACgAbABlAG4AXwBuACAAPAA9ACAAMQA0ACwAIABsAGUAbgBfAG4ALAAgAEkARgAoAEkAUwBFAFYARQBOACgAbABlAG4AXwBuACkALAAgADEANAAsACAAMQAzACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHYAXwBzAHQAcgAsACAATABFAEYAVAAoAG4AbwByAG0AXwBuACwAIAB0AGEAawBlAF8AZABpAGcAaQB0AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHYAXwBuAHUAbQAsACAAVgBBAEwAVQBFACgAdgBfAHMAdAByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB6AGUAcgBvAF8AYwBvAHUAbgB0ACwAIAAoAGwAZQBuAF8AbgAgAC0AIAB0AGEAawBlAF8AZABpAGcAaQB0AHMAKQAgAC8AIAAyACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAZQBlAGQAXwBwAHIAZQBmAGkAeAAsACAAVABFAFgAVAAoAFIATwBVAE4ARABVAFAAKABTAFEAUgBUACgAdgBfAG4AdQBtACkALAAgADAAKQAgACsAIAAxACwAIABcACIAMABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAZQBlAGQAXwBzAHQAcgAsACAAcwBlAGUAZABfAHAAcgBlAGYAaQB4ACAAJgAgAFIARQBQAFQAKABcACIAMABcACIALAAgAHoAZQByAG8AXwBjAG8AdQBuAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGMAYQBsAGUAcwAgAGsAIABiAHkAIAB0AGgAZQAgAG0AYQB4AGkAbQB1AG0AIABvAHYAZQByAGwAYQBwACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAE0AVQBMAFwAIgAsACAAbABlAG4AXwBuACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBuACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABuAG8AcgBtAF8AbgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AcwBlAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAcwBlAGUAZABfAHMAdAByACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAcQByAHQAKABsAGkAbQBiAHMAXwBuACwAIABsAGkAbQBiAHMAXwBzAGUAZQBkACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAQwBvAG0AcAB1AHQAZQBzACAAdABoAGUAIABmAGEAYwB0AG8AcgBpAGEAbAAgAG8AZgAgAGEAIABCAGkAZwBJAG4AdAAgACgAbgAhACkALgBcAG4AIAAqACAAVQB0AGkAbABpAHoAZQBzACAATABlAGcAZQBuAGQAcgBlACcAcwAgAGYAbwByAG0AdQBsAGEAIABhAG4AZAAgAGwAbwBnAGEAcgBpAHQAaABtAGkAYwAgAHQAcgBlAGUAIABtAHUAbAB0AGkAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABiAHkAcABhAHMAcwAgAHMAdABhAGMAawAvAG0AZQBtAG8AcgB5ACAAbABpAG0AaQB0AHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AIABNAGEAeABpAG0AdQBtACAAcwB1AHAAcABvAHIAdABlAGQAIABpAG4AcAB1AHQAIABpAHMAIAA5ADIANwAzAC4AXABuACAAKgAvAFwAbgBGAGEAYwB0ACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AbgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBpAGcAbgBfAG4ALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBuACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AbgAgAD0AIAAtADEALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgBvAHIAbQBfAG4AIAA9ACAAXAAiADAAXAAiACwAIABcACIAMQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AbwByAG0AXwBuACAAPQAgAFwAIgAxAFwAIgAsACAAXAAiADEAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABGAGkAcgBlAHcAYQBsAGwAIAAxADoAIABUAHIAYQBwACAAbQBhAHMAcwBpAHYAZQAgAHMAdAByAGkAbgBnAHMAIABiAGUAZgBvAHIAZQAgAHQAaABlAHkAIABoAGkAdAAgAFYAQQBMAFUARQAoACkAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAEUATgAoAG4AbwByAG0AXwBuACkAIAA+ACAANAAsACAAIwBOAFUATQAhACwAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEYAaQByAGUAdwBhAGwAbAAgADIAOgAgAFQAcgBhAHAAIABtAGEAdABoAGUAbQBhAHQAaQBjAGEAbAAgAGMAZQBpAGwAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABWAEEATABVAEUAKABuAG8AcgBtAF8AbgApACAAPgAgADkAMgA3ADMALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AXwB2AGEAbAAsACAAVgBBAEwAVQBFACgAbgBvAHIAbQBfAG4AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAcgBpAG0AZQBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBOAGEAdABpAHYAZQBQAHIAaQBtAGUAcwAoAG4AXwB2AGEAbAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZQB4AHAAbwBuAGUAbgB0AHMALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE4AYQB0AGkAdgBlAEwAZQBnAGUAbgBkAHIAZQAoAG4AXwB2AGEAbAAsACAAcAByAGkAbQBlAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAE0AYQBwACAAbwB2AGUAcgAgAHAAcgBpAG0AZQBzACAAYQBuAGQAIABlAHgAcABvAG4AZQBuAHQAcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAcABeAGUALgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAbwBlAHIAYwBlACAAbgBhAHQAaQB2AGUAIABpAG4AdABlAGcAZQByAHMAIABiAGEAYwBrACAAdABvACAAcwB0AHIAaQBuAGcAcwAgAGYAbwByACAAdABoAGUAIABQAG8AdwAgAGIAbwB1AG4AZABhAHIAeQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAcgBpAG0AZQBfAHAAbwB3AGUAcgBzACwAIABNAEEAUAAoAHAAcgBpAG0AZQBzACwAIABlAHgAcABvAG4AZQBuAHQAcwAsACAATABBAE0AQgBEAEEAKABwACwAIABlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAbwB3ACgAcAAgACYAIABcACIAXAAiACwAIABlACAAJgAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBUAGUAeAB0AFQAcgBlAGUAUAByAG8AZAAoAHAAcgBpAG0AZQBfAHAAbwB3AGUAcgBzACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAKQApACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAuAEsAbgB1AHQAaABEAGkAdgBpAHMAaQBvAG4AIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgBpAHMAaQBvAG4AIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ARABpAHYAaQBzAGkAbwBuAEEAbABnAG8AcgBpAHQAaABtAHMAIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ARABpAHYAaQBzAGkAbwBuAEEAbABnAG8AcgBpAHQAaABtAEMAbwBtAHAAYQByAGkAcwBvAG4AIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4ARABpAHYAaQBzAGkAbwBuAEIAZQBuAGMAaABtAGEAcgBrAEMAYQBzAGUAcwAiACwAIgB0AGUAcwB0AF8AQgBpAGcASQBuAHQALgBBAHMAeQBtAG0AZQB0AHIAaQBjAEEAQgBHAHIAaQBkACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEMAYQByAHIAeQAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEMAbwBtAHAAYQByAGUAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBBAGQAZAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAdQBiACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQBhAHQAcgBpAHgAUwB1AG0AIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AQQBkAGQAUwB1AGIAUgBvAHUAdABlAHIAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBGAGkAbgBkAFEAdQBvAHQAaQBlAG4AdABMAGkAbQBiACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEsAbgB1AHQAaABEAGkAdgAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBEAGkAdgBSAG8AdQB0AGUAcgAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAFMAZQBlAGQAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBSAGUAYwBpAHAAcgBvAGMAYQBsACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4ARABpAHYAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBQAG8AdwAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAcQByAHQAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBhAHQAaQB2AGUAUAByAGkAbQBlAHMAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBhAHQAaQB2AGUATABlAGcAZQBuAGQAcgBlACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAVABlAHgAdABNAHUAbAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBUAGUAeAB0AFQAcgBlAGUAUAByAG8AZAAiACwAIgBCAGkAZwBJAG4AdAAuAE4AbwByAG0AIgAsACIAQgBpAGcASQBuAHQALgBTAGkAZwBuACIALAAiAEIAaQBnAEkAbgB0AC4ASQBzAFoAZQByAG8AIgAsACIAQgBpAGcASQBuAHQALgBJAHMATgBlAGcAIgAsACIAQgBpAGcASQBuAHQALgBJAHMARQB2AGUAbgAiACwAIgBCAGkAZwBJAG4AdAAuAEkAcwBPAGQAZAAiACwAIgBCAGkAZwBJAG4AdAAuAEEAYgBzACIALAAiAEIAaQBnAEkAbgB0AC4AQwBvAG0AcABhAHIAZQAiACwAIgBCAGkAZwBJAG4AdAAuAEEAZABkACIALAAiAEIAaQBnAEkAbgB0AC4AUwB1AGIAIgAsACIAQgBpAGcASQBuAHQALgBTAHUAbQAiACwAIgBCAGkAZwBJAG4AdAAuAE0AdQBsACIALAAiAEIAaQBnAEkAbgB0AC4AUgBhAG4AZABCAGkAZwBJAG4AdABBAHIAcgBhAHkAIgAsACIAQgBpAGcASQBuAHQALgBEAGkAdgBNAG8AZAAiACwAIgBCAGkAZwBJAG4AdAAuAEQAaQB2ACIALAAiAEIAaQBnAEkAbgB0AC4ATQBvAGQAIgAsACIAQgBpAGcASQBuAHQALgBQAG8AdwAiACwAIgBCAGkAZwBJAG4AdAAuAFMAcQByAHQAIgAsACIAQgBpAGcASQBuAHQALgBGAGEAYwB0ACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAFwAbgAvAC8AIABCAGkAZwAgAEkAbgB0AGUAZwBlAHIAIABBAHIAaQB0AGgAbQBlAHQAaQBjACAATABpAGIAcgBhAHIAeQAgAC8ALwBcAG4ALwAvACAAIAAgACAAIAAgACAAdABlAHMAdABfAEIAaQBnAEkAbgB0ACAATQBvAGQAdQBsAGUAIAAgACAAIAAgACAAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIAAgAFAAcgBpAHYAYQB0AGUAIABUAGUAcwB0AGkAbgBnACAAQQBQAEkAIAAgACAAIAAgACAALwAvAFwAbgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4AXABuAEsAbgB1AHQAaABEAGkAdgBpAHMAaQBvAG4APQBMAEEATQBCAEQAQQAoAGEALAAgAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2ACgAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYQAsACAAawApACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABiACwAIABrACkALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAEQAUgBPAFAAKABwAGEAYwBrAGUAZAAsACAASQBOAEQARQBYACgAcABhAGMAawBlAGQALAAgADEALAAgADEAKQAgACsAIAAxACkALAAgAGsAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAgAD0AIABMAEEATQBCAEQAQQAoAGEALAAgAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgAoAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAGEALAAgAGsAKQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAYgAsACAAawApACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABEAFIATwBQACgAcABhAGMAawBlAGQALAAgAEkATgBEAEUAWAAoAHAAYQBjAGsAZQBkACwAIAAxACwAIAAxACkAIAArACAAMQApACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAcwB0AHIAaQBuAGcAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAHMAdAByAGkAbgBnAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG0AbwBkAGUAIABcACIASwBOAFUAVABIAFwAIgAgAG8AcgAgAFwAIgBOAFIAXAAiAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGkAdABlAHIAcwAgAEkAbgBuAGUAcgAgAGwAbwBvAHAAIABjAG8AdQBuAHQAIAAoAHQAbwAgAGQAZQBmAGUAYQB0ACAAYwBoAHUAbgBrAHkAIABjAGwAbwBjAGsAIAByAGUAcwBvAGwAdQB0AGkAbwBuACkAXABuACAAKgAgAEAAcABhAHIAYQBtACAAcgBlAHAAZQBhAHQAcwAgAE8AdQB0AGUAcgAgAGwAbwBvAHAAIABjAG8AdQBuAHQAIAAoAHQAbwAgAGQAZQBmAGUAYQB0ACAATwBTAC8ARwBhAHIAYgBhAGcAZQAgAEMAbwBsAGwAZQBjAHQAaQBvAG4AIABuAG8AaQBzAGUAKQBcAG4AIAAqAC8AXABuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACAAPQAgAEwAQQBNAEIARABBACgAYQAsACAAYgAsACAAbQBvAGQAZQAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAE0AYQBwACAAdABoAGUAIABvAHUAdABlAHIAIAByAGUAcABlAGEAdABzACAAbABvAG8AcABcAG4AIAAgACAAIAAgACAAIAAgAGIAYQB0AGMAaABfAHQAaQBtAGUAcwAsACAATQBBAFAAKABTAEUAUQBVAEUATgBDAEUAKAByAGUAcABlAGEAdABzACkALAAgAEwAQQBNAEIARABBACgAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdAAsACAATgBPAFcAKAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATQBhAHAAIAB0AGgAZQAgAGkAbgBuAGUAcgAgAGUAeABlAGMAdQB0AGkAbwBuACAAbABvAG8AcABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAHUAbgAsACAASQBGACgAbQBvAGQAZQAgAD0AIABcACIASwBOAFUAVABIAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBQACgAUwBFAFEAVQBFAE4AQwBFACgAaQB0AGUAcgBzACkALAAgAEwAQQBNAEIARABBACgAaQAsACAASwBuAHUAdABoAEQAaQB2AGkAcwBpAG8AbgAoAGEALAAgAGIAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFAAKABTAEUAUQBVAEUATgBDAEUAKABpAHQAZQByAHMAKQAsACAATABBAE0AQgBEAEEAKABpACwAIABOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2AGkAcwBpAG8AbgAoAGEALAAgAGIAKQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEYAbwByAGMAZQAgAGUAdgBhAGwAdQBhAHQAaQBvAG4AIABiAGUAZgBvAHIAZQAgAHAAdQBsAGwAaQBuAGcAIABzAHQAbwBwACAAdABpAG0AZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAbwBwACwAIABOAE8AVwAoACkAIAArACAAKAAwACAAKgAgAEwARQBOACgASQBOAEQARQBYACgAcgB1AG4ALAAgADEALAAgADEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABUAG8AdABhAGwAIABiAGEAdABjAGgAIAB0AGkAbQBlACAAaQBuACAAbQBpAGwAbABpAHMAZQBjAG8AbgBkAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABzAHQAbwBwACAALQAgAHMAdABhAHIAdAApACAAKgAgADgANgA0ADAAMAAwADAAMABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAdABoAGUAIABjAGwAZQBhAG4AZQBzAHQAIAByAHUAbgAgAGEAbgBkACAAYQB2AGUAcgBhAGcAZQAgAGkAdAAgAGQAbwB3AG4AIAB0AG8AIABhACAAcwBpAG4AZwBsAGUAIABlAHgAZQBjAHUAdABpAG8AbgAgAHQAaQBtAGUAXABuACAAIAAgACAAIAAgACAAIABNAEkATgAoAGIAYQB0AGMAaABfAHQAaQBtAGUAcwApACAALwAgAGkAdABlAHIAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAARQB4AGUAYwB1AHQAZQBzACAAYQAgAHMAdAByAGkAYwB0AGwAeQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABiAGUAbgBjAGgAbQBhAHIAawAgAHMAdQBpAHQAZQAgAHQAbwAgAGEAdgBvAGkAZAAgAG0AdQBsAHQAaQAtAHQAaAByAGUAYQBkAGkAbgBnACAAYwBvAG4AdABhAG0AaQBuAGEAdABpAG8AbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHQAZQBzAHQAXwBjAGEAcwBlAHMAIABBAG4AIABOACAAeAAgADIAIABhAHIAcgBhAHkAIABvAGYAIAB0AGUAcwB0ACAAbABlAG4AZwB0AGgAcwA6ACAAWwBMAGUAbgBnAHQAaABfAEEALAAgAEwAZQBuAGcAdABoAF8AQgBdAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGkAdABlAHIAcwAgAE4AdQBtAGIAZQByACAAbwBmACAAaQB0AGUAcgBhAHQAaQBvAG4AcwAgAHAAZQByACAAYgBlAG4AYwBoAG0AYQByAGsAIAB0AG8AIABzAG0AbwBvAHQAaAAgAE4ATwBXACgAKQAgAHIAZQBzAG8AbAB1AHQAaQBvAG4ALgBcAG4AIAAqAC8AXABuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBDAG8AbQBwAGEAcgBpAHMAbwBuACAAPQAgAEwAQQBNAEIARABBACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwB0AGUAcwB0AHMALAAgAFIATwBXAFMAKAB0AGUAcwB0AF8AYwBhAHMAZQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAASQBuAGkAdABpAGEAbAAgAHMAdABhAHQAZQA6ACAARABhAHQAYQAgAGgAZQBhAGQAZQByAHMAIABmAG8AcgAgAEMAUwBWACAAZQB4AHAAbwByAHQAXABuACAAIAAgACAAIAAgACAAIABpAG4AaQB0AGkAYQBsACwAIAB7AFwAIgBMAGUAbgBfAEEAXAAiACwAIABcACIATABlAG4AXwBCAFwAIgAsACAAXAAiAEsAbgB1AHQAaABfAG0AcwBcACIALAAgAFwAIgBOAFIAXwBtAHMAXAAiAH0ALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsACwAIABTAEUAUQBVAEUATgBDAEUAKABuAF8AdABlAHMAdABzACkALAAgAEwAQQBNAEIARABBACgAYQBjAGMALAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAEkATgBEAEUAWAAoAHQAZQBzAHQAXwBjAGEAcwBlAHMALAAgAGkALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAASQBOAEQARQBYACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBrAGkAcAAgAEQAaQB2AGkAcwBvAHIAIAA+ACAARABpAHYAaQBkAGUAbgBkABQgaQB0ACcAcwAgAG4AZQB2AGUAcgAgAGEAbgAgAGkAbgB0AGUAZwBlAHIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbABlAG4AXwBiACAAPgAgAGwAZQBuAF8AYQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAYwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARwBlAG4AZQByAGEAdABlACAAZQB4AGEAYwB0AC0AbABlAG4AZwB0AGgAIAB0AGUAcwB0ACAAcwB0AHIAaQBuAGcAcwAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AHIAXwBhACwAIABSAEUAUABUACgAXAAiADkAXAAiACwAIABsAGUAbgBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAcgBfAGIALAAgAEkARgAoAGwAZQBuAF8AYgAgAD0AIAAxACwAIABcACIANwBcACIALAAgAFwAIgA3AFwAIgAgACYAIABSAEUAUABUACgAXAAiADMAXAAiACwAIABsAGUAbgBfAGIAIAAtACAAMQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeABlAGMAdQB0AGUAIABiAGUAbgBjAGgAbQBhAHIAawBzACAAcwB0AHIAaQBjAHQAbAB5ACAAbwBuAGUAIABhAGYAdABlAHIAIAB0AGgAZQAgAG8AdABoAGUAcgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABpAG0AZQBfAGsALAAgAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACgAcwB0AHIAXwBhACwAIABzAHQAcgBfAGIALAAgAFwAIgBLAE4AVQBUAEgAXAAiACwAIABpAHQAZQByAHMALAAgAHIAZQBwAGUAYQB0AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGkAbQBlAF8AbgByACwAIABEAGkAdgBpAHMAaQBvAG4AQQBsAGcAbwByAGkAdABoAG0AcwAoAHMAdAByAF8AYQAsACAAcwB0AHIAXwBiACwAIABcACIATgBSAFwAIgAsACAAaQB0AGUAcgBzACwAIAByAGUAcABlAGEAdABzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAcABwAGUAbgBkACAAdABoAGUAIAByAGUAcwB1AGwAdABzAC4AIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAGEAbABsAG8AYwBhAHQAaQBvAG4AIABkAGUAbABhAHkAIABvAGMAYwB1AHIAcwAgAGgAZQByAGUALAAgAHMAYQBmAGUAbAB5ACAAbwB1AHQAcwBpAGQAZQAgAHQAaABlACAAdABpAG0AZQBkACAAdwBpAG4AZABvAHcALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABhAGMAYwAsACAASABTAFQAQQBDAEsAKABsAGUAbgBfAGEALAAgAGwAZQBuAF8AYgAsACAAdABpAG0AZQBfAGsALAAgAHQAaQBtAGUAXwBuAHIAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgADIALQBjAG8AbAB1AG0AbgAgAGEAcgByAGEAeQAgAG8AZgAgAGUAdgBlAHIAeQAgAGMAbwBtAGIAaQBuAGEAdABpAG8AbgAgAG8AZgAgAGwAZQBuAGcAdABoAHMAXABuAEQAaQB2AGkAcwBpAG8AbgBCAGUAbgBjAGgAbQBhAHIAawBDAGEAcwBlAHMAIAA9ACAATABBAE0AQgBEAEEAKABzAHQAYQByAHQAXwBsAGUAbgAsACAAbQBhAHgAXwBsAGUAbgAsACAAcwB0AGUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQAsACAAUwBFAFEAVQBFAE4AQwBFACgAKABtAGEAeABfAGwAZQBuACAALQAgAHMAdABhAHIAdABfAGwAZQBuACkAIAAvACAAcwB0AGUAcAAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBsAGUAbgAsACAAcwB0AGUAcAApACwAXABuACAAIAAgACAAIAAgACAAIABuACwAIABSAE8AVwBTACgAcwBlAHEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAcgB0AGUAcwBpAGEAbgAgAEoAbwBpAG4AXABuACAAIAAgACAAIAAgACAAIABjAG8AbABfAGEALAAgAFQATwBDAE8ATAAoAEkARgAoAFMARQBRAFUARQBOAEMARQAoADEALAAgAG4AKQAsACAAcwBlAHEAKQApACwAXABuACAAIAAgACAAIAAgACAAIABjAG8AbABfAGIALAAgAFQATwBDAE8ATAAoAEkARgAoAFMARQBRAFUARQBOAEMARQAoAG4ALAAgADEAKQAsACAAVABPAFIATwBXACgAcwBlAHEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABjAG8AbABfAGEALAAgAGMAbwBsAF8AYgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAEcAZQBuAGUAcgBhAHQAZQBzACAAYQAgAEMAYQByAHQAZQBzAGkAYQBuACAAZwByAGkAZAAgAGYAcgBvAG0AIAB0AHcAbwAgAGkAbgBkAGUAcABlAG4AZABlAG4AdAAgAHMAZQBxAHUAZQBuAGMAZQBzAFwAbgBBAHMAeQBtAG0AZQB0AHIAaQBjAEEAQgBHAHIAaQBkACAAPQAgAEwAQQBNAEIARABBACgAcwB0AGEAcgB0AF8AYQAsACAAbQBhAHgAXwBhACwAIABzAHQAZQBwAF8AYQAsACAAcwB0AGEAcgB0AF8AYgAsACAAbQBhAHgAXwBiACwAIABzAHQAZQBwAF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGEALAAgAFMARQBRAFUARQBOAEMARQAoACgAbQBhAHgAXwBhACAALQAgAHMAdABhAHIAdABfAGEAKQAgAC8AIABzAHQAZQBwAF8AYQAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBhACwAIABzAHQAZQBwAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGIALAAgAFMARQBRAFUARQBOAEMARQAoACgAbQBhAHgAXwBiACAALQAgAHMAdABhAHIAdABfAGIAKQAgAC8AIABzAHQAZQBwAF8AYgAgACsAIAAxACwAIAAxACwAIABzAHQAYQByAHQAXwBiACwAIABzAHQAZQBwAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwBhACwAIABSAE8AVwBTACgAcwBlAHEAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4AXwBiACwAIABSAE8AVwBTACgAcwBlAHEAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAATwByAHQAaABvAGcAbwBuAGEAbAAgAGIAcgBvAGEAZABjAGEAcwB0ACAAdQBzAGkAbgBnACAAaQBuAGQAZQBwAGUAbgBkAGUAbgB0ACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIAAgACAAIAAgAGMAbwBsAF8AYQAsACAAVABPAEMATwBMACgASQBGACgAUwBFAFEAVQBFAE4AQwBFACgAMQAsACAAbgBfAGIAKQAsACAAcwBlAHEAXwBhACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBvAGwAXwBiACwAIABUAE8AQwBPAEwAKABJAEYAKABTAEUAUQBVAEUATgBDAEUAKABuAF8AYQApACwAIABUAE8AUgBPAFcAKABzAGUAcQBfAGIAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASABTAFQAQQBDAEsAKABjAG8AbABfAGEALAAgAGMAbwBsAF8AYgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEYAYQBjAHQAbwByAGkAYQBsAEEAbABnAG8AcgBpAHQAaABtAHMAIAA9ACAATABBAE0AQgBEAEEAKABpAG4AcAB1AHQALAAgAG0AbwBkAGUALAAgAGkAdABlAHIAcwAsACAAcgBlAHAAZQBhAHQAcwAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABNAGEAcAAgAHQAaABlACAAbwB1AHQAZQByACAAcgBlAHAAZQBhAHQAcwAgAGwAbwBvAHAAXABuACAAIAAgACAAIAAgACAAIABiAGEAdABjAGgAXwB0AGkAbQBlAHMALAAgAE0AQQBQACgAUwBFAFEAVQBFAE4AQwBFACgAcgBlAHAAZQBhAHQAcwApACwAIABMAEEATQBCAEQAQQAoAHIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQALAAgAE4ATwBXACgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAE0AYQBwACAAdABoAGUAIABpAG4AbgBlAHIAIABlAHgAZQBjAHUAdABpAG8AbgAgAGwAbwBvAHAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgB1AG4ALAAgAEkARgAoAG0AbwBkAGUAIAA9ACAAXAAiAEwAZQBnAGUAbgBkAHIAZQBcACIALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAUAAoAFMARQBRAFUARQBOAEMARQAoAGkAdABlAHIAcwApACwAIABMAEEATQBCAEQAQQAoAGkALAAgAEIAaQBnAEkAbgB0AC4ARgBhAGMAdAAoAGkAbgBwAHUAdAApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAUAAoAFMARQBRAFUARQBOAEMARQAoAGkAdABlAHIAcwApACwAIABMAEEATQBCAEQAQQAoAGkALAAgAEIAaQBnAEkAbgB0AC4ARgBhAGMAdABTAHcAaQBuAGcAKABpAG4AcAB1AHQAKQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEYAbwByAGMAZQAgAGUAdgBhAGwAdQBhAHQAaQBvAG4AIABiAGUAZgBvAHIAZQAgAHAAdQBsAGwAaQBuAGcAIABzAHQAbwBwACAAdABpAG0AZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHQAbwBwACwAIABOAE8AVwAoACkAIAArACAAKAAwACAAKgAgAEwARQBOACgASQBOAEQARQBYACgAcgB1AG4ALAAgADEALAAgADEAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABUAG8AdABhAGwAIABiAGEAdABjAGgAIAB0AGkAbQBlACAAaQBuACAAbQBpAGwAbABpAHMAZQBjAG8AbgBkAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABzAHQAbwBwACAALQAgAHMAdABhAHIAdAApACAAKgAgADgANgA0ADAAMAAwADAAMABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAdABoAGUAIABjAGwAZQBhAG4AZQBzAHQAIAByAHUAbgAgAGEAbgBkACAAYQB2AGUAcgBhAGcAZQAgAGkAdAAgAGQAbwB3AG4AIAB0AG8AIABhACAAcwBpAG4AZwBsAGUAIABlAHgAZQBjAHUAdABpAG8AbgAgAHQAaQBtAGUAXABuACAAIAAgACAAIAAgACAAIABNAEkATgAoAGIAYQB0AGMAaABfAHQAaQBtAGUAcwApACAALwAgAGkAdABlAHIAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAARQB4AGUAYwB1AHQAZQBzACAAYQAgAHMAdAByAGkAYwB0AGwAeQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABiAGUAbgBjAGgAbQBhAHIAawAgAHMAdQBpAHQAZQAgAHQAbwAgAGEAdgBvAGkAZAAgAG0AdQBsAHQAaQAtAHQAaAByAGUAYQBkAGkAbgBnACAAYwBvAG4AdABhAG0AaQBuAGEAdABpAG8AbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHQAZQBzAHQAXwBjAGEAcwBlAHMAIABBAG4AIABOACAAeAAgADEAIABhAHIAcgBhAHkAIABvAGYAIAB0AGUAcwB0ACAAaQBuAHAAdQB0AHMAXABuACAAKgAgAEAAcABhAHIAYQBtACAAaQB0AGUAcgBzACAATgB1AG0AYgBlAHIAIABvAGYAIABpAHQAZQByAGEAdABpAG8AbgBzACAAcABlAHIAIABzAGEAbQBwAGwAZQAgAHQAbwAgAHMAbQBvAG8AdABoACAATgBPAFcAKAApACAAcgBlAHMAbwBsAHUAdABpAG8AbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHIAZQBwAGUAYQB0AHMAIABOAHUAbQBiAGUAcgAgAG8AZgAgAGkAdABlAHIAYQB0AGkAbwBuAHMAIABwAGUAcgAgAGIAZQBuAGMAaABtAGEAcgBrACAAdABvACAAcwBtAG8AbwB0AGgAIABPAFMAIABhAG4AZAAgAGIAYQBjAGsAZwByAG8AdQBuAGQAIABuAG8AaQBzAGUALgBcAG4AIAAqAC8AXABuAEYAYQBjAHQAbwByAGkAYQBsAEMAbwBtAHAAYQByAGkAcwBvAG4AIAA9ACAATABBAE0AQgBEAEEAKAB0AGUAcwB0AF8AYwBhAHMAZQBzACwAIABpAHQAZQByAHMALAAgAHIAZQBwAGUAYQB0AHMALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBfAHQAZQBzAHQAcwAsACAAUgBPAFcAUwAoAHQAZQBzAHQAXwBjAGEAcwBlAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABJAG4AaQB0AGkAYQBsACAAcwB0AGEAdABlADoAIABEAGEAdABhACAAaABlAGEAZABlAHIAcwAgAGYAbwByACAAQwBTAFYAIABlAHgAcABvAHIAdABcAG4AIAAgACAAIAAgACAAIAAgAGkAbgBpAHQAaQBhAGwALAAgAHsAXAAiAE4AXAAiACwAIABcACIATABlAGcAZQBuAGQAcgBlAFwAIgAsACAAXAAiAFMAdwBpAG4AZwBcACIAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABSAEUARABVAEMARQAoAGkAbgBpAHQAaQBhAGwALAAgAFMARQBRAFUARQBOAEMARQAoAG4AXwB0AGUAcwB0AHMAKQAsACAATABBAE0AQgBEAEEAKABhAGMAYwAsACAAaQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAbgBwAHUAdAAsACAASQBOAEQARQBYACgAdABlAHMAdABfAGMAYQBzAGUAcwAsACAAaQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARQB4AGUAYwB1AHQAZQAgAGIAZQBuAGMAaABtAGEAcgBrAHMAIABzAHQAcgBpAGMAdABsAHkAIABvAG4AZQAgAGEAZgB0AGUAcgAgAHQAaABlACAAbwB0AGgAZQByAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAaQBtAGUAXwBsAGUAZwBlAG4AZAByAGUALAAgAEYAYQBjAHQAbwByAGkAYQBsAEEAbABnAG8AcgBpAHQAaABtAHMAKABpAG4AcAB1AHQALAAgAFwAIgBMAGUAZwBlAG4AZAByAGUAXAAiACwAIABpAHQAZQByAHMALAAgAHIAZQBwAGUAYQB0AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAaQBtAGUAXwBzAHcAaQBuAGcALAAgAEYAYQBjAHQAbwByAGkAYQBsAEEAbABnAG8AcgBpAHQAaABtAHMAKABpAG4AcAB1AHQALAAgAFwAIgBTAHcAaQBuAGcAXAAiACwAIABpAHQAZQByAHMALAAgAHIAZQBwAGUAYQB0AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAcABwAGUAbgBkACAAdABoAGUAIAByAGUAcwB1AGwAdABzAC4AIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAYQBsAGwAbwBjAGEAdABpAG8AbgAgAGQAZQBsAGEAeQAgAG8AYwBjAHUAcgBzACAAaABlAHIAZQAsACAAcwBhAGYAZQBsAHkAIABvAHUAdABzAGkAZABlACAAdABoAGUAIAB0AGkAbQBlAGQAIAB3AGkAbgBkAG8AdwAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAYQBjAGMALAAgAEgAUwBUAEEAQwBLACgAaQBuAHAAdQB0ACwAIAB0AGkAbQBlAF8AbABlAGcAZQBuAGQAcgBlACwAIAB0AGkAbQBlAF8AcwB3AGkAbgBnACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBjAG8AcgBlAF8AQgBpAGcASQBuAHQAIgAsACIAdABlAHgAdAAiADoAIgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4ALwAvACAAQgBpAGcAIABJAG4AdABlAGcAZQByACAAQQByAGkAdABoAG0AZQB0AGkAYwAgAEwAaQBiAHIAYQByAHkAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQAIABNAG8AZAB1AGwAZQAgACAAIAAgACAAIAAgACAALwAvAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIABQAHIAaQB2AGEAdABlACAAQQBQAEkAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwBcAG4ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8AXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEMAbwBtAHAAdQB0AGUAcwAgAHQAaABlACAAbQBhAHgAaQBtAHUAbQAgAHMAYQBmAGUAIABiAGEAcwBlAC0AMQAwACAAbABpAG0AYgAgAHMAaQB6AGUAIAAoAGsAKQAgAHQAbwAgAGEAdgBvAGkAZAAgAEkARQBFAEUALQA3ADUANAAgAHAAcgBlAGMAaQBzAGkAbwBuACAAbABvAHMAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG8AcABlAHIAYQB0AGkAbwBuADoAIABcACIAQQBEAEQAXAAiACwAIABcACIATQBVAEwAXAAiACwAIABvAHIAIABcACIARABJAFYAXAAiAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAWwBtAGEAeABfAGkAdABlAG0AcwBdACAAQQBEAEQAOgAgAG4AdQBtAGIAZQByACAAbwBmACAAbwBwAGUAcgBhAG4AZABzAC4AIABNAFUATAA6ACAAcwBoAG8AcgB0AGUAcwB0ACAAcwB0AHIAaQBuAGcAIABkAGkAZwBpAHQAcwAgAGMAbwB1AG4AdAAuAFwAbgAgACoALwBcAG4AUwBhAGYAZQBLACAAPQAgAEwAQQBNAEIARABBACgAbwBwAGUAcgBhAHQAaQBvAG4ALAAgAFsAbQBhAHgAXwBpAHQAZQBtAHMAXQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABpAHQAZQBtAHMALAAgAEkARgAoAE8AUgAoAG0AYQB4AF8AaQB0AGUAbQBzACAAPQAgAFwAIgBcACIALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAbQBhAHgAXwBpAHQAZQBtAHMAKQApACwAIAAyACwAIABNAEEAWAAoADIALAAgAG0AYQB4AF8AaQB0AGUAbQBzACkAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVwBJAFQAQwBIACgAbwBwAGUAcgBhAHQAaQBvAG4ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEARABEAFwAIgAsACAAMQA1ACAALQAgAEwARQBOACgAaQB0AGUAbQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFUATABcACIALAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARQB2AGEAbAB1AGEAdABlACAAcABvAHMAcwBpAGIAbABlACAAawAgAHYAYQBsAHUAZQBzACAAZAB5AG4AYQBtAGkAYwBhAGwAbAB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAZQBzAHQAXwBrACwAIAB7ADcAOwAgADYAOwAgADUAOwAgADQAOwAgADMAOwAgADIAOwAgADEAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AbwB2AGUAcgBsAGEAcAAsACAAUgBPAFUATgBEAFUAUAAoAGkAdABlAG0AcwAgAC8AIAB0AGUAcwB0AF8AawAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIAB0AGgAZQAgAGEAYgBzAG8AbAB1AHQAZQAgAHAAZQBhAGsAIAB2AGEAbAB1AGUAIABpAG4AcwBpAGQAZQAgAHQAaABlACAAZQBuAGcAaQBuAGUAIAAoAEMAbwBuAHYAbwBsAHUAdABpAG8AbgAgACsAIABDAGEAcgByAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB1AG4AYwBhAHIAcgBpAGUAZABfAG0AYQB4ACwAIABtAGEAeABfAG8AdgBlAHIAbABhAHAAIAAqACAAKAAxADAAXgB0AGUAcwB0AF8AawAgAC0AIAAxACkAXgAyACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAHgAXwBjAGEAcgByAHkALAAgAEkATgBUACgAdQBuAGMAYQByAHIAaQBlAGQAXwBtAGEAeAAgAC8AIAAxADAAXgB0AGUAcwB0AF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABlAGEAawBfAHYAYQBsACwAIAB1AG4AYwBhAHIAcgBpAGUAZABfAG0AYQB4ACAAKwAgAG0AYQB4AF8AYwBhAHIAcgB5ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHQAdQByAG4AIAB0AGgAZQAgAG0AYQB4ACAAawAgADwAPQAgAEUAeABjAGUAbAAnAHMAIAAxADUALQBkAGkAZwBpAHQAIABjAGUAaQBsAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgARgBJAEwAVABFAFIAKAB0AGUAcwB0AF8AawAsACAAcABlAGEAawBfAHYAYQBsACAAPAA9ACAAKAAxADAAXgAxADUAIAAtACAAMQApACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQASQBWAFwAIgAsACAANwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAE4AQQBNAEUAPwBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AaQBmAGkAZQBkACAAUwBwAGwAaQB0AHQAZQByAC4AIABTAHAAbABpAHQAcwAgAGIAbwB0AGgAIABzAGMAYQBsAGEAcgBzACAAYQBuAGQAIABhAHIAcgBhAHkAcwAgAGkAbgB0AG8AIABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuACAAbABpAG0AYgBzAC4AXABuACAAKgAgAFUAcwBlAHMAIABNAEEAWAAoACkAIAB0AG8AIABnAHUAYQByAGEAbgB0AGUAZQAgAHMAYwBhAGwAYQByACAAaQBuAHAAdQB0AHMAIAB0AG8AIAB0AGgAZQAgAFMARQBRAFUARQBOAEMARQAgAGUAbgBnAGkAbgBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABzACAAVABoAGUAIABzAHQAcgBpAG4AZwAgAG8AcgAgAGEAcgByAGEAeQAgAG8AZgAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFMAcABsAGkAdAAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAcwAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABiAGkAZwBfAGkAbgB0AF8AcgBvAHcALAAgAFQATwBSAE8AVwAoAGIAaQBnAF8AaQBuAHQAcwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBnAHQAaABzACwAIABMAEUATgAoAGIAaQBnAF8AaQBuAHQAXwByAG8AdwApACwAXABuACAAIAAgACAAIAAgACAAIABtAGEAeABfAGwAZQBuACwAIABNAEEAWAAoAGwAZQBuAGcAdABoAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBsAGUAbgAsACAAUgBPAFUATgBEAFUAUAAoAG0AYQB4AF8AbABlAG4AIAAvACAAawAsACAAMAApACAAKgAgAGsALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAZABlAGQALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAHAAYQBkAF8AbABlAG4AIAAtACAAbABlAG4AZwB0AGgAcwApACAAJgAgAGIAaQBnAF8AaQBuAHQAXwByAG8AdwAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALAAgAFMARQBRAFUARQBOAEMARQAoAHAAYQBkAF8AbABlAG4AIAAvACAAawAsACAAMQAsACAAcABhAGQAXwBsAGUAbgAgAC0AIABrACAAKwAgADEALAAgAC0AawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC0ALQBNAEkARAAoAHAAYQBkAGQAZQBkACwAIABzAHQAYQByAHQAcwAsACAAawApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAQwBvAG4AYwBhAHQAZQBuAGEAdABlAHMAIABhAG4AIABhAHIAcgBhAHkAIABvAGYAIABuAHUAbQBlAHIAaQBjACAAbABpAG0AYgBzACAAaQBuAHQAbwAgAGEAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnACwAIAB6AGUAcgBvAC0AcABhAGQAZABpAG4AZwAgAGEAbABsACAAYgB1AHQAIAB0AGgAZQAgAGYAaQByAHMAdAAgAGwAaQBtAGIALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAIABUAGgAZQAgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAG4AdQBtAGUAcgBpAGMAIABsAGkAbQBiAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABsAGkAbQBiACAAcwBpAHoAZQAgAHUAcwBlAGQAIABkAHUAcgBpAG4AZwAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAuAFwAbgAgACoALwBcAG4ATQBlAHIAZwBlACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AdQBtAF8AbABpAG0AYgBzACwAIABSAE8AVwBTACgAbABpAG0AYgBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQB2AF8AbABpAG0AYgBzACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAbABpAG0AYgBzACwAIABTAEUAUQBVAEUATgBDAEUAKABuAHUAbQBfAGwAaQBtAGIAcwAsACAAMQAsACAAbgB1AG0AXwBsAGkAbQBiAHMALAAgAC0AMQApACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AdQBtAF8AbABpAG0AYgBzACAAPQAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHYAXwBsAGkAbQBiAHMAIAAmACAAXAAiAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATgBDAEEAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAcgBlAHYAXwBsAGkAbQBiAHMALAAgADEAKQAgACYAIABcACIAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEUAWABUACgARABSAE8AUAAoAHIAZQB2AF8AbABpAG0AYgBzACwAIAAxACkALAAgAFIARQBQAFQAKABcACIAMABcACIALAAgAGsAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAUgBlAHMAbwBsAHYAZQBzACAAYwBhAHIAcgBpAGUAcwAgAHIAaQBnAGgAdAAtAHQAbwAtAGwAZQBmAHQAIABhAGMAcgBvAHMAcwAgAGEAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkAIABvAGYAIABiAGEAcwBlAC0AMQAwAF4AawAgAGwAaQBtAGIAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwAgAFQAaABlACAAYQByAHIAYQB5ACAAbwBmACAAbgB1AG0AZQByAGkAYwAgAGwAaQBtAGIAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGwAaQBtAGIAIABzAGkAegBlAC4AXABuACAAKgAvAFwAbgBDAGEAcgByAHkAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwApACwAXABuACAAIAAgACAAIAAgACAAIABiAGEAcwBlACwAIAAxADAAXgBrACwAXABuACAAIAAgACAAIAAgACAAIABzAGMAYQBuAG4AZQBkACwAIABTAEMAQQBOACgAMAAsACAAbABpAG0AYgBzACwAIABMAEEATQBCAEQAQQAoAGEAYwBjACwAIAB2AGEAbAAsACAAdgBhAGwAIAArACAASQBOAFQAKABhAGMAYwAgAC8AIABiAGEAcwBlACkAKQApACwAXABuACAAIAAgACAAIAAgACAAIAByAGUAbQBhAGkAbgBkAGUAcgBzACwAIABNAE8ARAAoAHMAYwBhAG4AbgBlAGQALAAgAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AYwBhAHIAcgB5ACwAIABJAE4AVAAoAEkATgBEAEUAWAAoAHMAYwBhAG4AbgBlAGQALAAgAG4ALAAgADEAKQAgAC8AIABiAGEAcwBlACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABmAGkAbgBhAGwAXwBjAGEAcgByAHkAIAA+ACAAMAAsACAAVgBTAFQAQQBDAEsAKAByAGUAbQBhAGkAbgBkAGUAcgBzACwAIABmAGkAbgBhAGwAXwBjAGEAcgByAHkAKQAsACAAcgBlAG0AYQBpAG4AZABlAHIAcwApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8ALwAgAC0ALQAtACAAVQBuAHMAaQBnAG4AZQBkACAASwBlAHIAbgBlAGwAcwAgAC0ALQAtACAAXABcAFwAXABcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAVQBuAHMAaQBnAG4AZQBkACAAYwBvAG0AcABhAHIAaQBzAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAMQAgACgAYQAgAD4AIABiACkALAAgAC0AMQAgACgAYQAgADwAIABiACkALAAgAG8AcgAgADAAIAAoAGEAIAA9ACAAYgApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAIABUAGgAZQAgAHMAZQBjAG8AbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoALwBcAG4AVQBDAG8AbQBwAGEAcgBlACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAeABfAHIAbwB3AHMALAAgAE0AQQBYACgAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEAKQAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAZABfAGEALAAgAEUAWABQAEEATgBEACgAbABpAG0AYgBzAF8AYQAsACAAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAYQBkAF8AYgAsACAARQBYAFAAQQBOAEQAKABsAGkAbQBiAHMAXwBiACwAIABtAGEAeABfAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABkAGkAZgBmACwAIABwAGEAZABfAGEAIAAtACAAcABhAGQAXwBiACwAXABuACAAIAAgACAAIAAgACAAIABtAHMAZABfAGkAZAB4ACwAIABYAE0AQQBUAEMASAAoAFQAUgBVAEUALAAgAGQAaQBmAGYAIAA8AD4AIAAwACwAIAAwACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATgBBACgAbQBzAGQAXwBpAGQAeAApACwAIAAwACwAIABTAEkARwBOACgASQBOAEQARQBYACgAZABpAGYAZgAsACAAbQBzAGQAXwBpAGQAeAAsACAAMQApACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAGEAZABkAGkAdABpAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFUAQQBkAGQAIAA9ACAATABBAE0AQgBEAEEAKABhACwAIABiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AcgBvAHcAcwAsACAATQBBAFgAKABSAE8AVwBTACgAYQApACwAIABSAE8AVwBTACgAYgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAYQBkAF8AYQAsACAARQBYAFAAQQBOAEQAKABhACwAIABtAGEAeABfAHIAbwB3AHMALAAgADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBiACwAIABFAFgAUABBAE4ARAAoAGIALAAgAG0AYQB4AF8AcgBvAHcAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHAAYQBkAF8AYQAgACsAIABwAGEAZABfAGIALAAgAGsAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAHMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAdwBvACAATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgAgAGwAaQBtAGIAIABhAHIAcgBhAHkAcwAuAFwAbgAgACoAIABBAHMAcwB1AG0AZQBzACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAgAEEAIAA+AD0AIABCAC4AIABSAGUAcwBvAGwAdgBlAHMAIABiAG8AcgByAG8AdwBzACAAdABvAHAALQB0AG8ALQBiAG8AdAB0AG8AbQAgAGEAbgBkACAAdAByAGkAbQBzACAAdAByAGEAaQBsAGkAbgBnACAAegBlAHIAbwBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAbQBpAG4AdQBlAG4AZAAgAGwAaQBtAGIAIABhAHIAcgBhAHkAIAAoAG0AdQBzAHQAIABiAGUAIAA+AD0AIABsAGkAbQBiAHMAXwBiACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABzAHUAYgB0AHIAYQBoAGUAbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AVQBTAHUAYgAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwByAG8AdwBzACwAIABNAEEAWAAoAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGQAXwBhACwAIABFAFgAUABBAE4ARAAoAGwAaQBtAGIAcwBfAGEALAAgAG0AYQB4AF8AcgBvAHcAcwAsACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIABwAGEAZABfAGIALAAgAEUAWABQAEEATgBEACgAbABpAG0AYgBzAF8AYgAsACAAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAZABpAGYAZgAsACAAcABhAGQAXwBhACAALQAgAHAAYQBkAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBlAHMAbwBsAHYAZQBkACwAIABDAGEAcgByAHkAKABkAGkAZgBmACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAbQBzAGQAXwBpAGQAeAAsACAAWABNAEEAVABDAEgAKABUAFIAVQBFACwAIAByAGUAcwBvAGwAdgBlAGQAIAA8AD4AIAAwACwAIAAwACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATgBBACgAbQBzAGQAXwBpAGQAeAApACwAIAB7ADAAfQAsACAAVABBAEsARQAoAHIAZQBzAG8AbAB2AGUAZAAsACAAbQBzAGQAXwBpAGQAeAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABWAGUAYwB0AG8AcgBpAHoAZQBkACAAbQBhAHQAcgBpAHgAIABzAHUAbQAgAG8AZgAgAHUAbgBzAGkAZwBuAGUAZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHUAYgBpAGcAXwBpAG4AdAAgAEgAbwByAGkAegBvAG4AdABhAGwAIABhAHIAcgBhAHkAIAAoADEAeABOACkAIABvAGYAIABuAG8AcgBtAGEAbABpAHoAZQBkACAAbQBhAGcAbgBpAHQAdQBkAGUAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAdQBuAGkAZgBpAGUAZAAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AVQBNAGEAdAByAGkAeABTAHUAbQAgAD0AIABMAEEATQBCAEQAQQAoAHUAYgBpAGcAXwBpAG4AdABzACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAGcAcgBpAGQALAAgAFMAcABsAGkAdAAoAHUAYgBpAGcAXwBpAG4AdABzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAYQB3AF8AbABpAG0AYgBzACwAIABCAFkAUgBPAFcAKABnAHIAaQBkACwAIABTAFUATQApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHIAYQB3AF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABSAG8AdQB0AGUAcwAgAGEAZABkAGkAdABpAG8AbgAvAHMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAGIAYQBzAGUAZAAgAG8AbgAgAHMAaQBnAG4AcwAgAGEAbgBkACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAuAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAYQAgAHQAdQBwAGwAZQAgAGEAcgByAGEAeQA6ACAAVgBTAFQAQQBDAEsAKABsAGkAbQBiAHMALAAgAGYAaQBuAGEAbABfAHMAaQBnAG4AKQAgAHcAaABlAHIAZQAgAHQAaABlACAAZgBpAG4AYQBsACAAcgBvAHcAIABpAHMAIAB0AGgAZQAgAHMAYwBhAGwAYQByACAAcwBpAGcAbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAGYAaQByAHMAdAAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAcwBlAGMAbwBuAGQAIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHMAaQBnAG4AXwBhACAAVABoAGUAIABzAGkAZwBuACAAbwBmACAAdABoAGUAIABmAGkAcgBzAHQAIABhAHIAcgBhAHkAIAAoADEALAAgAC0AMQAsACAAMAApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAcwBpAGcAbgBfAGIAIABUAGgAZQAgAHMAaQBnAG4AIABvAGYAIAB0AGgAZQAgAHMAZQBjAG8AbgBkACAAYQByAHIAYQB5ACAAKAAxACwAIAAtADEALAAgADAAKQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgAgACoALwBcAG4AQQBkAGQAUwB1AGIAUgBvAHUAdABlAHIAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABzAGkAZwBuAF8AYQAsACAAcwBpAGcAbgBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AcwBhAG0AZQBfAHMAaQBnAG4ALAAgAHMAaQBnAG4AXwBhACAAPQAgAHMAaQBnAG4AXwBiACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGkAcwBfAHMAYQBtAGUAXwBzAGkAZwBuACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEEAZABkAGkAdABpAG8AbgA6ACAAbQBhAGcAbgBpAHQAdQBkAGUAcwAgAGMAbwBtAGIAaQBuAGUALAAgAHMAaQBnAG4AIAByAGUAbQBhAGkAbgBzACAAdABoAGUAIABzAGEAbQBlAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVQBBAGQAZAAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsACAAcwBpAGcAbgBfAGEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwB1AGIAdAByAGEAYwB0AGkAbwBuADoAIABlAHYAYQBsAHUAYQB0AGUAIABtAGEAZwBuAGkAdAB1AGQAZQBzACAAdABvACAAcwBhAHQAaQBzAGYAeQAgAFUAUwB1AGIAIAAoAEEAIAA+AD0AIABCACkAIABwAHIAZQBjAG8AbgBkAGkAdABpAG8AbgAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcAAsACAAVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFQAbwB0AGEAbAAgAGMAYQBuAGMAZQBsAGwAYQB0AGkAbwBuADoAIAByAGUAdAB1AHIAbgAgAHsAMAB9ACAAbABpAG0AYgAgAGEAbgBkACAAMAAgAHMAaQBnAG4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHsAMAA7ADAAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABtAGEAZwBfAGMAbwBtAHAAIAA+ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABBACAAaQBzACAAbABhAHIAZwBlAHIAOgAgAHMAaQBnAG4AIABiAGUAbABvAG4AZwBzACAAdABvACAAQQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFUAUwB1AGIAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALAAgAHMAaQBnAG4AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEIAIABpAHMAIABsAGEAcgBnAGUAcgA6ACAAcgBvAHUAdABlACAAQgAgAGYAaQByAHMAdAAsACAAcwBpAGcAbgAgAGIAZQBsAG8AbgBnAHMAIAB0AG8AIABCAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAVQBTAHUAYgAoAGwAaQBtAGIAcwBfAGIALAAgAGwAaQBtAGIAcwBfAGEALAAgAGsAKQAsACAAcwBpAGcAbgBfAGIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABVAG4AcwBpAGcAbgBlAGQAIABtAHUAbAB0AGkAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIAB0AHcAbwAgAEwAaQB0AHQAbABlAC0ARQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5AHMALgBcAG4AIAAqACAAVQB0AGkAbABpAHoAZQBzACAAYQAgADEARAAgAEQAaQBzAGMAcgBlAHQAZQAgAEMAbwBuAHYAbwBsAHUAdABpAG8AbgAgACgAQwBhAHUAYwBoAHkAIABQAHIAbwBkAHUAYwB0ACkAIABhAHIAcgBhAHkALQBzAGwAaQBjAGkAbgBnACAAcwB0AHIAYQB0AGUAZwB5AC4AXABuACAAKgAgAFoAZQByAG8AIABkAHkAbgBhAG0AaQBjACAAbQBlAG0AbwByAHkAIAByAGUAYQBsAGwAbwBjAGEAdABpAG8AbgAuACAAJABPACgATgArAE0AKQAkACAAbQBlAG0AbwByAHkAIABmAG8AbwB0AHAAcgBpAG4AdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGEAIABUAGgAZQAgAG0AdQBsAHQAaQBwAGwAaQBjAGEAbgBkACAAbABpAG0AYgAgAGEAcgByAGEAeQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAIABUAGgAZQAgAG0AdQBsAHQAaQBwAGwAaQBlAHIAIABsAGkAbQBiACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBVAE0AdQBsACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwByAG8AdwBzACwAIABsAGUAbgBfAGEAIAArACAAbABlAG4AXwBiACAALQAgADEALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAATABvAG8AcAAgAHAAdQByAGUAbAB5ACAAbwB2AGUAcgAgAHQAaABlACAAbABlAG4AZwB0AGgAIABvAGYAIAB0AGgAZQAgAGYAaQBuAGEAbAAgAG8AdQB0AHAAdQB0ACAAYQByAHIAYQB5AFwAbgAgACAAIAAgACAAIAAgACAAcgBhAHcAXwBsAGkAbQBiAHMALAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAbQBhAHgAXwByAG8AdwBzACwAIAAxACwAIABMAEEATQBCAEQAQQAoAHIALAAgAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAbABjAHUAbABhAHQAZQAgAHQAaABlACAAdgBhAGwAaQBkACAAbwB2AGUAcgBsAGEAcABwAGkAbgBnACAAdwBpAG4AZABvAHcAIABvAGYAIABpAG4AZABpAGMAZQBzACAAZgBvAHIAIAB0AGgAaQBzACAAbQBhAGcAbgBpAHQAdQBkAGUAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AF8AaQAsACAATQBBAFgAKAAxACwAIAByACAALQAgAGwAZQBuAF8AYgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAG4AZABfAGkALAAgAE0ASQBOACgAcgAsACAAbABlAG4AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AdQBuAHQALAAgAGUAbgBkAF8AaQAgAC0AIABzAHQAYQByAHQAXwBpACAAKwAgADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGUAcQB1AGUAbgBjAGUAIABpACAAYwBvAHUAbgB0AHMAIABVAFAALgAgAFMAZQBxAHUAZQBuAGMAZQAgAGoAIABjAG8AdQBuAHQAcwAgAEQATwBXAE4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGUAcQBfAGkALAAgAFMARQBRAFUARQBOAEMARQAoAGMAbwB1AG4AdAAsACAAMQAsACAAcwB0AGEAcgB0AF8AaQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBlAHEAXwBqACwAIABTAEUAUQBVAEUATgBDAEUAKABjAG8AdQBuAHQALAAgADEALAAgAHIAIAAtACAAcwB0AGEAcgB0AF8AaQAgACsAIAAxACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAbABpAGMAZQAgAHQAaABlACAAZQB4AGEAYwB0ACAAaQBuAHQAZQByAHMAZQBjAHQAaQBuAGcAIABsAGkAbQBiAHMALAAgAG0AdQBsAHQAaQBwAGwAeQAsACAAYQBuAGQAIABzAHUAbQAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUATQAoAEkATgBEAEUAWAAoAGwAaQBtAGIAcwBfAGEALAAgAHMAZQBxAF8AaQAsACAAMQApACAAKgAgAEkATgBEAEUAWAAoAGwAaQBtAGIAcwBfAGIALAAgAHMAZQBxAF8AagAsACAAMQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUgBlAHMAbwBsAHYAZQAgAGEAbABsACAAYwBhAHIAcgBpAGUAcwAgAGIAbwB0AHQAbwBtAC0AdABvAC0AdABvAHAAIABlAHgAYQBjAHQAbAB5ACAAbwBuAGMAZQBcAG4AIAAgACAAIAAgACAAIAAgAEMAYQByAHIAeQAoAHIAYQB3AF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABCAGkAbgBhAHIAeQAgAHMAZQBhAHIAYwBoACAAdABvACAAZgBpAG4AZAAgAHQAaABlACAAaABpAGcAaABlAHMAdAAgAHMAYwBhAGwAYQByACAAcQB1AG8AdABpAGUAbgB0ACAAbABpAG0AYgAgAHEAIAAoADAAIAA8AD0AIABxACAAPAAgADEAMABeAGsAKQBcAG4AoAAqACAAcwB1AGMAaAAgAHQAaABhAHQAIABCACAAKgAgAHEAIAA8AD0AIABhAGMAYwAuACAARQBsAGkAbQBpAG4AYQB0AGUAcwAgAHQAaABlACAAbgBlAGUAZAAgAGYAbwByACAASwBuAHUAdABoACAARAAgAGYAbABvAGEAdAAtAGUAcwB0AGkAbQBhAHQAaQBvAG4ALgBcAG4AoAAqACAAQABwAGEAcgBhAG0AIABhAGMAYwAgAFQAaABlACAAYwB1AHIAcgBlAG4AdAAgAHIAZQBtAGEAaQBuAGQAZQByACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAuAFwAbgCgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgCgACoALwBcAG4ARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAgAD0AIABMAEEATQBCAEQAQQAoAGEAYwBjACwAIABiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAYQBsAGMAdQBsAGEAdABlACAAcgBlAHEAdQBpAHIAZQBkACAAYgBpAHQAcwAgAGQAeQBuAGEAbQBpAGMAYQBsAGwAeQAuACAARgBvAHIAIABtAGEAeAAgAGsAPQA3ACwAIAB0AGgAaQBzACAAZQB2AGEAbAB1AGEAdABlAHMAIAB0AG8AIAAyADQAIABiAGkAdABzAC4AXABuACAAIAAgACAAIAAgACAAIABiAGkAdABzACwAIABDAEUASQBMAEkATgBHAC4ATQBBAFQASAAoAEwATwBHACgAMQAwAF4AawAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAHAAbwB3AGUAcgBzACwAIAAyACAAXgAgAFMARQBRAFUARQBOAEMARQAoAGIAaQB0AHMALAAgADEALAAgAGIAaQB0AHMAIAAtACAAMQAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAUgBFAEQAVQBDAEUAKAAwACwAIABwAG8AdwBlAHIAcwAsACAATABBAE0AQgBEAEEAKABjAHUAcgByAF8AcQAsACAAcABvAHcAZQByACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABlAHMAdABfAHEALAAgAGMAdQByAHIAXwBxACAAKwAgAHAAbwB3AGUAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAawBpAHAAIABpAGYAIAB0AGUAcwB0AF8AcQAgAGUAeABjAGUAZQBkAHMAIAB0AGgAZQAgAGwAaQBtAGIAIABiAGEAcwBlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHQAZQBzAHQAXwBxACAAPgA9ACAAMQAwAF4AawAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAATQB1AGwAdABpAHAAbAB5ACAAQgAgAGIAeQAgAHMAYwBhAGwAYQByACAAdABlAHMAdABfAHEAIABhAG4AZAAgAHIAZQBzAG8AbAB2AGUAIABjAGEAcgByAGkAZQBzACAAbgBhAHQAaQB2AGUAbAB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGUAcwB0AF8AcAByAG8AZAAsACAAQwBhAHIAcgB5ACgAYgAgACoAIAB0AGUAcwB0AF8AcQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAFUAQwBvAG0AcABhAHIAZQAoAGEAYwBjACwAIAB0AGUAcwB0AF8AcAByAG8AZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABjAG8AbQBwACAAPgA9ACAAMAAsACAAdABlAHMAdABfAHEALAAgAGMAdQByAHIAXwBxACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABCAGEAcwBlAGMAYQBzAGUAIABEAGkAdgBpAHMAaQBvAG4AIAB2AGkAYQAgAHMAZQBxAHUAZQBuAHQAaQBhAGwAIABzAGgAaQBmAHQALQBhAG4AZAAtAHMAdQBiAHQAcgBhAGMAdAAuAFwAbgCgACoAIABSAGUAdAB1AHIAbgBzACAAYQAgAHAAYQBjAGsAZQBkACAAMQBEACAAYQByAHIAYQB5ADoAIABWAFMAVABBAEMASwAoAEwAZQBuAGcAdABoAF8AUgAsACAAUgBfAGwAaQBtAGIAcwAsACAAUQBfAGwAaQBtAGIAcwApAC4AXABuAKAAKgAgAEUAbABpAG0AaQBuAGEAdABlAHMAIAAyAEQAIABhAHIAcgBhAHkAIABwAGEAZABkAGkAbgBnACAAdABvACAAcwB0AHIAaQBjAHQAbAB5ACAAcAByAGUAcwBlAHIAdgBlACAAbQBlAG0AbwByAHkAIABlAGYAZgBpAGMAaQBlAG4AYwB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAgACgAYQBzAHMAdQBtAGUAZAAgAG4AbwBuAC0AegBlAHIAbwApAC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuAKAAKgAvAFwAbgBLAG4AdQB0AGgARABpAHYAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcAAsACAAVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAIAByAG8AdQB0AGkAbgBnACAAdwBpAHQAaAAgAHQAaABlACAAbgBlAHcAIABwAGEAYwBrAGUAZAAgAG0AZQBtAG8AcgB5ACAAYwBvAG4AdAByAGEAYwB0AFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbABpAG0AYgBzAF8AYQApACwAIABsAGkAbQBiAHMAXwBhACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAbQBhAGcAXwBjAG8AbQBwACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADEALAAgADAALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEkAdABlAHIAYQB0AGUAIABvAHYAZQByACAAQQAgAGYAcgBvAG0AIABNAFMAQgAgACgAdABvAHAAKQAgAHQAbwAgAEwAUwBCACAAKABiAG8AdAB0AG8AbQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHYAZQByAHMAZQBkAF8AYQAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEALAAgAFMARQBRAFUARQBOAEMARQAoAGwAZQBuAF8AYQAsACAAMQAsACAAbABlAG4AXwBhACwAIAAtADEAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAdABhAHQAZQAgAHMAZQBwAGEAcgBhAHQAbwByADoAIABWAFMAVABBAEMASwAoAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABxAHUAbwB0AGkAZQBuAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAbgBpAHQAaQBhAGwAXwBzAHQAYQB0AGUALAAgAFYAUwBUAEEAQwBLACgAMQAsACAAMAAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsAF8AcwB0AGEAdABlACwAIAByAGUAdgBlAHIAcwBlAGQAXwBhACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAdgBhAGwALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBtAGEAaQBuAGQAZQByACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcwB0AGEAdABlACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHEAdQBvAHQAaQBlAG4AdAAsACAARABSAE8AUAAoAHMAdABhAHQAZQAsACAAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGgAaQBmAHQAIABhAGMAYwAgAHUAcAAgAGIAeQAgADEAIABsAGkAbQBiACAAKABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuADoAIABpAG4AcwBlAHIAdAAgAGEAdAAgAGkAbgBkAGUAeAAgADEAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABlAHgAdABlAG4AZABlAGQAXwByAGUAbQBhAGkAbgBkAGUAcgAsACAASQBGACgAQQBOAEQAKABSAE8AVwBTACgAcgBlAG0AYQBpAG4AZABlAHIAKQAgAD0AIAAxACwAIABJAE4ARABFAFgAKAByAGUAbQBhAGkAbgBkAGUAcgAsACAAMQAsACAAMQApACAAPQAgADAAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB2AGEAbAAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAHYAYQBsACwAIAByAGUAbQBhAGkAbgBkAGUAcgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgAsACAARgBpAG4AZABRAHUAbwB0AGkAZQBuAHQATABpAG0AYgAoAGUAeAB0AGUAbgBkAGUAZABfAHIAZQBtAGEAaQBuAGQAZQByACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAHIAbwBkACwAIABDAGEAcgByAHkAKABsAGkAbQBiAHMAXwBiACAAKgAgAG4AZQB4AHQAXwBxAHUAbwB0AGkAZQBuAHQAXwBsAGkAbQBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAdwBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABVAFMAdQBiACgAZQB4AHQAZQBuAGQAZQBkAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAHAAcgBvAGQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGgAYQBzAF8AcQB1AG8AdABpAGUAbgB0ACwAIABPAFIAKABSAE8AVwBTACgAcQB1AG8AdABpAGUAbgB0ACkAIAA+ACAAMQAsACAASQBOAEQARQBYACgAcQB1AG8AdABpAGUAbgB0ACwAMQAsADEAKQAgAD4AIAAwACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQB1AG8AdAAsACAASQBGACgAaABhAHMAXwBxAHUAbwB0AGkAZQBuAHQALAAgAFYAUwBUAEEAQwBLACgAcQB1AG8AdABpAGUAbgB0ACwAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgApACwAIABuAGUAeAB0AF8AcQB1AG8AdABpAGUAbgB0AF8AbABpAG0AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbgBlAHcAXwByAGUAbQBhAGkAbgBkAGUAcgApACwAIABuAGUAdwBfAHIAZQBtAGEAaQBuAGQAZQByACwAIABuAGUAeAB0AF8AcQB1AG8AdAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcgBlAG0AYQBpAG4AZABlAHIALAAgAEkATgBEAEUAWAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAbQBhAGkAbgBkAGUAcgAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAsACAAMQAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQB2AGUAcgBzAGUAZABfAHEAdQBvAHQAaQBlAG4AdAAsACAARABSAE8AUAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAbABlAG4AXwByAGUAbQBhAGkAbgBkAGUAcgAgACsAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAcQB1AG8AdABfAHIAYQB3ACAAdwBhAHMAIABiAHUAaQBsAHQAIABNAFMAQgAgAHQAbwAgAEwAUwBCACAAKABCAGkAZwAtAEUAbgBkAGkAYQBuACkALgAgAFIAZQB2AGUAcgBzAGUAIAB0AG8AIABpAG4AdABlAHIAbgBhAGwAIABMAGkAdAB0AGwAZQAtAEUAbgBkAGkAYQBuAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHEAdQBvAHQAaQBlAG4AdAAsACAAUgBPAFcAUwAoAHIAZQB2AGUAcgBzAGUAZABfAHEAdQBvAHQAaQBlAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABxAHUAbwB0AGkAZQBuAHQALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKAByAGUAdgBlAHIAcwBlAGQAXwBxAHUAbwB0AGkAZQBuAHQALAAgAFMARQBRAFUARQBOAEMARQAoAGwAZQBuAF8AcQB1AG8AdABpAGUAbgB0ACwAIAAxACwAIABsAGUAbgBfAHEAdQBvAHQAaQBlAG4AdAAsACAALQAxACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAHMAdAByAGkAYwB0AGwAeQAgAHAAYQBjAGsAZQBkACAAMQBEACAAYQByAHIAYQB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABsAGUAbgBfAHIAZQBtAGEAaQBuAGQAZQByACwAIAByAGUAbQBhAGkAbgBkAGUAcgAsACAAcQB1AG8AdABpAGUAbgB0ACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuAKAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABIAHkAYgByAGkAZAAgAEQAaQB2AGkAcwBpAG8AbgAgAFIAbwB1AHQAZQByAC4AXABuAKAAKgAgAEQAaQByAGUAYwB0AHMAIABkAGkAdgBpAHMAaQBvAG4AIAB0AG8AIAB0AGgAZQAgAG8AcAB0AGkAbQBhAGwAIABrAGUAcgBuAGUAbAAgAGIAYQBzAGUAZAAgAG8AbgAgAEQAaQB2AGkAZABlAG4AZAAgAGwAZQBuAGcAdABoAC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAYQByAHIAYQB5AC4AXABuAKAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGEAcgByAGEAeQAuAFwAbgCgACoAIABAAHAAYQByAGEAbQAgAGsAIABUAGgAZQAgAGQAeQBuAGEAbQBpAGMAIABjAGgAdQBuAGsAIABzAGkAegBlACAAYwBvAG4AdABlAHgAdAAuAFwAbgCgACoALwBcAG4ARABpAHYAUgBvAHUAdABlAHIAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEQAaQBnAGkAdAAgAGMAbwB1AG4AdABzACAAYQByAGUAIABhAHAAcAByAG8AeABpAG0AYQB0AGUALAAgAGIAdQB0ACAAcwB1AGYAZgBpAGMAaQBlAG4AdABcAG4AIAAgACAAIAAgACAAIAAgAGQAaQBnAGkAdABzAF8AYQAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGEAKQAgACoAIABrACwAXABuACAAIAAgACAAIAAgACAAIABkAGkAZwBpAHQAcwBfAGIALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBiACkAIAAqACAAawAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABNAGEAYwBoAGkAbgBlAC0AbABlAGEAcgBuAGUAZAAgAGMAbwBlAGYAZgBpAGMAaQBlAG4AdABzACAAZgByAG8AbQAgAEwAbwBnAGkAcwB0AGkAYwAgAFIAZQBnAHIAZQBzAHMAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIABtACwAIAAwAC4AMQAwADcAOAAyADEAMQA5ADQAMgA3ADEAMgA5ADcALABcAG4AIAAgACAAIAAgACAAIAAgAGMALAAgAC0AMgAyADEALgA5ADAAMgAxADgAOQA0ADYAMgAwADYAOAAsAFwAbgAgACAAIAAgACAAIAAgACAAdABoAHIAZQBzAGgAbwBsAGQALAAgACgAbQAgACoAIABkAGkAZwBpAHQAcwBfAGEAKQAgACsAIABjACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGQAaQBnAGkAdABzAF8AYgAgADwAPQAgAHQAaAByAGUAcwBoAG8AbABkACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEsAbgB1AHQAaABEAGkAdgAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2ACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEcAZQBuAGUAcgBhAHQAZQBzACAAdABoAGUAIABlAHgAYQBjAHQAIAByAGUAYwBpAHAAcgBvAGMAYQBsACAAcwBlAGUAZAAgAGYAbwByACAATgBlAHcAdABvAG4ALQBSAGEAcABoAHMAbwBuACAARABpAHYAaQBzAGkAbwBuACAAdQBzAGkAbgBnACAASwBuAHUAdABoACAAQgBhAHMAZQBjAGEAcwBlAC4AXABuACAAKgAgAEUAeAB0AHIAYQBjAHQAcwAgAHUAcAAgAHQAbwAgAHQAaABlACAAdABvAHAAIAAzACAAbABpAG0AYgBzACAAbwBmACAAQgAgAGEAbgBkACAAYwBhAGwAYwB1AGwAYQB0AGUAcwAgAGYAbABvAG8AcgAoAEIAZQB0AGEAXgAoADIAKgBsAGUAbgApACAALwAgAEIAXwB0AG8AcAApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4AUwBlAGUAZAAgAD0AIABMAEEATQBCAEQAQQAoAGwAaQBtAGIAcwBfAGIALAAgAGsALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwBiACwAIABSAE8AVwBTACgAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABzAGUAZQBkAF8AbABlAG4ALAAgAE0ASQBOACgAMwAsACAAbABlAG4AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARQB4AHQAcgBhAGMAdAAgAHQAbwBwACAAJwBzAGUAZQBkAF8AbABlAG4AJwAgAGwAaQBtAGIAcwAgACgATABpAHQAdABsAGUALQBFAG4AZABpAGEAbgA6ACAAdABhAGsAZQAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAbwB0AHQAbwBtACkAXABuACAAIAAgACAAIAAgACAAIABiAF8AdABvAHAALAAgAFQAQQBLAEUAKABsAGkAbQBiAHMAXwBiACwAIAAtAHMAZQBlAGQAXwBsAGUAbgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAbwBuAHMAdAByAHUAYwB0ACAAQgBlAHQAYQBeACgAMgAgACoAIABzAGUAZQBkAF8AbABlAG4AKQAgAG4AYQB0AGkAdgBlAGwAeQBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAGUALgBnAC4ALAAgAGkAZgAgAHMAZQBlAGQAXwBsAGUAbgAgAD0AIAAxACwAIAB0AGgAZQBuACAAMQAgAGYAbwBsAGwAbwB3AGUAZAAgAGIAeQAgAHQAdwBvACAAegBlAHIAbwAgAGwAaQBtAGIAcwA6ACAAVgBTAFQAQQBDAEsAKAAwACwAIAAwACwAIAAxACkAXABuACAAIAAgACAAIAAgACAAIABiAGUAdABhAF8AMgBtACwAIABWAFMAVABBAEMASwAoAEUAWABQAEEATgBEACgAMAAsACAAMgAgACoAIABzAGUAZQBkAF8AbABlAG4ALAAgACwAIAAwACkALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABLAG4AdQB0AGgAIABEAGkAdgBpAHMAaQBvAG4AIAB5AGkAZQBsAGQAcwAgAGUAeABhAGMAdAAgAGkAbgBpAHQAaQBhAGwAIAByAGUAYwBpAHAAcgBvAGMAYQBsAFwAbgAgACAAIAAgACAAIAAgACAAcABhAGMAawBlAGQALAAgAEsAbgB1AHQAaABEAGkAdgAoAGIAZQB0AGEAXwAyAG0ALAAgAGIAXwB0AG8AcAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABRAHUAbwB0AGkAZQBuAHQAIABhAHIAcgBhAHkAIABmAHIAbwBtACAAdABoAGUAIABwAGEAYwBrAGUAZAAgAFYAUwBUAEEAQwBLAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwByACwAIABJAE4ARABFAFgAKABwAGEAYwBrAGUAZAAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAcABhAGMAawBlAGQALAAgAGwAZQBuAF8AcgAgACsAIAAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABDAG8AbQBwAHUAdABlAHMAIAB0AGgAZQAgAFIAZQBjAGkAcAByAG8AYwBhAGwAIABwAHIAbwBnAHIAZQBzAHMAaQB2AGUAbAB5ACAAcwBjAGEAbABpAG4AZwAgAHUAcAAgAHQAbwAgAHQAaABlACAARABpAHYAaQBkAGUAbgBkACcAcwAgAHAAcgBlAGMAaQBzAGkAbwBuAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAGwAaQBtAGIAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIAB0AGEAcgBnAGUAdABfAGwAZQBuACAAVABoAGUAIABsAGkAbQBiAC0AbABlAG4AZwB0AGgAIABvAGYAIABEAGkAdgBpAGQAZQBuAGQAIABBAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAFIAZQBjAGkAcAByAG8AYwBhAGwAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBiACwAIAB0AGEAcgBnAGUAdABfAGwAZQBuACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwBlAGUAZABfAGwAZQBuACwAIABNAEkATgAoADMALAAgAGwAZQBuAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAByAF8AcwBlAGUAZABfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBTAGUAZQBkACgAbABpAG0AYgBzAF8AYgAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKABzAGUAZQBkAF8AbABlAG4ALAAgAHIAXwBzAGUAZQBkAF8AbABpAG0AYgBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAHIAZQBxAF8AaQB0AGUAcgBzACwAIABNAEEAWAAoADAALAAgAEMARQBJAEwASQBOAEcALgBNAEEAVABIACgATABOACgAdABhAHIAZwBlAHQAXwBsAGUAbgAgAC8AIABzAGUAZQBkAF8AbABlAG4AKQAgAC8AIABMAE4AKAAyACkAKQApACAAKwAgADEALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKAByAGUAcQBfAGkAdABlAHIAcwAgAD0AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAXwBzAGUAZQBkAF8AbABpAG0AYgBzACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQB0AGUAcgBhAHQAaQBvAG4AcwAsACAAUwBFAFEAVQBFAE4AQwBFACgAcgBlAHEAXwBpAHQAZQByAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAUgBFAEQAVQBDAEUAKABpAG4AaQB0AGkAYQBsAF8AcwB0AGEAdABlACwAIABpAHQAZQByAGEAdABpAG8AbgBzACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAaQB0AGUAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwB1AHIAcgBfAGwAZQBuACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcgAsACAARABSAE8AUAAoAHMAdABhAHQAZQAsACAAMQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AbABlAG4ALAAgAE0ASQBOACgAYwB1AHIAcgBfAGwAZQBuACAAKgAgADIALAAgAHQAYQByAGcAZQB0AF8AbABlAG4AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAARAB5AG4AYQBtAGkAYwAgAFMAYwBhAGwAaQBuAGcAIABTAGgAaQBmAHQAOgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAASQBmACAAQgAgAGgAYQBzACAAcABsAGEAdABlAGEAdQBlAGQALAAgAFIAIABtAHUAcwB0ACAAcwBjAGEAbABlACAAYgB5ACAAMgAqACgAbgAtAG0AKQAuACAASQBmACAAQgAgAGkAcwAgAGcAcgBvAHcAaQBuAGcALAAgAFIAIABzAGMAYQBsAGUAcwAgAGIAeQAgACgAbgAtAG0AKQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAdABpAHYAZQBfAGMAdQByAHIALAAgAE0ASQBOACgAYwB1AHIAcgBfAGwAZQBuACwAIABsAGUAbgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGMAdABpAHYAZQBfAG4AZQB4AHQALAAgAE0ASQBOACgAbgBlAHgAdABfAGwAZQBuACwAIABsAGUAbgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGgAaQBmAHQAXwBsAGkAbQBiAHMALAAgADIAIAAqACAAKABuAGUAeAB0AF8AbABlAG4AIAAtACAAYwB1AHIAcgBfAGwAZQBuACkAIAAtACAAKABhAGMAdABpAHYAZQBfAG4AZQB4AHQAIAAtACAAYQBjAHQAaQB2AGUAXwBjAHUAcgByACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAXwBwAHIAaQBtAGUALAAgAEkARgAoAHMAaABpAGYAdABfAGwAaQBtAGIAcwAgAD4AIAAwACwAIABWAFMAVABBAEMASwAoAEUAWABQAEEATgBEACgAMAAsACAAcwBoAGkAZgB0AF8AbABpAG0AYgBzACwAIAAsACAAMAApACwAIABjAHUAcgByAF8AcgApACwAIABjAHUAcgByAF8AcgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABiAF8AYQBjAHQAaQB2AGUALAAgAFQAQQBLAEUAKABsAGkAbQBiAHMAXwBiACwAIAAtAGEAYwB0AGkAdgBlAF8AbgBlAHgAdAApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABQACAAaQBzACAAbgBhAHQAaQB2AGUAbAB5ACAAYQBsAGkAZwBuAGUAZAAgAHQAbwAgADIAKgBuAGUAeAB0AF8AbABlAG4AIABiAGUAYwBhAHUAcwBlACAAbwBmACAAdABoAGUAIABjAG8AcgByAGUAYwB0AGUAZAAgAHMAaABpAGYAdABfAGwAaQBtAGIAcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGIAXwBhAGMAdABpAHYAZQAsACAAcgBfAHAAcgBpAG0AZQAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AHcAbwBfAGIAZQB0AGEALAAgAFYAUwBUAEEAQwBLACgARQBYAFAAQQBOAEQAKAAwACwAIAAyACAAKgAgAG4AZQB4AHQAXwBsAGUAbgAsACAALAAgADAAKQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGUAcgByACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAdQBiACgAdAB3AG8AXwBiAGUAdABhACwAIABwACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwByAF8AdQBuAHMAYwBhAGwAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAcgBfAHAAcgBpAG0AZQAsACAAZQByAHIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcgAsACAASQBGACgAUgBPAFcAUwAoAG4AZQB4AHQAXwByAF8AdQBuAHMAYwBhAGwAZQBkACkAIAA8AD0AIAAyACAAKgAgAG4AZQB4AHQAXwBsAGUAbgAsACAAewAwAH0ALAAgAEQAUgBPAFAAKABuAGUAeAB0AF8AcgBfAHUAbgBzAGMAYQBsAGUAZAAsACAAMgAgACoAIABuAGUAeAB0AF8AbABlAG4AKQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAG4AZQB4AHQAXwBsAGUAbgAsACAAbgBlAHgAdABfAHIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARABSAE8AUAAoAGYAaQBuAGEAbABfAHMAdABhAHQAZQAsACAAMQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEgAZQBhAHYAeQB3AGUAaQBnAGgAdAAgAE4AZQB3AHQAbwBuAC0AUgBhAHAAaABzAG8AbgAgAEQAaQB2AGkAcwBpAG8AbgAuAFwAbgAgACoAIABJAG0AcABsAGUAbQBlAG4AdABzACAAcAByAG8AZwByAGUAcwBzAGkAdgBlACAAcwBjAGEAbABpAG4AZwAgAGIAbwB1AG4AZABlAGQAIAB0AG8AIABNAEEAWAAoAGwAZQBuAF8AYQAsACAAbABlAG4AXwBiACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBhACAAVABoAGUAIABkAGkAdgBpAGQAZQBuAGQAIABhAHIAcgBhAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABsAGkAbQBiAHMAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAEQAaQB2ACAAPQAgAEwAQQBNAEIARABBACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABsAGUAbgBfAGEALAAgAFIATwBXAFMAKABsAGkAbQBiAHMAXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAAUgBPAFcAUwAoAGwAaQBtAGIAcwBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAHIAZwBlAHQAXwBsAGUAbgAsACAATQBBAFgAKABsAGUAbgBfAGEALAAgAGwAZQBuAF8AYgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAMQAuACAAQwBhAGwAYwB1AGwAYQB0AGUAIAByAGUAYwBpAHAAcgBvAGMAYQBsACAAUgAgAHMAYwBhAGwAZQBkACAAZAB5AG4AYQBtAGkAYwBhAGwAbAB5ACAAdABvACAAMgAgACoAIAB0AGEAcgBnAGUAdABfAGwAZQBuAFwAbgAgACAAIAAgACAAIAAgACAAcgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBSAGUAYwBpAHAAcgBvAGMAYQBsACgAbABpAG0AYgBzAF8AYgAsACAAdABhAHIAZwBlAHQAXwBsAGUAbgAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAMgAuACAAQQBwAHAAcgBvAHgAaQBtAGEAdABlACAAUQB1AG8AdABpAGUAbgB0ADoAIABRAF8AYQBwAHAAcgBvAHgAIAA9ACAAQQAgACoAIABSACAALwAgAEIAZQB0AGEAXgAoADIAIAAqACAAdABhAHIAZwBlAHQAXwBsAGUAbgApAFwAbgAgACAAIAAgACAAIAAgACAAZAByAG8AcABfAGwAaQBtAGIAcwAsACAAMgAgACoAIAB0AGEAcgBnAGUAdABfAGwAZQBuACwAXABuACAAIAAgACAAIAAgACAAIABxAF8AdQBuAHMAYwBhAGwAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAbABpAG0AYgBzAF8AYQAsACAAcgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABxAF8AYQBwAHAAcgBvAHgALAAgAEkARgAoAFIATwBXAFMAKABxAF8AdQBuAHMAYwBhAGwAZQBkACkAIAA8AD0AIABkAHIAbwBwAF8AbABpAG0AYgBzACwAIAB7ADAAfQAsACAARABSAE8AUAAoAHEAXwB1AG4AcwBjAGEAbABlAGQALAAgAGQAcgBvAHAAXwBsAGkAbQBiAHMAKQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIAB0AGgAZQAgAG0AYQBzAHMAaQB2AGUAIABiAGEAcwBlAGwAaQBuAGUAIABwAHIAbwBkAHUAYwB0ACAAZQB4AGEAYwB0AGwAeQAgAE8ATgBDAEUAXABuACAAIAAgACAAIAAgACAAIABwAF8AYgBhAHMAZQBsAGkAbgBlACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAbABpAG0AYgBzAF8AYgAsACAAcQBfAGEAcABwAHIAbwB4ACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAAzAC4AIABCAG8AdQBuAGQAZQBkACAARQByAHIAbwByACAAQwBvAHIAcgBlAGMAdABpAG8AbgAgAFMAdwBlAGUAcAAgACgATwBwAHQAaQBtAGkAegBlAGQAIABPACgATgApACAAUwB0AGUAcABwAGkAbgBnACkAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABTAHQAYQB0AGUAIABwAGEAYwBrAGkAbgBnADoAIABWAFMAVABBAEMASwAoAEwAZQBuAGcAdABoAF8AUQAsACAAUQBfAGwAaQBtAGIAcwAsACAAUABfAGwAaQBtAGIAcwApAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAcQBfAGEAcABwAHIAbwB4ACkALAAgAHEAXwBhAHAAcAByAG8AeAAsACAAcABfAGIAYQBzAGUAbABpAG4AZQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUwB3AGUAZQBwACAARABvAHcAbgA6ACAASQBmACAAUAAgAD4AIABBACwAIABRACAAaQBzACAAdABvAG8AIABiAGkAZwAuACAAUwB0AGUAcAAgAFEAIABkAG8AdwBuACAAYgB5ACAAMQAsACAAYQBuAGQAIABQACAAZABvAHcAbgAgAGIAeQAgAEIALgBcAG4AIAAgACAAIAAgACAAIAAgAHMAdwBlAGUAcABfAGQAbwB3AG4ALAAgAFIARQBEAFUAQwBFACgAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAewAxADsAIAAyAH0ALAAgAEwAQQBNAEIARABBACgAcwB0AGEAdABlACwAIABpACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwBxACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwBxACwAIABDAEgATwBPAFMARQBSAE8AVwBTACgAcwB0AGEAdABlACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHEALAAgADEALAAgADIAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwB1AHIAcgBfAHAALAAgAEQAUgBPAFAAKABzAHQAYQB0AGUALAAgAGwAZQBuAF8AcQAgACsAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBDAG8AbQBwAGEAcgBlACgAYwB1AHIAcgBfAHAALAAgAGwAaQBtAGIAcwBfAGEAKQAgAD4AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGUAeAB0AF8AcQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBTAHUAYgAoAGMAdQByAHIAXwBxACwAIAB7ADEAfQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwBwACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAdQBiACgAYwB1AHIAcgBfAHAALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAFIATwBXAFMAKABuAGUAeAB0AF8AcQApACwAIABuAGUAeAB0AF8AcQAsACAAbgBlAHgAdABfAHAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAdABhAHQAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAUwB3AGUAZQBwACAAVQBwADoAIABJAGYAIABQACAAKwAgAEIAIAA8AD0AIABBACwAIABRACAAaQBzACAAdABvAG8AIABzAG0AYQBsAGwALgAgAFMAdABlAHAAIABRACAAdQBwACAAYgB5ACAAMQAsACAAYQBuAGQAIABQACAAdQBwACAAYgB5ACAAQgAuAFwAbgAgACAAIAAgACAAIAAgACAAcwB3AGUAZQBwAF8AdQBwACwAIABSAEUARABVAEMARQAoAHMAdwBlAGUAcABfAGQAbwB3AG4ALAAgAHsAMQA7ACAAMgB9ACwAIABMAEEATQBCAEQAQQAoAHMAdABhAHQAZQAsACAAaQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcQAsACAASQBOAEQARQBYACgAcwB0AGEAdABlACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAHUAcgByAF8AcQAsACAAQwBIAE8ATwBTAEUAUgBPAFcAUwAoAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABlAG4AXwBxACwAIAAxACwAIAAyACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwBwACwAIABEAFIATwBQACgAcwB0AGEAdABlACwAIABsAGUAbgBfAHEAIAArACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBlAHgAdABfAHAAXwB0AGUAcwB0ACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEEAZABkACgAYwB1AHIAcgBfAHAALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEMAbwBtAHAAYQByAGUAKABuAGUAeAB0AF8AcABfAHQAZQBzAHQALAAgAGwAaQBtAGIAcwBfAGEAKQAgADwAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQB4AHQAXwBxACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEEAZABkACgAYwB1AHIAcgBfAHEALAAgAHsAMQB9ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBTAFQAQQBDAEsAKABSAE8AVwBTACgAbgBlAHgAdABfAHEAKQAsACAAbgBlAHgAdABfAHEALAAgAG4AZQB4AHQAXwBwAF8AdABlAHMAdAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAdABlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAARgBpAG4AYQBsACAAUQAgAGEAbgBkACAAUABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAZQBuAF8AcQAsACAASQBOAEQARQBYACgAcwB3AGUAZQBwAF8AdQBwACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHEALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKABzAHcAZQBlAHAAXwB1AHAALAAgAFMARQBRAFUARQBOAEMARQAoAGYAaQBuAGEAbABfAGwAZQBuAF8AcQAsACAAMQAsACAAMgApACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHAALAAgAEQAUgBPAFAAKABzAHcAZQBlAHAAXwB1AHAALAAgAGYAaQBuAGEAbABfAGwAZQBuAF8AcQAgACsAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAA0AC4AIABFAHgAdAByAGEAYwB0ACAAVAByAHUAZQAgAFIAZQBtAGEAaQBuAGQAZQByACAAUwBhAGYAZQBsAHkAIAAoAEEAIAAtACAARgBpAG4AYQBsAF8AUAApAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBTAHUAYgAoAGwAaQBtAGIAcwBfAGEALAAgAGYAaQBuAGEAbABfAHAALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFYAUwBUAEEAQwBLACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABmAGkAbgBhAGwAXwByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAEIAYQBzAGUALQAxADAAIABMAGUAZgB0AC0AdABvAC0AUgBpAGcAaAB0ACAARQB4AHAAbwBuAGUAbgB0AGkAYQB0AGkAbwBuAC4AXABuACAAKgAgAEUAdgBhAGwAdQBhAHQAZQBzACAAdABoAGUAIABlAHgAcABvAG4AZQBuAHQAIABpAHQAZQByAGEAdABpAHYAZQBsAHkAIAB1AHMAaQBuAGcAIABhACAAcAByAGUALQBjAG8AbQBwAHUAdABlAGQAIAAxAC0AOQAgAGMAYQBjAGgAZQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAGIAYQBzAGUAIABUAGgAZQAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABsAGkAbQBiACAAYQByAHIAYQB5ACAAbwBmACAAdABoAGUAIABiAGEAcwBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAZQB4AHAAXwBzAHQAcgBpAG4AZwAgAFQAaABlACAAZQB4AGEAYwB0ACAAdABlAHgAdAAgAHMAdAByAGkAbgBnACAAbwBmACAAdABoAGUAIABlAHgAcABvAG4AZQBuAHQALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABrACAAVABoAGUAIABkAHkAbgBhAG0AaQBjACAAYwBoAHUAbgBrACAAcwBpAHoAZQAgAGMAbwBuAHQAZQB4AHQALgBcAG4AIAAqAC8AXABuAFUAUABvAHcAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBiAGEAcwBlACwAIABlAHgAcABfAHMAdAByAGkAbgBnACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFAAcgBlAC0AYwBvAG0AcAB1AHQAZQAgAHAAbwB3AGUAcgBzACAAMQAgAHQAaAByAG8AdQBnAGgAIAA5AC4AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQALAAgAGwAaQBtAGIAcwBfAGIAYQBzAGUALABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQBjAG8AbgBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAZgBpAHIAcwB0ACwAIABmAGkAcgBzAHQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABoAGkAcgBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAcwBlAGMAbwBuAGQALAAgAGYAaQByAHMAdAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABmAG8AdQByAHQAaAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAHMAZQBjAG8AbgBkACwAIABzAGUAYwBvAG4AZAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAZgB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABmAG8AdQByAHQAaAAsACAAZgBpAHIAcwB0ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQB4AHQAaAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAHQAaABpAHIAZAAsACAAdABoAGkAcgBkACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAZQB2AGUAbgB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABzAGkAeAB0AGgALAAgAGYAaQByAHMAdAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIABlAGkAZwB0AGgALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABmAG8AdQByAHQAaAAsACAAZgBvAHUAcgB0AGgALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBpAG4AdABoACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAZQBpAGcAdABoACwAIABmAGkAcgBzAHQALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAGUAeABwAF8AZABpAGcAaQB0AHMALAAgAC0ALQBNAEkARAAoAGUAeABwAF8AcwB0AHIAaQBuAGcALAAgAFMARQBRAFUARQBOAEMARQAoAEwARQBOACgAZQB4AHAAXwBzAHQAcgBpAG4AZwApACkALAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAFIARQBEAFUAQwBFACgAMQAsACAAZQB4AHAAXwBkAGkAZwBpAHQAcwAsACAATABBAE0AQgBEAEEAKABhAGMAYwAsACAAZABpAGcAaQB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBoAG8AcgB0AC0AYwBpAHIAYwB1AGkAdAA6ACAAUwBrAGkAcAAgAGMAYQBsAGMAdQBsAGEAdABpAG4AZwAgADEAXgAxADAAIABkAHUAcgBpAG4AZwAgAGwAZQBhAGQAaQBuAGcAIABpAHQAZQByAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAcwBfAG8AbgBlACwAIABBAE4ARAAoAFIATwBXAFMAKABhAGMAYwApACAAPQAgADEALAAgAEkATgBEAEUAWAAoAGEAYwBjACwAIAAxACwAIAAxACkAIAA9ACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAMQAuACAAUgBhAGkAcwBlACAAQQBjAGMAIAB0AG8AIAB0AGgAZQAgADEAMAB0AGgAIABwAG8AdwBlAHIAIAB1AHMAaQBuAGcAIABlAHgAYQBjAHQAbAB5ACAANAAgAG0AdQBsAHQAaQBwAGwAaQBjAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8AMQAwACwAIABJAEYAKABpAHMAXwBvAG4AZQAsACAAYQBjAGMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8AMgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGEAYwBjACwAIABhAGMAYwAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAYwBjAF8ANAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGEAYwBjAF8AMgAsACAAYQBjAGMAXwAyACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBjAGMAXwA4ACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAYQBjAGMAXwA0ACwAIABhAGMAYwBfADQALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAYQBjAGMAXwA4ACwAIABhAGMAYwBfADIALAAgAGsAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAyAC4AIABNAHUAbAB0AGkAcABsAHkAIABiAHkAIAB0AGgAZQAgAGMAbwByAHIAZQBzAHAAbwBuAGQAaQBuAGcAIABwAHIAZQAtAGMAbwBtAHAAdQB0AGUAZAAgAGMAYQBjAGgAZQAgAHYAYQBsAHUAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABkAGkAZwBpAHQAIAA9ACAAMAAsACAAYQBjAGMAXwAxADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAYQBjAGgAZQBfAHYAYQBsACwAIABDAEgATwBPAFMARQAoAGQAaQBnAGkAdAAsACAAZgBpAHIAcwB0ACwAIABzAGUAYwBvAG4AZAAsACAAdABoAGkAcgBkACwAIABmAG8AdQByAHQAaAAsACAAZgBpAGYAdABoACwAIABzAGkAeAB0AGgALAAgAHMAZQB2AGUAbgB0AGgALAAgAGUAaQBnAHQAaAAsACAAbgBpAG4AdABoACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAaQBzAF8AbwBuAGUALAAgAGMAYQBjAGgAZQBfAHYAYQBsACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACgAYQBjAGMAXwAxADAALAAgAGMAYQBjAGgAZQBfAHYAYQBsACwAIABrACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFUAbgBzAGkAZwBuAGUAZAAgAEkAbgB0AGUAZwBlAHIAIABTAHEAdQBhAHIAZQAgAFIAbwBvAHQAIAB1AHMAaQBuAGcAIABOAGUAdwB0AG8AbgAnAHMAIABNAGUAdABoAG8AZAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGwAaQBtAGIAcwBfAG4AIABSAGEAZABpAGMAYQBuAGQAIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAbABpAG0AYgBzAF8AcwBlAGUAZAAgAE8AdgBlAHIALQBlAHMAdABpAG0AYQB0AGUAZAAgAGwAaQB0AHQAbABlAC0AZQBuAGQAaQBhAG4AIABzAGUAZQBkACAAYQByAHIAYQB5AC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAawAgAFQAaABlACAAZAB5AG4AYQBtAGkAYwAgAGMAaAB1AG4AawAgAHMAaQB6AGUAIABjAG8AbgB0AGUAeAB0AC4AXABuACAAKgAvAFwAbgBVAFMAcQByAHQAIAA9ACAATABBAE0AQgBEAEEAKABsAGkAbQBiAHMAXwBuACwAIABsAGkAbQBiAHMAXwBzAGUAZQBkACwAIABrACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAdABhAHQAZQAgAGkAcwAgAHAAYQBjAGsAZQBkADoAIABWAFMAVABBAEMASwAoAGkAcwBfAGQAbwBuAGUAXwBmAGwAYQBnACwAIABjAHUAcgByAGUAbgB0AF8AeAApAFwAbgAgACAAIAAgACAAIAAgACAAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAVgBTAFQAQQBDAEsAKAAwACwAIABsAGkAbQBiAHMAXwBzAGUAZQBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQB4AF8AaQB0AGUAcgBzACwAIAAzADUALABcAG4AXABuACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAHQAYQB0AGUALAAgAFIARQBEAFUAQwBFACgAaQBuAGkAdABpAGEAbABfAHMAdABhAHQAZQAsACAAUwBFAFEAVQBFAE4AQwBFACgAbQBhAHgAXwBpAHQAZQByAHMAKQAsACAATABBAE0AQgBEAEEAKABzAHQAYQB0AGUALAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAHMAXwBkAG8AbgBlACwAIABJAE4ARABFAFgAKABzAHQAYQB0AGUALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAdQByAHIAXwB4ACwAIABEAFIATwBQACgAcwB0AGEAdABlACwAIAAxACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAaQBzAF8AZABvAG4AZQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB0AGEAdABlACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAxAC4AIABEAGkAdgBpAHMAaQBvAG4AOgAgAG4AIAAvACAAeABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZABpAHYAXwBwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ARABpAHYAUgBvAHUAdABlAHIAKABsAGkAbQBiAHMAXwBuACwAIABjAHUAcgByAF8AeAAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AcgAsACAASQBOAEQARQBYACgAZABpAHYAXwBwAGEAYwBrAGUAZAAsACAAMQAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHEALAAgAEQAUgBPAFAAKABkAGkAdgBfAHAAYQBjAGsAZQBkACwAIABsAGUAbgBfAHIAIAArACAAMQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAyAC4AIABBAGQAZABpAHQAaQBvAG4AOgAgAHgAIAArACAAKABuACAALwAgAHgAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwB1AG0AXwB4AHEALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQQBkAGQAKABjAHUAcgByAF8AeAAsACAAcQAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAAzAC4AIABIAGEAbAB2AGkAbgBnADoAIAAoAHgAIAArACAAKABuACAALwAgAHgAKQApACAALwAgADIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEsAbgB1AHQAaABEAGkAdgAgAGkAbgBoAGUAcgBlAG4AdABsAHkAIABzAHUAcABwAG8AcgB0AHMAIABzAGMAYQBsAGEAcgAgAGQAaQB2AGkAcwBvAHIAcwAgAHcAaQB0AGgAIAB6AGUAcgBvACAAbwB2AGUAcgBoAGUAYQBkAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGkAdgBfADIAXwBwAGEAYwBrAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2ACgAcwB1AG0AXwB4AHEALAAgAHsAMgB9ACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwByADIALAAgAEkATgBEAEUAWAAoAGQAaQB2AF8AMgBfAHAAYQBjAGsAZQBkACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAeABfAG4AZQB4AHQALAAgAEQAUgBPAFAAKABkAGkAdgBfADIAXwBwAGEAYwBrAGUAZAAsACAAbABlAG4AXwByADIAIAArACAAMQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIAA0AC4AIABDAG8AbgB2AGUAcgBnAGUAbgBjAGUAIABDAGgAZQBjAGsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQwBvAG0AcABhAHIAZQAoAHgAXwBuAGUAeAB0ACwAIABjAHUAcgByAF8AeAApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABOAGUAdwB0AG8AbgAnAHMAIABtAGUAdABoAG8AZAAgAGMAbwBuAHYAZQByAGcAZQBzACAAbwBuACAAdABoAGUAIABmAGwAbwBvAHIAIAByAG8AbwB0ACwAIABhAG4AZAAgAHMAdABhAGIAaQBsAGkAegBlAHMAIABvAHIAIABvAHMAYwBpAGwAbABhAHQAZQBzACAAdQBwACAAYgB5ACAAMQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABUAGgAZQByAGUAZgBvAHIAZQAsACAAaQBmACAAeABfAG4AZQB4AHQAIAA+AD0AIABjAHUAcgByAF8AeAAsACAAdABoAGUAIABhAGwAZwBvAHIAaQB0AGgAbQAgAGgAYQBzACAAYwBvAG4AdgBlAHIAZwBlAGQALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYwBvAG0AcAAgAD4APQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADEALAAgAGMAdQByAHIAXwB4ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoADAALAAgAHgAXwBuAGUAeAB0ACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABEAFIATwBQACgAZgBpAG4AYQBsAF8AcwB0AGEAdABlACwAIAAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABHAGUAbgBlAHIAYQB0AGUAcwAgAGEAIAAxAEQAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkAIABvAGYAIABhAGwAbAAgAHAAcgBpAG0AZQAgAG4AdQBtAGIAZQByAHMAIAB1AHAAIAB0AG8AIABuAC4AXABuACAAKgAgAEUAdgBhAGwAdQBhAHQAZQBzACAAcAB1AHIAZQBsAHkAIABpAG4AIABuAGEAdABpAHYAZQAgAEMAKwArACAAdQBzAGkAbgBnACAAYQAgAGQAeQBuAGEAbQBpAGMAIABzAGkAZQB2AGUALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABuACAAVABoAGUAIAB1AHAAcABlAHIAIABiAG8AdQBuAGQAIABpAG4AdABlAGcAZQByACAAKABhAHMAcwB1AG0AZQBkACAAPAA9ACAAOQAyADcAMwApAC4AXABuACAAKgAvAFwAbgBOAGEAdABpAHYAZQBQAHIAaQBtAGUAcwAgAD0AIABMAEEATQBCAEQAQQAoAG4ALABcAG4AIAAgACAAIABJAEYAKABuACAAPAAgADIALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBlAHEALAAgAFMARQBRAFUARQBOAEMARQAoAG4AIAAtACAAMQAsACAAMQAsACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAcwBlAHEALAAgAE0AQQBQACgAcwBlAHEALAAgAEwAQQBNAEIARABBACgAeAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBpAHQALAAgAEkATgBUACgAUwBRAFIAVAAoAHgAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABsAGkAbQBpAHQAIAA8ACAAMgAsACAAVABSAFUARQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAE0ATwBEACgAeAAsACAAUwBFAFEAVQBFAE4AQwBFACgAbABpAG0AaQB0ACAALQAgADEALAAgADEALAAgADIAKQApACkAIAA+ACAAMABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABbAEkAbgB0AGUAcgBuAGEAbABdACAAVQBuAHMAYQBmAGUALAAgAGgAaQBnAGgALQBwAGUAcgBmAG8AcgBtAGEAbgBjAGUAIAB0AGUAeAB0ACAAbQB1AGwAdABpAHAAbABpAGMAYQB0AGkAbwBuACAAZgBvAHIAIAB0AHIAdQBzAHQAZQBkACwAIABwAG8AcwBpAHQAaQB2AGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqACAAQgB5AHAAYQBzAHMAZQBzACAATABhAHkAZQByACAAMAAgAHYAYQBsAGkAZABhAHQAaQBvAG4ALgAgAEkAbQBwAGwAZQBtAGUAbgB0AHMAIABzAHQAcgBpAGMAdAAgAHMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAcwAgAGYAbwByACAAcABhAGQAZABpAG4AZwAgAG8AcAB0AGkAbQBpAHoAYQB0AGkAbwBuAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAcwB0AHIAXwBhACAAVABoAGUAIABmAGkAcgBzAHQAIAB0AHIAdQBzAHQAZQBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHMAdAByAF8AYgAgAFQAaABlACAAcwBlAGMAbwBuAGQAIAB0AHIAdQBzAHQAZQBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AVQBUAGUAeAB0AE0AdQBsACAAPQAgAEwAQQBNAEIARABBACgAcwB0AHIAXwBhACwAIABzAHQAcgBfAGIALABcAG4AIAAgACAAIABJAEYAKABPAFIAKABzAHQAcgBfAGEAIAA9ACAAXAAiADAAXAAiACwAIABzAHQAcgBfAGIAIAA9ACAAXAAiADAAXAAiACkALAAgAFwAIgAwAFwAIgAsAFwAbgAgACAAIAAgAEkARgAoAHMAdAByAF8AYQAgAD0AIABcACIAMQBcACIALAAgAHMAdAByAF8AYgAsAFwAbgAgACAAIAAgAEkARgAoAHMAdAByAF8AYgAgAD0AIABcACIAMQBcACIALAAgAHMAdAByAF8AYQAsAFwAbgAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwBhACwAIABMAEUATgAoAHMAdAByAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAATABFAE4AKABzAHQAcgBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIATQBVAEwAXAAiACwAIABNAEkATgAoAGwAZQBuAF8AYQAsACAAbABlAG4AXwBiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAcwB0AHIAXwBhACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAcwB0AHIAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAHUAbAAoAGwAaQBtAGIAcwBfAGEALAAgAGwAaQBtAGIAcwBfAGIALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAKQApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAFYAZQBjAHQAbwByAGkAegBlAGQAIABsAG8AZwBhAHIAaQB0AGgAbQBpAGMAIABwAHIAbwBkAHUAYwB0ACAAbwBmACAAYQBuACAAYQByAHIAYQB5ACAAbwBmACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAKgAgAFIAZQBjAHUAcgBzAGkAdgBlAGwAeQAgAGMAdQB0AHMAIAB0AGgAZQAgAGEAcgByAGEAeQAgAGkAbgAgAGgAYQBsAGYAIAB0AG8AIABiAHkAcABhAHMAcwAgAFIARQBEAFUAQwBFACAAcwBlAHEAdQBlAG4AdABpAGEAbAAgAG0AZQBtAG8AcgB5ACAAYQBsAGwAbwBjAGEAdABpAG8AbgBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAdABlAHgAdABfAGEAcgByACAAQQAgADEARAAgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoALwBcAG4AVABlAHgAdABUAHIAZQBlAFAAcgBvAGQAIAA9ACAATABBAE0AQgBEAEEAKAB0AGUAeAB0AF8AYQByAHIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgAsACAAUgBPAFcAUwAoAHQAZQB4AHQAXwBhAHIAcgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AIAA9ACAAMQAsACAASQBOAEQARQBYACgAdABlAHgAdABfAGEAcgByACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAcwBoAGEAcABlACAAYQByAHIAYQB5ACAAaQBuAHQAbwAgAHAAYQBpAHIAcwAuACAATwBkAGQALQBsAGUAbgBnAHQAaAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABzAGEAZgBlAGwAeQAgAHAAYQBkAGQAZQBkACAAdwBpAHQAaAAgAHQAaABlACAAbQB1AGwAdABpAHAAbABpAGMAYQB0AGkAdgBlACAAaQBkAGUAbgB0AGkAdAB5ACAAXAAiADEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAYQBpAHIAZQBkACwAIABXAFIAQQBQAFIATwBXAFMAKAB0AGUAeAB0AF8AYQByAHIALAAgADIALAAgAFwAIgAxAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAVgBlAGMAdABvAHIAaQB6AGUAZAAgAG0AdQBsAHQAaQBwAGwAaQBjAGEAdABpAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABwAGEAaQByAHMAIABzAGkAbQB1AGwAdABhAG4AZQBvAHUAcwBsAHkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBlAHgAdABfAGEAcgByACwAIABCAFkAUgBPAFcAKABwAGEAaQByAGUAZAAsACAATABBAE0AQgBEAEEAKAByAG8AdwAsACAAVQBUAGUAeAB0AE0AdQBsACgASQBOAEQARQBYACgAcgBvAHcALAAgADEALAAgADEAKQAsACAASQBOAEQARQBYACgAcgBvAHcALAAgADEALAAgADIAKQApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABhAGwAbABvAHcAIAByAGUAYwB1AHIAcwBpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBUAGUAeAB0AFQAcgBlAGUAUAByAG8AZAAoAG4AZQB4AHQAXwBhAHIAcgApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEMAYQBsAGMAdQBsAGEAdABlAHMAIAB0AGgAZQAgAGUAeABwAG8AbgBlAG4AdAAgAGYAbwByACAAYQBuACAAYQByAHIAYQB5ACAAbwBmACAAcAByAGkAbQBlAHMAIABpAG4AIAB0AGgAZQAgAFMAdwBpAG4AZwAgAHQAZQByAG0AIABvAGYAIABhACAAZgBhAGMAdABvAHIAaQBhAGwALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABuACAAVABoAGUAIABjAHUAcgByAGUAbgB0ACAAZgBhAGMAdABvAHIAaQBhAGwAIABtAGEAZwBuAGkAdAB1AGQAZQAgACgAPAA9ACAAOQAyADcAMwApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAcAByAGkAbQBlAHMAIABBACAAdgBlAHIAdABpAGMAYQBsACAAYQByAHIAYQB5ACAAbwBmACAAcAByAGkAbQBlACAAbgB1AG0AYgBlAHIAcwAgACgAPAA9ACAAbgApAC4AXABuACAAKgAvAFwAbgBOAGEAdABpAHYAZQBTAHcAaQBuAGcARQB4AHAAbwBuAGUAbgB0AHMAIAA9ACAATABBAE0AQgBEAEEAKABuACwAIABwAHIAaQBtAGUAcwAsAFwAbgAgACAAIAAgAE0AQQBQACgAcAByAGkAbQBlAHMALAAgAEwAQQBNAEIARABBACgAcAAsAFwAbgAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAHgAXwBrACwAIABJAE4AVAAoAEwATwBHACgAbgAsACAAcAApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABvAHcAZQByAHMALAAgAHAAIABeACAAUwBFAFEAVQBFAE4AQwBFACgAbQBhAHgAXwBrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAE0AKABNAE8ARAAoAEkATgBUACgAbgAgAC8AIABwAG8AdwBlAHIAcwApACwAIAAyACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAWwBJAG4AdABlAHIAbgBhAGwAXQAgAEMAYQBsAGMAdQBsAGEAdABlAHMAIAB0AGgAZQAgAG0AYQBzAHMAaQB2AGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnACAAZgBvAHIAIAB0AGgAZQAgAFMAdwBpAG4AZwAgAHQAZQByAG0AIABvAGYAIABhACAAZgBhAGMAdABvAHIAaQBhAGwALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABuACAAVABoAGUAIABjAHUAcgByAGUAbgB0ACAAZgBhAGMAdABvAHIAaQBhAGwAIABtAGEAZwBuAGkAdAB1AGQAZQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHQAaQBlAHIAXwBwAHIAaQBtAGUAcwAgAEEAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkAIABvAGYAIABwAHIAaQBtAGUAIABuAHUAbQBiAGUAcgBzACAAKAA8AD0AIABuACkALgBcAG4AIAAqAC8AXABuAFMAdwBpAG4AZwBUAGUAcgBtACAAPQAgAEwAQQBNAEIARABBACgAbgAsACAAdABpAGUAcgBfAHAAcgBpAG0AZQBzACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAGUAeABwAG8AbgBlAG4AdABzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBOAGEAdABpAHYAZQBTAHcAaQBuAGcARQB4AHAAbwBuAGUAbgB0AHMAKABuACwAIAB0AGkAZQByAF8AcAByAGkAbQBlAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AZwByAGUAYQB0AGUAcgBfAHQAaABhAG4AXwB6AGUAcgBvACwAIABlAHgAcABvAG4AZQBuAHQAcwAgAD4AIAAwACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEkAZgAgAGEAbABsACAAZQB4AHAAbwBuAGUAbgB0AHMAIABhAHIAZQAgADAALAAgAHQAaABlACAAcwB3AGkAbgBnACAAdABlAHIAbQAgAGkAcwAgADEALgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEEATgBEACgATgBPAFQAKABpAHMAXwBnAHIAZQBhAHQAZQByAF8AdABoAGEAbgBfAHoAZQByAG8AKQApACwAIABcACIAMQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbAB0AGUAcgBlAGQAXwBwAHIAaQBtAGUAcwAsACAARgBJAEwAVABFAFIAKAB0AGkAZQByAF8AcAByAGkAbQBlAHMALAAgAGkAcwBfAGcAcgBlAGEAdABlAHIAXwB0AGgAYQBuAF8AegBlAHIAbwApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAGwAdABlAHIAZQBkAF8AZQB4AHAAcwAsACAARgBJAEwAVABFAFIAKABlAHgAcABvAG4AZQBuAHQAcwAsACAAaQBzAF8AZwByAGUAYQB0AGUAcgBfAHQAaABhAG4AXwB6AGUAcgBvACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAHIAaQBtAGUAXwBwAG8AdwBlAHIAcwAsACAATQBBAFAAKABmAGkAbAB0AGUAcgBlAGQAXwBwAHIAaQBtAGUAcwAsACAAZgBpAGwAdABlAHIAZQBkAF8AZQB4AHAAcwAsACAATABBAE0AQgBEAEEAKABwACwAIABlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGUAIAA9ACAAMQAsACAAcAAgACYAIABcACIAXAAiACwAIABCAGkAZwBJAG4AdAAuAFAAbwB3ACgAcAAgACYAIABcACIAXAAiACwAIABlACAAJgAgAFwAIgBcACIAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFQAZQB4AHQAVAByAGUAZQBQAHIAbwBkACgAcAByAGkAbQBlAF8AcABvAHcAZQByAHMAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABSAGUAYwB1AHIAcwBpAHYAZQAgAHQAbwBwAC0AZABvAHcAbgAgAEwAQQBNAEIARABBACAAYwBhAGwAYwB1AGwAYQB0AGkAbgBnACAAdABoAGUAIABQAHIAaQBtAGUAIABTAHcAaQBuAGcAIABmAGEAYwB0AG8AcgBpAGEAbAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG4AIABUAGgAZQAgAGMAdQByAHIAZQBuAHQAIABmAGEAYwB0AG8AcgBpAGEAbAAgAG0AYQBnAG4AaQB0AHUAZABlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAZwBsAG8AYgBhAGwAXwBwAHIAaQBtAGUAcwAgAFQAaABlACAAdQBuAGkAZgBpAGUAZAAgAHYAZQByAHQAaQBjAGEAbAAgAGEAcgByAGEAeQAgAG8AZgAgAGEAbABsACAAcAByAGkAbQBlAHMAIAB1AHAAIAB0AG8AIAB0AGgAZQAgAHQAYQByAGcAZQB0ACAAZgBhAGMAdABvAHIAaQBhAGwALgBcAG4AIAAqAC8AXABuAFAAcgBpAG0AZQBTAHcAaQBuAGcASwBlAHIAbgBlAGwAIAA9ACAATABBAE0AQgBEAEEAKABuACwAIABnAGwAbwBiAGEAbABfAHAAcgBpAG0AZQBzACwAXABuACAAIAAgACAASQBGACgAbgAgADwAIAAyACwAIABcACIAMQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGgAYQBsAGYAXwBuACwAIABJAE4AVAAoAG4AIAAvACAAMgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGgAYQBsAGYAXwBmAGEAYwB0ACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBQAHIAaQBtAGUAUwB3AGkAbgBnAEsAZQByAG4AZQBsACgAaABhAGwAZgBfAG4ALAAgAGcAbABvAGIAYQBsAF8AcAByAGkAbQBlAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBxAHUAYQByAGUAIAB0AGgAZQAgAGgAYQBsAGYAdwBhAHkAIABwAG8AaQBuAHQAIAB1AHMAaQBuAGcAIAB0AGgAZQAgAHUAbgBzAGEAZgBlACAAawBlAHIAbgBlAGwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAcQB1AGEAcgBlAGQAXwBoAGEAbABmACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFQAZQB4AHQATQB1AGwAKABoAGEAbABmAF8AZgBhAGMAdAAsACAAaABhAGwAZgBfAGYAYQBjAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAASQBzAG8AbABhAHQAZQAgAHQAaABlACAAcAByAGkAbQBlAHMAIABuAGUAZQBkAGUAZAAgAGYAbwByACAAdABoAGkAcwAgAHQAaQBlAHIAIABhAG4AZAAgAGMAYQBsAGMAdQBsAGEAdABlACAAdABoAGUAIABzAHcAaQBuAGcAIAB0AGUAcgBtAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGkAZQByAF8AcAByAGkAbQBlAHMALAAgAEYASQBMAFQARQBSACgAZwBsAG8AYgBhAGwAXwBwAHIAaQBtAGUAcwAsACAAZwBsAG8AYgBhAGwAXwBwAHIAaQBtAGUAcwAgADwAPQAgAG4AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAHcAaQBuAGcALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAdwBpAG4AZwBUAGUAcgBtACgAbgAsACAAdABpAGUAcgBfAHAAcgBpAG0AZQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAVABlAHgAdABNAHUAbAAoAHMAcQB1AGEAcgBlAGQAXwBoAGEAbABmACwAIABzAHcAaQBuAGcAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsASQBuAHQAZQByAG4AYQBsAF0AIABSAGUAYwB1AHIAcwBpAHYAZQAgAHQAbwB1AHIAbgBhAG0AZQBuAHQAIAB0AHIAZQBlACAAZgBvAHIAIABNAGkAbgAvAE0AYQB4ACAAZQB2AGEAbAB1AGEAdABpAG8AbgBzAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYwBvAGwAIABBACAAMQBEACAAdgBlAHIAdABpAGMAYQBsACAAYQByAHIAYQB5ACAAbwBmACAAbgBvAHIAbQBhAGwAaQB6AGUAZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAG0AbwBkAGUAIAAxACAAZgBvAHIAIABNAGEAeABpAG0AdQBtACwAIAAtADEAIABmAG8AcgAgAE0AaQBuAGkAbQB1AG0ALgBcAG4AIAAqAC8AXABuAFQAcgBlAGUAQwBvAG0AcABhAHIAZQAgAD0AIABMAEEATQBCAEQAQQAoAGMAbwBsACwAIABtAG8AZABlACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4ALAAgAFIATwBXAFMAKABjAG8AbAApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AIAA9ACAAMQAsACAASQBOAEQARQBYACgAYwBvAGwALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAYQBpAHIAZQBkACwAIABXAFIAQQBQAFIATwBXAFMAKABjAG8AbAAsACAAMgAsACAAXAAiACMAUABBAEQAIwBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBsAF8AYQAsACAAVABBAEsARQAoAHAAYQBpAHIAZQBkACwAIAAsACAAMQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAGwAXwBiACwAIABUAEEASwBFACgAcABhAGkAcgBlAGQALAAgACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHcAaQBuAG4AZQByAHMALAAgAE0AQQBQACgAYwBvAGwAXwBhACwAIABjAG8AbABfAGIALAAgAEwAQQBNAEIARABBACgAYQAsACAAYgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAYgAgAD0AIABcACIAIwBQAEEARAAjAFwAIgAsACAAYQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwBtAHAALAAgAEIAaQBnAEkAbgB0AC4AQwBvAG0AcABhAHIAZQAoAGEALAAgAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGMAbwBtAHAAIAAqACAAbQBvAGQAZQAgAD4APQAgADAALAAgAGEALAAgAGIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVAByAGUAZQBDAG8AbQBwAGEAcgBlACgAdwBpAG4AbgBlAHIAcwAsACAAbQBvAGQAZQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBCAGkAZwBJAG4AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAFwAbgAvAC8AIABCAGkAZwAgAEkAbgB0AGUAZwBlAHIAIABBAHIAaQB0AGgAbQBlAHQAaQBjACAATABpAGIAcgBhAHIAeQAgAC8ALwBcAG4ALwAvACAAIAAgACAAIAAgACAAIABCAGkAZwBJAG4AdAAgAE0AbwBkAHUAbABlACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAgAFAAdQBiAGwAaQBjACAAQQBQAEkAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvAFwAbgAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwAvAC8ALwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABOAG8AcgBtAGEAbABpAHMAZQBzACAAYQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgAgAFMAdAByAGkAcABzACAAbABlAGEAZABpAG4AZwAgAHoAZQByAG8AcwAsACAAcgBlAHMAbwBsAHYAZQBzACAAXAAiAC0AMABcACIAIAB0AG8AIABcACIAMABcACIALAAgAGEAbgBkACAAdABoAHIAbwB3AHMAIAAjAFYAQQBMAFUARQAhACAAbwBuACAAaQBuAHYAYQBsAGkAZAAgAGMAaABhAHIAYQBjAHQAZQByAHMALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBOAG8AcgBtACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABzAHQAcgAsACAASQBGACgATwBSACgASQBTAE8ATQBJAFQAVABFAEQAKABiAGkAZwBfAGkAbgB0ACkALAAgAGIAaQBnAF8AaQBuAHQAIAA9ACAAXAAiAFwAIgApACwAIABcACIAMABcACIALAAgAGIAaQBnAF8AaQBuAHQAIAAmACAAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABpAHMAXwB2AGEAbABpAGQALAAgAFIARQBHAEUAWABUAEUAUwBUACgAcwB0AHIALAAgAFwAIgBeAC0APwBcAFwAZAArACQAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdAByAGkAcABwAGUAZAAsACAAUgBFAEcARQBYAFIARQBQAEwAQQBDAEUAKABzAHQAcgAsACAAXAAiAF4AKAAtAD8AKQAwACsAKAA/AD0AXABcAGQAKQBcACIALAAgAFwAIgAkADEAXAAiACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABOAE8AVAAoAGkAcwBfAHYAYQBsAGkAZAApACwAIABWAEEATABVAEUAKABcACIAIwBWAEEATABVAEUAIQBcACIAKQAsACAASQBGACgAcwB0AHIAaQBwAHAAZQBkACAAPQAgAFwAIgAtADAAXAAiACwAIABcACIAMABcACIALAAgAHMAdAByAGkAcABwAGUAZAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFIAZQB0AHUAcgBuAHMAIAB0AGgAZQAgAHMAaQBnAG4AIABvAGYAIABhACAAQgBpAGcASQBuAHQAOgAgADEAIAAoAHAAbwBzAGkAdABpAHYAZQApACwAIAAtADEAIAAoAG4AZQBnAGEAdABpAHYAZQApACwAIABvAHIAIAAwACAAKAB6AGUAcgBvACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBTAGkAZwBuACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsACAAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AZQBkACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIABTAFcASQBUAEMASAAoAEwARQBGAFQAKABuAG8AcgBtAGUAZAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAwAFwAIgAsACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAC0AMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvAC8AIAAtAC0ALQAgAFAAcgBlAGQAaQBjAGEAdABlAHMAIAAtAC0ALQAgAFwAXABcAFwAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAFQAUgBVAEUAIABpAGYAIAB0AGgAZQAgAEIAaQBnAEkAbgB0ACAAaQBzACAAZQB4AGEAYwB0AGwAeQAgAHoAZQByAG8ALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBJAHMAWgBlAHIAbwAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0ACkAIAA9ACAAXAAiADAAXAAiACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAVABSAFUARQAgAGkAZgAgAHQAaABlACAAQgBpAGcASQBuAHQAIABpAHMAIABuAGUAZwBhAHQAaQB2AGUALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0ACAAVABoAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBJAHMATgBlAGcAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAIABMAEUARgBUACgATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAKQApACAAPQAgAFwAIgAtAFwAIgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAFQAUgBVAEUAIABpAGYAIAB0AGgAZQAgAEIAaQBnAEkAbgB0ACAAaQBzACAAZQB2AGUAbgAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAIABUAGgAZQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEkAcwBFAHYAZQBuACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdAAsACAASQBTAEUAVgBFAE4AKABWAEEATABVAEUAKABSAEkARwBIAFQAKABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACkAKQApACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAVABSAFUARQAgAGkAZgAgAHQAaABlACAAQgBpAGcASQBuAHQAIABpAHMAIABvAGQAZAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAIABUAGgAZQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEkAcwBPAGQAZAAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALAAgAEkAUwBPAEQARAAoAFYAQQBMAFUARQAoAFIASQBHAEgAVAAoAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0ACkAKQApACkAKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFIAZQB0AHUAcgBuAHMAIAB0AGgAZQAgAHUAbgBzAGkAZwBuAGUAZAAgAG0AYQBnAG4AaQB0AHUAZABlACAAbwBmACAAYQAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAIAAoAGEAYgBzAG8AbAB1AHQAZQAgAHYAYQBsAHUAZQApAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AQQBiAHMAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAIABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgB1AG0ALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwARQBGAFQAKABuAHUAbQApACAAPQAgAFwAIgAtAFwAIgAsACAATQBJAEQAKABuAHUAbQAsACAAMgAsACAATABFAE4AKABuAHUAbQApACAALQAgADEAKQAsACAAbgB1AG0AKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAQwBvAG0AcABhAHIAZQBzACAAdAB3AG8AIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMALgAgAFIAZQB0AHUAcgBuAHMAIAAxACAAKABhACAAPgAgAGIAKQAsACAALQAxACAAKABhACAAPAAgAGIAKQAsACAAbwByACAAMAAgACgAYQAgAD0AIABiACkALgBcAG4AIAAqACAARQB2AGEAbAB1AGEAdABlAHMAIABzAGkAZwBuAHMAIABhAG4AZAAgAGwAZQBuAGcAdABoAHMALgAgAEkAZgAgAGkAZABlAG4AdABpAGMAYQBsACwAIABkAGUAbABlAGcAYQB0AGUAcwAgAHQAbwAgAG4AYQB0AGkAdgBlACAAbABpAG0AYgAgAGEAcgByAGEAeQAgAGMAbwBtAHAAYQByAGkAcwBvAG4ALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZgBpAHIAcwB0ACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABzAGUAYwBvAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAEMAbwBtAHAAYQByAGUAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGEALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBhACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgAsACAAQgBpAGcAaQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAHMAaQBnAG4AXwBhACAAPAA+ACAAcwBpAGcAbgBfAGIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBJAEcATgAoAHMAaQBnAG4AXwBhACAALQAgAHMAaQBnAG4AXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAcwBpAGcAbgBfAGEAIAA9ACAAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABlAG4AXwBhACwAIABMAEUATgAoAG4AbwByAG0AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAATABFAE4AKABuAG8AcgBtAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGwAZQBuAF8AYQAgADwAPgAgAGwAZQBuAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEkARwBOACgAbABlAG4AXwBhACAALQAgAGwAZQBuAF8AYgApACAAKgAgAHMAaQBnAG4AXwBhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEEARABEAFwAIgApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBhACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGEAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBiACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AYQBnAF8AYwBvAG0AcABhAHIAaQBzAG8AbgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBDAG8AbQBwAGEAcgBlACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBhAGcAXwBjAG8AbQBwAGEAcgBpAHMAbwBuACAAKgAgAHMAaQBnAG4AXwBhAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIAAtACAAQQBkAGQAaQB0AGkAbwBuACAAJgAgAFMAdQBiAHQAcgBhAGMAdABpAG8AbgAgAC0AIAAgACAAIAAgACAAIABcAFwAXABcAFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEEAZABkAHMAIAB0AHcAbwAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBhACAAVABoAGUAIABmAGkAcgBzAHQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGIAIABUAGgAZQAgAHMAZQBjAG8AbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4AQQBkAGQAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGEALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBhACwAIABCAGkAZwBpAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIAQQBEAEQAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGEALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYQApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYgApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHUAdABlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEEAZABkAFMAdQBiAFIAbwB1AHQAZQByACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAcwBpAGcAbgBfAGEALAAgAHMAaQBnAG4AXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAaQBnAG4ALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKAByAG8AdQB0AGUAZAAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAARABSAE8AUAAoAHIAbwB1AHQAZQBkACwAIAAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABtAGUAcgBnAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAFwAIgAtAFwAIgAgACYAIABtAGUAcgBnAGUAZAAsACAAbQBlAHIAZwBlAGQAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUwB1AGIAdAByAGEAYwB0AHMAIAB0AGgAZQAgAHMAZQBjAG8AbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAGYAaQByAHMAdAAgACgAQQAgAC0AIABCACkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAbQBpAG4AdQBlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAcwB1AGIAdAByAGEAaABlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAFMAdQBiACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBiACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdABfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABJAG4AdgBlAHIAdAAgAHQAaABlACAAcwBpAGcAbgAgAG8AZgAgAEIAIABhAHQAIAB0AGgAZQAgAHQAZQB4AHQAIABsAGUAdgBlAGwAXABuACAAIAAgACAAIAAgACAAIABpAG4AdgBfAGIALAAgAEkARgAoAG4AbwByAG0AXwBiACAAPQAgAFwAIgAwAFwAIgAsACAAXAAiADAAXAAiACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATABFAEYAVAAoAG4AbwByAG0AXwBiACkAIAA9ACAAXAAiAC0AXAAiACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkARAAoAG4AbwByAG0AXwBiACwAIAAyACwAIABMAEUATgAoAG4AbwByAG0AXwBiACkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACAAJgAgAG4AbwByAG0AXwBiAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABQAGEAcwBzACAAdABvACAAQQBkAGQAXABuACAAIAAgACAAIAAgACAAIABBAGQAZAAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABpAG4AdgBfAGIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUwB1AG0AcwAgAGEAbgAgAGEAcgByAGEAeQAgAG8AcgAgAHIAYQBuAGcAZQAgAG8AZgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAgAHYAaQBhACAAdgBlAGMAdABvAHIAaQB6AGUAZAAgAGcAcgBvAHUAcAAgAG0AYQB0AHIAaQBjAGUAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHIAYQBuAGcAZQAgAEEAIABjAG8AbgB0AGkAZwB1AG8AdQBzACAAcgBhAG4AZwBlACAAbwByACAAYQByAHIAYQB5ACAAbwBmACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAKgAvAFwAbgBTAHUAbQAgAD0AIABMAEEATQBCAEQAQQAoAHIAYQBuAGcAZQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABmAGwAYQB0ACwAIABUAE8AUgBPAFcAKAByAGEAbgBnAGUALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABJAFMARQBSAFIATwBSACgAZgBsAGEAdAApACwAIABDAE8ATABVAE0ATgBTACgAZgBsAGEAdAApACAAPQAgADAAKQAsACAAXAAiADAAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBzACwAIABNAEEAUAAoAGYAbABhAHQALAAgAEwAQQBNAEIARABBACgAeAAsACAATgBvAHIAbQAoAHgAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABzAGkAZwBuAHMALAAgAE0AQQBQACgATABFAEYAVAAoAG4AbwByAG0AcwApACwAIABMAEEATQBCAEQAQQAoAHgALAAgAEkARgAoAHgAIAA9ACAAXAAiADAAXAAiACwAIAAwACwAIABpAGYAKAB4ACAAPQAgAFwAIgAtAFwAIgAsACAALQAxACwAIAAxACkAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhAGIAcwBfAG4AbwByAG0AcwAsACAATQBBAFAAKABuAG8AcgBtAHMALAAgAHMAaQBnAG4AcwAsACAATABBAE0AQgBEAEEAKAB4ACwAIABzAGkAZwBuACwAIABJAEYAKABzAGkAZwBuACAAPQAgAC0AMQAsACAATQBJAEQAKAB4ACwAIAAyACwAIABMAEUATgAoAHgAKQAtADEAKQAsACAAeAApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAbwBzAF8AcwB0AHIAcwAsACAARgBJAEwAVABFAFIAKABhAGIAcwBfAG4AbwByAG0AcwAsACAAcwBpAGcAbgBzACAAPQAgADEALAAgAHsAXAAiADAAXAAiAH0AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQBnAF8AcwB0AHIAcwAsACAARgBJAEwAVABFAFIAKABhAGIAcwBfAG4AbwByAG0AcwAsACAAcwBpAGcAbgBzACAAPQAgAC0AMQAsACAAewBcACIAMABcACIAfQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdQBuAGkAZgBpAGUAZABfAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBBAEQARABcACIALAAgAEMATwBMAFUATQBOAFMAKABmAGwAYQB0ACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAbwBzAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AYQB0AHIAaQB4AFMAdQBtACgAcABvAHMAXwBzAHQAcgBzACwAIAB1AG4AaQBmAGkAZQBkAF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbgBlAGcAXwBsAGkAbQBiAHMALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQBhAHQAcgBpAHgAUwB1AG0AKABuAGUAZwBfAHMAdAByAHMALAAgAHUAbgBpAGYAaQBlAGQAXwBrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAG8AdQB0AGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AQQBkAGQAUwB1AGIAUgBvAHUAdABlAHIAKABwAG8AcwBfAGwAaQBtAGIAcwAsACAAbgBlAGcAXwBsAGkAbQBiAHMALAAgADEALAAgAC0AMQAsACAAdQBuAGkAZgBpAGUAZABfAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGYAaQBuAGEAbABfAHMAaQBnAG4ALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKAByAG8AdQB0AGUAZAAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAEQAUgBPAFAAKAByAG8AdQB0AGUAZAAsACAALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABtAGUAcgBnAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIAB1AG4AaQBmAGkAZQBkAF8AawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAZgBpAG4AYQBsAF8AcwBpAGcAbgAgAD0AIAAtADEALAAgAFwAIgAtAFwAIgAgACYAIABtAGUAcgBnAGUAZAAsACAAbQBlAHIAZwBlAGQAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAE0AdQBsAHQAaQBwAGwAaQBlAHMAIAB0AHcAbwAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcAcwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBhACAAVABoAGUAIABmAGkAcgBzAHQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGIAIABUAGgAZQAgAHMAZQBjAG8AbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoALwBcAG4ATQB1AGwAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGEALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBhACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABlAG4AXwBhACwAIABMAEUATgAoAG4AbwByAG0AXwBhACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAZQBuAF8AYgAsACAATABFAE4AKABuAG8AcgBtAF8AYgApACwAXABuACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAaABvAHIAdAAtAGMAaQByAGMAdQBpAHQAOgAgADAAIABtAHUAbAB0AGkAcABsAGkAZQBkACAAYgB5ACAAYQBuAHkAdABoAGkAbgBnACAAaQBzACAAMABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAE8AUgAoAHMAaQBnAG4AXwBhACAAPQAgADAALAAgAHMAaQBnAG4AXwBiACAAPQAgADAAKQAsACAAXAAiADAAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABsAGUAbgBfAGEAIAArACAAbABlAG4AXwBiACAAPgAgADMAMgA3ADYANgAsACAAIwBOAFUATQAhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBhAGwAYwB1AGwAYQB0AGUAIABkAHkAbgBhAG0AaQBjACAAcwBhAGYAZQAgAEsAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHMAaABvAHIAdABlAHMAdAAgAHMAdAByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGsALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAYQBmAGUASwAoAFwAIgBNAFUATABcACIALAAgAE0ASQBOACgAbABlAG4AXwBhACwAIABsAGUAbgBfAGIAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAUwBwAGwAaQB0ACAAYQBiAHMAbwBsAHUAdABlACAAcwB0AHIAaQBuAGcAcwAgAGkAbgB0AG8AIABsAGkAdAB0AGwAZQAtAGUAbgBkAGkAYQBuACAAYQByAHIAYQB5AHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AYQAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBhACkALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGwAaQBtAGIAcwBfAGIALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAoAEIAaQBnAEkAbgB0AC4AQQBiAHMAKABuAG8AcgBtAF8AYgApACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAbABjAHUAbABhAHQAZQAgAG0AYQBnAG4AaQB0AHUAZABlACAAYQBuAGQAIAByAGUAcwBvAGwAdgBlACAAcwBpAGcAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUATQB1AGwAKABsAGkAbQBiAHMAXwBhACwAIABsAGkAbQBiAHMAXwBiACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAGkAZwBuACwAIABzAGkAZwBuAF8AYQAgACoAIABzAGkAZwBuAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AZQByAGcAZQBkACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABmAGkAbgBhAGwAXwBsAGkAbQBiAHMALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAGYAaQBuAGEAbABfAHMAaQBnAG4AIAA9ACAALQAxACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQALAAgAG0AZQByAGcAZQBkACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAFsAVgBPAEwAQQBUAEkATABFAF0AIABHAGUAbgBlAHIAYQB0AGUAcwAgAGEAIABkAHkAbgBhAG0AaQBjACAAYQByAHIAYQB5ACAAbwBmACAAaQBuAHQAZQBnAGUAcgBzACAAYQBzACAAdABlAHgAdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAbgB1AG0AXwByAG8AdwBzAF0AIABhAHIAcgBhAHkAIABoAGUAaQBnAGgAdAAsACAAZABlAGYAYQB1AGwAdAAgADEALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAG4AdQBtAF8AYwBvAGwAcwBdACAAYQByAHIAYQB5ACAAdwBpAGQAdABoACwAIABkAGUAZgBhAHUAbAB0ACAAMQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAbQBpAG4AXwBkAGkAZwBpAHQAcwBdACAAbQBpAG4AaQBtAHUAbQAgAG4AdQBtAGIAZQByACAAbwBmACAAZABpAGcAaQB0AHMALAAgAGQAZQBmAGEAdQBsAHQAIAAxADYAIAAoAG0AaQBuACAAMQAgAGQAaQBnAGkAdAApAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAbQBhAHgAXwBkAGkAZwBpAHQAcwBdACAAbQBhAHgAaQBtAHUAbQAgAG4AdQBtAGIAZQByACAAbwBmACAAZABpAGcAaQB0AHMALAAgAGQAZQBmAGEAdQBsAHQAIAA1ADAAIAAoAG0AYQB4ACAAMwAyACwANwA2ADcAIABjAGgAYQByAHMALAAgAGkAbgBjAGwAdQBkAGkAbgBnACAAcwBpAGcAbgApAFwAbgAgACoALwBcAG4AUgBhAG4AZABCAGkAZwBJAG4AdABBAHIAcgBhAHkAIAA9ACAATABBAE0AQgBEAEEAKABbAG4AdQBtAF8AcgBvAHcAcwBdACwAIABbAG4AdQBtAF8AYwBvAGwAcwBdACwAIABbAG0AaQBuAF8AZABpAGcAaQB0AHMAXQAsACAAWwBtAGEAeABfAGQAaQBnAGkAdABzAF0ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBfAHIAbwB3AHMALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAbgB1AG0AXwByAG8AdwBzACkALAAgADEALAAgAG4AdQBtAF8AcgBvAHcAcwApACwAXABuACAAIAAgACAAIAAgACAAIABuAF8AYwBvAGwAcwAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABuAHUAbQBfAGMAbwBsAHMAKQAsACAAMQAsACAAbgB1AG0AXwBjAG8AbABzACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAbQBpAG4AXwBsAGUAbgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABtAGkAbgBfAGQAaQBnAGkAdABzACkALAAgADEANgAsACAATQBJAE4AKAAzADIANwA2ADcALAAgAE0AQQBYACgAMQAsACAAbQBpAG4AXwBkAGkAZwBpAHQAcwApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHgAXwBsAGUAbgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABtAGEAeABfAGQAaQBnAGkAdABzACkALAAgADUAMAAsACAATQBBAFgAKAAxACwAIABNAEkATgAoADMAMgA3ADYANgAsACAAbQBhAHgAXwBkAGkAZwBpAHQAcwApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBQACgAUgBBAE4ARABBAFIAUgBBAFkAKABuAF8AcgBvAHcAcwAsACAAbgBfAGMAbwBsAHMALAAgAG0AaQBuAF8AbABlAG4ALAAgAG0AYQB4AF8AbABlAG4ALAAgAFQAUgBVAEUAKQAsACAATABBAE0AQgBEAEEAKABsAGUAbgBnAHQAaAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAaQBnAG4ALAAgAEMASABPAE8AUwBFACgAUgBBAE4ARABCAEUAVABXAEUARQBOACgAMQAsACAAMgApACwAIABcACIAXAAiACwAIABcACIALQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGQAaQBnAGkAdABzACwAIABDAE8ATgBDAEEAVAAoAFIAQQBOAEQAQQBSAFIAQQBZACgAMQAsACAAbABlAG4AZwB0AGgALAAgADAALAAgADkALAAgAFQAUgBVAEUAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcwBpAGcAbgAgACYAIABSAEUARwBFAFgAUgBFAFAATABBAEMARQAoAGQAaQBnAGkAdABzACwAIABcACIAXgAwACoAXAAiACwAIABcACIAXAAiACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEQAaQB2AGkAZABlAHMAIAB0AGgAZQAgAGYAaQByAHMAdAAgAEIAaQBnAEkAbgB0ACAAYgB5ACAAdABoAGUAIABzAGUAYwBvAG4AZAAgACgAQQAgAC8AIABCACkALgAgAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIABxAHUAbwB0AGkAZQBuAHQAIABhAG4AZAAgAG0AbwBkAHUAbAB1AHMAIABpAG4AIAByAG8AdwBzACAAMQAgAGEAbgBkACAAMgAsACAAcgBlAHMAcABlAGMAdABpAHYAZQBsAHkALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAdQBzAGUAXwBmAGwAbwBvAHIAXQAgAE8AcAB0AGkAbwBuAGEAbAAgAGIAbwBvAGwAZQBhAG4ALgAgAFQAUgBVAEUAIABmAG8AcgAgAFAAeQB0AGgAbwBuAC0AcwB0AHkAbABlACAARgBsAG8AbwByACAAZABpAHYAaQBzAGkAbwBuACwAIABGAEEATABTAEUAIABmAG8AcgAgAFQAcgB1AG4AYwBhAHQAZQBkAC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIABGAEEATABTAEUALgBcAG4AIAAqAC8AXABuAEQAaQB2AE0AbwBkACAAPQAgAEwAQQBNAEIARABBACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAIABbAHUAcwBlAF8AZgBsAG8AbwByAF0ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGEALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0AF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgAsACAATgBvAHIAbQAoAGIAaQBnAF8AaQBuAHQAXwBiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBhACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AYgAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAGIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AZgBsAG8AbwByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHUAcwBlAF8AZgBsAG8AbwByACkALAAgAEYAQQBMAFMARQAsACAAdQBzAGUAXwBmAGwAbwBvAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AYgAgAD0AIAAwACwAIAAjAEQASQBWAC8AMAAhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAHMAaQBnAG4AXwBhACAAPQAgADAALAAgAHsAXAAiADAAXAAiADsAXAAiADAAXAAiAH0ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAEQASQBWAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBhACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGEAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBiACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGIAKQAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAYQBjAGsAZQBkAF8AcgBlAHMAdQBsAHQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEQAaQB2AFIAbwB1AHQAZQByACgAbABpAG0AYgBzAF8AYQAsACAAbABpAG0AYgBzAF8AYgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC8ALwAgAEUAeAB0AHIAYQBjAHQAIABSAGUAbQBhAGkAbgBkAGUAcgAgAGEAbgBkACAAUQB1AG8AdABpAGUAbgB0ACAAYQByAHIAYQB5AHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAHIALAAgAEkATgBEAEUAWAAoAHAAYQBjAGsAZQBkAF8AcgBlAHMAdQBsAHQALAAgADEALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAG0AXwBsAGkAbQBiAHMALAAgAEMASABPAE8AUwBFAFIATwBXAFMAKABwAGEAYwBrAGUAZABfAHIAZQBzAHUAbAB0ACwAIABTAEUAUQBVAEUATgBDAEUAKABsAGUAbgBfAHIALAAgADEALAAgADIAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABxAHUAbwB0AF8AbABpAG0AYgBzACwAIABEAFIATwBQACgAcABhAGMAawBlAGQAXwByAGUAcwB1AGwAdAAsACAAbABlAG4AXwByACAAKwAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAcwBvAGwAdgBlACAAVAByAHUAbgBjAGEAdABlAGQAIABzAGkAZwBuAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwBzAGkAZwBuACwAIABzAGkAZwBuAF8AYQAgACoAIABzAGkAZwBuAF8AYgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBlAHIAZwBlAGQAXwBxACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAKABxAHUAbwB0AF8AbABpAG0AYgBzACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG0AZQByAGcAZQBkAF8AcgAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAcgBlAG0AXwBsAGkAbQBiAHMALAAgAGsAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AHIAdQBuAGMAXwBxACwAIABJAEYAKABBAE4ARAAoAGYAaQBuAGEAbABfAHMAaQBnAG4AIAA9ACAALQAxACwAIABtAGUAcgBnAGUAZABfAHEAIAA8AD4AIABcACIAMABcACIAKQAgACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQAXwBxACwAIABtAGUAcgBnAGUAZABfAHEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdAByAHUAbgBjAF8AcgAsACAASQBGACgAYQBuAGQAKABzAGkAZwBuAF8AYQAgAD0AIAAtADEALAAgAG0AZQByAGcAZQBkAF8AcgAgADwAPgAgAFwAIgAwAFwAIgApACwAIABcACIALQBcACIAIAAmACAAbQBlAHIAZwBlAGQAXwByACwAIABtAGUAcgBnAGUAZABfAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABGAGwAbwBvAHIAIABDAG8AcgByAGUAYwB0AGkAbwBuADoAIABUAHIAaQBnAGcAZQByACAATwBOAEwAWQAgAGkAZgAgAGYAbABvAG8AcgAgAGkAcwAgAHIAZQBxAHUAZQBzAHQAZQBkACwAIABzAGkAZwBuAHMAIABkAGkAZgBmAGUAcgAsACAAYQBuAGQAIAByAGUAbQBhAGkAbgBkAGUAcgAgAGkAcwAgAG4AbwBuAC0AegBlAHIAbwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AZQBlAGQAcwBfAGMAbwByAHIAZQBjAHQAaQBvAG4ALAAgAEEATgBEACgAaQBzAF8AZgBsAG8AbwByACwAIABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAbQBlAHIAZwBlAGQAXwByACAAPAA+ACAAXAAiADAAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcQAsACAASQBGACgAbgBlAGUAZABzAF8AYwBvAHIAcgBlAGMAdABpAG8AbgAsACAAUwB1AGIAKAB0AHIAdQBuAGMAXwBxACwAIABcACIAMQBcACIAKQAsACAAdAByAHUAbgBjAF8AcQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbgBhAGwAXwByACwAIABJAEYAKABuAGUAZQBkAHMAXwBjAG8AcgByAGUAYwB0AGkAbwBuACwAIABBAGQAZAAoAHQAcgB1AG4AYwBfAHIALAAgAG4AbwByAG0AXwBiACkALAAgAHQAcgB1AG4AYwBfAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABWAFMAVABBAEMASwAoAGYAaQBuAGEAbABfAHEALAAgAGYAaQBuAGEAbABfAHIAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAARABpAHYAaQBkAGUAcwAgAHQAaABlACAAZgBpAHIAcwB0ACAAQgBpAGcASQBuAHQAIABiAHkAIAB0AGgAZQAgAHMAZQBjAG8AbgBkACAAKABBACAALwAgAEIAKQAuACAAXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdABfAGEAIABUAGgAZQAgAGQAaQB2AGkAZABlAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYgAgAFQAaABlACAAZABpAHYAaQBzAG8AcgAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABbAHUAcwBlAF8AZgBsAG8AbwByAF0AIABPAHAAdABpAG8AbgBhAGwAIABiAG8AbwBsAGUAYQBuAC4AIABUAFIAVQBFACAAZgBvAHIAIABQAHkAdABoAG8AbgAtAHMAdAB5AGwAZQAgAEYAbABvAG8AcgAgAGQAaQB2AGkAcwBpAG8AbgAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAARgBBAEwAUwBFAC4AXABuACAAKgAvAFwAbgBEAGkAdgAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQAXwBhACwAIABiAGkAZwBfAGkAbgB0AF8AYgAsACAAWwB1AHMAZQBfAGYAbABvAG8AcgBdACwAXABuACAAIAAgACAASQBOAEQARQBYACgARABpAHYATQBvAGQAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALAAgAHUAcwBlAF8AZgBsAG8AbwByACkALAAgADEALAAgADEAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACoAXABuACAAKgAgAEMAbwBtAHAAdQB0AGUAcwAgAHQAaABlACAAcgBlAG0AYQBpAG4AZABlAHIAIABvAGYAIABBACAALwAgAEIALgBcAG4AIAAqACAAQABwAGEAcgBhAG0AIABiAGkAZwBfAGkAbgB0AF8AYQAgAFQAaABlACAAZABpAHYAaQBkAGUAbgBkACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAXwBiACAAVABoAGUAIABkAGkAdgBpAHMAbwByACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAFsAdQBzAGUAXwBmAGwAbwBvAHIAXQAgAE8AcAB0AGkAbwBuAGEAbAAgAGIAbwBvAGwAZQBhAG4ALgAgAFQAUgBVAEUAIABmAG8AcgAgAFAAeQB0AGgAbwBuAC0AcwB0AHkAbABlACAATQBvAGQAdQBsAG8ALgAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAEYAQQBMAFMARQAuAFwAbgAgACoALwBcAG4ATQBvAGQAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0AF8AYQAsACAAYgBpAGcAXwBpAG4AdABfAGIALAAgAFsAdQBzAGUAXwBmAGwAbwBvAHIAXQAsAFwAbgAgACAAIAAgAEkATgBEAEUAWAAoAEQAaQB2AE0AbwBkACgAYgBpAGcAXwBpAG4AdABfAGEALAAgAGIAaQBnAF8AaQBuAHQAXwBiACwAIAB1AHMAZQBfAGYAbABvAG8AcgApACwAIAAyACwAIAAxACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGEAaQBzAGUAcwAgAGEAIABCAGkAZwBJAG4AdAAgAGIAYQBzAGUAIAB0AG8AIAB0AGgAZQAgAHAAbwB3AGUAcgAgAG8AZgAgAGEAIABCAGkAZwBJAG4AdAAgAGUAeABwAG8AbgBlAG4AdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAYQBzAGUAIABUAGgAZQAgAGIAYQBzAGUAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAZQB4AHAAbwBuAGUAbgB0ACAAVABoAGUAIABlAHgAcABvAG4AZQBuAHQAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAC4AXABuACAAKgAvAFwAbgBQAG8AdwAgAD0AIABMAEEATQBCAEQAQQAoAGIAYQBzAGUALAAgAGUAeABwAG8AbgBlAG4AdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABuAG8AcgBtAF8AYgBhAHMAZQAsACAATgBvAHIAbQAoAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAGUAeABwACwAIABOAG8AcgBtACgAZQB4AHAAbwBuAGUAbgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBiAGEAcwBlACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AYgBhAHMAZQApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AZQB4AHAALAAgAEIAaQBnAEkAbgB0AC4AUwBpAGcAbgAoAG4AbwByAG0AXwBlAHgAcAApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAYQBiAHMAXwBiAGEAcwBlACwAIABCAGkAZwBJAG4AdAAuAEEAYgBzACgAbgBvAHIAbQBfAGIAYQBzAGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAYQBiAHMAXwBlAHgAcAAsACAAQgBpAGcASQBuAHQALgBBAGIAcwAoAG4AbwByAG0AXwBlAHgAcAApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAaQBzAF8AZQB4AHAAXwBlAHYAZQBuACwAIABJAFMARQBWAEUATgAoAFYAQQBMAFUARQAoAFIASQBHAEgAVAAoAG4AbwByAG0AXwBlAHgAcAAsACAAMQApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AcwBpAGcAbgAsACAASQBGACgAcwBpAGcAbgBfAGIAYQBzAGUAIAA9ACAALQAxACwAIABJAEYAKABpAHMAXwBlAHgAcABfAGUAdgBlAG4ALAAgADEALAAgAC0AMQApACwAIABzAGkAZwBuAF8AYgBhAHMAZQApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAASABhAG4AZABsAGUAIABtAGEAdABoAGUAbQBhAHQAaQBjAGEAbAAgAGIAbwB1AG4AZABhAHIAaQBlAHMAIABhAG4AZAAgAGIAYQBzAGUAIABsAGkAbQBpAHQAcwBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAGEAYgBzAF8AYgBhAHMAZQAgAD0AIABcACIAMABcACIALAAgAEkARgAoAG4AbwByAG0AXwBlAHgAcAAgAD0AIABcACIAMABcACIALAAgACMATgBVAE0AIQAsACAAXAAiADAAXAAiACkALAAgAC8ALwAgADAAXgAwACAAaQBzACAAdQBuAGQAZQBmAGkAbgBlAGQAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABhAGIAcwBfAGIAYQBzAGUAIAA9ACAAXAAiADEAXAAiACwAIABJAEYAKABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAXAAiAC0AMQBcACIALAAgAFwAIgAxAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABzAGkAZwBuAF8AZQB4AHAAIAA9ACAALQAxACwAIABcACIAMABcACIALAAgAC8ALwAgAEkAbgB0AGUAZwBlAHIAIAB0AHIAdQBuAGMAYQB0AGkAbwBuADoAIABuAGUAZwBhAHQAaQB2AGUAIABlAHgAcABvAG4AZQBuAHQAcwAgAHkAaQBlAGwAZAAgADAAIABmAG8AcgAgAGIAYQBzAGUAcwAgAD4APQAgADIAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAG8AcgBtAF8AZQB4AHAAIAA9ACAAXAAiADAAXAAiACwAIABcACIAMQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAcwB1AGwAdABzACAAZgByAG8AbQAgAGUAeABwAG8AbgBlAG4AdABzACAAZwByAGUAYQB0AGUAcgAgAHQAaABhAG4AIAA2ACAAZABpAGcAaQB0AHMAIABjAGEAbgBuAG8AdAAgAGIAZQAgAGQAaQBzAHAAbABhAHkAZQBkAC4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAEUATgAoAG4AbwByAG0AXwBlAHgAcAApACAAPgAgADYALAAgACMATgBVAE0AIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG4AdQBtAF8AZQB4AHAALAAgAFYAQQBMAFUARQAoAG4AbwByAG0AXwBlAHgAcAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQQBwAHAAcgBvAHgAaQBtAGEAdABlACAAdABoAGUAIABmAGkAbgBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgAgAGMAbwB1AG4AdAA6ACAAQgAgACoAIABMAG8AZwAxADAAKABBACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYgBhAHMAZQBfAGwAbwBnADEAMAAsACAATABPAEcAMQAwACgAVgBBAEwAVQBFACgATABFAEYAVAAoAGEAYgBzAF8AYgBhAHMAZQAsACAAMQA0ACkAKQApACAAKwAgAE0AQQBYACgAMAAsACAATABFAE4AKABhAGIAcwBfAGIAYQBzAGUAKQAgAC0AIAAxADQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGEAcABwAHIAbwB4AF8AZABpAGcAaQB0AHMALAAgAG4AdQBtAF8AZQB4AHAAIAAqACAAYgBhAHMAZQBfAGwAbwBnADEAMAAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABhAHAAcAByAG8AeABfAGQAaQBnAGkAdABzACAAPgAgADMAMgA3ADYANgAsACAAIwBOAFUATQAhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABrACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAGEAZgBlAEsAKABcACIATQBVAEwAXAAiACwAIABhAHAAcAByAG8AeABfAGQAaQBnAGkAdABzACAALwAgADIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBiAGEAcwBlACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABhAGIAcwBfAGIAYQBzAGUALAAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFAAbwB3ACgAbABpAG0AYgBzAF8AYgBhAHMAZQAsACAAbgBvAHIAbQBfAGUAeABwACwAIABrACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQBlAHIAZwBlAGQALAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE0AZQByAGcAZQAoAGYAaQBuAGEAbABfAGwAaQBtAGIAcwAsACAAawApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABmAGkAbgBhAGwAXwBzAGkAZwBuACAAPQAgAC0AMQAsACAAXAAiAC0AXAAiACAAJgAgAG0AZQByAGcAZQBkACwAIABtAGUAcgBnAGUAZAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApACkAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABDAGEAbABjAHUAbABhAHQAZQBzACAAdABoAGUAIABpAG4AdABlAGcAZQByACAAcwBxAHUAYQByAGUAIAByAG8AbwB0ACAAKABmAGwAbwBvAHIAKQAgAG8AZgAgAGEAIABCAGkAZwBJAG4AdAAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAGIAaQBnAF8AaQBuAHQAIABUAGgAZQAgAHIAYQBkAGkAYwBhAG4AZAAgAEIAaQBnAEkAbgB0ACAAcwB0AHIAaQBuAGcALgBcAG4AIAAqAC8AXABuAFMAcQByAHQAIAA9ACAATABBAE0AQgBEAEEAKABiAGkAZwBfAGkAbgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG4AbwByAG0AXwBuACwAIABOAG8AcgBtACgAYgBpAGcAXwBpAG4AdAApACwAXABuACAAIAAgACAAIAAgACAAIABzAGkAZwBuAF8AbgAsACAAQgBpAGcASQBuAHQALgBTAGkAZwBuACgAbgBvAHIAbQBfAG4AKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAHMAaQBnAG4AXwBuACAAPQAgAC0AMQAsACAAIwBOAFUATQAhACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAG8AcgBtAF8AbgAgAD0AIABcACIAMABcACIALAAgAFwAIgAwAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgBvAHIAbQBfAG4AIAA9ACAAXAAiADEAXAAiACwAIABcACIAMQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGUAbgBfAG4ALAAgAEwARQBOACgAbgBvAHIAbQBfAG4AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAYQBrAGUAXwBkAGkAZwBpAHQAcwAsACAASQBGACgAbABlAG4AXwBuACAAPAA9ACAAMQA0ACwAIABsAGUAbgBfAG4ALAAgAEkARgAoAEkAUwBFAFYARQBOACgAbABlAG4AXwBuACkALAAgADEANAAsACAAMQAzACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHYAXwBzAHQAcgAsACAATABFAEYAVAAoAG4AbwByAG0AXwBuACwAIAB0AGEAawBlAF8AZABpAGcAaQB0AHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHYAXwBuAHUAbQAsACAAVgBBAEwAVQBFACgAdgBfAHMAdAByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB6AGUAcgBvAF8AYwBvAHUAbgB0ACwAIAAoAGwAZQBuAF8AbgAgAC0AIAB0AGEAawBlAF8AZABpAGcAaQB0AHMAKQAgAC8AIAAyACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAZQBlAGQAXwBwAHIAZQBmAGkAeAAsACAAVABFAFgAVAAoAFIATwBVAE4ARABVAFAAKABTAFEAUgBUACgAdgBfAG4AdQBtACkALAAgADAAKQAgACsAIAAxACwAIABcACIAMABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAZQBlAGQAXwBzAHQAcgAsACAAcwBlAGUAZABfAHAAcgBlAGYAaQB4ACAAJgAgAFIARQBQAFQAKABcACIAMABcACIALAAgAHoAZQByAG8AXwBjAG8AdQBuAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGMAYQBsAGUAcwAgAGsAIABiAHkAIAB0AGgAZQAgAG0AYQB4AGkAbQB1AG0AIABvAHYAZQByAGwAYQBwACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAawAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACgAXAAiAE0AVQBMAFwAIgAsACAAbABlAG4AXwBuACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABsAGkAbQBiAHMAXwBuACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBTAHAAbABpAHQAKABuAG8AcgBtAF8AbgAsACAAawApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbABpAG0AYgBzAF8AcwBlAGUAZAAsACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBwAGwAaQB0ACgAcwBlAGUAZABfAHMAdAByACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFMAcQByAHQAKABsAGkAbQBiAHMAXwBuACwAIABsAGkAbQBiAHMAXwBzAGUAZQBkACwAIABrACkALABcAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATQBlAHIAZwBlACgAZgBpAG4AYQBsAF8AbABpAG0AYgBzACwAIABrACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACAAIAApACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAQwBvAG0AcAB1AHQAZQBzACAAdABoAGUAIABmAGEAYwB0AG8AcgBpAGEAbAAgAG8AZgAgAGEAIABCAGkAZwBJAG4AdAAgACgAbgAhACkAIAB1AHMAaQBuAGcAIABQAGUAdABlAHIAIABMAHUAcwBjAGgAbgB5ACcAcwAgAFAAcgBpAG0AZQAgAFMAdwBpAG4AZwAgAGEAbABnAG8AcgBpAHQAaABtAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAYgBpAGcAXwBpAG4AdAAgAFQAaABlACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwAuACAATQBhAHgAaQBtAHUAbQAgAHMAdQBwAHAAbwByAHQAZQBkACAAaQBuAHAAdQB0ACAAaQBzACAAOQAyADcAMwAuAFwAbgAgACoALwBcAG4ARgBhAGMAdAAgAD0AIABMAEEATQBCAEQAQQAoAGIAaQBnAF8AaQBuAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbgBvAHIAbQBfAG4ALAAgAE4AbwByAG0AKABiAGkAZwBfAGkAbgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAaQBnAG4AXwBuACwAIABCAGkAZwBJAG4AdAAuAFMAaQBnAG4AKABuAG8AcgBtAF8AbgApACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAcwBpAGcAbgBfAG4AIAA9ACAALQAxACwAIAAjAE4AVQBNACEALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4AbwByAG0AXwBuACAAPQAgAFwAIgAwAFwAIgAsACAAXAAiADEAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAG8AcgBtAF8AbgAgAD0AIABcACIAMQBcACIALAAgAFwAIgAxAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARgBpAHIAZQB3AGEAbABsACAAMQA6ACAAVAByAGEAcAAgAG0AYQBzAHMAaQB2AGUAIABzAHQAcgBpAG4AZwBzACAAYgBlAGYAbwByAGUAIAB0AGgAZQB5ACAAaABpAHQAIABWAEEATABVAEUAKAApAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABFAE4AKABuAG8AcgBtAF8AbgApACAAPgAgADQALAAgACMATgBVAE0AIQAsACAAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABGAGkAcgBlAHcAYQBsAGwAIAAyADoAIABUAHIAYQBwACAAbQBhAHQAaABlAG0AYQB0AGkAYwBhAGwAIABjAGUAaQBsAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAVgBBAEwAVQBFACgAbgBvAHIAbQBfAG4AKQAgAD4AIAA5ADIANwAzACwAIAAjAE4AVQBNACEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAF8AdgBhAGwALAAgAFYAQQBMAFUARQAoAG4AbwByAG0AXwBuACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABnAGwAbwBiAGEAbABfAHAAcgBpAG0AZQBzACwAIABjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBOAGEAdABpAHYAZQBQAHIAaQBtAGUAcwAoAG4AXwB2AGEAbAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUAByAGkAbQBlAFMAdwBpAG4AZwBLAGUAcgBuAGUAbAAoAG4AXwB2AGEAbAAsACAAZwBsAG8AYgBhAGwAXwBwAHIAaQBtAGUAcwApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQApACkAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAC8AKgAqAFwAbgAgACoAIABSAGUAdAB1AHIAbgBzACAAdABoAGUAIABtAGkAbgBpAG0AdQBtACAAQgBpAGcASQBuAHQAIABmAHIAbwBtACAAYQBuACAAYQByAHIAYQB5ACAAbwByACAAcgBhAG4AZwBlAC4AXABuACAAKgAgAEAAcABhAHIAYQBtACAAcgBhAG4AZwBlACAAQQAgAGMAbwBuAHQAaQBnAHUAbwB1AHMAIAByAGEAbgBnAGUAIABvAHIAIABhAHIAcgBhAHkAIABvAGYAIABCAGkAZwBJAG4AdAAgAHMAdAByAGkAbgBnAHMALgBcAG4AIAAqAC8AXABuAE0AaQBuACAAPQAgAEwAQQBNAEIARABBACgAcgBhAG4AZwBlACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAGMAbABlAGEAbgBfAGMAbwBsACwAIABUAE8AQwBPAEwAKAByAGEAbgBnAGUALAAgADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABJAFMARQBSAFIATwBSACgAYwBsAGUAYQBuAF8AYwBvAGwAKQAsACAAUgBPAFcAUwAoAGMAbABlAGEAbgBfAGMAbwBsACkAIAA9ACAAMAApACwAIABcACIAMABcACIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVAByAGUAZQBDAG8AbQBwAGEAcgBlACgATQBBAFAAKABjAGwAZQBhAG4AXwBjAG8AbAAsACAAQgBpAGcASQBuAHQALgBOAG8AcgBtACkALAAgAC0AMQApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAKgBcAG4AIAAqACAAUgBlAHQAdQByAG4AcwAgAHQAaABlACAAbQBhAHgAaQBtAHUAbQAgAEIAaQBnAEkAbgB0ACAAZgByAG8AbQAgAGEAbgAgAGEAcgByAGEAeQAgAG8AcgAgAHIAYQBuAGcAZQAuAFwAbgAgACoAIABAAHAAYQByAGEAbQAgAHIAYQBuAGcAZQAgAEEAIABjAG8AbgB0AGkAZwB1AG8AdQBzACAAcgBhAG4AZwBlACAAbwByACAAYQByAHIAYQB5ACAAbwBmACAAQgBpAGcASQBuAHQAIABzAHQAcgBpAG4AZwBzAC4AXABuACAAKgAvAFwAbgBNAGEAeAAgAD0AIABMAEEATQBCAEQAQQAoAHIAYQBuAGcAZQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABjAGwAZQBhAG4AXwBjAG8AbAAsACAAVABPAEMATwBMACgAcgBhAG4AZwBlACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATwBSACgASQBTAEUAUgBSAE8AUgAoAGMAbABlAGEAbgBfAGMAbwBsACkALAAgAFIATwBXAFMAKABjAGwAZQBhAG4AXwBjAG8AbAApACAAPQAgADAAKQAsACAAXAAiADAAXAAiACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFQAcgBlAGUAQwBvAG0AcABhAHIAZQAoAE0AQQBQACgAYwBsAGUAYQBuAF8AYwBvAGwALAAgAEIAaQBnAEkAbgB0AC4ATgBvAHIAbQApACwAIAAxACkAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgB0AGUAcwB0AF8AQgBpAGcASQBuAHQALgBLAG4AdQB0AGgARABpAHYAaQBzAGkAbwBuACIALAAiAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4ARABpAHYAaQBzAGkAbwBuACIALAAiAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBzACIALAAiAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAuAEQAaQB2AGkAcwBpAG8AbgBBAGwAZwBvAHIAaQB0AGgAbQBDAG8AbQBwAGEAcgBpAHMAbwBuACIALAAiAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAuAEQAaQB2AGkAcwBpAG8AbgBCAGUAbgBjAGgAbQBhAHIAawBDAGEAcwBlAHMAIgAsACIAdABlAHMAdABfAEIAaQBnAEkAbgB0AC4AQQBzAHkAbQBtAGUAdAByAGkAYwBBAEIARwByAGkAZAAiACwAIgB0AGUAcwB0AF8AQgBpAGcASQBuAHQALgBGAGEAYwB0AG8AcgBpAGEAbABBAGwAZwBvAHIAaQB0AGgAbQBzACIALAAiAHQAZQBzAHQAXwBCAGkAZwBJAG4AdAAuAEYAYQBjAHQAbwByAGkAYQBsAEMAbwBtAHAAYQByAGkAcwBvAG4AIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AUwBhAGYAZQBLACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAcABsAGkAdAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBNAGUAcgBnAGUAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AQwBhAHIAcgB5ACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAQwBvAG0AcABhAHIAZQAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAEEAZABkACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAUwB1AGIAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVQBNAGEAdAByAGkAeABTAHUAbQAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBBAGQAZABTAHUAYgBSAG8AdQB0AGUAcgAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAE0AdQBsACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEYAaQBuAGQAUQB1AG8AdABpAGUAbgB0AEwAaQBtAGIAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ASwBuAHUAdABoAEQAaQB2ACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAEQAaQB2AFIAbwB1AHQAZQByACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAE4AZQB3AHQAbwBuAFIAYQBwAGgAcwBvAG4AUwBlAGUAZAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBOAGUAdwB0AG8AbgBSAGEAcABoAHMAbwBuAFIAZQBjAGkAcAByAG8AYwBhAGwAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBlAHcAdABvAG4AUgBhAHAAaABzAG8AbgBEAGkAdgAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFAAbwB3ACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFUAUwBxAHIAdAAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBOAGEAdABpAHYAZQBQAHIAaQBtAGUAcwAiACwAIgBjAG8AcgBlAF8AQgBpAGcASQBuAHQALgBVAFQAZQB4AHQATQB1AGwAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVABlAHgAdABUAHIAZQBlAFAAcgBvAGQAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4ATgBhAHQAaQB2AGUAUwB3AGkAbgBnAEUAeABwAG8AbgBlAG4AdABzACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFMAdwBpAG4AZwBUAGUAcgBtACIALAAiAGMAbwByAGUAXwBCAGkAZwBJAG4AdAAuAFAAcgBpAG0AZQBTAHcAaQBuAGcASwBlAHIAbgBlAGwAIgAsACIAYwBvAHIAZQBfAEIAaQBnAEkAbgB0AC4AVAByAGUAZQBDAG8AbQBwAGEAcgBlACIALAAiAEIAaQBnAEkAbgB0AC4ATgBvAHIAbQAiACwAIgBCAGkAZwBJAG4AdAAuAFMAaQBnAG4AIgAsACIAQgBpAGcASQBuAHQALgBJAHMAWgBlAHIAbwAiACwAIgBCAGkAZwBJAG4AdAAuAEkAcwBOAGUAZwAiACwAIgBCAGkAZwBJAG4AdAAuAEkAcwBFAHYAZQBuACIALAAiAEIAaQBnAEkAbgB0AC4ASQBzAE8AZABkACIALAAiAEIAaQBnAEkAbgB0AC4AQQBiAHMAIgAsACIAQgBpAGcASQBuAHQALgBDAG8AbQBwAGEAcgBlACIALAAiAEIAaQBnAEkAbgB0AC4AQQBkAGQAIgAsACIAQgBpAGcASQBuAHQALgBTAHUAYgAiACwAIgBCAGkAZwBJAG4AdAAuAFMAdQBtACIALAAiAEIAaQBnAEkAbgB0AC4ATQB1AGwAIgAsACIAQgBpAGcASQBuAHQALgBSAGEAbgBkAEIAaQBnAEkAbgB0AEEAcgByAGEAeQAiACwAIgBCAGkAZwBJAG4AdAAuAEQAaQB2AE0AbwBkACIALAAiAEIAaQBnAEkAbgB0AC4ARABpAHYAIgAsACIAQgBpAGcASQBuAHQALgBNAG8AZAAiACwAIgBCAGkAZwBJAG4AdAAuAFAAbwB3ACIALAAiAEIAaQBnAEkAbgB0AC4AUwBxAHIAdAAiACwAIgBCAGkAZwBJAG4AdAAuAEYAYQBjAHQAIgAsACIAQgBpAGcASQBuAHQALgBNAGkAbgAiACwAIgBCAGkAZwBJAG4AdAAuAE0AYQB4ACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/XL-Int.xlsx
+++ b/XL-Int.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\foolu\Workspace\Excel\BigInt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\foolu\Workspace\Excel\xl-int\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D93F4D3-4B6A-4C8A-BBEF-A27586E65BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2273CAF-7F9F-4B41-9A4D-4B0FE9B4C2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24560" windowHeight="21000" xr2:uid="{36490472-0618-4E80-9469-F609392FABC8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{36490472-0618-4E80-9469-F609392FABC8}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -8065,7 +8065,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -8106,18 +8106,12 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Input" xfId="1" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="452">
+  <dxfs count="329">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -8140,6 +8134,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -8170,6 +8174,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -8370,6 +8394,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -8510,6 +8554,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -8660,1303 +8724,20 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -9964,6 +8745,15 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -9981,11 +8771,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -10011,13 +8805,14 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -10027,7 +8822,6 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -10045,13 +8839,14 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -10061,7 +8856,6 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -10079,40 +8873,10 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -12075,12 +10839,12 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7798C9D4-D9A3-414B-919E-1762A05E858C}" name="Norm_Tests" displayName="Norm_Tests" ref="A7:E26" totalsRowCount="1">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2D415719-D29C-4B5B-8EEC-D6B547CA5D0E}" name="input" dataDxfId="451"/>
+    <tableColumn id="1" xr3:uid="{2D415719-D29C-4B5B-8EEC-D6B547CA5D0E}" name="input" dataDxfId="328"/>
     <tableColumn id="3" xr3:uid="{0ACC712F-EB7B-43DA-9965-8A4957A95DA2}" name="expected"/>
-    <tableColumn id="2" xr3:uid="{25F1E681-6FC0-4609-BF1F-1FF79BEB3CD8}" name="output" dataDxfId="450">
+    <tableColumn id="2" xr3:uid="{25F1E681-6FC0-4609-BF1F-1FF79BEB3CD8}" name="output" dataDxfId="327">
       <calculatedColumnFormula array="1">internal.xlInt.Norm(Norm_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{20432306-08A1-43B4-9B37-03610B79D73B}" name="passing" totalsRowFunction="custom" dataDxfId="449">
+    <tableColumn id="4" xr3:uid="{20432306-08A1-43B4-9B37-03610B79D73B}" name="passing" totalsRowFunction="custom" dataDxfId="326">
       <calculatedColumnFormula>IF(ISERROR(Norm_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Norm_Tests[[#This Row],[expected]]) = ERROR.TYPE(Norm_Tests[[#This Row],[output]]),
     Norm_Tests[[#This Row],[expected]] = Norm_Tests[[#This Row],[output]]
@@ -12094,11 +10858,11 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DCEBF05F-998F-47D8-A8F8-63C4E2771074}" name="UCompare_Tests" displayName="UCompare_Tests" ref="A127:E135" totalsRowCount="1" dataDxfId="410">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DCEBF05F-998F-47D8-A8F8-63C4E2771074}" name="UCompare_Tests" displayName="UCompare_Tests" ref="A127:E135" totalsRowCount="1" dataDxfId="287">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3554FEAC-3E95-4439-BF1F-B262B64D139D}" name="input" dataDxfId="409"/>
-    <tableColumn id="2" xr3:uid="{0EA61E63-F894-4F39-983A-67C6CDEA4B1D}" name="expected" dataDxfId="408"/>
-    <tableColumn id="3" xr3:uid="{B6F49B44-504D-4599-9F1E-49B98046B44D}" name="output" dataDxfId="407">
+    <tableColumn id="1" xr3:uid="{3554FEAC-3E95-4439-BF1F-B262B64D139D}" name="input" dataDxfId="286"/>
+    <tableColumn id="2" xr3:uid="{0EA61E63-F894-4F39-983A-67C6CDEA4B1D}" name="expected" dataDxfId="285"/>
+    <tableColumn id="3" xr3:uid="{B6F49B44-504D-4599-9F1E-49B98046B44D}" name="output" dataDxfId="284">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(UCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -12108,46 +10872,46 @@
     internal.xlInt.UCompare(_xlpm.limbs_a, _xlpm.limbs_b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{96B8A7F0-899C-4301-95D3-41FB0BA096A7}" name="passing" totalsRowFunction="custom" dataDxfId="406">
+    <tableColumn id="4" xr3:uid="{96B8A7F0-899C-4301-95D3-41FB0BA096A7}" name="passing" totalsRowFunction="custom" dataDxfId="283">
       <calculatedColumnFormula>IF(ISERROR(UCompare_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(UCompare_Tests[[#This Row],[output]]),
     UCompare_Tests[[#This Row],[expected]] = UCompare_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UCompare_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C5539D24-4ADC-4D77-B82F-27DAF4B3F109}" name="test" dataDxfId="405"/>
+    <tableColumn id="5" xr3:uid="{C5539D24-4ADC-4D77-B82F-27DAF4B3F109}" name="test" dataDxfId="282"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5E817537-E6E9-4069-8E14-531A3E42821F}" name="Internal_Sign_Tests" displayName="Internal_Sign_Tests" ref="A49:E60" totalsRowCount="1" tableBorderDxfId="404">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{5E817537-E6E9-4069-8E14-531A3E42821F}" name="Internal_Sign_Tests" displayName="Internal_Sign_Tests" ref="A49:E60" totalsRowCount="1" tableBorderDxfId="281">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{C5C6E024-5D15-4650-BC06-AE3A9A4A3F9E}" name="input"/>
     <tableColumn id="2" xr3:uid="{2E349FE8-D8E4-4ABE-B47E-F0985AA6C672}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{49844921-4B71-4B13-957C-917C2841A9A3}" name="output" dataDxfId="403">
+    <tableColumn id="3" xr3:uid="{49844921-4B71-4B13-957C-917C2841A9A3}" name="output" dataDxfId="280">
       <calculatedColumnFormula array="1">xlInt.Sign(Internal_Sign_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0236DB85-60E5-4DC6-9655-C6D58A63C8D4}" name="passing" totalsRowFunction="custom" dataDxfId="402">
+    <tableColumn id="4" xr3:uid="{0236DB85-60E5-4DC6-9655-C6D58A63C8D4}" name="passing" totalsRowFunction="custom" dataDxfId="279">
       <calculatedColumnFormula>IF(ISERROR(Internal_Sign_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Internal_Sign_Tests[[#This Row],[expected]]) = ERROR.TYPE(Internal_Sign_Tests[[#This Row],[output]]),
     Internal_Sign_Tests[[#This Row],[expected]] = Internal_Sign_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Internal_Sign_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{396092C1-DC4F-4532-BB59-E0E779D9A525}" name="test" dataDxfId="401"/>
+    <tableColumn id="5" xr3:uid="{396092C1-DC4F-4532-BB59-E0E779D9A525}" name="test" dataDxfId="278"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1BF11AA1-9F01-403A-A5A2-CDAF85E5F9D0}" name="USub_Tests" displayName="USub_Tests" ref="A138:E146" totalsRowCount="1" dataDxfId="400">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1BF11AA1-9F01-403A-A5A2-CDAF85E5F9D0}" name="USub_Tests" displayName="USub_Tests" ref="A138:E146" totalsRowCount="1" dataDxfId="277">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5B979D84-AD0F-45AF-AB26-6C75CA981E58}" name="input" dataDxfId="399"/>
-    <tableColumn id="2" xr3:uid="{D8895FB5-11F4-4379-9B45-0D72ADA71E57}" name="expected" dataDxfId="398"/>
-    <tableColumn id="3" xr3:uid="{A4DDD8AE-0CC0-457E-A08D-2C94591CF878}" name="output" dataDxfId="397">
+    <tableColumn id="1" xr3:uid="{5B979D84-AD0F-45AF-AB26-6C75CA981E58}" name="input" dataDxfId="276"/>
+    <tableColumn id="2" xr3:uid="{D8895FB5-11F4-4379-9B45-0D72ADA71E57}" name="expected" dataDxfId="275"/>
+    <tableColumn id="3" xr3:uid="{A4DDD8AE-0CC0-457E-A08D-2C94591CF878}" name="output" dataDxfId="274">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(USub_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -12159,25 +10923,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BF616718-1C7F-4627-B496-8B6339CC2735}" name="passing" totalsRowFunction="custom" dataDxfId="396">
+    <tableColumn id="4" xr3:uid="{BF616718-1C7F-4627-B496-8B6339CC2735}" name="passing" totalsRowFunction="custom" dataDxfId="273">
       <calculatedColumnFormula>IF(ISERROR(USub_Tests[[#This Row],[expected]]),
     ERROR.TYPE(USub_Tests[[#This Row],[expected]]) = ERROR.TYPE(USub_Tests[[#This Row],[output]]),
     USub_Tests[[#This Row],[expected]] = USub_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(USub_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FCF52C7D-4E82-4BAA-8C93-974211CAC2AF}" name="test" dataDxfId="395"/>
+    <tableColumn id="5" xr3:uid="{FCF52C7D-4E82-4BAA-8C93-974211CAC2AF}" name="test" dataDxfId="272"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B5433254-33A6-4D35-8484-91940B628217}" name="Table6" displayName="Table6" ref="A149:E160" totalsRowCount="1" dataDxfId="394">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B5433254-33A6-4D35-8484-91940B628217}" name="Table6" displayName="Table6" ref="A149:E160" totalsRowCount="1" dataDxfId="271">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D52F6D10-66CD-4765-927A-94A578D3C30A}" name="input" dataDxfId="393" totalsRowDxfId="392"/>
-    <tableColumn id="2" xr3:uid="{DF2BEEE3-E1EF-4EA0-A6A8-77B06FB5C3EE}" name="expected" dataDxfId="391"/>
-    <tableColumn id="3" xr3:uid="{4FDE8849-AFE2-471E-8131-C5B45620EBDC}" name="output" dataDxfId="390">
+    <tableColumn id="1" xr3:uid="{D52F6D10-66CD-4765-927A-94A578D3C30A}" name="input" dataDxfId="270" totalsRowDxfId="269"/>
+    <tableColumn id="2" xr3:uid="{DF2BEEE3-E1EF-4EA0-A6A8-77B06FB5C3EE}" name="expected" dataDxfId="268"/>
+    <tableColumn id="3" xr3:uid="{4FDE8849-AFE2-471E-8131-C5B45620EBDC}" name="output" dataDxfId="267">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.input, _xlfn.REGEXEXTRACT(Table6[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.input,1,1),
@@ -12191,25 +10955,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5813AECE-7F35-45E7-8E1F-50DCC8404156}" name="passing" totalsRowFunction="custom" dataDxfId="389" totalsRowDxfId="388">
+    <tableColumn id="4" xr3:uid="{5813AECE-7F35-45E7-8E1F-50DCC8404156}" name="passing" totalsRowFunction="custom" dataDxfId="266" totalsRowDxfId="265">
       <calculatedColumnFormula>IF(ISERROR(Table6[[#This Row],[expected]]),
     ERROR.TYPE(Table6[[#This Row],[expected]]) = ERROR.TYPE(Table6[[#This Row],[output]]),
     Table6[[#This Row],[expected]] = Table6[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Table6[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6FEE6B80-DF03-48AD-BE0B-5CF10BB9952D}" name="test" dataDxfId="387"/>
+    <tableColumn id="5" xr3:uid="{6FEE6B80-DF03-48AD-BE0B-5CF10BB9952D}" name="test" dataDxfId="264"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{99918742-71F1-4CEE-8B31-04D0864B12BE}" name="Add_Tests" displayName="Add_Tests" ref="A163:E169" totalsRowCount="1" dataDxfId="386">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{99918742-71F1-4CEE-8B31-04D0864B12BE}" name="Add_Tests" displayName="Add_Tests" ref="A163:E169" totalsRowCount="1" dataDxfId="263">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BEDCABA1-70E6-4A6B-A326-B96D805DC792}" name="input" dataDxfId="385"/>
-    <tableColumn id="2" xr3:uid="{D2C344B5-4A5B-4F69-8FCC-B73D81DE29AD}" name="expected" dataDxfId="384"/>
-    <tableColumn id="3" xr3:uid="{B095BBF3-B41C-4F5B-9689-A075BCD3B3C6}" name="output" dataDxfId="383">
+    <tableColumn id="1" xr3:uid="{BEDCABA1-70E6-4A6B-A326-B96D805DC792}" name="input" dataDxfId="262"/>
+    <tableColumn id="2" xr3:uid="{D2C344B5-4A5B-4F69-8FCC-B73D81DE29AD}" name="expected" dataDxfId="261"/>
+    <tableColumn id="3" xr3:uid="{B095BBF3-B41C-4F5B-9689-A075BCD3B3C6}" name="output" dataDxfId="260">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Add_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -12217,25 +10981,25 @@
     xlInt.Add(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8A3FC5E9-718D-42AA-90B8-83E1D4F3B18A}" name="passing" totalsRowFunction="custom" dataDxfId="382" totalsRowDxfId="381">
+    <tableColumn id="4" xr3:uid="{8A3FC5E9-718D-42AA-90B8-83E1D4F3B18A}" name="passing" totalsRowFunction="custom" dataDxfId="259" totalsRowDxfId="258">
       <calculatedColumnFormula>IF(ISERROR(Add_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Add_Tests[[#This Row],[expected]]) = ERROR.TYPE(Add_Tests[[#This Row],[output]]),
     Add_Tests[[#This Row],[expected]] = Add_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Add_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DCB35414-E71F-476D-B8FC-5C98625552A8}" name="test" dataDxfId="380"/>
+    <tableColumn id="5" xr3:uid="{DCB35414-E71F-476D-B8FC-5C98625552A8}" name="test" dataDxfId="257"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{DE30AD6A-E7CB-4B0A-9AF6-2A68597C812D}" name="Sub_Tests" displayName="Sub_Tests" ref="A172:E176" totalsRowCount="1" dataDxfId="379">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{DE30AD6A-E7CB-4B0A-9AF6-2A68597C812D}" name="Sub_Tests" displayName="Sub_Tests" ref="A172:E176" totalsRowCount="1" dataDxfId="256">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{03074968-5409-421B-94C4-D5670F4C41D8}" name="input" dataDxfId="378"/>
-    <tableColumn id="2" xr3:uid="{DDFFA8C5-FCAB-4C4D-9AD1-92357F9E25A7}" name="expected" dataDxfId="377"/>
-    <tableColumn id="3" xr3:uid="{799B106A-FDF6-4F6C-8D67-8B6355524DD8}" name="output" dataDxfId="376">
+    <tableColumn id="1" xr3:uid="{03074968-5409-421B-94C4-D5670F4C41D8}" name="input" dataDxfId="255"/>
+    <tableColumn id="2" xr3:uid="{DDFFA8C5-FCAB-4C4D-9AD1-92357F9E25A7}" name="expected" dataDxfId="254"/>
+    <tableColumn id="3" xr3:uid="{799B106A-FDF6-4F6C-8D67-8B6355524DD8}" name="output" dataDxfId="253">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Sub_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -12243,25 +11007,25 @@
     xlInt.Sub(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{365F4930-D4D1-407A-94F0-4578BEFB456D}" name="passing" totalsRowFunction="custom" dataDxfId="375" totalsRowDxfId="374">
+    <tableColumn id="4" xr3:uid="{365F4930-D4D1-407A-94F0-4578BEFB456D}" name="passing" totalsRowFunction="custom" dataDxfId="252" totalsRowDxfId="251">
       <calculatedColumnFormula>IF(ISERROR(Sub_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Sub_Tests[[#This Row],[expected]]) = ERROR.TYPE(Sub_Tests[[#This Row],[output]]),
     Sub_Tests[[#This Row],[expected]] = Sub_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Sub_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CD9B4489-0AA4-43C4-9B29-8D70A32DD746}" name="test" dataDxfId="373"/>
+    <tableColumn id="5" xr3:uid="{CD9B4489-0AA4-43C4-9B29-8D70A32DD746}" name="test" dataDxfId="250"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{9E3906E7-DD79-4AAB-8367-36E413E4200E}" name="Split_Tests" displayName="Split_Tests" ref="A179:E183" totalsRowCount="1" dataDxfId="372">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{9E3906E7-DD79-4AAB-8367-36E413E4200E}" name="Split_Tests" displayName="Split_Tests" ref="A179:E183" totalsRowCount="1" dataDxfId="249">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{14CAD510-CB82-4DB3-9F1C-40F2CB704D1C}" name="input" dataDxfId="371"/>
-    <tableColumn id="2" xr3:uid="{5035D4AE-F48A-40D0-AF90-BDA3391536CB}" name="expected" dataDxfId="370"/>
-    <tableColumn id="3" xr3:uid="{99876D23-ABB8-4C24-98A4-1BEEEEDD07C4}" name="output" dataDxfId="369">
+    <tableColumn id="1" xr3:uid="{14CAD510-CB82-4DB3-9F1C-40F2CB704D1C}" name="input" dataDxfId="248"/>
+    <tableColumn id="2" xr3:uid="{5035D4AE-F48A-40D0-AF90-BDA3391536CB}" name="expected" dataDxfId="247"/>
+    <tableColumn id="3" xr3:uid="{99876D23-ABB8-4C24-98A4-1BEEEEDD07C4}" name="output" dataDxfId="246">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.input_k, _xlfn.REGEXEXTRACT(Split_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.input, INDEX(_xlpm.input_k,1,1),
@@ -12271,25 +11035,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A5A07BB4-21F2-4B01-9D44-1AA4366EAB7F}" name="passing" totalsRowFunction="custom" dataDxfId="368" totalsRowDxfId="367">
+    <tableColumn id="4" xr3:uid="{A5A07BB4-21F2-4B01-9D44-1AA4366EAB7F}" name="passing" totalsRowFunction="custom" dataDxfId="245" totalsRowDxfId="244">
       <calculatedColumnFormula>IF(ISERROR(Split_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Split_Tests[[#This Row],[expected]]) = ERROR.TYPE(Split_Tests[[#This Row],[output]]),
     Split_Tests[[#This Row],[expected]] = Split_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Split_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{12903E1A-EF63-4775-8029-4AC6E1371182}" name="test" dataDxfId="366"/>
+    <tableColumn id="5" xr3:uid="{12903E1A-EF63-4775-8029-4AC6E1371182}" name="test" dataDxfId="243"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{B4199465-17FF-401D-8825-47D1965ACDD0}" name="UMatrixSum_Tests" displayName="UMatrixSum_Tests" ref="A186:E191" totalsRowCount="1" dataDxfId="365">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{B4199465-17FF-401D-8825-47D1965ACDD0}" name="UMatrixSum_Tests" displayName="UMatrixSum_Tests" ref="A186:E191" totalsRowCount="1" dataDxfId="242">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{02600896-7D14-484F-821B-B4456983BB28}" name="input" dataDxfId="364"/>
-    <tableColumn id="2" xr3:uid="{173735CF-904D-4F11-81E2-08E18A2E350F}" name="expected" dataDxfId="363"/>
-    <tableColumn id="3" xr3:uid="{39C7D243-2D28-43C6-84E9-009686A8BE25}" name="output" dataDxfId="362">
+    <tableColumn id="1" xr3:uid="{02600896-7D14-484F-821B-B4456983BB28}" name="input" dataDxfId="241"/>
+    <tableColumn id="2" xr3:uid="{173735CF-904D-4F11-81E2-08E18A2E350F}" name="expected" dataDxfId="240"/>
+    <tableColumn id="3" xr3:uid="{39C7D243-2D28-43C6-84E9-009686A8BE25}" name="output" dataDxfId="239">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.limbs_k, _xlfn.REGEXEXTRACT(UMatrixSum_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.limbs, _xlfn.TEXTSPLIT(INDEX(_xlpm.limbs_k,1,1), ",", ";"),
@@ -12298,14 +11062,14 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{708213D7-3DCF-48EE-85F0-411FE836D86B}" name="passing" totalsRowFunction="custom" dataDxfId="361" totalsRowDxfId="360">
+    <tableColumn id="4" xr3:uid="{708213D7-3DCF-48EE-85F0-411FE836D86B}" name="passing" totalsRowFunction="custom" dataDxfId="238" totalsRowDxfId="237">
       <calculatedColumnFormula>IF(ISERROR(UMatrixSum_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UMatrixSum_Tests[[#This Row],[expected]]) = ERROR.TYPE(UMatrixSum_Tests[[#This Row],[output]]),
     UMatrixSum_Tests[[#This Row],[expected]] = UMatrixSum_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UMatrixSum_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{1A2B4059-059A-4B6D-8573-AF782E91D2A9}" name="test" dataDxfId="359"/>
+    <tableColumn id="5" xr3:uid="{1A2B4059-059A-4B6D-8573-AF782E91D2A9}" name="test" dataDxfId="236"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12316,14 +11080,14 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9C2FC9B7-0634-4588-8EFB-AD967A0F24A8}" name="input"/>
     <tableColumn id="2" xr3:uid="{282A94A0-1EBE-4152-8A9A-8F0EF95A0338}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{1B45BBB4-DEF0-4F8A-9D99-3837C2C1D0A6}" name="output" dataDxfId="358">
+    <tableColumn id="3" xr3:uid="{1B45BBB4-DEF0-4F8A-9D99-3837C2C1D0A6}" name="output" dataDxfId="235">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.range, _xlfn.REGEXEXTRACT(Sum_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.big_ints, IFERROR(_xlfn.TEXTSPLIT(INDEX(_xlpm.range,1,1), ",", ";"), ""),
     xlInt.Sum(_xlpm.big_ints)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EE8AD54F-5219-409B-ABCC-BA23AB35B017}" name="passing" totalsRowFunction="custom" dataDxfId="357" totalsRowDxfId="356">
+    <tableColumn id="4" xr3:uid="{EE8AD54F-5219-409B-ABCC-BA23AB35B017}" name="passing" totalsRowFunction="custom" dataDxfId="234" totalsRowDxfId="233">
       <calculatedColumnFormula>IF(ISERROR(Sum_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Sum_Tests[[#This Row],[expected]]) = ERROR.TYPE(Sum_Tests[[#This Row],[output]]),
     Sum_Tests[[#This Row],[expected]] = Sum_Tests[[#This Row],[output]]
@@ -12337,11 +11101,11 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{106EA359-E4B0-4842-9C9A-062E9FF7B5FB}" name="UMul_Tests" displayName="UMul_Tests" ref="A205:E211" totalsRowCount="1" dataDxfId="355">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{106EA359-E4B0-4842-9C9A-062E9FF7B5FB}" name="UMul_Tests" displayName="UMul_Tests" ref="A205:E211" totalsRowCount="1" dataDxfId="232">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8D4F0565-063F-4316-9C57-705162867D2A}" name="input" dataDxfId="354"/>
-    <tableColumn id="2" xr3:uid="{DAD4A921-C714-4DCC-AADE-BAF6086A3636}" name="expected" dataDxfId="353"/>
-    <tableColumn id="3" xr3:uid="{97E6E3DD-CA0A-4372-AC3D-9A495F7C3A53}" name="output" dataDxfId="352">
+    <tableColumn id="1" xr3:uid="{8D4F0565-063F-4316-9C57-705162867D2A}" name="input" dataDxfId="231"/>
+    <tableColumn id="2" xr3:uid="{DAD4A921-C714-4DCC-AADE-BAF6086A3636}" name="expected" dataDxfId="230"/>
+    <tableColumn id="3" xr3:uid="{97E6E3DD-CA0A-4372-AC3D-9A495F7C3A53}" name="output" dataDxfId="229">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(UMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -12353,25 +11117,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E46610B1-FA9D-4582-8D0C-63D1EC61D64E}" name="passing" totalsRowFunction="custom" dataDxfId="351" totalsRowDxfId="350">
+    <tableColumn id="4" xr3:uid="{E46610B1-FA9D-4582-8D0C-63D1EC61D64E}" name="passing" totalsRowFunction="custom" dataDxfId="228" totalsRowDxfId="227">
       <calculatedColumnFormula>IF(ISERROR(UMul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UMul_Tests[[#This Row],[output]]),
     UMul_Tests[[#This Row],[expected]] = UMul_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UMul_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5337E378-248A-4061-ABD9-D618DD84E539}" name="test" dataDxfId="349"/>
+    <tableColumn id="5" xr3:uid="{5337E378-248A-4061-ABD9-D618DD84E539}" name="test" dataDxfId="226"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D11AB36-7D48-42C4-B8E7-63DA272F75B3}" name="SafeK_Tests" displayName="SafeK_Tests" ref="A29:E37" totalsRowCount="1" dataDxfId="448">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D11AB36-7D48-42C4-B8E7-63DA272F75B3}" name="SafeK_Tests" displayName="SafeK_Tests" ref="A29:E37" totalsRowCount="1" dataDxfId="325">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{CD46518C-03B6-4B43-A7B8-7360525A290D}" name="input" dataDxfId="447"/>
-    <tableColumn id="3" xr3:uid="{F3B44865-B013-44C5-A9D4-1A13BFE5AA81}" name="expected" dataDxfId="446"/>
-    <tableColumn id="4" xr3:uid="{F40E0393-EF6C-4B2D-9F49-5CBB088EB267}" name="output" dataDxfId="445">
+    <tableColumn id="2" xr3:uid="{CD46518C-03B6-4B43-A7B8-7360525A290D}" name="input" dataDxfId="324"/>
+    <tableColumn id="3" xr3:uid="{F3B44865-B013-44C5-A9D4-1A13BFE5AA81}" name="expected" dataDxfId="323"/>
+    <tableColumn id="4" xr3:uid="{F40E0393-EF6C-4B2D-9F49-5CBB088EB267}" name="output" dataDxfId="322">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.op_items, _xlfn.REGEXEXTRACT(SafeK_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.op, INDEX(_xlpm.op_items,1,1),
@@ -12380,25 +11144,25 @@
     internal.xlInt.SafeK(_xlpm.op, _xlpm.max_items)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{62988A37-52EF-4F3E-82FE-0F2CD420BEF5}" name="passing" totalsRowFunction="custom" dataDxfId="444">
+    <tableColumn id="5" xr3:uid="{62988A37-52EF-4F3E-82FE-0F2CD420BEF5}" name="passing" totalsRowFunction="custom" dataDxfId="321">
       <calculatedColumnFormula>IF(ISERROR(SafeK_Tests[[#This Row],[expected]]),
     ERROR.TYPE(SafeK_Tests[[#This Row],[expected]]) = ERROR.TYPE(SafeK_Tests[[#This Row],[output]]),
     SafeK_Tests[[#This Row],[expected]] = SafeK_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(SafeK_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{FB9EC421-276B-4C54-8F46-BB5C01271314}" name="test" dataDxfId="443"/>
+    <tableColumn id="6" xr3:uid="{FB9EC421-276B-4C54-8F46-BB5C01271314}" name="test" dataDxfId="320"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C927379E-9D9F-446A-A7F8-18937FDB3BE9}" name="Mul_Tests" displayName="Mul_Tests" ref="A214:E221" totalsRowCount="1" dataDxfId="348">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C927379E-9D9F-446A-A7F8-18937FDB3BE9}" name="Mul_Tests" displayName="Mul_Tests" ref="A214:E221" totalsRowCount="1" dataDxfId="225">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3AEB129A-112F-4626-87D9-516E40338A3B}" name="input" dataDxfId="347" totalsRowDxfId="346"/>
-    <tableColumn id="2" xr3:uid="{17E1D158-0134-4800-97A0-9A914A48AA8F}" name="expected" dataDxfId="345" totalsRowDxfId="344"/>
-    <tableColumn id="3" xr3:uid="{B25D54E8-D438-48E6-9956-B82746478514}" name="output" dataDxfId="343" totalsRowDxfId="342">
+    <tableColumn id="1" xr3:uid="{3AEB129A-112F-4626-87D9-516E40338A3B}" name="input" dataDxfId="224" totalsRowDxfId="223"/>
+    <tableColumn id="2" xr3:uid="{17E1D158-0134-4800-97A0-9A914A48AA8F}" name="expected" dataDxfId="222" totalsRowDxfId="221"/>
+    <tableColumn id="3" xr3:uid="{B25D54E8-D438-48E6-9956-B82746478514}" name="output" dataDxfId="220" totalsRowDxfId="219">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Mul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -12406,25 +11170,25 @@
     xlInt.Mul(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5D503E6C-603A-418E-8D29-E96FF9E82626}" name="passing" totalsRowFunction="custom" dataDxfId="341" totalsRowDxfId="340">
+    <tableColumn id="4" xr3:uid="{5D503E6C-603A-418E-8D29-E96FF9E82626}" name="passing" totalsRowFunction="custom" dataDxfId="218" totalsRowDxfId="217">
       <calculatedColumnFormula>IF(ISERROR(Mul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Mul_Tests[[#This Row],[expected]]) = ERROR.TYPE(Mul_Tests[[#This Row],[output]]),
     Mul_Tests[[#This Row],[expected]] = Mul_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Mul_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{785B4909-13EC-4ABC-ADF8-0A6E8C364AE8}" name="test" dataDxfId="339" totalsRowDxfId="338"/>
+    <tableColumn id="5" xr3:uid="{785B4909-13EC-4ABC-ADF8-0A6E8C364AE8}" name="test" dataDxfId="216" totalsRowDxfId="215"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{4706FBB1-54D9-4F64-9481-F1D8984AE18E}" name="KnuthDiv_Tests" displayName="KnuthDiv_Tests" ref="A224:E233" totalsRowCount="1" dataDxfId="337">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{4706FBB1-54D9-4F64-9481-F1D8984AE18E}" name="KnuthDiv_Tests" displayName="KnuthDiv_Tests" ref="A224:E233" totalsRowCount="1" dataDxfId="214">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C9306945-CA62-4719-882E-A0FFCFC80239}" name="input" dataDxfId="336"/>
-    <tableColumn id="2" xr3:uid="{FF30C91E-2B8D-47FA-B34B-6CA5257E3EB7}" name="expected" dataDxfId="335"/>
-    <tableColumn id="3" xr3:uid="{3B324DA4-4AAE-408C-B627-929F7D5C7CBF}" name="output" dataDxfId="334">
+    <tableColumn id="1" xr3:uid="{C9306945-CA62-4719-882E-A0FFCFC80239}" name="input" dataDxfId="213"/>
+    <tableColumn id="2" xr3:uid="{FF30C91E-2B8D-47FA-B34B-6CA5257E3EB7}" name="expected" dataDxfId="212"/>
+    <tableColumn id="3" xr3:uid="{3B324DA4-4AAE-408C-B627-929F7D5C7CBF}" name="output" dataDxfId="211">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(KnuthDiv_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -12436,25 +11200,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{439AD3AD-5C90-48C6-AB74-B9DDF87C40B5}" name="passing" totalsRowFunction="custom" dataDxfId="333" totalsRowDxfId="332">
+    <tableColumn id="4" xr3:uid="{439AD3AD-5C90-48C6-AB74-B9DDF87C40B5}" name="passing" totalsRowFunction="custom" dataDxfId="210" totalsRowDxfId="209">
       <calculatedColumnFormula>IF(ISERROR(KnuthDiv_Tests[[#This Row],[expected]]),
     ERROR.TYPE(KnuthDiv_Tests[[#This Row],[expected]]) = ERROR.TYPE(KnuthDiv_Tests[[#This Row],[output]]),
     KnuthDiv_Tests[[#This Row],[expected]] = KnuthDiv_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(KnuthDiv_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7D4887A2-EC0B-4C52-8336-E300544022A1}" name="test" dataDxfId="331"/>
+    <tableColumn id="5" xr3:uid="{7D4887A2-EC0B-4C52-8336-E300544022A1}" name="test" dataDxfId="208"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B0C6E940-EAB6-4373-8987-1B7722C2CC79}" name="Div_Tests" displayName="Div_Tests" ref="A236:E247" totalsRowCount="1" dataDxfId="330">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B0C6E940-EAB6-4373-8987-1B7722C2CC79}" name="Div_Tests" displayName="Div_Tests" ref="A236:E247" totalsRowCount="1" dataDxfId="207">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{0A49EAE4-5B09-4D2D-A863-D634A4825565}" name="input" dataDxfId="329" totalsRowDxfId="328"/>
-    <tableColumn id="2" xr3:uid="{4BF042F3-E337-4B63-A1E8-414D47019404}" name="expected" dataDxfId="327" totalsRowDxfId="326"/>
-    <tableColumn id="3" xr3:uid="{118ABB7A-7163-40CB-974E-69BFF6BE2BE0}" name="output" dataDxfId="325" totalsRowDxfId="324">
+    <tableColumn id="1" xr3:uid="{0A49EAE4-5B09-4D2D-A863-D634A4825565}" name="input" dataDxfId="206" totalsRowDxfId="205"/>
+    <tableColumn id="2" xr3:uid="{4BF042F3-E337-4B63-A1E8-414D47019404}" name="expected" dataDxfId="204" totalsRowDxfId="203"/>
+    <tableColumn id="3" xr3:uid="{118ABB7A-7163-40CB-974E-69BFF6BE2BE0}" name="output" dataDxfId="202" totalsRowDxfId="201">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Div_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -12462,25 +11226,25 @@
     xlInt.Div(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4344C6C8-3F96-4048-96D0-CA621258C1D7}" name="passing" totalsRowFunction="custom" dataDxfId="323" totalsRowDxfId="322">
+    <tableColumn id="4" xr3:uid="{4344C6C8-3F96-4048-96D0-CA621258C1D7}" name="passing" totalsRowFunction="custom" dataDxfId="200" totalsRowDxfId="199">
       <calculatedColumnFormula>IF(ISERROR(Div_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Div_Tests[[#This Row],[expected]]) = ERROR.TYPE(Div_Tests[[#This Row],[output]]),
     Div_Tests[[#This Row],[expected]] = Div_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Div_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7CF48835-D05B-4120-863E-A47318569688}" name="test" dataDxfId="321" totalsRowDxfId="320"/>
+    <tableColumn id="5" xr3:uid="{7CF48835-D05B-4120-863E-A47318569688}" name="test" dataDxfId="198" totalsRowDxfId="197"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{B3179C39-4489-4B3E-A2D2-1A2B50DC058E}" name="Mod_Tests" displayName="Mod_Tests" ref="A250:E261" totalsRowCount="1" dataDxfId="319">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{B3179C39-4489-4B3E-A2D2-1A2B50DC058E}" name="Mod_Tests" displayName="Mod_Tests" ref="A250:E261" totalsRowCount="1" dataDxfId="196">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F1BCBD73-ACF5-4609-87F5-A9FAB549955E}" name="input" dataDxfId="318" totalsRowDxfId="317"/>
-    <tableColumn id="2" xr3:uid="{E9604163-FD58-4190-8D72-28AA7831E8C8}" name="expected" dataDxfId="316" totalsRowDxfId="315"/>
-    <tableColumn id="3" xr3:uid="{9D21CE79-D00B-4182-97B3-60EF6DC8B18F}" name="output" dataDxfId="314" totalsRowDxfId="313">
+    <tableColumn id="1" xr3:uid="{F1BCBD73-ACF5-4609-87F5-A9FAB549955E}" name="input" dataDxfId="195" totalsRowDxfId="194"/>
+    <tableColumn id="2" xr3:uid="{E9604163-FD58-4190-8D72-28AA7831E8C8}" name="expected" dataDxfId="193" totalsRowDxfId="192"/>
+    <tableColumn id="3" xr3:uid="{9D21CE79-D00B-4182-97B3-60EF6DC8B18F}" name="output" dataDxfId="191" totalsRowDxfId="190">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Mod_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -12488,25 +11252,25 @@
     xlInt.Mod(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CEF047D2-0521-425D-99C4-E3B997A68B32}" name="passing" totalsRowFunction="custom" dataDxfId="312" totalsRowDxfId="311">
+    <tableColumn id="4" xr3:uid="{CEF047D2-0521-425D-99C4-E3B997A68B32}" name="passing" totalsRowFunction="custom" dataDxfId="189" totalsRowDxfId="188">
       <calculatedColumnFormula>IF(ISERROR(Mod_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Mod_Tests[[#This Row],[expected]]) = ERROR.TYPE(Mod_Tests[[#This Row],[output]]),
     Mod_Tests[[#This Row],[expected]] = Mod_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Mod_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{BB0A3941-EEFB-445E-AE7B-833C36649910}" name="test" dataDxfId="310" totalsRowDxfId="309"/>
+    <tableColumn id="5" xr3:uid="{BB0A3941-EEFB-445E-AE7B-833C36649910}" name="test" dataDxfId="187" totalsRowDxfId="186"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{82953E35-FA6B-4DA1-B4AC-195D4F1BB7C8}" name="DivMod_Tests" displayName="DivMod_Tests" ref="A264:E280" totalsRowCount="1" dataDxfId="308">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{82953E35-FA6B-4DA1-B4AC-195D4F1BB7C8}" name="DivMod_Tests" displayName="DivMod_Tests" ref="A264:E280" totalsRowCount="1" dataDxfId="185">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E51BC97B-AA0D-4705-AF36-89CB4A3501FF}" name="input" dataDxfId="307" totalsRowDxfId="306"/>
-    <tableColumn id="2" xr3:uid="{6D6483DD-139D-4DFE-BFEA-8BAA3E5C6FCF}" name="expected" dataDxfId="305" totalsRowDxfId="304"/>
-    <tableColumn id="3" xr3:uid="{17DE90BB-4525-4C2D-9577-C4372DCD74B3}" name="output" dataDxfId="303" totalsRowDxfId="302">
+    <tableColumn id="1" xr3:uid="{E51BC97B-AA0D-4705-AF36-89CB4A3501FF}" name="input" dataDxfId="184" totalsRowDxfId="183"/>
+    <tableColumn id="2" xr3:uid="{6D6483DD-139D-4DFE-BFEA-8BAA3E5C6FCF}" name="expected" dataDxfId="182" totalsRowDxfId="181"/>
+    <tableColumn id="3" xr3:uid="{17DE90BB-4525-4C2D-9577-C4372DCD74B3}" name="output" dataDxfId="180" totalsRowDxfId="179">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.ab_flag, _xlfn.REGEXEXTRACT(DivMod_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab_flag,1,1),
@@ -12515,25 +11279,25 @@
     _xlfn.ARRAYTOTEXT(xlInt.DivMod(_xlpm.a, _xlpm.b, _xlpm.use_floor), 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{08745616-1601-437B-82EA-C1952393A99B}" name="passing" totalsRowFunction="custom" dataDxfId="301" totalsRowDxfId="300">
+    <tableColumn id="4" xr3:uid="{08745616-1601-437B-82EA-C1952393A99B}" name="passing" totalsRowFunction="custom" dataDxfId="178" totalsRowDxfId="177">
       <calculatedColumnFormula>IF(ISERROR(DivMod_Tests[[#This Row],[expected]]),
     ERROR.TYPE(DivMod_Tests[[#This Row],[expected]]) = ERROR.TYPE(DivMod_Tests[[#This Row],[output]]),
     DivMod_Tests[[#This Row],[expected]] = DivMod_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(DivMod_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{10C8AB14-1CD9-4B06-8A65-2B27B32A2550}" name="test" dataDxfId="299" totalsRowDxfId="298"/>
+    <tableColumn id="5" xr3:uid="{10C8AB14-1CD9-4B06-8A65-2B27B32A2550}" name="test" dataDxfId="176" totalsRowDxfId="175"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{3400C680-561E-4111-B80A-CA24DB597E3F}" name="Table25" displayName="Table25" ref="A283:E289" totalsRowCount="1" dataDxfId="297">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{3400C680-561E-4111-B80A-CA24DB597E3F}" name="Table25" displayName="Table25" ref="A283:E289" totalsRowCount="1" dataDxfId="174">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{37EA378F-E179-45E1-BF1A-FBA82C305DBA}" name="input" dataDxfId="296"/>
-    <tableColumn id="2" xr3:uid="{11DFB020-1D5E-4E26-A86F-6B73428F3709}" name="expected" dataDxfId="295"/>
-    <tableColumn id="3" xr3:uid="{943FD3EB-6145-4BEE-9408-F68BE0795A47}" name="output" dataDxfId="294">
+    <tableColumn id="1" xr3:uid="{37EA378F-E179-45E1-BF1A-FBA82C305DBA}" name="input" dataDxfId="173"/>
+    <tableColumn id="2" xr3:uid="{11DFB020-1D5E-4E26-A86F-6B73428F3709}" name="expected" dataDxfId="172"/>
+    <tableColumn id="3" xr3:uid="{943FD3EB-6145-4BEE-9408-F68BE0795A47}" name="output" dataDxfId="171">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.bk, _xlfn.REGEXEXTRACT(Table25[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.b, INDEX(_xlpm.bk,1,1),
@@ -12543,49 +11307,49 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{165ECACC-11AD-4EB0-AE14-7D528DA64799}" name="passing" totalsRowFunction="custom" dataDxfId="293" totalsRowDxfId="292">
+    <tableColumn id="4" xr3:uid="{165ECACC-11AD-4EB0-AE14-7D528DA64799}" name="passing" totalsRowFunction="custom" dataDxfId="170" totalsRowDxfId="169">
       <calculatedColumnFormula>IF(ISERROR(Table25[[#This Row],[expected]]),
     ERROR.TYPE(Table25[[#This Row],[expected]]) = ERROR.TYPE(Table25[[#This Row],[output]]),
     Table25[[#This Row],[expected]] = Table25[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Table25[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6FA8F2E3-9F29-41C5-8B60-45E4EF5BFD33}" name="test" dataDxfId="291"/>
+    <tableColumn id="5" xr3:uid="{6FA8F2E3-9F29-41C5-8B60-45E4EF5BFD33}" name="test" dataDxfId="168"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{12A27437-8E10-4142-9D59-10A781936664}" name="IsEven_Tests" displayName="IsEven_Tests" ref="A292:E301" totalsRowCount="1" tableBorderDxfId="290">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{12A27437-8E10-4142-9D59-10A781936664}" name="IsEven_Tests" displayName="IsEven_Tests" ref="A292:E301" totalsRowCount="1" tableBorderDxfId="167">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{72B34F2A-D724-472B-AEA6-85847044F8BB}" name="input"/>
     <tableColumn id="2" xr3:uid="{8F1A9828-E68A-40FE-8534-E28D2B59C43A}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{90993922-EF49-4320-BFDE-A85AAC37995B}" name="output" dataDxfId="289">
+    <tableColumn id="3" xr3:uid="{90993922-EF49-4320-BFDE-A85AAC37995B}" name="output" dataDxfId="166">
       <calculatedColumnFormula array="1">BigInt.IsEven(IsEven_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4CD10349-78F4-4A08-8AD3-6AFDD4218B3F}" name="passing" totalsRowFunction="custom" dataDxfId="288">
+    <tableColumn id="4" xr3:uid="{4CD10349-78F4-4A08-8AD3-6AFDD4218B3F}" name="passing" totalsRowFunction="custom" dataDxfId="165">
       <calculatedColumnFormula>IF(ISERROR(IsEven_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsEven_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsEven_Tests[[#This Row],[output]]),
     IsEven_Tests[[#This Row],[expected]] = IsEven_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(IsEven_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9C811914-2121-4942-94F0-B4760C307266}" name="test" dataDxfId="287"/>
+    <tableColumn id="5" xr3:uid="{9C811914-2121-4942-94F0-B4760C307266}" name="test" dataDxfId="164"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{29B30C5B-F766-4073-878A-FEDF3C607366}" name="IsOdd_Tests" displayName="IsOdd_Tests" ref="A304:E313" totalsRowCount="1" tableBorderDxfId="286">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{29B30C5B-F766-4073-878A-FEDF3C607366}" name="IsOdd_Tests" displayName="IsOdd_Tests" ref="A304:E313" totalsRowCount="1" tableBorderDxfId="163">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8D247229-1BE2-49B1-BEC8-19AFBBF671FC}" name="input"/>
     <tableColumn id="2" xr3:uid="{9F1FC5CC-11FA-4EB1-BA6E-3C18F4379652}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{6B07B988-F191-4E41-81FA-8D0020D0AEF2}" name="output" dataDxfId="285">
+    <tableColumn id="3" xr3:uid="{6B07B988-F191-4E41-81FA-8D0020D0AEF2}" name="output" dataDxfId="162">
       <calculatedColumnFormula array="1">BigInt.IsOdd(IsOdd_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{15820A65-99F4-420C-A89B-1F6FB8202BCC}" name="passing" totalsRowFunction="custom" dataDxfId="284">
+    <tableColumn id="4" xr3:uid="{15820A65-99F4-420C-A89B-1F6FB8202BCC}" name="passing" totalsRowFunction="custom" dataDxfId="161">
       <calculatedColumnFormula>IF(ISERROR(IsOdd_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsOdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsOdd_Tests[[#This Row],[output]]),
     IsOdd_Tests[[#This Row],[expected]] = IsOdd_Tests[[#This Row],[output]]
@@ -12599,11 +11363,11 @@
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{371705AE-DD2A-4348-9D77-10A58AFED934}" name="Pow_Tests" displayName="Pow_Tests" ref="A327:E341" totalsRowCount="1" dataDxfId="283">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{371705AE-DD2A-4348-9D77-10A58AFED934}" name="Pow_Tests" displayName="Pow_Tests" ref="A327:E341" totalsRowCount="1" dataDxfId="160">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{428DC074-F3C2-4541-81E6-FDDAE2482D27}" name="input" dataDxfId="282"/>
-    <tableColumn id="2" xr3:uid="{B5FD2A40-BCC5-4580-B8CD-768791024AC5}" name="expected" dataDxfId="281"/>
-    <tableColumn id="3" xr3:uid="{F4E39208-EEA5-4CF3-B04A-4707F3E1FB8E}" name="output" dataDxfId="280">
+    <tableColumn id="1" xr3:uid="{428DC074-F3C2-4541-81E6-FDDAE2482D27}" name="input" dataDxfId="159"/>
+    <tableColumn id="2" xr3:uid="{B5FD2A40-BCC5-4580-B8CD-768791024AC5}" name="expected" dataDxfId="158"/>
+    <tableColumn id="3" xr3:uid="{F4E39208-EEA5-4CF3-B04A-4707F3E1FB8E}" name="output" dataDxfId="157">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Pow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab, 1, 1),
@@ -12611,25 +11375,25 @@
     BigInt.Pow(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B407AC33-1B59-4CB2-91F2-8CA96B7CE117}" name="passing" totalsRowFunction="custom" dataDxfId="279">
+    <tableColumn id="4" xr3:uid="{B407AC33-1B59-4CB2-91F2-8CA96B7CE117}" name="passing" totalsRowFunction="custom" dataDxfId="156">
       <calculatedColumnFormula>IF(ISERROR(Pow_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Pow_Tests[[#This Row],[expected]]) = ERROR.TYPE(Pow_Tests[[#This Row],[output]]),
     Pow_Tests[[#This Row],[expected]] = Pow_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Pow_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A1A7E0C2-F1B0-41A5-A740-EDF94ACD6051}" name="test" dataDxfId="278"/>
+    <tableColumn id="5" xr3:uid="{A1A7E0C2-F1B0-41A5-A740-EDF94ACD6051}" name="test" dataDxfId="155"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{83160072-B1B0-4FD1-88FC-006B8639CBE0}" name="UPow_Tests" displayName="UPow_Tests" ref="A316:E324" totalsRowCount="1" dataDxfId="277">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{83160072-B1B0-4FD1-88FC-006B8639CBE0}" name="UPow_Tests" displayName="UPow_Tests" ref="A316:E324" totalsRowCount="1" dataDxfId="154">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{20145995-7ED4-4B73-887D-9D74DA0828CF}" name="input" dataDxfId="276"/>
-    <tableColumn id="2" xr3:uid="{82FBC2F1-B0A2-4D85-8D2F-0E9C3548EF52}" name="expected" dataDxfId="275"/>
-    <tableColumn id="3" xr3:uid="{30FC05F3-7A85-4F3C-B4CB-146B4FEBD37A}" name="output" dataDxfId="274">
+    <tableColumn id="1" xr3:uid="{20145995-7ED4-4B73-887D-9D74DA0828CF}" name="input" dataDxfId="153"/>
+    <tableColumn id="2" xr3:uid="{82FBC2F1-B0A2-4D85-8D2F-0E9C3548EF52}" name="expected" dataDxfId="152"/>
+    <tableColumn id="3" xr3:uid="{30FC05F3-7A85-4F3C-B4CB-146B4FEBD37A}" name="output" dataDxfId="151">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.bek, _xlfn.REGEXEXTRACT(UPow_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.base, INDEX(_xlpm.bek,1,1),
@@ -12640,14 +11404,14 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{13DDE135-8BB6-470E-A96F-6482CA5075E2}" name="passing" totalsRowFunction="custom" dataDxfId="273">
+    <tableColumn id="4" xr3:uid="{13DDE135-8BB6-470E-A96F-6482CA5075E2}" name="passing" totalsRowFunction="custom" dataDxfId="150">
       <calculatedColumnFormula>IF(ISERROR(UPow_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UPow_Tests[[#This Row],[expected]]) = ERROR.TYPE(UPow_Tests[[#This Row],[output]]),
     UPow_Tests[[#This Row],[expected]] = UPow_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UPow_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{45AF5A50-06F2-4581-B704-1F7379E7EFDB}" name="test" dataDxfId="272"/>
+    <tableColumn id="5" xr3:uid="{45AF5A50-06F2-4581-B704-1F7379E7EFDB}" name="test" dataDxfId="149"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12658,7 +11422,7 @@
   <tableColumns count="5">
     <tableColumn id="2" xr3:uid="{2286D15B-F261-49FF-90E5-E32FAEEEA489}" name="input"/>
     <tableColumn id="3" xr3:uid="{1D45A0AC-7049-4C3E-9D4F-CF777F60006B}" name="expected"/>
-    <tableColumn id="4" xr3:uid="{725B7147-ED3D-42D7-9030-A0FCAF6502D0}" name="output" dataDxfId="442">
+    <tableColumn id="4" xr3:uid="{725B7147-ED3D-42D7-9030-A0FCAF6502D0}" name="output" dataDxfId="319">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.limbs_k, _xlfn.REGEXEXTRACT(Merge_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.limbs_text, INDEX(_xlpm.limbs_k,1,1),
@@ -12667,25 +11431,25 @@
     internal.xlInt.Merge(_xlpm.limbs, _xlpm.k)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7D40DA54-4D50-4770-9171-9F50106783D7}" name="passing" totalsRowFunction="custom" dataDxfId="441">
+    <tableColumn id="5" xr3:uid="{7D40DA54-4D50-4770-9171-9F50106783D7}" name="passing" totalsRowFunction="custom" dataDxfId="318">
       <calculatedColumnFormula>IF(ISERROR(Merge_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Merge_Tests[[#This Row],[expected]]) = ERROR.TYPE(Merge_Tests[[#This Row],[output]]),
     Merge_Tests[[#This Row],[expected]] = Merge_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Merge_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F906F95B-0DD5-4F50-9A36-C63DEC4B514C}" name="test" dataDxfId="440"/>
+    <tableColumn id="6" xr3:uid="{F906F95B-0DD5-4F50-9A36-C63DEC4B514C}" name="test" dataDxfId="317"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{56E07932-566C-4BD6-8077-730BDDB685D7}" name="USqrt_Tests" displayName="USqrt_Tests" ref="A344:E348" totalsRowCount="1" dataDxfId="271">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{56E07932-566C-4BD6-8077-730BDDB685D7}" name="USqrt_Tests" displayName="USqrt_Tests" ref="A344:E348" totalsRowCount="1" dataDxfId="148">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7D0B28FD-9EB7-4A3D-892B-9C8FB4B3B2F5}" name="input" dataDxfId="270"/>
-    <tableColumn id="2" xr3:uid="{CFF29D88-DF87-4564-930E-26EAF1CB3332}" name="expected" dataDxfId="269"/>
-    <tableColumn id="3" xr3:uid="{4738BA38-2D1B-4B90-8625-6A923FAABAE8}" name="output" dataDxfId="268">
+    <tableColumn id="1" xr3:uid="{7D0B28FD-9EB7-4A3D-892B-9C8FB4B3B2F5}" name="input" dataDxfId="147"/>
+    <tableColumn id="2" xr3:uid="{CFF29D88-DF87-4564-930E-26EAF1CB3332}" name="expected" dataDxfId="146"/>
+    <tableColumn id="3" xr3:uid="{4738BA38-2D1B-4B90-8625-6A923FAABAE8}" name="output" dataDxfId="145">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.radicand_seed_k, _xlfn.REGEXEXTRACT(USqrt_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.radicand, INDEX(_xlpm.radicand_seed_k,1,1),
@@ -12697,25 +11461,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{118D95C4-A916-4992-AEA0-6F30E3EE33F9}" name="passing" totalsRowFunction="custom" dataDxfId="267" totalsRowDxfId="266">
+    <tableColumn id="4" xr3:uid="{118D95C4-A916-4992-AEA0-6F30E3EE33F9}" name="passing" totalsRowFunction="custom" dataDxfId="144" totalsRowDxfId="143">
       <calculatedColumnFormula>IF(ISERROR(USqrt_Tests[[#This Row],[expected]]),
     ERROR.TYPE(USqrt_Tests[[#This Row],[expected]]) = ERROR.TYPE(USqrt_Tests[[#This Row],[output]]),
     USqrt_Tests[[#This Row],[expected]] = USqrt_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(USqrt_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{36AF6E6D-247D-40D4-8B02-20DF4A48BDF2}" name="test" dataDxfId="265"/>
+    <tableColumn id="5" xr3:uid="{36AF6E6D-247D-40D4-8B02-20DF4A48BDF2}" name="test" dataDxfId="142"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{A9B2C3B0-D156-4BA1-8DBC-CCD97E178DEB}" name="NewtonRaphsonReciprocal_Tests" displayName="NewtonRaphsonReciprocal_Tests" ref="A351:E356" totalsRowCount="1" dataDxfId="264">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{A9B2C3B0-D156-4BA1-8DBC-CCD97E178DEB}" name="NewtonRaphsonReciprocal_Tests" displayName="NewtonRaphsonReciprocal_Tests" ref="A351:E356" totalsRowCount="1" dataDxfId="141">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{668CC6CC-FAA8-4201-AF7C-80B23CDDC2E9}" name="input" dataDxfId="263"/>
-    <tableColumn id="2" xr3:uid="{25DCB2CE-672E-4637-9E18-5B6DB9547223}" name="expected" dataDxfId="262"/>
-    <tableColumn id="3" xr3:uid="{90B5F5EA-1862-438B-A0B0-E7B33D47B422}" name="output" dataDxfId="261">
+    <tableColumn id="1" xr3:uid="{668CC6CC-FAA8-4201-AF7C-80B23CDDC2E9}" name="input" dataDxfId="140"/>
+    <tableColumn id="2" xr3:uid="{25DCB2CE-672E-4637-9E18-5B6DB9547223}" name="expected" dataDxfId="139"/>
+    <tableColumn id="3" xr3:uid="{90B5F5EA-1862-438B-A0B0-E7B33D47B422}" name="output" dataDxfId="138">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.b_len_k, _xlfn.REGEXEXTRACT(NewtonRaphsonReciprocal_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.b, INDEX(_xlpm.b_len_k,1,1),
@@ -12726,25 +11490,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A229F032-C11B-467F-A66D-15E5E90AC98D}" name="passing" totalsRowFunction="custom" dataDxfId="260" totalsRowDxfId="259">
+    <tableColumn id="4" xr3:uid="{A229F032-C11B-467F-A66D-15E5E90AC98D}" name="passing" totalsRowFunction="custom" dataDxfId="137" totalsRowDxfId="136">
       <calculatedColumnFormula>IF(ISERROR(NewtonRaphsonReciprocal_Tests[[#This Row],[expected]]),
     ERROR.TYPE(NewtonRaphsonReciprocal_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonReciprocal_Tests[[#This Row],[output]]),
     NewtonRaphsonReciprocal_Tests[[#This Row],[expected]] = NewtonRaphsonReciprocal_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(NewtonRaphsonReciprocal_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F159BE0D-B6F5-4516-9322-421576A9CFAC}" name="test" dataDxfId="258"/>
+    <tableColumn id="5" xr3:uid="{F159BE0D-B6F5-4516-9322-421576A9CFAC}" name="test" dataDxfId="135"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{9E5B9787-3CCB-4F73-B127-FE62EEB658A9}" name="NewtonRaphsonDiv_Tests" displayName="NewtonRaphsonDiv_Tests" ref="A359:E365" totalsRowCount="1" dataDxfId="257">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{9E5B9787-3CCB-4F73-B127-FE62EEB658A9}" name="NewtonRaphsonDiv_Tests" displayName="NewtonRaphsonDiv_Tests" ref="A359:E365" totalsRowCount="1" dataDxfId="134">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1DD49B57-7E7E-4B1C-B300-6AC09AA4507D}" name="input" dataDxfId="256"/>
-    <tableColumn id="2" xr3:uid="{F726FD71-2E54-4ACE-8BDB-45E8C22B8958}" name="expected" dataDxfId="255"/>
-    <tableColumn id="3" xr3:uid="{51451E9D-81A3-4433-AABC-FCAE4ED0B82C}" name="output" dataDxfId="254">
+    <tableColumn id="1" xr3:uid="{1DD49B57-7E7E-4B1C-B300-6AC09AA4507D}" name="input" dataDxfId="133"/>
+    <tableColumn id="2" xr3:uid="{F726FD71-2E54-4ACE-8BDB-45E8C22B8958}" name="expected" dataDxfId="132"/>
+    <tableColumn id="3" xr3:uid="{51451E9D-81A3-4433-AABC-FCAE4ED0B82C}" name="output" dataDxfId="131">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(NewtonRaphsonDiv_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -12756,71 +11520,71 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3511251B-5389-4721-A1A1-8AE06E90F9D7}" name="passing" totalsRowFunction="custom" dataDxfId="253" totalsRowDxfId="252">
+    <tableColumn id="4" xr3:uid="{3511251B-5389-4721-A1A1-8AE06E90F9D7}" name="passing" totalsRowFunction="custom" dataDxfId="130" totalsRowDxfId="129">
       <calculatedColumnFormula>IF(ISERROR(NewtonRaphsonDiv_Tests[[#This Row],[expected]]),
     ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[expected]]) = ERROR.TYPE(NewtonRaphsonDiv_Tests[[#This Row],[output]]),
     NewtonRaphsonDiv_Tests[[#This Row],[expected]] = NewtonRaphsonDiv_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(NewtonRaphsonDiv_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8FBD496E-700B-47C8-B9CA-AD0871776B53}" name="test" dataDxfId="251"/>
+    <tableColumn id="5" xr3:uid="{8FBD496E-700B-47C8-B9CA-AD0871776B53}" name="test" dataDxfId="128"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{27C0A819-84B9-4A0A-8097-03A8C95F5E27}" name="NativePrimes_Tests" displayName="NativePrimes_Tests" ref="A368:E374" totalsRowCount="1" dataDxfId="250" tableBorderDxfId="249">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{27C0A819-84B9-4A0A-8097-03A8C95F5E27}" name="NativePrimes_Tests" displayName="NativePrimes_Tests" ref="A368:E374" totalsRowCount="1" dataDxfId="127" tableBorderDxfId="126">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F29CD078-1065-436A-811B-D67567316769}" name="input" dataDxfId="248"/>
-    <tableColumn id="2" xr3:uid="{6122EAC1-506A-441B-8004-4B02E143A802}" name="expected" dataDxfId="247"/>
-    <tableColumn id="3" xr3:uid="{778AEC62-886A-4A2A-BD39-EB9F715A732B}" name="output" dataDxfId="246">
+    <tableColumn id="1" xr3:uid="{F29CD078-1065-436A-811B-D67567316769}" name="input" dataDxfId="125"/>
+    <tableColumn id="2" xr3:uid="{6122EAC1-506A-441B-8004-4B02E143A802}" name="expected" dataDxfId="124"/>
+    <tableColumn id="3" xr3:uid="{778AEC62-886A-4A2A-BD39-EB9F715A732B}" name="output" dataDxfId="123">
       <calculatedColumnFormula>_xlfn.ARRAYTOTEXT(core_BigInt.NativePrimes(NativePrimes_Tests[[#This Row],[input]]), 1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F3546CB4-2246-45FB-B499-CB4B13BA76E1}" name="passing" totalsRowFunction="custom" dataDxfId="245">
+    <tableColumn id="4" xr3:uid="{F3546CB4-2246-45FB-B499-CB4B13BA76E1}" name="passing" totalsRowFunction="custom" dataDxfId="122">
       <calculatedColumnFormula>IF(ISERROR(NativePrimes_Tests[[#This Row],[expected]]),
     ERROR.TYPE(NativePrimes_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativePrimes_Tests[[#This Row],[output]]),
     NativePrimes_Tests[[#This Row],[expected]] = NativePrimes_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(NativePrimes_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8190D20C-0392-4F85-929A-69F9BDF57A0A}" name="test" dataDxfId="244"/>
+    <tableColumn id="5" xr3:uid="{8190D20C-0392-4F85-929A-69F9BDF57A0A}" name="test" dataDxfId="121"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table34.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{49BD0AFE-381A-4E2F-A35C-4D1CCCA7584E}" name="TextTreeProd_Tests37" displayName="TextTreeProd_Tests37" ref="A386:E391" totalsRowCount="1" dataDxfId="243">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{49BD0AFE-381A-4E2F-A35C-4D1CCCA7584E}" name="TextTreeProd_Tests37" displayName="TextTreeProd_Tests37" ref="A386:E391" totalsRowCount="1" dataDxfId="120">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{998EF311-8CF0-4498-BF3E-C7591D617740}" name="input" dataDxfId="242"/>
-    <tableColumn id="2" xr3:uid="{030D33E6-C011-4057-AFBE-F1FEC05B0E3D}" name="expected" dataDxfId="241"/>
-    <tableColumn id="3" xr3:uid="{4A32034C-1A35-45CF-A8F5-5BB1FB3300A5}" name="output" dataDxfId="240">
+    <tableColumn id="1" xr3:uid="{998EF311-8CF0-4498-BF3E-C7591D617740}" name="input" dataDxfId="119"/>
+    <tableColumn id="2" xr3:uid="{030D33E6-C011-4057-AFBE-F1FEC05B0E3D}" name="expected" dataDxfId="118"/>
+    <tableColumn id="3" xr3:uid="{4A32034C-1A35-45CF-A8F5-5BB1FB3300A5}" name="output" dataDxfId="117">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.big_ints, _xlfn.REGEXEXTRACT(TextTreeProd_Tests37[[#This Row],[input]], "{\K[\w,; .-]*"),
     _xlpm.big_int_arr, _xlfn.TEXTSPLIT(_xlpm.big_ints,",",";"),
     core_BigInt.TextTreeProd(_xlpm.big_int_arr)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F4493AC7-8D4A-4E9D-A9A4-52B87367C964}" name="passing" totalsRowFunction="custom" dataDxfId="239" totalsRowDxfId="238">
+    <tableColumn id="4" xr3:uid="{F4493AC7-8D4A-4E9D-A9A4-52B87367C964}" name="passing" totalsRowFunction="custom" dataDxfId="116" totalsRowDxfId="115">
       <calculatedColumnFormula>IF(ISERROR(TextTreeProd_Tests37[[#This Row],[expected]]),
     ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[expected]]) = ERROR.TYPE(TextTreeProd_Tests37[[#This Row],[output]]),
     TextTreeProd_Tests37[[#This Row],[expected]] = TextTreeProd_Tests37[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(TextTreeProd_Tests37[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9E2E183E-0AFC-4266-8D1C-760BDBA95E9A}" name="test" dataDxfId="237"/>
+    <tableColumn id="5" xr3:uid="{9E2E183E-0AFC-4266-8D1C-760BDBA95E9A}" name="test" dataDxfId="114"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table35.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{4BA5BDEF-A87F-4855-AD37-C3A378790A0D}" name="UTextMul_Tests" displayName="UTextMul_Tests" ref="A377:E383" totalsRowCount="1" dataDxfId="236">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{4BA5BDEF-A87F-4855-AD37-C3A378790A0D}" name="UTextMul_Tests" displayName="UTextMul_Tests" ref="A377:E383" totalsRowCount="1" dataDxfId="113">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3F5F3FFD-5DC8-4A88-908C-7CEE90688FD2}" name="input" dataDxfId="235" totalsRowDxfId="234"/>
-    <tableColumn id="2" xr3:uid="{6AD81AC4-371F-4E12-BB01-43913712ADEC}" name="expected" dataDxfId="233" totalsRowDxfId="232"/>
-    <tableColumn id="3" xr3:uid="{554D388F-417A-46F4-9FA2-AACDEAA24237}" name="output" dataDxfId="231" totalsRowDxfId="230">
+    <tableColumn id="1" xr3:uid="{3F5F3FFD-5DC8-4A88-908C-7CEE90688FD2}" name="input" dataDxfId="112" totalsRowDxfId="111"/>
+    <tableColumn id="2" xr3:uid="{6AD81AC4-371F-4E12-BB01-43913712ADEC}" name="expected" dataDxfId="110" totalsRowDxfId="109"/>
+    <tableColumn id="3" xr3:uid="{554D388F-417A-46F4-9FA2-AACDEAA24237}" name="output" dataDxfId="108" totalsRowDxfId="107">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(UTextMul_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -12828,46 +11592,46 @@
     core_BigInt.UTextMul(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{98F15F6B-80F5-487B-9965-2D3178956C0C}" name="passing" totalsRowFunction="custom" dataDxfId="229" totalsRowDxfId="228">
+    <tableColumn id="4" xr3:uid="{98F15F6B-80F5-487B-9965-2D3178956C0C}" name="passing" totalsRowFunction="custom" dataDxfId="106" totalsRowDxfId="105">
       <calculatedColumnFormula>IF(ISERROR(UTextMul_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UTextMul_Tests[[#This Row],[expected]]) = ERROR.TYPE(UTextMul_Tests[[#This Row],[output]]),
     UTextMul_Tests[[#This Row],[expected]] = UTextMul_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UTextMul_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{2218ADB1-42B3-401A-BDE3-B0DC0D6D6959}" name="test" dataDxfId="227" totalsRowDxfId="226"/>
+    <tableColumn id="5" xr3:uid="{2218ADB1-42B3-401A-BDE3-B0DC0D6D6959}" name="test" dataDxfId="104" totalsRowDxfId="103"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table36.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{C18280EB-8AA6-4449-955D-681E77E7D1F0}" name="Fact_Tests" displayName="Fact_Tests" ref="A394:E402" totalsRowCount="1" dataDxfId="225" tableBorderDxfId="224">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{C18280EB-8AA6-4449-955D-681E77E7D1F0}" name="Fact_Tests" displayName="Fact_Tests" ref="A394:E402" totalsRowCount="1" dataDxfId="102" tableBorderDxfId="101">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D95EE39E-5251-4170-8888-9530E87C134B}" name="input" dataDxfId="223"/>
-    <tableColumn id="2" xr3:uid="{15AD0C64-A61C-4834-B444-C19248449496}" name="expected" dataDxfId="222"/>
-    <tableColumn id="3" xr3:uid="{B1B2AF0C-A9CA-494D-9393-F9EB601C03AE}" name="output" dataDxfId="221">
+    <tableColumn id="1" xr3:uid="{D95EE39E-5251-4170-8888-9530E87C134B}" name="input" dataDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{15AD0C64-A61C-4834-B444-C19248449496}" name="expected" dataDxfId="99"/>
+    <tableColumn id="3" xr3:uid="{B1B2AF0C-A9CA-494D-9393-F9EB601C03AE}" name="output" dataDxfId="98">
       <calculatedColumnFormula array="1">BigInt.Fact(Fact_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{67D2CAD7-A3A0-464E-A151-2D279B301872}" name="passing" totalsRowFunction="custom" dataDxfId="220">
+    <tableColumn id="4" xr3:uid="{67D2CAD7-A3A0-464E-A151-2D279B301872}" name="passing" totalsRowFunction="custom" dataDxfId="97">
       <calculatedColumnFormula>IF(ISERROR(Fact_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Fact_Tests[[#This Row],[expected]]) = ERROR.TYPE(Fact_Tests[[#This Row],[output]]),
     Fact_Tests[[#This Row],[expected]] = Fact_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Fact_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{AD0FAFD6-A476-479B-A804-9F518E2EB8F4}" name="test" dataDxfId="219"/>
+    <tableColumn id="5" xr3:uid="{AD0FAFD6-A476-479B-A804-9F518E2EB8F4}" name="test" dataDxfId="96"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table37.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{1A442966-F97C-4CA5-BF93-28001E9F3115}" name="NativeSwingExponents_Tests" displayName="NativeSwingExponents_Tests" ref="A405:E408" totalsRowCount="1" dataDxfId="218">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{1A442966-F97C-4CA5-BF93-28001E9F3115}" name="NativeSwingExponents_Tests" displayName="NativeSwingExponents_Tests" ref="A405:E408" totalsRowCount="1" dataDxfId="95">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A9F64071-671A-4BD5-BB0B-5605FA9B2FB2}" name="input" dataDxfId="217"/>
-    <tableColumn id="2" xr3:uid="{02211327-69A6-4349-A560-3AF62381C788}" name="expected" dataDxfId="216"/>
-    <tableColumn id="3" xr3:uid="{89446F11-EFC2-42C7-B521-B662FB138191}" name="output" dataDxfId="212">
+    <tableColumn id="1" xr3:uid="{A9F64071-671A-4BD5-BB0B-5605FA9B2FB2}" name="input" dataDxfId="94"/>
+    <tableColumn id="2" xr3:uid="{02211327-69A6-4349-A560-3AF62381C788}" name="expected" dataDxfId="93"/>
+    <tableColumn id="3" xr3:uid="{89446F11-EFC2-42C7-B521-B662FB138191}" name="output" dataDxfId="92">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.n_primes, _xlfn.REGEXEXTRACT(NativeSwingExponents_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.n, --INDEX(_xlpm.n_primes,1,1),
@@ -12877,25 +11641,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C52D135F-5CEB-4D1A-8E45-EA8B58B2B163}" name="passing" totalsRowFunction="custom" dataDxfId="215" totalsRowDxfId="213">
+    <tableColumn id="4" xr3:uid="{C52D135F-5CEB-4D1A-8E45-EA8B58B2B163}" name="passing" totalsRowFunction="custom" dataDxfId="91" totalsRowDxfId="90">
       <calculatedColumnFormula>IF(ISERROR(NativeSwingExponents_Tests[[#This Row],[expected]]),
     ERROR.TYPE(NativeSwingExponents_Tests[[#This Row],[expected]]) = ERROR.TYPE(NativeSwingExponents_Tests[[#This Row],[output]]),
     NativeSwingExponents_Tests[[#This Row],[expected]] = NativeSwingExponents_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(NativeSwingExponents_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B46E3978-1116-4B1A-913F-71B5FB4747AC}" name="test" dataDxfId="214"/>
+    <tableColumn id="5" xr3:uid="{B46E3978-1116-4B1A-913F-71B5FB4747AC}" name="test" dataDxfId="89"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table38.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{A5FEA778-9E36-4BC2-B573-658FC407B11D}" name="PrimeSwingKernel_Tests" displayName="PrimeSwingKernel_Tests" ref="A411:E414" totalsRowCount="1" dataDxfId="211">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{A5FEA778-9E36-4BC2-B573-658FC407B11D}" name="PrimeSwingKernel_Tests" displayName="PrimeSwingKernel_Tests" ref="A411:E414" totalsRowCount="1" dataDxfId="88">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D9194B1A-7653-4C25-AD75-58E73FE195C9}" name="input" dataDxfId="210"/>
-    <tableColumn id="2" xr3:uid="{AE2B8C19-C9AE-4F57-A1CB-20DBB45C5BC7}" name="expected" dataDxfId="209"/>
-    <tableColumn id="3" xr3:uid="{D8958B27-2C1B-4EE7-ACB4-6D260A9AA527}" name="output" dataDxfId="205">
+    <tableColumn id="1" xr3:uid="{D9194B1A-7653-4C25-AD75-58E73FE195C9}" name="input" dataDxfId="87"/>
+    <tableColumn id="2" xr3:uid="{AE2B8C19-C9AE-4F57-A1CB-20DBB45C5BC7}" name="expected" dataDxfId="86"/>
+    <tableColumn id="3" xr3:uid="{D8958B27-2C1B-4EE7-ACB4-6D260A9AA527}" name="output" dataDxfId="85">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.n_primes, _xlfn.REGEXEXTRACT(PrimeSwingKernel_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.n, --INDEX(_xlpm.n_primes,1,1),
@@ -12904,25 +11668,25 @@
     core_BigInt.PrimeSwingKernel(_xlpm.n, _xlpm.primes_arr)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3AABFC76-CC2A-401A-82D6-2360A18DBD72}" name="passing" totalsRowFunction="custom" dataDxfId="207" totalsRowDxfId="208">
+    <tableColumn id="4" xr3:uid="{3AABFC76-CC2A-401A-82D6-2360A18DBD72}" name="passing" totalsRowFunction="custom" dataDxfId="84" totalsRowDxfId="83">
       <calculatedColumnFormula>IF(ISERROR(PrimeSwingKernel_Tests[[#This Row],[expected]]),
     ERROR.TYPE(PrimeSwingKernel_Tests[[#This Row],[expected]]) = ERROR.TYPE(PrimeSwingKernel_Tests[[#This Row],[output]]),
     PrimeSwingKernel_Tests[[#This Row],[expected]] = PrimeSwingKernel_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(PrimeSwingKernel_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{819A85D8-0038-49F4-92B3-29D2B3DA3DA7}" name="test" dataDxfId="206"/>
+    <tableColumn id="5" xr3:uid="{819A85D8-0038-49F4-92B3-29D2B3DA3DA7}" name="test" dataDxfId="82"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table39.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{B9017739-8F7A-45C0-8849-8DA270727275}" name="TreeCompare_Tests" displayName="TreeCompare_Tests" ref="A417:E425" totalsRowCount="1" dataDxfId="204">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{B9017739-8F7A-45C0-8849-8DA270727275}" name="TreeCompare_Tests" displayName="TreeCompare_Tests" ref="A417:E425" totalsRowCount="1" dataDxfId="81">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BDAA1AA4-B401-4C1E-B07A-E7D2C895F02A}" name="input" dataDxfId="203"/>
-    <tableColumn id="2" xr3:uid="{EC652947-23C8-4457-88DD-80381C7FB3A2}" name="expected" dataDxfId="202"/>
-    <tableColumn id="3" xr3:uid="{9CE537BC-E9A5-4F26-88D5-ABBB9201C75C}" name="output" dataDxfId="198">
+    <tableColumn id="1" xr3:uid="{BDAA1AA4-B401-4C1E-B07A-E7D2C895F02A}" name="input" dataDxfId="80"/>
+    <tableColumn id="2" xr3:uid="{EC652947-23C8-4457-88DD-80381C7FB3A2}" name="expected" dataDxfId="79"/>
+    <tableColumn id="3" xr3:uid="{9CE537BC-E9A5-4F26-88D5-ABBB9201C75C}" name="output" dataDxfId="78">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.range_mode, _xlfn.REGEXEXTRACT(TreeCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.range, INDEX(_xlpm.range_mode,1,1),
@@ -12931,28 +11695,28 @@
     core_BigInt.TreeCompare(_xlpm.range_arr, _xlpm.mode)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{998A2330-0955-43FD-AA71-94CBD47AD512}" name="passing" totalsRowFunction="custom" dataDxfId="200" totalsRowDxfId="201">
+    <tableColumn id="4" xr3:uid="{998A2330-0955-43FD-AA71-94CBD47AD512}" name="passing" totalsRowFunction="custom" dataDxfId="77" totalsRowDxfId="76">
       <calculatedColumnFormula>IF(ISERROR(TreeCompare_Tests[[#This Row],[expected]]),
     ERROR.TYPE(TreeCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(TreeCompare_Tests[[#This Row],[output]]),
     TreeCompare_Tests[[#This Row],[expected]] = TreeCompare_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(TreeCompare_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{785CE4BC-B5F9-4152-BB85-92FDF88F26FE}" name="test" dataDxfId="199"/>
+    <tableColumn id="5" xr3:uid="{785CE4BC-B5F9-4152-BB85-92FDF88F26FE}" name="test" dataDxfId="75"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{8BE14E9C-9052-4C6B-91B5-74156B78161B}" name="IsZero_Tests" displayName="IsZero_Tests" ref="A63:E71" totalsRowCount="1" tableBorderDxfId="439">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{8BE14E9C-9052-4C6B-91B5-74156B78161B}" name="IsZero_Tests" displayName="IsZero_Tests" ref="A63:E71" totalsRowCount="1" tableBorderDxfId="316">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F079B266-FBE5-40B3-929D-6B075F83B32A}" name="input"/>
     <tableColumn id="2" xr3:uid="{D2EFB528-67FC-4490-876A-C72813F17A1C}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{735E5B6C-B3DA-49E2-B1F3-88323DE570B4}" name="output" dataDxfId="438">
+    <tableColumn id="3" xr3:uid="{735E5B6C-B3DA-49E2-B1F3-88323DE570B4}" name="output" dataDxfId="315">
       <calculatedColumnFormula array="1">xlInt.IsZero(IsZero_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BCB92B9B-DD7D-407D-BA1B-01844C06231A}" name="passing" totalsRowFunction="custom" dataDxfId="437">
+    <tableColumn id="4" xr3:uid="{BCB92B9B-DD7D-407D-BA1B-01844C06231A}" name="passing" totalsRowFunction="custom" dataDxfId="314">
       <calculatedColumnFormula>IF(ISERROR(IsZero_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsZero_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsZero_Tests[[#This Row],[output]]),
     IsZero_Tests[[#This Row],[expected]] = IsZero_Tests[[#This Row],[output]]
@@ -12966,11 +11730,11 @@
 </file>
 
 <file path=xl/tables/table40.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{DF19CB3E-C2E9-4DDF-B4F3-1CD37989A54B}" name="Max_Tests" displayName="Max_Tests" ref="A428:E434" totalsRowCount="1" dataDxfId="197">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{DF19CB3E-C2E9-4DDF-B4F3-1CD37989A54B}" name="Max_Tests" displayName="Max_Tests" ref="A428:E434" totalsRowCount="1" dataDxfId="74">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{70E3AE18-4391-4958-8A2F-0E14867BC728}" name="input" dataDxfId="196"/>
-    <tableColumn id="2" xr3:uid="{8003646D-7F33-486B-B89C-73BC90D27E5F}" name="expected" dataDxfId="195"/>
-    <tableColumn id="3" xr3:uid="{0DDD1364-1D88-485D-9D85-7DBBD316CE60}" name="output" dataDxfId="185">
+    <tableColumn id="1" xr3:uid="{70E3AE18-4391-4958-8A2F-0E14867BC728}" name="input" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{8003646D-7F33-486B-B89C-73BC90D27E5F}" name="expected" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{0DDD1364-1D88-485D-9D85-7DBBD316CE60}" name="output" dataDxfId="71">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.range_mode, _xlfn.REGEXEXTRACT(Max_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.range, INDEX(_xlpm.range_mode,1,1),
@@ -12978,25 +11742,25 @@
     BigInt.Max(_xlpm.range_arr)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{93AA2604-CFEC-494D-8458-265B34FBDD48}" name="passing" totalsRowFunction="custom" dataDxfId="193" totalsRowDxfId="194">
+    <tableColumn id="4" xr3:uid="{93AA2604-CFEC-494D-8458-265B34FBDD48}" name="passing" totalsRowFunction="custom" dataDxfId="70" totalsRowDxfId="69">
       <calculatedColumnFormula>IF(ISERROR(Max_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Max_Tests[[#This Row],[expected]]) = ERROR.TYPE(Max_Tests[[#This Row],[output]]),
     Max_Tests[[#This Row],[expected]] = Max_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Max_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7BB76139-B909-48EB-BBE4-1B5FAEDF08FF}" name="test" dataDxfId="192"/>
+    <tableColumn id="5" xr3:uid="{7BB76139-B909-48EB-BBE4-1B5FAEDF08FF}" name="test" dataDxfId="68"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table41.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="43" xr:uid="{96C2916B-F8E5-4BCB-878F-6E93D4C2588B}" name="Min_Tests" displayName="Min_Tests" ref="A436:E442" totalsRowCount="1" dataDxfId="191">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="43" xr:uid="{96C2916B-F8E5-4BCB-878F-6E93D4C2588B}" name="Min_Tests" displayName="Min_Tests" ref="A436:E442" totalsRowCount="1" dataDxfId="67">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7CB0024C-89AB-4AF4-B981-D0D9DC861640}" name="input" dataDxfId="190"/>
-    <tableColumn id="2" xr3:uid="{6E7270F8-57D3-4993-A767-C9138198E9D0}" name="expected" dataDxfId="189"/>
-    <tableColumn id="3" xr3:uid="{B2BFCE87-E91A-4BF5-91C3-2864C634D5AD}" name="output" dataDxfId="184">
+    <tableColumn id="1" xr3:uid="{7CB0024C-89AB-4AF4-B981-D0D9DC861640}" name="input" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{6E7270F8-57D3-4993-A767-C9138198E9D0}" name="expected" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{B2BFCE87-E91A-4BF5-91C3-2864C634D5AD}" name="output" dataDxfId="64">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.range_mode, _xlfn.REGEXEXTRACT(Min_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.range, INDEX(_xlpm.range_mode,1,1),
@@ -13004,14 +11768,14 @@
     BigInt.Min(_xlpm.range_arr)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{119495E5-A70B-4977-B718-87E0A3787A9E}" name="passing" totalsRowFunction="custom" dataDxfId="187" totalsRowDxfId="188">
+    <tableColumn id="4" xr3:uid="{119495E5-A70B-4977-B718-87E0A3787A9E}" name="passing" totalsRowFunction="custom" dataDxfId="63" totalsRowDxfId="62">
       <calculatedColumnFormula>IF(ISERROR(Min_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Min_Tests[[#This Row],[expected]]) = ERROR.TYPE(Min_Tests[[#This Row],[output]]),
     Min_Tests[[#This Row],[expected]] = Min_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Min_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D2764F64-B563-420B-8C69-F976F65330B5}" name="test" dataDxfId="186"/>
+    <tableColumn id="5" xr3:uid="{D2764F64-B563-420B-8C69-F976F65330B5}" name="test" dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13029,14 +11793,14 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{5F9E4160-7872-486B-BC10-496D23C60B5A}" name="IsNeg_Tests" displayName="IsNeg_Tests" ref="A74:E82" totalsRowCount="1" tableBorderDxfId="436">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{5F9E4160-7872-486B-BC10-496D23C60B5A}" name="IsNeg_Tests" displayName="IsNeg_Tests" ref="A74:E82" totalsRowCount="1" tableBorderDxfId="313">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A7BB892B-ECAA-4176-AFC6-3449690829CA}" name="input"/>
     <tableColumn id="2" xr3:uid="{4B67C433-DA3F-4DC8-A14F-97407C2E1925}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{49ED0D04-2AA3-4848-8297-CAE5A7D726CD}" name="output" dataDxfId="435">
+    <tableColumn id="3" xr3:uid="{49ED0D04-2AA3-4848-8297-CAE5A7D726CD}" name="output" dataDxfId="312">
       <calculatedColumnFormula array="1">xlInt.IsNeg(IsNeg_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{186FF00B-FED3-490C-BB63-2A0FC55A43D4}" name="passing" totalsRowFunction="custom" dataDxfId="434">
+    <tableColumn id="4" xr3:uid="{186FF00B-FED3-490C-BB63-2A0FC55A43D4}" name="passing" totalsRowFunction="custom" dataDxfId="311">
       <calculatedColumnFormula>IF(ISERROR(IsNeg_Tests[[#This Row],[expected]]),
     ERROR.TYPE(IsNeg_Tests[[#This Row],[expected]]) = ERROR.TYPE(IsNeg_Tests[[#This Row],[output]]),
     IsNeg_Tests[[#This Row],[expected]] = IsNeg_Tests[[#This Row],[output]]
@@ -13050,14 +11814,14 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1631B68B-6D5A-402C-92F6-EDA45141B375}" name="Abs_Tests" displayName="Abs_Tests" ref="A85:E94" totalsRowCount="1" tableBorderDxfId="433">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1631B68B-6D5A-402C-92F6-EDA45141B375}" name="Abs_Tests" displayName="Abs_Tests" ref="A85:E94" totalsRowCount="1" tableBorderDxfId="310">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{631C43FF-F966-4712-8BEB-7647066AF179}" name="input"/>
     <tableColumn id="2" xr3:uid="{70F5476C-B45C-439B-BA01-326EAD467334}" name="expected"/>
-    <tableColumn id="3" xr3:uid="{1E90CD50-A25E-4E12-84D5-66BAAE6BAF0C}" name="output" dataDxfId="432">
+    <tableColumn id="3" xr3:uid="{1E90CD50-A25E-4E12-84D5-66BAAE6BAF0C}" name="output" dataDxfId="309">
       <calculatedColumnFormula array="1">BigInt.Abs(Abs_Tests[[#This Row],[input]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6A0B92CA-92B2-4515-86E8-D91A4279D44E}" name="passing" totalsRowFunction="custom" dataDxfId="431">
+    <tableColumn id="4" xr3:uid="{6A0B92CA-92B2-4515-86E8-D91A4279D44E}" name="passing" totalsRowFunction="custom" dataDxfId="308">
       <calculatedColumnFormula>IF(ISERROR(Abs_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Abs_Tests[[#This Row],[expected]]) = ERROR.TYPE(Abs_Tests[[#This Row],[output]]),
     Abs_Tests[[#This Row],[expected]] = Abs_Tests[[#This Row],[output]]
@@ -13071,11 +11835,11 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{A4A096D6-4E75-4455-A80B-D324779CD007}" name="Compare_Tests" displayName="Compare_Tests" ref="A97:E104" totalsRowCount="1" dataDxfId="430" tableBorderDxfId="429">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{A4A096D6-4E75-4455-A80B-D324779CD007}" name="Compare_Tests" displayName="Compare_Tests" ref="A97:E104" totalsRowCount="1" dataDxfId="307" tableBorderDxfId="306">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{6ED51130-CCEE-49F5-AE6A-C115477DEEC1}" name="input" dataDxfId="428"/>
-    <tableColumn id="3" xr3:uid="{33B3A3D6-83B3-431F-A0B0-9371BBC16D08}" name="expected" dataDxfId="427"/>
-    <tableColumn id="4" xr3:uid="{C0A2BAFD-DD64-4B6D-8350-F0AF699F41AB}" name="output" dataDxfId="426">
+    <tableColumn id="2" xr3:uid="{6ED51130-CCEE-49F5-AE6A-C115477DEEC1}" name="input" dataDxfId="305"/>
+    <tableColumn id="3" xr3:uid="{33B3A3D6-83B3-431F-A0B0-9371BBC16D08}" name="expected" dataDxfId="304"/>
+    <tableColumn id="4" xr3:uid="{C0A2BAFD-DD64-4B6D-8350-F0AF699F41AB}" name="output" dataDxfId="303">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.ab, _xlfn.REGEXEXTRACT(Compare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.ab,1,1),
@@ -13083,25 +11847,25 @@
     xlInt.Compare(_xlpm.a, _xlpm.b)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{25151C64-2D6E-4B12-87AA-02A64ED9EF2B}" name="passing" totalsRowFunction="custom" dataDxfId="425">
+    <tableColumn id="5" xr3:uid="{25151C64-2D6E-4B12-87AA-02A64ED9EF2B}" name="passing" totalsRowFunction="custom" dataDxfId="302">
       <calculatedColumnFormula>IF(ISERROR(Compare_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Compare_Tests[[#This Row],[expected]]) = ERROR.TYPE(Compare_Tests[[#This Row],[output]]),
     Compare_Tests[[#This Row],[expected]] = Compare_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Compare_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D859FAE6-EDFC-42C5-8B0C-0116D05E04F4}" name="test" dataDxfId="424"/>
+    <tableColumn id="6" xr3:uid="{D859FAE6-EDFC-42C5-8B0C-0116D05E04F4}" name="test" dataDxfId="301"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{AB2483E8-D478-4FD2-B96C-83A98FDDE6FA}" name="Carry_Tests" displayName="Carry_Tests" ref="A107:E114" totalsRowCount="1" dataDxfId="423">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{AB2483E8-D478-4FD2-B96C-83A98FDDE6FA}" name="Carry_Tests" displayName="Carry_Tests" ref="A107:E114" totalsRowCount="1" dataDxfId="300">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{58CF3EAC-5FAD-4E1D-8349-AFD0026A5A6F}" name="input" dataDxfId="422"/>
-    <tableColumn id="3" xr3:uid="{8D4EBB1D-1F70-4D9A-B9FB-C7B03997C3F4}" name="expected" dataDxfId="421"/>
-    <tableColumn id="4" xr3:uid="{54C37EF8-27DA-477C-BC79-632DD5E54F03}" name="output" dataDxfId="420">
+    <tableColumn id="2" xr3:uid="{58CF3EAC-5FAD-4E1D-8349-AFD0026A5A6F}" name="input" dataDxfId="299"/>
+    <tableColumn id="3" xr3:uid="{8D4EBB1D-1F70-4D9A-B9FB-C7B03997C3F4}" name="expected" dataDxfId="298"/>
+    <tableColumn id="4" xr3:uid="{54C37EF8-27DA-477C-BC79-632DD5E54F03}" name="output" dataDxfId="297">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.limbs_k, _xlfn.REGEXEXTRACT(Carry_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.limbs_text, INDEX(_xlpm.limbs_k,1,1),
@@ -13111,25 +11875,25 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9B430B30-AE60-423D-A6BE-D7D881CBC2A0}" name="passing" totalsRowFunction="custom" dataDxfId="419">
+    <tableColumn id="5" xr3:uid="{9B430B30-AE60-423D-A6BE-D7D881CBC2A0}" name="passing" totalsRowFunction="custom" dataDxfId="296">
       <calculatedColumnFormula>IF(ISERROR(Carry_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Carry_Tests[[#This Row],[expected]]) = ERROR.TYPE(Carry_Tests[[#This Row],[output]]),
     Carry_Tests[[#This Row],[expected]] = Carry_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(Carry_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{5F961C10-163D-49CE-93C1-9CA6C9C623CA}" name="test" dataDxfId="418"/>
+    <tableColumn id="6" xr3:uid="{5F961C10-163D-49CE-93C1-9CA6C9C623CA}" name="test" dataDxfId="295"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{9541B332-DEB4-4260-9226-40E8C97DC59F}" name="UAdd_Tests" displayName="UAdd_Tests" ref="A117:E124" totalsRowCount="1" dataDxfId="417" tableBorderDxfId="416">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{9541B332-DEB4-4260-9226-40E8C97DC59F}" name="UAdd_Tests" displayName="UAdd_Tests" ref="A117:E124" totalsRowCount="1" dataDxfId="294" tableBorderDxfId="293">
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{6C5FB7CE-3B1F-447E-9ED3-14E839061137}" name="input" dataDxfId="415"/>
-    <tableColumn id="3" xr3:uid="{56E7CDEA-877C-47CA-B875-1A1313998480}" name="expected" dataDxfId="414"/>
-    <tableColumn id="4" xr3:uid="{0AB7FE18-4035-4604-909F-956B1054DE95}" name="output" dataDxfId="413">
+    <tableColumn id="2" xr3:uid="{6C5FB7CE-3B1F-447E-9ED3-14E839061137}" name="input" dataDxfId="292"/>
+    <tableColumn id="3" xr3:uid="{56E7CDEA-877C-47CA-B875-1A1313998480}" name="expected" dataDxfId="291"/>
+    <tableColumn id="4" xr3:uid="{0AB7FE18-4035-4604-909F-956B1054DE95}" name="output" dataDxfId="290">
       <calculatedColumnFormula array="1">_xlfn.LET(
     _xlpm.abk, _xlfn.REGEXEXTRACT(UAdd_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.a, INDEX(_xlpm.abk,1,1),
@@ -13141,14 +11905,14 @@
     _xlfn.ARRAYTOTEXT(_xlpm.output, 1)
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{148597F1-9D9D-45C9-949B-CA15D869DE95}" name="passing" totalsRowFunction="custom" dataDxfId="412">
+    <tableColumn id="5" xr3:uid="{148597F1-9D9D-45C9-949B-CA15D869DE95}" name="passing" totalsRowFunction="custom" dataDxfId="289">
       <calculatedColumnFormula>IF(ISERROR(UAdd_Tests[[#This Row],[expected]]),
     ERROR.TYPE(UAdd_Tests[[#This Row],[expected]]) = ERROR.TYPE(UAdd_Tests[[#This Row],[output]]),
     UAdd_Tests[[#This Row],[expected]] = UAdd_Tests[[#This Row],[output]]
 )</calculatedColumnFormula>
       <totalsRowFormula>AND(UAdd_Tests[passing])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{58290239-17D2-42FA-BE94-887F938260F4}" name="test" dataDxfId="411"/>
+    <tableColumn id="6" xr3:uid="{58290239-17D2-42FA-BE94-887F938260F4}" name="test" dataDxfId="288"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13471,7 +12235,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="1103" row="6">
+  <wetp:taskpane dockstate="right" visibility="0" width="1805" row="6">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -21762,7 +20526,7 @@
       <c r="B419" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C419" s="18" t="str" cm="1">
+      <c r="C419" s="12" t="str" cm="1">
         <f t="array" ref="C419">_xlfn.LET(
     _xlpm.range_mode, _xlfn.REGEXEXTRACT(TreeCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.range, INDEX(_xlpm.range_mode,1,1),
@@ -21772,14 +20536,14 @@
 )</f>
         <v>5</v>
       </c>
-      <c r="D419" s="18" t="b">
+      <c r="D419" s="12" t="b">
         <f>IF(ISERROR(TreeCompare_Tests[[#This Row],[expected]]),
     ERROR.TYPE(TreeCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(TreeCompare_Tests[[#This Row],[output]]),
     TreeCompare_Tests[[#This Row],[expected]] = TreeCompare_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E419" s="19" t="s">
+      <c r="E419" s="12" t="s">
         <v>637</v>
       </c>
     </row>
@@ -21790,7 +20554,7 @@
       <c r="B420" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="C420" s="18" t="str" cm="1">
+      <c r="C420" s="12" t="str" cm="1">
         <f t="array" ref="C420">_xlfn.LET(
     _xlpm.range_mode, _xlfn.REGEXEXTRACT(TreeCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.range, INDEX(_xlpm.range_mode,1,1),
@@ -21800,14 +20564,14 @@
 )</f>
         <v>30</v>
       </c>
-      <c r="D420" s="18" t="b">
+      <c r="D420" s="12" t="b">
         <f>IF(ISERROR(TreeCompare_Tests[[#This Row],[expected]]),
     ERROR.TYPE(TreeCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(TreeCompare_Tests[[#This Row],[output]]),
     TreeCompare_Tests[[#This Row],[expected]] = TreeCompare_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E420" s="19" t="s">
+      <c r="E420" s="12" t="s">
         <v>638</v>
       </c>
     </row>
@@ -21818,7 +20582,7 @@
       <c r="B421" s="12" t="s">
         <v>610</v>
       </c>
-      <c r="C421" s="18" t="str" cm="1">
+      <c r="C421" s="12" t="str" cm="1">
         <f t="array" ref="C421">_xlfn.LET(
     _xlpm.range_mode, _xlfn.REGEXEXTRACT(TreeCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.range, INDEX(_xlpm.range_mode,1,1),
@@ -21828,14 +20592,14 @@
 )</f>
         <v>10</v>
       </c>
-      <c r="D421" s="18" t="b">
+      <c r="D421" s="12" t="b">
         <f>IF(ISERROR(TreeCompare_Tests[[#This Row],[expected]]),
     ERROR.TYPE(TreeCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(TreeCompare_Tests[[#This Row],[output]]),
     TreeCompare_Tests[[#This Row],[expected]] = TreeCompare_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E421" s="19" t="s">
+      <c r="E421" s="12" t="s">
         <v>639</v>
       </c>
     </row>
@@ -21846,7 +20610,7 @@
       <c r="B422" s="12" t="s">
         <v>628</v>
       </c>
-      <c r="C422" s="18" t="str" cm="1">
+      <c r="C422" s="12" t="str" cm="1">
         <f t="array" ref="C422">_xlfn.LET(
     _xlpm.range_mode, _xlfn.REGEXEXTRACT(TreeCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.range, INDEX(_xlpm.range_mode,1,1),
@@ -21856,14 +20620,14 @@
 )</f>
         <v>-10</v>
       </c>
-      <c r="D422" s="18" t="b">
+      <c r="D422" s="12" t="b">
         <f>IF(ISERROR(TreeCompare_Tests[[#This Row],[expected]]),
     ERROR.TYPE(TreeCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(TreeCompare_Tests[[#This Row],[output]]),
     TreeCompare_Tests[[#This Row],[expected]] = TreeCompare_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E422" s="19" t="s">
+      <c r="E422" s="12" t="s">
         <v>640</v>
       </c>
     </row>
@@ -21874,7 +20638,7 @@
       <c r="B423" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C423" s="18" t="str" cm="1">
+      <c r="C423" s="12" t="str" cm="1">
         <f t="array" ref="C423">_xlfn.LET(
     _xlpm.range_mode, _xlfn.REGEXEXTRACT(TreeCompare_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.range, INDEX(_xlpm.range_mode,1,1),
@@ -21884,14 +20648,14 @@
 )</f>
         <v>5</v>
       </c>
-      <c r="D423" s="18" t="b">
+      <c r="D423" s="12" t="b">
         <f>IF(ISERROR(TreeCompare_Tests[[#This Row],[expected]]),
     ERROR.TYPE(TreeCompare_Tests[[#This Row],[expected]]) = ERROR.TYPE(TreeCompare_Tests[[#This Row],[output]]),
     TreeCompare_Tests[[#This Row],[expected]] = TreeCompare_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E423" s="19" t="s">
+      <c r="E423" s="12" t="s">
         <v>641</v>
       </c>
     </row>
@@ -21990,7 +20754,7 @@
       <c r="B430" s="12" t="s">
         <v>649</v>
       </c>
-      <c r="C430" s="18" t="str" cm="1">
+      <c r="C430" s="12" t="str" cm="1">
         <f t="array" ref="C430">_xlfn.LET(
     _xlpm.range_mode, _xlfn.REGEXEXTRACT(Max_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.range, INDEX(_xlpm.range_mode,1,1),
@@ -21999,14 +20763,14 @@
 )</f>
         <v>9</v>
       </c>
-      <c r="D430" s="18" t="b">
+      <c r="D430" s="12" t="b">
         <f>IF(ISERROR(Max_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Max_Tests[[#This Row],[expected]]) = ERROR.TYPE(Max_Tests[[#This Row],[output]]),
     Max_Tests[[#This Row],[expected]] = Max_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E430" s="19" t="s">
+      <c r="E430" s="12" t="s">
         <v>652</v>
       </c>
     </row>
@@ -22017,7 +20781,7 @@
       <c r="B431" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C431" s="18" t="str" cm="1">
+      <c r="C431" s="12" t="str" cm="1">
         <f t="array" ref="C431">_xlfn.LET(
     _xlpm.range_mode, _xlfn.REGEXEXTRACT(Max_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.range, INDEX(_xlpm.range_mode,1,1),
@@ -22026,14 +20790,14 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D431" s="18" t="b">
+      <c r="D431" s="12" t="b">
         <f>IF(ISERROR(Max_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Max_Tests[[#This Row],[expected]]) = ERROR.TYPE(Max_Tests[[#This Row],[output]]),
     Max_Tests[[#This Row],[expected]] = Max_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E431" s="19" t="s">
+      <c r="E431" s="12" t="s">
         <v>654</v>
       </c>
     </row>
@@ -22044,7 +20808,7 @@
       <c r="B432" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C432" s="18" t="str" cm="1">
+      <c r="C432" s="12" t="str" cm="1">
         <f t="array" ref="C432">_xlfn.LET(
     _xlpm.range_mode, _xlfn.REGEXEXTRACT(Max_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.range, INDEX(_xlpm.range_mode,1,1),
@@ -22053,14 +20817,14 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="D432" s="18" t="b">
+      <c r="D432" s="12" t="b">
         <f>IF(ISERROR(Max_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Max_Tests[[#This Row],[expected]]) = ERROR.TYPE(Max_Tests[[#This Row],[output]]),
     Max_Tests[[#This Row],[expected]] = Max_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E432" s="19" t="s">
+      <c r="E432" s="12" t="s">
         <v>657</v>
       </c>
     </row>
@@ -22071,7 +20835,7 @@
       <c r="B433" s="12" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="C433" s="18" t="e" cm="1">
+      <c r="C433" s="12" t="e" cm="1">
         <f t="array" ref="C433">_xlfn.LET(
     _xlpm.range_mode, _xlfn.REGEXEXTRACT(Max_Tests[[#This Row],[input]], "=\s*\{?\K[\w,; .-]*", 1),
     _xlpm.range, INDEX(_xlpm.range_mode,1,1),
@@ -22080,14 +20844,14 @@
 )</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D433" s="18" t="b">
+      <c r="D433" s="12" t="b">
         <f>IF(ISERROR(Max_Tests[[#This Row],[expected]]),
     ERROR.TYPE(Max_Tests[[#This Row],[expected]]) = ERROR.TYPE(Max_Tests[[#This Row],[output]]),
     Max_Tests[[#This Row],[expected]] = Max_Tests[[#This Row],[output]]
 )</f>
         <v>1</v>
       </c>
-      <c r="E433" s="19" t="s">
+      <c r="E433" s="12" t="s">
         <v>653</v>
       </c>
     </row>
@@ -22157,7 +20921,7 @@
       <c r="B438" s="7" t="s">
         <v>656</v>
       </c>
-      <c r="C438" s="18" t="str" cm="1">
+      <c r="C438" s="12" t="str" cm="1">
         <f t="array" ref="C4